--- a/hunt/board.xlsx
+++ b/hunt/board.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4272" uniqueCount="1586">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4285" uniqueCount="1590">
   <si>
     <t>Column</t>
   </si>
@@ -3528,6 +3528,18 @@
   </si>
   <si>
     <t>https://www.workingnomads.com/job/go/1773143/</t>
+  </si>
+  <si>
+    <t>2026-08-28T21:39:33.433Z</t>
+  </si>
+  <si>
+    <t>Trusted-advisor/architecture-ownership engagement model matches the candidate's Customer Engineer background almost exactly | Remote role with confirmed $180K base, hitting the candidate's salary floor | Customer-facing technical strategy and platform adoption work maps well to 10 years of enterprise advisory experience</t>
+  </si>
+  <si>
+    <t>Databricks SAs are expected to have deep data/AI platform depth (Spark, Delta Lake, lakehouse, ML pipelines) — the candidate's profile is DevOps/CI-CD and Azure governance, not data engineering | 'Strat Media' archetype implies media/adtech vertical specialization plus a required technical domain depth the candidate hasn't demonstrated | Databricks SA work is heavily AWS/multi-cloud; Azure-only depth is credited but is a partial fit, and there is no evidence of Databricks/Spark hands-on</t>
+  </si>
+  <si>
+    <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8755462002</t>
   </si>
   <si>
     <t>Northeast - United States; Southeast - United States</t>
@@ -5150,7 +5162,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q237"/>
+  <dimension ref="A1:Q238"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -17030,6 +17042,59 @@
       </c>
       <c r="Q237" t="s">
         <v>1171</v>
+      </c>
+    </row>
+    <row r="238" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>17</v>
+      </c>
+      <c r="B238">
+        <v>45</v>
+      </c>
+      <c r="C238">
+        <v>42</v>
+      </c>
+      <c r="D238" t="s">
+        <v>343</v>
+      </c>
+      <c r="E238" t="s">
+        <v>117</v>
+      </c>
+      <c r="F238" t="s">
+        <v>1026</v>
+      </c>
+      <c r="G238" t="s">
+        <v>21</v>
+      </c>
+      <c r="H238">
+        <v>180000</v>
+      </c>
+      <c r="I238">
+        <v>180000</v>
+      </c>
+      <c r="J238" t="s">
+        <v>44</v>
+      </c>
+      <c r="K238" t="s">
+        <v>92</v>
+      </c>
+      <c r="L238" t="s">
+        <v>1172</v>
+      </c>
+      <c r="M238" t="s">
+        <v>33</v>
+      </c>
+      <c r="N238" t="s">
+        <v>26</v>
+      </c>
+      <c r="O238" t="s">
+        <v>1173</v>
+      </c>
+      <c r="P238" t="s">
+        <v>1174</v>
+      </c>
+      <c r="Q238" t="s">
+        <v>1175</v>
       </c>
     </row>
   </sheetData>
@@ -17128,10 +17193,10 @@
         <v>117</v>
       </c>
       <c r="F2" t="s">
-        <v>1172</v>
+        <v>1176</v>
       </c>
       <c r="G2" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="J2" t="s">
         <v>22</v>
@@ -17146,16 +17211,16 @@
         <v>25</v>
       </c>
       <c r="N2" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O2" t="s">
-        <v>1175</v>
+        <v>1179</v>
       </c>
       <c r="P2" t="s">
-        <v>1176</v>
+        <v>1180</v>
       </c>
       <c r="Q2" t="s">
-        <v>1177</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -17169,16 +17234,16 @@
         <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>1178</v>
+        <v>1182</v>
       </c>
       <c r="E3" t="s">
         <v>117</v>
       </c>
       <c r="F3" t="s">
-        <v>1179</v>
+        <v>1183</v>
       </c>
       <c r="G3" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="H3">
         <v>180000</v>
@@ -17199,16 +17264,16 @@
         <v>33</v>
       </c>
       <c r="N3" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O3" t="s">
-        <v>1180</v>
+        <v>1184</v>
       </c>
       <c r="P3" t="s">
-        <v>1181</v>
+        <v>1185</v>
       </c>
       <c r="Q3" t="s">
-        <v>1182</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
@@ -17222,16 +17287,16 @@
         <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>1183</v>
+        <v>1187</v>
       </c>
       <c r="E4" t="s">
-        <v>1184</v>
+        <v>1188</v>
       </c>
       <c r="F4" t="s">
-        <v>1185</v>
+        <v>1189</v>
       </c>
       <c r="G4" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="H4">
         <v>200000</v>
@@ -17252,16 +17317,16 @@
         <v>25</v>
       </c>
       <c r="N4" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O4" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="P4" t="s">
-        <v>1187</v>
+        <v>1191</v>
       </c>
       <c r="Q4" t="s">
-        <v>1188</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -17275,16 +17340,16 @@
         <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>1189</v>
+        <v>1193</v>
       </c>
       <c r="E5" t="s">
-        <v>1184</v>
+        <v>1188</v>
       </c>
       <c r="F5" t="s">
         <v>1081</v>
       </c>
       <c r="G5" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="H5">
         <v>184200</v>
@@ -17305,16 +17370,16 @@
         <v>25</v>
       </c>
       <c r="N5" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O5" t="s">
-        <v>1190</v>
+        <v>1194</v>
       </c>
       <c r="P5" t="s">
-        <v>1191</v>
+        <v>1195</v>
       </c>
       <c r="Q5" t="s">
-        <v>1192</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -17334,10 +17399,10 @@
         <v>1066</v>
       </c>
       <c r="F6" t="s">
-        <v>1193</v>
+        <v>1197</v>
       </c>
       <c r="G6" t="s">
-        <v>1194</v>
+        <v>1198</v>
       </c>
       <c r="J6" t="s">
         <v>22</v>
@@ -17352,16 +17417,16 @@
         <v>25</v>
       </c>
       <c r="N6" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O6" t="s">
-        <v>1195</v>
+        <v>1199</v>
       </c>
       <c r="P6" t="s">
-        <v>1196</v>
+        <v>1200</v>
       </c>
       <c r="Q6" t="s">
-        <v>1197</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -17375,16 +17440,16 @@
         <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>1198</v>
+        <v>1202</v>
       </c>
       <c r="E7" t="s">
         <v>90</v>
       </c>
       <c r="F7" t="s">
-        <v>1199</v>
+        <v>1203</v>
       </c>
       <c r="G7" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="J7" t="s">
         <v>22</v>
@@ -17399,16 +17464,16 @@
         <v>25</v>
       </c>
       <c r="N7" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O7" t="s">
-        <v>1200</v>
+        <v>1204</v>
       </c>
       <c r="P7" t="s">
-        <v>1201</v>
+        <v>1205</v>
       </c>
       <c r="Q7" t="s">
-        <v>1202</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -17422,16 +17487,16 @@
         <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>1203</v>
+        <v>1207</v>
       </c>
       <c r="E8" t="s">
         <v>90</v>
       </c>
       <c r="F8" t="s">
-        <v>1204</v>
+        <v>1208</v>
       </c>
       <c r="G8" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="J8" t="s">
         <v>22</v>
@@ -17446,16 +17511,16 @@
         <v>25</v>
       </c>
       <c r="N8" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O8" t="s">
-        <v>1205</v>
+        <v>1209</v>
       </c>
       <c r="P8" t="s">
-        <v>1206</v>
+        <v>1210</v>
       </c>
       <c r="Q8" t="s">
-        <v>1207</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -17469,16 +17534,16 @@
         <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>1208</v>
+        <v>1212</v>
       </c>
       <c r="E9" t="s">
         <v>117</v>
       </c>
       <c r="F9" t="s">
-        <v>1193</v>
+        <v>1197</v>
       </c>
       <c r="G9" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="J9" t="s">
         <v>22</v>
@@ -17493,16 +17558,16 @@
         <v>33</v>
       </c>
       <c r="N9" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O9" t="s">
-        <v>1209</v>
+        <v>1213</v>
       </c>
       <c r="P9" t="s">
-        <v>1210</v>
+        <v>1214</v>
       </c>
       <c r="Q9" t="s">
-        <v>1211</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -17516,16 +17581,16 @@
         <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>1212</v>
+        <v>1216</v>
       </c>
       <c r="E10" t="s">
-        <v>1213</v>
+        <v>1217</v>
       </c>
       <c r="F10" t="s">
-        <v>1214</v>
+        <v>1218</v>
       </c>
       <c r="G10" t="s">
-        <v>1194</v>
+        <v>1198</v>
       </c>
       <c r="J10" t="s">
         <v>22</v>
@@ -17540,16 +17605,16 @@
         <v>25</v>
       </c>
       <c r="N10" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O10" t="s">
-        <v>1215</v>
+        <v>1219</v>
       </c>
       <c r="P10" t="s">
-        <v>1216</v>
+        <v>1220</v>
       </c>
       <c r="Q10" t="s">
-        <v>1217</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -17563,16 +17628,16 @@
         <v>12</v>
       </c>
       <c r="D11" t="s">
-        <v>1218</v>
+        <v>1222</v>
       </c>
       <c r="E11" t="s">
-        <v>1219</v>
+        <v>1223</v>
       </c>
       <c r="F11" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="G11" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="J11" t="s">
         <v>22</v>
@@ -17587,16 +17652,16 @@
         <v>25</v>
       </c>
       <c r="N11" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O11" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="P11" t="s">
-        <v>1222</v>
+        <v>1226</v>
       </c>
       <c r="Q11" t="s">
-        <v>1223</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -17610,7 +17675,7 @@
         <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
       <c r="E12" t="s">
         <v>117</v>
@@ -17619,7 +17684,7 @@
         <v>20</v>
       </c>
       <c r="G12" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="H12">
         <v>217800</v>
@@ -17640,16 +17705,16 @@
         <v>33</v>
       </c>
       <c r="N12" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O12" t="s">
-        <v>1225</v>
+        <v>1229</v>
       </c>
       <c r="P12" t="s">
-        <v>1226</v>
+        <v>1230</v>
       </c>
       <c r="Q12" t="s">
-        <v>1227</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
@@ -17663,16 +17728,16 @@
         <v>45</v>
       </c>
       <c r="D13" t="s">
-        <v>1228</v>
+        <v>1232</v>
       </c>
       <c r="E13" t="s">
         <v>117</v>
       </c>
       <c r="F13" t="s">
-        <v>1229</v>
+        <v>1233</v>
       </c>
       <c r="G13" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="H13">
         <v>219100</v>
@@ -17693,16 +17758,16 @@
         <v>33</v>
       </c>
       <c r="N13" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O13" t="s">
-        <v>1230</v>
+        <v>1234</v>
       </c>
       <c r="P13" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
       <c r="Q13" t="s">
-        <v>1232</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
@@ -17722,10 +17787,10 @@
         <v>1066</v>
       </c>
       <c r="F14" t="s">
-        <v>1233</v>
+        <v>1237</v>
       </c>
       <c r="G14" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="J14" t="s">
         <v>22</v>
@@ -17740,16 +17805,16 @@
         <v>25</v>
       </c>
       <c r="N14" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O14" t="s">
-        <v>1234</v>
+        <v>1238</v>
       </c>
       <c r="P14" t="s">
-        <v>1235</v>
+        <v>1239</v>
       </c>
       <c r="Q14" t="s">
-        <v>1236</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -17763,16 +17828,16 @@
         <v>40</v>
       </c>
       <c r="D15" t="s">
-        <v>1237</v>
+        <v>1241</v>
       </c>
       <c r="E15" t="s">
-        <v>1238</v>
+        <v>1242</v>
       </c>
       <c r="F15" t="s">
-        <v>1239</v>
+        <v>1243</v>
       </c>
       <c r="G15" t="s">
-        <v>1194</v>
+        <v>1198</v>
       </c>
       <c r="J15" t="s">
         <v>22</v>
@@ -17787,16 +17852,16 @@
         <v>25</v>
       </c>
       <c r="N15" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O15" t="s">
-        <v>1240</v>
+        <v>1244</v>
       </c>
       <c r="P15" t="s">
-        <v>1241</v>
+        <v>1245</v>
       </c>
       <c r="Q15" t="s">
-        <v>1242</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
@@ -17810,16 +17875,16 @@
         <v>35</v>
       </c>
       <c r="D16" t="s">
-        <v>1243</v>
+        <v>1247</v>
       </c>
       <c r="E16" t="s">
-        <v>1244</v>
+        <v>1248</v>
       </c>
       <c r="F16" t="s">
-        <v>1245</v>
+        <v>1249</v>
       </c>
       <c r="G16" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="J16" t="s">
         <v>22</v>
@@ -17834,16 +17899,16 @@
         <v>25</v>
       </c>
       <c r="N16" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O16" t="s">
-        <v>1246</v>
+        <v>1250</v>
       </c>
       <c r="P16" t="s">
-        <v>1247</v>
+        <v>1251</v>
       </c>
       <c r="Q16" t="s">
-        <v>1248</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
@@ -17857,16 +17922,16 @@
         <v>55</v>
       </c>
       <c r="D17" t="s">
-        <v>1249</v>
+        <v>1253</v>
       </c>
       <c r="E17" t="s">
-        <v>1244</v>
+        <v>1248</v>
       </c>
       <c r="F17" t="s">
-        <v>1250</v>
+        <v>1254</v>
       </c>
       <c r="G17" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="J17" t="s">
         <v>22</v>
@@ -17881,16 +17946,16 @@
         <v>25</v>
       </c>
       <c r="N17" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O17" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
       <c r="P17" t="s">
-        <v>1252</v>
+        <v>1256</v>
       </c>
       <c r="Q17" t="s">
-        <v>1253</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
@@ -17904,16 +17969,16 @@
         <v>40</v>
       </c>
       <c r="D18" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="E18" t="s">
-        <v>1244</v>
+        <v>1248</v>
       </c>
       <c r="F18" t="s">
-        <v>1245</v>
+        <v>1249</v>
       </c>
       <c r="G18" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="J18" t="s">
         <v>22</v>
@@ -17928,16 +17993,16 @@
         <v>25</v>
       </c>
       <c r="N18" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O18" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="P18" t="s">
-        <v>1256</v>
+        <v>1260</v>
       </c>
       <c r="Q18" t="s">
-        <v>1257</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -17951,16 +18016,16 @@
         <v>5</v>
       </c>
       <c r="D19" t="s">
-        <v>1258</v>
+        <v>1262</v>
       </c>
       <c r="E19" t="s">
-        <v>1259</v>
+        <v>1263</v>
       </c>
       <c r="F19" t="s">
-        <v>1260</v>
+        <v>1264</v>
       </c>
       <c r="G19" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="J19" t="s">
         <v>22</v>
@@ -17975,16 +18040,16 @@
         <v>25</v>
       </c>
       <c r="N19" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O19" t="s">
-        <v>1261</v>
+        <v>1265</v>
       </c>
       <c r="P19" t="s">
-        <v>1262</v>
+        <v>1266</v>
       </c>
       <c r="Q19" t="s">
-        <v>1263</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -17998,16 +18063,16 @@
         <v>45</v>
       </c>
       <c r="D20" t="s">
-        <v>1264</v>
+        <v>1268</v>
       </c>
       <c r="E20" t="s">
-        <v>1259</v>
+        <v>1263</v>
       </c>
       <c r="F20" t="s">
-        <v>1193</v>
+        <v>1197</v>
       </c>
       <c r="G20" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="J20" t="s">
         <v>22</v>
@@ -18022,16 +18087,16 @@
         <v>25</v>
       </c>
       <c r="N20" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O20" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="P20" t="s">
-        <v>1266</v>
+        <v>1270</v>
       </c>
       <c r="Q20" t="s">
-        <v>1267</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
@@ -18045,16 +18110,16 @@
         <v>5</v>
       </c>
       <c r="D21" t="s">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="E21" t="s">
-        <v>1259</v>
+        <v>1263</v>
       </c>
       <c r="F21" t="s">
-        <v>1260</v>
+        <v>1264</v>
       </c>
       <c r="G21" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="J21" t="s">
         <v>22</v>
@@ -18069,16 +18134,16 @@
         <v>25</v>
       </c>
       <c r="N21" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O21" t="s">
-        <v>1269</v>
+        <v>1273</v>
       </c>
       <c r="P21" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
       <c r="Q21" t="s">
-        <v>1271</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -18092,16 +18157,16 @@
         <v>5</v>
       </c>
       <c r="D22" t="s">
-        <v>1272</v>
+        <v>1276</v>
       </c>
       <c r="E22" t="s">
-        <v>1259</v>
+        <v>1263</v>
       </c>
       <c r="F22" t="s">
-        <v>1260</v>
+        <v>1264</v>
       </c>
       <c r="G22" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="J22" t="s">
         <v>22</v>
@@ -18116,16 +18181,16 @@
         <v>25</v>
       </c>
       <c r="N22" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O22" t="s">
-        <v>1273</v>
+        <v>1277</v>
       </c>
       <c r="P22" t="s">
-        <v>1274</v>
+        <v>1278</v>
       </c>
       <c r="Q22" t="s">
-        <v>1275</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
@@ -18139,16 +18204,16 @@
         <v>18</v>
       </c>
       <c r="D23" t="s">
-        <v>1276</v>
+        <v>1280</v>
       </c>
       <c r="E23" t="s">
-        <v>1259</v>
+        <v>1263</v>
       </c>
       <c r="F23" t="s">
-        <v>1260</v>
+        <v>1264</v>
       </c>
       <c r="G23" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="J23" t="s">
         <v>22</v>
@@ -18163,16 +18228,16 @@
         <v>25</v>
       </c>
       <c r="N23" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O23" t="s">
-        <v>1277</v>
+        <v>1281</v>
       </c>
       <c r="P23" t="s">
-        <v>1278</v>
+        <v>1282</v>
       </c>
       <c r="Q23" t="s">
-        <v>1279</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
@@ -18186,16 +18251,16 @@
         <v>5</v>
       </c>
       <c r="D24" t="s">
-        <v>1280</v>
+        <v>1284</v>
       </c>
       <c r="E24" t="s">
-        <v>1259</v>
+        <v>1263</v>
       </c>
       <c r="F24" t="s">
-        <v>1260</v>
+        <v>1264</v>
       </c>
       <c r="G24" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="J24" t="s">
         <v>22</v>
@@ -18210,16 +18275,16 @@
         <v>25</v>
       </c>
       <c r="N24" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O24" t="s">
-        <v>1281</v>
+        <v>1285</v>
       </c>
       <c r="P24" t="s">
-        <v>1282</v>
+        <v>1286</v>
       </c>
       <c r="Q24" t="s">
-        <v>1283</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
@@ -18233,16 +18298,16 @@
         <v>40</v>
       </c>
       <c r="D25" t="s">
-        <v>1284</v>
+        <v>1288</v>
       </c>
       <c r="E25" t="s">
-        <v>1259</v>
+        <v>1263</v>
       </c>
       <c r="F25" t="s">
-        <v>1260</v>
+        <v>1264</v>
       </c>
       <c r="G25" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="J25" t="s">
         <v>22</v>
@@ -18257,16 +18322,16 @@
         <v>25</v>
       </c>
       <c r="N25" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O25" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
       <c r="P25" t="s">
-        <v>1286</v>
+        <v>1290</v>
       </c>
       <c r="Q25" t="s">
-        <v>1287</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
@@ -18280,16 +18345,16 @@
         <v>45</v>
       </c>
       <c r="D26" t="s">
-        <v>1288</v>
+        <v>1292</v>
       </c>
       <c r="E26" t="s">
-        <v>1259</v>
+        <v>1263</v>
       </c>
       <c r="F26" t="s">
-        <v>1260</v>
+        <v>1264</v>
       </c>
       <c r="G26" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="J26" t="s">
         <v>22</v>
@@ -18304,16 +18369,16 @@
         <v>25</v>
       </c>
       <c r="N26" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O26" t="s">
-        <v>1289</v>
+        <v>1293</v>
       </c>
       <c r="P26" t="s">
-        <v>1290</v>
+        <v>1294</v>
       </c>
       <c r="Q26" t="s">
-        <v>1291</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
@@ -18327,16 +18392,16 @@
         <v>3</v>
       </c>
       <c r="D27" t="s">
-        <v>1292</v>
+        <v>1296</v>
       </c>
       <c r="E27" t="s">
-        <v>1259</v>
+        <v>1263</v>
       </c>
       <c r="F27" t="s">
-        <v>1260</v>
+        <v>1264</v>
       </c>
       <c r="G27" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="J27" t="s">
         <v>22</v>
@@ -18351,16 +18416,16 @@
         <v>25</v>
       </c>
       <c r="N27" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O27" t="s">
-        <v>1293</v>
+        <v>1297</v>
       </c>
       <c r="P27" t="s">
-        <v>1294</v>
+        <v>1298</v>
       </c>
       <c r="Q27" t="s">
-        <v>1295</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
@@ -18374,7 +18439,7 @@
         <v>42</v>
       </c>
       <c r="D28" t="s">
-        <v>1296</v>
+        <v>1300</v>
       </c>
       <c r="E28" t="s">
         <v>117</v>
@@ -18383,7 +18448,7 @@
         <v>20</v>
       </c>
       <c r="G28" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="J28" t="s">
         <v>22</v>
@@ -18398,16 +18463,16 @@
         <v>25</v>
       </c>
       <c r="N28" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O28" t="s">
-        <v>1297</v>
+        <v>1301</v>
       </c>
       <c r="P28" t="s">
-        <v>1298</v>
+        <v>1302</v>
       </c>
       <c r="Q28" t="s">
-        <v>1299</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
@@ -18421,7 +18486,7 @@
         <v>40</v>
       </c>
       <c r="D29" t="s">
-        <v>1300</v>
+        <v>1304</v>
       </c>
       <c r="E29" t="s">
         <v>117</v>
@@ -18430,7 +18495,7 @@
         <v>20</v>
       </c>
       <c r="G29" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="J29" t="s">
         <v>22</v>
@@ -18445,16 +18510,16 @@
         <v>25</v>
       </c>
       <c r="N29" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O29" t="s">
-        <v>1301</v>
+        <v>1305</v>
       </c>
       <c r="P29" t="s">
-        <v>1302</v>
+        <v>1306</v>
       </c>
       <c r="Q29" t="s">
-        <v>1303</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
@@ -18474,10 +18539,10 @@
         <v>117</v>
       </c>
       <c r="F30" t="s">
-        <v>1304</v>
+        <v>1308</v>
       </c>
       <c r="G30" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="H30">
         <v>180000</v>
@@ -18498,16 +18563,16 @@
         <v>33</v>
       </c>
       <c r="N30" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O30" t="s">
-        <v>1305</v>
+        <v>1309</v>
       </c>
       <c r="P30" t="s">
-        <v>1306</v>
+        <v>1310</v>
       </c>
       <c r="Q30" t="s">
-        <v>1307</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
@@ -18521,7 +18586,7 @@
         <v>52</v>
       </c>
       <c r="D31" t="s">
-        <v>1308</v>
+        <v>1312</v>
       </c>
       <c r="E31" t="s">
         <v>117</v>
@@ -18530,7 +18595,7 @@
         <v>20</v>
       </c>
       <c r="G31" t="s">
-        <v>1194</v>
+        <v>1198</v>
       </c>
       <c r="H31">
         <v>180000</v>
@@ -18551,16 +18616,16 @@
         <v>33</v>
       </c>
       <c r="N31" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O31" t="s">
-        <v>1309</v>
+        <v>1313</v>
       </c>
       <c r="P31" t="s">
-        <v>1310</v>
+        <v>1314</v>
       </c>
       <c r="Q31" t="s">
-        <v>1311</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
@@ -18574,7 +18639,7 @@
         <v>55</v>
       </c>
       <c r="D32" t="s">
-        <v>1312</v>
+        <v>1316</v>
       </c>
       <c r="E32" t="s">
         <v>117</v>
@@ -18583,7 +18648,7 @@
         <v>20</v>
       </c>
       <c r="G32" t="s">
-        <v>1194</v>
+        <v>1198</v>
       </c>
       <c r="H32">
         <v>180000</v>
@@ -18604,16 +18669,16 @@
         <v>33</v>
       </c>
       <c r="N32" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O32" t="s">
-        <v>1313</v>
+        <v>1317</v>
       </c>
       <c r="P32" t="s">
-        <v>1314</v>
+        <v>1318</v>
       </c>
       <c r="Q32" t="s">
-        <v>1315</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
@@ -18627,16 +18692,16 @@
         <v>48</v>
       </c>
       <c r="D33" t="s">
-        <v>1316</v>
+        <v>1320</v>
       </c>
       <c r="E33" t="s">
         <v>117</v>
       </c>
       <c r="F33" t="s">
-        <v>1317</v>
+        <v>1321</v>
       </c>
       <c r="G33" t="s">
-        <v>1194</v>
+        <v>1198</v>
       </c>
       <c r="H33">
         <v>219100</v>
@@ -18657,16 +18722,16 @@
         <v>33</v>
       </c>
       <c r="N33" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O33" t="s">
-        <v>1318</v>
+        <v>1322</v>
       </c>
       <c r="P33" t="s">
-        <v>1319</v>
+        <v>1323</v>
       </c>
       <c r="Q33" t="s">
-        <v>1320</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
@@ -18680,16 +18745,16 @@
         <v>45</v>
       </c>
       <c r="D34" t="s">
-        <v>1321</v>
+        <v>1325</v>
       </c>
       <c r="E34" t="s">
         <v>117</v>
       </c>
       <c r="F34" t="s">
-        <v>1322</v>
+        <v>1326</v>
       </c>
       <c r="G34" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="H34">
         <v>180000</v>
@@ -18710,16 +18775,16 @@
         <v>33</v>
       </c>
       <c r="N34" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O34" t="s">
-        <v>1323</v>
+        <v>1327</v>
       </c>
       <c r="P34" t="s">
-        <v>1324</v>
+        <v>1328</v>
       </c>
       <c r="Q34" t="s">
-        <v>1325</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
@@ -18733,7 +18798,7 @@
         <v>30</v>
       </c>
       <c r="D35" t="s">
-        <v>1326</v>
+        <v>1330</v>
       </c>
       <c r="E35" t="s">
         <v>117</v>
@@ -18742,7 +18807,7 @@
         <v>20</v>
       </c>
       <c r="G35" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="H35">
         <v>219100</v>
@@ -18763,16 +18828,16 @@
         <v>25</v>
       </c>
       <c r="N35" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O35" t="s">
-        <v>1327</v>
+        <v>1331</v>
       </c>
       <c r="P35" t="s">
-        <v>1328</v>
+        <v>1332</v>
       </c>
       <c r="Q35" t="s">
-        <v>1329</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
@@ -18786,7 +18851,7 @@
         <v>45</v>
       </c>
       <c r="D36" t="s">
-        <v>1330</v>
+        <v>1334</v>
       </c>
       <c r="E36" t="s">
         <v>117</v>
@@ -18795,7 +18860,7 @@
         <v>20</v>
       </c>
       <c r="G36" t="s">
-        <v>1194</v>
+        <v>1198</v>
       </c>
       <c r="H36">
         <v>219100</v>
@@ -18816,16 +18881,16 @@
         <v>33</v>
       </c>
       <c r="N36" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O36" t="s">
-        <v>1331</v>
+        <v>1335</v>
       </c>
       <c r="P36" t="s">
-        <v>1332</v>
+        <v>1336</v>
       </c>
       <c r="Q36" t="s">
-        <v>1333</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
@@ -18839,16 +18904,16 @@
         <v>30</v>
       </c>
       <c r="D37" t="s">
-        <v>1334</v>
+        <v>1338</v>
       </c>
       <c r="E37" t="s">
         <v>117</v>
       </c>
       <c r="F37" t="s">
-        <v>1335</v>
+        <v>1339</v>
       </c>
       <c r="G37" t="s">
-        <v>1194</v>
+        <v>1198</v>
       </c>
       <c r="J37" t="s">
         <v>22</v>
@@ -18863,16 +18928,16 @@
         <v>25</v>
       </c>
       <c r="N37" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O37" t="s">
-        <v>1336</v>
+        <v>1340</v>
       </c>
       <c r="P37" t="s">
-        <v>1337</v>
+        <v>1341</v>
       </c>
       <c r="Q37" t="s">
-        <v>1338</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
@@ -18886,16 +18951,16 @@
         <v>58</v>
       </c>
       <c r="D38" t="s">
-        <v>1339</v>
+        <v>1343</v>
       </c>
       <c r="E38" t="s">
-        <v>1340</v>
+        <v>1344</v>
       </c>
       <c r="F38" t="s">
-        <v>1341</v>
+        <v>1345</v>
       </c>
       <c r="G38" t="s">
-        <v>1194</v>
+        <v>1198</v>
       </c>
       <c r="H38">
         <v>257000</v>
@@ -18916,16 +18981,16 @@
         <v>33</v>
       </c>
       <c r="N38" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O38" t="s">
-        <v>1342</v>
+        <v>1346</v>
       </c>
       <c r="P38" t="s">
-        <v>1343</v>
+        <v>1347</v>
       </c>
       <c r="Q38" t="s">
-        <v>1344</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
@@ -18942,13 +19007,13 @@
         <v>541</v>
       </c>
       <c r="E39" t="s">
-        <v>1184</v>
+        <v>1188</v>
       </c>
       <c r="F39" t="s">
-        <v>1345</v>
+        <v>1349</v>
       </c>
       <c r="G39" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="H39">
         <v>200000</v>
@@ -18969,16 +19034,16 @@
         <v>25</v>
       </c>
       <c r="N39" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O39" t="s">
-        <v>1346</v>
+        <v>1350</v>
       </c>
       <c r="P39" t="s">
-        <v>1347</v>
+        <v>1351</v>
       </c>
       <c r="Q39" t="s">
-        <v>1348</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
@@ -18992,16 +19057,16 @@
         <v>20</v>
       </c>
       <c r="D40" t="s">
-        <v>1349</v>
+        <v>1353</v>
       </c>
       <c r="E40" t="s">
         <v>1066</v>
       </c>
       <c r="F40" t="s">
-        <v>1350</v>
+        <v>1354</v>
       </c>
       <c r="G40" t="s">
-        <v>1194</v>
+        <v>1198</v>
       </c>
       <c r="J40" t="s">
         <v>22</v>
@@ -19016,16 +19081,16 @@
         <v>25</v>
       </c>
       <c r="N40" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O40" t="s">
-        <v>1351</v>
+        <v>1355</v>
       </c>
       <c r="P40" t="s">
-        <v>1352</v>
+        <v>1356</v>
       </c>
       <c r="Q40" t="s">
-        <v>1353</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
@@ -19045,10 +19110,10 @@
         <v>1066</v>
       </c>
       <c r="F41" t="s">
-        <v>1354</v>
+        <v>1358</v>
       </c>
       <c r="G41" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="J41" t="s">
         <v>22</v>
@@ -19063,16 +19128,16 @@
         <v>25</v>
       </c>
       <c r="N41" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O41" t="s">
-        <v>1355</v>
+        <v>1359</v>
       </c>
       <c r="P41" t="s">
-        <v>1356</v>
+        <v>1360</v>
       </c>
       <c r="Q41" t="s">
-        <v>1357</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
@@ -19086,16 +19151,16 @@
         <v>15</v>
       </c>
       <c r="D42" t="s">
-        <v>1358</v>
+        <v>1362</v>
       </c>
       <c r="E42" t="s">
         <v>1066</v>
       </c>
       <c r="F42" t="s">
-        <v>1359</v>
+        <v>1363</v>
       </c>
       <c r="G42" t="s">
-        <v>1194</v>
+        <v>1198</v>
       </c>
       <c r="H42">
         <v>500000</v>
@@ -19116,16 +19181,16 @@
         <v>25</v>
       </c>
       <c r="N42" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O42" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="P42" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="Q42" t="s">
-        <v>1362</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
@@ -19139,16 +19204,16 @@
         <v>18</v>
       </c>
       <c r="D43" t="s">
-        <v>1363</v>
+        <v>1367</v>
       </c>
       <c r="E43" t="s">
         <v>90</v>
       </c>
       <c r="F43" t="s">
-        <v>1204</v>
+        <v>1208</v>
       </c>
       <c r="G43" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="H43">
         <v>274456</v>
@@ -19169,16 +19234,16 @@
         <v>25</v>
       </c>
       <c r="N43" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O43" t="s">
-        <v>1364</v>
+        <v>1368</v>
       </c>
       <c r="P43" t="s">
-        <v>1365</v>
+        <v>1369</v>
       </c>
       <c r="Q43" t="s">
-        <v>1366</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
@@ -19192,16 +19257,16 @@
         <v>30</v>
       </c>
       <c r="D44" t="s">
-        <v>1367</v>
+        <v>1371</v>
       </c>
       <c r="E44" t="s">
         <v>90</v>
       </c>
       <c r="F44" t="s">
-        <v>1368</v>
+        <v>1372</v>
       </c>
       <c r="G44" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="J44" t="s">
         <v>22</v>
@@ -19216,16 +19281,16 @@
         <v>25</v>
       </c>
       <c r="N44" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O44" t="s">
-        <v>1369</v>
+        <v>1373</v>
       </c>
       <c r="P44" t="s">
-        <v>1370</v>
+        <v>1374</v>
       </c>
       <c r="Q44" t="s">
-        <v>1371</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
@@ -19239,16 +19304,16 @@
         <v>22</v>
       </c>
       <c r="D45" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="E45" t="s">
         <v>90</v>
       </c>
       <c r="F45" t="s">
-        <v>1373</v>
+        <v>1377</v>
       </c>
       <c r="G45" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="J45" t="s">
         <v>22</v>
@@ -19263,16 +19328,16 @@
         <v>25</v>
       </c>
       <c r="N45" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O45" t="s">
-        <v>1374</v>
+        <v>1378</v>
       </c>
       <c r="P45" t="s">
-        <v>1375</v>
+        <v>1379</v>
       </c>
       <c r="Q45" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
@@ -19286,16 +19351,16 @@
         <v>48</v>
       </c>
       <c r="D46" t="s">
-        <v>1377</v>
+        <v>1381</v>
       </c>
       <c r="E46" t="s">
         <v>90</v>
       </c>
       <c r="F46" t="s">
-        <v>1378</v>
+        <v>1382</v>
       </c>
       <c r="G46" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="J46" t="s">
         <v>22</v>
@@ -19310,16 +19375,16 @@
         <v>33</v>
       </c>
       <c r="N46" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O46" t="s">
-        <v>1379</v>
+        <v>1383</v>
       </c>
       <c r="P46" t="s">
-        <v>1380</v>
+        <v>1384</v>
       </c>
       <c r="Q46" t="s">
-        <v>1381</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
@@ -19333,16 +19398,16 @@
         <v>25</v>
       </c>
       <c r="D47" t="s">
-        <v>1382</v>
+        <v>1386</v>
       </c>
       <c r="E47" t="s">
         <v>90</v>
       </c>
       <c r="F47" t="s">
-        <v>1193</v>
+        <v>1197</v>
       </c>
       <c r="G47" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="J47" t="s">
         <v>22</v>
@@ -19357,16 +19422,16 @@
         <v>25</v>
       </c>
       <c r="N47" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O47" t="s">
-        <v>1383</v>
+        <v>1387</v>
       </c>
       <c r="P47" t="s">
-        <v>1384</v>
+        <v>1388</v>
       </c>
       <c r="Q47" t="s">
-        <v>1385</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
@@ -19380,16 +19445,16 @@
         <v>40</v>
       </c>
       <c r="D48" t="s">
-        <v>1386</v>
+        <v>1390</v>
       </c>
       <c r="E48" t="s">
         <v>90</v>
       </c>
       <c r="F48" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="G48" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="J48" t="s">
         <v>22</v>
@@ -19404,16 +19469,16 @@
         <v>25</v>
       </c>
       <c r="N48" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O48" t="s">
-        <v>1388</v>
+        <v>1392</v>
       </c>
       <c r="P48" t="s">
-        <v>1389</v>
+        <v>1393</v>
       </c>
       <c r="Q48" t="s">
-        <v>1390</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
@@ -19427,16 +19492,16 @@
         <v>70</v>
       </c>
       <c r="D49" t="s">
-        <v>1391</v>
+        <v>1395</v>
       </c>
       <c r="E49" t="s">
-        <v>1392</v>
+        <v>1396</v>
       </c>
       <c r="F49" t="s">
-        <v>1393</v>
+        <v>1397</v>
       </c>
       <c r="G49" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="J49" t="s">
         <v>22</v>
@@ -19451,16 +19516,16 @@
         <v>25</v>
       </c>
       <c r="N49" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O49" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="P49" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="Q49" t="s">
-        <v>1396</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
@@ -19474,16 +19539,16 @@
         <v>58</v>
       </c>
       <c r="D50" t="s">
-        <v>1397</v>
+        <v>1401</v>
       </c>
       <c r="E50" t="s">
-        <v>1398</v>
+        <v>1402</v>
       </c>
       <c r="F50" t="s">
-        <v>1193</v>
+        <v>1197</v>
       </c>
       <c r="G50" t="s">
-        <v>1194</v>
+        <v>1198</v>
       </c>
       <c r="J50" t="s">
         <v>22</v>
@@ -19498,16 +19563,16 @@
         <v>25</v>
       </c>
       <c r="N50" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O50" t="s">
-        <v>1399</v>
+        <v>1403</v>
       </c>
       <c r="P50" t="s">
-        <v>1400</v>
+        <v>1404</v>
       </c>
       <c r="Q50" t="s">
-        <v>1401</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
@@ -19521,16 +19586,16 @@
         <v>32</v>
       </c>
       <c r="D51" t="s">
-        <v>1402</v>
+        <v>1406</v>
       </c>
       <c r="E51" t="s">
-        <v>1403</v>
+        <v>1407</v>
       </c>
       <c r="F51" t="s">
-        <v>1404</v>
+        <v>1408</v>
       </c>
       <c r="G51" t="s">
-        <v>1194</v>
+        <v>1198</v>
       </c>
       <c r="J51" t="s">
         <v>22</v>
@@ -19545,16 +19610,16 @@
         <v>25</v>
       </c>
       <c r="N51" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O51" t="s">
-        <v>1405</v>
+        <v>1409</v>
       </c>
       <c r="P51" t="s">
-        <v>1406</v>
+        <v>1410</v>
       </c>
       <c r="Q51" t="s">
-        <v>1407</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
@@ -19568,16 +19633,16 @@
         <v>4</v>
       </c>
       <c r="D52" t="s">
-        <v>1408</v>
+        <v>1412</v>
       </c>
       <c r="E52" t="s">
-        <v>1409</v>
+        <v>1413</v>
       </c>
       <c r="F52" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="G52" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="J52" t="s">
         <v>22</v>
@@ -19592,16 +19657,16 @@
         <v>25</v>
       </c>
       <c r="N52" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O52" t="s">
-        <v>1411</v>
+        <v>1415</v>
       </c>
       <c r="P52" t="s">
-        <v>1412</v>
+        <v>1416</v>
       </c>
       <c r="Q52" t="s">
-        <v>1413</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
@@ -19615,16 +19680,16 @@
         <v>25</v>
       </c>
       <c r="D53" t="s">
-        <v>1414</v>
+        <v>1418</v>
       </c>
       <c r="E53" t="s">
-        <v>1415</v>
+        <v>1419</v>
       </c>
       <c r="F53" t="s">
-        <v>1250</v>
+        <v>1254</v>
       </c>
       <c r="G53" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="J53" t="s">
         <v>22</v>
@@ -19639,16 +19704,16 @@
         <v>25</v>
       </c>
       <c r="N53" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O53" t="s">
-        <v>1416</v>
+        <v>1420</v>
       </c>
       <c r="P53" t="s">
-        <v>1417</v>
+        <v>1421</v>
       </c>
       <c r="Q53" t="s">
-        <v>1418</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
@@ -19662,16 +19727,16 @@
         <v>30</v>
       </c>
       <c r="D54" t="s">
-        <v>1419</v>
+        <v>1423</v>
       </c>
       <c r="E54" t="s">
-        <v>1420</v>
+        <v>1424</v>
       </c>
       <c r="F54" t="s">
-        <v>1421</v>
+        <v>1425</v>
       </c>
       <c r="G54" t="s">
-        <v>1194</v>
+        <v>1198</v>
       </c>
       <c r="J54" t="s">
         <v>22</v>
@@ -19686,16 +19751,16 @@
         <v>25</v>
       </c>
       <c r="N54" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O54" t="s">
-        <v>1422</v>
+        <v>1426</v>
       </c>
       <c r="P54" t="s">
-        <v>1423</v>
+        <v>1427</v>
       </c>
       <c r="Q54" t="s">
-        <v>1424</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
@@ -19709,16 +19774,16 @@
         <v>52</v>
       </c>
       <c r="D55" t="s">
-        <v>1425</v>
+        <v>1429</v>
       </c>
       <c r="E55" t="s">
         <v>117</v>
       </c>
       <c r="F55" t="s">
-        <v>1426</v>
+        <v>1430</v>
       </c>
       <c r="G55" t="s">
-        <v>1194</v>
+        <v>1198</v>
       </c>
       <c r="H55">
         <v>180000</v>
@@ -19739,16 +19804,16 @@
         <v>33</v>
       </c>
       <c r="N55" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O55" t="s">
-        <v>1427</v>
+        <v>1431</v>
       </c>
       <c r="P55" t="s">
-        <v>1428</v>
+        <v>1432</v>
       </c>
       <c r="Q55" t="s">
-        <v>1429</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
@@ -19762,7 +19827,7 @@
         <v>50</v>
       </c>
       <c r="D56" t="s">
-        <v>1430</v>
+        <v>1434</v>
       </c>
       <c r="E56" t="s">
         <v>117</v>
@@ -19771,7 +19836,7 @@
         <v>20</v>
       </c>
       <c r="G56" t="s">
-        <v>1194</v>
+        <v>1198</v>
       </c>
       <c r="H56">
         <v>180000</v>
@@ -19792,16 +19857,16 @@
         <v>33</v>
       </c>
       <c r="N56" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O56" t="s">
-        <v>1431</v>
+        <v>1435</v>
       </c>
       <c r="P56" t="s">
-        <v>1432</v>
+        <v>1436</v>
       </c>
       <c r="Q56" t="s">
-        <v>1433</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
@@ -19815,7 +19880,7 @@
         <v>46</v>
       </c>
       <c r="D57" t="s">
-        <v>1434</v>
+        <v>1438</v>
       </c>
       <c r="E57" t="s">
         <v>117</v>
@@ -19824,7 +19889,7 @@
         <v>20</v>
       </c>
       <c r="G57" t="s">
-        <v>1194</v>
+        <v>1198</v>
       </c>
       <c r="H57">
         <v>180000</v>
@@ -19845,16 +19910,16 @@
         <v>33</v>
       </c>
       <c r="N57" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O57" t="s">
-        <v>1435</v>
+        <v>1439</v>
       </c>
       <c r="P57" t="s">
-        <v>1436</v>
+        <v>1440</v>
       </c>
       <c r="Q57" t="s">
-        <v>1437</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
@@ -19868,7 +19933,7 @@
         <v>38</v>
       </c>
       <c r="D58" t="s">
-        <v>1438</v>
+        <v>1442</v>
       </c>
       <c r="E58" t="s">
         <v>117</v>
@@ -19877,7 +19942,7 @@
         <v>20</v>
       </c>
       <c r="G58" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="H58">
         <v>217800</v>
@@ -19898,16 +19963,16 @@
         <v>25</v>
       </c>
       <c r="N58" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O58" t="s">
-        <v>1439</v>
+        <v>1443</v>
       </c>
       <c r="P58" t="s">
-        <v>1440</v>
+        <v>1444</v>
       </c>
       <c r="Q58" t="s">
-        <v>1441</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
@@ -19927,10 +19992,10 @@
         <v>117</v>
       </c>
       <c r="F59" t="s">
-        <v>1442</v>
+        <v>1446</v>
       </c>
       <c r="G59" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="H59">
         <v>180000</v>
@@ -19951,16 +20016,16 @@
         <v>33</v>
       </c>
       <c r="N59" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O59" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="P59" t="s">
-        <v>1444</v>
+        <v>1448</v>
       </c>
       <c r="Q59" t="s">
-        <v>1445</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
@@ -19974,16 +20039,16 @@
         <v>45</v>
       </c>
       <c r="D60" t="s">
-        <v>1446</v>
+        <v>1450</v>
       </c>
       <c r="E60" t="s">
         <v>117</v>
       </c>
       <c r="F60" t="s">
-        <v>1447</v>
+        <v>1451</v>
       </c>
       <c r="G60" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="H60">
         <v>219100</v>
@@ -20004,16 +20069,16 @@
         <v>33</v>
       </c>
       <c r="N60" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O60" t="s">
-        <v>1448</v>
+        <v>1452</v>
       </c>
       <c r="P60" t="s">
-        <v>1449</v>
+        <v>1453</v>
       </c>
       <c r="Q60" t="s">
-        <v>1450</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
@@ -20027,16 +20092,16 @@
         <v>42</v>
       </c>
       <c r="D61" t="s">
-        <v>1451</v>
+        <v>1455</v>
       </c>
       <c r="E61" t="s">
         <v>117</v>
       </c>
       <c r="F61" t="s">
-        <v>1452</v>
+        <v>1456</v>
       </c>
       <c r="G61" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="H61">
         <v>180000</v>
@@ -20057,16 +20122,16 @@
         <v>33</v>
       </c>
       <c r="N61" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O61" t="s">
-        <v>1453</v>
+        <v>1457</v>
       </c>
       <c r="P61" t="s">
-        <v>1454</v>
+        <v>1458</v>
       </c>
       <c r="Q61" t="s">
-        <v>1455</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
@@ -20080,7 +20145,7 @@
         <v>32</v>
       </c>
       <c r="D62" t="s">
-        <v>1456</v>
+        <v>1460</v>
       </c>
       <c r="E62" t="s">
         <v>117</v>
@@ -20089,7 +20154,7 @@
         <v>20</v>
       </c>
       <c r="G62" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="H62">
         <v>219100</v>
@@ -20110,16 +20175,16 @@
         <v>25</v>
       </c>
       <c r="N62" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O62" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
       <c r="P62" t="s">
-        <v>1458</v>
+        <v>1462</v>
       </c>
       <c r="Q62" t="s">
-        <v>1459</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
@@ -20133,7 +20198,7 @@
         <v>35</v>
       </c>
       <c r="D63" t="s">
-        <v>1460</v>
+        <v>1464</v>
       </c>
       <c r="E63" t="s">
         <v>117</v>
@@ -20142,7 +20207,7 @@
         <v>20</v>
       </c>
       <c r="G63" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="H63">
         <v>219100</v>
@@ -20163,16 +20228,16 @@
         <v>25</v>
       </c>
       <c r="N63" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O63" t="s">
-        <v>1461</v>
+        <v>1465</v>
       </c>
       <c r="P63" t="s">
-        <v>1462</v>
+        <v>1466</v>
       </c>
       <c r="Q63" t="s">
-        <v>1463</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
@@ -20186,16 +20251,16 @@
         <v>40</v>
       </c>
       <c r="D64" t="s">
-        <v>1464</v>
+        <v>1468</v>
       </c>
       <c r="E64" t="s">
         <v>117</v>
       </c>
       <c r="F64" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="G64" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="H64">
         <v>219100</v>
@@ -20216,16 +20281,16 @@
         <v>33</v>
       </c>
       <c r="N64" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O64" t="s">
-        <v>1466</v>
+        <v>1470</v>
       </c>
       <c r="P64" t="s">
-        <v>1467</v>
+        <v>1471</v>
       </c>
       <c r="Q64" t="s">
-        <v>1468</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
@@ -20239,7 +20304,7 @@
         <v>38</v>
       </c>
       <c r="D65" t="s">
-        <v>1469</v>
+        <v>1473</v>
       </c>
       <c r="E65" t="s">
         <v>117</v>
@@ -20248,7 +20313,7 @@
         <v>818</v>
       </c>
       <c r="G65" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="H65">
         <v>219100</v>
@@ -20269,16 +20334,16 @@
         <v>25</v>
       </c>
       <c r="N65" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O65" t="s">
-        <v>1470</v>
+        <v>1474</v>
       </c>
       <c r="P65" t="s">
-        <v>1471</v>
+        <v>1475</v>
       </c>
       <c r="Q65" t="s">
-        <v>1472</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
@@ -20292,7 +20357,7 @@
         <v>40</v>
       </c>
       <c r="D66" t="s">
-        <v>1473</v>
+        <v>1477</v>
       </c>
       <c r="E66" t="s">
         <v>117</v>
@@ -20301,7 +20366,7 @@
         <v>20</v>
       </c>
       <c r="G66" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="H66">
         <v>219100</v>
@@ -20322,16 +20387,16 @@
         <v>33</v>
       </c>
       <c r="N66" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O66" t="s">
-        <v>1474</v>
+        <v>1478</v>
       </c>
       <c r="P66" t="s">
-        <v>1475</v>
+        <v>1479</v>
       </c>
       <c r="Q66" t="s">
-        <v>1476</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
@@ -20345,16 +20410,16 @@
         <v>33</v>
       </c>
       <c r="D67" t="s">
-        <v>1477</v>
+        <v>1481</v>
       </c>
       <c r="E67" t="s">
         <v>117</v>
       </c>
       <c r="F67" t="s">
-        <v>1478</v>
+        <v>1482</v>
       </c>
       <c r="G67" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="H67">
         <v>219100</v>
@@ -20375,16 +20440,16 @@
         <v>25</v>
       </c>
       <c r="N67" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O67" t="s">
-        <v>1479</v>
+        <v>1483</v>
       </c>
       <c r="P67" t="s">
-        <v>1480</v>
+        <v>1484</v>
       </c>
       <c r="Q67" t="s">
-        <v>1481</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
@@ -20398,16 +20463,16 @@
         <v>48</v>
       </c>
       <c r="D68" t="s">
-        <v>1482</v>
+        <v>1486</v>
       </c>
       <c r="E68" t="s">
-        <v>1340</v>
+        <v>1344</v>
       </c>
       <c r="F68" t="s">
-        <v>1483</v>
+        <v>1487</v>
       </c>
       <c r="G68" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="J68" t="s">
         <v>22</v>
@@ -20422,16 +20487,16 @@
         <v>33</v>
       </c>
       <c r="N68" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O68" t="s">
-        <v>1484</v>
+        <v>1488</v>
       </c>
       <c r="P68" t="s">
-        <v>1485</v>
+        <v>1489</v>
       </c>
       <c r="Q68" t="s">
-        <v>1486</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
@@ -20445,16 +20510,16 @@
         <v>40</v>
       </c>
       <c r="D69" t="s">
-        <v>1189</v>
+        <v>1193</v>
       </c>
       <c r="E69" t="s">
-        <v>1184</v>
+        <v>1188</v>
       </c>
       <c r="F69" t="s">
-        <v>1487</v>
+        <v>1491</v>
       </c>
       <c r="G69" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="H69">
         <v>184200</v>
@@ -20475,16 +20540,16 @@
         <v>33</v>
       </c>
       <c r="N69" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O69" t="s">
-        <v>1488</v>
+        <v>1492</v>
       </c>
       <c r="P69" t="s">
-        <v>1489</v>
+        <v>1493</v>
       </c>
       <c r="Q69" t="s">
-        <v>1490</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
@@ -20498,16 +20563,16 @@
         <v>30</v>
       </c>
       <c r="D70" t="s">
-        <v>1491</v>
+        <v>1495</v>
       </c>
       <c r="E70" t="s">
-        <v>1184</v>
+        <v>1188</v>
       </c>
       <c r="F70" t="s">
-        <v>1492</v>
+        <v>1496</v>
       </c>
       <c r="G70" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="H70">
         <v>200000</v>
@@ -20528,16 +20593,16 @@
         <v>25</v>
       </c>
       <c r="N70" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O70" t="s">
-        <v>1493</v>
+        <v>1497</v>
       </c>
       <c r="P70" t="s">
-        <v>1494</v>
+        <v>1498</v>
       </c>
       <c r="Q70" t="s">
-        <v>1495</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
@@ -20551,7 +20616,7 @@
         <v>30</v>
       </c>
       <c r="D71" t="s">
-        <v>1496</v>
+        <v>1500</v>
       </c>
       <c r="E71" t="s">
         <v>1066</v>
@@ -20560,7 +20625,7 @@
         <v>1075</v>
       </c>
       <c r="G71" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="J71" t="s">
         <v>22</v>
@@ -20575,16 +20640,16 @@
         <v>25</v>
       </c>
       <c r="N71" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O71" t="s">
-        <v>1497</v>
+        <v>1501</v>
       </c>
       <c r="P71" t="s">
-        <v>1498</v>
+        <v>1502</v>
       </c>
       <c r="Q71" t="s">
-        <v>1499</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
@@ -20598,16 +20663,16 @@
         <v>32</v>
       </c>
       <c r="D72" t="s">
-        <v>1500</v>
+        <v>1504</v>
       </c>
       <c r="E72" t="s">
         <v>1066</v>
       </c>
       <c r="F72" t="s">
-        <v>1354</v>
+        <v>1358</v>
       </c>
       <c r="G72" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="J72" t="s">
         <v>22</v>
@@ -20622,16 +20687,16 @@
         <v>25</v>
       </c>
       <c r="N72" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O72" t="s">
-        <v>1501</v>
+        <v>1505</v>
       </c>
       <c r="P72" t="s">
-        <v>1502</v>
+        <v>1506</v>
       </c>
       <c r="Q72" t="s">
-        <v>1503</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
@@ -20645,7 +20710,7 @@
         <v>32</v>
       </c>
       <c r="D73" t="s">
-        <v>1504</v>
+        <v>1508</v>
       </c>
       <c r="E73" t="s">
         <v>1066</v>
@@ -20654,7 +20719,7 @@
         <v>1075</v>
       </c>
       <c r="G73" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="J73" t="s">
         <v>22</v>
@@ -20669,16 +20734,16 @@
         <v>25</v>
       </c>
       <c r="N73" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O73" t="s">
-        <v>1505</v>
+        <v>1509</v>
       </c>
       <c r="P73" t="s">
-        <v>1506</v>
+        <v>1510</v>
       </c>
       <c r="Q73" t="s">
-        <v>1507</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
@@ -20692,16 +20757,16 @@
         <v>45</v>
       </c>
       <c r="D74" t="s">
-        <v>1508</v>
+        <v>1512</v>
       </c>
       <c r="E74" t="s">
         <v>90</v>
       </c>
       <c r="F74" t="s">
-        <v>1199</v>
+        <v>1203</v>
       </c>
       <c r="G74" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="J74" t="s">
         <v>22</v>
@@ -20716,16 +20781,16 @@
         <v>33</v>
       </c>
       <c r="N74" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O74" t="s">
-        <v>1509</v>
+        <v>1513</v>
       </c>
       <c r="P74" t="s">
-        <v>1510</v>
+        <v>1514</v>
       </c>
       <c r="Q74" t="s">
-        <v>1511</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
@@ -20739,16 +20804,16 @@
         <v>35</v>
       </c>
       <c r="D75" t="s">
-        <v>1512</v>
+        <v>1516</v>
       </c>
       <c r="E75" t="s">
         <v>90</v>
       </c>
       <c r="F75" t="s">
-        <v>1513</v>
+        <v>1517</v>
       </c>
       <c r="G75" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="J75" t="s">
         <v>22</v>
@@ -20763,16 +20828,16 @@
         <v>25</v>
       </c>
       <c r="N75" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O75" t="s">
-        <v>1514</v>
+        <v>1518</v>
       </c>
       <c r="P75" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="Q75" t="s">
-        <v>1516</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
@@ -20786,7 +20851,7 @@
         <v>35</v>
       </c>
       <c r="D76" t="s">
-        <v>1517</v>
+        <v>1521</v>
       </c>
       <c r="E76" t="s">
         <v>90</v>
@@ -20795,7 +20860,7 @@
         <v>152</v>
       </c>
       <c r="G76" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="J76" t="s">
         <v>22</v>
@@ -20810,16 +20875,16 @@
         <v>25</v>
       </c>
       <c r="N76" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O76" t="s">
-        <v>1518</v>
+        <v>1522</v>
       </c>
       <c r="P76" t="s">
-        <v>1519</v>
+        <v>1523</v>
       </c>
       <c r="Q76" t="s">
-        <v>1520</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
@@ -20833,16 +20898,16 @@
         <v>15</v>
       </c>
       <c r="D77" t="s">
-        <v>1521</v>
+        <v>1525</v>
       </c>
       <c r="E77" t="s">
         <v>90</v>
       </c>
       <c r="F77" t="s">
-        <v>1522</v>
+        <v>1526</v>
       </c>
       <c r="G77" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="J77" t="s">
         <v>22</v>
@@ -20857,16 +20922,16 @@
         <v>25</v>
       </c>
       <c r="N77" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O77" t="s">
-        <v>1523</v>
+        <v>1527</v>
       </c>
       <c r="P77" t="s">
-        <v>1524</v>
+        <v>1528</v>
       </c>
       <c r="Q77" t="s">
-        <v>1525</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
@@ -20880,16 +20945,16 @@
         <v>25</v>
       </c>
       <c r="D78" t="s">
-        <v>1526</v>
+        <v>1530</v>
       </c>
       <c r="E78" t="s">
         <v>90</v>
       </c>
       <c r="F78" t="s">
-        <v>1527</v>
+        <v>1531</v>
       </c>
       <c r="G78" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="J78" t="s">
         <v>22</v>
@@ -20904,16 +20969,16 @@
         <v>25</v>
       </c>
       <c r="N78" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O78" t="s">
-        <v>1528</v>
+        <v>1532</v>
       </c>
       <c r="P78" t="s">
-        <v>1529</v>
+        <v>1533</v>
       </c>
       <c r="Q78" t="s">
-        <v>1530</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
@@ -20927,16 +20992,16 @@
         <v>30</v>
       </c>
       <c r="D79" t="s">
-        <v>1531</v>
+        <v>1535</v>
       </c>
       <c r="E79" t="s">
         <v>90</v>
       </c>
       <c r="F79" t="s">
-        <v>1532</v>
+        <v>1536</v>
       </c>
       <c r="G79" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="J79" t="s">
         <v>22</v>
@@ -20951,16 +21016,16 @@
         <v>25</v>
       </c>
       <c r="N79" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O79" t="s">
-        <v>1533</v>
+        <v>1537</v>
       </c>
       <c r="P79" t="s">
-        <v>1534</v>
+        <v>1538</v>
       </c>
       <c r="Q79" t="s">
-        <v>1535</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
@@ -20980,10 +21045,10 @@
         <v>117</v>
       </c>
       <c r="F80" t="s">
-        <v>1492</v>
+        <v>1496</v>
       </c>
       <c r="G80" t="s">
-        <v>1194</v>
+        <v>1198</v>
       </c>
       <c r="J80" t="s">
         <v>22</v>
@@ -20998,16 +21063,16 @@
         <v>25</v>
       </c>
       <c r="N80" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O80" t="s">
-        <v>1536</v>
+        <v>1540</v>
       </c>
       <c r="P80" t="s">
-        <v>1537</v>
+        <v>1541</v>
       </c>
       <c r="Q80" t="s">
-        <v>1538</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
@@ -21027,10 +21092,10 @@
         <v>117</v>
       </c>
       <c r="F81" t="s">
-        <v>1539</v>
+        <v>1543</v>
       </c>
       <c r="G81" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="J81" t="s">
         <v>22</v>
@@ -21045,16 +21110,16 @@
         <v>33</v>
       </c>
       <c r="N81" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O81" t="s">
-        <v>1540</v>
+        <v>1544</v>
       </c>
       <c r="P81" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="Q81" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
@@ -21077,7 +21142,7 @@
         <v>1132</v>
       </c>
       <c r="G82" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="H82">
         <v>180000</v>
@@ -21098,16 +21163,16 @@
         <v>25</v>
       </c>
       <c r="N82" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O82" t="s">
-        <v>1543</v>
+        <v>1547</v>
       </c>
       <c r="P82" t="s">
-        <v>1544</v>
+        <v>1548</v>
       </c>
       <c r="Q82" t="s">
-        <v>1545</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
@@ -21127,10 +21192,10 @@
         <v>117</v>
       </c>
       <c r="F83" t="s">
-        <v>1546</v>
+        <v>1550</v>
       </c>
       <c r="G83" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="H83">
         <v>180000</v>
@@ -21151,16 +21216,16 @@
         <v>25</v>
       </c>
       <c r="N83" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O83" t="s">
-        <v>1547</v>
+        <v>1551</v>
       </c>
       <c r="P83" t="s">
-        <v>1548</v>
+        <v>1552</v>
       </c>
       <c r="Q83" t="s">
-        <v>1549</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
@@ -21174,16 +21239,16 @@
         <v>20</v>
       </c>
       <c r="D84" t="s">
-        <v>1550</v>
+        <v>1554</v>
       </c>
       <c r="E84" t="s">
-        <v>1551</v>
+        <v>1555</v>
       </c>
       <c r="F84" t="s">
-        <v>1552</v>
+        <v>1556</v>
       </c>
       <c r="G84" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="J84" t="s">
         <v>22</v>
@@ -21198,16 +21263,16 @@
         <v>25</v>
       </c>
       <c r="N84" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O84" t="s">
-        <v>1553</v>
+        <v>1557</v>
       </c>
       <c r="P84" t="s">
-        <v>1554</v>
+        <v>1558</v>
       </c>
       <c r="Q84" t="s">
-        <v>1555</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
@@ -21221,16 +21286,16 @@
         <v>50</v>
       </c>
       <c r="D85" t="s">
-        <v>1556</v>
+        <v>1560</v>
       </c>
       <c r="E85" t="s">
-        <v>1551</v>
+        <v>1555</v>
       </c>
       <c r="F85" t="s">
         <v>20</v>
       </c>
       <c r="G85" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="H85">
         <v>250000</v>
@@ -21251,16 +21316,16 @@
         <v>33</v>
       </c>
       <c r="N85" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O85" t="s">
-        <v>1557</v>
+        <v>1561</v>
       </c>
       <c r="P85" t="s">
-        <v>1558</v>
+        <v>1562</v>
       </c>
       <c r="Q85" t="s">
-        <v>1559</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
@@ -21274,16 +21339,16 @@
         <v>55</v>
       </c>
       <c r="D86" t="s">
-        <v>1560</v>
+        <v>1564</v>
       </c>
       <c r="E86" t="s">
-        <v>1551</v>
+        <v>1555</v>
       </c>
       <c r="F86" t="s">
         <v>20</v>
       </c>
       <c r="G86" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="H86">
         <v>200000</v>
@@ -21304,16 +21369,16 @@
         <v>33</v>
       </c>
       <c r="N86" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O86" t="s">
-        <v>1561</v>
+        <v>1565</v>
       </c>
       <c r="P86" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="Q86" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
@@ -21327,16 +21392,16 @@
         <v>52</v>
       </c>
       <c r="D87" t="s">
-        <v>1564</v>
+        <v>1568</v>
       </c>
       <c r="E87" t="s">
-        <v>1551</v>
+        <v>1555</v>
       </c>
       <c r="F87" t="s">
         <v>20</v>
       </c>
       <c r="G87" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="H87">
         <v>250000</v>
@@ -21357,16 +21422,16 @@
         <v>33</v>
       </c>
       <c r="N87" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O87" t="s">
-        <v>1565</v>
+        <v>1569</v>
       </c>
       <c r="P87" t="s">
-        <v>1566</v>
+        <v>1570</v>
       </c>
       <c r="Q87" t="s">
-        <v>1567</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
@@ -21380,16 +21445,16 @@
         <v>53</v>
       </c>
       <c r="D88" t="s">
-        <v>1568</v>
+        <v>1572</v>
       </c>
       <c r="E88" t="s">
-        <v>1551</v>
+        <v>1555</v>
       </c>
       <c r="F88" t="s">
         <v>20</v>
       </c>
       <c r="G88" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="H88">
         <v>200000</v>
@@ -21410,16 +21475,16 @@
         <v>33</v>
       </c>
       <c r="N88" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O88" t="s">
-        <v>1569</v>
+        <v>1573</v>
       </c>
       <c r="P88" t="s">
-        <v>1570</v>
+        <v>1574</v>
       </c>
       <c r="Q88" t="s">
-        <v>1571</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
@@ -21433,16 +21498,16 @@
         <v>50</v>
       </c>
       <c r="D89" t="s">
-        <v>1572</v>
+        <v>1576</v>
       </c>
       <c r="E89" t="s">
-        <v>1551</v>
+        <v>1555</v>
       </c>
       <c r="F89" t="s">
         <v>20</v>
       </c>
       <c r="G89" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="H89">
         <v>200000</v>
@@ -21463,16 +21528,16 @@
         <v>33</v>
       </c>
       <c r="N89" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O89" t="s">
-        <v>1573</v>
+        <v>1577</v>
       </c>
       <c r="P89" t="s">
-        <v>1574</v>
+        <v>1578</v>
       </c>
       <c r="Q89" t="s">
-        <v>1575</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
@@ -21486,16 +21551,16 @@
         <v>55</v>
       </c>
       <c r="D90" t="s">
-        <v>1576</v>
+        <v>1580</v>
       </c>
       <c r="E90" t="s">
-        <v>1551</v>
+        <v>1555</v>
       </c>
       <c r="F90" t="s">
         <v>20</v>
       </c>
       <c r="G90" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="H90">
         <v>250000</v>
@@ -21516,16 +21581,16 @@
         <v>33</v>
       </c>
       <c r="N90" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O90" t="s">
-        <v>1577</v>
+        <v>1581</v>
       </c>
       <c r="P90" t="s">
-        <v>1578</v>
+        <v>1582</v>
       </c>
       <c r="Q90" t="s">
-        <v>1579</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
@@ -21539,16 +21604,16 @@
         <v>45</v>
       </c>
       <c r="D91" t="s">
-        <v>1580</v>
+        <v>1584</v>
       </c>
       <c r="E91" t="s">
-        <v>1581</v>
+        <v>1585</v>
       </c>
       <c r="F91" t="s">
-        <v>1582</v>
+        <v>1586</v>
       </c>
       <c r="G91" t="s">
-        <v>1194</v>
+        <v>1198</v>
       </c>
       <c r="H91">
         <v>154000</v>
@@ -21569,16 +21634,16 @@
         <v>25</v>
       </c>
       <c r="N91" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="O91" t="s">
-        <v>1583</v>
+        <v>1587</v>
       </c>
       <c r="P91" t="s">
-        <v>1584</v>
+        <v>1588</v>
       </c>
       <c r="Q91" t="s">
-        <v>1585</v>
+        <v>1589</v>
       </c>
     </row>
   </sheetData>

--- a/hunt/board.xlsx
+++ b/hunt/board.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4285" uniqueCount="1590">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4337" uniqueCount="1607">
   <si>
     <t>Column</t>
   </si>
@@ -3542,6 +3542,27 @@
     <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8755462002</t>
   </si>
   <si>
+    <t>Senior Platform Architect</t>
+  </si>
+  <si>
+    <t>temporal</t>
+  </si>
+  <si>
+    <t>London, England</t>
+  </si>
+  <si>
+    <t>2026-08-29T05:13:36.482Z</t>
+  </si>
+  <si>
+    <t>Post-sales technical delivery/advisory ownership (production readiness, guardrails, reliability best practices) fits the candidate's DevOps and platform-engineering strengths better than pre-sales | Establishing operational standards, enablement, and repeatable delivery patterns overlaps with candidate's DevOps maturity assessment and CI/CD architecture work | Remote posting, so no relocation question</t>
+  </si>
+  <si>
+    <t>Stated comp of €64,400–€84,525 is far below the $180K USD floor — roughly a third of target | London/UK-based remote role, outside the candidate's US market scope and likely needs UK work authorization | Requires deep Temporal SDK/workflow-orchestration and distributed-systems expertise the candidate has not demonstrated</t>
+  </si>
+  <si>
+    <t>https://jobs.ashbyhq.com/temporal/e75ff82a-19e2-470e-ac4b-49f0a87acd76</t>
+  </si>
+  <si>
     <t>Northeast - United States; Southeast - United States</t>
   </si>
   <si>
@@ -4679,9 +4700,6 @@
     <t>Staff Solutions Architect, Banking - India</t>
   </si>
   <si>
-    <t>temporal</t>
-  </si>
-  <si>
     <t>Bengaluru, Karnataka</t>
   </si>
   <si>
@@ -4782,6 +4800,39 @@
   </si>
   <si>
     <t>https://jobs.ashbyhq.com/benchling/8f47c31f-4fd1-4108-92c0-98fc85feb7b0</t>
+  </si>
+  <si>
+    <t>Central US location aligns with candidate's Houston-area base, likely field-based with travel rather than relocation | Trusted-advisor / technical leadership engagement model with large enterprises matches candidate's Customer Engineer experience at Microsoft-style accounts | Confirmed base of $180K meets the candidate's salary floor exactly</t>
+  </si>
+  <si>
+    <t>Core requirement is deep Databricks/Lakehouse, ML &amp; AI and data platform expertise — candidate's depth is Azure DevOps, GitHub, governance and CI/CD, not data engineering or ML | Quota-adjacent enterprise pre-sales with value-selling emphasis; candidate has advisory but not documented pre-sales/value-selling track record | No credit for Azure-native skills here since the platform specialization is Databricks-specific</t>
+  </si>
+  <si>
+    <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8633225002</t>
+  </si>
+  <si>
+    <t>$219K confirmed base is well above the $180K floor and matches principal-level comp targets | Senior scope — defining technical strategy for the largest enterprise accounts — aligns with candidate's principal-level ambitions | Executive trusted-advisor relationship ownership mirrors candidate's enterprise customer advisory model</t>
+  </si>
+  <si>
+    <t>Restricted to NY, NJ, OH, MI, IN — requires relocation from Texas with no remote option stated | Requires demonstrable ML/AI and data-platform depth on Databricks; candidate has no data/ML platform track record | Pre-sales/value-selling background is an explicit expectation the candidate cannot evidence</t>
+  </si>
+  <si>
+    <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8632383002</t>
+  </si>
+  <si>
+    <t>Sr. Solutions Architect - FSI</t>
+  </si>
+  <si>
+    <t>Munich</t>
+  </si>
+  <si>
+    <t>FSI (financial services) vertical focus is a strong precedent match for the candidate's compliance-heavy HIPAA/PCI/SOX background | Role is genuinely technical-authority/advisory work rather than pure quota carrying</t>
+  </si>
+  <si>
+    <t>Located in Munich, Germany — outside the candidate's stated US market scope and likely requires EU work authorization | Requires a declared deep Databricks/data &amp; AI technical archetype the candidate does not have | German-market comp for this role will almost certainly fall below the $180K USD floor</t>
+  </si>
+  <si>
+    <t>https://www.arbeitnow.com/jobs/companies/databricks/sr-solutions-architect-fsi-munich-349241</t>
   </si>
 </sst>
 </file>
@@ -5162,7 +5213,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q238"/>
+  <dimension ref="A1:Q239"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -17097,6 +17148,53 @@
         <v>1175</v>
       </c>
     </row>
+    <row r="239" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>17</v>
+      </c>
+      <c r="B239">
+        <v>30</v>
+      </c>
+      <c r="C239">
+        <v>40</v>
+      </c>
+      <c r="D239" t="s">
+        <v>1176</v>
+      </c>
+      <c r="E239" t="s">
+        <v>1177</v>
+      </c>
+      <c r="F239" t="s">
+        <v>1178</v>
+      </c>
+      <c r="G239" t="s">
+        <v>21</v>
+      </c>
+      <c r="J239" t="s">
+        <v>22</v>
+      </c>
+      <c r="K239" t="s">
+        <v>1143</v>
+      </c>
+      <c r="L239" t="s">
+        <v>1179</v>
+      </c>
+      <c r="M239" t="s">
+        <v>25</v>
+      </c>
+      <c r="N239" t="s">
+        <v>26</v>
+      </c>
+      <c r="O239" t="s">
+        <v>1180</v>
+      </c>
+      <c r="P239" t="s">
+        <v>1181</v>
+      </c>
+      <c r="Q239" t="s">
+        <v>1182</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:Q1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17106,7 +17204,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q91"/>
+  <dimension ref="A1:Q94"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -17193,10 +17291,10 @@
         <v>117</v>
       </c>
       <c r="F2" t="s">
-        <v>1176</v>
+        <v>1183</v>
       </c>
       <c r="G2" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="J2" t="s">
         <v>22</v>
@@ -17211,16 +17309,16 @@
         <v>25</v>
       </c>
       <c r="N2" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O2" t="s">
-        <v>1179</v>
+        <v>1186</v>
       </c>
       <c r="P2" t="s">
-        <v>1180</v>
+        <v>1187</v>
       </c>
       <c r="Q2" t="s">
-        <v>1181</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -17234,16 +17332,16 @@
         <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>1182</v>
+        <v>1189</v>
       </c>
       <c r="E3" t="s">
         <v>117</v>
       </c>
       <c r="F3" t="s">
-        <v>1183</v>
+        <v>1190</v>
       </c>
       <c r="G3" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="H3">
         <v>180000</v>
@@ -17264,16 +17362,16 @@
         <v>33</v>
       </c>
       <c r="N3" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O3" t="s">
-        <v>1184</v>
+        <v>1191</v>
       </c>
       <c r="P3" t="s">
-        <v>1185</v>
+        <v>1192</v>
       </c>
       <c r="Q3" t="s">
-        <v>1186</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
@@ -17287,16 +17385,16 @@
         <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>1187</v>
+        <v>1194</v>
       </c>
       <c r="E4" t="s">
-        <v>1188</v>
+        <v>1195</v>
       </c>
       <c r="F4" t="s">
-        <v>1189</v>
+        <v>1196</v>
       </c>
       <c r="G4" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="H4">
         <v>200000</v>
@@ -17317,16 +17415,16 @@
         <v>25</v>
       </c>
       <c r="N4" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O4" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
       <c r="P4" t="s">
-        <v>1191</v>
+        <v>1198</v>
       </c>
       <c r="Q4" t="s">
-        <v>1192</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -17340,16 +17438,16 @@
         <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>1193</v>
+        <v>1200</v>
       </c>
       <c r="E5" t="s">
-        <v>1188</v>
+        <v>1195</v>
       </c>
       <c r="F5" t="s">
         <v>1081</v>
       </c>
       <c r="G5" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="H5">
         <v>184200</v>
@@ -17370,16 +17468,16 @@
         <v>25</v>
       </c>
       <c r="N5" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O5" t="s">
-        <v>1194</v>
+        <v>1201</v>
       </c>
       <c r="P5" t="s">
-        <v>1195</v>
+        <v>1202</v>
       </c>
       <c r="Q5" t="s">
-        <v>1196</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -17399,10 +17497,10 @@
         <v>1066</v>
       </c>
       <c r="F6" t="s">
-        <v>1197</v>
+        <v>1204</v>
       </c>
       <c r="G6" t="s">
-        <v>1198</v>
+        <v>1205</v>
       </c>
       <c r="J6" t="s">
         <v>22</v>
@@ -17417,16 +17515,16 @@
         <v>25</v>
       </c>
       <c r="N6" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O6" t="s">
-        <v>1199</v>
+        <v>1206</v>
       </c>
       <c r="P6" t="s">
-        <v>1200</v>
+        <v>1207</v>
       </c>
       <c r="Q6" t="s">
-        <v>1201</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -17440,16 +17538,16 @@
         <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="E7" t="s">
         <v>90</v>
       </c>
       <c r="F7" t="s">
-        <v>1203</v>
+        <v>1210</v>
       </c>
       <c r="G7" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="J7" t="s">
         <v>22</v>
@@ -17464,16 +17562,16 @@
         <v>25</v>
       </c>
       <c r="N7" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O7" t="s">
-        <v>1204</v>
+        <v>1211</v>
       </c>
       <c r="P7" t="s">
-        <v>1205</v>
+        <v>1212</v>
       </c>
       <c r="Q7" t="s">
-        <v>1206</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -17487,16 +17585,16 @@
         <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>1207</v>
+        <v>1214</v>
       </c>
       <c r="E8" t="s">
         <v>90</v>
       </c>
       <c r="F8" t="s">
-        <v>1208</v>
+        <v>1215</v>
       </c>
       <c r="G8" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="J8" t="s">
         <v>22</v>
@@ -17511,16 +17609,16 @@
         <v>25</v>
       </c>
       <c r="N8" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O8" t="s">
-        <v>1209</v>
+        <v>1216</v>
       </c>
       <c r="P8" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="Q8" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -17534,16 +17632,16 @@
         <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>1212</v>
+        <v>1219</v>
       </c>
       <c r="E9" t="s">
         <v>117</v>
       </c>
       <c r="F9" t="s">
-        <v>1197</v>
+        <v>1204</v>
       </c>
       <c r="G9" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="J9" t="s">
         <v>22</v>
@@ -17558,16 +17656,16 @@
         <v>33</v>
       </c>
       <c r="N9" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O9" t="s">
-        <v>1213</v>
+        <v>1220</v>
       </c>
       <c r="P9" t="s">
-        <v>1214</v>
+        <v>1221</v>
       </c>
       <c r="Q9" t="s">
-        <v>1215</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -17581,16 +17679,16 @@
         <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>1216</v>
+        <v>1223</v>
       </c>
       <c r="E10" t="s">
-        <v>1217</v>
+        <v>1224</v>
       </c>
       <c r="F10" t="s">
-        <v>1218</v>
+        <v>1225</v>
       </c>
       <c r="G10" t="s">
-        <v>1198</v>
+        <v>1205</v>
       </c>
       <c r="J10" t="s">
         <v>22</v>
@@ -17605,16 +17703,16 @@
         <v>25</v>
       </c>
       <c r="N10" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O10" t="s">
-        <v>1219</v>
+        <v>1226</v>
       </c>
       <c r="P10" t="s">
-        <v>1220</v>
+        <v>1227</v>
       </c>
       <c r="Q10" t="s">
-        <v>1221</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -17628,16 +17726,16 @@
         <v>12</v>
       </c>
       <c r="D11" t="s">
-        <v>1222</v>
+        <v>1229</v>
       </c>
       <c r="E11" t="s">
-        <v>1223</v>
+        <v>1230</v>
       </c>
       <c r="F11" t="s">
-        <v>1224</v>
+        <v>1231</v>
       </c>
       <c r="G11" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="J11" t="s">
         <v>22</v>
@@ -17652,16 +17750,16 @@
         <v>25</v>
       </c>
       <c r="N11" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O11" t="s">
-        <v>1225</v>
+        <v>1232</v>
       </c>
       <c r="P11" t="s">
-        <v>1226</v>
+        <v>1233</v>
       </c>
       <c r="Q11" t="s">
-        <v>1227</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -17675,7 +17773,7 @@
         <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>1228</v>
+        <v>1235</v>
       </c>
       <c r="E12" t="s">
         <v>117</v>
@@ -17684,7 +17782,7 @@
         <v>20</v>
       </c>
       <c r="G12" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="H12">
         <v>217800</v>
@@ -17705,16 +17803,16 @@
         <v>33</v>
       </c>
       <c r="N12" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O12" t="s">
-        <v>1229</v>
+        <v>1236</v>
       </c>
       <c r="P12" t="s">
-        <v>1230</v>
+        <v>1237</v>
       </c>
       <c r="Q12" t="s">
-        <v>1231</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
@@ -17728,16 +17826,16 @@
         <v>45</v>
       </c>
       <c r="D13" t="s">
-        <v>1232</v>
+        <v>1239</v>
       </c>
       <c r="E13" t="s">
         <v>117</v>
       </c>
       <c r="F13" t="s">
-        <v>1233</v>
+        <v>1240</v>
       </c>
       <c r="G13" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="H13">
         <v>219100</v>
@@ -17758,16 +17856,16 @@
         <v>33</v>
       </c>
       <c r="N13" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O13" t="s">
-        <v>1234</v>
+        <v>1241</v>
       </c>
       <c r="P13" t="s">
-        <v>1235</v>
+        <v>1242</v>
       </c>
       <c r="Q13" t="s">
-        <v>1236</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
@@ -17787,10 +17885,10 @@
         <v>1066</v>
       </c>
       <c r="F14" t="s">
-        <v>1237</v>
+        <v>1244</v>
       </c>
       <c r="G14" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="J14" t="s">
         <v>22</v>
@@ -17805,16 +17903,16 @@
         <v>25</v>
       </c>
       <c r="N14" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O14" t="s">
-        <v>1238</v>
+        <v>1245</v>
       </c>
       <c r="P14" t="s">
-        <v>1239</v>
+        <v>1246</v>
       </c>
       <c r="Q14" t="s">
-        <v>1240</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -17828,16 +17926,16 @@
         <v>40</v>
       </c>
       <c r="D15" t="s">
-        <v>1241</v>
+        <v>1248</v>
       </c>
       <c r="E15" t="s">
-        <v>1242</v>
+        <v>1249</v>
       </c>
       <c r="F15" t="s">
-        <v>1243</v>
+        <v>1250</v>
       </c>
       <c r="G15" t="s">
-        <v>1198</v>
+        <v>1205</v>
       </c>
       <c r="J15" t="s">
         <v>22</v>
@@ -17852,16 +17950,16 @@
         <v>25</v>
       </c>
       <c r="N15" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O15" t="s">
-        <v>1244</v>
+        <v>1251</v>
       </c>
       <c r="P15" t="s">
-        <v>1245</v>
+        <v>1252</v>
       </c>
       <c r="Q15" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
@@ -17875,16 +17973,16 @@
         <v>35</v>
       </c>
       <c r="D16" t="s">
-        <v>1247</v>
+        <v>1254</v>
       </c>
       <c r="E16" t="s">
-        <v>1248</v>
+        <v>1255</v>
       </c>
       <c r="F16" t="s">
-        <v>1249</v>
+        <v>1256</v>
       </c>
       <c r="G16" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="J16" t="s">
         <v>22</v>
@@ -17899,16 +17997,16 @@
         <v>25</v>
       </c>
       <c r="N16" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O16" t="s">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="P16" t="s">
-        <v>1251</v>
+        <v>1258</v>
       </c>
       <c r="Q16" t="s">
-        <v>1252</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
@@ -17922,16 +18020,16 @@
         <v>55</v>
       </c>
       <c r="D17" t="s">
-        <v>1253</v>
+        <v>1260</v>
       </c>
       <c r="E17" t="s">
-        <v>1248</v>
+        <v>1255</v>
       </c>
       <c r="F17" t="s">
-        <v>1254</v>
+        <v>1261</v>
       </c>
       <c r="G17" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="J17" t="s">
         <v>22</v>
@@ -17946,16 +18044,16 @@
         <v>25</v>
       </c>
       <c r="N17" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O17" t="s">
-        <v>1255</v>
+        <v>1262</v>
       </c>
       <c r="P17" t="s">
-        <v>1256</v>
+        <v>1263</v>
       </c>
       <c r="Q17" t="s">
-        <v>1257</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
@@ -17969,16 +18067,16 @@
         <v>40</v>
       </c>
       <c r="D18" t="s">
-        <v>1258</v>
+        <v>1265</v>
       </c>
       <c r="E18" t="s">
-        <v>1248</v>
+        <v>1255</v>
       </c>
       <c r="F18" t="s">
-        <v>1249</v>
+        <v>1256</v>
       </c>
       <c r="G18" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="J18" t="s">
         <v>22</v>
@@ -17993,16 +18091,16 @@
         <v>25</v>
       </c>
       <c r="N18" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O18" t="s">
-        <v>1259</v>
+        <v>1266</v>
       </c>
       <c r="P18" t="s">
-        <v>1260</v>
+        <v>1267</v>
       </c>
       <c r="Q18" t="s">
-        <v>1261</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -18016,16 +18114,16 @@
         <v>5</v>
       </c>
       <c r="D19" t="s">
-        <v>1262</v>
+        <v>1269</v>
       </c>
       <c r="E19" t="s">
-        <v>1263</v>
+        <v>1270</v>
       </c>
       <c r="F19" t="s">
-        <v>1264</v>
+        <v>1271</v>
       </c>
       <c r="G19" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="J19" t="s">
         <v>22</v>
@@ -18040,16 +18138,16 @@
         <v>25</v>
       </c>
       <c r="N19" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O19" t="s">
-        <v>1265</v>
+        <v>1272</v>
       </c>
       <c r="P19" t="s">
-        <v>1266</v>
+        <v>1273</v>
       </c>
       <c r="Q19" t="s">
-        <v>1267</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -18063,16 +18161,16 @@
         <v>45</v>
       </c>
       <c r="D20" t="s">
-        <v>1268</v>
+        <v>1275</v>
       </c>
       <c r="E20" t="s">
-        <v>1263</v>
+        <v>1270</v>
       </c>
       <c r="F20" t="s">
-        <v>1197</v>
+        <v>1204</v>
       </c>
       <c r="G20" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="J20" t="s">
         <v>22</v>
@@ -18087,16 +18185,16 @@
         <v>25</v>
       </c>
       <c r="N20" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O20" t="s">
-        <v>1269</v>
+        <v>1276</v>
       </c>
       <c r="P20" t="s">
-        <v>1270</v>
+        <v>1277</v>
       </c>
       <c r="Q20" t="s">
-        <v>1271</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
@@ -18110,16 +18208,16 @@
         <v>5</v>
       </c>
       <c r="D21" t="s">
-        <v>1272</v>
+        <v>1279</v>
       </c>
       <c r="E21" t="s">
-        <v>1263</v>
+        <v>1270</v>
       </c>
       <c r="F21" t="s">
-        <v>1264</v>
+        <v>1271</v>
       </c>
       <c r="G21" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="J21" t="s">
         <v>22</v>
@@ -18134,16 +18232,16 @@
         <v>25</v>
       </c>
       <c r="N21" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O21" t="s">
-        <v>1273</v>
+        <v>1280</v>
       </c>
       <c r="P21" t="s">
-        <v>1274</v>
+        <v>1281</v>
       </c>
       <c r="Q21" t="s">
-        <v>1275</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -18157,16 +18255,16 @@
         <v>5</v>
       </c>
       <c r="D22" t="s">
-        <v>1276</v>
+        <v>1283</v>
       </c>
       <c r="E22" t="s">
-        <v>1263</v>
+        <v>1270</v>
       </c>
       <c r="F22" t="s">
-        <v>1264</v>
+        <v>1271</v>
       </c>
       <c r="G22" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="J22" t="s">
         <v>22</v>
@@ -18181,16 +18279,16 @@
         <v>25</v>
       </c>
       <c r="N22" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O22" t="s">
-        <v>1277</v>
+        <v>1284</v>
       </c>
       <c r="P22" t="s">
-        <v>1278</v>
+        <v>1285</v>
       </c>
       <c r="Q22" t="s">
-        <v>1279</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
@@ -18204,16 +18302,16 @@
         <v>18</v>
       </c>
       <c r="D23" t="s">
-        <v>1280</v>
+        <v>1287</v>
       </c>
       <c r="E23" t="s">
-        <v>1263</v>
+        <v>1270</v>
       </c>
       <c r="F23" t="s">
-        <v>1264</v>
+        <v>1271</v>
       </c>
       <c r="G23" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="J23" t="s">
         <v>22</v>
@@ -18228,16 +18326,16 @@
         <v>25</v>
       </c>
       <c r="N23" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O23" t="s">
-        <v>1281</v>
+        <v>1288</v>
       </c>
       <c r="P23" t="s">
-        <v>1282</v>
+        <v>1289</v>
       </c>
       <c r="Q23" t="s">
-        <v>1283</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
@@ -18251,16 +18349,16 @@
         <v>5</v>
       </c>
       <c r="D24" t="s">
-        <v>1284</v>
+        <v>1291</v>
       </c>
       <c r="E24" t="s">
-        <v>1263</v>
+        <v>1270</v>
       </c>
       <c r="F24" t="s">
-        <v>1264</v>
+        <v>1271</v>
       </c>
       <c r="G24" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="J24" t="s">
         <v>22</v>
@@ -18275,16 +18373,16 @@
         <v>25</v>
       </c>
       <c r="N24" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O24" t="s">
-        <v>1285</v>
+        <v>1292</v>
       </c>
       <c r="P24" t="s">
-        <v>1286</v>
+        <v>1293</v>
       </c>
       <c r="Q24" t="s">
-        <v>1287</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
@@ -18298,16 +18396,16 @@
         <v>40</v>
       </c>
       <c r="D25" t="s">
-        <v>1288</v>
+        <v>1295</v>
       </c>
       <c r="E25" t="s">
-        <v>1263</v>
+        <v>1270</v>
       </c>
       <c r="F25" t="s">
-        <v>1264</v>
+        <v>1271</v>
       </c>
       <c r="G25" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="J25" t="s">
         <v>22</v>
@@ -18322,16 +18420,16 @@
         <v>25</v>
       </c>
       <c r="N25" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O25" t="s">
-        <v>1289</v>
+        <v>1296</v>
       </c>
       <c r="P25" t="s">
-        <v>1290</v>
+        <v>1297</v>
       </c>
       <c r="Q25" t="s">
-        <v>1291</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
@@ -18345,16 +18443,16 @@
         <v>45</v>
       </c>
       <c r="D26" t="s">
-        <v>1292</v>
+        <v>1299</v>
       </c>
       <c r="E26" t="s">
-        <v>1263</v>
+        <v>1270</v>
       </c>
       <c r="F26" t="s">
-        <v>1264</v>
+        <v>1271</v>
       </c>
       <c r="G26" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="J26" t="s">
         <v>22</v>
@@ -18369,16 +18467,16 @@
         <v>25</v>
       </c>
       <c r="N26" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O26" t="s">
-        <v>1293</v>
+        <v>1300</v>
       </c>
       <c r="P26" t="s">
-        <v>1294</v>
+        <v>1301</v>
       </c>
       <c r="Q26" t="s">
-        <v>1295</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
@@ -18392,16 +18490,16 @@
         <v>3</v>
       </c>
       <c r="D27" t="s">
-        <v>1296</v>
+        <v>1303</v>
       </c>
       <c r="E27" t="s">
-        <v>1263</v>
+        <v>1270</v>
       </c>
       <c r="F27" t="s">
-        <v>1264</v>
+        <v>1271</v>
       </c>
       <c r="G27" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="J27" t="s">
         <v>22</v>
@@ -18416,16 +18514,16 @@
         <v>25</v>
       </c>
       <c r="N27" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O27" t="s">
-        <v>1297</v>
+        <v>1304</v>
       </c>
       <c r="P27" t="s">
-        <v>1298</v>
+        <v>1305</v>
       </c>
       <c r="Q27" t="s">
-        <v>1299</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
@@ -18439,7 +18537,7 @@
         <v>42</v>
       </c>
       <c r="D28" t="s">
-        <v>1300</v>
+        <v>1307</v>
       </c>
       <c r="E28" t="s">
         <v>117</v>
@@ -18448,7 +18546,7 @@
         <v>20</v>
       </c>
       <c r="G28" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="J28" t="s">
         <v>22</v>
@@ -18463,16 +18561,16 @@
         <v>25</v>
       </c>
       <c r="N28" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O28" t="s">
-        <v>1301</v>
+        <v>1308</v>
       </c>
       <c r="P28" t="s">
-        <v>1302</v>
+        <v>1309</v>
       </c>
       <c r="Q28" t="s">
-        <v>1303</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
@@ -18486,7 +18584,7 @@
         <v>40</v>
       </c>
       <c r="D29" t="s">
-        <v>1304</v>
+        <v>1311</v>
       </c>
       <c r="E29" t="s">
         <v>117</v>
@@ -18495,7 +18593,7 @@
         <v>20</v>
       </c>
       <c r="G29" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="J29" t="s">
         <v>22</v>
@@ -18510,16 +18608,16 @@
         <v>25</v>
       </c>
       <c r="N29" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O29" t="s">
-        <v>1305</v>
+        <v>1312</v>
       </c>
       <c r="P29" t="s">
-        <v>1306</v>
+        <v>1313</v>
       </c>
       <c r="Q29" t="s">
-        <v>1307</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
@@ -18539,10 +18637,10 @@
         <v>117</v>
       </c>
       <c r="F30" t="s">
-        <v>1308</v>
+        <v>1315</v>
       </c>
       <c r="G30" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="H30">
         <v>180000</v>
@@ -18563,16 +18661,16 @@
         <v>33</v>
       </c>
       <c r="N30" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O30" t="s">
-        <v>1309</v>
+        <v>1316</v>
       </c>
       <c r="P30" t="s">
-        <v>1310</v>
+        <v>1317</v>
       </c>
       <c r="Q30" t="s">
-        <v>1311</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
@@ -18586,7 +18684,7 @@
         <v>52</v>
       </c>
       <c r="D31" t="s">
-        <v>1312</v>
+        <v>1319</v>
       </c>
       <c r="E31" t="s">
         <v>117</v>
@@ -18595,7 +18693,7 @@
         <v>20</v>
       </c>
       <c r="G31" t="s">
-        <v>1198</v>
+        <v>1205</v>
       </c>
       <c r="H31">
         <v>180000</v>
@@ -18616,16 +18714,16 @@
         <v>33</v>
       </c>
       <c r="N31" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O31" t="s">
-        <v>1313</v>
+        <v>1320</v>
       </c>
       <c r="P31" t="s">
-        <v>1314</v>
+        <v>1321</v>
       </c>
       <c r="Q31" t="s">
-        <v>1315</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
@@ -18639,7 +18737,7 @@
         <v>55</v>
       </c>
       <c r="D32" t="s">
-        <v>1316</v>
+        <v>1323</v>
       </c>
       <c r="E32" t="s">
         <v>117</v>
@@ -18648,7 +18746,7 @@
         <v>20</v>
       </c>
       <c r="G32" t="s">
-        <v>1198</v>
+        <v>1205</v>
       </c>
       <c r="H32">
         <v>180000</v>
@@ -18669,16 +18767,16 @@
         <v>33</v>
       </c>
       <c r="N32" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O32" t="s">
-        <v>1317</v>
+        <v>1324</v>
       </c>
       <c r="P32" t="s">
-        <v>1318</v>
+        <v>1325</v>
       </c>
       <c r="Q32" t="s">
-        <v>1319</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
@@ -18692,16 +18790,16 @@
         <v>48</v>
       </c>
       <c r="D33" t="s">
-        <v>1320</v>
+        <v>1327</v>
       </c>
       <c r="E33" t="s">
         <v>117</v>
       </c>
       <c r="F33" t="s">
-        <v>1321</v>
+        <v>1328</v>
       </c>
       <c r="G33" t="s">
-        <v>1198</v>
+        <v>1205</v>
       </c>
       <c r="H33">
         <v>219100</v>
@@ -18722,16 +18820,16 @@
         <v>33</v>
       </c>
       <c r="N33" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O33" t="s">
-        <v>1322</v>
+        <v>1329</v>
       </c>
       <c r="P33" t="s">
-        <v>1323</v>
+        <v>1330</v>
       </c>
       <c r="Q33" t="s">
-        <v>1324</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
@@ -18745,16 +18843,16 @@
         <v>45</v>
       </c>
       <c r="D34" t="s">
-        <v>1325</v>
+        <v>1332</v>
       </c>
       <c r="E34" t="s">
         <v>117</v>
       </c>
       <c r="F34" t="s">
-        <v>1326</v>
+        <v>1333</v>
       </c>
       <c r="G34" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="H34">
         <v>180000</v>
@@ -18775,16 +18873,16 @@
         <v>33</v>
       </c>
       <c r="N34" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O34" t="s">
-        <v>1327</v>
+        <v>1334</v>
       </c>
       <c r="P34" t="s">
-        <v>1328</v>
+        <v>1335</v>
       </c>
       <c r="Q34" t="s">
-        <v>1329</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
@@ -18798,7 +18896,7 @@
         <v>30</v>
       </c>
       <c r="D35" t="s">
-        <v>1330</v>
+        <v>1337</v>
       </c>
       <c r="E35" t="s">
         <v>117</v>
@@ -18807,7 +18905,7 @@
         <v>20</v>
       </c>
       <c r="G35" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="H35">
         <v>219100</v>
@@ -18828,16 +18926,16 @@
         <v>25</v>
       </c>
       <c r="N35" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O35" t="s">
-        <v>1331</v>
+        <v>1338</v>
       </c>
       <c r="P35" t="s">
-        <v>1332</v>
+        <v>1339</v>
       </c>
       <c r="Q35" t="s">
-        <v>1333</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
@@ -18851,7 +18949,7 @@
         <v>45</v>
       </c>
       <c r="D36" t="s">
-        <v>1334</v>
+        <v>1341</v>
       </c>
       <c r="E36" t="s">
         <v>117</v>
@@ -18860,7 +18958,7 @@
         <v>20</v>
       </c>
       <c r="G36" t="s">
-        <v>1198</v>
+        <v>1205</v>
       </c>
       <c r="H36">
         <v>219100</v>
@@ -18881,16 +18979,16 @@
         <v>33</v>
       </c>
       <c r="N36" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O36" t="s">
-        <v>1335</v>
+        <v>1342</v>
       </c>
       <c r="P36" t="s">
-        <v>1336</v>
+        <v>1343</v>
       </c>
       <c r="Q36" t="s">
-        <v>1337</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
@@ -18904,16 +19002,16 @@
         <v>30</v>
       </c>
       <c r="D37" t="s">
-        <v>1338</v>
+        <v>1345</v>
       </c>
       <c r="E37" t="s">
         <v>117</v>
       </c>
       <c r="F37" t="s">
-        <v>1339</v>
+        <v>1346</v>
       </c>
       <c r="G37" t="s">
-        <v>1198</v>
+        <v>1205</v>
       </c>
       <c r="J37" t="s">
         <v>22</v>
@@ -18928,16 +19026,16 @@
         <v>25</v>
       </c>
       <c r="N37" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O37" t="s">
-        <v>1340</v>
+        <v>1347</v>
       </c>
       <c r="P37" t="s">
-        <v>1341</v>
+        <v>1348</v>
       </c>
       <c r="Q37" t="s">
-        <v>1342</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
@@ -18951,16 +19049,16 @@
         <v>58</v>
       </c>
       <c r="D38" t="s">
-        <v>1343</v>
+        <v>1350</v>
       </c>
       <c r="E38" t="s">
-        <v>1344</v>
+        <v>1351</v>
       </c>
       <c r="F38" t="s">
-        <v>1345</v>
+        <v>1352</v>
       </c>
       <c r="G38" t="s">
-        <v>1198</v>
+        <v>1205</v>
       </c>
       <c r="H38">
         <v>257000</v>
@@ -18981,16 +19079,16 @@
         <v>33</v>
       </c>
       <c r="N38" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O38" t="s">
-        <v>1346</v>
+        <v>1353</v>
       </c>
       <c r="P38" t="s">
-        <v>1347</v>
+        <v>1354</v>
       </c>
       <c r="Q38" t="s">
-        <v>1348</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
@@ -19007,13 +19105,13 @@
         <v>541</v>
       </c>
       <c r="E39" t="s">
-        <v>1188</v>
+        <v>1195</v>
       </c>
       <c r="F39" t="s">
-        <v>1349</v>
+        <v>1356</v>
       </c>
       <c r="G39" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="H39">
         <v>200000</v>
@@ -19034,16 +19132,16 @@
         <v>25</v>
       </c>
       <c r="N39" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O39" t="s">
-        <v>1350</v>
+        <v>1357</v>
       </c>
       <c r="P39" t="s">
-        <v>1351</v>
+        <v>1358</v>
       </c>
       <c r="Q39" t="s">
-        <v>1352</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
@@ -19057,16 +19155,16 @@
         <v>20</v>
       </c>
       <c r="D40" t="s">
-        <v>1353</v>
+        <v>1360</v>
       </c>
       <c r="E40" t="s">
         <v>1066</v>
       </c>
       <c r="F40" t="s">
-        <v>1354</v>
+        <v>1361</v>
       </c>
       <c r="G40" t="s">
-        <v>1198</v>
+        <v>1205</v>
       </c>
       <c r="J40" t="s">
         <v>22</v>
@@ -19081,16 +19179,16 @@
         <v>25</v>
       </c>
       <c r="N40" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O40" t="s">
-        <v>1355</v>
+        <v>1362</v>
       </c>
       <c r="P40" t="s">
-        <v>1356</v>
+        <v>1363</v>
       </c>
       <c r="Q40" t="s">
-        <v>1357</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
@@ -19110,10 +19208,10 @@
         <v>1066</v>
       </c>
       <c r="F41" t="s">
-        <v>1358</v>
+        <v>1365</v>
       </c>
       <c r="G41" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="J41" t="s">
         <v>22</v>
@@ -19128,16 +19226,16 @@
         <v>25</v>
       </c>
       <c r="N41" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O41" t="s">
-        <v>1359</v>
+        <v>1366</v>
       </c>
       <c r="P41" t="s">
-        <v>1360</v>
+        <v>1367</v>
       </c>
       <c r="Q41" t="s">
-        <v>1361</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
@@ -19151,16 +19249,16 @@
         <v>15</v>
       </c>
       <c r="D42" t="s">
-        <v>1362</v>
+        <v>1369</v>
       </c>
       <c r="E42" t="s">
         <v>1066</v>
       </c>
       <c r="F42" t="s">
-        <v>1363</v>
+        <v>1370</v>
       </c>
       <c r="G42" t="s">
-        <v>1198</v>
+        <v>1205</v>
       </c>
       <c r="H42">
         <v>500000</v>
@@ -19181,16 +19279,16 @@
         <v>25</v>
       </c>
       <c r="N42" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O42" t="s">
-        <v>1364</v>
+        <v>1371</v>
       </c>
       <c r="P42" t="s">
-        <v>1365</v>
+        <v>1372</v>
       </c>
       <c r="Q42" t="s">
-        <v>1366</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
@@ -19204,16 +19302,16 @@
         <v>18</v>
       </c>
       <c r="D43" t="s">
-        <v>1367</v>
+        <v>1374</v>
       </c>
       <c r="E43" t="s">
         <v>90</v>
       </c>
       <c r="F43" t="s">
-        <v>1208</v>
+        <v>1215</v>
       </c>
       <c r="G43" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="H43">
         <v>274456</v>
@@ -19234,16 +19332,16 @@
         <v>25</v>
       </c>
       <c r="N43" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O43" t="s">
-        <v>1368</v>
+        <v>1375</v>
       </c>
       <c r="P43" t="s">
-        <v>1369</v>
+        <v>1376</v>
       </c>
       <c r="Q43" t="s">
-        <v>1370</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
@@ -19257,16 +19355,16 @@
         <v>30</v>
       </c>
       <c r="D44" t="s">
-        <v>1371</v>
+        <v>1378</v>
       </c>
       <c r="E44" t="s">
         <v>90</v>
       </c>
       <c r="F44" t="s">
-        <v>1372</v>
+        <v>1379</v>
       </c>
       <c r="G44" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="J44" t="s">
         <v>22</v>
@@ -19281,16 +19379,16 @@
         <v>25</v>
       </c>
       <c r="N44" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O44" t="s">
-        <v>1373</v>
+        <v>1380</v>
       </c>
       <c r="P44" t="s">
-        <v>1374</v>
+        <v>1381</v>
       </c>
       <c r="Q44" t="s">
-        <v>1375</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
@@ -19304,16 +19402,16 @@
         <v>22</v>
       </c>
       <c r="D45" t="s">
-        <v>1376</v>
+        <v>1383</v>
       </c>
       <c r="E45" t="s">
         <v>90</v>
       </c>
       <c r="F45" t="s">
-        <v>1377</v>
+        <v>1384</v>
       </c>
       <c r="G45" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="J45" t="s">
         <v>22</v>
@@ -19328,16 +19426,16 @@
         <v>25</v>
       </c>
       <c r="N45" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O45" t="s">
-        <v>1378</v>
+        <v>1385</v>
       </c>
       <c r="P45" t="s">
-        <v>1379</v>
+        <v>1386</v>
       </c>
       <c r="Q45" t="s">
-        <v>1380</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
@@ -19351,16 +19449,16 @@
         <v>48</v>
       </c>
       <c r="D46" t="s">
-        <v>1381</v>
+        <v>1388</v>
       </c>
       <c r="E46" t="s">
         <v>90</v>
       </c>
       <c r="F46" t="s">
-        <v>1382</v>
+        <v>1389</v>
       </c>
       <c r="G46" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="J46" t="s">
         <v>22</v>
@@ -19375,16 +19473,16 @@
         <v>33</v>
       </c>
       <c r="N46" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O46" t="s">
-        <v>1383</v>
+        <v>1390</v>
       </c>
       <c r="P46" t="s">
-        <v>1384</v>
+        <v>1391</v>
       </c>
       <c r="Q46" t="s">
-        <v>1385</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
@@ -19398,16 +19496,16 @@
         <v>25</v>
       </c>
       <c r="D47" t="s">
-        <v>1386</v>
+        <v>1393</v>
       </c>
       <c r="E47" t="s">
         <v>90</v>
       </c>
       <c r="F47" t="s">
-        <v>1197</v>
+        <v>1204</v>
       </c>
       <c r="G47" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="J47" t="s">
         <v>22</v>
@@ -19422,16 +19520,16 @@
         <v>25</v>
       </c>
       <c r="N47" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O47" t="s">
-        <v>1387</v>
+        <v>1394</v>
       </c>
       <c r="P47" t="s">
-        <v>1388</v>
+        <v>1395</v>
       </c>
       <c r="Q47" t="s">
-        <v>1389</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
@@ -19445,16 +19543,16 @@
         <v>40</v>
       </c>
       <c r="D48" t="s">
-        <v>1390</v>
+        <v>1397</v>
       </c>
       <c r="E48" t="s">
         <v>90</v>
       </c>
       <c r="F48" t="s">
-        <v>1391</v>
+        <v>1398</v>
       </c>
       <c r="G48" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="J48" t="s">
         <v>22</v>
@@ -19469,16 +19567,16 @@
         <v>25</v>
       </c>
       <c r="N48" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O48" t="s">
-        <v>1392</v>
+        <v>1399</v>
       </c>
       <c r="P48" t="s">
-        <v>1393</v>
+        <v>1400</v>
       </c>
       <c r="Q48" t="s">
-        <v>1394</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
@@ -19492,16 +19590,16 @@
         <v>70</v>
       </c>
       <c r="D49" t="s">
-        <v>1395</v>
+        <v>1402</v>
       </c>
       <c r="E49" t="s">
-        <v>1396</v>
+        <v>1403</v>
       </c>
       <c r="F49" t="s">
-        <v>1397</v>
+        <v>1404</v>
       </c>
       <c r="G49" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="J49" t="s">
         <v>22</v>
@@ -19516,16 +19614,16 @@
         <v>25</v>
       </c>
       <c r="N49" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O49" t="s">
-        <v>1398</v>
+        <v>1405</v>
       </c>
       <c r="P49" t="s">
-        <v>1399</v>
+        <v>1406</v>
       </c>
       <c r="Q49" t="s">
-        <v>1400</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
@@ -19539,16 +19637,16 @@
         <v>58</v>
       </c>
       <c r="D50" t="s">
-        <v>1401</v>
+        <v>1408</v>
       </c>
       <c r="E50" t="s">
-        <v>1402</v>
+        <v>1409</v>
       </c>
       <c r="F50" t="s">
-        <v>1197</v>
+        <v>1204</v>
       </c>
       <c r="G50" t="s">
-        <v>1198</v>
+        <v>1205</v>
       </c>
       <c r="J50" t="s">
         <v>22</v>
@@ -19563,16 +19661,16 @@
         <v>25</v>
       </c>
       <c r="N50" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O50" t="s">
-        <v>1403</v>
+        <v>1410</v>
       </c>
       <c r="P50" t="s">
-        <v>1404</v>
+        <v>1411</v>
       </c>
       <c r="Q50" t="s">
-        <v>1405</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
@@ -19586,16 +19684,16 @@
         <v>32</v>
       </c>
       <c r="D51" t="s">
-        <v>1406</v>
+        <v>1413</v>
       </c>
       <c r="E51" t="s">
-        <v>1407</v>
+        <v>1414</v>
       </c>
       <c r="F51" t="s">
-        <v>1408</v>
+        <v>1415</v>
       </c>
       <c r="G51" t="s">
-        <v>1198</v>
+        <v>1205</v>
       </c>
       <c r="J51" t="s">
         <v>22</v>
@@ -19610,16 +19708,16 @@
         <v>25</v>
       </c>
       <c r="N51" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O51" t="s">
-        <v>1409</v>
+        <v>1416</v>
       </c>
       <c r="P51" t="s">
-        <v>1410</v>
+        <v>1417</v>
       </c>
       <c r="Q51" t="s">
-        <v>1411</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
@@ -19633,16 +19731,16 @@
         <v>4</v>
       </c>
       <c r="D52" t="s">
-        <v>1412</v>
+        <v>1419</v>
       </c>
       <c r="E52" t="s">
-        <v>1413</v>
+        <v>1420</v>
       </c>
       <c r="F52" t="s">
-        <v>1414</v>
+        <v>1421</v>
       </c>
       <c r="G52" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="J52" t="s">
         <v>22</v>
@@ -19657,16 +19755,16 @@
         <v>25</v>
       </c>
       <c r="N52" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O52" t="s">
-        <v>1415</v>
+        <v>1422</v>
       </c>
       <c r="P52" t="s">
-        <v>1416</v>
+        <v>1423</v>
       </c>
       <c r="Q52" t="s">
-        <v>1417</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
@@ -19680,16 +19778,16 @@
         <v>25</v>
       </c>
       <c r="D53" t="s">
-        <v>1418</v>
+        <v>1425</v>
       </c>
       <c r="E53" t="s">
-        <v>1419</v>
+        <v>1426</v>
       </c>
       <c r="F53" t="s">
-        <v>1254</v>
+        <v>1261</v>
       </c>
       <c r="G53" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="J53" t="s">
         <v>22</v>
@@ -19704,16 +19802,16 @@
         <v>25</v>
       </c>
       <c r="N53" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O53" t="s">
-        <v>1420</v>
+        <v>1427</v>
       </c>
       <c r="P53" t="s">
-        <v>1421</v>
+        <v>1428</v>
       </c>
       <c r="Q53" t="s">
-        <v>1422</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
@@ -19727,16 +19825,16 @@
         <v>30</v>
       </c>
       <c r="D54" t="s">
-        <v>1423</v>
+        <v>1430</v>
       </c>
       <c r="E54" t="s">
-        <v>1424</v>
+        <v>1431</v>
       </c>
       <c r="F54" t="s">
-        <v>1425</v>
+        <v>1432</v>
       </c>
       <c r="G54" t="s">
-        <v>1198</v>
+        <v>1205</v>
       </c>
       <c r="J54" t="s">
         <v>22</v>
@@ -19751,16 +19849,16 @@
         <v>25</v>
       </c>
       <c r="N54" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O54" t="s">
-        <v>1426</v>
+        <v>1433</v>
       </c>
       <c r="P54" t="s">
-        <v>1427</v>
+        <v>1434</v>
       </c>
       <c r="Q54" t="s">
-        <v>1428</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
@@ -19774,16 +19872,16 @@
         <v>52</v>
       </c>
       <c r="D55" t="s">
-        <v>1429</v>
+        <v>1436</v>
       </c>
       <c r="E55" t="s">
         <v>117</v>
       </c>
       <c r="F55" t="s">
-        <v>1430</v>
+        <v>1437</v>
       </c>
       <c r="G55" t="s">
-        <v>1198</v>
+        <v>1205</v>
       </c>
       <c r="H55">
         <v>180000</v>
@@ -19804,16 +19902,16 @@
         <v>33</v>
       </c>
       <c r="N55" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O55" t="s">
-        <v>1431</v>
+        <v>1438</v>
       </c>
       <c r="P55" t="s">
-        <v>1432</v>
+        <v>1439</v>
       </c>
       <c r="Q55" t="s">
-        <v>1433</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
@@ -19827,7 +19925,7 @@
         <v>50</v>
       </c>
       <c r="D56" t="s">
-        <v>1434</v>
+        <v>1441</v>
       </c>
       <c r="E56" t="s">
         <v>117</v>
@@ -19836,7 +19934,7 @@
         <v>20</v>
       </c>
       <c r="G56" t="s">
-        <v>1198</v>
+        <v>1205</v>
       </c>
       <c r="H56">
         <v>180000</v>
@@ -19857,16 +19955,16 @@
         <v>33</v>
       </c>
       <c r="N56" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O56" t="s">
-        <v>1435</v>
+        <v>1442</v>
       </c>
       <c r="P56" t="s">
-        <v>1436</v>
+        <v>1443</v>
       </c>
       <c r="Q56" t="s">
-        <v>1437</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
@@ -19880,7 +19978,7 @@
         <v>46</v>
       </c>
       <c r="D57" t="s">
-        <v>1438</v>
+        <v>1445</v>
       </c>
       <c r="E57" t="s">
         <v>117</v>
@@ -19889,7 +19987,7 @@
         <v>20</v>
       </c>
       <c r="G57" t="s">
-        <v>1198</v>
+        <v>1205</v>
       </c>
       <c r="H57">
         <v>180000</v>
@@ -19910,16 +20008,16 @@
         <v>33</v>
       </c>
       <c r="N57" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O57" t="s">
-        <v>1439</v>
+        <v>1446</v>
       </c>
       <c r="P57" t="s">
-        <v>1440</v>
+        <v>1447</v>
       </c>
       <c r="Q57" t="s">
-        <v>1441</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
@@ -19933,7 +20031,7 @@
         <v>38</v>
       </c>
       <c r="D58" t="s">
-        <v>1442</v>
+        <v>1449</v>
       </c>
       <c r="E58" t="s">
         <v>117</v>
@@ -19942,7 +20040,7 @@
         <v>20</v>
       </c>
       <c r="G58" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="H58">
         <v>217800</v>
@@ -19963,16 +20061,16 @@
         <v>25</v>
       </c>
       <c r="N58" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O58" t="s">
-        <v>1443</v>
+        <v>1450</v>
       </c>
       <c r="P58" t="s">
-        <v>1444</v>
+        <v>1451</v>
       </c>
       <c r="Q58" t="s">
-        <v>1445</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
@@ -19992,10 +20090,10 @@
         <v>117</v>
       </c>
       <c r="F59" t="s">
-        <v>1446</v>
+        <v>1453</v>
       </c>
       <c r="G59" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="H59">
         <v>180000</v>
@@ -20016,16 +20114,16 @@
         <v>33</v>
       </c>
       <c r="N59" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O59" t="s">
-        <v>1447</v>
+        <v>1454</v>
       </c>
       <c r="P59" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
       <c r="Q59" t="s">
-        <v>1449</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
@@ -20039,16 +20137,16 @@
         <v>45</v>
       </c>
       <c r="D60" t="s">
-        <v>1450</v>
+        <v>1457</v>
       </c>
       <c r="E60" t="s">
         <v>117</v>
       </c>
       <c r="F60" t="s">
-        <v>1451</v>
+        <v>1458</v>
       </c>
       <c r="G60" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="H60">
         <v>219100</v>
@@ -20069,16 +20167,16 @@
         <v>33</v>
       </c>
       <c r="N60" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O60" t="s">
-        <v>1452</v>
+        <v>1459</v>
       </c>
       <c r="P60" t="s">
-        <v>1453</v>
+        <v>1460</v>
       </c>
       <c r="Q60" t="s">
-        <v>1454</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
@@ -20092,16 +20190,16 @@
         <v>42</v>
       </c>
       <c r="D61" t="s">
-        <v>1455</v>
+        <v>1462</v>
       </c>
       <c r="E61" t="s">
         <v>117</v>
       </c>
       <c r="F61" t="s">
-        <v>1456</v>
+        <v>1463</v>
       </c>
       <c r="G61" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="H61">
         <v>180000</v>
@@ -20122,16 +20220,16 @@
         <v>33</v>
       </c>
       <c r="N61" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O61" t="s">
-        <v>1457</v>
+        <v>1464</v>
       </c>
       <c r="P61" t="s">
-        <v>1458</v>
+        <v>1465</v>
       </c>
       <c r="Q61" t="s">
-        <v>1459</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
@@ -20145,7 +20243,7 @@
         <v>32</v>
       </c>
       <c r="D62" t="s">
-        <v>1460</v>
+        <v>1467</v>
       </c>
       <c r="E62" t="s">
         <v>117</v>
@@ -20154,7 +20252,7 @@
         <v>20</v>
       </c>
       <c r="G62" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="H62">
         <v>219100</v>
@@ -20175,16 +20273,16 @@
         <v>25</v>
       </c>
       <c r="N62" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O62" t="s">
-        <v>1461</v>
+        <v>1468</v>
       </c>
       <c r="P62" t="s">
-        <v>1462</v>
+        <v>1469</v>
       </c>
       <c r="Q62" t="s">
-        <v>1463</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
@@ -20198,7 +20296,7 @@
         <v>35</v>
       </c>
       <c r="D63" t="s">
-        <v>1464</v>
+        <v>1471</v>
       </c>
       <c r="E63" t="s">
         <v>117</v>
@@ -20207,7 +20305,7 @@
         <v>20</v>
       </c>
       <c r="G63" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="H63">
         <v>219100</v>
@@ -20228,16 +20326,16 @@
         <v>25</v>
       </c>
       <c r="N63" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O63" t="s">
-        <v>1465</v>
+        <v>1472</v>
       </c>
       <c r="P63" t="s">
-        <v>1466</v>
+        <v>1473</v>
       </c>
       <c r="Q63" t="s">
-        <v>1467</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
@@ -20251,16 +20349,16 @@
         <v>40</v>
       </c>
       <c r="D64" t="s">
-        <v>1468</v>
+        <v>1475</v>
       </c>
       <c r="E64" t="s">
         <v>117</v>
       </c>
       <c r="F64" t="s">
-        <v>1469</v>
+        <v>1476</v>
       </c>
       <c r="G64" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="H64">
         <v>219100</v>
@@ -20281,16 +20379,16 @@
         <v>33</v>
       </c>
       <c r="N64" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O64" t="s">
-        <v>1470</v>
+        <v>1477</v>
       </c>
       <c r="P64" t="s">
-        <v>1471</v>
+        <v>1478</v>
       </c>
       <c r="Q64" t="s">
-        <v>1472</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
@@ -20304,7 +20402,7 @@
         <v>38</v>
       </c>
       <c r="D65" t="s">
-        <v>1473</v>
+        <v>1480</v>
       </c>
       <c r="E65" t="s">
         <v>117</v>
@@ -20313,7 +20411,7 @@
         <v>818</v>
       </c>
       <c r="G65" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="H65">
         <v>219100</v>
@@ -20334,16 +20432,16 @@
         <v>25</v>
       </c>
       <c r="N65" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O65" t="s">
-        <v>1474</v>
+        <v>1481</v>
       </c>
       <c r="P65" t="s">
-        <v>1475</v>
+        <v>1482</v>
       </c>
       <c r="Q65" t="s">
-        <v>1476</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
@@ -20357,7 +20455,7 @@
         <v>40</v>
       </c>
       <c r="D66" t="s">
-        <v>1477</v>
+        <v>1484</v>
       </c>
       <c r="E66" t="s">
         <v>117</v>
@@ -20366,7 +20464,7 @@
         <v>20</v>
       </c>
       <c r="G66" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="H66">
         <v>219100</v>
@@ -20387,16 +20485,16 @@
         <v>33</v>
       </c>
       <c r="N66" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O66" t="s">
-        <v>1478</v>
+        <v>1485</v>
       </c>
       <c r="P66" t="s">
-        <v>1479</v>
+        <v>1486</v>
       </c>
       <c r="Q66" t="s">
-        <v>1480</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
@@ -20410,16 +20508,16 @@
         <v>33</v>
       </c>
       <c r="D67" t="s">
-        <v>1481</v>
+        <v>1488</v>
       </c>
       <c r="E67" t="s">
         <v>117</v>
       </c>
       <c r="F67" t="s">
-        <v>1482</v>
+        <v>1489</v>
       </c>
       <c r="G67" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="H67">
         <v>219100</v>
@@ -20440,16 +20538,16 @@
         <v>25</v>
       </c>
       <c r="N67" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O67" t="s">
-        <v>1483</v>
+        <v>1490</v>
       </c>
       <c r="P67" t="s">
-        <v>1484</v>
+        <v>1491</v>
       </c>
       <c r="Q67" t="s">
-        <v>1485</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
@@ -20463,16 +20561,16 @@
         <v>48</v>
       </c>
       <c r="D68" t="s">
-        <v>1486</v>
+        <v>1493</v>
       </c>
       <c r="E68" t="s">
-        <v>1344</v>
+        <v>1351</v>
       </c>
       <c r="F68" t="s">
-        <v>1487</v>
+        <v>1494</v>
       </c>
       <c r="G68" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="J68" t="s">
         <v>22</v>
@@ -20487,16 +20585,16 @@
         <v>33</v>
       </c>
       <c r="N68" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O68" t="s">
-        <v>1488</v>
+        <v>1495</v>
       </c>
       <c r="P68" t="s">
-        <v>1489</v>
+        <v>1496</v>
       </c>
       <c r="Q68" t="s">
-        <v>1490</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
@@ -20510,16 +20608,16 @@
         <v>40</v>
       </c>
       <c r="D69" t="s">
-        <v>1193</v>
+        <v>1200</v>
       </c>
       <c r="E69" t="s">
-        <v>1188</v>
+        <v>1195</v>
       </c>
       <c r="F69" t="s">
-        <v>1491</v>
+        <v>1498</v>
       </c>
       <c r="G69" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="H69">
         <v>184200</v>
@@ -20540,16 +20638,16 @@
         <v>33</v>
       </c>
       <c r="N69" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O69" t="s">
-        <v>1492</v>
+        <v>1499</v>
       </c>
       <c r="P69" t="s">
-        <v>1493</v>
+        <v>1500</v>
       </c>
       <c r="Q69" t="s">
-        <v>1494</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
@@ -20563,16 +20661,16 @@
         <v>30</v>
       </c>
       <c r="D70" t="s">
-        <v>1495</v>
+        <v>1502</v>
       </c>
       <c r="E70" t="s">
-        <v>1188</v>
+        <v>1195</v>
       </c>
       <c r="F70" t="s">
-        <v>1496</v>
+        <v>1503</v>
       </c>
       <c r="G70" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="H70">
         <v>200000</v>
@@ -20593,16 +20691,16 @@
         <v>25</v>
       </c>
       <c r="N70" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O70" t="s">
-        <v>1497</v>
+        <v>1504</v>
       </c>
       <c r="P70" t="s">
-        <v>1498</v>
+        <v>1505</v>
       </c>
       <c r="Q70" t="s">
-        <v>1499</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
@@ -20616,7 +20714,7 @@
         <v>30</v>
       </c>
       <c r="D71" t="s">
-        <v>1500</v>
+        <v>1507</v>
       </c>
       <c r="E71" t="s">
         <v>1066</v>
@@ -20625,7 +20723,7 @@
         <v>1075</v>
       </c>
       <c r="G71" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="J71" t="s">
         <v>22</v>
@@ -20640,16 +20738,16 @@
         <v>25</v>
       </c>
       <c r="N71" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O71" t="s">
-        <v>1501</v>
+        <v>1508</v>
       </c>
       <c r="P71" t="s">
-        <v>1502</v>
+        <v>1509</v>
       </c>
       <c r="Q71" t="s">
-        <v>1503</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
@@ -20663,16 +20761,16 @@
         <v>32</v>
       </c>
       <c r="D72" t="s">
-        <v>1504</v>
+        <v>1511</v>
       </c>
       <c r="E72" t="s">
         <v>1066</v>
       </c>
       <c r="F72" t="s">
-        <v>1358</v>
+        <v>1365</v>
       </c>
       <c r="G72" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="J72" t="s">
         <v>22</v>
@@ -20687,16 +20785,16 @@
         <v>25</v>
       </c>
       <c r="N72" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O72" t="s">
-        <v>1505</v>
+        <v>1512</v>
       </c>
       <c r="P72" t="s">
-        <v>1506</v>
+        <v>1513</v>
       </c>
       <c r="Q72" t="s">
-        <v>1507</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
@@ -20710,7 +20808,7 @@
         <v>32</v>
       </c>
       <c r="D73" t="s">
-        <v>1508</v>
+        <v>1515</v>
       </c>
       <c r="E73" t="s">
         <v>1066</v>
@@ -20719,7 +20817,7 @@
         <v>1075</v>
       </c>
       <c r="G73" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="J73" t="s">
         <v>22</v>
@@ -20734,16 +20832,16 @@
         <v>25</v>
       </c>
       <c r="N73" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O73" t="s">
-        <v>1509</v>
+        <v>1516</v>
       </c>
       <c r="P73" t="s">
-        <v>1510</v>
+        <v>1517</v>
       </c>
       <c r="Q73" t="s">
-        <v>1511</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
@@ -20757,16 +20855,16 @@
         <v>45</v>
       </c>
       <c r="D74" t="s">
-        <v>1512</v>
+        <v>1519</v>
       </c>
       <c r="E74" t="s">
         <v>90</v>
       </c>
       <c r="F74" t="s">
-        <v>1203</v>
+        <v>1210</v>
       </c>
       <c r="G74" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="J74" t="s">
         <v>22</v>
@@ -20781,16 +20879,16 @@
         <v>33</v>
       </c>
       <c r="N74" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O74" t="s">
-        <v>1513</v>
+        <v>1520</v>
       </c>
       <c r="P74" t="s">
-        <v>1514</v>
+        <v>1521</v>
       </c>
       <c r="Q74" t="s">
-        <v>1515</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
@@ -20804,16 +20902,16 @@
         <v>35</v>
       </c>
       <c r="D75" t="s">
-        <v>1516</v>
+        <v>1523</v>
       </c>
       <c r="E75" t="s">
         <v>90</v>
       </c>
       <c r="F75" t="s">
-        <v>1517</v>
+        <v>1524</v>
       </c>
       <c r="G75" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="J75" t="s">
         <v>22</v>
@@ -20828,16 +20926,16 @@
         <v>25</v>
       </c>
       <c r="N75" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O75" t="s">
-        <v>1518</v>
+        <v>1525</v>
       </c>
       <c r="P75" t="s">
-        <v>1519</v>
+        <v>1526</v>
       </c>
       <c r="Q75" t="s">
-        <v>1520</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
@@ -20851,7 +20949,7 @@
         <v>35</v>
       </c>
       <c r="D76" t="s">
-        <v>1521</v>
+        <v>1528</v>
       </c>
       <c r="E76" t="s">
         <v>90</v>
@@ -20860,7 +20958,7 @@
         <v>152</v>
       </c>
       <c r="G76" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="J76" t="s">
         <v>22</v>
@@ -20875,16 +20973,16 @@
         <v>25</v>
       </c>
       <c r="N76" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O76" t="s">
-        <v>1522</v>
+        <v>1529</v>
       </c>
       <c r="P76" t="s">
-        <v>1523</v>
+        <v>1530</v>
       </c>
       <c r="Q76" t="s">
-        <v>1524</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
@@ -20898,16 +20996,16 @@
         <v>15</v>
       </c>
       <c r="D77" t="s">
-        <v>1525</v>
+        <v>1532</v>
       </c>
       <c r="E77" t="s">
         <v>90</v>
       </c>
       <c r="F77" t="s">
-        <v>1526</v>
+        <v>1533</v>
       </c>
       <c r="G77" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="J77" t="s">
         <v>22</v>
@@ -20922,16 +21020,16 @@
         <v>25</v>
       </c>
       <c r="N77" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O77" t="s">
-        <v>1527</v>
+        <v>1534</v>
       </c>
       <c r="P77" t="s">
-        <v>1528</v>
+        <v>1535</v>
       </c>
       <c r="Q77" t="s">
-        <v>1529</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
@@ -20945,16 +21043,16 @@
         <v>25</v>
       </c>
       <c r="D78" t="s">
-        <v>1530</v>
+        <v>1537</v>
       </c>
       <c r="E78" t="s">
         <v>90</v>
       </c>
       <c r="F78" t="s">
-        <v>1531</v>
+        <v>1538</v>
       </c>
       <c r="G78" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="J78" t="s">
         <v>22</v>
@@ -20969,16 +21067,16 @@
         <v>25</v>
       </c>
       <c r="N78" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O78" t="s">
-        <v>1532</v>
+        <v>1539</v>
       </c>
       <c r="P78" t="s">
-        <v>1533</v>
+        <v>1540</v>
       </c>
       <c r="Q78" t="s">
-        <v>1534</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
@@ -20992,16 +21090,16 @@
         <v>30</v>
       </c>
       <c r="D79" t="s">
-        <v>1535</v>
+        <v>1542</v>
       </c>
       <c r="E79" t="s">
         <v>90</v>
       </c>
       <c r="F79" t="s">
-        <v>1536</v>
+        <v>1543</v>
       </c>
       <c r="G79" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="J79" t="s">
         <v>22</v>
@@ -21016,16 +21114,16 @@
         <v>25</v>
       </c>
       <c r="N79" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O79" t="s">
-        <v>1537</v>
+        <v>1544</v>
       </c>
       <c r="P79" t="s">
-        <v>1538</v>
+        <v>1545</v>
       </c>
       <c r="Q79" t="s">
-        <v>1539</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
@@ -21045,10 +21143,10 @@
         <v>117</v>
       </c>
       <c r="F80" t="s">
-        <v>1496</v>
+        <v>1503</v>
       </c>
       <c r="G80" t="s">
-        <v>1198</v>
+        <v>1205</v>
       </c>
       <c r="J80" t="s">
         <v>22</v>
@@ -21063,16 +21161,16 @@
         <v>25</v>
       </c>
       <c r="N80" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O80" t="s">
-        <v>1540</v>
+        <v>1547</v>
       </c>
       <c r="P80" t="s">
-        <v>1541</v>
+        <v>1548</v>
       </c>
       <c r="Q80" t="s">
-        <v>1542</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
@@ -21092,10 +21190,10 @@
         <v>117</v>
       </c>
       <c r="F81" t="s">
-        <v>1543</v>
+        <v>1550</v>
       </c>
       <c r="G81" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="J81" t="s">
         <v>22</v>
@@ -21110,16 +21208,16 @@
         <v>33</v>
       </c>
       <c r="N81" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O81" t="s">
-        <v>1544</v>
+        <v>1551</v>
       </c>
       <c r="P81" t="s">
-        <v>1545</v>
+        <v>1552</v>
       </c>
       <c r="Q81" t="s">
-        <v>1546</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
@@ -21142,7 +21240,7 @@
         <v>1132</v>
       </c>
       <c r="G82" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="H82">
         <v>180000</v>
@@ -21163,16 +21261,16 @@
         <v>25</v>
       </c>
       <c r="N82" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O82" t="s">
-        <v>1547</v>
+        <v>1554</v>
       </c>
       <c r="P82" t="s">
-        <v>1548</v>
+        <v>1555</v>
       </c>
       <c r="Q82" t="s">
-        <v>1549</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
@@ -21192,10 +21290,10 @@
         <v>117</v>
       </c>
       <c r="F83" t="s">
-        <v>1550</v>
+        <v>1557</v>
       </c>
       <c r="G83" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="H83">
         <v>180000</v>
@@ -21216,16 +21314,16 @@
         <v>25</v>
       </c>
       <c r="N83" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O83" t="s">
-        <v>1551</v>
+        <v>1558</v>
       </c>
       <c r="P83" t="s">
-        <v>1552</v>
+        <v>1559</v>
       </c>
       <c r="Q83" t="s">
-        <v>1553</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
@@ -21239,16 +21337,16 @@
         <v>20</v>
       </c>
       <c r="D84" t="s">
-        <v>1554</v>
+        <v>1561</v>
       </c>
       <c r="E84" t="s">
-        <v>1555</v>
+        <v>1177</v>
       </c>
       <c r="F84" t="s">
-        <v>1556</v>
+        <v>1562</v>
       </c>
       <c r="G84" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="J84" t="s">
         <v>22</v>
@@ -21263,16 +21361,16 @@
         <v>25</v>
       </c>
       <c r="N84" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O84" t="s">
-        <v>1557</v>
+        <v>1563</v>
       </c>
       <c r="P84" t="s">
-        <v>1558</v>
+        <v>1564</v>
       </c>
       <c r="Q84" t="s">
-        <v>1559</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
@@ -21286,16 +21384,16 @@
         <v>50</v>
       </c>
       <c r="D85" t="s">
-        <v>1560</v>
+        <v>1566</v>
       </c>
       <c r="E85" t="s">
-        <v>1555</v>
+        <v>1177</v>
       </c>
       <c r="F85" t="s">
         <v>20</v>
       </c>
       <c r="G85" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="H85">
         <v>250000</v>
@@ -21316,16 +21414,16 @@
         <v>33</v>
       </c>
       <c r="N85" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O85" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="P85" t="s">
-        <v>1562</v>
+        <v>1568</v>
       </c>
       <c r="Q85" t="s">
-        <v>1563</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
@@ -21339,16 +21437,16 @@
         <v>55</v>
       </c>
       <c r="D86" t="s">
-        <v>1564</v>
+        <v>1570</v>
       </c>
       <c r="E86" t="s">
-        <v>1555</v>
+        <v>1177</v>
       </c>
       <c r="F86" t="s">
         <v>20</v>
       </c>
       <c r="G86" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="H86">
         <v>200000</v>
@@ -21369,16 +21467,16 @@
         <v>33</v>
       </c>
       <c r="N86" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O86" t="s">
-        <v>1565</v>
+        <v>1571</v>
       </c>
       <c r="P86" t="s">
-        <v>1566</v>
+        <v>1572</v>
       </c>
       <c r="Q86" t="s">
-        <v>1567</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
@@ -21392,16 +21490,16 @@
         <v>52</v>
       </c>
       <c r="D87" t="s">
-        <v>1568</v>
+        <v>1574</v>
       </c>
       <c r="E87" t="s">
-        <v>1555</v>
+        <v>1177</v>
       </c>
       <c r="F87" t="s">
         <v>20</v>
       </c>
       <c r="G87" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="H87">
         <v>250000</v>
@@ -21422,16 +21520,16 @@
         <v>33</v>
       </c>
       <c r="N87" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O87" t="s">
-        <v>1569</v>
+        <v>1575</v>
       </c>
       <c r="P87" t="s">
-        <v>1570</v>
+        <v>1576</v>
       </c>
       <c r="Q87" t="s">
-        <v>1571</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
@@ -21445,16 +21543,16 @@
         <v>53</v>
       </c>
       <c r="D88" t="s">
-        <v>1572</v>
+        <v>1578</v>
       </c>
       <c r="E88" t="s">
-        <v>1555</v>
+        <v>1177</v>
       </c>
       <c r="F88" t="s">
         <v>20</v>
       </c>
       <c r="G88" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="H88">
         <v>200000</v>
@@ -21475,16 +21573,16 @@
         <v>33</v>
       </c>
       <c r="N88" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O88" t="s">
-        <v>1573</v>
+        <v>1579</v>
       </c>
       <c r="P88" t="s">
-        <v>1574</v>
+        <v>1580</v>
       </c>
       <c r="Q88" t="s">
-        <v>1575</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
@@ -21498,16 +21596,16 @@
         <v>50</v>
       </c>
       <c r="D89" t="s">
-        <v>1576</v>
+        <v>1582</v>
       </c>
       <c r="E89" t="s">
-        <v>1555</v>
+        <v>1177</v>
       </c>
       <c r="F89" t="s">
         <v>20</v>
       </c>
       <c r="G89" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="H89">
         <v>200000</v>
@@ -21528,16 +21626,16 @@
         <v>33</v>
       </c>
       <c r="N89" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O89" t="s">
-        <v>1577</v>
+        <v>1583</v>
       </c>
       <c r="P89" t="s">
-        <v>1578</v>
+        <v>1584</v>
       </c>
       <c r="Q89" t="s">
-        <v>1579</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
@@ -21551,16 +21649,16 @@
         <v>55</v>
       </c>
       <c r="D90" t="s">
-        <v>1580</v>
+        <v>1586</v>
       </c>
       <c r="E90" t="s">
-        <v>1555</v>
+        <v>1177</v>
       </c>
       <c r="F90" t="s">
         <v>20</v>
       </c>
       <c r="G90" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="H90">
         <v>250000</v>
@@ -21581,16 +21679,16 @@
         <v>33</v>
       </c>
       <c r="N90" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O90" t="s">
-        <v>1581</v>
+        <v>1587</v>
       </c>
       <c r="P90" t="s">
-        <v>1582</v>
+        <v>1588</v>
       </c>
       <c r="Q90" t="s">
-        <v>1583</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
@@ -21604,16 +21702,16 @@
         <v>45</v>
       </c>
       <c r="D91" t="s">
-        <v>1584</v>
+        <v>1590</v>
       </c>
       <c r="E91" t="s">
-        <v>1585</v>
+        <v>1591</v>
       </c>
       <c r="F91" t="s">
-        <v>1586</v>
+        <v>1592</v>
       </c>
       <c r="G91" t="s">
-        <v>1198</v>
+        <v>1205</v>
       </c>
       <c r="H91">
         <v>154000</v>
@@ -21634,16 +21732,169 @@
         <v>25</v>
       </c>
       <c r="N91" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="O91" t="s">
-        <v>1587</v>
+        <v>1593</v>
       </c>
       <c r="P91" t="s">
-        <v>1588</v>
+        <v>1594</v>
       </c>
       <c r="Q91" t="s">
-        <v>1589</v>
+        <v>1595</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>17</v>
+      </c>
+      <c r="B92">
+        <v>45</v>
+      </c>
+      <c r="C92">
+        <v>42</v>
+      </c>
+      <c r="D92" t="s">
+        <v>30</v>
+      </c>
+      <c r="E92" t="s">
+        <v>117</v>
+      </c>
+      <c r="F92" t="s">
+        <v>818</v>
+      </c>
+      <c r="G92" t="s">
+        <v>1184</v>
+      </c>
+      <c r="H92">
+        <v>180000</v>
+      </c>
+      <c r="I92">
+        <v>180000</v>
+      </c>
+      <c r="J92" t="s">
+        <v>44</v>
+      </c>
+      <c r="K92" t="s">
+        <v>92</v>
+      </c>
+      <c r="L92" t="s">
+        <v>1179</v>
+      </c>
+      <c r="M92" t="s">
+        <v>33</v>
+      </c>
+      <c r="N92" t="s">
+        <v>1185</v>
+      </c>
+      <c r="O92" t="s">
+        <v>1596</v>
+      </c>
+      <c r="P92" t="s">
+        <v>1597</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>17</v>
+      </c>
+      <c r="B93">
+        <v>40</v>
+      </c>
+      <c r="C93">
+        <v>38</v>
+      </c>
+      <c r="D93" t="s">
+        <v>373</v>
+      </c>
+      <c r="E93" t="s">
+        <v>117</v>
+      </c>
+      <c r="F93" t="s">
+        <v>1453</v>
+      </c>
+      <c r="G93" t="s">
+        <v>1184</v>
+      </c>
+      <c r="H93">
+        <v>219100</v>
+      </c>
+      <c r="I93">
+        <v>219100</v>
+      </c>
+      <c r="J93" t="s">
+        <v>44</v>
+      </c>
+      <c r="K93" t="s">
+        <v>92</v>
+      </c>
+      <c r="L93" t="s">
+        <v>1179</v>
+      </c>
+      <c r="M93" t="s">
+        <v>25</v>
+      </c>
+      <c r="N93" t="s">
+        <v>1185</v>
+      </c>
+      <c r="O93" t="s">
+        <v>1599</v>
+      </c>
+      <c r="P93" t="s">
+        <v>1600</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>1601</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>17</v>
+      </c>
+      <c r="B94">
+        <v>20</v>
+      </c>
+      <c r="C94">
+        <v>25</v>
+      </c>
+      <c r="D94" t="s">
+        <v>1602</v>
+      </c>
+      <c r="E94" t="s">
+        <v>117</v>
+      </c>
+      <c r="F94" t="s">
+        <v>1603</v>
+      </c>
+      <c r="G94" t="s">
+        <v>1184</v>
+      </c>
+      <c r="J94" t="s">
+        <v>22</v>
+      </c>
+      <c r="K94" t="s">
+        <v>218</v>
+      </c>
+      <c r="L94" t="s">
+        <v>1179</v>
+      </c>
+      <c r="M94" t="s">
+        <v>25</v>
+      </c>
+      <c r="N94" t="s">
+        <v>1185</v>
+      </c>
+      <c r="O94" t="s">
+        <v>1604</v>
+      </c>
+      <c r="P94" t="s">
+        <v>1605</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>1606</v>
       </c>
     </row>
   </sheetData>

--- a/hunt/board.xlsx
+++ b/hunt/board.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4194" uniqueCount="1560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4324" uniqueCount="1607">
   <si>
     <t>Column</t>
   </si>
@@ -3422,6 +3422,84 @@
     <t>https://www.arbeitnow.com/jobs/companies/trusteq-gmbh/cloud-senior-engineer-architect-m-w-d-koln-293569</t>
   </si>
   <si>
+    <t>2026-08-30T03:05:52.684Z</t>
+  </si>
+  <si>
+    <t>Direct title match: Cloud Solutions Architect, 100% remote US, W2 full-time | Scope covers compute, networking, data, identity, security governance on a major cloud — aligns with candidate's Azure Policy/CAF/WAF, Entra ID, Key Vault, Defender for Cloud experience | Salary top of band ($190K) clears the $180K floor</t>
+  </si>
+  <si>
+    <t>Posting states 13+ years experience required; candidate has ~10, a hard gap on the stated minimum | Bottom of range ($140K) is well below the $180K floor, so offer risk is real | Staffing/consulting shop — engagement quality and cloud platform (may be AWS-primary) unspecified</t>
+  </si>
+  <si>
+    <t>https://himalayas.app/companies/bright-vision-technologies/jobs/cloud-solutions-architect-4970300016</t>
+  </si>
+  <si>
+    <t>Stripe</t>
+  </si>
+  <si>
+    <t>Customer-facing trusted-advisor pre-sales model mirrors candidate's Customer Engineer engagement style with enterprise stakeholders | Fintech/payments domain is adjacent to candidate's PCI/SOX compliance-driven architecture work | Remote US role at a top-tier employer with strong comp norms</t>
+  </si>
+  <si>
+    <t>Role centers on Stripe API/payments platform and financial services product depth, not Azure/DevOps governance — candidate's core stack is not credited here | Heavy pre-sales, deal-cycle orientation with C-level finance audiences; candidate has no payments-platform implementation track record | No cloud-infrastructure architecture component to leverage AZ-104/GHAS/pipeline expertise</t>
+  </si>
+  <si>
+    <t>https://himalayas.app/companies/stripe/jobs/solutions-architect-platforms-presales</t>
+  </si>
+  <si>
+    <t>Principal Cloud Infrastructure Architect</t>
+  </si>
+  <si>
+    <t>Empower Pharmacy</t>
+  </si>
+  <si>
+    <t>Principal-level cloud infrastructure architecture — exactly the scope tier the candidate is targeting | Healthcare/pharma employer means HIPAA and FDA-regulated compliance architecture, a direct precedent match to candidate's HIPAA/NIST/FIPS work | Houston-based company (candidate is in Humble, TX) posted as remote — low friction on location and possible onsite optionality</t>
+  </si>
+  <si>
+    <t>Principal infrastructure architect roles often expect deep networking/datacenter/hybrid depth and 12+ years; candidate is ~10 years and more DevOps/governance-weighted | No salary posted; principal titles at a private pharma may still land below the $180K floor | AZ-305/AZ-400 still in progress — architect-expert cert may be an expectation at principal level</t>
+  </si>
+  <si>
+    <t>https://himalayas.app/companies/empower-pharmacy/jobs/principal-cloud-infrastructure-architect</t>
+  </si>
+  <si>
+    <t>Salesforce Solution Architect, Sales Cloud</t>
+  </si>
+  <si>
+    <t>Remote US consulting-delivery architecture role with a very wide posted band topping at $266K | Customer-facing solution architecture engagement model overlaps with candidate's advisory experience</t>
+  </si>
+  <si>
+    <t>Requires deep Salesforce Sales Cloud / Agentforce / Einstein platform expertise which the candidate does not have at all | AWS + Salesforce ecosystem focus; no Azure, DevOps, or GHAS relevance | Band starts at $87.4K — realistic offer for a non-Salesforce-certified candidate would be far below the $180K floor</t>
+  </si>
+  <si>
+    <t>https://himalayas.app/companies/neuraflash/jobs/salesforce-solution-architect-sales-cloud-3771104363</t>
+  </si>
+  <si>
+    <t>Senior Native Cloud Architect</t>
+  </si>
+  <si>
+    <t>Pure Storage</t>
+  </si>
+  <si>
+    <t>Remote senior architect role with high-impact technical advisory framing inside Portworx Professional Services | Enterprise customer advisory delivery model matches candidate's trusted-advisor engagement background</t>
+  </si>
+  <si>
+    <t>Core requirement is deep Kubernetes and container storage (Portworx, CSI, stateful workloads) — not a demonstrated strength on the candidate's profile | Multi-cloud/cloud-native infrastructure depth expected, with no credit for Azure DevOps/GitHub governance specialization | No salary posted and professional-services roles here may include travel expectations</t>
+  </si>
+  <si>
+    <t>https://himalayas.app/companies/pure-storage/jobs/senior-native-cloud-architect</t>
+  </si>
+  <si>
+    <t>Specialist Solutions Architect, Tax</t>
+  </si>
+  <si>
+    <t>Remote-eligible with Chicago/Atlanta options at a top-tier employer | Specialist advisory role aligned to specific solution offerings — similar consultative pattern to candidate's Customer Engineer work</t>
+  </si>
+  <si>
+    <t>Requires deep tax/indirect-tax domain expertise and Stripe Tax product knowledge, which the candidate has none of | No cloud infrastructure, DevOps, or security architecture component to leverage | Pre-sales specialist role tied to product sellers and deal cycles, far from principal cloud architect scope</t>
+  </si>
+  <si>
+    <t>https://stripe.com/jobs/search?gh_jid=8090244</t>
+  </si>
+  <si>
     <t>Principal AI Ecosystem Architect - OpenAI/Anthropic</t>
   </si>
   <si>
@@ -4692,6 +4770,69 @@
   </si>
   <si>
     <t>https://www.arbeitnow.com/jobs/companies/isaraerospace/senior-plm-architect-ottobrunn-bavaria-457909</t>
+  </si>
+  <si>
+    <t>Solutions Architect - Financial Services (Professional Services)</t>
+  </si>
+  <si>
+    <t>Illinois; Massachusetts; New Jersey; New York; Washington, D.C.</t>
+  </si>
+  <si>
+    <t>Financial services vertical is a strong precedent match for candidate's PCI/SOX compliance-driven architecture work | Customer-facing trusted-advisor architecture role with implementation guidance — delivery/advisory rather than pure quota carrying | Confirmed $180K figure meets the salary floor exactly</t>
+  </si>
+  <si>
+    <t>Requires data engineering / Spark / Delta Lake / ML platform depth the candidate does not list | Location-restricted to IL/MA/NJ/NY/DC — not remote-friendly for a Humble, TX candidate | Databricks platform expertise is the central hiring bar; Azure DevOps/GHAS skills only tangentially relevant</t>
+  </si>
+  <si>
+    <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8502991002</t>
+  </si>
+  <si>
+    <t>Senior Solutions Architect (NATO)</t>
+  </si>
+  <si>
+    <t>Belgium</t>
+  </si>
+  <si>
+    <t>Senior Solutions Architect scope with enterprise technical advisory responsibilities the candidate performs today | Search/observability/security platform work touches candidate's security tooling familiarity</t>
+  </si>
+  <si>
+    <t>Based in Belgium supporting NATO — almost certainly requires EU work authorization and NATO security clearance, which the candidate does not hold | Elastic Stack (Elasticsearch, Kibana, ELK) depth is the core requirement, not Azure DevOps/GitHub | Outside candidate's stated US market scope</t>
+  </si>
+  <si>
+    <t>https://jobs.elastic.co/jobs?gh_jid=7349982&amp;gh_jid=7349982</t>
+  </si>
+  <si>
+    <t>Applied AI Architect, Digital Natives Business</t>
+  </si>
+  <si>
+    <t>anthropic</t>
+  </si>
+  <si>
+    <t>Pre-sales trusted technical advisor model for large enterprises directly mirrors the candidate's current Customer Engineer engagement style | Anthropic is a premium employer and the role emphasizes architecting integrations into customer technology stacks</t>
+  </si>
+  <si>
+    <t>Munich-based hybrid role requiring German work authorization — outside the candidate's US market scope | Requires LLM/AI solution architecture depth (prompting, agents, model deployment) which the candidate has only touched via Copilot licensing, not deep implementation | Digital-natives segment expects startup-style API engineering fluency (Python-heavy) beyond candidate's demonstrated depth</t>
+  </si>
+  <si>
+    <t>https://www.arbeitnow.com/jobs/companies/anthropic/applied-ai-architect-digital-natives-business-munich-42292</t>
+  </si>
+  <si>
+    <t>Senior ABAP Developer / Architect Produktentwicklung  (m/w/d)</t>
+  </si>
+  <si>
+    <t>cbs Corporate Business Solutions GmbH</t>
+  </si>
+  <si>
+    <t>Heidelberg, Baden-Württemberg, Deutschland</t>
+  </si>
+  <si>
+    <t>Senior architect-level product development scope with enterprise transformation context</t>
+  </si>
+  <si>
+    <t>Requires senior SAP ABAP development expertise — completely outside the candidate's skill set | German-language posting in Heidelberg requiring German work authorization and likely fluency | No cloud, DevOps, or advisory overlap whatsoever with the candidate's profile</t>
+  </si>
+  <si>
+    <t>https://www.arbeitnow.com/jobs/companies/cbs-corporate-business-solutions-gmbh/senior-abap-developer-architect-produktentwicklung-heidelberg-178660</t>
   </si>
 </sst>
 </file>
@@ -5072,7 +5213,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q228"/>
+  <dimension ref="A1:Q234"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -16519,6 +16660,300 @@
         <v>1135</v>
       </c>
     </row>
+    <row r="229" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>17</v>
+      </c>
+      <c r="B229">
+        <v>60</v>
+      </c>
+      <c r="C229">
+        <v>58</v>
+      </c>
+      <c r="D229" t="s">
+        <v>18</v>
+      </c>
+      <c r="E229" t="s">
+        <v>19</v>
+      </c>
+      <c r="F229" t="s">
+        <v>20</v>
+      </c>
+      <c r="G229" t="s">
+        <v>21</v>
+      </c>
+      <c r="H229">
+        <v>140000</v>
+      </c>
+      <c r="I229">
+        <v>190000</v>
+      </c>
+      <c r="J229" t="s">
+        <v>22</v>
+      </c>
+      <c r="K229" t="s">
+        <v>23</v>
+      </c>
+      <c r="L229" t="s">
+        <v>1136</v>
+      </c>
+      <c r="M229" t="s">
+        <v>39</v>
+      </c>
+      <c r="N229" t="s">
+        <v>26</v>
+      </c>
+      <c r="O229" t="s">
+        <v>1137</v>
+      </c>
+      <c r="P229" t="s">
+        <v>1138</v>
+      </c>
+      <c r="Q229" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="230" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>17</v>
+      </c>
+      <c r="B230">
+        <v>55</v>
+      </c>
+      <c r="C230">
+        <v>45</v>
+      </c>
+      <c r="D230" t="s">
+        <v>803</v>
+      </c>
+      <c r="E230" t="s">
+        <v>1140</v>
+      </c>
+      <c r="F230" t="s">
+        <v>20</v>
+      </c>
+      <c r="G230" t="s">
+        <v>21</v>
+      </c>
+      <c r="J230" t="s">
+        <v>32</v>
+      </c>
+      <c r="K230" t="s">
+        <v>23</v>
+      </c>
+      <c r="L230" t="s">
+        <v>1136</v>
+      </c>
+      <c r="M230" t="s">
+        <v>39</v>
+      </c>
+      <c r="N230" t="s">
+        <v>26</v>
+      </c>
+      <c r="O230" t="s">
+        <v>1141</v>
+      </c>
+      <c r="P230" t="s">
+        <v>1142</v>
+      </c>
+      <c r="Q230" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="231" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>17</v>
+      </c>
+      <c r="B231">
+        <v>82</v>
+      </c>
+      <c r="C231">
+        <v>72</v>
+      </c>
+      <c r="D231" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E231" t="s">
+        <v>1145</v>
+      </c>
+      <c r="F231" t="s">
+        <v>20</v>
+      </c>
+      <c r="G231" t="s">
+        <v>21</v>
+      </c>
+      <c r="J231" t="s">
+        <v>32</v>
+      </c>
+      <c r="K231" t="s">
+        <v>23</v>
+      </c>
+      <c r="L231" t="s">
+        <v>1136</v>
+      </c>
+      <c r="M231" t="s">
+        <v>25</v>
+      </c>
+      <c r="N231" t="s">
+        <v>26</v>
+      </c>
+      <c r="O231" t="s">
+        <v>1146</v>
+      </c>
+      <c r="P231" t="s">
+        <v>1147</v>
+      </c>
+      <c r="Q231" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="232" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>17</v>
+      </c>
+      <c r="B232">
+        <v>25</v>
+      </c>
+      <c r="C232">
+        <v>18</v>
+      </c>
+      <c r="D232" t="s">
+        <v>1149</v>
+      </c>
+      <c r="E232" t="s">
+        <v>409</v>
+      </c>
+      <c r="F232" t="s">
+        <v>20</v>
+      </c>
+      <c r="G232" t="s">
+        <v>21</v>
+      </c>
+      <c r="H232">
+        <v>87400</v>
+      </c>
+      <c r="I232">
+        <v>266300</v>
+      </c>
+      <c r="J232" t="s">
+        <v>22</v>
+      </c>
+      <c r="K232" t="s">
+        <v>23</v>
+      </c>
+      <c r="L232" t="s">
+        <v>1136</v>
+      </c>
+      <c r="M232" t="s">
+        <v>33</v>
+      </c>
+      <c r="N232" t="s">
+        <v>26</v>
+      </c>
+      <c r="O232" t="s">
+        <v>1150</v>
+      </c>
+      <c r="P232" t="s">
+        <v>1151</v>
+      </c>
+      <c r="Q232" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="233" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>17</v>
+      </c>
+      <c r="B233">
+        <v>48</v>
+      </c>
+      <c r="C233">
+        <v>38</v>
+      </c>
+      <c r="D233" t="s">
+        <v>1153</v>
+      </c>
+      <c r="E233" t="s">
+        <v>1154</v>
+      </c>
+      <c r="F233" t="s">
+        <v>20</v>
+      </c>
+      <c r="G233" t="s">
+        <v>21</v>
+      </c>
+      <c r="J233" t="s">
+        <v>32</v>
+      </c>
+      <c r="K233" t="s">
+        <v>23</v>
+      </c>
+      <c r="L233" t="s">
+        <v>1136</v>
+      </c>
+      <c r="M233" t="s">
+        <v>33</v>
+      </c>
+      <c r="N233" t="s">
+        <v>26</v>
+      </c>
+      <c r="O233" t="s">
+        <v>1155</v>
+      </c>
+      <c r="P233" t="s">
+        <v>1156</v>
+      </c>
+      <c r="Q233" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="234" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>17</v>
+      </c>
+      <c r="B234">
+        <v>42</v>
+      </c>
+      <c r="C234">
+        <v>30</v>
+      </c>
+      <c r="D234" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E234" t="s">
+        <v>798</v>
+      </c>
+      <c r="F234" t="s">
+        <v>799</v>
+      </c>
+      <c r="G234" t="s">
+        <v>21</v>
+      </c>
+      <c r="J234" t="s">
+        <v>32</v>
+      </c>
+      <c r="K234" t="s">
+        <v>51</v>
+      </c>
+      <c r="L234" t="s">
+        <v>1136</v>
+      </c>
+      <c r="M234" t="s">
+        <v>33</v>
+      </c>
+      <c r="N234" t="s">
+        <v>26</v>
+      </c>
+      <c r="O234" t="s">
+        <v>1159</v>
+      </c>
+      <c r="P234" t="s">
+        <v>1160</v>
+      </c>
+      <c r="Q234" t="s">
+        <v>1161</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:Q1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16528,7 +16963,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q94"/>
+  <dimension ref="A1:Q98"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -16609,16 +17044,16 @@
         <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>1136</v>
+        <v>1162</v>
       </c>
       <c r="E2" t="s">
-        <v>1137</v>
+        <v>1163</v>
       </c>
       <c r="F2" t="s">
         <v>1023</v>
       </c>
       <c r="G2" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="H2">
         <v>184200</v>
@@ -16639,16 +17074,16 @@
         <v>33</v>
       </c>
       <c r="N2" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O2" t="s">
-        <v>1140</v>
+        <v>1166</v>
       </c>
       <c r="P2" t="s">
-        <v>1141</v>
+        <v>1167</v>
       </c>
       <c r="Q2" t="s">
-        <v>1142</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -16668,10 +17103,10 @@
         <v>1008</v>
       </c>
       <c r="F3" t="s">
-        <v>1143</v>
+        <v>1169</v>
       </c>
       <c r="G3" t="s">
-        <v>1144</v>
+        <v>1170</v>
       </c>
       <c r="J3" t="s">
         <v>32</v>
@@ -16686,16 +17121,16 @@
         <v>33</v>
       </c>
       <c r="N3" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O3" t="s">
-        <v>1145</v>
+        <v>1171</v>
       </c>
       <c r="P3" t="s">
-        <v>1146</v>
+        <v>1172</v>
       </c>
       <c r="Q3" t="s">
-        <v>1147</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
@@ -16709,16 +17144,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>1148</v>
+        <v>1174</v>
       </c>
       <c r="E4" t="s">
         <v>798</v>
       </c>
       <c r="F4" t="s">
-        <v>1149</v>
+        <v>1175</v>
       </c>
       <c r="G4" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="J4" t="s">
         <v>32</v>
@@ -16733,16 +17168,16 @@
         <v>33</v>
       </c>
       <c r="N4" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O4" t="s">
-        <v>1150</v>
+        <v>1176</v>
       </c>
       <c r="P4" t="s">
-        <v>1151</v>
+        <v>1177</v>
       </c>
       <c r="Q4" t="s">
-        <v>1152</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -16756,16 +17191,16 @@
         <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>1153</v>
+        <v>1179</v>
       </c>
       <c r="E5" t="s">
         <v>798</v>
       </c>
       <c r="F5" t="s">
-        <v>1154</v>
+        <v>1180</v>
       </c>
       <c r="G5" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="J5" t="s">
         <v>32</v>
@@ -16780,16 +17215,16 @@
         <v>33</v>
       </c>
       <c r="N5" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O5" t="s">
-        <v>1155</v>
+        <v>1181</v>
       </c>
       <c r="P5" t="s">
-        <v>1156</v>
+        <v>1182</v>
       </c>
       <c r="Q5" t="s">
-        <v>1157</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -16803,16 +17238,16 @@
         <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>1158</v>
+        <v>1184</v>
       </c>
       <c r="E6" t="s">
         <v>49</v>
       </c>
       <c r="F6" t="s">
-        <v>1143</v>
+        <v>1169</v>
       </c>
       <c r="G6" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="J6" t="s">
         <v>32</v>
@@ -16827,16 +17262,16 @@
         <v>39</v>
       </c>
       <c r="N6" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O6" t="s">
-        <v>1159</v>
+        <v>1185</v>
       </c>
       <c r="P6" t="s">
-        <v>1160</v>
+        <v>1186</v>
       </c>
       <c r="Q6" t="s">
-        <v>1161</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -16850,16 +17285,16 @@
         <v>48</v>
       </c>
       <c r="D7" t="s">
-        <v>1162</v>
+        <v>1188</v>
       </c>
       <c r="E7" t="s">
-        <v>1163</v>
+        <v>1189</v>
       </c>
       <c r="F7" t="s">
-        <v>1164</v>
+        <v>1190</v>
       </c>
       <c r="G7" t="s">
-        <v>1144</v>
+        <v>1170</v>
       </c>
       <c r="J7" t="s">
         <v>32</v>
@@ -16874,16 +17309,16 @@
         <v>33</v>
       </c>
       <c r="N7" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O7" t="s">
-        <v>1165</v>
+        <v>1191</v>
       </c>
       <c r="P7" t="s">
-        <v>1166</v>
+        <v>1192</v>
       </c>
       <c r="Q7" t="s">
-        <v>1167</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -16897,16 +17332,16 @@
         <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>1168</v>
+        <v>1194</v>
       </c>
       <c r="E8" t="s">
-        <v>1169</v>
+        <v>1195</v>
       </c>
       <c r="F8" t="s">
-        <v>1170</v>
+        <v>1196</v>
       </c>
       <c r="G8" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="J8" t="s">
         <v>32</v>
@@ -16921,16 +17356,16 @@
         <v>33</v>
       </c>
       <c r="N8" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O8" t="s">
-        <v>1171</v>
+        <v>1197</v>
       </c>
       <c r="P8" t="s">
-        <v>1172</v>
+        <v>1198</v>
       </c>
       <c r="Q8" t="s">
-        <v>1173</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -16944,7 +17379,7 @@
         <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>1174</v>
+        <v>1200</v>
       </c>
       <c r="E9" t="s">
         <v>49</v>
@@ -16953,7 +17388,7 @@
         <v>20</v>
       </c>
       <c r="G9" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="H9">
         <v>217800</v>
@@ -16974,16 +17409,16 @@
         <v>39</v>
       </c>
       <c r="N9" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O9" t="s">
-        <v>1175</v>
+        <v>1201</v>
       </c>
       <c r="P9" t="s">
-        <v>1176</v>
+        <v>1202</v>
       </c>
       <c r="Q9" t="s">
-        <v>1177</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -16997,16 +17432,16 @@
         <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>1178</v>
+        <v>1204</v>
       </c>
       <c r="E10" t="s">
         <v>49</v>
       </c>
       <c r="F10" t="s">
-        <v>1179</v>
+        <v>1205</v>
       </c>
       <c r="G10" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="H10">
         <v>219100</v>
@@ -17027,16 +17462,16 @@
         <v>39</v>
       </c>
       <c r="N10" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O10" t="s">
-        <v>1180</v>
+        <v>1206</v>
       </c>
       <c r="P10" t="s">
-        <v>1181</v>
+        <v>1207</v>
       </c>
       <c r="Q10" t="s">
-        <v>1182</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -17056,10 +17491,10 @@
         <v>1008</v>
       </c>
       <c r="F11" t="s">
-        <v>1183</v>
+        <v>1209</v>
       </c>
       <c r="G11" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="J11" t="s">
         <v>32</v>
@@ -17074,16 +17509,16 @@
         <v>33</v>
       </c>
       <c r="N11" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O11" t="s">
-        <v>1184</v>
+        <v>1210</v>
       </c>
       <c r="P11" t="s">
-        <v>1185</v>
+        <v>1211</v>
       </c>
       <c r="Q11" t="s">
-        <v>1186</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -17097,16 +17532,16 @@
         <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>1187</v>
+        <v>1213</v>
       </c>
       <c r="E12" t="s">
-        <v>1188</v>
+        <v>1214</v>
       </c>
       <c r="F12" t="s">
-        <v>1189</v>
+        <v>1215</v>
       </c>
       <c r="G12" t="s">
-        <v>1144</v>
+        <v>1170</v>
       </c>
       <c r="J12" t="s">
         <v>32</v>
@@ -17121,16 +17556,16 @@
         <v>33</v>
       </c>
       <c r="N12" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O12" t="s">
-        <v>1190</v>
+        <v>1216</v>
       </c>
       <c r="P12" t="s">
-        <v>1191</v>
+        <v>1217</v>
       </c>
       <c r="Q12" t="s">
-        <v>1192</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
@@ -17144,16 +17579,16 @@
         <v>35</v>
       </c>
       <c r="D13" t="s">
-        <v>1193</v>
+        <v>1219</v>
       </c>
       <c r="E13" t="s">
-        <v>1194</v>
+        <v>1220</v>
       </c>
       <c r="F13" t="s">
-        <v>1195</v>
+        <v>1221</v>
       </c>
       <c r="G13" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="J13" t="s">
         <v>32</v>
@@ -17168,16 +17603,16 @@
         <v>33</v>
       </c>
       <c r="N13" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O13" t="s">
-        <v>1196</v>
+        <v>1222</v>
       </c>
       <c r="P13" t="s">
-        <v>1197</v>
+        <v>1223</v>
       </c>
       <c r="Q13" t="s">
-        <v>1198</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
@@ -17191,16 +17626,16 @@
         <v>55</v>
       </c>
       <c r="D14" t="s">
-        <v>1199</v>
+        <v>1225</v>
       </c>
       <c r="E14" t="s">
-        <v>1194</v>
+        <v>1220</v>
       </c>
       <c r="F14" t="s">
-        <v>1200</v>
+        <v>1226</v>
       </c>
       <c r="G14" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="J14" t="s">
         <v>32</v>
@@ -17215,16 +17650,16 @@
         <v>33</v>
       </c>
       <c r="N14" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O14" t="s">
-        <v>1201</v>
+        <v>1227</v>
       </c>
       <c r="P14" t="s">
-        <v>1202</v>
+        <v>1228</v>
       </c>
       <c r="Q14" t="s">
-        <v>1203</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -17238,16 +17673,16 @@
         <v>40</v>
       </c>
       <c r="D15" t="s">
-        <v>1204</v>
+        <v>1230</v>
       </c>
       <c r="E15" t="s">
-        <v>1194</v>
+        <v>1220</v>
       </c>
       <c r="F15" t="s">
-        <v>1195</v>
+        <v>1221</v>
       </c>
       <c r="G15" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="J15" t="s">
         <v>32</v>
@@ -17262,16 +17697,16 @@
         <v>33</v>
       </c>
       <c r="N15" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O15" t="s">
-        <v>1205</v>
+        <v>1231</v>
       </c>
       <c r="P15" t="s">
-        <v>1206</v>
+        <v>1232</v>
       </c>
       <c r="Q15" t="s">
-        <v>1207</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
@@ -17285,16 +17720,16 @@
         <v>5</v>
       </c>
       <c r="D16" t="s">
-        <v>1208</v>
+        <v>1234</v>
       </c>
       <c r="E16" t="s">
-        <v>1209</v>
+        <v>1235</v>
       </c>
       <c r="F16" t="s">
-        <v>1210</v>
+        <v>1236</v>
       </c>
       <c r="G16" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="J16" t="s">
         <v>32</v>
@@ -17309,16 +17744,16 @@
         <v>33</v>
       </c>
       <c r="N16" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O16" t="s">
-        <v>1211</v>
+        <v>1237</v>
       </c>
       <c r="P16" t="s">
-        <v>1212</v>
+        <v>1238</v>
       </c>
       <c r="Q16" t="s">
-        <v>1213</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
@@ -17332,16 +17767,16 @@
         <v>45</v>
       </c>
       <c r="D17" t="s">
-        <v>1214</v>
+        <v>1240</v>
       </c>
       <c r="E17" t="s">
-        <v>1209</v>
+        <v>1235</v>
       </c>
       <c r="F17" t="s">
-        <v>1143</v>
+        <v>1169</v>
       </c>
       <c r="G17" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="J17" t="s">
         <v>32</v>
@@ -17356,16 +17791,16 @@
         <v>33</v>
       </c>
       <c r="N17" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O17" t="s">
-        <v>1215</v>
+        <v>1241</v>
       </c>
       <c r="P17" t="s">
-        <v>1216</v>
+        <v>1242</v>
       </c>
       <c r="Q17" t="s">
-        <v>1217</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
@@ -17379,16 +17814,16 @@
         <v>5</v>
       </c>
       <c r="D18" t="s">
-        <v>1218</v>
+        <v>1244</v>
       </c>
       <c r="E18" t="s">
-        <v>1209</v>
+        <v>1235</v>
       </c>
       <c r="F18" t="s">
-        <v>1210</v>
+        <v>1236</v>
       </c>
       <c r="G18" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="J18" t="s">
         <v>32</v>
@@ -17403,16 +17838,16 @@
         <v>33</v>
       </c>
       <c r="N18" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O18" t="s">
-        <v>1219</v>
+        <v>1245</v>
       </c>
       <c r="P18" t="s">
-        <v>1220</v>
+        <v>1246</v>
       </c>
       <c r="Q18" t="s">
-        <v>1221</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -17426,16 +17861,16 @@
         <v>5</v>
       </c>
       <c r="D19" t="s">
-        <v>1222</v>
+        <v>1248</v>
       </c>
       <c r="E19" t="s">
-        <v>1209</v>
+        <v>1235</v>
       </c>
       <c r="F19" t="s">
-        <v>1210</v>
+        <v>1236</v>
       </c>
       <c r="G19" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="J19" t="s">
         <v>32</v>
@@ -17450,16 +17885,16 @@
         <v>33</v>
       </c>
       <c r="N19" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O19" t="s">
-        <v>1223</v>
+        <v>1249</v>
       </c>
       <c r="P19" t="s">
-        <v>1224</v>
+        <v>1250</v>
       </c>
       <c r="Q19" t="s">
-        <v>1225</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -17473,16 +17908,16 @@
         <v>18</v>
       </c>
       <c r="D20" t="s">
-        <v>1226</v>
+        <v>1252</v>
       </c>
       <c r="E20" t="s">
-        <v>1209</v>
+        <v>1235</v>
       </c>
       <c r="F20" t="s">
-        <v>1210</v>
+        <v>1236</v>
       </c>
       <c r="G20" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="J20" t="s">
         <v>32</v>
@@ -17497,16 +17932,16 @@
         <v>33</v>
       </c>
       <c r="N20" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O20" t="s">
-        <v>1227</v>
+        <v>1253</v>
       </c>
       <c r="P20" t="s">
-        <v>1228</v>
+        <v>1254</v>
       </c>
       <c r="Q20" t="s">
-        <v>1229</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
@@ -17520,16 +17955,16 @@
         <v>5</v>
       </c>
       <c r="D21" t="s">
-        <v>1230</v>
+        <v>1256</v>
       </c>
       <c r="E21" t="s">
-        <v>1209</v>
+        <v>1235</v>
       </c>
       <c r="F21" t="s">
-        <v>1210</v>
+        <v>1236</v>
       </c>
       <c r="G21" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="J21" t="s">
         <v>32</v>
@@ -17544,16 +17979,16 @@
         <v>33</v>
       </c>
       <c r="N21" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O21" t="s">
-        <v>1231</v>
+        <v>1257</v>
       </c>
       <c r="P21" t="s">
-        <v>1232</v>
+        <v>1258</v>
       </c>
       <c r="Q21" t="s">
-        <v>1233</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -17567,16 +18002,16 @@
         <v>40</v>
       </c>
       <c r="D22" t="s">
-        <v>1234</v>
+        <v>1260</v>
       </c>
       <c r="E22" t="s">
-        <v>1209</v>
+        <v>1235</v>
       </c>
       <c r="F22" t="s">
-        <v>1210</v>
+        <v>1236</v>
       </c>
       <c r="G22" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="J22" t="s">
         <v>32</v>
@@ -17591,16 +18026,16 @@
         <v>33</v>
       </c>
       <c r="N22" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O22" t="s">
-        <v>1235</v>
+        <v>1261</v>
       </c>
       <c r="P22" t="s">
-        <v>1236</v>
+        <v>1262</v>
       </c>
       <c r="Q22" t="s">
-        <v>1237</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
@@ -17614,16 +18049,16 @@
         <v>45</v>
       </c>
       <c r="D23" t="s">
-        <v>1238</v>
+        <v>1264</v>
       </c>
       <c r="E23" t="s">
-        <v>1209</v>
+        <v>1235</v>
       </c>
       <c r="F23" t="s">
-        <v>1210</v>
+        <v>1236</v>
       </c>
       <c r="G23" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="J23" t="s">
         <v>32</v>
@@ -17638,16 +18073,16 @@
         <v>33</v>
       </c>
       <c r="N23" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O23" t="s">
-        <v>1239</v>
+        <v>1265</v>
       </c>
       <c r="P23" t="s">
-        <v>1240</v>
+        <v>1266</v>
       </c>
       <c r="Q23" t="s">
-        <v>1241</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
@@ -17661,16 +18096,16 @@
         <v>3</v>
       </c>
       <c r="D24" t="s">
-        <v>1242</v>
+        <v>1268</v>
       </c>
       <c r="E24" t="s">
-        <v>1209</v>
+        <v>1235</v>
       </c>
       <c r="F24" t="s">
-        <v>1210</v>
+        <v>1236</v>
       </c>
       <c r="G24" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="J24" t="s">
         <v>32</v>
@@ -17685,16 +18120,16 @@
         <v>33</v>
       </c>
       <c r="N24" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O24" t="s">
-        <v>1243</v>
+        <v>1269</v>
       </c>
       <c r="P24" t="s">
-        <v>1244</v>
+        <v>1270</v>
       </c>
       <c r="Q24" t="s">
-        <v>1245</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
@@ -17708,7 +18143,7 @@
         <v>42</v>
       </c>
       <c r="D25" t="s">
-        <v>1246</v>
+        <v>1272</v>
       </c>
       <c r="E25" t="s">
         <v>49</v>
@@ -17717,7 +18152,7 @@
         <v>20</v>
       </c>
       <c r="G25" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="J25" t="s">
         <v>32</v>
@@ -17732,16 +18167,16 @@
         <v>33</v>
       </c>
       <c r="N25" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O25" t="s">
-        <v>1247</v>
+        <v>1273</v>
       </c>
       <c r="P25" t="s">
-        <v>1248</v>
+        <v>1274</v>
       </c>
       <c r="Q25" t="s">
-        <v>1249</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
@@ -17755,7 +18190,7 @@
         <v>40</v>
       </c>
       <c r="D26" t="s">
-        <v>1250</v>
+        <v>1276</v>
       </c>
       <c r="E26" t="s">
         <v>49</v>
@@ -17764,7 +18199,7 @@
         <v>20</v>
       </c>
       <c r="G26" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="J26" t="s">
         <v>32</v>
@@ -17779,16 +18214,16 @@
         <v>33</v>
       </c>
       <c r="N26" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O26" t="s">
-        <v>1251</v>
+        <v>1277</v>
       </c>
       <c r="P26" t="s">
-        <v>1252</v>
+        <v>1278</v>
       </c>
       <c r="Q26" t="s">
-        <v>1253</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
@@ -17808,10 +18243,10 @@
         <v>49</v>
       </c>
       <c r="F27" t="s">
-        <v>1254</v>
+        <v>1280</v>
       </c>
       <c r="G27" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="H27">
         <v>180000</v>
@@ -17832,16 +18267,16 @@
         <v>39</v>
       </c>
       <c r="N27" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O27" t="s">
-        <v>1255</v>
+        <v>1281</v>
       </c>
       <c r="P27" t="s">
-        <v>1256</v>
+        <v>1282</v>
       </c>
       <c r="Q27" t="s">
-        <v>1257</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
@@ -17855,7 +18290,7 @@
         <v>52</v>
       </c>
       <c r="D28" t="s">
-        <v>1258</v>
+        <v>1284</v>
       </c>
       <c r="E28" t="s">
         <v>49</v>
@@ -17864,7 +18299,7 @@
         <v>20</v>
       </c>
       <c r="G28" t="s">
-        <v>1144</v>
+        <v>1170</v>
       </c>
       <c r="H28">
         <v>180000</v>
@@ -17885,16 +18320,16 @@
         <v>39</v>
       </c>
       <c r="N28" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O28" t="s">
-        <v>1259</v>
+        <v>1285</v>
       </c>
       <c r="P28" t="s">
-        <v>1260</v>
+        <v>1286</v>
       </c>
       <c r="Q28" t="s">
-        <v>1261</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
@@ -17908,7 +18343,7 @@
         <v>55</v>
       </c>
       <c r="D29" t="s">
-        <v>1262</v>
+        <v>1288</v>
       </c>
       <c r="E29" t="s">
         <v>49</v>
@@ -17917,7 +18352,7 @@
         <v>20</v>
       </c>
       <c r="G29" t="s">
-        <v>1144</v>
+        <v>1170</v>
       </c>
       <c r="H29">
         <v>180000</v>
@@ -17938,16 +18373,16 @@
         <v>39</v>
       </c>
       <c r="N29" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O29" t="s">
-        <v>1263</v>
+        <v>1289</v>
       </c>
       <c r="P29" t="s">
-        <v>1264</v>
+        <v>1290</v>
       </c>
       <c r="Q29" t="s">
-        <v>1265</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
@@ -17961,16 +18396,16 @@
         <v>48</v>
       </c>
       <c r="D30" t="s">
-        <v>1266</v>
+        <v>1292</v>
       </c>
       <c r="E30" t="s">
         <v>49</v>
       </c>
       <c r="F30" t="s">
-        <v>1267</v>
+        <v>1293</v>
       </c>
       <c r="G30" t="s">
-        <v>1144</v>
+        <v>1170</v>
       </c>
       <c r="H30">
         <v>219100</v>
@@ -17991,16 +18426,16 @@
         <v>39</v>
       </c>
       <c r="N30" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O30" t="s">
-        <v>1268</v>
+        <v>1294</v>
       </c>
       <c r="P30" t="s">
-        <v>1269</v>
+        <v>1295</v>
       </c>
       <c r="Q30" t="s">
-        <v>1270</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
@@ -18014,16 +18449,16 @@
         <v>45</v>
       </c>
       <c r="D31" t="s">
-        <v>1271</v>
+        <v>1297</v>
       </c>
       <c r="E31" t="s">
         <v>49</v>
       </c>
       <c r="F31" t="s">
-        <v>1272</v>
+        <v>1298</v>
       </c>
       <c r="G31" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="H31">
         <v>180000</v>
@@ -18044,16 +18479,16 @@
         <v>39</v>
       </c>
       <c r="N31" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O31" t="s">
-        <v>1273</v>
+        <v>1299</v>
       </c>
       <c r="P31" t="s">
-        <v>1274</v>
+        <v>1300</v>
       </c>
       <c r="Q31" t="s">
-        <v>1275</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
@@ -18067,7 +18502,7 @@
         <v>30</v>
       </c>
       <c r="D32" t="s">
-        <v>1276</v>
+        <v>1302</v>
       </c>
       <c r="E32" t="s">
         <v>49</v>
@@ -18076,7 +18511,7 @@
         <v>20</v>
       </c>
       <c r="G32" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="H32">
         <v>219100</v>
@@ -18097,16 +18532,16 @@
         <v>33</v>
       </c>
       <c r="N32" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O32" t="s">
-        <v>1277</v>
+        <v>1303</v>
       </c>
       <c r="P32" t="s">
-        <v>1278</v>
+        <v>1304</v>
       </c>
       <c r="Q32" t="s">
-        <v>1279</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
@@ -18120,7 +18555,7 @@
         <v>45</v>
       </c>
       <c r="D33" t="s">
-        <v>1280</v>
+        <v>1306</v>
       </c>
       <c r="E33" t="s">
         <v>49</v>
@@ -18129,7 +18564,7 @@
         <v>20</v>
       </c>
       <c r="G33" t="s">
-        <v>1144</v>
+        <v>1170</v>
       </c>
       <c r="H33">
         <v>219100</v>
@@ -18150,16 +18585,16 @@
         <v>39</v>
       </c>
       <c r="N33" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O33" t="s">
-        <v>1281</v>
+        <v>1307</v>
       </c>
       <c r="P33" t="s">
-        <v>1282</v>
+        <v>1308</v>
       </c>
       <c r="Q33" t="s">
-        <v>1283</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
@@ -18173,16 +18608,16 @@
         <v>30</v>
       </c>
       <c r="D34" t="s">
-        <v>1284</v>
+        <v>1310</v>
       </c>
       <c r="E34" t="s">
         <v>49</v>
       </c>
       <c r="F34" t="s">
-        <v>1285</v>
+        <v>1311</v>
       </c>
       <c r="G34" t="s">
-        <v>1144</v>
+        <v>1170</v>
       </c>
       <c r="J34" t="s">
         <v>32</v>
@@ -18197,16 +18632,16 @@
         <v>33</v>
       </c>
       <c r="N34" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O34" t="s">
-        <v>1286</v>
+        <v>1312</v>
       </c>
       <c r="P34" t="s">
-        <v>1287</v>
+        <v>1313</v>
       </c>
       <c r="Q34" t="s">
-        <v>1288</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
@@ -18220,16 +18655,16 @@
         <v>58</v>
       </c>
       <c r="D35" t="s">
-        <v>1289</v>
+        <v>1315</v>
       </c>
       <c r="E35" t="s">
-        <v>1290</v>
+        <v>1316</v>
       </c>
       <c r="F35" t="s">
-        <v>1291</v>
+        <v>1317</v>
       </c>
       <c r="G35" t="s">
-        <v>1144</v>
+        <v>1170</v>
       </c>
       <c r="H35">
         <v>257000</v>
@@ -18250,16 +18685,16 @@
         <v>39</v>
       </c>
       <c r="N35" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O35" t="s">
-        <v>1292</v>
+        <v>1318</v>
       </c>
       <c r="P35" t="s">
-        <v>1293</v>
+        <v>1319</v>
       </c>
       <c r="Q35" t="s">
-        <v>1294</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
@@ -18276,13 +18711,13 @@
         <v>478</v>
       </c>
       <c r="E36" t="s">
-        <v>1137</v>
+        <v>1163</v>
       </c>
       <c r="F36" t="s">
-        <v>1295</v>
+        <v>1321</v>
       </c>
       <c r="G36" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="H36">
         <v>200000</v>
@@ -18303,16 +18738,16 @@
         <v>33</v>
       </c>
       <c r="N36" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O36" t="s">
-        <v>1296</v>
+        <v>1322</v>
       </c>
       <c r="P36" t="s">
-        <v>1297</v>
+        <v>1323</v>
       </c>
       <c r="Q36" t="s">
-        <v>1298</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
@@ -18326,16 +18761,16 @@
         <v>20</v>
       </c>
       <c r="D37" t="s">
-        <v>1299</v>
+        <v>1325</v>
       </c>
       <c r="E37" t="s">
         <v>1008</v>
       </c>
       <c r="F37" t="s">
-        <v>1300</v>
+        <v>1326</v>
       </c>
       <c r="G37" t="s">
-        <v>1144</v>
+        <v>1170</v>
       </c>
       <c r="J37" t="s">
         <v>32</v>
@@ -18350,16 +18785,16 @@
         <v>33</v>
       </c>
       <c r="N37" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O37" t="s">
-        <v>1301</v>
+        <v>1327</v>
       </c>
       <c r="P37" t="s">
-        <v>1302</v>
+        <v>1328</v>
       </c>
       <c r="Q37" t="s">
-        <v>1303</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
@@ -18379,10 +18814,10 @@
         <v>1008</v>
       </c>
       <c r="F38" t="s">
-        <v>1304</v>
+        <v>1330</v>
       </c>
       <c r="G38" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="J38" t="s">
         <v>32</v>
@@ -18397,16 +18832,16 @@
         <v>33</v>
       </c>
       <c r="N38" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O38" t="s">
-        <v>1305</v>
+        <v>1331</v>
       </c>
       <c r="P38" t="s">
-        <v>1306</v>
+        <v>1332</v>
       </c>
       <c r="Q38" t="s">
-        <v>1307</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
@@ -18420,16 +18855,16 @@
         <v>15</v>
       </c>
       <c r="D39" t="s">
-        <v>1308</v>
+        <v>1334</v>
       </c>
       <c r="E39" t="s">
         <v>1008</v>
       </c>
       <c r="F39" t="s">
-        <v>1309</v>
+        <v>1335</v>
       </c>
       <c r="G39" t="s">
-        <v>1144</v>
+        <v>1170</v>
       </c>
       <c r="H39">
         <v>500000</v>
@@ -18450,16 +18885,16 @@
         <v>33</v>
       </c>
       <c r="N39" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O39" t="s">
-        <v>1310</v>
+        <v>1336</v>
       </c>
       <c r="P39" t="s">
-        <v>1311</v>
+        <v>1337</v>
       </c>
       <c r="Q39" t="s">
-        <v>1312</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
@@ -18473,16 +18908,16 @@
         <v>18</v>
       </c>
       <c r="D40" t="s">
-        <v>1313</v>
+        <v>1339</v>
       </c>
       <c r="E40" t="s">
         <v>798</v>
       </c>
       <c r="F40" t="s">
-        <v>1154</v>
+        <v>1180</v>
       </c>
       <c r="G40" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="H40">
         <v>274456</v>
@@ -18503,16 +18938,16 @@
         <v>33</v>
       </c>
       <c r="N40" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O40" t="s">
-        <v>1314</v>
+        <v>1340</v>
       </c>
       <c r="P40" t="s">
-        <v>1315</v>
+        <v>1341</v>
       </c>
       <c r="Q40" t="s">
-        <v>1316</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
@@ -18526,16 +18961,16 @@
         <v>30</v>
       </c>
       <c r="D41" t="s">
-        <v>1317</v>
+        <v>1343</v>
       </c>
       <c r="E41" t="s">
         <v>798</v>
       </c>
       <c r="F41" t="s">
-        <v>1318</v>
+        <v>1344</v>
       </c>
       <c r="G41" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="J41" t="s">
         <v>32</v>
@@ -18550,16 +18985,16 @@
         <v>33</v>
       </c>
       <c r="N41" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O41" t="s">
-        <v>1319</v>
+        <v>1345</v>
       </c>
       <c r="P41" t="s">
-        <v>1320</v>
+        <v>1346</v>
       </c>
       <c r="Q41" t="s">
-        <v>1321</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
@@ -18573,16 +19008,16 @@
         <v>22</v>
       </c>
       <c r="D42" t="s">
-        <v>1322</v>
+        <v>1348</v>
       </c>
       <c r="E42" t="s">
         <v>798</v>
       </c>
       <c r="F42" t="s">
-        <v>1323</v>
+        <v>1349</v>
       </c>
       <c r="G42" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="J42" t="s">
         <v>32</v>
@@ -18597,16 +19032,16 @@
         <v>33</v>
       </c>
       <c r="N42" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O42" t="s">
-        <v>1324</v>
+        <v>1350</v>
       </c>
       <c r="P42" t="s">
-        <v>1325</v>
+        <v>1351</v>
       </c>
       <c r="Q42" t="s">
-        <v>1326</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
@@ -18620,16 +19055,16 @@
         <v>48</v>
       </c>
       <c r="D43" t="s">
-        <v>1327</v>
+        <v>1353</v>
       </c>
       <c r="E43" t="s">
         <v>798</v>
       </c>
       <c r="F43" t="s">
-        <v>1328</v>
+        <v>1354</v>
       </c>
       <c r="G43" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="J43" t="s">
         <v>32</v>
@@ -18644,16 +19079,16 @@
         <v>39</v>
       </c>
       <c r="N43" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O43" t="s">
-        <v>1329</v>
+        <v>1355</v>
       </c>
       <c r="P43" t="s">
-        <v>1330</v>
+        <v>1356</v>
       </c>
       <c r="Q43" t="s">
-        <v>1331</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
@@ -18667,16 +19102,16 @@
         <v>25</v>
       </c>
       <c r="D44" t="s">
-        <v>1332</v>
+        <v>1358</v>
       </c>
       <c r="E44" t="s">
         <v>798</v>
       </c>
       <c r="F44" t="s">
-        <v>1143</v>
+        <v>1169</v>
       </c>
       <c r="G44" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="J44" t="s">
         <v>32</v>
@@ -18691,16 +19126,16 @@
         <v>33</v>
       </c>
       <c r="N44" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O44" t="s">
-        <v>1333</v>
+        <v>1359</v>
       </c>
       <c r="P44" t="s">
-        <v>1334</v>
+        <v>1360</v>
       </c>
       <c r="Q44" t="s">
-        <v>1335</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
@@ -18714,16 +19149,16 @@
         <v>40</v>
       </c>
       <c r="D45" t="s">
-        <v>1336</v>
+        <v>1362</v>
       </c>
       <c r="E45" t="s">
         <v>798</v>
       </c>
       <c r="F45" t="s">
-        <v>1337</v>
+        <v>1363</v>
       </c>
       <c r="G45" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="J45" t="s">
         <v>32</v>
@@ -18738,16 +19173,16 @@
         <v>33</v>
       </c>
       <c r="N45" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O45" t="s">
-        <v>1338</v>
+        <v>1364</v>
       </c>
       <c r="P45" t="s">
-        <v>1339</v>
+        <v>1365</v>
       </c>
       <c r="Q45" t="s">
-        <v>1340</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
@@ -18761,16 +19196,16 @@
         <v>70</v>
       </c>
       <c r="D46" t="s">
-        <v>1341</v>
+        <v>1367</v>
       </c>
       <c r="E46" t="s">
-        <v>1342</v>
+        <v>1368</v>
       </c>
       <c r="F46" t="s">
-        <v>1343</v>
+        <v>1369</v>
       </c>
       <c r="G46" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="J46" t="s">
         <v>32</v>
@@ -18785,16 +19220,16 @@
         <v>33</v>
       </c>
       <c r="N46" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O46" t="s">
-        <v>1344</v>
+        <v>1370</v>
       </c>
       <c r="P46" t="s">
-        <v>1345</v>
+        <v>1371</v>
       </c>
       <c r="Q46" t="s">
-        <v>1346</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
@@ -18808,16 +19243,16 @@
         <v>58</v>
       </c>
       <c r="D47" t="s">
-        <v>1347</v>
+        <v>1373</v>
       </c>
       <c r="E47" t="s">
-        <v>1348</v>
+        <v>1374</v>
       </c>
       <c r="F47" t="s">
-        <v>1143</v>
+        <v>1169</v>
       </c>
       <c r="G47" t="s">
-        <v>1144</v>
+        <v>1170</v>
       </c>
       <c r="J47" t="s">
         <v>32</v>
@@ -18832,16 +19267,16 @@
         <v>33</v>
       </c>
       <c r="N47" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O47" t="s">
-        <v>1349</v>
+        <v>1375</v>
       </c>
       <c r="P47" t="s">
-        <v>1350</v>
+        <v>1376</v>
       </c>
       <c r="Q47" t="s">
-        <v>1351</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
@@ -18855,16 +19290,16 @@
         <v>32</v>
       </c>
       <c r="D48" t="s">
-        <v>1352</v>
+        <v>1378</v>
       </c>
       <c r="E48" t="s">
-        <v>1353</v>
+        <v>1379</v>
       </c>
       <c r="F48" t="s">
-        <v>1354</v>
+        <v>1380</v>
       </c>
       <c r="G48" t="s">
-        <v>1144</v>
+        <v>1170</v>
       </c>
       <c r="J48" t="s">
         <v>32</v>
@@ -18879,16 +19314,16 @@
         <v>33</v>
       </c>
       <c r="N48" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O48" t="s">
-        <v>1355</v>
+        <v>1381</v>
       </c>
       <c r="P48" t="s">
-        <v>1356</v>
+        <v>1382</v>
       </c>
       <c r="Q48" t="s">
-        <v>1357</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
@@ -18902,16 +19337,16 @@
         <v>4</v>
       </c>
       <c r="D49" t="s">
-        <v>1358</v>
+        <v>1384</v>
       </c>
       <c r="E49" t="s">
-        <v>1359</v>
+        <v>1385</v>
       </c>
       <c r="F49" t="s">
-        <v>1360</v>
+        <v>1386</v>
       </c>
       <c r="G49" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="J49" t="s">
         <v>32</v>
@@ -18926,16 +19361,16 @@
         <v>33</v>
       </c>
       <c r="N49" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O49" t="s">
-        <v>1361</v>
+        <v>1387</v>
       </c>
       <c r="P49" t="s">
-        <v>1362</v>
+        <v>1388</v>
       </c>
       <c r="Q49" t="s">
-        <v>1363</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
@@ -18949,16 +19384,16 @@
         <v>25</v>
       </c>
       <c r="D50" t="s">
-        <v>1364</v>
+        <v>1390</v>
       </c>
       <c r="E50" t="s">
-        <v>1365</v>
+        <v>1391</v>
       </c>
       <c r="F50" t="s">
-        <v>1200</v>
+        <v>1226</v>
       </c>
       <c r="G50" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="J50" t="s">
         <v>32</v>
@@ -18973,16 +19408,16 @@
         <v>33</v>
       </c>
       <c r="N50" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O50" t="s">
-        <v>1366</v>
+        <v>1392</v>
       </c>
       <c r="P50" t="s">
-        <v>1367</v>
+        <v>1393</v>
       </c>
       <c r="Q50" t="s">
-        <v>1368</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
@@ -18996,16 +19431,16 @@
         <v>30</v>
       </c>
       <c r="D51" t="s">
-        <v>1369</v>
+        <v>1395</v>
       </c>
       <c r="E51" t="s">
-        <v>1370</v>
+        <v>1396</v>
       </c>
       <c r="F51" t="s">
-        <v>1371</v>
+        <v>1397</v>
       </c>
       <c r="G51" t="s">
-        <v>1144</v>
+        <v>1170</v>
       </c>
       <c r="J51" t="s">
         <v>32</v>
@@ -19020,16 +19455,16 @@
         <v>33</v>
       </c>
       <c r="N51" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O51" t="s">
-        <v>1372</v>
+        <v>1398</v>
       </c>
       <c r="P51" t="s">
-        <v>1373</v>
+        <v>1399</v>
       </c>
       <c r="Q51" t="s">
-        <v>1374</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
@@ -19043,16 +19478,16 @@
         <v>52</v>
       </c>
       <c r="D52" t="s">
-        <v>1375</v>
+        <v>1401</v>
       </c>
       <c r="E52" t="s">
         <v>49</v>
       </c>
       <c r="F52" t="s">
-        <v>1376</v>
+        <v>1402</v>
       </c>
       <c r="G52" t="s">
-        <v>1144</v>
+        <v>1170</v>
       </c>
       <c r="H52">
         <v>180000</v>
@@ -19073,16 +19508,16 @@
         <v>39</v>
       </c>
       <c r="N52" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O52" t="s">
-        <v>1377</v>
+        <v>1403</v>
       </c>
       <c r="P52" t="s">
-        <v>1378</v>
+        <v>1404</v>
       </c>
       <c r="Q52" t="s">
-        <v>1379</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
@@ -19096,7 +19531,7 @@
         <v>50</v>
       </c>
       <c r="D53" t="s">
-        <v>1380</v>
+        <v>1406</v>
       </c>
       <c r="E53" t="s">
         <v>49</v>
@@ -19105,7 +19540,7 @@
         <v>20</v>
       </c>
       <c r="G53" t="s">
-        <v>1144</v>
+        <v>1170</v>
       </c>
       <c r="H53">
         <v>180000</v>
@@ -19126,16 +19561,16 @@
         <v>39</v>
       </c>
       <c r="N53" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O53" t="s">
-        <v>1381</v>
+        <v>1407</v>
       </c>
       <c r="P53" t="s">
-        <v>1382</v>
+        <v>1408</v>
       </c>
       <c r="Q53" t="s">
-        <v>1383</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
@@ -19149,7 +19584,7 @@
         <v>46</v>
       </c>
       <c r="D54" t="s">
-        <v>1384</v>
+        <v>1410</v>
       </c>
       <c r="E54" t="s">
         <v>49</v>
@@ -19158,7 +19593,7 @@
         <v>20</v>
       </c>
       <c r="G54" t="s">
-        <v>1144</v>
+        <v>1170</v>
       </c>
       <c r="H54">
         <v>180000</v>
@@ -19179,16 +19614,16 @@
         <v>39</v>
       </c>
       <c r="N54" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O54" t="s">
-        <v>1385</v>
+        <v>1411</v>
       </c>
       <c r="P54" t="s">
-        <v>1386</v>
+        <v>1412</v>
       </c>
       <c r="Q54" t="s">
-        <v>1387</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
@@ -19202,7 +19637,7 @@
         <v>38</v>
       </c>
       <c r="D55" t="s">
-        <v>1388</v>
+        <v>1414</v>
       </c>
       <c r="E55" t="s">
         <v>49</v>
@@ -19211,7 +19646,7 @@
         <v>20</v>
       </c>
       <c r="G55" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="H55">
         <v>217800</v>
@@ -19232,16 +19667,16 @@
         <v>33</v>
       </c>
       <c r="N55" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O55" t="s">
-        <v>1389</v>
+        <v>1415</v>
       </c>
       <c r="P55" t="s">
-        <v>1390</v>
+        <v>1416</v>
       </c>
       <c r="Q55" t="s">
-        <v>1391</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
@@ -19261,10 +19696,10 @@
         <v>49</v>
       </c>
       <c r="F56" t="s">
-        <v>1392</v>
+        <v>1418</v>
       </c>
       <c r="G56" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="H56">
         <v>180000</v>
@@ -19285,16 +19720,16 @@
         <v>39</v>
       </c>
       <c r="N56" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O56" t="s">
-        <v>1393</v>
+        <v>1419</v>
       </c>
       <c r="P56" t="s">
-        <v>1394</v>
+        <v>1420</v>
       </c>
       <c r="Q56" t="s">
-        <v>1395</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
@@ -19308,16 +19743,16 @@
         <v>45</v>
       </c>
       <c r="D57" t="s">
-        <v>1396</v>
+        <v>1422</v>
       </c>
       <c r="E57" t="s">
         <v>49</v>
       </c>
       <c r="F57" t="s">
-        <v>1397</v>
+        <v>1423</v>
       </c>
       <c r="G57" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="H57">
         <v>219100</v>
@@ -19338,16 +19773,16 @@
         <v>39</v>
       </c>
       <c r="N57" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O57" t="s">
-        <v>1398</v>
+        <v>1424</v>
       </c>
       <c r="P57" t="s">
-        <v>1399</v>
+        <v>1425</v>
       </c>
       <c r="Q57" t="s">
-        <v>1400</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
@@ -19361,16 +19796,16 @@
         <v>42</v>
       </c>
       <c r="D58" t="s">
-        <v>1401</v>
+        <v>1427</v>
       </c>
       <c r="E58" t="s">
         <v>49</v>
       </c>
       <c r="F58" t="s">
-        <v>1402</v>
+        <v>1428</v>
       </c>
       <c r="G58" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="H58">
         <v>180000</v>
@@ -19391,16 +19826,16 @@
         <v>39</v>
       </c>
       <c r="N58" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O58" t="s">
-        <v>1403</v>
+        <v>1429</v>
       </c>
       <c r="P58" t="s">
-        <v>1404</v>
+        <v>1430</v>
       </c>
       <c r="Q58" t="s">
-        <v>1405</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
@@ -19414,7 +19849,7 @@
         <v>32</v>
       </c>
       <c r="D59" t="s">
-        <v>1406</v>
+        <v>1432</v>
       </c>
       <c r="E59" t="s">
         <v>49</v>
@@ -19423,7 +19858,7 @@
         <v>20</v>
       </c>
       <c r="G59" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="H59">
         <v>219100</v>
@@ -19444,16 +19879,16 @@
         <v>33</v>
       </c>
       <c r="N59" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O59" t="s">
-        <v>1407</v>
+        <v>1433</v>
       </c>
       <c r="P59" t="s">
-        <v>1408</v>
+        <v>1434</v>
       </c>
       <c r="Q59" t="s">
-        <v>1409</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
@@ -19467,7 +19902,7 @@
         <v>35</v>
       </c>
       <c r="D60" t="s">
-        <v>1410</v>
+        <v>1436</v>
       </c>
       <c r="E60" t="s">
         <v>49</v>
@@ -19476,7 +19911,7 @@
         <v>20</v>
       </c>
       <c r="G60" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="H60">
         <v>219100</v>
@@ -19497,16 +19932,16 @@
         <v>33</v>
       </c>
       <c r="N60" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O60" t="s">
-        <v>1411</v>
+        <v>1437</v>
       </c>
       <c r="P60" t="s">
-        <v>1412</v>
+        <v>1438</v>
       </c>
       <c r="Q60" t="s">
-        <v>1413</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
@@ -19520,16 +19955,16 @@
         <v>40</v>
       </c>
       <c r="D61" t="s">
-        <v>1414</v>
+        <v>1440</v>
       </c>
       <c r="E61" t="s">
         <v>49</v>
       </c>
       <c r="F61" t="s">
-        <v>1415</v>
+        <v>1441</v>
       </c>
       <c r="G61" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="H61">
         <v>219100</v>
@@ -19550,16 +19985,16 @@
         <v>39</v>
       </c>
       <c r="N61" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O61" t="s">
-        <v>1416</v>
+        <v>1442</v>
       </c>
       <c r="P61" t="s">
-        <v>1417</v>
+        <v>1443</v>
       </c>
       <c r="Q61" t="s">
-        <v>1418</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
@@ -19573,7 +20008,7 @@
         <v>38</v>
       </c>
       <c r="D62" t="s">
-        <v>1419</v>
+        <v>1445</v>
       </c>
       <c r="E62" t="s">
         <v>49</v>
@@ -19582,7 +20017,7 @@
         <v>757</v>
       </c>
       <c r="G62" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="H62">
         <v>219100</v>
@@ -19603,16 +20038,16 @@
         <v>33</v>
       </c>
       <c r="N62" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O62" t="s">
-        <v>1420</v>
+        <v>1446</v>
       </c>
       <c r="P62" t="s">
-        <v>1421</v>
+        <v>1447</v>
       </c>
       <c r="Q62" t="s">
-        <v>1422</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
@@ -19626,7 +20061,7 @@
         <v>40</v>
       </c>
       <c r="D63" t="s">
-        <v>1423</v>
+        <v>1449</v>
       </c>
       <c r="E63" t="s">
         <v>49</v>
@@ -19635,7 +20070,7 @@
         <v>20</v>
       </c>
       <c r="G63" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="H63">
         <v>219100</v>
@@ -19656,16 +20091,16 @@
         <v>39</v>
       </c>
       <c r="N63" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O63" t="s">
-        <v>1424</v>
+        <v>1450</v>
       </c>
       <c r="P63" t="s">
-        <v>1425</v>
+        <v>1451</v>
       </c>
       <c r="Q63" t="s">
-        <v>1426</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
@@ -19679,16 +20114,16 @@
         <v>33</v>
       </c>
       <c r="D64" t="s">
-        <v>1427</v>
+        <v>1453</v>
       </c>
       <c r="E64" t="s">
         <v>49</v>
       </c>
       <c r="F64" t="s">
-        <v>1428</v>
+        <v>1454</v>
       </c>
       <c r="G64" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="H64">
         <v>219100</v>
@@ -19709,16 +20144,16 @@
         <v>33</v>
       </c>
       <c r="N64" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O64" t="s">
-        <v>1429</v>
+        <v>1455</v>
       </c>
       <c r="P64" t="s">
-        <v>1430</v>
+        <v>1456</v>
       </c>
       <c r="Q64" t="s">
-        <v>1431</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
@@ -19732,16 +20167,16 @@
         <v>48</v>
       </c>
       <c r="D65" t="s">
-        <v>1432</v>
+        <v>1458</v>
       </c>
       <c r="E65" t="s">
-        <v>1290</v>
+        <v>1316</v>
       </c>
       <c r="F65" t="s">
-        <v>1433</v>
+        <v>1459</v>
       </c>
       <c r="G65" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="J65" t="s">
         <v>32</v>
@@ -19756,16 +20191,16 @@
         <v>39</v>
       </c>
       <c r="N65" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O65" t="s">
-        <v>1434</v>
+        <v>1460</v>
       </c>
       <c r="P65" t="s">
-        <v>1435</v>
+        <v>1461</v>
       </c>
       <c r="Q65" t="s">
-        <v>1436</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
@@ -19779,16 +20214,16 @@
         <v>40</v>
       </c>
       <c r="D66" t="s">
-        <v>1136</v>
+        <v>1162</v>
       </c>
       <c r="E66" t="s">
-        <v>1137</v>
+        <v>1163</v>
       </c>
       <c r="F66" t="s">
-        <v>1437</v>
+        <v>1463</v>
       </c>
       <c r="G66" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="H66">
         <v>184200</v>
@@ -19809,16 +20244,16 @@
         <v>39</v>
       </c>
       <c r="N66" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O66" t="s">
-        <v>1438</v>
+        <v>1464</v>
       </c>
       <c r="P66" t="s">
-        <v>1439</v>
+        <v>1465</v>
       </c>
       <c r="Q66" t="s">
-        <v>1440</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
@@ -19832,16 +20267,16 @@
         <v>30</v>
       </c>
       <c r="D67" t="s">
-        <v>1441</v>
+        <v>1467</v>
       </c>
       <c r="E67" t="s">
-        <v>1137</v>
+        <v>1163</v>
       </c>
       <c r="F67" t="s">
-        <v>1442</v>
+        <v>1468</v>
       </c>
       <c r="G67" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="H67">
         <v>200000</v>
@@ -19862,16 +20297,16 @@
         <v>33</v>
       </c>
       <c r="N67" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O67" t="s">
-        <v>1443</v>
+        <v>1469</v>
       </c>
       <c r="P67" t="s">
-        <v>1444</v>
+        <v>1470</v>
       </c>
       <c r="Q67" t="s">
-        <v>1445</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
@@ -19885,7 +20320,7 @@
         <v>30</v>
       </c>
       <c r="D68" t="s">
-        <v>1446</v>
+        <v>1472</v>
       </c>
       <c r="E68" t="s">
         <v>1008</v>
@@ -19894,7 +20329,7 @@
         <v>1017</v>
       </c>
       <c r="G68" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="J68" t="s">
         <v>32</v>
@@ -19909,16 +20344,16 @@
         <v>33</v>
       </c>
       <c r="N68" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O68" t="s">
-        <v>1447</v>
+        <v>1473</v>
       </c>
       <c r="P68" t="s">
-        <v>1448</v>
+        <v>1474</v>
       </c>
       <c r="Q68" t="s">
-        <v>1449</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
@@ -19932,16 +20367,16 @@
         <v>32</v>
       </c>
       <c r="D69" t="s">
-        <v>1450</v>
+        <v>1476</v>
       </c>
       <c r="E69" t="s">
         <v>1008</v>
       </c>
       <c r="F69" t="s">
-        <v>1304</v>
+        <v>1330</v>
       </c>
       <c r="G69" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="J69" t="s">
         <v>32</v>
@@ -19956,16 +20391,16 @@
         <v>33</v>
       </c>
       <c r="N69" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O69" t="s">
-        <v>1451</v>
+        <v>1477</v>
       </c>
       <c r="P69" t="s">
-        <v>1452</v>
+        <v>1478</v>
       </c>
       <c r="Q69" t="s">
-        <v>1453</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
@@ -19979,7 +20414,7 @@
         <v>32</v>
       </c>
       <c r="D70" t="s">
-        <v>1454</v>
+        <v>1480</v>
       </c>
       <c r="E70" t="s">
         <v>1008</v>
@@ -19988,7 +20423,7 @@
         <v>1017</v>
       </c>
       <c r="G70" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="J70" t="s">
         <v>32</v>
@@ -20003,16 +20438,16 @@
         <v>33</v>
       </c>
       <c r="N70" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O70" t="s">
-        <v>1455</v>
+        <v>1481</v>
       </c>
       <c r="P70" t="s">
-        <v>1456</v>
+        <v>1482</v>
       </c>
       <c r="Q70" t="s">
-        <v>1457</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
@@ -20026,16 +20461,16 @@
         <v>45</v>
       </c>
       <c r="D71" t="s">
-        <v>1458</v>
+        <v>1484</v>
       </c>
       <c r="E71" t="s">
         <v>798</v>
       </c>
       <c r="F71" t="s">
-        <v>1149</v>
+        <v>1175</v>
       </c>
       <c r="G71" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="J71" t="s">
         <v>32</v>
@@ -20050,16 +20485,16 @@
         <v>39</v>
       </c>
       <c r="N71" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O71" t="s">
-        <v>1459</v>
+        <v>1485</v>
       </c>
       <c r="P71" t="s">
-        <v>1460</v>
+        <v>1486</v>
       </c>
       <c r="Q71" t="s">
-        <v>1461</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
@@ -20073,16 +20508,16 @@
         <v>35</v>
       </c>
       <c r="D72" t="s">
-        <v>1462</v>
+        <v>1488</v>
       </c>
       <c r="E72" t="s">
         <v>798</v>
       </c>
       <c r="F72" t="s">
-        <v>1463</v>
+        <v>1489</v>
       </c>
       <c r="G72" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="J72" t="s">
         <v>32</v>
@@ -20097,16 +20532,16 @@
         <v>33</v>
       </c>
       <c r="N72" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O72" t="s">
-        <v>1464</v>
+        <v>1490</v>
       </c>
       <c r="P72" t="s">
-        <v>1465</v>
+        <v>1491</v>
       </c>
       <c r="Q72" t="s">
-        <v>1466</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
@@ -20120,7 +20555,7 @@
         <v>35</v>
       </c>
       <c r="D73" t="s">
-        <v>1467</v>
+        <v>1493</v>
       </c>
       <c r="E73" t="s">
         <v>798</v>
@@ -20129,7 +20564,7 @@
         <v>85</v>
       </c>
       <c r="G73" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="J73" t="s">
         <v>32</v>
@@ -20144,16 +20579,16 @@
         <v>33</v>
       </c>
       <c r="N73" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O73" t="s">
-        <v>1468</v>
+        <v>1494</v>
       </c>
       <c r="P73" t="s">
-        <v>1469</v>
+        <v>1495</v>
       </c>
       <c r="Q73" t="s">
-        <v>1470</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
@@ -20167,16 +20602,16 @@
         <v>15</v>
       </c>
       <c r="D74" t="s">
-        <v>1471</v>
+        <v>1497</v>
       </c>
       <c r="E74" t="s">
         <v>798</v>
       </c>
       <c r="F74" t="s">
-        <v>1472</v>
+        <v>1498</v>
       </c>
       <c r="G74" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="J74" t="s">
         <v>32</v>
@@ -20191,16 +20626,16 @@
         <v>33</v>
       </c>
       <c r="N74" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O74" t="s">
-        <v>1473</v>
+        <v>1499</v>
       </c>
       <c r="P74" t="s">
-        <v>1474</v>
+        <v>1500</v>
       </c>
       <c r="Q74" t="s">
-        <v>1475</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
@@ -20214,16 +20649,16 @@
         <v>25</v>
       </c>
       <c r="D75" t="s">
-        <v>1476</v>
+        <v>1502</v>
       </c>
       <c r="E75" t="s">
         <v>798</v>
       </c>
       <c r="F75" t="s">
-        <v>1477</v>
+        <v>1503</v>
       </c>
       <c r="G75" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="J75" t="s">
         <v>32</v>
@@ -20238,16 +20673,16 @@
         <v>33</v>
       </c>
       <c r="N75" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O75" t="s">
-        <v>1478</v>
+        <v>1504</v>
       </c>
       <c r="P75" t="s">
-        <v>1479</v>
+        <v>1505</v>
       </c>
       <c r="Q75" t="s">
-        <v>1480</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
@@ -20261,16 +20696,16 @@
         <v>30</v>
       </c>
       <c r="D76" t="s">
-        <v>1481</v>
+        <v>1507</v>
       </c>
       <c r="E76" t="s">
         <v>798</v>
       </c>
       <c r="F76" t="s">
-        <v>1482</v>
+        <v>1508</v>
       </c>
       <c r="G76" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="J76" t="s">
         <v>32</v>
@@ -20285,16 +20720,16 @@
         <v>33</v>
       </c>
       <c r="N76" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O76" t="s">
-        <v>1483</v>
+        <v>1509</v>
       </c>
       <c r="P76" t="s">
-        <v>1484</v>
+        <v>1510</v>
       </c>
       <c r="Q76" t="s">
-        <v>1485</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
@@ -20314,10 +20749,10 @@
         <v>49</v>
       </c>
       <c r="F77" t="s">
-        <v>1442</v>
+        <v>1468</v>
       </c>
       <c r="G77" t="s">
-        <v>1144</v>
+        <v>1170</v>
       </c>
       <c r="J77" t="s">
         <v>32</v>
@@ -20332,16 +20767,16 @@
         <v>33</v>
       </c>
       <c r="N77" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O77" t="s">
-        <v>1486</v>
+        <v>1512</v>
       </c>
       <c r="P77" t="s">
-        <v>1487</v>
+        <v>1513</v>
       </c>
       <c r="Q77" t="s">
-        <v>1488</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
@@ -20361,10 +20796,10 @@
         <v>49</v>
       </c>
       <c r="F78" t="s">
-        <v>1489</v>
+        <v>1515</v>
       </c>
       <c r="G78" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="J78" t="s">
         <v>32</v>
@@ -20379,16 +20814,16 @@
         <v>39</v>
       </c>
       <c r="N78" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O78" t="s">
-        <v>1490</v>
+        <v>1516</v>
       </c>
       <c r="P78" t="s">
-        <v>1491</v>
+        <v>1517</v>
       </c>
       <c r="Q78" t="s">
-        <v>1492</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
@@ -20411,7 +20846,7 @@
         <v>1074</v>
       </c>
       <c r="G79" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="H79">
         <v>180000</v>
@@ -20432,16 +20867,16 @@
         <v>33</v>
       </c>
       <c r="N79" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O79" t="s">
-        <v>1493</v>
+        <v>1519</v>
       </c>
       <c r="P79" t="s">
-        <v>1494</v>
+        <v>1520</v>
       </c>
       <c r="Q79" t="s">
-        <v>1495</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
@@ -20461,10 +20896,10 @@
         <v>49</v>
       </c>
       <c r="F80" t="s">
-        <v>1496</v>
+        <v>1522</v>
       </c>
       <c r="G80" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="H80">
         <v>180000</v>
@@ -20485,16 +20920,16 @@
         <v>33</v>
       </c>
       <c r="N80" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O80" t="s">
-        <v>1497</v>
+        <v>1523</v>
       </c>
       <c r="P80" t="s">
-        <v>1498</v>
+        <v>1524</v>
       </c>
       <c r="Q80" t="s">
-        <v>1499</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
@@ -20508,16 +20943,16 @@
         <v>20</v>
       </c>
       <c r="D81" t="s">
-        <v>1500</v>
+        <v>1526</v>
       </c>
       <c r="E81" t="s">
         <v>1119</v>
       </c>
       <c r="F81" t="s">
-        <v>1501</v>
+        <v>1527</v>
       </c>
       <c r="G81" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="J81" t="s">
         <v>32</v>
@@ -20532,16 +20967,16 @@
         <v>33</v>
       </c>
       <c r="N81" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O81" t="s">
-        <v>1502</v>
+        <v>1528</v>
       </c>
       <c r="P81" t="s">
-        <v>1503</v>
+        <v>1529</v>
       </c>
       <c r="Q81" t="s">
-        <v>1504</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
@@ -20555,7 +20990,7 @@
         <v>50</v>
       </c>
       <c r="D82" t="s">
-        <v>1505</v>
+        <v>1531</v>
       </c>
       <c r="E82" t="s">
         <v>1119</v>
@@ -20564,7 +20999,7 @@
         <v>20</v>
       </c>
       <c r="G82" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="H82">
         <v>250000</v>
@@ -20585,16 +21020,16 @@
         <v>39</v>
       </c>
       <c r="N82" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O82" t="s">
-        <v>1506</v>
+        <v>1532</v>
       </c>
       <c r="P82" t="s">
-        <v>1507</v>
+        <v>1533</v>
       </c>
       <c r="Q82" t="s">
-        <v>1508</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
@@ -20608,7 +21043,7 @@
         <v>55</v>
       </c>
       <c r="D83" t="s">
-        <v>1509</v>
+        <v>1535</v>
       </c>
       <c r="E83" t="s">
         <v>1119</v>
@@ -20617,7 +21052,7 @@
         <v>20</v>
       </c>
       <c r="G83" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="H83">
         <v>200000</v>
@@ -20638,16 +21073,16 @@
         <v>39</v>
       </c>
       <c r="N83" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O83" t="s">
-        <v>1510</v>
+        <v>1536</v>
       </c>
       <c r="P83" t="s">
-        <v>1511</v>
+        <v>1537</v>
       </c>
       <c r="Q83" t="s">
-        <v>1512</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
@@ -20661,7 +21096,7 @@
         <v>52</v>
       </c>
       <c r="D84" t="s">
-        <v>1513</v>
+        <v>1539</v>
       </c>
       <c r="E84" t="s">
         <v>1119</v>
@@ -20670,7 +21105,7 @@
         <v>20</v>
       </c>
       <c r="G84" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="H84">
         <v>250000</v>
@@ -20691,16 +21126,16 @@
         <v>39</v>
       </c>
       <c r="N84" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O84" t="s">
-        <v>1514</v>
+        <v>1540</v>
       </c>
       <c r="P84" t="s">
-        <v>1515</v>
+        <v>1541</v>
       </c>
       <c r="Q84" t="s">
-        <v>1516</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
@@ -20714,7 +21149,7 @@
         <v>53</v>
       </c>
       <c r="D85" t="s">
-        <v>1517</v>
+        <v>1543</v>
       </c>
       <c r="E85" t="s">
         <v>1119</v>
@@ -20723,7 +21158,7 @@
         <v>20</v>
       </c>
       <c r="G85" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="H85">
         <v>200000</v>
@@ -20744,16 +21179,16 @@
         <v>39</v>
       </c>
       <c r="N85" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O85" t="s">
-        <v>1518</v>
+        <v>1544</v>
       </c>
       <c r="P85" t="s">
-        <v>1519</v>
+        <v>1545</v>
       </c>
       <c r="Q85" t="s">
-        <v>1520</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
@@ -20767,7 +21202,7 @@
         <v>50</v>
       </c>
       <c r="D86" t="s">
-        <v>1521</v>
+        <v>1547</v>
       </c>
       <c r="E86" t="s">
         <v>1119</v>
@@ -20776,7 +21211,7 @@
         <v>20</v>
       </c>
       <c r="G86" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="H86">
         <v>200000</v>
@@ -20797,16 +21232,16 @@
         <v>39</v>
       </c>
       <c r="N86" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O86" t="s">
-        <v>1522</v>
+        <v>1548</v>
       </c>
       <c r="P86" t="s">
-        <v>1523</v>
+        <v>1549</v>
       </c>
       <c r="Q86" t="s">
-        <v>1524</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
@@ -20820,7 +21255,7 @@
         <v>55</v>
       </c>
       <c r="D87" t="s">
-        <v>1525</v>
+        <v>1551</v>
       </c>
       <c r="E87" t="s">
         <v>1119</v>
@@ -20829,7 +21264,7 @@
         <v>20</v>
       </c>
       <c r="G87" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="H87">
         <v>250000</v>
@@ -20850,16 +21285,16 @@
         <v>39</v>
       </c>
       <c r="N87" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O87" t="s">
-        <v>1526</v>
+        <v>1552</v>
       </c>
       <c r="P87" t="s">
-        <v>1527</v>
+        <v>1553</v>
       </c>
       <c r="Q87" t="s">
-        <v>1528</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
@@ -20873,16 +21308,16 @@
         <v>45</v>
       </c>
       <c r="D88" t="s">
-        <v>1529</v>
+        <v>1555</v>
       </c>
       <c r="E88" t="s">
-        <v>1530</v>
+        <v>1556</v>
       </c>
       <c r="F88" t="s">
-        <v>1531</v>
+        <v>1557</v>
       </c>
       <c r="G88" t="s">
-        <v>1144</v>
+        <v>1170</v>
       </c>
       <c r="H88">
         <v>154000</v>
@@ -20903,16 +21338,16 @@
         <v>33</v>
       </c>
       <c r="N88" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O88" t="s">
-        <v>1532</v>
+        <v>1558</v>
       </c>
       <c r="P88" t="s">
-        <v>1533</v>
+        <v>1559</v>
       </c>
       <c r="Q88" t="s">
-        <v>1534</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
@@ -20935,7 +21370,7 @@
         <v>757</v>
       </c>
       <c r="G89" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="H89">
         <v>180000</v>
@@ -20956,16 +21391,16 @@
         <v>39</v>
       </c>
       <c r="N89" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O89" t="s">
-        <v>1535</v>
+        <v>1561</v>
       </c>
       <c r="P89" t="s">
-        <v>1536</v>
+        <v>1562</v>
       </c>
       <c r="Q89" t="s">
-        <v>1537</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
@@ -20985,10 +21420,10 @@
         <v>49</v>
       </c>
       <c r="F90" t="s">
-        <v>1392</v>
+        <v>1418</v>
       </c>
       <c r="G90" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="H90">
         <v>219100</v>
@@ -21009,16 +21444,16 @@
         <v>33</v>
       </c>
       <c r="N90" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O90" t="s">
-        <v>1538</v>
+        <v>1564</v>
       </c>
       <c r="P90" t="s">
-        <v>1539</v>
+        <v>1565</v>
       </c>
       <c r="Q90" t="s">
-        <v>1540</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
@@ -21032,16 +21467,16 @@
         <v>25</v>
       </c>
       <c r="D91" t="s">
-        <v>1541</v>
+        <v>1567</v>
       </c>
       <c r="E91" t="s">
         <v>49</v>
       </c>
       <c r="F91" t="s">
-        <v>1542</v>
+        <v>1568</v>
       </c>
       <c r="G91" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="J91" t="s">
         <v>32</v>
@@ -21056,16 +21491,16 @@
         <v>33</v>
       </c>
       <c r="N91" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O91" t="s">
-        <v>1543</v>
+        <v>1569</v>
       </c>
       <c r="P91" t="s">
-        <v>1544</v>
+        <v>1570</v>
       </c>
       <c r="Q91" t="s">
-        <v>1545</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
@@ -21085,10 +21520,10 @@
         <v>1008</v>
       </c>
       <c r="F92" t="s">
-        <v>1143</v>
+        <v>1169</v>
       </c>
       <c r="G92" t="s">
-        <v>1144</v>
+        <v>1170</v>
       </c>
       <c r="J92" t="s">
         <v>32</v>
@@ -21103,16 +21538,16 @@
         <v>33</v>
       </c>
       <c r="N92" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O92" t="s">
-        <v>1546</v>
+        <v>1572</v>
       </c>
       <c r="P92" t="s">
-        <v>1547</v>
+        <v>1573</v>
       </c>
       <c r="Q92" t="s">
-        <v>1548</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
@@ -21126,16 +21561,16 @@
         <v>15</v>
       </c>
       <c r="D93" t="s">
-        <v>1549</v>
+        <v>1575</v>
       </c>
       <c r="E93" t="s">
-        <v>1550</v>
+        <v>1576</v>
       </c>
       <c r="F93" t="s">
-        <v>1360</v>
+        <v>1386</v>
       </c>
       <c r="G93" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="J93" t="s">
         <v>32</v>
@@ -21150,16 +21585,16 @@
         <v>33</v>
       </c>
       <c r="N93" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O93" t="s">
-        <v>1551</v>
+        <v>1577</v>
       </c>
       <c r="P93" t="s">
-        <v>1552</v>
+        <v>1578</v>
       </c>
       <c r="Q93" t="s">
-        <v>1553</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
@@ -21173,16 +21608,16 @@
         <v>12</v>
       </c>
       <c r="D94" t="s">
-        <v>1554</v>
+        <v>1580</v>
       </c>
       <c r="E94" t="s">
-        <v>1555</v>
+        <v>1581</v>
       </c>
       <c r="F94" t="s">
-        <v>1556</v>
+        <v>1582</v>
       </c>
       <c r="G94" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="J94" t="s">
         <v>32</v>
@@ -21197,16 +21632,216 @@
         <v>33</v>
       </c>
       <c r="N94" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
       <c r="O94" t="s">
-        <v>1557</v>
+        <v>1583</v>
       </c>
       <c r="P94" t="s">
-        <v>1558</v>
+        <v>1584</v>
       </c>
       <c r="Q94" t="s">
-        <v>1559</v>
+        <v>1585</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>17</v>
+      </c>
+      <c r="B95">
+        <v>55</v>
+      </c>
+      <c r="C95">
+        <v>42</v>
+      </c>
+      <c r="D95" t="s">
+        <v>1586</v>
+      </c>
+      <c r="E95" t="s">
+        <v>49</v>
+      </c>
+      <c r="F95" t="s">
+        <v>1587</v>
+      </c>
+      <c r="G95" t="s">
+        <v>1164</v>
+      </c>
+      <c r="H95">
+        <v>180000</v>
+      </c>
+      <c r="I95">
+        <v>180000</v>
+      </c>
+      <c r="J95" t="s">
+        <v>22</v>
+      </c>
+      <c r="K95" t="s">
+        <v>51</v>
+      </c>
+      <c r="L95" t="s">
+        <v>1136</v>
+      </c>
+      <c r="M95" t="s">
+        <v>39</v>
+      </c>
+      <c r="N95" t="s">
+        <v>1165</v>
+      </c>
+      <c r="O95" t="s">
+        <v>1588</v>
+      </c>
+      <c r="P95" t="s">
+        <v>1589</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>17</v>
+      </c>
+      <c r="B96">
+        <v>20</v>
+      </c>
+      <c r="C96">
+        <v>22</v>
+      </c>
+      <c r="D96" t="s">
+        <v>1591</v>
+      </c>
+      <c r="E96" t="s">
+        <v>1163</v>
+      </c>
+      <c r="F96" t="s">
+        <v>1592</v>
+      </c>
+      <c r="G96" t="s">
+        <v>1164</v>
+      </c>
+      <c r="H96">
+        <v>200000</v>
+      </c>
+      <c r="I96">
+        <v>200000</v>
+      </c>
+      <c r="J96" t="s">
+        <v>22</v>
+      </c>
+      <c r="K96" t="s">
+        <v>51</v>
+      </c>
+      <c r="L96" t="s">
+        <v>1136</v>
+      </c>
+      <c r="M96" t="s">
+        <v>33</v>
+      </c>
+      <c r="N96" t="s">
+        <v>1165</v>
+      </c>
+      <c r="O96" t="s">
+        <v>1593</v>
+      </c>
+      <c r="P96" t="s">
+        <v>1594</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>1595</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>17</v>
+      </c>
+      <c r="B97">
+        <v>35</v>
+      </c>
+      <c r="C97">
+        <v>28</v>
+      </c>
+      <c r="D97" t="s">
+        <v>1596</v>
+      </c>
+      <c r="E97" t="s">
+        <v>1597</v>
+      </c>
+      <c r="F97" t="s">
+        <v>1568</v>
+      </c>
+      <c r="G97" t="s">
+        <v>1170</v>
+      </c>
+      <c r="J97" t="s">
+        <v>32</v>
+      </c>
+      <c r="K97" t="s">
+        <v>151</v>
+      </c>
+      <c r="L97" t="s">
+        <v>1136</v>
+      </c>
+      <c r="M97" t="s">
+        <v>33</v>
+      </c>
+      <c r="N97" t="s">
+        <v>1165</v>
+      </c>
+      <c r="O97" t="s">
+        <v>1598</v>
+      </c>
+      <c r="P97" t="s">
+        <v>1599</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>17</v>
+      </c>
+      <c r="B98">
+        <v>8</v>
+      </c>
+      <c r="C98">
+        <v>5</v>
+      </c>
+      <c r="D98" t="s">
+        <v>1601</v>
+      </c>
+      <c r="E98" t="s">
+        <v>1602</v>
+      </c>
+      <c r="F98" t="s">
+        <v>1603</v>
+      </c>
+      <c r="G98" t="s">
+        <v>1164</v>
+      </c>
+      <c r="J98" t="s">
+        <v>32</v>
+      </c>
+      <c r="K98" t="s">
+        <v>151</v>
+      </c>
+      <c r="L98" t="s">
+        <v>1136</v>
+      </c>
+      <c r="M98" t="s">
+        <v>33</v>
+      </c>
+      <c r="N98" t="s">
+        <v>1165</v>
+      </c>
+      <c r="O98" t="s">
+        <v>1604</v>
+      </c>
+      <c r="P98" t="s">
+        <v>1605</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>1606</v>
       </c>
     </row>
   </sheetData>

--- a/hunt/board.xlsx
+++ b/hunt/board.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4324" uniqueCount="1607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4441" uniqueCount="1646">
   <si>
     <t>Column</t>
   </si>
@@ -3500,6 +3500,114 @@
     <t>https://stripe.com/jobs/search?gh_jid=8090244</t>
   </si>
   <si>
+    <t>Orkes</t>
+  </si>
+  <si>
+    <t>2026-08-30T15:52:59.820Z</t>
+  </si>
+  <si>
+    <t>Solutions Architect title with enterprise customer-facing advisory model matching candidate's trusted-advisor Customer Engineer experience | Regulated-industry workflow customers (fintech, healthcare) align with candidate's HIPAA/PCI/SOX compliance architecture background | Salary band top ($200K) clears the $180K floor and role is fully remote US</t>
+  </si>
+  <si>
+    <t>Core product is Netflix Conductor / distributed event-driven workflow orchestration — candidate has no demonstrated depth in workflow orchestration engines or Java/microservices runtime internals | Emphasis on distributed systems infrastructure rather than Azure platform governance/CI-CD, which is candidate's strongest lane | Startup pre-sales SA scope may be below the principal-level scope the candidate is targeting</t>
+  </si>
+  <si>
+    <t>https://himalayas.app/companies/orkes/jobs/solutions-architect-680785132</t>
+  </si>
+  <si>
+    <t>Principal Solutions Architect</t>
+  </si>
+  <si>
+    <t>Leidos</t>
+  </si>
+  <si>
+    <t>Principal-level scope and public sector/DoD modernization work is a strong industry precedent for compliance-driven architecture (NIST, FIPS) | 100% remote with only occasional Reston, VA travel; band tops out at $237K</t>
+  </si>
+  <si>
+    <t>Hard requirement for an active DoD Secret clearance, which the candidate does not hold — effectively disqualifying at application stage | DoDNet/enterprise IT service portfolio focus is more program-engineering than Azure DevOps/GitHub platform work | Lower end of band ($131K) is well below the $180K floor, so offer level is uncertain</t>
+  </si>
+  <si>
+    <t>https://himalayas.app/companies/leidos/jobs/principal-solutions-architect-6018211811</t>
+  </si>
+  <si>
+    <t>Salesforce Data Cloud &amp; AI Architect Senior Manager</t>
+  </si>
+  <si>
+    <t>Accenture</t>
+  </si>
+  <si>
+    <t>Senior Manager scope and enterprise architecture advisory model align with candidate's consultative engagement experience | Very wide band reaching $302K and Life Sciences (regulated) client base</t>
+  </si>
+  <si>
+    <t>Requires deep Salesforce Data Cloud / Einstein / CRM platform architecture expertise — candidate has none of this stack | Data &amp; AI architecture on Salesforce is unrelated to candidate's Azure DevOps/GitHub/governance specialty | Accenture typically expects Salesforce certifications and prior consulting-at-Accenture-level Salesforce delivery history</t>
+  </si>
+  <si>
+    <t>https://himalayas.app/companies/accenture/jobs/salesforce-data-cloud-ai-architect-senior-manager</t>
+  </si>
+  <si>
+    <t>Azure Architect</t>
+  </si>
+  <si>
+    <t>Explicitly Azure-centric architect role with enterprise cloud governance and DevSecOps mindset — near-direct match to candidate's Azure Policy/CAF/WAF and pipeline security work | Regulated enterprise environment focus maps to candidate's HIPAA/PCI/SOX/NIST compliance architecture experience | Lead/strategic-oversight scope matches the principal-level target; AWS depth is covered by a partner architect, not required of this role</t>
+  </si>
+  <si>
+    <t>Contingent on contract award — timeline and existence of the role are uncertain | Application modernization portfolio analysis (COTS/custom, on-prem migration) is adjacent to but not identical to candidate's DevOps platform emphasis | Band midpoint sits near the $180K floor; top of $202K leaves limited premium</t>
+  </si>
+  <si>
+    <t>https://himalayas.app/companies/icf/jobs/azure-architect</t>
+  </si>
+  <si>
+    <t>Cloud-Native Architect</t>
+  </si>
+  <si>
+    <t>10+ years experience requirement matches candidate exactly, and role is 100% remote direct W2 | Cloud-native platform and consulting delivery context fits candidate's advisory/architecture background</t>
+  </si>
+  <si>
+    <t>Requires 10+ years of software engineering with distributed systems design depth — candidate's background is platform/DevOps rather than product software engineering | Max salary of $180K only just meets the floor with zero upside | Staffing/consulting firm posting; vague on stack and likely client-dependent scope below principal level</t>
+  </si>
+  <si>
+    <t>https://himalayas.app/companies/bright-vision-technologies/jobs/cloud-native-architect-4954920767</t>
+  </si>
+  <si>
+    <t>Sr. Platform Engineer (Infra Pod)</t>
+  </si>
+  <si>
+    <t>Pair Team</t>
+  </si>
+  <si>
+    <t>Salary band $180K–$220K fully clears the floor with real upside, fully remote | Healthcare/Medicaid environment plays directly to candidate's HIPAA-driven compliance architecture experience | Platform/infra engineering with IaC and CI/CD overlaps candidate's Terraform, pipelines, and automation skill set</t>
+  </si>
+  <si>
+    <t>Hands-on senior IC platform engineering, not architecture/advisory — likely below candidate's targeted principal scope | Healthcare startups on this stack typically run AWS-primary infra; candidate's depth is Azure | Deep production Kubernetes/observability ownership may exceed candidate's demonstrated hands-on runtime experience</t>
+  </si>
+  <si>
+    <t>https://himalayas.app/companies/pair-team/jobs/sr-platform-engineer-infra-pod</t>
+  </si>
+  <si>
+    <t>Sr Staff AI Platform Engineer</t>
+  </si>
+  <si>
+    <t>wex</t>
+  </si>
+  <si>
+    <t>Compensation of $220K–$255K is well above the candidate's floor and remote US | Fintech/payments enterprise environment matches candidate's financial-services compliance precedent | Agentic AI / Copilot-adjacent platform strategy connects to candidate's GitHub Copilot and Agentic DevOps enablement work</t>
+  </si>
+  <si>
+    <t>Explicitly a Systems Architect with distributed systems and systems programming core expertise — candidate is not a systems-programming or data-orchestration engineer | Requires building SDKs, engines, and retrieval infrastructure (hands-on deep software engineering), not governance/CI-CD advisory | Multi-cloud compute optimization implies AWS/GCP depth beyond candidate's Azure focus</t>
+  </si>
+  <si>
+    <t>https://himalayas.app/companies/wex/jobs/sr-staff-ai-platform-engineer</t>
+  </si>
+  <si>
+    <t>Confirmed $180K base meeting the salary floor, plus remote flexibility beyond Central US | Enterprise SA role owning technical strategy for major accounts is a direct analog to candidate's current Customer Engineer advisory scope | Databricks brand and enterprise-account exposure would strengthen a solutions-architecture career track</t>
+  </si>
+  <si>
+    <t>Requires track record with data platforms and ML/AI adoption use cases; candidate's portfolio is Azure DevOps/GitHub governance, not lakehouse/Spark | Pre-sales value-selling orientation is a tradeoff against candidate's hands-on technical delivery strengths | Non-principal SA level may be a lateral or slight step down in scope</t>
+  </si>
+  <si>
+    <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8633227002</t>
+  </si>
+  <si>
     <t>Principal AI Ecosystem Architect - OpenAI/Anthropic</t>
   </si>
   <si>
@@ -4442,9 +4550,6 @@
     <t>https://www.mongodb.com/careers/job/?gh_jid=7847296</t>
   </si>
   <si>
-    <t>Principal Solutions Architect</t>
-  </si>
-  <si>
     <t>Principal-level scope aligns with candidate's target titles | Legacy application modernization and GenAI-tooling work overlaps with candidate's Copilot/Agentic DevOps exposure</t>
   </si>
   <si>
@@ -4833,6 +4938,18 @@
   </si>
   <si>
     <t>https://www.arbeitnow.com/jobs/companies/cbs-corporate-business-solutions-gmbh/senior-abap-developer-architect-produktentwicklung-heidelberg-178660</t>
+  </si>
+  <si>
+    <t>Central - United States; Northeast - United States; Southeast - United States</t>
+  </si>
+  <si>
+    <t>Senior pre-sales SA role with technical strategy ownership for largest enterprise accounts — mirrors candidate's Customer Engineer trusted-advisor engagement model | Enterprise-scale technical account leadership aligns with candidate's advisory and DevOps maturity assessment work</t>
+  </si>
+  <si>
+    <t>Requires demonstrated ML/AI use-case fluency and Databricks/Spark data platform depth the candidate does not list | Quota-adjacent pre-sales motion with value selling emphasis; less of the governance/CI-CD delivery work candidate excels at | Workplace type unknown and location is regional East/Central — may require in-territory presence</t>
+  </si>
+  <si>
+    <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8567957002</t>
   </si>
 </sst>
 </file>
@@ -5213,7 +5330,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q234"/>
+  <dimension ref="A1:Q242"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -16954,6 +17071,430 @@
         <v>1161</v>
       </c>
     </row>
+    <row r="235" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>17</v>
+      </c>
+      <c r="B235">
+        <v>58</v>
+      </c>
+      <c r="C235">
+        <v>55</v>
+      </c>
+      <c r="D235" t="s">
+        <v>413</v>
+      </c>
+      <c r="E235" t="s">
+        <v>1162</v>
+      </c>
+      <c r="F235" t="s">
+        <v>20</v>
+      </c>
+      <c r="G235" t="s">
+        <v>21</v>
+      </c>
+      <c r="H235">
+        <v>160000</v>
+      </c>
+      <c r="I235">
+        <v>200000</v>
+      </c>
+      <c r="J235" t="s">
+        <v>22</v>
+      </c>
+      <c r="K235" t="s">
+        <v>23</v>
+      </c>
+      <c r="L235" t="s">
+        <v>1163</v>
+      </c>
+      <c r="M235" t="s">
+        <v>39</v>
+      </c>
+      <c r="N235" t="s">
+        <v>26</v>
+      </c>
+      <c r="O235" t="s">
+        <v>1164</v>
+      </c>
+      <c r="P235" t="s">
+        <v>1165</v>
+      </c>
+      <c r="Q235" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="236" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>17</v>
+      </c>
+      <c r="B236">
+        <v>45</v>
+      </c>
+      <c r="C236">
+        <v>25</v>
+      </c>
+      <c r="D236" t="s">
+        <v>1167</v>
+      </c>
+      <c r="E236" t="s">
+        <v>1168</v>
+      </c>
+      <c r="F236" t="s">
+        <v>20</v>
+      </c>
+      <c r="G236" t="s">
+        <v>21</v>
+      </c>
+      <c r="H236">
+        <v>131300</v>
+      </c>
+      <c r="I236">
+        <v>237350</v>
+      </c>
+      <c r="J236" t="s">
+        <v>22</v>
+      </c>
+      <c r="K236" t="s">
+        <v>23</v>
+      </c>
+      <c r="L236" t="s">
+        <v>1163</v>
+      </c>
+      <c r="M236" t="s">
+        <v>33</v>
+      </c>
+      <c r="N236" t="s">
+        <v>26</v>
+      </c>
+      <c r="O236" t="s">
+        <v>1169</v>
+      </c>
+      <c r="P236" t="s">
+        <v>1170</v>
+      </c>
+      <c r="Q236" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="237" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>17</v>
+      </c>
+      <c r="B237">
+        <v>30</v>
+      </c>
+      <c r="C237">
+        <v>20</v>
+      </c>
+      <c r="D237" t="s">
+        <v>1172</v>
+      </c>
+      <c r="E237" t="s">
+        <v>1173</v>
+      </c>
+      <c r="F237" t="s">
+        <v>20</v>
+      </c>
+      <c r="G237" t="s">
+        <v>21</v>
+      </c>
+      <c r="H237">
+        <v>112900</v>
+      </c>
+      <c r="I237">
+        <v>302400</v>
+      </c>
+      <c r="J237" t="s">
+        <v>22</v>
+      </c>
+      <c r="K237" t="s">
+        <v>23</v>
+      </c>
+      <c r="L237" t="s">
+        <v>1163</v>
+      </c>
+      <c r="M237" t="s">
+        <v>33</v>
+      </c>
+      <c r="N237" t="s">
+        <v>26</v>
+      </c>
+      <c r="O237" t="s">
+        <v>1174</v>
+      </c>
+      <c r="P237" t="s">
+        <v>1175</v>
+      </c>
+      <c r="Q237" t="s">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="238" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>17</v>
+      </c>
+      <c r="B238">
+        <v>82</v>
+      </c>
+      <c r="C238">
+        <v>85</v>
+      </c>
+      <c r="D238" t="s">
+        <v>1177</v>
+      </c>
+      <c r="E238" t="s">
+        <v>540</v>
+      </c>
+      <c r="F238" t="s">
+        <v>20</v>
+      </c>
+      <c r="G238" t="s">
+        <v>21</v>
+      </c>
+      <c r="H238">
+        <v>119323</v>
+      </c>
+      <c r="I238">
+        <v>202850</v>
+      </c>
+      <c r="J238" t="s">
+        <v>22</v>
+      </c>
+      <c r="K238" t="s">
+        <v>23</v>
+      </c>
+      <c r="L238" t="s">
+        <v>1163</v>
+      </c>
+      <c r="M238" t="s">
+        <v>593</v>
+      </c>
+      <c r="N238" t="s">
+        <v>26</v>
+      </c>
+      <c r="O238" t="s">
+        <v>1178</v>
+      </c>
+      <c r="P238" t="s">
+        <v>1179</v>
+      </c>
+      <c r="Q238" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="239" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>17</v>
+      </c>
+      <c r="B239">
+        <v>45</v>
+      </c>
+      <c r="C239">
+        <v>55</v>
+      </c>
+      <c r="D239" t="s">
+        <v>1181</v>
+      </c>
+      <c r="E239" t="s">
+        <v>19</v>
+      </c>
+      <c r="F239" t="s">
+        <v>20</v>
+      </c>
+      <c r="G239" t="s">
+        <v>21</v>
+      </c>
+      <c r="H239">
+        <v>130000</v>
+      </c>
+      <c r="I239">
+        <v>180000</v>
+      </c>
+      <c r="J239" t="s">
+        <v>22</v>
+      </c>
+      <c r="K239" t="s">
+        <v>23</v>
+      </c>
+      <c r="L239" t="s">
+        <v>1163</v>
+      </c>
+      <c r="M239" t="s">
+        <v>39</v>
+      </c>
+      <c r="N239" t="s">
+        <v>26</v>
+      </c>
+      <c r="O239" t="s">
+        <v>1182</v>
+      </c>
+      <c r="P239" t="s">
+        <v>1183</v>
+      </c>
+      <c r="Q239" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="240" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>17</v>
+      </c>
+      <c r="B240">
+        <v>62</v>
+      </c>
+      <c r="C240">
+        <v>58</v>
+      </c>
+      <c r="D240" t="s">
+        <v>1185</v>
+      </c>
+      <c r="E240" t="s">
+        <v>1186</v>
+      </c>
+      <c r="F240" t="s">
+        <v>20</v>
+      </c>
+      <c r="G240" t="s">
+        <v>21</v>
+      </c>
+      <c r="H240">
+        <v>180000</v>
+      </c>
+      <c r="I240">
+        <v>220000</v>
+      </c>
+      <c r="J240" t="s">
+        <v>22</v>
+      </c>
+      <c r="K240" t="s">
+        <v>23</v>
+      </c>
+      <c r="L240" t="s">
+        <v>1163</v>
+      </c>
+      <c r="M240" t="s">
+        <v>39</v>
+      </c>
+      <c r="N240" t="s">
+        <v>26</v>
+      </c>
+      <c r="O240" t="s">
+        <v>1187</v>
+      </c>
+      <c r="P240" t="s">
+        <v>1188</v>
+      </c>
+      <c r="Q240" t="s">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="241" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>17</v>
+      </c>
+      <c r="B241">
+        <v>58</v>
+      </c>
+      <c r="C241">
+        <v>45</v>
+      </c>
+      <c r="D241" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E241" t="s">
+        <v>1191</v>
+      </c>
+      <c r="F241" t="s">
+        <v>20</v>
+      </c>
+      <c r="G241" t="s">
+        <v>21</v>
+      </c>
+      <c r="H241">
+        <v>220000</v>
+      </c>
+      <c r="I241">
+        <v>255800</v>
+      </c>
+      <c r="J241" t="s">
+        <v>22</v>
+      </c>
+      <c r="K241" t="s">
+        <v>23</v>
+      </c>
+      <c r="L241" t="s">
+        <v>1163</v>
+      </c>
+      <c r="M241" t="s">
+        <v>39</v>
+      </c>
+      <c r="N241" t="s">
+        <v>26</v>
+      </c>
+      <c r="O241" t="s">
+        <v>1192</v>
+      </c>
+      <c r="P241" t="s">
+        <v>1193</v>
+      </c>
+      <c r="Q241" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="242" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>17</v>
+      </c>
+      <c r="B242">
+        <v>55</v>
+      </c>
+      <c r="C242">
+        <v>48</v>
+      </c>
+      <c r="D242" t="s">
+        <v>413</v>
+      </c>
+      <c r="E242" t="s">
+        <v>49</v>
+      </c>
+      <c r="F242" t="s">
+        <v>757</v>
+      </c>
+      <c r="G242" t="s">
+        <v>21</v>
+      </c>
+      <c r="H242">
+        <v>180000</v>
+      </c>
+      <c r="I242">
+        <v>180000</v>
+      </c>
+      <c r="J242" t="s">
+        <v>22</v>
+      </c>
+      <c r="K242" t="s">
+        <v>51</v>
+      </c>
+      <c r="L242" t="s">
+        <v>1163</v>
+      </c>
+      <c r="M242" t="s">
+        <v>39</v>
+      </c>
+      <c r="N242" t="s">
+        <v>26</v>
+      </c>
+      <c r="O242" t="s">
+        <v>1195</v>
+      </c>
+      <c r="P242" t="s">
+        <v>1196</v>
+      </c>
+      <c r="Q242" t="s">
+        <v>1197</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:Q1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16963,7 +17504,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q98"/>
+  <dimension ref="A1:Q99"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -17044,16 +17585,16 @@
         <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>1162</v>
+        <v>1198</v>
       </c>
       <c r="E2" t="s">
-        <v>1163</v>
+        <v>1199</v>
       </c>
       <c r="F2" t="s">
         <v>1023</v>
       </c>
       <c r="G2" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="H2">
         <v>184200</v>
@@ -17074,16 +17615,16 @@
         <v>33</v>
       </c>
       <c r="N2" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O2" t="s">
-        <v>1166</v>
+        <v>1202</v>
       </c>
       <c r="P2" t="s">
-        <v>1167</v>
+        <v>1203</v>
       </c>
       <c r="Q2" t="s">
-        <v>1168</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -17103,10 +17644,10 @@
         <v>1008</v>
       </c>
       <c r="F3" t="s">
-        <v>1169</v>
+        <v>1205</v>
       </c>
       <c r="G3" t="s">
-        <v>1170</v>
+        <v>1206</v>
       </c>
       <c r="J3" t="s">
         <v>32</v>
@@ -17121,16 +17662,16 @@
         <v>33</v>
       </c>
       <c r="N3" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O3" t="s">
-        <v>1171</v>
+        <v>1207</v>
       </c>
       <c r="P3" t="s">
-        <v>1172</v>
+        <v>1208</v>
       </c>
       <c r="Q3" t="s">
-        <v>1173</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
@@ -17144,16 +17685,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>1174</v>
+        <v>1210</v>
       </c>
       <c r="E4" t="s">
         <v>798</v>
       </c>
       <c r="F4" t="s">
-        <v>1175</v>
+        <v>1211</v>
       </c>
       <c r="G4" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="J4" t="s">
         <v>32</v>
@@ -17168,16 +17709,16 @@
         <v>33</v>
       </c>
       <c r="N4" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O4" t="s">
-        <v>1176</v>
+        <v>1212</v>
       </c>
       <c r="P4" t="s">
-        <v>1177</v>
+        <v>1213</v>
       </c>
       <c r="Q4" t="s">
-        <v>1178</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -17191,16 +17732,16 @@
         <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>1179</v>
+        <v>1215</v>
       </c>
       <c r="E5" t="s">
         <v>798</v>
       </c>
       <c r="F5" t="s">
-        <v>1180</v>
+        <v>1216</v>
       </c>
       <c r="G5" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="J5" t="s">
         <v>32</v>
@@ -17215,16 +17756,16 @@
         <v>33</v>
       </c>
       <c r="N5" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O5" t="s">
-        <v>1181</v>
+        <v>1217</v>
       </c>
       <c r="P5" t="s">
-        <v>1182</v>
+        <v>1218</v>
       </c>
       <c r="Q5" t="s">
-        <v>1183</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -17238,16 +17779,16 @@
         <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>1184</v>
+        <v>1220</v>
       </c>
       <c r="E6" t="s">
         <v>49</v>
       </c>
       <c r="F6" t="s">
-        <v>1169</v>
+        <v>1205</v>
       </c>
       <c r="G6" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="J6" t="s">
         <v>32</v>
@@ -17262,16 +17803,16 @@
         <v>39</v>
       </c>
       <c r="N6" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O6" t="s">
-        <v>1185</v>
+        <v>1221</v>
       </c>
       <c r="P6" t="s">
-        <v>1186</v>
+        <v>1222</v>
       </c>
       <c r="Q6" t="s">
-        <v>1187</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -17285,16 +17826,16 @@
         <v>48</v>
       </c>
       <c r="D7" t="s">
-        <v>1188</v>
+        <v>1224</v>
       </c>
       <c r="E7" t="s">
-        <v>1189</v>
+        <v>1225</v>
       </c>
       <c r="F7" t="s">
-        <v>1190</v>
+        <v>1226</v>
       </c>
       <c r="G7" t="s">
-        <v>1170</v>
+        <v>1206</v>
       </c>
       <c r="J7" t="s">
         <v>32</v>
@@ -17309,16 +17850,16 @@
         <v>33</v>
       </c>
       <c r="N7" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O7" t="s">
-        <v>1191</v>
+        <v>1227</v>
       </c>
       <c r="P7" t="s">
-        <v>1192</v>
+        <v>1228</v>
       </c>
       <c r="Q7" t="s">
-        <v>1193</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -17332,16 +17873,16 @@
         <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>1194</v>
+        <v>1230</v>
       </c>
       <c r="E8" t="s">
-        <v>1195</v>
+        <v>1231</v>
       </c>
       <c r="F8" t="s">
-        <v>1196</v>
+        <v>1232</v>
       </c>
       <c r="G8" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="J8" t="s">
         <v>32</v>
@@ -17356,16 +17897,16 @@
         <v>33</v>
       </c>
       <c r="N8" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O8" t="s">
-        <v>1197</v>
+        <v>1233</v>
       </c>
       <c r="P8" t="s">
-        <v>1198</v>
+        <v>1234</v>
       </c>
       <c r="Q8" t="s">
-        <v>1199</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -17379,7 +17920,7 @@
         <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>1200</v>
+        <v>1236</v>
       </c>
       <c r="E9" t="s">
         <v>49</v>
@@ -17388,7 +17929,7 @@
         <v>20</v>
       </c>
       <c r="G9" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="H9">
         <v>217800</v>
@@ -17409,16 +17950,16 @@
         <v>39</v>
       </c>
       <c r="N9" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O9" t="s">
-        <v>1201</v>
+        <v>1237</v>
       </c>
       <c r="P9" t="s">
-        <v>1202</v>
+        <v>1238</v>
       </c>
       <c r="Q9" t="s">
-        <v>1203</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -17432,16 +17973,16 @@
         <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>1204</v>
+        <v>1240</v>
       </c>
       <c r="E10" t="s">
         <v>49</v>
       </c>
       <c r="F10" t="s">
-        <v>1205</v>
+        <v>1241</v>
       </c>
       <c r="G10" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="H10">
         <v>219100</v>
@@ -17462,16 +18003,16 @@
         <v>39</v>
       </c>
       <c r="N10" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O10" t="s">
-        <v>1206</v>
+        <v>1242</v>
       </c>
       <c r="P10" t="s">
-        <v>1207</v>
+        <v>1243</v>
       </c>
       <c r="Q10" t="s">
-        <v>1208</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -17491,10 +18032,10 @@
         <v>1008</v>
       </c>
       <c r="F11" t="s">
-        <v>1209</v>
+        <v>1245</v>
       </c>
       <c r="G11" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="J11" t="s">
         <v>32</v>
@@ -17509,16 +18050,16 @@
         <v>33</v>
       </c>
       <c r="N11" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O11" t="s">
-        <v>1210</v>
+        <v>1246</v>
       </c>
       <c r="P11" t="s">
-        <v>1211</v>
+        <v>1247</v>
       </c>
       <c r="Q11" t="s">
-        <v>1212</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -17532,16 +18073,16 @@
         <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>1213</v>
+        <v>1249</v>
       </c>
       <c r="E12" t="s">
-        <v>1214</v>
+        <v>1250</v>
       </c>
       <c r="F12" t="s">
-        <v>1215</v>
+        <v>1251</v>
       </c>
       <c r="G12" t="s">
-        <v>1170</v>
+        <v>1206</v>
       </c>
       <c r="J12" t="s">
         <v>32</v>
@@ -17556,16 +18097,16 @@
         <v>33</v>
       </c>
       <c r="N12" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O12" t="s">
-        <v>1216</v>
+        <v>1252</v>
       </c>
       <c r="P12" t="s">
-        <v>1217</v>
+        <v>1253</v>
       </c>
       <c r="Q12" t="s">
-        <v>1218</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
@@ -17579,16 +18120,16 @@
         <v>35</v>
       </c>
       <c r="D13" t="s">
-        <v>1219</v>
+        <v>1255</v>
       </c>
       <c r="E13" t="s">
-        <v>1220</v>
+        <v>1256</v>
       </c>
       <c r="F13" t="s">
-        <v>1221</v>
+        <v>1257</v>
       </c>
       <c r="G13" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="J13" t="s">
         <v>32</v>
@@ -17603,16 +18144,16 @@
         <v>33</v>
       </c>
       <c r="N13" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O13" t="s">
-        <v>1222</v>
+        <v>1258</v>
       </c>
       <c r="P13" t="s">
-        <v>1223</v>
+        <v>1259</v>
       </c>
       <c r="Q13" t="s">
-        <v>1224</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
@@ -17626,16 +18167,16 @@
         <v>55</v>
       </c>
       <c r="D14" t="s">
-        <v>1225</v>
+        <v>1261</v>
       </c>
       <c r="E14" t="s">
-        <v>1220</v>
+        <v>1256</v>
       </c>
       <c r="F14" t="s">
-        <v>1226</v>
+        <v>1262</v>
       </c>
       <c r="G14" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="J14" t="s">
         <v>32</v>
@@ -17650,16 +18191,16 @@
         <v>33</v>
       </c>
       <c r="N14" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O14" t="s">
-        <v>1227</v>
+        <v>1263</v>
       </c>
       <c r="P14" t="s">
-        <v>1228</v>
+        <v>1264</v>
       </c>
       <c r="Q14" t="s">
-        <v>1229</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -17673,16 +18214,16 @@
         <v>40</v>
       </c>
       <c r="D15" t="s">
-        <v>1230</v>
+        <v>1266</v>
       </c>
       <c r="E15" t="s">
-        <v>1220</v>
+        <v>1256</v>
       </c>
       <c r="F15" t="s">
-        <v>1221</v>
+        <v>1257</v>
       </c>
       <c r="G15" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="J15" t="s">
         <v>32</v>
@@ -17697,16 +18238,16 @@
         <v>33</v>
       </c>
       <c r="N15" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O15" t="s">
-        <v>1231</v>
+        <v>1267</v>
       </c>
       <c r="P15" t="s">
-        <v>1232</v>
+        <v>1268</v>
       </c>
       <c r="Q15" t="s">
-        <v>1233</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
@@ -17720,16 +18261,16 @@
         <v>5</v>
       </c>
       <c r="D16" t="s">
-        <v>1234</v>
+        <v>1270</v>
       </c>
       <c r="E16" t="s">
-        <v>1235</v>
+        <v>1271</v>
       </c>
       <c r="F16" t="s">
-        <v>1236</v>
+        <v>1272</v>
       </c>
       <c r="G16" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="J16" t="s">
         <v>32</v>
@@ -17744,16 +18285,16 @@
         <v>33</v>
       </c>
       <c r="N16" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O16" t="s">
-        <v>1237</v>
+        <v>1273</v>
       </c>
       <c r="P16" t="s">
-        <v>1238</v>
+        <v>1274</v>
       </c>
       <c r="Q16" t="s">
-        <v>1239</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
@@ -17767,16 +18308,16 @@
         <v>45</v>
       </c>
       <c r="D17" t="s">
-        <v>1240</v>
+        <v>1276</v>
       </c>
       <c r="E17" t="s">
-        <v>1235</v>
+        <v>1271</v>
       </c>
       <c r="F17" t="s">
-        <v>1169</v>
+        <v>1205</v>
       </c>
       <c r="G17" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="J17" t="s">
         <v>32</v>
@@ -17791,16 +18332,16 @@
         <v>33</v>
       </c>
       <c r="N17" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O17" t="s">
-        <v>1241</v>
+        <v>1277</v>
       </c>
       <c r="P17" t="s">
-        <v>1242</v>
+        <v>1278</v>
       </c>
       <c r="Q17" t="s">
-        <v>1243</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
@@ -17814,16 +18355,16 @@
         <v>5</v>
       </c>
       <c r="D18" t="s">
-        <v>1244</v>
+        <v>1280</v>
       </c>
       <c r="E18" t="s">
-        <v>1235</v>
+        <v>1271</v>
       </c>
       <c r="F18" t="s">
-        <v>1236</v>
+        <v>1272</v>
       </c>
       <c r="G18" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="J18" t="s">
         <v>32</v>
@@ -17838,16 +18379,16 @@
         <v>33</v>
       </c>
       <c r="N18" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O18" t="s">
-        <v>1245</v>
+        <v>1281</v>
       </c>
       <c r="P18" t="s">
-        <v>1246</v>
+        <v>1282</v>
       </c>
       <c r="Q18" t="s">
-        <v>1247</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -17861,16 +18402,16 @@
         <v>5</v>
       </c>
       <c r="D19" t="s">
-        <v>1248</v>
+        <v>1284</v>
       </c>
       <c r="E19" t="s">
-        <v>1235</v>
+        <v>1271</v>
       </c>
       <c r="F19" t="s">
-        <v>1236</v>
+        <v>1272</v>
       </c>
       <c r="G19" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="J19" t="s">
         <v>32</v>
@@ -17885,16 +18426,16 @@
         <v>33</v>
       </c>
       <c r="N19" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O19" t="s">
-        <v>1249</v>
+        <v>1285</v>
       </c>
       <c r="P19" t="s">
-        <v>1250</v>
+        <v>1286</v>
       </c>
       <c r="Q19" t="s">
-        <v>1251</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -17908,16 +18449,16 @@
         <v>18</v>
       </c>
       <c r="D20" t="s">
-        <v>1252</v>
+        <v>1288</v>
       </c>
       <c r="E20" t="s">
-        <v>1235</v>
+        <v>1271</v>
       </c>
       <c r="F20" t="s">
-        <v>1236</v>
+        <v>1272</v>
       </c>
       <c r="G20" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="J20" t="s">
         <v>32</v>
@@ -17932,16 +18473,16 @@
         <v>33</v>
       </c>
       <c r="N20" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O20" t="s">
-        <v>1253</v>
+        <v>1289</v>
       </c>
       <c r="P20" t="s">
-        <v>1254</v>
+        <v>1290</v>
       </c>
       <c r="Q20" t="s">
-        <v>1255</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
@@ -17955,16 +18496,16 @@
         <v>5</v>
       </c>
       <c r="D21" t="s">
-        <v>1256</v>
+        <v>1292</v>
       </c>
       <c r="E21" t="s">
-        <v>1235</v>
+        <v>1271</v>
       </c>
       <c r="F21" t="s">
-        <v>1236</v>
+        <v>1272</v>
       </c>
       <c r="G21" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="J21" t="s">
         <v>32</v>
@@ -17979,16 +18520,16 @@
         <v>33</v>
       </c>
       <c r="N21" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O21" t="s">
-        <v>1257</v>
+        <v>1293</v>
       </c>
       <c r="P21" t="s">
-        <v>1258</v>
+        <v>1294</v>
       </c>
       <c r="Q21" t="s">
-        <v>1259</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -18002,16 +18543,16 @@
         <v>40</v>
       </c>
       <c r="D22" t="s">
-        <v>1260</v>
+        <v>1296</v>
       </c>
       <c r="E22" t="s">
-        <v>1235</v>
+        <v>1271</v>
       </c>
       <c r="F22" t="s">
-        <v>1236</v>
+        <v>1272</v>
       </c>
       <c r="G22" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="J22" t="s">
         <v>32</v>
@@ -18026,16 +18567,16 @@
         <v>33</v>
       </c>
       <c r="N22" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O22" t="s">
-        <v>1261</v>
+        <v>1297</v>
       </c>
       <c r="P22" t="s">
-        <v>1262</v>
+        <v>1298</v>
       </c>
       <c r="Q22" t="s">
-        <v>1263</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
@@ -18049,16 +18590,16 @@
         <v>45</v>
       </c>
       <c r="D23" t="s">
-        <v>1264</v>
+        <v>1300</v>
       </c>
       <c r="E23" t="s">
-        <v>1235</v>
+        <v>1271</v>
       </c>
       <c r="F23" t="s">
-        <v>1236</v>
+        <v>1272</v>
       </c>
       <c r="G23" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="J23" t="s">
         <v>32</v>
@@ -18073,16 +18614,16 @@
         <v>33</v>
       </c>
       <c r="N23" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O23" t="s">
-        <v>1265</v>
+        <v>1301</v>
       </c>
       <c r="P23" t="s">
-        <v>1266</v>
+        <v>1302</v>
       </c>
       <c r="Q23" t="s">
-        <v>1267</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
@@ -18096,16 +18637,16 @@
         <v>3</v>
       </c>
       <c r="D24" t="s">
-        <v>1268</v>
+        <v>1304</v>
       </c>
       <c r="E24" t="s">
-        <v>1235</v>
+        <v>1271</v>
       </c>
       <c r="F24" t="s">
-        <v>1236</v>
+        <v>1272</v>
       </c>
       <c r="G24" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="J24" t="s">
         <v>32</v>
@@ -18120,16 +18661,16 @@
         <v>33</v>
       </c>
       <c r="N24" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O24" t="s">
-        <v>1269</v>
+        <v>1305</v>
       </c>
       <c r="P24" t="s">
-        <v>1270</v>
+        <v>1306</v>
       </c>
       <c r="Q24" t="s">
-        <v>1271</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
@@ -18143,7 +18684,7 @@
         <v>42</v>
       </c>
       <c r="D25" t="s">
-        <v>1272</v>
+        <v>1308</v>
       </c>
       <c r="E25" t="s">
         <v>49</v>
@@ -18152,7 +18693,7 @@
         <v>20</v>
       </c>
       <c r="G25" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="J25" t="s">
         <v>32</v>
@@ -18167,16 +18708,16 @@
         <v>33</v>
       </c>
       <c r="N25" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O25" t="s">
-        <v>1273</v>
+        <v>1309</v>
       </c>
       <c r="P25" t="s">
-        <v>1274</v>
+        <v>1310</v>
       </c>
       <c r="Q25" t="s">
-        <v>1275</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
@@ -18190,7 +18731,7 @@
         <v>40</v>
       </c>
       <c r="D26" t="s">
-        <v>1276</v>
+        <v>1312</v>
       </c>
       <c r="E26" t="s">
         <v>49</v>
@@ -18199,7 +18740,7 @@
         <v>20</v>
       </c>
       <c r="G26" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="J26" t="s">
         <v>32</v>
@@ -18214,16 +18755,16 @@
         <v>33</v>
       </c>
       <c r="N26" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O26" t="s">
-        <v>1277</v>
+        <v>1313</v>
       </c>
       <c r="P26" t="s">
-        <v>1278</v>
+        <v>1314</v>
       </c>
       <c r="Q26" t="s">
-        <v>1279</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
@@ -18243,10 +18784,10 @@
         <v>49</v>
       </c>
       <c r="F27" t="s">
-        <v>1280</v>
+        <v>1316</v>
       </c>
       <c r="G27" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="H27">
         <v>180000</v>
@@ -18267,16 +18808,16 @@
         <v>39</v>
       </c>
       <c r="N27" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O27" t="s">
-        <v>1281</v>
+        <v>1317</v>
       </c>
       <c r="P27" t="s">
-        <v>1282</v>
+        <v>1318</v>
       </c>
       <c r="Q27" t="s">
-        <v>1283</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
@@ -18290,7 +18831,7 @@
         <v>52</v>
       </c>
       <c r="D28" t="s">
-        <v>1284</v>
+        <v>1320</v>
       </c>
       <c r="E28" t="s">
         <v>49</v>
@@ -18299,7 +18840,7 @@
         <v>20</v>
       </c>
       <c r="G28" t="s">
-        <v>1170</v>
+        <v>1206</v>
       </c>
       <c r="H28">
         <v>180000</v>
@@ -18320,16 +18861,16 @@
         <v>39</v>
       </c>
       <c r="N28" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O28" t="s">
-        <v>1285</v>
+        <v>1321</v>
       </c>
       <c r="P28" t="s">
-        <v>1286</v>
+        <v>1322</v>
       </c>
       <c r="Q28" t="s">
-        <v>1287</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
@@ -18343,7 +18884,7 @@
         <v>55</v>
       </c>
       <c r="D29" t="s">
-        <v>1288</v>
+        <v>1324</v>
       </c>
       <c r="E29" t="s">
         <v>49</v>
@@ -18352,7 +18893,7 @@
         <v>20</v>
       </c>
       <c r="G29" t="s">
-        <v>1170</v>
+        <v>1206</v>
       </c>
       <c r="H29">
         <v>180000</v>
@@ -18373,16 +18914,16 @@
         <v>39</v>
       </c>
       <c r="N29" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O29" t="s">
-        <v>1289</v>
+        <v>1325</v>
       </c>
       <c r="P29" t="s">
-        <v>1290</v>
+        <v>1326</v>
       </c>
       <c r="Q29" t="s">
-        <v>1291</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
@@ -18396,16 +18937,16 @@
         <v>48</v>
       </c>
       <c r="D30" t="s">
-        <v>1292</v>
+        <v>1328</v>
       </c>
       <c r="E30" t="s">
         <v>49</v>
       </c>
       <c r="F30" t="s">
-        <v>1293</v>
+        <v>1329</v>
       </c>
       <c r="G30" t="s">
-        <v>1170</v>
+        <v>1206</v>
       </c>
       <c r="H30">
         <v>219100</v>
@@ -18426,16 +18967,16 @@
         <v>39</v>
       </c>
       <c r="N30" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O30" t="s">
-        <v>1294</v>
+        <v>1330</v>
       </c>
       <c r="P30" t="s">
-        <v>1295</v>
+        <v>1331</v>
       </c>
       <c r="Q30" t="s">
-        <v>1296</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
@@ -18449,16 +18990,16 @@
         <v>45</v>
       </c>
       <c r="D31" t="s">
-        <v>1297</v>
+        <v>1333</v>
       </c>
       <c r="E31" t="s">
         <v>49</v>
       </c>
       <c r="F31" t="s">
-        <v>1298</v>
+        <v>1334</v>
       </c>
       <c r="G31" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="H31">
         <v>180000</v>
@@ -18479,16 +19020,16 @@
         <v>39</v>
       </c>
       <c r="N31" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O31" t="s">
-        <v>1299</v>
+        <v>1335</v>
       </c>
       <c r="P31" t="s">
-        <v>1300</v>
+        <v>1336</v>
       </c>
       <c r="Q31" t="s">
-        <v>1301</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
@@ -18502,7 +19043,7 @@
         <v>30</v>
       </c>
       <c r="D32" t="s">
-        <v>1302</v>
+        <v>1338</v>
       </c>
       <c r="E32" t="s">
         <v>49</v>
@@ -18511,7 +19052,7 @@
         <v>20</v>
       </c>
       <c r="G32" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="H32">
         <v>219100</v>
@@ -18532,16 +19073,16 @@
         <v>33</v>
       </c>
       <c r="N32" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O32" t="s">
-        <v>1303</v>
+        <v>1339</v>
       </c>
       <c r="P32" t="s">
-        <v>1304</v>
+        <v>1340</v>
       </c>
       <c r="Q32" t="s">
-        <v>1305</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
@@ -18555,7 +19096,7 @@
         <v>45</v>
       </c>
       <c r="D33" t="s">
-        <v>1306</v>
+        <v>1342</v>
       </c>
       <c r="E33" t="s">
         <v>49</v>
@@ -18564,7 +19105,7 @@
         <v>20</v>
       </c>
       <c r="G33" t="s">
-        <v>1170</v>
+        <v>1206</v>
       </c>
       <c r="H33">
         <v>219100</v>
@@ -18585,16 +19126,16 @@
         <v>39</v>
       </c>
       <c r="N33" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O33" t="s">
-        <v>1307</v>
+        <v>1343</v>
       </c>
       <c r="P33" t="s">
-        <v>1308</v>
+        <v>1344</v>
       </c>
       <c r="Q33" t="s">
-        <v>1309</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
@@ -18608,16 +19149,16 @@
         <v>30</v>
       </c>
       <c r="D34" t="s">
-        <v>1310</v>
+        <v>1346</v>
       </c>
       <c r="E34" t="s">
         <v>49</v>
       </c>
       <c r="F34" t="s">
-        <v>1311</v>
+        <v>1347</v>
       </c>
       <c r="G34" t="s">
-        <v>1170</v>
+        <v>1206</v>
       </c>
       <c r="J34" t="s">
         <v>32</v>
@@ -18632,16 +19173,16 @@
         <v>33</v>
       </c>
       <c r="N34" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O34" t="s">
-        <v>1312</v>
+        <v>1348</v>
       </c>
       <c r="P34" t="s">
-        <v>1313</v>
+        <v>1349</v>
       </c>
       <c r="Q34" t="s">
-        <v>1314</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
@@ -18655,16 +19196,16 @@
         <v>58</v>
       </c>
       <c r="D35" t="s">
-        <v>1315</v>
+        <v>1351</v>
       </c>
       <c r="E35" t="s">
-        <v>1316</v>
+        <v>1352</v>
       </c>
       <c r="F35" t="s">
-        <v>1317</v>
+        <v>1353</v>
       </c>
       <c r="G35" t="s">
-        <v>1170</v>
+        <v>1206</v>
       </c>
       <c r="H35">
         <v>257000</v>
@@ -18685,16 +19226,16 @@
         <v>39</v>
       </c>
       <c r="N35" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O35" t="s">
-        <v>1318</v>
+        <v>1354</v>
       </c>
       <c r="P35" t="s">
-        <v>1319</v>
+        <v>1355</v>
       </c>
       <c r="Q35" t="s">
-        <v>1320</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
@@ -18711,13 +19252,13 @@
         <v>478</v>
       </c>
       <c r="E36" t="s">
-        <v>1163</v>
+        <v>1199</v>
       </c>
       <c r="F36" t="s">
-        <v>1321</v>
+        <v>1357</v>
       </c>
       <c r="G36" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="H36">
         <v>200000</v>
@@ -18738,16 +19279,16 @@
         <v>33</v>
       </c>
       <c r="N36" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O36" t="s">
-        <v>1322</v>
+        <v>1358</v>
       </c>
       <c r="P36" t="s">
-        <v>1323</v>
+        <v>1359</v>
       </c>
       <c r="Q36" t="s">
-        <v>1324</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
@@ -18761,16 +19302,16 @@
         <v>20</v>
       </c>
       <c r="D37" t="s">
-        <v>1325</v>
+        <v>1361</v>
       </c>
       <c r="E37" t="s">
         <v>1008</v>
       </c>
       <c r="F37" t="s">
-        <v>1326</v>
+        <v>1362</v>
       </c>
       <c r="G37" t="s">
-        <v>1170</v>
+        <v>1206</v>
       </c>
       <c r="J37" t="s">
         <v>32</v>
@@ -18785,16 +19326,16 @@
         <v>33</v>
       </c>
       <c r="N37" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O37" t="s">
-        <v>1327</v>
+        <v>1363</v>
       </c>
       <c r="P37" t="s">
-        <v>1328</v>
+        <v>1364</v>
       </c>
       <c r="Q37" t="s">
-        <v>1329</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
@@ -18814,10 +19355,10 @@
         <v>1008</v>
       </c>
       <c r="F38" t="s">
-        <v>1330</v>
+        <v>1366</v>
       </c>
       <c r="G38" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="J38" t="s">
         <v>32</v>
@@ -18832,16 +19373,16 @@
         <v>33</v>
       </c>
       <c r="N38" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O38" t="s">
-        <v>1331</v>
+        <v>1367</v>
       </c>
       <c r="P38" t="s">
-        <v>1332</v>
+        <v>1368</v>
       </c>
       <c r="Q38" t="s">
-        <v>1333</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
@@ -18855,16 +19396,16 @@
         <v>15</v>
       </c>
       <c r="D39" t="s">
-        <v>1334</v>
+        <v>1370</v>
       </c>
       <c r="E39" t="s">
         <v>1008</v>
       </c>
       <c r="F39" t="s">
-        <v>1335</v>
+        <v>1371</v>
       </c>
       <c r="G39" t="s">
-        <v>1170</v>
+        <v>1206</v>
       </c>
       <c r="H39">
         <v>500000</v>
@@ -18885,16 +19426,16 @@
         <v>33</v>
       </c>
       <c r="N39" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O39" t="s">
-        <v>1336</v>
+        <v>1372</v>
       </c>
       <c r="P39" t="s">
-        <v>1337</v>
+        <v>1373</v>
       </c>
       <c r="Q39" t="s">
-        <v>1338</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
@@ -18908,16 +19449,16 @@
         <v>18</v>
       </c>
       <c r="D40" t="s">
-        <v>1339</v>
+        <v>1375</v>
       </c>
       <c r="E40" t="s">
         <v>798</v>
       </c>
       <c r="F40" t="s">
-        <v>1180</v>
+        <v>1216</v>
       </c>
       <c r="G40" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="H40">
         <v>274456</v>
@@ -18938,16 +19479,16 @@
         <v>33</v>
       </c>
       <c r="N40" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O40" t="s">
-        <v>1340</v>
+        <v>1376</v>
       </c>
       <c r="P40" t="s">
-        <v>1341</v>
+        <v>1377</v>
       </c>
       <c r="Q40" t="s">
-        <v>1342</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
@@ -18961,16 +19502,16 @@
         <v>30</v>
       </c>
       <c r="D41" t="s">
-        <v>1343</v>
+        <v>1379</v>
       </c>
       <c r="E41" t="s">
         <v>798</v>
       </c>
       <c r="F41" t="s">
-        <v>1344</v>
+        <v>1380</v>
       </c>
       <c r="G41" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="J41" t="s">
         <v>32</v>
@@ -18985,16 +19526,16 @@
         <v>33</v>
       </c>
       <c r="N41" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O41" t="s">
-        <v>1345</v>
+        <v>1381</v>
       </c>
       <c r="P41" t="s">
-        <v>1346</v>
+        <v>1382</v>
       </c>
       <c r="Q41" t="s">
-        <v>1347</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
@@ -19008,16 +19549,16 @@
         <v>22</v>
       </c>
       <c r="D42" t="s">
-        <v>1348</v>
+        <v>1384</v>
       </c>
       <c r="E42" t="s">
         <v>798</v>
       </c>
       <c r="F42" t="s">
-        <v>1349</v>
+        <v>1385</v>
       </c>
       <c r="G42" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="J42" t="s">
         <v>32</v>
@@ -19032,16 +19573,16 @@
         <v>33</v>
       </c>
       <c r="N42" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O42" t="s">
-        <v>1350</v>
+        <v>1386</v>
       </c>
       <c r="P42" t="s">
-        <v>1351</v>
+        <v>1387</v>
       </c>
       <c r="Q42" t="s">
-        <v>1352</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
@@ -19055,16 +19596,16 @@
         <v>48</v>
       </c>
       <c r="D43" t="s">
-        <v>1353</v>
+        <v>1389</v>
       </c>
       <c r="E43" t="s">
         <v>798</v>
       </c>
       <c r="F43" t="s">
-        <v>1354</v>
+        <v>1390</v>
       </c>
       <c r="G43" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="J43" t="s">
         <v>32</v>
@@ -19079,16 +19620,16 @@
         <v>39</v>
       </c>
       <c r="N43" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O43" t="s">
-        <v>1355</v>
+        <v>1391</v>
       </c>
       <c r="P43" t="s">
-        <v>1356</v>
+        <v>1392</v>
       </c>
       <c r="Q43" t="s">
-        <v>1357</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
@@ -19102,16 +19643,16 @@
         <v>25</v>
       </c>
       <c r="D44" t="s">
-        <v>1358</v>
+        <v>1394</v>
       </c>
       <c r="E44" t="s">
         <v>798</v>
       </c>
       <c r="F44" t="s">
-        <v>1169</v>
+        <v>1205</v>
       </c>
       <c r="G44" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="J44" t="s">
         <v>32</v>
@@ -19126,16 +19667,16 @@
         <v>33</v>
       </c>
       <c r="N44" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O44" t="s">
-        <v>1359</v>
+        <v>1395</v>
       </c>
       <c r="P44" t="s">
-        <v>1360</v>
+        <v>1396</v>
       </c>
       <c r="Q44" t="s">
-        <v>1361</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
@@ -19149,16 +19690,16 @@
         <v>40</v>
       </c>
       <c r="D45" t="s">
-        <v>1362</v>
+        <v>1398</v>
       </c>
       <c r="E45" t="s">
         <v>798</v>
       </c>
       <c r="F45" t="s">
-        <v>1363</v>
+        <v>1399</v>
       </c>
       <c r="G45" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="J45" t="s">
         <v>32</v>
@@ -19173,16 +19714,16 @@
         <v>33</v>
       </c>
       <c r="N45" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O45" t="s">
-        <v>1364</v>
+        <v>1400</v>
       </c>
       <c r="P45" t="s">
-        <v>1365</v>
+        <v>1401</v>
       </c>
       <c r="Q45" t="s">
-        <v>1366</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
@@ -19196,16 +19737,16 @@
         <v>70</v>
       </c>
       <c r="D46" t="s">
-        <v>1367</v>
+        <v>1403</v>
       </c>
       <c r="E46" t="s">
-        <v>1368</v>
+        <v>1404</v>
       </c>
       <c r="F46" t="s">
-        <v>1369</v>
+        <v>1405</v>
       </c>
       <c r="G46" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="J46" t="s">
         <v>32</v>
@@ -19220,16 +19761,16 @@
         <v>33</v>
       </c>
       <c r="N46" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O46" t="s">
-        <v>1370</v>
+        <v>1406</v>
       </c>
       <c r="P46" t="s">
-        <v>1371</v>
+        <v>1407</v>
       </c>
       <c r="Q46" t="s">
-        <v>1372</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
@@ -19243,16 +19784,16 @@
         <v>58</v>
       </c>
       <c r="D47" t="s">
-        <v>1373</v>
+        <v>1409</v>
       </c>
       <c r="E47" t="s">
-        <v>1374</v>
+        <v>1410</v>
       </c>
       <c r="F47" t="s">
-        <v>1169</v>
+        <v>1205</v>
       </c>
       <c r="G47" t="s">
-        <v>1170</v>
+        <v>1206</v>
       </c>
       <c r="J47" t="s">
         <v>32</v>
@@ -19267,16 +19808,16 @@
         <v>33</v>
       </c>
       <c r="N47" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O47" t="s">
-        <v>1375</v>
+        <v>1411</v>
       </c>
       <c r="P47" t="s">
-        <v>1376</v>
+        <v>1412</v>
       </c>
       <c r="Q47" t="s">
-        <v>1377</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
@@ -19290,16 +19831,16 @@
         <v>32</v>
       </c>
       <c r="D48" t="s">
-        <v>1378</v>
+        <v>1414</v>
       </c>
       <c r="E48" t="s">
-        <v>1379</v>
+        <v>1415</v>
       </c>
       <c r="F48" t="s">
-        <v>1380</v>
+        <v>1416</v>
       </c>
       <c r="G48" t="s">
-        <v>1170</v>
+        <v>1206</v>
       </c>
       <c r="J48" t="s">
         <v>32</v>
@@ -19314,16 +19855,16 @@
         <v>33</v>
       </c>
       <c r="N48" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O48" t="s">
-        <v>1381</v>
+        <v>1417</v>
       </c>
       <c r="P48" t="s">
-        <v>1382</v>
+        <v>1418</v>
       </c>
       <c r="Q48" t="s">
-        <v>1383</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
@@ -19337,16 +19878,16 @@
         <v>4</v>
       </c>
       <c r="D49" t="s">
-        <v>1384</v>
+        <v>1420</v>
       </c>
       <c r="E49" t="s">
-        <v>1385</v>
+        <v>1421</v>
       </c>
       <c r="F49" t="s">
-        <v>1386</v>
+        <v>1422</v>
       </c>
       <c r="G49" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="J49" t="s">
         <v>32</v>
@@ -19361,16 +19902,16 @@
         <v>33</v>
       </c>
       <c r="N49" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O49" t="s">
-        <v>1387</v>
+        <v>1423</v>
       </c>
       <c r="P49" t="s">
-        <v>1388</v>
+        <v>1424</v>
       </c>
       <c r="Q49" t="s">
-        <v>1389</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
@@ -19384,16 +19925,16 @@
         <v>25</v>
       </c>
       <c r="D50" t="s">
-        <v>1390</v>
+        <v>1426</v>
       </c>
       <c r="E50" t="s">
-        <v>1391</v>
+        <v>1427</v>
       </c>
       <c r="F50" t="s">
-        <v>1226</v>
+        <v>1262</v>
       </c>
       <c r="G50" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="J50" t="s">
         <v>32</v>
@@ -19408,16 +19949,16 @@
         <v>33</v>
       </c>
       <c r="N50" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O50" t="s">
-        <v>1392</v>
+        <v>1428</v>
       </c>
       <c r="P50" t="s">
-        <v>1393</v>
+        <v>1429</v>
       </c>
       <c r="Q50" t="s">
-        <v>1394</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
@@ -19431,16 +19972,16 @@
         <v>30</v>
       </c>
       <c r="D51" t="s">
-        <v>1395</v>
+        <v>1431</v>
       </c>
       <c r="E51" t="s">
-        <v>1396</v>
+        <v>1432</v>
       </c>
       <c r="F51" t="s">
-        <v>1397</v>
+        <v>1433</v>
       </c>
       <c r="G51" t="s">
-        <v>1170</v>
+        <v>1206</v>
       </c>
       <c r="J51" t="s">
         <v>32</v>
@@ -19455,16 +19996,16 @@
         <v>33</v>
       </c>
       <c r="N51" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O51" t="s">
-        <v>1398</v>
+        <v>1434</v>
       </c>
       <c r="P51" t="s">
-        <v>1399</v>
+        <v>1435</v>
       </c>
       <c r="Q51" t="s">
-        <v>1400</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
@@ -19478,16 +20019,16 @@
         <v>52</v>
       </c>
       <c r="D52" t="s">
-        <v>1401</v>
+        <v>1437</v>
       </c>
       <c r="E52" t="s">
         <v>49</v>
       </c>
       <c r="F52" t="s">
-        <v>1402</v>
+        <v>1438</v>
       </c>
       <c r="G52" t="s">
-        <v>1170</v>
+        <v>1206</v>
       </c>
       <c r="H52">
         <v>180000</v>
@@ -19508,16 +20049,16 @@
         <v>39</v>
       </c>
       <c r="N52" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O52" t="s">
-        <v>1403</v>
+        <v>1439</v>
       </c>
       <c r="P52" t="s">
-        <v>1404</v>
+        <v>1440</v>
       </c>
       <c r="Q52" t="s">
-        <v>1405</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
@@ -19531,7 +20072,7 @@
         <v>50</v>
       </c>
       <c r="D53" t="s">
-        <v>1406</v>
+        <v>1442</v>
       </c>
       <c r="E53" t="s">
         <v>49</v>
@@ -19540,7 +20081,7 @@
         <v>20</v>
       </c>
       <c r="G53" t="s">
-        <v>1170</v>
+        <v>1206</v>
       </c>
       <c r="H53">
         <v>180000</v>
@@ -19561,16 +20102,16 @@
         <v>39</v>
       </c>
       <c r="N53" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O53" t="s">
-        <v>1407</v>
+        <v>1443</v>
       </c>
       <c r="P53" t="s">
-        <v>1408</v>
+        <v>1444</v>
       </c>
       <c r="Q53" t="s">
-        <v>1409</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
@@ -19584,7 +20125,7 @@
         <v>46</v>
       </c>
       <c r="D54" t="s">
-        <v>1410</v>
+        <v>1446</v>
       </c>
       <c r="E54" t="s">
         <v>49</v>
@@ -19593,7 +20134,7 @@
         <v>20</v>
       </c>
       <c r="G54" t="s">
-        <v>1170</v>
+        <v>1206</v>
       </c>
       <c r="H54">
         <v>180000</v>
@@ -19614,16 +20155,16 @@
         <v>39</v>
       </c>
       <c r="N54" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O54" t="s">
-        <v>1411</v>
+        <v>1447</v>
       </c>
       <c r="P54" t="s">
-        <v>1412</v>
+        <v>1448</v>
       </c>
       <c r="Q54" t="s">
-        <v>1413</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
@@ -19637,7 +20178,7 @@
         <v>38</v>
       </c>
       <c r="D55" t="s">
-        <v>1414</v>
+        <v>1450</v>
       </c>
       <c r="E55" t="s">
         <v>49</v>
@@ -19646,7 +20187,7 @@
         <v>20</v>
       </c>
       <c r="G55" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="H55">
         <v>217800</v>
@@ -19667,16 +20208,16 @@
         <v>33</v>
       </c>
       <c r="N55" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O55" t="s">
-        <v>1415</v>
+        <v>1451</v>
       </c>
       <c r="P55" t="s">
-        <v>1416</v>
+        <v>1452</v>
       </c>
       <c r="Q55" t="s">
-        <v>1417</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
@@ -19696,10 +20237,10 @@
         <v>49</v>
       </c>
       <c r="F56" t="s">
-        <v>1418</v>
+        <v>1454</v>
       </c>
       <c r="G56" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="H56">
         <v>180000</v>
@@ -19720,16 +20261,16 @@
         <v>39</v>
       </c>
       <c r="N56" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O56" t="s">
-        <v>1419</v>
+        <v>1455</v>
       </c>
       <c r="P56" t="s">
-        <v>1420</v>
+        <v>1456</v>
       </c>
       <c r="Q56" t="s">
-        <v>1421</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
@@ -19743,16 +20284,16 @@
         <v>45</v>
       </c>
       <c r="D57" t="s">
-        <v>1422</v>
+        <v>1458</v>
       </c>
       <c r="E57" t="s">
         <v>49</v>
       </c>
       <c r="F57" t="s">
-        <v>1423</v>
+        <v>1459</v>
       </c>
       <c r="G57" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="H57">
         <v>219100</v>
@@ -19773,16 +20314,16 @@
         <v>39</v>
       </c>
       <c r="N57" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O57" t="s">
-        <v>1424</v>
+        <v>1460</v>
       </c>
       <c r="P57" t="s">
-        <v>1425</v>
+        <v>1461</v>
       </c>
       <c r="Q57" t="s">
-        <v>1426</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
@@ -19796,16 +20337,16 @@
         <v>42</v>
       </c>
       <c r="D58" t="s">
-        <v>1427</v>
+        <v>1463</v>
       </c>
       <c r="E58" t="s">
         <v>49</v>
       </c>
       <c r="F58" t="s">
-        <v>1428</v>
+        <v>1464</v>
       </c>
       <c r="G58" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="H58">
         <v>180000</v>
@@ -19826,16 +20367,16 @@
         <v>39</v>
       </c>
       <c r="N58" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O58" t="s">
-        <v>1429</v>
+        <v>1465</v>
       </c>
       <c r="P58" t="s">
-        <v>1430</v>
+        <v>1466</v>
       </c>
       <c r="Q58" t="s">
-        <v>1431</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
@@ -19849,7 +20390,7 @@
         <v>32</v>
       </c>
       <c r="D59" t="s">
-        <v>1432</v>
+        <v>1468</v>
       </c>
       <c r="E59" t="s">
         <v>49</v>
@@ -19858,7 +20399,7 @@
         <v>20</v>
       </c>
       <c r="G59" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="H59">
         <v>219100</v>
@@ -19879,16 +20420,16 @@
         <v>33</v>
       </c>
       <c r="N59" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O59" t="s">
-        <v>1433</v>
+        <v>1469</v>
       </c>
       <c r="P59" t="s">
-        <v>1434</v>
+        <v>1470</v>
       </c>
       <c r="Q59" t="s">
-        <v>1435</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
@@ -19902,7 +20443,7 @@
         <v>35</v>
       </c>
       <c r="D60" t="s">
-        <v>1436</v>
+        <v>1472</v>
       </c>
       <c r="E60" t="s">
         <v>49</v>
@@ -19911,7 +20452,7 @@
         <v>20</v>
       </c>
       <c r="G60" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="H60">
         <v>219100</v>
@@ -19932,16 +20473,16 @@
         <v>33</v>
       </c>
       <c r="N60" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O60" t="s">
-        <v>1437</v>
+        <v>1473</v>
       </c>
       <c r="P60" t="s">
-        <v>1438</v>
+        <v>1474</v>
       </c>
       <c r="Q60" t="s">
-        <v>1439</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
@@ -19955,16 +20496,16 @@
         <v>40</v>
       </c>
       <c r="D61" t="s">
-        <v>1440</v>
+        <v>1476</v>
       </c>
       <c r="E61" t="s">
         <v>49</v>
       </c>
       <c r="F61" t="s">
-        <v>1441</v>
+        <v>1477</v>
       </c>
       <c r="G61" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="H61">
         <v>219100</v>
@@ -19985,16 +20526,16 @@
         <v>39</v>
       </c>
       <c r="N61" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O61" t="s">
-        <v>1442</v>
+        <v>1478</v>
       </c>
       <c r="P61" t="s">
-        <v>1443</v>
+        <v>1479</v>
       </c>
       <c r="Q61" t="s">
-        <v>1444</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
@@ -20008,7 +20549,7 @@
         <v>38</v>
       </c>
       <c r="D62" t="s">
-        <v>1445</v>
+        <v>1481</v>
       </c>
       <c r="E62" t="s">
         <v>49</v>
@@ -20017,7 +20558,7 @@
         <v>757</v>
       </c>
       <c r="G62" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="H62">
         <v>219100</v>
@@ -20038,16 +20579,16 @@
         <v>33</v>
       </c>
       <c r="N62" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O62" t="s">
-        <v>1446</v>
+        <v>1482</v>
       </c>
       <c r="P62" t="s">
-        <v>1447</v>
+        <v>1483</v>
       </c>
       <c r="Q62" t="s">
-        <v>1448</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
@@ -20061,7 +20602,7 @@
         <v>40</v>
       </c>
       <c r="D63" t="s">
-        <v>1449</v>
+        <v>1485</v>
       </c>
       <c r="E63" t="s">
         <v>49</v>
@@ -20070,7 +20611,7 @@
         <v>20</v>
       </c>
       <c r="G63" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="H63">
         <v>219100</v>
@@ -20091,16 +20632,16 @@
         <v>39</v>
       </c>
       <c r="N63" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O63" t="s">
-        <v>1450</v>
+        <v>1486</v>
       </c>
       <c r="P63" t="s">
-        <v>1451</v>
+        <v>1487</v>
       </c>
       <c r="Q63" t="s">
-        <v>1452</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
@@ -20114,16 +20655,16 @@
         <v>33</v>
       </c>
       <c r="D64" t="s">
-        <v>1453</v>
+        <v>1489</v>
       </c>
       <c r="E64" t="s">
         <v>49</v>
       </c>
       <c r="F64" t="s">
-        <v>1454</v>
+        <v>1490</v>
       </c>
       <c r="G64" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="H64">
         <v>219100</v>
@@ -20144,16 +20685,16 @@
         <v>33</v>
       </c>
       <c r="N64" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O64" t="s">
-        <v>1455</v>
+        <v>1491</v>
       </c>
       <c r="P64" t="s">
-        <v>1456</v>
+        <v>1492</v>
       </c>
       <c r="Q64" t="s">
-        <v>1457</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
@@ -20167,16 +20708,16 @@
         <v>48</v>
       </c>
       <c r="D65" t="s">
-        <v>1458</v>
+        <v>1494</v>
       </c>
       <c r="E65" t="s">
-        <v>1316</v>
+        <v>1352</v>
       </c>
       <c r="F65" t="s">
-        <v>1459</v>
+        <v>1495</v>
       </c>
       <c r="G65" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="J65" t="s">
         <v>32</v>
@@ -20191,16 +20732,16 @@
         <v>39</v>
       </c>
       <c r="N65" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O65" t="s">
-        <v>1460</v>
+        <v>1496</v>
       </c>
       <c r="P65" t="s">
-        <v>1461</v>
+        <v>1497</v>
       </c>
       <c r="Q65" t="s">
-        <v>1462</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
@@ -20214,16 +20755,16 @@
         <v>40</v>
       </c>
       <c r="D66" t="s">
-        <v>1162</v>
+        <v>1198</v>
       </c>
       <c r="E66" t="s">
-        <v>1163</v>
+        <v>1199</v>
       </c>
       <c r="F66" t="s">
-        <v>1463</v>
+        <v>1499</v>
       </c>
       <c r="G66" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="H66">
         <v>184200</v>
@@ -20244,16 +20785,16 @@
         <v>39</v>
       </c>
       <c r="N66" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O66" t="s">
-        <v>1464</v>
+        <v>1500</v>
       </c>
       <c r="P66" t="s">
-        <v>1465</v>
+        <v>1501</v>
       </c>
       <c r="Q66" t="s">
-        <v>1466</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
@@ -20267,16 +20808,16 @@
         <v>30</v>
       </c>
       <c r="D67" t="s">
-        <v>1467</v>
+        <v>1503</v>
       </c>
       <c r="E67" t="s">
-        <v>1163</v>
+        <v>1199</v>
       </c>
       <c r="F67" t="s">
-        <v>1468</v>
+        <v>1504</v>
       </c>
       <c r="G67" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="H67">
         <v>200000</v>
@@ -20297,16 +20838,16 @@
         <v>33</v>
       </c>
       <c r="N67" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O67" t="s">
-        <v>1469</v>
+        <v>1505</v>
       </c>
       <c r="P67" t="s">
-        <v>1470</v>
+        <v>1506</v>
       </c>
       <c r="Q67" t="s">
-        <v>1471</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
@@ -20320,7 +20861,7 @@
         <v>30</v>
       </c>
       <c r="D68" t="s">
-        <v>1472</v>
+        <v>1508</v>
       </c>
       <c r="E68" t="s">
         <v>1008</v>
@@ -20329,7 +20870,7 @@
         <v>1017</v>
       </c>
       <c r="G68" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="J68" t="s">
         <v>32</v>
@@ -20344,16 +20885,16 @@
         <v>33</v>
       </c>
       <c r="N68" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O68" t="s">
-        <v>1473</v>
+        <v>1509</v>
       </c>
       <c r="P68" t="s">
-        <v>1474</v>
+        <v>1510</v>
       </c>
       <c r="Q68" t="s">
-        <v>1475</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
@@ -20367,16 +20908,16 @@
         <v>32</v>
       </c>
       <c r="D69" t="s">
-        <v>1476</v>
+        <v>1167</v>
       </c>
       <c r="E69" t="s">
         <v>1008</v>
       </c>
       <c r="F69" t="s">
-        <v>1330</v>
+        <v>1366</v>
       </c>
       <c r="G69" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="J69" t="s">
         <v>32</v>
@@ -20391,16 +20932,16 @@
         <v>33</v>
       </c>
       <c r="N69" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O69" t="s">
-        <v>1477</v>
+        <v>1512</v>
       </c>
       <c r="P69" t="s">
-        <v>1478</v>
+        <v>1513</v>
       </c>
       <c r="Q69" t="s">
-        <v>1479</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
@@ -20414,7 +20955,7 @@
         <v>32</v>
       </c>
       <c r="D70" t="s">
-        <v>1480</v>
+        <v>1515</v>
       </c>
       <c r="E70" t="s">
         <v>1008</v>
@@ -20423,7 +20964,7 @@
         <v>1017</v>
       </c>
       <c r="G70" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="J70" t="s">
         <v>32</v>
@@ -20438,16 +20979,16 @@
         <v>33</v>
       </c>
       <c r="N70" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O70" t="s">
-        <v>1481</v>
+        <v>1516</v>
       </c>
       <c r="P70" t="s">
-        <v>1482</v>
+        <v>1517</v>
       </c>
       <c r="Q70" t="s">
-        <v>1483</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
@@ -20461,16 +21002,16 @@
         <v>45</v>
       </c>
       <c r="D71" t="s">
-        <v>1484</v>
+        <v>1519</v>
       </c>
       <c r="E71" t="s">
         <v>798</v>
       </c>
       <c r="F71" t="s">
-        <v>1175</v>
+        <v>1211</v>
       </c>
       <c r="G71" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="J71" t="s">
         <v>32</v>
@@ -20485,16 +21026,16 @@
         <v>39</v>
       </c>
       <c r="N71" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O71" t="s">
-        <v>1485</v>
+        <v>1520</v>
       </c>
       <c r="P71" t="s">
-        <v>1486</v>
+        <v>1521</v>
       </c>
       <c r="Q71" t="s">
-        <v>1487</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
@@ -20508,16 +21049,16 @@
         <v>35</v>
       </c>
       <c r="D72" t="s">
-        <v>1488</v>
+        <v>1523</v>
       </c>
       <c r="E72" t="s">
         <v>798</v>
       </c>
       <c r="F72" t="s">
-        <v>1489</v>
+        <v>1524</v>
       </c>
       <c r="G72" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="J72" t="s">
         <v>32</v>
@@ -20532,16 +21073,16 @@
         <v>33</v>
       </c>
       <c r="N72" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O72" t="s">
-        <v>1490</v>
+        <v>1525</v>
       </c>
       <c r="P72" t="s">
-        <v>1491</v>
+        <v>1526</v>
       </c>
       <c r="Q72" t="s">
-        <v>1492</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
@@ -20555,7 +21096,7 @@
         <v>35</v>
       </c>
       <c r="D73" t="s">
-        <v>1493</v>
+        <v>1528</v>
       </c>
       <c r="E73" t="s">
         <v>798</v>
@@ -20564,7 +21105,7 @@
         <v>85</v>
       </c>
       <c r="G73" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="J73" t="s">
         <v>32</v>
@@ -20579,16 +21120,16 @@
         <v>33</v>
       </c>
       <c r="N73" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O73" t="s">
-        <v>1494</v>
+        <v>1529</v>
       </c>
       <c r="P73" t="s">
-        <v>1495</v>
+        <v>1530</v>
       </c>
       <c r="Q73" t="s">
-        <v>1496</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
@@ -20602,16 +21143,16 @@
         <v>15</v>
       </c>
       <c r="D74" t="s">
-        <v>1497</v>
+        <v>1532</v>
       </c>
       <c r="E74" t="s">
         <v>798</v>
       </c>
       <c r="F74" t="s">
-        <v>1498</v>
+        <v>1533</v>
       </c>
       <c r="G74" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="J74" t="s">
         <v>32</v>
@@ -20626,16 +21167,16 @@
         <v>33</v>
       </c>
       <c r="N74" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O74" t="s">
-        <v>1499</v>
+        <v>1534</v>
       </c>
       <c r="P74" t="s">
-        <v>1500</v>
+        <v>1535</v>
       </c>
       <c r="Q74" t="s">
-        <v>1501</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
@@ -20649,16 +21190,16 @@
         <v>25</v>
       </c>
       <c r="D75" t="s">
-        <v>1502</v>
+        <v>1537</v>
       </c>
       <c r="E75" t="s">
         <v>798</v>
       </c>
       <c r="F75" t="s">
-        <v>1503</v>
+        <v>1538</v>
       </c>
       <c r="G75" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="J75" t="s">
         <v>32</v>
@@ -20673,16 +21214,16 @@
         <v>33</v>
       </c>
       <c r="N75" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O75" t="s">
-        <v>1504</v>
+        <v>1539</v>
       </c>
       <c r="P75" t="s">
-        <v>1505</v>
+        <v>1540</v>
       </c>
       <c r="Q75" t="s">
-        <v>1506</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
@@ -20696,16 +21237,16 @@
         <v>30</v>
       </c>
       <c r="D76" t="s">
-        <v>1507</v>
+        <v>1542</v>
       </c>
       <c r="E76" t="s">
         <v>798</v>
       </c>
       <c r="F76" t="s">
-        <v>1508</v>
+        <v>1543</v>
       </c>
       <c r="G76" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="J76" t="s">
         <v>32</v>
@@ -20720,16 +21261,16 @@
         <v>33</v>
       </c>
       <c r="N76" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O76" t="s">
-        <v>1509</v>
+        <v>1544</v>
       </c>
       <c r="P76" t="s">
-        <v>1510</v>
+        <v>1545</v>
       </c>
       <c r="Q76" t="s">
-        <v>1511</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
@@ -20749,10 +21290,10 @@
         <v>49</v>
       </c>
       <c r="F77" t="s">
-        <v>1468</v>
+        <v>1504</v>
       </c>
       <c r="G77" t="s">
-        <v>1170</v>
+        <v>1206</v>
       </c>
       <c r="J77" t="s">
         <v>32</v>
@@ -20767,16 +21308,16 @@
         <v>33</v>
       </c>
       <c r="N77" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O77" t="s">
-        <v>1512</v>
+        <v>1547</v>
       </c>
       <c r="P77" t="s">
-        <v>1513</v>
+        <v>1548</v>
       </c>
       <c r="Q77" t="s">
-        <v>1514</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
@@ -20796,10 +21337,10 @@
         <v>49</v>
       </c>
       <c r="F78" t="s">
-        <v>1515</v>
+        <v>1550</v>
       </c>
       <c r="G78" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="J78" t="s">
         <v>32</v>
@@ -20814,16 +21355,16 @@
         <v>39</v>
       </c>
       <c r="N78" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O78" t="s">
-        <v>1516</v>
+        <v>1551</v>
       </c>
       <c r="P78" t="s">
-        <v>1517</v>
+        <v>1552</v>
       </c>
       <c r="Q78" t="s">
-        <v>1518</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
@@ -20846,7 +21387,7 @@
         <v>1074</v>
       </c>
       <c r="G79" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="H79">
         <v>180000</v>
@@ -20867,16 +21408,16 @@
         <v>33</v>
       </c>
       <c r="N79" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O79" t="s">
-        <v>1519</v>
+        <v>1554</v>
       </c>
       <c r="P79" t="s">
-        <v>1520</v>
+        <v>1555</v>
       </c>
       <c r="Q79" t="s">
-        <v>1521</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
@@ -20896,10 +21437,10 @@
         <v>49</v>
       </c>
       <c r="F80" t="s">
-        <v>1522</v>
+        <v>1557</v>
       </c>
       <c r="G80" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="H80">
         <v>180000</v>
@@ -20920,16 +21461,16 @@
         <v>33</v>
       </c>
       <c r="N80" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O80" t="s">
-        <v>1523</v>
+        <v>1558</v>
       </c>
       <c r="P80" t="s">
-        <v>1524</v>
+        <v>1559</v>
       </c>
       <c r="Q80" t="s">
-        <v>1525</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
@@ -20943,16 +21484,16 @@
         <v>20</v>
       </c>
       <c r="D81" t="s">
-        <v>1526</v>
+        <v>1561</v>
       </c>
       <c r="E81" t="s">
         <v>1119</v>
       </c>
       <c r="F81" t="s">
-        <v>1527</v>
+        <v>1562</v>
       </c>
       <c r="G81" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="J81" t="s">
         <v>32</v>
@@ -20967,16 +21508,16 @@
         <v>33</v>
       </c>
       <c r="N81" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O81" t="s">
-        <v>1528</v>
+        <v>1563</v>
       </c>
       <c r="P81" t="s">
-        <v>1529</v>
+        <v>1564</v>
       </c>
       <c r="Q81" t="s">
-        <v>1530</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
@@ -20990,7 +21531,7 @@
         <v>50</v>
       </c>
       <c r="D82" t="s">
-        <v>1531</v>
+        <v>1566</v>
       </c>
       <c r="E82" t="s">
         <v>1119</v>
@@ -20999,7 +21540,7 @@
         <v>20</v>
       </c>
       <c r="G82" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="H82">
         <v>250000</v>
@@ -21020,16 +21561,16 @@
         <v>39</v>
       </c>
       <c r="N82" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O82" t="s">
-        <v>1532</v>
+        <v>1567</v>
       </c>
       <c r="P82" t="s">
-        <v>1533</v>
+        <v>1568</v>
       </c>
       <c r="Q82" t="s">
-        <v>1534</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
@@ -21043,7 +21584,7 @@
         <v>55</v>
       </c>
       <c r="D83" t="s">
-        <v>1535</v>
+        <v>1570</v>
       </c>
       <c r="E83" t="s">
         <v>1119</v>
@@ -21052,7 +21593,7 @@
         <v>20</v>
       </c>
       <c r="G83" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="H83">
         <v>200000</v>
@@ -21073,16 +21614,16 @@
         <v>39</v>
       </c>
       <c r="N83" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O83" t="s">
-        <v>1536</v>
+        <v>1571</v>
       </c>
       <c r="P83" t="s">
-        <v>1537</v>
+        <v>1572</v>
       </c>
       <c r="Q83" t="s">
-        <v>1538</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
@@ -21096,7 +21637,7 @@
         <v>52</v>
       </c>
       <c r="D84" t="s">
-        <v>1539</v>
+        <v>1574</v>
       </c>
       <c r="E84" t="s">
         <v>1119</v>
@@ -21105,7 +21646,7 @@
         <v>20</v>
       </c>
       <c r="G84" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="H84">
         <v>250000</v>
@@ -21126,16 +21667,16 @@
         <v>39</v>
       </c>
       <c r="N84" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O84" t="s">
-        <v>1540</v>
+        <v>1575</v>
       </c>
       <c r="P84" t="s">
-        <v>1541</v>
+        <v>1576</v>
       </c>
       <c r="Q84" t="s">
-        <v>1542</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
@@ -21149,7 +21690,7 @@
         <v>53</v>
       </c>
       <c r="D85" t="s">
-        <v>1543</v>
+        <v>1578</v>
       </c>
       <c r="E85" t="s">
         <v>1119</v>
@@ -21158,7 +21699,7 @@
         <v>20</v>
       </c>
       <c r="G85" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="H85">
         <v>200000</v>
@@ -21179,16 +21720,16 @@
         <v>39</v>
       </c>
       <c r="N85" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O85" t="s">
-        <v>1544</v>
+        <v>1579</v>
       </c>
       <c r="P85" t="s">
-        <v>1545</v>
+        <v>1580</v>
       </c>
       <c r="Q85" t="s">
-        <v>1546</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
@@ -21202,7 +21743,7 @@
         <v>50</v>
       </c>
       <c r="D86" t="s">
-        <v>1547</v>
+        <v>1582</v>
       </c>
       <c r="E86" t="s">
         <v>1119</v>
@@ -21211,7 +21752,7 @@
         <v>20</v>
       </c>
       <c r="G86" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="H86">
         <v>200000</v>
@@ -21232,16 +21773,16 @@
         <v>39</v>
       </c>
       <c r="N86" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O86" t="s">
-        <v>1548</v>
+        <v>1583</v>
       </c>
       <c r="P86" t="s">
-        <v>1549</v>
+        <v>1584</v>
       </c>
       <c r="Q86" t="s">
-        <v>1550</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
@@ -21255,7 +21796,7 @@
         <v>55</v>
       </c>
       <c r="D87" t="s">
-        <v>1551</v>
+        <v>1586</v>
       </c>
       <c r="E87" t="s">
         <v>1119</v>
@@ -21264,7 +21805,7 @@
         <v>20</v>
       </c>
       <c r="G87" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="H87">
         <v>250000</v>
@@ -21285,16 +21826,16 @@
         <v>39</v>
       </c>
       <c r="N87" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O87" t="s">
-        <v>1552</v>
+        <v>1587</v>
       </c>
       <c r="P87" t="s">
-        <v>1553</v>
+        <v>1588</v>
       </c>
       <c r="Q87" t="s">
-        <v>1554</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
@@ -21308,16 +21849,16 @@
         <v>45</v>
       </c>
       <c r="D88" t="s">
-        <v>1555</v>
+        <v>1590</v>
       </c>
       <c r="E88" t="s">
-        <v>1556</v>
+        <v>1591</v>
       </c>
       <c r="F88" t="s">
-        <v>1557</v>
+        <v>1592</v>
       </c>
       <c r="G88" t="s">
-        <v>1170</v>
+        <v>1206</v>
       </c>
       <c r="H88">
         <v>154000</v>
@@ -21338,16 +21879,16 @@
         <v>33</v>
       </c>
       <c r="N88" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O88" t="s">
-        <v>1558</v>
+        <v>1593</v>
       </c>
       <c r="P88" t="s">
-        <v>1559</v>
+        <v>1594</v>
       </c>
       <c r="Q88" t="s">
-        <v>1560</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
@@ -21370,7 +21911,7 @@
         <v>757</v>
       </c>
       <c r="G89" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="H89">
         <v>180000</v>
@@ -21391,16 +21932,16 @@
         <v>39</v>
       </c>
       <c r="N89" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O89" t="s">
-        <v>1561</v>
+        <v>1596</v>
       </c>
       <c r="P89" t="s">
-        <v>1562</v>
+        <v>1597</v>
       </c>
       <c r="Q89" t="s">
-        <v>1563</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
@@ -21420,10 +21961,10 @@
         <v>49</v>
       </c>
       <c r="F90" t="s">
-        <v>1418</v>
+        <v>1454</v>
       </c>
       <c r="G90" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="H90">
         <v>219100</v>
@@ -21444,16 +21985,16 @@
         <v>33</v>
       </c>
       <c r="N90" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O90" t="s">
-        <v>1564</v>
+        <v>1599</v>
       </c>
       <c r="P90" t="s">
-        <v>1565</v>
+        <v>1600</v>
       </c>
       <c r="Q90" t="s">
-        <v>1566</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
@@ -21467,16 +22008,16 @@
         <v>25</v>
       </c>
       <c r="D91" t="s">
-        <v>1567</v>
+        <v>1602</v>
       </c>
       <c r="E91" t="s">
         <v>49</v>
       </c>
       <c r="F91" t="s">
-        <v>1568</v>
+        <v>1603</v>
       </c>
       <c r="G91" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="J91" t="s">
         <v>32</v>
@@ -21491,16 +22032,16 @@
         <v>33</v>
       </c>
       <c r="N91" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O91" t="s">
-        <v>1569</v>
+        <v>1604</v>
       </c>
       <c r="P91" t="s">
-        <v>1570</v>
+        <v>1605</v>
       </c>
       <c r="Q91" t="s">
-        <v>1571</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
@@ -21520,10 +22061,10 @@
         <v>1008</v>
       </c>
       <c r="F92" t="s">
-        <v>1169</v>
+        <v>1205</v>
       </c>
       <c r="G92" t="s">
-        <v>1170</v>
+        <v>1206</v>
       </c>
       <c r="J92" t="s">
         <v>32</v>
@@ -21538,16 +22079,16 @@
         <v>33</v>
       </c>
       <c r="N92" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O92" t="s">
-        <v>1572</v>
+        <v>1607</v>
       </c>
       <c r="P92" t="s">
-        <v>1573</v>
+        <v>1608</v>
       </c>
       <c r="Q92" t="s">
-        <v>1574</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
@@ -21561,16 +22102,16 @@
         <v>15</v>
       </c>
       <c r="D93" t="s">
-        <v>1575</v>
+        <v>1610</v>
       </c>
       <c r="E93" t="s">
-        <v>1576</v>
+        <v>1611</v>
       </c>
       <c r="F93" t="s">
-        <v>1386</v>
+        <v>1422</v>
       </c>
       <c r="G93" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="J93" t="s">
         <v>32</v>
@@ -21585,16 +22126,16 @@
         <v>33</v>
       </c>
       <c r="N93" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O93" t="s">
-        <v>1577</v>
+        <v>1612</v>
       </c>
       <c r="P93" t="s">
-        <v>1578</v>
+        <v>1613</v>
       </c>
       <c r="Q93" t="s">
-        <v>1579</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
@@ -21608,16 +22149,16 @@
         <v>12</v>
       </c>
       <c r="D94" t="s">
-        <v>1580</v>
+        <v>1615</v>
       </c>
       <c r="E94" t="s">
-        <v>1581</v>
+        <v>1616</v>
       </c>
       <c r="F94" t="s">
-        <v>1582</v>
+        <v>1617</v>
       </c>
       <c r="G94" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="J94" t="s">
         <v>32</v>
@@ -21632,16 +22173,16 @@
         <v>33</v>
       </c>
       <c r="N94" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O94" t="s">
-        <v>1583</v>
+        <v>1618</v>
       </c>
       <c r="P94" t="s">
-        <v>1584</v>
+        <v>1619</v>
       </c>
       <c r="Q94" t="s">
-        <v>1585</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
@@ -21655,16 +22196,16 @@
         <v>42</v>
       </c>
       <c r="D95" t="s">
-        <v>1586</v>
+        <v>1621</v>
       </c>
       <c r="E95" t="s">
         <v>49</v>
       </c>
       <c r="F95" t="s">
-        <v>1587</v>
+        <v>1622</v>
       </c>
       <c r="G95" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="H95">
         <v>180000</v>
@@ -21685,16 +22226,16 @@
         <v>39</v>
       </c>
       <c r="N95" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O95" t="s">
-        <v>1588</v>
+        <v>1623</v>
       </c>
       <c r="P95" t="s">
-        <v>1589</v>
+        <v>1624</v>
       </c>
       <c r="Q95" t="s">
-        <v>1590</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
@@ -21708,16 +22249,16 @@
         <v>22</v>
       </c>
       <c r="D96" t="s">
-        <v>1591</v>
+        <v>1626</v>
       </c>
       <c r="E96" t="s">
-        <v>1163</v>
+        <v>1199</v>
       </c>
       <c r="F96" t="s">
-        <v>1592</v>
+        <v>1627</v>
       </c>
       <c r="G96" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="H96">
         <v>200000</v>
@@ -21738,16 +22279,16 @@
         <v>33</v>
       </c>
       <c r="N96" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O96" t="s">
-        <v>1593</v>
+        <v>1628</v>
       </c>
       <c r="P96" t="s">
-        <v>1594</v>
+        <v>1629</v>
       </c>
       <c r="Q96" t="s">
-        <v>1595</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
@@ -21761,16 +22302,16 @@
         <v>28</v>
       </c>
       <c r="D97" t="s">
-        <v>1596</v>
+        <v>1631</v>
       </c>
       <c r="E97" t="s">
-        <v>1597</v>
+        <v>1632</v>
       </c>
       <c r="F97" t="s">
-        <v>1568</v>
+        <v>1603</v>
       </c>
       <c r="G97" t="s">
-        <v>1170</v>
+        <v>1206</v>
       </c>
       <c r="J97" t="s">
         <v>32</v>
@@ -21785,16 +22326,16 @@
         <v>33</v>
       </c>
       <c r="N97" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O97" t="s">
-        <v>1598</v>
+        <v>1633</v>
       </c>
       <c r="P97" t="s">
-        <v>1599</v>
+        <v>1634</v>
       </c>
       <c r="Q97" t="s">
-        <v>1600</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
@@ -21808,16 +22349,16 @@
         <v>5</v>
       </c>
       <c r="D98" t="s">
-        <v>1601</v>
+        <v>1636</v>
       </c>
       <c r="E98" t="s">
-        <v>1602</v>
+        <v>1637</v>
       </c>
       <c r="F98" t="s">
-        <v>1603</v>
+        <v>1638</v>
       </c>
       <c r="G98" t="s">
-        <v>1164</v>
+        <v>1200</v>
       </c>
       <c r="J98" t="s">
         <v>32</v>
@@ -21832,16 +22373,63 @@
         <v>33</v>
       </c>
       <c r="N98" t="s">
-        <v>1165</v>
+        <v>1201</v>
       </c>
       <c r="O98" t="s">
-        <v>1604</v>
+        <v>1639</v>
       </c>
       <c r="P98" t="s">
-        <v>1605</v>
+        <v>1640</v>
       </c>
       <c r="Q98" t="s">
-        <v>1606</v>
+        <v>1641</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>17</v>
+      </c>
+      <c r="B99">
+        <v>50</v>
+      </c>
+      <c r="C99">
+        <v>45</v>
+      </c>
+      <c r="D99" t="s">
+        <v>472</v>
+      </c>
+      <c r="E99" t="s">
+        <v>49</v>
+      </c>
+      <c r="F99" t="s">
+        <v>1642</v>
+      </c>
+      <c r="G99" t="s">
+        <v>1200</v>
+      </c>
+      <c r="J99" t="s">
+        <v>32</v>
+      </c>
+      <c r="K99" t="s">
+        <v>51</v>
+      </c>
+      <c r="L99" t="s">
+        <v>1163</v>
+      </c>
+      <c r="M99" t="s">
+        <v>39</v>
+      </c>
+      <c r="N99" t="s">
+        <v>1201</v>
+      </c>
+      <c r="O99" t="s">
+        <v>1643</v>
+      </c>
+      <c r="P99" t="s">
+        <v>1644</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>1645</v>
       </c>
     </row>
   </sheetData>

--- a/hunt/board.xlsx
+++ b/hunt/board.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4441" uniqueCount="1646">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4493" uniqueCount="1667">
   <si>
     <t>Column</t>
   </si>
@@ -3608,6 +3608,54 @@
     <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8633227002</t>
   </si>
   <si>
+    <t>AI Solutions Architect (United States)</t>
+  </si>
+  <si>
+    <t>Testlio</t>
+  </si>
+  <si>
+    <t>2026-08-31T02:59:41.128Z</t>
+  </si>
+  <si>
+    <t>100% remote US role with confirmed $300K comp, far above the $180K floor | Solutions-architect scope with customer-facing advisory and delivery methodology ownership — matches candidate's trusted-advisor engagement experience | Agentic AI framing overlaps with candidate's GitHub Copilot / Agentic DevOps workflow exposure</t>
+  </si>
+  <si>
+    <t>Core requirement is deep QA/test engineering practitioner depth for AI-powered and agentic applications — candidate's resume shows no software testing or test automation framework background | Role owns offering packaging and delivery methodology for a testing product, not cloud platform/DevOps architecture where the candidate's Azure/GHAS depth lives | No Azure governance, IaC, or CI/CD platform work signaled, so most of the candidate's differentiators go unused</t>
+  </si>
+  <si>
+    <t>https://jobicy.com/jobs/152087-ai-solutions-architect-united-states</t>
+  </si>
+  <si>
+    <t>AI Solution Architect (m/w/d)</t>
+  </si>
+  <si>
+    <t>virtual7 GmbH</t>
+  </si>
+  <si>
+    <t>Homeoffice</t>
+  </si>
+  <si>
+    <t>Explicitly Microsoft Azure–centric enterprise cloud architecture, directly matching the candidate's AZ-104 and Azure platform depth | Public-sector digitalization work is a strong industry precedent match for the candidate's compliance-driven architecture experience | Remote (Homeoffice) posting</t>
+  </si>
+  <si>
+    <t>Requires ML Engineering, RAG architecture, and MLOps depth that the candidate's resume does not demonstrate | German-language posting for a German employer — German fluency and EU work authorization are implicit hard requirements outside the candidate's US market scope | No compensation listed and German salary bands are very unlikely to hit $180K</t>
+  </si>
+  <si>
+    <t>https://www.arbeitnow.com/jobs/companies/virtual7-gmbh/remote-ai-solution-architect-nurnberg-mittelfranken-280706</t>
+  </si>
+  <si>
+    <t>Senior IT Architect (m/w/d)</t>
+  </si>
+  <si>
+    <t>Healthcare/statutory health insurance domain aligns with candidate's HIPAA and compliance-driven architecture background | Ownership of architecture decisions and stakeholder guidance matches the candidate's advisory-architect operating style | Remote (Homeoffice) arrangement</t>
+  </si>
+  <si>
+    <t>German-language role requiring knowledge of German statutory health insurance (GKV) regulation — a domain the candidate has no exposure to | Employer is a German public-sector IT services provider; EU authorization and German fluency are effectively mandatory, outside the stated US scope | No Azure DevOps/GitHub platform or cloud-governance focus, so the candidate's strongest skills aren't leveraged; no salary posted</t>
+  </si>
+  <si>
+    <t>https://www.arbeitnow.com/jobs/companies/virtual7-gmbh/remote-senior-it-architect-karlsruhe-320449</t>
+  </si>
+  <si>
     <t>Principal AI Ecosystem Architect - OpenAI/Anthropic</t>
   </si>
   <si>
@@ -4950,6 +4998,21 @@
   </si>
   <si>
     <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8567957002</t>
+  </si>
+  <si>
+    <t>Sr Agent Architect (Germany)</t>
+  </si>
+  <si>
+    <t>parloa</t>
+  </si>
+  <si>
+    <t>Enterprise solution-architect role designing end-to-end integrations into complex enterprise environments — aligns with candidate's enterprise advisory model | Named enterprise customers in insurance/travel/SAP space fit candidate's compliance-heavy enterprise precedent</t>
+  </si>
+  <si>
+    <t>Role is based in Germany, outside the candidate's stated US market scope, and likely requires local work authorization plus German-market presence | Focus is conversational/agentic AI agent design on Parloa's proprietary platform — no Azure DevOps, GHAS, or IaC governance depth credited | No salary posted and European comp is unlikely to reach the $180K floor</t>
+  </si>
+  <si>
+    <t>https://www.arbeitnow.com/jobs/companies/parloa/sr-agent-architect-germany-432325</t>
   </si>
 </sst>
 </file>
@@ -5330,7 +5393,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q242"/>
+  <dimension ref="A1:Q245"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -17495,6 +17558,153 @@
         <v>1197</v>
       </c>
     </row>
+    <row r="243" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>17</v>
+      </c>
+      <c r="B243">
+        <v>48</v>
+      </c>
+      <c r="C243">
+        <v>42</v>
+      </c>
+      <c r="D243" t="s">
+        <v>1198</v>
+      </c>
+      <c r="E243" t="s">
+        <v>1199</v>
+      </c>
+      <c r="F243" t="s">
+        <v>85</v>
+      </c>
+      <c r="G243" t="s">
+        <v>21</v>
+      </c>
+      <c r="H243">
+        <v>300000</v>
+      </c>
+      <c r="I243">
+        <v>300000</v>
+      </c>
+      <c r="J243" t="s">
+        <v>22</v>
+      </c>
+      <c r="K243" t="s">
+        <v>73</v>
+      </c>
+      <c r="L243" t="s">
+        <v>1200</v>
+      </c>
+      <c r="M243" t="s">
+        <v>39</v>
+      </c>
+      <c r="N243" t="s">
+        <v>26</v>
+      </c>
+      <c r="O243" t="s">
+        <v>1201</v>
+      </c>
+      <c r="P243" t="s">
+        <v>1202</v>
+      </c>
+      <c r="Q243" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="244" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>17</v>
+      </c>
+      <c r="B244">
+        <v>33</v>
+      </c>
+      <c r="C244">
+        <v>45</v>
+      </c>
+      <c r="D244" t="s">
+        <v>1204</v>
+      </c>
+      <c r="E244" t="s">
+        <v>1205</v>
+      </c>
+      <c r="F244" t="s">
+        <v>1206</v>
+      </c>
+      <c r="G244" t="s">
+        <v>21</v>
+      </c>
+      <c r="J244" t="s">
+        <v>32</v>
+      </c>
+      <c r="K244" t="s">
+        <v>151</v>
+      </c>
+      <c r="L244" t="s">
+        <v>1200</v>
+      </c>
+      <c r="M244" t="s">
+        <v>33</v>
+      </c>
+      <c r="N244" t="s">
+        <v>26</v>
+      </c>
+      <c r="O244" t="s">
+        <v>1207</v>
+      </c>
+      <c r="P244" t="s">
+        <v>1208</v>
+      </c>
+      <c r="Q244" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="245" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>17</v>
+      </c>
+      <c r="B245">
+        <v>30</v>
+      </c>
+      <c r="C245">
+        <v>38</v>
+      </c>
+      <c r="D245" t="s">
+        <v>1210</v>
+      </c>
+      <c r="E245" t="s">
+        <v>1205</v>
+      </c>
+      <c r="F245" t="s">
+        <v>1206</v>
+      </c>
+      <c r="G245" t="s">
+        <v>21</v>
+      </c>
+      <c r="J245" t="s">
+        <v>32</v>
+      </c>
+      <c r="K245" t="s">
+        <v>151</v>
+      </c>
+      <c r="L245" t="s">
+        <v>1200</v>
+      </c>
+      <c r="M245" t="s">
+        <v>33</v>
+      </c>
+      <c r="N245" t="s">
+        <v>26</v>
+      </c>
+      <c r="O245" t="s">
+        <v>1211</v>
+      </c>
+      <c r="P245" t="s">
+        <v>1212</v>
+      </c>
+      <c r="Q245" t="s">
+        <v>1213</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:Q1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17504,7 +17714,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q99"/>
+  <dimension ref="A1:Q100"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -17585,16 +17795,16 @@
         <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>1198</v>
+        <v>1214</v>
       </c>
       <c r="E2" t="s">
-        <v>1199</v>
+        <v>1215</v>
       </c>
       <c r="F2" t="s">
         <v>1023</v>
       </c>
       <c r="G2" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="H2">
         <v>184200</v>
@@ -17615,16 +17825,16 @@
         <v>33</v>
       </c>
       <c r="N2" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O2" t="s">
-        <v>1202</v>
+        <v>1218</v>
       </c>
       <c r="P2" t="s">
-        <v>1203</v>
+        <v>1219</v>
       </c>
       <c r="Q2" t="s">
-        <v>1204</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -17644,10 +17854,10 @@
         <v>1008</v>
       </c>
       <c r="F3" t="s">
-        <v>1205</v>
+        <v>1221</v>
       </c>
       <c r="G3" t="s">
-        <v>1206</v>
+        <v>1222</v>
       </c>
       <c r="J3" t="s">
         <v>32</v>
@@ -17662,16 +17872,16 @@
         <v>33</v>
       </c>
       <c r="N3" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O3" t="s">
-        <v>1207</v>
+        <v>1223</v>
       </c>
       <c r="P3" t="s">
-        <v>1208</v>
+        <v>1224</v>
       </c>
       <c r="Q3" t="s">
-        <v>1209</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
@@ -17685,16 +17895,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>1210</v>
+        <v>1226</v>
       </c>
       <c r="E4" t="s">
         <v>798</v>
       </c>
       <c r="F4" t="s">
-        <v>1211</v>
+        <v>1227</v>
       </c>
       <c r="G4" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="J4" t="s">
         <v>32</v>
@@ -17709,16 +17919,16 @@
         <v>33</v>
       </c>
       <c r="N4" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O4" t="s">
-        <v>1212</v>
+        <v>1228</v>
       </c>
       <c r="P4" t="s">
-        <v>1213</v>
+        <v>1229</v>
       </c>
       <c r="Q4" t="s">
-        <v>1214</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -17732,16 +17942,16 @@
         <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>1215</v>
+        <v>1231</v>
       </c>
       <c r="E5" t="s">
         <v>798</v>
       </c>
       <c r="F5" t="s">
+        <v>1232</v>
+      </c>
+      <c r="G5" t="s">
         <v>1216</v>
-      </c>
-      <c r="G5" t="s">
-        <v>1200</v>
       </c>
       <c r="J5" t="s">
         <v>32</v>
@@ -17756,16 +17966,16 @@
         <v>33</v>
       </c>
       <c r="N5" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O5" t="s">
-        <v>1217</v>
+        <v>1233</v>
       </c>
       <c r="P5" t="s">
-        <v>1218</v>
+        <v>1234</v>
       </c>
       <c r="Q5" t="s">
-        <v>1219</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -17779,16 +17989,16 @@
         <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>1220</v>
+        <v>1236</v>
       </c>
       <c r="E6" t="s">
         <v>49</v>
       </c>
       <c r="F6" t="s">
-        <v>1205</v>
+        <v>1221</v>
       </c>
       <c r="G6" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="J6" t="s">
         <v>32</v>
@@ -17803,16 +18013,16 @@
         <v>39</v>
       </c>
       <c r="N6" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O6" t="s">
-        <v>1221</v>
+        <v>1237</v>
       </c>
       <c r="P6" t="s">
-        <v>1222</v>
+        <v>1238</v>
       </c>
       <c r="Q6" t="s">
-        <v>1223</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -17826,16 +18036,16 @@
         <v>48</v>
       </c>
       <c r="D7" t="s">
-        <v>1224</v>
+        <v>1240</v>
       </c>
       <c r="E7" t="s">
-        <v>1225</v>
+        <v>1241</v>
       </c>
       <c r="F7" t="s">
-        <v>1226</v>
+        <v>1242</v>
       </c>
       <c r="G7" t="s">
-        <v>1206</v>
+        <v>1222</v>
       </c>
       <c r="J7" t="s">
         <v>32</v>
@@ -17850,16 +18060,16 @@
         <v>33</v>
       </c>
       <c r="N7" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O7" t="s">
-        <v>1227</v>
+        <v>1243</v>
       </c>
       <c r="P7" t="s">
-        <v>1228</v>
+        <v>1244</v>
       </c>
       <c r="Q7" t="s">
-        <v>1229</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -17873,16 +18083,16 @@
         <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>1230</v>
+        <v>1246</v>
       </c>
       <c r="E8" t="s">
-        <v>1231</v>
+        <v>1247</v>
       </c>
       <c r="F8" t="s">
-        <v>1232</v>
+        <v>1248</v>
       </c>
       <c r="G8" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="J8" t="s">
         <v>32</v>
@@ -17897,16 +18107,16 @@
         <v>33</v>
       </c>
       <c r="N8" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O8" t="s">
-        <v>1233</v>
+        <v>1249</v>
       </c>
       <c r="P8" t="s">
-        <v>1234</v>
+        <v>1250</v>
       </c>
       <c r="Q8" t="s">
-        <v>1235</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -17920,7 +18130,7 @@
         <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>1236</v>
+        <v>1252</v>
       </c>
       <c r="E9" t="s">
         <v>49</v>
@@ -17929,7 +18139,7 @@
         <v>20</v>
       </c>
       <c r="G9" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="H9">
         <v>217800</v>
@@ -17950,16 +18160,16 @@
         <v>39</v>
       </c>
       <c r="N9" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O9" t="s">
-        <v>1237</v>
+        <v>1253</v>
       </c>
       <c r="P9" t="s">
-        <v>1238</v>
+        <v>1254</v>
       </c>
       <c r="Q9" t="s">
-        <v>1239</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -17973,16 +18183,16 @@
         <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>1240</v>
+        <v>1256</v>
       </c>
       <c r="E10" t="s">
         <v>49</v>
       </c>
       <c r="F10" t="s">
-        <v>1241</v>
+        <v>1257</v>
       </c>
       <c r="G10" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="H10">
         <v>219100</v>
@@ -18003,16 +18213,16 @@
         <v>39</v>
       </c>
       <c r="N10" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O10" t="s">
-        <v>1242</v>
+        <v>1258</v>
       </c>
       <c r="P10" t="s">
-        <v>1243</v>
+        <v>1259</v>
       </c>
       <c r="Q10" t="s">
-        <v>1244</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -18032,10 +18242,10 @@
         <v>1008</v>
       </c>
       <c r="F11" t="s">
-        <v>1245</v>
+        <v>1261</v>
       </c>
       <c r="G11" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="J11" t="s">
         <v>32</v>
@@ -18050,16 +18260,16 @@
         <v>33</v>
       </c>
       <c r="N11" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O11" t="s">
-        <v>1246</v>
+        <v>1262</v>
       </c>
       <c r="P11" t="s">
-        <v>1247</v>
+        <v>1263</v>
       </c>
       <c r="Q11" t="s">
-        <v>1248</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -18073,16 +18283,16 @@
         <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>1249</v>
+        <v>1265</v>
       </c>
       <c r="E12" t="s">
-        <v>1250</v>
+        <v>1266</v>
       </c>
       <c r="F12" t="s">
-        <v>1251</v>
+        <v>1267</v>
       </c>
       <c r="G12" t="s">
-        <v>1206</v>
+        <v>1222</v>
       </c>
       <c r="J12" t="s">
         <v>32</v>
@@ -18097,16 +18307,16 @@
         <v>33</v>
       </c>
       <c r="N12" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O12" t="s">
-        <v>1252</v>
+        <v>1268</v>
       </c>
       <c r="P12" t="s">
-        <v>1253</v>
+        <v>1269</v>
       </c>
       <c r="Q12" t="s">
-        <v>1254</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
@@ -18120,16 +18330,16 @@
         <v>35</v>
       </c>
       <c r="D13" t="s">
-        <v>1255</v>
+        <v>1271</v>
       </c>
       <c r="E13" t="s">
-        <v>1256</v>
+        <v>1272</v>
       </c>
       <c r="F13" t="s">
-        <v>1257</v>
+        <v>1273</v>
       </c>
       <c r="G13" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="J13" t="s">
         <v>32</v>
@@ -18144,16 +18354,16 @@
         <v>33</v>
       </c>
       <c r="N13" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O13" t="s">
-        <v>1258</v>
+        <v>1274</v>
       </c>
       <c r="P13" t="s">
-        <v>1259</v>
+        <v>1275</v>
       </c>
       <c r="Q13" t="s">
-        <v>1260</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
@@ -18167,16 +18377,16 @@
         <v>55</v>
       </c>
       <c r="D14" t="s">
-        <v>1261</v>
+        <v>1277</v>
       </c>
       <c r="E14" t="s">
-        <v>1256</v>
+        <v>1272</v>
       </c>
       <c r="F14" t="s">
-        <v>1262</v>
+        <v>1278</v>
       </c>
       <c r="G14" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="J14" t="s">
         <v>32</v>
@@ -18191,16 +18401,16 @@
         <v>33</v>
       </c>
       <c r="N14" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O14" t="s">
-        <v>1263</v>
+        <v>1279</v>
       </c>
       <c r="P14" t="s">
-        <v>1264</v>
+        <v>1280</v>
       </c>
       <c r="Q14" t="s">
-        <v>1265</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -18214,16 +18424,16 @@
         <v>40</v>
       </c>
       <c r="D15" t="s">
-        <v>1266</v>
+        <v>1282</v>
       </c>
       <c r="E15" t="s">
-        <v>1256</v>
+        <v>1272</v>
       </c>
       <c r="F15" t="s">
-        <v>1257</v>
+        <v>1273</v>
       </c>
       <c r="G15" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="J15" t="s">
         <v>32</v>
@@ -18238,16 +18448,16 @@
         <v>33</v>
       </c>
       <c r="N15" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O15" t="s">
-        <v>1267</v>
+        <v>1283</v>
       </c>
       <c r="P15" t="s">
-        <v>1268</v>
+        <v>1284</v>
       </c>
       <c r="Q15" t="s">
-        <v>1269</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
@@ -18261,16 +18471,16 @@
         <v>5</v>
       </c>
       <c r="D16" t="s">
-        <v>1270</v>
+        <v>1286</v>
       </c>
       <c r="E16" t="s">
-        <v>1271</v>
+        <v>1287</v>
       </c>
       <c r="F16" t="s">
-        <v>1272</v>
+        <v>1288</v>
       </c>
       <c r="G16" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="J16" t="s">
         <v>32</v>
@@ -18285,16 +18495,16 @@
         <v>33</v>
       </c>
       <c r="N16" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O16" t="s">
-        <v>1273</v>
+        <v>1289</v>
       </c>
       <c r="P16" t="s">
-        <v>1274</v>
+        <v>1290</v>
       </c>
       <c r="Q16" t="s">
-        <v>1275</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
@@ -18308,16 +18518,16 @@
         <v>45</v>
       </c>
       <c r="D17" t="s">
-        <v>1276</v>
+        <v>1292</v>
       </c>
       <c r="E17" t="s">
-        <v>1271</v>
+        <v>1287</v>
       </c>
       <c r="F17" t="s">
-        <v>1205</v>
+        <v>1221</v>
       </c>
       <c r="G17" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="J17" t="s">
         <v>32</v>
@@ -18332,16 +18542,16 @@
         <v>33</v>
       </c>
       <c r="N17" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O17" t="s">
-        <v>1277</v>
+        <v>1293</v>
       </c>
       <c r="P17" t="s">
-        <v>1278</v>
+        <v>1294</v>
       </c>
       <c r="Q17" t="s">
-        <v>1279</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
@@ -18355,16 +18565,16 @@
         <v>5</v>
       </c>
       <c r="D18" t="s">
-        <v>1280</v>
+        <v>1296</v>
       </c>
       <c r="E18" t="s">
-        <v>1271</v>
+        <v>1287</v>
       </c>
       <c r="F18" t="s">
-        <v>1272</v>
+        <v>1288</v>
       </c>
       <c r="G18" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="J18" t="s">
         <v>32</v>
@@ -18379,16 +18589,16 @@
         <v>33</v>
       </c>
       <c r="N18" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O18" t="s">
-        <v>1281</v>
+        <v>1297</v>
       </c>
       <c r="P18" t="s">
-        <v>1282</v>
+        <v>1298</v>
       </c>
       <c r="Q18" t="s">
-        <v>1283</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -18402,16 +18612,16 @@
         <v>5</v>
       </c>
       <c r="D19" t="s">
-        <v>1284</v>
+        <v>1300</v>
       </c>
       <c r="E19" t="s">
-        <v>1271</v>
+        <v>1287</v>
       </c>
       <c r="F19" t="s">
-        <v>1272</v>
+        <v>1288</v>
       </c>
       <c r="G19" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="J19" t="s">
         <v>32</v>
@@ -18426,16 +18636,16 @@
         <v>33</v>
       </c>
       <c r="N19" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O19" t="s">
-        <v>1285</v>
+        <v>1301</v>
       </c>
       <c r="P19" t="s">
-        <v>1286</v>
+        <v>1302</v>
       </c>
       <c r="Q19" t="s">
-        <v>1287</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -18449,16 +18659,16 @@
         <v>18</v>
       </c>
       <c r="D20" t="s">
+        <v>1304</v>
+      </c>
+      <c r="E20" t="s">
+        <v>1287</v>
+      </c>
+      <c r="F20" t="s">
         <v>1288</v>
       </c>
-      <c r="E20" t="s">
-        <v>1271</v>
-      </c>
-      <c r="F20" t="s">
-        <v>1272</v>
-      </c>
       <c r="G20" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="J20" t="s">
         <v>32</v>
@@ -18473,16 +18683,16 @@
         <v>33</v>
       </c>
       <c r="N20" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O20" t="s">
-        <v>1289</v>
+        <v>1305</v>
       </c>
       <c r="P20" t="s">
-        <v>1290</v>
+        <v>1306</v>
       </c>
       <c r="Q20" t="s">
-        <v>1291</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
@@ -18496,16 +18706,16 @@
         <v>5</v>
       </c>
       <c r="D21" t="s">
-        <v>1292</v>
+        <v>1308</v>
       </c>
       <c r="E21" t="s">
-        <v>1271</v>
+        <v>1287</v>
       </c>
       <c r="F21" t="s">
-        <v>1272</v>
+        <v>1288</v>
       </c>
       <c r="G21" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="J21" t="s">
         <v>32</v>
@@ -18520,16 +18730,16 @@
         <v>33</v>
       </c>
       <c r="N21" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O21" t="s">
-        <v>1293</v>
+        <v>1309</v>
       </c>
       <c r="P21" t="s">
-        <v>1294</v>
+        <v>1310</v>
       </c>
       <c r="Q21" t="s">
-        <v>1295</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -18543,16 +18753,16 @@
         <v>40</v>
       </c>
       <c r="D22" t="s">
-        <v>1296</v>
+        <v>1312</v>
       </c>
       <c r="E22" t="s">
-        <v>1271</v>
+        <v>1287</v>
       </c>
       <c r="F22" t="s">
-        <v>1272</v>
+        <v>1288</v>
       </c>
       <c r="G22" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="J22" t="s">
         <v>32</v>
@@ -18567,16 +18777,16 @@
         <v>33</v>
       </c>
       <c r="N22" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O22" t="s">
-        <v>1297</v>
+        <v>1313</v>
       </c>
       <c r="P22" t="s">
-        <v>1298</v>
+        <v>1314</v>
       </c>
       <c r="Q22" t="s">
-        <v>1299</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
@@ -18590,16 +18800,16 @@
         <v>45</v>
       </c>
       <c r="D23" t="s">
-        <v>1300</v>
+        <v>1316</v>
       </c>
       <c r="E23" t="s">
-        <v>1271</v>
+        <v>1287</v>
       </c>
       <c r="F23" t="s">
-        <v>1272</v>
+        <v>1288</v>
       </c>
       <c r="G23" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="J23" t="s">
         <v>32</v>
@@ -18614,16 +18824,16 @@
         <v>33</v>
       </c>
       <c r="N23" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O23" t="s">
-        <v>1301</v>
+        <v>1317</v>
       </c>
       <c r="P23" t="s">
-        <v>1302</v>
+        <v>1318</v>
       </c>
       <c r="Q23" t="s">
-        <v>1303</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
@@ -18637,16 +18847,16 @@
         <v>3</v>
       </c>
       <c r="D24" t="s">
-        <v>1304</v>
+        <v>1320</v>
       </c>
       <c r="E24" t="s">
-        <v>1271</v>
+        <v>1287</v>
       </c>
       <c r="F24" t="s">
-        <v>1272</v>
+        <v>1288</v>
       </c>
       <c r="G24" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="J24" t="s">
         <v>32</v>
@@ -18661,16 +18871,16 @@
         <v>33</v>
       </c>
       <c r="N24" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O24" t="s">
-        <v>1305</v>
+        <v>1321</v>
       </c>
       <c r="P24" t="s">
-        <v>1306</v>
+        <v>1322</v>
       </c>
       <c r="Q24" t="s">
-        <v>1307</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
@@ -18684,7 +18894,7 @@
         <v>42</v>
       </c>
       <c r="D25" t="s">
-        <v>1308</v>
+        <v>1324</v>
       </c>
       <c r="E25" t="s">
         <v>49</v>
@@ -18693,7 +18903,7 @@
         <v>20</v>
       </c>
       <c r="G25" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="J25" t="s">
         <v>32</v>
@@ -18708,16 +18918,16 @@
         <v>33</v>
       </c>
       <c r="N25" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O25" t="s">
-        <v>1309</v>
+        <v>1325</v>
       </c>
       <c r="P25" t="s">
-        <v>1310</v>
+        <v>1326</v>
       </c>
       <c r="Q25" t="s">
-        <v>1311</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
@@ -18731,7 +18941,7 @@
         <v>40</v>
       </c>
       <c r="D26" t="s">
-        <v>1312</v>
+        <v>1328</v>
       </c>
       <c r="E26" t="s">
         <v>49</v>
@@ -18740,7 +18950,7 @@
         <v>20</v>
       </c>
       <c r="G26" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="J26" t="s">
         <v>32</v>
@@ -18755,16 +18965,16 @@
         <v>33</v>
       </c>
       <c r="N26" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O26" t="s">
-        <v>1313</v>
+        <v>1329</v>
       </c>
       <c r="P26" t="s">
-        <v>1314</v>
+        <v>1330</v>
       </c>
       <c r="Q26" t="s">
-        <v>1315</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
@@ -18784,10 +18994,10 @@
         <v>49</v>
       </c>
       <c r="F27" t="s">
-        <v>1316</v>
+        <v>1332</v>
       </c>
       <c r="G27" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="H27">
         <v>180000</v>
@@ -18808,16 +19018,16 @@
         <v>39</v>
       </c>
       <c r="N27" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O27" t="s">
-        <v>1317</v>
+        <v>1333</v>
       </c>
       <c r="P27" t="s">
-        <v>1318</v>
+        <v>1334</v>
       </c>
       <c r="Q27" t="s">
-        <v>1319</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
@@ -18831,7 +19041,7 @@
         <v>52</v>
       </c>
       <c r="D28" t="s">
-        <v>1320</v>
+        <v>1336</v>
       </c>
       <c r="E28" t="s">
         <v>49</v>
@@ -18840,7 +19050,7 @@
         <v>20</v>
       </c>
       <c r="G28" t="s">
-        <v>1206</v>
+        <v>1222</v>
       </c>
       <c r="H28">
         <v>180000</v>
@@ -18861,16 +19071,16 @@
         <v>39</v>
       </c>
       <c r="N28" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O28" t="s">
-        <v>1321</v>
+        <v>1337</v>
       </c>
       <c r="P28" t="s">
-        <v>1322</v>
+        <v>1338</v>
       </c>
       <c r="Q28" t="s">
-        <v>1323</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
@@ -18884,7 +19094,7 @@
         <v>55</v>
       </c>
       <c r="D29" t="s">
-        <v>1324</v>
+        <v>1340</v>
       </c>
       <c r="E29" t="s">
         <v>49</v>
@@ -18893,7 +19103,7 @@
         <v>20</v>
       </c>
       <c r="G29" t="s">
-        <v>1206</v>
+        <v>1222</v>
       </c>
       <c r="H29">
         <v>180000</v>
@@ -18914,16 +19124,16 @@
         <v>39</v>
       </c>
       <c r="N29" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O29" t="s">
-        <v>1325</v>
+        <v>1341</v>
       </c>
       <c r="P29" t="s">
-        <v>1326</v>
+        <v>1342</v>
       </c>
       <c r="Q29" t="s">
-        <v>1327</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
@@ -18937,16 +19147,16 @@
         <v>48</v>
       </c>
       <c r="D30" t="s">
-        <v>1328</v>
+        <v>1344</v>
       </c>
       <c r="E30" t="s">
         <v>49</v>
       </c>
       <c r="F30" t="s">
-        <v>1329</v>
+        <v>1345</v>
       </c>
       <c r="G30" t="s">
-        <v>1206</v>
+        <v>1222</v>
       </c>
       <c r="H30">
         <v>219100</v>
@@ -18967,16 +19177,16 @@
         <v>39</v>
       </c>
       <c r="N30" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O30" t="s">
-        <v>1330</v>
+        <v>1346</v>
       </c>
       <c r="P30" t="s">
-        <v>1331</v>
+        <v>1347</v>
       </c>
       <c r="Q30" t="s">
-        <v>1332</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
@@ -18990,16 +19200,16 @@
         <v>45</v>
       </c>
       <c r="D31" t="s">
-        <v>1333</v>
+        <v>1349</v>
       </c>
       <c r="E31" t="s">
         <v>49</v>
       </c>
       <c r="F31" t="s">
-        <v>1334</v>
+        <v>1350</v>
       </c>
       <c r="G31" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="H31">
         <v>180000</v>
@@ -19020,16 +19230,16 @@
         <v>39</v>
       </c>
       <c r="N31" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O31" t="s">
-        <v>1335</v>
+        <v>1351</v>
       </c>
       <c r="P31" t="s">
-        <v>1336</v>
+        <v>1352</v>
       </c>
       <c r="Q31" t="s">
-        <v>1337</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
@@ -19043,7 +19253,7 @@
         <v>30</v>
       </c>
       <c r="D32" t="s">
-        <v>1338</v>
+        <v>1354</v>
       </c>
       <c r="E32" t="s">
         <v>49</v>
@@ -19052,7 +19262,7 @@
         <v>20</v>
       </c>
       <c r="G32" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="H32">
         <v>219100</v>
@@ -19073,16 +19283,16 @@
         <v>33</v>
       </c>
       <c r="N32" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O32" t="s">
-        <v>1339</v>
+        <v>1355</v>
       </c>
       <c r="P32" t="s">
-        <v>1340</v>
+        <v>1356</v>
       </c>
       <c r="Q32" t="s">
-        <v>1341</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
@@ -19096,7 +19306,7 @@
         <v>45</v>
       </c>
       <c r="D33" t="s">
-        <v>1342</v>
+        <v>1358</v>
       </c>
       <c r="E33" t="s">
         <v>49</v>
@@ -19105,7 +19315,7 @@
         <v>20</v>
       </c>
       <c r="G33" t="s">
-        <v>1206</v>
+        <v>1222</v>
       </c>
       <c r="H33">
         <v>219100</v>
@@ -19126,16 +19336,16 @@
         <v>39</v>
       </c>
       <c r="N33" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O33" t="s">
-        <v>1343</v>
+        <v>1359</v>
       </c>
       <c r="P33" t="s">
-        <v>1344</v>
+        <v>1360</v>
       </c>
       <c r="Q33" t="s">
-        <v>1345</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
@@ -19149,16 +19359,16 @@
         <v>30</v>
       </c>
       <c r="D34" t="s">
-        <v>1346</v>
+        <v>1362</v>
       </c>
       <c r="E34" t="s">
         <v>49</v>
       </c>
       <c r="F34" t="s">
-        <v>1347</v>
+        <v>1363</v>
       </c>
       <c r="G34" t="s">
-        <v>1206</v>
+        <v>1222</v>
       </c>
       <c r="J34" t="s">
         <v>32</v>
@@ -19173,16 +19383,16 @@
         <v>33</v>
       </c>
       <c r="N34" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O34" t="s">
-        <v>1348</v>
+        <v>1364</v>
       </c>
       <c r="P34" t="s">
-        <v>1349</v>
+        <v>1365</v>
       </c>
       <c r="Q34" t="s">
-        <v>1350</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
@@ -19196,16 +19406,16 @@
         <v>58</v>
       </c>
       <c r="D35" t="s">
-        <v>1351</v>
+        <v>1367</v>
       </c>
       <c r="E35" t="s">
-        <v>1352</v>
+        <v>1368</v>
       </c>
       <c r="F35" t="s">
-        <v>1353</v>
+        <v>1369</v>
       </c>
       <c r="G35" t="s">
-        <v>1206</v>
+        <v>1222</v>
       </c>
       <c r="H35">
         <v>257000</v>
@@ -19226,16 +19436,16 @@
         <v>39</v>
       </c>
       <c r="N35" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O35" t="s">
-        <v>1354</v>
+        <v>1370</v>
       </c>
       <c r="P35" t="s">
-        <v>1355</v>
+        <v>1371</v>
       </c>
       <c r="Q35" t="s">
-        <v>1356</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
@@ -19252,13 +19462,13 @@
         <v>478</v>
       </c>
       <c r="E36" t="s">
-        <v>1199</v>
+        <v>1215</v>
       </c>
       <c r="F36" t="s">
-        <v>1357</v>
+        <v>1373</v>
       </c>
       <c r="G36" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="H36">
         <v>200000</v>
@@ -19279,16 +19489,16 @@
         <v>33</v>
       </c>
       <c r="N36" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O36" t="s">
-        <v>1358</v>
+        <v>1374</v>
       </c>
       <c r="P36" t="s">
-        <v>1359</v>
+        <v>1375</v>
       </c>
       <c r="Q36" t="s">
-        <v>1360</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
@@ -19302,16 +19512,16 @@
         <v>20</v>
       </c>
       <c r="D37" t="s">
-        <v>1361</v>
+        <v>1377</v>
       </c>
       <c r="E37" t="s">
         <v>1008</v>
       </c>
       <c r="F37" t="s">
-        <v>1362</v>
+        <v>1378</v>
       </c>
       <c r="G37" t="s">
-        <v>1206</v>
+        <v>1222</v>
       </c>
       <c r="J37" t="s">
         <v>32</v>
@@ -19326,16 +19536,16 @@
         <v>33</v>
       </c>
       <c r="N37" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O37" t="s">
-        <v>1363</v>
+        <v>1379</v>
       </c>
       <c r="P37" t="s">
-        <v>1364</v>
+        <v>1380</v>
       </c>
       <c r="Q37" t="s">
-        <v>1365</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
@@ -19355,10 +19565,10 @@
         <v>1008</v>
       </c>
       <c r="F38" t="s">
-        <v>1366</v>
+        <v>1382</v>
       </c>
       <c r="G38" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="J38" t="s">
         <v>32</v>
@@ -19373,16 +19583,16 @@
         <v>33</v>
       </c>
       <c r="N38" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O38" t="s">
-        <v>1367</v>
+        <v>1383</v>
       </c>
       <c r="P38" t="s">
-        <v>1368</v>
+        <v>1384</v>
       </c>
       <c r="Q38" t="s">
-        <v>1369</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
@@ -19396,16 +19606,16 @@
         <v>15</v>
       </c>
       <c r="D39" t="s">
-        <v>1370</v>
+        <v>1386</v>
       </c>
       <c r="E39" t="s">
         <v>1008</v>
       </c>
       <c r="F39" t="s">
-        <v>1371</v>
+        <v>1387</v>
       </c>
       <c r="G39" t="s">
-        <v>1206</v>
+        <v>1222</v>
       </c>
       <c r="H39">
         <v>500000</v>
@@ -19426,16 +19636,16 @@
         <v>33</v>
       </c>
       <c r="N39" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O39" t="s">
-        <v>1372</v>
+        <v>1388</v>
       </c>
       <c r="P39" t="s">
-        <v>1373</v>
+        <v>1389</v>
       </c>
       <c r="Q39" t="s">
-        <v>1374</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
@@ -19449,16 +19659,16 @@
         <v>18</v>
       </c>
       <c r="D40" t="s">
-        <v>1375</v>
+        <v>1391</v>
       </c>
       <c r="E40" t="s">
         <v>798</v>
       </c>
       <c r="F40" t="s">
+        <v>1232</v>
+      </c>
+      <c r="G40" t="s">
         <v>1216</v>
-      </c>
-      <c r="G40" t="s">
-        <v>1200</v>
       </c>
       <c r="H40">
         <v>274456</v>
@@ -19479,16 +19689,16 @@
         <v>33</v>
       </c>
       <c r="N40" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O40" t="s">
-        <v>1376</v>
+        <v>1392</v>
       </c>
       <c r="P40" t="s">
-        <v>1377</v>
+        <v>1393</v>
       </c>
       <c r="Q40" t="s">
-        <v>1378</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
@@ -19502,16 +19712,16 @@
         <v>30</v>
       </c>
       <c r="D41" t="s">
-        <v>1379</v>
+        <v>1395</v>
       </c>
       <c r="E41" t="s">
         <v>798</v>
       </c>
       <c r="F41" t="s">
-        <v>1380</v>
+        <v>1396</v>
       </c>
       <c r="G41" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="J41" t="s">
         <v>32</v>
@@ -19526,16 +19736,16 @@
         <v>33</v>
       </c>
       <c r="N41" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O41" t="s">
-        <v>1381</v>
+        <v>1397</v>
       </c>
       <c r="P41" t="s">
-        <v>1382</v>
+        <v>1398</v>
       </c>
       <c r="Q41" t="s">
-        <v>1383</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
@@ -19549,16 +19759,16 @@
         <v>22</v>
       </c>
       <c r="D42" t="s">
-        <v>1384</v>
+        <v>1400</v>
       </c>
       <c r="E42" t="s">
         <v>798</v>
       </c>
       <c r="F42" t="s">
-        <v>1385</v>
+        <v>1401</v>
       </c>
       <c r="G42" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="J42" t="s">
         <v>32</v>
@@ -19573,16 +19783,16 @@
         <v>33</v>
       </c>
       <c r="N42" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O42" t="s">
-        <v>1386</v>
+        <v>1402</v>
       </c>
       <c r="P42" t="s">
-        <v>1387</v>
+        <v>1403</v>
       </c>
       <c r="Q42" t="s">
-        <v>1388</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
@@ -19596,16 +19806,16 @@
         <v>48</v>
       </c>
       <c r="D43" t="s">
-        <v>1389</v>
+        <v>1405</v>
       </c>
       <c r="E43" t="s">
         <v>798</v>
       </c>
       <c r="F43" t="s">
-        <v>1390</v>
+        <v>1406</v>
       </c>
       <c r="G43" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="J43" t="s">
         <v>32</v>
@@ -19620,16 +19830,16 @@
         <v>39</v>
       </c>
       <c r="N43" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O43" t="s">
-        <v>1391</v>
+        <v>1407</v>
       </c>
       <c r="P43" t="s">
-        <v>1392</v>
+        <v>1408</v>
       </c>
       <c r="Q43" t="s">
-        <v>1393</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
@@ -19643,16 +19853,16 @@
         <v>25</v>
       </c>
       <c r="D44" t="s">
-        <v>1394</v>
+        <v>1410</v>
       </c>
       <c r="E44" t="s">
         <v>798</v>
       </c>
       <c r="F44" t="s">
-        <v>1205</v>
+        <v>1221</v>
       </c>
       <c r="G44" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="J44" t="s">
         <v>32</v>
@@ -19667,16 +19877,16 @@
         <v>33</v>
       </c>
       <c r="N44" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O44" t="s">
-        <v>1395</v>
+        <v>1411</v>
       </c>
       <c r="P44" t="s">
-        <v>1396</v>
+        <v>1412</v>
       </c>
       <c r="Q44" t="s">
-        <v>1397</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
@@ -19690,16 +19900,16 @@
         <v>40</v>
       </c>
       <c r="D45" t="s">
-        <v>1398</v>
+        <v>1414</v>
       </c>
       <c r="E45" t="s">
         <v>798</v>
       </c>
       <c r="F45" t="s">
-        <v>1399</v>
+        <v>1415</v>
       </c>
       <c r="G45" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="J45" t="s">
         <v>32</v>
@@ -19714,16 +19924,16 @@
         <v>33</v>
       </c>
       <c r="N45" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O45" t="s">
-        <v>1400</v>
+        <v>1416</v>
       </c>
       <c r="P45" t="s">
-        <v>1401</v>
+        <v>1417</v>
       </c>
       <c r="Q45" t="s">
-        <v>1402</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
@@ -19737,16 +19947,16 @@
         <v>70</v>
       </c>
       <c r="D46" t="s">
-        <v>1403</v>
+        <v>1419</v>
       </c>
       <c r="E46" t="s">
-        <v>1404</v>
+        <v>1420</v>
       </c>
       <c r="F46" t="s">
-        <v>1405</v>
+        <v>1421</v>
       </c>
       <c r="G46" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="J46" t="s">
         <v>32</v>
@@ -19761,16 +19971,16 @@
         <v>33</v>
       </c>
       <c r="N46" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O46" t="s">
-        <v>1406</v>
+        <v>1422</v>
       </c>
       <c r="P46" t="s">
-        <v>1407</v>
+        <v>1423</v>
       </c>
       <c r="Q46" t="s">
-        <v>1408</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
@@ -19784,16 +19994,16 @@
         <v>58</v>
       </c>
       <c r="D47" t="s">
-        <v>1409</v>
+        <v>1425</v>
       </c>
       <c r="E47" t="s">
-        <v>1410</v>
+        <v>1426</v>
       </c>
       <c r="F47" t="s">
-        <v>1205</v>
+        <v>1221</v>
       </c>
       <c r="G47" t="s">
-        <v>1206</v>
+        <v>1222</v>
       </c>
       <c r="J47" t="s">
         <v>32</v>
@@ -19808,16 +20018,16 @@
         <v>33</v>
       </c>
       <c r="N47" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O47" t="s">
-        <v>1411</v>
+        <v>1427</v>
       </c>
       <c r="P47" t="s">
-        <v>1412</v>
+        <v>1428</v>
       </c>
       <c r="Q47" t="s">
-        <v>1413</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
@@ -19831,16 +20041,16 @@
         <v>32</v>
       </c>
       <c r="D48" t="s">
-        <v>1414</v>
+        <v>1430</v>
       </c>
       <c r="E48" t="s">
-        <v>1415</v>
+        <v>1431</v>
       </c>
       <c r="F48" t="s">
-        <v>1416</v>
+        <v>1432</v>
       </c>
       <c r="G48" t="s">
-        <v>1206</v>
+        <v>1222</v>
       </c>
       <c r="J48" t="s">
         <v>32</v>
@@ -19855,16 +20065,16 @@
         <v>33</v>
       </c>
       <c r="N48" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O48" t="s">
-        <v>1417</v>
+        <v>1433</v>
       </c>
       <c r="P48" t="s">
-        <v>1418</v>
+        <v>1434</v>
       </c>
       <c r="Q48" t="s">
-        <v>1419</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
@@ -19878,16 +20088,16 @@
         <v>4</v>
       </c>
       <c r="D49" t="s">
-        <v>1420</v>
+        <v>1436</v>
       </c>
       <c r="E49" t="s">
-        <v>1421</v>
+        <v>1437</v>
       </c>
       <c r="F49" t="s">
-        <v>1422</v>
+        <v>1438</v>
       </c>
       <c r="G49" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="J49" t="s">
         <v>32</v>
@@ -19902,16 +20112,16 @@
         <v>33</v>
       </c>
       <c r="N49" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O49" t="s">
-        <v>1423</v>
+        <v>1439</v>
       </c>
       <c r="P49" t="s">
-        <v>1424</v>
+        <v>1440</v>
       </c>
       <c r="Q49" t="s">
-        <v>1425</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
@@ -19925,16 +20135,16 @@
         <v>25</v>
       </c>
       <c r="D50" t="s">
-        <v>1426</v>
+        <v>1442</v>
       </c>
       <c r="E50" t="s">
-        <v>1427</v>
+        <v>1443</v>
       </c>
       <c r="F50" t="s">
-        <v>1262</v>
+        <v>1278</v>
       </c>
       <c r="G50" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="J50" t="s">
         <v>32</v>
@@ -19949,16 +20159,16 @@
         <v>33</v>
       </c>
       <c r="N50" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O50" t="s">
-        <v>1428</v>
+        <v>1444</v>
       </c>
       <c r="P50" t="s">
-        <v>1429</v>
+        <v>1445</v>
       </c>
       <c r="Q50" t="s">
-        <v>1430</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
@@ -19972,16 +20182,16 @@
         <v>30</v>
       </c>
       <c r="D51" t="s">
-        <v>1431</v>
+        <v>1447</v>
       </c>
       <c r="E51" t="s">
-        <v>1432</v>
+        <v>1448</v>
       </c>
       <c r="F51" t="s">
-        <v>1433</v>
+        <v>1449</v>
       </c>
       <c r="G51" t="s">
-        <v>1206</v>
+        <v>1222</v>
       </c>
       <c r="J51" t="s">
         <v>32</v>
@@ -19996,16 +20206,16 @@
         <v>33</v>
       </c>
       <c r="N51" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O51" t="s">
-        <v>1434</v>
+        <v>1450</v>
       </c>
       <c r="P51" t="s">
-        <v>1435</v>
+        <v>1451</v>
       </c>
       <c r="Q51" t="s">
-        <v>1436</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
@@ -20019,16 +20229,16 @@
         <v>52</v>
       </c>
       <c r="D52" t="s">
-        <v>1437</v>
+        <v>1453</v>
       </c>
       <c r="E52" t="s">
         <v>49</v>
       </c>
       <c r="F52" t="s">
-        <v>1438</v>
+        <v>1454</v>
       </c>
       <c r="G52" t="s">
-        <v>1206</v>
+        <v>1222</v>
       </c>
       <c r="H52">
         <v>180000</v>
@@ -20049,16 +20259,16 @@
         <v>39</v>
       </c>
       <c r="N52" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O52" t="s">
-        <v>1439</v>
+        <v>1455</v>
       </c>
       <c r="P52" t="s">
-        <v>1440</v>
+        <v>1456</v>
       </c>
       <c r="Q52" t="s">
-        <v>1441</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
@@ -20072,7 +20282,7 @@
         <v>50</v>
       </c>
       <c r="D53" t="s">
-        <v>1442</v>
+        <v>1458</v>
       </c>
       <c r="E53" t="s">
         <v>49</v>
@@ -20081,7 +20291,7 @@
         <v>20</v>
       </c>
       <c r="G53" t="s">
-        <v>1206</v>
+        <v>1222</v>
       </c>
       <c r="H53">
         <v>180000</v>
@@ -20102,16 +20312,16 @@
         <v>39</v>
       </c>
       <c r="N53" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O53" t="s">
-        <v>1443</v>
+        <v>1459</v>
       </c>
       <c r="P53" t="s">
-        <v>1444</v>
+        <v>1460</v>
       </c>
       <c r="Q53" t="s">
-        <v>1445</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
@@ -20125,7 +20335,7 @@
         <v>46</v>
       </c>
       <c r="D54" t="s">
-        <v>1446</v>
+        <v>1462</v>
       </c>
       <c r="E54" t="s">
         <v>49</v>
@@ -20134,7 +20344,7 @@
         <v>20</v>
       </c>
       <c r="G54" t="s">
-        <v>1206</v>
+        <v>1222</v>
       </c>
       <c r="H54">
         <v>180000</v>
@@ -20155,16 +20365,16 @@
         <v>39</v>
       </c>
       <c r="N54" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O54" t="s">
-        <v>1447</v>
+        <v>1463</v>
       </c>
       <c r="P54" t="s">
-        <v>1448</v>
+        <v>1464</v>
       </c>
       <c r="Q54" t="s">
-        <v>1449</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
@@ -20178,7 +20388,7 @@
         <v>38</v>
       </c>
       <c r="D55" t="s">
-        <v>1450</v>
+        <v>1466</v>
       </c>
       <c r="E55" t="s">
         <v>49</v>
@@ -20187,7 +20397,7 @@
         <v>20</v>
       </c>
       <c r="G55" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="H55">
         <v>217800</v>
@@ -20208,16 +20418,16 @@
         <v>33</v>
       </c>
       <c r="N55" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O55" t="s">
-        <v>1451</v>
+        <v>1467</v>
       </c>
       <c r="P55" t="s">
-        <v>1452</v>
+        <v>1468</v>
       </c>
       <c r="Q55" t="s">
-        <v>1453</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
@@ -20237,10 +20447,10 @@
         <v>49</v>
       </c>
       <c r="F56" t="s">
-        <v>1454</v>
+        <v>1470</v>
       </c>
       <c r="G56" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="H56">
         <v>180000</v>
@@ -20261,16 +20471,16 @@
         <v>39</v>
       </c>
       <c r="N56" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O56" t="s">
-        <v>1455</v>
+        <v>1471</v>
       </c>
       <c r="P56" t="s">
-        <v>1456</v>
+        <v>1472</v>
       </c>
       <c r="Q56" t="s">
-        <v>1457</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
@@ -20284,16 +20494,16 @@
         <v>45</v>
       </c>
       <c r="D57" t="s">
-        <v>1458</v>
+        <v>1474</v>
       </c>
       <c r="E57" t="s">
         <v>49</v>
       </c>
       <c r="F57" t="s">
-        <v>1459</v>
+        <v>1475</v>
       </c>
       <c r="G57" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="H57">
         <v>219100</v>
@@ -20314,16 +20524,16 @@
         <v>39</v>
       </c>
       <c r="N57" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O57" t="s">
-        <v>1460</v>
+        <v>1476</v>
       </c>
       <c r="P57" t="s">
-        <v>1461</v>
+        <v>1477</v>
       </c>
       <c r="Q57" t="s">
-        <v>1462</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
@@ -20337,16 +20547,16 @@
         <v>42</v>
       </c>
       <c r="D58" t="s">
-        <v>1463</v>
+        <v>1479</v>
       </c>
       <c r="E58" t="s">
         <v>49</v>
       </c>
       <c r="F58" t="s">
-        <v>1464</v>
+        <v>1480</v>
       </c>
       <c r="G58" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="H58">
         <v>180000</v>
@@ -20367,16 +20577,16 @@
         <v>39</v>
       </c>
       <c r="N58" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O58" t="s">
-        <v>1465</v>
+        <v>1481</v>
       </c>
       <c r="P58" t="s">
-        <v>1466</v>
+        <v>1482</v>
       </c>
       <c r="Q58" t="s">
-        <v>1467</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
@@ -20390,7 +20600,7 @@
         <v>32</v>
       </c>
       <c r="D59" t="s">
-        <v>1468</v>
+        <v>1484</v>
       </c>
       <c r="E59" t="s">
         <v>49</v>
@@ -20399,7 +20609,7 @@
         <v>20</v>
       </c>
       <c r="G59" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="H59">
         <v>219100</v>
@@ -20420,16 +20630,16 @@
         <v>33</v>
       </c>
       <c r="N59" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O59" t="s">
-        <v>1469</v>
+        <v>1485</v>
       </c>
       <c r="P59" t="s">
-        <v>1470</v>
+        <v>1486</v>
       </c>
       <c r="Q59" t="s">
-        <v>1471</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
@@ -20443,7 +20653,7 @@
         <v>35</v>
       </c>
       <c r="D60" t="s">
-        <v>1472</v>
+        <v>1488</v>
       </c>
       <c r="E60" t="s">
         <v>49</v>
@@ -20452,7 +20662,7 @@
         <v>20</v>
       </c>
       <c r="G60" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="H60">
         <v>219100</v>
@@ -20473,16 +20683,16 @@
         <v>33</v>
       </c>
       <c r="N60" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O60" t="s">
-        <v>1473</v>
+        <v>1489</v>
       </c>
       <c r="P60" t="s">
-        <v>1474</v>
+        <v>1490</v>
       </c>
       <c r="Q60" t="s">
-        <v>1475</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
@@ -20496,16 +20706,16 @@
         <v>40</v>
       </c>
       <c r="D61" t="s">
-        <v>1476</v>
+        <v>1492</v>
       </c>
       <c r="E61" t="s">
         <v>49</v>
       </c>
       <c r="F61" t="s">
-        <v>1477</v>
+        <v>1493</v>
       </c>
       <c r="G61" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="H61">
         <v>219100</v>
@@ -20526,16 +20736,16 @@
         <v>39</v>
       </c>
       <c r="N61" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O61" t="s">
-        <v>1478</v>
+        <v>1494</v>
       </c>
       <c r="P61" t="s">
-        <v>1479</v>
+        <v>1495</v>
       </c>
       <c r="Q61" t="s">
-        <v>1480</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
@@ -20549,7 +20759,7 @@
         <v>38</v>
       </c>
       <c r="D62" t="s">
-        <v>1481</v>
+        <v>1497</v>
       </c>
       <c r="E62" t="s">
         <v>49</v>
@@ -20558,7 +20768,7 @@
         <v>757</v>
       </c>
       <c r="G62" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="H62">
         <v>219100</v>
@@ -20579,16 +20789,16 @@
         <v>33</v>
       </c>
       <c r="N62" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O62" t="s">
-        <v>1482</v>
+        <v>1498</v>
       </c>
       <c r="P62" t="s">
-        <v>1483</v>
+        <v>1499</v>
       </c>
       <c r="Q62" t="s">
-        <v>1484</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
@@ -20602,7 +20812,7 @@
         <v>40</v>
       </c>
       <c r="D63" t="s">
-        <v>1485</v>
+        <v>1501</v>
       </c>
       <c r="E63" t="s">
         <v>49</v>
@@ -20611,7 +20821,7 @@
         <v>20</v>
       </c>
       <c r="G63" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="H63">
         <v>219100</v>
@@ -20632,16 +20842,16 @@
         <v>39</v>
       </c>
       <c r="N63" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O63" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
       <c r="P63" t="s">
-        <v>1487</v>
+        <v>1503</v>
       </c>
       <c r="Q63" t="s">
-        <v>1488</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
@@ -20655,16 +20865,16 @@
         <v>33</v>
       </c>
       <c r="D64" t="s">
-        <v>1489</v>
+        <v>1505</v>
       </c>
       <c r="E64" t="s">
         <v>49</v>
       </c>
       <c r="F64" t="s">
-        <v>1490</v>
+        <v>1506</v>
       </c>
       <c r="G64" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="H64">
         <v>219100</v>
@@ -20685,16 +20895,16 @@
         <v>33</v>
       </c>
       <c r="N64" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O64" t="s">
-        <v>1491</v>
+        <v>1507</v>
       </c>
       <c r="P64" t="s">
-        <v>1492</v>
+        <v>1508</v>
       </c>
       <c r="Q64" t="s">
-        <v>1493</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
@@ -20708,16 +20918,16 @@
         <v>48</v>
       </c>
       <c r="D65" t="s">
-        <v>1494</v>
+        <v>1510</v>
       </c>
       <c r="E65" t="s">
-        <v>1352</v>
+        <v>1368</v>
       </c>
       <c r="F65" t="s">
-        <v>1495</v>
+        <v>1511</v>
       </c>
       <c r="G65" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="J65" t="s">
         <v>32</v>
@@ -20732,16 +20942,16 @@
         <v>39</v>
       </c>
       <c r="N65" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O65" t="s">
-        <v>1496</v>
+        <v>1512</v>
       </c>
       <c r="P65" t="s">
-        <v>1497</v>
+        <v>1513</v>
       </c>
       <c r="Q65" t="s">
-        <v>1498</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
@@ -20755,16 +20965,16 @@
         <v>40</v>
       </c>
       <c r="D66" t="s">
-        <v>1198</v>
+        <v>1214</v>
       </c>
       <c r="E66" t="s">
-        <v>1199</v>
+        <v>1215</v>
       </c>
       <c r="F66" t="s">
-        <v>1499</v>
+        <v>1515</v>
       </c>
       <c r="G66" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="H66">
         <v>184200</v>
@@ -20785,16 +20995,16 @@
         <v>39</v>
       </c>
       <c r="N66" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O66" t="s">
-        <v>1500</v>
+        <v>1516</v>
       </c>
       <c r="P66" t="s">
-        <v>1501</v>
+        <v>1517</v>
       </c>
       <c r="Q66" t="s">
-        <v>1502</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
@@ -20808,16 +21018,16 @@
         <v>30</v>
       </c>
       <c r="D67" t="s">
-        <v>1503</v>
+        <v>1519</v>
       </c>
       <c r="E67" t="s">
-        <v>1199</v>
+        <v>1215</v>
       </c>
       <c r="F67" t="s">
-        <v>1504</v>
+        <v>1520</v>
       </c>
       <c r="G67" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="H67">
         <v>200000</v>
@@ -20838,16 +21048,16 @@
         <v>33</v>
       </c>
       <c r="N67" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O67" t="s">
-        <v>1505</v>
+        <v>1521</v>
       </c>
       <c r="P67" t="s">
-        <v>1506</v>
+        <v>1522</v>
       </c>
       <c r="Q67" t="s">
-        <v>1507</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
@@ -20861,7 +21071,7 @@
         <v>30</v>
       </c>
       <c r="D68" t="s">
-        <v>1508</v>
+        <v>1524</v>
       </c>
       <c r="E68" t="s">
         <v>1008</v>
@@ -20870,7 +21080,7 @@
         <v>1017</v>
       </c>
       <c r="G68" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="J68" t="s">
         <v>32</v>
@@ -20885,16 +21095,16 @@
         <v>33</v>
       </c>
       <c r="N68" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O68" t="s">
-        <v>1509</v>
+        <v>1525</v>
       </c>
       <c r="P68" t="s">
-        <v>1510</v>
+        <v>1526</v>
       </c>
       <c r="Q68" t="s">
-        <v>1511</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
@@ -20914,10 +21124,10 @@
         <v>1008</v>
       </c>
       <c r="F69" t="s">
-        <v>1366</v>
+        <v>1382</v>
       </c>
       <c r="G69" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="J69" t="s">
         <v>32</v>
@@ -20932,16 +21142,16 @@
         <v>33</v>
       </c>
       <c r="N69" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O69" t="s">
-        <v>1512</v>
+        <v>1528</v>
       </c>
       <c r="P69" t="s">
-        <v>1513</v>
+        <v>1529</v>
       </c>
       <c r="Q69" t="s">
-        <v>1514</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
@@ -20955,7 +21165,7 @@
         <v>32</v>
       </c>
       <c r="D70" t="s">
-        <v>1515</v>
+        <v>1531</v>
       </c>
       <c r="E70" t="s">
         <v>1008</v>
@@ -20964,7 +21174,7 @@
         <v>1017</v>
       </c>
       <c r="G70" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="J70" t="s">
         <v>32</v>
@@ -20979,16 +21189,16 @@
         <v>33</v>
       </c>
       <c r="N70" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O70" t="s">
-        <v>1516</v>
+        <v>1532</v>
       </c>
       <c r="P70" t="s">
-        <v>1517</v>
+        <v>1533</v>
       </c>
       <c r="Q70" t="s">
-        <v>1518</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
@@ -21002,16 +21212,16 @@
         <v>45</v>
       </c>
       <c r="D71" t="s">
-        <v>1519</v>
+        <v>1535</v>
       </c>
       <c r="E71" t="s">
         <v>798</v>
       </c>
       <c r="F71" t="s">
-        <v>1211</v>
+        <v>1227</v>
       </c>
       <c r="G71" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="J71" t="s">
         <v>32</v>
@@ -21026,16 +21236,16 @@
         <v>39</v>
       </c>
       <c r="N71" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O71" t="s">
-        <v>1520</v>
+        <v>1536</v>
       </c>
       <c r="P71" t="s">
-        <v>1521</v>
+        <v>1537</v>
       </c>
       <c r="Q71" t="s">
-        <v>1522</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
@@ -21049,16 +21259,16 @@
         <v>35</v>
       </c>
       <c r="D72" t="s">
-        <v>1523</v>
+        <v>1539</v>
       </c>
       <c r="E72" t="s">
         <v>798</v>
       </c>
       <c r="F72" t="s">
-        <v>1524</v>
+        <v>1540</v>
       </c>
       <c r="G72" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="J72" t="s">
         <v>32</v>
@@ -21073,16 +21283,16 @@
         <v>33</v>
       </c>
       <c r="N72" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O72" t="s">
-        <v>1525</v>
+        <v>1541</v>
       </c>
       <c r="P72" t="s">
-        <v>1526</v>
+        <v>1542</v>
       </c>
       <c r="Q72" t="s">
-        <v>1527</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
@@ -21096,7 +21306,7 @@
         <v>35</v>
       </c>
       <c r="D73" t="s">
-        <v>1528</v>
+        <v>1544</v>
       </c>
       <c r="E73" t="s">
         <v>798</v>
@@ -21105,7 +21315,7 @@
         <v>85</v>
       </c>
       <c r="G73" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="J73" t="s">
         <v>32</v>
@@ -21120,16 +21330,16 @@
         <v>33</v>
       </c>
       <c r="N73" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O73" t="s">
-        <v>1529</v>
+        <v>1545</v>
       </c>
       <c r="P73" t="s">
-        <v>1530</v>
+        <v>1546</v>
       </c>
       <c r="Q73" t="s">
-        <v>1531</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
@@ -21143,16 +21353,16 @@
         <v>15</v>
       </c>
       <c r="D74" t="s">
-        <v>1532</v>
+        <v>1548</v>
       </c>
       <c r="E74" t="s">
         <v>798</v>
       </c>
       <c r="F74" t="s">
-        <v>1533</v>
+        <v>1549</v>
       </c>
       <c r="G74" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="J74" t="s">
         <v>32</v>
@@ -21167,16 +21377,16 @@
         <v>33</v>
       </c>
       <c r="N74" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O74" t="s">
-        <v>1534</v>
+        <v>1550</v>
       </c>
       <c r="P74" t="s">
-        <v>1535</v>
+        <v>1551</v>
       </c>
       <c r="Q74" t="s">
-        <v>1536</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
@@ -21190,16 +21400,16 @@
         <v>25</v>
       </c>
       <c r="D75" t="s">
-        <v>1537</v>
+        <v>1553</v>
       </c>
       <c r="E75" t="s">
         <v>798</v>
       </c>
       <c r="F75" t="s">
-        <v>1538</v>
+        <v>1554</v>
       </c>
       <c r="G75" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="J75" t="s">
         <v>32</v>
@@ -21214,16 +21424,16 @@
         <v>33</v>
       </c>
       <c r="N75" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O75" t="s">
-        <v>1539</v>
+        <v>1555</v>
       </c>
       <c r="P75" t="s">
-        <v>1540</v>
+        <v>1556</v>
       </c>
       <c r="Q75" t="s">
-        <v>1541</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
@@ -21237,16 +21447,16 @@
         <v>30</v>
       </c>
       <c r="D76" t="s">
-        <v>1542</v>
+        <v>1558</v>
       </c>
       <c r="E76" t="s">
         <v>798</v>
       </c>
       <c r="F76" t="s">
-        <v>1543</v>
+        <v>1559</v>
       </c>
       <c r="G76" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="J76" t="s">
         <v>32</v>
@@ -21261,16 +21471,16 @@
         <v>33</v>
       </c>
       <c r="N76" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O76" t="s">
-        <v>1544</v>
+        <v>1560</v>
       </c>
       <c r="P76" t="s">
-        <v>1545</v>
+        <v>1561</v>
       </c>
       <c r="Q76" t="s">
-        <v>1546</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
@@ -21290,10 +21500,10 @@
         <v>49</v>
       </c>
       <c r="F77" t="s">
-        <v>1504</v>
+        <v>1520</v>
       </c>
       <c r="G77" t="s">
-        <v>1206</v>
+        <v>1222</v>
       </c>
       <c r="J77" t="s">
         <v>32</v>
@@ -21308,16 +21518,16 @@
         <v>33</v>
       </c>
       <c r="N77" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O77" t="s">
-        <v>1547</v>
+        <v>1563</v>
       </c>
       <c r="P77" t="s">
-        <v>1548</v>
+        <v>1564</v>
       </c>
       <c r="Q77" t="s">
-        <v>1549</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
@@ -21337,10 +21547,10 @@
         <v>49</v>
       </c>
       <c r="F78" t="s">
-        <v>1550</v>
+        <v>1566</v>
       </c>
       <c r="G78" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="J78" t="s">
         <v>32</v>
@@ -21355,16 +21565,16 @@
         <v>39</v>
       </c>
       <c r="N78" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O78" t="s">
-        <v>1551</v>
+        <v>1567</v>
       </c>
       <c r="P78" t="s">
-        <v>1552</v>
+        <v>1568</v>
       </c>
       <c r="Q78" t="s">
-        <v>1553</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
@@ -21387,7 +21597,7 @@
         <v>1074</v>
       </c>
       <c r="G79" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="H79">
         <v>180000</v>
@@ -21408,16 +21618,16 @@
         <v>33</v>
       </c>
       <c r="N79" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O79" t="s">
-        <v>1554</v>
+        <v>1570</v>
       </c>
       <c r="P79" t="s">
-        <v>1555</v>
+        <v>1571</v>
       </c>
       <c r="Q79" t="s">
-        <v>1556</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
@@ -21437,10 +21647,10 @@
         <v>49</v>
       </c>
       <c r="F80" t="s">
-        <v>1557</v>
+        <v>1573</v>
       </c>
       <c r="G80" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="H80">
         <v>180000</v>
@@ -21461,16 +21671,16 @@
         <v>33</v>
       </c>
       <c r="N80" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O80" t="s">
-        <v>1558</v>
+        <v>1574</v>
       </c>
       <c r="P80" t="s">
-        <v>1559</v>
+        <v>1575</v>
       </c>
       <c r="Q80" t="s">
-        <v>1560</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
@@ -21484,16 +21694,16 @@
         <v>20</v>
       </c>
       <c r="D81" t="s">
-        <v>1561</v>
+        <v>1577</v>
       </c>
       <c r="E81" t="s">
         <v>1119</v>
       </c>
       <c r="F81" t="s">
-        <v>1562</v>
+        <v>1578</v>
       </c>
       <c r="G81" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="J81" t="s">
         <v>32</v>
@@ -21508,16 +21718,16 @@
         <v>33</v>
       </c>
       <c r="N81" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O81" t="s">
-        <v>1563</v>
+        <v>1579</v>
       </c>
       <c r="P81" t="s">
-        <v>1564</v>
+        <v>1580</v>
       </c>
       <c r="Q81" t="s">
-        <v>1565</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
@@ -21531,7 +21741,7 @@
         <v>50</v>
       </c>
       <c r="D82" t="s">
-        <v>1566</v>
+        <v>1582</v>
       </c>
       <c r="E82" t="s">
         <v>1119</v>
@@ -21540,7 +21750,7 @@
         <v>20</v>
       </c>
       <c r="G82" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="H82">
         <v>250000</v>
@@ -21561,16 +21771,16 @@
         <v>39</v>
       </c>
       <c r="N82" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O82" t="s">
-        <v>1567</v>
+        <v>1583</v>
       </c>
       <c r="P82" t="s">
-        <v>1568</v>
+        <v>1584</v>
       </c>
       <c r="Q82" t="s">
-        <v>1569</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
@@ -21584,7 +21794,7 @@
         <v>55</v>
       </c>
       <c r="D83" t="s">
-        <v>1570</v>
+        <v>1586</v>
       </c>
       <c r="E83" t="s">
         <v>1119</v>
@@ -21593,7 +21803,7 @@
         <v>20</v>
       </c>
       <c r="G83" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="H83">
         <v>200000</v>
@@ -21614,16 +21824,16 @@
         <v>39</v>
       </c>
       <c r="N83" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O83" t="s">
-        <v>1571</v>
+        <v>1587</v>
       </c>
       <c r="P83" t="s">
-        <v>1572</v>
+        <v>1588</v>
       </c>
       <c r="Q83" t="s">
-        <v>1573</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
@@ -21637,7 +21847,7 @@
         <v>52</v>
       </c>
       <c r="D84" t="s">
-        <v>1574</v>
+        <v>1590</v>
       </c>
       <c r="E84" t="s">
         <v>1119</v>
@@ -21646,7 +21856,7 @@
         <v>20</v>
       </c>
       <c r="G84" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="H84">
         <v>250000</v>
@@ -21667,16 +21877,16 @@
         <v>39</v>
       </c>
       <c r="N84" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O84" t="s">
-        <v>1575</v>
+        <v>1591</v>
       </c>
       <c r="P84" t="s">
-        <v>1576</v>
+        <v>1592</v>
       </c>
       <c r="Q84" t="s">
-        <v>1577</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
@@ -21690,7 +21900,7 @@
         <v>53</v>
       </c>
       <c r="D85" t="s">
-        <v>1578</v>
+        <v>1594</v>
       </c>
       <c r="E85" t="s">
         <v>1119</v>
@@ -21699,7 +21909,7 @@
         <v>20</v>
       </c>
       <c r="G85" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="H85">
         <v>200000</v>
@@ -21720,16 +21930,16 @@
         <v>39</v>
       </c>
       <c r="N85" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O85" t="s">
-        <v>1579</v>
+        <v>1595</v>
       </c>
       <c r="P85" t="s">
-        <v>1580</v>
+        <v>1596</v>
       </c>
       <c r="Q85" t="s">
-        <v>1581</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
@@ -21743,7 +21953,7 @@
         <v>50</v>
       </c>
       <c r="D86" t="s">
-        <v>1582</v>
+        <v>1598</v>
       </c>
       <c r="E86" t="s">
         <v>1119</v>
@@ -21752,7 +21962,7 @@
         <v>20</v>
       </c>
       <c r="G86" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="H86">
         <v>200000</v>
@@ -21773,16 +21983,16 @@
         <v>39</v>
       </c>
       <c r="N86" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O86" t="s">
-        <v>1583</v>
+        <v>1599</v>
       </c>
       <c r="P86" t="s">
-        <v>1584</v>
+        <v>1600</v>
       </c>
       <c r="Q86" t="s">
-        <v>1585</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
@@ -21796,7 +22006,7 @@
         <v>55</v>
       </c>
       <c r="D87" t="s">
-        <v>1586</v>
+        <v>1602</v>
       </c>
       <c r="E87" t="s">
         <v>1119</v>
@@ -21805,7 +22015,7 @@
         <v>20</v>
       </c>
       <c r="G87" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="H87">
         <v>250000</v>
@@ -21826,16 +22036,16 @@
         <v>39</v>
       </c>
       <c r="N87" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O87" t="s">
-        <v>1587</v>
+        <v>1603</v>
       </c>
       <c r="P87" t="s">
-        <v>1588</v>
+        <v>1604</v>
       </c>
       <c r="Q87" t="s">
-        <v>1589</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
@@ -21849,16 +22059,16 @@
         <v>45</v>
       </c>
       <c r="D88" t="s">
-        <v>1590</v>
+        <v>1606</v>
       </c>
       <c r="E88" t="s">
-        <v>1591</v>
+        <v>1607</v>
       </c>
       <c r="F88" t="s">
-        <v>1592</v>
+        <v>1608</v>
       </c>
       <c r="G88" t="s">
-        <v>1206</v>
+        <v>1222</v>
       </c>
       <c r="H88">
         <v>154000</v>
@@ -21879,16 +22089,16 @@
         <v>33</v>
       </c>
       <c r="N88" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O88" t="s">
-        <v>1593</v>
+        <v>1609</v>
       </c>
       <c r="P88" t="s">
-        <v>1594</v>
+        <v>1610</v>
       </c>
       <c r="Q88" t="s">
-        <v>1595</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
@@ -21911,7 +22121,7 @@
         <v>757</v>
       </c>
       <c r="G89" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="H89">
         <v>180000</v>
@@ -21932,16 +22142,16 @@
         <v>39</v>
       </c>
       <c r="N89" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O89" t="s">
-        <v>1596</v>
+        <v>1612</v>
       </c>
       <c r="P89" t="s">
-        <v>1597</v>
+        <v>1613</v>
       </c>
       <c r="Q89" t="s">
-        <v>1598</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
@@ -21961,10 +22171,10 @@
         <v>49</v>
       </c>
       <c r="F90" t="s">
-        <v>1454</v>
+        <v>1470</v>
       </c>
       <c r="G90" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="H90">
         <v>219100</v>
@@ -21985,16 +22195,16 @@
         <v>33</v>
       </c>
       <c r="N90" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O90" t="s">
-        <v>1599</v>
+        <v>1615</v>
       </c>
       <c r="P90" t="s">
-        <v>1600</v>
+        <v>1616</v>
       </c>
       <c r="Q90" t="s">
-        <v>1601</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
@@ -22008,16 +22218,16 @@
         <v>25</v>
       </c>
       <c r="D91" t="s">
-        <v>1602</v>
+        <v>1618</v>
       </c>
       <c r="E91" t="s">
         <v>49</v>
       </c>
       <c r="F91" t="s">
-        <v>1603</v>
+        <v>1619</v>
       </c>
       <c r="G91" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="J91" t="s">
         <v>32</v>
@@ -22032,16 +22242,16 @@
         <v>33</v>
       </c>
       <c r="N91" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O91" t="s">
-        <v>1604</v>
+        <v>1620</v>
       </c>
       <c r="P91" t="s">
-        <v>1605</v>
+        <v>1621</v>
       </c>
       <c r="Q91" t="s">
-        <v>1606</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
@@ -22061,10 +22271,10 @@
         <v>1008</v>
       </c>
       <c r="F92" t="s">
-        <v>1205</v>
+        <v>1221</v>
       </c>
       <c r="G92" t="s">
-        <v>1206</v>
+        <v>1222</v>
       </c>
       <c r="J92" t="s">
         <v>32</v>
@@ -22079,16 +22289,16 @@
         <v>33</v>
       </c>
       <c r="N92" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O92" t="s">
-        <v>1607</v>
+        <v>1623</v>
       </c>
       <c r="P92" t="s">
-        <v>1608</v>
+        <v>1624</v>
       </c>
       <c r="Q92" t="s">
-        <v>1609</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
@@ -22102,16 +22312,16 @@
         <v>15</v>
       </c>
       <c r="D93" t="s">
-        <v>1610</v>
+        <v>1626</v>
       </c>
       <c r="E93" t="s">
-        <v>1611</v>
+        <v>1627</v>
       </c>
       <c r="F93" t="s">
-        <v>1422</v>
+        <v>1438</v>
       </c>
       <c r="G93" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="J93" t="s">
         <v>32</v>
@@ -22126,16 +22336,16 @@
         <v>33</v>
       </c>
       <c r="N93" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O93" t="s">
-        <v>1612</v>
+        <v>1628</v>
       </c>
       <c r="P93" t="s">
-        <v>1613</v>
+        <v>1629</v>
       </c>
       <c r="Q93" t="s">
-        <v>1614</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
@@ -22149,16 +22359,16 @@
         <v>12</v>
       </c>
       <c r="D94" t="s">
-        <v>1615</v>
+        <v>1631</v>
       </c>
       <c r="E94" t="s">
-        <v>1616</v>
+        <v>1632</v>
       </c>
       <c r="F94" t="s">
-        <v>1617</v>
+        <v>1633</v>
       </c>
       <c r="G94" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="J94" t="s">
         <v>32</v>
@@ -22173,16 +22383,16 @@
         <v>33</v>
       </c>
       <c r="N94" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O94" t="s">
-        <v>1618</v>
+        <v>1634</v>
       </c>
       <c r="P94" t="s">
-        <v>1619</v>
+        <v>1635</v>
       </c>
       <c r="Q94" t="s">
-        <v>1620</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
@@ -22196,16 +22406,16 @@
         <v>42</v>
       </c>
       <c r="D95" t="s">
-        <v>1621</v>
+        <v>1637</v>
       </c>
       <c r="E95" t="s">
         <v>49</v>
       </c>
       <c r="F95" t="s">
-        <v>1622</v>
+        <v>1638</v>
       </c>
       <c r="G95" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="H95">
         <v>180000</v>
@@ -22226,16 +22436,16 @@
         <v>39</v>
       </c>
       <c r="N95" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O95" t="s">
-        <v>1623</v>
+        <v>1639</v>
       </c>
       <c r="P95" t="s">
-        <v>1624</v>
+        <v>1640</v>
       </c>
       <c r="Q95" t="s">
-        <v>1625</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
@@ -22249,16 +22459,16 @@
         <v>22</v>
       </c>
       <c r="D96" t="s">
-        <v>1626</v>
+        <v>1642</v>
       </c>
       <c r="E96" t="s">
-        <v>1199</v>
+        <v>1215</v>
       </c>
       <c r="F96" t="s">
-        <v>1627</v>
+        <v>1643</v>
       </c>
       <c r="G96" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="H96">
         <v>200000</v>
@@ -22279,16 +22489,16 @@
         <v>33</v>
       </c>
       <c r="N96" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O96" t="s">
-        <v>1628</v>
+        <v>1644</v>
       </c>
       <c r="P96" t="s">
-        <v>1629</v>
+        <v>1645</v>
       </c>
       <c r="Q96" t="s">
-        <v>1630</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
@@ -22302,16 +22512,16 @@
         <v>28</v>
       </c>
       <c r="D97" t="s">
-        <v>1631</v>
+        <v>1647</v>
       </c>
       <c r="E97" t="s">
-        <v>1632</v>
+        <v>1648</v>
       </c>
       <c r="F97" t="s">
-        <v>1603</v>
+        <v>1619</v>
       </c>
       <c r="G97" t="s">
-        <v>1206</v>
+        <v>1222</v>
       </c>
       <c r="J97" t="s">
         <v>32</v>
@@ -22326,16 +22536,16 @@
         <v>33</v>
       </c>
       <c r="N97" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O97" t="s">
-        <v>1633</v>
+        <v>1649</v>
       </c>
       <c r="P97" t="s">
-        <v>1634</v>
+        <v>1650</v>
       </c>
       <c r="Q97" t="s">
-        <v>1635</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
@@ -22349,16 +22559,16 @@
         <v>5</v>
       </c>
       <c r="D98" t="s">
-        <v>1636</v>
+        <v>1652</v>
       </c>
       <c r="E98" t="s">
-        <v>1637</v>
+        <v>1653</v>
       </c>
       <c r="F98" t="s">
-        <v>1638</v>
+        <v>1654</v>
       </c>
       <c r="G98" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="J98" t="s">
         <v>32</v>
@@ -22373,16 +22583,16 @@
         <v>33</v>
       </c>
       <c r="N98" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O98" t="s">
-        <v>1639</v>
+        <v>1655</v>
       </c>
       <c r="P98" t="s">
-        <v>1640</v>
+        <v>1656</v>
       </c>
       <c r="Q98" t="s">
-        <v>1641</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.25">
@@ -22402,10 +22612,10 @@
         <v>49</v>
       </c>
       <c r="F99" t="s">
-        <v>1642</v>
+        <v>1658</v>
       </c>
       <c r="G99" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="J99" t="s">
         <v>32</v>
@@ -22420,16 +22630,63 @@
         <v>39</v>
       </c>
       <c r="N99" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="O99" t="s">
-        <v>1643</v>
+        <v>1659</v>
       </c>
       <c r="P99" t="s">
-        <v>1644</v>
+        <v>1660</v>
       </c>
       <c r="Q99" t="s">
-        <v>1645</v>
+        <v>1661</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>17</v>
+      </c>
+      <c r="B100">
+        <v>25</v>
+      </c>
+      <c r="C100">
+        <v>35</v>
+      </c>
+      <c r="D100" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E100" t="s">
+        <v>1663</v>
+      </c>
+      <c r="F100" t="s">
+        <v>1432</v>
+      </c>
+      <c r="G100" t="s">
+        <v>1216</v>
+      </c>
+      <c r="J100" t="s">
+        <v>32</v>
+      </c>
+      <c r="K100" t="s">
+        <v>151</v>
+      </c>
+      <c r="L100" t="s">
+        <v>1200</v>
+      </c>
+      <c r="M100" t="s">
+        <v>33</v>
+      </c>
+      <c r="N100" t="s">
+        <v>1217</v>
+      </c>
+      <c r="O100" t="s">
+        <v>1664</v>
+      </c>
+      <c r="P100" t="s">
+        <v>1665</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>1666</v>
       </c>
     </row>
   </sheetData>

--- a/hunt/board.xlsx
+++ b/hunt/board.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4233" uniqueCount="1574">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4428" uniqueCount="1648">
   <si>
     <t>Column</t>
   </si>
@@ -3263,6 +3263,183 @@
     <t>https://databricks.com/company/careers/open-positions/job?gh_jid=6049142002</t>
   </si>
   <si>
+    <t>Architect, LTS Solutions - Remote</t>
+  </si>
+  <si>
+    <t>APL Logistics</t>
+  </si>
+  <si>
+    <t>2026-09-01T15:56:33.193Z</t>
+  </si>
+  <si>
+    <t>Fully remote, US-based | Architect-level title with customer-facing advisory framing similar to candidate's trusted-advisor model</t>
+  </si>
+  <si>
+    <t>This is a transportation/logistics network solutions design role (drayage, control tower, cross-border), not cloud/DevOps architecture | Requires domain expertise in multi-modal transport operations and APLL TMS platforms the candidate has none of | No Azure, CI/CD, or governance content in the requirements at all</t>
+  </si>
+  <si>
+    <t>https://himalayas.app/companies/apl-logistics/jobs/architect-lts-solutions-remote</t>
+  </si>
+  <si>
+    <t>Manager, Solutions Architects - SF Bay area</t>
+  </si>
+  <si>
+    <t>GitLab</t>
+  </si>
+  <si>
+    <t>GitLab DevSecOps platform maps closely to the candidate's CI/CD, GHAS-style security scanning, and DevOps maturity assessment experience | Remote US role with confirmed $154K–$231K band whose midpoint clears the $180K floor | Solutions Architect domain is exactly the candidate's current function</t>
+  </si>
+  <si>
+    <t>People-management role (Manager of SAs) — candidate has no documented team-management or SA leadership track record | SF Bay area territory focus may imply regional presence expectations | Pre-sales leadership with quota/pipeline accountability, a shift from hands-on advisory delivery</t>
+  </si>
+  <si>
+    <t>https://jobicy.com/jobs/144921-manager-solutions-architects-sf-bay-area</t>
+  </si>
+  <si>
+    <t>Power BI Architect</t>
+  </si>
+  <si>
+    <t>Tiger Analytics</t>
+  </si>
+  <si>
+    <t>Azure ecosystem grounding is relevant to the platform side of the role | Remote US consulting role with enterprise Fortune 100 clients</t>
+  </si>
+  <si>
+    <t>Requires deep Power BI/DAX/tabular modeling and BI governance expertise absent from the resume | Data/BI architecture is a different discipline from cloud platform and DevOps architecture | No compensation posted; consulting BI architect bands often fall under $180K</t>
+  </si>
+  <si>
+    <t>https://jobicy.com/jobs/143584-power-bi-architect</t>
+  </si>
+  <si>
+    <t>Ontology Architect</t>
+  </si>
+  <si>
+    <t>Remote US, architect-level title with enterprise Fortune 100 client exposure</t>
+  </si>
+  <si>
+    <t>Requires ontology/taxonomy modeling and knowledge-graph architecture (RDF/OWL/SPARQL) expertise the candidate does not have | No overlap with Azure DevOps, GitHub, IaC, or cloud governance skillset | Unposted comp at a consultancy, uncertain vs. $180K floor</t>
+  </si>
+  <si>
+    <t>https://jobicy.com/jobs/147512-ontology-architect</t>
+  </si>
+  <si>
+    <t>Cloud Solutions Architect - Alliances</t>
+  </si>
+  <si>
+    <t>Canonical</t>
+  </si>
+  <si>
+    <t>Cloud Solutions Architect title directly matches a target title, working with hyperscaler and silicon partners | Fully remote/distributed and partner-advisory in nature, close to the candidate's trusted-advisor engagement style</t>
+  </si>
+  <si>
+    <t>Canonical expects deep Linux/Ubuntu, open-source infrastructure and often AWS/GCP-centric depth rather than Azure DevOps/GitHub specialization | Canonical's known compensation bands and academic-transcript-heavy hiring process often fall below a $180K US floor | Requires several in-person global team sprints per year</t>
+  </si>
+  <si>
+    <t>https://jobicy.com/jobs/149568-cloud-solutions-architect-alliances</t>
+  </si>
+  <si>
+    <t>Partner Solution Architect - GSI</t>
+  </si>
+  <si>
+    <t>Zscaler</t>
+  </si>
+  <si>
+    <t>Confirmed $170.6K–$243.8K remote band comfortably supports the $180K target | Partner/GSI architect work is technical advisory with enterprise scope, aligned to candidate's customer engineer role | Zero Trust and cloud security governance touch the candidate's Entra ID, RBAC, and compliance (HIPAA/PCI/NIST) experience</t>
+  </si>
+  <si>
+    <t>Requires hands-on Zscaler/ZTNA network-security product depth (proxy, SASE) the resume doesn't demonstrate | CCNA is dated relative to the deep networking fluency these roles expect | Heavy GSI partner enablement and pre-sales orientation rather than hands-on DevOps delivery</t>
+  </si>
+  <si>
+    <t>https://jobicy.com/jobs/145918-partner-solution-architect-gsi</t>
+  </si>
+  <si>
+    <t>Customer Solution Architect Team Lead (AMER)</t>
+  </si>
+  <si>
+    <t>Remote AMER role with an unusually high posted comp figure ($500K listed, likely total/OTE) far above the floor | Customer solutions architecture with pre-sales discovery and proof-of-value maps to candidate's advisory experience</t>
+  </si>
+  <si>
+    <t>Team Lead role requiring people management of CSAs — no management experience on the resume | Requires deep Postgres, Supabase/edge-function and app-backend expertise rather than Azure DevOps/GitHub governance | Explicitly supports the East Coast region, which may conflict with Houston-based coverage expectations</t>
+  </si>
+  <si>
+    <t>https://jobicy.com/jobs/145204-customer-solution-architect-team-lead-amer</t>
+  </si>
+  <si>
+    <t>Senior Customer Architect</t>
+  </si>
+  <si>
+    <t>GrowthLoop</t>
+  </si>
+  <si>
+    <t>Confirmed $180K–$200K band exactly meets the salary floor for a remote US role | Owning strategic enterprise accounts and leading complex technical implementations mirrors the candidate's trusted-advisor delivery work | Enterprise cloud data platform work touches cloud architecture and identity/security governance familiarity</t>
+  </si>
+  <si>
+    <t>Core stack is CDP/marketing-data (BigQuery/Snowflake, audience activation) — candidate has no martech or data-warehouse activation experience | Google Cloud/BigQuery-centric data plumbing rather than Azure depth | Scope is senior IC customer architect, below the principal-level scope the candidate is targeting</t>
+  </si>
+  <si>
+    <t>https://jobicy.com/jobs/142087-senior-customer-architect</t>
+  </si>
+  <si>
+    <t>Software Architect - Containers / Virtualisation</t>
+  </si>
+  <si>
+    <t>EMEA,  LATAM,  Canada,  USA</t>
+  </si>
+  <si>
+    <t>Remote-first global role with architect-level title | Container/virtualization domain overlaps loosely with cloud platform work</t>
+  </si>
+  <si>
+    <t>Requires deep systems-level Go/C engineering on LXD and MicroCloud internals — a hands-on OSS product engineering role, not cloud advisory | No Azure DevOps, GitHub governance, or customer-facing architecture content | Unposted comp; Canonical bands often fall short of $180K USD</t>
+  </si>
+  <si>
+    <t>https://jobicy.com/jobs/149981-software-architect-containers-virtualisation</t>
+  </si>
+  <si>
+    <t>AWS DevOps Engineer (Senior) - Migration Project (VMware to AWS)</t>
+  </si>
+  <si>
+    <t>Mactores</t>
+  </si>
+  <si>
+    <t>Candidate has deep CI/CD pipeline architecture and IaC (Terraform, Bash, Python) experience that transfers to AWS pipeline/cutover work | Migration/modernization delivery with architecture ownership matches the candidate's advisory-plus-delivery engagement style | Fully remote, so no relocation friction</t>
+  </si>
+  <si>
+    <t>Role is explicitly AWS-primary (VMware-to-AWS estate migration); candidate's depth is Azure/Azure DevOps with no AWS credentials listed | No VMware estate or large-scale lift-and-shift migration experience evident in the profile | Senior IC engineer scope rather than the principal/architect-level scope the candidate targets</t>
+  </si>
+  <si>
+    <t>https://jobicy.com/jobs/152284-aws-devops-engineer-senior-migration-project-vmware-to-aws</t>
+  </si>
+  <si>
+    <t>AWS DevOps Engineer (Senior)</t>
+  </si>
+  <si>
+    <t>Pipeline building, release engineering, and production cutover ownership map to the candidate's CI/CD and automation strengths | Forward-deployed engineering model rewards the customer-facing trusted-advisor pattern the candidate already uses | Remote-anywhere posting</t>
+  </si>
+  <si>
+    <t>AWS-primary modernization firm; posting assumes AWS depth the candidate does not have (Azure-only cloud portfolio) | Senior IC delivery seat, below the principal/architect scope in the candidate's target titles | No compensation disclosed and consultancy senior DevOps bands often fall under $180K</t>
+  </si>
+  <si>
+    <t>https://jobicy.com/jobs/152282-aws-devops-engineer-senior</t>
+  </si>
+  <si>
+    <t>Senior DevOps / DevEx Engineer</t>
+  </si>
+  <si>
+    <t>RevenueCat</t>
+  </si>
+  <si>
+    <t>APAC,  EMEA,  Canada,  USA</t>
+  </si>
+  <si>
+    <t>Internal developer platform / DevEx work aligns directly with the candidate's Azure DevOps and GitHub Enterprise platform administration background | Confirmed $230K comp is well above the $180K floor | Remote-first company hiring across the USA, matching the primary workplace preference</t>
+  </si>
+  <si>
+    <t>Startup platform stack is likely AWS/Kubernetes/Terraform-centric rather than Azure DevOps/GHAS, so much of the candidate's specialized tooling depth won't transfer directly | Senior IC platform engineering role with heavy hands-on coding, not the enterprise architect/advisory scope the candidate targets | No enterprise compliance (HIPAA/PCI/SOX) angle where the candidate differentiates</t>
+  </si>
+  <si>
+    <t>https://jobicy.com/jobs/149932-senior-devops-devex-engineer</t>
+  </si>
+  <si>
     <t>Lead GTM Enablement &amp; Scale Architect, Field Engineering - Customer Skills</t>
   </si>
   <si>
@@ -4734,6 +4911,51 @@
   </si>
   <si>
     <t>https://www.arbeitnow.co.uk/jobs/companies/elastic/elastic-consulting-architect-public-sector-106294</t>
+  </si>
+  <si>
+    <t>Principal-level scope matches the candidate's target seniority | Confirmed comp at $184.2K clears the $180K floor | Ecosystem/partner architect work is advisory and technical, aligned with the candidate's customer engineer engagement model</t>
+  </si>
+  <si>
+    <t>Requires deep hands-on LLM/AI ecosystem and Elasticsearch/vector-search depth the resume doesn't show | Likely expects credibility with AI model providers (OpenAI/Anthropic integration patterns), a gap vs. Azure DevOps/GitHub specialization | San Francisco-based with unclear remote status — commute/relocation unresolved</t>
+  </si>
+  <si>
+    <t>https://jobs.elastic.co/jobs?gh_jid=8047165&amp;gh_jid=8047165</t>
+  </si>
+  <si>
+    <t>BT Architect &amp; Security Lead (m/w/d)</t>
+  </si>
+  <si>
+    <t>encontec GmbH</t>
+  </si>
+  <si>
+    <t>Backnang, Baden-Württemberg, Deutschland</t>
+  </si>
+  <si>
+    <t>Architecture and security-by-design leadership scope is nominally principal-level, matching the candidate's target seniority | Governance/segmentation and compliance enforcement themes overlap loosely with the candidate's Azure Policy and NIST work</t>
+  </si>
+  <si>
+    <t>Role is in Backnang, Germany and written in German — outside the candidate's US market scope and likely requires German fluency plus work authorization | OT/manufacturing network segmentation and aerospace shop-floor systems are outside the candidate's cloud/DevOps experience | No cloud platform, CI/CD, or Azure/GitHub content in the requirement set</t>
+  </si>
+  <si>
+    <t>https://www.arbeitnow.com/jobs/companies/encontec-gmbh/bt-architect-security-lead-backnang-337185</t>
+  </si>
+  <si>
+    <t>AI Agent Security Architect</t>
+  </si>
+  <si>
+    <t>replit</t>
+  </si>
+  <si>
+    <t>Foster City, CA</t>
+  </si>
+  <si>
+    <t>Confirmed $230K–$350K band comfortably exceeds the $180K floor | Candidate's GitHub Copilot / agentic DevOps exposure and GHAS secret/code scanning work give partial credibility on AI-agent security topics | Role is a senior technical authority position, matching the principal-level scope the candidate targets</t>
+  </si>
+  <si>
+    <t>Requires deep runtime defense, sandboxing, and guardrail framework engineering — a security-research-grade skill set the candidate does not demonstrate | Security architecture here is product/runtime-focused, not the compliance-and-governance (HIPAA/PCI/Azure Policy) security the candidate practices | Hybrid in Foster City, CA — requires relocation from Humble, TX</t>
+  </si>
+  <si>
+    <t>https://jobs.ashbyhq.com/replit/df7b6d30-9da1-4ace-8121-17c2aa55aa6f</t>
   </si>
 </sst>
 </file>
@@ -5114,7 +5336,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q217"/>
+  <dimension ref="A1:Q229"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -16038,6 +16260,600 @@
         <v>1082</v>
       </c>
     </row>
+    <row r="218" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>17</v>
+      </c>
+      <c r="B218">
+        <v>12</v>
+      </c>
+      <c r="C218">
+        <v>15</v>
+      </c>
+      <c r="D218" t="s">
+        <v>1083</v>
+      </c>
+      <c r="E218" t="s">
+        <v>1084</v>
+      </c>
+      <c r="F218" t="s">
+        <v>20</v>
+      </c>
+      <c r="G218" t="s">
+        <v>21</v>
+      </c>
+      <c r="J218" t="s">
+        <v>38</v>
+      </c>
+      <c r="K218" t="s">
+        <v>23</v>
+      </c>
+      <c r="L218" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M218" t="s">
+        <v>39</v>
+      </c>
+      <c r="N218" t="s">
+        <v>26</v>
+      </c>
+      <c r="O218" t="s">
+        <v>1086</v>
+      </c>
+      <c r="P218" t="s">
+        <v>1087</v>
+      </c>
+      <c r="Q218" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="219" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>17</v>
+      </c>
+      <c r="B219">
+        <v>58</v>
+      </c>
+      <c r="C219">
+        <v>62</v>
+      </c>
+      <c r="D219" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E219" t="s">
+        <v>1090</v>
+      </c>
+      <c r="F219" t="s">
+        <v>118</v>
+      </c>
+      <c r="G219" t="s">
+        <v>21</v>
+      </c>
+      <c r="H219">
+        <v>154200</v>
+      </c>
+      <c r="I219">
+        <v>231300</v>
+      </c>
+      <c r="J219" t="s">
+        <v>22</v>
+      </c>
+      <c r="K219" t="s">
+        <v>119</v>
+      </c>
+      <c r="L219" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M219" t="s">
+        <v>25</v>
+      </c>
+      <c r="N219" t="s">
+        <v>26</v>
+      </c>
+      <c r="O219" t="s">
+        <v>1091</v>
+      </c>
+      <c r="P219" t="s">
+        <v>1092</v>
+      </c>
+      <c r="Q219" t="s">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="220" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>17</v>
+      </c>
+      <c r="B220">
+        <v>25</v>
+      </c>
+      <c r="C220">
+        <v>30</v>
+      </c>
+      <c r="D220" t="s">
+        <v>1094</v>
+      </c>
+      <c r="E220" t="s">
+        <v>1095</v>
+      </c>
+      <c r="F220" t="s">
+        <v>118</v>
+      </c>
+      <c r="G220" t="s">
+        <v>21</v>
+      </c>
+      <c r="J220" t="s">
+        <v>38</v>
+      </c>
+      <c r="K220" t="s">
+        <v>119</v>
+      </c>
+      <c r="L220" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M220" t="s">
+        <v>39</v>
+      </c>
+      <c r="N220" t="s">
+        <v>26</v>
+      </c>
+      <c r="O220" t="s">
+        <v>1096</v>
+      </c>
+      <c r="P220" t="s">
+        <v>1097</v>
+      </c>
+      <c r="Q220" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="221" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>17</v>
+      </c>
+      <c r="B221">
+        <v>15</v>
+      </c>
+      <c r="C221">
+        <v>15</v>
+      </c>
+      <c r="D221" t="s">
+        <v>1099</v>
+      </c>
+      <c r="E221" t="s">
+        <v>1095</v>
+      </c>
+      <c r="F221" t="s">
+        <v>118</v>
+      </c>
+      <c r="G221" t="s">
+        <v>21</v>
+      </c>
+      <c r="J221" t="s">
+        <v>38</v>
+      </c>
+      <c r="K221" t="s">
+        <v>119</v>
+      </c>
+      <c r="L221" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M221" t="s">
+        <v>39</v>
+      </c>
+      <c r="N221" t="s">
+        <v>26</v>
+      </c>
+      <c r="O221" t="s">
+        <v>1100</v>
+      </c>
+      <c r="P221" t="s">
+        <v>1101</v>
+      </c>
+      <c r="Q221" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="222" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>17</v>
+      </c>
+      <c r="B222">
+        <v>50</v>
+      </c>
+      <c r="C222">
+        <v>52</v>
+      </c>
+      <c r="D222" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E222" t="s">
+        <v>1104</v>
+      </c>
+      <c r="F222" t="s">
+        <v>686</v>
+      </c>
+      <c r="G222" t="s">
+        <v>21</v>
+      </c>
+      <c r="J222" t="s">
+        <v>38</v>
+      </c>
+      <c r="K222" t="s">
+        <v>119</v>
+      </c>
+      <c r="L222" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M222" t="s">
+        <v>25</v>
+      </c>
+      <c r="N222" t="s">
+        <v>26</v>
+      </c>
+      <c r="O222" t="s">
+        <v>1105</v>
+      </c>
+      <c r="P222" t="s">
+        <v>1106</v>
+      </c>
+      <c r="Q222" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="223" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>17</v>
+      </c>
+      <c r="B223">
+        <v>65</v>
+      </c>
+      <c r="C223">
+        <v>58</v>
+      </c>
+      <c r="D223" t="s">
+        <v>1108</v>
+      </c>
+      <c r="E223" t="s">
+        <v>1109</v>
+      </c>
+      <c r="F223" t="s">
+        <v>118</v>
+      </c>
+      <c r="G223" t="s">
+        <v>21</v>
+      </c>
+      <c r="H223">
+        <v>170625</v>
+      </c>
+      <c r="I223">
+        <v>243750</v>
+      </c>
+      <c r="J223" t="s">
+        <v>22</v>
+      </c>
+      <c r="K223" t="s">
+        <v>119</v>
+      </c>
+      <c r="L223" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M223" t="s">
+        <v>25</v>
+      </c>
+      <c r="N223" t="s">
+        <v>26</v>
+      </c>
+      <c r="O223" t="s">
+        <v>1110</v>
+      </c>
+      <c r="P223" t="s">
+        <v>1111</v>
+      </c>
+      <c r="Q223" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="224" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>17</v>
+      </c>
+      <c r="B224">
+        <v>52</v>
+      </c>
+      <c r="C224">
+        <v>45</v>
+      </c>
+      <c r="D224" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E224" t="s">
+        <v>691</v>
+      </c>
+      <c r="F224" t="s">
+        <v>655</v>
+      </c>
+      <c r="G224" t="s">
+        <v>21</v>
+      </c>
+      <c r="H224">
+        <v>500000</v>
+      </c>
+      <c r="I224">
+        <v>500000</v>
+      </c>
+      <c r="J224" t="s">
+        <v>22</v>
+      </c>
+      <c r="K224" t="s">
+        <v>119</v>
+      </c>
+      <c r="L224" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M224" t="s">
+        <v>25</v>
+      </c>
+      <c r="N224" t="s">
+        <v>26</v>
+      </c>
+      <c r="O224" t="s">
+        <v>1114</v>
+      </c>
+      <c r="P224" t="s">
+        <v>1115</v>
+      </c>
+      <c r="Q224" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="225" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>17</v>
+      </c>
+      <c r="B225">
+        <v>58</v>
+      </c>
+      <c r="C225">
+        <v>55</v>
+      </c>
+      <c r="D225" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E225" t="s">
+        <v>1118</v>
+      </c>
+      <c r="F225" t="s">
+        <v>655</v>
+      </c>
+      <c r="G225" t="s">
+        <v>21</v>
+      </c>
+      <c r="H225">
+        <v>180000</v>
+      </c>
+      <c r="I225">
+        <v>200000</v>
+      </c>
+      <c r="J225" t="s">
+        <v>22</v>
+      </c>
+      <c r="K225" t="s">
+        <v>119</v>
+      </c>
+      <c r="L225" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M225" t="s">
+        <v>25</v>
+      </c>
+      <c r="N225" t="s">
+        <v>26</v>
+      </c>
+      <c r="O225" t="s">
+        <v>1119</v>
+      </c>
+      <c r="P225" t="s">
+        <v>1120</v>
+      </c>
+      <c r="Q225" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="226" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>17</v>
+      </c>
+      <c r="B226">
+        <v>22</v>
+      </c>
+      <c r="C226">
+        <v>25</v>
+      </c>
+      <c r="D226" t="s">
+        <v>1122</v>
+      </c>
+      <c r="E226" t="s">
+        <v>1104</v>
+      </c>
+      <c r="F226" t="s">
+        <v>1123</v>
+      </c>
+      <c r="G226" t="s">
+        <v>21</v>
+      </c>
+      <c r="J226" t="s">
+        <v>38</v>
+      </c>
+      <c r="K226" t="s">
+        <v>119</v>
+      </c>
+      <c r="L226" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M226" t="s">
+        <v>39</v>
+      </c>
+      <c r="N226" t="s">
+        <v>26</v>
+      </c>
+      <c r="O226" t="s">
+        <v>1124</v>
+      </c>
+      <c r="P226" t="s">
+        <v>1125</v>
+      </c>
+      <c r="Q226" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="227" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>17</v>
+      </c>
+      <c r="B227">
+        <v>35</v>
+      </c>
+      <c r="C227">
+        <v>38</v>
+      </c>
+      <c r="D227" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E227" t="s">
+        <v>1128</v>
+      </c>
+      <c r="F227" t="s">
+        <v>686</v>
+      </c>
+      <c r="G227" t="s">
+        <v>21</v>
+      </c>
+      <c r="J227" t="s">
+        <v>38</v>
+      </c>
+      <c r="K227" t="s">
+        <v>119</v>
+      </c>
+      <c r="L227" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M227" t="s">
+        <v>39</v>
+      </c>
+      <c r="N227" t="s">
+        <v>26</v>
+      </c>
+      <c r="O227" t="s">
+        <v>1129</v>
+      </c>
+      <c r="P227" t="s">
+        <v>1130</v>
+      </c>
+      <c r="Q227" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="228" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>17</v>
+      </c>
+      <c r="B228">
+        <v>35</v>
+      </c>
+      <c r="C228">
+        <v>38</v>
+      </c>
+      <c r="D228" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E228" t="s">
+        <v>1128</v>
+      </c>
+      <c r="F228" t="s">
+        <v>686</v>
+      </c>
+      <c r="G228" t="s">
+        <v>21</v>
+      </c>
+      <c r="J228" t="s">
+        <v>38</v>
+      </c>
+      <c r="K228" t="s">
+        <v>119</v>
+      </c>
+      <c r="L228" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M228" t="s">
+        <v>39</v>
+      </c>
+      <c r="N228" t="s">
+        <v>26</v>
+      </c>
+      <c r="O228" t="s">
+        <v>1133</v>
+      </c>
+      <c r="P228" t="s">
+        <v>1134</v>
+      </c>
+      <c r="Q228" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="229" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>17</v>
+      </c>
+      <c r="B229">
+        <v>58</v>
+      </c>
+      <c r="C229">
+        <v>55</v>
+      </c>
+      <c r="D229" t="s">
+        <v>1136</v>
+      </c>
+      <c r="E229" t="s">
+        <v>1137</v>
+      </c>
+      <c r="F229" t="s">
+        <v>1138</v>
+      </c>
+      <c r="G229" t="s">
+        <v>21</v>
+      </c>
+      <c r="H229">
+        <v>230000</v>
+      </c>
+      <c r="I229">
+        <v>230000</v>
+      </c>
+      <c r="J229" t="s">
+        <v>22</v>
+      </c>
+      <c r="K229" t="s">
+        <v>119</v>
+      </c>
+      <c r="L229" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M229" t="s">
+        <v>25</v>
+      </c>
+      <c r="N229" t="s">
+        <v>26</v>
+      </c>
+      <c r="O229" t="s">
+        <v>1139</v>
+      </c>
+      <c r="P229" t="s">
+        <v>1140</v>
+      </c>
+      <c r="Q229" t="s">
+        <v>1141</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:Q1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16047,7 +16863,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q108"/>
+  <dimension ref="A1:Q111"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -16128,7 +16944,7 @@
         <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>1083</v>
+        <v>1142</v>
       </c>
       <c r="E2" t="s">
         <v>55</v>
@@ -16137,7 +16953,7 @@
         <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="H2">
         <v>217800</v>
@@ -16158,16 +16974,16 @@
         <v>25</v>
       </c>
       <c r="N2" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O2" t="s">
-        <v>1086</v>
+        <v>1145</v>
       </c>
       <c r="P2" t="s">
-        <v>1087</v>
+        <v>1146</v>
       </c>
       <c r="Q2" t="s">
-        <v>1088</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -16181,16 +16997,16 @@
         <v>45</v>
       </c>
       <c r="D3" t="s">
-        <v>1089</v>
+        <v>1148</v>
       </c>
       <c r="E3" t="s">
         <v>55</v>
       </c>
       <c r="F3" t="s">
-        <v>1090</v>
+        <v>1149</v>
       </c>
       <c r="G3" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="H3">
         <v>219100</v>
@@ -16211,16 +17027,16 @@
         <v>25</v>
       </c>
       <c r="N3" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O3" t="s">
-        <v>1091</v>
+        <v>1150</v>
       </c>
       <c r="P3" t="s">
-        <v>1092</v>
+        <v>1151</v>
       </c>
       <c r="Q3" t="s">
-        <v>1093</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
@@ -16240,10 +17056,10 @@
         <v>846</v>
       </c>
       <c r="F4" t="s">
-        <v>1094</v>
+        <v>1153</v>
       </c>
       <c r="G4" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="J4" t="s">
         <v>38</v>
@@ -16258,16 +17074,16 @@
         <v>39</v>
       </c>
       <c r="N4" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O4" t="s">
-        <v>1095</v>
+        <v>1154</v>
       </c>
       <c r="P4" t="s">
-        <v>1096</v>
+        <v>1155</v>
       </c>
       <c r="Q4" t="s">
-        <v>1097</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -16281,16 +17097,16 @@
         <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>1098</v>
+        <v>1157</v>
       </c>
       <c r="E5" t="s">
-        <v>1099</v>
+        <v>1158</v>
       </c>
       <c r="F5" t="s">
-        <v>1100</v>
+        <v>1159</v>
       </c>
       <c r="G5" t="s">
-        <v>1101</v>
+        <v>1160</v>
       </c>
       <c r="J5" t="s">
         <v>38</v>
@@ -16305,16 +17121,16 @@
         <v>39</v>
       </c>
       <c r="N5" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O5" t="s">
-        <v>1102</v>
+        <v>1161</v>
       </c>
       <c r="P5" t="s">
-        <v>1103</v>
+        <v>1162</v>
       </c>
       <c r="Q5" t="s">
-        <v>1104</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -16328,16 +17144,16 @@
         <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>1105</v>
+        <v>1164</v>
       </c>
       <c r="E6" t="s">
-        <v>1106</v>
+        <v>1165</v>
       </c>
       <c r="F6" t="s">
-        <v>1107</v>
+        <v>1166</v>
       </c>
       <c r="G6" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="J6" t="s">
         <v>38</v>
@@ -16352,16 +17168,16 @@
         <v>39</v>
       </c>
       <c r="N6" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O6" t="s">
-        <v>1108</v>
+        <v>1167</v>
       </c>
       <c r="P6" t="s">
-        <v>1109</v>
+        <v>1168</v>
       </c>
       <c r="Q6" t="s">
-        <v>1110</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -16375,16 +17191,16 @@
         <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>1111</v>
+        <v>1170</v>
       </c>
       <c r="E7" t="s">
-        <v>1106</v>
+        <v>1165</v>
       </c>
       <c r="F7" t="s">
-        <v>1112</v>
+        <v>1171</v>
       </c>
       <c r="G7" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="J7" t="s">
         <v>38</v>
@@ -16399,16 +17215,16 @@
         <v>39</v>
       </c>
       <c r="N7" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O7" t="s">
-        <v>1113</v>
+        <v>1172</v>
       </c>
       <c r="P7" t="s">
-        <v>1114</v>
+        <v>1173</v>
       </c>
       <c r="Q7" t="s">
-        <v>1115</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -16422,16 +17238,16 @@
         <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>1116</v>
+        <v>1175</v>
       </c>
       <c r="E8" t="s">
-        <v>1106</v>
+        <v>1165</v>
       </c>
       <c r="F8" t="s">
-        <v>1107</v>
+        <v>1166</v>
       </c>
       <c r="G8" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="J8" t="s">
         <v>38</v>
@@ -16446,16 +17262,16 @@
         <v>39</v>
       </c>
       <c r="N8" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O8" t="s">
-        <v>1117</v>
+        <v>1176</v>
       </c>
       <c r="P8" t="s">
-        <v>1118</v>
+        <v>1177</v>
       </c>
       <c r="Q8" t="s">
-        <v>1119</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -16469,16 +17285,16 @@
         <v>5</v>
       </c>
       <c r="D9" t="s">
-        <v>1120</v>
+        <v>1179</v>
       </c>
       <c r="E9" t="s">
-        <v>1121</v>
+        <v>1180</v>
       </c>
       <c r="F9" t="s">
-        <v>1122</v>
+        <v>1181</v>
       </c>
       <c r="G9" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="J9" t="s">
         <v>38</v>
@@ -16493,16 +17309,16 @@
         <v>39</v>
       </c>
       <c r="N9" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O9" t="s">
-        <v>1123</v>
+        <v>1182</v>
       </c>
       <c r="P9" t="s">
-        <v>1124</v>
+        <v>1183</v>
       </c>
       <c r="Q9" t="s">
-        <v>1125</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -16516,16 +17332,16 @@
         <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>1126</v>
+        <v>1185</v>
       </c>
       <c r="E10" t="s">
-        <v>1121</v>
+        <v>1180</v>
       </c>
       <c r="F10" t="s">
-        <v>1127</v>
+        <v>1186</v>
       </c>
       <c r="G10" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="J10" t="s">
         <v>38</v>
@@ -16540,16 +17356,16 @@
         <v>39</v>
       </c>
       <c r="N10" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O10" t="s">
-        <v>1128</v>
+        <v>1187</v>
       </c>
       <c r="P10" t="s">
-        <v>1129</v>
+        <v>1188</v>
       </c>
       <c r="Q10" t="s">
-        <v>1130</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -16563,16 +17379,16 @@
         <v>5</v>
       </c>
       <c r="D11" t="s">
-        <v>1131</v>
+        <v>1190</v>
       </c>
       <c r="E11" t="s">
-        <v>1121</v>
+        <v>1180</v>
       </c>
       <c r="F11" t="s">
-        <v>1122</v>
+        <v>1181</v>
       </c>
       <c r="G11" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="J11" t="s">
         <v>38</v>
@@ -16587,16 +17403,16 @@
         <v>39</v>
       </c>
       <c r="N11" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O11" t="s">
-        <v>1132</v>
+        <v>1191</v>
       </c>
       <c r="P11" t="s">
-        <v>1133</v>
+        <v>1192</v>
       </c>
       <c r="Q11" t="s">
-        <v>1134</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -16610,16 +17426,16 @@
         <v>5</v>
       </c>
       <c r="D12" t="s">
-        <v>1135</v>
+        <v>1194</v>
       </c>
       <c r="E12" t="s">
-        <v>1121</v>
+        <v>1180</v>
       </c>
       <c r="F12" t="s">
-        <v>1122</v>
+        <v>1181</v>
       </c>
       <c r="G12" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="J12" t="s">
         <v>38</v>
@@ -16634,16 +17450,16 @@
         <v>39</v>
       </c>
       <c r="N12" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O12" t="s">
-        <v>1136</v>
+        <v>1195</v>
       </c>
       <c r="P12" t="s">
-        <v>1137</v>
+        <v>1196</v>
       </c>
       <c r="Q12" t="s">
-        <v>1138</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
@@ -16657,16 +17473,16 @@
         <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>1139</v>
+        <v>1198</v>
       </c>
       <c r="E13" t="s">
-        <v>1121</v>
+        <v>1180</v>
       </c>
       <c r="F13" t="s">
-        <v>1122</v>
+        <v>1181</v>
       </c>
       <c r="G13" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="J13" t="s">
         <v>38</v>
@@ -16681,16 +17497,16 @@
         <v>39</v>
       </c>
       <c r="N13" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O13" t="s">
-        <v>1140</v>
+        <v>1199</v>
       </c>
       <c r="P13" t="s">
-        <v>1141</v>
+        <v>1200</v>
       </c>
       <c r="Q13" t="s">
-        <v>1142</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
@@ -16704,16 +17520,16 @@
         <v>5</v>
       </c>
       <c r="D14" t="s">
+        <v>1202</v>
+      </c>
+      <c r="E14" t="s">
+        <v>1180</v>
+      </c>
+      <c r="F14" t="s">
+        <v>1181</v>
+      </c>
+      <c r="G14" t="s">
         <v>1143</v>
-      </c>
-      <c r="E14" t="s">
-        <v>1121</v>
-      </c>
-      <c r="F14" t="s">
-        <v>1122</v>
-      </c>
-      <c r="G14" t="s">
-        <v>1084</v>
       </c>
       <c r="J14" t="s">
         <v>38</v>
@@ -16728,16 +17544,16 @@
         <v>39</v>
       </c>
       <c r="N14" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O14" t="s">
-        <v>1144</v>
+        <v>1203</v>
       </c>
       <c r="P14" t="s">
-        <v>1145</v>
+        <v>1204</v>
       </c>
       <c r="Q14" t="s">
-        <v>1146</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -16751,16 +17567,16 @@
         <v>40</v>
       </c>
       <c r="D15" t="s">
-        <v>1147</v>
+        <v>1206</v>
       </c>
       <c r="E15" t="s">
-        <v>1121</v>
+        <v>1180</v>
       </c>
       <c r="F15" t="s">
-        <v>1122</v>
+        <v>1181</v>
       </c>
       <c r="G15" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="J15" t="s">
         <v>38</v>
@@ -16775,16 +17591,16 @@
         <v>39</v>
       </c>
       <c r="N15" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O15" t="s">
-        <v>1148</v>
+        <v>1207</v>
       </c>
       <c r="P15" t="s">
-        <v>1149</v>
+        <v>1208</v>
       </c>
       <c r="Q15" t="s">
-        <v>1150</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
@@ -16798,16 +17614,16 @@
         <v>45</v>
       </c>
       <c r="D16" t="s">
-        <v>1151</v>
+        <v>1210</v>
       </c>
       <c r="E16" t="s">
-        <v>1121</v>
+        <v>1180</v>
       </c>
       <c r="F16" t="s">
-        <v>1122</v>
+        <v>1181</v>
       </c>
       <c r="G16" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="J16" t="s">
         <v>38</v>
@@ -16822,16 +17638,16 @@
         <v>39</v>
       </c>
       <c r="N16" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O16" t="s">
-        <v>1152</v>
+        <v>1211</v>
       </c>
       <c r="P16" t="s">
-        <v>1153</v>
+        <v>1212</v>
       </c>
       <c r="Q16" t="s">
-        <v>1154</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
@@ -16845,16 +17661,16 @@
         <v>3</v>
       </c>
       <c r="D17" t="s">
-        <v>1155</v>
+        <v>1214</v>
       </c>
       <c r="E17" t="s">
-        <v>1121</v>
+        <v>1180</v>
       </c>
       <c r="F17" t="s">
-        <v>1122</v>
+        <v>1181</v>
       </c>
       <c r="G17" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="J17" t="s">
         <v>38</v>
@@ -16869,16 +17685,16 @@
         <v>39</v>
       </c>
       <c r="N17" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O17" t="s">
-        <v>1156</v>
+        <v>1215</v>
       </c>
       <c r="P17" t="s">
-        <v>1157</v>
+        <v>1216</v>
       </c>
       <c r="Q17" t="s">
-        <v>1158</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
@@ -16892,7 +17708,7 @@
         <v>42</v>
       </c>
       <c r="D18" t="s">
-        <v>1159</v>
+        <v>1218</v>
       </c>
       <c r="E18" t="s">
         <v>55</v>
@@ -16901,7 +17717,7 @@
         <v>20</v>
       </c>
       <c r="G18" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="J18" t="s">
         <v>38</v>
@@ -16916,16 +17732,16 @@
         <v>39</v>
       </c>
       <c r="N18" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O18" t="s">
-        <v>1160</v>
+        <v>1219</v>
       </c>
       <c r="P18" t="s">
-        <v>1161</v>
+        <v>1220</v>
       </c>
       <c r="Q18" t="s">
-        <v>1162</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -16939,7 +17755,7 @@
         <v>40</v>
       </c>
       <c r="D19" t="s">
-        <v>1163</v>
+        <v>1222</v>
       </c>
       <c r="E19" t="s">
         <v>55</v>
@@ -16948,7 +17764,7 @@
         <v>20</v>
       </c>
       <c r="G19" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="J19" t="s">
         <v>38</v>
@@ -16963,16 +17779,16 @@
         <v>39</v>
       </c>
       <c r="N19" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O19" t="s">
-        <v>1164</v>
+        <v>1223</v>
       </c>
       <c r="P19" t="s">
-        <v>1165</v>
+        <v>1224</v>
       </c>
       <c r="Q19" t="s">
-        <v>1166</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -16992,10 +17808,10 @@
         <v>55</v>
       </c>
       <c r="F20" t="s">
-        <v>1167</v>
+        <v>1226</v>
       </c>
       <c r="G20" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="H20">
         <v>180000</v>
@@ -17016,16 +17832,16 @@
         <v>25</v>
       </c>
       <c r="N20" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O20" t="s">
-        <v>1168</v>
+        <v>1227</v>
       </c>
       <c r="P20" t="s">
-        <v>1169</v>
+        <v>1228</v>
       </c>
       <c r="Q20" t="s">
-        <v>1170</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
@@ -17039,7 +17855,7 @@
         <v>52</v>
       </c>
       <c r="D21" t="s">
-        <v>1171</v>
+        <v>1230</v>
       </c>
       <c r="E21" t="s">
         <v>55</v>
@@ -17048,7 +17864,7 @@
         <v>20</v>
       </c>
       <c r="G21" t="s">
-        <v>1101</v>
+        <v>1160</v>
       </c>
       <c r="H21">
         <v>180000</v>
@@ -17069,16 +17885,16 @@
         <v>25</v>
       </c>
       <c r="N21" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O21" t="s">
-        <v>1172</v>
+        <v>1231</v>
       </c>
       <c r="P21" t="s">
-        <v>1173</v>
+        <v>1232</v>
       </c>
       <c r="Q21" t="s">
-        <v>1174</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -17092,7 +17908,7 @@
         <v>55</v>
       </c>
       <c r="D22" t="s">
-        <v>1175</v>
+        <v>1234</v>
       </c>
       <c r="E22" t="s">
         <v>55</v>
@@ -17101,7 +17917,7 @@
         <v>20</v>
       </c>
       <c r="G22" t="s">
-        <v>1101</v>
+        <v>1160</v>
       </c>
       <c r="H22">
         <v>180000</v>
@@ -17122,16 +17938,16 @@
         <v>25</v>
       </c>
       <c r="N22" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O22" t="s">
-        <v>1176</v>
+        <v>1235</v>
       </c>
       <c r="P22" t="s">
-        <v>1177</v>
+        <v>1236</v>
       </c>
       <c r="Q22" t="s">
-        <v>1178</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
@@ -17145,16 +17961,16 @@
         <v>48</v>
       </c>
       <c r="D23" t="s">
-        <v>1179</v>
+        <v>1238</v>
       </c>
       <c r="E23" t="s">
         <v>55</v>
       </c>
       <c r="F23" t="s">
-        <v>1180</v>
+        <v>1239</v>
       </c>
       <c r="G23" t="s">
-        <v>1101</v>
+        <v>1160</v>
       </c>
       <c r="H23">
         <v>219100</v>
@@ -17175,16 +17991,16 @@
         <v>25</v>
       </c>
       <c r="N23" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O23" t="s">
-        <v>1181</v>
+        <v>1240</v>
       </c>
       <c r="P23" t="s">
-        <v>1182</v>
+        <v>1241</v>
       </c>
       <c r="Q23" t="s">
-        <v>1183</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
@@ -17198,16 +18014,16 @@
         <v>45</v>
       </c>
       <c r="D24" t="s">
-        <v>1184</v>
+        <v>1243</v>
       </c>
       <c r="E24" t="s">
         <v>55</v>
       </c>
       <c r="F24" t="s">
-        <v>1185</v>
+        <v>1244</v>
       </c>
       <c r="G24" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="H24">
         <v>180000</v>
@@ -17228,16 +18044,16 @@
         <v>25</v>
       </c>
       <c r="N24" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O24" t="s">
-        <v>1186</v>
+        <v>1245</v>
       </c>
       <c r="P24" t="s">
-        <v>1187</v>
+        <v>1246</v>
       </c>
       <c r="Q24" t="s">
-        <v>1188</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
@@ -17251,7 +18067,7 @@
         <v>30</v>
       </c>
       <c r="D25" t="s">
-        <v>1189</v>
+        <v>1248</v>
       </c>
       <c r="E25" t="s">
         <v>55</v>
@@ -17260,7 +18076,7 @@
         <v>20</v>
       </c>
       <c r="G25" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="H25">
         <v>219100</v>
@@ -17281,16 +18097,16 @@
         <v>39</v>
       </c>
       <c r="N25" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O25" t="s">
-        <v>1190</v>
+        <v>1249</v>
       </c>
       <c r="P25" t="s">
-        <v>1191</v>
+        <v>1250</v>
       </c>
       <c r="Q25" t="s">
-        <v>1192</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
@@ -17304,7 +18120,7 @@
         <v>45</v>
       </c>
       <c r="D26" t="s">
-        <v>1193</v>
+        <v>1252</v>
       </c>
       <c r="E26" t="s">
         <v>55</v>
@@ -17313,7 +18129,7 @@
         <v>20</v>
       </c>
       <c r="G26" t="s">
-        <v>1101</v>
+        <v>1160</v>
       </c>
       <c r="H26">
         <v>219100</v>
@@ -17334,16 +18150,16 @@
         <v>25</v>
       </c>
       <c r="N26" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O26" t="s">
-        <v>1194</v>
+        <v>1253</v>
       </c>
       <c r="P26" t="s">
-        <v>1195</v>
+        <v>1254</v>
       </c>
       <c r="Q26" t="s">
-        <v>1196</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
@@ -17357,16 +18173,16 @@
         <v>30</v>
       </c>
       <c r="D27" t="s">
-        <v>1197</v>
+        <v>1256</v>
       </c>
       <c r="E27" t="s">
         <v>55</v>
       </c>
       <c r="F27" t="s">
-        <v>1198</v>
+        <v>1257</v>
       </c>
       <c r="G27" t="s">
-        <v>1101</v>
+        <v>1160</v>
       </c>
       <c r="J27" t="s">
         <v>38</v>
@@ -17381,16 +18197,16 @@
         <v>39</v>
       </c>
       <c r="N27" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O27" t="s">
-        <v>1199</v>
+        <v>1258</v>
       </c>
       <c r="P27" t="s">
-        <v>1200</v>
+        <v>1259</v>
       </c>
       <c r="Q27" t="s">
-        <v>1201</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
@@ -17404,16 +18220,16 @@
         <v>58</v>
       </c>
       <c r="D28" t="s">
-        <v>1202</v>
+        <v>1261</v>
       </c>
       <c r="E28" t="s">
-        <v>1203</v>
+        <v>1262</v>
       </c>
       <c r="F28" t="s">
-        <v>1204</v>
+        <v>1263</v>
       </c>
       <c r="G28" t="s">
-        <v>1101</v>
+        <v>1160</v>
       </c>
       <c r="H28">
         <v>257000</v>
@@ -17434,16 +18250,16 @@
         <v>25</v>
       </c>
       <c r="N28" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O28" t="s">
-        <v>1205</v>
+        <v>1264</v>
       </c>
       <c r="P28" t="s">
-        <v>1206</v>
+        <v>1265</v>
       </c>
       <c r="Q28" t="s">
-        <v>1207</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
@@ -17460,13 +18276,13 @@
         <v>311</v>
       </c>
       <c r="E29" t="s">
-        <v>1208</v>
+        <v>1267</v>
       </c>
       <c r="F29" t="s">
-        <v>1209</v>
+        <v>1268</v>
       </c>
       <c r="G29" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="H29">
         <v>200000</v>
@@ -17487,16 +18303,16 @@
         <v>39</v>
       </c>
       <c r="N29" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O29" t="s">
-        <v>1210</v>
+        <v>1269</v>
       </c>
       <c r="P29" t="s">
-        <v>1211</v>
+        <v>1270</v>
       </c>
       <c r="Q29" t="s">
-        <v>1212</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
@@ -17510,16 +18326,16 @@
         <v>20</v>
       </c>
       <c r="D30" t="s">
-        <v>1213</v>
+        <v>1272</v>
       </c>
       <c r="E30" t="s">
         <v>846</v>
       </c>
       <c r="F30" t="s">
-        <v>1214</v>
+        <v>1273</v>
       </c>
       <c r="G30" t="s">
-        <v>1101</v>
+        <v>1160</v>
       </c>
       <c r="J30" t="s">
         <v>38</v>
@@ -17534,16 +18350,16 @@
         <v>39</v>
       </c>
       <c r="N30" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O30" t="s">
-        <v>1215</v>
+        <v>1274</v>
       </c>
       <c r="P30" t="s">
-        <v>1216</v>
+        <v>1275</v>
       </c>
       <c r="Q30" t="s">
-        <v>1217</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
@@ -17563,10 +18379,10 @@
         <v>846</v>
       </c>
       <c r="F31" t="s">
-        <v>1218</v>
+        <v>1277</v>
       </c>
       <c r="G31" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="J31" t="s">
         <v>38</v>
@@ -17581,16 +18397,16 @@
         <v>39</v>
       </c>
       <c r="N31" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O31" t="s">
-        <v>1219</v>
+        <v>1278</v>
       </c>
       <c r="P31" t="s">
-        <v>1220</v>
+        <v>1279</v>
       </c>
       <c r="Q31" t="s">
-        <v>1221</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
@@ -17604,16 +18420,16 @@
         <v>15</v>
       </c>
       <c r="D32" t="s">
-        <v>1222</v>
+        <v>1281</v>
       </c>
       <c r="E32" t="s">
         <v>846</v>
       </c>
       <c r="F32" t="s">
-        <v>1223</v>
+        <v>1282</v>
       </c>
       <c r="G32" t="s">
-        <v>1101</v>
+        <v>1160</v>
       </c>
       <c r="H32">
         <v>500000</v>
@@ -17634,16 +18450,16 @@
         <v>39</v>
       </c>
       <c r="N32" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O32" t="s">
-        <v>1224</v>
+        <v>1283</v>
       </c>
       <c r="P32" t="s">
-        <v>1225</v>
+        <v>1284</v>
       </c>
       <c r="Q32" t="s">
-        <v>1226</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
@@ -17657,16 +18473,16 @@
         <v>18</v>
       </c>
       <c r="D33" t="s">
-        <v>1227</v>
+        <v>1286</v>
       </c>
       <c r="E33" t="s">
         <v>633</v>
       </c>
       <c r="F33" t="s">
-        <v>1228</v>
+        <v>1287</v>
       </c>
       <c r="G33" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="H33">
         <v>274456</v>
@@ -17687,16 +18503,16 @@
         <v>39</v>
       </c>
       <c r="N33" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O33" t="s">
-        <v>1229</v>
+        <v>1288</v>
       </c>
       <c r="P33" t="s">
-        <v>1230</v>
+        <v>1289</v>
       </c>
       <c r="Q33" t="s">
-        <v>1231</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
@@ -17710,16 +18526,16 @@
         <v>30</v>
       </c>
       <c r="D34" t="s">
-        <v>1232</v>
+        <v>1291</v>
       </c>
       <c r="E34" t="s">
         <v>633</v>
       </c>
       <c r="F34" t="s">
-        <v>1233</v>
+        <v>1292</v>
       </c>
       <c r="G34" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="J34" t="s">
         <v>38</v>
@@ -17734,16 +18550,16 @@
         <v>39</v>
       </c>
       <c r="N34" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O34" t="s">
-        <v>1234</v>
+        <v>1293</v>
       </c>
       <c r="P34" t="s">
-        <v>1235</v>
+        <v>1294</v>
       </c>
       <c r="Q34" t="s">
-        <v>1236</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
@@ -17757,16 +18573,16 @@
         <v>22</v>
       </c>
       <c r="D35" t="s">
-        <v>1237</v>
+        <v>1296</v>
       </c>
       <c r="E35" t="s">
         <v>633</v>
       </c>
       <c r="F35" t="s">
-        <v>1238</v>
+        <v>1297</v>
       </c>
       <c r="G35" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="J35" t="s">
         <v>38</v>
@@ -17781,16 +18597,16 @@
         <v>39</v>
       </c>
       <c r="N35" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O35" t="s">
-        <v>1239</v>
+        <v>1298</v>
       </c>
       <c r="P35" t="s">
-        <v>1240</v>
+        <v>1299</v>
       </c>
       <c r="Q35" t="s">
-        <v>1241</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
@@ -17804,16 +18620,16 @@
         <v>48</v>
       </c>
       <c r="D36" t="s">
-        <v>1242</v>
+        <v>1301</v>
       </c>
       <c r="E36" t="s">
         <v>633</v>
       </c>
       <c r="F36" t="s">
-        <v>1243</v>
+        <v>1302</v>
       </c>
       <c r="G36" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="J36" t="s">
         <v>38</v>
@@ -17828,16 +18644,16 @@
         <v>25</v>
       </c>
       <c r="N36" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O36" t="s">
-        <v>1244</v>
+        <v>1303</v>
       </c>
       <c r="P36" t="s">
-        <v>1245</v>
+        <v>1304</v>
       </c>
       <c r="Q36" t="s">
-        <v>1246</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
@@ -17851,16 +18667,16 @@
         <v>25</v>
       </c>
       <c r="D37" t="s">
-        <v>1247</v>
+        <v>1306</v>
       </c>
       <c r="E37" t="s">
         <v>633</v>
       </c>
       <c r="F37" t="s">
-        <v>1127</v>
+        <v>1186</v>
       </c>
       <c r="G37" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="J37" t="s">
         <v>38</v>
@@ -17875,16 +18691,16 @@
         <v>39</v>
       </c>
       <c r="N37" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O37" t="s">
-        <v>1248</v>
+        <v>1307</v>
       </c>
       <c r="P37" t="s">
-        <v>1249</v>
+        <v>1308</v>
       </c>
       <c r="Q37" t="s">
-        <v>1250</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
@@ -17898,16 +18714,16 @@
         <v>40</v>
       </c>
       <c r="D38" t="s">
-        <v>1251</v>
+        <v>1310</v>
       </c>
       <c r="E38" t="s">
         <v>633</v>
       </c>
       <c r="F38" t="s">
-        <v>1252</v>
+        <v>1311</v>
       </c>
       <c r="G38" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="J38" t="s">
         <v>38</v>
@@ -17922,16 +18738,16 @@
         <v>39</v>
       </c>
       <c r="N38" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O38" t="s">
-        <v>1253</v>
+        <v>1312</v>
       </c>
       <c r="P38" t="s">
-        <v>1254</v>
+        <v>1313</v>
       </c>
       <c r="Q38" t="s">
-        <v>1255</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
@@ -17945,16 +18761,16 @@
         <v>70</v>
       </c>
       <c r="D39" t="s">
-        <v>1256</v>
+        <v>1315</v>
       </c>
       <c r="E39" t="s">
-        <v>1257</v>
+        <v>1316</v>
       </c>
       <c r="F39" t="s">
-        <v>1258</v>
+        <v>1317</v>
       </c>
       <c r="G39" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="J39" t="s">
         <v>38</v>
@@ -17969,16 +18785,16 @@
         <v>39</v>
       </c>
       <c r="N39" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O39" t="s">
-        <v>1259</v>
+        <v>1318</v>
       </c>
       <c r="P39" t="s">
-        <v>1260</v>
+        <v>1319</v>
       </c>
       <c r="Q39" t="s">
-        <v>1261</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
@@ -17992,16 +18808,16 @@
         <v>58</v>
       </c>
       <c r="D40" t="s">
-        <v>1262</v>
+        <v>1321</v>
       </c>
       <c r="E40" t="s">
-        <v>1263</v>
+        <v>1322</v>
       </c>
       <c r="F40" t="s">
-        <v>1127</v>
+        <v>1186</v>
       </c>
       <c r="G40" t="s">
-        <v>1101</v>
+        <v>1160</v>
       </c>
       <c r="J40" t="s">
         <v>38</v>
@@ -18016,16 +18832,16 @@
         <v>39</v>
       </c>
       <c r="N40" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O40" t="s">
-        <v>1264</v>
+        <v>1323</v>
       </c>
       <c r="P40" t="s">
-        <v>1265</v>
+        <v>1324</v>
       </c>
       <c r="Q40" t="s">
-        <v>1266</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
@@ -18039,16 +18855,16 @@
         <v>32</v>
       </c>
       <c r="D41" t="s">
-        <v>1267</v>
+        <v>1326</v>
       </c>
       <c r="E41" t="s">
-        <v>1268</v>
+        <v>1327</v>
       </c>
       <c r="F41" t="s">
-        <v>1269</v>
+        <v>1328</v>
       </c>
       <c r="G41" t="s">
-        <v>1101</v>
+        <v>1160</v>
       </c>
       <c r="J41" t="s">
         <v>38</v>
@@ -18063,16 +18879,16 @@
         <v>39</v>
       </c>
       <c r="N41" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O41" t="s">
-        <v>1270</v>
+        <v>1329</v>
       </c>
       <c r="P41" t="s">
-        <v>1271</v>
+        <v>1330</v>
       </c>
       <c r="Q41" t="s">
-        <v>1272</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
@@ -18086,16 +18902,16 @@
         <v>4</v>
       </c>
       <c r="D42" t="s">
-        <v>1273</v>
+        <v>1332</v>
       </c>
       <c r="E42" t="s">
-        <v>1274</v>
+        <v>1333</v>
       </c>
       <c r="F42" t="s">
-        <v>1275</v>
+        <v>1334</v>
       </c>
       <c r="G42" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="J42" t="s">
         <v>38</v>
@@ -18110,16 +18926,16 @@
         <v>39</v>
       </c>
       <c r="N42" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O42" t="s">
-        <v>1276</v>
+        <v>1335</v>
       </c>
       <c r="P42" t="s">
-        <v>1277</v>
+        <v>1336</v>
       </c>
       <c r="Q42" t="s">
-        <v>1278</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
@@ -18133,16 +18949,16 @@
         <v>25</v>
       </c>
       <c r="D43" t="s">
-        <v>1279</v>
+        <v>1338</v>
       </c>
       <c r="E43" t="s">
-        <v>1280</v>
+        <v>1339</v>
       </c>
       <c r="F43" t="s">
-        <v>1112</v>
+        <v>1171</v>
       </c>
       <c r="G43" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="J43" t="s">
         <v>38</v>
@@ -18157,16 +18973,16 @@
         <v>39</v>
       </c>
       <c r="N43" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O43" t="s">
-        <v>1281</v>
+        <v>1340</v>
       </c>
       <c r="P43" t="s">
-        <v>1282</v>
+        <v>1341</v>
       </c>
       <c r="Q43" t="s">
-        <v>1283</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
@@ -18180,16 +18996,16 @@
         <v>30</v>
       </c>
       <c r="D44" t="s">
-        <v>1284</v>
+        <v>1343</v>
       </c>
       <c r="E44" t="s">
-        <v>1285</v>
+        <v>1344</v>
       </c>
       <c r="F44" t="s">
-        <v>1286</v>
+        <v>1345</v>
       </c>
       <c r="G44" t="s">
-        <v>1101</v>
+        <v>1160</v>
       </c>
       <c r="J44" t="s">
         <v>38</v>
@@ -18204,16 +19020,16 @@
         <v>39</v>
       </c>
       <c r="N44" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O44" t="s">
-        <v>1287</v>
+        <v>1346</v>
       </c>
       <c r="P44" t="s">
-        <v>1288</v>
+        <v>1347</v>
       </c>
       <c r="Q44" t="s">
-        <v>1289</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
@@ -18227,16 +19043,16 @@
         <v>52</v>
       </c>
       <c r="D45" t="s">
-        <v>1290</v>
+        <v>1349</v>
       </c>
       <c r="E45" t="s">
         <v>55</v>
       </c>
       <c r="F45" t="s">
-        <v>1291</v>
+        <v>1350</v>
       </c>
       <c r="G45" t="s">
-        <v>1101</v>
+        <v>1160</v>
       </c>
       <c r="H45">
         <v>180000</v>
@@ -18257,16 +19073,16 @@
         <v>25</v>
       </c>
       <c r="N45" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O45" t="s">
-        <v>1292</v>
+        <v>1351</v>
       </c>
       <c r="P45" t="s">
-        <v>1293</v>
+        <v>1352</v>
       </c>
       <c r="Q45" t="s">
-        <v>1294</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
@@ -18280,7 +19096,7 @@
         <v>50</v>
       </c>
       <c r="D46" t="s">
-        <v>1295</v>
+        <v>1354</v>
       </c>
       <c r="E46" t="s">
         <v>55</v>
@@ -18289,7 +19105,7 @@
         <v>20</v>
       </c>
       <c r="G46" t="s">
-        <v>1101</v>
+        <v>1160</v>
       </c>
       <c r="H46">
         <v>180000</v>
@@ -18310,16 +19126,16 @@
         <v>25</v>
       </c>
       <c r="N46" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O46" t="s">
-        <v>1296</v>
+        <v>1355</v>
       </c>
       <c r="P46" t="s">
-        <v>1297</v>
+        <v>1356</v>
       </c>
       <c r="Q46" t="s">
-        <v>1298</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
@@ -18333,7 +19149,7 @@
         <v>46</v>
       </c>
       <c r="D47" t="s">
-        <v>1299</v>
+        <v>1358</v>
       </c>
       <c r="E47" t="s">
         <v>55</v>
@@ -18342,7 +19158,7 @@
         <v>20</v>
       </c>
       <c r="G47" t="s">
-        <v>1101</v>
+        <v>1160</v>
       </c>
       <c r="H47">
         <v>180000</v>
@@ -18363,16 +19179,16 @@
         <v>25</v>
       </c>
       <c r="N47" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O47" t="s">
-        <v>1300</v>
+        <v>1359</v>
       </c>
       <c r="P47" t="s">
-        <v>1301</v>
+        <v>1360</v>
       </c>
       <c r="Q47" t="s">
-        <v>1302</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
@@ -18386,7 +19202,7 @@
         <v>38</v>
       </c>
       <c r="D48" t="s">
-        <v>1303</v>
+        <v>1362</v>
       </c>
       <c r="E48" t="s">
         <v>55</v>
@@ -18395,7 +19211,7 @@
         <v>20</v>
       </c>
       <c r="G48" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="H48">
         <v>217800</v>
@@ -18416,16 +19232,16 @@
         <v>39</v>
       </c>
       <c r="N48" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O48" t="s">
-        <v>1304</v>
+        <v>1363</v>
       </c>
       <c r="P48" t="s">
-        <v>1305</v>
+        <v>1364</v>
       </c>
       <c r="Q48" t="s">
-        <v>1306</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
@@ -18445,10 +19261,10 @@
         <v>55</v>
       </c>
       <c r="F49" t="s">
-        <v>1307</v>
+        <v>1366</v>
       </c>
       <c r="G49" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="H49">
         <v>180000</v>
@@ -18469,16 +19285,16 @@
         <v>25</v>
       </c>
       <c r="N49" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O49" t="s">
-        <v>1308</v>
+        <v>1367</v>
       </c>
       <c r="P49" t="s">
-        <v>1309</v>
+        <v>1368</v>
       </c>
       <c r="Q49" t="s">
-        <v>1310</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
@@ -18492,16 +19308,16 @@
         <v>45</v>
       </c>
       <c r="D50" t="s">
-        <v>1311</v>
+        <v>1370</v>
       </c>
       <c r="E50" t="s">
         <v>55</v>
       </c>
       <c r="F50" t="s">
-        <v>1312</v>
+        <v>1371</v>
       </c>
       <c r="G50" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="H50">
         <v>219100</v>
@@ -18522,16 +19338,16 @@
         <v>25</v>
       </c>
       <c r="N50" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O50" t="s">
-        <v>1313</v>
+        <v>1372</v>
       </c>
       <c r="P50" t="s">
-        <v>1314</v>
+        <v>1373</v>
       </c>
       <c r="Q50" t="s">
-        <v>1315</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
@@ -18545,16 +19361,16 @@
         <v>42</v>
       </c>
       <c r="D51" t="s">
-        <v>1316</v>
+        <v>1375</v>
       </c>
       <c r="E51" t="s">
         <v>55</v>
       </c>
       <c r="F51" t="s">
-        <v>1317</v>
+        <v>1376</v>
       </c>
       <c r="G51" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="H51">
         <v>180000</v>
@@ -18575,16 +19391,16 @@
         <v>25</v>
       </c>
       <c r="N51" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O51" t="s">
-        <v>1318</v>
+        <v>1377</v>
       </c>
       <c r="P51" t="s">
-        <v>1319</v>
+        <v>1378</v>
       </c>
       <c r="Q51" t="s">
-        <v>1320</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
@@ -18598,7 +19414,7 @@
         <v>32</v>
       </c>
       <c r="D52" t="s">
-        <v>1321</v>
+        <v>1380</v>
       </c>
       <c r="E52" t="s">
         <v>55</v>
@@ -18607,7 +19423,7 @@
         <v>20</v>
       </c>
       <c r="G52" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="H52">
         <v>219100</v>
@@ -18628,16 +19444,16 @@
         <v>39</v>
       </c>
       <c r="N52" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O52" t="s">
-        <v>1322</v>
+        <v>1381</v>
       </c>
       <c r="P52" t="s">
-        <v>1323</v>
+        <v>1382</v>
       </c>
       <c r="Q52" t="s">
-        <v>1324</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
@@ -18651,7 +19467,7 @@
         <v>35</v>
       </c>
       <c r="D53" t="s">
-        <v>1325</v>
+        <v>1384</v>
       </c>
       <c r="E53" t="s">
         <v>55</v>
@@ -18660,7 +19476,7 @@
         <v>20</v>
       </c>
       <c r="G53" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="H53">
         <v>219100</v>
@@ -18681,16 +19497,16 @@
         <v>39</v>
       </c>
       <c r="N53" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O53" t="s">
-        <v>1326</v>
+        <v>1385</v>
       </c>
       <c r="P53" t="s">
-        <v>1327</v>
+        <v>1386</v>
       </c>
       <c r="Q53" t="s">
-        <v>1328</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
@@ -18704,16 +19520,16 @@
         <v>40</v>
       </c>
       <c r="D54" t="s">
-        <v>1329</v>
+        <v>1388</v>
       </c>
       <c r="E54" t="s">
         <v>55</v>
       </c>
       <c r="F54" t="s">
-        <v>1330</v>
+        <v>1389</v>
       </c>
       <c r="G54" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="H54">
         <v>219100</v>
@@ -18734,16 +19550,16 @@
         <v>25</v>
       </c>
       <c r="N54" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O54" t="s">
-        <v>1331</v>
+        <v>1390</v>
       </c>
       <c r="P54" t="s">
-        <v>1332</v>
+        <v>1391</v>
       </c>
       <c r="Q54" t="s">
-        <v>1333</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
@@ -18757,7 +19573,7 @@
         <v>38</v>
       </c>
       <c r="D55" t="s">
-        <v>1334</v>
+        <v>1393</v>
       </c>
       <c r="E55" t="s">
         <v>55</v>
@@ -18766,7 +19582,7 @@
         <v>592</v>
       </c>
       <c r="G55" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="H55">
         <v>219100</v>
@@ -18787,16 +19603,16 @@
         <v>39</v>
       </c>
       <c r="N55" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O55" t="s">
-        <v>1335</v>
+        <v>1394</v>
       </c>
       <c r="P55" t="s">
-        <v>1336</v>
+        <v>1395</v>
       </c>
       <c r="Q55" t="s">
-        <v>1337</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
@@ -18810,7 +19626,7 @@
         <v>40</v>
       </c>
       <c r="D56" t="s">
-        <v>1338</v>
+        <v>1397</v>
       </c>
       <c r="E56" t="s">
         <v>55</v>
@@ -18819,7 +19635,7 @@
         <v>20</v>
       </c>
       <c r="G56" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="H56">
         <v>219100</v>
@@ -18840,16 +19656,16 @@
         <v>25</v>
       </c>
       <c r="N56" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O56" t="s">
-        <v>1339</v>
+        <v>1398</v>
       </c>
       <c r="P56" t="s">
-        <v>1340</v>
+        <v>1399</v>
       </c>
       <c r="Q56" t="s">
-        <v>1341</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
@@ -18863,16 +19679,16 @@
         <v>33</v>
       </c>
       <c r="D57" t="s">
-        <v>1342</v>
+        <v>1401</v>
       </c>
       <c r="E57" t="s">
         <v>55</v>
       </c>
       <c r="F57" t="s">
-        <v>1343</v>
+        <v>1402</v>
       </c>
       <c r="G57" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="H57">
         <v>219100</v>
@@ -18893,16 +19709,16 @@
         <v>39</v>
       </c>
       <c r="N57" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O57" t="s">
-        <v>1344</v>
+        <v>1403</v>
       </c>
       <c r="P57" t="s">
-        <v>1345</v>
+        <v>1404</v>
       </c>
       <c r="Q57" t="s">
-        <v>1346</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
@@ -18916,16 +19732,16 @@
         <v>48</v>
       </c>
       <c r="D58" t="s">
-        <v>1347</v>
+        <v>1406</v>
       </c>
       <c r="E58" t="s">
-        <v>1203</v>
+        <v>1262</v>
       </c>
       <c r="F58" t="s">
-        <v>1348</v>
+        <v>1407</v>
       </c>
       <c r="G58" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="J58" t="s">
         <v>38</v>
@@ -18940,16 +19756,16 @@
         <v>25</v>
       </c>
       <c r="N58" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O58" t="s">
-        <v>1349</v>
+        <v>1408</v>
       </c>
       <c r="P58" t="s">
-        <v>1350</v>
+        <v>1409</v>
       </c>
       <c r="Q58" t="s">
-        <v>1351</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
@@ -18963,16 +19779,16 @@
         <v>40</v>
       </c>
       <c r="D59" t="s">
-        <v>1352</v>
+        <v>1411</v>
       </c>
       <c r="E59" t="s">
-        <v>1208</v>
+        <v>1267</v>
       </c>
       <c r="F59" t="s">
-        <v>1353</v>
+        <v>1412</v>
       </c>
       <c r="G59" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="H59">
         <v>184200</v>
@@ -18993,16 +19809,16 @@
         <v>25</v>
       </c>
       <c r="N59" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O59" t="s">
-        <v>1354</v>
+        <v>1413</v>
       </c>
       <c r="P59" t="s">
-        <v>1355</v>
+        <v>1414</v>
       </c>
       <c r="Q59" t="s">
-        <v>1356</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
@@ -19016,16 +19832,16 @@
         <v>30</v>
       </c>
       <c r="D60" t="s">
-        <v>1357</v>
+        <v>1416</v>
       </c>
       <c r="E60" t="s">
-        <v>1208</v>
+        <v>1267</v>
       </c>
       <c r="F60" t="s">
-        <v>1358</v>
+        <v>1417</v>
       </c>
       <c r="G60" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="H60">
         <v>200000</v>
@@ -19046,16 +19862,16 @@
         <v>39</v>
       </c>
       <c r="N60" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O60" t="s">
-        <v>1359</v>
+        <v>1418</v>
       </c>
       <c r="P60" t="s">
-        <v>1360</v>
+        <v>1419</v>
       </c>
       <c r="Q60" t="s">
-        <v>1361</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
@@ -19069,7 +19885,7 @@
         <v>30</v>
       </c>
       <c r="D61" t="s">
-        <v>1362</v>
+        <v>1421</v>
       </c>
       <c r="E61" t="s">
         <v>846</v>
@@ -19078,7 +19894,7 @@
         <v>855</v>
       </c>
       <c r="G61" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="J61" t="s">
         <v>38</v>
@@ -19093,16 +19909,16 @@
         <v>39</v>
       </c>
       <c r="N61" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O61" t="s">
-        <v>1363</v>
+        <v>1422</v>
       </c>
       <c r="P61" t="s">
-        <v>1364</v>
+        <v>1423</v>
       </c>
       <c r="Q61" t="s">
-        <v>1365</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
@@ -19122,10 +19938,10 @@
         <v>846</v>
       </c>
       <c r="F62" t="s">
-        <v>1218</v>
+        <v>1277</v>
       </c>
       <c r="G62" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="J62" t="s">
         <v>38</v>
@@ -19140,16 +19956,16 @@
         <v>39</v>
       </c>
       <c r="N62" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O62" t="s">
-        <v>1366</v>
+        <v>1425</v>
       </c>
       <c r="P62" t="s">
-        <v>1367</v>
+        <v>1426</v>
       </c>
       <c r="Q62" t="s">
-        <v>1368</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
@@ -19163,7 +19979,7 @@
         <v>32</v>
       </c>
       <c r="D63" t="s">
-        <v>1369</v>
+        <v>1428</v>
       </c>
       <c r="E63" t="s">
         <v>846</v>
@@ -19172,7 +19988,7 @@
         <v>855</v>
       </c>
       <c r="G63" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="J63" t="s">
         <v>38</v>
@@ -19187,16 +20003,16 @@
         <v>39</v>
       </c>
       <c r="N63" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O63" t="s">
-        <v>1370</v>
+        <v>1429</v>
       </c>
       <c r="P63" t="s">
-        <v>1371</v>
+        <v>1430</v>
       </c>
       <c r="Q63" t="s">
-        <v>1372</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
@@ -19210,16 +20026,16 @@
         <v>45</v>
       </c>
       <c r="D64" t="s">
-        <v>1373</v>
+        <v>1432</v>
       </c>
       <c r="E64" t="s">
         <v>633</v>
       </c>
       <c r="F64" t="s">
-        <v>1374</v>
+        <v>1433</v>
       </c>
       <c r="G64" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="J64" t="s">
         <v>38</v>
@@ -19234,16 +20050,16 @@
         <v>25</v>
       </c>
       <c r="N64" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O64" t="s">
-        <v>1375</v>
+        <v>1434</v>
       </c>
       <c r="P64" t="s">
-        <v>1376</v>
+        <v>1435</v>
       </c>
       <c r="Q64" t="s">
-        <v>1377</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
@@ -19257,16 +20073,16 @@
         <v>35</v>
       </c>
       <c r="D65" t="s">
-        <v>1378</v>
+        <v>1437</v>
       </c>
       <c r="E65" t="s">
         <v>633</v>
       </c>
       <c r="F65" t="s">
-        <v>1379</v>
+        <v>1438</v>
       </c>
       <c r="G65" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="J65" t="s">
         <v>38</v>
@@ -19281,16 +20097,16 @@
         <v>39</v>
       </c>
       <c r="N65" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O65" t="s">
-        <v>1380</v>
+        <v>1439</v>
       </c>
       <c r="P65" t="s">
-        <v>1381</v>
+        <v>1440</v>
       </c>
       <c r="Q65" t="s">
-        <v>1382</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
@@ -19304,7 +20120,7 @@
         <v>35</v>
       </c>
       <c r="D66" t="s">
-        <v>1383</v>
+        <v>1442</v>
       </c>
       <c r="E66" t="s">
         <v>633</v>
@@ -19313,7 +20129,7 @@
         <v>118</v>
       </c>
       <c r="G66" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="J66" t="s">
         <v>38</v>
@@ -19328,16 +20144,16 @@
         <v>39</v>
       </c>
       <c r="N66" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O66" t="s">
-        <v>1384</v>
+        <v>1443</v>
       </c>
       <c r="P66" t="s">
-        <v>1385</v>
+        <v>1444</v>
       </c>
       <c r="Q66" t="s">
-        <v>1386</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
@@ -19351,16 +20167,16 @@
         <v>15</v>
       </c>
       <c r="D67" t="s">
-        <v>1387</v>
+        <v>1446</v>
       </c>
       <c r="E67" t="s">
         <v>633</v>
       </c>
       <c r="F67" t="s">
-        <v>1388</v>
+        <v>1447</v>
       </c>
       <c r="G67" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="J67" t="s">
         <v>38</v>
@@ -19375,16 +20191,16 @@
         <v>39</v>
       </c>
       <c r="N67" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O67" t="s">
-        <v>1389</v>
+        <v>1448</v>
       </c>
       <c r="P67" t="s">
-        <v>1390</v>
+        <v>1449</v>
       </c>
       <c r="Q67" t="s">
-        <v>1391</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
@@ -19398,16 +20214,16 @@
         <v>25</v>
       </c>
       <c r="D68" t="s">
-        <v>1392</v>
+        <v>1451</v>
       </c>
       <c r="E68" t="s">
         <v>633</v>
       </c>
       <c r="F68" t="s">
-        <v>1393</v>
+        <v>1452</v>
       </c>
       <c r="G68" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="J68" t="s">
         <v>38</v>
@@ -19422,16 +20238,16 @@
         <v>39</v>
       </c>
       <c r="N68" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O68" t="s">
-        <v>1394</v>
+        <v>1453</v>
       </c>
       <c r="P68" t="s">
-        <v>1395</v>
+        <v>1454</v>
       </c>
       <c r="Q68" t="s">
-        <v>1396</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
@@ -19445,16 +20261,16 @@
         <v>30</v>
       </c>
       <c r="D69" t="s">
-        <v>1397</v>
+        <v>1456</v>
       </c>
       <c r="E69" t="s">
         <v>633</v>
       </c>
       <c r="F69" t="s">
-        <v>1398</v>
+        <v>1457</v>
       </c>
       <c r="G69" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="J69" t="s">
         <v>38</v>
@@ -19469,16 +20285,16 @@
         <v>39</v>
       </c>
       <c r="N69" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O69" t="s">
-        <v>1399</v>
+        <v>1458</v>
       </c>
       <c r="P69" t="s">
-        <v>1400</v>
+        <v>1459</v>
       </c>
       <c r="Q69" t="s">
-        <v>1401</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
@@ -19498,10 +20314,10 @@
         <v>55</v>
       </c>
       <c r="F70" t="s">
-        <v>1358</v>
+        <v>1417</v>
       </c>
       <c r="G70" t="s">
-        <v>1101</v>
+        <v>1160</v>
       </c>
       <c r="J70" t="s">
         <v>38</v>
@@ -19516,16 +20332,16 @@
         <v>39</v>
       </c>
       <c r="N70" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O70" t="s">
-        <v>1402</v>
+        <v>1461</v>
       </c>
       <c r="P70" t="s">
-        <v>1403</v>
+        <v>1462</v>
       </c>
       <c r="Q70" t="s">
-        <v>1404</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
@@ -19545,10 +20361,10 @@
         <v>55</v>
       </c>
       <c r="F71" t="s">
-        <v>1405</v>
+        <v>1464</v>
       </c>
       <c r="G71" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="J71" t="s">
         <v>38</v>
@@ -19563,16 +20379,16 @@
         <v>25</v>
       </c>
       <c r="N71" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O71" t="s">
-        <v>1406</v>
+        <v>1465</v>
       </c>
       <c r="P71" t="s">
-        <v>1407</v>
+        <v>1466</v>
       </c>
       <c r="Q71" t="s">
-        <v>1408</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
@@ -19595,7 +20411,7 @@
         <v>912</v>
       </c>
       <c r="G72" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="H72">
         <v>180000</v>
@@ -19616,16 +20432,16 @@
         <v>39</v>
       </c>
       <c r="N72" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O72" t="s">
-        <v>1409</v>
+        <v>1468</v>
       </c>
       <c r="P72" t="s">
-        <v>1410</v>
+        <v>1469</v>
       </c>
       <c r="Q72" t="s">
-        <v>1411</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
@@ -19645,10 +20461,10 @@
         <v>55</v>
       </c>
       <c r="F73" t="s">
-        <v>1412</v>
+        <v>1471</v>
       </c>
       <c r="G73" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="H73">
         <v>180000</v>
@@ -19669,16 +20485,16 @@
         <v>39</v>
       </c>
       <c r="N73" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O73" t="s">
-        <v>1413</v>
+        <v>1472</v>
       </c>
       <c r="P73" t="s">
-        <v>1414</v>
+        <v>1473</v>
       </c>
       <c r="Q73" t="s">
-        <v>1415</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
@@ -19692,16 +20508,16 @@
         <v>20</v>
       </c>
       <c r="D74" t="s">
-        <v>1416</v>
+        <v>1475</v>
       </c>
       <c r="E74" t="s">
         <v>957</v>
       </c>
       <c r="F74" t="s">
-        <v>1417</v>
+        <v>1476</v>
       </c>
       <c r="G74" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="J74" t="s">
         <v>38</v>
@@ -19716,16 +20532,16 @@
         <v>39</v>
       </c>
       <c r="N74" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O74" t="s">
-        <v>1418</v>
+        <v>1477</v>
       </c>
       <c r="P74" t="s">
-        <v>1419</v>
+        <v>1478</v>
       </c>
       <c r="Q74" t="s">
-        <v>1420</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
@@ -19739,7 +20555,7 @@
         <v>50</v>
       </c>
       <c r="D75" t="s">
-        <v>1421</v>
+        <v>1480</v>
       </c>
       <c r="E75" t="s">
         <v>957</v>
@@ -19748,7 +20564,7 @@
         <v>20</v>
       </c>
       <c r="G75" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="H75">
         <v>250000</v>
@@ -19769,16 +20585,16 @@
         <v>25</v>
       </c>
       <c r="N75" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O75" t="s">
-        <v>1422</v>
+        <v>1481</v>
       </c>
       <c r="P75" t="s">
-        <v>1423</v>
+        <v>1482</v>
       </c>
       <c r="Q75" t="s">
-        <v>1424</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
@@ -19792,7 +20608,7 @@
         <v>55</v>
       </c>
       <c r="D76" t="s">
-        <v>1425</v>
+        <v>1484</v>
       </c>
       <c r="E76" t="s">
         <v>957</v>
@@ -19801,7 +20617,7 @@
         <v>20</v>
       </c>
       <c r="G76" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="H76">
         <v>200000</v>
@@ -19822,16 +20638,16 @@
         <v>25</v>
       </c>
       <c r="N76" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O76" t="s">
-        <v>1426</v>
+        <v>1485</v>
       </c>
       <c r="P76" t="s">
-        <v>1427</v>
+        <v>1486</v>
       </c>
       <c r="Q76" t="s">
-        <v>1428</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
@@ -19845,7 +20661,7 @@
         <v>52</v>
       </c>
       <c r="D77" t="s">
-        <v>1429</v>
+        <v>1488</v>
       </c>
       <c r="E77" t="s">
         <v>957</v>
@@ -19854,7 +20670,7 @@
         <v>20</v>
       </c>
       <c r="G77" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="H77">
         <v>250000</v>
@@ -19875,16 +20691,16 @@
         <v>25</v>
       </c>
       <c r="N77" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O77" t="s">
-        <v>1430</v>
+        <v>1489</v>
       </c>
       <c r="P77" t="s">
-        <v>1431</v>
+        <v>1490</v>
       </c>
       <c r="Q77" t="s">
-        <v>1432</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
@@ -19898,7 +20714,7 @@
         <v>53</v>
       </c>
       <c r="D78" t="s">
-        <v>1433</v>
+        <v>1492</v>
       </c>
       <c r="E78" t="s">
         <v>957</v>
@@ -19907,7 +20723,7 @@
         <v>20</v>
       </c>
       <c r="G78" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="H78">
         <v>200000</v>
@@ -19928,16 +20744,16 @@
         <v>25</v>
       </c>
       <c r="N78" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O78" t="s">
-        <v>1434</v>
+        <v>1493</v>
       </c>
       <c r="P78" t="s">
-        <v>1435</v>
+        <v>1494</v>
       </c>
       <c r="Q78" t="s">
-        <v>1436</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
@@ -19951,7 +20767,7 @@
         <v>50</v>
       </c>
       <c r="D79" t="s">
-        <v>1437</v>
+        <v>1496</v>
       </c>
       <c r="E79" t="s">
         <v>957</v>
@@ -19960,7 +20776,7 @@
         <v>20</v>
       </c>
       <c r="G79" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="H79">
         <v>200000</v>
@@ -19981,16 +20797,16 @@
         <v>25</v>
       </c>
       <c r="N79" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O79" t="s">
-        <v>1438</v>
+        <v>1497</v>
       </c>
       <c r="P79" t="s">
-        <v>1439</v>
+        <v>1498</v>
       </c>
       <c r="Q79" t="s">
-        <v>1440</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
@@ -20004,7 +20820,7 @@
         <v>55</v>
       </c>
       <c r="D80" t="s">
-        <v>1441</v>
+        <v>1500</v>
       </c>
       <c r="E80" t="s">
         <v>957</v>
@@ -20013,7 +20829,7 @@
         <v>20</v>
       </c>
       <c r="G80" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="H80">
         <v>250000</v>
@@ -20034,16 +20850,16 @@
         <v>25</v>
       </c>
       <c r="N80" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O80" t="s">
-        <v>1442</v>
+        <v>1501</v>
       </c>
       <c r="P80" t="s">
-        <v>1443</v>
+        <v>1502</v>
       </c>
       <c r="Q80" t="s">
-        <v>1444</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
@@ -20057,16 +20873,16 @@
         <v>45</v>
       </c>
       <c r="D81" t="s">
-        <v>1445</v>
+        <v>1504</v>
       </c>
       <c r="E81" t="s">
-        <v>1446</v>
+        <v>1505</v>
       </c>
       <c r="F81" t="s">
-        <v>1447</v>
+        <v>1506</v>
       </c>
       <c r="G81" t="s">
-        <v>1101</v>
+        <v>1160</v>
       </c>
       <c r="H81">
         <v>154000</v>
@@ -20087,16 +20903,16 @@
         <v>39</v>
       </c>
       <c r="N81" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O81" t="s">
-        <v>1448</v>
+        <v>1507</v>
       </c>
       <c r="P81" t="s">
-        <v>1449</v>
+        <v>1508</v>
       </c>
       <c r="Q81" t="s">
-        <v>1450</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
@@ -20119,7 +20935,7 @@
         <v>592</v>
       </c>
       <c r="G82" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="H82">
         <v>180000</v>
@@ -20140,16 +20956,16 @@
         <v>25</v>
       </c>
       <c r="N82" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O82" t="s">
-        <v>1451</v>
+        <v>1510</v>
       </c>
       <c r="P82" t="s">
-        <v>1452</v>
+        <v>1511</v>
       </c>
       <c r="Q82" t="s">
-        <v>1453</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
@@ -20169,10 +20985,10 @@
         <v>55</v>
       </c>
       <c r="F83" t="s">
-        <v>1307</v>
+        <v>1366</v>
       </c>
       <c r="G83" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="H83">
         <v>219100</v>
@@ -20193,16 +21009,16 @@
         <v>39</v>
       </c>
       <c r="N83" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O83" t="s">
-        <v>1454</v>
+        <v>1513</v>
       </c>
       <c r="P83" t="s">
-        <v>1455</v>
+        <v>1514</v>
       </c>
       <c r="Q83" t="s">
-        <v>1456</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
@@ -20216,16 +21032,16 @@
         <v>25</v>
       </c>
       <c r="D84" t="s">
-        <v>1457</v>
+        <v>1516</v>
       </c>
       <c r="E84" t="s">
         <v>55</v>
       </c>
       <c r="F84" t="s">
-        <v>1458</v>
+        <v>1517</v>
       </c>
       <c r="G84" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="J84" t="s">
         <v>38</v>
@@ -20240,16 +21056,16 @@
         <v>39</v>
       </c>
       <c r="N84" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O84" t="s">
-        <v>1459</v>
+        <v>1518</v>
       </c>
       <c r="P84" t="s">
-        <v>1460</v>
+        <v>1519</v>
       </c>
       <c r="Q84" t="s">
-        <v>1461</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
@@ -20269,10 +21085,10 @@
         <v>846</v>
       </c>
       <c r="F85" t="s">
-        <v>1127</v>
+        <v>1186</v>
       </c>
       <c r="G85" t="s">
-        <v>1101</v>
+        <v>1160</v>
       </c>
       <c r="J85" t="s">
         <v>38</v>
@@ -20287,16 +21103,16 @@
         <v>39</v>
       </c>
       <c r="N85" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O85" t="s">
-        <v>1462</v>
+        <v>1521</v>
       </c>
       <c r="P85" t="s">
-        <v>1463</v>
+        <v>1522</v>
       </c>
       <c r="Q85" t="s">
-        <v>1464</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
@@ -20310,16 +21126,16 @@
         <v>15</v>
       </c>
       <c r="D86" t="s">
-        <v>1465</v>
+        <v>1524</v>
       </c>
       <c r="E86" t="s">
-        <v>1466</v>
+        <v>1525</v>
       </c>
       <c r="F86" t="s">
-        <v>1275</v>
+        <v>1334</v>
       </c>
       <c r="G86" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="J86" t="s">
         <v>38</v>
@@ -20334,16 +21150,16 @@
         <v>39</v>
       </c>
       <c r="N86" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O86" t="s">
-        <v>1467</v>
+        <v>1526</v>
       </c>
       <c r="P86" t="s">
-        <v>1468</v>
+        <v>1527</v>
       </c>
       <c r="Q86" t="s">
-        <v>1469</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
@@ -20357,16 +21173,16 @@
         <v>12</v>
       </c>
       <c r="D87" t="s">
-        <v>1470</v>
+        <v>1529</v>
       </c>
       <c r="E87" t="s">
-        <v>1471</v>
+        <v>1530</v>
       </c>
       <c r="F87" t="s">
-        <v>1472</v>
+        <v>1531</v>
       </c>
       <c r="G87" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="J87" t="s">
         <v>38</v>
@@ -20381,16 +21197,16 @@
         <v>39</v>
       </c>
       <c r="N87" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O87" t="s">
-        <v>1473</v>
+        <v>1532</v>
       </c>
       <c r="P87" t="s">
-        <v>1474</v>
+        <v>1533</v>
       </c>
       <c r="Q87" t="s">
-        <v>1475</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
@@ -20404,16 +21220,16 @@
         <v>42</v>
       </c>
       <c r="D88" t="s">
-        <v>1476</v>
+        <v>1535</v>
       </c>
       <c r="E88" t="s">
         <v>55</v>
       </c>
       <c r="F88" t="s">
-        <v>1477</v>
+        <v>1536</v>
       </c>
       <c r="G88" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="H88">
         <v>180000</v>
@@ -20434,16 +21250,16 @@
         <v>25</v>
       </c>
       <c r="N88" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O88" t="s">
-        <v>1478</v>
+        <v>1537</v>
       </c>
       <c r="P88" t="s">
-        <v>1479</v>
+        <v>1538</v>
       </c>
       <c r="Q88" t="s">
-        <v>1480</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
@@ -20457,16 +21273,16 @@
         <v>22</v>
       </c>
       <c r="D89" t="s">
-        <v>1481</v>
+        <v>1540</v>
       </c>
       <c r="E89" t="s">
-        <v>1208</v>
+        <v>1267</v>
       </c>
       <c r="F89" t="s">
-        <v>1482</v>
+        <v>1541</v>
       </c>
       <c r="G89" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="H89">
         <v>200000</v>
@@ -20487,16 +21303,16 @@
         <v>39</v>
       </c>
       <c r="N89" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O89" t="s">
-        <v>1483</v>
+        <v>1542</v>
       </c>
       <c r="P89" t="s">
-        <v>1484</v>
+        <v>1543</v>
       </c>
       <c r="Q89" t="s">
-        <v>1485</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
@@ -20510,16 +21326,16 @@
         <v>28</v>
       </c>
       <c r="D90" t="s">
-        <v>1486</v>
+        <v>1545</v>
       </c>
       <c r="E90" t="s">
-        <v>1487</v>
+        <v>1546</v>
       </c>
       <c r="F90" t="s">
-        <v>1458</v>
+        <v>1517</v>
       </c>
       <c r="G90" t="s">
-        <v>1101</v>
+        <v>1160</v>
       </c>
       <c r="J90" t="s">
         <v>38</v>
@@ -20534,16 +21350,16 @@
         <v>39</v>
       </c>
       <c r="N90" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O90" t="s">
-        <v>1488</v>
+        <v>1547</v>
       </c>
       <c r="P90" t="s">
-        <v>1489</v>
+        <v>1548</v>
       </c>
       <c r="Q90" t="s">
-        <v>1490</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
@@ -20557,16 +21373,16 @@
         <v>5</v>
       </c>
       <c r="D91" t="s">
-        <v>1491</v>
+        <v>1550</v>
       </c>
       <c r="E91" t="s">
-        <v>1492</v>
+        <v>1551</v>
       </c>
       <c r="F91" t="s">
-        <v>1493</v>
+        <v>1552</v>
       </c>
       <c r="G91" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="J91" t="s">
         <v>38</v>
@@ -20581,16 +21397,16 @@
         <v>39</v>
       </c>
       <c r="N91" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O91" t="s">
-        <v>1494</v>
+        <v>1553</v>
       </c>
       <c r="P91" t="s">
-        <v>1495</v>
+        <v>1554</v>
       </c>
       <c r="Q91" t="s">
-        <v>1496</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
@@ -20610,10 +21426,10 @@
         <v>55</v>
       </c>
       <c r="F92" t="s">
-        <v>1497</v>
+        <v>1556</v>
       </c>
       <c r="G92" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="J92" t="s">
         <v>38</v>
@@ -20628,16 +21444,16 @@
         <v>25</v>
       </c>
       <c r="N92" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O92" t="s">
-        <v>1498</v>
+        <v>1557</v>
       </c>
       <c r="P92" t="s">
-        <v>1499</v>
+        <v>1558</v>
       </c>
       <c r="Q92" t="s">
-        <v>1500</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
@@ -20651,16 +21467,16 @@
         <v>35</v>
       </c>
       <c r="D93" t="s">
-        <v>1501</v>
+        <v>1560</v>
       </c>
       <c r="E93" t="s">
-        <v>1502</v>
+        <v>1561</v>
       </c>
       <c r="F93" t="s">
-        <v>1269</v>
+        <v>1328</v>
       </c>
       <c r="G93" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="J93" t="s">
         <v>38</v>
@@ -20675,16 +21491,16 @@
         <v>39</v>
       </c>
       <c r="N93" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O93" t="s">
-        <v>1503</v>
+        <v>1562</v>
       </c>
       <c r="P93" t="s">
-        <v>1504</v>
+        <v>1563</v>
       </c>
       <c r="Q93" t="s">
-        <v>1505</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
@@ -20698,16 +21514,16 @@
         <v>55</v>
       </c>
       <c r="D94" t="s">
-        <v>1506</v>
+        <v>1565</v>
       </c>
       <c r="E94" t="s">
         <v>55</v>
       </c>
       <c r="F94" t="s">
-        <v>1307</v>
+        <v>1366</v>
       </c>
       <c r="G94" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="H94">
         <v>219100</v>
@@ -20722,22 +21538,22 @@
         <v>57</v>
       </c>
       <c r="L94" t="s">
-        <v>1507</v>
+        <v>1566</v>
       </c>
       <c r="M94" t="s">
         <v>25</v>
       </c>
       <c r="N94" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O94" t="s">
-        <v>1508</v>
+        <v>1567</v>
       </c>
       <c r="P94" t="s">
-        <v>1509</v>
+        <v>1568</v>
       </c>
       <c r="Q94" t="s">
-        <v>1510</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
@@ -20751,16 +21567,16 @@
         <v>50</v>
       </c>
       <c r="D95" t="s">
-        <v>1511</v>
+        <v>1570</v>
       </c>
       <c r="E95" t="s">
-        <v>1208</v>
+        <v>1267</v>
       </c>
       <c r="F95" t="s">
         <v>20</v>
       </c>
       <c r="G95" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="H95">
         <v>200000</v>
@@ -20775,22 +21591,22 @@
         <v>57</v>
       </c>
       <c r="L95" t="s">
-        <v>1507</v>
+        <v>1566</v>
       </c>
       <c r="M95" t="s">
         <v>25</v>
       </c>
       <c r="N95" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O95" t="s">
-        <v>1512</v>
+        <v>1571</v>
       </c>
       <c r="P95" t="s">
-        <v>1513</v>
+        <v>1572</v>
       </c>
       <c r="Q95" t="s">
-        <v>1514</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
@@ -20804,16 +21620,16 @@
         <v>12</v>
       </c>
       <c r="D96" t="s">
-        <v>1515</v>
+        <v>1574</v>
       </c>
       <c r="E96" t="s">
-        <v>1516</v>
+        <v>1575</v>
       </c>
       <c r="F96" t="s">
-        <v>1458</v>
+        <v>1517</v>
       </c>
       <c r="G96" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="J96" t="s">
         <v>38</v>
@@ -20822,22 +21638,22 @@
         <v>130</v>
       </c>
       <c r="L96" t="s">
-        <v>1507</v>
+        <v>1566</v>
       </c>
       <c r="M96" t="s">
         <v>39</v>
       </c>
       <c r="N96" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O96" t="s">
-        <v>1517</v>
+        <v>1576</v>
       </c>
       <c r="P96" t="s">
-        <v>1518</v>
+        <v>1577</v>
       </c>
       <c r="Q96" t="s">
-        <v>1519</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
@@ -20851,16 +21667,16 @@
         <v>12</v>
       </c>
       <c r="D97" t="s">
-        <v>1520</v>
+        <v>1579</v>
       </c>
       <c r="E97" t="s">
-        <v>1516</v>
+        <v>1575</v>
       </c>
       <c r="F97" t="s">
-        <v>1458</v>
+        <v>1517</v>
       </c>
       <c r="G97" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="J97" t="s">
         <v>38</v>
@@ -20869,22 +21685,22 @@
         <v>130</v>
       </c>
       <c r="L97" t="s">
-        <v>1507</v>
+        <v>1566</v>
       </c>
       <c r="M97" t="s">
         <v>39</v>
       </c>
       <c r="N97" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O97" t="s">
-        <v>1521</v>
+        <v>1580</v>
       </c>
       <c r="P97" t="s">
-        <v>1522</v>
+        <v>1581</v>
       </c>
       <c r="Q97" t="s">
-        <v>1523</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
@@ -20898,16 +21714,16 @@
         <v>3</v>
       </c>
       <c r="D98" t="s">
-        <v>1524</v>
+        <v>1583</v>
       </c>
       <c r="E98" t="s">
-        <v>1516</v>
+        <v>1575</v>
       </c>
       <c r="F98" t="s">
-        <v>1458</v>
+        <v>1517</v>
       </c>
       <c r="G98" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="J98" t="s">
         <v>38</v>
@@ -20916,22 +21732,22 @@
         <v>130</v>
       </c>
       <c r="L98" t="s">
-        <v>1507</v>
+        <v>1566</v>
       </c>
       <c r="M98" t="s">
         <v>39</v>
       </c>
       <c r="N98" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O98" t="s">
-        <v>1525</v>
+        <v>1584</v>
       </c>
       <c r="P98" t="s">
-        <v>1526</v>
+        <v>1585</v>
       </c>
       <c r="Q98" t="s">
-        <v>1527</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.25">
@@ -20945,16 +21761,16 @@
         <v>25</v>
       </c>
       <c r="D99" t="s">
-        <v>1528</v>
+        <v>1587</v>
       </c>
       <c r="E99" t="s">
-        <v>1529</v>
+        <v>1588</v>
       </c>
       <c r="F99" t="s">
-        <v>1530</v>
+        <v>1589</v>
       </c>
       <c r="G99" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="J99" t="s">
         <v>38</v>
@@ -20963,22 +21779,22 @@
         <v>130</v>
       </c>
       <c r="L99" t="s">
-        <v>1507</v>
+        <v>1566</v>
       </c>
       <c r="M99" t="s">
         <v>39</v>
       </c>
       <c r="N99" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O99" t="s">
-        <v>1531</v>
+        <v>1590</v>
       </c>
       <c r="P99" t="s">
-        <v>1532</v>
+        <v>1591</v>
       </c>
       <c r="Q99" t="s">
-        <v>1533</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.25">
@@ -20992,16 +21808,16 @@
         <v>62</v>
       </c>
       <c r="D100" t="s">
-        <v>1534</v>
+        <v>1593</v>
       </c>
       <c r="E100" t="s">
-        <v>1535</v>
+        <v>1594</v>
       </c>
       <c r="F100" t="s">
-        <v>1536</v>
+        <v>1595</v>
       </c>
       <c r="G100" t="s">
-        <v>1101</v>
+        <v>1160</v>
       </c>
       <c r="J100" t="s">
         <v>38</v>
@@ -21010,22 +21826,22 @@
         <v>130</v>
       </c>
       <c r="L100" t="s">
-        <v>1507</v>
+        <v>1566</v>
       </c>
       <c r="M100" t="s">
         <v>39</v>
       </c>
       <c r="N100" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O100" t="s">
-        <v>1537</v>
+        <v>1596</v>
       </c>
       <c r="P100" t="s">
-        <v>1538</v>
+        <v>1597</v>
       </c>
       <c r="Q100" t="s">
-        <v>1539</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.25">
@@ -21039,16 +21855,16 @@
         <v>68</v>
       </c>
       <c r="D101" t="s">
-        <v>1540</v>
+        <v>1599</v>
       </c>
       <c r="E101" t="s">
-        <v>1535</v>
+        <v>1594</v>
       </c>
       <c r="F101" t="s">
-        <v>1536</v>
+        <v>1595</v>
       </c>
       <c r="G101" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="J101" t="s">
         <v>38</v>
@@ -21057,22 +21873,22 @@
         <v>130</v>
       </c>
       <c r="L101" t="s">
-        <v>1507</v>
+        <v>1566</v>
       </c>
       <c r="M101" t="s">
         <v>39</v>
       </c>
       <c r="N101" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O101" t="s">
-        <v>1541</v>
+        <v>1600</v>
       </c>
       <c r="P101" t="s">
-        <v>1542</v>
+        <v>1601</v>
       </c>
       <c r="Q101" t="s">
-        <v>1543</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.25">
@@ -21092,10 +21908,10 @@
         <v>55</v>
       </c>
       <c r="F102" t="s">
-        <v>1544</v>
+        <v>1603</v>
       </c>
       <c r="G102" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="H102">
         <v>180000</v>
@@ -21116,16 +21932,16 @@
         <v>25</v>
       </c>
       <c r="N102" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O102" t="s">
-        <v>1545</v>
+        <v>1604</v>
       </c>
       <c r="P102" t="s">
-        <v>1546</v>
+        <v>1605</v>
       </c>
       <c r="Q102" t="s">
-        <v>1547</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.25">
@@ -21145,10 +21961,10 @@
         <v>55</v>
       </c>
       <c r="F103" t="s">
-        <v>1548</v>
+        <v>1607</v>
       </c>
       <c r="G103" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="H103">
         <v>180000</v>
@@ -21169,16 +21985,16 @@
         <v>25</v>
       </c>
       <c r="N103" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O103" t="s">
-        <v>1549</v>
+        <v>1608</v>
       </c>
       <c r="P103" t="s">
-        <v>1550</v>
+        <v>1609</v>
       </c>
       <c r="Q103" t="s">
-        <v>1551</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.25">
@@ -21192,16 +22008,16 @@
         <v>35</v>
       </c>
       <c r="D104" t="s">
-        <v>1552</v>
+        <v>1611</v>
       </c>
       <c r="E104" t="s">
         <v>55</v>
       </c>
       <c r="F104" t="s">
-        <v>1553</v>
+        <v>1612</v>
       </c>
       <c r="G104" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="H104">
         <v>219100</v>
@@ -21222,16 +22038,16 @@
         <v>25</v>
       </c>
       <c r="N104" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O104" t="s">
-        <v>1554</v>
+        <v>1613</v>
       </c>
       <c r="P104" t="s">
-        <v>1555</v>
+        <v>1614</v>
       </c>
       <c r="Q104" t="s">
-        <v>1556</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.25">
@@ -21245,16 +22061,16 @@
         <v>25</v>
       </c>
       <c r="D105" t="s">
-        <v>1557</v>
+        <v>1616</v>
       </c>
       <c r="E105" t="s">
         <v>633</v>
       </c>
       <c r="F105" t="s">
-        <v>1374</v>
+        <v>1433</v>
       </c>
       <c r="G105" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="J105" t="s">
         <v>38</v>
@@ -21269,16 +22085,16 @@
         <v>39</v>
       </c>
       <c r="N105" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O105" t="s">
-        <v>1558</v>
+        <v>1617</v>
       </c>
       <c r="P105" t="s">
-        <v>1559</v>
+        <v>1618</v>
       </c>
       <c r="Q105" t="s">
-        <v>1560</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.25">
@@ -21292,16 +22108,16 @@
         <v>35</v>
       </c>
       <c r="D106" t="s">
-        <v>1561</v>
+        <v>1620</v>
       </c>
       <c r="E106" t="s">
-        <v>1562</v>
+        <v>1621</v>
       </c>
       <c r="F106" t="s">
-        <v>1127</v>
+        <v>1186</v>
       </c>
       <c r="G106" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="J106" t="s">
         <v>38</v>
@@ -21316,16 +22132,16 @@
         <v>39</v>
       </c>
       <c r="N106" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O106" t="s">
-        <v>1563</v>
+        <v>1622</v>
       </c>
       <c r="P106" t="s">
-        <v>1564</v>
+        <v>1623</v>
       </c>
       <c r="Q106" t="s">
-        <v>1565</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.25">
@@ -21342,13 +22158,13 @@
         <v>305</v>
       </c>
       <c r="E107" t="s">
-        <v>1566</v>
+        <v>1625</v>
       </c>
       <c r="F107" t="s">
-        <v>1269</v>
+        <v>1328</v>
       </c>
       <c r="G107" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="H107">
         <v>200000</v>
@@ -21369,16 +22185,16 @@
         <v>39</v>
       </c>
       <c r="N107" t="s">
-        <v>1085</v>
+        <v>1144</v>
       </c>
       <c r="O107" t="s">
-        <v>1567</v>
+        <v>1626</v>
       </c>
       <c r="P107" t="s">
-        <v>1568</v>
+        <v>1627</v>
       </c>
       <c r="Q107" t="s">
-        <v>1569</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.25">
@@ -21392,16 +22208,16 @@
         <v>38</v>
       </c>
       <c r="D108" t="s">
-        <v>1570</v>
+        <v>1629</v>
       </c>
       <c r="E108" t="s">
-        <v>1566</v>
+        <v>1625</v>
       </c>
       <c r="F108" t="s">
-        <v>1269</v>
+        <v>1328</v>
       </c>
       <c r="G108" t="s">
-        <v>1084</v>
+        <v>1143</v>
       </c>
       <c r="H108">
         <v>200000</v>
@@ -21422,16 +22238,169 @@
         <v>39</v>
       </c>
       <c r="N108" t="s">
+        <v>1144</v>
+      </c>
+      <c r="O108" t="s">
+        <v>1630</v>
+      </c>
+      <c r="P108" t="s">
+        <v>1631</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>1632</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>17</v>
+      </c>
+      <c r="B109">
+        <v>48</v>
+      </c>
+      <c r="C109">
+        <v>40</v>
+      </c>
+      <c r="D109" t="s">
+        <v>1411</v>
+      </c>
+      <c r="E109" t="s">
+        <v>1267</v>
+      </c>
+      <c r="F109" t="s">
+        <v>861</v>
+      </c>
+      <c r="G109" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H109">
+        <v>184200</v>
+      </c>
+      <c r="I109">
+        <v>184200</v>
+      </c>
+      <c r="J109" t="s">
+        <v>22</v>
+      </c>
+      <c r="K109" t="s">
+        <v>57</v>
+      </c>
+      <c r="L109" t="s">
         <v>1085</v>
       </c>
-      <c r="O108" t="s">
-        <v>1571</v>
-      </c>
-      <c r="P108" t="s">
-        <v>1572</v>
-      </c>
-      <c r="Q108" t="s">
-        <v>1573</v>
+      <c r="M109" t="s">
+        <v>39</v>
+      </c>
+      <c r="N109" t="s">
+        <v>1144</v>
+      </c>
+      <c r="O109" t="s">
+        <v>1633</v>
+      </c>
+      <c r="P109" t="s">
+        <v>1634</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>1635</v>
+      </c>
+    </row>
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>17</v>
+      </c>
+      <c r="B110">
+        <v>12</v>
+      </c>
+      <c r="C110">
+        <v>20</v>
+      </c>
+      <c r="D110" t="s">
+        <v>1636</v>
+      </c>
+      <c r="E110" t="s">
+        <v>1637</v>
+      </c>
+      <c r="F110" t="s">
+        <v>1638</v>
+      </c>
+      <c r="G110" t="s">
+        <v>1143</v>
+      </c>
+      <c r="J110" t="s">
+        <v>38</v>
+      </c>
+      <c r="K110" t="s">
+        <v>130</v>
+      </c>
+      <c r="L110" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M110" t="s">
+        <v>39</v>
+      </c>
+      <c r="N110" t="s">
+        <v>1144</v>
+      </c>
+      <c r="O110" t="s">
+        <v>1639</v>
+      </c>
+      <c r="P110" t="s">
+        <v>1640</v>
+      </c>
+      <c r="Q110" t="s">
+        <v>1641</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>17</v>
+      </c>
+      <c r="B111">
+        <v>42</v>
+      </c>
+      <c r="C111">
+        <v>35</v>
+      </c>
+      <c r="D111" t="s">
+        <v>1642</v>
+      </c>
+      <c r="E111" t="s">
+        <v>1643</v>
+      </c>
+      <c r="F111" t="s">
+        <v>1644</v>
+      </c>
+      <c r="G111" t="s">
+        <v>1160</v>
+      </c>
+      <c r="H111">
+        <v>230000</v>
+      </c>
+      <c r="I111">
+        <v>350000</v>
+      </c>
+      <c r="J111" t="s">
+        <v>22</v>
+      </c>
+      <c r="K111" t="s">
+        <v>923</v>
+      </c>
+      <c r="L111" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M111" t="s">
+        <v>39</v>
+      </c>
+      <c r="N111" t="s">
+        <v>1144</v>
+      </c>
+      <c r="O111" t="s">
+        <v>1645</v>
+      </c>
+      <c r="P111" t="s">
+        <v>1646</v>
+      </c>
+      <c r="Q111" t="s">
+        <v>1647</v>
       </c>
     </row>
   </sheetData>

--- a/hunt/board.xlsx
+++ b/hunt/board.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4428" uniqueCount="1648">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4545" uniqueCount="1689">
   <si>
     <t>Column</t>
   </si>
@@ -3440,6 +3440,21 @@
     <t>https://jobicy.com/jobs/149932-senior-devops-devex-engineer</t>
   </si>
   <si>
+    <t>InfoTrust</t>
+  </si>
+  <si>
+    <t>2026-09-02T02:26:37.047Z</t>
+  </si>
+  <si>
+    <t>Fully remote US role, matching the candidate's primary workplace preference | Founding DevOps hire scope — standing up CI/CD, cloud infra, reliability and security standards maps directly to the candidate's Azure DevOps/GitHub platform and governance experience | Greenfield 'write the playbook' mandate aligns with the candidate's DevOps maturity assessment and advisory background</t>
+  </si>
+  <si>
+    <t>Titled Senior DevOps Engineer, not principal/architect scope the candidate is targeting; likely hands-on IC without team leverage | InfoTrust's digital analytics/marketing stack is typically GCP-heavy, which may not credit Azure-first depth | No salary posted; a founding-hire role at a mid-size private firm may land below the $180K floor</t>
+  </si>
+  <si>
+    <t>https://himalayas.app/companies/infotrust/jobs/senior-devops-engineer</t>
+  </si>
+  <si>
     <t>Lead GTM Enablement &amp; Scale Architect, Field Engineering - Customer Skills</t>
   </si>
   <si>
@@ -4956,6 +4971,114 @@
   </si>
   <si>
     <t>https://jobs.ashbyhq.com/replit/df7b6d30-9da1-4ace-8121-17c2aa55aa6f</t>
+  </si>
+  <si>
+    <t>Denver, Colorado</t>
+  </si>
+  <si>
+    <t>Confirmed comp at $219,100 well above the $180K floor | Senior Solutions Architect is squarely on the candidate's target title list, and posting explicitly says candidates outside Denver will be considered | Customer-facing technical advisory model matches the candidate's Customer Engineer trusted-advisor engagement experience</t>
+  </si>
+  <si>
+    <t>Databricks SAs need deep data/lakehouse, Spark, SQL and data engineering depth that the resume does not show | Cloud exposure at Databricks is multi-cloud with heavy AWS presence; Azure-only depth is only partial coverage | Location listed as Denver with unclear remote status — relocation implications unresolved</t>
+  </si>
+  <si>
+    <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8769768002</t>
+  </si>
+  <si>
+    <t>SAP Integration Architect</t>
+  </si>
+  <si>
+    <t>Architect-level, customer-facing role inside an SAP Center of Excellence with enterprise brands | Integration architecture work touches API/platform design, adjacent to the candidate's platform background</t>
+  </si>
+  <si>
+    <t>Requires deep SAP ecosystem expertise (BTP, integration suite, SAP CX) that the candidate has none of | Hybrid role with no stated US location — likely Germany-based, and no relocation criteria set | No Azure DevOps/GitHub governance relevance to the candidate's differentiators</t>
+  </si>
+  <si>
+    <t>https://www.arbeitnow.com/jobs/companies/parloa/sap-integration-architect-329226</t>
+  </si>
+  <si>
+    <t>Senior AI Architect &amp; Consultant (m/w/d)</t>
+  </si>
+  <si>
+    <t>Mayflower</t>
+  </si>
+  <si>
+    <t>Consultative architecture role with C-level advisory scope, similar engagement model to the candidate's customer-facing work | Production AI infrastructure ownership overlaps loosely with platform/DevOps skills</t>
+  </si>
+  <si>
+    <t>Requires hands-on LLM/agentic depth (LangGraph, PydanticAI, evaluation pipelines) the resume does not demonstrate | German-language posting based in Munich — outside the candidate's US market scope | No Azure governance/GHAS relevance and no salary transparency</t>
+  </si>
+  <si>
+    <t>https://www.arbeitnow.com/jobs/companies/mayflower/senior-ai-architect-consultant-munchen-419121</t>
+  </si>
+  <si>
+    <t>Fluidic System Engineer / Architect (m/f/d)</t>
+  </si>
+  <si>
+    <t>Deltavision</t>
+  </si>
+  <si>
+    <t>Architect-titled role with technical leadership and customer interfacing responsibilities</t>
+  </si>
+  <si>
+    <t>Requires spacecraft propulsion fluidics, CFD simulation and MBSE — completely outside the candidate's cloud/DevOps domain | Munich-based onsite aerospace hardware role, not US remote software | Zero overlap with Azure, CI/CD or governance skill set</t>
+  </si>
+  <si>
+    <t>https://www.arbeitnow.com/jobs/companies/deltavision/fluidic-system-engineer-architect-munchen-56978</t>
+  </si>
+  <si>
+    <t>Principal Systems Architect (m/w/d) Defence &amp; Security</t>
+  </si>
+  <si>
+    <t>Defence Recruiting</t>
+  </si>
+  <si>
+    <t>Principal-level architecture scope matches the candidate's seniority target | Containerized distributed architectures, cloud platform evaluation and orchestration overlap with the candidate's platform experience | Workshop-based technical consulting mirrors the trusted-advisor engagement model</t>
+  </si>
+  <si>
+    <t>German-language, Munich-based defence role that will almost certainly require German nationality/security vetting the candidate lacks | Focus on safety-critical embedded/defence systems rather than Azure DevOps or GitHub governance | No compensation posted and outside the candidate's US market scope</t>
+  </si>
+  <si>
+    <t>https://www.arbeitnow.com/jobs/companies/defence-recruiting/principal-systems-architect-defence-security-munich-490548</t>
+  </si>
+  <si>
+    <t>Global Solutions Architect - Cloud</t>
+  </si>
+  <si>
+    <t>Rubrik</t>
+  </si>
+  <si>
+    <t>Technical Director-level individual contributor scope in cloud architecture — matches the candidate's principal-level ambition | Work involves reference architectures, enablement and flagship customer engagements, a strong match to the trusted-advisor delivery model | Public cloud architecture focus overlaps with the candidate's Azure platform and IaC depth</t>
+  </si>
+  <si>
+    <t>Positioned as the firm's most senior public cloud authority, typically expecting deep multi-cloud (AWS-primary) data protection expertise beyond the candidate's Azure-centric 10 years | London-based role, outside the candidate's stated US market scope | No salary published; UK banding likely below the $180K USD floor</t>
+  </si>
+  <si>
+    <t>https://www.arbeitnow.co.uk/jobs/companies/rubrik/global-solutions-architect-cloud-london-119074</t>
+  </si>
+  <si>
+    <t>Consulting-project delivery for enterprise clients (AXA, BMW, Deutsche Bahn) matches the candidate's enterprise advisory precedent, including insurance | Explicitly names Azure alongside AWS/GCP, plus Terraform, Kubernetes, GitOps and Continuous Delivery — solid overlap with the candidate's IaC and CI/CD skills</t>
+  </si>
+  <si>
+    <t>German-language posting in Frankfurt; fluent German is effectively required for these consulting projects | Senior engineer scope rather than the principal/architect level the candidate targets | German consulting salaries (~€75K–€110K) fall far below the $180K floor</t>
+  </si>
+  <si>
+    <t>https://www.arbeitnow.com/jobs/companies/accso-accelerated-solutions-gmbh/senior-cloud-devops-engineer-frankfurt-am-main-52872</t>
+  </si>
+  <si>
+    <t>Technical Solution Architect</t>
+  </si>
+  <si>
+    <t>San Francisco, CA, Boston, MA</t>
+  </si>
+  <si>
+    <t>Solutions architect title on the candidate's target list, with customer-facing technical delivery focus | Published range topping at $209K clears the $180K floor at the upper end | Life-sciences R&amp;D platform work implies regulated-industry data handling, adjacent to the candidate's HIPAA/compliance architecture experience</t>
+  </si>
+  <si>
+    <t>Benchling architects need scientific/biotech domain fluency and application/data modeling depth the resume doesn't show | Hybrid in San Francisco or Boston — high-cost markets and relocation criteria are undefined | Range starts at $154K, so a mid-band offer would fall under the salary floor</t>
+  </si>
+  <si>
+    <t>https://jobs.ashbyhq.com/benchling/65d30858-1165-4c3f-8ba1-38489fa2e63f</t>
   </si>
 </sst>
 </file>
@@ -5336,7 +5459,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q229"/>
+  <dimension ref="A1:Q230"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -16854,6 +16977,53 @@
         <v>1141</v>
       </c>
     </row>
+    <row r="230" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>17</v>
+      </c>
+      <c r="B230">
+        <v>68</v>
+      </c>
+      <c r="C230">
+        <v>72</v>
+      </c>
+      <c r="D230" t="s">
+        <v>43</v>
+      </c>
+      <c r="E230" t="s">
+        <v>1142</v>
+      </c>
+      <c r="F230" t="s">
+        <v>20</v>
+      </c>
+      <c r="G230" t="s">
+        <v>21</v>
+      </c>
+      <c r="J230" t="s">
+        <v>38</v>
+      </c>
+      <c r="K230" t="s">
+        <v>23</v>
+      </c>
+      <c r="L230" t="s">
+        <v>1143</v>
+      </c>
+      <c r="M230" t="s">
+        <v>32</v>
+      </c>
+      <c r="N230" t="s">
+        <v>26</v>
+      </c>
+      <c r="O230" t="s">
+        <v>1144</v>
+      </c>
+      <c r="P230" t="s">
+        <v>1145</v>
+      </c>
+      <c r="Q230" t="s">
+        <v>1146</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:Q1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16863,7 +17033,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q111"/>
+  <dimension ref="A1:Q119"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -16944,7 +17114,7 @@
         <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>1142</v>
+        <v>1147</v>
       </c>
       <c r="E2" t="s">
         <v>55</v>
@@ -16953,7 +17123,7 @@
         <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="H2">
         <v>217800</v>
@@ -16974,16 +17144,16 @@
         <v>25</v>
       </c>
       <c r="N2" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O2" t="s">
-        <v>1145</v>
+        <v>1150</v>
       </c>
       <c r="P2" t="s">
-        <v>1146</v>
+        <v>1151</v>
       </c>
       <c r="Q2" t="s">
-        <v>1147</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -16997,16 +17167,16 @@
         <v>45</v>
       </c>
       <c r="D3" t="s">
-        <v>1148</v>
+        <v>1153</v>
       </c>
       <c r="E3" t="s">
         <v>55</v>
       </c>
       <c r="F3" t="s">
-        <v>1149</v>
+        <v>1154</v>
       </c>
       <c r="G3" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="H3">
         <v>219100</v>
@@ -17027,16 +17197,16 @@
         <v>25</v>
       </c>
       <c r="N3" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O3" t="s">
-        <v>1150</v>
+        <v>1155</v>
       </c>
       <c r="P3" t="s">
-        <v>1151</v>
+        <v>1156</v>
       </c>
       <c r="Q3" t="s">
-        <v>1152</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
@@ -17056,10 +17226,10 @@
         <v>846</v>
       </c>
       <c r="F4" t="s">
-        <v>1153</v>
+        <v>1158</v>
       </c>
       <c r="G4" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J4" t="s">
         <v>38</v>
@@ -17074,16 +17244,16 @@
         <v>39</v>
       </c>
       <c r="N4" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O4" t="s">
-        <v>1154</v>
+        <v>1159</v>
       </c>
       <c r="P4" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
       <c r="Q4" t="s">
-        <v>1156</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -17097,16 +17267,16 @@
         <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>1157</v>
+        <v>1162</v>
       </c>
       <c r="E5" t="s">
-        <v>1158</v>
+        <v>1163</v>
       </c>
       <c r="F5" t="s">
-        <v>1159</v>
+        <v>1164</v>
       </c>
       <c r="G5" t="s">
-        <v>1160</v>
+        <v>1165</v>
       </c>
       <c r="J5" t="s">
         <v>38</v>
@@ -17121,16 +17291,16 @@
         <v>39</v>
       </c>
       <c r="N5" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O5" t="s">
-        <v>1161</v>
+        <v>1166</v>
       </c>
       <c r="P5" t="s">
-        <v>1162</v>
+        <v>1167</v>
       </c>
       <c r="Q5" t="s">
-        <v>1163</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -17144,16 +17314,16 @@
         <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>1164</v>
+        <v>1169</v>
       </c>
       <c r="E6" t="s">
-        <v>1165</v>
+        <v>1170</v>
       </c>
       <c r="F6" t="s">
-        <v>1166</v>
+        <v>1171</v>
       </c>
       <c r="G6" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J6" t="s">
         <v>38</v>
@@ -17168,16 +17338,16 @@
         <v>39</v>
       </c>
       <c r="N6" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O6" t="s">
-        <v>1167</v>
+        <v>1172</v>
       </c>
       <c r="P6" t="s">
-        <v>1168</v>
+        <v>1173</v>
       </c>
       <c r="Q6" t="s">
-        <v>1169</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -17191,16 +17361,16 @@
         <v>55</v>
       </c>
       <c r="D7" t="s">
+        <v>1175</v>
+      </c>
+      <c r="E7" t="s">
         <v>1170</v>
       </c>
-      <c r="E7" t="s">
-        <v>1165</v>
-      </c>
       <c r="F7" t="s">
-        <v>1171</v>
+        <v>1176</v>
       </c>
       <c r="G7" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J7" t="s">
         <v>38</v>
@@ -17215,16 +17385,16 @@
         <v>39</v>
       </c>
       <c r="N7" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O7" t="s">
-        <v>1172</v>
+        <v>1177</v>
       </c>
       <c r="P7" t="s">
-        <v>1173</v>
+        <v>1178</v>
       </c>
       <c r="Q7" t="s">
-        <v>1174</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -17238,16 +17408,16 @@
         <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>1175</v>
+        <v>1180</v>
       </c>
       <c r="E8" t="s">
-        <v>1165</v>
+        <v>1170</v>
       </c>
       <c r="F8" t="s">
-        <v>1166</v>
+        <v>1171</v>
       </c>
       <c r="G8" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J8" t="s">
         <v>38</v>
@@ -17262,16 +17432,16 @@
         <v>39</v>
       </c>
       <c r="N8" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O8" t="s">
-        <v>1176</v>
+        <v>1181</v>
       </c>
       <c r="P8" t="s">
-        <v>1177</v>
+        <v>1182</v>
       </c>
       <c r="Q8" t="s">
-        <v>1178</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -17285,16 +17455,16 @@
         <v>5</v>
       </c>
       <c r="D9" t="s">
-        <v>1179</v>
+        <v>1184</v>
       </c>
       <c r="E9" t="s">
-        <v>1180</v>
+        <v>1185</v>
       </c>
       <c r="F9" t="s">
-        <v>1181</v>
+        <v>1186</v>
       </c>
       <c r="G9" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J9" t="s">
         <v>38</v>
@@ -17309,16 +17479,16 @@
         <v>39</v>
       </c>
       <c r="N9" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O9" t="s">
-        <v>1182</v>
+        <v>1187</v>
       </c>
       <c r="P9" t="s">
-        <v>1183</v>
+        <v>1188</v>
       </c>
       <c r="Q9" t="s">
-        <v>1184</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -17332,16 +17502,16 @@
         <v>45</v>
       </c>
       <c r="D10" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E10" t="s">
         <v>1185</v>
       </c>
-      <c r="E10" t="s">
-        <v>1180</v>
-      </c>
       <c r="F10" t="s">
-        <v>1186</v>
+        <v>1191</v>
       </c>
       <c r="G10" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J10" t="s">
         <v>38</v>
@@ -17356,16 +17526,16 @@
         <v>39</v>
       </c>
       <c r="N10" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O10" t="s">
-        <v>1187</v>
+        <v>1192</v>
       </c>
       <c r="P10" t="s">
-        <v>1188</v>
+        <v>1193</v>
       </c>
       <c r="Q10" t="s">
-        <v>1189</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -17379,16 +17549,16 @@
         <v>5</v>
       </c>
       <c r="D11" t="s">
-        <v>1190</v>
+        <v>1195</v>
       </c>
       <c r="E11" t="s">
-        <v>1180</v>
+        <v>1185</v>
       </c>
       <c r="F11" t="s">
-        <v>1181</v>
+        <v>1186</v>
       </c>
       <c r="G11" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J11" t="s">
         <v>38</v>
@@ -17403,16 +17573,16 @@
         <v>39</v>
       </c>
       <c r="N11" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O11" t="s">
-        <v>1191</v>
+        <v>1196</v>
       </c>
       <c r="P11" t="s">
-        <v>1192</v>
+        <v>1197</v>
       </c>
       <c r="Q11" t="s">
-        <v>1193</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -17426,16 +17596,16 @@
         <v>5</v>
       </c>
       <c r="D12" t="s">
-        <v>1194</v>
+        <v>1199</v>
       </c>
       <c r="E12" t="s">
-        <v>1180</v>
+        <v>1185</v>
       </c>
       <c r="F12" t="s">
-        <v>1181</v>
+        <v>1186</v>
       </c>
       <c r="G12" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J12" t="s">
         <v>38</v>
@@ -17450,16 +17620,16 @@
         <v>39</v>
       </c>
       <c r="N12" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O12" t="s">
-        <v>1195</v>
+        <v>1200</v>
       </c>
       <c r="P12" t="s">
-        <v>1196</v>
+        <v>1201</v>
       </c>
       <c r="Q12" t="s">
-        <v>1197</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
@@ -17473,16 +17643,16 @@
         <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>1198</v>
+        <v>1203</v>
       </c>
       <c r="E13" t="s">
-        <v>1180</v>
+        <v>1185</v>
       </c>
       <c r="F13" t="s">
-        <v>1181</v>
+        <v>1186</v>
       </c>
       <c r="G13" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J13" t="s">
         <v>38</v>
@@ -17497,16 +17667,16 @@
         <v>39</v>
       </c>
       <c r="N13" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O13" t="s">
-        <v>1199</v>
+        <v>1204</v>
       </c>
       <c r="P13" t="s">
-        <v>1200</v>
+        <v>1205</v>
       </c>
       <c r="Q13" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
@@ -17520,16 +17690,16 @@
         <v>5</v>
       </c>
       <c r="D14" t="s">
-        <v>1202</v>
+        <v>1207</v>
       </c>
       <c r="E14" t="s">
-        <v>1180</v>
+        <v>1185</v>
       </c>
       <c r="F14" t="s">
-        <v>1181</v>
+        <v>1186</v>
       </c>
       <c r="G14" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J14" t="s">
         <v>38</v>
@@ -17544,16 +17714,16 @@
         <v>39</v>
       </c>
       <c r="N14" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O14" t="s">
-        <v>1203</v>
+        <v>1208</v>
       </c>
       <c r="P14" t="s">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="Q14" t="s">
-        <v>1205</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -17567,16 +17737,16 @@
         <v>40</v>
       </c>
       <c r="D15" t="s">
-        <v>1206</v>
+        <v>1211</v>
       </c>
       <c r="E15" t="s">
-        <v>1180</v>
+        <v>1185</v>
       </c>
       <c r="F15" t="s">
-        <v>1181</v>
+        <v>1186</v>
       </c>
       <c r="G15" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J15" t="s">
         <v>38</v>
@@ -17591,16 +17761,16 @@
         <v>39</v>
       </c>
       <c r="N15" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O15" t="s">
-        <v>1207</v>
+        <v>1212</v>
       </c>
       <c r="P15" t="s">
-        <v>1208</v>
+        <v>1213</v>
       </c>
       <c r="Q15" t="s">
-        <v>1209</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
@@ -17614,16 +17784,16 @@
         <v>45</v>
       </c>
       <c r="D16" t="s">
-        <v>1210</v>
+        <v>1215</v>
       </c>
       <c r="E16" t="s">
-        <v>1180</v>
+        <v>1185</v>
       </c>
       <c r="F16" t="s">
-        <v>1181</v>
+        <v>1186</v>
       </c>
       <c r="G16" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J16" t="s">
         <v>38</v>
@@ -17638,16 +17808,16 @@
         <v>39</v>
       </c>
       <c r="N16" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O16" t="s">
-        <v>1211</v>
+        <v>1216</v>
       </c>
       <c r="P16" t="s">
-        <v>1212</v>
+        <v>1217</v>
       </c>
       <c r="Q16" t="s">
-        <v>1213</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
@@ -17661,16 +17831,16 @@
         <v>3</v>
       </c>
       <c r="D17" t="s">
-        <v>1214</v>
+        <v>1219</v>
       </c>
       <c r="E17" t="s">
-        <v>1180</v>
+        <v>1185</v>
       </c>
       <c r="F17" t="s">
-        <v>1181</v>
+        <v>1186</v>
       </c>
       <c r="G17" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J17" t="s">
         <v>38</v>
@@ -17685,16 +17855,16 @@
         <v>39</v>
       </c>
       <c r="N17" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O17" t="s">
-        <v>1215</v>
+        <v>1220</v>
       </c>
       <c r="P17" t="s">
-        <v>1216</v>
+        <v>1221</v>
       </c>
       <c r="Q17" t="s">
-        <v>1217</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
@@ -17708,7 +17878,7 @@
         <v>42</v>
       </c>
       <c r="D18" t="s">
-        <v>1218</v>
+        <v>1223</v>
       </c>
       <c r="E18" t="s">
         <v>55</v>
@@ -17717,7 +17887,7 @@
         <v>20</v>
       </c>
       <c r="G18" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J18" t="s">
         <v>38</v>
@@ -17732,16 +17902,16 @@
         <v>39</v>
       </c>
       <c r="N18" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O18" t="s">
-        <v>1219</v>
+        <v>1224</v>
       </c>
       <c r="P18" t="s">
-        <v>1220</v>
+        <v>1225</v>
       </c>
       <c r="Q18" t="s">
-        <v>1221</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -17755,7 +17925,7 @@
         <v>40</v>
       </c>
       <c r="D19" t="s">
-        <v>1222</v>
+        <v>1227</v>
       </c>
       <c r="E19" t="s">
         <v>55</v>
@@ -17764,7 +17934,7 @@
         <v>20</v>
       </c>
       <c r="G19" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J19" t="s">
         <v>38</v>
@@ -17779,16 +17949,16 @@
         <v>39</v>
       </c>
       <c r="N19" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O19" t="s">
-        <v>1223</v>
+        <v>1228</v>
       </c>
       <c r="P19" t="s">
-        <v>1224</v>
+        <v>1229</v>
       </c>
       <c r="Q19" t="s">
-        <v>1225</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -17808,10 +17978,10 @@
         <v>55</v>
       </c>
       <c r="F20" t="s">
-        <v>1226</v>
+        <v>1231</v>
       </c>
       <c r="G20" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="H20">
         <v>180000</v>
@@ -17832,16 +18002,16 @@
         <v>25</v>
       </c>
       <c r="N20" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O20" t="s">
-        <v>1227</v>
+        <v>1232</v>
       </c>
       <c r="P20" t="s">
-        <v>1228</v>
+        <v>1233</v>
       </c>
       <c r="Q20" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
@@ -17855,7 +18025,7 @@
         <v>52</v>
       </c>
       <c r="D21" t="s">
-        <v>1230</v>
+        <v>1235</v>
       </c>
       <c r="E21" t="s">
         <v>55</v>
@@ -17864,7 +18034,7 @@
         <v>20</v>
       </c>
       <c r="G21" t="s">
-        <v>1160</v>
+        <v>1165</v>
       </c>
       <c r="H21">
         <v>180000</v>
@@ -17885,16 +18055,16 @@
         <v>25</v>
       </c>
       <c r="N21" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O21" t="s">
-        <v>1231</v>
+        <v>1236</v>
       </c>
       <c r="P21" t="s">
-        <v>1232</v>
+        <v>1237</v>
       </c>
       <c r="Q21" t="s">
-        <v>1233</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -17908,7 +18078,7 @@
         <v>55</v>
       </c>
       <c r="D22" t="s">
-        <v>1234</v>
+        <v>1239</v>
       </c>
       <c r="E22" t="s">
         <v>55</v>
@@ -17917,7 +18087,7 @@
         <v>20</v>
       </c>
       <c r="G22" t="s">
-        <v>1160</v>
+        <v>1165</v>
       </c>
       <c r="H22">
         <v>180000</v>
@@ -17938,16 +18108,16 @@
         <v>25</v>
       </c>
       <c r="N22" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O22" t="s">
-        <v>1235</v>
+        <v>1240</v>
       </c>
       <c r="P22" t="s">
-        <v>1236</v>
+        <v>1241</v>
       </c>
       <c r="Q22" t="s">
-        <v>1237</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
@@ -17961,16 +18131,16 @@
         <v>48</v>
       </c>
       <c r="D23" t="s">
-        <v>1238</v>
+        <v>1243</v>
       </c>
       <c r="E23" t="s">
         <v>55</v>
       </c>
       <c r="F23" t="s">
-        <v>1239</v>
+        <v>1244</v>
       </c>
       <c r="G23" t="s">
-        <v>1160</v>
+        <v>1165</v>
       </c>
       <c r="H23">
         <v>219100</v>
@@ -17991,16 +18161,16 @@
         <v>25</v>
       </c>
       <c r="N23" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O23" t="s">
-        <v>1240</v>
+        <v>1245</v>
       </c>
       <c r="P23" t="s">
-        <v>1241</v>
+        <v>1246</v>
       </c>
       <c r="Q23" t="s">
-        <v>1242</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
@@ -18014,16 +18184,16 @@
         <v>45</v>
       </c>
       <c r="D24" t="s">
-        <v>1243</v>
+        <v>1248</v>
       </c>
       <c r="E24" t="s">
         <v>55</v>
       </c>
       <c r="F24" t="s">
-        <v>1244</v>
+        <v>1249</v>
       </c>
       <c r="G24" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="H24">
         <v>180000</v>
@@ -18044,16 +18214,16 @@
         <v>25</v>
       </c>
       <c r="N24" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O24" t="s">
-        <v>1245</v>
+        <v>1250</v>
       </c>
       <c r="P24" t="s">
-        <v>1246</v>
+        <v>1251</v>
       </c>
       <c r="Q24" t="s">
-        <v>1247</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
@@ -18067,7 +18237,7 @@
         <v>30</v>
       </c>
       <c r="D25" t="s">
-        <v>1248</v>
+        <v>1253</v>
       </c>
       <c r="E25" t="s">
         <v>55</v>
@@ -18076,7 +18246,7 @@
         <v>20</v>
       </c>
       <c r="G25" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="H25">
         <v>219100</v>
@@ -18097,16 +18267,16 @@
         <v>39</v>
       </c>
       <c r="N25" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O25" t="s">
-        <v>1249</v>
+        <v>1254</v>
       </c>
       <c r="P25" t="s">
-        <v>1250</v>
+        <v>1255</v>
       </c>
       <c r="Q25" t="s">
-        <v>1251</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
@@ -18120,7 +18290,7 @@
         <v>45</v>
       </c>
       <c r="D26" t="s">
-        <v>1252</v>
+        <v>1257</v>
       </c>
       <c r="E26" t="s">
         <v>55</v>
@@ -18129,7 +18299,7 @@
         <v>20</v>
       </c>
       <c r="G26" t="s">
-        <v>1160</v>
+        <v>1165</v>
       </c>
       <c r="H26">
         <v>219100</v>
@@ -18150,16 +18320,16 @@
         <v>25</v>
       </c>
       <c r="N26" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O26" t="s">
-        <v>1253</v>
+        <v>1258</v>
       </c>
       <c r="P26" t="s">
-        <v>1254</v>
+        <v>1259</v>
       </c>
       <c r="Q26" t="s">
-        <v>1255</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
@@ -18173,16 +18343,16 @@
         <v>30</v>
       </c>
       <c r="D27" t="s">
-        <v>1256</v>
+        <v>1261</v>
       </c>
       <c r="E27" t="s">
         <v>55</v>
       </c>
       <c r="F27" t="s">
-        <v>1257</v>
+        <v>1262</v>
       </c>
       <c r="G27" t="s">
-        <v>1160</v>
+        <v>1165</v>
       </c>
       <c r="J27" t="s">
         <v>38</v>
@@ -18197,16 +18367,16 @@
         <v>39</v>
       </c>
       <c r="N27" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O27" t="s">
-        <v>1258</v>
+        <v>1263</v>
       </c>
       <c r="P27" t="s">
-        <v>1259</v>
+        <v>1264</v>
       </c>
       <c r="Q27" t="s">
-        <v>1260</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
@@ -18220,16 +18390,16 @@
         <v>58</v>
       </c>
       <c r="D28" t="s">
-        <v>1261</v>
+        <v>1266</v>
       </c>
       <c r="E28" t="s">
-        <v>1262</v>
+        <v>1267</v>
       </c>
       <c r="F28" t="s">
-        <v>1263</v>
+        <v>1268</v>
       </c>
       <c r="G28" t="s">
-        <v>1160</v>
+        <v>1165</v>
       </c>
       <c r="H28">
         <v>257000</v>
@@ -18250,16 +18420,16 @@
         <v>25</v>
       </c>
       <c r="N28" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O28" t="s">
-        <v>1264</v>
+        <v>1269</v>
       </c>
       <c r="P28" t="s">
-        <v>1265</v>
+        <v>1270</v>
       </c>
       <c r="Q28" t="s">
-        <v>1266</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
@@ -18276,13 +18446,13 @@
         <v>311</v>
       </c>
       <c r="E29" t="s">
-        <v>1267</v>
+        <v>1272</v>
       </c>
       <c r="F29" t="s">
-        <v>1268</v>
+        <v>1273</v>
       </c>
       <c r="G29" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="H29">
         <v>200000</v>
@@ -18303,16 +18473,16 @@
         <v>39</v>
       </c>
       <c r="N29" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O29" t="s">
-        <v>1269</v>
+        <v>1274</v>
       </c>
       <c r="P29" t="s">
-        <v>1270</v>
+        <v>1275</v>
       </c>
       <c r="Q29" t="s">
-        <v>1271</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
@@ -18326,16 +18496,16 @@
         <v>20</v>
       </c>
       <c r="D30" t="s">
-        <v>1272</v>
+        <v>1277</v>
       </c>
       <c r="E30" t="s">
         <v>846</v>
       </c>
       <c r="F30" t="s">
-        <v>1273</v>
+        <v>1278</v>
       </c>
       <c r="G30" t="s">
-        <v>1160</v>
+        <v>1165</v>
       </c>
       <c r="J30" t="s">
         <v>38</v>
@@ -18350,16 +18520,16 @@
         <v>39</v>
       </c>
       <c r="N30" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O30" t="s">
-        <v>1274</v>
+        <v>1279</v>
       </c>
       <c r="P30" t="s">
-        <v>1275</v>
+        <v>1280</v>
       </c>
       <c r="Q30" t="s">
-        <v>1276</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
@@ -18379,10 +18549,10 @@
         <v>846</v>
       </c>
       <c r="F31" t="s">
-        <v>1277</v>
+        <v>1282</v>
       </c>
       <c r="G31" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J31" t="s">
         <v>38</v>
@@ -18397,16 +18567,16 @@
         <v>39</v>
       </c>
       <c r="N31" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O31" t="s">
-        <v>1278</v>
+        <v>1283</v>
       </c>
       <c r="P31" t="s">
-        <v>1279</v>
+        <v>1284</v>
       </c>
       <c r="Q31" t="s">
-        <v>1280</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
@@ -18420,16 +18590,16 @@
         <v>15</v>
       </c>
       <c r="D32" t="s">
-        <v>1281</v>
+        <v>1286</v>
       </c>
       <c r="E32" t="s">
         <v>846</v>
       </c>
       <c r="F32" t="s">
-        <v>1282</v>
+        <v>1287</v>
       </c>
       <c r="G32" t="s">
-        <v>1160</v>
+        <v>1165</v>
       </c>
       <c r="H32">
         <v>500000</v>
@@ -18450,16 +18620,16 @@
         <v>39</v>
       </c>
       <c r="N32" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O32" t="s">
-        <v>1283</v>
+        <v>1288</v>
       </c>
       <c r="P32" t="s">
-        <v>1284</v>
+        <v>1289</v>
       </c>
       <c r="Q32" t="s">
-        <v>1285</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
@@ -18473,16 +18643,16 @@
         <v>18</v>
       </c>
       <c r="D33" t="s">
-        <v>1286</v>
+        <v>1291</v>
       </c>
       <c r="E33" t="s">
         <v>633</v>
       </c>
       <c r="F33" t="s">
-        <v>1287</v>
+        <v>1292</v>
       </c>
       <c r="G33" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="H33">
         <v>274456</v>
@@ -18503,16 +18673,16 @@
         <v>39</v>
       </c>
       <c r="N33" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O33" t="s">
-        <v>1288</v>
+        <v>1293</v>
       </c>
       <c r="P33" t="s">
-        <v>1289</v>
+        <v>1294</v>
       </c>
       <c r="Q33" t="s">
-        <v>1290</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
@@ -18526,16 +18696,16 @@
         <v>30</v>
       </c>
       <c r="D34" t="s">
-        <v>1291</v>
+        <v>1296</v>
       </c>
       <c r="E34" t="s">
         <v>633</v>
       </c>
       <c r="F34" t="s">
-        <v>1292</v>
+        <v>1297</v>
       </c>
       <c r="G34" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J34" t="s">
         <v>38</v>
@@ -18550,16 +18720,16 @@
         <v>39</v>
       </c>
       <c r="N34" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O34" t="s">
-        <v>1293</v>
+        <v>1298</v>
       </c>
       <c r="P34" t="s">
-        <v>1294</v>
+        <v>1299</v>
       </c>
       <c r="Q34" t="s">
-        <v>1295</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
@@ -18573,16 +18743,16 @@
         <v>22</v>
       </c>
       <c r="D35" t="s">
-        <v>1296</v>
+        <v>1301</v>
       </c>
       <c r="E35" t="s">
         <v>633</v>
       </c>
       <c r="F35" t="s">
-        <v>1297</v>
+        <v>1302</v>
       </c>
       <c r="G35" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J35" t="s">
         <v>38</v>
@@ -18597,16 +18767,16 @@
         <v>39</v>
       </c>
       <c r="N35" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O35" t="s">
-        <v>1298</v>
+        <v>1303</v>
       </c>
       <c r="P35" t="s">
-        <v>1299</v>
+        <v>1304</v>
       </c>
       <c r="Q35" t="s">
-        <v>1300</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
@@ -18620,16 +18790,16 @@
         <v>48</v>
       </c>
       <c r="D36" t="s">
-        <v>1301</v>
+        <v>1306</v>
       </c>
       <c r="E36" t="s">
         <v>633</v>
       </c>
       <c r="F36" t="s">
-        <v>1302</v>
+        <v>1307</v>
       </c>
       <c r="G36" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J36" t="s">
         <v>38</v>
@@ -18644,16 +18814,16 @@
         <v>25</v>
       </c>
       <c r="N36" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O36" t="s">
-        <v>1303</v>
+        <v>1308</v>
       </c>
       <c r="P36" t="s">
-        <v>1304</v>
+        <v>1309</v>
       </c>
       <c r="Q36" t="s">
-        <v>1305</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
@@ -18667,16 +18837,16 @@
         <v>25</v>
       </c>
       <c r="D37" t="s">
-        <v>1306</v>
+        <v>1311</v>
       </c>
       <c r="E37" t="s">
         <v>633</v>
       </c>
       <c r="F37" t="s">
-        <v>1186</v>
+        <v>1191</v>
       </c>
       <c r="G37" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J37" t="s">
         <v>38</v>
@@ -18691,16 +18861,16 @@
         <v>39</v>
       </c>
       <c r="N37" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O37" t="s">
-        <v>1307</v>
+        <v>1312</v>
       </c>
       <c r="P37" t="s">
-        <v>1308</v>
+        <v>1313</v>
       </c>
       <c r="Q37" t="s">
-        <v>1309</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
@@ -18714,16 +18884,16 @@
         <v>40</v>
       </c>
       <c r="D38" t="s">
-        <v>1310</v>
+        <v>1315</v>
       </c>
       <c r="E38" t="s">
         <v>633</v>
       </c>
       <c r="F38" t="s">
-        <v>1311</v>
+        <v>1316</v>
       </c>
       <c r="G38" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J38" t="s">
         <v>38</v>
@@ -18738,16 +18908,16 @@
         <v>39</v>
       </c>
       <c r="N38" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O38" t="s">
-        <v>1312</v>
+        <v>1317</v>
       </c>
       <c r="P38" t="s">
-        <v>1313</v>
+        <v>1318</v>
       </c>
       <c r="Q38" t="s">
-        <v>1314</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
@@ -18761,16 +18931,16 @@
         <v>70</v>
       </c>
       <c r="D39" t="s">
-        <v>1315</v>
+        <v>1320</v>
       </c>
       <c r="E39" t="s">
-        <v>1316</v>
+        <v>1321</v>
       </c>
       <c r="F39" t="s">
-        <v>1317</v>
+        <v>1322</v>
       </c>
       <c r="G39" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J39" t="s">
         <v>38</v>
@@ -18785,16 +18955,16 @@
         <v>39</v>
       </c>
       <c r="N39" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O39" t="s">
-        <v>1318</v>
+        <v>1323</v>
       </c>
       <c r="P39" t="s">
-        <v>1319</v>
+        <v>1324</v>
       </c>
       <c r="Q39" t="s">
-        <v>1320</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
@@ -18808,16 +18978,16 @@
         <v>58</v>
       </c>
       <c r="D40" t="s">
-        <v>1321</v>
+        <v>1326</v>
       </c>
       <c r="E40" t="s">
-        <v>1322</v>
+        <v>1327</v>
       </c>
       <c r="F40" t="s">
-        <v>1186</v>
+        <v>1191</v>
       </c>
       <c r="G40" t="s">
-        <v>1160</v>
+        <v>1165</v>
       </c>
       <c r="J40" t="s">
         <v>38</v>
@@ -18832,16 +19002,16 @@
         <v>39</v>
       </c>
       <c r="N40" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O40" t="s">
-        <v>1323</v>
+        <v>1328</v>
       </c>
       <c r="P40" t="s">
-        <v>1324</v>
+        <v>1329</v>
       </c>
       <c r="Q40" t="s">
-        <v>1325</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
@@ -18855,16 +19025,16 @@
         <v>32</v>
       </c>
       <c r="D41" t="s">
-        <v>1326</v>
+        <v>1331</v>
       </c>
       <c r="E41" t="s">
-        <v>1327</v>
+        <v>1332</v>
       </c>
       <c r="F41" t="s">
-        <v>1328</v>
+        <v>1333</v>
       </c>
       <c r="G41" t="s">
-        <v>1160</v>
+        <v>1165</v>
       </c>
       <c r="J41" t="s">
         <v>38</v>
@@ -18879,16 +19049,16 @@
         <v>39</v>
       </c>
       <c r="N41" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O41" t="s">
-        <v>1329</v>
+        <v>1334</v>
       </c>
       <c r="P41" t="s">
-        <v>1330</v>
+        <v>1335</v>
       </c>
       <c r="Q41" t="s">
-        <v>1331</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
@@ -18902,16 +19072,16 @@
         <v>4</v>
       </c>
       <c r="D42" t="s">
-        <v>1332</v>
+        <v>1337</v>
       </c>
       <c r="E42" t="s">
-        <v>1333</v>
+        <v>1338</v>
       </c>
       <c r="F42" t="s">
-        <v>1334</v>
+        <v>1339</v>
       </c>
       <c r="G42" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J42" t="s">
         <v>38</v>
@@ -18926,16 +19096,16 @@
         <v>39</v>
       </c>
       <c r="N42" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O42" t="s">
-        <v>1335</v>
+        <v>1340</v>
       </c>
       <c r="P42" t="s">
-        <v>1336</v>
+        <v>1341</v>
       </c>
       <c r="Q42" t="s">
-        <v>1337</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
@@ -18949,16 +19119,16 @@
         <v>25</v>
       </c>
       <c r="D43" t="s">
-        <v>1338</v>
+        <v>1343</v>
       </c>
       <c r="E43" t="s">
-        <v>1339</v>
+        <v>1344</v>
       </c>
       <c r="F43" t="s">
-        <v>1171</v>
+        <v>1176</v>
       </c>
       <c r="G43" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J43" t="s">
         <v>38</v>
@@ -18973,16 +19143,16 @@
         <v>39</v>
       </c>
       <c r="N43" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O43" t="s">
-        <v>1340</v>
+        <v>1345</v>
       </c>
       <c r="P43" t="s">
-        <v>1341</v>
+        <v>1346</v>
       </c>
       <c r="Q43" t="s">
-        <v>1342</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
@@ -18996,16 +19166,16 @@
         <v>30</v>
       </c>
       <c r="D44" t="s">
-        <v>1343</v>
+        <v>1348</v>
       </c>
       <c r="E44" t="s">
-        <v>1344</v>
+        <v>1349</v>
       </c>
       <c r="F44" t="s">
-        <v>1345</v>
+        <v>1350</v>
       </c>
       <c r="G44" t="s">
-        <v>1160</v>
+        <v>1165</v>
       </c>
       <c r="J44" t="s">
         <v>38</v>
@@ -19020,16 +19190,16 @@
         <v>39</v>
       </c>
       <c r="N44" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O44" t="s">
-        <v>1346</v>
+        <v>1351</v>
       </c>
       <c r="P44" t="s">
-        <v>1347</v>
+        <v>1352</v>
       </c>
       <c r="Q44" t="s">
-        <v>1348</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
@@ -19043,16 +19213,16 @@
         <v>52</v>
       </c>
       <c r="D45" t="s">
-        <v>1349</v>
+        <v>1354</v>
       </c>
       <c r="E45" t="s">
         <v>55</v>
       </c>
       <c r="F45" t="s">
-        <v>1350</v>
+        <v>1355</v>
       </c>
       <c r="G45" t="s">
-        <v>1160</v>
+        <v>1165</v>
       </c>
       <c r="H45">
         <v>180000</v>
@@ -19073,16 +19243,16 @@
         <v>25</v>
       </c>
       <c r="N45" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O45" t="s">
-        <v>1351</v>
+        <v>1356</v>
       </c>
       <c r="P45" t="s">
-        <v>1352</v>
+        <v>1357</v>
       </c>
       <c r="Q45" t="s">
-        <v>1353</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
@@ -19096,7 +19266,7 @@
         <v>50</v>
       </c>
       <c r="D46" t="s">
-        <v>1354</v>
+        <v>1359</v>
       </c>
       <c r="E46" t="s">
         <v>55</v>
@@ -19105,7 +19275,7 @@
         <v>20</v>
       </c>
       <c r="G46" t="s">
-        <v>1160</v>
+        <v>1165</v>
       </c>
       <c r="H46">
         <v>180000</v>
@@ -19126,16 +19296,16 @@
         <v>25</v>
       </c>
       <c r="N46" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O46" t="s">
-        <v>1355</v>
+        <v>1360</v>
       </c>
       <c r="P46" t="s">
-        <v>1356</v>
+        <v>1361</v>
       </c>
       <c r="Q46" t="s">
-        <v>1357</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
@@ -19149,7 +19319,7 @@
         <v>46</v>
       </c>
       <c r="D47" t="s">
-        <v>1358</v>
+        <v>1363</v>
       </c>
       <c r="E47" t="s">
         <v>55</v>
@@ -19158,7 +19328,7 @@
         <v>20</v>
       </c>
       <c r="G47" t="s">
-        <v>1160</v>
+        <v>1165</v>
       </c>
       <c r="H47">
         <v>180000</v>
@@ -19179,16 +19349,16 @@
         <v>25</v>
       </c>
       <c r="N47" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O47" t="s">
-        <v>1359</v>
+        <v>1364</v>
       </c>
       <c r="P47" t="s">
-        <v>1360</v>
+        <v>1365</v>
       </c>
       <c r="Q47" t="s">
-        <v>1361</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
@@ -19202,7 +19372,7 @@
         <v>38</v>
       </c>
       <c r="D48" t="s">
-        <v>1362</v>
+        <v>1367</v>
       </c>
       <c r="E48" t="s">
         <v>55</v>
@@ -19211,7 +19381,7 @@
         <v>20</v>
       </c>
       <c r="G48" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="H48">
         <v>217800</v>
@@ -19232,16 +19402,16 @@
         <v>39</v>
       </c>
       <c r="N48" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O48" t="s">
-        <v>1363</v>
+        <v>1368</v>
       </c>
       <c r="P48" t="s">
-        <v>1364</v>
+        <v>1369</v>
       </c>
       <c r="Q48" t="s">
-        <v>1365</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
@@ -19261,10 +19431,10 @@
         <v>55</v>
       </c>
       <c r="F49" t="s">
-        <v>1366</v>
+        <v>1371</v>
       </c>
       <c r="G49" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="H49">
         <v>180000</v>
@@ -19285,16 +19455,16 @@
         <v>25</v>
       </c>
       <c r="N49" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O49" t="s">
-        <v>1367</v>
+        <v>1372</v>
       </c>
       <c r="P49" t="s">
-        <v>1368</v>
+        <v>1373</v>
       </c>
       <c r="Q49" t="s">
-        <v>1369</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
@@ -19308,16 +19478,16 @@
         <v>45</v>
       </c>
       <c r="D50" t="s">
-        <v>1370</v>
+        <v>1375</v>
       </c>
       <c r="E50" t="s">
         <v>55</v>
       </c>
       <c r="F50" t="s">
-        <v>1371</v>
+        <v>1376</v>
       </c>
       <c r="G50" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="H50">
         <v>219100</v>
@@ -19338,16 +19508,16 @@
         <v>25</v>
       </c>
       <c r="N50" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O50" t="s">
-        <v>1372</v>
+        <v>1377</v>
       </c>
       <c r="P50" t="s">
-        <v>1373</v>
+        <v>1378</v>
       </c>
       <c r="Q50" t="s">
-        <v>1374</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
@@ -19361,16 +19531,16 @@
         <v>42</v>
       </c>
       <c r="D51" t="s">
-        <v>1375</v>
+        <v>1380</v>
       </c>
       <c r="E51" t="s">
         <v>55</v>
       </c>
       <c r="F51" t="s">
-        <v>1376</v>
+        <v>1381</v>
       </c>
       <c r="G51" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="H51">
         <v>180000</v>
@@ -19391,16 +19561,16 @@
         <v>25</v>
       </c>
       <c r="N51" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O51" t="s">
-        <v>1377</v>
+        <v>1382</v>
       </c>
       <c r="P51" t="s">
-        <v>1378</v>
+        <v>1383</v>
       </c>
       <c r="Q51" t="s">
-        <v>1379</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
@@ -19414,7 +19584,7 @@
         <v>32</v>
       </c>
       <c r="D52" t="s">
-        <v>1380</v>
+        <v>1385</v>
       </c>
       <c r="E52" t="s">
         <v>55</v>
@@ -19423,7 +19593,7 @@
         <v>20</v>
       </c>
       <c r="G52" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="H52">
         <v>219100</v>
@@ -19444,16 +19614,16 @@
         <v>39</v>
       </c>
       <c r="N52" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O52" t="s">
-        <v>1381</v>
+        <v>1386</v>
       </c>
       <c r="P52" t="s">
-        <v>1382</v>
+        <v>1387</v>
       </c>
       <c r="Q52" t="s">
-        <v>1383</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
@@ -19467,7 +19637,7 @@
         <v>35</v>
       </c>
       <c r="D53" t="s">
-        <v>1384</v>
+        <v>1389</v>
       </c>
       <c r="E53" t="s">
         <v>55</v>
@@ -19476,7 +19646,7 @@
         <v>20</v>
       </c>
       <c r="G53" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="H53">
         <v>219100</v>
@@ -19497,16 +19667,16 @@
         <v>39</v>
       </c>
       <c r="N53" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O53" t="s">
-        <v>1385</v>
+        <v>1390</v>
       </c>
       <c r="P53" t="s">
-        <v>1386</v>
+        <v>1391</v>
       </c>
       <c r="Q53" t="s">
-        <v>1387</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
@@ -19520,16 +19690,16 @@
         <v>40</v>
       </c>
       <c r="D54" t="s">
-        <v>1388</v>
+        <v>1393</v>
       </c>
       <c r="E54" t="s">
         <v>55</v>
       </c>
       <c r="F54" t="s">
-        <v>1389</v>
+        <v>1394</v>
       </c>
       <c r="G54" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="H54">
         <v>219100</v>
@@ -19550,16 +19720,16 @@
         <v>25</v>
       </c>
       <c r="N54" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O54" t="s">
-        <v>1390</v>
+        <v>1395</v>
       </c>
       <c r="P54" t="s">
-        <v>1391</v>
+        <v>1396</v>
       </c>
       <c r="Q54" t="s">
-        <v>1392</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
@@ -19573,7 +19743,7 @@
         <v>38</v>
       </c>
       <c r="D55" t="s">
-        <v>1393</v>
+        <v>1398</v>
       </c>
       <c r="E55" t="s">
         <v>55</v>
@@ -19582,7 +19752,7 @@
         <v>592</v>
       </c>
       <c r="G55" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="H55">
         <v>219100</v>
@@ -19603,16 +19773,16 @@
         <v>39</v>
       </c>
       <c r="N55" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O55" t="s">
-        <v>1394</v>
+        <v>1399</v>
       </c>
       <c r="P55" t="s">
-        <v>1395</v>
+        <v>1400</v>
       </c>
       <c r="Q55" t="s">
-        <v>1396</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
@@ -19626,7 +19796,7 @@
         <v>40</v>
       </c>
       <c r="D56" t="s">
-        <v>1397</v>
+        <v>1402</v>
       </c>
       <c r="E56" t="s">
         <v>55</v>
@@ -19635,7 +19805,7 @@
         <v>20</v>
       </c>
       <c r="G56" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="H56">
         <v>219100</v>
@@ -19656,16 +19826,16 @@
         <v>25</v>
       </c>
       <c r="N56" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O56" t="s">
-        <v>1398</v>
+        <v>1403</v>
       </c>
       <c r="P56" t="s">
-        <v>1399</v>
+        <v>1404</v>
       </c>
       <c r="Q56" t="s">
-        <v>1400</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
@@ -19679,16 +19849,16 @@
         <v>33</v>
       </c>
       <c r="D57" t="s">
-        <v>1401</v>
+        <v>1406</v>
       </c>
       <c r="E57" t="s">
         <v>55</v>
       </c>
       <c r="F57" t="s">
-        <v>1402</v>
+        <v>1407</v>
       </c>
       <c r="G57" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="H57">
         <v>219100</v>
@@ -19709,16 +19879,16 @@
         <v>39</v>
       </c>
       <c r="N57" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O57" t="s">
-        <v>1403</v>
+        <v>1408</v>
       </c>
       <c r="P57" t="s">
-        <v>1404</v>
+        <v>1409</v>
       </c>
       <c r="Q57" t="s">
-        <v>1405</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
@@ -19732,16 +19902,16 @@
         <v>48</v>
       </c>
       <c r="D58" t="s">
-        <v>1406</v>
+        <v>1411</v>
       </c>
       <c r="E58" t="s">
-        <v>1262</v>
+        <v>1267</v>
       </c>
       <c r="F58" t="s">
-        <v>1407</v>
+        <v>1412</v>
       </c>
       <c r="G58" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J58" t="s">
         <v>38</v>
@@ -19756,16 +19926,16 @@
         <v>25</v>
       </c>
       <c r="N58" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O58" t="s">
-        <v>1408</v>
+        <v>1413</v>
       </c>
       <c r="P58" t="s">
-        <v>1409</v>
+        <v>1414</v>
       </c>
       <c r="Q58" t="s">
-        <v>1410</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
@@ -19779,16 +19949,16 @@
         <v>40</v>
       </c>
       <c r="D59" t="s">
-        <v>1411</v>
+        <v>1416</v>
       </c>
       <c r="E59" t="s">
-        <v>1267</v>
+        <v>1272</v>
       </c>
       <c r="F59" t="s">
-        <v>1412</v>
+        <v>1417</v>
       </c>
       <c r="G59" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="H59">
         <v>184200</v>
@@ -19809,16 +19979,16 @@
         <v>25</v>
       </c>
       <c r="N59" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O59" t="s">
-        <v>1413</v>
+        <v>1418</v>
       </c>
       <c r="P59" t="s">
-        <v>1414</v>
+        <v>1419</v>
       </c>
       <c r="Q59" t="s">
-        <v>1415</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
@@ -19832,16 +20002,16 @@
         <v>30</v>
       </c>
       <c r="D60" t="s">
-        <v>1416</v>
+        <v>1421</v>
       </c>
       <c r="E60" t="s">
-        <v>1267</v>
+        <v>1272</v>
       </c>
       <c r="F60" t="s">
-        <v>1417</v>
+        <v>1422</v>
       </c>
       <c r="G60" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="H60">
         <v>200000</v>
@@ -19862,16 +20032,16 @@
         <v>39</v>
       </c>
       <c r="N60" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O60" t="s">
-        <v>1418</v>
+        <v>1423</v>
       </c>
       <c r="P60" t="s">
-        <v>1419</v>
+        <v>1424</v>
       </c>
       <c r="Q60" t="s">
-        <v>1420</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
@@ -19885,7 +20055,7 @@
         <v>30</v>
       </c>
       <c r="D61" t="s">
-        <v>1421</v>
+        <v>1426</v>
       </c>
       <c r="E61" t="s">
         <v>846</v>
@@ -19894,7 +20064,7 @@
         <v>855</v>
       </c>
       <c r="G61" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J61" t="s">
         <v>38</v>
@@ -19909,16 +20079,16 @@
         <v>39</v>
       </c>
       <c r="N61" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O61" t="s">
-        <v>1422</v>
+        <v>1427</v>
       </c>
       <c r="P61" t="s">
-        <v>1423</v>
+        <v>1428</v>
       </c>
       <c r="Q61" t="s">
-        <v>1424</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
@@ -19938,10 +20108,10 @@
         <v>846</v>
       </c>
       <c r="F62" t="s">
-        <v>1277</v>
+        <v>1282</v>
       </c>
       <c r="G62" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J62" t="s">
         <v>38</v>
@@ -19956,16 +20126,16 @@
         <v>39</v>
       </c>
       <c r="N62" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O62" t="s">
-        <v>1425</v>
+        <v>1430</v>
       </c>
       <c r="P62" t="s">
-        <v>1426</v>
+        <v>1431</v>
       </c>
       <c r="Q62" t="s">
-        <v>1427</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
@@ -19979,7 +20149,7 @@
         <v>32</v>
       </c>
       <c r="D63" t="s">
-        <v>1428</v>
+        <v>1433</v>
       </c>
       <c r="E63" t="s">
         <v>846</v>
@@ -19988,7 +20158,7 @@
         <v>855</v>
       </c>
       <c r="G63" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J63" t="s">
         <v>38</v>
@@ -20003,16 +20173,16 @@
         <v>39</v>
       </c>
       <c r="N63" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O63" t="s">
-        <v>1429</v>
+        <v>1434</v>
       </c>
       <c r="P63" t="s">
-        <v>1430</v>
+        <v>1435</v>
       </c>
       <c r="Q63" t="s">
-        <v>1431</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
@@ -20026,16 +20196,16 @@
         <v>45</v>
       </c>
       <c r="D64" t="s">
-        <v>1432</v>
+        <v>1437</v>
       </c>
       <c r="E64" t="s">
         <v>633</v>
       </c>
       <c r="F64" t="s">
-        <v>1433</v>
+        <v>1438</v>
       </c>
       <c r="G64" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J64" t="s">
         <v>38</v>
@@ -20050,16 +20220,16 @@
         <v>25</v>
       </c>
       <c r="N64" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O64" t="s">
-        <v>1434</v>
+        <v>1439</v>
       </c>
       <c r="P64" t="s">
-        <v>1435</v>
+        <v>1440</v>
       </c>
       <c r="Q64" t="s">
-        <v>1436</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
@@ -20073,16 +20243,16 @@
         <v>35</v>
       </c>
       <c r="D65" t="s">
-        <v>1437</v>
+        <v>1442</v>
       </c>
       <c r="E65" t="s">
         <v>633</v>
       </c>
       <c r="F65" t="s">
-        <v>1438</v>
+        <v>1443</v>
       </c>
       <c r="G65" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J65" t="s">
         <v>38</v>
@@ -20097,16 +20267,16 @@
         <v>39</v>
       </c>
       <c r="N65" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O65" t="s">
-        <v>1439</v>
+        <v>1444</v>
       </c>
       <c r="P65" t="s">
-        <v>1440</v>
+        <v>1445</v>
       </c>
       <c r="Q65" t="s">
-        <v>1441</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
@@ -20120,7 +20290,7 @@
         <v>35</v>
       </c>
       <c r="D66" t="s">
-        <v>1442</v>
+        <v>1447</v>
       </c>
       <c r="E66" t="s">
         <v>633</v>
@@ -20129,7 +20299,7 @@
         <v>118</v>
       </c>
       <c r="G66" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J66" t="s">
         <v>38</v>
@@ -20144,16 +20314,16 @@
         <v>39</v>
       </c>
       <c r="N66" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O66" t="s">
-        <v>1443</v>
+        <v>1448</v>
       </c>
       <c r="P66" t="s">
-        <v>1444</v>
+        <v>1449</v>
       </c>
       <c r="Q66" t="s">
-        <v>1445</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
@@ -20167,16 +20337,16 @@
         <v>15</v>
       </c>
       <c r="D67" t="s">
-        <v>1446</v>
+        <v>1451</v>
       </c>
       <c r="E67" t="s">
         <v>633</v>
       </c>
       <c r="F67" t="s">
-        <v>1447</v>
+        <v>1452</v>
       </c>
       <c r="G67" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J67" t="s">
         <v>38</v>
@@ -20191,16 +20361,16 @@
         <v>39</v>
       </c>
       <c r="N67" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O67" t="s">
-        <v>1448</v>
+        <v>1453</v>
       </c>
       <c r="P67" t="s">
-        <v>1449</v>
+        <v>1454</v>
       </c>
       <c r="Q67" t="s">
-        <v>1450</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
@@ -20214,16 +20384,16 @@
         <v>25</v>
       </c>
       <c r="D68" t="s">
-        <v>1451</v>
+        <v>1456</v>
       </c>
       <c r="E68" t="s">
         <v>633</v>
       </c>
       <c r="F68" t="s">
-        <v>1452</v>
+        <v>1457</v>
       </c>
       <c r="G68" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J68" t="s">
         <v>38</v>
@@ -20238,16 +20408,16 @@
         <v>39</v>
       </c>
       <c r="N68" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O68" t="s">
-        <v>1453</v>
+        <v>1458</v>
       </c>
       <c r="P68" t="s">
-        <v>1454</v>
+        <v>1459</v>
       </c>
       <c r="Q68" t="s">
-        <v>1455</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
@@ -20261,16 +20431,16 @@
         <v>30</v>
       </c>
       <c r="D69" t="s">
-        <v>1456</v>
+        <v>1461</v>
       </c>
       <c r="E69" t="s">
         <v>633</v>
       </c>
       <c r="F69" t="s">
-        <v>1457</v>
+        <v>1462</v>
       </c>
       <c r="G69" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J69" t="s">
         <v>38</v>
@@ -20285,16 +20455,16 @@
         <v>39</v>
       </c>
       <c r="N69" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O69" t="s">
-        <v>1458</v>
+        <v>1463</v>
       </c>
       <c r="P69" t="s">
-        <v>1459</v>
+        <v>1464</v>
       </c>
       <c r="Q69" t="s">
-        <v>1460</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
@@ -20314,10 +20484,10 @@
         <v>55</v>
       </c>
       <c r="F70" t="s">
-        <v>1417</v>
+        <v>1422</v>
       </c>
       <c r="G70" t="s">
-        <v>1160</v>
+        <v>1165</v>
       </c>
       <c r="J70" t="s">
         <v>38</v>
@@ -20332,16 +20502,16 @@
         <v>39</v>
       </c>
       <c r="N70" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O70" t="s">
-        <v>1461</v>
+        <v>1466</v>
       </c>
       <c r="P70" t="s">
-        <v>1462</v>
+        <v>1467</v>
       </c>
       <c r="Q70" t="s">
-        <v>1463</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
@@ -20361,10 +20531,10 @@
         <v>55</v>
       </c>
       <c r="F71" t="s">
-        <v>1464</v>
+        <v>1469</v>
       </c>
       <c r="G71" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J71" t="s">
         <v>38</v>
@@ -20379,16 +20549,16 @@
         <v>25</v>
       </c>
       <c r="N71" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O71" t="s">
-        <v>1465</v>
+        <v>1470</v>
       </c>
       <c r="P71" t="s">
-        <v>1466</v>
+        <v>1471</v>
       </c>
       <c r="Q71" t="s">
-        <v>1467</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
@@ -20411,7 +20581,7 @@
         <v>912</v>
       </c>
       <c r="G72" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="H72">
         <v>180000</v>
@@ -20432,16 +20602,16 @@
         <v>39</v>
       </c>
       <c r="N72" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O72" t="s">
-        <v>1468</v>
+        <v>1473</v>
       </c>
       <c r="P72" t="s">
-        <v>1469</v>
+        <v>1474</v>
       </c>
       <c r="Q72" t="s">
-        <v>1470</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
@@ -20461,10 +20631,10 @@
         <v>55</v>
       </c>
       <c r="F73" t="s">
-        <v>1471</v>
+        <v>1476</v>
       </c>
       <c r="G73" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="H73">
         <v>180000</v>
@@ -20485,16 +20655,16 @@
         <v>39</v>
       </c>
       <c r="N73" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O73" t="s">
-        <v>1472</v>
+        <v>1477</v>
       </c>
       <c r="P73" t="s">
-        <v>1473</v>
+        <v>1478</v>
       </c>
       <c r="Q73" t="s">
-        <v>1474</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
@@ -20508,16 +20678,16 @@
         <v>20</v>
       </c>
       <c r="D74" t="s">
-        <v>1475</v>
+        <v>1480</v>
       </c>
       <c r="E74" t="s">
         <v>957</v>
       </c>
       <c r="F74" t="s">
-        <v>1476</v>
+        <v>1481</v>
       </c>
       <c r="G74" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J74" t="s">
         <v>38</v>
@@ -20532,16 +20702,16 @@
         <v>39</v>
       </c>
       <c r="N74" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O74" t="s">
-        <v>1477</v>
+        <v>1482</v>
       </c>
       <c r="P74" t="s">
-        <v>1478</v>
+        <v>1483</v>
       </c>
       <c r="Q74" t="s">
-        <v>1479</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
@@ -20555,7 +20725,7 @@
         <v>50</v>
       </c>
       <c r="D75" t="s">
-        <v>1480</v>
+        <v>1485</v>
       </c>
       <c r="E75" t="s">
         <v>957</v>
@@ -20564,7 +20734,7 @@
         <v>20</v>
       </c>
       <c r="G75" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="H75">
         <v>250000</v>
@@ -20585,16 +20755,16 @@
         <v>25</v>
       </c>
       <c r="N75" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O75" t="s">
-        <v>1481</v>
+        <v>1486</v>
       </c>
       <c r="P75" t="s">
-        <v>1482</v>
+        <v>1487</v>
       </c>
       <c r="Q75" t="s">
-        <v>1483</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
@@ -20608,7 +20778,7 @@
         <v>55</v>
       </c>
       <c r="D76" t="s">
-        <v>1484</v>
+        <v>1489</v>
       </c>
       <c r="E76" t="s">
         <v>957</v>
@@ -20617,7 +20787,7 @@
         <v>20</v>
       </c>
       <c r="G76" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="H76">
         <v>200000</v>
@@ -20638,16 +20808,16 @@
         <v>25</v>
       </c>
       <c r="N76" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O76" t="s">
-        <v>1485</v>
+        <v>1490</v>
       </c>
       <c r="P76" t="s">
-        <v>1486</v>
+        <v>1491</v>
       </c>
       <c r="Q76" t="s">
-        <v>1487</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
@@ -20661,7 +20831,7 @@
         <v>52</v>
       </c>
       <c r="D77" t="s">
-        <v>1488</v>
+        <v>1493</v>
       </c>
       <c r="E77" t="s">
         <v>957</v>
@@ -20670,7 +20840,7 @@
         <v>20</v>
       </c>
       <c r="G77" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="H77">
         <v>250000</v>
@@ -20691,16 +20861,16 @@
         <v>25</v>
       </c>
       <c r="N77" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O77" t="s">
-        <v>1489</v>
+        <v>1494</v>
       </c>
       <c r="P77" t="s">
-        <v>1490</v>
+        <v>1495</v>
       </c>
       <c r="Q77" t="s">
-        <v>1491</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
@@ -20714,7 +20884,7 @@
         <v>53</v>
       </c>
       <c r="D78" t="s">
-        <v>1492</v>
+        <v>1497</v>
       </c>
       <c r="E78" t="s">
         <v>957</v>
@@ -20723,7 +20893,7 @@
         <v>20</v>
       </c>
       <c r="G78" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="H78">
         <v>200000</v>
@@ -20744,16 +20914,16 @@
         <v>25</v>
       </c>
       <c r="N78" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O78" t="s">
-        <v>1493</v>
+        <v>1498</v>
       </c>
       <c r="P78" t="s">
-        <v>1494</v>
+        <v>1499</v>
       </c>
       <c r="Q78" t="s">
-        <v>1495</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
@@ -20767,7 +20937,7 @@
         <v>50</v>
       </c>
       <c r="D79" t="s">
-        <v>1496</v>
+        <v>1501</v>
       </c>
       <c r="E79" t="s">
         <v>957</v>
@@ -20776,7 +20946,7 @@
         <v>20</v>
       </c>
       <c r="G79" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="H79">
         <v>200000</v>
@@ -20797,16 +20967,16 @@
         <v>25</v>
       </c>
       <c r="N79" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O79" t="s">
-        <v>1497</v>
+        <v>1502</v>
       </c>
       <c r="P79" t="s">
-        <v>1498</v>
+        <v>1503</v>
       </c>
       <c r="Q79" t="s">
-        <v>1499</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
@@ -20820,7 +20990,7 @@
         <v>55</v>
       </c>
       <c r="D80" t="s">
-        <v>1500</v>
+        <v>1505</v>
       </c>
       <c r="E80" t="s">
         <v>957</v>
@@ -20829,7 +20999,7 @@
         <v>20</v>
       </c>
       <c r="G80" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="H80">
         <v>250000</v>
@@ -20850,16 +21020,16 @@
         <v>25</v>
       </c>
       <c r="N80" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O80" t="s">
-        <v>1501</v>
+        <v>1506</v>
       </c>
       <c r="P80" t="s">
-        <v>1502</v>
+        <v>1507</v>
       </c>
       <c r="Q80" t="s">
-        <v>1503</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
@@ -20873,16 +21043,16 @@
         <v>45</v>
       </c>
       <c r="D81" t="s">
-        <v>1504</v>
+        <v>1509</v>
       </c>
       <c r="E81" t="s">
-        <v>1505</v>
+        <v>1510</v>
       </c>
       <c r="F81" t="s">
-        <v>1506</v>
+        <v>1511</v>
       </c>
       <c r="G81" t="s">
-        <v>1160</v>
+        <v>1165</v>
       </c>
       <c r="H81">
         <v>154000</v>
@@ -20903,16 +21073,16 @@
         <v>39</v>
       </c>
       <c r="N81" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O81" t="s">
-        <v>1507</v>
+        <v>1512</v>
       </c>
       <c r="P81" t="s">
-        <v>1508</v>
+        <v>1513</v>
       </c>
       <c r="Q81" t="s">
-        <v>1509</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
@@ -20935,7 +21105,7 @@
         <v>592</v>
       </c>
       <c r="G82" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="H82">
         <v>180000</v>
@@ -20956,16 +21126,16 @@
         <v>25</v>
       </c>
       <c r="N82" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O82" t="s">
-        <v>1510</v>
+        <v>1515</v>
       </c>
       <c r="P82" t="s">
-        <v>1511</v>
+        <v>1516</v>
       </c>
       <c r="Q82" t="s">
-        <v>1512</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
@@ -20985,10 +21155,10 @@
         <v>55</v>
       </c>
       <c r="F83" t="s">
-        <v>1366</v>
+        <v>1371</v>
       </c>
       <c r="G83" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="H83">
         <v>219100</v>
@@ -21009,16 +21179,16 @@
         <v>39</v>
       </c>
       <c r="N83" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O83" t="s">
-        <v>1513</v>
+        <v>1518</v>
       </c>
       <c r="P83" t="s">
-        <v>1514</v>
+        <v>1519</v>
       </c>
       <c r="Q83" t="s">
-        <v>1515</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
@@ -21032,16 +21202,16 @@
         <v>25</v>
       </c>
       <c r="D84" t="s">
-        <v>1516</v>
+        <v>1521</v>
       </c>
       <c r="E84" t="s">
         <v>55</v>
       </c>
       <c r="F84" t="s">
-        <v>1517</v>
+        <v>1522</v>
       </c>
       <c r="G84" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J84" t="s">
         <v>38</v>
@@ -21056,16 +21226,16 @@
         <v>39</v>
       </c>
       <c r="N84" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O84" t="s">
-        <v>1518</v>
+        <v>1523</v>
       </c>
       <c r="P84" t="s">
-        <v>1519</v>
+        <v>1524</v>
       </c>
       <c r="Q84" t="s">
-        <v>1520</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
@@ -21085,10 +21255,10 @@
         <v>846</v>
       </c>
       <c r="F85" t="s">
-        <v>1186</v>
+        <v>1191</v>
       </c>
       <c r="G85" t="s">
-        <v>1160</v>
+        <v>1165</v>
       </c>
       <c r="J85" t="s">
         <v>38</v>
@@ -21103,16 +21273,16 @@
         <v>39</v>
       </c>
       <c r="N85" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O85" t="s">
-        <v>1521</v>
+        <v>1526</v>
       </c>
       <c r="P85" t="s">
-        <v>1522</v>
+        <v>1527</v>
       </c>
       <c r="Q85" t="s">
-        <v>1523</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
@@ -21126,16 +21296,16 @@
         <v>15</v>
       </c>
       <c r="D86" t="s">
-        <v>1524</v>
+        <v>1529</v>
       </c>
       <c r="E86" t="s">
-        <v>1525</v>
+        <v>1530</v>
       </c>
       <c r="F86" t="s">
-        <v>1334</v>
+        <v>1339</v>
       </c>
       <c r="G86" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J86" t="s">
         <v>38</v>
@@ -21150,16 +21320,16 @@
         <v>39</v>
       </c>
       <c r="N86" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O86" t="s">
-        <v>1526</v>
+        <v>1531</v>
       </c>
       <c r="P86" t="s">
-        <v>1527</v>
+        <v>1532</v>
       </c>
       <c r="Q86" t="s">
-        <v>1528</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
@@ -21173,16 +21343,16 @@
         <v>12</v>
       </c>
       <c r="D87" t="s">
-        <v>1529</v>
+        <v>1534</v>
       </c>
       <c r="E87" t="s">
-        <v>1530</v>
+        <v>1535</v>
       </c>
       <c r="F87" t="s">
-        <v>1531</v>
+        <v>1536</v>
       </c>
       <c r="G87" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J87" t="s">
         <v>38</v>
@@ -21197,16 +21367,16 @@
         <v>39</v>
       </c>
       <c r="N87" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O87" t="s">
-        <v>1532</v>
+        <v>1537</v>
       </c>
       <c r="P87" t="s">
-        <v>1533</v>
+        <v>1538</v>
       </c>
       <c r="Q87" t="s">
-        <v>1534</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
@@ -21220,16 +21390,16 @@
         <v>42</v>
       </c>
       <c r="D88" t="s">
-        <v>1535</v>
+        <v>1540</v>
       </c>
       <c r="E88" t="s">
         <v>55</v>
       </c>
       <c r="F88" t="s">
-        <v>1536</v>
+        <v>1541</v>
       </c>
       <c r="G88" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="H88">
         <v>180000</v>
@@ -21250,16 +21420,16 @@
         <v>25</v>
       </c>
       <c r="N88" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O88" t="s">
-        <v>1537</v>
+        <v>1542</v>
       </c>
       <c r="P88" t="s">
-        <v>1538</v>
+        <v>1543</v>
       </c>
       <c r="Q88" t="s">
-        <v>1539</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
@@ -21273,16 +21443,16 @@
         <v>22</v>
       </c>
       <c r="D89" t="s">
-        <v>1540</v>
+        <v>1545</v>
       </c>
       <c r="E89" t="s">
-        <v>1267</v>
+        <v>1272</v>
       </c>
       <c r="F89" t="s">
-        <v>1541</v>
+        <v>1546</v>
       </c>
       <c r="G89" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="H89">
         <v>200000</v>
@@ -21303,16 +21473,16 @@
         <v>39</v>
       </c>
       <c r="N89" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O89" t="s">
-        <v>1542</v>
+        <v>1547</v>
       </c>
       <c r="P89" t="s">
-        <v>1543</v>
+        <v>1548</v>
       </c>
       <c r="Q89" t="s">
-        <v>1544</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
@@ -21326,16 +21496,16 @@
         <v>28</v>
       </c>
       <c r="D90" t="s">
-        <v>1545</v>
+        <v>1550</v>
       </c>
       <c r="E90" t="s">
-        <v>1546</v>
+        <v>1551</v>
       </c>
       <c r="F90" t="s">
-        <v>1517</v>
+        <v>1522</v>
       </c>
       <c r="G90" t="s">
-        <v>1160</v>
+        <v>1165</v>
       </c>
       <c r="J90" t="s">
         <v>38</v>
@@ -21350,16 +21520,16 @@
         <v>39</v>
       </c>
       <c r="N90" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O90" t="s">
-        <v>1547</v>
+        <v>1552</v>
       </c>
       <c r="P90" t="s">
-        <v>1548</v>
+        <v>1553</v>
       </c>
       <c r="Q90" t="s">
-        <v>1549</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
@@ -21373,16 +21543,16 @@
         <v>5</v>
       </c>
       <c r="D91" t="s">
-        <v>1550</v>
+        <v>1555</v>
       </c>
       <c r="E91" t="s">
-        <v>1551</v>
+        <v>1556</v>
       </c>
       <c r="F91" t="s">
-        <v>1552</v>
+        <v>1557</v>
       </c>
       <c r="G91" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J91" t="s">
         <v>38</v>
@@ -21397,16 +21567,16 @@
         <v>39</v>
       </c>
       <c r="N91" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O91" t="s">
-        <v>1553</v>
+        <v>1558</v>
       </c>
       <c r="P91" t="s">
-        <v>1554</v>
+        <v>1559</v>
       </c>
       <c r="Q91" t="s">
-        <v>1555</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
@@ -21426,10 +21596,10 @@
         <v>55</v>
       </c>
       <c r="F92" t="s">
-        <v>1556</v>
+        <v>1561</v>
       </c>
       <c r="G92" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J92" t="s">
         <v>38</v>
@@ -21444,16 +21614,16 @@
         <v>25</v>
       </c>
       <c r="N92" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O92" t="s">
-        <v>1557</v>
+        <v>1562</v>
       </c>
       <c r="P92" t="s">
-        <v>1558</v>
+        <v>1563</v>
       </c>
       <c r="Q92" t="s">
-        <v>1559</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
@@ -21467,16 +21637,16 @@
         <v>35</v>
       </c>
       <c r="D93" t="s">
-        <v>1560</v>
+        <v>1565</v>
       </c>
       <c r="E93" t="s">
-        <v>1561</v>
+        <v>1566</v>
       </c>
       <c r="F93" t="s">
-        <v>1328</v>
+        <v>1333</v>
       </c>
       <c r="G93" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J93" t="s">
         <v>38</v>
@@ -21491,16 +21661,16 @@
         <v>39</v>
       </c>
       <c r="N93" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O93" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="P93" t="s">
-        <v>1563</v>
+        <v>1568</v>
       </c>
       <c r="Q93" t="s">
-        <v>1564</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
@@ -21514,16 +21684,16 @@
         <v>55</v>
       </c>
       <c r="D94" t="s">
-        <v>1565</v>
+        <v>1570</v>
       </c>
       <c r="E94" t="s">
         <v>55</v>
       </c>
       <c r="F94" t="s">
-        <v>1366</v>
+        <v>1371</v>
       </c>
       <c r="G94" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="H94">
         <v>219100</v>
@@ -21538,22 +21708,22 @@
         <v>57</v>
       </c>
       <c r="L94" t="s">
-        <v>1566</v>
+        <v>1571</v>
       </c>
       <c r="M94" t="s">
         <v>25</v>
       </c>
       <c r="N94" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O94" t="s">
-        <v>1567</v>
+        <v>1572</v>
       </c>
       <c r="P94" t="s">
-        <v>1568</v>
+        <v>1573</v>
       </c>
       <c r="Q94" t="s">
-        <v>1569</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
@@ -21567,16 +21737,16 @@
         <v>50</v>
       </c>
       <c r="D95" t="s">
-        <v>1570</v>
+        <v>1575</v>
       </c>
       <c r="E95" t="s">
-        <v>1267</v>
+        <v>1272</v>
       </c>
       <c r="F95" t="s">
         <v>20</v>
       </c>
       <c r="G95" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="H95">
         <v>200000</v>
@@ -21591,22 +21761,22 @@
         <v>57</v>
       </c>
       <c r="L95" t="s">
-        <v>1566</v>
+        <v>1571</v>
       </c>
       <c r="M95" t="s">
         <v>25</v>
       </c>
       <c r="N95" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O95" t="s">
-        <v>1571</v>
+        <v>1576</v>
       </c>
       <c r="P95" t="s">
-        <v>1572</v>
+        <v>1577</v>
       </c>
       <c r="Q95" t="s">
-        <v>1573</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
@@ -21620,16 +21790,16 @@
         <v>12</v>
       </c>
       <c r="D96" t="s">
-        <v>1574</v>
+        <v>1579</v>
       </c>
       <c r="E96" t="s">
-        <v>1575</v>
+        <v>1580</v>
       </c>
       <c r="F96" t="s">
-        <v>1517</v>
+        <v>1522</v>
       </c>
       <c r="G96" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J96" t="s">
         <v>38</v>
@@ -21638,22 +21808,22 @@
         <v>130</v>
       </c>
       <c r="L96" t="s">
-        <v>1566</v>
+        <v>1571</v>
       </c>
       <c r="M96" t="s">
         <v>39</v>
       </c>
       <c r="N96" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O96" t="s">
-        <v>1576</v>
+        <v>1581</v>
       </c>
       <c r="P96" t="s">
-        <v>1577</v>
+        <v>1582</v>
       </c>
       <c r="Q96" t="s">
-        <v>1578</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
@@ -21667,16 +21837,16 @@
         <v>12</v>
       </c>
       <c r="D97" t="s">
-        <v>1579</v>
+        <v>1584</v>
       </c>
       <c r="E97" t="s">
-        <v>1575</v>
+        <v>1580</v>
       </c>
       <c r="F97" t="s">
-        <v>1517</v>
+        <v>1522</v>
       </c>
       <c r="G97" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J97" t="s">
         <v>38</v>
@@ -21685,22 +21855,22 @@
         <v>130</v>
       </c>
       <c r="L97" t="s">
-        <v>1566</v>
+        <v>1571</v>
       </c>
       <c r="M97" t="s">
         <v>39</v>
       </c>
       <c r="N97" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O97" t="s">
-        <v>1580</v>
+        <v>1585</v>
       </c>
       <c r="P97" t="s">
-        <v>1581</v>
+        <v>1586</v>
       </c>
       <c r="Q97" t="s">
-        <v>1582</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
@@ -21714,16 +21884,16 @@
         <v>3</v>
       </c>
       <c r="D98" t="s">
-        <v>1583</v>
+        <v>1588</v>
       </c>
       <c r="E98" t="s">
-        <v>1575</v>
+        <v>1580</v>
       </c>
       <c r="F98" t="s">
-        <v>1517</v>
+        <v>1522</v>
       </c>
       <c r="G98" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J98" t="s">
         <v>38</v>
@@ -21732,22 +21902,22 @@
         <v>130</v>
       </c>
       <c r="L98" t="s">
-        <v>1566</v>
+        <v>1571</v>
       </c>
       <c r="M98" t="s">
         <v>39</v>
       </c>
       <c r="N98" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O98" t="s">
-        <v>1584</v>
+        <v>1589</v>
       </c>
       <c r="P98" t="s">
-        <v>1585</v>
+        <v>1590</v>
       </c>
       <c r="Q98" t="s">
-        <v>1586</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.25">
@@ -21761,16 +21931,16 @@
         <v>25</v>
       </c>
       <c r="D99" t="s">
-        <v>1587</v>
+        <v>1592</v>
       </c>
       <c r="E99" t="s">
-        <v>1588</v>
+        <v>1593</v>
       </c>
       <c r="F99" t="s">
-        <v>1589</v>
+        <v>1594</v>
       </c>
       <c r="G99" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J99" t="s">
         <v>38</v>
@@ -21779,22 +21949,22 @@
         <v>130</v>
       </c>
       <c r="L99" t="s">
-        <v>1566</v>
+        <v>1571</v>
       </c>
       <c r="M99" t="s">
         <v>39</v>
       </c>
       <c r="N99" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O99" t="s">
-        <v>1590</v>
+        <v>1595</v>
       </c>
       <c r="P99" t="s">
-        <v>1591</v>
+        <v>1596</v>
       </c>
       <c r="Q99" t="s">
-        <v>1592</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.25">
@@ -21808,16 +21978,16 @@
         <v>62</v>
       </c>
       <c r="D100" t="s">
-        <v>1593</v>
+        <v>1598</v>
       </c>
       <c r="E100" t="s">
-        <v>1594</v>
+        <v>1599</v>
       </c>
       <c r="F100" t="s">
-        <v>1595</v>
+        <v>1600</v>
       </c>
       <c r="G100" t="s">
-        <v>1160</v>
+        <v>1165</v>
       </c>
       <c r="J100" t="s">
         <v>38</v>
@@ -21826,22 +21996,22 @@
         <v>130</v>
       </c>
       <c r="L100" t="s">
-        <v>1566</v>
+        <v>1571</v>
       </c>
       <c r="M100" t="s">
         <v>39</v>
       </c>
       <c r="N100" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O100" t="s">
-        <v>1596</v>
+        <v>1601</v>
       </c>
       <c r="P100" t="s">
-        <v>1597</v>
+        <v>1602</v>
       </c>
       <c r="Q100" t="s">
-        <v>1598</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.25">
@@ -21855,16 +22025,16 @@
         <v>68</v>
       </c>
       <c r="D101" t="s">
+        <v>1604</v>
+      </c>
+      <c r="E101" t="s">
         <v>1599</v>
       </c>
-      <c r="E101" t="s">
-        <v>1594</v>
-      </c>
       <c r="F101" t="s">
-        <v>1595</v>
+        <v>1600</v>
       </c>
       <c r="G101" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J101" t="s">
         <v>38</v>
@@ -21873,22 +22043,22 @@
         <v>130</v>
       </c>
       <c r="L101" t="s">
-        <v>1566</v>
+        <v>1571</v>
       </c>
       <c r="M101" t="s">
         <v>39</v>
       </c>
       <c r="N101" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O101" t="s">
-        <v>1600</v>
+        <v>1605</v>
       </c>
       <c r="P101" t="s">
-        <v>1601</v>
+        <v>1606</v>
       </c>
       <c r="Q101" t="s">
-        <v>1602</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.25">
@@ -21908,10 +22078,10 @@
         <v>55</v>
       </c>
       <c r="F102" t="s">
-        <v>1603</v>
+        <v>1608</v>
       </c>
       <c r="G102" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="H102">
         <v>180000</v>
@@ -21932,16 +22102,16 @@
         <v>25</v>
       </c>
       <c r="N102" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O102" t="s">
-        <v>1604</v>
+        <v>1609</v>
       </c>
       <c r="P102" t="s">
-        <v>1605</v>
+        <v>1610</v>
       </c>
       <c r="Q102" t="s">
-        <v>1606</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.25">
@@ -21961,10 +22131,10 @@
         <v>55</v>
       </c>
       <c r="F103" t="s">
-        <v>1607</v>
+        <v>1612</v>
       </c>
       <c r="G103" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="H103">
         <v>180000</v>
@@ -21985,16 +22155,16 @@
         <v>25</v>
       </c>
       <c r="N103" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O103" t="s">
-        <v>1608</v>
+        <v>1613</v>
       </c>
       <c r="P103" t="s">
-        <v>1609</v>
+        <v>1614</v>
       </c>
       <c r="Q103" t="s">
-        <v>1610</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.25">
@@ -22008,16 +22178,16 @@
         <v>35</v>
       </c>
       <c r="D104" t="s">
-        <v>1611</v>
+        <v>1616</v>
       </c>
       <c r="E104" t="s">
         <v>55</v>
       </c>
       <c r="F104" t="s">
-        <v>1612</v>
+        <v>1617</v>
       </c>
       <c r="G104" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="H104">
         <v>219100</v>
@@ -22038,16 +22208,16 @@
         <v>25</v>
       </c>
       <c r="N104" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O104" t="s">
-        <v>1613</v>
+        <v>1618</v>
       </c>
       <c r="P104" t="s">
-        <v>1614</v>
+        <v>1619</v>
       </c>
       <c r="Q104" t="s">
-        <v>1615</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.25">
@@ -22061,16 +22231,16 @@
         <v>25</v>
       </c>
       <c r="D105" t="s">
-        <v>1616</v>
+        <v>1621</v>
       </c>
       <c r="E105" t="s">
         <v>633</v>
       </c>
       <c r="F105" t="s">
-        <v>1433</v>
+        <v>1438</v>
       </c>
       <c r="G105" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J105" t="s">
         <v>38</v>
@@ -22085,16 +22255,16 @@
         <v>39</v>
       </c>
       <c r="N105" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O105" t="s">
-        <v>1617</v>
+        <v>1622</v>
       </c>
       <c r="P105" t="s">
-        <v>1618</v>
+        <v>1623</v>
       </c>
       <c r="Q105" t="s">
-        <v>1619</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.25">
@@ -22108,16 +22278,16 @@
         <v>35</v>
       </c>
       <c r="D106" t="s">
-        <v>1620</v>
+        <v>1625</v>
       </c>
       <c r="E106" t="s">
-        <v>1621</v>
+        <v>1626</v>
       </c>
       <c r="F106" t="s">
-        <v>1186</v>
+        <v>1191</v>
       </c>
       <c r="G106" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J106" t="s">
         <v>38</v>
@@ -22132,16 +22302,16 @@
         <v>39</v>
       </c>
       <c r="N106" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O106" t="s">
-        <v>1622</v>
+        <v>1627</v>
       </c>
       <c r="P106" t="s">
-        <v>1623</v>
+        <v>1628</v>
       </c>
       <c r="Q106" t="s">
-        <v>1624</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.25">
@@ -22158,13 +22328,13 @@
         <v>305</v>
       </c>
       <c r="E107" t="s">
-        <v>1625</v>
+        <v>1630</v>
       </c>
       <c r="F107" t="s">
-        <v>1328</v>
+        <v>1333</v>
       </c>
       <c r="G107" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="H107">
         <v>200000</v>
@@ -22185,16 +22355,16 @@
         <v>39</v>
       </c>
       <c r="N107" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O107" t="s">
-        <v>1626</v>
+        <v>1631</v>
       </c>
       <c r="P107" t="s">
-        <v>1627</v>
+        <v>1632</v>
       </c>
       <c r="Q107" t="s">
-        <v>1628</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.25">
@@ -22208,16 +22378,16 @@
         <v>38</v>
       </c>
       <c r="D108" t="s">
-        <v>1629</v>
+        <v>1634</v>
       </c>
       <c r="E108" t="s">
-        <v>1625</v>
+        <v>1630</v>
       </c>
       <c r="F108" t="s">
-        <v>1328</v>
+        <v>1333</v>
       </c>
       <c r="G108" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="H108">
         <v>200000</v>
@@ -22238,16 +22408,16 @@
         <v>39</v>
       </c>
       <c r="N108" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O108" t="s">
-        <v>1630</v>
+        <v>1635</v>
       </c>
       <c r="P108" t="s">
-        <v>1631</v>
+        <v>1636</v>
       </c>
       <c r="Q108" t="s">
-        <v>1632</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.25">
@@ -22261,16 +22431,16 @@
         <v>40</v>
       </c>
       <c r="D109" t="s">
-        <v>1411</v>
+        <v>1416</v>
       </c>
       <c r="E109" t="s">
-        <v>1267</v>
+        <v>1272</v>
       </c>
       <c r="F109" t="s">
         <v>861</v>
       </c>
       <c r="G109" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="H109">
         <v>184200</v>
@@ -22291,16 +22461,16 @@
         <v>39</v>
       </c>
       <c r="N109" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O109" t="s">
-        <v>1633</v>
+        <v>1638</v>
       </c>
       <c r="P109" t="s">
-        <v>1634</v>
+        <v>1639</v>
       </c>
       <c r="Q109" t="s">
-        <v>1635</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.25">
@@ -22314,16 +22484,16 @@
         <v>20</v>
       </c>
       <c r="D110" t="s">
-        <v>1636</v>
+        <v>1641</v>
       </c>
       <c r="E110" t="s">
-        <v>1637</v>
+        <v>1642</v>
       </c>
       <c r="F110" t="s">
-        <v>1638</v>
+        <v>1643</v>
       </c>
       <c r="G110" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="J110" t="s">
         <v>38</v>
@@ -22338,16 +22508,16 @@
         <v>39</v>
       </c>
       <c r="N110" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O110" t="s">
-        <v>1639</v>
+        <v>1644</v>
       </c>
       <c r="P110" t="s">
-        <v>1640</v>
+        <v>1645</v>
       </c>
       <c r="Q110" t="s">
-        <v>1641</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.25">
@@ -22361,16 +22531,16 @@
         <v>35</v>
       </c>
       <c r="D111" t="s">
-        <v>1642</v>
+        <v>1647</v>
       </c>
       <c r="E111" t="s">
-        <v>1643</v>
+        <v>1648</v>
       </c>
       <c r="F111" t="s">
-        <v>1644</v>
+        <v>1649</v>
       </c>
       <c r="G111" t="s">
-        <v>1160</v>
+        <v>1165</v>
       </c>
       <c r="H111">
         <v>230000</v>
@@ -22391,16 +22561,404 @@
         <v>39</v>
       </c>
       <c r="N111" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="O111" t="s">
-        <v>1645</v>
+        <v>1650</v>
       </c>
       <c r="P111" t="s">
-        <v>1646</v>
+        <v>1651</v>
       </c>
       <c r="Q111" t="s">
-        <v>1647</v>
+        <v>1652</v>
+      </c>
+    </row>
+    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>17</v>
+      </c>
+      <c r="B112">
+        <v>70</v>
+      </c>
+      <c r="C112">
+        <v>66</v>
+      </c>
+      <c r="D112" t="s">
+        <v>134</v>
+      </c>
+      <c r="E112" t="s">
+        <v>55</v>
+      </c>
+      <c r="F112" t="s">
+        <v>1653</v>
+      </c>
+      <c r="G112" t="s">
+        <v>1148</v>
+      </c>
+      <c r="H112">
+        <v>219100</v>
+      </c>
+      <c r="I112">
+        <v>219100</v>
+      </c>
+      <c r="J112" t="s">
+        <v>22</v>
+      </c>
+      <c r="K112" t="s">
+        <v>57</v>
+      </c>
+      <c r="L112" t="s">
+        <v>1143</v>
+      </c>
+      <c r="M112" t="s">
+        <v>32</v>
+      </c>
+      <c r="N112" t="s">
+        <v>1149</v>
+      </c>
+      <c r="O112" t="s">
+        <v>1654</v>
+      </c>
+      <c r="P112" t="s">
+        <v>1655</v>
+      </c>
+      <c r="Q112" t="s">
+        <v>1656</v>
+      </c>
+    </row>
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>17</v>
+      </c>
+      <c r="B113">
+        <v>22</v>
+      </c>
+      <c r="C113">
+        <v>25</v>
+      </c>
+      <c r="D113" t="s">
+        <v>1657</v>
+      </c>
+      <c r="E113" t="s">
+        <v>1566</v>
+      </c>
+      <c r="F113" t="s">
+        <v>1333</v>
+      </c>
+      <c r="G113" t="s">
+        <v>1165</v>
+      </c>
+      <c r="J113" t="s">
+        <v>38</v>
+      </c>
+      <c r="K113" t="s">
+        <v>130</v>
+      </c>
+      <c r="L113" t="s">
+        <v>1143</v>
+      </c>
+      <c r="M113" t="s">
+        <v>39</v>
+      </c>
+      <c r="N113" t="s">
+        <v>1149</v>
+      </c>
+      <c r="O113" t="s">
+        <v>1658</v>
+      </c>
+      <c r="P113" t="s">
+        <v>1659</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>1660</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>17</v>
+      </c>
+      <c r="B114">
+        <v>20</v>
+      </c>
+      <c r="C114">
+        <v>22</v>
+      </c>
+      <c r="D114" t="s">
+        <v>1661</v>
+      </c>
+      <c r="E114" t="s">
+        <v>1662</v>
+      </c>
+      <c r="F114" t="s">
+        <v>1171</v>
+      </c>
+      <c r="G114" t="s">
+        <v>1148</v>
+      </c>
+      <c r="J114" t="s">
+        <v>38</v>
+      </c>
+      <c r="K114" t="s">
+        <v>130</v>
+      </c>
+      <c r="L114" t="s">
+        <v>1143</v>
+      </c>
+      <c r="M114" t="s">
+        <v>39</v>
+      </c>
+      <c r="N114" t="s">
+        <v>1149</v>
+      </c>
+      <c r="O114" t="s">
+        <v>1663</v>
+      </c>
+      <c r="P114" t="s">
+        <v>1664</v>
+      </c>
+      <c r="Q114" t="s">
+        <v>1665</v>
+      </c>
+    </row>
+    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>17</v>
+      </c>
+      <c r="B115">
+        <v>3</v>
+      </c>
+      <c r="C115">
+        <v>3</v>
+      </c>
+      <c r="D115" t="s">
+        <v>1666</v>
+      </c>
+      <c r="E115" t="s">
+        <v>1667</v>
+      </c>
+      <c r="F115" t="s">
+        <v>1171</v>
+      </c>
+      <c r="G115" t="s">
+        <v>1148</v>
+      </c>
+      <c r="J115" t="s">
+        <v>38</v>
+      </c>
+      <c r="K115" t="s">
+        <v>130</v>
+      </c>
+      <c r="L115" t="s">
+        <v>1143</v>
+      </c>
+      <c r="M115" t="s">
+        <v>39</v>
+      </c>
+      <c r="N115" t="s">
+        <v>1149</v>
+      </c>
+      <c r="O115" t="s">
+        <v>1668</v>
+      </c>
+      <c r="P115" t="s">
+        <v>1669</v>
+      </c>
+      <c r="Q115" t="s">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>17</v>
+      </c>
+      <c r="B116">
+        <v>25</v>
+      </c>
+      <c r="C116">
+        <v>28</v>
+      </c>
+      <c r="D116" t="s">
+        <v>1671</v>
+      </c>
+      <c r="E116" t="s">
+        <v>1672</v>
+      </c>
+      <c r="F116" t="s">
+        <v>1522</v>
+      </c>
+      <c r="G116" t="s">
+        <v>1148</v>
+      </c>
+      <c r="J116" t="s">
+        <v>38</v>
+      </c>
+      <c r="K116" t="s">
+        <v>130</v>
+      </c>
+      <c r="L116" t="s">
+        <v>1143</v>
+      </c>
+      <c r="M116" t="s">
+        <v>39</v>
+      </c>
+      <c r="N116" t="s">
+        <v>1149</v>
+      </c>
+      <c r="O116" t="s">
+        <v>1673</v>
+      </c>
+      <c r="P116" t="s">
+        <v>1674</v>
+      </c>
+      <c r="Q116" t="s">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>17</v>
+      </c>
+      <c r="B117">
+        <v>52</v>
+      </c>
+      <c r="C117">
+        <v>45</v>
+      </c>
+      <c r="D117" t="s">
+        <v>1676</v>
+      </c>
+      <c r="E117" t="s">
+        <v>1677</v>
+      </c>
+      <c r="F117" t="s">
+        <v>1191</v>
+      </c>
+      <c r="G117" t="s">
+        <v>1148</v>
+      </c>
+      <c r="J117" t="s">
+        <v>38</v>
+      </c>
+      <c r="K117" t="s">
+        <v>130</v>
+      </c>
+      <c r="L117" t="s">
+        <v>1143</v>
+      </c>
+      <c r="M117" t="s">
+        <v>25</v>
+      </c>
+      <c r="N117" t="s">
+        <v>1149</v>
+      </c>
+      <c r="O117" t="s">
+        <v>1678</v>
+      </c>
+      <c r="P117" t="s">
+        <v>1679</v>
+      </c>
+      <c r="Q117" t="s">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>17</v>
+      </c>
+      <c r="B118">
+        <v>40</v>
+      </c>
+      <c r="C118">
+        <v>50</v>
+      </c>
+      <c r="D118" t="s">
+        <v>1175</v>
+      </c>
+      <c r="E118" t="s">
+        <v>1170</v>
+      </c>
+      <c r="F118" t="s">
+        <v>1176</v>
+      </c>
+      <c r="G118" t="s">
+        <v>1148</v>
+      </c>
+      <c r="J118" t="s">
+        <v>38</v>
+      </c>
+      <c r="K118" t="s">
+        <v>130</v>
+      </c>
+      <c r="L118" t="s">
+        <v>1143</v>
+      </c>
+      <c r="M118" t="s">
+        <v>25</v>
+      </c>
+      <c r="N118" t="s">
+        <v>1149</v>
+      </c>
+      <c r="O118" t="s">
+        <v>1681</v>
+      </c>
+      <c r="P118" t="s">
+        <v>1682</v>
+      </c>
+      <c r="Q118" t="s">
+        <v>1683</v>
+      </c>
+    </row>
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>17</v>
+      </c>
+      <c r="B119">
+        <v>45</v>
+      </c>
+      <c r="C119">
+        <v>48</v>
+      </c>
+      <c r="D119" t="s">
+        <v>1684</v>
+      </c>
+      <c r="E119" t="s">
+        <v>1510</v>
+      </c>
+      <c r="F119" t="s">
+        <v>1685</v>
+      </c>
+      <c r="G119" t="s">
+        <v>1165</v>
+      </c>
+      <c r="H119">
+        <v>154000</v>
+      </c>
+      <c r="I119">
+        <v>209000</v>
+      </c>
+      <c r="J119" t="s">
+        <v>22</v>
+      </c>
+      <c r="K119" t="s">
+        <v>923</v>
+      </c>
+      <c r="L119" t="s">
+        <v>1143</v>
+      </c>
+      <c r="M119" t="s">
+        <v>25</v>
+      </c>
+      <c r="N119" t="s">
+        <v>1149</v>
+      </c>
+      <c r="O119" t="s">
+        <v>1686</v>
+      </c>
+      <c r="P119" t="s">
+        <v>1687</v>
+      </c>
+      <c r="Q119" t="s">
+        <v>1688</v>
       </c>
     </row>
   </sheetData>

--- a/hunt/board.xlsx
+++ b/hunt/board.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4545" uniqueCount="1689">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4701" uniqueCount="1736">
   <si>
     <t>Column</t>
   </si>
@@ -3455,6 +3455,72 @@
     <t>https://himalayas.app/companies/infotrust/jobs/senior-devops-engineer</t>
   </si>
   <si>
+    <t>Billing Solutions Architect</t>
+  </si>
+  <si>
+    <t>2026-09-02T15:48:53.236Z</t>
+  </si>
+  <si>
+    <t>Remote role with trusted-advisor engagement model that matches candidate's customer engineer/advisory experience | Solutions Architect title and pre-sales/custom-solution scope align with target titles | Stripe SA roles value API-heavy technical consulting, and candidate has REST API/integration experience</t>
+  </si>
+  <si>
+    <t>Requires deep subscription/billing/payments domain expertise the candidate's Azure DevOps/GHAS background doesn't cover | Not a cloud infrastructure or DevOps governance role — little use of candidate's Azure Policy, GHAS, CI/CD depth | Heavily tied to sales-team collaboration on Stripe product specifics; steep domain ramp</t>
+  </si>
+  <si>
+    <t>https://himalayas.app/companies/stripe/jobs/billing-solutions-architect-4179540574</t>
+  </si>
+  <si>
+    <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Digital Native Business)</t>
+  </si>
+  <si>
+    <t>Fully remote US role with explicit trusted-advisor-to-customer-architects framing that matches candidate's Customer Engineer model | Confirmed $180K base meets the salary floor exactly | End-to-end technical ownership from discovery to production deployment suits candidate's enterprise advisory experience</t>
+  </si>
+  <si>
+    <t>Demands deep specialist depth in data engineering/warehousing (Spark, Delta, Lakehouse, SQL warehousing) which is not in the candidate's skill set | Digital Native segment expects hands-on data platform architecture, not Azure DevOps/GHAS governance | Databricks Field Engineering bar for 'specialist archetype' generally requires prior data platform delivery experience</t>
+  </si>
+  <si>
+    <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8761732002</t>
+  </si>
+  <si>
+    <t>Payments Solutions Architect (US or EMEA)</t>
+  </si>
+  <si>
+    <t>EMEA,  USA</t>
+  </si>
+  <si>
+    <t>Confirmed $300K comp well above the $180K floor | 100% remote and open to US candidates | Hands-on architecture leadership role with offering-definition scope at a principal-ish level</t>
+  </si>
+  <si>
+    <t>Core requirement is deep digital payments/fintech practitioner expertise (payment methods, transaction flows) that candidate lacks | QA/test engineering orientation is unrelated to candidate's cloud/DevOps advisory background | Restricted to Eastern US residency — candidate is in Texas</t>
+  </si>
+  <si>
+    <t>https://jobicy.com/jobs/152380-payments-solutions-architect-us-or-emea</t>
+  </si>
+  <si>
+    <t>Sr. Solutions Architect - Life Sciences</t>
+  </si>
+  <si>
+    <t>Munich</t>
+  </si>
+  <si>
+    <t>Expert-level technical authority with executive relationship ownership matches candidate's principal-scope ambitions | Remote-friendly posting and strong trusted-advisor framing</t>
+  </si>
+  <si>
+    <t>Germany-based (Frankfurt/Berlin/Munich) role — outside candidate's US market scope and likely requires EU work rights plus German | Requires Life Sciences domain plus deep Databricks/data-and-AI platform expertise the candidate lacks | No comp posted; EMEA bands unlikely to hit the $180K floor</t>
+  </si>
+  <si>
+    <t>https://www.arbeitnow.com/jobs/companies/databricks/sr-solutions-architect-life-sciences-munich-36699</t>
+  </si>
+  <si>
+    <t>Fully remote and squarely in the DevSecOps/CI-CD domain where the candidate has deep hands-on depth (Azure DevOps Pipelines, GHAS, GitHub Enterprise admin) — GitLab SA work maps closely to that toolchain knowledge | Role is a customer-facing trusted-advisor/technical pre-sales function, which mirrors his current Customer Engineer engagement model with enterprise accounts | Compliance-driven architecture experience (HIPAA, PCI, SOX, NIST) is directly relevant to GitLab's security/compliance value narrative to Fortune 100 buyers</t>
+  </si>
+  <si>
+    <t>GitLab Senior SA is a quota-adjacent pre-sales role tied to revenue targets, not principal-level architecture delivery — a step sideways from his 'Principal Cloud Architect' target scope | His GitLab-specific platform experience is thin; his CI/CD depth is Azure DevOps and GitHub Actions, so he'd be learning the competitor's product he'd be selling against | Posting text truncated — no confirmation of Kubernetes/multi-cloud (AWS/GCP) demo requirements that GitLab SA roles usually list</t>
+  </si>
+  <si>
+    <t>https://www.arbeitnow.com/jobs/companies/gitlab/remote-senior-solutions-architect-343490</t>
+  </si>
+  <si>
     <t>Lead GTM Enablement &amp; Scale Architect, Field Engineering - Customer Skills</t>
   </si>
   <si>
@@ -4580,9 +4646,6 @@
     <t>Sr. Solutions Architect - FSI</t>
   </si>
   <si>
-    <t>Munich</t>
-  </si>
-  <si>
     <t>FSI (financial services) vertical focus is a strong precedent match for the candidate's compliance-heavy HIPAA/PCI/SOX background | Role is genuinely technical-authority/advisory work rather than pure quota carrying</t>
   </si>
   <si>
@@ -5079,6 +5142,84 @@
   </si>
   <si>
     <t>https://jobs.ashbyhq.com/benchling/65d30858-1165-4c3f-8ba1-38489fa2e63f</t>
+  </si>
+  <si>
+    <t>Solution Architect (m/w/d) – Financial Services</t>
+  </si>
+  <si>
+    <t>Financial services consulting domain is a strong precedent match for candidate's compliance-heavy (SOX/PCI) architecture work | Solution Architect scope aligns with target titles</t>
+  </si>
+  <si>
+    <t>German-language posting for a Germany-based Capco role — outside the candidate's US market scope | Requires German fluency and likely EU work authorization | No salary posted and no remote designation</t>
+  </si>
+  <si>
+    <t>https://www.arbeitnow.com/jobs/companies/capco/solution-architect-financial-services-142284</t>
+  </si>
+  <si>
+    <t>Guardrails/security and compliance framing for AI systems overlaps with candidate's governance and policy-as-code experience | Agentic architecture focus connects loosely to candidate's GitHub Copilot / Agentic DevOps exposure</t>
+  </si>
+  <si>
+    <t>Requires hands-on RAG pipeline, vector search, and AI framework depth the candidate has not demonstrated | Capco Germany-based role with no location or remote clarity and no posted comp | Not a cloud infrastructure/DevOps advisory role</t>
+  </si>
+  <si>
+    <t>https://www.arbeitnow.com/jobs/companies/capco/ai-architect-388301</t>
+  </si>
+  <si>
+    <t>End-to-end solution architecture and business-to-IT translation matches candidate's advisory strengths | Enterprise clients (AXA, BMW, Deutsche Bahn) are the kind of large regulated accounts candidate has served</t>
+  </si>
+  <si>
+    <t>Munich-based German-language role requiring German fluency and EU work rights | Emphasis on hands-on software development with LLM/codegen frameworks, not cloud platform governance | No salary posted; German consulting bands are far below the $180K floor</t>
+  </si>
+  <si>
+    <t>https://www.arbeitnow.com/jobs/companies/accso-accelerated-solutions-gmbh/senior-solution-architect-facharchitekt-munchen-448556</t>
+  </si>
+  <si>
+    <t>Darmstadt</t>
+  </si>
+  <si>
+    <t>Strongest technical overlap of the Accso roles: Terraform IaC, Azure public cloud, CI/CD delivery pipelines, GitOps | Consulting-plus-delivery model mirrors candidate's customer-facing engineering work</t>
+  </si>
+  <si>
+    <t>Darmstadt, Germany role requiring German language and EU authorization — outside US market scope | Kubernetes/Docker/Prometheus/ArgoCD depth is heavier than candidate's Azure DevOps-centric profile | Engineer-level scope, below the principal architect target, with no comp posted</t>
+  </si>
+  <si>
+    <t>https://www.arbeitnow.com/jobs/companies/accso-accelerated-solutions-gmbh/senior-cloud-devops-engineer-darmstadt-460829</t>
+  </si>
+  <si>
+    <t>Client-facing technical ownership across the full project lifecycle aligns with candidate's trusted-advisor model | Modern AI-assisted development tooling focus touches candidate's Copilot/Agentic DevOps exposure</t>
+  </si>
+  <si>
+    <t>Core requirement is hands-on complex software architecture and coding, not cloud/DevOps platform advisory | Darmstadt, Germany, German-language posting outside candidate's US market scope | No compensation posted and German bands sit well under the $180K floor</t>
+  </si>
+  <si>
+    <t>https://www.arbeitnow.com/jobs/companies/accso-accelerated-solutions-gmbh/senior-software-architect-darmstadt-40303</t>
+  </si>
+  <si>
+    <t>Sr. Solutions Architect - Automotive</t>
+  </si>
+  <si>
+    <t>Senior architect scope with executive-level technical authority matches candidate's target seniority | Consumption/adoption advisory model resembles candidate's enterprise customer engineering work</t>
+  </si>
+  <si>
+    <t>Munich-based onsite/hybrid role in Germany, outside the candidate's US market scope | Requires declared data/AI platform specialization plus automotive industry depth candidate does not have | No salary posted; EMEA comp likely well under the $180K floor</t>
+  </si>
+  <si>
+    <t>https://www.arbeitnow.com/jobs/companies/databricks/sr-solutions-architect-automotive-munich-463574</t>
+  </si>
+  <si>
+    <t>Member of Technical Staff - Platform Engineering</t>
+  </si>
+  <si>
+    <t>modal</t>
+  </si>
+  <si>
+    <t>Confirmed $220K–$300K band comfortably clears his $180K salary floor | Infrastructure/platform focus (containers, storage, GPU orchestration) touches adjacent cloud-platform concepts he's worked with</t>
+  </si>
+  <si>
+    <t>This is a deep IC systems-engineering role (sub-second container starts, low-level runtime/infra build work) — not cloud advisory or architecture, matching his 'not qualified' signal for IC coding-bar-raiser roles | Modal's stack is AWS/GCP-style bare-metal and GPU infrastructure in Rust/Go/Python; his Azure governance, Azure DevOps, and GHAS depth doesn't transfer as credited experience | New York-based and likely in-office at a fast-scaling startup, versus his remote-primary preference</t>
+  </si>
+  <si>
+    <t>https://jobs.ashbyhq.com/modal/84467a68-6876-4730-9d80-6c6f3d0c2d71</t>
   </si>
 </sst>
 </file>
@@ -5459,7 +5600,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q230"/>
+  <dimension ref="A1:Q235"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -17024,6 +17165,253 @@
         <v>1146</v>
       </c>
     </row>
+    <row r="231" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>17</v>
+      </c>
+      <c r="B231">
+        <v>45</v>
+      </c>
+      <c r="C231">
+        <v>42</v>
+      </c>
+      <c r="D231" t="s">
+        <v>1147</v>
+      </c>
+      <c r="E231" t="s">
+        <v>978</v>
+      </c>
+      <c r="F231" t="s">
+        <v>45</v>
+      </c>
+      <c r="G231" t="s">
+        <v>21</v>
+      </c>
+      <c r="J231" t="s">
+        <v>38</v>
+      </c>
+      <c r="K231" t="s">
+        <v>23</v>
+      </c>
+      <c r="L231" t="s">
+        <v>1148</v>
+      </c>
+      <c r="M231" t="s">
+        <v>25</v>
+      </c>
+      <c r="N231" t="s">
+        <v>26</v>
+      </c>
+      <c r="O231" t="s">
+        <v>1149</v>
+      </c>
+      <c r="P231" t="s">
+        <v>1150</v>
+      </c>
+      <c r="Q231" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="232" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>17</v>
+      </c>
+      <c r="B232">
+        <v>58</v>
+      </c>
+      <c r="C232">
+        <v>48</v>
+      </c>
+      <c r="D232" t="s">
+        <v>1152</v>
+      </c>
+      <c r="E232" t="s">
+        <v>55</v>
+      </c>
+      <c r="F232" t="s">
+        <v>20</v>
+      </c>
+      <c r="G232" t="s">
+        <v>21</v>
+      </c>
+      <c r="H232">
+        <v>180000</v>
+      </c>
+      <c r="I232">
+        <v>180000</v>
+      </c>
+      <c r="J232" t="s">
+        <v>22</v>
+      </c>
+      <c r="K232" t="s">
+        <v>57</v>
+      </c>
+      <c r="L232" t="s">
+        <v>1148</v>
+      </c>
+      <c r="M232" t="s">
+        <v>25</v>
+      </c>
+      <c r="N232" t="s">
+        <v>26</v>
+      </c>
+      <c r="O232" t="s">
+        <v>1153</v>
+      </c>
+      <c r="P232" t="s">
+        <v>1154</v>
+      </c>
+      <c r="Q232" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="233" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>17</v>
+      </c>
+      <c r="B233">
+        <v>40</v>
+      </c>
+      <c r="C233">
+        <v>35</v>
+      </c>
+      <c r="D233" t="s">
+        <v>1156</v>
+      </c>
+      <c r="E233" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F233" t="s">
+        <v>1157</v>
+      </c>
+      <c r="G233" t="s">
+        <v>21</v>
+      </c>
+      <c r="H233">
+        <v>300000</v>
+      </c>
+      <c r="I233">
+        <v>300000</v>
+      </c>
+      <c r="J233" t="s">
+        <v>22</v>
+      </c>
+      <c r="K233" t="s">
+        <v>119</v>
+      </c>
+      <c r="L233" t="s">
+        <v>1148</v>
+      </c>
+      <c r="M233" t="s">
+        <v>39</v>
+      </c>
+      <c r="N233" t="s">
+        <v>26</v>
+      </c>
+      <c r="O233" t="s">
+        <v>1158</v>
+      </c>
+      <c r="P233" t="s">
+        <v>1159</v>
+      </c>
+      <c r="Q233" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="234" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>17</v>
+      </c>
+      <c r="B234">
+        <v>32</v>
+      </c>
+      <c r="C234">
+        <v>35</v>
+      </c>
+      <c r="D234" t="s">
+        <v>1161</v>
+      </c>
+      <c r="E234" t="s">
+        <v>55</v>
+      </c>
+      <c r="F234" t="s">
+        <v>1162</v>
+      </c>
+      <c r="G234" t="s">
+        <v>21</v>
+      </c>
+      <c r="J234" t="s">
+        <v>38</v>
+      </c>
+      <c r="K234" t="s">
+        <v>130</v>
+      </c>
+      <c r="L234" t="s">
+        <v>1148</v>
+      </c>
+      <c r="M234" t="s">
+        <v>39</v>
+      </c>
+      <c r="N234" t="s">
+        <v>26</v>
+      </c>
+      <c r="O234" t="s">
+        <v>1163</v>
+      </c>
+      <c r="P234" t="s">
+        <v>1164</v>
+      </c>
+      <c r="Q234" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="235" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>17</v>
+      </c>
+      <c r="B235">
+        <v>72</v>
+      </c>
+      <c r="C235">
+        <v>70</v>
+      </c>
+      <c r="D235" t="s">
+        <v>305</v>
+      </c>
+      <c r="E235" t="s">
+        <v>627</v>
+      </c>
+      <c r="F235" t="s">
+        <v>185</v>
+      </c>
+      <c r="G235" t="s">
+        <v>21</v>
+      </c>
+      <c r="J235" t="s">
+        <v>38</v>
+      </c>
+      <c r="K235" t="s">
+        <v>130</v>
+      </c>
+      <c r="L235" t="s">
+        <v>1148</v>
+      </c>
+      <c r="M235" t="s">
+        <v>32</v>
+      </c>
+      <c r="N235" t="s">
+        <v>26</v>
+      </c>
+      <c r="O235" t="s">
+        <v>1166</v>
+      </c>
+      <c r="P235" t="s">
+        <v>1167</v>
+      </c>
+      <c r="Q235" t="s">
+        <v>1168</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:Q1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17033,7 +17421,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q119"/>
+  <dimension ref="A1:Q126"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -17114,7 +17502,7 @@
         <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>1147</v>
+        <v>1169</v>
       </c>
       <c r="E2" t="s">
         <v>55</v>
@@ -17123,7 +17511,7 @@
         <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="H2">
         <v>217800</v>
@@ -17144,16 +17532,16 @@
         <v>25</v>
       </c>
       <c r="N2" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O2" t="s">
-        <v>1150</v>
+        <v>1172</v>
       </c>
       <c r="P2" t="s">
-        <v>1151</v>
+        <v>1173</v>
       </c>
       <c r="Q2" t="s">
-        <v>1152</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -17167,16 +17555,16 @@
         <v>45</v>
       </c>
       <c r="D3" t="s">
-        <v>1153</v>
+        <v>1175</v>
       </c>
       <c r="E3" t="s">
         <v>55</v>
       </c>
       <c r="F3" t="s">
-        <v>1154</v>
+        <v>1176</v>
       </c>
       <c r="G3" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="H3">
         <v>219100</v>
@@ -17197,16 +17585,16 @@
         <v>25</v>
       </c>
       <c r="N3" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O3" t="s">
-        <v>1155</v>
+        <v>1177</v>
       </c>
       <c r="P3" t="s">
-        <v>1156</v>
+        <v>1178</v>
       </c>
       <c r="Q3" t="s">
-        <v>1157</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
@@ -17226,10 +17614,10 @@
         <v>846</v>
       </c>
       <c r="F4" t="s">
-        <v>1158</v>
+        <v>1180</v>
       </c>
       <c r="G4" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J4" t="s">
         <v>38</v>
@@ -17244,16 +17632,16 @@
         <v>39</v>
       </c>
       <c r="N4" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O4" t="s">
-        <v>1159</v>
+        <v>1181</v>
       </c>
       <c r="P4" t="s">
-        <v>1160</v>
+        <v>1182</v>
       </c>
       <c r="Q4" t="s">
-        <v>1161</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -17267,16 +17655,16 @@
         <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>1162</v>
+        <v>1184</v>
       </c>
       <c r="E5" t="s">
-        <v>1163</v>
+        <v>1185</v>
       </c>
       <c r="F5" t="s">
-        <v>1164</v>
+        <v>1186</v>
       </c>
       <c r="G5" t="s">
-        <v>1165</v>
+        <v>1187</v>
       </c>
       <c r="J5" t="s">
         <v>38</v>
@@ -17291,16 +17679,16 @@
         <v>39</v>
       </c>
       <c r="N5" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O5" t="s">
-        <v>1166</v>
+        <v>1188</v>
       </c>
       <c r="P5" t="s">
-        <v>1167</v>
+        <v>1189</v>
       </c>
       <c r="Q5" t="s">
-        <v>1168</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -17314,16 +17702,16 @@
         <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>1169</v>
+        <v>1191</v>
       </c>
       <c r="E6" t="s">
+        <v>1192</v>
+      </c>
+      <c r="F6" t="s">
+        <v>1193</v>
+      </c>
+      <c r="G6" t="s">
         <v>1170</v>
-      </c>
-      <c r="F6" t="s">
-        <v>1171</v>
-      </c>
-      <c r="G6" t="s">
-        <v>1148</v>
       </c>
       <c r="J6" t="s">
         <v>38</v>
@@ -17338,16 +17726,16 @@
         <v>39</v>
       </c>
       <c r="N6" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O6" t="s">
-        <v>1172</v>
+        <v>1194</v>
       </c>
       <c r="P6" t="s">
-        <v>1173</v>
+        <v>1195</v>
       </c>
       <c r="Q6" t="s">
-        <v>1174</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -17361,16 +17749,16 @@
         <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>1175</v>
+        <v>1197</v>
       </c>
       <c r="E7" t="s">
+        <v>1192</v>
+      </c>
+      <c r="F7" t="s">
+        <v>1198</v>
+      </c>
+      <c r="G7" t="s">
         <v>1170</v>
-      </c>
-      <c r="F7" t="s">
-        <v>1176</v>
-      </c>
-      <c r="G7" t="s">
-        <v>1148</v>
       </c>
       <c r="J7" t="s">
         <v>38</v>
@@ -17385,16 +17773,16 @@
         <v>39</v>
       </c>
       <c r="N7" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O7" t="s">
-        <v>1177</v>
+        <v>1199</v>
       </c>
       <c r="P7" t="s">
-        <v>1178</v>
+        <v>1200</v>
       </c>
       <c r="Q7" t="s">
-        <v>1179</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -17408,16 +17796,16 @@
         <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>1180</v>
+        <v>1202</v>
       </c>
       <c r="E8" t="s">
+        <v>1192</v>
+      </c>
+      <c r="F8" t="s">
+        <v>1193</v>
+      </c>
+      <c r="G8" t="s">
         <v>1170</v>
-      </c>
-      <c r="F8" t="s">
-        <v>1171</v>
-      </c>
-      <c r="G8" t="s">
-        <v>1148</v>
       </c>
       <c r="J8" t="s">
         <v>38</v>
@@ -17432,16 +17820,16 @@
         <v>39</v>
       </c>
       <c r="N8" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O8" t="s">
-        <v>1181</v>
+        <v>1203</v>
       </c>
       <c r="P8" t="s">
-        <v>1182</v>
+        <v>1204</v>
       </c>
       <c r="Q8" t="s">
-        <v>1183</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -17455,16 +17843,16 @@
         <v>5</v>
       </c>
       <c r="D9" t="s">
-        <v>1184</v>
+        <v>1206</v>
       </c>
       <c r="E9" t="s">
-        <v>1185</v>
+        <v>1207</v>
       </c>
       <c r="F9" t="s">
-        <v>1186</v>
+        <v>1208</v>
       </c>
       <c r="G9" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J9" t="s">
         <v>38</v>
@@ -17479,16 +17867,16 @@
         <v>39</v>
       </c>
       <c r="N9" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O9" t="s">
-        <v>1187</v>
+        <v>1209</v>
       </c>
       <c r="P9" t="s">
-        <v>1188</v>
+        <v>1210</v>
       </c>
       <c r="Q9" t="s">
-        <v>1189</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -17502,16 +17890,16 @@
         <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>1190</v>
+        <v>1212</v>
       </c>
       <c r="E10" t="s">
-        <v>1185</v>
+        <v>1207</v>
       </c>
       <c r="F10" t="s">
-        <v>1191</v>
+        <v>1213</v>
       </c>
       <c r="G10" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J10" t="s">
         <v>38</v>
@@ -17526,16 +17914,16 @@
         <v>39</v>
       </c>
       <c r="N10" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O10" t="s">
-        <v>1192</v>
+        <v>1214</v>
       </c>
       <c r="P10" t="s">
-        <v>1193</v>
+        <v>1215</v>
       </c>
       <c r="Q10" t="s">
-        <v>1194</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -17549,16 +17937,16 @@
         <v>5</v>
       </c>
       <c r="D11" t="s">
-        <v>1195</v>
+        <v>1217</v>
       </c>
       <c r="E11" t="s">
-        <v>1185</v>
+        <v>1207</v>
       </c>
       <c r="F11" t="s">
-        <v>1186</v>
+        <v>1208</v>
       </c>
       <c r="G11" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J11" t="s">
         <v>38</v>
@@ -17573,16 +17961,16 @@
         <v>39</v>
       </c>
       <c r="N11" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O11" t="s">
-        <v>1196</v>
+        <v>1218</v>
       </c>
       <c r="P11" t="s">
-        <v>1197</v>
+        <v>1219</v>
       </c>
       <c r="Q11" t="s">
-        <v>1198</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -17596,16 +17984,16 @@
         <v>5</v>
       </c>
       <c r="D12" t="s">
-        <v>1199</v>
+        <v>1221</v>
       </c>
       <c r="E12" t="s">
-        <v>1185</v>
+        <v>1207</v>
       </c>
       <c r="F12" t="s">
-        <v>1186</v>
+        <v>1208</v>
       </c>
       <c r="G12" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J12" t="s">
         <v>38</v>
@@ -17620,16 +18008,16 @@
         <v>39</v>
       </c>
       <c r="N12" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O12" t="s">
-        <v>1200</v>
+        <v>1222</v>
       </c>
       <c r="P12" t="s">
-        <v>1201</v>
+        <v>1223</v>
       </c>
       <c r="Q12" t="s">
-        <v>1202</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
@@ -17643,16 +18031,16 @@
         <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>1203</v>
+        <v>1225</v>
       </c>
       <c r="E13" t="s">
-        <v>1185</v>
+        <v>1207</v>
       </c>
       <c r="F13" t="s">
-        <v>1186</v>
+        <v>1208</v>
       </c>
       <c r="G13" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J13" t="s">
         <v>38</v>
@@ -17667,16 +18055,16 @@
         <v>39</v>
       </c>
       <c r="N13" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O13" t="s">
-        <v>1204</v>
+        <v>1226</v>
       </c>
       <c r="P13" t="s">
-        <v>1205</v>
+        <v>1227</v>
       </c>
       <c r="Q13" t="s">
-        <v>1206</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
@@ -17690,16 +18078,16 @@
         <v>5</v>
       </c>
       <c r="D14" t="s">
+        <v>1229</v>
+      </c>
+      <c r="E14" t="s">
         <v>1207</v>
       </c>
-      <c r="E14" t="s">
-        <v>1185</v>
-      </c>
       <c r="F14" t="s">
-        <v>1186</v>
+        <v>1208</v>
       </c>
       <c r="G14" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J14" t="s">
         <v>38</v>
@@ -17714,16 +18102,16 @@
         <v>39</v>
       </c>
       <c r="N14" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O14" t="s">
-        <v>1208</v>
+        <v>1230</v>
       </c>
       <c r="P14" t="s">
-        <v>1209</v>
+        <v>1231</v>
       </c>
       <c r="Q14" t="s">
-        <v>1210</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -17737,16 +18125,16 @@
         <v>40</v>
       </c>
       <c r="D15" t="s">
-        <v>1211</v>
+        <v>1233</v>
       </c>
       <c r="E15" t="s">
-        <v>1185</v>
+        <v>1207</v>
       </c>
       <c r="F15" t="s">
-        <v>1186</v>
+        <v>1208</v>
       </c>
       <c r="G15" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J15" t="s">
         <v>38</v>
@@ -17761,16 +18149,16 @@
         <v>39</v>
       </c>
       <c r="N15" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O15" t="s">
-        <v>1212</v>
+        <v>1234</v>
       </c>
       <c r="P15" t="s">
-        <v>1213</v>
+        <v>1235</v>
       </c>
       <c r="Q15" t="s">
-        <v>1214</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
@@ -17784,16 +18172,16 @@
         <v>45</v>
       </c>
       <c r="D16" t="s">
-        <v>1215</v>
+        <v>1237</v>
       </c>
       <c r="E16" t="s">
-        <v>1185</v>
+        <v>1207</v>
       </c>
       <c r="F16" t="s">
-        <v>1186</v>
+        <v>1208</v>
       </c>
       <c r="G16" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J16" t="s">
         <v>38</v>
@@ -17808,16 +18196,16 @@
         <v>39</v>
       </c>
       <c r="N16" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O16" t="s">
-        <v>1216</v>
+        <v>1238</v>
       </c>
       <c r="P16" t="s">
-        <v>1217</v>
+        <v>1239</v>
       </c>
       <c r="Q16" t="s">
-        <v>1218</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
@@ -17831,16 +18219,16 @@
         <v>3</v>
       </c>
       <c r="D17" t="s">
-        <v>1219</v>
+        <v>1241</v>
       </c>
       <c r="E17" t="s">
-        <v>1185</v>
+        <v>1207</v>
       </c>
       <c r="F17" t="s">
-        <v>1186</v>
+        <v>1208</v>
       </c>
       <c r="G17" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J17" t="s">
         <v>38</v>
@@ -17855,16 +18243,16 @@
         <v>39</v>
       </c>
       <c r="N17" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O17" t="s">
-        <v>1220</v>
+        <v>1242</v>
       </c>
       <c r="P17" t="s">
-        <v>1221</v>
+        <v>1243</v>
       </c>
       <c r="Q17" t="s">
-        <v>1222</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
@@ -17878,7 +18266,7 @@
         <v>42</v>
       </c>
       <c r="D18" t="s">
-        <v>1223</v>
+        <v>1245</v>
       </c>
       <c r="E18" t="s">
         <v>55</v>
@@ -17887,7 +18275,7 @@
         <v>20</v>
       </c>
       <c r="G18" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J18" t="s">
         <v>38</v>
@@ -17902,16 +18290,16 @@
         <v>39</v>
       </c>
       <c r="N18" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O18" t="s">
-        <v>1224</v>
+        <v>1246</v>
       </c>
       <c r="P18" t="s">
-        <v>1225</v>
+        <v>1247</v>
       </c>
       <c r="Q18" t="s">
-        <v>1226</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -17925,7 +18313,7 @@
         <v>40</v>
       </c>
       <c r="D19" t="s">
-        <v>1227</v>
+        <v>1249</v>
       </c>
       <c r="E19" t="s">
         <v>55</v>
@@ -17934,7 +18322,7 @@
         <v>20</v>
       </c>
       <c r="G19" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J19" t="s">
         <v>38</v>
@@ -17949,16 +18337,16 @@
         <v>39</v>
       </c>
       <c r="N19" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O19" t="s">
-        <v>1228</v>
+        <v>1250</v>
       </c>
       <c r="P19" t="s">
-        <v>1229</v>
+        <v>1251</v>
       </c>
       <c r="Q19" t="s">
-        <v>1230</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -17978,10 +18366,10 @@
         <v>55</v>
       </c>
       <c r="F20" t="s">
-        <v>1231</v>
+        <v>1253</v>
       </c>
       <c r="G20" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="H20">
         <v>180000</v>
@@ -18002,16 +18390,16 @@
         <v>25</v>
       </c>
       <c r="N20" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O20" t="s">
-        <v>1232</v>
+        <v>1254</v>
       </c>
       <c r="P20" t="s">
-        <v>1233</v>
+        <v>1255</v>
       </c>
       <c r="Q20" t="s">
-        <v>1234</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
@@ -18025,7 +18413,7 @@
         <v>52</v>
       </c>
       <c r="D21" t="s">
-        <v>1235</v>
+        <v>1257</v>
       </c>
       <c r="E21" t="s">
         <v>55</v>
@@ -18034,7 +18422,7 @@
         <v>20</v>
       </c>
       <c r="G21" t="s">
-        <v>1165</v>
+        <v>1187</v>
       </c>
       <c r="H21">
         <v>180000</v>
@@ -18055,16 +18443,16 @@
         <v>25</v>
       </c>
       <c r="N21" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O21" t="s">
-        <v>1236</v>
+        <v>1258</v>
       </c>
       <c r="P21" t="s">
-        <v>1237</v>
+        <v>1259</v>
       </c>
       <c r="Q21" t="s">
-        <v>1238</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -18078,7 +18466,7 @@
         <v>55</v>
       </c>
       <c r="D22" t="s">
-        <v>1239</v>
+        <v>1261</v>
       </c>
       <c r="E22" t="s">
         <v>55</v>
@@ -18087,7 +18475,7 @@
         <v>20</v>
       </c>
       <c r="G22" t="s">
-        <v>1165</v>
+        <v>1187</v>
       </c>
       <c r="H22">
         <v>180000</v>
@@ -18108,16 +18496,16 @@
         <v>25</v>
       </c>
       <c r="N22" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O22" t="s">
-        <v>1240</v>
+        <v>1262</v>
       </c>
       <c r="P22" t="s">
-        <v>1241</v>
+        <v>1263</v>
       </c>
       <c r="Q22" t="s">
-        <v>1242</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
@@ -18131,16 +18519,16 @@
         <v>48</v>
       </c>
       <c r="D23" t="s">
-        <v>1243</v>
+        <v>1265</v>
       </c>
       <c r="E23" t="s">
         <v>55</v>
       </c>
       <c r="F23" t="s">
-        <v>1244</v>
+        <v>1266</v>
       </c>
       <c r="G23" t="s">
-        <v>1165</v>
+        <v>1187</v>
       </c>
       <c r="H23">
         <v>219100</v>
@@ -18161,16 +18549,16 @@
         <v>25</v>
       </c>
       <c r="N23" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O23" t="s">
-        <v>1245</v>
+        <v>1267</v>
       </c>
       <c r="P23" t="s">
-        <v>1246</v>
+        <v>1268</v>
       </c>
       <c r="Q23" t="s">
-        <v>1247</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
@@ -18184,16 +18572,16 @@
         <v>45</v>
       </c>
       <c r="D24" t="s">
-        <v>1248</v>
+        <v>1270</v>
       </c>
       <c r="E24" t="s">
         <v>55</v>
       </c>
       <c r="F24" t="s">
-        <v>1249</v>
+        <v>1271</v>
       </c>
       <c r="G24" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="H24">
         <v>180000</v>
@@ -18214,16 +18602,16 @@
         <v>25</v>
       </c>
       <c r="N24" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O24" t="s">
-        <v>1250</v>
+        <v>1272</v>
       </c>
       <c r="P24" t="s">
-        <v>1251</v>
+        <v>1273</v>
       </c>
       <c r="Q24" t="s">
-        <v>1252</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
@@ -18237,7 +18625,7 @@
         <v>30</v>
       </c>
       <c r="D25" t="s">
-        <v>1253</v>
+        <v>1275</v>
       </c>
       <c r="E25" t="s">
         <v>55</v>
@@ -18246,7 +18634,7 @@
         <v>20</v>
       </c>
       <c r="G25" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="H25">
         <v>219100</v>
@@ -18267,16 +18655,16 @@
         <v>39</v>
       </c>
       <c r="N25" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O25" t="s">
-        <v>1254</v>
+        <v>1276</v>
       </c>
       <c r="P25" t="s">
-        <v>1255</v>
+        <v>1277</v>
       </c>
       <c r="Q25" t="s">
-        <v>1256</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
@@ -18290,7 +18678,7 @@
         <v>45</v>
       </c>
       <c r="D26" t="s">
-        <v>1257</v>
+        <v>1279</v>
       </c>
       <c r="E26" t="s">
         <v>55</v>
@@ -18299,7 +18687,7 @@
         <v>20</v>
       </c>
       <c r="G26" t="s">
-        <v>1165</v>
+        <v>1187</v>
       </c>
       <c r="H26">
         <v>219100</v>
@@ -18320,16 +18708,16 @@
         <v>25</v>
       </c>
       <c r="N26" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O26" t="s">
-        <v>1258</v>
+        <v>1280</v>
       </c>
       <c r="P26" t="s">
-        <v>1259</v>
+        <v>1281</v>
       </c>
       <c r="Q26" t="s">
-        <v>1260</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
@@ -18343,16 +18731,16 @@
         <v>30</v>
       </c>
       <c r="D27" t="s">
-        <v>1261</v>
+        <v>1283</v>
       </c>
       <c r="E27" t="s">
         <v>55</v>
       </c>
       <c r="F27" t="s">
-        <v>1262</v>
+        <v>1284</v>
       </c>
       <c r="G27" t="s">
-        <v>1165</v>
+        <v>1187</v>
       </c>
       <c r="J27" t="s">
         <v>38</v>
@@ -18367,16 +18755,16 @@
         <v>39</v>
       </c>
       <c r="N27" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O27" t="s">
-        <v>1263</v>
+        <v>1285</v>
       </c>
       <c r="P27" t="s">
-        <v>1264</v>
+        <v>1286</v>
       </c>
       <c r="Q27" t="s">
-        <v>1265</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
@@ -18390,16 +18778,16 @@
         <v>58</v>
       </c>
       <c r="D28" t="s">
-        <v>1266</v>
+        <v>1288</v>
       </c>
       <c r="E28" t="s">
-        <v>1267</v>
+        <v>1289</v>
       </c>
       <c r="F28" t="s">
-        <v>1268</v>
+        <v>1290</v>
       </c>
       <c r="G28" t="s">
-        <v>1165</v>
+        <v>1187</v>
       </c>
       <c r="H28">
         <v>257000</v>
@@ -18420,16 +18808,16 @@
         <v>25</v>
       </c>
       <c r="N28" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O28" t="s">
-        <v>1269</v>
+        <v>1291</v>
       </c>
       <c r="P28" t="s">
-        <v>1270</v>
+        <v>1292</v>
       </c>
       <c r="Q28" t="s">
-        <v>1271</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
@@ -18446,13 +18834,13 @@
         <v>311</v>
       </c>
       <c r="E29" t="s">
-        <v>1272</v>
+        <v>1294</v>
       </c>
       <c r="F29" t="s">
-        <v>1273</v>
+        <v>1295</v>
       </c>
       <c r="G29" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="H29">
         <v>200000</v>
@@ -18473,16 +18861,16 @@
         <v>39</v>
       </c>
       <c r="N29" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O29" t="s">
-        <v>1274</v>
+        <v>1296</v>
       </c>
       <c r="P29" t="s">
-        <v>1275</v>
+        <v>1297</v>
       </c>
       <c r="Q29" t="s">
-        <v>1276</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
@@ -18496,16 +18884,16 @@
         <v>20</v>
       </c>
       <c r="D30" t="s">
-        <v>1277</v>
+        <v>1299</v>
       </c>
       <c r="E30" t="s">
         <v>846</v>
       </c>
       <c r="F30" t="s">
-        <v>1278</v>
+        <v>1300</v>
       </c>
       <c r="G30" t="s">
-        <v>1165</v>
+        <v>1187</v>
       </c>
       <c r="J30" t="s">
         <v>38</v>
@@ -18520,16 +18908,16 @@
         <v>39</v>
       </c>
       <c r="N30" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O30" t="s">
-        <v>1279</v>
+        <v>1301</v>
       </c>
       <c r="P30" t="s">
-        <v>1280</v>
+        <v>1302</v>
       </c>
       <c r="Q30" t="s">
-        <v>1281</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
@@ -18549,10 +18937,10 @@
         <v>846</v>
       </c>
       <c r="F31" t="s">
-        <v>1282</v>
+        <v>1304</v>
       </c>
       <c r="G31" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J31" t="s">
         <v>38</v>
@@ -18567,16 +18955,16 @@
         <v>39</v>
       </c>
       <c r="N31" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O31" t="s">
-        <v>1283</v>
+        <v>1305</v>
       </c>
       <c r="P31" t="s">
-        <v>1284</v>
+        <v>1306</v>
       </c>
       <c r="Q31" t="s">
-        <v>1285</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
@@ -18590,16 +18978,16 @@
         <v>15</v>
       </c>
       <c r="D32" t="s">
-        <v>1286</v>
+        <v>1308</v>
       </c>
       <c r="E32" t="s">
         <v>846</v>
       </c>
       <c r="F32" t="s">
-        <v>1287</v>
+        <v>1309</v>
       </c>
       <c r="G32" t="s">
-        <v>1165</v>
+        <v>1187</v>
       </c>
       <c r="H32">
         <v>500000</v>
@@ -18620,16 +19008,16 @@
         <v>39</v>
       </c>
       <c r="N32" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O32" t="s">
-        <v>1288</v>
+        <v>1310</v>
       </c>
       <c r="P32" t="s">
-        <v>1289</v>
+        <v>1311</v>
       </c>
       <c r="Q32" t="s">
-        <v>1290</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
@@ -18643,16 +19031,16 @@
         <v>18</v>
       </c>
       <c r="D33" t="s">
-        <v>1291</v>
+        <v>1313</v>
       </c>
       <c r="E33" t="s">
         <v>633</v>
       </c>
       <c r="F33" t="s">
-        <v>1292</v>
+        <v>1314</v>
       </c>
       <c r="G33" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="H33">
         <v>274456</v>
@@ -18673,16 +19061,16 @@
         <v>39</v>
       </c>
       <c r="N33" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O33" t="s">
-        <v>1293</v>
+        <v>1315</v>
       </c>
       <c r="P33" t="s">
-        <v>1294</v>
+        <v>1316</v>
       </c>
       <c r="Q33" t="s">
-        <v>1295</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
@@ -18696,16 +19084,16 @@
         <v>30</v>
       </c>
       <c r="D34" t="s">
-        <v>1296</v>
+        <v>1318</v>
       </c>
       <c r="E34" t="s">
         <v>633</v>
       </c>
       <c r="F34" t="s">
-        <v>1297</v>
+        <v>1319</v>
       </c>
       <c r="G34" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J34" t="s">
         <v>38</v>
@@ -18720,16 +19108,16 @@
         <v>39</v>
       </c>
       <c r="N34" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O34" t="s">
-        <v>1298</v>
+        <v>1320</v>
       </c>
       <c r="P34" t="s">
-        <v>1299</v>
+        <v>1321</v>
       </c>
       <c r="Q34" t="s">
-        <v>1300</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
@@ -18743,16 +19131,16 @@
         <v>22</v>
       </c>
       <c r="D35" t="s">
-        <v>1301</v>
+        <v>1323</v>
       </c>
       <c r="E35" t="s">
         <v>633</v>
       </c>
       <c r="F35" t="s">
-        <v>1302</v>
+        <v>1324</v>
       </c>
       <c r="G35" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J35" t="s">
         <v>38</v>
@@ -18767,16 +19155,16 @@
         <v>39</v>
       </c>
       <c r="N35" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O35" t="s">
-        <v>1303</v>
+        <v>1325</v>
       </c>
       <c r="P35" t="s">
-        <v>1304</v>
+        <v>1326</v>
       </c>
       <c r="Q35" t="s">
-        <v>1305</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
@@ -18790,16 +19178,16 @@
         <v>48</v>
       </c>
       <c r="D36" t="s">
-        <v>1306</v>
+        <v>1328</v>
       </c>
       <c r="E36" t="s">
         <v>633</v>
       </c>
       <c r="F36" t="s">
-        <v>1307</v>
+        <v>1329</v>
       </c>
       <c r="G36" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J36" t="s">
         <v>38</v>
@@ -18814,16 +19202,16 @@
         <v>25</v>
       </c>
       <c r="N36" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O36" t="s">
-        <v>1308</v>
+        <v>1330</v>
       </c>
       <c r="P36" t="s">
-        <v>1309</v>
+        <v>1331</v>
       </c>
       <c r="Q36" t="s">
-        <v>1310</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
@@ -18837,16 +19225,16 @@
         <v>25</v>
       </c>
       <c r="D37" t="s">
-        <v>1311</v>
+        <v>1333</v>
       </c>
       <c r="E37" t="s">
         <v>633</v>
       </c>
       <c r="F37" t="s">
-        <v>1191</v>
+        <v>1213</v>
       </c>
       <c r="G37" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J37" t="s">
         <v>38</v>
@@ -18861,16 +19249,16 @@
         <v>39</v>
       </c>
       <c r="N37" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O37" t="s">
-        <v>1312</v>
+        <v>1334</v>
       </c>
       <c r="P37" t="s">
-        <v>1313</v>
+        <v>1335</v>
       </c>
       <c r="Q37" t="s">
-        <v>1314</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
@@ -18884,16 +19272,16 @@
         <v>40</v>
       </c>
       <c r="D38" t="s">
-        <v>1315</v>
+        <v>1337</v>
       </c>
       <c r="E38" t="s">
         <v>633</v>
       </c>
       <c r="F38" t="s">
-        <v>1316</v>
+        <v>1338</v>
       </c>
       <c r="G38" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J38" t="s">
         <v>38</v>
@@ -18908,16 +19296,16 @@
         <v>39</v>
       </c>
       <c r="N38" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O38" t="s">
-        <v>1317</v>
+        <v>1339</v>
       </c>
       <c r="P38" t="s">
-        <v>1318</v>
+        <v>1340</v>
       </c>
       <c r="Q38" t="s">
-        <v>1319</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
@@ -18931,16 +19319,16 @@
         <v>70</v>
       </c>
       <c r="D39" t="s">
-        <v>1320</v>
+        <v>1342</v>
       </c>
       <c r="E39" t="s">
-        <v>1321</v>
+        <v>1343</v>
       </c>
       <c r="F39" t="s">
-        <v>1322</v>
+        <v>1344</v>
       </c>
       <c r="G39" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J39" t="s">
         <v>38</v>
@@ -18955,16 +19343,16 @@
         <v>39</v>
       </c>
       <c r="N39" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O39" t="s">
-        <v>1323</v>
+        <v>1345</v>
       </c>
       <c r="P39" t="s">
-        <v>1324</v>
+        <v>1346</v>
       </c>
       <c r="Q39" t="s">
-        <v>1325</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
@@ -18978,16 +19366,16 @@
         <v>58</v>
       </c>
       <c r="D40" t="s">
-        <v>1326</v>
+        <v>1348</v>
       </c>
       <c r="E40" t="s">
-        <v>1327</v>
+        <v>1349</v>
       </c>
       <c r="F40" t="s">
-        <v>1191</v>
+        <v>1213</v>
       </c>
       <c r="G40" t="s">
-        <v>1165</v>
+        <v>1187</v>
       </c>
       <c r="J40" t="s">
         <v>38</v>
@@ -19002,16 +19390,16 @@
         <v>39</v>
       </c>
       <c r="N40" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O40" t="s">
-        <v>1328</v>
+        <v>1350</v>
       </c>
       <c r="P40" t="s">
-        <v>1329</v>
+        <v>1351</v>
       </c>
       <c r="Q40" t="s">
-        <v>1330</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
@@ -19025,16 +19413,16 @@
         <v>32</v>
       </c>
       <c r="D41" t="s">
-        <v>1331</v>
+        <v>1353</v>
       </c>
       <c r="E41" t="s">
-        <v>1332</v>
+        <v>1354</v>
       </c>
       <c r="F41" t="s">
-        <v>1333</v>
+        <v>1355</v>
       </c>
       <c r="G41" t="s">
-        <v>1165</v>
+        <v>1187</v>
       </c>
       <c r="J41" t="s">
         <v>38</v>
@@ -19049,16 +19437,16 @@
         <v>39</v>
       </c>
       <c r="N41" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O41" t="s">
-        <v>1334</v>
+        <v>1356</v>
       </c>
       <c r="P41" t="s">
-        <v>1335</v>
+        <v>1357</v>
       </c>
       <c r="Q41" t="s">
-        <v>1336</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
@@ -19072,16 +19460,16 @@
         <v>4</v>
       </c>
       <c r="D42" t="s">
-        <v>1337</v>
+        <v>1359</v>
       </c>
       <c r="E42" t="s">
-        <v>1338</v>
+        <v>1360</v>
       </c>
       <c r="F42" t="s">
-        <v>1339</v>
+        <v>1361</v>
       </c>
       <c r="G42" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J42" t="s">
         <v>38</v>
@@ -19096,16 +19484,16 @@
         <v>39</v>
       </c>
       <c r="N42" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O42" t="s">
-        <v>1340</v>
+        <v>1362</v>
       </c>
       <c r="P42" t="s">
-        <v>1341</v>
+        <v>1363</v>
       </c>
       <c r="Q42" t="s">
-        <v>1342</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
@@ -19119,16 +19507,16 @@
         <v>25</v>
       </c>
       <c r="D43" t="s">
-        <v>1343</v>
+        <v>1365</v>
       </c>
       <c r="E43" t="s">
-        <v>1344</v>
+        <v>1366</v>
       </c>
       <c r="F43" t="s">
-        <v>1176</v>
+        <v>1198</v>
       </c>
       <c r="G43" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J43" t="s">
         <v>38</v>
@@ -19143,16 +19531,16 @@
         <v>39</v>
       </c>
       <c r="N43" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O43" t="s">
-        <v>1345</v>
+        <v>1367</v>
       </c>
       <c r="P43" t="s">
-        <v>1346</v>
+        <v>1368</v>
       </c>
       <c r="Q43" t="s">
-        <v>1347</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
@@ -19166,16 +19554,16 @@
         <v>30</v>
       </c>
       <c r="D44" t="s">
-        <v>1348</v>
+        <v>1370</v>
       </c>
       <c r="E44" t="s">
-        <v>1349</v>
+        <v>1371</v>
       </c>
       <c r="F44" t="s">
-        <v>1350</v>
+        <v>1372</v>
       </c>
       <c r="G44" t="s">
-        <v>1165</v>
+        <v>1187</v>
       </c>
       <c r="J44" t="s">
         <v>38</v>
@@ -19190,16 +19578,16 @@
         <v>39</v>
       </c>
       <c r="N44" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O44" t="s">
-        <v>1351</v>
+        <v>1373</v>
       </c>
       <c r="P44" t="s">
-        <v>1352</v>
+        <v>1374</v>
       </c>
       <c r="Q44" t="s">
-        <v>1353</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
@@ -19213,16 +19601,16 @@
         <v>52</v>
       </c>
       <c r="D45" t="s">
-        <v>1354</v>
+        <v>1376</v>
       </c>
       <c r="E45" t="s">
         <v>55</v>
       </c>
       <c r="F45" t="s">
-        <v>1355</v>
+        <v>1377</v>
       </c>
       <c r="G45" t="s">
-        <v>1165</v>
+        <v>1187</v>
       </c>
       <c r="H45">
         <v>180000</v>
@@ -19243,16 +19631,16 @@
         <v>25</v>
       </c>
       <c r="N45" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O45" t="s">
-        <v>1356</v>
+        <v>1378</v>
       </c>
       <c r="P45" t="s">
-        <v>1357</v>
+        <v>1379</v>
       </c>
       <c r="Q45" t="s">
-        <v>1358</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
@@ -19266,7 +19654,7 @@
         <v>50</v>
       </c>
       <c r="D46" t="s">
-        <v>1359</v>
+        <v>1381</v>
       </c>
       <c r="E46" t="s">
         <v>55</v>
@@ -19275,7 +19663,7 @@
         <v>20</v>
       </c>
       <c r="G46" t="s">
-        <v>1165</v>
+        <v>1187</v>
       </c>
       <c r="H46">
         <v>180000</v>
@@ -19296,16 +19684,16 @@
         <v>25</v>
       </c>
       <c r="N46" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O46" t="s">
-        <v>1360</v>
+        <v>1382</v>
       </c>
       <c r="P46" t="s">
-        <v>1361</v>
+        <v>1383</v>
       </c>
       <c r="Q46" t="s">
-        <v>1362</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
@@ -19319,7 +19707,7 @@
         <v>46</v>
       </c>
       <c r="D47" t="s">
-        <v>1363</v>
+        <v>1385</v>
       </c>
       <c r="E47" t="s">
         <v>55</v>
@@ -19328,7 +19716,7 @@
         <v>20</v>
       </c>
       <c r="G47" t="s">
-        <v>1165</v>
+        <v>1187</v>
       </c>
       <c r="H47">
         <v>180000</v>
@@ -19349,16 +19737,16 @@
         <v>25</v>
       </c>
       <c r="N47" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O47" t="s">
-        <v>1364</v>
+        <v>1386</v>
       </c>
       <c r="P47" t="s">
-        <v>1365</v>
+        <v>1387</v>
       </c>
       <c r="Q47" t="s">
-        <v>1366</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
@@ -19372,7 +19760,7 @@
         <v>38</v>
       </c>
       <c r="D48" t="s">
-        <v>1367</v>
+        <v>1389</v>
       </c>
       <c r="E48" t="s">
         <v>55</v>
@@ -19381,7 +19769,7 @@
         <v>20</v>
       </c>
       <c r="G48" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="H48">
         <v>217800</v>
@@ -19402,16 +19790,16 @@
         <v>39</v>
       </c>
       <c r="N48" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O48" t="s">
-        <v>1368</v>
+        <v>1390</v>
       </c>
       <c r="P48" t="s">
-        <v>1369</v>
+        <v>1391</v>
       </c>
       <c r="Q48" t="s">
-        <v>1370</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
@@ -19431,10 +19819,10 @@
         <v>55</v>
       </c>
       <c r="F49" t="s">
-        <v>1371</v>
+        <v>1393</v>
       </c>
       <c r="G49" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="H49">
         <v>180000</v>
@@ -19455,16 +19843,16 @@
         <v>25</v>
       </c>
       <c r="N49" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O49" t="s">
-        <v>1372</v>
+        <v>1394</v>
       </c>
       <c r="P49" t="s">
-        <v>1373</v>
+        <v>1395</v>
       </c>
       <c r="Q49" t="s">
-        <v>1374</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
@@ -19478,16 +19866,16 @@
         <v>45</v>
       </c>
       <c r="D50" t="s">
-        <v>1375</v>
+        <v>1397</v>
       </c>
       <c r="E50" t="s">
         <v>55</v>
       </c>
       <c r="F50" t="s">
-        <v>1376</v>
+        <v>1398</v>
       </c>
       <c r="G50" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="H50">
         <v>219100</v>
@@ -19508,16 +19896,16 @@
         <v>25</v>
       </c>
       <c r="N50" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O50" t="s">
-        <v>1377</v>
+        <v>1399</v>
       </c>
       <c r="P50" t="s">
-        <v>1378</v>
+        <v>1400</v>
       </c>
       <c r="Q50" t="s">
-        <v>1379</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
@@ -19531,16 +19919,16 @@
         <v>42</v>
       </c>
       <c r="D51" t="s">
-        <v>1380</v>
+        <v>1402</v>
       </c>
       <c r="E51" t="s">
         <v>55</v>
       </c>
       <c r="F51" t="s">
-        <v>1381</v>
+        <v>1403</v>
       </c>
       <c r="G51" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="H51">
         <v>180000</v>
@@ -19561,16 +19949,16 @@
         <v>25</v>
       </c>
       <c r="N51" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O51" t="s">
-        <v>1382</v>
+        <v>1404</v>
       </c>
       <c r="P51" t="s">
-        <v>1383</v>
+        <v>1405</v>
       </c>
       <c r="Q51" t="s">
-        <v>1384</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
@@ -19584,7 +19972,7 @@
         <v>32</v>
       </c>
       <c r="D52" t="s">
-        <v>1385</v>
+        <v>1407</v>
       </c>
       <c r="E52" t="s">
         <v>55</v>
@@ -19593,7 +19981,7 @@
         <v>20</v>
       </c>
       <c r="G52" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="H52">
         <v>219100</v>
@@ -19614,16 +20002,16 @@
         <v>39</v>
       </c>
       <c r="N52" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O52" t="s">
-        <v>1386</v>
+        <v>1408</v>
       </c>
       <c r="P52" t="s">
-        <v>1387</v>
+        <v>1409</v>
       </c>
       <c r="Q52" t="s">
-        <v>1388</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
@@ -19637,7 +20025,7 @@
         <v>35</v>
       </c>
       <c r="D53" t="s">
-        <v>1389</v>
+        <v>1411</v>
       </c>
       <c r="E53" t="s">
         <v>55</v>
@@ -19646,7 +20034,7 @@
         <v>20</v>
       </c>
       <c r="G53" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="H53">
         <v>219100</v>
@@ -19667,16 +20055,16 @@
         <v>39</v>
       </c>
       <c r="N53" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O53" t="s">
-        <v>1390</v>
+        <v>1412</v>
       </c>
       <c r="P53" t="s">
-        <v>1391</v>
+        <v>1413</v>
       </c>
       <c r="Q53" t="s">
-        <v>1392</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
@@ -19690,16 +20078,16 @@
         <v>40</v>
       </c>
       <c r="D54" t="s">
-        <v>1393</v>
+        <v>1415</v>
       </c>
       <c r="E54" t="s">
         <v>55</v>
       </c>
       <c r="F54" t="s">
-        <v>1394</v>
+        <v>1416</v>
       </c>
       <c r="G54" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="H54">
         <v>219100</v>
@@ -19720,16 +20108,16 @@
         <v>25</v>
       </c>
       <c r="N54" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O54" t="s">
-        <v>1395</v>
+        <v>1417</v>
       </c>
       <c r="P54" t="s">
-        <v>1396</v>
+        <v>1418</v>
       </c>
       <c r="Q54" t="s">
-        <v>1397</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
@@ -19743,7 +20131,7 @@
         <v>38</v>
       </c>
       <c r="D55" t="s">
-        <v>1398</v>
+        <v>1420</v>
       </c>
       <c r="E55" t="s">
         <v>55</v>
@@ -19752,7 +20140,7 @@
         <v>592</v>
       </c>
       <c r="G55" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="H55">
         <v>219100</v>
@@ -19773,16 +20161,16 @@
         <v>39</v>
       </c>
       <c r="N55" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O55" t="s">
-        <v>1399</v>
+        <v>1421</v>
       </c>
       <c r="P55" t="s">
-        <v>1400</v>
+        <v>1422</v>
       </c>
       <c r="Q55" t="s">
-        <v>1401</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
@@ -19796,7 +20184,7 @@
         <v>40</v>
       </c>
       <c r="D56" t="s">
-        <v>1402</v>
+        <v>1424</v>
       </c>
       <c r="E56" t="s">
         <v>55</v>
@@ -19805,7 +20193,7 @@
         <v>20</v>
       </c>
       <c r="G56" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="H56">
         <v>219100</v>
@@ -19826,16 +20214,16 @@
         <v>25</v>
       </c>
       <c r="N56" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O56" t="s">
-        <v>1403</v>
+        <v>1425</v>
       </c>
       <c r="P56" t="s">
-        <v>1404</v>
+        <v>1426</v>
       </c>
       <c r="Q56" t="s">
-        <v>1405</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
@@ -19849,16 +20237,16 @@
         <v>33</v>
       </c>
       <c r="D57" t="s">
-        <v>1406</v>
+        <v>1428</v>
       </c>
       <c r="E57" t="s">
         <v>55</v>
       </c>
       <c r="F57" t="s">
-        <v>1407</v>
+        <v>1429</v>
       </c>
       <c r="G57" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="H57">
         <v>219100</v>
@@ -19879,16 +20267,16 @@
         <v>39</v>
       </c>
       <c r="N57" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O57" t="s">
-        <v>1408</v>
+        <v>1430</v>
       </c>
       <c r="P57" t="s">
-        <v>1409</v>
+        <v>1431</v>
       </c>
       <c r="Q57" t="s">
-        <v>1410</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
@@ -19902,16 +20290,16 @@
         <v>48</v>
       </c>
       <c r="D58" t="s">
-        <v>1411</v>
+        <v>1433</v>
       </c>
       <c r="E58" t="s">
-        <v>1267</v>
+        <v>1289</v>
       </c>
       <c r="F58" t="s">
-        <v>1412</v>
+        <v>1434</v>
       </c>
       <c r="G58" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J58" t="s">
         <v>38</v>
@@ -19926,16 +20314,16 @@
         <v>25</v>
       </c>
       <c r="N58" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O58" t="s">
-        <v>1413</v>
+        <v>1435</v>
       </c>
       <c r="P58" t="s">
-        <v>1414</v>
+        <v>1436</v>
       </c>
       <c r="Q58" t="s">
-        <v>1415</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
@@ -19949,16 +20337,16 @@
         <v>40</v>
       </c>
       <c r="D59" t="s">
-        <v>1416</v>
+        <v>1438</v>
       </c>
       <c r="E59" t="s">
-        <v>1272</v>
+        <v>1294</v>
       </c>
       <c r="F59" t="s">
-        <v>1417</v>
+        <v>1439</v>
       </c>
       <c r="G59" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="H59">
         <v>184200</v>
@@ -19979,16 +20367,16 @@
         <v>25</v>
       </c>
       <c r="N59" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O59" t="s">
-        <v>1418</v>
+        <v>1440</v>
       </c>
       <c r="P59" t="s">
-        <v>1419</v>
+        <v>1441</v>
       </c>
       <c r="Q59" t="s">
-        <v>1420</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
@@ -20002,16 +20390,16 @@
         <v>30</v>
       </c>
       <c r="D60" t="s">
-        <v>1421</v>
+        <v>1443</v>
       </c>
       <c r="E60" t="s">
-        <v>1272</v>
+        <v>1294</v>
       </c>
       <c r="F60" t="s">
-        <v>1422</v>
+        <v>1444</v>
       </c>
       <c r="G60" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="H60">
         <v>200000</v>
@@ -20032,16 +20420,16 @@
         <v>39</v>
       </c>
       <c r="N60" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O60" t="s">
-        <v>1423</v>
+        <v>1445</v>
       </c>
       <c r="P60" t="s">
-        <v>1424</v>
+        <v>1446</v>
       </c>
       <c r="Q60" t="s">
-        <v>1425</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
@@ -20055,7 +20443,7 @@
         <v>30</v>
       </c>
       <c r="D61" t="s">
-        <v>1426</v>
+        <v>1448</v>
       </c>
       <c r="E61" t="s">
         <v>846</v>
@@ -20064,7 +20452,7 @@
         <v>855</v>
       </c>
       <c r="G61" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J61" t="s">
         <v>38</v>
@@ -20079,16 +20467,16 @@
         <v>39</v>
       </c>
       <c r="N61" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O61" t="s">
-        <v>1427</v>
+        <v>1449</v>
       </c>
       <c r="P61" t="s">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="Q61" t="s">
-        <v>1429</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
@@ -20108,10 +20496,10 @@
         <v>846</v>
       </c>
       <c r="F62" t="s">
-        <v>1282</v>
+        <v>1304</v>
       </c>
       <c r="G62" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J62" t="s">
         <v>38</v>
@@ -20126,16 +20514,16 @@
         <v>39</v>
       </c>
       <c r="N62" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O62" t="s">
-        <v>1430</v>
+        <v>1452</v>
       </c>
       <c r="P62" t="s">
-        <v>1431</v>
+        <v>1453</v>
       </c>
       <c r="Q62" t="s">
-        <v>1432</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
@@ -20149,7 +20537,7 @@
         <v>32</v>
       </c>
       <c r="D63" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="E63" t="s">
         <v>846</v>
@@ -20158,7 +20546,7 @@
         <v>855</v>
       </c>
       <c r="G63" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J63" t="s">
         <v>38</v>
@@ -20173,16 +20561,16 @@
         <v>39</v>
       </c>
       <c r="N63" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O63" t="s">
-        <v>1434</v>
+        <v>1456</v>
       </c>
       <c r="P63" t="s">
-        <v>1435</v>
+        <v>1457</v>
       </c>
       <c r="Q63" t="s">
-        <v>1436</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
@@ -20196,16 +20584,16 @@
         <v>45</v>
       </c>
       <c r="D64" t="s">
-        <v>1437</v>
+        <v>1459</v>
       </c>
       <c r="E64" t="s">
         <v>633</v>
       </c>
       <c r="F64" t="s">
-        <v>1438</v>
+        <v>1460</v>
       </c>
       <c r="G64" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J64" t="s">
         <v>38</v>
@@ -20220,16 +20608,16 @@
         <v>25</v>
       </c>
       <c r="N64" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O64" t="s">
-        <v>1439</v>
+        <v>1461</v>
       </c>
       <c r="P64" t="s">
-        <v>1440</v>
+        <v>1462</v>
       </c>
       <c r="Q64" t="s">
-        <v>1441</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
@@ -20243,16 +20631,16 @@
         <v>35</v>
       </c>
       <c r="D65" t="s">
-        <v>1442</v>
+        <v>1464</v>
       </c>
       <c r="E65" t="s">
         <v>633</v>
       </c>
       <c r="F65" t="s">
-        <v>1443</v>
+        <v>1465</v>
       </c>
       <c r="G65" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J65" t="s">
         <v>38</v>
@@ -20267,16 +20655,16 @@
         <v>39</v>
       </c>
       <c r="N65" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O65" t="s">
-        <v>1444</v>
+        <v>1466</v>
       </c>
       <c r="P65" t="s">
-        <v>1445</v>
+        <v>1467</v>
       </c>
       <c r="Q65" t="s">
-        <v>1446</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
@@ -20290,7 +20678,7 @@
         <v>35</v>
       </c>
       <c r="D66" t="s">
-        <v>1447</v>
+        <v>1469</v>
       </c>
       <c r="E66" t="s">
         <v>633</v>
@@ -20299,7 +20687,7 @@
         <v>118</v>
       </c>
       <c r="G66" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J66" t="s">
         <v>38</v>
@@ -20314,16 +20702,16 @@
         <v>39</v>
       </c>
       <c r="N66" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O66" t="s">
-        <v>1448</v>
+        <v>1470</v>
       </c>
       <c r="P66" t="s">
-        <v>1449</v>
+        <v>1471</v>
       </c>
       <c r="Q66" t="s">
-        <v>1450</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
@@ -20337,16 +20725,16 @@
         <v>15</v>
       </c>
       <c r="D67" t="s">
-        <v>1451</v>
+        <v>1473</v>
       </c>
       <c r="E67" t="s">
         <v>633</v>
       </c>
       <c r="F67" t="s">
-        <v>1452</v>
+        <v>1474</v>
       </c>
       <c r="G67" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J67" t="s">
         <v>38</v>
@@ -20361,16 +20749,16 @@
         <v>39</v>
       </c>
       <c r="N67" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O67" t="s">
-        <v>1453</v>
+        <v>1475</v>
       </c>
       <c r="P67" t="s">
-        <v>1454</v>
+        <v>1476</v>
       </c>
       <c r="Q67" t="s">
-        <v>1455</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
@@ -20384,16 +20772,16 @@
         <v>25</v>
       </c>
       <c r="D68" t="s">
-        <v>1456</v>
+        <v>1478</v>
       </c>
       <c r="E68" t="s">
         <v>633</v>
       </c>
       <c r="F68" t="s">
-        <v>1457</v>
+        <v>1479</v>
       </c>
       <c r="G68" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J68" t="s">
         <v>38</v>
@@ -20408,16 +20796,16 @@
         <v>39</v>
       </c>
       <c r="N68" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O68" t="s">
-        <v>1458</v>
+        <v>1480</v>
       </c>
       <c r="P68" t="s">
-        <v>1459</v>
+        <v>1481</v>
       </c>
       <c r="Q68" t="s">
-        <v>1460</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
@@ -20431,16 +20819,16 @@
         <v>30</v>
       </c>
       <c r="D69" t="s">
-        <v>1461</v>
+        <v>1483</v>
       </c>
       <c r="E69" t="s">
         <v>633</v>
       </c>
       <c r="F69" t="s">
-        <v>1462</v>
+        <v>1484</v>
       </c>
       <c r="G69" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J69" t="s">
         <v>38</v>
@@ -20455,16 +20843,16 @@
         <v>39</v>
       </c>
       <c r="N69" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O69" t="s">
-        <v>1463</v>
+        <v>1485</v>
       </c>
       <c r="P69" t="s">
-        <v>1464</v>
+        <v>1486</v>
       </c>
       <c r="Q69" t="s">
-        <v>1465</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
@@ -20484,10 +20872,10 @@
         <v>55</v>
       </c>
       <c r="F70" t="s">
-        <v>1422</v>
+        <v>1444</v>
       </c>
       <c r="G70" t="s">
-        <v>1165</v>
+        <v>1187</v>
       </c>
       <c r="J70" t="s">
         <v>38</v>
@@ -20502,16 +20890,16 @@
         <v>39</v>
       </c>
       <c r="N70" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O70" t="s">
-        <v>1466</v>
+        <v>1488</v>
       </c>
       <c r="P70" t="s">
-        <v>1467</v>
+        <v>1489</v>
       </c>
       <c r="Q70" t="s">
-        <v>1468</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
@@ -20531,10 +20919,10 @@
         <v>55</v>
       </c>
       <c r="F71" t="s">
-        <v>1469</v>
+        <v>1491</v>
       </c>
       <c r="G71" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J71" t="s">
         <v>38</v>
@@ -20549,16 +20937,16 @@
         <v>25</v>
       </c>
       <c r="N71" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O71" t="s">
-        <v>1470</v>
+        <v>1492</v>
       </c>
       <c r="P71" t="s">
-        <v>1471</v>
+        <v>1493</v>
       </c>
       <c r="Q71" t="s">
-        <v>1472</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
@@ -20581,7 +20969,7 @@
         <v>912</v>
       </c>
       <c r="G72" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="H72">
         <v>180000</v>
@@ -20602,16 +20990,16 @@
         <v>39</v>
       </c>
       <c r="N72" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O72" t="s">
-        <v>1473</v>
+        <v>1495</v>
       </c>
       <c r="P72" t="s">
-        <v>1474</v>
+        <v>1496</v>
       </c>
       <c r="Q72" t="s">
-        <v>1475</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
@@ -20631,10 +21019,10 @@
         <v>55</v>
       </c>
       <c r="F73" t="s">
-        <v>1476</v>
+        <v>1498</v>
       </c>
       <c r="G73" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="H73">
         <v>180000</v>
@@ -20655,16 +21043,16 @@
         <v>39</v>
       </c>
       <c r="N73" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O73" t="s">
-        <v>1477</v>
+        <v>1499</v>
       </c>
       <c r="P73" t="s">
-        <v>1478</v>
+        <v>1500</v>
       </c>
       <c r="Q73" t="s">
-        <v>1479</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
@@ -20678,16 +21066,16 @@
         <v>20</v>
       </c>
       <c r="D74" t="s">
-        <v>1480</v>
+        <v>1502</v>
       </c>
       <c r="E74" t="s">
         <v>957</v>
       </c>
       <c r="F74" t="s">
-        <v>1481</v>
+        <v>1503</v>
       </c>
       <c r="G74" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J74" t="s">
         <v>38</v>
@@ -20702,16 +21090,16 @@
         <v>39</v>
       </c>
       <c r="N74" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O74" t="s">
-        <v>1482</v>
+        <v>1504</v>
       </c>
       <c r="P74" t="s">
-        <v>1483</v>
+        <v>1505</v>
       </c>
       <c r="Q74" t="s">
-        <v>1484</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
@@ -20725,7 +21113,7 @@
         <v>50</v>
       </c>
       <c r="D75" t="s">
-        <v>1485</v>
+        <v>1507</v>
       </c>
       <c r="E75" t="s">
         <v>957</v>
@@ -20734,7 +21122,7 @@
         <v>20</v>
       </c>
       <c r="G75" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="H75">
         <v>250000</v>
@@ -20755,16 +21143,16 @@
         <v>25</v>
       </c>
       <c r="N75" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O75" t="s">
-        <v>1486</v>
+        <v>1508</v>
       </c>
       <c r="P75" t="s">
-        <v>1487</v>
+        <v>1509</v>
       </c>
       <c r="Q75" t="s">
-        <v>1488</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
@@ -20778,7 +21166,7 @@
         <v>55</v>
       </c>
       <c r="D76" t="s">
-        <v>1489</v>
+        <v>1511</v>
       </c>
       <c r="E76" t="s">
         <v>957</v>
@@ -20787,7 +21175,7 @@
         <v>20</v>
       </c>
       <c r="G76" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="H76">
         <v>200000</v>
@@ -20808,16 +21196,16 @@
         <v>25</v>
       </c>
       <c r="N76" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O76" t="s">
-        <v>1490</v>
+        <v>1512</v>
       </c>
       <c r="P76" t="s">
-        <v>1491</v>
+        <v>1513</v>
       </c>
       <c r="Q76" t="s">
-        <v>1492</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
@@ -20831,7 +21219,7 @@
         <v>52</v>
       </c>
       <c r="D77" t="s">
-        <v>1493</v>
+        <v>1515</v>
       </c>
       <c r="E77" t="s">
         <v>957</v>
@@ -20840,7 +21228,7 @@
         <v>20</v>
       </c>
       <c r="G77" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="H77">
         <v>250000</v>
@@ -20861,16 +21249,16 @@
         <v>25</v>
       </c>
       <c r="N77" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O77" t="s">
-        <v>1494</v>
+        <v>1516</v>
       </c>
       <c r="P77" t="s">
-        <v>1495</v>
+        <v>1517</v>
       </c>
       <c r="Q77" t="s">
-        <v>1496</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
@@ -20884,7 +21272,7 @@
         <v>53</v>
       </c>
       <c r="D78" t="s">
-        <v>1497</v>
+        <v>1519</v>
       </c>
       <c r="E78" t="s">
         <v>957</v>
@@ -20893,7 +21281,7 @@
         <v>20</v>
       </c>
       <c r="G78" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="H78">
         <v>200000</v>
@@ -20914,16 +21302,16 @@
         <v>25</v>
       </c>
       <c r="N78" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O78" t="s">
-        <v>1498</v>
+        <v>1520</v>
       </c>
       <c r="P78" t="s">
-        <v>1499</v>
+        <v>1521</v>
       </c>
       <c r="Q78" t="s">
-        <v>1500</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
@@ -20937,7 +21325,7 @@
         <v>50</v>
       </c>
       <c r="D79" t="s">
-        <v>1501</v>
+        <v>1523</v>
       </c>
       <c r="E79" t="s">
         <v>957</v>
@@ -20946,7 +21334,7 @@
         <v>20</v>
       </c>
       <c r="G79" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="H79">
         <v>200000</v>
@@ -20967,16 +21355,16 @@
         <v>25</v>
       </c>
       <c r="N79" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O79" t="s">
-        <v>1502</v>
+        <v>1524</v>
       </c>
       <c r="P79" t="s">
-        <v>1503</v>
+        <v>1525</v>
       </c>
       <c r="Q79" t="s">
-        <v>1504</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
@@ -20990,7 +21378,7 @@
         <v>55</v>
       </c>
       <c r="D80" t="s">
-        <v>1505</v>
+        <v>1527</v>
       </c>
       <c r="E80" t="s">
         <v>957</v>
@@ -20999,7 +21387,7 @@
         <v>20</v>
       </c>
       <c r="G80" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="H80">
         <v>250000</v>
@@ -21020,16 +21408,16 @@
         <v>25</v>
       </c>
       <c r="N80" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O80" t="s">
-        <v>1506</v>
+        <v>1528</v>
       </c>
       <c r="P80" t="s">
-        <v>1507</v>
+        <v>1529</v>
       </c>
       <c r="Q80" t="s">
-        <v>1508</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
@@ -21043,16 +21431,16 @@
         <v>45</v>
       </c>
       <c r="D81" t="s">
-        <v>1509</v>
+        <v>1531</v>
       </c>
       <c r="E81" t="s">
-        <v>1510</v>
+        <v>1532</v>
       </c>
       <c r="F81" t="s">
-        <v>1511</v>
+        <v>1533</v>
       </c>
       <c r="G81" t="s">
-        <v>1165</v>
+        <v>1187</v>
       </c>
       <c r="H81">
         <v>154000</v>
@@ -21073,16 +21461,16 @@
         <v>39</v>
       </c>
       <c r="N81" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O81" t="s">
-        <v>1512</v>
+        <v>1534</v>
       </c>
       <c r="P81" t="s">
-        <v>1513</v>
+        <v>1535</v>
       </c>
       <c r="Q81" t="s">
-        <v>1514</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
@@ -21105,7 +21493,7 @@
         <v>592</v>
       </c>
       <c r="G82" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="H82">
         <v>180000</v>
@@ -21126,16 +21514,16 @@
         <v>25</v>
       </c>
       <c r="N82" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O82" t="s">
-        <v>1515</v>
+        <v>1537</v>
       </c>
       <c r="P82" t="s">
-        <v>1516</v>
+        <v>1538</v>
       </c>
       <c r="Q82" t="s">
-        <v>1517</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
@@ -21155,10 +21543,10 @@
         <v>55</v>
       </c>
       <c r="F83" t="s">
-        <v>1371</v>
+        <v>1393</v>
       </c>
       <c r="G83" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="H83">
         <v>219100</v>
@@ -21179,16 +21567,16 @@
         <v>39</v>
       </c>
       <c r="N83" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O83" t="s">
-        <v>1518</v>
+        <v>1540</v>
       </c>
       <c r="P83" t="s">
-        <v>1519</v>
+        <v>1541</v>
       </c>
       <c r="Q83" t="s">
-        <v>1520</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
@@ -21202,16 +21590,16 @@
         <v>25</v>
       </c>
       <c r="D84" t="s">
-        <v>1521</v>
+        <v>1543</v>
       </c>
       <c r="E84" t="s">
         <v>55</v>
       </c>
       <c r="F84" t="s">
-        <v>1522</v>
+        <v>1162</v>
       </c>
       <c r="G84" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J84" t="s">
         <v>38</v>
@@ -21226,16 +21614,16 @@
         <v>39</v>
       </c>
       <c r="N84" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O84" t="s">
-        <v>1523</v>
+        <v>1544</v>
       </c>
       <c r="P84" t="s">
-        <v>1524</v>
+        <v>1545</v>
       </c>
       <c r="Q84" t="s">
-        <v>1525</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
@@ -21255,10 +21643,10 @@
         <v>846</v>
       </c>
       <c r="F85" t="s">
-        <v>1191</v>
+        <v>1213</v>
       </c>
       <c r="G85" t="s">
-        <v>1165</v>
+        <v>1187</v>
       </c>
       <c r="J85" t="s">
         <v>38</v>
@@ -21273,16 +21661,16 @@
         <v>39</v>
       </c>
       <c r="N85" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O85" t="s">
-        <v>1526</v>
+        <v>1547</v>
       </c>
       <c r="P85" t="s">
-        <v>1527</v>
+        <v>1548</v>
       </c>
       <c r="Q85" t="s">
-        <v>1528</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
@@ -21296,16 +21684,16 @@
         <v>15</v>
       </c>
       <c r="D86" t="s">
-        <v>1529</v>
+        <v>1550</v>
       </c>
       <c r="E86" t="s">
-        <v>1530</v>
+        <v>1551</v>
       </c>
       <c r="F86" t="s">
-        <v>1339</v>
+        <v>1361</v>
       </c>
       <c r="G86" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J86" t="s">
         <v>38</v>
@@ -21320,16 +21708,16 @@
         <v>39</v>
       </c>
       <c r="N86" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O86" t="s">
-        <v>1531</v>
+        <v>1552</v>
       </c>
       <c r="P86" t="s">
-        <v>1532</v>
+        <v>1553</v>
       </c>
       <c r="Q86" t="s">
-        <v>1533</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
@@ -21343,16 +21731,16 @@
         <v>12</v>
       </c>
       <c r="D87" t="s">
-        <v>1534</v>
+        <v>1555</v>
       </c>
       <c r="E87" t="s">
-        <v>1535</v>
+        <v>1556</v>
       </c>
       <c r="F87" t="s">
-        <v>1536</v>
+        <v>1557</v>
       </c>
       <c r="G87" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J87" t="s">
         <v>38</v>
@@ -21367,16 +21755,16 @@
         <v>39</v>
       </c>
       <c r="N87" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O87" t="s">
-        <v>1537</v>
+        <v>1558</v>
       </c>
       <c r="P87" t="s">
-        <v>1538</v>
+        <v>1559</v>
       </c>
       <c r="Q87" t="s">
-        <v>1539</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
@@ -21390,16 +21778,16 @@
         <v>42</v>
       </c>
       <c r="D88" t="s">
-        <v>1540</v>
+        <v>1561</v>
       </c>
       <c r="E88" t="s">
         <v>55</v>
       </c>
       <c r="F88" t="s">
-        <v>1541</v>
+        <v>1562</v>
       </c>
       <c r="G88" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="H88">
         <v>180000</v>
@@ -21420,16 +21808,16 @@
         <v>25</v>
       </c>
       <c r="N88" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O88" t="s">
-        <v>1542</v>
+        <v>1563</v>
       </c>
       <c r="P88" t="s">
-        <v>1543</v>
+        <v>1564</v>
       </c>
       <c r="Q88" t="s">
-        <v>1544</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
@@ -21443,16 +21831,16 @@
         <v>22</v>
       </c>
       <c r="D89" t="s">
-        <v>1545</v>
+        <v>1566</v>
       </c>
       <c r="E89" t="s">
-        <v>1272</v>
+        <v>1294</v>
       </c>
       <c r="F89" t="s">
-        <v>1546</v>
+        <v>1567</v>
       </c>
       <c r="G89" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="H89">
         <v>200000</v>
@@ -21473,16 +21861,16 @@
         <v>39</v>
       </c>
       <c r="N89" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O89" t="s">
-        <v>1547</v>
+        <v>1568</v>
       </c>
       <c r="P89" t="s">
-        <v>1548</v>
+        <v>1569</v>
       </c>
       <c r="Q89" t="s">
-        <v>1549</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
@@ -21496,16 +21884,16 @@
         <v>28</v>
       </c>
       <c r="D90" t="s">
-        <v>1550</v>
+        <v>1571</v>
       </c>
       <c r="E90" t="s">
-        <v>1551</v>
+        <v>1572</v>
       </c>
       <c r="F90" t="s">
-        <v>1522</v>
+        <v>1162</v>
       </c>
       <c r="G90" t="s">
-        <v>1165</v>
+        <v>1187</v>
       </c>
       <c r="J90" t="s">
         <v>38</v>
@@ -21520,16 +21908,16 @@
         <v>39</v>
       </c>
       <c r="N90" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O90" t="s">
-        <v>1552</v>
+        <v>1573</v>
       </c>
       <c r="P90" t="s">
-        <v>1553</v>
+        <v>1574</v>
       </c>
       <c r="Q90" t="s">
-        <v>1554</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
@@ -21543,16 +21931,16 @@
         <v>5</v>
       </c>
       <c r="D91" t="s">
-        <v>1555</v>
+        <v>1576</v>
       </c>
       <c r="E91" t="s">
-        <v>1556</v>
+        <v>1577</v>
       </c>
       <c r="F91" t="s">
-        <v>1557</v>
+        <v>1578</v>
       </c>
       <c r="G91" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J91" t="s">
         <v>38</v>
@@ -21567,16 +21955,16 @@
         <v>39</v>
       </c>
       <c r="N91" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O91" t="s">
-        <v>1558</v>
+        <v>1579</v>
       </c>
       <c r="P91" t="s">
-        <v>1559</v>
+        <v>1580</v>
       </c>
       <c r="Q91" t="s">
-        <v>1560</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
@@ -21596,10 +21984,10 @@
         <v>55</v>
       </c>
       <c r="F92" t="s">
-        <v>1561</v>
+        <v>1582</v>
       </c>
       <c r="G92" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J92" t="s">
         <v>38</v>
@@ -21614,16 +22002,16 @@
         <v>25</v>
       </c>
       <c r="N92" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O92" t="s">
-        <v>1562</v>
+        <v>1583</v>
       </c>
       <c r="P92" t="s">
-        <v>1563</v>
+        <v>1584</v>
       </c>
       <c r="Q92" t="s">
-        <v>1564</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
@@ -21637,16 +22025,16 @@
         <v>35</v>
       </c>
       <c r="D93" t="s">
-        <v>1565</v>
+        <v>1586</v>
       </c>
       <c r="E93" t="s">
-        <v>1566</v>
+        <v>1587</v>
       </c>
       <c r="F93" t="s">
-        <v>1333</v>
+        <v>1355</v>
       </c>
       <c r="G93" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J93" t="s">
         <v>38</v>
@@ -21661,16 +22049,16 @@
         <v>39</v>
       </c>
       <c r="N93" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O93" t="s">
-        <v>1567</v>
+        <v>1588</v>
       </c>
       <c r="P93" t="s">
-        <v>1568</v>
+        <v>1589</v>
       </c>
       <c r="Q93" t="s">
-        <v>1569</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
@@ -21684,16 +22072,16 @@
         <v>55</v>
       </c>
       <c r="D94" t="s">
-        <v>1570</v>
+        <v>1591</v>
       </c>
       <c r="E94" t="s">
         <v>55</v>
       </c>
       <c r="F94" t="s">
-        <v>1371</v>
+        <v>1393</v>
       </c>
       <c r="G94" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="H94">
         <v>219100</v>
@@ -21708,22 +22096,22 @@
         <v>57</v>
       </c>
       <c r="L94" t="s">
-        <v>1571</v>
+        <v>1592</v>
       </c>
       <c r="M94" t="s">
         <v>25</v>
       </c>
       <c r="N94" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O94" t="s">
-        <v>1572</v>
+        <v>1593</v>
       </c>
       <c r="P94" t="s">
-        <v>1573</v>
+        <v>1594</v>
       </c>
       <c r="Q94" t="s">
-        <v>1574</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
@@ -21737,16 +22125,16 @@
         <v>50</v>
       </c>
       <c r="D95" t="s">
-        <v>1575</v>
+        <v>1596</v>
       </c>
       <c r="E95" t="s">
-        <v>1272</v>
+        <v>1294</v>
       </c>
       <c r="F95" t="s">
         <v>20</v>
       </c>
       <c r="G95" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="H95">
         <v>200000</v>
@@ -21761,22 +22149,22 @@
         <v>57</v>
       </c>
       <c r="L95" t="s">
-        <v>1571</v>
+        <v>1592</v>
       </c>
       <c r="M95" t="s">
         <v>25</v>
       </c>
       <c r="N95" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O95" t="s">
-        <v>1576</v>
+        <v>1597</v>
       </c>
       <c r="P95" t="s">
-        <v>1577</v>
+        <v>1598</v>
       </c>
       <c r="Q95" t="s">
-        <v>1578</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
@@ -21790,16 +22178,16 @@
         <v>12</v>
       </c>
       <c r="D96" t="s">
-        <v>1579</v>
+        <v>1600</v>
       </c>
       <c r="E96" t="s">
-        <v>1580</v>
+        <v>1601</v>
       </c>
       <c r="F96" t="s">
-        <v>1522</v>
+        <v>1162</v>
       </c>
       <c r="G96" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J96" t="s">
         <v>38</v>
@@ -21808,22 +22196,22 @@
         <v>130</v>
       </c>
       <c r="L96" t="s">
-        <v>1571</v>
+        <v>1592</v>
       </c>
       <c r="M96" t="s">
         <v>39</v>
       </c>
       <c r="N96" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O96" t="s">
-        <v>1581</v>
+        <v>1602</v>
       </c>
       <c r="P96" t="s">
-        <v>1582</v>
+        <v>1603</v>
       </c>
       <c r="Q96" t="s">
-        <v>1583</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
@@ -21837,16 +22225,16 @@
         <v>12</v>
       </c>
       <c r="D97" t="s">
-        <v>1584</v>
+        <v>1605</v>
       </c>
       <c r="E97" t="s">
-        <v>1580</v>
+        <v>1601</v>
       </c>
       <c r="F97" t="s">
-        <v>1522</v>
+        <v>1162</v>
       </c>
       <c r="G97" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J97" t="s">
         <v>38</v>
@@ -21855,22 +22243,22 @@
         <v>130</v>
       </c>
       <c r="L97" t="s">
-        <v>1571</v>
+        <v>1592</v>
       </c>
       <c r="M97" t="s">
         <v>39</v>
       </c>
       <c r="N97" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O97" t="s">
-        <v>1585</v>
+        <v>1606</v>
       </c>
       <c r="P97" t="s">
-        <v>1586</v>
+        <v>1607</v>
       </c>
       <c r="Q97" t="s">
-        <v>1587</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
@@ -21884,16 +22272,16 @@
         <v>3</v>
       </c>
       <c r="D98" t="s">
-        <v>1588</v>
+        <v>1609</v>
       </c>
       <c r="E98" t="s">
-        <v>1580</v>
+        <v>1601</v>
       </c>
       <c r="F98" t="s">
-        <v>1522</v>
+        <v>1162</v>
       </c>
       <c r="G98" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J98" t="s">
         <v>38</v>
@@ -21902,22 +22290,22 @@
         <v>130</v>
       </c>
       <c r="L98" t="s">
-        <v>1571</v>
+        <v>1592</v>
       </c>
       <c r="M98" t="s">
         <v>39</v>
       </c>
       <c r="N98" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O98" t="s">
-        <v>1589</v>
+        <v>1610</v>
       </c>
       <c r="P98" t="s">
-        <v>1590</v>
+        <v>1611</v>
       </c>
       <c r="Q98" t="s">
-        <v>1591</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.25">
@@ -21931,16 +22319,16 @@
         <v>25</v>
       </c>
       <c r="D99" t="s">
-        <v>1592</v>
+        <v>1613</v>
       </c>
       <c r="E99" t="s">
-        <v>1593</v>
+        <v>1614</v>
       </c>
       <c r="F99" t="s">
-        <v>1594</v>
+        <v>1615</v>
       </c>
       <c r="G99" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J99" t="s">
         <v>38</v>
@@ -21949,22 +22337,22 @@
         <v>130</v>
       </c>
       <c r="L99" t="s">
-        <v>1571</v>
+        <v>1592</v>
       </c>
       <c r="M99" t="s">
         <v>39</v>
       </c>
       <c r="N99" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O99" t="s">
-        <v>1595</v>
+        <v>1616</v>
       </c>
       <c r="P99" t="s">
-        <v>1596</v>
+        <v>1617</v>
       </c>
       <c r="Q99" t="s">
-        <v>1597</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.25">
@@ -21978,16 +22366,16 @@
         <v>62</v>
       </c>
       <c r="D100" t="s">
-        <v>1598</v>
+        <v>1619</v>
       </c>
       <c r="E100" t="s">
-        <v>1599</v>
+        <v>1620</v>
       </c>
       <c r="F100" t="s">
-        <v>1600</v>
+        <v>1621</v>
       </c>
       <c r="G100" t="s">
-        <v>1165</v>
+        <v>1187</v>
       </c>
       <c r="J100" t="s">
         <v>38</v>
@@ -21996,22 +22384,22 @@
         <v>130</v>
       </c>
       <c r="L100" t="s">
-        <v>1571</v>
+        <v>1592</v>
       </c>
       <c r="M100" t="s">
         <v>39</v>
       </c>
       <c r="N100" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O100" t="s">
-        <v>1601</v>
+        <v>1622</v>
       </c>
       <c r="P100" t="s">
-        <v>1602</v>
+        <v>1623</v>
       </c>
       <c r="Q100" t="s">
-        <v>1603</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.25">
@@ -22025,16 +22413,16 @@
         <v>68</v>
       </c>
       <c r="D101" t="s">
-        <v>1604</v>
+        <v>1625</v>
       </c>
       <c r="E101" t="s">
-        <v>1599</v>
+        <v>1620</v>
       </c>
       <c r="F101" t="s">
-        <v>1600</v>
+        <v>1621</v>
       </c>
       <c r="G101" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J101" t="s">
         <v>38</v>
@@ -22043,22 +22431,22 @@
         <v>130</v>
       </c>
       <c r="L101" t="s">
-        <v>1571</v>
+        <v>1592</v>
       </c>
       <c r="M101" t="s">
         <v>39</v>
       </c>
       <c r="N101" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O101" t="s">
-        <v>1605</v>
+        <v>1626</v>
       </c>
       <c r="P101" t="s">
-        <v>1606</v>
+        <v>1627</v>
       </c>
       <c r="Q101" t="s">
-        <v>1607</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.25">
@@ -22078,10 +22466,10 @@
         <v>55</v>
       </c>
       <c r="F102" t="s">
-        <v>1608</v>
+        <v>1629</v>
       </c>
       <c r="G102" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="H102">
         <v>180000</v>
@@ -22102,16 +22490,16 @@
         <v>25</v>
       </c>
       <c r="N102" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O102" t="s">
-        <v>1609</v>
+        <v>1630</v>
       </c>
       <c r="P102" t="s">
-        <v>1610</v>
+        <v>1631</v>
       </c>
       <c r="Q102" t="s">
-        <v>1611</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.25">
@@ -22131,10 +22519,10 @@
         <v>55</v>
       </c>
       <c r="F103" t="s">
-        <v>1612</v>
+        <v>1633</v>
       </c>
       <c r="G103" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="H103">
         <v>180000</v>
@@ -22155,16 +22543,16 @@
         <v>25</v>
       </c>
       <c r="N103" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O103" t="s">
-        <v>1613</v>
+        <v>1634</v>
       </c>
       <c r="P103" t="s">
-        <v>1614</v>
+        <v>1635</v>
       </c>
       <c r="Q103" t="s">
-        <v>1615</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.25">
@@ -22178,16 +22566,16 @@
         <v>35</v>
       </c>
       <c r="D104" t="s">
-        <v>1616</v>
+        <v>1637</v>
       </c>
       <c r="E104" t="s">
         <v>55</v>
       </c>
       <c r="F104" t="s">
-        <v>1617</v>
+        <v>1638</v>
       </c>
       <c r="G104" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="H104">
         <v>219100</v>
@@ -22208,16 +22596,16 @@
         <v>25</v>
       </c>
       <c r="N104" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O104" t="s">
-        <v>1618</v>
+        <v>1639</v>
       </c>
       <c r="P104" t="s">
-        <v>1619</v>
+        <v>1640</v>
       </c>
       <c r="Q104" t="s">
-        <v>1620</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.25">
@@ -22231,16 +22619,16 @@
         <v>25</v>
       </c>
       <c r="D105" t="s">
-        <v>1621</v>
+        <v>1642</v>
       </c>
       <c r="E105" t="s">
         <v>633</v>
       </c>
       <c r="F105" t="s">
-        <v>1438</v>
+        <v>1460</v>
       </c>
       <c r="G105" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J105" t="s">
         <v>38</v>
@@ -22255,16 +22643,16 @@
         <v>39</v>
       </c>
       <c r="N105" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O105" t="s">
-        <v>1622</v>
+        <v>1643</v>
       </c>
       <c r="P105" t="s">
-        <v>1623</v>
+        <v>1644</v>
       </c>
       <c r="Q105" t="s">
-        <v>1624</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.25">
@@ -22278,16 +22666,16 @@
         <v>35</v>
       </c>
       <c r="D106" t="s">
-        <v>1625</v>
+        <v>1646</v>
       </c>
       <c r="E106" t="s">
-        <v>1626</v>
+        <v>1647</v>
       </c>
       <c r="F106" t="s">
-        <v>1191</v>
+        <v>1213</v>
       </c>
       <c r="G106" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J106" t="s">
         <v>38</v>
@@ -22302,16 +22690,16 @@
         <v>39</v>
       </c>
       <c r="N106" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O106" t="s">
-        <v>1627</v>
+        <v>1648</v>
       </c>
       <c r="P106" t="s">
-        <v>1628</v>
+        <v>1649</v>
       </c>
       <c r="Q106" t="s">
-        <v>1629</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.25">
@@ -22328,13 +22716,13 @@
         <v>305</v>
       </c>
       <c r="E107" t="s">
-        <v>1630</v>
+        <v>1651</v>
       </c>
       <c r="F107" t="s">
-        <v>1333</v>
+        <v>1355</v>
       </c>
       <c r="G107" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="H107">
         <v>200000</v>
@@ -22355,16 +22743,16 @@
         <v>39</v>
       </c>
       <c r="N107" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O107" t="s">
-        <v>1631</v>
+        <v>1652</v>
       </c>
       <c r="P107" t="s">
-        <v>1632</v>
+        <v>1653</v>
       </c>
       <c r="Q107" t="s">
-        <v>1633</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.25">
@@ -22378,16 +22766,16 @@
         <v>38</v>
       </c>
       <c r="D108" t="s">
-        <v>1634</v>
+        <v>1655</v>
       </c>
       <c r="E108" t="s">
-        <v>1630</v>
+        <v>1651</v>
       </c>
       <c r="F108" t="s">
-        <v>1333</v>
+        <v>1355</v>
       </c>
       <c r="G108" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="H108">
         <v>200000</v>
@@ -22408,16 +22796,16 @@
         <v>39</v>
       </c>
       <c r="N108" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O108" t="s">
-        <v>1635</v>
+        <v>1656</v>
       </c>
       <c r="P108" t="s">
-        <v>1636</v>
+        <v>1657</v>
       </c>
       <c r="Q108" t="s">
-        <v>1637</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.25">
@@ -22431,16 +22819,16 @@
         <v>40</v>
       </c>
       <c r="D109" t="s">
-        <v>1416</v>
+        <v>1438</v>
       </c>
       <c r="E109" t="s">
-        <v>1272</v>
+        <v>1294</v>
       </c>
       <c r="F109" t="s">
         <v>861</v>
       </c>
       <c r="G109" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="H109">
         <v>184200</v>
@@ -22461,16 +22849,16 @@
         <v>39</v>
       </c>
       <c r="N109" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O109" t="s">
-        <v>1638</v>
+        <v>1659</v>
       </c>
       <c r="P109" t="s">
-        <v>1639</v>
+        <v>1660</v>
       </c>
       <c r="Q109" t="s">
-        <v>1640</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.25">
@@ -22484,16 +22872,16 @@
         <v>20</v>
       </c>
       <c r="D110" t="s">
-        <v>1641</v>
+        <v>1662</v>
       </c>
       <c r="E110" t="s">
-        <v>1642</v>
+        <v>1663</v>
       </c>
       <c r="F110" t="s">
-        <v>1643</v>
+        <v>1664</v>
       </c>
       <c r="G110" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J110" t="s">
         <v>38</v>
@@ -22508,16 +22896,16 @@
         <v>39</v>
       </c>
       <c r="N110" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O110" t="s">
-        <v>1644</v>
+        <v>1665</v>
       </c>
       <c r="P110" t="s">
-        <v>1645</v>
+        <v>1666</v>
       </c>
       <c r="Q110" t="s">
-        <v>1646</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.25">
@@ -22531,16 +22919,16 @@
         <v>35</v>
       </c>
       <c r="D111" t="s">
-        <v>1647</v>
+        <v>1668</v>
       </c>
       <c r="E111" t="s">
-        <v>1648</v>
+        <v>1669</v>
       </c>
       <c r="F111" t="s">
-        <v>1649</v>
+        <v>1670</v>
       </c>
       <c r="G111" t="s">
-        <v>1165</v>
+        <v>1187</v>
       </c>
       <c r="H111">
         <v>230000</v>
@@ -22561,16 +22949,16 @@
         <v>39</v>
       </c>
       <c r="N111" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O111" t="s">
-        <v>1650</v>
+        <v>1671</v>
       </c>
       <c r="P111" t="s">
-        <v>1651</v>
+        <v>1672</v>
       </c>
       <c r="Q111" t="s">
-        <v>1652</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.25">
@@ -22590,10 +22978,10 @@
         <v>55</v>
       </c>
       <c r="F112" t="s">
-        <v>1653</v>
+        <v>1674</v>
       </c>
       <c r="G112" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="H112">
         <v>219100</v>
@@ -22614,16 +23002,16 @@
         <v>32</v>
       </c>
       <c r="N112" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O112" t="s">
-        <v>1654</v>
+        <v>1675</v>
       </c>
       <c r="P112" t="s">
-        <v>1655</v>
+        <v>1676</v>
       </c>
       <c r="Q112" t="s">
-        <v>1656</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.25">
@@ -22637,16 +23025,16 @@
         <v>25</v>
       </c>
       <c r="D113" t="s">
-        <v>1657</v>
+        <v>1678</v>
       </c>
       <c r="E113" t="s">
-        <v>1566</v>
+        <v>1587</v>
       </c>
       <c r="F113" t="s">
-        <v>1333</v>
+        <v>1355</v>
       </c>
       <c r="G113" t="s">
-        <v>1165</v>
+        <v>1187</v>
       </c>
       <c r="J113" t="s">
         <v>38</v>
@@ -22661,16 +23049,16 @@
         <v>39</v>
       </c>
       <c r="N113" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O113" t="s">
-        <v>1658</v>
+        <v>1679</v>
       </c>
       <c r="P113" t="s">
-        <v>1659</v>
+        <v>1680</v>
       </c>
       <c r="Q113" t="s">
-        <v>1660</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.25">
@@ -22684,16 +23072,16 @@
         <v>22</v>
       </c>
       <c r="D114" t="s">
-        <v>1661</v>
+        <v>1682</v>
       </c>
       <c r="E114" t="s">
-        <v>1662</v>
+        <v>1683</v>
       </c>
       <c r="F114" t="s">
-        <v>1171</v>
+        <v>1193</v>
       </c>
       <c r="G114" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J114" t="s">
         <v>38</v>
@@ -22708,16 +23096,16 @@
         <v>39</v>
       </c>
       <c r="N114" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O114" t="s">
-        <v>1663</v>
+        <v>1684</v>
       </c>
       <c r="P114" t="s">
-        <v>1664</v>
+        <v>1685</v>
       </c>
       <c r="Q114" t="s">
-        <v>1665</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.25">
@@ -22731,16 +23119,16 @@
         <v>3</v>
       </c>
       <c r="D115" t="s">
-        <v>1666</v>
+        <v>1687</v>
       </c>
       <c r="E115" t="s">
-        <v>1667</v>
+        <v>1688</v>
       </c>
       <c r="F115" t="s">
-        <v>1171</v>
+        <v>1193</v>
       </c>
       <c r="G115" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J115" t="s">
         <v>38</v>
@@ -22755,16 +23143,16 @@
         <v>39</v>
       </c>
       <c r="N115" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O115" t="s">
-        <v>1668</v>
+        <v>1689</v>
       </c>
       <c r="P115" t="s">
-        <v>1669</v>
+        <v>1690</v>
       </c>
       <c r="Q115" t="s">
-        <v>1670</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.25">
@@ -22778,16 +23166,16 @@
         <v>28</v>
       </c>
       <c r="D116" t="s">
-        <v>1671</v>
+        <v>1692</v>
       </c>
       <c r="E116" t="s">
-        <v>1672</v>
+        <v>1693</v>
       </c>
       <c r="F116" t="s">
-        <v>1522</v>
+        <v>1162</v>
       </c>
       <c r="G116" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J116" t="s">
         <v>38</v>
@@ -22802,16 +23190,16 @@
         <v>39</v>
       </c>
       <c r="N116" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O116" t="s">
-        <v>1673</v>
+        <v>1694</v>
       </c>
       <c r="P116" t="s">
-        <v>1674</v>
+        <v>1695</v>
       </c>
       <c r="Q116" t="s">
-        <v>1675</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.25">
@@ -22825,16 +23213,16 @@
         <v>45</v>
       </c>
       <c r="D117" t="s">
-        <v>1676</v>
+        <v>1697</v>
       </c>
       <c r="E117" t="s">
-        <v>1677</v>
+        <v>1698</v>
       </c>
       <c r="F117" t="s">
-        <v>1191</v>
+        <v>1213</v>
       </c>
       <c r="G117" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="J117" t="s">
         <v>38</v>
@@ -22849,16 +23237,16 @@
         <v>25</v>
       </c>
       <c r="N117" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O117" t="s">
-        <v>1678</v>
+        <v>1699</v>
       </c>
       <c r="P117" t="s">
-        <v>1679</v>
+        <v>1700</v>
       </c>
       <c r="Q117" t="s">
-        <v>1680</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.25">
@@ -22872,16 +23260,16 @@
         <v>50</v>
       </c>
       <c r="D118" t="s">
-        <v>1175</v>
+        <v>1197</v>
       </c>
       <c r="E118" t="s">
+        <v>1192</v>
+      </c>
+      <c r="F118" t="s">
+        <v>1198</v>
+      </c>
+      <c r="G118" t="s">
         <v>1170</v>
-      </c>
-      <c r="F118" t="s">
-        <v>1176</v>
-      </c>
-      <c r="G118" t="s">
-        <v>1148</v>
       </c>
       <c r="J118" t="s">
         <v>38</v>
@@ -22896,16 +23284,16 @@
         <v>25</v>
       </c>
       <c r="N118" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O118" t="s">
-        <v>1681</v>
+        <v>1702</v>
       </c>
       <c r="P118" t="s">
-        <v>1682</v>
+        <v>1703</v>
       </c>
       <c r="Q118" t="s">
-        <v>1683</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.25">
@@ -22919,16 +23307,16 @@
         <v>48</v>
       </c>
       <c r="D119" t="s">
-        <v>1684</v>
+        <v>1705</v>
       </c>
       <c r="E119" t="s">
-        <v>1510</v>
+        <v>1532</v>
       </c>
       <c r="F119" t="s">
-        <v>1685</v>
+        <v>1706</v>
       </c>
       <c r="G119" t="s">
-        <v>1165</v>
+        <v>1187</v>
       </c>
       <c r="H119">
         <v>154000</v>
@@ -22949,16 +23337,351 @@
         <v>25</v>
       </c>
       <c r="N119" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="O119" t="s">
-        <v>1686</v>
+        <v>1707</v>
       </c>
       <c r="P119" t="s">
-        <v>1687</v>
+        <v>1708</v>
       </c>
       <c r="Q119" t="s">
-        <v>1688</v>
+        <v>1709</v>
+      </c>
+    </row>
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>17</v>
+      </c>
+      <c r="B120">
+        <v>22</v>
+      </c>
+      <c r="C120">
+        <v>25</v>
+      </c>
+      <c r="D120" t="s">
+        <v>1710</v>
+      </c>
+      <c r="E120" t="s">
+        <v>1354</v>
+      </c>
+      <c r="F120" t="s">
+        <v>1355</v>
+      </c>
+      <c r="G120" t="s">
+        <v>1170</v>
+      </c>
+      <c r="J120" t="s">
+        <v>38</v>
+      </c>
+      <c r="K120" t="s">
+        <v>130</v>
+      </c>
+      <c r="L120" t="s">
+        <v>1148</v>
+      </c>
+      <c r="M120" t="s">
+        <v>39</v>
+      </c>
+      <c r="N120" t="s">
+        <v>1171</v>
+      </c>
+      <c r="O120" t="s">
+        <v>1711</v>
+      </c>
+      <c r="P120" t="s">
+        <v>1712</v>
+      </c>
+      <c r="Q120" t="s">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>17</v>
+      </c>
+      <c r="B121">
+        <v>30</v>
+      </c>
+      <c r="C121">
+        <v>32</v>
+      </c>
+      <c r="D121" t="s">
+        <v>1613</v>
+      </c>
+      <c r="E121" t="s">
+        <v>1354</v>
+      </c>
+      <c r="F121" t="s">
+        <v>1355</v>
+      </c>
+      <c r="G121" t="s">
+        <v>1170</v>
+      </c>
+      <c r="J121" t="s">
+        <v>38</v>
+      </c>
+      <c r="K121" t="s">
+        <v>130</v>
+      </c>
+      <c r="L121" t="s">
+        <v>1148</v>
+      </c>
+      <c r="M121" t="s">
+        <v>39</v>
+      </c>
+      <c r="N121" t="s">
+        <v>1171</v>
+      </c>
+      <c r="O121" t="s">
+        <v>1714</v>
+      </c>
+      <c r="P121" t="s">
+        <v>1715</v>
+      </c>
+      <c r="Q121" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>17</v>
+      </c>
+      <c r="B122">
+        <v>20</v>
+      </c>
+      <c r="C122">
+        <v>22</v>
+      </c>
+      <c r="D122" t="s">
+        <v>1202</v>
+      </c>
+      <c r="E122" t="s">
+        <v>1192</v>
+      </c>
+      <c r="F122" t="s">
+        <v>1193</v>
+      </c>
+      <c r="G122" t="s">
+        <v>1170</v>
+      </c>
+      <c r="J122" t="s">
+        <v>38</v>
+      </c>
+      <c r="K122" t="s">
+        <v>130</v>
+      </c>
+      <c r="L122" t="s">
+        <v>1148</v>
+      </c>
+      <c r="M122" t="s">
+        <v>39</v>
+      </c>
+      <c r="N122" t="s">
+        <v>1171</v>
+      </c>
+      <c r="O122" t="s">
+        <v>1717</v>
+      </c>
+      <c r="P122" t="s">
+        <v>1718</v>
+      </c>
+      <c r="Q122" t="s">
+        <v>1719</v>
+      </c>
+    </row>
+    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>17</v>
+      </c>
+      <c r="B123">
+        <v>30</v>
+      </c>
+      <c r="C123">
+        <v>55</v>
+      </c>
+      <c r="D123" t="s">
+        <v>1197</v>
+      </c>
+      <c r="E123" t="s">
+        <v>1192</v>
+      </c>
+      <c r="F123" t="s">
+        <v>1720</v>
+      </c>
+      <c r="G123" t="s">
+        <v>1170</v>
+      </c>
+      <c r="J123" t="s">
+        <v>38</v>
+      </c>
+      <c r="K123" t="s">
+        <v>130</v>
+      </c>
+      <c r="L123" t="s">
+        <v>1148</v>
+      </c>
+      <c r="M123" t="s">
+        <v>39</v>
+      </c>
+      <c r="N123" t="s">
+        <v>1171</v>
+      </c>
+      <c r="O123" t="s">
+        <v>1721</v>
+      </c>
+      <c r="P123" t="s">
+        <v>1722</v>
+      </c>
+      <c r="Q123" t="s">
+        <v>1723</v>
+      </c>
+    </row>
+    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>17</v>
+      </c>
+      <c r="B124">
+        <v>20</v>
+      </c>
+      <c r="C124">
+        <v>25</v>
+      </c>
+      <c r="D124" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E124" t="s">
+        <v>1192</v>
+      </c>
+      <c r="F124" t="s">
+        <v>1720</v>
+      </c>
+      <c r="G124" t="s">
+        <v>1170</v>
+      </c>
+      <c r="J124" t="s">
+        <v>38</v>
+      </c>
+      <c r="K124" t="s">
+        <v>130</v>
+      </c>
+      <c r="L124" t="s">
+        <v>1148</v>
+      </c>
+      <c r="M124" t="s">
+        <v>39</v>
+      </c>
+      <c r="N124" t="s">
+        <v>1171</v>
+      </c>
+      <c r="O124" t="s">
+        <v>1724</v>
+      </c>
+      <c r="P124" t="s">
+        <v>1725</v>
+      </c>
+      <c r="Q124" t="s">
+        <v>1726</v>
+      </c>
+    </row>
+    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>17</v>
+      </c>
+      <c r="B125">
+        <v>28</v>
+      </c>
+      <c r="C125">
+        <v>33</v>
+      </c>
+      <c r="D125" t="s">
+        <v>1727</v>
+      </c>
+      <c r="E125" t="s">
+        <v>55</v>
+      </c>
+      <c r="F125" t="s">
+        <v>1162</v>
+      </c>
+      <c r="G125" t="s">
+        <v>1170</v>
+      </c>
+      <c r="J125" t="s">
+        <v>38</v>
+      </c>
+      <c r="K125" t="s">
+        <v>130</v>
+      </c>
+      <c r="L125" t="s">
+        <v>1148</v>
+      </c>
+      <c r="M125" t="s">
+        <v>39</v>
+      </c>
+      <c r="N125" t="s">
+        <v>1171</v>
+      </c>
+      <c r="O125" t="s">
+        <v>1728</v>
+      </c>
+      <c r="P125" t="s">
+        <v>1729</v>
+      </c>
+      <c r="Q125" t="s">
+        <v>1730</v>
+      </c>
+    </row>
+    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>17</v>
+      </c>
+      <c r="B126">
+        <v>32</v>
+      </c>
+      <c r="C126">
+        <v>38</v>
+      </c>
+      <c r="D126" t="s">
+        <v>1731</v>
+      </c>
+      <c r="E126" t="s">
+        <v>1732</v>
+      </c>
+      <c r="F126" t="s">
+        <v>1465</v>
+      </c>
+      <c r="G126" t="s">
+        <v>1170</v>
+      </c>
+      <c r="H126">
+        <v>220000</v>
+      </c>
+      <c r="I126">
+        <v>300000</v>
+      </c>
+      <c r="J126" t="s">
+        <v>22</v>
+      </c>
+      <c r="K126" t="s">
+        <v>923</v>
+      </c>
+      <c r="L126" t="s">
+        <v>1148</v>
+      </c>
+      <c r="M126" t="s">
+        <v>39</v>
+      </c>
+      <c r="N126" t="s">
+        <v>1171</v>
+      </c>
+      <c r="O126" t="s">
+        <v>1733</v>
+      </c>
+      <c r="P126" t="s">
+        <v>1734</v>
+      </c>
+      <c r="Q126" t="s">
+        <v>1735</v>
       </c>
     </row>
   </sheetData>

--- a/hunt/board.xlsx
+++ b/hunt/board.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4480" uniqueCount="1662">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4558" uniqueCount="1689">
   <si>
     <t>Column</t>
   </si>
@@ -3473,6 +3473,48 @@
     <t>https://www.arbeitnow.com/jobs/companies/wavestone-germany-ag/senior-kubernetes-platform-engineer-refnr-47602-stuttgart-338304</t>
   </si>
   <si>
+    <t>Scientific Games</t>
+  </si>
+  <si>
+    <t>2026-09-03T15:38:08.668Z</t>
+  </si>
+  <si>
+    <t>Core ask — infrastructure automation, CI/CD, containers, deployment reliability — maps directly to candidate's pipeline architecture and IaC experience | Fully remote, matching the candidate's primary workplace preference | Regulated/gaming-lottery environment with heavy security requirements aligns with his HIPAA/PCI/SOX compliance-architecture background</t>
+  </si>
+  <si>
+    <t>Senior DevOps Engineer is a hands-on IC title below the principal/architect scope he is targeting | Remote-worldwide postings often benchmark comp well under a $180K US floor | Lottery/betting platforms typically lean AWS/Linux/Kubernetes rather than his Azure DevOps + GitHub Enterprise specialty</t>
+  </si>
+  <si>
+    <t>https://himalayas.app/companies/scientific-games/jobs/senior-devops-engineer</t>
+  </si>
+  <si>
+    <t>Solutions Architect - Digital Native Business, Named Accounts</t>
+  </si>
+  <si>
+    <t>Nevada; Remote - California; Remote - Colorado; Remote - Oregon; Remote - Washington</t>
+  </si>
+  <si>
+    <t>Explicitly #LI-REMOTE and open to candidates outside listed states, so Texas-based remote is viable | Confirmed $180K base exactly meets his salary floor, plus Databricks equity upside | Customer-facing architecture and use-case design work mirrors his current Customer Engineer advisory engagement model</t>
+  </si>
+  <si>
+    <t>Requires deep data engineering/Spark/Delta Lake/ML platform expertise that is absent from his profile | Digital-native pre-sales SA role is quota-adjacent and typically demands prior big-data pre-sales wins | No credit given for his Azure DevOps/GitHub Advanced Security specialization here</t>
+  </si>
+  <si>
+    <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8569640002</t>
+  </si>
+  <si>
+    <t>Senior Cloud Test &amp; DevOps Engineer (m/w/d)</t>
+  </si>
+  <si>
+    <t>Cloud-native platform CI/CD and automation focus touches his pipeline and IaC toolset | Largely remote (90%) engagement structure</t>
+  </si>
+  <si>
+    <t>Requires German-language proficiency and remote work only from within Germany — he is US-based | Requires willingness to obtain German SÜ2 security clearance (Geheim/Sabotageschutz), which he cannot hold | Fixed-term contract (Oct–Dec 2026) with a test-engineering emphasis, not full-time principal architecture work</t>
+  </si>
+  <si>
+    <t>https://www.arbeitnow.com/jobs/companies/virtual7-gmbh/remote-senior-cloud-test-devops-engineer-berlin-312220</t>
+  </si>
+  <si>
     <t>Solutions Architect - Agencies</t>
   </si>
   <si>
@@ -4998,6 +5040,45 @@
   </si>
   <si>
     <t>https://www.arbeitnow.com/jobs/companies/accso-accelerated-solutions-gmbh/senior-cloud-devops-engineer-frankfurt-am-main-162264</t>
+  </si>
+  <si>
+    <t>Lead GTM Enablement &amp; Scale Architect, Field Engineering - Customer Skills</t>
+  </si>
+  <si>
+    <t>Lead-level scope and $217.8K confirmed comp clear his $180K floor comfortably | Role centers on customer-facing technical advisory skills and enablement, echoing his trusted-advisor Customer Engineer model | Field Engineering org work at scale matches his DevOps maturity assessment / enablement experience (ITIL, Prosci)</t>
+  </si>
+  <si>
+    <t>This is a GTM enablement/program role requiring Databricks-platform and data/AI field expertise he does not have | Databricks solutions depth centers on Spark/Delta/Lakehouse on AWS+Azure data stacks, not Azure DevOps/GitHub governance | Location listed only as 'United States' with unclear remote status; likely expects proximity to a Databricks hub</t>
+  </si>
+  <si>
+    <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8644006002</t>
+  </si>
+  <si>
+    <t>Sr. Solutions Architect - Financial Services (Strategic Banking)</t>
+  </si>
+  <si>
+    <t>Georgia; Massachusetts; New York; North Carolina</t>
+  </si>
+  <si>
+    <t>$219.1K confirmed base well above his $180K floor at senior scope | Strategic banking vertical is a strong precedent match for his SOX/PCI/FIPS compliance-driven architecture work | Trusted-advisor role guiding customers from architecture through implementation matches how he already works with enterprise customers</t>
+  </si>
+  <si>
+    <t>Core requirement is Apache Spark/Delta Lake/MLflow data platform depth he lacks | East Coast location expectation (GA/MA/NY/NC) conflicts with his Humble, TX base and remote-first preference | Pre-sales SA motion with deal influence rather than the DevOps/platform architecture he targets</t>
+  </si>
+  <si>
+    <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8568013002</t>
+  </si>
+  <si>
+    <t>Shenzhen</t>
+  </si>
+  <si>
+    <t>Pre-sales solutions architect trusted-advisor framing overlaps with his enterprise customer advisory experience | Senior SA title is broadly in his target title set</t>
+  </si>
+  <si>
+    <t>Role is based in Shenzhen, China — completely outside his US market scope and almost certainly requires local work authorization and Mandarin | Requires MongoDB/data-platform and software architecture depth, not Azure DevOps/GitHub governance | No salary posted and China-market comp would fall far below his $180K floor</t>
+  </si>
+  <si>
+    <t>https://www.mongodb.com/careers/job/?gh_jid=7157100</t>
   </si>
 </sst>
 </file>
@@ -5378,7 +5459,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q231"/>
+  <dimension ref="A1:Q234"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -16978,6 +17059,153 @@
         <v>1152</v>
       </c>
     </row>
+    <row r="232" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>17</v>
+      </c>
+      <c r="B232">
+        <v>52</v>
+      </c>
+      <c r="C232">
+        <v>68</v>
+      </c>
+      <c r="D232" t="s">
+        <v>123</v>
+      </c>
+      <c r="E232" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F232" t="s">
+        <v>125</v>
+      </c>
+      <c r="G232" t="s">
+        <v>21</v>
+      </c>
+      <c r="J232" t="s">
+        <v>32</v>
+      </c>
+      <c r="K232" t="s">
+        <v>23</v>
+      </c>
+      <c r="L232" t="s">
+        <v>1154</v>
+      </c>
+      <c r="M232" t="s">
+        <v>38</v>
+      </c>
+      <c r="N232" t="s">
+        <v>26</v>
+      </c>
+      <c r="O232" t="s">
+        <v>1155</v>
+      </c>
+      <c r="P232" t="s">
+        <v>1156</v>
+      </c>
+      <c r="Q232" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="233" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>17</v>
+      </c>
+      <c r="B233">
+        <v>55</v>
+      </c>
+      <c r="C233">
+        <v>45</v>
+      </c>
+      <c r="D233" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E233" t="s">
+        <v>63</v>
+      </c>
+      <c r="F233" t="s">
+        <v>1159</v>
+      </c>
+      <c r="G233" t="s">
+        <v>21</v>
+      </c>
+      <c r="H233">
+        <v>180000</v>
+      </c>
+      <c r="I233">
+        <v>180000</v>
+      </c>
+      <c r="J233" t="s">
+        <v>22</v>
+      </c>
+      <c r="K233" t="s">
+        <v>65</v>
+      </c>
+      <c r="L233" t="s">
+        <v>1154</v>
+      </c>
+      <c r="M233" t="s">
+        <v>38</v>
+      </c>
+      <c r="N233" t="s">
+        <v>26</v>
+      </c>
+      <c r="O233" t="s">
+        <v>1160</v>
+      </c>
+      <c r="P233" t="s">
+        <v>1161</v>
+      </c>
+      <c r="Q233" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="234" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>17</v>
+      </c>
+      <c r="B234">
+        <v>15</v>
+      </c>
+      <c r="C234">
+        <v>22</v>
+      </c>
+      <c r="D234" t="s">
+        <v>1163</v>
+      </c>
+      <c r="E234" t="s">
+        <v>1014</v>
+      </c>
+      <c r="F234" t="s">
+        <v>1015</v>
+      </c>
+      <c r="G234" t="s">
+        <v>21</v>
+      </c>
+      <c r="J234" t="s">
+        <v>32</v>
+      </c>
+      <c r="K234" t="s">
+        <v>99</v>
+      </c>
+      <c r="L234" t="s">
+        <v>1154</v>
+      </c>
+      <c r="M234" t="s">
+        <v>25</v>
+      </c>
+      <c r="N234" t="s">
+        <v>26</v>
+      </c>
+      <c r="O234" t="s">
+        <v>1164</v>
+      </c>
+      <c r="P234" t="s">
+        <v>1165</v>
+      </c>
+      <c r="Q234" t="s">
+        <v>1166</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:Q1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16987,7 +17215,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q113"/>
+  <dimension ref="A1:Q116"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -17068,7 +17296,7 @@
         <v>42</v>
       </c>
       <c r="D2" t="s">
-        <v>1153</v>
+        <v>1167</v>
       </c>
       <c r="E2" t="s">
         <v>63</v>
@@ -17077,7 +17305,7 @@
         <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J2" t="s">
         <v>32</v>
@@ -17092,16 +17320,16 @@
         <v>25</v>
       </c>
       <c r="N2" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O2" t="s">
-        <v>1156</v>
+        <v>1170</v>
       </c>
       <c r="P2" t="s">
-        <v>1157</v>
+        <v>1171</v>
       </c>
       <c r="Q2" t="s">
-        <v>1158</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -17115,7 +17343,7 @@
         <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>1159</v>
+        <v>1173</v>
       </c>
       <c r="E3" t="s">
         <v>63</v>
@@ -17124,7 +17352,7 @@
         <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J3" t="s">
         <v>32</v>
@@ -17139,16 +17367,16 @@
         <v>25</v>
       </c>
       <c r="N3" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O3" t="s">
-        <v>1160</v>
+        <v>1174</v>
       </c>
       <c r="P3" t="s">
-        <v>1161</v>
+        <v>1175</v>
       </c>
       <c r="Q3" t="s">
-        <v>1162</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
@@ -17168,10 +17396,10 @@
         <v>63</v>
       </c>
       <c r="F4" t="s">
-        <v>1163</v>
+        <v>1177</v>
       </c>
       <c r="G4" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="H4">
         <v>180000</v>
@@ -17192,16 +17420,16 @@
         <v>38</v>
       </c>
       <c r="N4" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O4" t="s">
-        <v>1164</v>
+        <v>1178</v>
       </c>
       <c r="P4" t="s">
-        <v>1165</v>
+        <v>1179</v>
       </c>
       <c r="Q4" t="s">
-        <v>1166</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -17215,7 +17443,7 @@
         <v>52</v>
       </c>
       <c r="D5" t="s">
-        <v>1167</v>
+        <v>1181</v>
       </c>
       <c r="E5" t="s">
         <v>63</v>
@@ -17224,7 +17452,7 @@
         <v>20</v>
       </c>
       <c r="G5" t="s">
-        <v>1168</v>
+        <v>1182</v>
       </c>
       <c r="H5">
         <v>180000</v>
@@ -17245,16 +17473,16 @@
         <v>38</v>
       </c>
       <c r="N5" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O5" t="s">
-        <v>1169</v>
+        <v>1183</v>
       </c>
       <c r="P5" t="s">
-        <v>1170</v>
+        <v>1184</v>
       </c>
       <c r="Q5" t="s">
-        <v>1171</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -17268,7 +17496,7 @@
         <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>1172</v>
+        <v>1186</v>
       </c>
       <c r="E6" t="s">
         <v>63</v>
@@ -17277,7 +17505,7 @@
         <v>20</v>
       </c>
       <c r="G6" t="s">
-        <v>1168</v>
+        <v>1182</v>
       </c>
       <c r="H6">
         <v>180000</v>
@@ -17298,16 +17526,16 @@
         <v>38</v>
       </c>
       <c r="N6" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O6" t="s">
-        <v>1173</v>
+        <v>1187</v>
       </c>
       <c r="P6" t="s">
-        <v>1174</v>
+        <v>1188</v>
       </c>
       <c r="Q6" t="s">
-        <v>1175</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -17321,16 +17549,16 @@
         <v>48</v>
       </c>
       <c r="D7" t="s">
-        <v>1176</v>
+        <v>1190</v>
       </c>
       <c r="E7" t="s">
         <v>63</v>
       </c>
       <c r="F7" t="s">
-        <v>1177</v>
+        <v>1191</v>
       </c>
       <c r="G7" t="s">
-        <v>1168</v>
+        <v>1182</v>
       </c>
       <c r="H7">
         <v>219100</v>
@@ -17351,16 +17579,16 @@
         <v>38</v>
       </c>
       <c r="N7" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O7" t="s">
-        <v>1178</v>
+        <v>1192</v>
       </c>
       <c r="P7" t="s">
-        <v>1179</v>
+        <v>1193</v>
       </c>
       <c r="Q7" t="s">
-        <v>1180</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -17374,16 +17602,16 @@
         <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>1181</v>
+        <v>1195</v>
       </c>
       <c r="E8" t="s">
         <v>63</v>
       </c>
       <c r="F8" t="s">
-        <v>1182</v>
+        <v>1196</v>
       </c>
       <c r="G8" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="H8">
         <v>180000</v>
@@ -17404,16 +17632,16 @@
         <v>38</v>
       </c>
       <c r="N8" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O8" t="s">
-        <v>1183</v>
+        <v>1197</v>
       </c>
       <c r="P8" t="s">
-        <v>1184</v>
+        <v>1198</v>
       </c>
       <c r="Q8" t="s">
-        <v>1185</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -17427,7 +17655,7 @@
         <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>1186</v>
+        <v>1200</v>
       </c>
       <c r="E9" t="s">
         <v>63</v>
@@ -17436,7 +17664,7 @@
         <v>20</v>
       </c>
       <c r="G9" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="H9">
         <v>219100</v>
@@ -17457,16 +17685,16 @@
         <v>25</v>
       </c>
       <c r="N9" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O9" t="s">
-        <v>1187</v>
+        <v>1201</v>
       </c>
       <c r="P9" t="s">
-        <v>1188</v>
+        <v>1202</v>
       </c>
       <c r="Q9" t="s">
-        <v>1189</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -17480,7 +17708,7 @@
         <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>1190</v>
+        <v>1204</v>
       </c>
       <c r="E10" t="s">
         <v>63</v>
@@ -17489,7 +17717,7 @@
         <v>20</v>
       </c>
       <c r="G10" t="s">
-        <v>1168</v>
+        <v>1182</v>
       </c>
       <c r="H10">
         <v>219100</v>
@@ -17510,16 +17738,16 @@
         <v>38</v>
       </c>
       <c r="N10" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O10" t="s">
-        <v>1191</v>
+        <v>1205</v>
       </c>
       <c r="P10" t="s">
-        <v>1192</v>
+        <v>1206</v>
       </c>
       <c r="Q10" t="s">
-        <v>1193</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -17533,16 +17761,16 @@
         <v>30</v>
       </c>
       <c r="D11" t="s">
-        <v>1194</v>
+        <v>1208</v>
       </c>
       <c r="E11" t="s">
         <v>63</v>
       </c>
       <c r="F11" t="s">
-        <v>1195</v>
+        <v>1209</v>
       </c>
       <c r="G11" t="s">
-        <v>1168</v>
+        <v>1182</v>
       </c>
       <c r="J11" t="s">
         <v>32</v>
@@ -17557,16 +17785,16 @@
         <v>25</v>
       </c>
       <c r="N11" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O11" t="s">
-        <v>1196</v>
+        <v>1210</v>
       </c>
       <c r="P11" t="s">
-        <v>1197</v>
+        <v>1211</v>
       </c>
       <c r="Q11" t="s">
-        <v>1198</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -17580,16 +17808,16 @@
         <v>58</v>
       </c>
       <c r="D12" t="s">
-        <v>1199</v>
+        <v>1213</v>
       </c>
       <c r="E12" t="s">
-        <v>1200</v>
+        <v>1214</v>
       </c>
       <c r="F12" t="s">
-        <v>1201</v>
+        <v>1215</v>
       </c>
       <c r="G12" t="s">
-        <v>1168</v>
+        <v>1182</v>
       </c>
       <c r="H12">
         <v>257000</v>
@@ -17610,16 +17838,16 @@
         <v>38</v>
       </c>
       <c r="N12" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O12" t="s">
-        <v>1202</v>
+        <v>1216</v>
       </c>
       <c r="P12" t="s">
-        <v>1203</v>
+        <v>1217</v>
       </c>
       <c r="Q12" t="s">
-        <v>1204</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
@@ -17636,13 +17864,13 @@
         <v>282</v>
       </c>
       <c r="E13" t="s">
-        <v>1205</v>
+        <v>1219</v>
       </c>
       <c r="F13" t="s">
-        <v>1206</v>
+        <v>1220</v>
       </c>
       <c r="G13" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="H13">
         <v>200000</v>
@@ -17663,16 +17891,16 @@
         <v>25</v>
       </c>
       <c r="N13" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O13" t="s">
-        <v>1207</v>
+        <v>1221</v>
       </c>
       <c r="P13" t="s">
-        <v>1208</v>
+        <v>1222</v>
       </c>
       <c r="Q13" t="s">
-        <v>1209</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
@@ -17686,16 +17914,16 @@
         <v>20</v>
       </c>
       <c r="D14" t="s">
-        <v>1210</v>
+        <v>1224</v>
       </c>
       <c r="E14" t="s">
         <v>817</v>
       </c>
       <c r="F14" t="s">
-        <v>1211</v>
+        <v>1225</v>
       </c>
       <c r="G14" t="s">
-        <v>1168</v>
+        <v>1182</v>
       </c>
       <c r="J14" t="s">
         <v>32</v>
@@ -17710,16 +17938,16 @@
         <v>25</v>
       </c>
       <c r="N14" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O14" t="s">
-        <v>1212</v>
+        <v>1226</v>
       </c>
       <c r="P14" t="s">
-        <v>1213</v>
+        <v>1227</v>
       </c>
       <c r="Q14" t="s">
-        <v>1214</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -17739,10 +17967,10 @@
         <v>817</v>
       </c>
       <c r="F15" t="s">
-        <v>1215</v>
+        <v>1229</v>
       </c>
       <c r="G15" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J15" t="s">
         <v>32</v>
@@ -17757,16 +17985,16 @@
         <v>25</v>
       </c>
       <c r="N15" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O15" t="s">
-        <v>1216</v>
+        <v>1230</v>
       </c>
       <c r="P15" t="s">
-        <v>1217</v>
+        <v>1231</v>
       </c>
       <c r="Q15" t="s">
-        <v>1218</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
@@ -17780,16 +18008,16 @@
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>1219</v>
+        <v>1233</v>
       </c>
       <c r="E16" t="s">
         <v>817</v>
       </c>
       <c r="F16" t="s">
-        <v>1220</v>
+        <v>1234</v>
       </c>
       <c r="G16" t="s">
-        <v>1168</v>
+        <v>1182</v>
       </c>
       <c r="H16">
         <v>500000</v>
@@ -17810,16 +18038,16 @@
         <v>25</v>
       </c>
       <c r="N16" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O16" t="s">
-        <v>1221</v>
+        <v>1235</v>
       </c>
       <c r="P16" t="s">
-        <v>1222</v>
+        <v>1236</v>
       </c>
       <c r="Q16" t="s">
-        <v>1223</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
@@ -17833,16 +18061,16 @@
         <v>18</v>
       </c>
       <c r="D17" t="s">
-        <v>1224</v>
+        <v>1238</v>
       </c>
       <c r="E17" t="s">
         <v>604</v>
       </c>
       <c r="F17" t="s">
-        <v>1225</v>
+        <v>1239</v>
       </c>
       <c r="G17" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="H17">
         <v>274456</v>
@@ -17863,16 +18091,16 @@
         <v>25</v>
       </c>
       <c r="N17" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O17" t="s">
-        <v>1226</v>
+        <v>1240</v>
       </c>
       <c r="P17" t="s">
-        <v>1227</v>
+        <v>1241</v>
       </c>
       <c r="Q17" t="s">
-        <v>1228</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
@@ -17886,16 +18114,16 @@
         <v>30</v>
       </c>
       <c r="D18" t="s">
-        <v>1229</v>
+        <v>1243</v>
       </c>
       <c r="E18" t="s">
         <v>604</v>
       </c>
       <c r="F18" t="s">
-        <v>1230</v>
+        <v>1244</v>
       </c>
       <c r="G18" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J18" t="s">
         <v>32</v>
@@ -17910,16 +18138,16 @@
         <v>25</v>
       </c>
       <c r="N18" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O18" t="s">
-        <v>1231</v>
+        <v>1245</v>
       </c>
       <c r="P18" t="s">
-        <v>1232</v>
+        <v>1246</v>
       </c>
       <c r="Q18" t="s">
-        <v>1233</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -17933,16 +18161,16 @@
         <v>22</v>
       </c>
       <c r="D19" t="s">
-        <v>1234</v>
+        <v>1248</v>
       </c>
       <c r="E19" t="s">
         <v>604</v>
       </c>
       <c r="F19" t="s">
-        <v>1235</v>
+        <v>1249</v>
       </c>
       <c r="G19" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J19" t="s">
         <v>32</v>
@@ -17957,16 +18185,16 @@
         <v>25</v>
       </c>
       <c r="N19" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O19" t="s">
-        <v>1236</v>
+        <v>1250</v>
       </c>
       <c r="P19" t="s">
-        <v>1237</v>
+        <v>1251</v>
       </c>
       <c r="Q19" t="s">
-        <v>1238</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -17980,16 +18208,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="s">
-        <v>1239</v>
+        <v>1253</v>
       </c>
       <c r="E20" t="s">
         <v>604</v>
       </c>
       <c r="F20" t="s">
-        <v>1240</v>
+        <v>1254</v>
       </c>
       <c r="G20" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J20" t="s">
         <v>32</v>
@@ -18004,16 +18232,16 @@
         <v>38</v>
       </c>
       <c r="N20" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O20" t="s">
-        <v>1241</v>
+        <v>1255</v>
       </c>
       <c r="P20" t="s">
-        <v>1242</v>
+        <v>1256</v>
       </c>
       <c r="Q20" t="s">
-        <v>1243</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
@@ -18027,16 +18255,16 @@
         <v>25</v>
       </c>
       <c r="D21" t="s">
-        <v>1244</v>
+        <v>1258</v>
       </c>
       <c r="E21" t="s">
         <v>604</v>
       </c>
       <c r="F21" t="s">
-        <v>1245</v>
+        <v>1259</v>
       </c>
       <c r="G21" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J21" t="s">
         <v>32</v>
@@ -18051,16 +18279,16 @@
         <v>25</v>
       </c>
       <c r="N21" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O21" t="s">
-        <v>1246</v>
+        <v>1260</v>
       </c>
       <c r="P21" t="s">
-        <v>1247</v>
+        <v>1261</v>
       </c>
       <c r="Q21" t="s">
-        <v>1248</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -18074,16 +18302,16 @@
         <v>40</v>
       </c>
       <c r="D22" t="s">
-        <v>1249</v>
+        <v>1263</v>
       </c>
       <c r="E22" t="s">
         <v>604</v>
       </c>
       <c r="F22" t="s">
-        <v>1250</v>
+        <v>1264</v>
       </c>
       <c r="G22" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J22" t="s">
         <v>32</v>
@@ -18098,16 +18326,16 @@
         <v>25</v>
       </c>
       <c r="N22" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O22" t="s">
-        <v>1251</v>
+        <v>1265</v>
       </c>
       <c r="P22" t="s">
-        <v>1252</v>
+        <v>1266</v>
       </c>
       <c r="Q22" t="s">
-        <v>1253</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
@@ -18121,16 +18349,16 @@
         <v>70</v>
       </c>
       <c r="D23" t="s">
-        <v>1254</v>
+        <v>1268</v>
       </c>
       <c r="E23" t="s">
-        <v>1255</v>
+        <v>1269</v>
       </c>
       <c r="F23" t="s">
-        <v>1256</v>
+        <v>1270</v>
       </c>
       <c r="G23" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J23" t="s">
         <v>32</v>
@@ -18145,16 +18373,16 @@
         <v>25</v>
       </c>
       <c r="N23" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O23" t="s">
-        <v>1257</v>
+        <v>1271</v>
       </c>
       <c r="P23" t="s">
-        <v>1258</v>
+        <v>1272</v>
       </c>
       <c r="Q23" t="s">
-        <v>1259</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
@@ -18168,16 +18396,16 @@
         <v>58</v>
       </c>
       <c r="D24" t="s">
-        <v>1260</v>
+        <v>1274</v>
       </c>
       <c r="E24" t="s">
-        <v>1261</v>
+        <v>1275</v>
       </c>
       <c r="F24" t="s">
-        <v>1245</v>
+        <v>1259</v>
       </c>
       <c r="G24" t="s">
-        <v>1168</v>
+        <v>1182</v>
       </c>
       <c r="J24" t="s">
         <v>32</v>
@@ -18192,16 +18420,16 @@
         <v>25</v>
       </c>
       <c r="N24" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O24" t="s">
-        <v>1262</v>
+        <v>1276</v>
       </c>
       <c r="P24" t="s">
-        <v>1263</v>
+        <v>1277</v>
       </c>
       <c r="Q24" t="s">
-        <v>1264</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
@@ -18215,16 +18443,16 @@
         <v>32</v>
       </c>
       <c r="D25" t="s">
-        <v>1265</v>
+        <v>1279</v>
       </c>
       <c r="E25" t="s">
-        <v>1266</v>
+        <v>1280</v>
       </c>
       <c r="F25" t="s">
-        <v>1267</v>
+        <v>1281</v>
       </c>
       <c r="G25" t="s">
-        <v>1168</v>
+        <v>1182</v>
       </c>
       <c r="J25" t="s">
         <v>32</v>
@@ -18239,16 +18467,16 @@
         <v>25</v>
       </c>
       <c r="N25" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O25" t="s">
-        <v>1268</v>
+        <v>1282</v>
       </c>
       <c r="P25" t="s">
-        <v>1269</v>
+        <v>1283</v>
       </c>
       <c r="Q25" t="s">
-        <v>1270</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
@@ -18262,16 +18490,16 @@
         <v>4</v>
       </c>
       <c r="D26" t="s">
-        <v>1271</v>
+        <v>1285</v>
       </c>
       <c r="E26" t="s">
-        <v>1272</v>
+        <v>1286</v>
       </c>
       <c r="F26" t="s">
         <v>1149</v>
       </c>
       <c r="G26" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J26" t="s">
         <v>32</v>
@@ -18286,16 +18514,16 @@
         <v>25</v>
       </c>
       <c r="N26" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O26" t="s">
-        <v>1273</v>
+        <v>1287</v>
       </c>
       <c r="P26" t="s">
-        <v>1274</v>
+        <v>1288</v>
       </c>
       <c r="Q26" t="s">
-        <v>1275</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
@@ -18309,16 +18537,16 @@
         <v>25</v>
       </c>
       <c r="D27" t="s">
-        <v>1276</v>
+        <v>1290</v>
       </c>
       <c r="E27" t="s">
-        <v>1277</v>
+        <v>1291</v>
       </c>
       <c r="F27" t="s">
-        <v>1278</v>
+        <v>1292</v>
       </c>
       <c r="G27" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J27" t="s">
         <v>32</v>
@@ -18333,16 +18561,16 @@
         <v>25</v>
       </c>
       <c r="N27" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O27" t="s">
-        <v>1279</v>
+        <v>1293</v>
       </c>
       <c r="P27" t="s">
-        <v>1280</v>
+        <v>1294</v>
       </c>
       <c r="Q27" t="s">
-        <v>1281</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
@@ -18356,16 +18584,16 @@
         <v>30</v>
       </c>
       <c r="D28" t="s">
-        <v>1282</v>
+        <v>1296</v>
       </c>
       <c r="E28" t="s">
-        <v>1283</v>
+        <v>1297</v>
       </c>
       <c r="F28" t="s">
         <v>1142</v>
       </c>
       <c r="G28" t="s">
-        <v>1168</v>
+        <v>1182</v>
       </c>
       <c r="J28" t="s">
         <v>32</v>
@@ -18380,16 +18608,16 @@
         <v>25</v>
       </c>
       <c r="N28" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O28" t="s">
-        <v>1284</v>
+        <v>1298</v>
       </c>
       <c r="P28" t="s">
-        <v>1285</v>
+        <v>1299</v>
       </c>
       <c r="Q28" t="s">
-        <v>1286</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
@@ -18403,16 +18631,16 @@
         <v>52</v>
       </c>
       <c r="D29" t="s">
-        <v>1287</v>
+        <v>1301</v>
       </c>
       <c r="E29" t="s">
         <v>63</v>
       </c>
       <c r="F29" t="s">
-        <v>1288</v>
+        <v>1302</v>
       </c>
       <c r="G29" t="s">
-        <v>1168</v>
+        <v>1182</v>
       </c>
       <c r="H29">
         <v>180000</v>
@@ -18433,16 +18661,16 @@
         <v>38</v>
       </c>
       <c r="N29" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O29" t="s">
-        <v>1289</v>
+        <v>1303</v>
       </c>
       <c r="P29" t="s">
-        <v>1290</v>
+        <v>1304</v>
       </c>
       <c r="Q29" t="s">
-        <v>1291</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
@@ -18456,7 +18684,7 @@
         <v>50</v>
       </c>
       <c r="D30" t="s">
-        <v>1292</v>
+        <v>1306</v>
       </c>
       <c r="E30" t="s">
         <v>63</v>
@@ -18465,7 +18693,7 @@
         <v>20</v>
       </c>
       <c r="G30" t="s">
-        <v>1168</v>
+        <v>1182</v>
       </c>
       <c r="H30">
         <v>180000</v>
@@ -18486,16 +18714,16 @@
         <v>38</v>
       </c>
       <c r="N30" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O30" t="s">
-        <v>1293</v>
+        <v>1307</v>
       </c>
       <c r="P30" t="s">
-        <v>1294</v>
+        <v>1308</v>
       </c>
       <c r="Q30" t="s">
-        <v>1295</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
@@ -18509,7 +18737,7 @@
         <v>46</v>
       </c>
       <c r="D31" t="s">
-        <v>1296</v>
+        <v>1310</v>
       </c>
       <c r="E31" t="s">
         <v>63</v>
@@ -18518,7 +18746,7 @@
         <v>20</v>
       </c>
       <c r="G31" t="s">
-        <v>1168</v>
+        <v>1182</v>
       </c>
       <c r="H31">
         <v>180000</v>
@@ -18539,16 +18767,16 @@
         <v>38</v>
       </c>
       <c r="N31" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O31" t="s">
-        <v>1297</v>
+        <v>1311</v>
       </c>
       <c r="P31" t="s">
-        <v>1298</v>
+        <v>1312</v>
       </c>
       <c r="Q31" t="s">
-        <v>1299</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
@@ -18562,7 +18790,7 @@
         <v>38</v>
       </c>
       <c r="D32" t="s">
-        <v>1300</v>
+        <v>1314</v>
       </c>
       <c r="E32" t="s">
         <v>63</v>
@@ -18571,7 +18799,7 @@
         <v>20</v>
       </c>
       <c r="G32" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="H32">
         <v>217800</v>
@@ -18592,16 +18820,16 @@
         <v>25</v>
       </c>
       <c r="N32" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O32" t="s">
-        <v>1301</v>
+        <v>1315</v>
       </c>
       <c r="P32" t="s">
-        <v>1302</v>
+        <v>1316</v>
       </c>
       <c r="Q32" t="s">
-        <v>1303</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
@@ -18621,10 +18849,10 @@
         <v>63</v>
       </c>
       <c r="F33" t="s">
-        <v>1304</v>
+        <v>1318</v>
       </c>
       <c r="G33" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="H33">
         <v>180000</v>
@@ -18645,16 +18873,16 @@
         <v>38</v>
       </c>
       <c r="N33" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O33" t="s">
-        <v>1305</v>
+        <v>1319</v>
       </c>
       <c r="P33" t="s">
-        <v>1306</v>
+        <v>1320</v>
       </c>
       <c r="Q33" t="s">
-        <v>1307</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
@@ -18668,16 +18896,16 @@
         <v>45</v>
       </c>
       <c r="D34" t="s">
-        <v>1308</v>
+        <v>1322</v>
       </c>
       <c r="E34" t="s">
         <v>63</v>
       </c>
       <c r="F34" t="s">
-        <v>1309</v>
+        <v>1323</v>
       </c>
       <c r="G34" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="H34">
         <v>219100</v>
@@ -18698,16 +18926,16 @@
         <v>38</v>
       </c>
       <c r="N34" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O34" t="s">
-        <v>1310</v>
+        <v>1324</v>
       </c>
       <c r="P34" t="s">
-        <v>1311</v>
+        <v>1325</v>
       </c>
       <c r="Q34" t="s">
-        <v>1312</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
@@ -18721,16 +18949,16 @@
         <v>42</v>
       </c>
       <c r="D35" t="s">
-        <v>1313</v>
+        <v>1327</v>
       </c>
       <c r="E35" t="s">
         <v>63</v>
       </c>
       <c r="F35" t="s">
-        <v>1314</v>
+        <v>1328</v>
       </c>
       <c r="G35" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="H35">
         <v>180000</v>
@@ -18751,16 +18979,16 @@
         <v>38</v>
       </c>
       <c r="N35" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O35" t="s">
-        <v>1315</v>
+        <v>1329</v>
       </c>
       <c r="P35" t="s">
-        <v>1316</v>
+        <v>1330</v>
       </c>
       <c r="Q35" t="s">
-        <v>1317</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
@@ -18774,7 +19002,7 @@
         <v>32</v>
       </c>
       <c r="D36" t="s">
-        <v>1318</v>
+        <v>1332</v>
       </c>
       <c r="E36" t="s">
         <v>63</v>
@@ -18783,7 +19011,7 @@
         <v>20</v>
       </c>
       <c r="G36" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="H36">
         <v>219100</v>
@@ -18804,16 +19032,16 @@
         <v>25</v>
       </c>
       <c r="N36" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O36" t="s">
-        <v>1319</v>
+        <v>1333</v>
       </c>
       <c r="P36" t="s">
-        <v>1320</v>
+        <v>1334</v>
       </c>
       <c r="Q36" t="s">
-        <v>1321</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
@@ -18827,7 +19055,7 @@
         <v>35</v>
       </c>
       <c r="D37" t="s">
-        <v>1322</v>
+        <v>1336</v>
       </c>
       <c r="E37" t="s">
         <v>63</v>
@@ -18836,7 +19064,7 @@
         <v>20</v>
       </c>
       <c r="G37" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="H37">
         <v>219100</v>
@@ -18857,16 +19085,16 @@
         <v>25</v>
       </c>
       <c r="N37" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O37" t="s">
-        <v>1323</v>
+        <v>1337</v>
       </c>
       <c r="P37" t="s">
-        <v>1324</v>
+        <v>1338</v>
       </c>
       <c r="Q37" t="s">
-        <v>1325</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
@@ -18880,16 +19108,16 @@
         <v>40</v>
       </c>
       <c r="D38" t="s">
-        <v>1326</v>
+        <v>1340</v>
       </c>
       <c r="E38" t="s">
         <v>63</v>
       </c>
       <c r="F38" t="s">
-        <v>1327</v>
+        <v>1341</v>
       </c>
       <c r="G38" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="H38">
         <v>219100</v>
@@ -18910,16 +19138,16 @@
         <v>38</v>
       </c>
       <c r="N38" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O38" t="s">
-        <v>1328</v>
+        <v>1342</v>
       </c>
       <c r="P38" t="s">
-        <v>1329</v>
+        <v>1343</v>
       </c>
       <c r="Q38" t="s">
-        <v>1330</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
@@ -18933,7 +19161,7 @@
         <v>38</v>
       </c>
       <c r="D39" t="s">
-        <v>1331</v>
+        <v>1345</v>
       </c>
       <c r="E39" t="s">
         <v>63</v>
@@ -18942,7 +19170,7 @@
         <v>563</v>
       </c>
       <c r="G39" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="H39">
         <v>219100</v>
@@ -18963,16 +19191,16 @@
         <v>25</v>
       </c>
       <c r="N39" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O39" t="s">
-        <v>1332</v>
+        <v>1346</v>
       </c>
       <c r="P39" t="s">
-        <v>1333</v>
+        <v>1347</v>
       </c>
       <c r="Q39" t="s">
-        <v>1334</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
@@ -18986,7 +19214,7 @@
         <v>40</v>
       </c>
       <c r="D40" t="s">
-        <v>1335</v>
+        <v>1349</v>
       </c>
       <c r="E40" t="s">
         <v>63</v>
@@ -18995,7 +19223,7 @@
         <v>20</v>
       </c>
       <c r="G40" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="H40">
         <v>219100</v>
@@ -19016,16 +19244,16 @@
         <v>38</v>
       </c>
       <c r="N40" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O40" t="s">
-        <v>1336</v>
+        <v>1350</v>
       </c>
       <c r="P40" t="s">
-        <v>1337</v>
+        <v>1351</v>
       </c>
       <c r="Q40" t="s">
-        <v>1338</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
@@ -19039,16 +19267,16 @@
         <v>33</v>
       </c>
       <c r="D41" t="s">
-        <v>1339</v>
+        <v>1353</v>
       </c>
       <c r="E41" t="s">
         <v>63</v>
       </c>
       <c r="F41" t="s">
-        <v>1340</v>
+        <v>1354</v>
       </c>
       <c r="G41" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="H41">
         <v>219100</v>
@@ -19069,16 +19297,16 @@
         <v>25</v>
       </c>
       <c r="N41" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O41" t="s">
-        <v>1341</v>
+        <v>1355</v>
       </c>
       <c r="P41" t="s">
-        <v>1342</v>
+        <v>1356</v>
       </c>
       <c r="Q41" t="s">
-        <v>1343</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
@@ -19092,16 +19320,16 @@
         <v>48</v>
       </c>
       <c r="D42" t="s">
-        <v>1344</v>
+        <v>1358</v>
       </c>
       <c r="E42" t="s">
-        <v>1200</v>
+        <v>1214</v>
       </c>
       <c r="F42" t="s">
-        <v>1345</v>
+        <v>1359</v>
       </c>
       <c r="G42" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J42" t="s">
         <v>32</v>
@@ -19116,16 +19344,16 @@
         <v>38</v>
       </c>
       <c r="N42" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O42" t="s">
-        <v>1346</v>
+        <v>1360</v>
       </c>
       <c r="P42" t="s">
-        <v>1347</v>
+        <v>1361</v>
       </c>
       <c r="Q42" t="s">
-        <v>1348</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
@@ -19139,16 +19367,16 @@
         <v>40</v>
       </c>
       <c r="D43" t="s">
-        <v>1349</v>
+        <v>1363</v>
       </c>
       <c r="E43" t="s">
-        <v>1205</v>
+        <v>1219</v>
       </c>
       <c r="F43" t="s">
-        <v>1350</v>
+        <v>1364</v>
       </c>
       <c r="G43" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="H43">
         <v>184200</v>
@@ -19169,16 +19397,16 @@
         <v>38</v>
       </c>
       <c r="N43" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O43" t="s">
-        <v>1351</v>
+        <v>1365</v>
       </c>
       <c r="P43" t="s">
-        <v>1352</v>
+        <v>1366</v>
       </c>
       <c r="Q43" t="s">
-        <v>1353</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
@@ -19192,16 +19420,16 @@
         <v>30</v>
       </c>
       <c r="D44" t="s">
-        <v>1354</v>
+        <v>1368</v>
       </c>
       <c r="E44" t="s">
-        <v>1205</v>
+        <v>1219</v>
       </c>
       <c r="F44" t="s">
-        <v>1355</v>
+        <v>1369</v>
       </c>
       <c r="G44" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="H44">
         <v>200000</v>
@@ -19222,16 +19450,16 @@
         <v>25</v>
       </c>
       <c r="N44" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O44" t="s">
-        <v>1356</v>
+        <v>1370</v>
       </c>
       <c r="P44" t="s">
-        <v>1357</v>
+        <v>1371</v>
       </c>
       <c r="Q44" t="s">
-        <v>1358</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
@@ -19245,7 +19473,7 @@
         <v>30</v>
       </c>
       <c r="D45" t="s">
-        <v>1359</v>
+        <v>1373</v>
       </c>
       <c r="E45" t="s">
         <v>817</v>
@@ -19254,7 +19482,7 @@
         <v>826</v>
       </c>
       <c r="G45" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J45" t="s">
         <v>32</v>
@@ -19269,16 +19497,16 @@
         <v>25</v>
       </c>
       <c r="N45" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O45" t="s">
-        <v>1360</v>
+        <v>1374</v>
       </c>
       <c r="P45" t="s">
-        <v>1361</v>
+        <v>1375</v>
       </c>
       <c r="Q45" t="s">
-        <v>1362</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
@@ -19298,10 +19526,10 @@
         <v>817</v>
       </c>
       <c r="F46" t="s">
-        <v>1215</v>
+        <v>1229</v>
       </c>
       <c r="G46" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J46" t="s">
         <v>32</v>
@@ -19316,16 +19544,16 @@
         <v>25</v>
       </c>
       <c r="N46" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O46" t="s">
-        <v>1363</v>
+        <v>1377</v>
       </c>
       <c r="P46" t="s">
-        <v>1364</v>
+        <v>1378</v>
       </c>
       <c r="Q46" t="s">
-        <v>1365</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
@@ -19339,7 +19567,7 @@
         <v>32</v>
       </c>
       <c r="D47" t="s">
-        <v>1366</v>
+        <v>1380</v>
       </c>
       <c r="E47" t="s">
         <v>817</v>
@@ -19348,7 +19576,7 @@
         <v>826</v>
       </c>
       <c r="G47" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J47" t="s">
         <v>32</v>
@@ -19363,16 +19591,16 @@
         <v>25</v>
       </c>
       <c r="N47" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O47" t="s">
-        <v>1367</v>
+        <v>1381</v>
       </c>
       <c r="P47" t="s">
-        <v>1368</v>
+        <v>1382</v>
       </c>
       <c r="Q47" t="s">
-        <v>1369</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
@@ -19386,16 +19614,16 @@
         <v>45</v>
       </c>
       <c r="D48" t="s">
-        <v>1370</v>
+        <v>1384</v>
       </c>
       <c r="E48" t="s">
         <v>604</v>
       </c>
       <c r="F48" t="s">
-        <v>1371</v>
+        <v>1385</v>
       </c>
       <c r="G48" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J48" t="s">
         <v>32</v>
@@ -19410,16 +19638,16 @@
         <v>38</v>
       </c>
       <c r="N48" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O48" t="s">
-        <v>1372</v>
+        <v>1386</v>
       </c>
       <c r="P48" t="s">
-        <v>1373</v>
+        <v>1387</v>
       </c>
       <c r="Q48" t="s">
-        <v>1374</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
@@ -19433,16 +19661,16 @@
         <v>35</v>
       </c>
       <c r="D49" t="s">
-        <v>1375</v>
+        <v>1389</v>
       </c>
       <c r="E49" t="s">
         <v>604</v>
       </c>
       <c r="F49" t="s">
-        <v>1376</v>
+        <v>1390</v>
       </c>
       <c r="G49" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J49" t="s">
         <v>32</v>
@@ -19457,16 +19685,16 @@
         <v>25</v>
       </c>
       <c r="N49" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O49" t="s">
-        <v>1377</v>
+        <v>1391</v>
       </c>
       <c r="P49" t="s">
-        <v>1378</v>
+        <v>1392</v>
       </c>
       <c r="Q49" t="s">
-        <v>1379</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
@@ -19480,7 +19708,7 @@
         <v>35</v>
       </c>
       <c r="D50" t="s">
-        <v>1380</v>
+        <v>1394</v>
       </c>
       <c r="E50" t="s">
         <v>604</v>
@@ -19489,7 +19717,7 @@
         <v>87</v>
       </c>
       <c r="G50" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J50" t="s">
         <v>32</v>
@@ -19504,16 +19732,16 @@
         <v>25</v>
       </c>
       <c r="N50" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O50" t="s">
-        <v>1381</v>
+        <v>1395</v>
       </c>
       <c r="P50" t="s">
-        <v>1382</v>
+        <v>1396</v>
       </c>
       <c r="Q50" t="s">
-        <v>1383</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
@@ -19527,16 +19755,16 @@
         <v>15</v>
       </c>
       <c r="D51" t="s">
-        <v>1384</v>
+        <v>1398</v>
       </c>
       <c r="E51" t="s">
         <v>604</v>
       </c>
       <c r="F51" t="s">
-        <v>1385</v>
+        <v>1399</v>
       </c>
       <c r="G51" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J51" t="s">
         <v>32</v>
@@ -19551,16 +19779,16 @@
         <v>25</v>
       </c>
       <c r="N51" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O51" t="s">
-        <v>1386</v>
+        <v>1400</v>
       </c>
       <c r="P51" t="s">
-        <v>1387</v>
+        <v>1401</v>
       </c>
       <c r="Q51" t="s">
-        <v>1388</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
@@ -19574,16 +19802,16 @@
         <v>25</v>
       </c>
       <c r="D52" t="s">
-        <v>1389</v>
+        <v>1403</v>
       </c>
       <c r="E52" t="s">
         <v>604</v>
       </c>
       <c r="F52" t="s">
-        <v>1390</v>
+        <v>1404</v>
       </c>
       <c r="G52" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J52" t="s">
         <v>32</v>
@@ -19598,16 +19826,16 @@
         <v>25</v>
       </c>
       <c r="N52" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O52" t="s">
-        <v>1391</v>
+        <v>1405</v>
       </c>
       <c r="P52" t="s">
-        <v>1392</v>
+        <v>1406</v>
       </c>
       <c r="Q52" t="s">
-        <v>1393</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
@@ -19621,16 +19849,16 @@
         <v>30</v>
       </c>
       <c r="D53" t="s">
-        <v>1394</v>
+        <v>1408</v>
       </c>
       <c r="E53" t="s">
         <v>604</v>
       </c>
       <c r="F53" t="s">
-        <v>1395</v>
+        <v>1409</v>
       </c>
       <c r="G53" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J53" t="s">
         <v>32</v>
@@ -19645,16 +19873,16 @@
         <v>25</v>
       </c>
       <c r="N53" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O53" t="s">
-        <v>1396</v>
+        <v>1410</v>
       </c>
       <c r="P53" t="s">
-        <v>1397</v>
+        <v>1411</v>
       </c>
       <c r="Q53" t="s">
-        <v>1398</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
@@ -19674,10 +19902,10 @@
         <v>63</v>
       </c>
       <c r="F54" t="s">
-        <v>1355</v>
+        <v>1369</v>
       </c>
       <c r="G54" t="s">
-        <v>1168</v>
+        <v>1182</v>
       </c>
       <c r="J54" t="s">
         <v>32</v>
@@ -19692,16 +19920,16 @@
         <v>25</v>
       </c>
       <c r="N54" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O54" t="s">
-        <v>1399</v>
+        <v>1413</v>
       </c>
       <c r="P54" t="s">
-        <v>1400</v>
+        <v>1414</v>
       </c>
       <c r="Q54" t="s">
-        <v>1401</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
@@ -19721,10 +19949,10 @@
         <v>63</v>
       </c>
       <c r="F55" t="s">
-        <v>1402</v>
+        <v>1416</v>
       </c>
       <c r="G55" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J55" t="s">
         <v>32</v>
@@ -19739,16 +19967,16 @@
         <v>38</v>
       </c>
       <c r="N55" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O55" t="s">
-        <v>1403</v>
+        <v>1417</v>
       </c>
       <c r="P55" t="s">
-        <v>1404</v>
+        <v>1418</v>
       </c>
       <c r="Q55" t="s">
-        <v>1405</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
@@ -19771,7 +19999,7 @@
         <v>883</v>
       </c>
       <c r="G56" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="H56">
         <v>180000</v>
@@ -19792,16 +20020,16 @@
         <v>25</v>
       </c>
       <c r="N56" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O56" t="s">
-        <v>1406</v>
+        <v>1420</v>
       </c>
       <c r="P56" t="s">
-        <v>1407</v>
+        <v>1421</v>
       </c>
       <c r="Q56" t="s">
-        <v>1408</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
@@ -19821,10 +20049,10 @@
         <v>63</v>
       </c>
       <c r="F57" t="s">
-        <v>1409</v>
+        <v>1423</v>
       </c>
       <c r="G57" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="H57">
         <v>180000</v>
@@ -19845,16 +20073,16 @@
         <v>25</v>
       </c>
       <c r="N57" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O57" t="s">
-        <v>1410</v>
+        <v>1424</v>
       </c>
       <c r="P57" t="s">
-        <v>1411</v>
+        <v>1425</v>
       </c>
       <c r="Q57" t="s">
-        <v>1412</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
@@ -19868,16 +20096,16 @@
         <v>20</v>
       </c>
       <c r="D58" t="s">
-        <v>1413</v>
+        <v>1427</v>
       </c>
       <c r="E58" t="s">
         <v>928</v>
       </c>
       <c r="F58" t="s">
-        <v>1414</v>
+        <v>1428</v>
       </c>
       <c r="G58" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J58" t="s">
         <v>32</v>
@@ -19892,16 +20120,16 @@
         <v>25</v>
       </c>
       <c r="N58" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O58" t="s">
-        <v>1415</v>
+        <v>1429</v>
       </c>
       <c r="P58" t="s">
-        <v>1416</v>
+        <v>1430</v>
       </c>
       <c r="Q58" t="s">
-        <v>1417</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
@@ -19915,7 +20143,7 @@
         <v>50</v>
       </c>
       <c r="D59" t="s">
-        <v>1418</v>
+        <v>1432</v>
       </c>
       <c r="E59" t="s">
         <v>928</v>
@@ -19924,7 +20152,7 @@
         <v>20</v>
       </c>
       <c r="G59" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="H59">
         <v>250000</v>
@@ -19945,16 +20173,16 @@
         <v>38</v>
       </c>
       <c r="N59" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O59" t="s">
-        <v>1419</v>
+        <v>1433</v>
       </c>
       <c r="P59" t="s">
-        <v>1420</v>
+        <v>1434</v>
       </c>
       <c r="Q59" t="s">
-        <v>1421</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
@@ -19968,7 +20196,7 @@
         <v>55</v>
       </c>
       <c r="D60" t="s">
-        <v>1422</v>
+        <v>1436</v>
       </c>
       <c r="E60" t="s">
         <v>928</v>
@@ -19977,7 +20205,7 @@
         <v>20</v>
       </c>
       <c r="G60" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="H60">
         <v>200000</v>
@@ -19998,16 +20226,16 @@
         <v>38</v>
       </c>
       <c r="N60" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O60" t="s">
-        <v>1423</v>
+        <v>1437</v>
       </c>
       <c r="P60" t="s">
-        <v>1424</v>
+        <v>1438</v>
       </c>
       <c r="Q60" t="s">
-        <v>1425</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
@@ -20021,7 +20249,7 @@
         <v>52</v>
       </c>
       <c r="D61" t="s">
-        <v>1426</v>
+        <v>1440</v>
       </c>
       <c r="E61" t="s">
         <v>928</v>
@@ -20030,7 +20258,7 @@
         <v>20</v>
       </c>
       <c r="G61" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="H61">
         <v>250000</v>
@@ -20051,16 +20279,16 @@
         <v>38</v>
       </c>
       <c r="N61" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O61" t="s">
-        <v>1427</v>
+        <v>1441</v>
       </c>
       <c r="P61" t="s">
-        <v>1428</v>
+        <v>1442</v>
       </c>
       <c r="Q61" t="s">
-        <v>1429</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
@@ -20074,7 +20302,7 @@
         <v>53</v>
       </c>
       <c r="D62" t="s">
-        <v>1430</v>
+        <v>1444</v>
       </c>
       <c r="E62" t="s">
         <v>928</v>
@@ -20083,7 +20311,7 @@
         <v>20</v>
       </c>
       <c r="G62" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="H62">
         <v>200000</v>
@@ -20104,16 +20332,16 @@
         <v>38</v>
       </c>
       <c r="N62" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O62" t="s">
-        <v>1431</v>
+        <v>1445</v>
       </c>
       <c r="P62" t="s">
-        <v>1432</v>
+        <v>1446</v>
       </c>
       <c r="Q62" t="s">
-        <v>1433</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
@@ -20127,7 +20355,7 @@
         <v>50</v>
       </c>
       <c r="D63" t="s">
-        <v>1434</v>
+        <v>1448</v>
       </c>
       <c r="E63" t="s">
         <v>928</v>
@@ -20136,7 +20364,7 @@
         <v>20</v>
       </c>
       <c r="G63" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="H63">
         <v>200000</v>
@@ -20157,16 +20385,16 @@
         <v>38</v>
       </c>
       <c r="N63" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O63" t="s">
-        <v>1435</v>
+        <v>1449</v>
       </c>
       <c r="P63" t="s">
-        <v>1436</v>
+        <v>1450</v>
       </c>
       <c r="Q63" t="s">
-        <v>1437</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
@@ -20180,7 +20408,7 @@
         <v>55</v>
       </c>
       <c r="D64" t="s">
-        <v>1438</v>
+        <v>1452</v>
       </c>
       <c r="E64" t="s">
         <v>928</v>
@@ -20189,7 +20417,7 @@
         <v>20</v>
       </c>
       <c r="G64" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="H64">
         <v>250000</v>
@@ -20210,16 +20438,16 @@
         <v>38</v>
       </c>
       <c r="N64" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O64" t="s">
-        <v>1439</v>
+        <v>1453</v>
       </c>
       <c r="P64" t="s">
-        <v>1440</v>
+        <v>1454</v>
       </c>
       <c r="Q64" t="s">
-        <v>1441</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
@@ -20233,16 +20461,16 @@
         <v>45</v>
       </c>
       <c r="D65" t="s">
-        <v>1442</v>
+        <v>1456</v>
       </c>
       <c r="E65" t="s">
-        <v>1443</v>
+        <v>1457</v>
       </c>
       <c r="F65" t="s">
-        <v>1444</v>
+        <v>1458</v>
       </c>
       <c r="G65" t="s">
-        <v>1168</v>
+        <v>1182</v>
       </c>
       <c r="H65">
         <v>154000</v>
@@ -20263,16 +20491,16 @@
         <v>25</v>
       </c>
       <c r="N65" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O65" t="s">
-        <v>1445</v>
+        <v>1459</v>
       </c>
       <c r="P65" t="s">
-        <v>1446</v>
+        <v>1460</v>
       </c>
       <c r="Q65" t="s">
-        <v>1447</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
@@ -20295,7 +20523,7 @@
         <v>563</v>
       </c>
       <c r="G66" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="H66">
         <v>180000</v>
@@ -20316,16 +20544,16 @@
         <v>38</v>
       </c>
       <c r="N66" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O66" t="s">
-        <v>1448</v>
+        <v>1462</v>
       </c>
       <c r="P66" t="s">
-        <v>1449</v>
+        <v>1463</v>
       </c>
       <c r="Q66" t="s">
-        <v>1450</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
@@ -20345,10 +20573,10 @@
         <v>63</v>
       </c>
       <c r="F67" t="s">
-        <v>1304</v>
+        <v>1318</v>
       </c>
       <c r="G67" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="H67">
         <v>219100</v>
@@ -20369,16 +20597,16 @@
         <v>25</v>
       </c>
       <c r="N67" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O67" t="s">
-        <v>1451</v>
+        <v>1465</v>
       </c>
       <c r="P67" t="s">
-        <v>1452</v>
+        <v>1466</v>
       </c>
       <c r="Q67" t="s">
-        <v>1453</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
@@ -20392,7 +20620,7 @@
         <v>25</v>
       </c>
       <c r="D68" t="s">
-        <v>1454</v>
+        <v>1468</v>
       </c>
       <c r="E68" t="s">
         <v>63</v>
@@ -20401,7 +20629,7 @@
         <v>1133</v>
       </c>
       <c r="G68" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J68" t="s">
         <v>32</v>
@@ -20416,16 +20644,16 @@
         <v>25</v>
       </c>
       <c r="N68" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O68" t="s">
-        <v>1455</v>
+        <v>1469</v>
       </c>
       <c r="P68" t="s">
-        <v>1456</v>
+        <v>1470</v>
       </c>
       <c r="Q68" t="s">
-        <v>1457</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
@@ -20445,10 +20673,10 @@
         <v>817</v>
       </c>
       <c r="F69" t="s">
-        <v>1245</v>
+        <v>1259</v>
       </c>
       <c r="G69" t="s">
-        <v>1168</v>
+        <v>1182</v>
       </c>
       <c r="J69" t="s">
         <v>32</v>
@@ -20463,16 +20691,16 @@
         <v>25</v>
       </c>
       <c r="N69" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O69" t="s">
-        <v>1458</v>
+        <v>1472</v>
       </c>
       <c r="P69" t="s">
-        <v>1459</v>
+        <v>1473</v>
       </c>
       <c r="Q69" t="s">
-        <v>1460</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
@@ -20486,16 +20714,16 @@
         <v>15</v>
       </c>
       <c r="D70" t="s">
-        <v>1461</v>
+        <v>1475</v>
       </c>
       <c r="E70" t="s">
-        <v>1462</v>
+        <v>1476</v>
       </c>
       <c r="F70" t="s">
         <v>1149</v>
       </c>
       <c r="G70" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J70" t="s">
         <v>32</v>
@@ -20510,16 +20738,16 @@
         <v>25</v>
       </c>
       <c r="N70" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O70" t="s">
-        <v>1463</v>
+        <v>1477</v>
       </c>
       <c r="P70" t="s">
-        <v>1464</v>
+        <v>1478</v>
       </c>
       <c r="Q70" t="s">
-        <v>1465</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
@@ -20533,16 +20761,16 @@
         <v>12</v>
       </c>
       <c r="D71" t="s">
-        <v>1466</v>
+        <v>1480</v>
       </c>
       <c r="E71" t="s">
-        <v>1467</v>
+        <v>1481</v>
       </c>
       <c r="F71" t="s">
-        <v>1468</v>
+        <v>1482</v>
       </c>
       <c r="G71" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J71" t="s">
         <v>32</v>
@@ -20557,16 +20785,16 @@
         <v>25</v>
       </c>
       <c r="N71" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O71" t="s">
-        <v>1469</v>
+        <v>1483</v>
       </c>
       <c r="P71" t="s">
-        <v>1470</v>
+        <v>1484</v>
       </c>
       <c r="Q71" t="s">
-        <v>1471</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
@@ -20580,16 +20808,16 @@
         <v>42</v>
       </c>
       <c r="D72" t="s">
-        <v>1472</v>
+        <v>1486</v>
       </c>
       <c r="E72" t="s">
         <v>63</v>
       </c>
       <c r="F72" t="s">
-        <v>1473</v>
+        <v>1487</v>
       </c>
       <c r="G72" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="H72">
         <v>180000</v>
@@ -20610,16 +20838,16 @@
         <v>38</v>
       </c>
       <c r="N72" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O72" t="s">
-        <v>1474</v>
+        <v>1488</v>
       </c>
       <c r="P72" t="s">
-        <v>1475</v>
+        <v>1489</v>
       </c>
       <c r="Q72" t="s">
-        <v>1476</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
@@ -20633,16 +20861,16 @@
         <v>22</v>
       </c>
       <c r="D73" t="s">
-        <v>1477</v>
+        <v>1491</v>
       </c>
       <c r="E73" t="s">
-        <v>1205</v>
+        <v>1219</v>
       </c>
       <c r="F73" t="s">
-        <v>1478</v>
+        <v>1492</v>
       </c>
       <c r="G73" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="H73">
         <v>200000</v>
@@ -20663,16 +20891,16 @@
         <v>25</v>
       </c>
       <c r="N73" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O73" t="s">
-        <v>1479</v>
+        <v>1493</v>
       </c>
       <c r="P73" t="s">
-        <v>1480</v>
+        <v>1494</v>
       </c>
       <c r="Q73" t="s">
-        <v>1481</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
@@ -20686,16 +20914,16 @@
         <v>28</v>
       </c>
       <c r="D74" t="s">
-        <v>1482</v>
+        <v>1496</v>
       </c>
       <c r="E74" t="s">
-        <v>1483</v>
+        <v>1497</v>
       </c>
       <c r="F74" t="s">
         <v>1133</v>
       </c>
       <c r="G74" t="s">
-        <v>1168</v>
+        <v>1182</v>
       </c>
       <c r="J74" t="s">
         <v>32</v>
@@ -20710,16 +20938,16 @@
         <v>25</v>
       </c>
       <c r="N74" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O74" t="s">
-        <v>1484</v>
+        <v>1498</v>
       </c>
       <c r="P74" t="s">
-        <v>1485</v>
+        <v>1499</v>
       </c>
       <c r="Q74" t="s">
-        <v>1486</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
@@ -20733,16 +20961,16 @@
         <v>5</v>
       </c>
       <c r="D75" t="s">
-        <v>1487</v>
+        <v>1501</v>
       </c>
       <c r="E75" t="s">
-        <v>1488</v>
+        <v>1502</v>
       </c>
       <c r="F75" t="s">
-        <v>1489</v>
+        <v>1503</v>
       </c>
       <c r="G75" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J75" t="s">
         <v>32</v>
@@ -20757,16 +20985,16 @@
         <v>25</v>
       </c>
       <c r="N75" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O75" t="s">
-        <v>1490</v>
+        <v>1504</v>
       </c>
       <c r="P75" t="s">
-        <v>1491</v>
+        <v>1505</v>
       </c>
       <c r="Q75" t="s">
-        <v>1492</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
@@ -20786,10 +21014,10 @@
         <v>63</v>
       </c>
       <c r="F76" t="s">
-        <v>1493</v>
+        <v>1507</v>
       </c>
       <c r="G76" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J76" t="s">
         <v>32</v>
@@ -20804,16 +21032,16 @@
         <v>38</v>
       </c>
       <c r="N76" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O76" t="s">
-        <v>1494</v>
+        <v>1508</v>
       </c>
       <c r="P76" t="s">
-        <v>1495</v>
+        <v>1509</v>
       </c>
       <c r="Q76" t="s">
-        <v>1496</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
@@ -20827,16 +21055,16 @@
         <v>35</v>
       </c>
       <c r="D77" t="s">
-        <v>1497</v>
+        <v>1511</v>
       </c>
       <c r="E77" t="s">
-        <v>1498</v>
+        <v>1512</v>
       </c>
       <c r="F77" t="s">
-        <v>1267</v>
+        <v>1281</v>
       </c>
       <c r="G77" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J77" t="s">
         <v>32</v>
@@ -20851,16 +21079,16 @@
         <v>25</v>
       </c>
       <c r="N77" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O77" t="s">
-        <v>1499</v>
+        <v>1513</v>
       </c>
       <c r="P77" t="s">
-        <v>1500</v>
+        <v>1514</v>
       </c>
       <c r="Q77" t="s">
-        <v>1501</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
@@ -20874,16 +21102,16 @@
         <v>55</v>
       </c>
       <c r="D78" t="s">
-        <v>1502</v>
+        <v>1516</v>
       </c>
       <c r="E78" t="s">
         <v>63</v>
       </c>
       <c r="F78" t="s">
-        <v>1304</v>
+        <v>1318</v>
       </c>
       <c r="G78" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="H78">
         <v>219100</v>
@@ -20898,22 +21126,22 @@
         <v>65</v>
       </c>
       <c r="L78" t="s">
-        <v>1503</v>
+        <v>1517</v>
       </c>
       <c r="M78" t="s">
         <v>38</v>
       </c>
       <c r="N78" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O78" t="s">
-        <v>1504</v>
+        <v>1518</v>
       </c>
       <c r="P78" t="s">
-        <v>1505</v>
+        <v>1519</v>
       </c>
       <c r="Q78" t="s">
-        <v>1506</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
@@ -20927,16 +21155,16 @@
         <v>50</v>
       </c>
       <c r="D79" t="s">
-        <v>1507</v>
+        <v>1521</v>
       </c>
       <c r="E79" t="s">
-        <v>1205</v>
+        <v>1219</v>
       </c>
       <c r="F79" t="s">
         <v>20</v>
       </c>
       <c r="G79" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="H79">
         <v>200000</v>
@@ -20951,22 +21179,22 @@
         <v>65</v>
       </c>
       <c r="L79" t="s">
-        <v>1503</v>
+        <v>1517</v>
       </c>
       <c r="M79" t="s">
         <v>38</v>
       </c>
       <c r="N79" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O79" t="s">
-        <v>1508</v>
+        <v>1522</v>
       </c>
       <c r="P79" t="s">
-        <v>1509</v>
+        <v>1523</v>
       </c>
       <c r="Q79" t="s">
-        <v>1510</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
@@ -20980,16 +21208,16 @@
         <v>12</v>
       </c>
       <c r="D80" t="s">
-        <v>1511</v>
+        <v>1525</v>
       </c>
       <c r="E80" t="s">
-        <v>1512</v>
+        <v>1526</v>
       </c>
       <c r="F80" t="s">
         <v>1133</v>
       </c>
       <c r="G80" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J80" t="s">
         <v>32</v>
@@ -20998,22 +21226,22 @@
         <v>99</v>
       </c>
       <c r="L80" t="s">
-        <v>1503</v>
+        <v>1517</v>
       </c>
       <c r="M80" t="s">
         <v>25</v>
       </c>
       <c r="N80" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O80" t="s">
-        <v>1513</v>
+        <v>1527</v>
       </c>
       <c r="P80" t="s">
-        <v>1514</v>
+        <v>1528</v>
       </c>
       <c r="Q80" t="s">
-        <v>1515</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
@@ -21027,16 +21255,16 @@
         <v>12</v>
       </c>
       <c r="D81" t="s">
-        <v>1516</v>
+        <v>1530</v>
       </c>
       <c r="E81" t="s">
-        <v>1512</v>
+        <v>1526</v>
       </c>
       <c r="F81" t="s">
         <v>1133</v>
       </c>
       <c r="G81" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J81" t="s">
         <v>32</v>
@@ -21045,22 +21273,22 @@
         <v>99</v>
       </c>
       <c r="L81" t="s">
-        <v>1503</v>
+        <v>1517</v>
       </c>
       <c r="M81" t="s">
         <v>25</v>
       </c>
       <c r="N81" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O81" t="s">
-        <v>1517</v>
+        <v>1531</v>
       </c>
       <c r="P81" t="s">
-        <v>1518</v>
+        <v>1532</v>
       </c>
       <c r="Q81" t="s">
-        <v>1519</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
@@ -21074,16 +21302,16 @@
         <v>3</v>
       </c>
       <c r="D82" t="s">
-        <v>1520</v>
+        <v>1534</v>
       </c>
       <c r="E82" t="s">
-        <v>1512</v>
+        <v>1526</v>
       </c>
       <c r="F82" t="s">
         <v>1133</v>
       </c>
       <c r="G82" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J82" t="s">
         <v>32</v>
@@ -21092,22 +21320,22 @@
         <v>99</v>
       </c>
       <c r="L82" t="s">
-        <v>1503</v>
+        <v>1517</v>
       </c>
       <c r="M82" t="s">
         <v>25</v>
       </c>
       <c r="N82" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O82" t="s">
-        <v>1521</v>
+        <v>1535</v>
       </c>
       <c r="P82" t="s">
-        <v>1522</v>
+        <v>1536</v>
       </c>
       <c r="Q82" t="s">
-        <v>1523</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
@@ -21121,16 +21349,16 @@
         <v>25</v>
       </c>
       <c r="D83" t="s">
-        <v>1524</v>
+        <v>1538</v>
       </c>
       <c r="E83" t="s">
-        <v>1525</v>
+        <v>1539</v>
       </c>
       <c r="F83" t="s">
-        <v>1526</v>
+        <v>1540</v>
       </c>
       <c r="G83" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J83" t="s">
         <v>32</v>
@@ -21139,22 +21367,22 @@
         <v>99</v>
       </c>
       <c r="L83" t="s">
-        <v>1503</v>
+        <v>1517</v>
       </c>
       <c r="M83" t="s">
         <v>25</v>
       </c>
       <c r="N83" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O83" t="s">
-        <v>1527</v>
+        <v>1541</v>
       </c>
       <c r="P83" t="s">
-        <v>1528</v>
+        <v>1542</v>
       </c>
       <c r="Q83" t="s">
-        <v>1529</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
@@ -21168,16 +21396,16 @@
         <v>62</v>
       </c>
       <c r="D84" t="s">
-        <v>1530</v>
+        <v>1544</v>
       </c>
       <c r="E84" t="s">
-        <v>1531</v>
+        <v>1545</v>
       </c>
       <c r="F84" t="s">
-        <v>1532</v>
+        <v>1546</v>
       </c>
       <c r="G84" t="s">
-        <v>1168</v>
+        <v>1182</v>
       </c>
       <c r="J84" t="s">
         <v>32</v>
@@ -21186,22 +21414,22 @@
         <v>99</v>
       </c>
       <c r="L84" t="s">
-        <v>1503</v>
+        <v>1517</v>
       </c>
       <c r="M84" t="s">
         <v>25</v>
       </c>
       <c r="N84" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O84" t="s">
-        <v>1533</v>
+        <v>1547</v>
       </c>
       <c r="P84" t="s">
-        <v>1534</v>
+        <v>1548</v>
       </c>
       <c r="Q84" t="s">
-        <v>1535</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
@@ -21215,16 +21443,16 @@
         <v>68</v>
       </c>
       <c r="D85" t="s">
-        <v>1536</v>
+        <v>1550</v>
       </c>
       <c r="E85" t="s">
-        <v>1531</v>
+        <v>1545</v>
       </c>
       <c r="F85" t="s">
-        <v>1532</v>
+        <v>1546</v>
       </c>
       <c r="G85" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J85" t="s">
         <v>32</v>
@@ -21233,22 +21461,22 @@
         <v>99</v>
       </c>
       <c r="L85" t="s">
-        <v>1503</v>
+        <v>1517</v>
       </c>
       <c r="M85" t="s">
         <v>25</v>
       </c>
       <c r="N85" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O85" t="s">
-        <v>1537</v>
+        <v>1551</v>
       </c>
       <c r="P85" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="Q85" t="s">
-        <v>1539</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
@@ -21268,10 +21496,10 @@
         <v>63</v>
       </c>
       <c r="F86" t="s">
-        <v>1540</v>
+        <v>1554</v>
       </c>
       <c r="G86" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="H86">
         <v>180000</v>
@@ -21292,16 +21520,16 @@
         <v>38</v>
       </c>
       <c r="N86" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O86" t="s">
-        <v>1541</v>
+        <v>1555</v>
       </c>
       <c r="P86" t="s">
-        <v>1542</v>
+        <v>1556</v>
       </c>
       <c r="Q86" t="s">
-        <v>1543</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
@@ -21321,10 +21549,10 @@
         <v>63</v>
       </c>
       <c r="F87" t="s">
-        <v>1544</v>
+        <v>1558</v>
       </c>
       <c r="G87" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="H87">
         <v>180000</v>
@@ -21345,16 +21573,16 @@
         <v>38</v>
       </c>
       <c r="N87" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O87" t="s">
-        <v>1545</v>
+        <v>1559</v>
       </c>
       <c r="P87" t="s">
-        <v>1546</v>
+        <v>1560</v>
       </c>
       <c r="Q87" t="s">
-        <v>1547</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
@@ -21368,16 +21596,16 @@
         <v>35</v>
       </c>
       <c r="D88" t="s">
-        <v>1548</v>
+        <v>1562</v>
       </c>
       <c r="E88" t="s">
         <v>63</v>
       </c>
       <c r="F88" t="s">
-        <v>1549</v>
+        <v>1563</v>
       </c>
       <c r="G88" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="H88">
         <v>219100</v>
@@ -21398,16 +21626,16 @@
         <v>38</v>
       </c>
       <c r="N88" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O88" t="s">
-        <v>1550</v>
+        <v>1564</v>
       </c>
       <c r="P88" t="s">
-        <v>1551</v>
+        <v>1565</v>
       </c>
       <c r="Q88" t="s">
-        <v>1552</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
@@ -21421,16 +21649,16 @@
         <v>25</v>
       </c>
       <c r="D89" t="s">
-        <v>1553</v>
+        <v>1567</v>
       </c>
       <c r="E89" t="s">
         <v>604</v>
       </c>
       <c r="F89" t="s">
-        <v>1371</v>
+        <v>1385</v>
       </c>
       <c r="G89" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J89" t="s">
         <v>32</v>
@@ -21445,16 +21673,16 @@
         <v>25</v>
       </c>
       <c r="N89" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O89" t="s">
-        <v>1554</v>
+        <v>1568</v>
       </c>
       <c r="P89" t="s">
-        <v>1555</v>
+        <v>1569</v>
       </c>
       <c r="Q89" t="s">
-        <v>1556</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
@@ -21468,16 +21696,16 @@
         <v>35</v>
       </c>
       <c r="D90" t="s">
-        <v>1557</v>
+        <v>1571</v>
       </c>
       <c r="E90" t="s">
-        <v>1558</v>
+        <v>1572</v>
       </c>
       <c r="F90" t="s">
-        <v>1245</v>
+        <v>1259</v>
       </c>
       <c r="G90" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J90" t="s">
         <v>32</v>
@@ -21492,16 +21720,16 @@
         <v>25</v>
       </c>
       <c r="N90" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O90" t="s">
-        <v>1559</v>
+        <v>1573</v>
       </c>
       <c r="P90" t="s">
-        <v>1560</v>
+        <v>1574</v>
       </c>
       <c r="Q90" t="s">
-        <v>1561</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
@@ -21518,13 +21746,13 @@
         <v>276</v>
       </c>
       <c r="E91" t="s">
-        <v>1562</v>
+        <v>1576</v>
       </c>
       <c r="F91" t="s">
-        <v>1267</v>
+        <v>1281</v>
       </c>
       <c r="G91" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="H91">
         <v>200000</v>
@@ -21545,16 +21773,16 @@
         <v>25</v>
       </c>
       <c r="N91" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O91" t="s">
-        <v>1563</v>
+        <v>1577</v>
       </c>
       <c r="P91" t="s">
-        <v>1564</v>
+        <v>1578</v>
       </c>
       <c r="Q91" t="s">
-        <v>1565</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
@@ -21568,16 +21796,16 @@
         <v>38</v>
       </c>
       <c r="D92" t="s">
-        <v>1566</v>
+        <v>1580</v>
       </c>
       <c r="E92" t="s">
-        <v>1562</v>
+        <v>1576</v>
       </c>
       <c r="F92" t="s">
-        <v>1267</v>
+        <v>1281</v>
       </c>
       <c r="G92" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="H92">
         <v>200000</v>
@@ -21598,16 +21826,16 @@
         <v>25</v>
       </c>
       <c r="N92" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O92" t="s">
-        <v>1567</v>
+        <v>1581</v>
       </c>
       <c r="P92" t="s">
-        <v>1568</v>
+        <v>1582</v>
       </c>
       <c r="Q92" t="s">
-        <v>1569</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
@@ -21621,16 +21849,16 @@
         <v>40</v>
       </c>
       <c r="D93" t="s">
-        <v>1349</v>
+        <v>1363</v>
       </c>
       <c r="E93" t="s">
-        <v>1205</v>
+        <v>1219</v>
       </c>
       <c r="F93" t="s">
         <v>832</v>
       </c>
       <c r="G93" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="H93">
         <v>184200</v>
@@ -21651,16 +21879,16 @@
         <v>25</v>
       </c>
       <c r="N93" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O93" t="s">
-        <v>1570</v>
+        <v>1584</v>
       </c>
       <c r="P93" t="s">
-        <v>1571</v>
+        <v>1585</v>
       </c>
       <c r="Q93" t="s">
-        <v>1572</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
@@ -21674,16 +21902,16 @@
         <v>20</v>
       </c>
       <c r="D94" t="s">
-        <v>1573</v>
+        <v>1587</v>
       </c>
       <c r="E94" t="s">
-        <v>1574</v>
+        <v>1588</v>
       </c>
       <c r="F94" t="s">
-        <v>1575</v>
+        <v>1589</v>
       </c>
       <c r="G94" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J94" t="s">
         <v>32</v>
@@ -21698,16 +21926,16 @@
         <v>25</v>
       </c>
       <c r="N94" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O94" t="s">
-        <v>1576</v>
+        <v>1590</v>
       </c>
       <c r="P94" t="s">
-        <v>1577</v>
+        <v>1591</v>
       </c>
       <c r="Q94" t="s">
-        <v>1578</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
@@ -21721,16 +21949,16 @@
         <v>35</v>
       </c>
       <c r="D95" t="s">
-        <v>1579</v>
+        <v>1593</v>
       </c>
       <c r="E95" t="s">
-        <v>1580</v>
+        <v>1594</v>
       </c>
       <c r="F95" t="s">
-        <v>1581</v>
+        <v>1595</v>
       </c>
       <c r="G95" t="s">
-        <v>1168</v>
+        <v>1182</v>
       </c>
       <c r="H95">
         <v>230000</v>
@@ -21751,16 +21979,16 @@
         <v>25</v>
       </c>
       <c r="N95" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O95" t="s">
-        <v>1582</v>
+        <v>1596</v>
       </c>
       <c r="P95" t="s">
-        <v>1583</v>
+        <v>1597</v>
       </c>
       <c r="Q95" t="s">
-        <v>1584</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
@@ -21780,10 +22008,10 @@
         <v>63</v>
       </c>
       <c r="F96" t="s">
-        <v>1585</v>
+        <v>1599</v>
       </c>
       <c r="G96" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="H96">
         <v>219100</v>
@@ -21804,16 +22032,16 @@
         <v>75</v>
       </c>
       <c r="N96" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O96" t="s">
-        <v>1586</v>
+        <v>1600</v>
       </c>
       <c r="P96" t="s">
-        <v>1587</v>
+        <v>1601</v>
       </c>
       <c r="Q96" t="s">
-        <v>1588</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
@@ -21827,16 +22055,16 @@
         <v>25</v>
       </c>
       <c r="D97" t="s">
-        <v>1589</v>
+        <v>1603</v>
       </c>
       <c r="E97" t="s">
-        <v>1498</v>
+        <v>1512</v>
       </c>
       <c r="F97" t="s">
-        <v>1267</v>
+        <v>1281</v>
       </c>
       <c r="G97" t="s">
-        <v>1168</v>
+        <v>1182</v>
       </c>
       <c r="J97" t="s">
         <v>32</v>
@@ -21851,16 +22079,16 @@
         <v>25</v>
       </c>
       <c r="N97" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O97" t="s">
-        <v>1590</v>
+        <v>1604</v>
       </c>
       <c r="P97" t="s">
-        <v>1591</v>
+        <v>1605</v>
       </c>
       <c r="Q97" t="s">
-        <v>1592</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
@@ -21874,16 +22102,16 @@
         <v>22</v>
       </c>
       <c r="D98" t="s">
-        <v>1593</v>
+        <v>1607</v>
       </c>
       <c r="E98" t="s">
-        <v>1594</v>
+        <v>1608</v>
       </c>
       <c r="F98" t="s">
-        <v>1595</v>
+        <v>1609</v>
       </c>
       <c r="G98" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J98" t="s">
         <v>32</v>
@@ -21898,16 +22126,16 @@
         <v>25</v>
       </c>
       <c r="N98" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O98" t="s">
-        <v>1596</v>
+        <v>1610</v>
       </c>
       <c r="P98" t="s">
-        <v>1597</v>
+        <v>1611</v>
       </c>
       <c r="Q98" t="s">
-        <v>1598</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.25">
@@ -21921,16 +22149,16 @@
         <v>3</v>
       </c>
       <c r="D99" t="s">
-        <v>1599</v>
+        <v>1613</v>
       </c>
       <c r="E99" t="s">
-        <v>1600</v>
+        <v>1614</v>
       </c>
       <c r="F99" t="s">
-        <v>1595</v>
+        <v>1609</v>
       </c>
       <c r="G99" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J99" t="s">
         <v>32</v>
@@ -21945,16 +22173,16 @@
         <v>25</v>
       </c>
       <c r="N99" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O99" t="s">
-        <v>1601</v>
+        <v>1615</v>
       </c>
       <c r="P99" t="s">
-        <v>1602</v>
+        <v>1616</v>
       </c>
       <c r="Q99" t="s">
-        <v>1603</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.25">
@@ -21968,16 +22196,16 @@
         <v>28</v>
       </c>
       <c r="D100" t="s">
-        <v>1604</v>
+        <v>1618</v>
       </c>
       <c r="E100" t="s">
-        <v>1605</v>
+        <v>1619</v>
       </c>
       <c r="F100" t="s">
         <v>1133</v>
       </c>
       <c r="G100" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J100" t="s">
         <v>32</v>
@@ -21992,16 +22220,16 @@
         <v>25</v>
       </c>
       <c r="N100" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O100" t="s">
-        <v>1606</v>
+        <v>1620</v>
       </c>
       <c r="P100" t="s">
-        <v>1607</v>
+        <v>1621</v>
       </c>
       <c r="Q100" t="s">
-        <v>1608</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.25">
@@ -22015,16 +22243,16 @@
         <v>45</v>
       </c>
       <c r="D101" t="s">
-        <v>1609</v>
+        <v>1623</v>
       </c>
       <c r="E101" t="s">
-        <v>1610</v>
+        <v>1624</v>
       </c>
       <c r="F101" t="s">
-        <v>1245</v>
+        <v>1259</v>
       </c>
       <c r="G101" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J101" t="s">
         <v>32</v>
@@ -22039,16 +22267,16 @@
         <v>38</v>
       </c>
       <c r="N101" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O101" t="s">
-        <v>1611</v>
+        <v>1625</v>
       </c>
       <c r="P101" t="s">
-        <v>1612</v>
+        <v>1626</v>
       </c>
       <c r="Q101" t="s">
-        <v>1613</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.25">
@@ -22062,16 +22290,16 @@
         <v>50</v>
       </c>
       <c r="D102" t="s">
-        <v>1614</v>
+        <v>1628</v>
       </c>
       <c r="E102" t="s">
-        <v>1615</v>
+        <v>1629</v>
       </c>
       <c r="F102" t="s">
-        <v>1278</v>
+        <v>1292</v>
       </c>
       <c r="G102" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J102" t="s">
         <v>32</v>
@@ -22086,16 +22314,16 @@
         <v>38</v>
       </c>
       <c r="N102" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O102" t="s">
-        <v>1616</v>
+        <v>1630</v>
       </c>
       <c r="P102" t="s">
-        <v>1617</v>
+        <v>1631</v>
       </c>
       <c r="Q102" t="s">
-        <v>1618</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.25">
@@ -22109,16 +22337,16 @@
         <v>48</v>
       </c>
       <c r="D103" t="s">
-        <v>1619</v>
+        <v>1633</v>
       </c>
       <c r="E103" t="s">
-        <v>1443</v>
+        <v>1457</v>
       </c>
       <c r="F103" t="s">
-        <v>1620</v>
+        <v>1634</v>
       </c>
       <c r="G103" t="s">
-        <v>1168</v>
+        <v>1182</v>
       </c>
       <c r="H103">
         <v>154000</v>
@@ -22139,16 +22367,16 @@
         <v>38</v>
       </c>
       <c r="N103" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O103" t="s">
-        <v>1621</v>
+        <v>1635</v>
       </c>
       <c r="P103" t="s">
-        <v>1622</v>
+        <v>1636</v>
       </c>
       <c r="Q103" t="s">
-        <v>1623</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.25">
@@ -22162,16 +22390,16 @@
         <v>25</v>
       </c>
       <c r="D104" t="s">
-        <v>1624</v>
+        <v>1638</v>
       </c>
       <c r="E104" t="s">
-        <v>1266</v>
+        <v>1280</v>
       </c>
       <c r="F104" t="s">
-        <v>1267</v>
+        <v>1281</v>
       </c>
       <c r="G104" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J104" t="s">
         <v>32</v>
@@ -22186,16 +22414,16 @@
         <v>25</v>
       </c>
       <c r="N104" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O104" t="s">
-        <v>1625</v>
+        <v>1639</v>
       </c>
       <c r="P104" t="s">
-        <v>1626</v>
+        <v>1640</v>
       </c>
       <c r="Q104" t="s">
-        <v>1627</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.25">
@@ -22209,16 +22437,16 @@
         <v>32</v>
       </c>
       <c r="D105" t="s">
-        <v>1524</v>
+        <v>1538</v>
       </c>
       <c r="E105" t="s">
-        <v>1266</v>
+        <v>1280</v>
       </c>
       <c r="F105" t="s">
-        <v>1267</v>
+        <v>1281</v>
       </c>
       <c r="G105" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J105" t="s">
         <v>32</v>
@@ -22233,16 +22461,16 @@
         <v>25</v>
       </c>
       <c r="N105" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O105" t="s">
-        <v>1628</v>
+        <v>1642</v>
       </c>
       <c r="P105" t="s">
-        <v>1629</v>
+        <v>1643</v>
       </c>
       <c r="Q105" t="s">
-        <v>1630</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.25">
@@ -22256,16 +22484,16 @@
         <v>22</v>
       </c>
       <c r="D106" t="s">
-        <v>1631</v>
+        <v>1645</v>
       </c>
       <c r="E106" t="s">
-        <v>1615</v>
+        <v>1629</v>
       </c>
       <c r="F106" t="s">
-        <v>1595</v>
+        <v>1609</v>
       </c>
       <c r="G106" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J106" t="s">
         <v>32</v>
@@ -22280,16 +22508,16 @@
         <v>25</v>
       </c>
       <c r="N106" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O106" t="s">
-        <v>1632</v>
+        <v>1646</v>
       </c>
       <c r="P106" t="s">
-        <v>1633</v>
+        <v>1647</v>
       </c>
       <c r="Q106" t="s">
-        <v>1634</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.25">
@@ -22303,16 +22531,16 @@
         <v>55</v>
       </c>
       <c r="D107" t="s">
-        <v>1614</v>
+        <v>1628</v>
       </c>
       <c r="E107" t="s">
-        <v>1615</v>
+        <v>1629</v>
       </c>
       <c r="F107" t="s">
-        <v>1635</v>
+        <v>1649</v>
       </c>
       <c r="G107" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J107" t="s">
         <v>32</v>
@@ -22327,16 +22555,16 @@
         <v>25</v>
       </c>
       <c r="N107" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O107" t="s">
-        <v>1636</v>
+        <v>1650</v>
       </c>
       <c r="P107" t="s">
-        <v>1637</v>
+        <v>1651</v>
       </c>
       <c r="Q107" t="s">
-        <v>1638</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.25">
@@ -22350,16 +22578,16 @@
         <v>25</v>
       </c>
       <c r="D108" t="s">
-        <v>1639</v>
+        <v>1653</v>
       </c>
       <c r="E108" t="s">
-        <v>1615</v>
+        <v>1629</v>
       </c>
       <c r="F108" t="s">
-        <v>1635</v>
+        <v>1649</v>
       </c>
       <c r="G108" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J108" t="s">
         <v>32</v>
@@ -22374,16 +22602,16 @@
         <v>25</v>
       </c>
       <c r="N108" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O108" t="s">
-        <v>1640</v>
+        <v>1654</v>
       </c>
       <c r="P108" t="s">
-        <v>1641</v>
+        <v>1655</v>
       </c>
       <c r="Q108" t="s">
-        <v>1642</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.25">
@@ -22397,7 +22625,7 @@
         <v>33</v>
       </c>
       <c r="D109" t="s">
-        <v>1643</v>
+        <v>1657</v>
       </c>
       <c r="E109" t="s">
         <v>63</v>
@@ -22406,7 +22634,7 @@
         <v>1133</v>
       </c>
       <c r="G109" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J109" t="s">
         <v>32</v>
@@ -22421,16 +22649,16 @@
         <v>25</v>
       </c>
       <c r="N109" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O109" t="s">
-        <v>1644</v>
+        <v>1658</v>
       </c>
       <c r="P109" t="s">
-        <v>1645</v>
+        <v>1659</v>
       </c>
       <c r="Q109" t="s">
-        <v>1646</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.25">
@@ -22444,16 +22672,16 @@
         <v>38</v>
       </c>
       <c r="D110" t="s">
-        <v>1647</v>
+        <v>1661</v>
       </c>
       <c r="E110" t="s">
-        <v>1648</v>
+        <v>1662</v>
       </c>
       <c r="F110" t="s">
-        <v>1376</v>
+        <v>1390</v>
       </c>
       <c r="G110" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="H110">
         <v>220000</v>
@@ -22474,16 +22702,16 @@
         <v>25</v>
       </c>
       <c r="N110" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O110" t="s">
-        <v>1649</v>
+        <v>1663</v>
       </c>
       <c r="P110" t="s">
-        <v>1650</v>
+        <v>1664</v>
       </c>
       <c r="Q110" t="s">
-        <v>1651</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.25">
@@ -22497,16 +22725,16 @@
         <v>62</v>
       </c>
       <c r="D111" t="s">
-        <v>1652</v>
+        <v>1666</v>
       </c>
       <c r="E111" t="s">
-        <v>1205</v>
+        <v>1219</v>
       </c>
       <c r="F111" t="s">
         <v>20</v>
       </c>
       <c r="G111" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="H111">
         <v>200000</v>
@@ -22527,16 +22755,16 @@
         <v>38</v>
       </c>
       <c r="N111" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O111" t="s">
-        <v>1653</v>
+        <v>1667</v>
       </c>
       <c r="P111" t="s">
-        <v>1654</v>
+        <v>1668</v>
       </c>
       <c r="Q111" t="s">
-        <v>1655</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.25">
@@ -22550,16 +22778,16 @@
         <v>30</v>
       </c>
       <c r="D112" t="s">
-        <v>1639</v>
+        <v>1653</v>
       </c>
       <c r="E112" t="s">
-        <v>1615</v>
+        <v>1629</v>
       </c>
       <c r="F112" t="s">
-        <v>1595</v>
+        <v>1609</v>
       </c>
       <c r="G112" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J112" t="s">
         <v>32</v>
@@ -22574,16 +22802,16 @@
         <v>25</v>
       </c>
       <c r="N112" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O112" t="s">
-        <v>1656</v>
+        <v>1670</v>
       </c>
       <c r="P112" t="s">
-        <v>1657</v>
+        <v>1671</v>
       </c>
       <c r="Q112" t="s">
-        <v>1658</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.25">
@@ -22597,16 +22825,16 @@
         <v>58</v>
       </c>
       <c r="D113" t="s">
-        <v>1614</v>
+        <v>1628</v>
       </c>
       <c r="E113" t="s">
-        <v>1615</v>
+        <v>1629</v>
       </c>
       <c r="F113" t="s">
-        <v>1278</v>
+        <v>1292</v>
       </c>
       <c r="G113" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
       <c r="J113" t="s">
         <v>32</v>
@@ -22621,16 +22849,169 @@
         <v>25</v>
       </c>
       <c r="N113" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="O113" t="s">
-        <v>1659</v>
+        <v>1673</v>
       </c>
       <c r="P113" t="s">
-        <v>1660</v>
+        <v>1674</v>
       </c>
       <c r="Q113" t="s">
-        <v>1661</v>
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>17</v>
+      </c>
+      <c r="B114">
+        <v>58</v>
+      </c>
+      <c r="C114">
+        <v>55</v>
+      </c>
+      <c r="D114" t="s">
+        <v>1676</v>
+      </c>
+      <c r="E114" t="s">
+        <v>63</v>
+      </c>
+      <c r="F114" t="s">
+        <v>20</v>
+      </c>
+      <c r="G114" t="s">
+        <v>1168</v>
+      </c>
+      <c r="H114">
+        <v>217800</v>
+      </c>
+      <c r="I114">
+        <v>217800</v>
+      </c>
+      <c r="J114" t="s">
+        <v>22</v>
+      </c>
+      <c r="K114" t="s">
+        <v>65</v>
+      </c>
+      <c r="L114" t="s">
+        <v>1154</v>
+      </c>
+      <c r="M114" t="s">
+        <v>38</v>
+      </c>
+      <c r="N114" t="s">
+        <v>1169</v>
+      </c>
+      <c r="O114" t="s">
+        <v>1677</v>
+      </c>
+      <c r="P114" t="s">
+        <v>1678</v>
+      </c>
+      <c r="Q114" t="s">
+        <v>1679</v>
+      </c>
+    </row>
+    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>17</v>
+      </c>
+      <c r="B115">
+        <v>58</v>
+      </c>
+      <c r="C115">
+        <v>45</v>
+      </c>
+      <c r="D115" t="s">
+        <v>1680</v>
+      </c>
+      <c r="E115" t="s">
+        <v>63</v>
+      </c>
+      <c r="F115" t="s">
+        <v>1681</v>
+      </c>
+      <c r="G115" t="s">
+        <v>1168</v>
+      </c>
+      <c r="H115">
+        <v>219100</v>
+      </c>
+      <c r="I115">
+        <v>219100</v>
+      </c>
+      <c r="J115" t="s">
+        <v>22</v>
+      </c>
+      <c r="K115" t="s">
+        <v>65</v>
+      </c>
+      <c r="L115" t="s">
+        <v>1154</v>
+      </c>
+      <c r="M115" t="s">
+        <v>38</v>
+      </c>
+      <c r="N115" t="s">
+        <v>1169</v>
+      </c>
+      <c r="O115" t="s">
+        <v>1682</v>
+      </c>
+      <c r="P115" t="s">
+        <v>1683</v>
+      </c>
+      <c r="Q115" t="s">
+        <v>1684</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>17</v>
+      </c>
+      <c r="B116">
+        <v>10</v>
+      </c>
+      <c r="C116">
+        <v>20</v>
+      </c>
+      <c r="D116" t="s">
+        <v>276</v>
+      </c>
+      <c r="E116" t="s">
+        <v>817</v>
+      </c>
+      <c r="F116" t="s">
+        <v>1685</v>
+      </c>
+      <c r="G116" t="s">
+        <v>1168</v>
+      </c>
+      <c r="J116" t="s">
+        <v>32</v>
+      </c>
+      <c r="K116" t="s">
+        <v>65</v>
+      </c>
+      <c r="L116" t="s">
+        <v>1154</v>
+      </c>
+      <c r="M116" t="s">
+        <v>25</v>
+      </c>
+      <c r="N116" t="s">
+        <v>1169</v>
+      </c>
+      <c r="O116" t="s">
+        <v>1686</v>
+      </c>
+      <c r="P116" t="s">
+        <v>1687</v>
+      </c>
+      <c r="Q116" t="s">
+        <v>1688</v>
       </c>
     </row>
   </sheetData>

--- a/hunt/board.xlsx
+++ b/hunt/board.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4558" uniqueCount="1689">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4753" uniqueCount="1754">
   <si>
     <t>Column</t>
   </si>
@@ -3515,6 +3515,132 @@
     <t>https://www.arbeitnow.com/jobs/companies/virtual7-gmbh/remote-senior-cloud-test-devops-engineer-berlin-312220</t>
   </si>
   <si>
+    <t>Senior Salesforce Solution Architect, Financial Services</t>
+  </si>
+  <si>
+    <t>Alithya</t>
+  </si>
+  <si>
+    <t>2026-09-04T02:33:01.997Z</t>
+  </si>
+  <si>
+    <t>Financial services domain and compliance-heavy client work aligns with candidate's HIPAA/PCI/SOX advisory background | Consulting/trusted-advisor engagement model matches candidate's Customer Engineer delivery style</t>
+  </si>
+  <si>
+    <t>Requires deep Salesforce platform architecture and declarative configuration — nowhere in candidate's Azure/DevOps skill set | No CI/CD, IaC, or cloud governance content in the role; Azure depth is not transferable credit here</t>
+  </si>
+  <si>
+    <t>https://himalayas.app/companies/alithya/jobs/senior-salesforce-solution-architect-financial-services</t>
+  </si>
+  <si>
+    <t>Core scope — compute, networking, data, identity, security governance on a major cloud — maps directly to candidate's Azure Policy/Entra ID/Key Vault/Defender experience | Explicitly a Cloud Solutions Architect title, exactly one of the candidate's target titles | Salary band tops out at $190K, above the $180K floor if negotiated at the high end</t>
+  </si>
+  <si>
+    <t>Posting states 13+ years experience required; candidate has ~10, a real gap for a staffing-style W2 role | Band midpoint ($165K) sits below the salary floor, so only a top-of-band offer works | 'Major cloud platform' is unspecified — could skew AWS-primary, which would undercut the Azure-heavy profile</t>
+  </si>
+  <si>
+    <t>https://himalayas.app/companies/bright-vision-technologies/jobs/cloud-solutions-architect-7823362380</t>
+  </si>
+  <si>
+    <t>Confirmed $180K–$230K band clears the salary floor outright | Technical liaison / co-solutioning / enablement model mirrors the candidate's trusted-advisor Customer Engineer role | Fintech/payments domain is adjacent to candidate's PCI-compliance architecture precedent</t>
+  </si>
+  <si>
+    <t>Depth expected is Stripe payments APIs and commerce partner ecosystems, not Azure/DevOps platform governance — a domain pivot | Partner-facing GTM orientation may de-emphasize the hands-on IaC/CI/CD work that is the candidate's strongest differentiator</t>
+  </si>
+  <si>
+    <t>https://himalayas.app/companies/stripe/jobs/partner-solutions-architect-commerce-partners-2179344095</t>
+  </si>
+  <si>
+    <t>Works with C-level, finance, and engineering leaders at global brands — matches candidate's enterprise advisory engagement experience | Solutions Architect title and prescriptive-solution advisory work align with target roles</t>
+  </si>
+  <si>
+    <t>Explicitly presales; quota-adjacent motion with Stripe API depth as the core technical bar, not Azure/DevOps | No CI/CD, IaC, or governance content — candidate's GHAS/Azure DevOps specialty is largely irrelevant here | Comp not posted, so floor clearance is unverified</t>
+  </si>
+  <si>
+    <t>https://himalayas.app/companies/stripe/jobs/solutions-architect-platforms-presales-5071714978</t>
+  </si>
+  <si>
+    <t>10+ years requirement matches candidate's experience exactly | Cloud-native platform and distributed systems architecture overlaps with candidate's Azure platform and IaC work</t>
+  </si>
+  <si>
+    <t>Emphasis is 10+ years of software engineering experience — candidate's background is DevOps/platform advisory, not deep product software engineering | Band caps at $180K, meaning the salary floor is only met at the absolute top of range | Staffing-consultancy posting with vague client/platform details</t>
+  </si>
+  <si>
+    <t>https://himalayas.app/companies/bright-vision-technologies/jobs/cloud-native-architect-2557521877</t>
+  </si>
+  <si>
+    <t>Senior Engineer, Build and DevOps - ADI</t>
+  </si>
+  <si>
+    <t>NVIDIA</t>
+  </si>
+  <si>
+    <t>Salary band $184K–$356.5K comfortably clears the $180K floor with strong upside | Build and CI/CD pipeline ownership is directly in the candidate's Azure DevOps/GitHub Actions wheelhouse | Remote US role at a top-tier employer with senior scope</t>
+  </si>
+  <si>
+    <t>RAPIDS/GPU data-science build tooling is Python/C++/conda-heavy open-source infrastructure, not Azure enterprise governance | Hands-on IC build engineering rather than customer-facing solutions architecture — a step away from the principal-architect target | GitHub-based OSS workflows help, but no credit for GHAS/Azure Policy/compliance specialization</t>
+  </si>
+  <si>
+    <t>https://himalayas.app/companies/nvidia/jobs/senior-engineer-build-and-devops-adi</t>
+  </si>
+  <si>
+    <t>(Senior) SAP ABAP Developer/ Architect – Technical Migration (m/w/d)</t>
+  </si>
+  <si>
+    <t>Remote role with architecture-level scope and client workshop/enablement components that echo the candidate's advisory style</t>
+  </si>
+  <si>
+    <t>Requires deep SAP ABAP and S/4HANA data-migration expertise the candidate has zero exposure to | German-language posting for a Germany-based employer — outside the candidate's US market scope and likely requires German fluency | No cloud, DevOps, or CI/CD content whatsoever</t>
+  </si>
+  <si>
+    <t>https://www.arbeitnow.com/jobs/companies/natuvion-gmbh/remote-senior-sap-abap-developer-architect-technical-migration-berlin-207465</t>
+  </si>
+  <si>
+    <t>(Senior) SAP ABAP Developer/Architect – Product Development (m/w/d)</t>
+  </si>
+  <si>
+    <t>Remote posting with product design/development ownership, and the candidate does have TypeScript/React product-build experience</t>
+  </si>
+  <si>
+    <t>Entirely ABAP-based product development on Natuvion's Data Conversion Suite — no ABAP or SAP background in the candidate's profile | German-language, Germany-based role outside the stated US market scope | Zero overlap with Azure, GitHub, or DevOps governance skills that define the candidate</t>
+  </si>
+  <si>
+    <t>https://www.arbeitnow.com/jobs/companies/natuvion-gmbh/remote-senior-sap-abap-developer-architect-product-development-berlin-428749</t>
+  </si>
+  <si>
+    <t>Consulting Architect - Security (EMEA / Public Sector eligible )</t>
+  </si>
+  <si>
+    <t>Elastic</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Remote role with confirmed $200K comp above the candidate's $180K floor | Public sector/government customer base is a strong precedent match for candidate's compliance-heavy (HIPAA, NIST, FIPS) architecture work | Consulting architect delivery work, not quota-carrying sales — fits candidate's advisory delivery style</t>
+  </si>
+  <si>
+    <t>EMEA-focused role; candidate is US-based and US market scope, so eligibility and time zone are real obstacles | Requires SIEM/Elastic Security product depth (detection engineering, threat hunting) that isn't in the candidate's Azure DevOps/GHAS-centric profile | Public sector engagements may require UK/EU security vetting the candidate does not hold</t>
+  </si>
+  <si>
+    <t>https://www.arbeitnow.com/jobs/companies/elastic/consulting-architect-security-emea-public-sector-eligible-468536</t>
+  </si>
+  <si>
+    <t>Staff Solutions Architect, Majors - East</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts, Raleigh, North Carolina, New York, New York, Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>Staff-level scope matches candidate's target principal/staff architect seniority | Fully remote across East Coast metros with a confirmed $168K–$220.5K band whose upper half clears the $180K floor | Customer-facing technical ownership of enterprise accounts mirrors candidate's Customer Engineer advisory work</t>
+  </si>
+  <si>
+    <t>Deep expertise in Temporal's durable-execution/distributed-workflow model and application architecture is central — candidate's background is cloud platform, CI/CD, and governance rather than app-level distributed systems design | Heavy pre-sales/technical-win orientation (positioning against alternatives, owning technical relationships) rather than DevOps platform delivery | Base of the posted range ($168K) sits below the candidate's $180K floor, so offer level matters</t>
+  </si>
+  <si>
+    <t>https://jobs.ashbyhq.com/temporal/cdabd368-1989-4ea8-801d-2be138c16523</t>
+  </si>
+  <si>
     <t>Solutions Architect - Agencies</t>
   </si>
   <si>
@@ -3857,9 +3983,6 @@
     <t>capco</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Financial services consulting context is a reasonable industry precedent for the candidate's compliance-heavy enterprise work | Cloud platform design element overlaps partially with Azure platform experience</t>
   </si>
   <si>
@@ -4742,9 +4865,6 @@
     <t>https://www.arbeitnow.co.uk/jobs/companies/coreweave/account-solution-architect-london-134799</t>
   </si>
   <si>
-    <t>Elastic</t>
-  </si>
-  <si>
     <t>Senior Solutions Architect scope matches candidate's target titles and trusted-advisor customer engagement experience | Elastic Cloud runs on Azure, so candidate's Azure platform, RBAC/Entra ID, and IaC background is partially relevant</t>
   </si>
   <si>
@@ -5079,6 +5199,81 @@
   </si>
   <si>
     <t>https://www.mongodb.com/careers/job/?gh_jid=7157100</t>
+  </si>
+  <si>
+    <t>Solutions Architect - CPG and Manufacturing</t>
+  </si>
+  <si>
+    <t>Zürich, Switzerland</t>
+  </si>
+  <si>
+    <t>Trusted technical partner / architecture-discussion ownership matches candidate's advisory engagement model | Platform adoption and end-to-end technical strategy scope is genuinely architect-level work</t>
+  </si>
+  <si>
+    <t>Located in Zürich, Switzerland — outside the candidate's stated US market scope and would require international relocation and work authorization | Requires Databricks/Spark data-and-AI platform depth (lakehouse, Delta, ML pipelines) that the candidate does not have | CPG/manufacturing vertical is not among the candidate's precedent industries</t>
+  </si>
+  <si>
+    <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8755662002</t>
+  </si>
+  <si>
+    <t>Sr. Solutions Architect, Customer Lake</t>
+  </si>
+  <si>
+    <t>Confirmed $219.1K OTE well above the $180K floor | Senior, global go-to-market solutions architect scope with real technical depth expectations</t>
+  </si>
+  <si>
+    <t>Core requirement is CDP/martech, identity resolution, and Lakehouse data architecture — no overlap with candidate's Azure DevOps/GHAS specialty | Marketing-data domain is outside the candidate's financial services/healthcare/compliance precedent | Listed as hybrid/onsite with location ambiguity, adding relocation uncertainty</t>
+  </si>
+  <si>
+    <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8762360002</t>
+  </si>
+  <si>
+    <t>UK - London - ADS - Cloud DBA &amp; Solution Architect, PowerBI</t>
+  </si>
+  <si>
+    <t>Jobposts</t>
+  </si>
+  <si>
+    <t>London, Greater London</t>
+  </si>
+  <si>
+    <t>Solution Architect title nominally overlaps with candidate's target Cloud Solutions Architect roles | Cloud architecture element could touch Azure data platform skills</t>
+  </si>
+  <si>
+    <t>Role is UK/London based — candidate is US-based (Humble, TX) and market scope is US only | Emphasis on DBA and PowerBI/BI reporting, not the candidate's DevOps/CI-CD/GitHub governance strength | Posting body is essentially an application acknowledgement with no real requirements listed — nothing verifiable</t>
+  </si>
+  <si>
+    <t>https://www.arbeitnow.co.uk/jobs/companies/jobposts/uk-london-ads-cloud-dba-solution-architect-powerbi-london-greater-london-272654</t>
+  </si>
+  <si>
+    <t>Microsoft Modern Work Architect (m/w/d)</t>
+  </si>
+  <si>
+    <t>Skaylink</t>
+  </si>
+  <si>
+    <t>Garching bei München, Bayern</t>
+  </si>
+  <si>
+    <t>Microsoft-ecosystem architect role (M365, Intune, Entra-adjacent security) aligns with candidate's deep Microsoft/Azure background | Advisory + presales workshop model matches candidate's trusted-advisor engagement experience</t>
+  </si>
+  <si>
+    <t>Posting is in German and based in Bayern, Germany — outside candidate's US market scope and likely requires German fluency | Focus is Modern Work (Teams, SharePoint, Exchange, Intune) rather than Azure DevOps/GitHub/CI-CD platform engineering | No Azure DevOps, IaC, or GHAS content — candidate's strongest differentiators are unused</t>
+  </si>
+  <si>
+    <t>https://www.arbeitnow.com/jobs/companies/skaylink/microsoft-modern-work-architect-garching-bei-munchen-bayern-53141</t>
+  </si>
+  <si>
+    <t>Senior Solution Architect - Enterprise</t>
+  </si>
+  <si>
+    <t>Customer-facing technical authority role matches candidate's Customer Engineer / trusted-advisor engagement model | Confirmed $200K comp clears the $180K salary floor | Enterprise segment scope aligns with candidate's target senior/principal solutions architect titles</t>
+  </si>
+  <si>
+    <t>Requires depth in Elastic's search/observability/AI stack — candidate's expertise is Azure DevOps, GitHub, and governance, not ELK | Location field is blank and bucketed hybrid/onsite, so geography and remote eligibility are unverified | Role leans pre-sales technical win-driving rather than the platform/DevOps architecture delivery the candidate does today</t>
+  </si>
+  <si>
+    <t>https://www.arbeitnow.com/jobs/companies/elastic/senior-solution-architect-enterprise-176532</t>
   </si>
 </sst>
 </file>
@@ -5459,7 +5654,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q234"/>
+  <dimension ref="A1:Q244"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -17206,6 +17401,512 @@
         <v>1166</v>
       </c>
     </row>
+    <row r="235" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>17</v>
+      </c>
+      <c r="B235">
+        <v>22</v>
+      </c>
+      <c r="C235">
+        <v>18</v>
+      </c>
+      <c r="D235" t="s">
+        <v>1167</v>
+      </c>
+      <c r="E235" t="s">
+        <v>1168</v>
+      </c>
+      <c r="F235" t="s">
+        <v>20</v>
+      </c>
+      <c r="G235" t="s">
+        <v>21</v>
+      </c>
+      <c r="J235" t="s">
+        <v>32</v>
+      </c>
+      <c r="K235" t="s">
+        <v>23</v>
+      </c>
+      <c r="L235" t="s">
+        <v>1169</v>
+      </c>
+      <c r="M235" t="s">
+        <v>25</v>
+      </c>
+      <c r="N235" t="s">
+        <v>26</v>
+      </c>
+      <c r="O235" t="s">
+        <v>1170</v>
+      </c>
+      <c r="P235" t="s">
+        <v>1171</v>
+      </c>
+      <c r="Q235" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="236" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>17</v>
+      </c>
+      <c r="B236">
+        <v>62</v>
+      </c>
+      <c r="C236">
+        <v>68</v>
+      </c>
+      <c r="D236" t="s">
+        <v>42</v>
+      </c>
+      <c r="E236" t="s">
+        <v>109</v>
+      </c>
+      <c r="F236" t="s">
+        <v>20</v>
+      </c>
+      <c r="G236" t="s">
+        <v>21</v>
+      </c>
+      <c r="H236">
+        <v>140000</v>
+      </c>
+      <c r="I236">
+        <v>190000</v>
+      </c>
+      <c r="J236" t="s">
+        <v>22</v>
+      </c>
+      <c r="K236" t="s">
+        <v>23</v>
+      </c>
+      <c r="L236" t="s">
+        <v>1169</v>
+      </c>
+      <c r="M236" t="s">
+        <v>75</v>
+      </c>
+      <c r="N236" t="s">
+        <v>26</v>
+      </c>
+      <c r="O236" t="s">
+        <v>1173</v>
+      </c>
+      <c r="P236" t="s">
+        <v>1174</v>
+      </c>
+      <c r="Q236" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="237" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>17</v>
+      </c>
+      <c r="B237">
+        <v>63</v>
+      </c>
+      <c r="C237">
+        <v>55</v>
+      </c>
+      <c r="D237" t="s">
+        <v>603</v>
+      </c>
+      <c r="E237" t="s">
+        <v>949</v>
+      </c>
+      <c r="F237" t="s">
+        <v>20</v>
+      </c>
+      <c r="G237" t="s">
+        <v>21</v>
+      </c>
+      <c r="H237">
+        <v>180000</v>
+      </c>
+      <c r="I237">
+        <v>230000</v>
+      </c>
+      <c r="J237" t="s">
+        <v>22</v>
+      </c>
+      <c r="K237" t="s">
+        <v>23</v>
+      </c>
+      <c r="L237" t="s">
+        <v>1169</v>
+      </c>
+      <c r="M237" t="s">
+        <v>38</v>
+      </c>
+      <c r="N237" t="s">
+        <v>26</v>
+      </c>
+      <c r="O237" t="s">
+        <v>1176</v>
+      </c>
+      <c r="P237" t="s">
+        <v>1177</v>
+      </c>
+      <c r="Q237" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="238" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>17</v>
+      </c>
+      <c r="B238">
+        <v>58</v>
+      </c>
+      <c r="C238">
+        <v>50</v>
+      </c>
+      <c r="D238" t="s">
+        <v>609</v>
+      </c>
+      <c r="E238" t="s">
+        <v>949</v>
+      </c>
+      <c r="F238" t="s">
+        <v>20</v>
+      </c>
+      <c r="G238" t="s">
+        <v>21</v>
+      </c>
+      <c r="J238" t="s">
+        <v>32</v>
+      </c>
+      <c r="K238" t="s">
+        <v>23</v>
+      </c>
+      <c r="L238" t="s">
+        <v>1169</v>
+      </c>
+      <c r="M238" t="s">
+        <v>38</v>
+      </c>
+      <c r="N238" t="s">
+        <v>26</v>
+      </c>
+      <c r="O238" t="s">
+        <v>1179</v>
+      </c>
+      <c r="P238" t="s">
+        <v>1180</v>
+      </c>
+      <c r="Q238" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="239" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>17</v>
+      </c>
+      <c r="B239">
+        <v>48</v>
+      </c>
+      <c r="C239">
+        <v>52</v>
+      </c>
+      <c r="D239" t="s">
+        <v>990</v>
+      </c>
+      <c r="E239" t="s">
+        <v>109</v>
+      </c>
+      <c r="F239" t="s">
+        <v>20</v>
+      </c>
+      <c r="G239" t="s">
+        <v>21</v>
+      </c>
+      <c r="H239">
+        <v>130000</v>
+      </c>
+      <c r="I239">
+        <v>180000</v>
+      </c>
+      <c r="J239" t="s">
+        <v>22</v>
+      </c>
+      <c r="K239" t="s">
+        <v>23</v>
+      </c>
+      <c r="L239" t="s">
+        <v>1169</v>
+      </c>
+      <c r="M239" t="s">
+        <v>38</v>
+      </c>
+      <c r="N239" t="s">
+        <v>26</v>
+      </c>
+      <c r="O239" t="s">
+        <v>1182</v>
+      </c>
+      <c r="P239" t="s">
+        <v>1183</v>
+      </c>
+      <c r="Q239" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="240" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>17</v>
+      </c>
+      <c r="B240">
+        <v>66</v>
+      </c>
+      <c r="C240">
+        <v>60</v>
+      </c>
+      <c r="D240" t="s">
+        <v>1185</v>
+      </c>
+      <c r="E240" t="s">
+        <v>1186</v>
+      </c>
+      <c r="F240" t="s">
+        <v>20</v>
+      </c>
+      <c r="G240" t="s">
+        <v>21</v>
+      </c>
+      <c r="H240">
+        <v>184000</v>
+      </c>
+      <c r="I240">
+        <v>356500</v>
+      </c>
+      <c r="J240" t="s">
+        <v>22</v>
+      </c>
+      <c r="K240" t="s">
+        <v>23</v>
+      </c>
+      <c r="L240" t="s">
+        <v>1169</v>
+      </c>
+      <c r="M240" t="s">
+        <v>75</v>
+      </c>
+      <c r="N240" t="s">
+        <v>26</v>
+      </c>
+      <c r="O240" t="s">
+        <v>1187</v>
+      </c>
+      <c r="P240" t="s">
+        <v>1188</v>
+      </c>
+      <c r="Q240" t="s">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="241" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>17</v>
+      </c>
+      <c r="B241">
+        <v>8</v>
+      </c>
+      <c r="C241">
+        <v>5</v>
+      </c>
+      <c r="D241" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E241" t="s">
+        <v>143</v>
+      </c>
+      <c r="F241" t="s">
+        <v>144</v>
+      </c>
+      <c r="G241" t="s">
+        <v>21</v>
+      </c>
+      <c r="J241" t="s">
+        <v>32</v>
+      </c>
+      <c r="K241" t="s">
+        <v>99</v>
+      </c>
+      <c r="L241" t="s">
+        <v>1169</v>
+      </c>
+      <c r="M241" t="s">
+        <v>25</v>
+      </c>
+      <c r="N241" t="s">
+        <v>26</v>
+      </c>
+      <c r="O241" t="s">
+        <v>1191</v>
+      </c>
+      <c r="P241" t="s">
+        <v>1192</v>
+      </c>
+      <c r="Q241" t="s">
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="242" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>17</v>
+      </c>
+      <c r="B242">
+        <v>7</v>
+      </c>
+      <c r="C242">
+        <v>5</v>
+      </c>
+      <c r="D242" t="s">
+        <v>1194</v>
+      </c>
+      <c r="E242" t="s">
+        <v>143</v>
+      </c>
+      <c r="F242" t="s">
+        <v>144</v>
+      </c>
+      <c r="G242" t="s">
+        <v>21</v>
+      </c>
+      <c r="J242" t="s">
+        <v>32</v>
+      </c>
+      <c r="K242" t="s">
+        <v>99</v>
+      </c>
+      <c r="L242" t="s">
+        <v>1169</v>
+      </c>
+      <c r="M242" t="s">
+        <v>25</v>
+      </c>
+      <c r="N242" t="s">
+        <v>26</v>
+      </c>
+      <c r="O242" t="s">
+        <v>1195</v>
+      </c>
+      <c r="P242" t="s">
+        <v>1196</v>
+      </c>
+      <c r="Q242" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="243" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>17</v>
+      </c>
+      <c r="B243">
+        <v>48</v>
+      </c>
+      <c r="C243">
+        <v>45</v>
+      </c>
+      <c r="D243" t="s">
+        <v>1198</v>
+      </c>
+      <c r="E243" t="s">
+        <v>1199</v>
+      </c>
+      <c r="F243" t="s">
+        <v>1200</v>
+      </c>
+      <c r="G243" t="s">
+        <v>21</v>
+      </c>
+      <c r="H243">
+        <v>200000</v>
+      </c>
+      <c r="I243">
+        <v>200000</v>
+      </c>
+      <c r="J243" t="s">
+        <v>22</v>
+      </c>
+      <c r="K243" t="s">
+        <v>99</v>
+      </c>
+      <c r="L243" t="s">
+        <v>1169</v>
+      </c>
+      <c r="M243" t="s">
+        <v>38</v>
+      </c>
+      <c r="N243" t="s">
+        <v>26</v>
+      </c>
+      <c r="O243" t="s">
+        <v>1201</v>
+      </c>
+      <c r="P243" t="s">
+        <v>1202</v>
+      </c>
+      <c r="Q243" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="244" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>17</v>
+      </c>
+      <c r="B244">
+        <v>65</v>
+      </c>
+      <c r="C244">
+        <v>58</v>
+      </c>
+      <c r="D244" t="s">
+        <v>1204</v>
+      </c>
+      <c r="E244" t="s">
+        <v>928</v>
+      </c>
+      <c r="F244" t="s">
+        <v>1205</v>
+      </c>
+      <c r="G244" t="s">
+        <v>21</v>
+      </c>
+      <c r="H244">
+        <v>168000</v>
+      </c>
+      <c r="I244">
+        <v>220000</v>
+      </c>
+      <c r="J244" t="s">
+        <v>22</v>
+      </c>
+      <c r="K244" t="s">
+        <v>894</v>
+      </c>
+      <c r="L244" t="s">
+        <v>1169</v>
+      </c>
+      <c r="M244" t="s">
+        <v>38</v>
+      </c>
+      <c r="N244" t="s">
+        <v>26</v>
+      </c>
+      <c r="O244" t="s">
+        <v>1206</v>
+      </c>
+      <c r="P244" t="s">
+        <v>1207</v>
+      </c>
+      <c r="Q244" t="s">
+        <v>1208</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:Q1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17215,7 +17916,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q116"/>
+  <dimension ref="A1:Q121"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -17296,7 +17997,7 @@
         <v>42</v>
       </c>
       <c r="D2" t="s">
-        <v>1167</v>
+        <v>1209</v>
       </c>
       <c r="E2" t="s">
         <v>63</v>
@@ -17305,7 +18006,7 @@
         <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J2" t="s">
         <v>32</v>
@@ -17320,16 +18021,16 @@
         <v>25</v>
       </c>
       <c r="N2" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O2" t="s">
-        <v>1170</v>
+        <v>1212</v>
       </c>
       <c r="P2" t="s">
-        <v>1171</v>
+        <v>1213</v>
       </c>
       <c r="Q2" t="s">
-        <v>1172</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -17343,7 +18044,7 @@
         <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>1173</v>
+        <v>1215</v>
       </c>
       <c r="E3" t="s">
         <v>63</v>
@@ -17352,7 +18053,7 @@
         <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J3" t="s">
         <v>32</v>
@@ -17367,16 +18068,16 @@
         <v>25</v>
       </c>
       <c r="N3" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O3" t="s">
-        <v>1174</v>
+        <v>1216</v>
       </c>
       <c r="P3" t="s">
-        <v>1175</v>
+        <v>1217</v>
       </c>
       <c r="Q3" t="s">
-        <v>1176</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
@@ -17396,10 +18097,10 @@
         <v>63</v>
       </c>
       <c r="F4" t="s">
-        <v>1177</v>
+        <v>1219</v>
       </c>
       <c r="G4" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="H4">
         <v>180000</v>
@@ -17420,16 +18121,16 @@
         <v>38</v>
       </c>
       <c r="N4" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O4" t="s">
-        <v>1178</v>
+        <v>1220</v>
       </c>
       <c r="P4" t="s">
-        <v>1179</v>
+        <v>1221</v>
       </c>
       <c r="Q4" t="s">
-        <v>1180</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -17443,7 +18144,7 @@
         <v>52</v>
       </c>
       <c r="D5" t="s">
-        <v>1181</v>
+        <v>1223</v>
       </c>
       <c r="E5" t="s">
         <v>63</v>
@@ -17452,7 +18153,7 @@
         <v>20</v>
       </c>
       <c r="G5" t="s">
-        <v>1182</v>
+        <v>1224</v>
       </c>
       <c r="H5">
         <v>180000</v>
@@ -17473,16 +18174,16 @@
         <v>38</v>
       </c>
       <c r="N5" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O5" t="s">
-        <v>1183</v>
+        <v>1225</v>
       </c>
       <c r="P5" t="s">
-        <v>1184</v>
+        <v>1226</v>
       </c>
       <c r="Q5" t="s">
-        <v>1185</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -17496,7 +18197,7 @@
         <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>1186</v>
+        <v>1228</v>
       </c>
       <c r="E6" t="s">
         <v>63</v>
@@ -17505,7 +18206,7 @@
         <v>20</v>
       </c>
       <c r="G6" t="s">
-        <v>1182</v>
+        <v>1224</v>
       </c>
       <c r="H6">
         <v>180000</v>
@@ -17526,16 +18227,16 @@
         <v>38</v>
       </c>
       <c r="N6" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O6" t="s">
-        <v>1187</v>
+        <v>1229</v>
       </c>
       <c r="P6" t="s">
-        <v>1188</v>
+        <v>1230</v>
       </c>
       <c r="Q6" t="s">
-        <v>1189</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -17549,16 +18250,16 @@
         <v>48</v>
       </c>
       <c r="D7" t="s">
-        <v>1190</v>
+        <v>1232</v>
       </c>
       <c r="E7" t="s">
         <v>63</v>
       </c>
       <c r="F7" t="s">
-        <v>1191</v>
+        <v>1233</v>
       </c>
       <c r="G7" t="s">
-        <v>1182</v>
+        <v>1224</v>
       </c>
       <c r="H7">
         <v>219100</v>
@@ -17579,16 +18280,16 @@
         <v>38</v>
       </c>
       <c r="N7" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O7" t="s">
-        <v>1192</v>
+        <v>1234</v>
       </c>
       <c r="P7" t="s">
-        <v>1193</v>
+        <v>1235</v>
       </c>
       <c r="Q7" t="s">
-        <v>1194</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -17602,16 +18303,16 @@
         <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>1195</v>
+        <v>1237</v>
       </c>
       <c r="E8" t="s">
         <v>63</v>
       </c>
       <c r="F8" t="s">
-        <v>1196</v>
+        <v>1238</v>
       </c>
       <c r="G8" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="H8">
         <v>180000</v>
@@ -17632,16 +18333,16 @@
         <v>38</v>
       </c>
       <c r="N8" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O8" t="s">
-        <v>1197</v>
+        <v>1239</v>
       </c>
       <c r="P8" t="s">
-        <v>1198</v>
+        <v>1240</v>
       </c>
       <c r="Q8" t="s">
-        <v>1199</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -17655,7 +18356,7 @@
         <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>1200</v>
+        <v>1242</v>
       </c>
       <c r="E9" t="s">
         <v>63</v>
@@ -17664,7 +18365,7 @@
         <v>20</v>
       </c>
       <c r="G9" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="H9">
         <v>219100</v>
@@ -17685,16 +18386,16 @@
         <v>25</v>
       </c>
       <c r="N9" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O9" t="s">
-        <v>1201</v>
+        <v>1243</v>
       </c>
       <c r="P9" t="s">
-        <v>1202</v>
+        <v>1244</v>
       </c>
       <c r="Q9" t="s">
-        <v>1203</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -17708,7 +18409,7 @@
         <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>1204</v>
+        <v>1246</v>
       </c>
       <c r="E10" t="s">
         <v>63</v>
@@ -17717,7 +18418,7 @@
         <v>20</v>
       </c>
       <c r="G10" t="s">
-        <v>1182</v>
+        <v>1224</v>
       </c>
       <c r="H10">
         <v>219100</v>
@@ -17738,16 +18439,16 @@
         <v>38</v>
       </c>
       <c r="N10" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O10" t="s">
-        <v>1205</v>
+        <v>1247</v>
       </c>
       <c r="P10" t="s">
-        <v>1206</v>
+        <v>1248</v>
       </c>
       <c r="Q10" t="s">
-        <v>1207</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -17761,16 +18462,16 @@
         <v>30</v>
       </c>
       <c r="D11" t="s">
-        <v>1208</v>
+        <v>1250</v>
       </c>
       <c r="E11" t="s">
         <v>63</v>
       </c>
       <c r="F11" t="s">
-        <v>1209</v>
+        <v>1251</v>
       </c>
       <c r="G11" t="s">
-        <v>1182</v>
+        <v>1224</v>
       </c>
       <c r="J11" t="s">
         <v>32</v>
@@ -17785,16 +18486,16 @@
         <v>25</v>
       </c>
       <c r="N11" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O11" t="s">
-        <v>1210</v>
+        <v>1252</v>
       </c>
       <c r="P11" t="s">
-        <v>1211</v>
+        <v>1253</v>
       </c>
       <c r="Q11" t="s">
-        <v>1212</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -17808,16 +18509,16 @@
         <v>58</v>
       </c>
       <c r="D12" t="s">
-        <v>1213</v>
+        <v>1255</v>
       </c>
       <c r="E12" t="s">
-        <v>1214</v>
+        <v>1256</v>
       </c>
       <c r="F12" t="s">
-        <v>1215</v>
+        <v>1257</v>
       </c>
       <c r="G12" t="s">
-        <v>1182</v>
+        <v>1224</v>
       </c>
       <c r="H12">
         <v>257000</v>
@@ -17838,16 +18539,16 @@
         <v>38</v>
       </c>
       <c r="N12" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O12" t="s">
-        <v>1216</v>
+        <v>1258</v>
       </c>
       <c r="P12" t="s">
-        <v>1217</v>
+        <v>1259</v>
       </c>
       <c r="Q12" t="s">
-        <v>1218</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
@@ -17864,13 +18565,13 @@
         <v>282</v>
       </c>
       <c r="E13" t="s">
-        <v>1219</v>
+        <v>1261</v>
       </c>
       <c r="F13" t="s">
-        <v>1220</v>
+        <v>1262</v>
       </c>
       <c r="G13" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="H13">
         <v>200000</v>
@@ -17891,16 +18592,16 @@
         <v>25</v>
       </c>
       <c r="N13" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O13" t="s">
-        <v>1221</v>
+        <v>1263</v>
       </c>
       <c r="P13" t="s">
-        <v>1222</v>
+        <v>1264</v>
       </c>
       <c r="Q13" t="s">
-        <v>1223</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
@@ -17914,16 +18615,16 @@
         <v>20</v>
       </c>
       <c r="D14" t="s">
-        <v>1224</v>
+        <v>1266</v>
       </c>
       <c r="E14" t="s">
         <v>817</v>
       </c>
       <c r="F14" t="s">
-        <v>1225</v>
+        <v>1267</v>
       </c>
       <c r="G14" t="s">
-        <v>1182</v>
+        <v>1224</v>
       </c>
       <c r="J14" t="s">
         <v>32</v>
@@ -17938,16 +18639,16 @@
         <v>25</v>
       </c>
       <c r="N14" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O14" t="s">
-        <v>1226</v>
+        <v>1268</v>
       </c>
       <c r="P14" t="s">
-        <v>1227</v>
+        <v>1269</v>
       </c>
       <c r="Q14" t="s">
-        <v>1228</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -17967,10 +18668,10 @@
         <v>817</v>
       </c>
       <c r="F15" t="s">
-        <v>1229</v>
+        <v>1271</v>
       </c>
       <c r="G15" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J15" t="s">
         <v>32</v>
@@ -17985,16 +18686,16 @@
         <v>25</v>
       </c>
       <c r="N15" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O15" t="s">
-        <v>1230</v>
+        <v>1272</v>
       </c>
       <c r="P15" t="s">
-        <v>1231</v>
+        <v>1273</v>
       </c>
       <c r="Q15" t="s">
-        <v>1232</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
@@ -18008,16 +18709,16 @@
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>1233</v>
+        <v>1275</v>
       </c>
       <c r="E16" t="s">
         <v>817</v>
       </c>
       <c r="F16" t="s">
-        <v>1234</v>
+        <v>1276</v>
       </c>
       <c r="G16" t="s">
-        <v>1182</v>
+        <v>1224</v>
       </c>
       <c r="H16">
         <v>500000</v>
@@ -18038,16 +18739,16 @@
         <v>25</v>
       </c>
       <c r="N16" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O16" t="s">
-        <v>1235</v>
+        <v>1277</v>
       </c>
       <c r="P16" t="s">
-        <v>1236</v>
+        <v>1278</v>
       </c>
       <c r="Q16" t="s">
-        <v>1237</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
@@ -18061,16 +18762,16 @@
         <v>18</v>
       </c>
       <c r="D17" t="s">
-        <v>1238</v>
+        <v>1280</v>
       </c>
       <c r="E17" t="s">
         <v>604</v>
       </c>
       <c r="F17" t="s">
-        <v>1239</v>
+        <v>1281</v>
       </c>
       <c r="G17" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="H17">
         <v>274456</v>
@@ -18091,16 +18792,16 @@
         <v>25</v>
       </c>
       <c r="N17" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O17" t="s">
-        <v>1240</v>
+        <v>1282</v>
       </c>
       <c r="P17" t="s">
-        <v>1241</v>
+        <v>1283</v>
       </c>
       <c r="Q17" t="s">
-        <v>1242</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
@@ -18114,16 +18815,16 @@
         <v>30</v>
       </c>
       <c r="D18" t="s">
-        <v>1243</v>
+        <v>1285</v>
       </c>
       <c r="E18" t="s">
         <v>604</v>
       </c>
       <c r="F18" t="s">
-        <v>1244</v>
+        <v>1286</v>
       </c>
       <c r="G18" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J18" t="s">
         <v>32</v>
@@ -18138,16 +18839,16 @@
         <v>25</v>
       </c>
       <c r="N18" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O18" t="s">
-        <v>1245</v>
+        <v>1287</v>
       </c>
       <c r="P18" t="s">
-        <v>1246</v>
+        <v>1288</v>
       </c>
       <c r="Q18" t="s">
-        <v>1247</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -18161,16 +18862,16 @@
         <v>22</v>
       </c>
       <c r="D19" t="s">
-        <v>1248</v>
+        <v>1290</v>
       </c>
       <c r="E19" t="s">
         <v>604</v>
       </c>
       <c r="F19" t="s">
-        <v>1249</v>
+        <v>1291</v>
       </c>
       <c r="G19" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J19" t="s">
         <v>32</v>
@@ -18185,16 +18886,16 @@
         <v>25</v>
       </c>
       <c r="N19" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O19" t="s">
-        <v>1250</v>
+        <v>1292</v>
       </c>
       <c r="P19" t="s">
-        <v>1251</v>
+        <v>1293</v>
       </c>
       <c r="Q19" t="s">
-        <v>1252</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -18208,16 +18909,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="s">
-        <v>1253</v>
+        <v>1295</v>
       </c>
       <c r="E20" t="s">
         <v>604</v>
       </c>
       <c r="F20" t="s">
-        <v>1254</v>
+        <v>1296</v>
       </c>
       <c r="G20" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J20" t="s">
         <v>32</v>
@@ -18232,16 +18933,16 @@
         <v>38</v>
       </c>
       <c r="N20" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O20" t="s">
-        <v>1255</v>
+        <v>1297</v>
       </c>
       <c r="P20" t="s">
-        <v>1256</v>
+        <v>1298</v>
       </c>
       <c r="Q20" t="s">
-        <v>1257</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
@@ -18255,16 +18956,16 @@
         <v>25</v>
       </c>
       <c r="D21" t="s">
-        <v>1258</v>
+        <v>1300</v>
       </c>
       <c r="E21" t="s">
         <v>604</v>
       </c>
       <c r="F21" t="s">
-        <v>1259</v>
+        <v>1301</v>
       </c>
       <c r="G21" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J21" t="s">
         <v>32</v>
@@ -18279,16 +18980,16 @@
         <v>25</v>
       </c>
       <c r="N21" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O21" t="s">
-        <v>1260</v>
+        <v>1302</v>
       </c>
       <c r="P21" t="s">
-        <v>1261</v>
+        <v>1303</v>
       </c>
       <c r="Q21" t="s">
-        <v>1262</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -18302,16 +19003,16 @@
         <v>40</v>
       </c>
       <c r="D22" t="s">
-        <v>1263</v>
+        <v>1305</v>
       </c>
       <c r="E22" t="s">
         <v>604</v>
       </c>
       <c r="F22" t="s">
-        <v>1264</v>
+        <v>1306</v>
       </c>
       <c r="G22" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J22" t="s">
         <v>32</v>
@@ -18326,16 +19027,16 @@
         <v>25</v>
       </c>
       <c r="N22" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O22" t="s">
-        <v>1265</v>
+        <v>1307</v>
       </c>
       <c r="P22" t="s">
-        <v>1266</v>
+        <v>1308</v>
       </c>
       <c r="Q22" t="s">
-        <v>1267</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
@@ -18349,16 +19050,16 @@
         <v>70</v>
       </c>
       <c r="D23" t="s">
-        <v>1268</v>
+        <v>1310</v>
       </c>
       <c r="E23" t="s">
-        <v>1269</v>
+        <v>1311</v>
       </c>
       <c r="F23" t="s">
-        <v>1270</v>
+        <v>1312</v>
       </c>
       <c r="G23" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J23" t="s">
         <v>32</v>
@@ -18373,16 +19074,16 @@
         <v>25</v>
       </c>
       <c r="N23" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O23" t="s">
-        <v>1271</v>
+        <v>1313</v>
       </c>
       <c r="P23" t="s">
-        <v>1272</v>
+        <v>1314</v>
       </c>
       <c r="Q23" t="s">
-        <v>1273</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
@@ -18396,16 +19097,16 @@
         <v>58</v>
       </c>
       <c r="D24" t="s">
-        <v>1274</v>
+        <v>1316</v>
       </c>
       <c r="E24" t="s">
-        <v>1275</v>
+        <v>1317</v>
       </c>
       <c r="F24" t="s">
-        <v>1259</v>
+        <v>1301</v>
       </c>
       <c r="G24" t="s">
-        <v>1182</v>
+        <v>1224</v>
       </c>
       <c r="J24" t="s">
         <v>32</v>
@@ -18420,16 +19121,16 @@
         <v>25</v>
       </c>
       <c r="N24" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O24" t="s">
-        <v>1276</v>
+        <v>1318</v>
       </c>
       <c r="P24" t="s">
-        <v>1277</v>
+        <v>1319</v>
       </c>
       <c r="Q24" t="s">
-        <v>1278</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
@@ -18443,16 +19144,16 @@
         <v>32</v>
       </c>
       <c r="D25" t="s">
-        <v>1279</v>
+        <v>1321</v>
       </c>
       <c r="E25" t="s">
-        <v>1280</v>
+        <v>1322</v>
       </c>
       <c r="F25" t="s">
-        <v>1281</v>
+        <v>1200</v>
       </c>
       <c r="G25" t="s">
-        <v>1182</v>
+        <v>1224</v>
       </c>
       <c r="J25" t="s">
         <v>32</v>
@@ -18467,16 +19168,16 @@
         <v>25</v>
       </c>
       <c r="N25" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O25" t="s">
-        <v>1282</v>
+        <v>1323</v>
       </c>
       <c r="P25" t="s">
-        <v>1283</v>
+        <v>1324</v>
       </c>
       <c r="Q25" t="s">
-        <v>1284</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
@@ -18490,16 +19191,16 @@
         <v>4</v>
       </c>
       <c r="D26" t="s">
-        <v>1285</v>
+        <v>1326</v>
       </c>
       <c r="E26" t="s">
-        <v>1286</v>
+        <v>1327</v>
       </c>
       <c r="F26" t="s">
         <v>1149</v>
       </c>
       <c r="G26" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J26" t="s">
         <v>32</v>
@@ -18514,16 +19215,16 @@
         <v>25</v>
       </c>
       <c r="N26" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O26" t="s">
-        <v>1287</v>
+        <v>1328</v>
       </c>
       <c r="P26" t="s">
-        <v>1288</v>
+        <v>1329</v>
       </c>
       <c r="Q26" t="s">
-        <v>1289</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
@@ -18537,16 +19238,16 @@
         <v>25</v>
       </c>
       <c r="D27" t="s">
-        <v>1290</v>
+        <v>1331</v>
       </c>
       <c r="E27" t="s">
-        <v>1291</v>
+        <v>1332</v>
       </c>
       <c r="F27" t="s">
-        <v>1292</v>
+        <v>1333</v>
       </c>
       <c r="G27" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J27" t="s">
         <v>32</v>
@@ -18561,16 +19262,16 @@
         <v>25</v>
       </c>
       <c r="N27" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O27" t="s">
-        <v>1293</v>
+        <v>1334</v>
       </c>
       <c r="P27" t="s">
-        <v>1294</v>
+        <v>1335</v>
       </c>
       <c r="Q27" t="s">
-        <v>1295</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
@@ -18584,16 +19285,16 @@
         <v>30</v>
       </c>
       <c r="D28" t="s">
-        <v>1296</v>
+        <v>1337</v>
       </c>
       <c r="E28" t="s">
-        <v>1297</v>
+        <v>1338</v>
       </c>
       <c r="F28" t="s">
         <v>1142</v>
       </c>
       <c r="G28" t="s">
-        <v>1182</v>
+        <v>1224</v>
       </c>
       <c r="J28" t="s">
         <v>32</v>
@@ -18608,16 +19309,16 @@
         <v>25</v>
       </c>
       <c r="N28" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O28" t="s">
-        <v>1298</v>
+        <v>1339</v>
       </c>
       <c r="P28" t="s">
-        <v>1299</v>
+        <v>1340</v>
       </c>
       <c r="Q28" t="s">
-        <v>1300</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
@@ -18631,16 +19332,16 @@
         <v>52</v>
       </c>
       <c r="D29" t="s">
-        <v>1301</v>
+        <v>1342</v>
       </c>
       <c r="E29" t="s">
         <v>63</v>
       </c>
       <c r="F29" t="s">
-        <v>1302</v>
+        <v>1343</v>
       </c>
       <c r="G29" t="s">
-        <v>1182</v>
+        <v>1224</v>
       </c>
       <c r="H29">
         <v>180000</v>
@@ -18661,16 +19362,16 @@
         <v>38</v>
       </c>
       <c r="N29" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O29" t="s">
-        <v>1303</v>
+        <v>1344</v>
       </c>
       <c r="P29" t="s">
-        <v>1304</v>
+        <v>1345</v>
       </c>
       <c r="Q29" t="s">
-        <v>1305</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
@@ -18684,7 +19385,7 @@
         <v>50</v>
       </c>
       <c r="D30" t="s">
-        <v>1306</v>
+        <v>1347</v>
       </c>
       <c r="E30" t="s">
         <v>63</v>
@@ -18693,7 +19394,7 @@
         <v>20</v>
       </c>
       <c r="G30" t="s">
-        <v>1182</v>
+        <v>1224</v>
       </c>
       <c r="H30">
         <v>180000</v>
@@ -18714,16 +19415,16 @@
         <v>38</v>
       </c>
       <c r="N30" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O30" t="s">
-        <v>1307</v>
+        <v>1348</v>
       </c>
       <c r="P30" t="s">
-        <v>1308</v>
+        <v>1349</v>
       </c>
       <c r="Q30" t="s">
-        <v>1309</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
@@ -18737,7 +19438,7 @@
         <v>46</v>
       </c>
       <c r="D31" t="s">
-        <v>1310</v>
+        <v>1351</v>
       </c>
       <c r="E31" t="s">
         <v>63</v>
@@ -18746,7 +19447,7 @@
         <v>20</v>
       </c>
       <c r="G31" t="s">
-        <v>1182</v>
+        <v>1224</v>
       </c>
       <c r="H31">
         <v>180000</v>
@@ -18767,16 +19468,16 @@
         <v>38</v>
       </c>
       <c r="N31" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O31" t="s">
-        <v>1311</v>
+        <v>1352</v>
       </c>
       <c r="P31" t="s">
-        <v>1312</v>
+        <v>1353</v>
       </c>
       <c r="Q31" t="s">
-        <v>1313</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
@@ -18790,7 +19491,7 @@
         <v>38</v>
       </c>
       <c r="D32" t="s">
-        <v>1314</v>
+        <v>1355</v>
       </c>
       <c r="E32" t="s">
         <v>63</v>
@@ -18799,7 +19500,7 @@
         <v>20</v>
       </c>
       <c r="G32" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="H32">
         <v>217800</v>
@@ -18820,16 +19521,16 @@
         <v>25</v>
       </c>
       <c r="N32" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O32" t="s">
-        <v>1315</v>
+        <v>1356</v>
       </c>
       <c r="P32" t="s">
-        <v>1316</v>
+        <v>1357</v>
       </c>
       <c r="Q32" t="s">
-        <v>1317</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
@@ -18849,10 +19550,10 @@
         <v>63</v>
       </c>
       <c r="F33" t="s">
-        <v>1318</v>
+        <v>1359</v>
       </c>
       <c r="G33" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="H33">
         <v>180000</v>
@@ -18873,16 +19574,16 @@
         <v>38</v>
       </c>
       <c r="N33" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O33" t="s">
-        <v>1319</v>
+        <v>1360</v>
       </c>
       <c r="P33" t="s">
-        <v>1320</v>
+        <v>1361</v>
       </c>
       <c r="Q33" t="s">
-        <v>1321</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
@@ -18896,16 +19597,16 @@
         <v>45</v>
       </c>
       <c r="D34" t="s">
-        <v>1322</v>
+        <v>1363</v>
       </c>
       <c r="E34" t="s">
         <v>63</v>
       </c>
       <c r="F34" t="s">
-        <v>1323</v>
+        <v>1364</v>
       </c>
       <c r="G34" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="H34">
         <v>219100</v>
@@ -18926,16 +19627,16 @@
         <v>38</v>
       </c>
       <c r="N34" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O34" t="s">
-        <v>1324</v>
+        <v>1365</v>
       </c>
       <c r="P34" t="s">
-        <v>1325</v>
+        <v>1366</v>
       </c>
       <c r="Q34" t="s">
-        <v>1326</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
@@ -18949,16 +19650,16 @@
         <v>42</v>
       </c>
       <c r="D35" t="s">
-        <v>1327</v>
+        <v>1368</v>
       </c>
       <c r="E35" t="s">
         <v>63</v>
       </c>
       <c r="F35" t="s">
-        <v>1328</v>
+        <v>1369</v>
       </c>
       <c r="G35" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="H35">
         <v>180000</v>
@@ -18979,16 +19680,16 @@
         <v>38</v>
       </c>
       <c r="N35" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O35" t="s">
-        <v>1329</v>
+        <v>1370</v>
       </c>
       <c r="P35" t="s">
-        <v>1330</v>
+        <v>1371</v>
       </c>
       <c r="Q35" t="s">
-        <v>1331</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
@@ -19002,7 +19703,7 @@
         <v>32</v>
       </c>
       <c r="D36" t="s">
-        <v>1332</v>
+        <v>1373</v>
       </c>
       <c r="E36" t="s">
         <v>63</v>
@@ -19011,7 +19712,7 @@
         <v>20</v>
       </c>
       <c r="G36" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="H36">
         <v>219100</v>
@@ -19032,16 +19733,16 @@
         <v>25</v>
       </c>
       <c r="N36" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O36" t="s">
-        <v>1333</v>
+        <v>1374</v>
       </c>
       <c r="P36" t="s">
-        <v>1334</v>
+        <v>1375</v>
       </c>
       <c r="Q36" t="s">
-        <v>1335</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
@@ -19055,7 +19756,7 @@
         <v>35</v>
       </c>
       <c r="D37" t="s">
-        <v>1336</v>
+        <v>1377</v>
       </c>
       <c r="E37" t="s">
         <v>63</v>
@@ -19064,7 +19765,7 @@
         <v>20</v>
       </c>
       <c r="G37" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="H37">
         <v>219100</v>
@@ -19085,16 +19786,16 @@
         <v>25</v>
       </c>
       <c r="N37" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O37" t="s">
-        <v>1337</v>
+        <v>1378</v>
       </c>
       <c r="P37" t="s">
-        <v>1338</v>
+        <v>1379</v>
       </c>
       <c r="Q37" t="s">
-        <v>1339</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
@@ -19108,16 +19809,16 @@
         <v>40</v>
       </c>
       <c r="D38" t="s">
-        <v>1340</v>
+        <v>1381</v>
       </c>
       <c r="E38" t="s">
         <v>63</v>
       </c>
       <c r="F38" t="s">
-        <v>1341</v>
+        <v>1382</v>
       </c>
       <c r="G38" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="H38">
         <v>219100</v>
@@ -19138,16 +19839,16 @@
         <v>38</v>
       </c>
       <c r="N38" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O38" t="s">
-        <v>1342</v>
+        <v>1383</v>
       </c>
       <c r="P38" t="s">
-        <v>1343</v>
+        <v>1384</v>
       </c>
       <c r="Q38" t="s">
-        <v>1344</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
@@ -19161,7 +19862,7 @@
         <v>38</v>
       </c>
       <c r="D39" t="s">
-        <v>1345</v>
+        <v>1386</v>
       </c>
       <c r="E39" t="s">
         <v>63</v>
@@ -19170,7 +19871,7 @@
         <v>563</v>
       </c>
       <c r="G39" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="H39">
         <v>219100</v>
@@ -19191,16 +19892,16 @@
         <v>25</v>
       </c>
       <c r="N39" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O39" t="s">
-        <v>1346</v>
+        <v>1387</v>
       </c>
       <c r="P39" t="s">
-        <v>1347</v>
+        <v>1388</v>
       </c>
       <c r="Q39" t="s">
-        <v>1348</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
@@ -19214,7 +19915,7 @@
         <v>40</v>
       </c>
       <c r="D40" t="s">
-        <v>1349</v>
+        <v>1390</v>
       </c>
       <c r="E40" t="s">
         <v>63</v>
@@ -19223,7 +19924,7 @@
         <v>20</v>
       </c>
       <c r="G40" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="H40">
         <v>219100</v>
@@ -19244,16 +19945,16 @@
         <v>38</v>
       </c>
       <c r="N40" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O40" t="s">
-        <v>1350</v>
+        <v>1391</v>
       </c>
       <c r="P40" t="s">
-        <v>1351</v>
+        <v>1392</v>
       </c>
       <c r="Q40" t="s">
-        <v>1352</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
@@ -19267,16 +19968,16 @@
         <v>33</v>
       </c>
       <c r="D41" t="s">
-        <v>1353</v>
+        <v>1394</v>
       </c>
       <c r="E41" t="s">
         <v>63</v>
       </c>
       <c r="F41" t="s">
-        <v>1354</v>
+        <v>1395</v>
       </c>
       <c r="G41" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="H41">
         <v>219100</v>
@@ -19297,16 +19998,16 @@
         <v>25</v>
       </c>
       <c r="N41" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O41" t="s">
-        <v>1355</v>
+        <v>1396</v>
       </c>
       <c r="P41" t="s">
-        <v>1356</v>
+        <v>1397</v>
       </c>
       <c r="Q41" t="s">
-        <v>1357</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
@@ -19320,16 +20021,16 @@
         <v>48</v>
       </c>
       <c r="D42" t="s">
-        <v>1358</v>
+        <v>1399</v>
       </c>
       <c r="E42" t="s">
-        <v>1214</v>
+        <v>1256</v>
       </c>
       <c r="F42" t="s">
-        <v>1359</v>
+        <v>1400</v>
       </c>
       <c r="G42" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J42" t="s">
         <v>32</v>
@@ -19344,16 +20045,16 @@
         <v>38</v>
       </c>
       <c r="N42" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O42" t="s">
-        <v>1360</v>
+        <v>1401</v>
       </c>
       <c r="P42" t="s">
-        <v>1361</v>
+        <v>1402</v>
       </c>
       <c r="Q42" t="s">
-        <v>1362</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
@@ -19367,16 +20068,16 @@
         <v>40</v>
       </c>
       <c r="D43" t="s">
-        <v>1363</v>
+        <v>1404</v>
       </c>
       <c r="E43" t="s">
-        <v>1219</v>
+        <v>1261</v>
       </c>
       <c r="F43" t="s">
-        <v>1364</v>
+        <v>1405</v>
       </c>
       <c r="G43" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="H43">
         <v>184200</v>
@@ -19397,16 +20098,16 @@
         <v>38</v>
       </c>
       <c r="N43" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O43" t="s">
-        <v>1365</v>
+        <v>1406</v>
       </c>
       <c r="P43" t="s">
-        <v>1366</v>
+        <v>1407</v>
       </c>
       <c r="Q43" t="s">
-        <v>1367</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
@@ -19420,16 +20121,16 @@
         <v>30</v>
       </c>
       <c r="D44" t="s">
-        <v>1368</v>
+        <v>1409</v>
       </c>
       <c r="E44" t="s">
-        <v>1219</v>
+        <v>1261</v>
       </c>
       <c r="F44" t="s">
-        <v>1369</v>
+        <v>1410</v>
       </c>
       <c r="G44" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="H44">
         <v>200000</v>
@@ -19450,16 +20151,16 @@
         <v>25</v>
       </c>
       <c r="N44" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O44" t="s">
-        <v>1370</v>
+        <v>1411</v>
       </c>
       <c r="P44" t="s">
-        <v>1371</v>
+        <v>1412</v>
       </c>
       <c r="Q44" t="s">
-        <v>1372</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
@@ -19473,7 +20174,7 @@
         <v>30</v>
       </c>
       <c r="D45" t="s">
-        <v>1373</v>
+        <v>1414</v>
       </c>
       <c r="E45" t="s">
         <v>817</v>
@@ -19482,7 +20183,7 @@
         <v>826</v>
       </c>
       <c r="G45" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J45" t="s">
         <v>32</v>
@@ -19497,16 +20198,16 @@
         <v>25</v>
       </c>
       <c r="N45" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O45" t="s">
-        <v>1374</v>
+        <v>1415</v>
       </c>
       <c r="P45" t="s">
-        <v>1375</v>
+        <v>1416</v>
       </c>
       <c r="Q45" t="s">
-        <v>1376</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
@@ -19526,10 +20227,10 @@
         <v>817</v>
       </c>
       <c r="F46" t="s">
-        <v>1229</v>
+        <v>1271</v>
       </c>
       <c r="G46" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J46" t="s">
         <v>32</v>
@@ -19544,16 +20245,16 @@
         <v>25</v>
       </c>
       <c r="N46" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O46" t="s">
-        <v>1377</v>
+        <v>1418</v>
       </c>
       <c r="P46" t="s">
-        <v>1378</v>
+        <v>1419</v>
       </c>
       <c r="Q46" t="s">
-        <v>1379</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
@@ -19567,7 +20268,7 @@
         <v>32</v>
       </c>
       <c r="D47" t="s">
-        <v>1380</v>
+        <v>1421</v>
       </c>
       <c r="E47" t="s">
         <v>817</v>
@@ -19576,7 +20277,7 @@
         <v>826</v>
       </c>
       <c r="G47" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J47" t="s">
         <v>32</v>
@@ -19591,16 +20292,16 @@
         <v>25</v>
       </c>
       <c r="N47" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O47" t="s">
-        <v>1381</v>
+        <v>1422</v>
       </c>
       <c r="P47" t="s">
-        <v>1382</v>
+        <v>1423</v>
       </c>
       <c r="Q47" t="s">
-        <v>1383</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
@@ -19614,16 +20315,16 @@
         <v>45</v>
       </c>
       <c r="D48" t="s">
-        <v>1384</v>
+        <v>1425</v>
       </c>
       <c r="E48" t="s">
         <v>604</v>
       </c>
       <c r="F48" t="s">
-        <v>1385</v>
+        <v>1426</v>
       </c>
       <c r="G48" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J48" t="s">
         <v>32</v>
@@ -19638,16 +20339,16 @@
         <v>38</v>
       </c>
       <c r="N48" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O48" t="s">
-        <v>1386</v>
+        <v>1427</v>
       </c>
       <c r="P48" t="s">
-        <v>1387</v>
+        <v>1428</v>
       </c>
       <c r="Q48" t="s">
-        <v>1388</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
@@ -19661,16 +20362,16 @@
         <v>35</v>
       </c>
       <c r="D49" t="s">
-        <v>1389</v>
+        <v>1430</v>
       </c>
       <c r="E49" t="s">
         <v>604</v>
       </c>
       <c r="F49" t="s">
-        <v>1390</v>
+        <v>1431</v>
       </c>
       <c r="G49" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J49" t="s">
         <v>32</v>
@@ -19685,16 +20386,16 @@
         <v>25</v>
       </c>
       <c r="N49" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O49" t="s">
-        <v>1391</v>
+        <v>1432</v>
       </c>
       <c r="P49" t="s">
-        <v>1392</v>
+        <v>1433</v>
       </c>
       <c r="Q49" t="s">
-        <v>1393</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
@@ -19708,7 +20409,7 @@
         <v>35</v>
       </c>
       <c r="D50" t="s">
-        <v>1394</v>
+        <v>1435</v>
       </c>
       <c r="E50" t="s">
         <v>604</v>
@@ -19717,7 +20418,7 @@
         <v>87</v>
       </c>
       <c r="G50" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J50" t="s">
         <v>32</v>
@@ -19732,16 +20433,16 @@
         <v>25</v>
       </c>
       <c r="N50" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O50" t="s">
-        <v>1395</v>
+        <v>1436</v>
       </c>
       <c r="P50" t="s">
-        <v>1396</v>
+        <v>1437</v>
       </c>
       <c r="Q50" t="s">
-        <v>1397</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
@@ -19755,16 +20456,16 @@
         <v>15</v>
       </c>
       <c r="D51" t="s">
-        <v>1398</v>
+        <v>1439</v>
       </c>
       <c r="E51" t="s">
         <v>604</v>
       </c>
       <c r="F51" t="s">
-        <v>1399</v>
+        <v>1440</v>
       </c>
       <c r="G51" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J51" t="s">
         <v>32</v>
@@ -19779,16 +20480,16 @@
         <v>25</v>
       </c>
       <c r="N51" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O51" t="s">
-        <v>1400</v>
+        <v>1441</v>
       </c>
       <c r="P51" t="s">
-        <v>1401</v>
+        <v>1442</v>
       </c>
       <c r="Q51" t="s">
-        <v>1402</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
@@ -19802,16 +20503,16 @@
         <v>25</v>
       </c>
       <c r="D52" t="s">
-        <v>1403</v>
+        <v>1444</v>
       </c>
       <c r="E52" t="s">
         <v>604</v>
       </c>
       <c r="F52" t="s">
-        <v>1404</v>
+        <v>1445</v>
       </c>
       <c r="G52" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J52" t="s">
         <v>32</v>
@@ -19826,16 +20527,16 @@
         <v>25</v>
       </c>
       <c r="N52" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O52" t="s">
-        <v>1405</v>
+        <v>1446</v>
       </c>
       <c r="P52" t="s">
-        <v>1406</v>
+        <v>1447</v>
       </c>
       <c r="Q52" t="s">
-        <v>1407</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
@@ -19849,16 +20550,16 @@
         <v>30</v>
       </c>
       <c r="D53" t="s">
-        <v>1408</v>
+        <v>1449</v>
       </c>
       <c r="E53" t="s">
         <v>604</v>
       </c>
       <c r="F53" t="s">
-        <v>1409</v>
+        <v>1450</v>
       </c>
       <c r="G53" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J53" t="s">
         <v>32</v>
@@ -19873,16 +20574,16 @@
         <v>25</v>
       </c>
       <c r="N53" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O53" t="s">
-        <v>1410</v>
+        <v>1451</v>
       </c>
       <c r="P53" t="s">
-        <v>1411</v>
+        <v>1452</v>
       </c>
       <c r="Q53" t="s">
-        <v>1412</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
@@ -19902,10 +20603,10 @@
         <v>63</v>
       </c>
       <c r="F54" t="s">
-        <v>1369</v>
+        <v>1410</v>
       </c>
       <c r="G54" t="s">
-        <v>1182</v>
+        <v>1224</v>
       </c>
       <c r="J54" t="s">
         <v>32</v>
@@ -19920,16 +20621,16 @@
         <v>25</v>
       </c>
       <c r="N54" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O54" t="s">
-        <v>1413</v>
+        <v>1454</v>
       </c>
       <c r="P54" t="s">
-        <v>1414</v>
+        <v>1455</v>
       </c>
       <c r="Q54" t="s">
-        <v>1415</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
@@ -19949,10 +20650,10 @@
         <v>63</v>
       </c>
       <c r="F55" t="s">
-        <v>1416</v>
+        <v>1457</v>
       </c>
       <c r="G55" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J55" t="s">
         <v>32</v>
@@ -19967,16 +20668,16 @@
         <v>38</v>
       </c>
       <c r="N55" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O55" t="s">
-        <v>1417</v>
+        <v>1458</v>
       </c>
       <c r="P55" t="s">
-        <v>1418</v>
+        <v>1459</v>
       </c>
       <c r="Q55" t="s">
-        <v>1419</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
@@ -19999,7 +20700,7 @@
         <v>883</v>
       </c>
       <c r="G56" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="H56">
         <v>180000</v>
@@ -20020,16 +20721,16 @@
         <v>25</v>
       </c>
       <c r="N56" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O56" t="s">
-        <v>1420</v>
+        <v>1461</v>
       </c>
       <c r="P56" t="s">
-        <v>1421</v>
+        <v>1462</v>
       </c>
       <c r="Q56" t="s">
-        <v>1422</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
@@ -20049,10 +20750,10 @@
         <v>63</v>
       </c>
       <c r="F57" t="s">
-        <v>1423</v>
+        <v>1464</v>
       </c>
       <c r="G57" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="H57">
         <v>180000</v>
@@ -20073,16 +20774,16 @@
         <v>25</v>
       </c>
       <c r="N57" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O57" t="s">
-        <v>1424</v>
+        <v>1465</v>
       </c>
       <c r="P57" t="s">
-        <v>1425</v>
+        <v>1466</v>
       </c>
       <c r="Q57" t="s">
-        <v>1426</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
@@ -20096,16 +20797,16 @@
         <v>20</v>
       </c>
       <c r="D58" t="s">
-        <v>1427</v>
+        <v>1468</v>
       </c>
       <c r="E58" t="s">
         <v>928</v>
       </c>
       <c r="F58" t="s">
-        <v>1428</v>
+        <v>1469</v>
       </c>
       <c r="G58" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J58" t="s">
         <v>32</v>
@@ -20120,16 +20821,16 @@
         <v>25</v>
       </c>
       <c r="N58" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O58" t="s">
-        <v>1429</v>
+        <v>1470</v>
       </c>
       <c r="P58" t="s">
-        <v>1430</v>
+        <v>1471</v>
       </c>
       <c r="Q58" t="s">
-        <v>1431</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
@@ -20143,7 +20844,7 @@
         <v>50</v>
       </c>
       <c r="D59" t="s">
-        <v>1432</v>
+        <v>1473</v>
       </c>
       <c r="E59" t="s">
         <v>928</v>
@@ -20152,7 +20853,7 @@
         <v>20</v>
       </c>
       <c r="G59" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="H59">
         <v>250000</v>
@@ -20173,16 +20874,16 @@
         <v>38</v>
       </c>
       <c r="N59" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O59" t="s">
-        <v>1433</v>
+        <v>1474</v>
       </c>
       <c r="P59" t="s">
-        <v>1434</v>
+        <v>1475</v>
       </c>
       <c r="Q59" t="s">
-        <v>1435</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
@@ -20196,7 +20897,7 @@
         <v>55</v>
       </c>
       <c r="D60" t="s">
-        <v>1436</v>
+        <v>1477</v>
       </c>
       <c r="E60" t="s">
         <v>928</v>
@@ -20205,7 +20906,7 @@
         <v>20</v>
       </c>
       <c r="G60" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="H60">
         <v>200000</v>
@@ -20226,16 +20927,16 @@
         <v>38</v>
       </c>
       <c r="N60" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O60" t="s">
-        <v>1437</v>
+        <v>1478</v>
       </c>
       <c r="P60" t="s">
-        <v>1438</v>
+        <v>1479</v>
       </c>
       <c r="Q60" t="s">
-        <v>1439</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
@@ -20249,7 +20950,7 @@
         <v>52</v>
       </c>
       <c r="D61" t="s">
-        <v>1440</v>
+        <v>1481</v>
       </c>
       <c r="E61" t="s">
         <v>928</v>
@@ -20258,7 +20959,7 @@
         <v>20</v>
       </c>
       <c r="G61" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="H61">
         <v>250000</v>
@@ -20279,16 +20980,16 @@
         <v>38</v>
       </c>
       <c r="N61" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O61" t="s">
-        <v>1441</v>
+        <v>1482</v>
       </c>
       <c r="P61" t="s">
-        <v>1442</v>
+        <v>1483</v>
       </c>
       <c r="Q61" t="s">
-        <v>1443</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
@@ -20302,7 +21003,7 @@
         <v>53</v>
       </c>
       <c r="D62" t="s">
-        <v>1444</v>
+        <v>1485</v>
       </c>
       <c r="E62" t="s">
         <v>928</v>
@@ -20311,7 +21012,7 @@
         <v>20</v>
       </c>
       <c r="G62" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="H62">
         <v>200000</v>
@@ -20332,16 +21033,16 @@
         <v>38</v>
       </c>
       <c r="N62" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O62" t="s">
-        <v>1445</v>
+        <v>1486</v>
       </c>
       <c r="P62" t="s">
-        <v>1446</v>
+        <v>1487</v>
       </c>
       <c r="Q62" t="s">
-        <v>1447</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
@@ -20355,7 +21056,7 @@
         <v>50</v>
       </c>
       <c r="D63" t="s">
-        <v>1448</v>
+        <v>1489</v>
       </c>
       <c r="E63" t="s">
         <v>928</v>
@@ -20364,7 +21065,7 @@
         <v>20</v>
       </c>
       <c r="G63" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="H63">
         <v>200000</v>
@@ -20385,16 +21086,16 @@
         <v>38</v>
       </c>
       <c r="N63" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O63" t="s">
-        <v>1449</v>
+        <v>1490</v>
       </c>
       <c r="P63" t="s">
-        <v>1450</v>
+        <v>1491</v>
       </c>
       <c r="Q63" t="s">
-        <v>1451</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
@@ -20408,7 +21109,7 @@
         <v>55</v>
       </c>
       <c r="D64" t="s">
-        <v>1452</v>
+        <v>1493</v>
       </c>
       <c r="E64" t="s">
         <v>928</v>
@@ -20417,7 +21118,7 @@
         <v>20</v>
       </c>
       <c r="G64" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="H64">
         <v>250000</v>
@@ -20438,16 +21139,16 @@
         <v>38</v>
       </c>
       <c r="N64" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O64" t="s">
-        <v>1453</v>
+        <v>1494</v>
       </c>
       <c r="P64" t="s">
-        <v>1454</v>
+        <v>1495</v>
       </c>
       <c r="Q64" t="s">
-        <v>1455</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
@@ -20461,16 +21162,16 @@
         <v>45</v>
       </c>
       <c r="D65" t="s">
-        <v>1456</v>
+        <v>1497</v>
       </c>
       <c r="E65" t="s">
-        <v>1457</v>
+        <v>1498</v>
       </c>
       <c r="F65" t="s">
-        <v>1458</v>
+        <v>1499</v>
       </c>
       <c r="G65" t="s">
-        <v>1182</v>
+        <v>1224</v>
       </c>
       <c r="H65">
         <v>154000</v>
@@ -20491,16 +21192,16 @@
         <v>25</v>
       </c>
       <c r="N65" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O65" t="s">
-        <v>1459</v>
+        <v>1500</v>
       </c>
       <c r="P65" t="s">
-        <v>1460</v>
+        <v>1501</v>
       </c>
       <c r="Q65" t="s">
-        <v>1461</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
@@ -20523,7 +21224,7 @@
         <v>563</v>
       </c>
       <c r="G66" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="H66">
         <v>180000</v>
@@ -20544,16 +21245,16 @@
         <v>38</v>
       </c>
       <c r="N66" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O66" t="s">
-        <v>1462</v>
+        <v>1503</v>
       </c>
       <c r="P66" t="s">
-        <v>1463</v>
+        <v>1504</v>
       </c>
       <c r="Q66" t="s">
-        <v>1464</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
@@ -20573,10 +21274,10 @@
         <v>63</v>
       </c>
       <c r="F67" t="s">
-        <v>1318</v>
+        <v>1359</v>
       </c>
       <c r="G67" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="H67">
         <v>219100</v>
@@ -20597,16 +21298,16 @@
         <v>25</v>
       </c>
       <c r="N67" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O67" t="s">
-        <v>1465</v>
+        <v>1506</v>
       </c>
       <c r="P67" t="s">
-        <v>1466</v>
+        <v>1507</v>
       </c>
       <c r="Q67" t="s">
-        <v>1467</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
@@ -20620,7 +21321,7 @@
         <v>25</v>
       </c>
       <c r="D68" t="s">
-        <v>1468</v>
+        <v>1509</v>
       </c>
       <c r="E68" t="s">
         <v>63</v>
@@ -20629,7 +21330,7 @@
         <v>1133</v>
       </c>
       <c r="G68" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J68" t="s">
         <v>32</v>
@@ -20644,16 +21345,16 @@
         <v>25</v>
       </c>
       <c r="N68" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O68" t="s">
-        <v>1469</v>
+        <v>1510</v>
       </c>
       <c r="P68" t="s">
-        <v>1470</v>
+        <v>1511</v>
       </c>
       <c r="Q68" t="s">
-        <v>1471</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
@@ -20673,10 +21374,10 @@
         <v>817</v>
       </c>
       <c r="F69" t="s">
-        <v>1259</v>
+        <v>1301</v>
       </c>
       <c r="G69" t="s">
-        <v>1182</v>
+        <v>1224</v>
       </c>
       <c r="J69" t="s">
         <v>32</v>
@@ -20691,16 +21392,16 @@
         <v>25</v>
       </c>
       <c r="N69" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O69" t="s">
-        <v>1472</v>
+        <v>1513</v>
       </c>
       <c r="P69" t="s">
-        <v>1473</v>
+        <v>1514</v>
       </c>
       <c r="Q69" t="s">
-        <v>1474</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
@@ -20714,16 +21415,16 @@
         <v>15</v>
       </c>
       <c r="D70" t="s">
-        <v>1475</v>
+        <v>1516</v>
       </c>
       <c r="E70" t="s">
-        <v>1476</v>
+        <v>1517</v>
       </c>
       <c r="F70" t="s">
         <v>1149</v>
       </c>
       <c r="G70" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J70" t="s">
         <v>32</v>
@@ -20738,16 +21439,16 @@
         <v>25</v>
       </c>
       <c r="N70" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O70" t="s">
-        <v>1477</v>
+        <v>1518</v>
       </c>
       <c r="P70" t="s">
-        <v>1478</v>
+        <v>1519</v>
       </c>
       <c r="Q70" t="s">
-        <v>1479</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
@@ -20761,16 +21462,16 @@
         <v>12</v>
       </c>
       <c r="D71" t="s">
-        <v>1480</v>
+        <v>1521</v>
       </c>
       <c r="E71" t="s">
-        <v>1481</v>
+        <v>1522</v>
       </c>
       <c r="F71" t="s">
-        <v>1482</v>
+        <v>1523</v>
       </c>
       <c r="G71" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J71" t="s">
         <v>32</v>
@@ -20785,16 +21486,16 @@
         <v>25</v>
       </c>
       <c r="N71" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O71" t="s">
-        <v>1483</v>
+        <v>1524</v>
       </c>
       <c r="P71" t="s">
-        <v>1484</v>
+        <v>1525</v>
       </c>
       <c r="Q71" t="s">
-        <v>1485</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
@@ -20808,16 +21509,16 @@
         <v>42</v>
       </c>
       <c r="D72" t="s">
-        <v>1486</v>
+        <v>1527</v>
       </c>
       <c r="E72" t="s">
         <v>63</v>
       </c>
       <c r="F72" t="s">
-        <v>1487</v>
+        <v>1528</v>
       </c>
       <c r="G72" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="H72">
         <v>180000</v>
@@ -20838,16 +21539,16 @@
         <v>38</v>
       </c>
       <c r="N72" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O72" t="s">
-        <v>1488</v>
+        <v>1529</v>
       </c>
       <c r="P72" t="s">
-        <v>1489</v>
+        <v>1530</v>
       </c>
       <c r="Q72" t="s">
-        <v>1490</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
@@ -20861,16 +21562,16 @@
         <v>22</v>
       </c>
       <c r="D73" t="s">
-        <v>1491</v>
+        <v>1532</v>
       </c>
       <c r="E73" t="s">
-        <v>1219</v>
+        <v>1261</v>
       </c>
       <c r="F73" t="s">
-        <v>1492</v>
+        <v>1533</v>
       </c>
       <c r="G73" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="H73">
         <v>200000</v>
@@ -20891,16 +21592,16 @@
         <v>25</v>
       </c>
       <c r="N73" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O73" t="s">
-        <v>1493</v>
+        <v>1534</v>
       </c>
       <c r="P73" t="s">
-        <v>1494</v>
+        <v>1535</v>
       </c>
       <c r="Q73" t="s">
-        <v>1495</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
@@ -20914,16 +21615,16 @@
         <v>28</v>
       </c>
       <c r="D74" t="s">
-        <v>1496</v>
+        <v>1537</v>
       </c>
       <c r="E74" t="s">
-        <v>1497</v>
+        <v>1538</v>
       </c>
       <c r="F74" t="s">
         <v>1133</v>
       </c>
       <c r="G74" t="s">
-        <v>1182</v>
+        <v>1224</v>
       </c>
       <c r="J74" t="s">
         <v>32</v>
@@ -20938,16 +21639,16 @@
         <v>25</v>
       </c>
       <c r="N74" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O74" t="s">
-        <v>1498</v>
+        <v>1539</v>
       </c>
       <c r="P74" t="s">
-        <v>1499</v>
+        <v>1540</v>
       </c>
       <c r="Q74" t="s">
-        <v>1500</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
@@ -20961,16 +21662,16 @@
         <v>5</v>
       </c>
       <c r="D75" t="s">
-        <v>1501</v>
+        <v>1542</v>
       </c>
       <c r="E75" t="s">
-        <v>1502</v>
+        <v>1543</v>
       </c>
       <c r="F75" t="s">
-        <v>1503</v>
+        <v>1544</v>
       </c>
       <c r="G75" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J75" t="s">
         <v>32</v>
@@ -20985,16 +21686,16 @@
         <v>25</v>
       </c>
       <c r="N75" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O75" t="s">
-        <v>1504</v>
+        <v>1545</v>
       </c>
       <c r="P75" t="s">
-        <v>1505</v>
+        <v>1546</v>
       </c>
       <c r="Q75" t="s">
-        <v>1506</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
@@ -21014,10 +21715,10 @@
         <v>63</v>
       </c>
       <c r="F76" t="s">
-        <v>1507</v>
+        <v>1548</v>
       </c>
       <c r="G76" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J76" t="s">
         <v>32</v>
@@ -21032,16 +21733,16 @@
         <v>38</v>
       </c>
       <c r="N76" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O76" t="s">
-        <v>1508</v>
+        <v>1549</v>
       </c>
       <c r="P76" t="s">
-        <v>1509</v>
+        <v>1550</v>
       </c>
       <c r="Q76" t="s">
-        <v>1510</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
@@ -21055,16 +21756,16 @@
         <v>35</v>
       </c>
       <c r="D77" t="s">
-        <v>1511</v>
+        <v>1552</v>
       </c>
       <c r="E77" t="s">
-        <v>1512</v>
+        <v>1553</v>
       </c>
       <c r="F77" t="s">
-        <v>1281</v>
+        <v>1200</v>
       </c>
       <c r="G77" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J77" t="s">
         <v>32</v>
@@ -21079,16 +21780,16 @@
         <v>25</v>
       </c>
       <c r="N77" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O77" t="s">
-        <v>1513</v>
+        <v>1554</v>
       </c>
       <c r="P77" t="s">
-        <v>1514</v>
+        <v>1555</v>
       </c>
       <c r="Q77" t="s">
-        <v>1515</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
@@ -21102,16 +21803,16 @@
         <v>55</v>
       </c>
       <c r="D78" t="s">
-        <v>1516</v>
+        <v>1557</v>
       </c>
       <c r="E78" t="s">
         <v>63</v>
       </c>
       <c r="F78" t="s">
-        <v>1318</v>
+        <v>1359</v>
       </c>
       <c r="G78" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="H78">
         <v>219100</v>
@@ -21126,22 +21827,22 @@
         <v>65</v>
       </c>
       <c r="L78" t="s">
-        <v>1517</v>
+        <v>1558</v>
       </c>
       <c r="M78" t="s">
         <v>38</v>
       </c>
       <c r="N78" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O78" t="s">
-        <v>1518</v>
+        <v>1559</v>
       </c>
       <c r="P78" t="s">
-        <v>1519</v>
+        <v>1560</v>
       </c>
       <c r="Q78" t="s">
-        <v>1520</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
@@ -21155,16 +21856,16 @@
         <v>50</v>
       </c>
       <c r="D79" t="s">
-        <v>1521</v>
+        <v>1562</v>
       </c>
       <c r="E79" t="s">
-        <v>1219</v>
+        <v>1261</v>
       </c>
       <c r="F79" t="s">
         <v>20</v>
       </c>
       <c r="G79" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="H79">
         <v>200000</v>
@@ -21179,22 +21880,22 @@
         <v>65</v>
       </c>
       <c r="L79" t="s">
-        <v>1517</v>
+        <v>1558</v>
       </c>
       <c r="M79" t="s">
         <v>38</v>
       </c>
       <c r="N79" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O79" t="s">
-        <v>1522</v>
+        <v>1563</v>
       </c>
       <c r="P79" t="s">
-        <v>1523</v>
+        <v>1564</v>
       </c>
       <c r="Q79" t="s">
-        <v>1524</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
@@ -21208,16 +21909,16 @@
         <v>12</v>
       </c>
       <c r="D80" t="s">
-        <v>1525</v>
+        <v>1566</v>
       </c>
       <c r="E80" t="s">
-        <v>1526</v>
+        <v>1567</v>
       </c>
       <c r="F80" t="s">
         <v>1133</v>
       </c>
       <c r="G80" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J80" t="s">
         <v>32</v>
@@ -21226,22 +21927,22 @@
         <v>99</v>
       </c>
       <c r="L80" t="s">
-        <v>1517</v>
+        <v>1558</v>
       </c>
       <c r="M80" t="s">
         <v>25</v>
       </c>
       <c r="N80" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O80" t="s">
-        <v>1527</v>
+        <v>1568</v>
       </c>
       <c r="P80" t="s">
-        <v>1528</v>
+        <v>1569</v>
       </c>
       <c r="Q80" t="s">
-        <v>1529</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
@@ -21255,16 +21956,16 @@
         <v>12</v>
       </c>
       <c r="D81" t="s">
-        <v>1530</v>
+        <v>1571</v>
       </c>
       <c r="E81" t="s">
-        <v>1526</v>
+        <v>1567</v>
       </c>
       <c r="F81" t="s">
         <v>1133</v>
       </c>
       <c r="G81" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J81" t="s">
         <v>32</v>
@@ -21273,22 +21974,22 @@
         <v>99</v>
       </c>
       <c r="L81" t="s">
-        <v>1517</v>
+        <v>1558</v>
       </c>
       <c r="M81" t="s">
         <v>25</v>
       </c>
       <c r="N81" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O81" t="s">
-        <v>1531</v>
+        <v>1572</v>
       </c>
       <c r="P81" t="s">
-        <v>1532</v>
+        <v>1573</v>
       </c>
       <c r="Q81" t="s">
-        <v>1533</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
@@ -21302,16 +22003,16 @@
         <v>3</v>
       </c>
       <c r="D82" t="s">
-        <v>1534</v>
+        <v>1575</v>
       </c>
       <c r="E82" t="s">
-        <v>1526</v>
+        <v>1567</v>
       </c>
       <c r="F82" t="s">
         <v>1133</v>
       </c>
       <c r="G82" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J82" t="s">
         <v>32</v>
@@ -21320,22 +22021,22 @@
         <v>99</v>
       </c>
       <c r="L82" t="s">
-        <v>1517</v>
+        <v>1558</v>
       </c>
       <c r="M82" t="s">
         <v>25</v>
       </c>
       <c r="N82" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O82" t="s">
-        <v>1535</v>
+        <v>1576</v>
       </c>
       <c r="P82" t="s">
-        <v>1536</v>
+        <v>1577</v>
       </c>
       <c r="Q82" t="s">
-        <v>1537</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
@@ -21349,16 +22050,16 @@
         <v>25</v>
       </c>
       <c r="D83" t="s">
-        <v>1538</v>
+        <v>1579</v>
       </c>
       <c r="E83" t="s">
-        <v>1539</v>
+        <v>1580</v>
       </c>
       <c r="F83" t="s">
-        <v>1540</v>
+        <v>1581</v>
       </c>
       <c r="G83" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J83" t="s">
         <v>32</v>
@@ -21367,22 +22068,22 @@
         <v>99</v>
       </c>
       <c r="L83" t="s">
-        <v>1517</v>
+        <v>1558</v>
       </c>
       <c r="M83" t="s">
         <v>25</v>
       </c>
       <c r="N83" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O83" t="s">
-        <v>1541</v>
+        <v>1582</v>
       </c>
       <c r="P83" t="s">
-        <v>1542</v>
+        <v>1583</v>
       </c>
       <c r="Q83" t="s">
-        <v>1543</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
@@ -21396,16 +22097,16 @@
         <v>62</v>
       </c>
       <c r="D84" t="s">
-        <v>1544</v>
+        <v>1585</v>
       </c>
       <c r="E84" t="s">
-        <v>1545</v>
+        <v>1586</v>
       </c>
       <c r="F84" t="s">
-        <v>1546</v>
+        <v>1587</v>
       </c>
       <c r="G84" t="s">
-        <v>1182</v>
+        <v>1224</v>
       </c>
       <c r="J84" t="s">
         <v>32</v>
@@ -21414,22 +22115,22 @@
         <v>99</v>
       </c>
       <c r="L84" t="s">
-        <v>1517</v>
+        <v>1558</v>
       </c>
       <c r="M84" t="s">
         <v>25</v>
       </c>
       <c r="N84" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O84" t="s">
-        <v>1547</v>
+        <v>1588</v>
       </c>
       <c r="P84" t="s">
-        <v>1548</v>
+        <v>1589</v>
       </c>
       <c r="Q84" t="s">
-        <v>1549</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
@@ -21443,16 +22144,16 @@
         <v>68</v>
       </c>
       <c r="D85" t="s">
-        <v>1550</v>
+        <v>1591</v>
       </c>
       <c r="E85" t="s">
-        <v>1545</v>
+        <v>1586</v>
       </c>
       <c r="F85" t="s">
-        <v>1546</v>
+        <v>1587</v>
       </c>
       <c r="G85" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J85" t="s">
         <v>32</v>
@@ -21461,22 +22162,22 @@
         <v>99</v>
       </c>
       <c r="L85" t="s">
-        <v>1517</v>
+        <v>1558</v>
       </c>
       <c r="M85" t="s">
         <v>25</v>
       </c>
       <c r="N85" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O85" t="s">
-        <v>1551</v>
+        <v>1592</v>
       </c>
       <c r="P85" t="s">
-        <v>1552</v>
+        <v>1593</v>
       </c>
       <c r="Q85" t="s">
-        <v>1553</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
@@ -21496,10 +22197,10 @@
         <v>63</v>
       </c>
       <c r="F86" t="s">
-        <v>1554</v>
+        <v>1595</v>
       </c>
       <c r="G86" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="H86">
         <v>180000</v>
@@ -21520,16 +22221,16 @@
         <v>38</v>
       </c>
       <c r="N86" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O86" t="s">
-        <v>1555</v>
+        <v>1596</v>
       </c>
       <c r="P86" t="s">
-        <v>1556</v>
+        <v>1597</v>
       </c>
       <c r="Q86" t="s">
-        <v>1557</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
@@ -21549,10 +22250,10 @@
         <v>63</v>
       </c>
       <c r="F87" t="s">
-        <v>1558</v>
+        <v>1599</v>
       </c>
       <c r="G87" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="H87">
         <v>180000</v>
@@ -21573,16 +22274,16 @@
         <v>38</v>
       </c>
       <c r="N87" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O87" t="s">
-        <v>1559</v>
+        <v>1600</v>
       </c>
       <c r="P87" t="s">
-        <v>1560</v>
+        <v>1601</v>
       </c>
       <c r="Q87" t="s">
-        <v>1561</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
@@ -21596,16 +22297,16 @@
         <v>35</v>
       </c>
       <c r="D88" t="s">
-        <v>1562</v>
+        <v>1603</v>
       </c>
       <c r="E88" t="s">
         <v>63</v>
       </c>
       <c r="F88" t="s">
-        <v>1563</v>
+        <v>1604</v>
       </c>
       <c r="G88" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="H88">
         <v>219100</v>
@@ -21626,16 +22327,16 @@
         <v>38</v>
       </c>
       <c r="N88" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O88" t="s">
-        <v>1564</v>
+        <v>1605</v>
       </c>
       <c r="P88" t="s">
-        <v>1565</v>
+        <v>1606</v>
       </c>
       <c r="Q88" t="s">
-        <v>1566</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
@@ -21649,16 +22350,16 @@
         <v>25</v>
       </c>
       <c r="D89" t="s">
-        <v>1567</v>
+        <v>1608</v>
       </c>
       <c r="E89" t="s">
         <v>604</v>
       </c>
       <c r="F89" t="s">
-        <v>1385</v>
+        <v>1426</v>
       </c>
       <c r="G89" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J89" t="s">
         <v>32</v>
@@ -21673,16 +22374,16 @@
         <v>25</v>
       </c>
       <c r="N89" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O89" t="s">
-        <v>1568</v>
+        <v>1609</v>
       </c>
       <c r="P89" t="s">
-        <v>1569</v>
+        <v>1610</v>
       </c>
       <c r="Q89" t="s">
-        <v>1570</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
@@ -21696,16 +22397,16 @@
         <v>35</v>
       </c>
       <c r="D90" t="s">
-        <v>1571</v>
+        <v>1612</v>
       </c>
       <c r="E90" t="s">
-        <v>1572</v>
+        <v>1613</v>
       </c>
       <c r="F90" t="s">
-        <v>1259</v>
+        <v>1301</v>
       </c>
       <c r="G90" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J90" t="s">
         <v>32</v>
@@ -21720,16 +22421,16 @@
         <v>25</v>
       </c>
       <c r="N90" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O90" t="s">
-        <v>1573</v>
+        <v>1614</v>
       </c>
       <c r="P90" t="s">
-        <v>1574</v>
+        <v>1615</v>
       </c>
       <c r="Q90" t="s">
-        <v>1575</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
@@ -21746,13 +22447,13 @@
         <v>276</v>
       </c>
       <c r="E91" t="s">
-        <v>1576</v>
+        <v>1199</v>
       </c>
       <c r="F91" t="s">
-        <v>1281</v>
+        <v>1200</v>
       </c>
       <c r="G91" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="H91">
         <v>200000</v>
@@ -21773,16 +22474,16 @@
         <v>25</v>
       </c>
       <c r="N91" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O91" t="s">
-        <v>1577</v>
+        <v>1617</v>
       </c>
       <c r="P91" t="s">
-        <v>1578</v>
+        <v>1618</v>
       </c>
       <c r="Q91" t="s">
-        <v>1579</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
@@ -21796,16 +22497,16 @@
         <v>38</v>
       </c>
       <c r="D92" t="s">
-        <v>1580</v>
+        <v>1620</v>
       </c>
       <c r="E92" t="s">
-        <v>1576</v>
+        <v>1199</v>
       </c>
       <c r="F92" t="s">
-        <v>1281</v>
+        <v>1200</v>
       </c>
       <c r="G92" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="H92">
         <v>200000</v>
@@ -21826,16 +22527,16 @@
         <v>25</v>
       </c>
       <c r="N92" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O92" t="s">
-        <v>1581</v>
+        <v>1621</v>
       </c>
       <c r="P92" t="s">
-        <v>1582</v>
+        <v>1622</v>
       </c>
       <c r="Q92" t="s">
-        <v>1583</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
@@ -21849,16 +22550,16 @@
         <v>40</v>
       </c>
       <c r="D93" t="s">
-        <v>1363</v>
+        <v>1404</v>
       </c>
       <c r="E93" t="s">
-        <v>1219</v>
+        <v>1261</v>
       </c>
       <c r="F93" t="s">
         <v>832</v>
       </c>
       <c r="G93" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="H93">
         <v>184200</v>
@@ -21879,16 +22580,16 @@
         <v>25</v>
       </c>
       <c r="N93" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O93" t="s">
-        <v>1584</v>
+        <v>1624</v>
       </c>
       <c r="P93" t="s">
-        <v>1585</v>
+        <v>1625</v>
       </c>
       <c r="Q93" t="s">
-        <v>1586</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
@@ -21902,16 +22603,16 @@
         <v>20</v>
       </c>
       <c r="D94" t="s">
-        <v>1587</v>
+        <v>1627</v>
       </c>
       <c r="E94" t="s">
-        <v>1588</v>
+        <v>1628</v>
       </c>
       <c r="F94" t="s">
-        <v>1589</v>
+        <v>1629</v>
       </c>
       <c r="G94" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J94" t="s">
         <v>32</v>
@@ -21926,16 +22627,16 @@
         <v>25</v>
       </c>
       <c r="N94" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O94" t="s">
-        <v>1590</v>
+        <v>1630</v>
       </c>
       <c r="P94" t="s">
-        <v>1591</v>
+        <v>1631</v>
       </c>
       <c r="Q94" t="s">
-        <v>1592</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
@@ -21949,16 +22650,16 @@
         <v>35</v>
       </c>
       <c r="D95" t="s">
-        <v>1593</v>
+        <v>1633</v>
       </c>
       <c r="E95" t="s">
-        <v>1594</v>
+        <v>1634</v>
       </c>
       <c r="F95" t="s">
-        <v>1595</v>
+        <v>1635</v>
       </c>
       <c r="G95" t="s">
-        <v>1182</v>
+        <v>1224</v>
       </c>
       <c r="H95">
         <v>230000</v>
@@ -21979,16 +22680,16 @@
         <v>25</v>
       </c>
       <c r="N95" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O95" t="s">
-        <v>1596</v>
+        <v>1636</v>
       </c>
       <c r="P95" t="s">
-        <v>1597</v>
+        <v>1637</v>
       </c>
       <c r="Q95" t="s">
-        <v>1598</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
@@ -22008,10 +22709,10 @@
         <v>63</v>
       </c>
       <c r="F96" t="s">
-        <v>1599</v>
+        <v>1639</v>
       </c>
       <c r="G96" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="H96">
         <v>219100</v>
@@ -22032,16 +22733,16 @@
         <v>75</v>
       </c>
       <c r="N96" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O96" t="s">
-        <v>1600</v>
+        <v>1640</v>
       </c>
       <c r="P96" t="s">
-        <v>1601</v>
+        <v>1641</v>
       </c>
       <c r="Q96" t="s">
-        <v>1602</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
@@ -22055,16 +22756,16 @@
         <v>25</v>
       </c>
       <c r="D97" t="s">
-        <v>1603</v>
+        <v>1643</v>
       </c>
       <c r="E97" t="s">
-        <v>1512</v>
+        <v>1553</v>
       </c>
       <c r="F97" t="s">
-        <v>1281</v>
+        <v>1200</v>
       </c>
       <c r="G97" t="s">
-        <v>1182</v>
+        <v>1224</v>
       </c>
       <c r="J97" t="s">
         <v>32</v>
@@ -22079,16 +22780,16 @@
         <v>25</v>
       </c>
       <c r="N97" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O97" t="s">
-        <v>1604</v>
+        <v>1644</v>
       </c>
       <c r="P97" t="s">
-        <v>1605</v>
+        <v>1645</v>
       </c>
       <c r="Q97" t="s">
-        <v>1606</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
@@ -22102,16 +22803,16 @@
         <v>22</v>
       </c>
       <c r="D98" t="s">
-        <v>1607</v>
+        <v>1647</v>
       </c>
       <c r="E98" t="s">
-        <v>1608</v>
+        <v>1648</v>
       </c>
       <c r="F98" t="s">
-        <v>1609</v>
+        <v>1649</v>
       </c>
       <c r="G98" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J98" t="s">
         <v>32</v>
@@ -22126,16 +22827,16 @@
         <v>25</v>
       </c>
       <c r="N98" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O98" t="s">
-        <v>1610</v>
+        <v>1650</v>
       </c>
       <c r="P98" t="s">
-        <v>1611</v>
+        <v>1651</v>
       </c>
       <c r="Q98" t="s">
-        <v>1612</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.25">
@@ -22149,16 +22850,16 @@
         <v>3</v>
       </c>
       <c r="D99" t="s">
-        <v>1613</v>
+        <v>1653</v>
       </c>
       <c r="E99" t="s">
-        <v>1614</v>
+        <v>1654</v>
       </c>
       <c r="F99" t="s">
-        <v>1609</v>
+        <v>1649</v>
       </c>
       <c r="G99" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J99" t="s">
         <v>32</v>
@@ -22173,16 +22874,16 @@
         <v>25</v>
       </c>
       <c r="N99" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O99" t="s">
-        <v>1615</v>
+        <v>1655</v>
       </c>
       <c r="P99" t="s">
-        <v>1616</v>
+        <v>1656</v>
       </c>
       <c r="Q99" t="s">
-        <v>1617</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.25">
@@ -22196,16 +22897,16 @@
         <v>28</v>
       </c>
       <c r="D100" t="s">
-        <v>1618</v>
+        <v>1658</v>
       </c>
       <c r="E100" t="s">
-        <v>1619</v>
+        <v>1659</v>
       </c>
       <c r="F100" t="s">
         <v>1133</v>
       </c>
       <c r="G100" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J100" t="s">
         <v>32</v>
@@ -22220,16 +22921,16 @@
         <v>25</v>
       </c>
       <c r="N100" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O100" t="s">
-        <v>1620</v>
+        <v>1660</v>
       </c>
       <c r="P100" t="s">
-        <v>1621</v>
+        <v>1661</v>
       </c>
       <c r="Q100" t="s">
-        <v>1622</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.25">
@@ -22243,16 +22944,16 @@
         <v>45</v>
       </c>
       <c r="D101" t="s">
-        <v>1623</v>
+        <v>1663</v>
       </c>
       <c r="E101" t="s">
-        <v>1624</v>
+        <v>1664</v>
       </c>
       <c r="F101" t="s">
-        <v>1259</v>
+        <v>1301</v>
       </c>
       <c r="G101" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J101" t="s">
         <v>32</v>
@@ -22267,16 +22968,16 @@
         <v>38</v>
       </c>
       <c r="N101" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O101" t="s">
-        <v>1625</v>
+        <v>1665</v>
       </c>
       <c r="P101" t="s">
-        <v>1626</v>
+        <v>1666</v>
       </c>
       <c r="Q101" t="s">
-        <v>1627</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.25">
@@ -22290,16 +22991,16 @@
         <v>50</v>
       </c>
       <c r="D102" t="s">
-        <v>1628</v>
+        <v>1668</v>
       </c>
       <c r="E102" t="s">
-        <v>1629</v>
+        <v>1669</v>
       </c>
       <c r="F102" t="s">
-        <v>1292</v>
+        <v>1333</v>
       </c>
       <c r="G102" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J102" t="s">
         <v>32</v>
@@ -22314,16 +23015,16 @@
         <v>38</v>
       </c>
       <c r="N102" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O102" t="s">
-        <v>1630</v>
+        <v>1670</v>
       </c>
       <c r="P102" t="s">
-        <v>1631</v>
+        <v>1671</v>
       </c>
       <c r="Q102" t="s">
-        <v>1632</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.25">
@@ -22337,16 +23038,16 @@
         <v>48</v>
       </c>
       <c r="D103" t="s">
-        <v>1633</v>
+        <v>1673</v>
       </c>
       <c r="E103" t="s">
-        <v>1457</v>
+        <v>1498</v>
       </c>
       <c r="F103" t="s">
-        <v>1634</v>
+        <v>1674</v>
       </c>
       <c r="G103" t="s">
-        <v>1182</v>
+        <v>1224</v>
       </c>
       <c r="H103">
         <v>154000</v>
@@ -22367,16 +23068,16 @@
         <v>38</v>
       </c>
       <c r="N103" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O103" t="s">
-        <v>1635</v>
+        <v>1675</v>
       </c>
       <c r="P103" t="s">
-        <v>1636</v>
+        <v>1676</v>
       </c>
       <c r="Q103" t="s">
-        <v>1637</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.25">
@@ -22390,16 +23091,16 @@
         <v>25</v>
       </c>
       <c r="D104" t="s">
-        <v>1638</v>
+        <v>1678</v>
       </c>
       <c r="E104" t="s">
-        <v>1280</v>
+        <v>1322</v>
       </c>
       <c r="F104" t="s">
-        <v>1281</v>
+        <v>1200</v>
       </c>
       <c r="G104" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J104" t="s">
         <v>32</v>
@@ -22414,16 +23115,16 @@
         <v>25</v>
       </c>
       <c r="N104" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O104" t="s">
-        <v>1639</v>
+        <v>1679</v>
       </c>
       <c r="P104" t="s">
-        <v>1640</v>
+        <v>1680</v>
       </c>
       <c r="Q104" t="s">
-        <v>1641</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.25">
@@ -22437,16 +23138,16 @@
         <v>32</v>
       </c>
       <c r="D105" t="s">
-        <v>1538</v>
+        <v>1579</v>
       </c>
       <c r="E105" t="s">
-        <v>1280</v>
+        <v>1322</v>
       </c>
       <c r="F105" t="s">
-        <v>1281</v>
+        <v>1200</v>
       </c>
       <c r="G105" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J105" t="s">
         <v>32</v>
@@ -22461,16 +23162,16 @@
         <v>25</v>
       </c>
       <c r="N105" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O105" t="s">
-        <v>1642</v>
+        <v>1682</v>
       </c>
       <c r="P105" t="s">
-        <v>1643</v>
+        <v>1683</v>
       </c>
       <c r="Q105" t="s">
-        <v>1644</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.25">
@@ -22484,16 +23185,16 @@
         <v>22</v>
       </c>
       <c r="D106" t="s">
-        <v>1645</v>
+        <v>1685</v>
       </c>
       <c r="E106" t="s">
-        <v>1629</v>
+        <v>1669</v>
       </c>
       <c r="F106" t="s">
-        <v>1609</v>
+        <v>1649</v>
       </c>
       <c r="G106" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J106" t="s">
         <v>32</v>
@@ -22508,16 +23209,16 @@
         <v>25</v>
       </c>
       <c r="N106" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O106" t="s">
-        <v>1646</v>
+        <v>1686</v>
       </c>
       <c r="P106" t="s">
-        <v>1647</v>
+        <v>1687</v>
       </c>
       <c r="Q106" t="s">
-        <v>1648</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.25">
@@ -22531,16 +23232,16 @@
         <v>55</v>
       </c>
       <c r="D107" t="s">
-        <v>1628</v>
+        <v>1668</v>
       </c>
       <c r="E107" t="s">
-        <v>1629</v>
+        <v>1669</v>
       </c>
       <c r="F107" t="s">
-        <v>1649</v>
+        <v>1689</v>
       </c>
       <c r="G107" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J107" t="s">
         <v>32</v>
@@ -22555,16 +23256,16 @@
         <v>25</v>
       </c>
       <c r="N107" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O107" t="s">
-        <v>1650</v>
+        <v>1690</v>
       </c>
       <c r="P107" t="s">
-        <v>1651</v>
+        <v>1691</v>
       </c>
       <c r="Q107" t="s">
-        <v>1652</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.25">
@@ -22578,16 +23279,16 @@
         <v>25</v>
       </c>
       <c r="D108" t="s">
-        <v>1653</v>
+        <v>1693</v>
       </c>
       <c r="E108" t="s">
-        <v>1629</v>
+        <v>1669</v>
       </c>
       <c r="F108" t="s">
-        <v>1649</v>
+        <v>1689</v>
       </c>
       <c r="G108" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J108" t="s">
         <v>32</v>
@@ -22602,16 +23303,16 @@
         <v>25</v>
       </c>
       <c r="N108" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O108" t="s">
-        <v>1654</v>
+        <v>1694</v>
       </c>
       <c r="P108" t="s">
-        <v>1655</v>
+        <v>1695</v>
       </c>
       <c r="Q108" t="s">
-        <v>1656</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.25">
@@ -22625,7 +23326,7 @@
         <v>33</v>
       </c>
       <c r="D109" t="s">
-        <v>1657</v>
+        <v>1697</v>
       </c>
       <c r="E109" t="s">
         <v>63</v>
@@ -22634,7 +23335,7 @@
         <v>1133</v>
       </c>
       <c r="G109" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J109" t="s">
         <v>32</v>
@@ -22649,16 +23350,16 @@
         <v>25</v>
       </c>
       <c r="N109" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O109" t="s">
-        <v>1658</v>
+        <v>1698</v>
       </c>
       <c r="P109" t="s">
-        <v>1659</v>
+        <v>1699</v>
       </c>
       <c r="Q109" t="s">
-        <v>1660</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.25">
@@ -22672,16 +23373,16 @@
         <v>38</v>
       </c>
       <c r="D110" t="s">
-        <v>1661</v>
+        <v>1701</v>
       </c>
       <c r="E110" t="s">
-        <v>1662</v>
+        <v>1702</v>
       </c>
       <c r="F110" t="s">
-        <v>1390</v>
+        <v>1431</v>
       </c>
       <c r="G110" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="H110">
         <v>220000</v>
@@ -22702,16 +23403,16 @@
         <v>25</v>
       </c>
       <c r="N110" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O110" t="s">
-        <v>1663</v>
+        <v>1703</v>
       </c>
       <c r="P110" t="s">
-        <v>1664</v>
+        <v>1704</v>
       </c>
       <c r="Q110" t="s">
-        <v>1665</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.25">
@@ -22725,16 +23426,16 @@
         <v>62</v>
       </c>
       <c r="D111" t="s">
-        <v>1666</v>
+        <v>1706</v>
       </c>
       <c r="E111" t="s">
-        <v>1219</v>
+        <v>1261</v>
       </c>
       <c r="F111" t="s">
         <v>20</v>
       </c>
       <c r="G111" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="H111">
         <v>200000</v>
@@ -22755,16 +23456,16 @@
         <v>38</v>
       </c>
       <c r="N111" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O111" t="s">
-        <v>1667</v>
+        <v>1707</v>
       </c>
       <c r="P111" t="s">
-        <v>1668</v>
+        <v>1708</v>
       </c>
       <c r="Q111" t="s">
-        <v>1669</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.25">
@@ -22778,16 +23479,16 @@
         <v>30</v>
       </c>
       <c r="D112" t="s">
-        <v>1653</v>
+        <v>1693</v>
       </c>
       <c r="E112" t="s">
-        <v>1629</v>
+        <v>1669</v>
       </c>
       <c r="F112" t="s">
-        <v>1609</v>
+        <v>1649</v>
       </c>
       <c r="G112" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J112" t="s">
         <v>32</v>
@@ -22802,16 +23503,16 @@
         <v>25</v>
       </c>
       <c r="N112" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O112" t="s">
-        <v>1670</v>
+        <v>1710</v>
       </c>
       <c r="P112" t="s">
-        <v>1671</v>
+        <v>1711</v>
       </c>
       <c r="Q112" t="s">
-        <v>1672</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.25">
@@ -22825,16 +23526,16 @@
         <v>58</v>
       </c>
       <c r="D113" t="s">
-        <v>1628</v>
+        <v>1668</v>
       </c>
       <c r="E113" t="s">
-        <v>1629</v>
+        <v>1669</v>
       </c>
       <c r="F113" t="s">
-        <v>1292</v>
+        <v>1333</v>
       </c>
       <c r="G113" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J113" t="s">
         <v>32</v>
@@ -22849,16 +23550,16 @@
         <v>25</v>
       </c>
       <c r="N113" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O113" t="s">
-        <v>1673</v>
+        <v>1713</v>
       </c>
       <c r="P113" t="s">
-        <v>1674</v>
+        <v>1714</v>
       </c>
       <c r="Q113" t="s">
-        <v>1675</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.25">
@@ -22872,7 +23573,7 @@
         <v>55</v>
       </c>
       <c r="D114" t="s">
-        <v>1676</v>
+        <v>1716</v>
       </c>
       <c r="E114" t="s">
         <v>63</v>
@@ -22881,7 +23582,7 @@
         <v>20</v>
       </c>
       <c r="G114" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="H114">
         <v>217800</v>
@@ -22902,16 +23603,16 @@
         <v>38</v>
       </c>
       <c r="N114" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O114" t="s">
-        <v>1677</v>
+        <v>1717</v>
       </c>
       <c r="P114" t="s">
-        <v>1678</v>
+        <v>1718</v>
       </c>
       <c r="Q114" t="s">
-        <v>1679</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.25">
@@ -22925,16 +23626,16 @@
         <v>45</v>
       </c>
       <c r="D115" t="s">
-        <v>1680</v>
+        <v>1720</v>
       </c>
       <c r="E115" t="s">
         <v>63</v>
       </c>
       <c r="F115" t="s">
-        <v>1681</v>
+        <v>1721</v>
       </c>
       <c r="G115" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="H115">
         <v>219100</v>
@@ -22955,16 +23656,16 @@
         <v>38</v>
       </c>
       <c r="N115" t="s">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="O115" t="s">
-        <v>1682</v>
+        <v>1722</v>
       </c>
       <c r="P115" t="s">
-        <v>1683</v>
+        <v>1723</v>
       </c>
       <c r="Q115" t="s">
-        <v>1684</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.25">
@@ -22984,10 +23685,10 @@
         <v>817</v>
       </c>
       <c r="F116" t="s">
-        <v>1685</v>
+        <v>1725</v>
       </c>
       <c r="G116" t="s">
-        <v>1168</v>
+        <v>1210</v>
       </c>
       <c r="J116" t="s">
         <v>32</v>
@@ -23002,16 +23703,263 @@
         <v>25</v>
       </c>
       <c r="N116" t="s">
+        <v>1211</v>
+      </c>
+      <c r="O116" t="s">
+        <v>1726</v>
+      </c>
+      <c r="P116" t="s">
+        <v>1727</v>
+      </c>
+      <c r="Q116" t="s">
+        <v>1728</v>
+      </c>
+    </row>
+    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>17</v>
+      </c>
+      <c r="B117">
+        <v>25</v>
+      </c>
+      <c r="C117">
+        <v>35</v>
+      </c>
+      <c r="D117" t="s">
+        <v>1729</v>
+      </c>
+      <c r="E117" t="s">
+        <v>63</v>
+      </c>
+      <c r="F117" t="s">
+        <v>1730</v>
+      </c>
+      <c r="G117" t="s">
+        <v>1210</v>
+      </c>
+      <c r="J117" t="s">
+        <v>32</v>
+      </c>
+      <c r="K117" t="s">
+        <v>65</v>
+      </c>
+      <c r="L117" t="s">
         <v>1169</v>
       </c>
-      <c r="O116" t="s">
-        <v>1686</v>
-      </c>
-      <c r="P116" t="s">
-        <v>1687</v>
-      </c>
-      <c r="Q116" t="s">
-        <v>1688</v>
+      <c r="M117" t="s">
+        <v>25</v>
+      </c>
+      <c r="N117" t="s">
+        <v>1211</v>
+      </c>
+      <c r="O117" t="s">
+        <v>1731</v>
+      </c>
+      <c r="P117" t="s">
+        <v>1732</v>
+      </c>
+      <c r="Q117" t="s">
+        <v>1733</v>
+      </c>
+    </row>
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>17</v>
+      </c>
+      <c r="B118">
+        <v>42</v>
+      </c>
+      <c r="C118">
+        <v>38</v>
+      </c>
+      <c r="D118" t="s">
+        <v>1734</v>
+      </c>
+      <c r="E118" t="s">
+        <v>63</v>
+      </c>
+      <c r="F118" t="s">
+        <v>20</v>
+      </c>
+      <c r="G118" t="s">
+        <v>1210</v>
+      </c>
+      <c r="H118">
+        <v>219100</v>
+      </c>
+      <c r="I118">
+        <v>219100</v>
+      </c>
+      <c r="J118" t="s">
+        <v>22</v>
+      </c>
+      <c r="K118" t="s">
+        <v>65</v>
+      </c>
+      <c r="L118" t="s">
+        <v>1169</v>
+      </c>
+      <c r="M118" t="s">
+        <v>25</v>
+      </c>
+      <c r="N118" t="s">
+        <v>1211</v>
+      </c>
+      <c r="O118" t="s">
+        <v>1735</v>
+      </c>
+      <c r="P118" t="s">
+        <v>1736</v>
+      </c>
+      <c r="Q118" t="s">
+        <v>1737</v>
+      </c>
+    </row>
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>17</v>
+      </c>
+      <c r="B119">
+        <v>15</v>
+      </c>
+      <c r="C119">
+        <v>22</v>
+      </c>
+      <c r="D119" t="s">
+        <v>1738</v>
+      </c>
+      <c r="E119" t="s">
+        <v>1739</v>
+      </c>
+      <c r="F119" t="s">
+        <v>1740</v>
+      </c>
+      <c r="G119" t="s">
+        <v>1210</v>
+      </c>
+      <c r="J119" t="s">
+        <v>32</v>
+      </c>
+      <c r="K119" t="s">
+        <v>99</v>
+      </c>
+      <c r="L119" t="s">
+        <v>1169</v>
+      </c>
+      <c r="M119" t="s">
+        <v>25</v>
+      </c>
+      <c r="N119" t="s">
+        <v>1211</v>
+      </c>
+      <c r="O119" t="s">
+        <v>1741</v>
+      </c>
+      <c r="P119" t="s">
+        <v>1742</v>
+      </c>
+      <c r="Q119" t="s">
+        <v>1743</v>
+      </c>
+    </row>
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>17</v>
+      </c>
+      <c r="B120">
+        <v>20</v>
+      </c>
+      <c r="C120">
+        <v>35</v>
+      </c>
+      <c r="D120" t="s">
+        <v>1744</v>
+      </c>
+      <c r="E120" t="s">
+        <v>1745</v>
+      </c>
+      <c r="F120" t="s">
+        <v>1746</v>
+      </c>
+      <c r="G120" t="s">
+        <v>1210</v>
+      </c>
+      <c r="J120" t="s">
+        <v>32</v>
+      </c>
+      <c r="K120" t="s">
+        <v>99</v>
+      </c>
+      <c r="L120" t="s">
+        <v>1169</v>
+      </c>
+      <c r="M120" t="s">
+        <v>25</v>
+      </c>
+      <c r="N120" t="s">
+        <v>1211</v>
+      </c>
+      <c r="O120" t="s">
+        <v>1747</v>
+      </c>
+      <c r="P120" t="s">
+        <v>1748</v>
+      </c>
+      <c r="Q120" t="s">
+        <v>1749</v>
+      </c>
+    </row>
+    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>17</v>
+      </c>
+      <c r="B121">
+        <v>60</v>
+      </c>
+      <c r="C121">
+        <v>55</v>
+      </c>
+      <c r="D121" t="s">
+        <v>1750</v>
+      </c>
+      <c r="E121" t="s">
+        <v>1199</v>
+      </c>
+      <c r="F121" t="s">
+        <v>1200</v>
+      </c>
+      <c r="G121" t="s">
+        <v>1210</v>
+      </c>
+      <c r="H121">
+        <v>200000</v>
+      </c>
+      <c r="I121">
+        <v>200000</v>
+      </c>
+      <c r="J121" t="s">
+        <v>22</v>
+      </c>
+      <c r="K121" t="s">
+        <v>99</v>
+      </c>
+      <c r="L121" t="s">
+        <v>1169</v>
+      </c>
+      <c r="M121" t="s">
+        <v>38</v>
+      </c>
+      <c r="N121" t="s">
+        <v>1211</v>
+      </c>
+      <c r="O121" t="s">
+        <v>1751</v>
+      </c>
+      <c r="P121" t="s">
+        <v>1752</v>
+      </c>
+      <c r="Q121" t="s">
+        <v>1753</v>
       </c>
     </row>
   </sheetData>

--- a/hunt/board.xlsx
+++ b/hunt/board.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4753" uniqueCount="1754">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4831" uniqueCount="1777">
   <si>
     <t>Column</t>
   </si>
@@ -3641,6 +3641,27 @@
     <t>https://jobs.ashbyhq.com/temporal/cdabd368-1989-4ea8-801d-2be138c16523</t>
   </si>
   <si>
+    <t>Senior Infrastructure DevOps Engineer (100% Remote Germany)</t>
+  </si>
+  <si>
+    <t>Innocraft</t>
+  </si>
+  <si>
+    <t>Frankfurt</t>
+  </si>
+  <si>
+    <t>2026-09-04T15:36:38.857Z</t>
+  </si>
+  <si>
+    <t>Fully remote and centered on infrastructure architecture, automation, and reliability — core to the candidate's CI/CD and IaC skill set | High-autonomy ownership of platform architecture aligns with principal-level scope ambitions | Open-source, data-sovereignty-focused product suits candidate's compliance-driven architecture background</t>
+  </si>
+  <si>
+    <t>Remote is restricted to Germany — candidate is US-based, so eligibility is likely a hard blocker | Likely Linux/Kubernetes/bare-metal-heavy stack rather than Azure-native, where candidate's depth lies | IC infrastructure engineering role, not customer-facing architecture advisory</t>
+  </si>
+  <si>
+    <t>https://www.arbeitnow.com/jobs/companies/innocraft/senior-infrastructure-devops-engineer-100-remote-germany-frankfurt-381413</t>
+  </si>
+  <si>
     <t>Solutions Architect - Agencies</t>
   </si>
   <si>
@@ -5274,6 +5295,54 @@
   </si>
   <si>
     <t>https://www.arbeitnow.com/jobs/companies/elastic/senior-solution-architect-enterprise-176532</t>
+  </si>
+  <si>
+    <t>West Coast - United States</t>
+  </si>
+  <si>
+    <t>Trusted-advisor architecture engagement model matches candidate's Customer Engineer experience directly | Salary confirmed at $180K, which meets the candidate's floor | Cloud ecosystem breadth and technical strategy ownership align with target Solutions Architect titles</t>
+  </si>
+  <si>
+    <t>Databricks SA roles require deep data/AI platform depth (Spark, Delta Lake, ML pipelines) that isn't in the candidate's profile | 'Strat Media' vertical implies media/adtech domain specialization and expects a developed technical archetype the candidate lacks | West Coast US location requirement conflicts with Humble, TX base and pre-sales quota-adjacent work is a tradeoff</t>
+  </si>
+  <si>
+    <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8755461002</t>
+  </si>
+  <si>
+    <t>Pre-sales trusted-advisor model overlaps with candidate's enterprise customer advisory experience | Scalable systems design and deployment/operations focus touches candidate's DevOps and cloud architecture background</t>
+  </si>
+  <si>
+    <t>London-based hybrid role — outside the candidate's stated US market scope and likely needs UK work authorization | Requires MongoDB/NoSQL data platform depth and data modeling expertise absent from the candidate's Azure/DevOps profile | Heavily sales-aligned pre-sales role tied to deal cycles, a weaker match than technical delivery/architecture advisory</t>
+  </si>
+  <si>
+    <t>https://www.mongodb.com/careers/job/?gh_jid=8174075</t>
+  </si>
+  <si>
+    <t>Trusted-advisor customer engagement across startups to large enterprises mirrors candidate's advisory model | Solutions Architect title matches candidate's target titles directly</t>
+  </si>
+  <si>
+    <t>Requires MongoDB/NoSQL data platform and data modeling depth the candidate does not have | No location or workplace type listed, so US remote eligibility and comp are unknown | Quota-adjacent pre-sales role tied to winning deals rather than technical delivery architecture</t>
+  </si>
+  <si>
+    <t>https://www.arbeitnow.com/jobs/companies/mongodb/solutions-architect-101416</t>
+  </si>
+  <si>
+    <t>Senior Solutions Architect is an exact target title with senior-level scope | Pre-sales advisory responsibility for customer success and deployment design overlaps candidate's Customer Engineer work | Wide customer range from startups to global enterprises fits candidate's enterprise advisory experience</t>
+  </si>
+  <si>
+    <t>Core requirement is MongoDB/NoSQL data platform expertise, not Azure/DevOps platform depth | Location and workplace type are unspecified, leaving US eligibility and onsite expectations unclear | Pre-sales, deal-driven motion is a tradeoff versus the candidate's technical delivery orientation</t>
+  </si>
+  <si>
+    <t>https://www.arbeitnow.com/jobs/companies/mongodb/senior-solutions-architect-301835</t>
+  </si>
+  <si>
+    <t>Senior/principal-level architecture ownership scope matches candidate's target seniority | Candidate's TypeScript/JavaScript product development experience touches the Node.js side of the role</t>
+  </si>
+  <si>
+    <t>Requires deep Node.js microservices and SAP Private Cloud platform architecture expertise — SAP experience is entirely absent from the candidate's profile | Hamburg-based hybrid role in Germany, outside the candidate's US market scope and requiring EU work authorization | No cloud governance/DevOps advisory focus where the candidate's Azure strengths lie</t>
+  </si>
+  <si>
+    <t>https://www.arbeitnow.com/jobs/companies/implico-gmbh/senior-technical-architect-hybrid-product-platform-hamburg-434079</t>
   </si>
 </sst>
 </file>
@@ -5654,7 +5723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q244"/>
+  <dimension ref="A1:Q245"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -17907,6 +17976,53 @@
         <v>1208</v>
       </c>
     </row>
+    <row r="245" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>17</v>
+      </c>
+      <c r="B245">
+        <v>40</v>
+      </c>
+      <c r="C245">
+        <v>55</v>
+      </c>
+      <c r="D245" t="s">
+        <v>1209</v>
+      </c>
+      <c r="E245" t="s">
+        <v>1210</v>
+      </c>
+      <c r="F245" t="s">
+        <v>1211</v>
+      </c>
+      <c r="G245" t="s">
+        <v>21</v>
+      </c>
+      <c r="J245" t="s">
+        <v>32</v>
+      </c>
+      <c r="K245" t="s">
+        <v>99</v>
+      </c>
+      <c r="L245" t="s">
+        <v>1212</v>
+      </c>
+      <c r="M245" t="s">
+        <v>38</v>
+      </c>
+      <c r="N245" t="s">
+        <v>26</v>
+      </c>
+      <c r="O245" t="s">
+        <v>1213</v>
+      </c>
+      <c r="P245" t="s">
+        <v>1214</v>
+      </c>
+      <c r="Q245" t="s">
+        <v>1215</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:Q1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17916,7 +18032,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q121"/>
+  <dimension ref="A1:Q126"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -17997,7 +18113,7 @@
         <v>42</v>
       </c>
       <c r="D2" t="s">
-        <v>1209</v>
+        <v>1216</v>
       </c>
       <c r="E2" t="s">
         <v>63</v>
@@ -18006,7 +18122,7 @@
         <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J2" t="s">
         <v>32</v>
@@ -18021,16 +18137,16 @@
         <v>25</v>
       </c>
       <c r="N2" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O2" t="s">
-        <v>1212</v>
+        <v>1219</v>
       </c>
       <c r="P2" t="s">
-        <v>1213</v>
+        <v>1220</v>
       </c>
       <c r="Q2" t="s">
-        <v>1214</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -18044,7 +18160,7 @@
         <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>1215</v>
+        <v>1222</v>
       </c>
       <c r="E3" t="s">
         <v>63</v>
@@ -18053,7 +18169,7 @@
         <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J3" t="s">
         <v>32</v>
@@ -18068,16 +18184,16 @@
         <v>25</v>
       </c>
       <c r="N3" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O3" t="s">
-        <v>1216</v>
+        <v>1223</v>
       </c>
       <c r="P3" t="s">
-        <v>1217</v>
+        <v>1224</v>
       </c>
       <c r="Q3" t="s">
-        <v>1218</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
@@ -18097,10 +18213,10 @@
         <v>63</v>
       </c>
       <c r="F4" t="s">
-        <v>1219</v>
+        <v>1226</v>
       </c>
       <c r="G4" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="H4">
         <v>180000</v>
@@ -18121,16 +18237,16 @@
         <v>38</v>
       </c>
       <c r="N4" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O4" t="s">
-        <v>1220</v>
+        <v>1227</v>
       </c>
       <c r="P4" t="s">
-        <v>1221</v>
+        <v>1228</v>
       </c>
       <c r="Q4" t="s">
-        <v>1222</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -18144,7 +18260,7 @@
         <v>52</v>
       </c>
       <c r="D5" t="s">
-        <v>1223</v>
+        <v>1230</v>
       </c>
       <c r="E5" t="s">
         <v>63</v>
@@ -18153,7 +18269,7 @@
         <v>20</v>
       </c>
       <c r="G5" t="s">
-        <v>1224</v>
+        <v>1231</v>
       </c>
       <c r="H5">
         <v>180000</v>
@@ -18174,16 +18290,16 @@
         <v>38</v>
       </c>
       <c r="N5" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O5" t="s">
-        <v>1225</v>
+        <v>1232</v>
       </c>
       <c r="P5" t="s">
-        <v>1226</v>
+        <v>1233</v>
       </c>
       <c r="Q5" t="s">
-        <v>1227</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -18197,7 +18313,7 @@
         <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>1228</v>
+        <v>1235</v>
       </c>
       <c r="E6" t="s">
         <v>63</v>
@@ -18206,7 +18322,7 @@
         <v>20</v>
       </c>
       <c r="G6" t="s">
-        <v>1224</v>
+        <v>1231</v>
       </c>
       <c r="H6">
         <v>180000</v>
@@ -18227,16 +18343,16 @@
         <v>38</v>
       </c>
       <c r="N6" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O6" t="s">
-        <v>1229</v>
+        <v>1236</v>
       </c>
       <c r="P6" t="s">
-        <v>1230</v>
+        <v>1237</v>
       </c>
       <c r="Q6" t="s">
-        <v>1231</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -18250,16 +18366,16 @@
         <v>48</v>
       </c>
       <c r="D7" t="s">
-        <v>1232</v>
+        <v>1239</v>
       </c>
       <c r="E7" t="s">
         <v>63</v>
       </c>
       <c r="F7" t="s">
-        <v>1233</v>
+        <v>1240</v>
       </c>
       <c r="G7" t="s">
-        <v>1224</v>
+        <v>1231</v>
       </c>
       <c r="H7">
         <v>219100</v>
@@ -18280,16 +18396,16 @@
         <v>38</v>
       </c>
       <c r="N7" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O7" t="s">
-        <v>1234</v>
+        <v>1241</v>
       </c>
       <c r="P7" t="s">
-        <v>1235</v>
+        <v>1242</v>
       </c>
       <c r="Q7" t="s">
-        <v>1236</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -18303,16 +18419,16 @@
         <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>1237</v>
+        <v>1244</v>
       </c>
       <c r="E8" t="s">
         <v>63</v>
       </c>
       <c r="F8" t="s">
-        <v>1238</v>
+        <v>1245</v>
       </c>
       <c r="G8" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="H8">
         <v>180000</v>
@@ -18333,16 +18449,16 @@
         <v>38</v>
       </c>
       <c r="N8" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O8" t="s">
-        <v>1239</v>
+        <v>1246</v>
       </c>
       <c r="P8" t="s">
-        <v>1240</v>
+        <v>1247</v>
       </c>
       <c r="Q8" t="s">
-        <v>1241</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -18356,7 +18472,7 @@
         <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>1242</v>
+        <v>1249</v>
       </c>
       <c r="E9" t="s">
         <v>63</v>
@@ -18365,7 +18481,7 @@
         <v>20</v>
       </c>
       <c r="G9" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="H9">
         <v>219100</v>
@@ -18386,16 +18502,16 @@
         <v>25</v>
       </c>
       <c r="N9" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O9" t="s">
-        <v>1243</v>
+        <v>1250</v>
       </c>
       <c r="P9" t="s">
-        <v>1244</v>
+        <v>1251</v>
       </c>
       <c r="Q9" t="s">
-        <v>1245</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -18409,7 +18525,7 @@
         <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="E10" t="s">
         <v>63</v>
@@ -18418,7 +18534,7 @@
         <v>20</v>
       </c>
       <c r="G10" t="s">
-        <v>1224</v>
+        <v>1231</v>
       </c>
       <c r="H10">
         <v>219100</v>
@@ -18439,16 +18555,16 @@
         <v>38</v>
       </c>
       <c r="N10" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O10" t="s">
-        <v>1247</v>
+        <v>1254</v>
       </c>
       <c r="P10" t="s">
-        <v>1248</v>
+        <v>1255</v>
       </c>
       <c r="Q10" t="s">
-        <v>1249</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -18462,16 +18578,16 @@
         <v>30</v>
       </c>
       <c r="D11" t="s">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="E11" t="s">
         <v>63</v>
       </c>
       <c r="F11" t="s">
-        <v>1251</v>
+        <v>1258</v>
       </c>
       <c r="G11" t="s">
-        <v>1224</v>
+        <v>1231</v>
       </c>
       <c r="J11" t="s">
         <v>32</v>
@@ -18486,16 +18602,16 @@
         <v>25</v>
       </c>
       <c r="N11" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O11" t="s">
-        <v>1252</v>
+        <v>1259</v>
       </c>
       <c r="P11" t="s">
-        <v>1253</v>
+        <v>1260</v>
       </c>
       <c r="Q11" t="s">
-        <v>1254</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -18509,16 +18625,16 @@
         <v>58</v>
       </c>
       <c r="D12" t="s">
-        <v>1255</v>
+        <v>1262</v>
       </c>
       <c r="E12" t="s">
-        <v>1256</v>
+        <v>1263</v>
       </c>
       <c r="F12" t="s">
-        <v>1257</v>
+        <v>1264</v>
       </c>
       <c r="G12" t="s">
-        <v>1224</v>
+        <v>1231</v>
       </c>
       <c r="H12">
         <v>257000</v>
@@ -18539,16 +18655,16 @@
         <v>38</v>
       </c>
       <c r="N12" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O12" t="s">
-        <v>1258</v>
+        <v>1265</v>
       </c>
       <c r="P12" t="s">
-        <v>1259</v>
+        <v>1266</v>
       </c>
       <c r="Q12" t="s">
-        <v>1260</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
@@ -18565,13 +18681,13 @@
         <v>282</v>
       </c>
       <c r="E13" t="s">
-        <v>1261</v>
+        <v>1268</v>
       </c>
       <c r="F13" t="s">
-        <v>1262</v>
+        <v>1269</v>
       </c>
       <c r="G13" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="H13">
         <v>200000</v>
@@ -18592,16 +18708,16 @@
         <v>25</v>
       </c>
       <c r="N13" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O13" t="s">
-        <v>1263</v>
+        <v>1270</v>
       </c>
       <c r="P13" t="s">
-        <v>1264</v>
+        <v>1271</v>
       </c>
       <c r="Q13" t="s">
-        <v>1265</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
@@ -18615,16 +18731,16 @@
         <v>20</v>
       </c>
       <c r="D14" t="s">
-        <v>1266</v>
+        <v>1273</v>
       </c>
       <c r="E14" t="s">
         <v>817</v>
       </c>
       <c r="F14" t="s">
-        <v>1267</v>
+        <v>1274</v>
       </c>
       <c r="G14" t="s">
-        <v>1224</v>
+        <v>1231</v>
       </c>
       <c r="J14" t="s">
         <v>32</v>
@@ -18639,16 +18755,16 @@
         <v>25</v>
       </c>
       <c r="N14" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O14" t="s">
-        <v>1268</v>
+        <v>1275</v>
       </c>
       <c r="P14" t="s">
-        <v>1269</v>
+        <v>1276</v>
       </c>
       <c r="Q14" t="s">
-        <v>1270</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -18668,10 +18784,10 @@
         <v>817</v>
       </c>
       <c r="F15" t="s">
-        <v>1271</v>
+        <v>1278</v>
       </c>
       <c r="G15" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J15" t="s">
         <v>32</v>
@@ -18686,16 +18802,16 @@
         <v>25</v>
       </c>
       <c r="N15" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O15" t="s">
-        <v>1272</v>
+        <v>1279</v>
       </c>
       <c r="P15" t="s">
-        <v>1273</v>
+        <v>1280</v>
       </c>
       <c r="Q15" t="s">
-        <v>1274</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
@@ -18709,16 +18825,16 @@
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>1275</v>
+        <v>1282</v>
       </c>
       <c r="E16" t="s">
         <v>817</v>
       </c>
       <c r="F16" t="s">
-        <v>1276</v>
+        <v>1283</v>
       </c>
       <c r="G16" t="s">
-        <v>1224</v>
+        <v>1231</v>
       </c>
       <c r="H16">
         <v>500000</v>
@@ -18739,16 +18855,16 @@
         <v>25</v>
       </c>
       <c r="N16" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O16" t="s">
-        <v>1277</v>
+        <v>1284</v>
       </c>
       <c r="P16" t="s">
-        <v>1278</v>
+        <v>1285</v>
       </c>
       <c r="Q16" t="s">
-        <v>1279</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
@@ -18762,16 +18878,16 @@
         <v>18</v>
       </c>
       <c r="D17" t="s">
-        <v>1280</v>
+        <v>1287</v>
       </c>
       <c r="E17" t="s">
         <v>604</v>
       </c>
       <c r="F17" t="s">
-        <v>1281</v>
+        <v>1288</v>
       </c>
       <c r="G17" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="H17">
         <v>274456</v>
@@ -18792,16 +18908,16 @@
         <v>25</v>
       </c>
       <c r="N17" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O17" t="s">
-        <v>1282</v>
+        <v>1289</v>
       </c>
       <c r="P17" t="s">
-        <v>1283</v>
+        <v>1290</v>
       </c>
       <c r="Q17" t="s">
-        <v>1284</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
@@ -18815,16 +18931,16 @@
         <v>30</v>
       </c>
       <c r="D18" t="s">
-        <v>1285</v>
+        <v>1292</v>
       </c>
       <c r="E18" t="s">
         <v>604</v>
       </c>
       <c r="F18" t="s">
-        <v>1286</v>
+        <v>1293</v>
       </c>
       <c r="G18" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J18" t="s">
         <v>32</v>
@@ -18839,16 +18955,16 @@
         <v>25</v>
       </c>
       <c r="N18" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O18" t="s">
-        <v>1287</v>
+        <v>1294</v>
       </c>
       <c r="P18" t="s">
-        <v>1288</v>
+        <v>1295</v>
       </c>
       <c r="Q18" t="s">
-        <v>1289</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -18862,16 +18978,16 @@
         <v>22</v>
       </c>
       <c r="D19" t="s">
-        <v>1290</v>
+        <v>1297</v>
       </c>
       <c r="E19" t="s">
         <v>604</v>
       </c>
       <c r="F19" t="s">
-        <v>1291</v>
+        <v>1298</v>
       </c>
       <c r="G19" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J19" t="s">
         <v>32</v>
@@ -18886,16 +19002,16 @@
         <v>25</v>
       </c>
       <c r="N19" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O19" t="s">
-        <v>1292</v>
+        <v>1299</v>
       </c>
       <c r="P19" t="s">
-        <v>1293</v>
+        <v>1300</v>
       </c>
       <c r="Q19" t="s">
-        <v>1294</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -18909,16 +19025,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="s">
-        <v>1295</v>
+        <v>1302</v>
       </c>
       <c r="E20" t="s">
         <v>604</v>
       </c>
       <c r="F20" t="s">
-        <v>1296</v>
+        <v>1303</v>
       </c>
       <c r="G20" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J20" t="s">
         <v>32</v>
@@ -18933,16 +19049,16 @@
         <v>38</v>
       </c>
       <c r="N20" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O20" t="s">
-        <v>1297</v>
+        <v>1304</v>
       </c>
       <c r="P20" t="s">
-        <v>1298</v>
+        <v>1305</v>
       </c>
       <c r="Q20" t="s">
-        <v>1299</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
@@ -18956,16 +19072,16 @@
         <v>25</v>
       </c>
       <c r="D21" t="s">
-        <v>1300</v>
+        <v>1307</v>
       </c>
       <c r="E21" t="s">
         <v>604</v>
       </c>
       <c r="F21" t="s">
-        <v>1301</v>
+        <v>1308</v>
       </c>
       <c r="G21" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J21" t="s">
         <v>32</v>
@@ -18980,16 +19096,16 @@
         <v>25</v>
       </c>
       <c r="N21" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O21" t="s">
-        <v>1302</v>
+        <v>1309</v>
       </c>
       <c r="P21" t="s">
-        <v>1303</v>
+        <v>1310</v>
       </c>
       <c r="Q21" t="s">
-        <v>1304</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -19003,16 +19119,16 @@
         <v>40</v>
       </c>
       <c r="D22" t="s">
-        <v>1305</v>
+        <v>1312</v>
       </c>
       <c r="E22" t="s">
         <v>604</v>
       </c>
       <c r="F22" t="s">
-        <v>1306</v>
+        <v>1313</v>
       </c>
       <c r="G22" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J22" t="s">
         <v>32</v>
@@ -19027,16 +19143,16 @@
         <v>25</v>
       </c>
       <c r="N22" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O22" t="s">
-        <v>1307</v>
+        <v>1314</v>
       </c>
       <c r="P22" t="s">
-        <v>1308</v>
+        <v>1315</v>
       </c>
       <c r="Q22" t="s">
-        <v>1309</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
@@ -19050,16 +19166,16 @@
         <v>70</v>
       </c>
       <c r="D23" t="s">
-        <v>1310</v>
+        <v>1317</v>
       </c>
       <c r="E23" t="s">
-        <v>1311</v>
+        <v>1318</v>
       </c>
       <c r="F23" t="s">
-        <v>1312</v>
+        <v>1319</v>
       </c>
       <c r="G23" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J23" t="s">
         <v>32</v>
@@ -19074,16 +19190,16 @@
         <v>25</v>
       </c>
       <c r="N23" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O23" t="s">
-        <v>1313</v>
+        <v>1320</v>
       </c>
       <c r="P23" t="s">
-        <v>1314</v>
+        <v>1321</v>
       </c>
       <c r="Q23" t="s">
-        <v>1315</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
@@ -19097,16 +19213,16 @@
         <v>58</v>
       </c>
       <c r="D24" t="s">
-        <v>1316</v>
+        <v>1323</v>
       </c>
       <c r="E24" t="s">
-        <v>1317</v>
+        <v>1324</v>
       </c>
       <c r="F24" t="s">
-        <v>1301</v>
+        <v>1308</v>
       </c>
       <c r="G24" t="s">
-        <v>1224</v>
+        <v>1231</v>
       </c>
       <c r="J24" t="s">
         <v>32</v>
@@ -19121,16 +19237,16 @@
         <v>25</v>
       </c>
       <c r="N24" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O24" t="s">
-        <v>1318</v>
+        <v>1325</v>
       </c>
       <c r="P24" t="s">
-        <v>1319</v>
+        <v>1326</v>
       </c>
       <c r="Q24" t="s">
-        <v>1320</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
@@ -19144,16 +19260,16 @@
         <v>32</v>
       </c>
       <c r="D25" t="s">
-        <v>1321</v>
+        <v>1328</v>
       </c>
       <c r="E25" t="s">
-        <v>1322</v>
+        <v>1329</v>
       </c>
       <c r="F25" t="s">
         <v>1200</v>
       </c>
       <c r="G25" t="s">
-        <v>1224</v>
+        <v>1231</v>
       </c>
       <c r="J25" t="s">
         <v>32</v>
@@ -19168,16 +19284,16 @@
         <v>25</v>
       </c>
       <c r="N25" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O25" t="s">
-        <v>1323</v>
+        <v>1330</v>
       </c>
       <c r="P25" t="s">
-        <v>1324</v>
+        <v>1331</v>
       </c>
       <c r="Q25" t="s">
-        <v>1325</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
@@ -19191,16 +19307,16 @@
         <v>4</v>
       </c>
       <c r="D26" t="s">
-        <v>1326</v>
+        <v>1333</v>
       </c>
       <c r="E26" t="s">
-        <v>1327</v>
+        <v>1334</v>
       </c>
       <c r="F26" t="s">
         <v>1149</v>
       </c>
       <c r="G26" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J26" t="s">
         <v>32</v>
@@ -19215,16 +19331,16 @@
         <v>25</v>
       </c>
       <c r="N26" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O26" t="s">
-        <v>1328</v>
+        <v>1335</v>
       </c>
       <c r="P26" t="s">
-        <v>1329</v>
+        <v>1336</v>
       </c>
       <c r="Q26" t="s">
-        <v>1330</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
@@ -19238,16 +19354,16 @@
         <v>25</v>
       </c>
       <c r="D27" t="s">
-        <v>1331</v>
+        <v>1338</v>
       </c>
       <c r="E27" t="s">
-        <v>1332</v>
+        <v>1339</v>
       </c>
       <c r="F27" t="s">
-        <v>1333</v>
+        <v>1340</v>
       </c>
       <c r="G27" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J27" t="s">
         <v>32</v>
@@ -19262,16 +19378,16 @@
         <v>25</v>
       </c>
       <c r="N27" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O27" t="s">
-        <v>1334</v>
+        <v>1341</v>
       </c>
       <c r="P27" t="s">
-        <v>1335</v>
+        <v>1342</v>
       </c>
       <c r="Q27" t="s">
-        <v>1336</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
@@ -19285,16 +19401,16 @@
         <v>30</v>
       </c>
       <c r="D28" t="s">
-        <v>1337</v>
+        <v>1344</v>
       </c>
       <c r="E28" t="s">
-        <v>1338</v>
+        <v>1345</v>
       </c>
       <c r="F28" t="s">
         <v>1142</v>
       </c>
       <c r="G28" t="s">
-        <v>1224</v>
+        <v>1231</v>
       </c>
       <c r="J28" t="s">
         <v>32</v>
@@ -19309,16 +19425,16 @@
         <v>25</v>
       </c>
       <c r="N28" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O28" t="s">
-        <v>1339</v>
+        <v>1346</v>
       </c>
       <c r="P28" t="s">
-        <v>1340</v>
+        <v>1347</v>
       </c>
       <c r="Q28" t="s">
-        <v>1341</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
@@ -19332,16 +19448,16 @@
         <v>52</v>
       </c>
       <c r="D29" t="s">
-        <v>1342</v>
+        <v>1349</v>
       </c>
       <c r="E29" t="s">
         <v>63</v>
       </c>
       <c r="F29" t="s">
-        <v>1343</v>
+        <v>1350</v>
       </c>
       <c r="G29" t="s">
-        <v>1224</v>
+        <v>1231</v>
       </c>
       <c r="H29">
         <v>180000</v>
@@ -19362,16 +19478,16 @@
         <v>38</v>
       </c>
       <c r="N29" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O29" t="s">
-        <v>1344</v>
+        <v>1351</v>
       </c>
       <c r="P29" t="s">
-        <v>1345</v>
+        <v>1352</v>
       </c>
       <c r="Q29" t="s">
-        <v>1346</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
@@ -19385,7 +19501,7 @@
         <v>50</v>
       </c>
       <c r="D30" t="s">
-        <v>1347</v>
+        <v>1354</v>
       </c>
       <c r="E30" t="s">
         <v>63</v>
@@ -19394,7 +19510,7 @@
         <v>20</v>
       </c>
       <c r="G30" t="s">
-        <v>1224</v>
+        <v>1231</v>
       </c>
       <c r="H30">
         <v>180000</v>
@@ -19415,16 +19531,16 @@
         <v>38</v>
       </c>
       <c r="N30" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O30" t="s">
-        <v>1348</v>
+        <v>1355</v>
       </c>
       <c r="P30" t="s">
-        <v>1349</v>
+        <v>1356</v>
       </c>
       <c r="Q30" t="s">
-        <v>1350</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
@@ -19438,7 +19554,7 @@
         <v>46</v>
       </c>
       <c r="D31" t="s">
-        <v>1351</v>
+        <v>1358</v>
       </c>
       <c r="E31" t="s">
         <v>63</v>
@@ -19447,7 +19563,7 @@
         <v>20</v>
       </c>
       <c r="G31" t="s">
-        <v>1224</v>
+        <v>1231</v>
       </c>
       <c r="H31">
         <v>180000</v>
@@ -19468,16 +19584,16 @@
         <v>38</v>
       </c>
       <c r="N31" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O31" t="s">
-        <v>1352</v>
+        <v>1359</v>
       </c>
       <c r="P31" t="s">
-        <v>1353</v>
+        <v>1360</v>
       </c>
       <c r="Q31" t="s">
-        <v>1354</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
@@ -19491,7 +19607,7 @@
         <v>38</v>
       </c>
       <c r="D32" t="s">
-        <v>1355</v>
+        <v>1362</v>
       </c>
       <c r="E32" t="s">
         <v>63</v>
@@ -19500,7 +19616,7 @@
         <v>20</v>
       </c>
       <c r="G32" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="H32">
         <v>217800</v>
@@ -19521,16 +19637,16 @@
         <v>25</v>
       </c>
       <c r="N32" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O32" t="s">
-        <v>1356</v>
+        <v>1363</v>
       </c>
       <c r="P32" t="s">
-        <v>1357</v>
+        <v>1364</v>
       </c>
       <c r="Q32" t="s">
-        <v>1358</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
@@ -19550,10 +19666,10 @@
         <v>63</v>
       </c>
       <c r="F33" t="s">
-        <v>1359</v>
+        <v>1366</v>
       </c>
       <c r="G33" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="H33">
         <v>180000</v>
@@ -19574,16 +19690,16 @@
         <v>38</v>
       </c>
       <c r="N33" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O33" t="s">
-        <v>1360</v>
+        <v>1367</v>
       </c>
       <c r="P33" t="s">
-        <v>1361</v>
+        <v>1368</v>
       </c>
       <c r="Q33" t="s">
-        <v>1362</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
@@ -19597,16 +19713,16 @@
         <v>45</v>
       </c>
       <c r="D34" t="s">
-        <v>1363</v>
+        <v>1370</v>
       </c>
       <c r="E34" t="s">
         <v>63</v>
       </c>
       <c r="F34" t="s">
-        <v>1364</v>
+        <v>1371</v>
       </c>
       <c r="G34" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="H34">
         <v>219100</v>
@@ -19627,16 +19743,16 @@
         <v>38</v>
       </c>
       <c r="N34" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O34" t="s">
-        <v>1365</v>
+        <v>1372</v>
       </c>
       <c r="P34" t="s">
-        <v>1366</v>
+        <v>1373</v>
       </c>
       <c r="Q34" t="s">
-        <v>1367</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
@@ -19650,16 +19766,16 @@
         <v>42</v>
       </c>
       <c r="D35" t="s">
-        <v>1368</v>
+        <v>1375</v>
       </c>
       <c r="E35" t="s">
         <v>63</v>
       </c>
       <c r="F35" t="s">
-        <v>1369</v>
+        <v>1376</v>
       </c>
       <c r="G35" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="H35">
         <v>180000</v>
@@ -19680,16 +19796,16 @@
         <v>38</v>
       </c>
       <c r="N35" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O35" t="s">
-        <v>1370</v>
+        <v>1377</v>
       </c>
       <c r="P35" t="s">
-        <v>1371</v>
+        <v>1378</v>
       </c>
       <c r="Q35" t="s">
-        <v>1372</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
@@ -19703,7 +19819,7 @@
         <v>32</v>
       </c>
       <c r="D36" t="s">
-        <v>1373</v>
+        <v>1380</v>
       </c>
       <c r="E36" t="s">
         <v>63</v>
@@ -19712,7 +19828,7 @@
         <v>20</v>
       </c>
       <c r="G36" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="H36">
         <v>219100</v>
@@ -19733,16 +19849,16 @@
         <v>25</v>
       </c>
       <c r="N36" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O36" t="s">
-        <v>1374</v>
+        <v>1381</v>
       </c>
       <c r="P36" t="s">
-        <v>1375</v>
+        <v>1382</v>
       </c>
       <c r="Q36" t="s">
-        <v>1376</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
@@ -19756,7 +19872,7 @@
         <v>35</v>
       </c>
       <c r="D37" t="s">
-        <v>1377</v>
+        <v>1384</v>
       </c>
       <c r="E37" t="s">
         <v>63</v>
@@ -19765,7 +19881,7 @@
         <v>20</v>
       </c>
       <c r="G37" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="H37">
         <v>219100</v>
@@ -19786,16 +19902,16 @@
         <v>25</v>
       </c>
       <c r="N37" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O37" t="s">
-        <v>1378</v>
+        <v>1385</v>
       </c>
       <c r="P37" t="s">
-        <v>1379</v>
+        <v>1386</v>
       </c>
       <c r="Q37" t="s">
-        <v>1380</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
@@ -19809,16 +19925,16 @@
         <v>40</v>
       </c>
       <c r="D38" t="s">
-        <v>1381</v>
+        <v>1388</v>
       </c>
       <c r="E38" t="s">
         <v>63</v>
       </c>
       <c r="F38" t="s">
-        <v>1382</v>
+        <v>1389</v>
       </c>
       <c r="G38" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="H38">
         <v>219100</v>
@@ -19839,16 +19955,16 @@
         <v>38</v>
       </c>
       <c r="N38" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O38" t="s">
-        <v>1383</v>
+        <v>1390</v>
       </c>
       <c r="P38" t="s">
-        <v>1384</v>
+        <v>1391</v>
       </c>
       <c r="Q38" t="s">
-        <v>1385</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
@@ -19862,7 +19978,7 @@
         <v>38</v>
       </c>
       <c r="D39" t="s">
-        <v>1386</v>
+        <v>1393</v>
       </c>
       <c r="E39" t="s">
         <v>63</v>
@@ -19871,7 +19987,7 @@
         <v>563</v>
       </c>
       <c r="G39" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="H39">
         <v>219100</v>
@@ -19892,16 +20008,16 @@
         <v>25</v>
       </c>
       <c r="N39" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O39" t="s">
-        <v>1387</v>
+        <v>1394</v>
       </c>
       <c r="P39" t="s">
-        <v>1388</v>
+        <v>1395</v>
       </c>
       <c r="Q39" t="s">
-        <v>1389</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
@@ -19915,7 +20031,7 @@
         <v>40</v>
       </c>
       <c r="D40" t="s">
-        <v>1390</v>
+        <v>1397</v>
       </c>
       <c r="E40" t="s">
         <v>63</v>
@@ -19924,7 +20040,7 @@
         <v>20</v>
       </c>
       <c r="G40" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="H40">
         <v>219100</v>
@@ -19945,16 +20061,16 @@
         <v>38</v>
       </c>
       <c r="N40" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O40" t="s">
-        <v>1391</v>
+        <v>1398</v>
       </c>
       <c r="P40" t="s">
-        <v>1392</v>
+        <v>1399</v>
       </c>
       <c r="Q40" t="s">
-        <v>1393</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
@@ -19968,16 +20084,16 @@
         <v>33</v>
       </c>
       <c r="D41" t="s">
-        <v>1394</v>
+        <v>1401</v>
       </c>
       <c r="E41" t="s">
         <v>63</v>
       </c>
       <c r="F41" t="s">
-        <v>1395</v>
+        <v>1402</v>
       </c>
       <c r="G41" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="H41">
         <v>219100</v>
@@ -19998,16 +20114,16 @@
         <v>25</v>
       </c>
       <c r="N41" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O41" t="s">
-        <v>1396</v>
+        <v>1403</v>
       </c>
       <c r="P41" t="s">
-        <v>1397</v>
+        <v>1404</v>
       </c>
       <c r="Q41" t="s">
-        <v>1398</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
@@ -20021,16 +20137,16 @@
         <v>48</v>
       </c>
       <c r="D42" t="s">
-        <v>1399</v>
+        <v>1406</v>
       </c>
       <c r="E42" t="s">
-        <v>1256</v>
+        <v>1263</v>
       </c>
       <c r="F42" t="s">
-        <v>1400</v>
+        <v>1407</v>
       </c>
       <c r="G42" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J42" t="s">
         <v>32</v>
@@ -20045,16 +20161,16 @@
         <v>38</v>
       </c>
       <c r="N42" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O42" t="s">
-        <v>1401</v>
+        <v>1408</v>
       </c>
       <c r="P42" t="s">
-        <v>1402</v>
+        <v>1409</v>
       </c>
       <c r="Q42" t="s">
-        <v>1403</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
@@ -20068,16 +20184,16 @@
         <v>40</v>
       </c>
       <c r="D43" t="s">
-        <v>1404</v>
+        <v>1411</v>
       </c>
       <c r="E43" t="s">
-        <v>1261</v>
+        <v>1268</v>
       </c>
       <c r="F43" t="s">
-        <v>1405</v>
+        <v>1412</v>
       </c>
       <c r="G43" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="H43">
         <v>184200</v>
@@ -20098,16 +20214,16 @@
         <v>38</v>
       </c>
       <c r="N43" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O43" t="s">
-        <v>1406</v>
+        <v>1413</v>
       </c>
       <c r="P43" t="s">
-        <v>1407</v>
+        <v>1414</v>
       </c>
       <c r="Q43" t="s">
-        <v>1408</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
@@ -20121,16 +20237,16 @@
         <v>30</v>
       </c>
       <c r="D44" t="s">
-        <v>1409</v>
+        <v>1416</v>
       </c>
       <c r="E44" t="s">
-        <v>1261</v>
+        <v>1268</v>
       </c>
       <c r="F44" t="s">
-        <v>1410</v>
+        <v>1417</v>
       </c>
       <c r="G44" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="H44">
         <v>200000</v>
@@ -20151,16 +20267,16 @@
         <v>25</v>
       </c>
       <c r="N44" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O44" t="s">
-        <v>1411</v>
+        <v>1418</v>
       </c>
       <c r="P44" t="s">
-        <v>1412</v>
+        <v>1419</v>
       </c>
       <c r="Q44" t="s">
-        <v>1413</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
@@ -20174,7 +20290,7 @@
         <v>30</v>
       </c>
       <c r="D45" t="s">
-        <v>1414</v>
+        <v>1421</v>
       </c>
       <c r="E45" t="s">
         <v>817</v>
@@ -20183,7 +20299,7 @@
         <v>826</v>
       </c>
       <c r="G45" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J45" t="s">
         <v>32</v>
@@ -20198,16 +20314,16 @@
         <v>25</v>
       </c>
       <c r="N45" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O45" t="s">
-        <v>1415</v>
+        <v>1422</v>
       </c>
       <c r="P45" t="s">
-        <v>1416</v>
+        <v>1423</v>
       </c>
       <c r="Q45" t="s">
-        <v>1417</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
@@ -20227,10 +20343,10 @@
         <v>817</v>
       </c>
       <c r="F46" t="s">
-        <v>1271</v>
+        <v>1278</v>
       </c>
       <c r="G46" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J46" t="s">
         <v>32</v>
@@ -20245,16 +20361,16 @@
         <v>25</v>
       </c>
       <c r="N46" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O46" t="s">
-        <v>1418</v>
+        <v>1425</v>
       </c>
       <c r="P46" t="s">
-        <v>1419</v>
+        <v>1426</v>
       </c>
       <c r="Q46" t="s">
-        <v>1420</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
@@ -20268,7 +20384,7 @@
         <v>32</v>
       </c>
       <c r="D47" t="s">
-        <v>1421</v>
+        <v>1428</v>
       </c>
       <c r="E47" t="s">
         <v>817</v>
@@ -20277,7 +20393,7 @@
         <v>826</v>
       </c>
       <c r="G47" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J47" t="s">
         <v>32</v>
@@ -20292,16 +20408,16 @@
         <v>25</v>
       </c>
       <c r="N47" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O47" t="s">
-        <v>1422</v>
+        <v>1429</v>
       </c>
       <c r="P47" t="s">
-        <v>1423</v>
+        <v>1430</v>
       </c>
       <c r="Q47" t="s">
-        <v>1424</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
@@ -20315,16 +20431,16 @@
         <v>45</v>
       </c>
       <c r="D48" t="s">
-        <v>1425</v>
+        <v>1432</v>
       </c>
       <c r="E48" t="s">
         <v>604</v>
       </c>
       <c r="F48" t="s">
-        <v>1426</v>
+        <v>1433</v>
       </c>
       <c r="G48" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J48" t="s">
         <v>32</v>
@@ -20339,16 +20455,16 @@
         <v>38</v>
       </c>
       <c r="N48" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O48" t="s">
-        <v>1427</v>
+        <v>1434</v>
       </c>
       <c r="P48" t="s">
-        <v>1428</v>
+        <v>1435</v>
       </c>
       <c r="Q48" t="s">
-        <v>1429</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
@@ -20362,16 +20478,16 @@
         <v>35</v>
       </c>
       <c r="D49" t="s">
-        <v>1430</v>
+        <v>1437</v>
       </c>
       <c r="E49" t="s">
         <v>604</v>
       </c>
       <c r="F49" t="s">
-        <v>1431</v>
+        <v>1438</v>
       </c>
       <c r="G49" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J49" t="s">
         <v>32</v>
@@ -20386,16 +20502,16 @@
         <v>25</v>
       </c>
       <c r="N49" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O49" t="s">
-        <v>1432</v>
+        <v>1439</v>
       </c>
       <c r="P49" t="s">
-        <v>1433</v>
+        <v>1440</v>
       </c>
       <c r="Q49" t="s">
-        <v>1434</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
@@ -20409,7 +20525,7 @@
         <v>35</v>
       </c>
       <c r="D50" t="s">
-        <v>1435</v>
+        <v>1442</v>
       </c>
       <c r="E50" t="s">
         <v>604</v>
@@ -20418,7 +20534,7 @@
         <v>87</v>
       </c>
       <c r="G50" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J50" t="s">
         <v>32</v>
@@ -20433,16 +20549,16 @@
         <v>25</v>
       </c>
       <c r="N50" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O50" t="s">
-        <v>1436</v>
+        <v>1443</v>
       </c>
       <c r="P50" t="s">
-        <v>1437</v>
+        <v>1444</v>
       </c>
       <c r="Q50" t="s">
-        <v>1438</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
@@ -20456,16 +20572,16 @@
         <v>15</v>
       </c>
       <c r="D51" t="s">
-        <v>1439</v>
+        <v>1446</v>
       </c>
       <c r="E51" t="s">
         <v>604</v>
       </c>
       <c r="F51" t="s">
-        <v>1440</v>
+        <v>1447</v>
       </c>
       <c r="G51" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J51" t="s">
         <v>32</v>
@@ -20480,16 +20596,16 @@
         <v>25</v>
       </c>
       <c r="N51" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O51" t="s">
-        <v>1441</v>
+        <v>1448</v>
       </c>
       <c r="P51" t="s">
-        <v>1442</v>
+        <v>1449</v>
       </c>
       <c r="Q51" t="s">
-        <v>1443</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
@@ -20503,16 +20619,16 @@
         <v>25</v>
       </c>
       <c r="D52" t="s">
-        <v>1444</v>
+        <v>1451</v>
       </c>
       <c r="E52" t="s">
         <v>604</v>
       </c>
       <c r="F52" t="s">
-        <v>1445</v>
+        <v>1452</v>
       </c>
       <c r="G52" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J52" t="s">
         <v>32</v>
@@ -20527,16 +20643,16 @@
         <v>25</v>
       </c>
       <c r="N52" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O52" t="s">
-        <v>1446</v>
+        <v>1453</v>
       </c>
       <c r="P52" t="s">
-        <v>1447</v>
+        <v>1454</v>
       </c>
       <c r="Q52" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
@@ -20550,16 +20666,16 @@
         <v>30</v>
       </c>
       <c r="D53" t="s">
-        <v>1449</v>
+        <v>1456</v>
       </c>
       <c r="E53" t="s">
         <v>604</v>
       </c>
       <c r="F53" t="s">
-        <v>1450</v>
+        <v>1457</v>
       </c>
       <c r="G53" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J53" t="s">
         <v>32</v>
@@ -20574,16 +20690,16 @@
         <v>25</v>
       </c>
       <c r="N53" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O53" t="s">
-        <v>1451</v>
+        <v>1458</v>
       </c>
       <c r="P53" t="s">
-        <v>1452</v>
+        <v>1459</v>
       </c>
       <c r="Q53" t="s">
-        <v>1453</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
@@ -20603,10 +20719,10 @@
         <v>63</v>
       </c>
       <c r="F54" t="s">
-        <v>1410</v>
+        <v>1417</v>
       </c>
       <c r="G54" t="s">
-        <v>1224</v>
+        <v>1231</v>
       </c>
       <c r="J54" t="s">
         <v>32</v>
@@ -20621,16 +20737,16 @@
         <v>25</v>
       </c>
       <c r="N54" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O54" t="s">
-        <v>1454</v>
+        <v>1461</v>
       </c>
       <c r="P54" t="s">
-        <v>1455</v>
+        <v>1462</v>
       </c>
       <c r="Q54" t="s">
-        <v>1456</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
@@ -20650,10 +20766,10 @@
         <v>63</v>
       </c>
       <c r="F55" t="s">
-        <v>1457</v>
+        <v>1464</v>
       </c>
       <c r="G55" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J55" t="s">
         <v>32</v>
@@ -20668,16 +20784,16 @@
         <v>38</v>
       </c>
       <c r="N55" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O55" t="s">
-        <v>1458</v>
+        <v>1465</v>
       </c>
       <c r="P55" t="s">
-        <v>1459</v>
+        <v>1466</v>
       </c>
       <c r="Q55" t="s">
-        <v>1460</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
@@ -20700,7 +20816,7 @@
         <v>883</v>
       </c>
       <c r="G56" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="H56">
         <v>180000</v>
@@ -20721,16 +20837,16 @@
         <v>25</v>
       </c>
       <c r="N56" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O56" t="s">
-        <v>1461</v>
+        <v>1468</v>
       </c>
       <c r="P56" t="s">
-        <v>1462</v>
+        <v>1469</v>
       </c>
       <c r="Q56" t="s">
-        <v>1463</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
@@ -20750,10 +20866,10 @@
         <v>63</v>
       </c>
       <c r="F57" t="s">
-        <v>1464</v>
+        <v>1471</v>
       </c>
       <c r="G57" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="H57">
         <v>180000</v>
@@ -20774,16 +20890,16 @@
         <v>25</v>
       </c>
       <c r="N57" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O57" t="s">
-        <v>1465</v>
+        <v>1472</v>
       </c>
       <c r="P57" t="s">
-        <v>1466</v>
+        <v>1473</v>
       </c>
       <c r="Q57" t="s">
-        <v>1467</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
@@ -20797,16 +20913,16 @@
         <v>20</v>
       </c>
       <c r="D58" t="s">
-        <v>1468</v>
+        <v>1475</v>
       </c>
       <c r="E58" t="s">
         <v>928</v>
       </c>
       <c r="F58" t="s">
-        <v>1469</v>
+        <v>1476</v>
       </c>
       <c r="G58" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J58" t="s">
         <v>32</v>
@@ -20821,16 +20937,16 @@
         <v>25</v>
       </c>
       <c r="N58" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O58" t="s">
-        <v>1470</v>
+        <v>1477</v>
       </c>
       <c r="P58" t="s">
-        <v>1471</v>
+        <v>1478</v>
       </c>
       <c r="Q58" t="s">
-        <v>1472</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
@@ -20844,7 +20960,7 @@
         <v>50</v>
       </c>
       <c r="D59" t="s">
-        <v>1473</v>
+        <v>1480</v>
       </c>
       <c r="E59" t="s">
         <v>928</v>
@@ -20853,7 +20969,7 @@
         <v>20</v>
       </c>
       <c r="G59" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="H59">
         <v>250000</v>
@@ -20874,16 +20990,16 @@
         <v>38</v>
       </c>
       <c r="N59" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O59" t="s">
-        <v>1474</v>
+        <v>1481</v>
       </c>
       <c r="P59" t="s">
-        <v>1475</v>
+        <v>1482</v>
       </c>
       <c r="Q59" t="s">
-        <v>1476</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
@@ -20897,7 +21013,7 @@
         <v>55</v>
       </c>
       <c r="D60" t="s">
-        <v>1477</v>
+        <v>1484</v>
       </c>
       <c r="E60" t="s">
         <v>928</v>
@@ -20906,7 +21022,7 @@
         <v>20</v>
       </c>
       <c r="G60" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="H60">
         <v>200000</v>
@@ -20927,16 +21043,16 @@
         <v>38</v>
       </c>
       <c r="N60" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O60" t="s">
-        <v>1478</v>
+        <v>1485</v>
       </c>
       <c r="P60" t="s">
-        <v>1479</v>
+        <v>1486</v>
       </c>
       <c r="Q60" t="s">
-        <v>1480</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
@@ -20950,7 +21066,7 @@
         <v>52</v>
       </c>
       <c r="D61" t="s">
-        <v>1481</v>
+        <v>1488</v>
       </c>
       <c r="E61" t="s">
         <v>928</v>
@@ -20959,7 +21075,7 @@
         <v>20</v>
       </c>
       <c r="G61" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="H61">
         <v>250000</v>
@@ -20980,16 +21096,16 @@
         <v>38</v>
       </c>
       <c r="N61" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O61" t="s">
-        <v>1482</v>
+        <v>1489</v>
       </c>
       <c r="P61" t="s">
-        <v>1483</v>
+        <v>1490</v>
       </c>
       <c r="Q61" t="s">
-        <v>1484</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
@@ -21003,7 +21119,7 @@
         <v>53</v>
       </c>
       <c r="D62" t="s">
-        <v>1485</v>
+        <v>1492</v>
       </c>
       <c r="E62" t="s">
         <v>928</v>
@@ -21012,7 +21128,7 @@
         <v>20</v>
       </c>
       <c r="G62" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="H62">
         <v>200000</v>
@@ -21033,16 +21149,16 @@
         <v>38</v>
       </c>
       <c r="N62" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O62" t="s">
-        <v>1486</v>
+        <v>1493</v>
       </c>
       <c r="P62" t="s">
-        <v>1487</v>
+        <v>1494</v>
       </c>
       <c r="Q62" t="s">
-        <v>1488</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
@@ -21056,7 +21172,7 @@
         <v>50</v>
       </c>
       <c r="D63" t="s">
-        <v>1489</v>
+        <v>1496</v>
       </c>
       <c r="E63" t="s">
         <v>928</v>
@@ -21065,7 +21181,7 @@
         <v>20</v>
       </c>
       <c r="G63" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="H63">
         <v>200000</v>
@@ -21086,16 +21202,16 @@
         <v>38</v>
       </c>
       <c r="N63" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O63" t="s">
-        <v>1490</v>
+        <v>1497</v>
       </c>
       <c r="P63" t="s">
-        <v>1491</v>
+        <v>1498</v>
       </c>
       <c r="Q63" t="s">
-        <v>1492</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
@@ -21109,7 +21225,7 @@
         <v>55</v>
       </c>
       <c r="D64" t="s">
-        <v>1493</v>
+        <v>1500</v>
       </c>
       <c r="E64" t="s">
         <v>928</v>
@@ -21118,7 +21234,7 @@
         <v>20</v>
       </c>
       <c r="G64" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="H64">
         <v>250000</v>
@@ -21139,16 +21255,16 @@
         <v>38</v>
       </c>
       <c r="N64" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O64" t="s">
-        <v>1494</v>
+        <v>1501</v>
       </c>
       <c r="P64" t="s">
-        <v>1495</v>
+        <v>1502</v>
       </c>
       <c r="Q64" t="s">
-        <v>1496</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
@@ -21162,16 +21278,16 @@
         <v>45</v>
       </c>
       <c r="D65" t="s">
-        <v>1497</v>
+        <v>1504</v>
       </c>
       <c r="E65" t="s">
-        <v>1498</v>
+        <v>1505</v>
       </c>
       <c r="F65" t="s">
-        <v>1499</v>
+        <v>1506</v>
       </c>
       <c r="G65" t="s">
-        <v>1224</v>
+        <v>1231</v>
       </c>
       <c r="H65">
         <v>154000</v>
@@ -21192,16 +21308,16 @@
         <v>25</v>
       </c>
       <c r="N65" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O65" t="s">
-        <v>1500</v>
+        <v>1507</v>
       </c>
       <c r="P65" t="s">
-        <v>1501</v>
+        <v>1508</v>
       </c>
       <c r="Q65" t="s">
-        <v>1502</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
@@ -21224,7 +21340,7 @@
         <v>563</v>
       </c>
       <c r="G66" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="H66">
         <v>180000</v>
@@ -21245,16 +21361,16 @@
         <v>38</v>
       </c>
       <c r="N66" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O66" t="s">
-        <v>1503</v>
+        <v>1510</v>
       </c>
       <c r="P66" t="s">
-        <v>1504</v>
+        <v>1511</v>
       </c>
       <c r="Q66" t="s">
-        <v>1505</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
@@ -21274,10 +21390,10 @@
         <v>63</v>
       </c>
       <c r="F67" t="s">
-        <v>1359</v>
+        <v>1366</v>
       </c>
       <c r="G67" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="H67">
         <v>219100</v>
@@ -21298,16 +21414,16 @@
         <v>25</v>
       </c>
       <c r="N67" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O67" t="s">
-        <v>1506</v>
+        <v>1513</v>
       </c>
       <c r="P67" t="s">
-        <v>1507</v>
+        <v>1514</v>
       </c>
       <c r="Q67" t="s">
-        <v>1508</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
@@ -21321,7 +21437,7 @@
         <v>25</v>
       </c>
       <c r="D68" t="s">
-        <v>1509</v>
+        <v>1516</v>
       </c>
       <c r="E68" t="s">
         <v>63</v>
@@ -21330,7 +21446,7 @@
         <v>1133</v>
       </c>
       <c r="G68" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J68" t="s">
         <v>32</v>
@@ -21345,16 +21461,16 @@
         <v>25</v>
       </c>
       <c r="N68" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O68" t="s">
-        <v>1510</v>
+        <v>1517</v>
       </c>
       <c r="P68" t="s">
-        <v>1511</v>
+        <v>1518</v>
       </c>
       <c r="Q68" t="s">
-        <v>1512</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
@@ -21374,10 +21490,10 @@
         <v>817</v>
       </c>
       <c r="F69" t="s">
-        <v>1301</v>
+        <v>1308</v>
       </c>
       <c r="G69" t="s">
-        <v>1224</v>
+        <v>1231</v>
       </c>
       <c r="J69" t="s">
         <v>32</v>
@@ -21392,16 +21508,16 @@
         <v>25</v>
       </c>
       <c r="N69" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O69" t="s">
-        <v>1513</v>
+        <v>1520</v>
       </c>
       <c r="P69" t="s">
-        <v>1514</v>
+        <v>1521</v>
       </c>
       <c r="Q69" t="s">
-        <v>1515</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
@@ -21415,16 +21531,16 @@
         <v>15</v>
       </c>
       <c r="D70" t="s">
-        <v>1516</v>
+        <v>1523</v>
       </c>
       <c r="E70" t="s">
-        <v>1517</v>
+        <v>1524</v>
       </c>
       <c r="F70" t="s">
         <v>1149</v>
       </c>
       <c r="G70" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J70" t="s">
         <v>32</v>
@@ -21439,16 +21555,16 @@
         <v>25</v>
       </c>
       <c r="N70" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O70" t="s">
-        <v>1518</v>
+        <v>1525</v>
       </c>
       <c r="P70" t="s">
-        <v>1519</v>
+        <v>1526</v>
       </c>
       <c r="Q70" t="s">
-        <v>1520</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
@@ -21462,16 +21578,16 @@
         <v>12</v>
       </c>
       <c r="D71" t="s">
-        <v>1521</v>
+        <v>1528</v>
       </c>
       <c r="E71" t="s">
-        <v>1522</v>
+        <v>1529</v>
       </c>
       <c r="F71" t="s">
-        <v>1523</v>
+        <v>1530</v>
       </c>
       <c r="G71" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J71" t="s">
         <v>32</v>
@@ -21486,16 +21602,16 @@
         <v>25</v>
       </c>
       <c r="N71" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O71" t="s">
-        <v>1524</v>
+        <v>1531</v>
       </c>
       <c r="P71" t="s">
-        <v>1525</v>
+        <v>1532</v>
       </c>
       <c r="Q71" t="s">
-        <v>1526</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
@@ -21509,16 +21625,16 @@
         <v>42</v>
       </c>
       <c r="D72" t="s">
-        <v>1527</v>
+        <v>1534</v>
       </c>
       <c r="E72" t="s">
         <v>63</v>
       </c>
       <c r="F72" t="s">
-        <v>1528</v>
+        <v>1535</v>
       </c>
       <c r="G72" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="H72">
         <v>180000</v>
@@ -21539,16 +21655,16 @@
         <v>38</v>
       </c>
       <c r="N72" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O72" t="s">
-        <v>1529</v>
+        <v>1536</v>
       </c>
       <c r="P72" t="s">
-        <v>1530</v>
+        <v>1537</v>
       </c>
       <c r="Q72" t="s">
-        <v>1531</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
@@ -21562,16 +21678,16 @@
         <v>22</v>
       </c>
       <c r="D73" t="s">
-        <v>1532</v>
+        <v>1539</v>
       </c>
       <c r="E73" t="s">
-        <v>1261</v>
+        <v>1268</v>
       </c>
       <c r="F73" t="s">
-        <v>1533</v>
+        <v>1540</v>
       </c>
       <c r="G73" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="H73">
         <v>200000</v>
@@ -21592,16 +21708,16 @@
         <v>25</v>
       </c>
       <c r="N73" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O73" t="s">
-        <v>1534</v>
+        <v>1541</v>
       </c>
       <c r="P73" t="s">
-        <v>1535</v>
+        <v>1542</v>
       </c>
       <c r="Q73" t="s">
-        <v>1536</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
@@ -21615,16 +21731,16 @@
         <v>28</v>
       </c>
       <c r="D74" t="s">
-        <v>1537</v>
+        <v>1544</v>
       </c>
       <c r="E74" t="s">
-        <v>1538</v>
+        <v>1545</v>
       </c>
       <c r="F74" t="s">
         <v>1133</v>
       </c>
       <c r="G74" t="s">
-        <v>1224</v>
+        <v>1231</v>
       </c>
       <c r="J74" t="s">
         <v>32</v>
@@ -21639,16 +21755,16 @@
         <v>25</v>
       </c>
       <c r="N74" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O74" t="s">
-        <v>1539</v>
+        <v>1546</v>
       </c>
       <c r="P74" t="s">
-        <v>1540</v>
+        <v>1547</v>
       </c>
       <c r="Q74" t="s">
-        <v>1541</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
@@ -21662,16 +21778,16 @@
         <v>5</v>
       </c>
       <c r="D75" t="s">
-        <v>1542</v>
+        <v>1549</v>
       </c>
       <c r="E75" t="s">
-        <v>1543</v>
+        <v>1550</v>
       </c>
       <c r="F75" t="s">
-        <v>1544</v>
+        <v>1551</v>
       </c>
       <c r="G75" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J75" t="s">
         <v>32</v>
@@ -21686,16 +21802,16 @@
         <v>25</v>
       </c>
       <c r="N75" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O75" t="s">
-        <v>1545</v>
+        <v>1552</v>
       </c>
       <c r="P75" t="s">
-        <v>1546</v>
+        <v>1553</v>
       </c>
       <c r="Q75" t="s">
-        <v>1547</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
@@ -21715,10 +21831,10 @@
         <v>63</v>
       </c>
       <c r="F76" t="s">
-        <v>1548</v>
+        <v>1555</v>
       </c>
       <c r="G76" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J76" t="s">
         <v>32</v>
@@ -21733,16 +21849,16 @@
         <v>38</v>
       </c>
       <c r="N76" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O76" t="s">
-        <v>1549</v>
+        <v>1556</v>
       </c>
       <c r="P76" t="s">
-        <v>1550</v>
+        <v>1557</v>
       </c>
       <c r="Q76" t="s">
-        <v>1551</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
@@ -21756,16 +21872,16 @@
         <v>35</v>
       </c>
       <c r="D77" t="s">
-        <v>1552</v>
+        <v>1559</v>
       </c>
       <c r="E77" t="s">
-        <v>1553</v>
+        <v>1560</v>
       </c>
       <c r="F77" t="s">
         <v>1200</v>
       </c>
       <c r="G77" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J77" t="s">
         <v>32</v>
@@ -21780,16 +21896,16 @@
         <v>25</v>
       </c>
       <c r="N77" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O77" t="s">
-        <v>1554</v>
+        <v>1561</v>
       </c>
       <c r="P77" t="s">
-        <v>1555</v>
+        <v>1562</v>
       </c>
       <c r="Q77" t="s">
-        <v>1556</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
@@ -21803,16 +21919,16 @@
         <v>55</v>
       </c>
       <c r="D78" t="s">
-        <v>1557</v>
+        <v>1564</v>
       </c>
       <c r="E78" t="s">
         <v>63</v>
       </c>
       <c r="F78" t="s">
-        <v>1359</v>
+        <v>1366</v>
       </c>
       <c r="G78" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="H78">
         <v>219100</v>
@@ -21827,22 +21943,22 @@
         <v>65</v>
       </c>
       <c r="L78" t="s">
-        <v>1558</v>
+        <v>1565</v>
       </c>
       <c r="M78" t="s">
         <v>38</v>
       </c>
       <c r="N78" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O78" t="s">
-        <v>1559</v>
+        <v>1566</v>
       </c>
       <c r="P78" t="s">
-        <v>1560</v>
+        <v>1567</v>
       </c>
       <c r="Q78" t="s">
-        <v>1561</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
@@ -21856,16 +21972,16 @@
         <v>50</v>
       </c>
       <c r="D79" t="s">
-        <v>1562</v>
+        <v>1569</v>
       </c>
       <c r="E79" t="s">
-        <v>1261</v>
+        <v>1268</v>
       </c>
       <c r="F79" t="s">
         <v>20</v>
       </c>
       <c r="G79" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="H79">
         <v>200000</v>
@@ -21880,22 +21996,22 @@
         <v>65</v>
       </c>
       <c r="L79" t="s">
-        <v>1558</v>
+        <v>1565</v>
       </c>
       <c r="M79" t="s">
         <v>38</v>
       </c>
       <c r="N79" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O79" t="s">
-        <v>1563</v>
+        <v>1570</v>
       </c>
       <c r="P79" t="s">
-        <v>1564</v>
+        <v>1571</v>
       </c>
       <c r="Q79" t="s">
-        <v>1565</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
@@ -21909,16 +22025,16 @@
         <v>12</v>
       </c>
       <c r="D80" t="s">
-        <v>1566</v>
+        <v>1573</v>
       </c>
       <c r="E80" t="s">
-        <v>1567</v>
+        <v>1574</v>
       </c>
       <c r="F80" t="s">
         <v>1133</v>
       </c>
       <c r="G80" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J80" t="s">
         <v>32</v>
@@ -21927,22 +22043,22 @@
         <v>99</v>
       </c>
       <c r="L80" t="s">
-        <v>1558</v>
+        <v>1565</v>
       </c>
       <c r="M80" t="s">
         <v>25</v>
       </c>
       <c r="N80" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O80" t="s">
-        <v>1568</v>
+        <v>1575</v>
       </c>
       <c r="P80" t="s">
-        <v>1569</v>
+        <v>1576</v>
       </c>
       <c r="Q80" t="s">
-        <v>1570</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
@@ -21956,16 +22072,16 @@
         <v>12</v>
       </c>
       <c r="D81" t="s">
-        <v>1571</v>
+        <v>1578</v>
       </c>
       <c r="E81" t="s">
-        <v>1567</v>
+        <v>1574</v>
       </c>
       <c r="F81" t="s">
         <v>1133</v>
       </c>
       <c r="G81" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J81" t="s">
         <v>32</v>
@@ -21974,22 +22090,22 @@
         <v>99</v>
       </c>
       <c r="L81" t="s">
-        <v>1558</v>
+        <v>1565</v>
       </c>
       <c r="M81" t="s">
         <v>25</v>
       </c>
       <c r="N81" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O81" t="s">
-        <v>1572</v>
+        <v>1579</v>
       </c>
       <c r="P81" t="s">
-        <v>1573</v>
+        <v>1580</v>
       </c>
       <c r="Q81" t="s">
-        <v>1574</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
@@ -22003,16 +22119,16 @@
         <v>3</v>
       </c>
       <c r="D82" t="s">
-        <v>1575</v>
+        <v>1582</v>
       </c>
       <c r="E82" t="s">
-        <v>1567</v>
+        <v>1574</v>
       </c>
       <c r="F82" t="s">
         <v>1133</v>
       </c>
       <c r="G82" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J82" t="s">
         <v>32</v>
@@ -22021,22 +22137,22 @@
         <v>99</v>
       </c>
       <c r="L82" t="s">
-        <v>1558</v>
+        <v>1565</v>
       </c>
       <c r="M82" t="s">
         <v>25</v>
       </c>
       <c r="N82" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O82" t="s">
-        <v>1576</v>
+        <v>1583</v>
       </c>
       <c r="P82" t="s">
-        <v>1577</v>
+        <v>1584</v>
       </c>
       <c r="Q82" t="s">
-        <v>1578</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
@@ -22050,16 +22166,16 @@
         <v>25</v>
       </c>
       <c r="D83" t="s">
-        <v>1579</v>
+        <v>1586</v>
       </c>
       <c r="E83" t="s">
-        <v>1580</v>
+        <v>1587</v>
       </c>
       <c r="F83" t="s">
-        <v>1581</v>
+        <v>1588</v>
       </c>
       <c r="G83" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J83" t="s">
         <v>32</v>
@@ -22068,22 +22184,22 @@
         <v>99</v>
       </c>
       <c r="L83" t="s">
-        <v>1558</v>
+        <v>1565</v>
       </c>
       <c r="M83" t="s">
         <v>25</v>
       </c>
       <c r="N83" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O83" t="s">
-        <v>1582</v>
+        <v>1589</v>
       </c>
       <c r="P83" t="s">
-        <v>1583</v>
+        <v>1590</v>
       </c>
       <c r="Q83" t="s">
-        <v>1584</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
@@ -22097,16 +22213,16 @@
         <v>62</v>
       </c>
       <c r="D84" t="s">
-        <v>1585</v>
+        <v>1592</v>
       </c>
       <c r="E84" t="s">
-        <v>1586</v>
+        <v>1593</v>
       </c>
       <c r="F84" t="s">
-        <v>1587</v>
+        <v>1594</v>
       </c>
       <c r="G84" t="s">
-        <v>1224</v>
+        <v>1231</v>
       </c>
       <c r="J84" t="s">
         <v>32</v>
@@ -22115,22 +22231,22 @@
         <v>99</v>
       </c>
       <c r="L84" t="s">
-        <v>1558</v>
+        <v>1565</v>
       </c>
       <c r="M84" t="s">
         <v>25</v>
       </c>
       <c r="N84" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O84" t="s">
-        <v>1588</v>
+        <v>1595</v>
       </c>
       <c r="P84" t="s">
-        <v>1589</v>
+        <v>1596</v>
       </c>
       <c r="Q84" t="s">
-        <v>1590</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
@@ -22144,16 +22260,16 @@
         <v>68</v>
       </c>
       <c r="D85" t="s">
-        <v>1591</v>
+        <v>1598</v>
       </c>
       <c r="E85" t="s">
-        <v>1586</v>
+        <v>1593</v>
       </c>
       <c r="F85" t="s">
-        <v>1587</v>
+        <v>1594</v>
       </c>
       <c r="G85" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J85" t="s">
         <v>32</v>
@@ -22162,22 +22278,22 @@
         <v>99</v>
       </c>
       <c r="L85" t="s">
-        <v>1558</v>
+        <v>1565</v>
       </c>
       <c r="M85" t="s">
         <v>25</v>
       </c>
       <c r="N85" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O85" t="s">
-        <v>1592</v>
+        <v>1599</v>
       </c>
       <c r="P85" t="s">
-        <v>1593</v>
+        <v>1600</v>
       </c>
       <c r="Q85" t="s">
-        <v>1594</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
@@ -22197,10 +22313,10 @@
         <v>63</v>
       </c>
       <c r="F86" t="s">
-        <v>1595</v>
+        <v>1602</v>
       </c>
       <c r="G86" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="H86">
         <v>180000</v>
@@ -22221,16 +22337,16 @@
         <v>38</v>
       </c>
       <c r="N86" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O86" t="s">
-        <v>1596</v>
+        <v>1603</v>
       </c>
       <c r="P86" t="s">
-        <v>1597</v>
+        <v>1604</v>
       </c>
       <c r="Q86" t="s">
-        <v>1598</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
@@ -22250,10 +22366,10 @@
         <v>63</v>
       </c>
       <c r="F87" t="s">
-        <v>1599</v>
+        <v>1606</v>
       </c>
       <c r="G87" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="H87">
         <v>180000</v>
@@ -22274,16 +22390,16 @@
         <v>38</v>
       </c>
       <c r="N87" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O87" t="s">
-        <v>1600</v>
+        <v>1607</v>
       </c>
       <c r="P87" t="s">
-        <v>1601</v>
+        <v>1608</v>
       </c>
       <c r="Q87" t="s">
-        <v>1602</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
@@ -22297,16 +22413,16 @@
         <v>35</v>
       </c>
       <c r="D88" t="s">
-        <v>1603</v>
+        <v>1610</v>
       </c>
       <c r="E88" t="s">
         <v>63</v>
       </c>
       <c r="F88" t="s">
-        <v>1604</v>
+        <v>1611</v>
       </c>
       <c r="G88" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="H88">
         <v>219100</v>
@@ -22327,16 +22443,16 @@
         <v>38</v>
       </c>
       <c r="N88" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O88" t="s">
-        <v>1605</v>
+        <v>1612</v>
       </c>
       <c r="P88" t="s">
-        <v>1606</v>
+        <v>1613</v>
       </c>
       <c r="Q88" t="s">
-        <v>1607</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
@@ -22350,16 +22466,16 @@
         <v>25</v>
       </c>
       <c r="D89" t="s">
-        <v>1608</v>
+        <v>1615</v>
       </c>
       <c r="E89" t="s">
         <v>604</v>
       </c>
       <c r="F89" t="s">
-        <v>1426</v>
+        <v>1433</v>
       </c>
       <c r="G89" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J89" t="s">
         <v>32</v>
@@ -22374,16 +22490,16 @@
         <v>25</v>
       </c>
       <c r="N89" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O89" t="s">
-        <v>1609</v>
+        <v>1616</v>
       </c>
       <c r="P89" t="s">
-        <v>1610</v>
+        <v>1617</v>
       </c>
       <c r="Q89" t="s">
-        <v>1611</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
@@ -22397,16 +22513,16 @@
         <v>35</v>
       </c>
       <c r="D90" t="s">
-        <v>1612</v>
+        <v>1619</v>
       </c>
       <c r="E90" t="s">
-        <v>1613</v>
+        <v>1620</v>
       </c>
       <c r="F90" t="s">
-        <v>1301</v>
+        <v>1308</v>
       </c>
       <c r="G90" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J90" t="s">
         <v>32</v>
@@ -22421,16 +22537,16 @@
         <v>25</v>
       </c>
       <c r="N90" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O90" t="s">
-        <v>1614</v>
+        <v>1621</v>
       </c>
       <c r="P90" t="s">
-        <v>1615</v>
+        <v>1622</v>
       </c>
       <c r="Q90" t="s">
-        <v>1616</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
@@ -22453,7 +22569,7 @@
         <v>1200</v>
       </c>
       <c r="G91" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="H91">
         <v>200000</v>
@@ -22474,16 +22590,16 @@
         <v>25</v>
       </c>
       <c r="N91" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O91" t="s">
-        <v>1617</v>
+        <v>1624</v>
       </c>
       <c r="P91" t="s">
-        <v>1618</v>
+        <v>1625</v>
       </c>
       <c r="Q91" t="s">
-        <v>1619</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
@@ -22497,7 +22613,7 @@
         <v>38</v>
       </c>
       <c r="D92" t="s">
-        <v>1620</v>
+        <v>1627</v>
       </c>
       <c r="E92" t="s">
         <v>1199</v>
@@ -22506,7 +22622,7 @@
         <v>1200</v>
       </c>
       <c r="G92" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="H92">
         <v>200000</v>
@@ -22527,16 +22643,16 @@
         <v>25</v>
       </c>
       <c r="N92" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O92" t="s">
-        <v>1621</v>
+        <v>1628</v>
       </c>
       <c r="P92" t="s">
-        <v>1622</v>
+        <v>1629</v>
       </c>
       <c r="Q92" t="s">
-        <v>1623</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
@@ -22550,16 +22666,16 @@
         <v>40</v>
       </c>
       <c r="D93" t="s">
-        <v>1404</v>
+        <v>1411</v>
       </c>
       <c r="E93" t="s">
-        <v>1261</v>
+        <v>1268</v>
       </c>
       <c r="F93" t="s">
         <v>832</v>
       </c>
       <c r="G93" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="H93">
         <v>184200</v>
@@ -22580,16 +22696,16 @@
         <v>25</v>
       </c>
       <c r="N93" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O93" t="s">
-        <v>1624</v>
+        <v>1631</v>
       </c>
       <c r="P93" t="s">
-        <v>1625</v>
+        <v>1632</v>
       </c>
       <c r="Q93" t="s">
-        <v>1626</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
@@ -22603,16 +22719,16 @@
         <v>20</v>
       </c>
       <c r="D94" t="s">
-        <v>1627</v>
+        <v>1634</v>
       </c>
       <c r="E94" t="s">
-        <v>1628</v>
+        <v>1635</v>
       </c>
       <c r="F94" t="s">
-        <v>1629</v>
+        <v>1636</v>
       </c>
       <c r="G94" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J94" t="s">
         <v>32</v>
@@ -22627,16 +22743,16 @@
         <v>25</v>
       </c>
       <c r="N94" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O94" t="s">
-        <v>1630</v>
+        <v>1637</v>
       </c>
       <c r="P94" t="s">
-        <v>1631</v>
+        <v>1638</v>
       </c>
       <c r="Q94" t="s">
-        <v>1632</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
@@ -22650,16 +22766,16 @@
         <v>35</v>
       </c>
       <c r="D95" t="s">
-        <v>1633</v>
+        <v>1640</v>
       </c>
       <c r="E95" t="s">
-        <v>1634</v>
+        <v>1641</v>
       </c>
       <c r="F95" t="s">
-        <v>1635</v>
+        <v>1642</v>
       </c>
       <c r="G95" t="s">
-        <v>1224</v>
+        <v>1231</v>
       </c>
       <c r="H95">
         <v>230000</v>
@@ -22680,16 +22796,16 @@
         <v>25</v>
       </c>
       <c r="N95" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O95" t="s">
-        <v>1636</v>
+        <v>1643</v>
       </c>
       <c r="P95" t="s">
-        <v>1637</v>
+        <v>1644</v>
       </c>
       <c r="Q95" t="s">
-        <v>1638</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
@@ -22709,10 +22825,10 @@
         <v>63</v>
       </c>
       <c r="F96" t="s">
-        <v>1639</v>
+        <v>1646</v>
       </c>
       <c r="G96" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="H96">
         <v>219100</v>
@@ -22733,16 +22849,16 @@
         <v>75</v>
       </c>
       <c r="N96" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O96" t="s">
-        <v>1640</v>
+        <v>1647</v>
       </c>
       <c r="P96" t="s">
-        <v>1641</v>
+        <v>1648</v>
       </c>
       <c r="Q96" t="s">
-        <v>1642</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
@@ -22756,16 +22872,16 @@
         <v>25</v>
       </c>
       <c r="D97" t="s">
-        <v>1643</v>
+        <v>1650</v>
       </c>
       <c r="E97" t="s">
-        <v>1553</v>
+        <v>1560</v>
       </c>
       <c r="F97" t="s">
         <v>1200</v>
       </c>
       <c r="G97" t="s">
-        <v>1224</v>
+        <v>1231</v>
       </c>
       <c r="J97" t="s">
         <v>32</v>
@@ -22780,16 +22896,16 @@
         <v>25</v>
       </c>
       <c r="N97" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O97" t="s">
-        <v>1644</v>
+        <v>1651</v>
       </c>
       <c r="P97" t="s">
-        <v>1645</v>
+        <v>1652</v>
       </c>
       <c r="Q97" t="s">
-        <v>1646</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
@@ -22803,16 +22919,16 @@
         <v>22</v>
       </c>
       <c r="D98" t="s">
-        <v>1647</v>
+        <v>1654</v>
       </c>
       <c r="E98" t="s">
-        <v>1648</v>
+        <v>1655</v>
       </c>
       <c r="F98" t="s">
-        <v>1649</v>
+        <v>1656</v>
       </c>
       <c r="G98" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J98" t="s">
         <v>32</v>
@@ -22827,16 +22943,16 @@
         <v>25</v>
       </c>
       <c r="N98" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O98" t="s">
-        <v>1650</v>
+        <v>1657</v>
       </c>
       <c r="P98" t="s">
-        <v>1651</v>
+        <v>1658</v>
       </c>
       <c r="Q98" t="s">
-        <v>1652</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.25">
@@ -22850,16 +22966,16 @@
         <v>3</v>
       </c>
       <c r="D99" t="s">
-        <v>1653</v>
+        <v>1660</v>
       </c>
       <c r="E99" t="s">
-        <v>1654</v>
+        <v>1661</v>
       </c>
       <c r="F99" t="s">
-        <v>1649</v>
+        <v>1656</v>
       </c>
       <c r="G99" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J99" t="s">
         <v>32</v>
@@ -22874,16 +22990,16 @@
         <v>25</v>
       </c>
       <c r="N99" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O99" t="s">
-        <v>1655</v>
+        <v>1662</v>
       </c>
       <c r="P99" t="s">
-        <v>1656</v>
+        <v>1663</v>
       </c>
       <c r="Q99" t="s">
-        <v>1657</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.25">
@@ -22897,16 +23013,16 @@
         <v>28</v>
       </c>
       <c r="D100" t="s">
-        <v>1658</v>
+        <v>1665</v>
       </c>
       <c r="E100" t="s">
-        <v>1659</v>
+        <v>1666</v>
       </c>
       <c r="F100" t="s">
         <v>1133</v>
       </c>
       <c r="G100" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J100" t="s">
         <v>32</v>
@@ -22921,16 +23037,16 @@
         <v>25</v>
       </c>
       <c r="N100" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O100" t="s">
-        <v>1660</v>
+        <v>1667</v>
       </c>
       <c r="P100" t="s">
-        <v>1661</v>
+        <v>1668</v>
       </c>
       <c r="Q100" t="s">
-        <v>1662</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.25">
@@ -22944,16 +23060,16 @@
         <v>45</v>
       </c>
       <c r="D101" t="s">
-        <v>1663</v>
+        <v>1670</v>
       </c>
       <c r="E101" t="s">
-        <v>1664</v>
+        <v>1671</v>
       </c>
       <c r="F101" t="s">
-        <v>1301</v>
+        <v>1308</v>
       </c>
       <c r="G101" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J101" t="s">
         <v>32</v>
@@ -22968,16 +23084,16 @@
         <v>38</v>
       </c>
       <c r="N101" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O101" t="s">
-        <v>1665</v>
+        <v>1672</v>
       </c>
       <c r="P101" t="s">
-        <v>1666</v>
+        <v>1673</v>
       </c>
       <c r="Q101" t="s">
-        <v>1667</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.25">
@@ -22991,16 +23107,16 @@
         <v>50</v>
       </c>
       <c r="D102" t="s">
-        <v>1668</v>
+        <v>1675</v>
       </c>
       <c r="E102" t="s">
-        <v>1669</v>
+        <v>1676</v>
       </c>
       <c r="F102" t="s">
-        <v>1333</v>
+        <v>1340</v>
       </c>
       <c r="G102" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J102" t="s">
         <v>32</v>
@@ -23015,16 +23131,16 @@
         <v>38</v>
       </c>
       <c r="N102" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O102" t="s">
-        <v>1670</v>
+        <v>1677</v>
       </c>
       <c r="P102" t="s">
-        <v>1671</v>
+        <v>1678</v>
       </c>
       <c r="Q102" t="s">
-        <v>1672</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.25">
@@ -23038,16 +23154,16 @@
         <v>48</v>
       </c>
       <c r="D103" t="s">
-        <v>1673</v>
+        <v>1680</v>
       </c>
       <c r="E103" t="s">
-        <v>1498</v>
+        <v>1505</v>
       </c>
       <c r="F103" t="s">
-        <v>1674</v>
+        <v>1681</v>
       </c>
       <c r="G103" t="s">
-        <v>1224</v>
+        <v>1231</v>
       </c>
       <c r="H103">
         <v>154000</v>
@@ -23068,16 +23184,16 @@
         <v>38</v>
       </c>
       <c r="N103" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O103" t="s">
-        <v>1675</v>
+        <v>1682</v>
       </c>
       <c r="P103" t="s">
-        <v>1676</v>
+        <v>1683</v>
       </c>
       <c r="Q103" t="s">
-        <v>1677</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.25">
@@ -23091,16 +23207,16 @@
         <v>25</v>
       </c>
       <c r="D104" t="s">
-        <v>1678</v>
+        <v>1685</v>
       </c>
       <c r="E104" t="s">
-        <v>1322</v>
+        <v>1329</v>
       </c>
       <c r="F104" t="s">
         <v>1200</v>
       </c>
       <c r="G104" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J104" t="s">
         <v>32</v>
@@ -23115,16 +23231,16 @@
         <v>25</v>
       </c>
       <c r="N104" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O104" t="s">
-        <v>1679</v>
+        <v>1686</v>
       </c>
       <c r="P104" t="s">
-        <v>1680</v>
+        <v>1687</v>
       </c>
       <c r="Q104" t="s">
-        <v>1681</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.25">
@@ -23138,16 +23254,16 @@
         <v>32</v>
       </c>
       <c r="D105" t="s">
-        <v>1579</v>
+        <v>1586</v>
       </c>
       <c r="E105" t="s">
-        <v>1322</v>
+        <v>1329</v>
       </c>
       <c r="F105" t="s">
         <v>1200</v>
       </c>
       <c r="G105" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J105" t="s">
         <v>32</v>
@@ -23162,16 +23278,16 @@
         <v>25</v>
       </c>
       <c r="N105" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O105" t="s">
-        <v>1682</v>
+        <v>1689</v>
       </c>
       <c r="P105" t="s">
-        <v>1683</v>
+        <v>1690</v>
       </c>
       <c r="Q105" t="s">
-        <v>1684</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.25">
@@ -23185,16 +23301,16 @@
         <v>22</v>
       </c>
       <c r="D106" t="s">
-        <v>1685</v>
+        <v>1692</v>
       </c>
       <c r="E106" t="s">
-        <v>1669</v>
+        <v>1676</v>
       </c>
       <c r="F106" t="s">
-        <v>1649</v>
+        <v>1656</v>
       </c>
       <c r="G106" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J106" t="s">
         <v>32</v>
@@ -23209,16 +23325,16 @@
         <v>25</v>
       </c>
       <c r="N106" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O106" t="s">
-        <v>1686</v>
+        <v>1693</v>
       </c>
       <c r="P106" t="s">
-        <v>1687</v>
+        <v>1694</v>
       </c>
       <c r="Q106" t="s">
-        <v>1688</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.25">
@@ -23232,16 +23348,16 @@
         <v>55</v>
       </c>
       <c r="D107" t="s">
-        <v>1668</v>
+        <v>1675</v>
       </c>
       <c r="E107" t="s">
-        <v>1669</v>
+        <v>1676</v>
       </c>
       <c r="F107" t="s">
-        <v>1689</v>
+        <v>1696</v>
       </c>
       <c r="G107" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J107" t="s">
         <v>32</v>
@@ -23256,16 +23372,16 @@
         <v>25</v>
       </c>
       <c r="N107" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O107" t="s">
-        <v>1690</v>
+        <v>1697</v>
       </c>
       <c r="P107" t="s">
-        <v>1691</v>
+        <v>1698</v>
       </c>
       <c r="Q107" t="s">
-        <v>1692</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.25">
@@ -23279,16 +23395,16 @@
         <v>25</v>
       </c>
       <c r="D108" t="s">
-        <v>1693</v>
+        <v>1700</v>
       </c>
       <c r="E108" t="s">
-        <v>1669</v>
+        <v>1676</v>
       </c>
       <c r="F108" t="s">
-        <v>1689</v>
+        <v>1696</v>
       </c>
       <c r="G108" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J108" t="s">
         <v>32</v>
@@ -23303,16 +23419,16 @@
         <v>25</v>
       </c>
       <c r="N108" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O108" t="s">
-        <v>1694</v>
+        <v>1701</v>
       </c>
       <c r="P108" t="s">
-        <v>1695</v>
+        <v>1702</v>
       </c>
       <c r="Q108" t="s">
-        <v>1696</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.25">
@@ -23326,7 +23442,7 @@
         <v>33</v>
       </c>
       <c r="D109" t="s">
-        <v>1697</v>
+        <v>1704</v>
       </c>
       <c r="E109" t="s">
         <v>63</v>
@@ -23335,7 +23451,7 @@
         <v>1133</v>
       </c>
       <c r="G109" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J109" t="s">
         <v>32</v>
@@ -23350,16 +23466,16 @@
         <v>25</v>
       </c>
       <c r="N109" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O109" t="s">
-        <v>1698</v>
+        <v>1705</v>
       </c>
       <c r="P109" t="s">
-        <v>1699</v>
+        <v>1706</v>
       </c>
       <c r="Q109" t="s">
-        <v>1700</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.25">
@@ -23373,16 +23489,16 @@
         <v>38</v>
       </c>
       <c r="D110" t="s">
-        <v>1701</v>
+        <v>1708</v>
       </c>
       <c r="E110" t="s">
-        <v>1702</v>
+        <v>1709</v>
       </c>
       <c r="F110" t="s">
-        <v>1431</v>
+        <v>1438</v>
       </c>
       <c r="G110" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="H110">
         <v>220000</v>
@@ -23403,16 +23519,16 @@
         <v>25</v>
       </c>
       <c r="N110" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O110" t="s">
-        <v>1703</v>
+        <v>1710</v>
       </c>
       <c r="P110" t="s">
-        <v>1704</v>
+        <v>1711</v>
       </c>
       <c r="Q110" t="s">
-        <v>1705</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.25">
@@ -23426,16 +23542,16 @@
         <v>62</v>
       </c>
       <c r="D111" t="s">
-        <v>1706</v>
+        <v>1713</v>
       </c>
       <c r="E111" t="s">
-        <v>1261</v>
+        <v>1268</v>
       </c>
       <c r="F111" t="s">
         <v>20</v>
       </c>
       <c r="G111" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="H111">
         <v>200000</v>
@@ -23456,16 +23572,16 @@
         <v>38</v>
       </c>
       <c r="N111" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O111" t="s">
-        <v>1707</v>
+        <v>1714</v>
       </c>
       <c r="P111" t="s">
-        <v>1708</v>
+        <v>1715</v>
       </c>
       <c r="Q111" t="s">
-        <v>1709</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.25">
@@ -23479,16 +23595,16 @@
         <v>30</v>
       </c>
       <c r="D112" t="s">
-        <v>1693</v>
+        <v>1700</v>
       </c>
       <c r="E112" t="s">
-        <v>1669</v>
+        <v>1676</v>
       </c>
       <c r="F112" t="s">
-        <v>1649</v>
+        <v>1656</v>
       </c>
       <c r="G112" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J112" t="s">
         <v>32</v>
@@ -23503,16 +23619,16 @@
         <v>25</v>
       </c>
       <c r="N112" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O112" t="s">
-        <v>1710</v>
+        <v>1717</v>
       </c>
       <c r="P112" t="s">
-        <v>1711</v>
+        <v>1718</v>
       </c>
       <c r="Q112" t="s">
-        <v>1712</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.25">
@@ -23526,16 +23642,16 @@
         <v>58</v>
       </c>
       <c r="D113" t="s">
-        <v>1668</v>
+        <v>1675</v>
       </c>
       <c r="E113" t="s">
-        <v>1669</v>
+        <v>1676</v>
       </c>
       <c r="F113" t="s">
-        <v>1333</v>
+        <v>1340</v>
       </c>
       <c r="G113" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J113" t="s">
         <v>32</v>
@@ -23550,16 +23666,16 @@
         <v>25</v>
       </c>
       <c r="N113" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O113" t="s">
-        <v>1713</v>
+        <v>1720</v>
       </c>
       <c r="P113" t="s">
-        <v>1714</v>
+        <v>1721</v>
       </c>
       <c r="Q113" t="s">
-        <v>1715</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.25">
@@ -23573,7 +23689,7 @@
         <v>55</v>
       </c>
       <c r="D114" t="s">
-        <v>1716</v>
+        <v>1723</v>
       </c>
       <c r="E114" t="s">
         <v>63</v>
@@ -23582,7 +23698,7 @@
         <v>20</v>
       </c>
       <c r="G114" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="H114">
         <v>217800</v>
@@ -23603,16 +23719,16 @@
         <v>38</v>
       </c>
       <c r="N114" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O114" t="s">
-        <v>1717</v>
+        <v>1724</v>
       </c>
       <c r="P114" t="s">
-        <v>1718</v>
+        <v>1725</v>
       </c>
       <c r="Q114" t="s">
-        <v>1719</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.25">
@@ -23626,16 +23742,16 @@
         <v>45</v>
       </c>
       <c r="D115" t="s">
-        <v>1720</v>
+        <v>1727</v>
       </c>
       <c r="E115" t="s">
         <v>63</v>
       </c>
       <c r="F115" t="s">
-        <v>1721</v>
+        <v>1728</v>
       </c>
       <c r="G115" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="H115">
         <v>219100</v>
@@ -23656,16 +23772,16 @@
         <v>38</v>
       </c>
       <c r="N115" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O115" t="s">
-        <v>1722</v>
+        <v>1729</v>
       </c>
       <c r="P115" t="s">
-        <v>1723</v>
+        <v>1730</v>
       </c>
       <c r="Q115" t="s">
-        <v>1724</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.25">
@@ -23685,10 +23801,10 @@
         <v>817</v>
       </c>
       <c r="F116" t="s">
-        <v>1725</v>
+        <v>1732</v>
       </c>
       <c r="G116" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J116" t="s">
         <v>32</v>
@@ -23703,16 +23819,16 @@
         <v>25</v>
       </c>
       <c r="N116" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O116" t="s">
-        <v>1726</v>
+        <v>1733</v>
       </c>
       <c r="P116" t="s">
-        <v>1727</v>
+        <v>1734</v>
       </c>
       <c r="Q116" t="s">
-        <v>1728</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.25">
@@ -23726,16 +23842,16 @@
         <v>35</v>
       </c>
       <c r="D117" t="s">
-        <v>1729</v>
+        <v>1736</v>
       </c>
       <c r="E117" t="s">
         <v>63</v>
       </c>
       <c r="F117" t="s">
-        <v>1730</v>
+        <v>1737</v>
       </c>
       <c r="G117" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J117" t="s">
         <v>32</v>
@@ -23750,16 +23866,16 @@
         <v>25</v>
       </c>
       <c r="N117" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O117" t="s">
-        <v>1731</v>
+        <v>1738</v>
       </c>
       <c r="P117" t="s">
-        <v>1732</v>
+        <v>1739</v>
       </c>
       <c r="Q117" t="s">
-        <v>1733</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.25">
@@ -23773,7 +23889,7 @@
         <v>38</v>
       </c>
       <c r="D118" t="s">
-        <v>1734</v>
+        <v>1741</v>
       </c>
       <c r="E118" t="s">
         <v>63</v>
@@ -23782,7 +23898,7 @@
         <v>20</v>
       </c>
       <c r="G118" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="H118">
         <v>219100</v>
@@ -23803,16 +23919,16 @@
         <v>25</v>
       </c>
       <c r="N118" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O118" t="s">
-        <v>1735</v>
+        <v>1742</v>
       </c>
       <c r="P118" t="s">
-        <v>1736</v>
+        <v>1743</v>
       </c>
       <c r="Q118" t="s">
-        <v>1737</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.25">
@@ -23826,16 +23942,16 @@
         <v>22</v>
       </c>
       <c r="D119" t="s">
-        <v>1738</v>
+        <v>1745</v>
       </c>
       <c r="E119" t="s">
-        <v>1739</v>
+        <v>1746</v>
       </c>
       <c r="F119" t="s">
-        <v>1740</v>
+        <v>1747</v>
       </c>
       <c r="G119" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J119" t="s">
         <v>32</v>
@@ -23850,16 +23966,16 @@
         <v>25</v>
       </c>
       <c r="N119" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O119" t="s">
-        <v>1741</v>
+        <v>1748</v>
       </c>
       <c r="P119" t="s">
-        <v>1742</v>
+        <v>1749</v>
       </c>
       <c r="Q119" t="s">
-        <v>1743</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.25">
@@ -23873,16 +23989,16 @@
         <v>35</v>
       </c>
       <c r="D120" t="s">
-        <v>1744</v>
+        <v>1751</v>
       </c>
       <c r="E120" t="s">
-        <v>1745</v>
+        <v>1752</v>
       </c>
       <c r="F120" t="s">
-        <v>1746</v>
+        <v>1753</v>
       </c>
       <c r="G120" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="J120" t="s">
         <v>32</v>
@@ -23897,16 +24013,16 @@
         <v>25</v>
       </c>
       <c r="N120" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O120" t="s">
-        <v>1747</v>
+        <v>1754</v>
       </c>
       <c r="P120" t="s">
-        <v>1748</v>
+        <v>1755</v>
       </c>
       <c r="Q120" t="s">
-        <v>1749</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.25">
@@ -23920,7 +24036,7 @@
         <v>55</v>
       </c>
       <c r="D121" t="s">
-        <v>1750</v>
+        <v>1757</v>
       </c>
       <c r="E121" t="s">
         <v>1199</v>
@@ -23929,7 +24045,7 @@
         <v>1200</v>
       </c>
       <c r="G121" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="H121">
         <v>200000</v>
@@ -23950,16 +24066,257 @@
         <v>38</v>
       </c>
       <c r="N121" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="O121" t="s">
-        <v>1751</v>
+        <v>1758</v>
       </c>
       <c r="P121" t="s">
-        <v>1752</v>
+        <v>1759</v>
       </c>
       <c r="Q121" t="s">
-        <v>1753</v>
+        <v>1760</v>
+      </c>
+    </row>
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>17</v>
+      </c>
+      <c r="B122">
+        <v>50</v>
+      </c>
+      <c r="C122">
+        <v>52</v>
+      </c>
+      <c r="D122" t="s">
+        <v>69</v>
+      </c>
+      <c r="E122" t="s">
+        <v>63</v>
+      </c>
+      <c r="F122" t="s">
+        <v>1761</v>
+      </c>
+      <c r="G122" t="s">
+        <v>1217</v>
+      </c>
+      <c r="H122">
+        <v>180000</v>
+      </c>
+      <c r="I122">
+        <v>180000</v>
+      </c>
+      <c r="J122" t="s">
+        <v>22</v>
+      </c>
+      <c r="K122" t="s">
+        <v>65</v>
+      </c>
+      <c r="L122" t="s">
+        <v>1212</v>
+      </c>
+      <c r="M122" t="s">
+        <v>38</v>
+      </c>
+      <c r="N122" t="s">
+        <v>1218</v>
+      </c>
+      <c r="O122" t="s">
+        <v>1762</v>
+      </c>
+      <c r="P122" t="s">
+        <v>1763</v>
+      </c>
+      <c r="Q122" t="s">
+        <v>1764</v>
+      </c>
+    </row>
+    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>17</v>
+      </c>
+      <c r="B123">
+        <v>30</v>
+      </c>
+      <c r="C123">
+        <v>38</v>
+      </c>
+      <c r="D123" t="s">
+        <v>217</v>
+      </c>
+      <c r="E123" t="s">
+        <v>817</v>
+      </c>
+      <c r="F123" t="s">
+        <v>1308</v>
+      </c>
+      <c r="G123" t="s">
+        <v>1231</v>
+      </c>
+      <c r="J123" t="s">
+        <v>32</v>
+      </c>
+      <c r="K123" t="s">
+        <v>65</v>
+      </c>
+      <c r="L123" t="s">
+        <v>1212</v>
+      </c>
+      <c r="M123" t="s">
+        <v>25</v>
+      </c>
+      <c r="N123" t="s">
+        <v>1218</v>
+      </c>
+      <c r="O123" t="s">
+        <v>1765</v>
+      </c>
+      <c r="P123" t="s">
+        <v>1766</v>
+      </c>
+      <c r="Q123" t="s">
+        <v>1767</v>
+      </c>
+    </row>
+    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>17</v>
+      </c>
+      <c r="B124">
+        <v>35</v>
+      </c>
+      <c r="C124">
+        <v>40</v>
+      </c>
+      <c r="D124" t="s">
+        <v>217</v>
+      </c>
+      <c r="E124" t="s">
+        <v>817</v>
+      </c>
+      <c r="F124" t="s">
+        <v>1200</v>
+      </c>
+      <c r="G124" t="s">
+        <v>1217</v>
+      </c>
+      <c r="J124" t="s">
+        <v>32</v>
+      </c>
+      <c r="K124" t="s">
+        <v>99</v>
+      </c>
+      <c r="L124" t="s">
+        <v>1212</v>
+      </c>
+      <c r="M124" t="s">
+        <v>25</v>
+      </c>
+      <c r="N124" t="s">
+        <v>1218</v>
+      </c>
+      <c r="O124" t="s">
+        <v>1768</v>
+      </c>
+      <c r="P124" t="s">
+        <v>1769</v>
+      </c>
+      <c r="Q124" t="s">
+        <v>1770</v>
+      </c>
+    </row>
+    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>17</v>
+      </c>
+      <c r="B125">
+        <v>40</v>
+      </c>
+      <c r="C125">
+        <v>44</v>
+      </c>
+      <c r="D125" t="s">
+        <v>276</v>
+      </c>
+      <c r="E125" t="s">
+        <v>817</v>
+      </c>
+      <c r="F125" t="s">
+        <v>1200</v>
+      </c>
+      <c r="G125" t="s">
+        <v>1217</v>
+      </c>
+      <c r="J125" t="s">
+        <v>32</v>
+      </c>
+      <c r="K125" t="s">
+        <v>99</v>
+      </c>
+      <c r="L125" t="s">
+        <v>1212</v>
+      </c>
+      <c r="M125" t="s">
+        <v>38</v>
+      </c>
+      <c r="N125" t="s">
+        <v>1218</v>
+      </c>
+      <c r="O125" t="s">
+        <v>1771</v>
+      </c>
+      <c r="P125" t="s">
+        <v>1772</v>
+      </c>
+      <c r="Q125" t="s">
+        <v>1773</v>
+      </c>
+    </row>
+    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>17</v>
+      </c>
+      <c r="B126">
+        <v>25</v>
+      </c>
+      <c r="C126">
+        <v>32</v>
+      </c>
+      <c r="D126" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E126" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F126" t="s">
+        <v>1142</v>
+      </c>
+      <c r="G126" t="s">
+        <v>1231</v>
+      </c>
+      <c r="J126" t="s">
+        <v>32</v>
+      </c>
+      <c r="K126" t="s">
+        <v>99</v>
+      </c>
+      <c r="L126" t="s">
+        <v>1212</v>
+      </c>
+      <c r="M126" t="s">
+        <v>25</v>
+      </c>
+      <c r="N126" t="s">
+        <v>1218</v>
+      </c>
+      <c r="O126" t="s">
+        <v>1774</v>
+      </c>
+      <c r="P126" t="s">
+        <v>1775</v>
+      </c>
+      <c r="Q126" t="s">
+        <v>1776</v>
       </c>
     </row>
   </sheetData>

--- a/hunt/board.xlsx
+++ b/hunt/board.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4831" uniqueCount="1772">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4948" uniqueCount="1813">
   <si>
     <t>Column</t>
   </si>
@@ -3584,6 +3584,66 @@
     <t>https://www.arbeitnow.co.uk/jobs/companies/purestorage/remote-cloud-native-senior-architect-portworx-206761</t>
   </si>
   <si>
+    <t>Education Cloud Architect</t>
+  </si>
+  <si>
+    <t>Salesforce</t>
+  </si>
+  <si>
+    <t>2026-09-05T14:24:34.571Z</t>
+  </si>
+  <si>
+    <t>Remote US role with confirmed band ($173K–$232K) that reaches the candidate's $180K floor at midpoint | Architect-level customer-facing advisory scope, matching the trusted-advisor engagement model the candidate practices today | Salesforce benefits and brand strength for enterprise architecture career growth</t>
+  </si>
+  <si>
+    <t>Explicitly asks for real-world Salesforce platform experience (Education Cloud, Agentforce) — candidate's depth is Azure/GitHub, not the Salesforce ecosystem | Categorized under 'Sales' job family, likely pre-sales solutioning rather than DevOps/cloud platform architecture | No credit given for Azure DevOps, GHAS, or IaC skills that form the core of the candidate's resume</t>
+  </si>
+  <si>
+    <t>https://himalayas.app/companies/salesforce/jobs/education-cloud-architect</t>
+  </si>
+  <si>
+    <t>Staff Software Engineer - Platform Engineering</t>
+  </si>
+  <si>
+    <t>Cohere Health</t>
+  </si>
+  <si>
+    <t>Core scope is CI/CD improvement, deployment/release strategy, and developer experience — direct overlap with the candidate's Azure DevOps/GitHub pipeline architecture work | Healthcare (prior-auth) domain aligns with the candidate's HIPAA/compliance-driven architecture background | Confirmed $185K–$210K remote band clears the $180K floor</t>
+  </si>
+  <si>
+    <t>Staff Software Engineer framing implies hands-on coding and platform build ownership, less of the advisory/architect scope the candidate targets | Likely AWS/Kubernetes-centric platform stack; candidate's depth is Azure-first with Terraform as the transferable bridge | Observability/SRE incident-response ownership is a lighter area on the candidate's resume</t>
+  </si>
+  <si>
+    <t>https://himalayas.app/companies/cohere-health/jobs/staff-software-engineer-platform-engineering</t>
+  </si>
+  <si>
+    <t>Principal DevOps Engineer</t>
+  </si>
+  <si>
+    <t>NBCUniversal</t>
+  </si>
+  <si>
+    <t>Principal DevOps Engineer title matches the candidate's stated target titles and principal-level scope ambition | Confirmed $180K–$230K remote US band starts exactly at the salary floor | Large enterprise media environment suits the candidate's enterprise CI/CD, governance, and platform advisory experience</t>
+  </si>
+  <si>
+    <t>Media/streaming stacks at NBCU are typically AWS-heavy; Azure-primary depth may need to be reframed | Principal IC bar likely expects deep production SRE/Kubernetes and coding rigor beyond the candidate's advisory-weighted resume | AZ-400 still in progress; no AWS certifications to offset stack mismatch</t>
+  </si>
+  <si>
+    <t>https://jobicy.com/jobs/148200-principal-devops-engineer-2</t>
+  </si>
+  <si>
+    <t>(Senior) SAP ABAP Developer / Architect – Data Management &amp; ILM (m/w/d)</t>
+  </si>
+  <si>
+    <t>Remote arrangement and architect-level solution design responsibilities | Compliance/data-retention theme loosely touches the candidate's regulatory architecture exposure</t>
+  </si>
+  <si>
+    <t>Requires SAP ABAP development and SAP ILM expertise the candidate has zero background in | German-language posting for a Germany-based role, outside the candidate's stated US market scope | No Azure, CI/CD, or GitHub content in the role at all</t>
+  </si>
+  <si>
+    <t>https://www.arbeitnow.com/jobs/companies/natuvion-gmbh/remote-senior-sap-abap-developer-architect-data-management-ilm-berlin-78818</t>
+  </si>
+  <si>
     <t>Arizona; California; Utah</t>
   </si>
   <si>
@@ -5328,6 +5388,69 @@
   </si>
   <si>
     <t>https://www.arbeitnow.co.uk/jobs/companies/octopus-energy-group/senior-data-platform-engineer-london-gb-220448</t>
+  </si>
+  <si>
+    <t>Senior Cloud Engineer</t>
+  </si>
+  <si>
+    <t>Sharkninjaoperatingllc</t>
+  </si>
+  <si>
+    <t>Battersea Power Station</t>
+  </si>
+  <si>
+    <t>Senior Cloud Engineer scope is genuinely adjacent to the candidate's cloud platform and automation skill set | SharkNinja is an established global product company with a stated benefits package</t>
+  </si>
+  <si>
+    <t>Located at Battersea Power Station, London — outside the candidate's US market scope and requires international relocation/work authorization | No salary posted and UK bands for this role rarely approach a $180K equivalent | Posting gives no signal on Azure vs AWS, so stack alignment is unverified</t>
+  </si>
+  <si>
+    <t>https://www.arbeitnow.co.uk/jobs/companies/sharkninjaoperatingllc/senior-cloud-engineer-battersea-power-station-98014</t>
+  </si>
+  <si>
+    <t>Software Architect</t>
+  </si>
+  <si>
+    <t>nice</t>
+  </si>
+  <si>
+    <t>AI-native platform rebuild with AI tooling in the delivery pipeline overlaps with the candidate's GitHub Copilot / Agentic DevOps experience | Architect-level scope with influence over delivery transformation matches the target seniority</t>
+  </si>
+  <si>
+    <t>Reads as a hands-on software/product architecture role (digital evidence platform), not cloud infrastructure or DevOps advisory | Location field is blank with hybrid designation — likely UK/Israel based on NICE's structure, unverified against US scope | No salary posted and no stated Azure/DevOps toolchain requirements to anchor the candidate's strengths</t>
+  </si>
+  <si>
+    <t>https://www.arbeitnow.co.uk/jobs/companies/nice/software-architect-377105</t>
+  </si>
+  <si>
+    <t>Senior Software Architect</t>
+  </si>
+  <si>
+    <t>Same AI-led delivery transformation mandate touches the candidate's Copilot/agentic DevOps enablement work | Senior/Lead architect scope is consistent with the candidate's principal-level targeting</t>
+  </si>
+  <si>
+    <t>Duplicate of the other NICE Lead Software Architect posting — application effort would be redundant | Software/product architecture focus rather than cloud platform, governance, or CI/CD architecture | Blank location plus hybrid requirement and no posted compensation</t>
+  </si>
+  <si>
+    <t>https://www.arbeitnow.co.uk/jobs/companies/nice/senior-software-architect-356646</t>
+  </si>
+  <si>
+    <t>Central architecture function defining technical guidelines and software toolchains — governance framing is conceptually similar to the candidate's Azure Policy/CAF work | Well-funded defence tech company with meaningful engineering scope</t>
+  </si>
+  <si>
+    <t>Systems engineering for unmanned aerial platforms requires hardware/MBSE requirements expertise the candidate does not have | Munich-based onsite role, outside the candidate's US market scope and likely requiring EU work authorization | Defence sector will typically require NATO/EU clearance eligibility the candidate does not hold</t>
+  </si>
+  <si>
+    <t>https://www.arbeitnow.com/jobs/companies/stark/systems-architect-all-genders-munich-325920</t>
+  </si>
+  <si>
+    <t>Architect-titled role at a fast-scaling defence technology company</t>
+  </si>
+  <si>
+    <t>Requires battery pack design, thermal/cycle-life engineering, and firmware collaboration — entirely outside the candidate's cloud/DevOps skill set | Munich onsite hardware role, incompatible with the candidate's US remote-first target | No cloud, CI/CD, or governance content whatsoever</t>
+  </si>
+  <si>
+    <t>https://www.arbeitnow.com/jobs/companies/stark/battery-system-engineer-architect-all-genders-munich-272216</t>
   </si>
 </sst>
 </file>
@@ -5708,7 +5831,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q240"/>
+  <dimension ref="A1:Q244"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -17731,6 +17854,212 @@
         <v>1189</v>
       </c>
     </row>
+    <row r="241" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>17</v>
+      </c>
+      <c r="B241">
+        <v>40</v>
+      </c>
+      <c r="C241">
+        <v>35</v>
+      </c>
+      <c r="D241" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E241" t="s">
+        <v>1191</v>
+      </c>
+      <c r="F241" t="s">
+        <v>20</v>
+      </c>
+      <c r="G241" t="s">
+        <v>21</v>
+      </c>
+      <c r="H241">
+        <v>173460</v>
+      </c>
+      <c r="I241">
+        <v>231980</v>
+      </c>
+      <c r="J241" t="s">
+        <v>22</v>
+      </c>
+      <c r="K241" t="s">
+        <v>23</v>
+      </c>
+      <c r="L241" t="s">
+        <v>1192</v>
+      </c>
+      <c r="M241" t="s">
+        <v>25</v>
+      </c>
+      <c r="N241" t="s">
+        <v>26</v>
+      </c>
+      <c r="O241" t="s">
+        <v>1193</v>
+      </c>
+      <c r="P241" t="s">
+        <v>1194</v>
+      </c>
+      <c r="Q241" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="242" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>17</v>
+      </c>
+      <c r="B242">
+        <v>72</v>
+      </c>
+      <c r="C242">
+        <v>68</v>
+      </c>
+      <c r="D242" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E242" t="s">
+        <v>1197</v>
+      </c>
+      <c r="F242" t="s">
+        <v>20</v>
+      </c>
+      <c r="G242" t="s">
+        <v>21</v>
+      </c>
+      <c r="H242">
+        <v>185000</v>
+      </c>
+      <c r="I242">
+        <v>210000</v>
+      </c>
+      <c r="J242" t="s">
+        <v>22</v>
+      </c>
+      <c r="K242" t="s">
+        <v>23</v>
+      </c>
+      <c r="L242" t="s">
+        <v>1192</v>
+      </c>
+      <c r="M242" t="s">
+        <v>32</v>
+      </c>
+      <c r="N242" t="s">
+        <v>26</v>
+      </c>
+      <c r="O242" t="s">
+        <v>1198</v>
+      </c>
+      <c r="P242" t="s">
+        <v>1199</v>
+      </c>
+      <c r="Q242" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="243" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>17</v>
+      </c>
+      <c r="B243">
+        <v>80</v>
+      </c>
+      <c r="C243">
+        <v>74</v>
+      </c>
+      <c r="D243" t="s">
+        <v>1201</v>
+      </c>
+      <c r="E243" t="s">
+        <v>1202</v>
+      </c>
+      <c r="F243" t="s">
+        <v>566</v>
+      </c>
+      <c r="G243" t="s">
+        <v>21</v>
+      </c>
+      <c r="H243">
+        <v>180000</v>
+      </c>
+      <c r="I243">
+        <v>230000</v>
+      </c>
+      <c r="J243" t="s">
+        <v>22</v>
+      </c>
+      <c r="K243" t="s">
+        <v>560</v>
+      </c>
+      <c r="L243" t="s">
+        <v>1192</v>
+      </c>
+      <c r="M243" t="s">
+        <v>32</v>
+      </c>
+      <c r="N243" t="s">
+        <v>26</v>
+      </c>
+      <c r="O243" t="s">
+        <v>1203</v>
+      </c>
+      <c r="P243" t="s">
+        <v>1204</v>
+      </c>
+      <c r="Q243" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="244" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>17</v>
+      </c>
+      <c r="B244">
+        <v>10</v>
+      </c>
+      <c r="C244">
+        <v>8</v>
+      </c>
+      <c r="D244" t="s">
+        <v>1206</v>
+      </c>
+      <c r="E244" t="s">
+        <v>68</v>
+      </c>
+      <c r="F244" t="s">
+        <v>69</v>
+      </c>
+      <c r="G244" t="s">
+        <v>21</v>
+      </c>
+      <c r="J244" t="s">
+        <v>38</v>
+      </c>
+      <c r="K244" t="s">
+        <v>70</v>
+      </c>
+      <c r="L244" t="s">
+        <v>1192</v>
+      </c>
+      <c r="M244" t="s">
+        <v>25</v>
+      </c>
+      <c r="N244" t="s">
+        <v>26</v>
+      </c>
+      <c r="O244" t="s">
+        <v>1207</v>
+      </c>
+      <c r="P244" t="s">
+        <v>1208</v>
+      </c>
+      <c r="Q244" t="s">
+        <v>1209</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:Q1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17740,7 +18069,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q131"/>
+  <dimension ref="A1:Q136"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -17827,10 +18156,10 @@
         <v>480</v>
       </c>
       <c r="F2" t="s">
-        <v>1190</v>
+        <v>1210</v>
       </c>
       <c r="G2" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="H2">
         <v>180000</v>
@@ -17851,16 +18180,16 @@
         <v>44</v>
       </c>
       <c r="N2" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O2" t="s">
-        <v>1193</v>
+        <v>1213</v>
       </c>
       <c r="P2" t="s">
-        <v>1194</v>
+        <v>1214</v>
       </c>
       <c r="Q2" t="s">
-        <v>1195</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -17874,7 +18203,7 @@
         <v>52</v>
       </c>
       <c r="D3" t="s">
-        <v>1196</v>
+        <v>1216</v>
       </c>
       <c r="E3" t="s">
         <v>480</v>
@@ -17883,7 +18212,7 @@
         <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>1197</v>
+        <v>1217</v>
       </c>
       <c r="H3">
         <v>180000</v>
@@ -17904,16 +18233,16 @@
         <v>44</v>
       </c>
       <c r="N3" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O3" t="s">
-        <v>1198</v>
+        <v>1218</v>
       </c>
       <c r="P3" t="s">
-        <v>1199</v>
+        <v>1219</v>
       </c>
       <c r="Q3" t="s">
-        <v>1200</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
@@ -17927,7 +18256,7 @@
         <v>55</v>
       </c>
       <c r="D4" t="s">
-        <v>1201</v>
+        <v>1221</v>
       </c>
       <c r="E4" t="s">
         <v>480</v>
@@ -17936,7 +18265,7 @@
         <v>20</v>
       </c>
       <c r="G4" t="s">
-        <v>1197</v>
+        <v>1217</v>
       </c>
       <c r="H4">
         <v>180000</v>
@@ -17957,16 +18286,16 @@
         <v>44</v>
       </c>
       <c r="N4" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O4" t="s">
-        <v>1202</v>
+        <v>1222</v>
       </c>
       <c r="P4" t="s">
-        <v>1203</v>
+        <v>1223</v>
       </c>
       <c r="Q4" t="s">
-        <v>1204</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -17980,16 +18309,16 @@
         <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>1205</v>
+        <v>1225</v>
       </c>
       <c r="E5" t="s">
         <v>480</v>
       </c>
       <c r="F5" t="s">
-        <v>1206</v>
+        <v>1226</v>
       </c>
       <c r="G5" t="s">
-        <v>1197</v>
+        <v>1217</v>
       </c>
       <c r="H5">
         <v>219100</v>
@@ -18010,16 +18339,16 @@
         <v>44</v>
       </c>
       <c r="N5" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O5" t="s">
-        <v>1207</v>
+        <v>1227</v>
       </c>
       <c r="P5" t="s">
-        <v>1208</v>
+        <v>1228</v>
       </c>
       <c r="Q5" t="s">
-        <v>1209</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -18033,16 +18362,16 @@
         <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>1210</v>
+        <v>1230</v>
       </c>
       <c r="E6" t="s">
         <v>480</v>
       </c>
       <c r="F6" t="s">
+        <v>1231</v>
+      </c>
+      <c r="G6" t="s">
         <v>1211</v>
-      </c>
-      <c r="G6" t="s">
-        <v>1191</v>
       </c>
       <c r="H6">
         <v>180000</v>
@@ -18063,16 +18392,16 @@
         <v>44</v>
       </c>
       <c r="N6" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O6" t="s">
-        <v>1212</v>
+        <v>1232</v>
       </c>
       <c r="P6" t="s">
-        <v>1213</v>
+        <v>1233</v>
       </c>
       <c r="Q6" t="s">
-        <v>1214</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -18086,7 +18415,7 @@
         <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>1215</v>
+        <v>1235</v>
       </c>
       <c r="E7" t="s">
         <v>480</v>
@@ -18095,7 +18424,7 @@
         <v>20</v>
       </c>
       <c r="G7" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="H7">
         <v>219100</v>
@@ -18116,16 +18445,16 @@
         <v>25</v>
       </c>
       <c r="N7" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O7" t="s">
-        <v>1216</v>
+        <v>1236</v>
       </c>
       <c r="P7" t="s">
-        <v>1217</v>
+        <v>1237</v>
       </c>
       <c r="Q7" t="s">
-        <v>1218</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -18139,7 +18468,7 @@
         <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>1219</v>
+        <v>1239</v>
       </c>
       <c r="E8" t="s">
         <v>480</v>
@@ -18148,7 +18477,7 @@
         <v>20</v>
       </c>
       <c r="G8" t="s">
-        <v>1197</v>
+        <v>1217</v>
       </c>
       <c r="H8">
         <v>219100</v>
@@ -18169,16 +18498,16 @@
         <v>44</v>
       </c>
       <c r="N8" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O8" t="s">
-        <v>1220</v>
+        <v>1240</v>
       </c>
       <c r="P8" t="s">
-        <v>1221</v>
+        <v>1241</v>
       </c>
       <c r="Q8" t="s">
-        <v>1222</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -18192,16 +18521,16 @@
         <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>1223</v>
+        <v>1243</v>
       </c>
       <c r="E9" t="s">
         <v>480</v>
       </c>
       <c r="F9" t="s">
-        <v>1224</v>
+        <v>1244</v>
       </c>
       <c r="G9" t="s">
-        <v>1197</v>
+        <v>1217</v>
       </c>
       <c r="J9" t="s">
         <v>38</v>
@@ -18216,16 +18545,16 @@
         <v>25</v>
       </c>
       <c r="N9" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O9" t="s">
-        <v>1225</v>
+        <v>1245</v>
       </c>
       <c r="P9" t="s">
-        <v>1226</v>
+        <v>1246</v>
       </c>
       <c r="Q9" t="s">
-        <v>1227</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -18239,16 +18568,16 @@
         <v>58</v>
       </c>
       <c r="D10" t="s">
-        <v>1228</v>
+        <v>1248</v>
       </c>
       <c r="E10" t="s">
-        <v>1229</v>
+        <v>1249</v>
       </c>
       <c r="F10" t="s">
-        <v>1230</v>
+        <v>1250</v>
       </c>
       <c r="G10" t="s">
-        <v>1197</v>
+        <v>1217</v>
       </c>
       <c r="H10">
         <v>257000</v>
@@ -18269,16 +18598,16 @@
         <v>44</v>
       </c>
       <c r="N10" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O10" t="s">
-        <v>1231</v>
+        <v>1251</v>
       </c>
       <c r="P10" t="s">
-        <v>1232</v>
+        <v>1252</v>
       </c>
       <c r="Q10" t="s">
-        <v>1233</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -18295,13 +18624,13 @@
         <v>208</v>
       </c>
       <c r="E11" t="s">
-        <v>1234</v>
+        <v>1254</v>
       </c>
       <c r="F11" t="s">
-        <v>1235</v>
+        <v>1255</v>
       </c>
       <c r="G11" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="H11">
         <v>200000</v>
@@ -18322,16 +18651,16 @@
         <v>25</v>
       </c>
       <c r="N11" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O11" t="s">
-        <v>1236</v>
+        <v>1256</v>
       </c>
       <c r="P11" t="s">
-        <v>1237</v>
+        <v>1257</v>
       </c>
       <c r="Q11" t="s">
-        <v>1238</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -18345,16 +18674,16 @@
         <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>1239</v>
+        <v>1259</v>
       </c>
       <c r="E12" t="s">
         <v>753</v>
       </c>
       <c r="F12" t="s">
-        <v>1240</v>
+        <v>1260</v>
       </c>
       <c r="G12" t="s">
-        <v>1197</v>
+        <v>1217</v>
       </c>
       <c r="J12" t="s">
         <v>38</v>
@@ -18369,16 +18698,16 @@
         <v>25</v>
       </c>
       <c r="N12" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O12" t="s">
-        <v>1241</v>
+        <v>1261</v>
       </c>
       <c r="P12" t="s">
-        <v>1242</v>
+        <v>1262</v>
       </c>
       <c r="Q12" t="s">
-        <v>1243</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
@@ -18398,10 +18727,10 @@
         <v>753</v>
       </c>
       <c r="F13" t="s">
-        <v>1244</v>
+        <v>1264</v>
       </c>
       <c r="G13" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J13" t="s">
         <v>38</v>
@@ -18416,16 +18745,16 @@
         <v>25</v>
       </c>
       <c r="N13" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O13" t="s">
-        <v>1245</v>
+        <v>1265</v>
       </c>
       <c r="P13" t="s">
-        <v>1246</v>
+        <v>1266</v>
       </c>
       <c r="Q13" t="s">
-        <v>1247</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
@@ -18439,16 +18768,16 @@
         <v>15</v>
       </c>
       <c r="D14" t="s">
-        <v>1248</v>
+        <v>1268</v>
       </c>
       <c r="E14" t="s">
         <v>753</v>
       </c>
       <c r="F14" t="s">
-        <v>1249</v>
+        <v>1269</v>
       </c>
       <c r="G14" t="s">
-        <v>1197</v>
+        <v>1217</v>
       </c>
       <c r="H14">
         <v>500000</v>
@@ -18469,16 +18798,16 @@
         <v>25</v>
       </c>
       <c r="N14" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O14" t="s">
-        <v>1250</v>
+        <v>1270</v>
       </c>
       <c r="P14" t="s">
-        <v>1251</v>
+        <v>1271</v>
       </c>
       <c r="Q14" t="s">
-        <v>1252</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -18492,16 +18821,16 @@
         <v>18</v>
       </c>
       <c r="D15" t="s">
-        <v>1253</v>
+        <v>1273</v>
       </c>
       <c r="E15" t="s">
         <v>537</v>
       </c>
       <c r="F15" t="s">
-        <v>1254</v>
+        <v>1274</v>
       </c>
       <c r="G15" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="H15">
         <v>274456</v>
@@ -18522,16 +18851,16 @@
         <v>25</v>
       </c>
       <c r="N15" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O15" t="s">
-        <v>1255</v>
+        <v>1275</v>
       </c>
       <c r="P15" t="s">
-        <v>1256</v>
+        <v>1276</v>
       </c>
       <c r="Q15" t="s">
-        <v>1257</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
@@ -18545,16 +18874,16 @@
         <v>30</v>
       </c>
       <c r="D16" t="s">
-        <v>1258</v>
+        <v>1278</v>
       </c>
       <c r="E16" t="s">
         <v>537</v>
       </c>
       <c r="F16" t="s">
-        <v>1259</v>
+        <v>1279</v>
       </c>
       <c r="G16" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J16" t="s">
         <v>38</v>
@@ -18569,16 +18898,16 @@
         <v>25</v>
       </c>
       <c r="N16" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O16" t="s">
-        <v>1260</v>
+        <v>1280</v>
       </c>
       <c r="P16" t="s">
-        <v>1261</v>
+        <v>1281</v>
       </c>
       <c r="Q16" t="s">
-        <v>1262</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
@@ -18592,16 +18921,16 @@
         <v>22</v>
       </c>
       <c r="D17" t="s">
-        <v>1263</v>
+        <v>1283</v>
       </c>
       <c r="E17" t="s">
         <v>537</v>
       </c>
       <c r="F17" t="s">
-        <v>1264</v>
+        <v>1284</v>
       </c>
       <c r="G17" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J17" t="s">
         <v>38</v>
@@ -18616,16 +18945,16 @@
         <v>25</v>
       </c>
       <c r="N17" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O17" t="s">
-        <v>1265</v>
+        <v>1285</v>
       </c>
       <c r="P17" t="s">
-        <v>1266</v>
+        <v>1286</v>
       </c>
       <c r="Q17" t="s">
-        <v>1267</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
@@ -18639,16 +18968,16 @@
         <v>48</v>
       </c>
       <c r="D18" t="s">
-        <v>1268</v>
+        <v>1288</v>
       </c>
       <c r="E18" t="s">
         <v>537</v>
       </c>
       <c r="F18" t="s">
-        <v>1269</v>
+        <v>1289</v>
       </c>
       <c r="G18" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J18" t="s">
         <v>38</v>
@@ -18663,16 +18992,16 @@
         <v>44</v>
       </c>
       <c r="N18" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O18" t="s">
-        <v>1270</v>
+        <v>1290</v>
       </c>
       <c r="P18" t="s">
-        <v>1271</v>
+        <v>1291</v>
       </c>
       <c r="Q18" t="s">
-        <v>1272</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -18686,16 +19015,16 @@
         <v>25</v>
       </c>
       <c r="D19" t="s">
-        <v>1273</v>
+        <v>1293</v>
       </c>
       <c r="E19" t="s">
         <v>537</v>
       </c>
       <c r="F19" t="s">
-        <v>1274</v>
+        <v>1294</v>
       </c>
       <c r="G19" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J19" t="s">
         <v>38</v>
@@ -18710,16 +19039,16 @@
         <v>25</v>
       </c>
       <c r="N19" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O19" t="s">
-        <v>1275</v>
+        <v>1295</v>
       </c>
       <c r="P19" t="s">
-        <v>1276</v>
+        <v>1296</v>
       </c>
       <c r="Q19" t="s">
-        <v>1277</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -18733,16 +19062,16 @@
         <v>40</v>
       </c>
       <c r="D20" t="s">
-        <v>1278</v>
+        <v>1298</v>
       </c>
       <c r="E20" t="s">
         <v>537</v>
       </c>
       <c r="F20" t="s">
-        <v>1279</v>
+        <v>1299</v>
       </c>
       <c r="G20" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J20" t="s">
         <v>38</v>
@@ -18757,16 +19086,16 @@
         <v>25</v>
       </c>
       <c r="N20" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O20" t="s">
-        <v>1280</v>
+        <v>1300</v>
       </c>
       <c r="P20" t="s">
-        <v>1281</v>
+        <v>1301</v>
       </c>
       <c r="Q20" t="s">
-        <v>1282</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
@@ -18780,16 +19109,16 @@
         <v>70</v>
       </c>
       <c r="D21" t="s">
-        <v>1283</v>
+        <v>1303</v>
       </c>
       <c r="E21" t="s">
-        <v>1284</v>
+        <v>1304</v>
       </c>
       <c r="F21" t="s">
-        <v>1285</v>
+        <v>1305</v>
       </c>
       <c r="G21" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J21" t="s">
         <v>38</v>
@@ -18804,16 +19133,16 @@
         <v>25</v>
       </c>
       <c r="N21" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O21" t="s">
-        <v>1286</v>
+        <v>1306</v>
       </c>
       <c r="P21" t="s">
-        <v>1287</v>
+        <v>1307</v>
       </c>
       <c r="Q21" t="s">
-        <v>1288</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -18827,16 +19156,16 @@
         <v>58</v>
       </c>
       <c r="D22" t="s">
-        <v>1289</v>
+        <v>1309</v>
       </c>
       <c r="E22" t="s">
-        <v>1290</v>
+        <v>1310</v>
       </c>
       <c r="F22" t="s">
-        <v>1274</v>
+        <v>1294</v>
       </c>
       <c r="G22" t="s">
-        <v>1197</v>
+        <v>1217</v>
       </c>
       <c r="J22" t="s">
         <v>38</v>
@@ -18851,16 +19180,16 @@
         <v>25</v>
       </c>
       <c r="N22" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O22" t="s">
-        <v>1291</v>
+        <v>1311</v>
       </c>
       <c r="P22" t="s">
-        <v>1292</v>
+        <v>1312</v>
       </c>
       <c r="Q22" t="s">
-        <v>1293</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
@@ -18874,16 +19203,16 @@
         <v>32</v>
       </c>
       <c r="D23" t="s">
-        <v>1294</v>
+        <v>1314</v>
       </c>
       <c r="E23" t="s">
-        <v>1295</v>
+        <v>1315</v>
       </c>
       <c r="F23" t="s">
         <v>1137</v>
       </c>
       <c r="G23" t="s">
-        <v>1197</v>
+        <v>1217</v>
       </c>
       <c r="J23" t="s">
         <v>38</v>
@@ -18898,16 +19227,16 @@
         <v>25</v>
       </c>
       <c r="N23" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O23" t="s">
-        <v>1296</v>
+        <v>1316</v>
       </c>
       <c r="P23" t="s">
-        <v>1297</v>
+        <v>1317</v>
       </c>
       <c r="Q23" t="s">
-        <v>1298</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
@@ -18921,16 +19250,16 @@
         <v>4</v>
       </c>
       <c r="D24" t="s">
-        <v>1299</v>
+        <v>1319</v>
       </c>
       <c r="E24" t="s">
-        <v>1300</v>
+        <v>1320</v>
       </c>
       <c r="F24" t="s">
         <v>1086</v>
       </c>
       <c r="G24" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J24" t="s">
         <v>38</v>
@@ -18945,16 +19274,16 @@
         <v>25</v>
       </c>
       <c r="N24" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O24" t="s">
-        <v>1301</v>
+        <v>1321</v>
       </c>
       <c r="P24" t="s">
-        <v>1302</v>
+        <v>1322</v>
       </c>
       <c r="Q24" t="s">
-        <v>1303</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
@@ -18968,16 +19297,16 @@
         <v>25</v>
       </c>
       <c r="D25" t="s">
-        <v>1304</v>
+        <v>1324</v>
       </c>
       <c r="E25" t="s">
-        <v>1305</v>
+        <v>1325</v>
       </c>
       <c r="F25" t="s">
-        <v>1306</v>
+        <v>1326</v>
       </c>
       <c r="G25" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J25" t="s">
         <v>38</v>
@@ -18992,16 +19321,16 @@
         <v>25</v>
       </c>
       <c r="N25" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O25" t="s">
-        <v>1307</v>
+        <v>1327</v>
       </c>
       <c r="P25" t="s">
-        <v>1308</v>
+        <v>1328</v>
       </c>
       <c r="Q25" t="s">
-        <v>1309</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
@@ -19015,16 +19344,16 @@
         <v>30</v>
       </c>
       <c r="D26" t="s">
-        <v>1310</v>
+        <v>1330</v>
       </c>
       <c r="E26" t="s">
-        <v>1311</v>
+        <v>1331</v>
       </c>
       <c r="F26" t="s">
         <v>1079</v>
       </c>
       <c r="G26" t="s">
-        <v>1197</v>
+        <v>1217</v>
       </c>
       <c r="J26" t="s">
         <v>38</v>
@@ -19039,16 +19368,16 @@
         <v>25</v>
       </c>
       <c r="N26" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O26" t="s">
-        <v>1312</v>
+        <v>1332</v>
       </c>
       <c r="P26" t="s">
-        <v>1313</v>
+        <v>1333</v>
       </c>
       <c r="Q26" t="s">
-        <v>1314</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
@@ -19062,16 +19391,16 @@
         <v>52</v>
       </c>
       <c r="D27" t="s">
-        <v>1315</v>
+        <v>1335</v>
       </c>
       <c r="E27" t="s">
         <v>480</v>
       </c>
       <c r="F27" t="s">
-        <v>1316</v>
+        <v>1336</v>
       </c>
       <c r="G27" t="s">
-        <v>1197</v>
+        <v>1217</v>
       </c>
       <c r="H27">
         <v>180000</v>
@@ -19092,16 +19421,16 @@
         <v>44</v>
       </c>
       <c r="N27" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O27" t="s">
-        <v>1317</v>
+        <v>1337</v>
       </c>
       <c r="P27" t="s">
-        <v>1318</v>
+        <v>1338</v>
       </c>
       <c r="Q27" t="s">
-        <v>1319</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
@@ -19115,7 +19444,7 @@
         <v>50</v>
       </c>
       <c r="D28" t="s">
-        <v>1320</v>
+        <v>1340</v>
       </c>
       <c r="E28" t="s">
         <v>480</v>
@@ -19124,7 +19453,7 @@
         <v>20</v>
       </c>
       <c r="G28" t="s">
-        <v>1197</v>
+        <v>1217</v>
       </c>
       <c r="H28">
         <v>180000</v>
@@ -19145,16 +19474,16 @@
         <v>44</v>
       </c>
       <c r="N28" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O28" t="s">
-        <v>1321</v>
+        <v>1341</v>
       </c>
       <c r="P28" t="s">
-        <v>1322</v>
+        <v>1342</v>
       </c>
       <c r="Q28" t="s">
-        <v>1323</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
@@ -19168,7 +19497,7 @@
         <v>46</v>
       </c>
       <c r="D29" t="s">
-        <v>1324</v>
+        <v>1344</v>
       </c>
       <c r="E29" t="s">
         <v>480</v>
@@ -19177,7 +19506,7 @@
         <v>20</v>
       </c>
       <c r="G29" t="s">
-        <v>1197</v>
+        <v>1217</v>
       </c>
       <c r="H29">
         <v>180000</v>
@@ -19198,16 +19527,16 @@
         <v>44</v>
       </c>
       <c r="N29" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O29" t="s">
-        <v>1325</v>
+        <v>1345</v>
       </c>
       <c r="P29" t="s">
-        <v>1326</v>
+        <v>1346</v>
       </c>
       <c r="Q29" t="s">
-        <v>1327</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
@@ -19221,7 +19550,7 @@
         <v>38</v>
       </c>
       <c r="D30" t="s">
-        <v>1328</v>
+        <v>1348</v>
       </c>
       <c r="E30" t="s">
         <v>480</v>
@@ -19230,7 +19559,7 @@
         <v>20</v>
       </c>
       <c r="G30" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="H30">
         <v>217800</v>
@@ -19251,16 +19580,16 @@
         <v>25</v>
       </c>
       <c r="N30" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O30" t="s">
-        <v>1329</v>
+        <v>1349</v>
       </c>
       <c r="P30" t="s">
-        <v>1330</v>
+        <v>1350</v>
       </c>
       <c r="Q30" t="s">
-        <v>1331</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
@@ -19280,10 +19609,10 @@
         <v>480</v>
       </c>
       <c r="F31" t="s">
-        <v>1332</v>
+        <v>1352</v>
       </c>
       <c r="G31" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="H31">
         <v>180000</v>
@@ -19304,16 +19633,16 @@
         <v>44</v>
       </c>
       <c r="N31" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O31" t="s">
-        <v>1333</v>
+        <v>1353</v>
       </c>
       <c r="P31" t="s">
-        <v>1334</v>
+        <v>1354</v>
       </c>
       <c r="Q31" t="s">
-        <v>1335</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
@@ -19327,16 +19656,16 @@
         <v>45</v>
       </c>
       <c r="D32" t="s">
-        <v>1336</v>
+        <v>1356</v>
       </c>
       <c r="E32" t="s">
         <v>480</v>
       </c>
       <c r="F32" t="s">
-        <v>1337</v>
+        <v>1357</v>
       </c>
       <c r="G32" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="H32">
         <v>219100</v>
@@ -19357,16 +19686,16 @@
         <v>44</v>
       </c>
       <c r="N32" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O32" t="s">
-        <v>1338</v>
+        <v>1358</v>
       </c>
       <c r="P32" t="s">
-        <v>1339</v>
+        <v>1359</v>
       </c>
       <c r="Q32" t="s">
-        <v>1340</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
@@ -19380,16 +19709,16 @@
         <v>42</v>
       </c>
       <c r="D33" t="s">
-        <v>1341</v>
+        <v>1361</v>
       </c>
       <c r="E33" t="s">
         <v>480</v>
       </c>
       <c r="F33" t="s">
-        <v>1342</v>
+        <v>1362</v>
       </c>
       <c r="G33" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="H33">
         <v>180000</v>
@@ -19410,16 +19739,16 @@
         <v>44</v>
       </c>
       <c r="N33" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O33" t="s">
-        <v>1343</v>
+        <v>1363</v>
       </c>
       <c r="P33" t="s">
-        <v>1344</v>
+        <v>1364</v>
       </c>
       <c r="Q33" t="s">
-        <v>1345</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
@@ -19433,7 +19762,7 @@
         <v>32</v>
       </c>
       <c r="D34" t="s">
-        <v>1346</v>
+        <v>1366</v>
       </c>
       <c r="E34" t="s">
         <v>480</v>
@@ -19442,7 +19771,7 @@
         <v>20</v>
       </c>
       <c r="G34" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="H34">
         <v>219100</v>
@@ -19463,16 +19792,16 @@
         <v>25</v>
       </c>
       <c r="N34" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O34" t="s">
-        <v>1347</v>
+        <v>1367</v>
       </c>
       <c r="P34" t="s">
-        <v>1348</v>
+        <v>1368</v>
       </c>
       <c r="Q34" t="s">
-        <v>1349</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
@@ -19486,7 +19815,7 @@
         <v>35</v>
       </c>
       <c r="D35" t="s">
-        <v>1350</v>
+        <v>1370</v>
       </c>
       <c r="E35" t="s">
         <v>480</v>
@@ -19495,7 +19824,7 @@
         <v>20</v>
       </c>
       <c r="G35" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="H35">
         <v>219100</v>
@@ -19516,16 +19845,16 @@
         <v>25</v>
       </c>
       <c r="N35" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O35" t="s">
-        <v>1351</v>
+        <v>1371</v>
       </c>
       <c r="P35" t="s">
-        <v>1352</v>
+        <v>1372</v>
       </c>
       <c r="Q35" t="s">
-        <v>1353</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
@@ -19539,16 +19868,16 @@
         <v>40</v>
       </c>
       <c r="D36" t="s">
-        <v>1354</v>
+        <v>1374</v>
       </c>
       <c r="E36" t="s">
         <v>480</v>
       </c>
       <c r="F36" t="s">
-        <v>1355</v>
+        <v>1375</v>
       </c>
       <c r="G36" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="H36">
         <v>219100</v>
@@ -19569,16 +19898,16 @@
         <v>44</v>
       </c>
       <c r="N36" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O36" t="s">
-        <v>1356</v>
+        <v>1376</v>
       </c>
       <c r="P36" t="s">
-        <v>1357</v>
+        <v>1377</v>
       </c>
       <c r="Q36" t="s">
-        <v>1358</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
@@ -19592,7 +19921,7 @@
         <v>38</v>
       </c>
       <c r="D37" t="s">
-        <v>1359</v>
+        <v>1379</v>
       </c>
       <c r="E37" t="s">
         <v>480</v>
@@ -19601,7 +19930,7 @@
         <v>496</v>
       </c>
       <c r="G37" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="H37">
         <v>219100</v>
@@ -19622,16 +19951,16 @@
         <v>25</v>
       </c>
       <c r="N37" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O37" t="s">
-        <v>1360</v>
+        <v>1380</v>
       </c>
       <c r="P37" t="s">
-        <v>1361</v>
+        <v>1381</v>
       </c>
       <c r="Q37" t="s">
-        <v>1362</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
@@ -19645,7 +19974,7 @@
         <v>40</v>
       </c>
       <c r="D38" t="s">
-        <v>1363</v>
+        <v>1383</v>
       </c>
       <c r="E38" t="s">
         <v>480</v>
@@ -19654,7 +19983,7 @@
         <v>20</v>
       </c>
       <c r="G38" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="H38">
         <v>219100</v>
@@ -19675,16 +20004,16 @@
         <v>44</v>
       </c>
       <c r="N38" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O38" t="s">
-        <v>1364</v>
+        <v>1384</v>
       </c>
       <c r="P38" t="s">
-        <v>1365</v>
+        <v>1385</v>
       </c>
       <c r="Q38" t="s">
-        <v>1366</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
@@ -19698,16 +20027,16 @@
         <v>33</v>
       </c>
       <c r="D39" t="s">
-        <v>1367</v>
+        <v>1387</v>
       </c>
       <c r="E39" t="s">
         <v>480</v>
       </c>
       <c r="F39" t="s">
-        <v>1368</v>
+        <v>1388</v>
       </c>
       <c r="G39" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="H39">
         <v>219100</v>
@@ -19728,16 +20057,16 @@
         <v>25</v>
       </c>
       <c r="N39" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O39" t="s">
-        <v>1369</v>
+        <v>1389</v>
       </c>
       <c r="P39" t="s">
-        <v>1370</v>
+        <v>1390</v>
       </c>
       <c r="Q39" t="s">
-        <v>1371</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
@@ -19751,16 +20080,16 @@
         <v>48</v>
       </c>
       <c r="D40" t="s">
-        <v>1372</v>
+        <v>1392</v>
       </c>
       <c r="E40" t="s">
-        <v>1229</v>
+        <v>1249</v>
       </c>
       <c r="F40" t="s">
-        <v>1373</v>
+        <v>1393</v>
       </c>
       <c r="G40" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J40" t="s">
         <v>38</v>
@@ -19775,16 +20104,16 @@
         <v>44</v>
       </c>
       <c r="N40" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O40" t="s">
-        <v>1374</v>
+        <v>1394</v>
       </c>
       <c r="P40" t="s">
-        <v>1375</v>
+        <v>1395</v>
       </c>
       <c r="Q40" t="s">
-        <v>1376</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
@@ -19798,16 +20127,16 @@
         <v>40</v>
       </c>
       <c r="D41" t="s">
-        <v>1377</v>
+        <v>1397</v>
       </c>
       <c r="E41" t="s">
-        <v>1234</v>
+        <v>1254</v>
       </c>
       <c r="F41" t="s">
-        <v>1378</v>
+        <v>1398</v>
       </c>
       <c r="G41" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="H41">
         <v>184200</v>
@@ -19828,16 +20157,16 @@
         <v>44</v>
       </c>
       <c r="N41" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O41" t="s">
-        <v>1379</v>
+        <v>1399</v>
       </c>
       <c r="P41" t="s">
-        <v>1380</v>
+        <v>1400</v>
       </c>
       <c r="Q41" t="s">
-        <v>1381</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
@@ -19851,16 +20180,16 @@
         <v>30</v>
       </c>
       <c r="D42" t="s">
-        <v>1382</v>
+        <v>1402</v>
       </c>
       <c r="E42" t="s">
-        <v>1234</v>
+        <v>1254</v>
       </c>
       <c r="F42" t="s">
-        <v>1383</v>
+        <v>1403</v>
       </c>
       <c r="G42" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="H42">
         <v>200000</v>
@@ -19881,16 +20210,16 @@
         <v>25</v>
       </c>
       <c r="N42" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O42" t="s">
-        <v>1384</v>
+        <v>1404</v>
       </c>
       <c r="P42" t="s">
-        <v>1385</v>
+        <v>1405</v>
       </c>
       <c r="Q42" t="s">
-        <v>1386</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
@@ -19904,7 +20233,7 @@
         <v>30</v>
       </c>
       <c r="D43" t="s">
-        <v>1387</v>
+        <v>1407</v>
       </c>
       <c r="E43" t="s">
         <v>753</v>
@@ -19913,7 +20242,7 @@
         <v>762</v>
       </c>
       <c r="G43" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J43" t="s">
         <v>38</v>
@@ -19928,16 +20257,16 @@
         <v>25</v>
       </c>
       <c r="N43" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O43" t="s">
-        <v>1388</v>
+        <v>1408</v>
       </c>
       <c r="P43" t="s">
-        <v>1389</v>
+        <v>1409</v>
       </c>
       <c r="Q43" t="s">
-        <v>1390</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
@@ -19957,10 +20286,10 @@
         <v>753</v>
       </c>
       <c r="F44" t="s">
-        <v>1244</v>
+        <v>1264</v>
       </c>
       <c r="G44" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J44" t="s">
         <v>38</v>
@@ -19975,16 +20304,16 @@
         <v>25</v>
       </c>
       <c r="N44" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O44" t="s">
-        <v>1391</v>
+        <v>1411</v>
       </c>
       <c r="P44" t="s">
-        <v>1392</v>
+        <v>1412</v>
       </c>
       <c r="Q44" t="s">
-        <v>1393</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
@@ -19998,7 +20327,7 @@
         <v>32</v>
       </c>
       <c r="D45" t="s">
-        <v>1394</v>
+        <v>1414</v>
       </c>
       <c r="E45" t="s">
         <v>753</v>
@@ -20007,7 +20336,7 @@
         <v>762</v>
       </c>
       <c r="G45" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J45" t="s">
         <v>38</v>
@@ -20022,16 +20351,16 @@
         <v>25</v>
       </c>
       <c r="N45" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O45" t="s">
-        <v>1395</v>
+        <v>1415</v>
       </c>
       <c r="P45" t="s">
-        <v>1396</v>
+        <v>1416</v>
       </c>
       <c r="Q45" t="s">
-        <v>1397</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
@@ -20045,16 +20374,16 @@
         <v>45</v>
       </c>
       <c r="D46" t="s">
-        <v>1398</v>
+        <v>1418</v>
       </c>
       <c r="E46" t="s">
         <v>537</v>
       </c>
       <c r="F46" t="s">
-        <v>1399</v>
+        <v>1419</v>
       </c>
       <c r="G46" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J46" t="s">
         <v>38</v>
@@ -20069,16 +20398,16 @@
         <v>44</v>
       </c>
       <c r="N46" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O46" t="s">
-        <v>1400</v>
+        <v>1420</v>
       </c>
       <c r="P46" t="s">
-        <v>1401</v>
+        <v>1421</v>
       </c>
       <c r="Q46" t="s">
-        <v>1402</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
@@ -20092,16 +20421,16 @@
         <v>35</v>
       </c>
       <c r="D47" t="s">
-        <v>1403</v>
+        <v>1423</v>
       </c>
       <c r="E47" t="s">
         <v>537</v>
       </c>
       <c r="F47" t="s">
-        <v>1404</v>
+        <v>1424</v>
       </c>
       <c r="G47" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J47" t="s">
         <v>38</v>
@@ -20116,16 +20445,16 @@
         <v>25</v>
       </c>
       <c r="N47" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O47" t="s">
-        <v>1405</v>
+        <v>1425</v>
       </c>
       <c r="P47" t="s">
-        <v>1406</v>
+        <v>1426</v>
       </c>
       <c r="Q47" t="s">
-        <v>1407</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
@@ -20139,7 +20468,7 @@
         <v>35</v>
       </c>
       <c r="D48" t="s">
-        <v>1408</v>
+        <v>1428</v>
       </c>
       <c r="E48" t="s">
         <v>537</v>
@@ -20148,7 +20477,7 @@
         <v>566</v>
       </c>
       <c r="G48" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J48" t="s">
         <v>38</v>
@@ -20163,16 +20492,16 @@
         <v>25</v>
       </c>
       <c r="N48" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O48" t="s">
-        <v>1409</v>
+        <v>1429</v>
       </c>
       <c r="P48" t="s">
-        <v>1410</v>
+        <v>1430</v>
       </c>
       <c r="Q48" t="s">
-        <v>1411</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
@@ -20186,16 +20515,16 @@
         <v>15</v>
       </c>
       <c r="D49" t="s">
-        <v>1412</v>
+        <v>1432</v>
       </c>
       <c r="E49" t="s">
         <v>537</v>
       </c>
       <c r="F49" t="s">
-        <v>1413</v>
+        <v>1433</v>
       </c>
       <c r="G49" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J49" t="s">
         <v>38</v>
@@ -20210,16 +20539,16 @@
         <v>25</v>
       </c>
       <c r="N49" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O49" t="s">
-        <v>1414</v>
+        <v>1434</v>
       </c>
       <c r="P49" t="s">
-        <v>1415</v>
+        <v>1435</v>
       </c>
       <c r="Q49" t="s">
-        <v>1416</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
@@ -20233,16 +20562,16 @@
         <v>25</v>
       </c>
       <c r="D50" t="s">
-        <v>1417</v>
+        <v>1437</v>
       </c>
       <c r="E50" t="s">
         <v>537</v>
       </c>
       <c r="F50" t="s">
-        <v>1418</v>
+        <v>1438</v>
       </c>
       <c r="G50" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J50" t="s">
         <v>38</v>
@@ -20257,16 +20586,16 @@
         <v>25</v>
       </c>
       <c r="N50" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O50" t="s">
-        <v>1419</v>
+        <v>1439</v>
       </c>
       <c r="P50" t="s">
-        <v>1420</v>
+        <v>1440</v>
       </c>
       <c r="Q50" t="s">
-        <v>1421</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
@@ -20280,16 +20609,16 @@
         <v>30</v>
       </c>
       <c r="D51" t="s">
-        <v>1422</v>
+        <v>1442</v>
       </c>
       <c r="E51" t="s">
         <v>537</v>
       </c>
       <c r="F51" t="s">
-        <v>1423</v>
+        <v>1443</v>
       </c>
       <c r="G51" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J51" t="s">
         <v>38</v>
@@ -20304,16 +20633,16 @@
         <v>25</v>
       </c>
       <c r="N51" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O51" t="s">
-        <v>1424</v>
+        <v>1444</v>
       </c>
       <c r="P51" t="s">
-        <v>1425</v>
+        <v>1445</v>
       </c>
       <c r="Q51" t="s">
-        <v>1426</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
@@ -20333,10 +20662,10 @@
         <v>480</v>
       </c>
       <c r="F52" t="s">
-        <v>1383</v>
+        <v>1403</v>
       </c>
       <c r="G52" t="s">
-        <v>1197</v>
+        <v>1217</v>
       </c>
       <c r="J52" t="s">
         <v>38</v>
@@ -20351,16 +20680,16 @@
         <v>25</v>
       </c>
       <c r="N52" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O52" t="s">
-        <v>1427</v>
+        <v>1447</v>
       </c>
       <c r="P52" t="s">
-        <v>1428</v>
+        <v>1448</v>
       </c>
       <c r="Q52" t="s">
-        <v>1429</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
@@ -20380,10 +20709,10 @@
         <v>480</v>
       </c>
       <c r="F53" t="s">
-        <v>1430</v>
+        <v>1450</v>
       </c>
       <c r="G53" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J53" t="s">
         <v>38</v>
@@ -20398,16 +20727,16 @@
         <v>44</v>
       </c>
       <c r="N53" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O53" t="s">
-        <v>1431</v>
+        <v>1451</v>
       </c>
       <c r="P53" t="s">
-        <v>1432</v>
+        <v>1452</v>
       </c>
       <c r="Q53" t="s">
-        <v>1433</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
@@ -20430,7 +20759,7 @@
         <v>819</v>
       </c>
       <c r="G54" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="H54">
         <v>180000</v>
@@ -20451,16 +20780,16 @@
         <v>25</v>
       </c>
       <c r="N54" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O54" t="s">
-        <v>1434</v>
+        <v>1454</v>
       </c>
       <c r="P54" t="s">
-        <v>1435</v>
+        <v>1455</v>
       </c>
       <c r="Q54" t="s">
-        <v>1436</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
@@ -20480,10 +20809,10 @@
         <v>480</v>
       </c>
       <c r="F55" t="s">
-        <v>1437</v>
+        <v>1457</v>
       </c>
       <c r="G55" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="H55">
         <v>180000</v>
@@ -20504,16 +20833,16 @@
         <v>25</v>
       </c>
       <c r="N55" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O55" t="s">
-        <v>1438</v>
+        <v>1458</v>
       </c>
       <c r="P55" t="s">
-        <v>1439</v>
+        <v>1459</v>
       </c>
       <c r="Q55" t="s">
-        <v>1440</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
@@ -20527,16 +20856,16 @@
         <v>20</v>
       </c>
       <c r="D56" t="s">
-        <v>1441</v>
+        <v>1461</v>
       </c>
       <c r="E56" t="s">
         <v>865</v>
       </c>
       <c r="F56" t="s">
-        <v>1442</v>
+        <v>1462</v>
       </c>
       <c r="G56" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J56" t="s">
         <v>38</v>
@@ -20551,16 +20880,16 @@
         <v>25</v>
       </c>
       <c r="N56" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O56" t="s">
-        <v>1443</v>
+        <v>1463</v>
       </c>
       <c r="P56" t="s">
-        <v>1444</v>
+        <v>1464</v>
       </c>
       <c r="Q56" t="s">
-        <v>1445</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
@@ -20574,7 +20903,7 @@
         <v>50</v>
       </c>
       <c r="D57" t="s">
-        <v>1446</v>
+        <v>1466</v>
       </c>
       <c r="E57" t="s">
         <v>865</v>
@@ -20583,7 +20912,7 @@
         <v>20</v>
       </c>
       <c r="G57" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="H57">
         <v>250000</v>
@@ -20604,16 +20933,16 @@
         <v>44</v>
       </c>
       <c r="N57" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O57" t="s">
-        <v>1447</v>
+        <v>1467</v>
       </c>
       <c r="P57" t="s">
-        <v>1448</v>
+        <v>1468</v>
       </c>
       <c r="Q57" t="s">
-        <v>1449</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
@@ -20627,7 +20956,7 @@
         <v>55</v>
       </c>
       <c r="D58" t="s">
-        <v>1450</v>
+        <v>1470</v>
       </c>
       <c r="E58" t="s">
         <v>865</v>
@@ -20636,7 +20965,7 @@
         <v>20</v>
       </c>
       <c r="G58" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="H58">
         <v>200000</v>
@@ -20657,16 +20986,16 @@
         <v>44</v>
       </c>
       <c r="N58" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O58" t="s">
-        <v>1451</v>
+        <v>1471</v>
       </c>
       <c r="P58" t="s">
-        <v>1452</v>
+        <v>1472</v>
       </c>
       <c r="Q58" t="s">
-        <v>1453</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
@@ -20680,7 +21009,7 @@
         <v>52</v>
       </c>
       <c r="D59" t="s">
-        <v>1454</v>
+        <v>1474</v>
       </c>
       <c r="E59" t="s">
         <v>865</v>
@@ -20689,7 +21018,7 @@
         <v>20</v>
       </c>
       <c r="G59" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="H59">
         <v>250000</v>
@@ -20710,16 +21039,16 @@
         <v>44</v>
       </c>
       <c r="N59" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O59" t="s">
-        <v>1455</v>
+        <v>1475</v>
       </c>
       <c r="P59" t="s">
-        <v>1456</v>
+        <v>1476</v>
       </c>
       <c r="Q59" t="s">
-        <v>1457</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
@@ -20733,7 +21062,7 @@
         <v>53</v>
       </c>
       <c r="D60" t="s">
-        <v>1458</v>
+        <v>1478</v>
       </c>
       <c r="E60" t="s">
         <v>865</v>
@@ -20742,7 +21071,7 @@
         <v>20</v>
       </c>
       <c r="G60" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="H60">
         <v>200000</v>
@@ -20763,16 +21092,16 @@
         <v>44</v>
       </c>
       <c r="N60" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O60" t="s">
-        <v>1459</v>
+        <v>1479</v>
       </c>
       <c r="P60" t="s">
-        <v>1460</v>
+        <v>1480</v>
       </c>
       <c r="Q60" t="s">
-        <v>1461</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
@@ -20786,7 +21115,7 @@
         <v>50</v>
       </c>
       <c r="D61" t="s">
-        <v>1462</v>
+        <v>1482</v>
       </c>
       <c r="E61" t="s">
         <v>865</v>
@@ -20795,7 +21124,7 @@
         <v>20</v>
       </c>
       <c r="G61" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="H61">
         <v>200000</v>
@@ -20816,16 +21145,16 @@
         <v>44</v>
       </c>
       <c r="N61" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O61" t="s">
-        <v>1463</v>
+        <v>1483</v>
       </c>
       <c r="P61" t="s">
-        <v>1464</v>
+        <v>1484</v>
       </c>
       <c r="Q61" t="s">
-        <v>1465</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
@@ -20839,7 +21168,7 @@
         <v>55</v>
       </c>
       <c r="D62" t="s">
-        <v>1466</v>
+        <v>1486</v>
       </c>
       <c r="E62" t="s">
         <v>865</v>
@@ -20848,7 +21177,7 @@
         <v>20</v>
       </c>
       <c r="G62" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="H62">
         <v>250000</v>
@@ -20869,16 +21198,16 @@
         <v>44</v>
       </c>
       <c r="N62" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O62" t="s">
-        <v>1467</v>
+        <v>1487</v>
       </c>
       <c r="P62" t="s">
-        <v>1468</v>
+        <v>1488</v>
       </c>
       <c r="Q62" t="s">
-        <v>1469</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
@@ -20892,16 +21221,16 @@
         <v>45</v>
       </c>
       <c r="D63" t="s">
-        <v>1470</v>
+        <v>1490</v>
       </c>
       <c r="E63" t="s">
-        <v>1471</v>
+        <v>1491</v>
       </c>
       <c r="F63" t="s">
-        <v>1472</v>
+        <v>1492</v>
       </c>
       <c r="G63" t="s">
-        <v>1197</v>
+        <v>1217</v>
       </c>
       <c r="H63">
         <v>154000</v>
@@ -20922,16 +21251,16 @@
         <v>25</v>
       </c>
       <c r="N63" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O63" t="s">
-        <v>1473</v>
+        <v>1493</v>
       </c>
       <c r="P63" t="s">
-        <v>1474</v>
+        <v>1494</v>
       </c>
       <c r="Q63" t="s">
-        <v>1475</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
@@ -20954,7 +21283,7 @@
         <v>496</v>
       </c>
       <c r="G64" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="H64">
         <v>180000</v>
@@ -20975,16 +21304,16 @@
         <v>44</v>
       </c>
       <c r="N64" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O64" t="s">
-        <v>1476</v>
+        <v>1496</v>
       </c>
       <c r="P64" t="s">
-        <v>1477</v>
+        <v>1497</v>
       </c>
       <c r="Q64" t="s">
-        <v>1478</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
@@ -21004,10 +21333,10 @@
         <v>480</v>
       </c>
       <c r="F65" t="s">
-        <v>1332</v>
+        <v>1352</v>
       </c>
       <c r="G65" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="H65">
         <v>219100</v>
@@ -21028,16 +21357,16 @@
         <v>25</v>
       </c>
       <c r="N65" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O65" t="s">
-        <v>1479</v>
+        <v>1499</v>
       </c>
       <c r="P65" t="s">
-        <v>1480</v>
+        <v>1500</v>
       </c>
       <c r="Q65" t="s">
-        <v>1481</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
@@ -21051,7 +21380,7 @@
         <v>25</v>
       </c>
       <c r="D66" t="s">
-        <v>1482</v>
+        <v>1502</v>
       </c>
       <c r="E66" t="s">
         <v>480</v>
@@ -21060,7 +21389,7 @@
         <v>1070</v>
       </c>
       <c r="G66" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J66" t="s">
         <v>38</v>
@@ -21075,16 +21404,16 @@
         <v>25</v>
       </c>
       <c r="N66" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O66" t="s">
-        <v>1483</v>
+        <v>1503</v>
       </c>
       <c r="P66" t="s">
-        <v>1484</v>
+        <v>1504</v>
       </c>
       <c r="Q66" t="s">
-        <v>1485</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
@@ -21104,10 +21433,10 @@
         <v>753</v>
       </c>
       <c r="F67" t="s">
-        <v>1274</v>
+        <v>1294</v>
       </c>
       <c r="G67" t="s">
-        <v>1197</v>
+        <v>1217</v>
       </c>
       <c r="J67" t="s">
         <v>38</v>
@@ -21122,16 +21451,16 @@
         <v>25</v>
       </c>
       <c r="N67" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O67" t="s">
-        <v>1486</v>
+        <v>1506</v>
       </c>
       <c r="P67" t="s">
-        <v>1487</v>
+        <v>1507</v>
       </c>
       <c r="Q67" t="s">
-        <v>1488</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
@@ -21145,16 +21474,16 @@
         <v>15</v>
       </c>
       <c r="D68" t="s">
-        <v>1489</v>
+        <v>1509</v>
       </c>
       <c r="E68" t="s">
-        <v>1490</v>
+        <v>1510</v>
       </c>
       <c r="F68" t="s">
         <v>1086</v>
       </c>
       <c r="G68" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J68" t="s">
         <v>38</v>
@@ -21169,16 +21498,16 @@
         <v>25</v>
       </c>
       <c r="N68" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O68" t="s">
-        <v>1491</v>
+        <v>1511</v>
       </c>
       <c r="P68" t="s">
-        <v>1492</v>
+        <v>1512</v>
       </c>
       <c r="Q68" t="s">
-        <v>1493</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
@@ -21192,16 +21521,16 @@
         <v>12</v>
       </c>
       <c r="D69" t="s">
-        <v>1494</v>
+        <v>1514</v>
       </c>
       <c r="E69" t="s">
-        <v>1495</v>
+        <v>1515</v>
       </c>
       <c r="F69" t="s">
-        <v>1496</v>
+        <v>1516</v>
       </c>
       <c r="G69" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J69" t="s">
         <v>38</v>
@@ -21216,16 +21545,16 @@
         <v>25</v>
       </c>
       <c r="N69" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O69" t="s">
-        <v>1497</v>
+        <v>1517</v>
       </c>
       <c r="P69" t="s">
-        <v>1498</v>
+        <v>1518</v>
       </c>
       <c r="Q69" t="s">
-        <v>1499</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
@@ -21239,16 +21568,16 @@
         <v>42</v>
       </c>
       <c r="D70" t="s">
-        <v>1500</v>
+        <v>1520</v>
       </c>
       <c r="E70" t="s">
         <v>480</v>
       </c>
       <c r="F70" t="s">
-        <v>1501</v>
+        <v>1521</v>
       </c>
       <c r="G70" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="H70">
         <v>180000</v>
@@ -21269,16 +21598,16 @@
         <v>44</v>
       </c>
       <c r="N70" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O70" t="s">
-        <v>1502</v>
+        <v>1522</v>
       </c>
       <c r="P70" t="s">
-        <v>1503</v>
+        <v>1523</v>
       </c>
       <c r="Q70" t="s">
-        <v>1504</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
@@ -21292,16 +21621,16 @@
         <v>22</v>
       </c>
       <c r="D71" t="s">
-        <v>1505</v>
+        <v>1525</v>
       </c>
       <c r="E71" t="s">
-        <v>1234</v>
+        <v>1254</v>
       </c>
       <c r="F71" t="s">
-        <v>1506</v>
+        <v>1526</v>
       </c>
       <c r="G71" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="H71">
         <v>200000</v>
@@ -21322,16 +21651,16 @@
         <v>25</v>
       </c>
       <c r="N71" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O71" t="s">
-        <v>1507</v>
+        <v>1527</v>
       </c>
       <c r="P71" t="s">
-        <v>1508</v>
+        <v>1528</v>
       </c>
       <c r="Q71" t="s">
-        <v>1509</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
@@ -21345,16 +21674,16 @@
         <v>28</v>
       </c>
       <c r="D72" t="s">
-        <v>1510</v>
+        <v>1530</v>
       </c>
       <c r="E72" t="s">
-        <v>1511</v>
+        <v>1531</v>
       </c>
       <c r="F72" t="s">
         <v>1070</v>
       </c>
       <c r="G72" t="s">
-        <v>1197</v>
+        <v>1217</v>
       </c>
       <c r="J72" t="s">
         <v>38</v>
@@ -21369,16 +21698,16 @@
         <v>25</v>
       </c>
       <c r="N72" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O72" t="s">
-        <v>1512</v>
+        <v>1532</v>
       </c>
       <c r="P72" t="s">
-        <v>1513</v>
+        <v>1533</v>
       </c>
       <c r="Q72" t="s">
-        <v>1514</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
@@ -21392,16 +21721,16 @@
         <v>5</v>
       </c>
       <c r="D73" t="s">
-        <v>1515</v>
+        <v>1535</v>
       </c>
       <c r="E73" t="s">
-        <v>1516</v>
+        <v>1536</v>
       </c>
       <c r="F73" t="s">
-        <v>1517</v>
+        <v>1537</v>
       </c>
       <c r="G73" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J73" t="s">
         <v>38</v>
@@ -21416,16 +21745,16 @@
         <v>25</v>
       </c>
       <c r="N73" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O73" t="s">
-        <v>1518</v>
+        <v>1538</v>
       </c>
       <c r="P73" t="s">
-        <v>1519</v>
+        <v>1539</v>
       </c>
       <c r="Q73" t="s">
-        <v>1520</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
@@ -21445,10 +21774,10 @@
         <v>480</v>
       </c>
       <c r="F74" t="s">
-        <v>1521</v>
+        <v>1541</v>
       </c>
       <c r="G74" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J74" t="s">
         <v>38</v>
@@ -21463,16 +21792,16 @@
         <v>44</v>
       </c>
       <c r="N74" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O74" t="s">
-        <v>1522</v>
+        <v>1542</v>
       </c>
       <c r="P74" t="s">
-        <v>1523</v>
+        <v>1543</v>
       </c>
       <c r="Q74" t="s">
-        <v>1524</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
@@ -21486,16 +21815,16 @@
         <v>35</v>
       </c>
       <c r="D75" t="s">
-        <v>1525</v>
+        <v>1545</v>
       </c>
       <c r="E75" t="s">
-        <v>1526</v>
+        <v>1546</v>
       </c>
       <c r="F75" t="s">
         <v>1137</v>
       </c>
       <c r="G75" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J75" t="s">
         <v>38</v>
@@ -21510,16 +21839,16 @@
         <v>25</v>
       </c>
       <c r="N75" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O75" t="s">
-        <v>1527</v>
+        <v>1547</v>
       </c>
       <c r="P75" t="s">
-        <v>1528</v>
+        <v>1548</v>
       </c>
       <c r="Q75" t="s">
-        <v>1529</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
@@ -21533,16 +21862,16 @@
         <v>55</v>
       </c>
       <c r="D76" t="s">
-        <v>1530</v>
+        <v>1550</v>
       </c>
       <c r="E76" t="s">
         <v>480</v>
       </c>
       <c r="F76" t="s">
-        <v>1332</v>
+        <v>1352</v>
       </c>
       <c r="G76" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="H76">
         <v>219100</v>
@@ -21557,22 +21886,22 @@
         <v>482</v>
       </c>
       <c r="L76" t="s">
-        <v>1531</v>
+        <v>1551</v>
       </c>
       <c r="M76" t="s">
         <v>44</v>
       </c>
       <c r="N76" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O76" t="s">
-        <v>1532</v>
+        <v>1552</v>
       </c>
       <c r="P76" t="s">
-        <v>1533</v>
+        <v>1553</v>
       </c>
       <c r="Q76" t="s">
-        <v>1534</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
@@ -21586,16 +21915,16 @@
         <v>50</v>
       </c>
       <c r="D77" t="s">
-        <v>1535</v>
+        <v>1555</v>
       </c>
       <c r="E77" t="s">
-        <v>1234</v>
+        <v>1254</v>
       </c>
       <c r="F77" t="s">
         <v>20</v>
       </c>
       <c r="G77" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="H77">
         <v>200000</v>
@@ -21610,22 +21939,22 @@
         <v>482</v>
       </c>
       <c r="L77" t="s">
-        <v>1531</v>
+        <v>1551</v>
       </c>
       <c r="M77" t="s">
         <v>44</v>
       </c>
       <c r="N77" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O77" t="s">
-        <v>1536</v>
+        <v>1556</v>
       </c>
       <c r="P77" t="s">
-        <v>1537</v>
+        <v>1557</v>
       </c>
       <c r="Q77" t="s">
-        <v>1538</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
@@ -21639,16 +21968,16 @@
         <v>12</v>
       </c>
       <c r="D78" t="s">
-        <v>1539</v>
+        <v>1559</v>
       </c>
       <c r="E78" t="s">
-        <v>1540</v>
+        <v>1560</v>
       </c>
       <c r="F78" t="s">
         <v>1070</v>
       </c>
       <c r="G78" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J78" t="s">
         <v>38</v>
@@ -21657,22 +21986,22 @@
         <v>70</v>
       </c>
       <c r="L78" t="s">
-        <v>1531</v>
+        <v>1551</v>
       </c>
       <c r="M78" t="s">
         <v>25</v>
       </c>
       <c r="N78" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O78" t="s">
-        <v>1541</v>
+        <v>1561</v>
       </c>
       <c r="P78" t="s">
-        <v>1542</v>
+        <v>1562</v>
       </c>
       <c r="Q78" t="s">
-        <v>1543</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
@@ -21686,16 +22015,16 @@
         <v>12</v>
       </c>
       <c r="D79" t="s">
-        <v>1544</v>
+        <v>1564</v>
       </c>
       <c r="E79" t="s">
-        <v>1540</v>
+        <v>1560</v>
       </c>
       <c r="F79" t="s">
         <v>1070</v>
       </c>
       <c r="G79" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J79" t="s">
         <v>38</v>
@@ -21704,22 +22033,22 @@
         <v>70</v>
       </c>
       <c r="L79" t="s">
-        <v>1531</v>
+        <v>1551</v>
       </c>
       <c r="M79" t="s">
         <v>25</v>
       </c>
       <c r="N79" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O79" t="s">
-        <v>1545</v>
+        <v>1565</v>
       </c>
       <c r="P79" t="s">
-        <v>1546</v>
+        <v>1566</v>
       </c>
       <c r="Q79" t="s">
-        <v>1547</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
@@ -21733,16 +22062,16 @@
         <v>3</v>
       </c>
       <c r="D80" t="s">
-        <v>1548</v>
+        <v>1568</v>
       </c>
       <c r="E80" t="s">
-        <v>1540</v>
+        <v>1560</v>
       </c>
       <c r="F80" t="s">
         <v>1070</v>
       </c>
       <c r="G80" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J80" t="s">
         <v>38</v>
@@ -21751,22 +22080,22 @@
         <v>70</v>
       </c>
       <c r="L80" t="s">
-        <v>1531</v>
+        <v>1551</v>
       </c>
       <c r="M80" t="s">
         <v>25</v>
       </c>
       <c r="N80" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O80" t="s">
-        <v>1549</v>
+        <v>1569</v>
       </c>
       <c r="P80" t="s">
-        <v>1550</v>
+        <v>1570</v>
       </c>
       <c r="Q80" t="s">
-        <v>1551</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
@@ -21780,16 +22109,16 @@
         <v>25</v>
       </c>
       <c r="D81" t="s">
-        <v>1552</v>
+        <v>1572</v>
       </c>
       <c r="E81" t="s">
-        <v>1553</v>
+        <v>1573</v>
       </c>
       <c r="F81" t="s">
-        <v>1554</v>
+        <v>1574</v>
       </c>
       <c r="G81" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J81" t="s">
         <v>38</v>
@@ -21798,22 +22127,22 @@
         <v>70</v>
       </c>
       <c r="L81" t="s">
-        <v>1531</v>
+        <v>1551</v>
       </c>
       <c r="M81" t="s">
         <v>25</v>
       </c>
       <c r="N81" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O81" t="s">
-        <v>1555</v>
+        <v>1575</v>
       </c>
       <c r="P81" t="s">
-        <v>1556</v>
+        <v>1576</v>
       </c>
       <c r="Q81" t="s">
-        <v>1557</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
@@ -21827,16 +22156,16 @@
         <v>62</v>
       </c>
       <c r="D82" t="s">
-        <v>1558</v>
+        <v>1578</v>
       </c>
       <c r="E82" t="s">
-        <v>1559</v>
+        <v>1579</v>
       </c>
       <c r="F82" t="s">
-        <v>1560</v>
+        <v>1580</v>
       </c>
       <c r="G82" t="s">
-        <v>1197</v>
+        <v>1217</v>
       </c>
       <c r="J82" t="s">
         <v>38</v>
@@ -21845,22 +22174,22 @@
         <v>70</v>
       </c>
       <c r="L82" t="s">
-        <v>1531</v>
+        <v>1551</v>
       </c>
       <c r="M82" t="s">
         <v>25</v>
       </c>
       <c r="N82" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O82" t="s">
-        <v>1561</v>
+        <v>1581</v>
       </c>
       <c r="P82" t="s">
-        <v>1562</v>
+        <v>1582</v>
       </c>
       <c r="Q82" t="s">
-        <v>1563</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
@@ -21874,16 +22203,16 @@
         <v>68</v>
       </c>
       <c r="D83" t="s">
-        <v>1564</v>
+        <v>1584</v>
       </c>
       <c r="E83" t="s">
-        <v>1559</v>
+        <v>1579</v>
       </c>
       <c r="F83" t="s">
-        <v>1560</v>
+        <v>1580</v>
       </c>
       <c r="G83" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J83" t="s">
         <v>38</v>
@@ -21892,22 +22221,22 @@
         <v>70</v>
       </c>
       <c r="L83" t="s">
-        <v>1531</v>
+        <v>1551</v>
       </c>
       <c r="M83" t="s">
         <v>25</v>
       </c>
       <c r="N83" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O83" t="s">
-        <v>1565</v>
+        <v>1585</v>
       </c>
       <c r="P83" t="s">
-        <v>1566</v>
+        <v>1586</v>
       </c>
       <c r="Q83" t="s">
-        <v>1567</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
@@ -21927,10 +22256,10 @@
         <v>480</v>
       </c>
       <c r="F84" t="s">
-        <v>1568</v>
+        <v>1588</v>
       </c>
       <c r="G84" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="H84">
         <v>180000</v>
@@ -21951,16 +22280,16 @@
         <v>44</v>
       </c>
       <c r="N84" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O84" t="s">
-        <v>1569</v>
+        <v>1589</v>
       </c>
       <c r="P84" t="s">
-        <v>1570</v>
+        <v>1590</v>
       </c>
       <c r="Q84" t="s">
-        <v>1571</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
@@ -21980,10 +22309,10 @@
         <v>480</v>
       </c>
       <c r="F85" t="s">
-        <v>1572</v>
+        <v>1592</v>
       </c>
       <c r="G85" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="H85">
         <v>180000</v>
@@ -22004,16 +22333,16 @@
         <v>44</v>
       </c>
       <c r="N85" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O85" t="s">
-        <v>1573</v>
+        <v>1593</v>
       </c>
       <c r="P85" t="s">
-        <v>1574</v>
+        <v>1594</v>
       </c>
       <c r="Q85" t="s">
-        <v>1575</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
@@ -22027,16 +22356,16 @@
         <v>35</v>
       </c>
       <c r="D86" t="s">
-        <v>1576</v>
+        <v>1596</v>
       </c>
       <c r="E86" t="s">
         <v>480</v>
       </c>
       <c r="F86" t="s">
-        <v>1577</v>
+        <v>1597</v>
       </c>
       <c r="G86" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="H86">
         <v>219100</v>
@@ -22057,16 +22386,16 @@
         <v>44</v>
       </c>
       <c r="N86" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O86" t="s">
-        <v>1578</v>
+        <v>1598</v>
       </c>
       <c r="P86" t="s">
-        <v>1579</v>
+        <v>1599</v>
       </c>
       <c r="Q86" t="s">
-        <v>1580</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
@@ -22080,16 +22409,16 @@
         <v>25</v>
       </c>
       <c r="D87" t="s">
-        <v>1581</v>
+        <v>1601</v>
       </c>
       <c r="E87" t="s">
         <v>537</v>
       </c>
       <c r="F87" t="s">
-        <v>1399</v>
+        <v>1419</v>
       </c>
       <c r="G87" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J87" t="s">
         <v>38</v>
@@ -22104,16 +22433,16 @@
         <v>25</v>
       </c>
       <c r="N87" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O87" t="s">
-        <v>1582</v>
+        <v>1602</v>
       </c>
       <c r="P87" t="s">
-        <v>1583</v>
+        <v>1603</v>
       </c>
       <c r="Q87" t="s">
-        <v>1584</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
@@ -22127,16 +22456,16 @@
         <v>35</v>
       </c>
       <c r="D88" t="s">
-        <v>1585</v>
+        <v>1605</v>
       </c>
       <c r="E88" t="s">
-        <v>1586</v>
+        <v>1606</v>
       </c>
       <c r="F88" t="s">
-        <v>1274</v>
+        <v>1294</v>
       </c>
       <c r="G88" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J88" t="s">
         <v>38</v>
@@ -22151,16 +22480,16 @@
         <v>25</v>
       </c>
       <c r="N88" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O88" t="s">
-        <v>1587</v>
+        <v>1607</v>
       </c>
       <c r="P88" t="s">
-        <v>1588</v>
+        <v>1608</v>
       </c>
       <c r="Q88" t="s">
-        <v>1589</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
@@ -22183,7 +22512,7 @@
         <v>1137</v>
       </c>
       <c r="G89" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="H89">
         <v>200000</v>
@@ -22204,16 +22533,16 @@
         <v>25</v>
       </c>
       <c r="N89" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O89" t="s">
-        <v>1590</v>
+        <v>1610</v>
       </c>
       <c r="P89" t="s">
-        <v>1591</v>
+        <v>1611</v>
       </c>
       <c r="Q89" t="s">
-        <v>1592</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
@@ -22227,7 +22556,7 @@
         <v>38</v>
       </c>
       <c r="D90" t="s">
-        <v>1593</v>
+        <v>1613</v>
       </c>
       <c r="E90" t="s">
         <v>1136</v>
@@ -22236,7 +22565,7 @@
         <v>1137</v>
       </c>
       <c r="G90" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="H90">
         <v>200000</v>
@@ -22257,16 +22586,16 @@
         <v>25</v>
       </c>
       <c r="N90" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O90" t="s">
-        <v>1594</v>
+        <v>1614</v>
       </c>
       <c r="P90" t="s">
-        <v>1595</v>
+        <v>1615</v>
       </c>
       <c r="Q90" t="s">
-        <v>1596</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
@@ -22280,16 +22609,16 @@
         <v>40</v>
       </c>
       <c r="D91" t="s">
-        <v>1377</v>
+        <v>1397</v>
       </c>
       <c r="E91" t="s">
-        <v>1234</v>
+        <v>1254</v>
       </c>
       <c r="F91" t="s">
         <v>768</v>
       </c>
       <c r="G91" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="H91">
         <v>184200</v>
@@ -22310,16 +22639,16 @@
         <v>25</v>
       </c>
       <c r="N91" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O91" t="s">
-        <v>1597</v>
+        <v>1617</v>
       </c>
       <c r="P91" t="s">
-        <v>1598</v>
+        <v>1618</v>
       </c>
       <c r="Q91" t="s">
-        <v>1599</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
@@ -22333,16 +22662,16 @@
         <v>20</v>
       </c>
       <c r="D92" t="s">
-        <v>1600</v>
+        <v>1620</v>
       </c>
       <c r="E92" t="s">
-        <v>1601</v>
+        <v>1621</v>
       </c>
       <c r="F92" t="s">
-        <v>1602</v>
+        <v>1622</v>
       </c>
       <c r="G92" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J92" t="s">
         <v>38</v>
@@ -22357,16 +22686,16 @@
         <v>25</v>
       </c>
       <c r="N92" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O92" t="s">
-        <v>1603</v>
+        <v>1623</v>
       </c>
       <c r="P92" t="s">
-        <v>1604</v>
+        <v>1624</v>
       </c>
       <c r="Q92" t="s">
-        <v>1605</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
@@ -22380,16 +22709,16 @@
         <v>35</v>
       </c>
       <c r="D93" t="s">
-        <v>1606</v>
+        <v>1626</v>
       </c>
       <c r="E93" t="s">
-        <v>1607</v>
+        <v>1627</v>
       </c>
       <c r="F93" t="s">
-        <v>1608</v>
+        <v>1628</v>
       </c>
       <c r="G93" t="s">
-        <v>1197</v>
+        <v>1217</v>
       </c>
       <c r="H93">
         <v>230000</v>
@@ -22410,16 +22739,16 @@
         <v>25</v>
       </c>
       <c r="N93" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O93" t="s">
-        <v>1609</v>
+        <v>1629</v>
       </c>
       <c r="P93" t="s">
-        <v>1610</v>
+        <v>1630</v>
       </c>
       <c r="Q93" t="s">
-        <v>1611</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
@@ -22439,10 +22768,10 @@
         <v>480</v>
       </c>
       <c r="F94" t="s">
-        <v>1612</v>
+        <v>1632</v>
       </c>
       <c r="G94" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="H94">
         <v>219100</v>
@@ -22463,16 +22792,16 @@
         <v>32</v>
       </c>
       <c r="N94" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O94" t="s">
-        <v>1613</v>
+        <v>1633</v>
       </c>
       <c r="P94" t="s">
-        <v>1614</v>
+        <v>1634</v>
       </c>
       <c r="Q94" t="s">
-        <v>1615</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
@@ -22486,16 +22815,16 @@
         <v>25</v>
       </c>
       <c r="D95" t="s">
-        <v>1616</v>
+        <v>1636</v>
       </c>
       <c r="E95" t="s">
-        <v>1526</v>
+        <v>1546</v>
       </c>
       <c r="F95" t="s">
         <v>1137</v>
       </c>
       <c r="G95" t="s">
-        <v>1197</v>
+        <v>1217</v>
       </c>
       <c r="J95" t="s">
         <v>38</v>
@@ -22510,16 +22839,16 @@
         <v>25</v>
       </c>
       <c r="N95" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O95" t="s">
-        <v>1617</v>
+        <v>1637</v>
       </c>
       <c r="P95" t="s">
-        <v>1618</v>
+        <v>1638</v>
       </c>
       <c r="Q95" t="s">
-        <v>1619</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
@@ -22533,16 +22862,16 @@
         <v>22</v>
       </c>
       <c r="D96" t="s">
-        <v>1620</v>
+        <v>1640</v>
       </c>
       <c r="E96" t="s">
-        <v>1621</v>
+        <v>1641</v>
       </c>
       <c r="F96" t="s">
-        <v>1622</v>
+        <v>1642</v>
       </c>
       <c r="G96" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J96" t="s">
         <v>38</v>
@@ -22557,16 +22886,16 @@
         <v>25</v>
       </c>
       <c r="N96" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O96" t="s">
-        <v>1623</v>
+        <v>1643</v>
       </c>
       <c r="P96" t="s">
-        <v>1624</v>
+        <v>1644</v>
       </c>
       <c r="Q96" t="s">
-        <v>1625</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
@@ -22580,16 +22909,16 @@
         <v>3</v>
       </c>
       <c r="D97" t="s">
-        <v>1626</v>
+        <v>1646</v>
       </c>
       <c r="E97" t="s">
-        <v>1627</v>
+        <v>1647</v>
       </c>
       <c r="F97" t="s">
-        <v>1622</v>
+        <v>1642</v>
       </c>
       <c r="G97" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J97" t="s">
         <v>38</v>
@@ -22604,16 +22933,16 @@
         <v>25</v>
       </c>
       <c r="N97" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O97" t="s">
-        <v>1628</v>
+        <v>1648</v>
       </c>
       <c r="P97" t="s">
-        <v>1629</v>
+        <v>1649</v>
       </c>
       <c r="Q97" t="s">
-        <v>1630</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
@@ -22627,16 +22956,16 @@
         <v>28</v>
       </c>
       <c r="D98" t="s">
-        <v>1631</v>
+        <v>1651</v>
       </c>
       <c r="E98" t="s">
-        <v>1632</v>
+        <v>1652</v>
       </c>
       <c r="F98" t="s">
         <v>1070</v>
       </c>
       <c r="G98" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J98" t="s">
         <v>38</v>
@@ -22651,16 +22980,16 @@
         <v>25</v>
       </c>
       <c r="N98" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O98" t="s">
-        <v>1633</v>
+        <v>1653</v>
       </c>
       <c r="P98" t="s">
-        <v>1634</v>
+        <v>1654</v>
       </c>
       <c r="Q98" t="s">
-        <v>1635</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.25">
@@ -22674,16 +23003,16 @@
         <v>45</v>
       </c>
       <c r="D99" t="s">
-        <v>1636</v>
+        <v>1656</v>
       </c>
       <c r="E99" t="s">
-        <v>1637</v>
+        <v>1657</v>
       </c>
       <c r="F99" t="s">
-        <v>1274</v>
+        <v>1294</v>
       </c>
       <c r="G99" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J99" t="s">
         <v>38</v>
@@ -22698,16 +23027,16 @@
         <v>44</v>
       </c>
       <c r="N99" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O99" t="s">
-        <v>1638</v>
+        <v>1658</v>
       </c>
       <c r="P99" t="s">
-        <v>1639</v>
+        <v>1659</v>
       </c>
       <c r="Q99" t="s">
-        <v>1640</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.25">
@@ -22721,16 +23050,16 @@
         <v>50</v>
       </c>
       <c r="D100" t="s">
-        <v>1641</v>
+        <v>1661</v>
       </c>
       <c r="E100" t="s">
-        <v>1642</v>
+        <v>1662</v>
       </c>
       <c r="F100" t="s">
-        <v>1306</v>
+        <v>1326</v>
       </c>
       <c r="G100" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J100" t="s">
         <v>38</v>
@@ -22745,16 +23074,16 @@
         <v>44</v>
       </c>
       <c r="N100" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O100" t="s">
-        <v>1643</v>
+        <v>1663</v>
       </c>
       <c r="P100" t="s">
-        <v>1644</v>
+        <v>1664</v>
       </c>
       <c r="Q100" t="s">
-        <v>1645</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.25">
@@ -22768,16 +23097,16 @@
         <v>48</v>
       </c>
       <c r="D101" t="s">
-        <v>1646</v>
+        <v>1666</v>
       </c>
       <c r="E101" t="s">
-        <v>1471</v>
+        <v>1491</v>
       </c>
       <c r="F101" t="s">
-        <v>1647</v>
+        <v>1667</v>
       </c>
       <c r="G101" t="s">
-        <v>1197</v>
+        <v>1217</v>
       </c>
       <c r="H101">
         <v>154000</v>
@@ -22798,16 +23127,16 @@
         <v>44</v>
       </c>
       <c r="N101" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O101" t="s">
-        <v>1648</v>
+        <v>1668</v>
       </c>
       <c r="P101" t="s">
-        <v>1649</v>
+        <v>1669</v>
       </c>
       <c r="Q101" t="s">
-        <v>1650</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.25">
@@ -22821,16 +23150,16 @@
         <v>25</v>
       </c>
       <c r="D102" t="s">
-        <v>1651</v>
+        <v>1671</v>
       </c>
       <c r="E102" t="s">
-        <v>1295</v>
+        <v>1315</v>
       </c>
       <c r="F102" t="s">
         <v>1137</v>
       </c>
       <c r="G102" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J102" t="s">
         <v>38</v>
@@ -22845,16 +23174,16 @@
         <v>25</v>
       </c>
       <c r="N102" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O102" t="s">
-        <v>1652</v>
+        <v>1672</v>
       </c>
       <c r="P102" t="s">
-        <v>1653</v>
+        <v>1673</v>
       </c>
       <c r="Q102" t="s">
-        <v>1654</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.25">
@@ -22868,16 +23197,16 @@
         <v>32</v>
       </c>
       <c r="D103" t="s">
-        <v>1552</v>
+        <v>1572</v>
       </c>
       <c r="E103" t="s">
-        <v>1295</v>
+        <v>1315</v>
       </c>
       <c r="F103" t="s">
         <v>1137</v>
       </c>
       <c r="G103" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J103" t="s">
         <v>38</v>
@@ -22892,16 +23221,16 @@
         <v>25</v>
       </c>
       <c r="N103" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O103" t="s">
-        <v>1655</v>
+        <v>1675</v>
       </c>
       <c r="P103" t="s">
-        <v>1656</v>
+        <v>1676</v>
       </c>
       <c r="Q103" t="s">
-        <v>1657</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.25">
@@ -22915,16 +23244,16 @@
         <v>22</v>
       </c>
       <c r="D104" t="s">
-        <v>1658</v>
+        <v>1678</v>
       </c>
       <c r="E104" t="s">
+        <v>1662</v>
+      </c>
+      <c r="F104" t="s">
         <v>1642</v>
       </c>
-      <c r="F104" t="s">
-        <v>1622</v>
-      </c>
       <c r="G104" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J104" t="s">
         <v>38</v>
@@ -22939,16 +23268,16 @@
         <v>25</v>
       </c>
       <c r="N104" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O104" t="s">
-        <v>1659</v>
+        <v>1679</v>
       </c>
       <c r="P104" t="s">
-        <v>1660</v>
+        <v>1680</v>
       </c>
       <c r="Q104" t="s">
-        <v>1661</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.25">
@@ -22962,16 +23291,16 @@
         <v>55</v>
       </c>
       <c r="D105" t="s">
-        <v>1641</v>
+        <v>1661</v>
       </c>
       <c r="E105" t="s">
-        <v>1642</v>
+        <v>1662</v>
       </c>
       <c r="F105" t="s">
-        <v>1662</v>
+        <v>1682</v>
       </c>
       <c r="G105" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J105" t="s">
         <v>38</v>
@@ -22986,16 +23315,16 @@
         <v>25</v>
       </c>
       <c r="N105" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O105" t="s">
-        <v>1663</v>
+        <v>1683</v>
       </c>
       <c r="P105" t="s">
-        <v>1664</v>
+        <v>1684</v>
       </c>
       <c r="Q105" t="s">
-        <v>1665</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.25">
@@ -23009,16 +23338,16 @@
         <v>25</v>
       </c>
       <c r="D106" t="s">
-        <v>1666</v>
+        <v>1686</v>
       </c>
       <c r="E106" t="s">
-        <v>1642</v>
+        <v>1662</v>
       </c>
       <c r="F106" t="s">
-        <v>1662</v>
+        <v>1682</v>
       </c>
       <c r="G106" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J106" t="s">
         <v>38</v>
@@ -23033,16 +23362,16 @@
         <v>25</v>
       </c>
       <c r="N106" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O106" t="s">
-        <v>1667</v>
+        <v>1687</v>
       </c>
       <c r="P106" t="s">
-        <v>1668</v>
+        <v>1688</v>
       </c>
       <c r="Q106" t="s">
-        <v>1669</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.25">
@@ -23056,7 +23385,7 @@
         <v>33</v>
       </c>
       <c r="D107" t="s">
-        <v>1670</v>
+        <v>1690</v>
       </c>
       <c r="E107" t="s">
         <v>480</v>
@@ -23065,7 +23394,7 @@
         <v>1070</v>
       </c>
       <c r="G107" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J107" t="s">
         <v>38</v>
@@ -23080,16 +23409,16 @@
         <v>25</v>
       </c>
       <c r="N107" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O107" t="s">
-        <v>1671</v>
+        <v>1691</v>
       </c>
       <c r="P107" t="s">
-        <v>1672</v>
+        <v>1692</v>
       </c>
       <c r="Q107" t="s">
-        <v>1673</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.25">
@@ -23103,16 +23432,16 @@
         <v>38</v>
       </c>
       <c r="D108" t="s">
-        <v>1674</v>
+        <v>1694</v>
       </c>
       <c r="E108" t="s">
-        <v>1675</v>
+        <v>1695</v>
       </c>
       <c r="F108" t="s">
-        <v>1404</v>
+        <v>1424</v>
       </c>
       <c r="G108" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="H108">
         <v>220000</v>
@@ -23133,16 +23462,16 @@
         <v>25</v>
       </c>
       <c r="N108" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O108" t="s">
-        <v>1676</v>
+        <v>1696</v>
       </c>
       <c r="P108" t="s">
-        <v>1677</v>
+        <v>1697</v>
       </c>
       <c r="Q108" t="s">
-        <v>1678</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.25">
@@ -23156,16 +23485,16 @@
         <v>62</v>
       </c>
       <c r="D109" t="s">
-        <v>1679</v>
+        <v>1699</v>
       </c>
       <c r="E109" t="s">
-        <v>1234</v>
+        <v>1254</v>
       </c>
       <c r="F109" t="s">
         <v>20</v>
       </c>
       <c r="G109" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="H109">
         <v>200000</v>
@@ -23186,16 +23515,16 @@
         <v>44</v>
       </c>
       <c r="N109" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O109" t="s">
-        <v>1680</v>
+        <v>1700</v>
       </c>
       <c r="P109" t="s">
-        <v>1681</v>
+        <v>1701</v>
       </c>
       <c r="Q109" t="s">
-        <v>1682</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.25">
@@ -23209,16 +23538,16 @@
         <v>30</v>
       </c>
       <c r="D110" t="s">
-        <v>1666</v>
+        <v>1686</v>
       </c>
       <c r="E110" t="s">
+        <v>1662</v>
+      </c>
+      <c r="F110" t="s">
         <v>1642</v>
       </c>
-      <c r="F110" t="s">
-        <v>1622</v>
-      </c>
       <c r="G110" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J110" t="s">
         <v>38</v>
@@ -23233,16 +23562,16 @@
         <v>25</v>
       </c>
       <c r="N110" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O110" t="s">
-        <v>1683</v>
+        <v>1703</v>
       </c>
       <c r="P110" t="s">
-        <v>1684</v>
+        <v>1704</v>
       </c>
       <c r="Q110" t="s">
-        <v>1685</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.25">
@@ -23256,16 +23585,16 @@
         <v>58</v>
       </c>
       <c r="D111" t="s">
-        <v>1641</v>
+        <v>1661</v>
       </c>
       <c r="E111" t="s">
-        <v>1642</v>
+        <v>1662</v>
       </c>
       <c r="F111" t="s">
-        <v>1306</v>
+        <v>1326</v>
       </c>
       <c r="G111" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J111" t="s">
         <v>38</v>
@@ -23280,16 +23609,16 @@
         <v>25</v>
       </c>
       <c r="N111" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O111" t="s">
-        <v>1686</v>
+        <v>1706</v>
       </c>
       <c r="P111" t="s">
-        <v>1687</v>
+        <v>1707</v>
       </c>
       <c r="Q111" t="s">
-        <v>1688</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.25">
@@ -23303,7 +23632,7 @@
         <v>55</v>
       </c>
       <c r="D112" t="s">
-        <v>1689</v>
+        <v>1709</v>
       </c>
       <c r="E112" t="s">
         <v>480</v>
@@ -23312,7 +23641,7 @@
         <v>20</v>
       </c>
       <c r="G112" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="H112">
         <v>217800</v>
@@ -23333,16 +23662,16 @@
         <v>44</v>
       </c>
       <c r="N112" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O112" t="s">
-        <v>1690</v>
+        <v>1710</v>
       </c>
       <c r="P112" t="s">
-        <v>1691</v>
+        <v>1711</v>
       </c>
       <c r="Q112" t="s">
-        <v>1692</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.25">
@@ -23356,16 +23685,16 @@
         <v>45</v>
       </c>
       <c r="D113" t="s">
-        <v>1693</v>
+        <v>1713</v>
       </c>
       <c r="E113" t="s">
         <v>480</v>
       </c>
       <c r="F113" t="s">
-        <v>1694</v>
+        <v>1714</v>
       </c>
       <c r="G113" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="H113">
         <v>219100</v>
@@ -23386,16 +23715,16 @@
         <v>44</v>
       </c>
       <c r="N113" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O113" t="s">
-        <v>1695</v>
+        <v>1715</v>
       </c>
       <c r="P113" t="s">
-        <v>1696</v>
+        <v>1716</v>
       </c>
       <c r="Q113" t="s">
-        <v>1697</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.25">
@@ -23415,10 +23744,10 @@
         <v>753</v>
       </c>
       <c r="F114" t="s">
-        <v>1698</v>
+        <v>1718</v>
       </c>
       <c r="G114" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J114" t="s">
         <v>38</v>
@@ -23433,16 +23762,16 @@
         <v>25</v>
       </c>
       <c r="N114" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O114" t="s">
-        <v>1699</v>
+        <v>1719</v>
       </c>
       <c r="P114" t="s">
-        <v>1700</v>
+        <v>1720</v>
       </c>
       <c r="Q114" t="s">
-        <v>1701</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.25">
@@ -23456,16 +23785,16 @@
         <v>35</v>
       </c>
       <c r="D115" t="s">
-        <v>1702</v>
+        <v>1722</v>
       </c>
       <c r="E115" t="s">
         <v>480</v>
       </c>
       <c r="F115" t="s">
-        <v>1703</v>
+        <v>1723</v>
       </c>
       <c r="G115" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J115" t="s">
         <v>38</v>
@@ -23480,16 +23809,16 @@
         <v>25</v>
       </c>
       <c r="N115" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O115" t="s">
-        <v>1704</v>
+        <v>1724</v>
       </c>
       <c r="P115" t="s">
-        <v>1705</v>
+        <v>1725</v>
       </c>
       <c r="Q115" t="s">
-        <v>1706</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.25">
@@ -23503,7 +23832,7 @@
         <v>38</v>
       </c>
       <c r="D116" t="s">
-        <v>1707</v>
+        <v>1727</v>
       </c>
       <c r="E116" t="s">
         <v>480</v>
@@ -23512,7 +23841,7 @@
         <v>20</v>
       </c>
       <c r="G116" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="H116">
         <v>219100</v>
@@ -23533,16 +23862,16 @@
         <v>25</v>
       </c>
       <c r="N116" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O116" t="s">
-        <v>1708</v>
+        <v>1728</v>
       </c>
       <c r="P116" t="s">
-        <v>1709</v>
+        <v>1729</v>
       </c>
       <c r="Q116" t="s">
-        <v>1710</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.25">
@@ -23556,16 +23885,16 @@
         <v>22</v>
       </c>
       <c r="D117" t="s">
-        <v>1711</v>
+        <v>1731</v>
       </c>
       <c r="E117" t="s">
-        <v>1712</v>
+        <v>1732</v>
       </c>
       <c r="F117" t="s">
-        <v>1713</v>
+        <v>1733</v>
       </c>
       <c r="G117" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J117" t="s">
         <v>38</v>
@@ -23580,16 +23909,16 @@
         <v>25</v>
       </c>
       <c r="N117" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O117" t="s">
-        <v>1714</v>
+        <v>1734</v>
       </c>
       <c r="P117" t="s">
-        <v>1715</v>
+        <v>1735</v>
       </c>
       <c r="Q117" t="s">
-        <v>1716</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.25">
@@ -23603,16 +23932,16 @@
         <v>35</v>
       </c>
       <c r="D118" t="s">
-        <v>1717</v>
+        <v>1737</v>
       </c>
       <c r="E118" t="s">
-        <v>1718</v>
+        <v>1738</v>
       </c>
       <c r="F118" t="s">
-        <v>1719</v>
+        <v>1739</v>
       </c>
       <c r="G118" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J118" t="s">
         <v>38</v>
@@ -23627,16 +23956,16 @@
         <v>25</v>
       </c>
       <c r="N118" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O118" t="s">
-        <v>1720</v>
+        <v>1740</v>
       </c>
       <c r="P118" t="s">
-        <v>1721</v>
+        <v>1741</v>
       </c>
       <c r="Q118" t="s">
-        <v>1722</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.25">
@@ -23650,7 +23979,7 @@
         <v>55</v>
       </c>
       <c r="D119" t="s">
-        <v>1723</v>
+        <v>1743</v>
       </c>
       <c r="E119" t="s">
         <v>1136</v>
@@ -23659,7 +23988,7 @@
         <v>1137</v>
       </c>
       <c r="G119" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="H119">
         <v>200000</v>
@@ -23680,16 +24009,16 @@
         <v>44</v>
       </c>
       <c r="N119" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O119" t="s">
-        <v>1724</v>
+        <v>1744</v>
       </c>
       <c r="P119" t="s">
-        <v>1725</v>
+        <v>1745</v>
       </c>
       <c r="Q119" t="s">
-        <v>1726</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.25">
@@ -23709,10 +24038,10 @@
         <v>480</v>
       </c>
       <c r="F120" t="s">
-        <v>1727</v>
+        <v>1747</v>
       </c>
       <c r="G120" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="H120">
         <v>180000</v>
@@ -23733,16 +24062,16 @@
         <v>44</v>
       </c>
       <c r="N120" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O120" t="s">
-        <v>1728</v>
+        <v>1748</v>
       </c>
       <c r="P120" t="s">
-        <v>1729</v>
+        <v>1749</v>
       </c>
       <c r="Q120" t="s">
-        <v>1730</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.25">
@@ -23762,10 +24091,10 @@
         <v>753</v>
       </c>
       <c r="F121" t="s">
-        <v>1274</v>
+        <v>1294</v>
       </c>
       <c r="G121" t="s">
-        <v>1197</v>
+        <v>1217</v>
       </c>
       <c r="J121" t="s">
         <v>38</v>
@@ -23780,16 +24109,16 @@
         <v>25</v>
       </c>
       <c r="N121" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O121" t="s">
-        <v>1731</v>
+        <v>1751</v>
       </c>
       <c r="P121" t="s">
-        <v>1732</v>
+        <v>1752</v>
       </c>
       <c r="Q121" t="s">
-        <v>1733</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.25">
@@ -23812,7 +24141,7 @@
         <v>1137</v>
       </c>
       <c r="G122" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J122" t="s">
         <v>38</v>
@@ -23827,16 +24156,16 @@
         <v>25</v>
       </c>
       <c r="N122" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O122" t="s">
-        <v>1734</v>
+        <v>1754</v>
       </c>
       <c r="P122" t="s">
-        <v>1735</v>
+        <v>1755</v>
       </c>
       <c r="Q122" t="s">
-        <v>1736</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.25">
@@ -23859,7 +24188,7 @@
         <v>1137</v>
       </c>
       <c r="G123" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J123" t="s">
         <v>38</v>
@@ -23874,16 +24203,16 @@
         <v>44</v>
       </c>
       <c r="N123" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O123" t="s">
-        <v>1737</v>
+        <v>1757</v>
       </c>
       <c r="P123" t="s">
-        <v>1738</v>
+        <v>1758</v>
       </c>
       <c r="Q123" t="s">
-        <v>1739</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.25">
@@ -23897,16 +24226,16 @@
         <v>32</v>
       </c>
       <c r="D124" t="s">
-        <v>1310</v>
+        <v>1330</v>
       </c>
       <c r="E124" t="s">
-        <v>1311</v>
+        <v>1331</v>
       </c>
       <c r="F124" t="s">
         <v>1079</v>
       </c>
       <c r="G124" t="s">
-        <v>1197</v>
+        <v>1217</v>
       </c>
       <c r="J124" t="s">
         <v>38</v>
@@ -23921,16 +24250,16 @@
         <v>25</v>
       </c>
       <c r="N124" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O124" t="s">
-        <v>1740</v>
+        <v>1760</v>
       </c>
       <c r="P124" t="s">
-        <v>1741</v>
+        <v>1761</v>
       </c>
       <c r="Q124" t="s">
-        <v>1742</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.25">
@@ -23944,7 +24273,7 @@
         <v>30</v>
       </c>
       <c r="D125" t="s">
-        <v>1743</v>
+        <v>1763</v>
       </c>
       <c r="E125" t="s">
         <v>753</v>
@@ -23953,7 +24282,7 @@
         <v>762</v>
       </c>
       <c r="G125" t="s">
-        <v>1197</v>
+        <v>1217</v>
       </c>
       <c r="J125" t="s">
         <v>38</v>
@@ -23968,16 +24297,16 @@
         <v>25</v>
       </c>
       <c r="N125" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O125" t="s">
-        <v>1744</v>
+        <v>1764</v>
       </c>
       <c r="P125" t="s">
-        <v>1745</v>
+        <v>1765</v>
       </c>
       <c r="Q125" t="s">
-        <v>1746</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.25">
@@ -23991,16 +24320,16 @@
         <v>5</v>
       </c>
       <c r="D126" t="s">
-        <v>1299</v>
+        <v>1319</v>
       </c>
       <c r="E126" t="s">
-        <v>1300</v>
+        <v>1320</v>
       </c>
       <c r="F126" t="s">
         <v>1086</v>
       </c>
       <c r="G126" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J126" t="s">
         <v>38</v>
@@ -24015,16 +24344,16 @@
         <v>25</v>
       </c>
       <c r="N126" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O126" t="s">
-        <v>1747</v>
+        <v>1767</v>
       </c>
       <c r="P126" t="s">
-        <v>1748</v>
+        <v>1768</v>
       </c>
       <c r="Q126" t="s">
-        <v>1749</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.25">
@@ -24038,16 +24367,16 @@
         <v>30</v>
       </c>
       <c r="D127" t="s">
-        <v>1304</v>
+        <v>1324</v>
       </c>
       <c r="E127" t="s">
-        <v>1305</v>
+        <v>1325</v>
       </c>
       <c r="F127" t="s">
-        <v>1306</v>
+        <v>1326</v>
       </c>
       <c r="G127" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J127" t="s">
         <v>38</v>
@@ -24062,16 +24391,16 @@
         <v>25</v>
       </c>
       <c r="N127" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O127" t="s">
-        <v>1750</v>
+        <v>1770</v>
       </c>
       <c r="P127" t="s">
-        <v>1751</v>
+        <v>1771</v>
       </c>
       <c r="Q127" t="s">
-        <v>1752</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.25">
@@ -24085,16 +24414,16 @@
         <v>40</v>
       </c>
       <c r="D128" t="s">
-        <v>1753</v>
+        <v>1773</v>
       </c>
       <c r="E128" t="s">
-        <v>1754</v>
+        <v>1774</v>
       </c>
       <c r="F128" t="s">
-        <v>1755</v>
+        <v>1775</v>
       </c>
       <c r="G128" t="s">
-        <v>1197</v>
+        <v>1217</v>
       </c>
       <c r="J128" t="s">
         <v>38</v>
@@ -24109,16 +24438,16 @@
         <v>25</v>
       </c>
       <c r="N128" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O128" t="s">
-        <v>1756</v>
+        <v>1776</v>
       </c>
       <c r="P128" t="s">
-        <v>1757</v>
+        <v>1777</v>
       </c>
       <c r="Q128" t="s">
-        <v>1758</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="129" spans="1:17" x14ac:dyDescent="0.25">
@@ -24132,16 +24461,16 @@
         <v>38</v>
       </c>
       <c r="D129" t="s">
-        <v>1759</v>
+        <v>1779</v>
       </c>
       <c r="E129" t="s">
         <v>480</v>
       </c>
       <c r="F129" t="s">
-        <v>1274</v>
+        <v>1294</v>
       </c>
       <c r="G129" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J129" t="s">
         <v>38</v>
@@ -24156,16 +24485,16 @@
         <v>25</v>
       </c>
       <c r="N129" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O129" t="s">
-        <v>1760</v>
+        <v>1780</v>
       </c>
       <c r="P129" t="s">
-        <v>1761</v>
+        <v>1781</v>
       </c>
       <c r="Q129" t="s">
-        <v>1762</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="130" spans="1:17" x14ac:dyDescent="0.25">
@@ -24179,16 +24508,16 @@
         <v>36</v>
       </c>
       <c r="D130" t="s">
-        <v>1763</v>
+        <v>1783</v>
       </c>
       <c r="E130" t="s">
         <v>480</v>
       </c>
       <c r="F130" t="s">
-        <v>1274</v>
+        <v>1294</v>
       </c>
       <c r="G130" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J130" t="s">
         <v>38</v>
@@ -24203,16 +24532,16 @@
         <v>25</v>
       </c>
       <c r="N130" t="s">
-        <v>1192</v>
+        <v>1212</v>
       </c>
       <c r="O130" t="s">
-        <v>1764</v>
+        <v>1784</v>
       </c>
       <c r="P130" t="s">
-        <v>1765</v>
+        <v>1785</v>
       </c>
       <c r="Q130" t="s">
-        <v>1766</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="131" spans="1:17" x14ac:dyDescent="0.25">
@@ -24229,13 +24558,13 @@
         <v>608</v>
       </c>
       <c r="E131" t="s">
-        <v>1767</v>
+        <v>1787</v>
       </c>
       <c r="F131" t="s">
-        <v>1768</v>
+        <v>1788</v>
       </c>
       <c r="G131" t="s">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="J131" t="s">
         <v>38</v>
@@ -24250,16 +24579,251 @@
         <v>25</v>
       </c>
       <c r="N131" t="s">
+        <v>1212</v>
+      </c>
+      <c r="O131" t="s">
+        <v>1789</v>
+      </c>
+      <c r="P131" t="s">
+        <v>1790</v>
+      </c>
+      <c r="Q131" t="s">
+        <v>1791</v>
+      </c>
+    </row>
+    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>17</v>
+      </c>
+      <c r="B132">
+        <v>30</v>
+      </c>
+      <c r="C132">
+        <v>45</v>
+      </c>
+      <c r="D132" t="s">
+        <v>1792</v>
+      </c>
+      <c r="E132" t="s">
+        <v>1793</v>
+      </c>
+      <c r="F132" t="s">
+        <v>1794</v>
+      </c>
+      <c r="G132" t="s">
+        <v>1211</v>
+      </c>
+      <c r="J132" t="s">
+        <v>38</v>
+      </c>
+      <c r="K132" t="s">
+        <v>70</v>
+      </c>
+      <c r="L132" t="s">
         <v>1192</v>
       </c>
-      <c r="O131" t="s">
-        <v>1769</v>
-      </c>
-      <c r="P131" t="s">
-        <v>1770</v>
-      </c>
-      <c r="Q131" t="s">
-        <v>1771</v>
+      <c r="M132" t="s">
+        <v>25</v>
+      </c>
+      <c r="N132" t="s">
+        <v>1212</v>
+      </c>
+      <c r="O132" t="s">
+        <v>1795</v>
+      </c>
+      <c r="P132" t="s">
+        <v>1796</v>
+      </c>
+      <c r="Q132" t="s">
+        <v>1797</v>
+      </c>
+    </row>
+    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>17</v>
+      </c>
+      <c r="B133">
+        <v>42</v>
+      </c>
+      <c r="C133">
+        <v>40</v>
+      </c>
+      <c r="D133" t="s">
+        <v>1798</v>
+      </c>
+      <c r="E133" t="s">
+        <v>1799</v>
+      </c>
+      <c r="F133" t="s">
+        <v>1137</v>
+      </c>
+      <c r="G133" t="s">
+        <v>1217</v>
+      </c>
+      <c r="J133" t="s">
+        <v>38</v>
+      </c>
+      <c r="K133" t="s">
+        <v>70</v>
+      </c>
+      <c r="L133" t="s">
+        <v>1192</v>
+      </c>
+      <c r="M133" t="s">
+        <v>25</v>
+      </c>
+      <c r="N133" t="s">
+        <v>1212</v>
+      </c>
+      <c r="O133" t="s">
+        <v>1800</v>
+      </c>
+      <c r="P133" t="s">
+        <v>1801</v>
+      </c>
+      <c r="Q133" t="s">
+        <v>1802</v>
+      </c>
+    </row>
+    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>17</v>
+      </c>
+      <c r="B134">
+        <v>42</v>
+      </c>
+      <c r="C134">
+        <v>40</v>
+      </c>
+      <c r="D134" t="s">
+        <v>1803</v>
+      </c>
+      <c r="E134" t="s">
+        <v>1799</v>
+      </c>
+      <c r="F134" t="s">
+        <v>1137</v>
+      </c>
+      <c r="G134" t="s">
+        <v>1217</v>
+      </c>
+      <c r="J134" t="s">
+        <v>38</v>
+      </c>
+      <c r="K134" t="s">
+        <v>70</v>
+      </c>
+      <c r="L134" t="s">
+        <v>1192</v>
+      </c>
+      <c r="M134" t="s">
+        <v>25</v>
+      </c>
+      <c r="N134" t="s">
+        <v>1212</v>
+      </c>
+      <c r="O134" t="s">
+        <v>1804</v>
+      </c>
+      <c r="P134" t="s">
+        <v>1805</v>
+      </c>
+      <c r="Q134" t="s">
+        <v>1806</v>
+      </c>
+    </row>
+    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>17</v>
+      </c>
+      <c r="B135">
+        <v>15</v>
+      </c>
+      <c r="C135">
+        <v>18</v>
+      </c>
+      <c r="D135" t="s">
+        <v>1559</v>
+      </c>
+      <c r="E135" t="s">
+        <v>1560</v>
+      </c>
+      <c r="F135" t="s">
+        <v>1070</v>
+      </c>
+      <c r="G135" t="s">
+        <v>1211</v>
+      </c>
+      <c r="J135" t="s">
+        <v>38</v>
+      </c>
+      <c r="K135" t="s">
+        <v>70</v>
+      </c>
+      <c r="L135" t="s">
+        <v>1192</v>
+      </c>
+      <c r="M135" t="s">
+        <v>25</v>
+      </c>
+      <c r="N135" t="s">
+        <v>1212</v>
+      </c>
+      <c r="O135" t="s">
+        <v>1807</v>
+      </c>
+      <c r="P135" t="s">
+        <v>1808</v>
+      </c>
+      <c r="Q135" t="s">
+        <v>1809</v>
+      </c>
+    </row>
+    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>17</v>
+      </c>
+      <c r="B136">
+        <v>5</v>
+      </c>
+      <c r="C136">
+        <v>3</v>
+      </c>
+      <c r="D136" t="s">
+        <v>1568</v>
+      </c>
+      <c r="E136" t="s">
+        <v>1560</v>
+      </c>
+      <c r="F136" t="s">
+        <v>1070</v>
+      </c>
+      <c r="G136" t="s">
+        <v>1211</v>
+      </c>
+      <c r="J136" t="s">
+        <v>38</v>
+      </c>
+      <c r="K136" t="s">
+        <v>70</v>
+      </c>
+      <c r="L136" t="s">
+        <v>1192</v>
+      </c>
+      <c r="M136" t="s">
+        <v>25</v>
+      </c>
+      <c r="N136" t="s">
+        <v>1212</v>
+      </c>
+      <c r="O136" t="s">
+        <v>1810</v>
+      </c>
+      <c r="P136" t="s">
+        <v>1811</v>
+      </c>
+      <c r="Q136" t="s">
+        <v>1812</v>
       </c>
     </row>
   </sheetData>

--- a/hunt/board.xlsx
+++ b/hunt/board.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6313" uniqueCount="2299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6339" uniqueCount="2307">
   <si>
     <t>Column</t>
   </si>
@@ -4091,6 +4091,18 @@
     <t>https://apply.workable.com/j/4C902EC8EC</t>
   </si>
   <si>
+    <t>2026-09-06T02:27:17.212Z</t>
+  </si>
+  <si>
+    <t>Role centers on owning DevOps strategy, reference architectures, reusable IaC modules and pipeline templates — directly matches candidate's CI/CD architecture and Azure DevOps/GitHub platform work | Fully remote US, matching the candidate's primary workplace preference | Mentoring/coaching and standards-setting scope aligns with the candidate's trusted-advisor and DevOps maturity assessment experience</t>
+  </si>
+  <si>
+    <t>Consultancy/services model across many client stacks likely expects strong AWS (and possibly GCP) depth, while candidate is Azure-primary | 'Lead DevOps Engineer' at a services firm may sit below the principal/architect scope the candidate is targeting, and hands-on Kubernetes/Terraform delivery depth may be tested heavily | No salary posted — services firms often land under the $180K floor for lead-level roles</t>
+  </si>
+  <si>
+    <t>https://himalayas.app/companies/particle41/jobs/lead-devops-engineer</t>
+  </si>
+  <si>
     <t>Delivery Solutions Architect - Communications, Media, Entertainment &amp; Games</t>
   </si>
   <si>
@@ -6909,6 +6921,18 @@
   </si>
   <si>
     <t>https://apply.workable.com/j/9B4B19236B</t>
+  </si>
+  <si>
+    <t>New York City, New York</t>
+  </si>
+  <si>
+    <t>Confirmed comp at $219,100 clears the $180K salary floor comfortably | Senior Solutions Architect title and customer-facing technical advisory model match the candidate's current Customer Engineer / trusted-advisor engagement style | Posting explicitly says candidates outside the listed NYC location will be considered, opening remote/flexible possibilities</t>
+  </si>
+  <si>
+    <t>Databricks SA roles demand deep data engineering/lakehouse expertise — Spark, Delta Lake, ML pipelines, SQL/Python data workloads — which is not evident in the candidate's DevOps/governance-centric profile | Typically AWS/Azure/GCP multi-cloud data platform depth expected; candidate's Azure DevOps/GHAS specialization is only tangentially relevant | Pre-sales SA role tied to consumption/quota targets and NYC-anchored, adding location and role-type friction</t>
+  </si>
+  <si>
+    <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8769750002</t>
   </si>
 </sst>
 </file>
@@ -7289,7 +7313,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q276"/>
+  <dimension ref="A1:Q277"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -21046,6 +21070,53 @@
         <v>1358</v>
       </c>
     </row>
+    <row r="277" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>17</v>
+      </c>
+      <c r="B277">
+        <v>68</v>
+      </c>
+      <c r="C277">
+        <v>72</v>
+      </c>
+      <c r="D277" t="s">
+        <v>291</v>
+      </c>
+      <c r="E277" t="s">
+        <v>114</v>
+      </c>
+      <c r="F277" t="s">
+        <v>20</v>
+      </c>
+      <c r="G277" t="s">
+        <v>21</v>
+      </c>
+      <c r="J277" t="s">
+        <v>22</v>
+      </c>
+      <c r="K277" t="s">
+        <v>23</v>
+      </c>
+      <c r="L277" t="s">
+        <v>1359</v>
+      </c>
+      <c r="M277" t="s">
+        <v>32</v>
+      </c>
+      <c r="N277" t="s">
+        <v>26</v>
+      </c>
+      <c r="O277" t="s">
+        <v>1360</v>
+      </c>
+      <c r="P277" t="s">
+        <v>1361</v>
+      </c>
+      <c r="Q277" t="s">
+        <v>1362</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:Q1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -21055,7 +21126,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q209"/>
+  <dimension ref="A1:Q210"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -21136,7 +21207,7 @@
         <v>52</v>
       </c>
       <c r="D2" t="s">
-        <v>1359</v>
+        <v>1363</v>
       </c>
       <c r="E2" t="s">
         <v>421</v>
@@ -21145,7 +21216,7 @@
         <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="H2">
         <v>180000</v>
@@ -21166,16 +21237,16 @@
         <v>25</v>
       </c>
       <c r="N2" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O2" t="s">
-        <v>1362</v>
+        <v>1366</v>
       </c>
       <c r="P2" t="s">
-        <v>1363</v>
+        <v>1367</v>
       </c>
       <c r="Q2" t="s">
-        <v>1364</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -21189,7 +21260,7 @@
         <v>55</v>
       </c>
       <c r="D3" t="s">
-        <v>1365</v>
+        <v>1369</v>
       </c>
       <c r="E3" t="s">
         <v>421</v>
@@ -21198,7 +21269,7 @@
         <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="H3">
         <v>180000</v>
@@ -21219,16 +21290,16 @@
         <v>25</v>
       </c>
       <c r="N3" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O3" t="s">
-        <v>1366</v>
+        <v>1370</v>
       </c>
       <c r="P3" t="s">
-        <v>1367</v>
+        <v>1371</v>
       </c>
       <c r="Q3" t="s">
-        <v>1368</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
@@ -21242,16 +21313,16 @@
         <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>1369</v>
+        <v>1373</v>
       </c>
       <c r="E4" t="s">
         <v>421</v>
       </c>
       <c r="F4" t="s">
-        <v>1370</v>
+        <v>1374</v>
       </c>
       <c r="G4" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="H4">
         <v>219100</v>
@@ -21272,16 +21343,16 @@
         <v>25</v>
       </c>
       <c r="N4" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O4" t="s">
-        <v>1371</v>
+        <v>1375</v>
       </c>
       <c r="P4" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="Q4" t="s">
-        <v>1373</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -21295,16 +21366,16 @@
         <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>1374</v>
+        <v>1378</v>
       </c>
       <c r="E5" t="s">
         <v>421</v>
       </c>
       <c r="F5" t="s">
-        <v>1375</v>
+        <v>1379</v>
       </c>
       <c r="G5" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="H5">
         <v>180000</v>
@@ -21325,16 +21396,16 @@
         <v>25</v>
       </c>
       <c r="N5" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O5" t="s">
-        <v>1377</v>
+        <v>1381</v>
       </c>
       <c r="P5" t="s">
-        <v>1378</v>
+        <v>1382</v>
       </c>
       <c r="Q5" t="s">
-        <v>1379</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -21348,7 +21419,7 @@
         <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>1380</v>
+        <v>1384</v>
       </c>
       <c r="E6" t="s">
         <v>421</v>
@@ -21357,7 +21428,7 @@
         <v>20</v>
       </c>
       <c r="G6" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="H6">
         <v>219100</v>
@@ -21378,16 +21449,16 @@
         <v>38</v>
       </c>
       <c r="N6" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O6" t="s">
-        <v>1381</v>
+        <v>1385</v>
       </c>
       <c r="P6" t="s">
-        <v>1382</v>
+        <v>1386</v>
       </c>
       <c r="Q6" t="s">
-        <v>1383</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -21401,7 +21472,7 @@
         <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>1384</v>
+        <v>1388</v>
       </c>
       <c r="E7" t="s">
         <v>421</v>
@@ -21410,7 +21481,7 @@
         <v>20</v>
       </c>
       <c r="G7" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="H7">
         <v>219100</v>
@@ -21431,16 +21502,16 @@
         <v>25</v>
       </c>
       <c r="N7" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O7" t="s">
-        <v>1385</v>
+        <v>1389</v>
       </c>
       <c r="P7" t="s">
-        <v>1386</v>
+        <v>1390</v>
       </c>
       <c r="Q7" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -21454,16 +21525,16 @@
         <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>1388</v>
+        <v>1392</v>
       </c>
       <c r="E8" t="s">
         <v>421</v>
       </c>
       <c r="F8" t="s">
-        <v>1389</v>
+        <v>1393</v>
       </c>
       <c r="G8" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J8" t="s">
         <v>22</v>
@@ -21478,16 +21549,16 @@
         <v>38</v>
       </c>
       <c r="N8" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O8" t="s">
-        <v>1390</v>
+        <v>1394</v>
       </c>
       <c r="P8" t="s">
-        <v>1391</v>
+        <v>1395</v>
       </c>
       <c r="Q8" t="s">
-        <v>1392</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -21501,16 +21572,16 @@
         <v>58</v>
       </c>
       <c r="D9" t="s">
-        <v>1393</v>
+        <v>1397</v>
       </c>
       <c r="E9" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="F9" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="G9" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="H9">
         <v>257000</v>
@@ -21531,16 +21602,16 @@
         <v>25</v>
       </c>
       <c r="N9" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O9" t="s">
-        <v>1396</v>
+        <v>1400</v>
       </c>
       <c r="P9" t="s">
-        <v>1397</v>
+        <v>1401</v>
       </c>
       <c r="Q9" t="s">
-        <v>1398</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -21557,13 +21628,13 @@
         <v>145</v>
       </c>
       <c r="E10" t="s">
-        <v>1399</v>
+        <v>1403</v>
       </c>
       <c r="F10" t="s">
-        <v>1400</v>
+        <v>1404</v>
       </c>
       <c r="G10" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="H10">
         <v>200000</v>
@@ -21584,16 +21655,16 @@
         <v>38</v>
       </c>
       <c r="N10" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O10" t="s">
-        <v>1401</v>
+        <v>1405</v>
       </c>
       <c r="P10" t="s">
-        <v>1402</v>
+        <v>1406</v>
       </c>
       <c r="Q10" t="s">
-        <v>1403</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -21607,16 +21678,16 @@
         <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>1404</v>
+        <v>1408</v>
       </c>
       <c r="E11" t="s">
         <v>698</v>
       </c>
       <c r="F11" t="s">
-        <v>1405</v>
+        <v>1409</v>
       </c>
       <c r="G11" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J11" t="s">
         <v>22</v>
@@ -21631,16 +21702,16 @@
         <v>38</v>
       </c>
       <c r="N11" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O11" t="s">
-        <v>1406</v>
+        <v>1410</v>
       </c>
       <c r="P11" t="s">
-        <v>1407</v>
+        <v>1411</v>
       </c>
       <c r="Q11" t="s">
-        <v>1408</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -21660,10 +21731,10 @@
         <v>698</v>
       </c>
       <c r="F12" t="s">
-        <v>1409</v>
+        <v>1413</v>
       </c>
       <c r="G12" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J12" t="s">
         <v>22</v>
@@ -21678,16 +21749,16 @@
         <v>38</v>
       </c>
       <c r="N12" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O12" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="P12" t="s">
-        <v>1411</v>
+        <v>1415</v>
       </c>
       <c r="Q12" t="s">
-        <v>1412</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
@@ -21701,16 +21772,16 @@
         <v>15</v>
       </c>
       <c r="D13" t="s">
-        <v>1413</v>
+        <v>1417</v>
       </c>
       <c r="E13" t="s">
         <v>698</v>
       </c>
       <c r="F13" t="s">
-        <v>1414</v>
+        <v>1418</v>
       </c>
       <c r="G13" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="H13">
         <v>500000</v>
@@ -21731,16 +21802,16 @@
         <v>38</v>
       </c>
       <c r="N13" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O13" t="s">
-        <v>1415</v>
+        <v>1419</v>
       </c>
       <c r="P13" t="s">
-        <v>1416</v>
+        <v>1420</v>
       </c>
       <c r="Q13" t="s">
-        <v>1417</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
@@ -21754,16 +21825,16 @@
         <v>18</v>
       </c>
       <c r="D14" t="s">
-        <v>1418</v>
+        <v>1422</v>
       </c>
       <c r="E14" t="s">
         <v>478</v>
       </c>
       <c r="F14" t="s">
-        <v>1419</v>
+        <v>1423</v>
       </c>
       <c r="G14" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="H14">
         <v>274456</v>
@@ -21784,16 +21855,16 @@
         <v>38</v>
       </c>
       <c r="N14" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O14" t="s">
-        <v>1420</v>
+        <v>1424</v>
       </c>
       <c r="P14" t="s">
-        <v>1421</v>
+        <v>1425</v>
       </c>
       <c r="Q14" t="s">
-        <v>1422</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -21807,16 +21878,16 @@
         <v>30</v>
       </c>
       <c r="D15" t="s">
-        <v>1423</v>
+        <v>1427</v>
       </c>
       <c r="E15" t="s">
         <v>478</v>
       </c>
       <c r="F15" t="s">
-        <v>1424</v>
+        <v>1428</v>
       </c>
       <c r="G15" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J15" t="s">
         <v>22</v>
@@ -21831,16 +21902,16 @@
         <v>38</v>
       </c>
       <c r="N15" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O15" t="s">
-        <v>1425</v>
+        <v>1429</v>
       </c>
       <c r="P15" t="s">
-        <v>1426</v>
+        <v>1430</v>
       </c>
       <c r="Q15" t="s">
-        <v>1427</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
@@ -21854,16 +21925,16 @@
         <v>22</v>
       </c>
       <c r="D16" t="s">
-        <v>1428</v>
+        <v>1432</v>
       </c>
       <c r="E16" t="s">
         <v>478</v>
       </c>
       <c r="F16" t="s">
-        <v>1429</v>
+        <v>1433</v>
       </c>
       <c r="G16" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J16" t="s">
         <v>22</v>
@@ -21878,16 +21949,16 @@
         <v>38</v>
       </c>
       <c r="N16" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O16" t="s">
-        <v>1430</v>
+        <v>1434</v>
       </c>
       <c r="P16" t="s">
-        <v>1431</v>
+        <v>1435</v>
       </c>
       <c r="Q16" t="s">
-        <v>1432</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
@@ -21901,16 +21972,16 @@
         <v>48</v>
       </c>
       <c r="D17" t="s">
-        <v>1433</v>
+        <v>1437</v>
       </c>
       <c r="E17" t="s">
         <v>478</v>
       </c>
       <c r="F17" t="s">
-        <v>1434</v>
+        <v>1438</v>
       </c>
       <c r="G17" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J17" t="s">
         <v>22</v>
@@ -21925,16 +21996,16 @@
         <v>25</v>
       </c>
       <c r="N17" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O17" t="s">
-        <v>1435</v>
+        <v>1439</v>
       </c>
       <c r="P17" t="s">
-        <v>1436</v>
+        <v>1440</v>
       </c>
       <c r="Q17" t="s">
-        <v>1437</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
@@ -21948,16 +22019,16 @@
         <v>25</v>
       </c>
       <c r="D18" t="s">
-        <v>1438</v>
+        <v>1442</v>
       </c>
       <c r="E18" t="s">
         <v>478</v>
       </c>
       <c r="F18" t="s">
-        <v>1439</v>
+        <v>1443</v>
       </c>
       <c r="G18" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J18" t="s">
         <v>22</v>
@@ -21972,16 +22043,16 @@
         <v>38</v>
       </c>
       <c r="N18" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O18" t="s">
-        <v>1440</v>
+        <v>1444</v>
       </c>
       <c r="P18" t="s">
-        <v>1441</v>
+        <v>1445</v>
       </c>
       <c r="Q18" t="s">
-        <v>1442</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -21995,16 +22066,16 @@
         <v>40</v>
       </c>
       <c r="D19" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="E19" t="s">
         <v>478</v>
       </c>
       <c r="F19" t="s">
-        <v>1444</v>
+        <v>1448</v>
       </c>
       <c r="G19" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J19" t="s">
         <v>22</v>
@@ -22019,16 +22090,16 @@
         <v>38</v>
       </c>
       <c r="N19" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O19" t="s">
-        <v>1445</v>
+        <v>1449</v>
       </c>
       <c r="P19" t="s">
-        <v>1446</v>
+        <v>1450</v>
       </c>
       <c r="Q19" t="s">
-        <v>1447</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -22042,16 +22113,16 @@
         <v>70</v>
       </c>
       <c r="D20" t="s">
-        <v>1448</v>
+        <v>1452</v>
       </c>
       <c r="E20" t="s">
-        <v>1449</v>
+        <v>1453</v>
       </c>
       <c r="F20" t="s">
-        <v>1450</v>
+        <v>1454</v>
       </c>
       <c r="G20" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J20" t="s">
         <v>22</v>
@@ -22066,16 +22137,16 @@
         <v>38</v>
       </c>
       <c r="N20" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O20" t="s">
-        <v>1451</v>
+        <v>1455</v>
       </c>
       <c r="P20" t="s">
-        <v>1452</v>
+        <v>1456</v>
       </c>
       <c r="Q20" t="s">
-        <v>1453</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
@@ -22089,16 +22160,16 @@
         <v>58</v>
       </c>
       <c r="D21" t="s">
-        <v>1454</v>
+        <v>1458</v>
       </c>
       <c r="E21" t="s">
-        <v>1455</v>
+        <v>1459</v>
       </c>
       <c r="F21" t="s">
-        <v>1439</v>
+        <v>1443</v>
       </c>
       <c r="G21" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J21" t="s">
         <v>22</v>
@@ -22113,16 +22184,16 @@
         <v>38</v>
       </c>
       <c r="N21" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O21" t="s">
-        <v>1456</v>
+        <v>1460</v>
       </c>
       <c r="P21" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
       <c r="Q21" t="s">
-        <v>1458</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -22136,16 +22207,16 @@
         <v>32</v>
       </c>
       <c r="D22" t="s">
-        <v>1459</v>
+        <v>1463</v>
       </c>
       <c r="E22" t="s">
-        <v>1460</v>
+        <v>1464</v>
       </c>
       <c r="F22" t="s">
         <v>1085</v>
       </c>
       <c r="G22" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J22" t="s">
         <v>22</v>
@@ -22160,16 +22231,16 @@
         <v>38</v>
       </c>
       <c r="N22" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O22" t="s">
-        <v>1461</v>
+        <v>1465</v>
       </c>
       <c r="P22" t="s">
-        <v>1462</v>
+        <v>1466</v>
       </c>
       <c r="Q22" t="s">
-        <v>1463</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
@@ -22183,16 +22254,16 @@
         <v>4</v>
       </c>
       <c r="D23" t="s">
-        <v>1464</v>
+        <v>1468</v>
       </c>
       <c r="E23" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F23" t="s">
         <v>1032</v>
       </c>
       <c r="G23" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J23" t="s">
         <v>22</v>
@@ -22207,16 +22278,16 @@
         <v>38</v>
       </c>
       <c r="N23" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O23" t="s">
-        <v>1466</v>
+        <v>1470</v>
       </c>
       <c r="P23" t="s">
-        <v>1467</v>
+        <v>1471</v>
       </c>
       <c r="Q23" t="s">
-        <v>1468</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
@@ -22230,16 +22301,16 @@
         <v>25</v>
       </c>
       <c r="D24" t="s">
-        <v>1469</v>
+        <v>1473</v>
       </c>
       <c r="E24" t="s">
-        <v>1470</v>
+        <v>1474</v>
       </c>
       <c r="F24" t="s">
-        <v>1471</v>
+        <v>1475</v>
       </c>
       <c r="G24" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J24" t="s">
         <v>22</v>
@@ -22254,16 +22325,16 @@
         <v>38</v>
       </c>
       <c r="N24" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O24" t="s">
-        <v>1472</v>
+        <v>1476</v>
       </c>
       <c r="P24" t="s">
-        <v>1473</v>
+        <v>1477</v>
       </c>
       <c r="Q24" t="s">
-        <v>1474</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
@@ -22277,16 +22348,16 @@
         <v>30</v>
       </c>
       <c r="D25" t="s">
-        <v>1475</v>
+        <v>1479</v>
       </c>
       <c r="E25" t="s">
-        <v>1476</v>
+        <v>1480</v>
       </c>
       <c r="F25" t="s">
         <v>1025</v>
       </c>
       <c r="G25" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J25" t="s">
         <v>22</v>
@@ -22301,16 +22372,16 @@
         <v>38</v>
       </c>
       <c r="N25" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O25" t="s">
-        <v>1477</v>
+        <v>1481</v>
       </c>
       <c r="P25" t="s">
-        <v>1478</v>
+        <v>1482</v>
       </c>
       <c r="Q25" t="s">
-        <v>1479</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
@@ -22324,16 +22395,16 @@
         <v>52</v>
       </c>
       <c r="D26" t="s">
-        <v>1480</v>
+        <v>1484</v>
       </c>
       <c r="E26" t="s">
         <v>421</v>
       </c>
       <c r="F26" t="s">
-        <v>1481</v>
+        <v>1485</v>
       </c>
       <c r="G26" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="H26">
         <v>180000</v>
@@ -22354,16 +22425,16 @@
         <v>25</v>
       </c>
       <c r="N26" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O26" t="s">
-        <v>1482</v>
+        <v>1486</v>
       </c>
       <c r="P26" t="s">
-        <v>1483</v>
+        <v>1487</v>
       </c>
       <c r="Q26" t="s">
-        <v>1484</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
@@ -22377,7 +22448,7 @@
         <v>50</v>
       </c>
       <c r="D27" t="s">
-        <v>1485</v>
+        <v>1489</v>
       </c>
       <c r="E27" t="s">
         <v>421</v>
@@ -22386,7 +22457,7 @@
         <v>20</v>
       </c>
       <c r="G27" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="H27">
         <v>180000</v>
@@ -22407,16 +22478,16 @@
         <v>25</v>
       </c>
       <c r="N27" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O27" t="s">
-        <v>1486</v>
+        <v>1490</v>
       </c>
       <c r="P27" t="s">
-        <v>1487</v>
+        <v>1491</v>
       </c>
       <c r="Q27" t="s">
-        <v>1488</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
@@ -22430,7 +22501,7 @@
         <v>46</v>
       </c>
       <c r="D28" t="s">
-        <v>1489</v>
+        <v>1493</v>
       </c>
       <c r="E28" t="s">
         <v>421</v>
@@ -22439,7 +22510,7 @@
         <v>20</v>
       </c>
       <c r="G28" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="H28">
         <v>180000</v>
@@ -22460,16 +22531,16 @@
         <v>25</v>
       </c>
       <c r="N28" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O28" t="s">
-        <v>1490</v>
+        <v>1494</v>
       </c>
       <c r="P28" t="s">
-        <v>1491</v>
+        <v>1495</v>
       </c>
       <c r="Q28" t="s">
-        <v>1492</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
@@ -22483,7 +22554,7 @@
         <v>38</v>
       </c>
       <c r="D29" t="s">
-        <v>1493</v>
+        <v>1497</v>
       </c>
       <c r="E29" t="s">
         <v>421</v>
@@ -22492,7 +22563,7 @@
         <v>20</v>
       </c>
       <c r="G29" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="H29">
         <v>217800</v>
@@ -22513,16 +22584,16 @@
         <v>38</v>
       </c>
       <c r="N29" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O29" t="s">
-        <v>1494</v>
+        <v>1498</v>
       </c>
       <c r="P29" t="s">
-        <v>1495</v>
+        <v>1499</v>
       </c>
       <c r="Q29" t="s">
-        <v>1496</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
@@ -22542,10 +22613,10 @@
         <v>421</v>
       </c>
       <c r="F30" t="s">
-        <v>1497</v>
+        <v>1501</v>
       </c>
       <c r="G30" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="H30">
         <v>180000</v>
@@ -22566,16 +22637,16 @@
         <v>25</v>
       </c>
       <c r="N30" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O30" t="s">
-        <v>1498</v>
+        <v>1502</v>
       </c>
       <c r="P30" t="s">
-        <v>1499</v>
+        <v>1503</v>
       </c>
       <c r="Q30" t="s">
-        <v>1500</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
@@ -22589,16 +22660,16 @@
         <v>45</v>
       </c>
       <c r="D31" t="s">
-        <v>1501</v>
+        <v>1505</v>
       </c>
       <c r="E31" t="s">
         <v>421</v>
       </c>
       <c r="F31" t="s">
-        <v>1502</v>
+        <v>1506</v>
       </c>
       <c r="G31" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="H31">
         <v>219100</v>
@@ -22619,16 +22690,16 @@
         <v>25</v>
       </c>
       <c r="N31" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O31" t="s">
-        <v>1503</v>
+        <v>1507</v>
       </c>
       <c r="P31" t="s">
-        <v>1504</v>
+        <v>1508</v>
       </c>
       <c r="Q31" t="s">
-        <v>1505</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
@@ -22642,16 +22713,16 @@
         <v>42</v>
       </c>
       <c r="D32" t="s">
-        <v>1506</v>
+        <v>1510</v>
       </c>
       <c r="E32" t="s">
         <v>421</v>
       </c>
       <c r="F32" t="s">
-        <v>1507</v>
+        <v>1511</v>
       </c>
       <c r="G32" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="H32">
         <v>180000</v>
@@ -22672,16 +22743,16 @@
         <v>25</v>
       </c>
       <c r="N32" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O32" t="s">
-        <v>1508</v>
+        <v>1512</v>
       </c>
       <c r="P32" t="s">
-        <v>1509</v>
+        <v>1513</v>
       </c>
       <c r="Q32" t="s">
-        <v>1510</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
@@ -22695,7 +22766,7 @@
         <v>32</v>
       </c>
       <c r="D33" t="s">
-        <v>1511</v>
+        <v>1515</v>
       </c>
       <c r="E33" t="s">
         <v>421</v>
@@ -22704,7 +22775,7 @@
         <v>20</v>
       </c>
       <c r="G33" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="H33">
         <v>219100</v>
@@ -22725,16 +22796,16 @@
         <v>38</v>
       </c>
       <c r="N33" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O33" t="s">
-        <v>1512</v>
+        <v>1516</v>
       </c>
       <c r="P33" t="s">
-        <v>1513</v>
+        <v>1517</v>
       </c>
       <c r="Q33" t="s">
-        <v>1514</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
@@ -22748,7 +22819,7 @@
         <v>35</v>
       </c>
       <c r="D34" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="E34" t="s">
         <v>421</v>
@@ -22757,7 +22828,7 @@
         <v>20</v>
       </c>
       <c r="G34" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="H34">
         <v>219100</v>
@@ -22778,16 +22849,16 @@
         <v>38</v>
       </c>
       <c r="N34" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O34" t="s">
-        <v>1516</v>
+        <v>1520</v>
       </c>
       <c r="P34" t="s">
-        <v>1517</v>
+        <v>1521</v>
       </c>
       <c r="Q34" t="s">
-        <v>1518</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
@@ -22801,16 +22872,16 @@
         <v>40</v>
       </c>
       <c r="D35" t="s">
-        <v>1519</v>
+        <v>1523</v>
       </c>
       <c r="E35" t="s">
         <v>421</v>
       </c>
       <c r="F35" t="s">
-        <v>1520</v>
+        <v>1524</v>
       </c>
       <c r="G35" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="H35">
         <v>219100</v>
@@ -22831,16 +22902,16 @@
         <v>25</v>
       </c>
       <c r="N35" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O35" t="s">
-        <v>1521</v>
+        <v>1525</v>
       </c>
       <c r="P35" t="s">
-        <v>1522</v>
+        <v>1526</v>
       </c>
       <c r="Q35" t="s">
-        <v>1523</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
@@ -22854,7 +22925,7 @@
         <v>38</v>
       </c>
       <c r="D36" t="s">
-        <v>1524</v>
+        <v>1528</v>
       </c>
       <c r="E36" t="s">
         <v>421</v>
@@ -22863,7 +22934,7 @@
         <v>437</v>
       </c>
       <c r="G36" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="H36">
         <v>219100</v>
@@ -22884,16 +22955,16 @@
         <v>38</v>
       </c>
       <c r="N36" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O36" t="s">
-        <v>1525</v>
+        <v>1529</v>
       </c>
       <c r="P36" t="s">
-        <v>1526</v>
+        <v>1530</v>
       </c>
       <c r="Q36" t="s">
-        <v>1527</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
@@ -22907,7 +22978,7 @@
         <v>40</v>
       </c>
       <c r="D37" t="s">
-        <v>1528</v>
+        <v>1532</v>
       </c>
       <c r="E37" t="s">
         <v>421</v>
@@ -22916,7 +22987,7 @@
         <v>20</v>
       </c>
       <c r="G37" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="H37">
         <v>219100</v>
@@ -22937,16 +23008,16 @@
         <v>25</v>
       </c>
       <c r="N37" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O37" t="s">
-        <v>1529</v>
+        <v>1533</v>
       </c>
       <c r="P37" t="s">
-        <v>1530</v>
+        <v>1534</v>
       </c>
       <c r="Q37" t="s">
-        <v>1531</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
@@ -22960,16 +23031,16 @@
         <v>33</v>
       </c>
       <c r="D38" t="s">
-        <v>1532</v>
+        <v>1536</v>
       </c>
       <c r="E38" t="s">
         <v>421</v>
       </c>
       <c r="F38" t="s">
-        <v>1533</v>
+        <v>1537</v>
       </c>
       <c r="G38" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="H38">
         <v>219100</v>
@@ -22990,16 +23061,16 @@
         <v>38</v>
       </c>
       <c r="N38" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O38" t="s">
-        <v>1534</v>
+        <v>1538</v>
       </c>
       <c r="P38" t="s">
-        <v>1535</v>
+        <v>1539</v>
       </c>
       <c r="Q38" t="s">
-        <v>1536</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
@@ -23013,16 +23084,16 @@
         <v>48</v>
       </c>
       <c r="D39" t="s">
-        <v>1537</v>
+        <v>1541</v>
       </c>
       <c r="E39" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="F39" t="s">
-        <v>1538</v>
+        <v>1542</v>
       </c>
       <c r="G39" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J39" t="s">
         <v>22</v>
@@ -23037,16 +23108,16 @@
         <v>25</v>
       </c>
       <c r="N39" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O39" t="s">
-        <v>1539</v>
+        <v>1543</v>
       </c>
       <c r="P39" t="s">
-        <v>1540</v>
+        <v>1544</v>
       </c>
       <c r="Q39" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
@@ -23060,16 +23131,16 @@
         <v>40</v>
       </c>
       <c r="D40" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
       <c r="E40" t="s">
-        <v>1399</v>
+        <v>1403</v>
       </c>
       <c r="F40" t="s">
-        <v>1543</v>
+        <v>1547</v>
       </c>
       <c r="G40" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="H40">
         <v>184200</v>
@@ -23090,16 +23161,16 @@
         <v>25</v>
       </c>
       <c r="N40" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O40" t="s">
-        <v>1544</v>
+        <v>1548</v>
       </c>
       <c r="P40" t="s">
-        <v>1545</v>
+        <v>1549</v>
       </c>
       <c r="Q40" t="s">
-        <v>1546</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
@@ -23116,13 +23187,13 @@
         <v>1343</v>
       </c>
       <c r="E41" t="s">
-        <v>1399</v>
+        <v>1403</v>
       </c>
       <c r="F41" t="s">
-        <v>1547</v>
+        <v>1551</v>
       </c>
       <c r="G41" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="H41">
         <v>200000</v>
@@ -23143,16 +23214,16 @@
         <v>38</v>
       </c>
       <c r="N41" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O41" t="s">
-        <v>1548</v>
+        <v>1552</v>
       </c>
       <c r="P41" t="s">
-        <v>1549</v>
+        <v>1553</v>
       </c>
       <c r="Q41" t="s">
-        <v>1550</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
@@ -23166,7 +23237,7 @@
         <v>30</v>
       </c>
       <c r="D42" t="s">
-        <v>1551</v>
+        <v>1555</v>
       </c>
       <c r="E42" t="s">
         <v>698</v>
@@ -23175,7 +23246,7 @@
         <v>707</v>
       </c>
       <c r="G42" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J42" t="s">
         <v>22</v>
@@ -23190,16 +23261,16 @@
         <v>38</v>
       </c>
       <c r="N42" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O42" t="s">
-        <v>1552</v>
+        <v>1556</v>
       </c>
       <c r="P42" t="s">
-        <v>1553</v>
+        <v>1557</v>
       </c>
       <c r="Q42" t="s">
-        <v>1554</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
@@ -23219,10 +23290,10 @@
         <v>698</v>
       </c>
       <c r="F43" t="s">
-        <v>1409</v>
+        <v>1413</v>
       </c>
       <c r="G43" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J43" t="s">
         <v>22</v>
@@ -23237,16 +23308,16 @@
         <v>38</v>
       </c>
       <c r="N43" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O43" t="s">
-        <v>1555</v>
+        <v>1559</v>
       </c>
       <c r="P43" t="s">
-        <v>1556</v>
+        <v>1560</v>
       </c>
       <c r="Q43" t="s">
-        <v>1557</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
@@ -23260,7 +23331,7 @@
         <v>32</v>
       </c>
       <c r="D44" t="s">
-        <v>1558</v>
+        <v>1562</v>
       </c>
       <c r="E44" t="s">
         <v>698</v>
@@ -23269,7 +23340,7 @@
         <v>707</v>
       </c>
       <c r="G44" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J44" t="s">
         <v>22</v>
@@ -23284,16 +23355,16 @@
         <v>38</v>
       </c>
       <c r="N44" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O44" t="s">
-        <v>1559</v>
+        <v>1563</v>
       </c>
       <c r="P44" t="s">
-        <v>1560</v>
+        <v>1564</v>
       </c>
       <c r="Q44" t="s">
-        <v>1561</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
@@ -23307,16 +23378,16 @@
         <v>45</v>
       </c>
       <c r="D45" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="E45" t="s">
         <v>478</v>
       </c>
       <c r="F45" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="G45" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J45" t="s">
         <v>22</v>
@@ -23331,16 +23402,16 @@
         <v>25</v>
       </c>
       <c r="N45" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O45" t="s">
-        <v>1564</v>
+        <v>1568</v>
       </c>
       <c r="P45" t="s">
-        <v>1565</v>
+        <v>1569</v>
       </c>
       <c r="Q45" t="s">
-        <v>1566</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
@@ -23354,16 +23425,16 @@
         <v>35</v>
       </c>
       <c r="D46" t="s">
-        <v>1567</v>
+        <v>1571</v>
       </c>
       <c r="E46" t="s">
         <v>478</v>
       </c>
       <c r="F46" t="s">
-        <v>1568</v>
+        <v>1572</v>
       </c>
       <c r="G46" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J46" t="s">
         <v>22</v>
@@ -23378,16 +23449,16 @@
         <v>38</v>
       </c>
       <c r="N46" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O46" t="s">
-        <v>1569</v>
+        <v>1573</v>
       </c>
       <c r="P46" t="s">
-        <v>1570</v>
+        <v>1574</v>
       </c>
       <c r="Q46" t="s">
-        <v>1571</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
@@ -23401,7 +23472,7 @@
         <v>35</v>
       </c>
       <c r="D47" t="s">
-        <v>1572</v>
+        <v>1576</v>
       </c>
       <c r="E47" t="s">
         <v>478</v>
@@ -23410,7 +23481,7 @@
         <v>507</v>
       </c>
       <c r="G47" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J47" t="s">
         <v>22</v>
@@ -23425,16 +23496,16 @@
         <v>38</v>
       </c>
       <c r="N47" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O47" t="s">
-        <v>1573</v>
+        <v>1577</v>
       </c>
       <c r="P47" t="s">
-        <v>1574</v>
+        <v>1578</v>
       </c>
       <c r="Q47" t="s">
-        <v>1575</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
@@ -23448,16 +23519,16 @@
         <v>15</v>
       </c>
       <c r="D48" t="s">
-        <v>1576</v>
+        <v>1580</v>
       </c>
       <c r="E48" t="s">
         <v>478</v>
       </c>
       <c r="F48" t="s">
-        <v>1577</v>
+        <v>1581</v>
       </c>
       <c r="G48" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J48" t="s">
         <v>22</v>
@@ -23472,16 +23543,16 @@
         <v>38</v>
       </c>
       <c r="N48" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O48" t="s">
-        <v>1578</v>
+        <v>1582</v>
       </c>
       <c r="P48" t="s">
-        <v>1579</v>
+        <v>1583</v>
       </c>
       <c r="Q48" t="s">
-        <v>1580</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
@@ -23495,16 +23566,16 @@
         <v>25</v>
       </c>
       <c r="D49" t="s">
-        <v>1581</v>
+        <v>1585</v>
       </c>
       <c r="E49" t="s">
         <v>478</v>
       </c>
       <c r="F49" t="s">
-        <v>1582</v>
+        <v>1586</v>
       </c>
       <c r="G49" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J49" t="s">
         <v>22</v>
@@ -23519,16 +23590,16 @@
         <v>38</v>
       </c>
       <c r="N49" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O49" t="s">
-        <v>1583</v>
+        <v>1587</v>
       </c>
       <c r="P49" t="s">
-        <v>1584</v>
+        <v>1588</v>
       </c>
       <c r="Q49" t="s">
-        <v>1585</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
@@ -23542,16 +23613,16 @@
         <v>30</v>
       </c>
       <c r="D50" t="s">
-        <v>1586</v>
+        <v>1590</v>
       </c>
       <c r="E50" t="s">
         <v>478</v>
       </c>
       <c r="F50" t="s">
-        <v>1587</v>
+        <v>1591</v>
       </c>
       <c r="G50" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J50" t="s">
         <v>22</v>
@@ -23566,16 +23637,16 @@
         <v>38</v>
       </c>
       <c r="N50" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O50" t="s">
-        <v>1588</v>
+        <v>1592</v>
       </c>
       <c r="P50" t="s">
-        <v>1589</v>
+        <v>1593</v>
       </c>
       <c r="Q50" t="s">
-        <v>1590</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
@@ -23595,10 +23666,10 @@
         <v>421</v>
       </c>
       <c r="F51" t="s">
-        <v>1547</v>
+        <v>1551</v>
       </c>
       <c r="G51" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J51" t="s">
         <v>22</v>
@@ -23613,16 +23684,16 @@
         <v>38</v>
       </c>
       <c r="N51" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O51" t="s">
-        <v>1591</v>
+        <v>1595</v>
       </c>
       <c r="P51" t="s">
-        <v>1592</v>
+        <v>1596</v>
       </c>
       <c r="Q51" t="s">
-        <v>1593</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
@@ -23642,10 +23713,10 @@
         <v>421</v>
       </c>
       <c r="F52" t="s">
-        <v>1594</v>
+        <v>1598</v>
       </c>
       <c r="G52" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J52" t="s">
         <v>22</v>
@@ -23660,16 +23731,16 @@
         <v>25</v>
       </c>
       <c r="N52" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O52" t="s">
-        <v>1595</v>
+        <v>1599</v>
       </c>
       <c r="P52" t="s">
-        <v>1596</v>
+        <v>1600</v>
       </c>
       <c r="Q52" t="s">
-        <v>1597</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
@@ -23692,7 +23763,7 @@
         <v>764</v>
       </c>
       <c r="G53" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="H53">
         <v>180000</v>
@@ -23713,16 +23784,16 @@
         <v>38</v>
       </c>
       <c r="N53" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O53" t="s">
-        <v>1598</v>
+        <v>1602</v>
       </c>
       <c r="P53" t="s">
-        <v>1599</v>
+        <v>1603</v>
       </c>
       <c r="Q53" t="s">
-        <v>1600</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
@@ -23742,10 +23813,10 @@
         <v>421</v>
       </c>
       <c r="F54" t="s">
-        <v>1601</v>
+        <v>1605</v>
       </c>
       <c r="G54" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="H54">
         <v>180000</v>
@@ -23766,16 +23837,16 @@
         <v>38</v>
       </c>
       <c r="N54" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O54" t="s">
-        <v>1602</v>
+        <v>1606</v>
       </c>
       <c r="P54" t="s">
-        <v>1603</v>
+        <v>1607</v>
       </c>
       <c r="Q54" t="s">
-        <v>1604</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
@@ -23789,16 +23860,16 @@
         <v>20</v>
       </c>
       <c r="D55" t="s">
-        <v>1605</v>
+        <v>1609</v>
       </c>
       <c r="E55" t="s">
         <v>811</v>
       </c>
       <c r="F55" t="s">
-        <v>1606</v>
+        <v>1610</v>
       </c>
       <c r="G55" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J55" t="s">
         <v>22</v>
@@ -23813,16 +23884,16 @@
         <v>38</v>
       </c>
       <c r="N55" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O55" t="s">
-        <v>1607</v>
+        <v>1611</v>
       </c>
       <c r="P55" t="s">
-        <v>1608</v>
+        <v>1612</v>
       </c>
       <c r="Q55" t="s">
-        <v>1609</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
@@ -23836,7 +23907,7 @@
         <v>50</v>
       </c>
       <c r="D56" t="s">
-        <v>1610</v>
+        <v>1614</v>
       </c>
       <c r="E56" t="s">
         <v>811</v>
@@ -23845,7 +23916,7 @@
         <v>20</v>
       </c>
       <c r="G56" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="H56">
         <v>250000</v>
@@ -23866,16 +23937,16 @@
         <v>25</v>
       </c>
       <c r="N56" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O56" t="s">
-        <v>1611</v>
+        <v>1615</v>
       </c>
       <c r="P56" t="s">
-        <v>1612</v>
+        <v>1616</v>
       </c>
       <c r="Q56" t="s">
-        <v>1613</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
@@ -23889,7 +23960,7 @@
         <v>55</v>
       </c>
       <c r="D57" t="s">
-        <v>1614</v>
+        <v>1618</v>
       </c>
       <c r="E57" t="s">
         <v>811</v>
@@ -23898,7 +23969,7 @@
         <v>20</v>
       </c>
       <c r="G57" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="H57">
         <v>200000</v>
@@ -23919,16 +23990,16 @@
         <v>25</v>
       </c>
       <c r="N57" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O57" t="s">
-        <v>1615</v>
+        <v>1619</v>
       </c>
       <c r="P57" t="s">
-        <v>1616</v>
+        <v>1620</v>
       </c>
       <c r="Q57" t="s">
-        <v>1617</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
@@ -23942,7 +24013,7 @@
         <v>52</v>
       </c>
       <c r="D58" t="s">
-        <v>1618</v>
+        <v>1622</v>
       </c>
       <c r="E58" t="s">
         <v>811</v>
@@ -23951,7 +24022,7 @@
         <v>20</v>
       </c>
       <c r="G58" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="H58">
         <v>250000</v>
@@ -23972,16 +24043,16 @@
         <v>25</v>
       </c>
       <c r="N58" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O58" t="s">
-        <v>1619</v>
+        <v>1623</v>
       </c>
       <c r="P58" t="s">
-        <v>1620</v>
+        <v>1624</v>
       </c>
       <c r="Q58" t="s">
-        <v>1621</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
@@ -23995,7 +24066,7 @@
         <v>53</v>
       </c>
       <c r="D59" t="s">
-        <v>1622</v>
+        <v>1626</v>
       </c>
       <c r="E59" t="s">
         <v>811</v>
@@ -24004,7 +24075,7 @@
         <v>20</v>
       </c>
       <c r="G59" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="H59">
         <v>200000</v>
@@ -24025,16 +24096,16 @@
         <v>25</v>
       </c>
       <c r="N59" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O59" t="s">
-        <v>1623</v>
+        <v>1627</v>
       </c>
       <c r="P59" t="s">
-        <v>1624</v>
+        <v>1628</v>
       </c>
       <c r="Q59" t="s">
-        <v>1625</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
@@ -24048,7 +24119,7 @@
         <v>50</v>
       </c>
       <c r="D60" t="s">
-        <v>1626</v>
+        <v>1630</v>
       </c>
       <c r="E60" t="s">
         <v>811</v>
@@ -24057,7 +24128,7 @@
         <v>20</v>
       </c>
       <c r="G60" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="H60">
         <v>200000</v>
@@ -24078,16 +24149,16 @@
         <v>25</v>
       </c>
       <c r="N60" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O60" t="s">
-        <v>1627</v>
+        <v>1631</v>
       </c>
       <c r="P60" t="s">
-        <v>1628</v>
+        <v>1632</v>
       </c>
       <c r="Q60" t="s">
-        <v>1629</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
@@ -24101,7 +24172,7 @@
         <v>55</v>
       </c>
       <c r="D61" t="s">
-        <v>1630</v>
+        <v>1634</v>
       </c>
       <c r="E61" t="s">
         <v>811</v>
@@ -24110,7 +24181,7 @@
         <v>20</v>
       </c>
       <c r="G61" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="H61">
         <v>250000</v>
@@ -24131,16 +24202,16 @@
         <v>25</v>
       </c>
       <c r="N61" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O61" t="s">
-        <v>1631</v>
+        <v>1635</v>
       </c>
       <c r="P61" t="s">
-        <v>1632</v>
+        <v>1636</v>
       </c>
       <c r="Q61" t="s">
-        <v>1633</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
@@ -24154,16 +24225,16 @@
         <v>45</v>
       </c>
       <c r="D62" t="s">
-        <v>1634</v>
+        <v>1638</v>
       </c>
       <c r="E62" t="s">
-        <v>1635</v>
+        <v>1639</v>
       </c>
       <c r="F62" t="s">
-        <v>1636</v>
+        <v>1640</v>
       </c>
       <c r="G62" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="H62">
         <v>154000</v>
@@ -24184,16 +24255,16 @@
         <v>38</v>
       </c>
       <c r="N62" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O62" t="s">
-        <v>1637</v>
+        <v>1641</v>
       </c>
       <c r="P62" t="s">
-        <v>1638</v>
+        <v>1642</v>
       </c>
       <c r="Q62" t="s">
-        <v>1639</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
@@ -24216,7 +24287,7 @@
         <v>437</v>
       </c>
       <c r="G63" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="H63">
         <v>180000</v>
@@ -24237,16 +24308,16 @@
         <v>25</v>
       </c>
       <c r="N63" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O63" t="s">
-        <v>1640</v>
+        <v>1644</v>
       </c>
       <c r="P63" t="s">
-        <v>1641</v>
+        <v>1645</v>
       </c>
       <c r="Q63" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
@@ -24266,10 +24337,10 @@
         <v>421</v>
       </c>
       <c r="F64" t="s">
-        <v>1497</v>
+        <v>1501</v>
       </c>
       <c r="G64" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="H64">
         <v>219100</v>
@@ -24290,16 +24361,16 @@
         <v>38</v>
       </c>
       <c r="N64" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O64" t="s">
-        <v>1643</v>
+        <v>1647</v>
       </c>
       <c r="P64" t="s">
-        <v>1644</v>
+        <v>1648</v>
       </c>
       <c r="Q64" t="s">
-        <v>1645</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
@@ -24313,7 +24384,7 @@
         <v>25</v>
       </c>
       <c r="D65" t="s">
-        <v>1646</v>
+        <v>1650</v>
       </c>
       <c r="E65" t="s">
         <v>421</v>
@@ -24322,7 +24393,7 @@
         <v>1016</v>
       </c>
       <c r="G65" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J65" t="s">
         <v>22</v>
@@ -24337,16 +24408,16 @@
         <v>38</v>
       </c>
       <c r="N65" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O65" t="s">
-        <v>1647</v>
+        <v>1651</v>
       </c>
       <c r="P65" t="s">
-        <v>1648</v>
+        <v>1652</v>
       </c>
       <c r="Q65" t="s">
-        <v>1649</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
@@ -24366,10 +24437,10 @@
         <v>698</v>
       </c>
       <c r="F66" t="s">
-        <v>1439</v>
+        <v>1443</v>
       </c>
       <c r="G66" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J66" t="s">
         <v>22</v>
@@ -24384,16 +24455,16 @@
         <v>38</v>
       </c>
       <c r="N66" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O66" t="s">
-        <v>1650</v>
+        <v>1654</v>
       </c>
       <c r="P66" t="s">
-        <v>1651</v>
+        <v>1655</v>
       </c>
       <c r="Q66" t="s">
-        <v>1652</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
@@ -24407,16 +24478,16 @@
         <v>15</v>
       </c>
       <c r="D67" t="s">
-        <v>1653</v>
+        <v>1657</v>
       </c>
       <c r="E67" t="s">
-        <v>1654</v>
+        <v>1658</v>
       </c>
       <c r="F67" t="s">
         <v>1032</v>
       </c>
       <c r="G67" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J67" t="s">
         <v>22</v>
@@ -24431,16 +24502,16 @@
         <v>38</v>
       </c>
       <c r="N67" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O67" t="s">
-        <v>1655</v>
+        <v>1659</v>
       </c>
       <c r="P67" t="s">
-        <v>1656</v>
+        <v>1660</v>
       </c>
       <c r="Q67" t="s">
-        <v>1657</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
@@ -24454,16 +24525,16 @@
         <v>12</v>
       </c>
       <c r="D68" t="s">
-        <v>1658</v>
+        <v>1662</v>
       </c>
       <c r="E68" t="s">
-        <v>1659</v>
+        <v>1663</v>
       </c>
       <c r="F68" t="s">
-        <v>1660</v>
+        <v>1664</v>
       </c>
       <c r="G68" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J68" t="s">
         <v>22</v>
@@ -24478,16 +24549,16 @@
         <v>38</v>
       </c>
       <c r="N68" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O68" t="s">
-        <v>1661</v>
+        <v>1665</v>
       </c>
       <c r="P68" t="s">
-        <v>1662</v>
+        <v>1666</v>
       </c>
       <c r="Q68" t="s">
-        <v>1663</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
@@ -24501,16 +24572,16 @@
         <v>42</v>
       </c>
       <c r="D69" t="s">
-        <v>1664</v>
+        <v>1668</v>
       </c>
       <c r="E69" t="s">
         <v>421</v>
       </c>
       <c r="F69" t="s">
-        <v>1665</v>
+        <v>1669</v>
       </c>
       <c r="G69" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="H69">
         <v>180000</v>
@@ -24531,16 +24602,16 @@
         <v>25</v>
       </c>
       <c r="N69" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O69" t="s">
-        <v>1666</v>
+        <v>1670</v>
       </c>
       <c r="P69" t="s">
-        <v>1667</v>
+        <v>1671</v>
       </c>
       <c r="Q69" t="s">
-        <v>1668</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
@@ -24554,16 +24625,16 @@
         <v>22</v>
       </c>
       <c r="D70" t="s">
-        <v>1669</v>
+        <v>1673</v>
       </c>
       <c r="E70" t="s">
-        <v>1399</v>
+        <v>1403</v>
       </c>
       <c r="F70" t="s">
-        <v>1670</v>
+        <v>1674</v>
       </c>
       <c r="G70" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="H70">
         <v>200000</v>
@@ -24584,16 +24655,16 @@
         <v>38</v>
       </c>
       <c r="N70" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O70" t="s">
-        <v>1671</v>
+        <v>1675</v>
       </c>
       <c r="P70" t="s">
-        <v>1672</v>
+        <v>1676</v>
       </c>
       <c r="Q70" t="s">
-        <v>1673</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
@@ -24607,16 +24678,16 @@
         <v>28</v>
       </c>
       <c r="D71" t="s">
-        <v>1674</v>
+        <v>1678</v>
       </c>
       <c r="E71" t="s">
-        <v>1675</v>
+        <v>1679</v>
       </c>
       <c r="F71" t="s">
         <v>1016</v>
       </c>
       <c r="G71" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J71" t="s">
         <v>22</v>
@@ -24631,16 +24702,16 @@
         <v>38</v>
       </c>
       <c r="N71" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O71" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="P71" t="s">
-        <v>1677</v>
+        <v>1681</v>
       </c>
       <c r="Q71" t="s">
-        <v>1678</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
@@ -24654,16 +24725,16 @@
         <v>5</v>
       </c>
       <c r="D72" t="s">
-        <v>1679</v>
+        <v>1683</v>
       </c>
       <c r="E72" t="s">
-        <v>1680</v>
+        <v>1684</v>
       </c>
       <c r="F72" t="s">
-        <v>1681</v>
+        <v>1685</v>
       </c>
       <c r="G72" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J72" t="s">
         <v>22</v>
@@ -24678,16 +24749,16 @@
         <v>38</v>
       </c>
       <c r="N72" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O72" t="s">
-        <v>1682</v>
+        <v>1686</v>
       </c>
       <c r="P72" t="s">
-        <v>1683</v>
+        <v>1687</v>
       </c>
       <c r="Q72" t="s">
-        <v>1684</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
@@ -24707,10 +24778,10 @@
         <v>421</v>
       </c>
       <c r="F73" t="s">
-        <v>1685</v>
+        <v>1689</v>
       </c>
       <c r="G73" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J73" t="s">
         <v>22</v>
@@ -24725,16 +24796,16 @@
         <v>25</v>
       </c>
       <c r="N73" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O73" t="s">
-        <v>1686</v>
+        <v>1690</v>
       </c>
       <c r="P73" t="s">
-        <v>1687</v>
+        <v>1691</v>
       </c>
       <c r="Q73" t="s">
-        <v>1688</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
@@ -24748,16 +24819,16 @@
         <v>35</v>
       </c>
       <c r="D74" t="s">
-        <v>1689</v>
+        <v>1693</v>
       </c>
       <c r="E74" t="s">
-        <v>1690</v>
+        <v>1694</v>
       </c>
       <c r="F74" t="s">
         <v>1085</v>
       </c>
       <c r="G74" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J74" t="s">
         <v>22</v>
@@ -24772,16 +24843,16 @@
         <v>38</v>
       </c>
       <c r="N74" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O74" t="s">
-        <v>1691</v>
+        <v>1695</v>
       </c>
       <c r="P74" t="s">
-        <v>1692</v>
+        <v>1696</v>
       </c>
       <c r="Q74" t="s">
-        <v>1693</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
@@ -24795,16 +24866,16 @@
         <v>55</v>
       </c>
       <c r="D75" t="s">
-        <v>1694</v>
+        <v>1698</v>
       </c>
       <c r="E75" t="s">
         <v>421</v>
       </c>
       <c r="F75" t="s">
-        <v>1497</v>
+        <v>1501</v>
       </c>
       <c r="G75" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="H75">
         <v>219100</v>
@@ -24819,22 +24890,22 @@
         <v>423</v>
       </c>
       <c r="L75" t="s">
-        <v>1695</v>
+        <v>1699</v>
       </c>
       <c r="M75" t="s">
         <v>25</v>
       </c>
       <c r="N75" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O75" t="s">
-        <v>1696</v>
+        <v>1700</v>
       </c>
       <c r="P75" t="s">
-        <v>1697</v>
+        <v>1701</v>
       </c>
       <c r="Q75" t="s">
-        <v>1698</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
@@ -24848,16 +24919,16 @@
         <v>50</v>
       </c>
       <c r="D76" t="s">
-        <v>1699</v>
+        <v>1703</v>
       </c>
       <c r="E76" t="s">
-        <v>1399</v>
+        <v>1403</v>
       </c>
       <c r="F76" t="s">
         <v>20</v>
       </c>
       <c r="G76" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="H76">
         <v>200000</v>
@@ -24872,22 +24943,22 @@
         <v>423</v>
       </c>
       <c r="L76" t="s">
-        <v>1695</v>
+        <v>1699</v>
       </c>
       <c r="M76" t="s">
         <v>25</v>
       </c>
       <c r="N76" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O76" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="P76" t="s">
-        <v>1701</v>
+        <v>1705</v>
       </c>
       <c r="Q76" t="s">
-        <v>1702</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
@@ -24901,16 +24972,16 @@
         <v>12</v>
       </c>
       <c r="D77" t="s">
-        <v>1703</v>
+        <v>1707</v>
       </c>
       <c r="E77" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="F77" t="s">
         <v>1016</v>
       </c>
       <c r="G77" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J77" t="s">
         <v>22</v>
@@ -24919,22 +24990,22 @@
         <v>557</v>
       </c>
       <c r="L77" t="s">
-        <v>1695</v>
+        <v>1699</v>
       </c>
       <c r="M77" t="s">
         <v>38</v>
       </c>
       <c r="N77" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O77" t="s">
-        <v>1705</v>
+        <v>1709</v>
       </c>
       <c r="P77" t="s">
-        <v>1706</v>
+        <v>1710</v>
       </c>
       <c r="Q77" t="s">
-        <v>1707</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
@@ -24948,16 +25019,16 @@
         <v>12</v>
       </c>
       <c r="D78" t="s">
+        <v>1712</v>
+      </c>
+      <c r="E78" t="s">
         <v>1708</v>
-      </c>
-      <c r="E78" t="s">
-        <v>1704</v>
       </c>
       <c r="F78" t="s">
         <v>1016</v>
       </c>
       <c r="G78" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J78" t="s">
         <v>22</v>
@@ -24966,22 +25037,22 @@
         <v>557</v>
       </c>
       <c r="L78" t="s">
-        <v>1695</v>
+        <v>1699</v>
       </c>
       <c r="M78" t="s">
         <v>38</v>
       </c>
       <c r="N78" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O78" t="s">
-        <v>1709</v>
+        <v>1713</v>
       </c>
       <c r="P78" t="s">
-        <v>1710</v>
+        <v>1714</v>
       </c>
       <c r="Q78" t="s">
-        <v>1711</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
@@ -24995,16 +25066,16 @@
         <v>3</v>
       </c>
       <c r="D79" t="s">
-        <v>1712</v>
+        <v>1716</v>
       </c>
       <c r="E79" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="F79" t="s">
         <v>1016</v>
       </c>
       <c r="G79" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J79" t="s">
         <v>22</v>
@@ -25013,22 +25084,22 @@
         <v>557</v>
       </c>
       <c r="L79" t="s">
-        <v>1695</v>
+        <v>1699</v>
       </c>
       <c r="M79" t="s">
         <v>38</v>
       </c>
       <c r="N79" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O79" t="s">
-        <v>1713</v>
+        <v>1717</v>
       </c>
       <c r="P79" t="s">
-        <v>1714</v>
+        <v>1718</v>
       </c>
       <c r="Q79" t="s">
-        <v>1715</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
@@ -25042,16 +25113,16 @@
         <v>25</v>
       </c>
       <c r="D80" t="s">
-        <v>1716</v>
+        <v>1720</v>
       </c>
       <c r="E80" t="s">
-        <v>1717</v>
+        <v>1721</v>
       </c>
       <c r="F80" t="s">
-        <v>1718</v>
+        <v>1722</v>
       </c>
       <c r="G80" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J80" t="s">
         <v>22</v>
@@ -25060,22 +25131,22 @@
         <v>557</v>
       </c>
       <c r="L80" t="s">
-        <v>1695</v>
+        <v>1699</v>
       </c>
       <c r="M80" t="s">
         <v>38</v>
       </c>
       <c r="N80" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O80" t="s">
-        <v>1719</v>
+        <v>1723</v>
       </c>
       <c r="P80" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="Q80" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
@@ -25089,16 +25160,16 @@
         <v>62</v>
       </c>
       <c r="D81" t="s">
-        <v>1722</v>
+        <v>1726</v>
       </c>
       <c r="E81" t="s">
-        <v>1723</v>
+        <v>1727</v>
       </c>
       <c r="F81" t="s">
-        <v>1724</v>
+        <v>1728</v>
       </c>
       <c r="G81" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J81" t="s">
         <v>22</v>
@@ -25107,22 +25178,22 @@
         <v>557</v>
       </c>
       <c r="L81" t="s">
-        <v>1695</v>
+        <v>1699</v>
       </c>
       <c r="M81" t="s">
         <v>38</v>
       </c>
       <c r="N81" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O81" t="s">
-        <v>1725</v>
+        <v>1729</v>
       </c>
       <c r="P81" t="s">
-        <v>1726</v>
+        <v>1730</v>
       </c>
       <c r="Q81" t="s">
-        <v>1727</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
@@ -25136,16 +25207,16 @@
         <v>68</v>
       </c>
       <c r="D82" t="s">
+        <v>1732</v>
+      </c>
+      <c r="E82" t="s">
+        <v>1727</v>
+      </c>
+      <c r="F82" t="s">
         <v>1728</v>
       </c>
-      <c r="E82" t="s">
-        <v>1723</v>
-      </c>
-      <c r="F82" t="s">
-        <v>1724</v>
-      </c>
       <c r="G82" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J82" t="s">
         <v>22</v>
@@ -25154,22 +25225,22 @@
         <v>557</v>
       </c>
       <c r="L82" t="s">
-        <v>1695</v>
+        <v>1699</v>
       </c>
       <c r="M82" t="s">
         <v>38</v>
       </c>
       <c r="N82" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O82" t="s">
-        <v>1729</v>
+        <v>1733</v>
       </c>
       <c r="P82" t="s">
-        <v>1730</v>
+        <v>1734</v>
       </c>
       <c r="Q82" t="s">
-        <v>1731</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
@@ -25189,10 +25260,10 @@
         <v>421</v>
       </c>
       <c r="F83" t="s">
-        <v>1732</v>
+        <v>1736</v>
       </c>
       <c r="G83" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="H83">
         <v>180000</v>
@@ -25213,16 +25284,16 @@
         <v>25</v>
       </c>
       <c r="N83" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O83" t="s">
-        <v>1733</v>
+        <v>1737</v>
       </c>
       <c r="P83" t="s">
-        <v>1734</v>
+        <v>1738</v>
       </c>
       <c r="Q83" t="s">
-        <v>1735</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
@@ -25242,10 +25313,10 @@
         <v>421</v>
       </c>
       <c r="F84" t="s">
-        <v>1736</v>
+        <v>1740</v>
       </c>
       <c r="G84" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="H84">
         <v>180000</v>
@@ -25266,16 +25337,16 @@
         <v>25</v>
       </c>
       <c r="N84" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O84" t="s">
-        <v>1737</v>
+        <v>1741</v>
       </c>
       <c r="P84" t="s">
-        <v>1738</v>
+        <v>1742</v>
       </c>
       <c r="Q84" t="s">
-        <v>1739</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
@@ -25289,16 +25360,16 @@
         <v>35</v>
       </c>
       <c r="D85" t="s">
-        <v>1740</v>
+        <v>1744</v>
       </c>
       <c r="E85" t="s">
         <v>421</v>
       </c>
       <c r="F85" t="s">
-        <v>1741</v>
+        <v>1745</v>
       </c>
       <c r="G85" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="H85">
         <v>219100</v>
@@ -25319,16 +25390,16 @@
         <v>25</v>
       </c>
       <c r="N85" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O85" t="s">
-        <v>1742</v>
+        <v>1746</v>
       </c>
       <c r="P85" t="s">
-        <v>1743</v>
+        <v>1747</v>
       </c>
       <c r="Q85" t="s">
-        <v>1744</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
@@ -25342,16 +25413,16 @@
         <v>25</v>
       </c>
       <c r="D86" t="s">
-        <v>1745</v>
+        <v>1749</v>
       </c>
       <c r="E86" t="s">
         <v>478</v>
       </c>
       <c r="F86" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="G86" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J86" t="s">
         <v>22</v>
@@ -25366,16 +25437,16 @@
         <v>38</v>
       </c>
       <c r="N86" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O86" t="s">
-        <v>1746</v>
+        <v>1750</v>
       </c>
       <c r="P86" t="s">
-        <v>1747</v>
+        <v>1751</v>
       </c>
       <c r="Q86" t="s">
-        <v>1748</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
@@ -25389,16 +25460,16 @@
         <v>35</v>
       </c>
       <c r="D87" t="s">
-        <v>1749</v>
+        <v>1753</v>
       </c>
       <c r="E87" t="s">
-        <v>1750</v>
+        <v>1754</v>
       </c>
       <c r="F87" t="s">
-        <v>1439</v>
+        <v>1443</v>
       </c>
       <c r="G87" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J87" t="s">
         <v>22</v>
@@ -25413,16 +25484,16 @@
         <v>38</v>
       </c>
       <c r="N87" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O87" t="s">
-        <v>1751</v>
+        <v>1755</v>
       </c>
       <c r="P87" t="s">
-        <v>1752</v>
+        <v>1756</v>
       </c>
       <c r="Q87" t="s">
-        <v>1753</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
@@ -25445,7 +25516,7 @@
         <v>1085</v>
       </c>
       <c r="G88" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="H88">
         <v>200000</v>
@@ -25466,16 +25537,16 @@
         <v>38</v>
       </c>
       <c r="N88" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O88" t="s">
-        <v>1754</v>
+        <v>1758</v>
       </c>
       <c r="P88" t="s">
-        <v>1755</v>
+        <v>1759</v>
       </c>
       <c r="Q88" t="s">
-        <v>1756</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
@@ -25489,7 +25560,7 @@
         <v>38</v>
       </c>
       <c r="D89" t="s">
-        <v>1757</v>
+        <v>1761</v>
       </c>
       <c r="E89" t="s">
         <v>1084</v>
@@ -25498,7 +25569,7 @@
         <v>1085</v>
       </c>
       <c r="G89" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="H89">
         <v>200000</v>
@@ -25519,16 +25590,16 @@
         <v>38</v>
       </c>
       <c r="N89" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O89" t="s">
-        <v>1758</v>
+        <v>1762</v>
       </c>
       <c r="P89" t="s">
-        <v>1759</v>
+        <v>1763</v>
       </c>
       <c r="Q89" t="s">
-        <v>1760</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
@@ -25542,16 +25613,16 @@
         <v>40</v>
       </c>
       <c r="D90" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
       <c r="E90" t="s">
-        <v>1399</v>
+        <v>1403</v>
       </c>
       <c r="F90" t="s">
         <v>713</v>
       </c>
       <c r="G90" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="H90">
         <v>184200</v>
@@ -25572,16 +25643,16 @@
         <v>38</v>
       </c>
       <c r="N90" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O90" t="s">
-        <v>1761</v>
+        <v>1765</v>
       </c>
       <c r="P90" t="s">
-        <v>1762</v>
+        <v>1766</v>
       </c>
       <c r="Q90" t="s">
-        <v>1763</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
@@ -25595,16 +25666,16 @@
         <v>20</v>
       </c>
       <c r="D91" t="s">
-        <v>1764</v>
+        <v>1768</v>
       </c>
       <c r="E91" t="s">
-        <v>1765</v>
+        <v>1769</v>
       </c>
       <c r="F91" t="s">
-        <v>1766</v>
+        <v>1770</v>
       </c>
       <c r="G91" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J91" t="s">
         <v>22</v>
@@ -25619,16 +25690,16 @@
         <v>38</v>
       </c>
       <c r="N91" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O91" t="s">
-        <v>1767</v>
+        <v>1771</v>
       </c>
       <c r="P91" t="s">
-        <v>1768</v>
+        <v>1772</v>
       </c>
       <c r="Q91" t="s">
-        <v>1769</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
@@ -25642,16 +25713,16 @@
         <v>35</v>
       </c>
       <c r="D92" t="s">
-        <v>1770</v>
+        <v>1774</v>
       </c>
       <c r="E92" t="s">
-        <v>1771</v>
+        <v>1775</v>
       </c>
       <c r="F92" t="s">
-        <v>1772</v>
+        <v>1776</v>
       </c>
       <c r="G92" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="H92">
         <v>230000</v>
@@ -25672,16 +25743,16 @@
         <v>38</v>
       </c>
       <c r="N92" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O92" t="s">
-        <v>1773</v>
+        <v>1777</v>
       </c>
       <c r="P92" t="s">
-        <v>1774</v>
+        <v>1778</v>
       </c>
       <c r="Q92" t="s">
-        <v>1775</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
@@ -25701,10 +25772,10 @@
         <v>421</v>
       </c>
       <c r="F93" t="s">
-        <v>1776</v>
+        <v>1780</v>
       </c>
       <c r="G93" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="H93">
         <v>219100</v>
@@ -25725,16 +25796,16 @@
         <v>32</v>
       </c>
       <c r="N93" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O93" t="s">
-        <v>1777</v>
+        <v>1781</v>
       </c>
       <c r="P93" t="s">
-        <v>1778</v>
+        <v>1782</v>
       </c>
       <c r="Q93" t="s">
-        <v>1779</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
@@ -25748,16 +25819,16 @@
         <v>25</v>
       </c>
       <c r="D94" t="s">
-        <v>1780</v>
+        <v>1784</v>
       </c>
       <c r="E94" t="s">
-        <v>1690</v>
+        <v>1694</v>
       </c>
       <c r="F94" t="s">
         <v>1085</v>
       </c>
       <c r="G94" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J94" t="s">
         <v>22</v>
@@ -25772,16 +25843,16 @@
         <v>38</v>
       </c>
       <c r="N94" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O94" t="s">
-        <v>1781</v>
+        <v>1785</v>
       </c>
       <c r="P94" t="s">
-        <v>1782</v>
+        <v>1786</v>
       </c>
       <c r="Q94" t="s">
-        <v>1783</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
@@ -25795,16 +25866,16 @@
         <v>22</v>
       </c>
       <c r="D95" t="s">
-        <v>1784</v>
+        <v>1788</v>
       </c>
       <c r="E95" t="s">
-        <v>1785</v>
+        <v>1789</v>
       </c>
       <c r="F95" t="s">
-        <v>1786</v>
+        <v>1790</v>
       </c>
       <c r="G95" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J95" t="s">
         <v>22</v>
@@ -25819,16 +25890,16 @@
         <v>38</v>
       </c>
       <c r="N95" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O95" t="s">
-        <v>1787</v>
+        <v>1791</v>
       </c>
       <c r="P95" t="s">
-        <v>1788</v>
+        <v>1792</v>
       </c>
       <c r="Q95" t="s">
-        <v>1789</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
@@ -25842,16 +25913,16 @@
         <v>3</v>
       </c>
       <c r="D96" t="s">
+        <v>1794</v>
+      </c>
+      <c r="E96" t="s">
+        <v>1795</v>
+      </c>
+      <c r="F96" t="s">
         <v>1790</v>
       </c>
-      <c r="E96" t="s">
-        <v>1791</v>
-      </c>
-      <c r="F96" t="s">
-        <v>1786</v>
-      </c>
       <c r="G96" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J96" t="s">
         <v>22</v>
@@ -25866,16 +25937,16 @@
         <v>38</v>
       </c>
       <c r="N96" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O96" t="s">
-        <v>1792</v>
+        <v>1796</v>
       </c>
       <c r="P96" t="s">
-        <v>1793</v>
+        <v>1797</v>
       </c>
       <c r="Q96" t="s">
-        <v>1794</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
@@ -25889,16 +25960,16 @@
         <v>28</v>
       </c>
       <c r="D97" t="s">
-        <v>1795</v>
+        <v>1799</v>
       </c>
       <c r="E97" t="s">
-        <v>1796</v>
+        <v>1800</v>
       </c>
       <c r="F97" t="s">
         <v>1016</v>
       </c>
       <c r="G97" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J97" t="s">
         <v>22</v>
@@ -25913,16 +25984,16 @@
         <v>38</v>
       </c>
       <c r="N97" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O97" t="s">
-        <v>1797</v>
+        <v>1801</v>
       </c>
       <c r="P97" t="s">
-        <v>1798</v>
+        <v>1802</v>
       </c>
       <c r="Q97" t="s">
-        <v>1799</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
@@ -25936,16 +26007,16 @@
         <v>45</v>
       </c>
       <c r="D98" t="s">
-        <v>1800</v>
+        <v>1804</v>
       </c>
       <c r="E98" t="s">
-        <v>1801</v>
+        <v>1805</v>
       </c>
       <c r="F98" t="s">
-        <v>1439</v>
+        <v>1443</v>
       </c>
       <c r="G98" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J98" t="s">
         <v>22</v>
@@ -25960,16 +26031,16 @@
         <v>25</v>
       </c>
       <c r="N98" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O98" t="s">
-        <v>1802</v>
+        <v>1806</v>
       </c>
       <c r="P98" t="s">
-        <v>1803</v>
+        <v>1807</v>
       </c>
       <c r="Q98" t="s">
-        <v>1804</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.25">
@@ -25983,16 +26054,16 @@
         <v>50</v>
       </c>
       <c r="D99" t="s">
-        <v>1805</v>
+        <v>1809</v>
       </c>
       <c r="E99" t="s">
-        <v>1806</v>
+        <v>1810</v>
       </c>
       <c r="F99" t="s">
-        <v>1471</v>
+        <v>1475</v>
       </c>
       <c r="G99" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J99" t="s">
         <v>22</v>
@@ -26007,16 +26078,16 @@
         <v>25</v>
       </c>
       <c r="N99" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O99" t="s">
-        <v>1807</v>
+        <v>1811</v>
       </c>
       <c r="P99" t="s">
-        <v>1808</v>
+        <v>1812</v>
       </c>
       <c r="Q99" t="s">
-        <v>1809</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.25">
@@ -26030,16 +26101,16 @@
         <v>48</v>
       </c>
       <c r="D100" t="s">
-        <v>1810</v>
+        <v>1814</v>
       </c>
       <c r="E100" t="s">
-        <v>1635</v>
+        <v>1639</v>
       </c>
       <c r="F100" t="s">
-        <v>1811</v>
+        <v>1815</v>
       </c>
       <c r="G100" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="H100">
         <v>154000</v>
@@ -26060,16 +26131,16 @@
         <v>25</v>
       </c>
       <c r="N100" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O100" t="s">
-        <v>1812</v>
+        <v>1816</v>
       </c>
       <c r="P100" t="s">
-        <v>1813</v>
+        <v>1817</v>
       </c>
       <c r="Q100" t="s">
-        <v>1814</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.25">
@@ -26083,16 +26154,16 @@
         <v>25</v>
       </c>
       <c r="D101" t="s">
-        <v>1815</v>
+        <v>1819</v>
       </c>
       <c r="E101" t="s">
-        <v>1460</v>
+        <v>1464</v>
       </c>
       <c r="F101" t="s">
         <v>1085</v>
       </c>
       <c r="G101" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J101" t="s">
         <v>22</v>
@@ -26107,16 +26178,16 @@
         <v>38</v>
       </c>
       <c r="N101" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O101" t="s">
-        <v>1816</v>
+        <v>1820</v>
       </c>
       <c r="P101" t="s">
-        <v>1817</v>
+        <v>1821</v>
       </c>
       <c r="Q101" t="s">
-        <v>1818</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.25">
@@ -26130,16 +26201,16 @@
         <v>32</v>
       </c>
       <c r="D102" t="s">
-        <v>1716</v>
+        <v>1720</v>
       </c>
       <c r="E102" t="s">
-        <v>1460</v>
+        <v>1464</v>
       </c>
       <c r="F102" t="s">
         <v>1085</v>
       </c>
       <c r="G102" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J102" t="s">
         <v>22</v>
@@ -26154,16 +26225,16 @@
         <v>38</v>
       </c>
       <c r="N102" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O102" t="s">
-        <v>1819</v>
+        <v>1823</v>
       </c>
       <c r="P102" t="s">
-        <v>1820</v>
+        <v>1824</v>
       </c>
       <c r="Q102" t="s">
-        <v>1821</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.25">
@@ -26177,16 +26248,16 @@
         <v>22</v>
       </c>
       <c r="D103" t="s">
-        <v>1822</v>
+        <v>1826</v>
       </c>
       <c r="E103" t="s">
-        <v>1806</v>
+        <v>1810</v>
       </c>
       <c r="F103" t="s">
-        <v>1786</v>
+        <v>1790</v>
       </c>
       <c r="G103" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J103" t="s">
         <v>22</v>
@@ -26201,16 +26272,16 @@
         <v>38</v>
       </c>
       <c r="N103" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O103" t="s">
-        <v>1823</v>
+        <v>1827</v>
       </c>
       <c r="P103" t="s">
-        <v>1824</v>
+        <v>1828</v>
       </c>
       <c r="Q103" t="s">
-        <v>1825</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.25">
@@ -26224,16 +26295,16 @@
         <v>55</v>
       </c>
       <c r="D104" t="s">
-        <v>1805</v>
+        <v>1809</v>
       </c>
       <c r="E104" t="s">
-        <v>1806</v>
+        <v>1810</v>
       </c>
       <c r="F104" t="s">
-        <v>1826</v>
+        <v>1830</v>
       </c>
       <c r="G104" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J104" t="s">
         <v>22</v>
@@ -26248,16 +26319,16 @@
         <v>38</v>
       </c>
       <c r="N104" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O104" t="s">
-        <v>1827</v>
+        <v>1831</v>
       </c>
       <c r="P104" t="s">
-        <v>1828</v>
+        <v>1832</v>
       </c>
       <c r="Q104" t="s">
-        <v>1829</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.25">
@@ -26271,16 +26342,16 @@
         <v>25</v>
       </c>
       <c r="D105" t="s">
+        <v>1834</v>
+      </c>
+      <c r="E105" t="s">
+        <v>1810</v>
+      </c>
+      <c r="F105" t="s">
         <v>1830</v>
       </c>
-      <c r="E105" t="s">
-        <v>1806</v>
-      </c>
-      <c r="F105" t="s">
-        <v>1826</v>
-      </c>
       <c r="G105" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J105" t="s">
         <v>22</v>
@@ -26295,16 +26366,16 @@
         <v>38</v>
       </c>
       <c r="N105" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O105" t="s">
-        <v>1831</v>
+        <v>1835</v>
       </c>
       <c r="P105" t="s">
-        <v>1832</v>
+        <v>1836</v>
       </c>
       <c r="Q105" t="s">
-        <v>1833</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.25">
@@ -26318,7 +26389,7 @@
         <v>33</v>
       </c>
       <c r="D106" t="s">
-        <v>1834</v>
+        <v>1838</v>
       </c>
       <c r="E106" t="s">
         <v>421</v>
@@ -26327,7 +26398,7 @@
         <v>1016</v>
       </c>
       <c r="G106" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J106" t="s">
         <v>22</v>
@@ -26342,16 +26413,16 @@
         <v>38</v>
       </c>
       <c r="N106" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O106" t="s">
-        <v>1835</v>
+        <v>1839</v>
       </c>
       <c r="P106" t="s">
-        <v>1836</v>
+        <v>1840</v>
       </c>
       <c r="Q106" t="s">
-        <v>1837</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.25">
@@ -26365,16 +26436,16 @@
         <v>38</v>
       </c>
       <c r="D107" t="s">
-        <v>1838</v>
+        <v>1842</v>
       </c>
       <c r="E107" t="s">
-        <v>1839</v>
+        <v>1843</v>
       </c>
       <c r="F107" t="s">
-        <v>1568</v>
+        <v>1572</v>
       </c>
       <c r="G107" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="H107">
         <v>220000</v>
@@ -26395,16 +26466,16 @@
         <v>38</v>
       </c>
       <c r="N107" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O107" t="s">
-        <v>1840</v>
+        <v>1844</v>
       </c>
       <c r="P107" t="s">
-        <v>1841</v>
+        <v>1845</v>
       </c>
       <c r="Q107" t="s">
-        <v>1842</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.25">
@@ -26418,16 +26489,16 @@
         <v>62</v>
       </c>
       <c r="D108" t="s">
-        <v>1843</v>
+        <v>1847</v>
       </c>
       <c r="E108" t="s">
-        <v>1399</v>
+        <v>1403</v>
       </c>
       <c r="F108" t="s">
         <v>20</v>
       </c>
       <c r="G108" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="H108">
         <v>200000</v>
@@ -26448,16 +26519,16 @@
         <v>25</v>
       </c>
       <c r="N108" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O108" t="s">
-        <v>1844</v>
+        <v>1848</v>
       </c>
       <c r="P108" t="s">
-        <v>1845</v>
+        <v>1849</v>
       </c>
       <c r="Q108" t="s">
-        <v>1846</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.25">
@@ -26471,16 +26542,16 @@
         <v>30</v>
       </c>
       <c r="D109" t="s">
-        <v>1830</v>
+        <v>1834</v>
       </c>
       <c r="E109" t="s">
-        <v>1806</v>
+        <v>1810</v>
       </c>
       <c r="F109" t="s">
-        <v>1786</v>
+        <v>1790</v>
       </c>
       <c r="G109" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J109" t="s">
         <v>22</v>
@@ -26495,16 +26566,16 @@
         <v>38</v>
       </c>
       <c r="N109" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O109" t="s">
-        <v>1847</v>
+        <v>1851</v>
       </c>
       <c r="P109" t="s">
-        <v>1848</v>
+        <v>1852</v>
       </c>
       <c r="Q109" t="s">
-        <v>1849</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.25">
@@ -26518,16 +26589,16 @@
         <v>58</v>
       </c>
       <c r="D110" t="s">
-        <v>1805</v>
+        <v>1809</v>
       </c>
       <c r="E110" t="s">
-        <v>1806</v>
+        <v>1810</v>
       </c>
       <c r="F110" t="s">
-        <v>1471</v>
+        <v>1475</v>
       </c>
       <c r="G110" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J110" t="s">
         <v>22</v>
@@ -26542,16 +26613,16 @@
         <v>38</v>
       </c>
       <c r="N110" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O110" t="s">
-        <v>1850</v>
+        <v>1854</v>
       </c>
       <c r="P110" t="s">
-        <v>1851</v>
+        <v>1855</v>
       </c>
       <c r="Q110" t="s">
-        <v>1852</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.25">
@@ -26565,7 +26636,7 @@
         <v>55</v>
       </c>
       <c r="D111" t="s">
-        <v>1853</v>
+        <v>1857</v>
       </c>
       <c r="E111" t="s">
         <v>421</v>
@@ -26574,7 +26645,7 @@
         <v>20</v>
       </c>
       <c r="G111" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="H111">
         <v>217800</v>
@@ -26595,16 +26666,16 @@
         <v>25</v>
       </c>
       <c r="N111" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O111" t="s">
-        <v>1854</v>
+        <v>1858</v>
       </c>
       <c r="P111" t="s">
-        <v>1855</v>
+        <v>1859</v>
       </c>
       <c r="Q111" t="s">
-        <v>1856</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.25">
@@ -26618,16 +26689,16 @@
         <v>45</v>
       </c>
       <c r="D112" t="s">
-        <v>1857</v>
+        <v>1861</v>
       </c>
       <c r="E112" t="s">
         <v>421</v>
       </c>
       <c r="F112" t="s">
-        <v>1858</v>
+        <v>1862</v>
       </c>
       <c r="G112" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="H112">
         <v>219100</v>
@@ -26648,16 +26719,16 @@
         <v>25</v>
       </c>
       <c r="N112" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O112" t="s">
-        <v>1859</v>
+        <v>1863</v>
       </c>
       <c r="P112" t="s">
-        <v>1860</v>
+        <v>1864</v>
       </c>
       <c r="Q112" t="s">
-        <v>1861</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.25">
@@ -26677,10 +26748,10 @@
         <v>698</v>
       </c>
       <c r="F113" t="s">
-        <v>1862</v>
+        <v>1866</v>
       </c>
       <c r="G113" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J113" t="s">
         <v>22</v>
@@ -26695,16 +26766,16 @@
         <v>38</v>
       </c>
       <c r="N113" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O113" t="s">
-        <v>1863</v>
+        <v>1867</v>
       </c>
       <c r="P113" t="s">
-        <v>1864</v>
+        <v>1868</v>
       </c>
       <c r="Q113" t="s">
-        <v>1865</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.25">
@@ -26718,16 +26789,16 @@
         <v>35</v>
       </c>
       <c r="D114" t="s">
-        <v>1866</v>
+        <v>1870</v>
       </c>
       <c r="E114" t="s">
         <v>421</v>
       </c>
       <c r="F114" t="s">
-        <v>1867</v>
+        <v>1871</v>
       </c>
       <c r="G114" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J114" t="s">
         <v>22</v>
@@ -26742,16 +26813,16 @@
         <v>38</v>
       </c>
       <c r="N114" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O114" t="s">
-        <v>1868</v>
+        <v>1872</v>
       </c>
       <c r="P114" t="s">
-        <v>1869</v>
+        <v>1873</v>
       </c>
       <c r="Q114" t="s">
-        <v>1870</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.25">
@@ -26765,7 +26836,7 @@
         <v>38</v>
       </c>
       <c r="D115" t="s">
-        <v>1871</v>
+        <v>1875</v>
       </c>
       <c r="E115" t="s">
         <v>421</v>
@@ -26774,7 +26845,7 @@
         <v>20</v>
       </c>
       <c r="G115" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="H115">
         <v>219100</v>
@@ -26795,16 +26866,16 @@
         <v>38</v>
       </c>
       <c r="N115" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O115" t="s">
-        <v>1872</v>
+        <v>1876</v>
       </c>
       <c r="P115" t="s">
-        <v>1873</v>
+        <v>1877</v>
       </c>
       <c r="Q115" t="s">
-        <v>1874</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.25">
@@ -26818,16 +26889,16 @@
         <v>22</v>
       </c>
       <c r="D116" t="s">
-        <v>1875</v>
+        <v>1879</v>
       </c>
       <c r="E116" t="s">
-        <v>1876</v>
+        <v>1880</v>
       </c>
       <c r="F116" t="s">
-        <v>1877</v>
+        <v>1881</v>
       </c>
       <c r="G116" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J116" t="s">
         <v>22</v>
@@ -26842,16 +26913,16 @@
         <v>38</v>
       </c>
       <c r="N116" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O116" t="s">
-        <v>1878</v>
+        <v>1882</v>
       </c>
       <c r="P116" t="s">
-        <v>1879</v>
+        <v>1883</v>
       </c>
       <c r="Q116" t="s">
-        <v>1880</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.25">
@@ -26865,16 +26936,16 @@
         <v>35</v>
       </c>
       <c r="D117" t="s">
-        <v>1881</v>
+        <v>1885</v>
       </c>
       <c r="E117" t="s">
-        <v>1882</v>
+        <v>1886</v>
       </c>
       <c r="F117" t="s">
-        <v>1883</v>
+        <v>1887</v>
       </c>
       <c r="G117" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J117" t="s">
         <v>22</v>
@@ -26889,16 +26960,16 @@
         <v>38</v>
       </c>
       <c r="N117" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O117" t="s">
-        <v>1884</v>
+        <v>1888</v>
       </c>
       <c r="P117" t="s">
-        <v>1885</v>
+        <v>1889</v>
       </c>
       <c r="Q117" t="s">
-        <v>1886</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.25">
@@ -26912,7 +26983,7 @@
         <v>55</v>
       </c>
       <c r="D118" t="s">
-        <v>1887</v>
+        <v>1891</v>
       </c>
       <c r="E118" t="s">
         <v>1084</v>
@@ -26921,7 +26992,7 @@
         <v>1085</v>
       </c>
       <c r="G118" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="H118">
         <v>200000</v>
@@ -26942,16 +27013,16 @@
         <v>25</v>
       </c>
       <c r="N118" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O118" t="s">
-        <v>1888</v>
+        <v>1892</v>
       </c>
       <c r="P118" t="s">
-        <v>1889</v>
+        <v>1893</v>
       </c>
       <c r="Q118" t="s">
-        <v>1890</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.25">
@@ -26971,10 +27042,10 @@
         <v>421</v>
       </c>
       <c r="F119" t="s">
-        <v>1891</v>
+        <v>1895</v>
       </c>
       <c r="G119" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="H119">
         <v>180000</v>
@@ -26995,16 +27066,16 @@
         <v>25</v>
       </c>
       <c r="N119" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O119" t="s">
-        <v>1892</v>
+        <v>1896</v>
       </c>
       <c r="P119" t="s">
-        <v>1893</v>
+        <v>1897</v>
       </c>
       <c r="Q119" t="s">
-        <v>1894</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.25">
@@ -27024,10 +27095,10 @@
         <v>698</v>
       </c>
       <c r="F120" t="s">
-        <v>1439</v>
+        <v>1443</v>
       </c>
       <c r="G120" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J120" t="s">
         <v>22</v>
@@ -27042,16 +27113,16 @@
         <v>38</v>
       </c>
       <c r="N120" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O120" t="s">
-        <v>1895</v>
+        <v>1899</v>
       </c>
       <c r="P120" t="s">
-        <v>1896</v>
+        <v>1900</v>
       </c>
       <c r="Q120" t="s">
-        <v>1897</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.25">
@@ -27074,7 +27145,7 @@
         <v>1085</v>
       </c>
       <c r="G121" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J121" t="s">
         <v>22</v>
@@ -27089,16 +27160,16 @@
         <v>38</v>
       </c>
       <c r="N121" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O121" t="s">
-        <v>1898</v>
+        <v>1902</v>
       </c>
       <c r="P121" t="s">
-        <v>1899</v>
+        <v>1903</v>
       </c>
       <c r="Q121" t="s">
-        <v>1900</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.25">
@@ -27121,7 +27192,7 @@
         <v>1085</v>
       </c>
       <c r="G122" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J122" t="s">
         <v>22</v>
@@ -27136,16 +27207,16 @@
         <v>25</v>
       </c>
       <c r="N122" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O122" t="s">
-        <v>1901</v>
+        <v>1905</v>
       </c>
       <c r="P122" t="s">
-        <v>1902</v>
+        <v>1906</v>
       </c>
       <c r="Q122" t="s">
-        <v>1903</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.25">
@@ -27159,16 +27230,16 @@
         <v>32</v>
       </c>
       <c r="D123" t="s">
-        <v>1475</v>
+        <v>1479</v>
       </c>
       <c r="E123" t="s">
-        <v>1476</v>
+        <v>1480</v>
       </c>
       <c r="F123" t="s">
         <v>1025</v>
       </c>
       <c r="G123" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J123" t="s">
         <v>22</v>
@@ -27183,16 +27254,16 @@
         <v>38</v>
       </c>
       <c r="N123" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O123" t="s">
-        <v>1904</v>
+        <v>1908</v>
       </c>
       <c r="P123" t="s">
-        <v>1905</v>
+        <v>1909</v>
       </c>
       <c r="Q123" t="s">
-        <v>1906</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.25">
@@ -27206,7 +27277,7 @@
         <v>30</v>
       </c>
       <c r="D124" t="s">
-        <v>1907</v>
+        <v>1911</v>
       </c>
       <c r="E124" t="s">
         <v>698</v>
@@ -27215,7 +27286,7 @@
         <v>707</v>
       </c>
       <c r="G124" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J124" t="s">
         <v>22</v>
@@ -27230,16 +27301,16 @@
         <v>38</v>
       </c>
       <c r="N124" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O124" t="s">
-        <v>1908</v>
+        <v>1912</v>
       </c>
       <c r="P124" t="s">
-        <v>1909</v>
+        <v>1913</v>
       </c>
       <c r="Q124" t="s">
-        <v>1910</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.25">
@@ -27253,16 +27324,16 @@
         <v>5</v>
       </c>
       <c r="D125" t="s">
-        <v>1464</v>
+        <v>1468</v>
       </c>
       <c r="E125" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F125" t="s">
         <v>1032</v>
       </c>
       <c r="G125" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J125" t="s">
         <v>22</v>
@@ -27277,16 +27348,16 @@
         <v>38</v>
       </c>
       <c r="N125" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O125" t="s">
-        <v>1911</v>
+        <v>1915</v>
       </c>
       <c r="P125" t="s">
-        <v>1912</v>
+        <v>1916</v>
       </c>
       <c r="Q125" t="s">
-        <v>1913</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.25">
@@ -27300,16 +27371,16 @@
         <v>30</v>
       </c>
       <c r="D126" t="s">
-        <v>1469</v>
+        <v>1473</v>
       </c>
       <c r="E126" t="s">
-        <v>1470</v>
+        <v>1474</v>
       </c>
       <c r="F126" t="s">
-        <v>1471</v>
+        <v>1475</v>
       </c>
       <c r="G126" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J126" t="s">
         <v>22</v>
@@ -27324,16 +27395,16 @@
         <v>38</v>
       </c>
       <c r="N126" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O126" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="P126" t="s">
-        <v>1915</v>
+        <v>1919</v>
       </c>
       <c r="Q126" t="s">
-        <v>1916</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.25">
@@ -27347,16 +27418,16 @@
         <v>40</v>
       </c>
       <c r="D127" t="s">
-        <v>1917</v>
+        <v>1921</v>
       </c>
       <c r="E127" t="s">
-        <v>1918</v>
+        <v>1922</v>
       </c>
       <c r="F127" t="s">
-        <v>1919</v>
+        <v>1923</v>
       </c>
       <c r="G127" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J127" t="s">
         <v>22</v>
@@ -27371,16 +27442,16 @@
         <v>38</v>
       </c>
       <c r="N127" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O127" t="s">
-        <v>1920</v>
+        <v>1924</v>
       </c>
       <c r="P127" t="s">
-        <v>1921</v>
+        <v>1925</v>
       </c>
       <c r="Q127" t="s">
-        <v>1922</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.25">
@@ -27394,16 +27465,16 @@
         <v>38</v>
       </c>
       <c r="D128" t="s">
-        <v>1923</v>
+        <v>1927</v>
       </c>
       <c r="E128" t="s">
         <v>421</v>
       </c>
       <c r="F128" t="s">
-        <v>1439</v>
+        <v>1443</v>
       </c>
       <c r="G128" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J128" t="s">
         <v>22</v>
@@ -27418,16 +27489,16 @@
         <v>38</v>
       </c>
       <c r="N128" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O128" t="s">
-        <v>1924</v>
+        <v>1928</v>
       </c>
       <c r="P128" t="s">
-        <v>1925</v>
+        <v>1929</v>
       </c>
       <c r="Q128" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="129" spans="1:17" x14ac:dyDescent="0.25">
@@ -27441,16 +27512,16 @@
         <v>36</v>
       </c>
       <c r="D129" t="s">
-        <v>1927</v>
+        <v>1931</v>
       </c>
       <c r="E129" t="s">
         <v>421</v>
       </c>
       <c r="F129" t="s">
-        <v>1439</v>
+        <v>1443</v>
       </c>
       <c r="G129" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J129" t="s">
         <v>22</v>
@@ -27465,16 +27536,16 @@
         <v>38</v>
       </c>
       <c r="N129" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O129" t="s">
-        <v>1928</v>
+        <v>1932</v>
       </c>
       <c r="P129" t="s">
-        <v>1929</v>
+        <v>1933</v>
       </c>
       <c r="Q129" t="s">
-        <v>1930</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="130" spans="1:17" x14ac:dyDescent="0.25">
@@ -27491,13 +27562,13 @@
         <v>549</v>
       </c>
       <c r="E130" t="s">
-        <v>1931</v>
+        <v>1935</v>
       </c>
       <c r="F130" t="s">
-        <v>1932</v>
+        <v>1936</v>
       </c>
       <c r="G130" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J130" t="s">
         <v>22</v>
@@ -27512,16 +27583,16 @@
         <v>38</v>
       </c>
       <c r="N130" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O130" t="s">
-        <v>1933</v>
+        <v>1937</v>
       </c>
       <c r="P130" t="s">
-        <v>1934</v>
+        <v>1938</v>
       </c>
       <c r="Q130" t="s">
-        <v>1935</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="131" spans="1:17" x14ac:dyDescent="0.25">
@@ -27535,16 +27606,16 @@
         <v>45</v>
       </c>
       <c r="D131" t="s">
-        <v>1936</v>
+        <v>1940</v>
       </c>
       <c r="E131" t="s">
-        <v>1937</v>
+        <v>1941</v>
       </c>
       <c r="F131" t="s">
-        <v>1938</v>
+        <v>1942</v>
       </c>
       <c r="G131" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J131" t="s">
         <v>22</v>
@@ -27559,16 +27630,16 @@
         <v>38</v>
       </c>
       <c r="N131" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O131" t="s">
-        <v>1939</v>
+        <v>1943</v>
       </c>
       <c r="P131" t="s">
-        <v>1940</v>
+        <v>1944</v>
       </c>
       <c r="Q131" t="s">
-        <v>1941</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="132" spans="1:17" x14ac:dyDescent="0.25">
@@ -27582,16 +27653,16 @@
         <v>40</v>
       </c>
       <c r="D132" t="s">
-        <v>1942</v>
+        <v>1946</v>
       </c>
       <c r="E132" t="s">
-        <v>1943</v>
+        <v>1947</v>
       </c>
       <c r="F132" t="s">
         <v>1085</v>
       </c>
       <c r="G132" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J132" t="s">
         <v>22</v>
@@ -27606,16 +27677,16 @@
         <v>38</v>
       </c>
       <c r="N132" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O132" t="s">
-        <v>1944</v>
+        <v>1948</v>
       </c>
       <c r="P132" t="s">
-        <v>1945</v>
+        <v>1949</v>
       </c>
       <c r="Q132" t="s">
-        <v>1946</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="133" spans="1:17" x14ac:dyDescent="0.25">
@@ -27629,16 +27700,16 @@
         <v>40</v>
       </c>
       <c r="D133" t="s">
+        <v>1951</v>
+      </c>
+      <c r="E133" t="s">
         <v>1947</v>
-      </c>
-      <c r="E133" t="s">
-        <v>1943</v>
       </c>
       <c r="F133" t="s">
         <v>1085</v>
       </c>
       <c r="G133" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J133" t="s">
         <v>22</v>
@@ -27653,16 +27724,16 @@
         <v>38</v>
       </c>
       <c r="N133" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O133" t="s">
-        <v>1948</v>
+        <v>1952</v>
       </c>
       <c r="P133" t="s">
-        <v>1949</v>
+        <v>1953</v>
       </c>
       <c r="Q133" t="s">
-        <v>1950</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="134" spans="1:17" x14ac:dyDescent="0.25">
@@ -27676,16 +27747,16 @@
         <v>18</v>
       </c>
       <c r="D134" t="s">
-        <v>1703</v>
+        <v>1707</v>
       </c>
       <c r="E134" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="F134" t="s">
         <v>1016</v>
       </c>
       <c r="G134" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J134" t="s">
         <v>22</v>
@@ -27700,16 +27771,16 @@
         <v>38</v>
       </c>
       <c r="N134" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O134" t="s">
-        <v>1951</v>
+        <v>1955</v>
       </c>
       <c r="P134" t="s">
-        <v>1952</v>
+        <v>1956</v>
       </c>
       <c r="Q134" t="s">
-        <v>1953</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="135" spans="1:17" x14ac:dyDescent="0.25">
@@ -27723,16 +27794,16 @@
         <v>3</v>
       </c>
       <c r="D135" t="s">
-        <v>1712</v>
+        <v>1716</v>
       </c>
       <c r="E135" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="F135" t="s">
         <v>1016</v>
       </c>
       <c r="G135" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J135" t="s">
         <v>22</v>
@@ -27747,16 +27818,16 @@
         <v>38</v>
       </c>
       <c r="N135" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O135" t="s">
-        <v>1954</v>
+        <v>1958</v>
       </c>
       <c r="P135" t="s">
-        <v>1955</v>
+        <v>1959</v>
       </c>
       <c r="Q135" t="s">
-        <v>1956</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="136" spans="1:17" x14ac:dyDescent="0.25">
@@ -27770,16 +27841,16 @@
         <v>38</v>
       </c>
       <c r="D136" t="s">
-        <v>1957</v>
+        <v>1961</v>
       </c>
       <c r="E136" t="s">
-        <v>1958</v>
+        <v>1962</v>
       </c>
       <c r="F136" t="s">
-        <v>1959</v>
+        <v>1963</v>
       </c>
       <c r="G136" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J136" t="s">
         <v>22</v>
@@ -27794,16 +27865,16 @@
         <v>38</v>
       </c>
       <c r="N136" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O136" t="s">
-        <v>1960</v>
+        <v>1964</v>
       </c>
       <c r="P136" t="s">
-        <v>1961</v>
+        <v>1965</v>
       </c>
       <c r="Q136" t="s">
-        <v>1962</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="137" spans="1:17" x14ac:dyDescent="0.25">
@@ -27817,16 +27888,16 @@
         <v>15</v>
       </c>
       <c r="D137" t="s">
-        <v>1963</v>
+        <v>1967</v>
       </c>
       <c r="E137" t="s">
-        <v>1958</v>
+        <v>1962</v>
       </c>
       <c r="F137" t="s">
-        <v>1964</v>
+        <v>1968</v>
       </c>
       <c r="G137" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J137" t="s">
         <v>22</v>
@@ -27841,16 +27912,16 @@
         <v>38</v>
       </c>
       <c r="N137" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O137" t="s">
-        <v>1965</v>
+        <v>1969</v>
       </c>
       <c r="P137" t="s">
-        <v>1966</v>
+        <v>1970</v>
       </c>
       <c r="Q137" t="s">
-        <v>1967</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.25">
@@ -27864,16 +27935,16 @@
         <v>33</v>
       </c>
       <c r="D138" t="s">
+        <v>1972</v>
+      </c>
+      <c r="E138" t="s">
+        <v>1962</v>
+      </c>
+      <c r="F138" t="s">
         <v>1968</v>
       </c>
-      <c r="E138" t="s">
-        <v>1958</v>
-      </c>
-      <c r="F138" t="s">
-        <v>1964</v>
-      </c>
       <c r="G138" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J138" t="s">
         <v>22</v>
@@ -27888,16 +27959,16 @@
         <v>38</v>
       </c>
       <c r="N138" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O138" t="s">
-        <v>1969</v>
+        <v>1973</v>
       </c>
       <c r="P138" t="s">
-        <v>1970</v>
+        <v>1974</v>
       </c>
       <c r="Q138" t="s">
-        <v>1971</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.25">
@@ -27911,16 +27982,16 @@
         <v>40</v>
       </c>
       <c r="D139" t="s">
-        <v>1972</v>
+        <v>1976</v>
       </c>
       <c r="E139" t="s">
-        <v>1958</v>
+        <v>1962</v>
       </c>
       <c r="F139" t="s">
-        <v>1973</v>
+        <v>1977</v>
       </c>
       <c r="G139" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J139" t="s">
         <v>22</v>
@@ -27935,16 +28006,16 @@
         <v>38</v>
       </c>
       <c r="N139" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O139" t="s">
-        <v>1974</v>
+        <v>1978</v>
       </c>
       <c r="P139" t="s">
-        <v>1975</v>
+        <v>1979</v>
       </c>
       <c r="Q139" t="s">
-        <v>1976</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.25">
@@ -27958,16 +28029,16 @@
         <v>38</v>
       </c>
       <c r="D140" t="s">
-        <v>1977</v>
+        <v>1981</v>
       </c>
       <c r="E140" t="s">
-        <v>1958</v>
+        <v>1962</v>
       </c>
       <c r="F140" t="s">
-        <v>1964</v>
+        <v>1968</v>
       </c>
       <c r="G140" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J140" t="s">
         <v>22</v>
@@ -27982,16 +28053,16 @@
         <v>38</v>
       </c>
       <c r="N140" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O140" t="s">
-        <v>1978</v>
+        <v>1982</v>
       </c>
       <c r="P140" t="s">
-        <v>1979</v>
+        <v>1983</v>
       </c>
       <c r="Q140" t="s">
-        <v>1980</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.25">
@@ -28005,16 +28076,16 @@
         <v>45</v>
       </c>
       <c r="D141" t="s">
-        <v>1981</v>
+        <v>1985</v>
       </c>
       <c r="E141" t="s">
-        <v>1958</v>
+        <v>1962</v>
       </c>
       <c r="F141" t="s">
-        <v>1982</v>
+        <v>1986</v>
       </c>
       <c r="G141" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J141" t="s">
         <v>22</v>
@@ -28029,16 +28100,16 @@
         <v>38</v>
       </c>
       <c r="N141" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O141" t="s">
-        <v>1983</v>
+        <v>1987</v>
       </c>
       <c r="P141" t="s">
-        <v>1984</v>
+        <v>1988</v>
       </c>
       <c r="Q141" t="s">
-        <v>1985</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.25">
@@ -28052,16 +28123,16 @@
         <v>18</v>
       </c>
       <c r="D142" t="s">
-        <v>1986</v>
+        <v>1990</v>
       </c>
       <c r="E142" t="s">
-        <v>1958</v>
+        <v>1962</v>
       </c>
       <c r="F142" t="s">
-        <v>1987</v>
+        <v>1991</v>
       </c>
       <c r="G142" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J142" t="s">
         <v>22</v>
@@ -28076,16 +28147,16 @@
         <v>38</v>
       </c>
       <c r="N142" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O142" t="s">
-        <v>1988</v>
+        <v>1992</v>
       </c>
       <c r="P142" t="s">
-        <v>1989</v>
+        <v>1993</v>
       </c>
       <c r="Q142" t="s">
-        <v>1990</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="143" spans="1:17" x14ac:dyDescent="0.25">
@@ -28099,16 +28170,16 @@
         <v>20</v>
       </c>
       <c r="D143" t="s">
-        <v>1991</v>
+        <v>1995</v>
       </c>
       <c r="E143" t="s">
-        <v>1958</v>
+        <v>1962</v>
       </c>
       <c r="F143" t="s">
-        <v>1964</v>
+        <v>1968</v>
       </c>
       <c r="G143" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J143" t="s">
         <v>22</v>
@@ -28123,16 +28194,16 @@
         <v>38</v>
       </c>
       <c r="N143" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O143" t="s">
-        <v>1992</v>
+        <v>1996</v>
       </c>
       <c r="P143" t="s">
-        <v>1993</v>
+        <v>1997</v>
       </c>
       <c r="Q143" t="s">
-        <v>1994</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="144" spans="1:17" x14ac:dyDescent="0.25">
@@ -28146,16 +28217,16 @@
         <v>60</v>
       </c>
       <c r="D144" t="s">
-        <v>1995</v>
+        <v>1999</v>
       </c>
       <c r="E144" t="s">
-        <v>1958</v>
+        <v>1962</v>
       </c>
       <c r="F144" t="s">
-        <v>1996</v>
+        <v>2000</v>
       </c>
       <c r="G144" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J144" t="s">
         <v>22</v>
@@ -28170,16 +28241,16 @@
         <v>38</v>
       </c>
       <c r="N144" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O144" t="s">
-        <v>1997</v>
+        <v>2001</v>
       </c>
       <c r="P144" t="s">
-        <v>1998</v>
+        <v>2002</v>
       </c>
       <c r="Q144" t="s">
-        <v>1999</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="145" spans="1:17" x14ac:dyDescent="0.25">
@@ -28193,16 +28264,16 @@
         <v>32</v>
       </c>
       <c r="D145" t="s">
-        <v>2000</v>
+        <v>2004</v>
       </c>
       <c r="E145" t="s">
-        <v>1958</v>
+        <v>1962</v>
       </c>
       <c r="F145" t="s">
-        <v>1973</v>
+        <v>1977</v>
       </c>
       <c r="G145" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J145" t="s">
         <v>22</v>
@@ -28217,16 +28288,16 @@
         <v>38</v>
       </c>
       <c r="N145" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O145" t="s">
-        <v>2001</v>
+        <v>2005</v>
       </c>
       <c r="P145" t="s">
-        <v>2002</v>
+        <v>2006</v>
       </c>
       <c r="Q145" t="s">
-        <v>2003</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="146" spans="1:17" x14ac:dyDescent="0.25">
@@ -28240,16 +28311,16 @@
         <v>15</v>
       </c>
       <c r="D146" t="s">
-        <v>2004</v>
+        <v>2008</v>
       </c>
       <c r="E146" t="s">
-        <v>1958</v>
+        <v>1962</v>
       </c>
       <c r="F146" t="s">
-        <v>2005</v>
+        <v>2009</v>
       </c>
       <c r="G146" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J146" t="s">
         <v>22</v>
@@ -28264,16 +28335,16 @@
         <v>38</v>
       </c>
       <c r="N146" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O146" t="s">
-        <v>2006</v>
+        <v>2010</v>
       </c>
       <c r="P146" t="s">
-        <v>2007</v>
+        <v>2011</v>
       </c>
       <c r="Q146" t="s">
-        <v>2008</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="147" spans="1:17" x14ac:dyDescent="0.25">
@@ -28290,13 +28361,13 @@
         <v>280</v>
       </c>
       <c r="E147" t="s">
-        <v>1958</v>
+        <v>1962</v>
       </c>
       <c r="F147" t="s">
-        <v>2009</v>
+        <v>2013</v>
       </c>
       <c r="G147" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J147" t="s">
         <v>22</v>
@@ -28311,16 +28382,16 @@
         <v>38</v>
       </c>
       <c r="N147" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O147" t="s">
-        <v>2010</v>
+        <v>2014</v>
       </c>
       <c r="P147" t="s">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="Q147" t="s">
-        <v>2012</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="148" spans="1:17" x14ac:dyDescent="0.25">
@@ -28334,16 +28405,16 @@
         <v>20</v>
       </c>
       <c r="D148" t="s">
-        <v>2013</v>
+        <v>2017</v>
       </c>
       <c r="E148" t="s">
-        <v>1958</v>
+        <v>1962</v>
       </c>
       <c r="F148" t="s">
-        <v>1973</v>
+        <v>1977</v>
       </c>
       <c r="G148" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J148" t="s">
         <v>22</v>
@@ -28358,16 +28429,16 @@
         <v>38</v>
       </c>
       <c r="N148" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O148" t="s">
-        <v>2014</v>
+        <v>2018</v>
       </c>
       <c r="P148" t="s">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="Q148" t="s">
-        <v>2016</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="149" spans="1:17" x14ac:dyDescent="0.25">
@@ -28381,16 +28452,16 @@
         <v>82</v>
       </c>
       <c r="D149" t="s">
-        <v>2017</v>
+        <v>2021</v>
       </c>
       <c r="E149" t="s">
-        <v>1958</v>
+        <v>1962</v>
       </c>
       <c r="F149" t="s">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="G149" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J149" t="s">
         <v>22</v>
@@ -28405,16 +28476,16 @@
         <v>25</v>
       </c>
       <c r="N149" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O149" t="s">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="P149" t="s">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="Q149" t="s">
-        <v>2021</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="150" spans="1:17" x14ac:dyDescent="0.25">
@@ -28428,16 +28499,16 @@
         <v>55</v>
       </c>
       <c r="D150" t="s">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="E150" t="s">
         <v>1163</v>
       </c>
       <c r="F150" t="s">
-        <v>2023</v>
+        <v>2027</v>
       </c>
       <c r="G150" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J150" t="s">
         <v>22</v>
@@ -28452,16 +28523,16 @@
         <v>38</v>
       </c>
       <c r="N150" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O150" t="s">
-        <v>2024</v>
+        <v>2028</v>
       </c>
       <c r="P150" t="s">
-        <v>2025</v>
+        <v>2029</v>
       </c>
       <c r="Q150" t="s">
-        <v>2026</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="151" spans="1:17" x14ac:dyDescent="0.25">
@@ -28475,16 +28546,16 @@
         <v>28</v>
       </c>
       <c r="D151" t="s">
-        <v>2027</v>
+        <v>2031</v>
       </c>
       <c r="E151" t="s">
         <v>1163</v>
       </c>
       <c r="F151" t="s">
-        <v>2028</v>
+        <v>2032</v>
       </c>
       <c r="G151" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J151" t="s">
         <v>22</v>
@@ -28499,16 +28570,16 @@
         <v>38</v>
       </c>
       <c r="N151" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O151" t="s">
-        <v>2029</v>
+        <v>2033</v>
       </c>
       <c r="P151" t="s">
-        <v>2030</v>
+        <v>2034</v>
       </c>
       <c r="Q151" t="s">
-        <v>2031</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="152" spans="1:17" x14ac:dyDescent="0.25">
@@ -28522,16 +28593,16 @@
         <v>7</v>
       </c>
       <c r="D152" t="s">
-        <v>2032</v>
+        <v>2036</v>
       </c>
       <c r="E152" t="s">
         <v>1163</v>
       </c>
       <c r="F152" t="s">
-        <v>2033</v>
+        <v>2037</v>
       </c>
       <c r="G152" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J152" t="s">
         <v>22</v>
@@ -28546,16 +28617,16 @@
         <v>38</v>
       </c>
       <c r="N152" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O152" t="s">
-        <v>2034</v>
+        <v>2038</v>
       </c>
       <c r="P152" t="s">
-        <v>2035</v>
+        <v>2039</v>
       </c>
       <c r="Q152" t="s">
-        <v>2036</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="153" spans="1:17" x14ac:dyDescent="0.25">
@@ -28569,16 +28640,16 @@
         <v>55</v>
       </c>
       <c r="D153" t="s">
-        <v>2037</v>
+        <v>2041</v>
       </c>
       <c r="E153" t="s">
         <v>1163</v>
       </c>
       <c r="F153" t="s">
-        <v>2038</v>
+        <v>2042</v>
       </c>
       <c r="G153" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="J153" t="s">
         <v>22</v>
@@ -28593,16 +28664,16 @@
         <v>38</v>
       </c>
       <c r="N153" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O153" t="s">
-        <v>2039</v>
+        <v>2043</v>
       </c>
       <c r="P153" t="s">
-        <v>2040</v>
+        <v>2044</v>
       </c>
       <c r="Q153" t="s">
-        <v>2041</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="154" spans="1:17" x14ac:dyDescent="0.25">
@@ -28616,16 +28687,16 @@
         <v>40</v>
       </c>
       <c r="D154" t="s">
-        <v>2042</v>
+        <v>2046</v>
       </c>
       <c r="E154" t="s">
-        <v>2043</v>
+        <v>2047</v>
       </c>
       <c r="F154" t="s">
         <v>1284</v>
       </c>
       <c r="G154" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J154" t="s">
         <v>22</v>
@@ -28640,16 +28711,16 @@
         <v>38</v>
       </c>
       <c r="N154" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O154" t="s">
-        <v>2044</v>
+        <v>2048</v>
       </c>
       <c r="P154" t="s">
-        <v>2045</v>
+        <v>2049</v>
       </c>
       <c r="Q154" t="s">
-        <v>2046</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="155" spans="1:17" x14ac:dyDescent="0.25">
@@ -28663,16 +28734,16 @@
         <v>45</v>
       </c>
       <c r="D155" t="s">
-        <v>2047</v>
+        <v>2051</v>
       </c>
       <c r="E155" t="s">
         <v>1198</v>
       </c>
       <c r="F155" t="s">
-        <v>2048</v>
+        <v>2052</v>
       </c>
       <c r="G155" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J155" t="s">
         <v>22</v>
@@ -28687,16 +28758,16 @@
         <v>38</v>
       </c>
       <c r="N155" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O155" t="s">
-        <v>2049</v>
+        <v>2053</v>
       </c>
       <c r="P155" t="s">
-        <v>2050</v>
+        <v>2054</v>
       </c>
       <c r="Q155" t="s">
-        <v>2051</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="156" spans="1:17" x14ac:dyDescent="0.25">
@@ -28710,16 +28781,16 @@
         <v>38</v>
       </c>
       <c r="D156" t="s">
-        <v>2052</v>
+        <v>2056</v>
       </c>
       <c r="E156" t="s">
         <v>1198</v>
       </c>
       <c r="F156" t="s">
-        <v>2053</v>
+        <v>2057</v>
       </c>
       <c r="G156" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J156" t="s">
         <v>22</v>
@@ -28734,16 +28805,16 @@
         <v>38</v>
       </c>
       <c r="N156" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O156" t="s">
-        <v>2054</v>
+        <v>2058</v>
       </c>
       <c r="P156" t="s">
-        <v>2055</v>
+        <v>2059</v>
       </c>
       <c r="Q156" t="s">
-        <v>2056</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="157" spans="1:17" x14ac:dyDescent="0.25">
@@ -28757,16 +28828,16 @@
         <v>68</v>
       </c>
       <c r="D157" t="s">
-        <v>2057</v>
+        <v>2061</v>
       </c>
       <c r="E157" t="s">
         <v>1198</v>
       </c>
       <c r="F157" t="s">
-        <v>2058</v>
+        <v>2062</v>
       </c>
       <c r="G157" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J157" t="s">
         <v>22</v>
@@ -28781,16 +28852,16 @@
         <v>38</v>
       </c>
       <c r="N157" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O157" t="s">
-        <v>2059</v>
+        <v>2063</v>
       </c>
       <c r="P157" t="s">
-        <v>2060</v>
+        <v>2064</v>
       </c>
       <c r="Q157" t="s">
-        <v>2061</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="158" spans="1:17" x14ac:dyDescent="0.25">
@@ -28810,10 +28881,10 @@
         <v>1198</v>
       </c>
       <c r="F158" t="s">
-        <v>2048</v>
+        <v>2052</v>
       </c>
       <c r="G158" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J158" t="s">
         <v>22</v>
@@ -28828,16 +28899,16 @@
         <v>38</v>
       </c>
       <c r="N158" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O158" t="s">
-        <v>2062</v>
+        <v>2066</v>
       </c>
       <c r="P158" t="s">
-        <v>2063</v>
+        <v>2067</v>
       </c>
       <c r="Q158" t="s">
-        <v>2064</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="159" spans="1:17" x14ac:dyDescent="0.25">
@@ -28857,10 +28928,10 @@
         <v>1198</v>
       </c>
       <c r="F159" t="s">
-        <v>2065</v>
+        <v>2069</v>
       </c>
       <c r="G159" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J159" t="s">
         <v>22</v>
@@ -28875,16 +28946,16 @@
         <v>38</v>
       </c>
       <c r="N159" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O159" t="s">
-        <v>2066</v>
+        <v>2070</v>
       </c>
       <c r="P159" t="s">
-        <v>2067</v>
+        <v>2071</v>
       </c>
       <c r="Q159" t="s">
-        <v>2068</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="160" spans="1:17" x14ac:dyDescent="0.25">
@@ -28898,16 +28969,16 @@
         <v>15</v>
       </c>
       <c r="D160" t="s">
-        <v>2069</v>
+        <v>2073</v>
       </c>
       <c r="E160" t="s">
         <v>1198</v>
       </c>
       <c r="F160" t="s">
-        <v>2048</v>
+        <v>2052</v>
       </c>
       <c r="G160" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J160" t="s">
         <v>22</v>
@@ -28922,16 +28993,16 @@
         <v>38</v>
       </c>
       <c r="N160" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O160" t="s">
-        <v>2070</v>
+        <v>2074</v>
       </c>
       <c r="P160" t="s">
-        <v>2071</v>
+        <v>2075</v>
       </c>
       <c r="Q160" t="s">
-        <v>2072</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="161" spans="1:17" x14ac:dyDescent="0.25">
@@ -28945,16 +29016,16 @@
         <v>22</v>
       </c>
       <c r="D161" t="s">
-        <v>2073</v>
+        <v>2077</v>
       </c>
       <c r="E161" t="s">
         <v>1198</v>
       </c>
       <c r="F161" t="s">
-        <v>2074</v>
+        <v>2078</v>
       </c>
       <c r="G161" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J161" t="s">
         <v>22</v>
@@ -28969,16 +29040,16 @@
         <v>38</v>
       </c>
       <c r="N161" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O161" t="s">
-        <v>2075</v>
+        <v>2079</v>
       </c>
       <c r="P161" t="s">
-        <v>2076</v>
+        <v>2080</v>
       </c>
       <c r="Q161" t="s">
-        <v>2077</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="162" spans="1:17" x14ac:dyDescent="0.25">
@@ -28992,7 +29063,7 @@
         <v>25</v>
       </c>
       <c r="D162" t="s">
-        <v>2078</v>
+        <v>2082</v>
       </c>
       <c r="E162" t="s">
         <v>1207</v>
@@ -29001,7 +29072,7 @@
         <v>1208</v>
       </c>
       <c r="G162" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J162" t="s">
         <v>22</v>
@@ -29016,16 +29087,16 @@
         <v>38</v>
       </c>
       <c r="N162" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O162" t="s">
-        <v>2079</v>
+        <v>2083</v>
       </c>
       <c r="P162" t="s">
-        <v>2080</v>
+        <v>2084</v>
       </c>
       <c r="Q162" t="s">
-        <v>2081</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="163" spans="1:17" x14ac:dyDescent="0.25">
@@ -29039,16 +29110,16 @@
         <v>20</v>
       </c>
       <c r="D163" t="s">
-        <v>2082</v>
+        <v>2086</v>
       </c>
       <c r="E163" t="s">
         <v>1207</v>
       </c>
       <c r="F163" t="s">
-        <v>2083</v>
+        <v>2087</v>
       </c>
       <c r="G163" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J163" t="s">
         <v>22</v>
@@ -29063,16 +29134,16 @@
         <v>38</v>
       </c>
       <c r="N163" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O163" t="s">
-        <v>2084</v>
+        <v>2088</v>
       </c>
       <c r="P163" t="s">
-        <v>2085</v>
+        <v>2089</v>
       </c>
       <c r="Q163" t="s">
-        <v>2086</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="164" spans="1:17" x14ac:dyDescent="0.25">
@@ -29086,16 +29157,16 @@
         <v>12</v>
       </c>
       <c r="D164" t="s">
-        <v>2087</v>
+        <v>2091</v>
       </c>
       <c r="E164" t="s">
         <v>1207</v>
       </c>
       <c r="F164" t="s">
-        <v>2088</v>
+        <v>2092</v>
       </c>
       <c r="G164" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J164" t="s">
         <v>22</v>
@@ -29110,16 +29181,16 @@
         <v>38</v>
       </c>
       <c r="N164" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O164" t="s">
-        <v>2089</v>
+        <v>2093</v>
       </c>
       <c r="P164" t="s">
-        <v>2090</v>
+        <v>2094</v>
       </c>
       <c r="Q164" t="s">
-        <v>2091</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="165" spans="1:17" x14ac:dyDescent="0.25">
@@ -29133,16 +29204,16 @@
         <v>15</v>
       </c>
       <c r="D165" t="s">
-        <v>2092</v>
+        <v>2096</v>
       </c>
       <c r="E165" t="s">
         <v>1207</v>
       </c>
       <c r="F165" t="s">
-        <v>2093</v>
+        <v>2097</v>
       </c>
       <c r="G165" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J165" t="s">
         <v>22</v>
@@ -29157,16 +29228,16 @@
         <v>38</v>
       </c>
       <c r="N165" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O165" t="s">
-        <v>2094</v>
+        <v>2098</v>
       </c>
       <c r="P165" t="s">
-        <v>2095</v>
+        <v>2099</v>
       </c>
       <c r="Q165" t="s">
-        <v>2096</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="166" spans="1:17" x14ac:dyDescent="0.25">
@@ -29180,16 +29251,16 @@
         <v>35</v>
       </c>
       <c r="D166" t="s">
-        <v>2097</v>
+        <v>2101</v>
       </c>
       <c r="E166" t="s">
         <v>1207</v>
       </c>
       <c r="F166" t="s">
-        <v>2098</v>
+        <v>2102</v>
       </c>
       <c r="G166" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J166" t="s">
         <v>22</v>
@@ -29204,16 +29275,16 @@
         <v>38</v>
       </c>
       <c r="N166" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O166" t="s">
-        <v>2099</v>
+        <v>2103</v>
       </c>
       <c r="P166" t="s">
-        <v>2100</v>
+        <v>2104</v>
       </c>
       <c r="Q166" t="s">
-        <v>2101</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="167" spans="1:17" x14ac:dyDescent="0.25">
@@ -29227,16 +29298,16 @@
         <v>20</v>
       </c>
       <c r="D167" t="s">
-        <v>2102</v>
+        <v>2106</v>
       </c>
       <c r="E167" t="s">
         <v>1207</v>
       </c>
       <c r="F167" t="s">
-        <v>2093</v>
+        <v>2097</v>
       </c>
       <c r="G167" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J167" t="s">
         <v>22</v>
@@ -29251,16 +29322,16 @@
         <v>38</v>
       </c>
       <c r="N167" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O167" t="s">
-        <v>2103</v>
+        <v>2107</v>
       </c>
       <c r="P167" t="s">
-        <v>2104</v>
+        <v>2108</v>
       </c>
       <c r="Q167" t="s">
-        <v>2105</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="168" spans="1:17" x14ac:dyDescent="0.25">
@@ -29274,16 +29345,16 @@
         <v>15</v>
       </c>
       <c r="D168" t="s">
-        <v>2106</v>
+        <v>2110</v>
       </c>
       <c r="E168" t="s">
         <v>1207</v>
       </c>
       <c r="F168" t="s">
-        <v>2107</v>
+        <v>2111</v>
       </c>
       <c r="G168" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J168" t="s">
         <v>22</v>
@@ -29298,16 +29369,16 @@
         <v>38</v>
       </c>
       <c r="N168" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O168" t="s">
-        <v>2108</v>
+        <v>2112</v>
       </c>
       <c r="P168" t="s">
-        <v>2109</v>
+        <v>2113</v>
       </c>
       <c r="Q168" t="s">
-        <v>2110</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="169" spans="1:17" x14ac:dyDescent="0.25">
@@ -29321,16 +29392,16 @@
         <v>45</v>
       </c>
       <c r="D169" t="s">
-        <v>2111</v>
+        <v>2115</v>
       </c>
       <c r="E169" t="s">
         <v>1207</v>
       </c>
       <c r="F169" t="s">
-        <v>2093</v>
+        <v>2097</v>
       </c>
       <c r="G169" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J169" t="s">
         <v>22</v>
@@ -29345,16 +29416,16 @@
         <v>38</v>
       </c>
       <c r="N169" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O169" t="s">
-        <v>2112</v>
+        <v>2116</v>
       </c>
       <c r="P169" t="s">
-        <v>2113</v>
+        <v>2117</v>
       </c>
       <c r="Q169" t="s">
-        <v>2114</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="170" spans="1:17" x14ac:dyDescent="0.25">
@@ -29368,16 +29439,16 @@
         <v>40</v>
       </c>
       <c r="D170" t="s">
-        <v>2115</v>
+        <v>2119</v>
       </c>
       <c r="E170" t="s">
         <v>1207</v>
       </c>
       <c r="F170" t="s">
-        <v>2116</v>
+        <v>2120</v>
       </c>
       <c r="G170" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J170" t="s">
         <v>22</v>
@@ -29392,16 +29463,16 @@
         <v>38</v>
       </c>
       <c r="N170" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O170" t="s">
-        <v>2117</v>
+        <v>2121</v>
       </c>
       <c r="P170" t="s">
-        <v>2118</v>
+        <v>2122</v>
       </c>
       <c r="Q170" t="s">
-        <v>2119</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="171" spans="1:17" x14ac:dyDescent="0.25">
@@ -29415,16 +29486,16 @@
         <v>60</v>
       </c>
       <c r="D171" t="s">
-        <v>2120</v>
+        <v>2124</v>
       </c>
       <c r="E171" t="s">
         <v>1207</v>
       </c>
       <c r="F171" t="s">
-        <v>2121</v>
+        <v>2125</v>
       </c>
       <c r="G171" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J171" t="s">
         <v>22</v>
@@ -29439,16 +29510,16 @@
         <v>38</v>
       </c>
       <c r="N171" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O171" t="s">
-        <v>2122</v>
+        <v>2126</v>
       </c>
       <c r="P171" t="s">
-        <v>2123</v>
+        <v>2127</v>
       </c>
       <c r="Q171" t="s">
-        <v>2124</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="172" spans="1:17" x14ac:dyDescent="0.25">
@@ -29462,16 +29533,16 @@
         <v>18</v>
       </c>
       <c r="D172" t="s">
-        <v>2125</v>
+        <v>2129</v>
       </c>
       <c r="E172" t="s">
         <v>1207</v>
       </c>
       <c r="F172" t="s">
-        <v>2121</v>
+        <v>2125</v>
       </c>
       <c r="G172" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J172" t="s">
         <v>22</v>
@@ -29486,16 +29557,16 @@
         <v>38</v>
       </c>
       <c r="N172" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O172" t="s">
-        <v>2126</v>
+        <v>2130</v>
       </c>
       <c r="P172" t="s">
-        <v>2127</v>
+        <v>2131</v>
       </c>
       <c r="Q172" t="s">
-        <v>2128</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="173" spans="1:17" x14ac:dyDescent="0.25">
@@ -29509,7 +29580,7 @@
         <v>12</v>
       </c>
       <c r="D173" t="s">
-        <v>2129</v>
+        <v>2133</v>
       </c>
       <c r="E173" t="s">
         <v>1207</v>
@@ -29518,7 +29589,7 @@
         <v>1208</v>
       </c>
       <c r="G173" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J173" t="s">
         <v>22</v>
@@ -29533,16 +29604,16 @@
         <v>38</v>
       </c>
       <c r="N173" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O173" t="s">
-        <v>2130</v>
+        <v>2134</v>
       </c>
       <c r="P173" t="s">
-        <v>2131</v>
+        <v>2135</v>
       </c>
       <c r="Q173" t="s">
-        <v>2132</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="174" spans="1:17" x14ac:dyDescent="0.25">
@@ -29556,7 +29627,7 @@
         <v>12</v>
       </c>
       <c r="D174" t="s">
-        <v>2133</v>
+        <v>2137</v>
       </c>
       <c r="E174" t="s">
         <v>1207</v>
@@ -29565,7 +29636,7 @@
         <v>1208</v>
       </c>
       <c r="G174" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J174" t="s">
         <v>22</v>
@@ -29580,16 +29651,16 @@
         <v>38</v>
       </c>
       <c r="N174" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O174" t="s">
-        <v>2134</v>
+        <v>2138</v>
       </c>
       <c r="P174" t="s">
-        <v>2135</v>
+        <v>2139</v>
       </c>
       <c r="Q174" t="s">
-        <v>2136</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="175" spans="1:17" x14ac:dyDescent="0.25">
@@ -29603,16 +29674,16 @@
         <v>10</v>
       </c>
       <c r="D175" t="s">
-        <v>2137</v>
+        <v>2141</v>
       </c>
       <c r="E175" t="s">
         <v>1207</v>
       </c>
       <c r="F175" t="s">
-        <v>2093</v>
+        <v>2097</v>
       </c>
       <c r="G175" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J175" t="s">
         <v>22</v>
@@ -29627,16 +29698,16 @@
         <v>38</v>
       </c>
       <c r="N175" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O175" t="s">
-        <v>2138</v>
+        <v>2142</v>
       </c>
       <c r="P175" t="s">
-        <v>2139</v>
+        <v>2143</v>
       </c>
       <c r="Q175" t="s">
-        <v>2140</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="176" spans="1:17" x14ac:dyDescent="0.25">
@@ -29650,16 +29721,16 @@
         <v>15</v>
       </c>
       <c r="D176" t="s">
-        <v>2141</v>
+        <v>2145</v>
       </c>
       <c r="E176" t="s">
         <v>1240</v>
       </c>
       <c r="F176" t="s">
-        <v>2142</v>
+        <v>2146</v>
       </c>
       <c r="G176" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="H176">
         <v>201300</v>
@@ -29680,16 +29751,16 @@
         <v>38</v>
       </c>
       <c r="N176" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O176" t="s">
-        <v>2143</v>
+        <v>2147</v>
       </c>
       <c r="P176" t="s">
-        <v>2144</v>
+        <v>2148</v>
       </c>
       <c r="Q176" t="s">
-        <v>2145</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="177" spans="1:17" x14ac:dyDescent="0.25">
@@ -29703,16 +29774,16 @@
         <v>15</v>
       </c>
       <c r="D177" t="s">
-        <v>2146</v>
+        <v>2150</v>
       </c>
       <c r="E177" t="s">
         <v>1240</v>
       </c>
       <c r="F177" t="s">
-        <v>2142</v>
+        <v>2146</v>
       </c>
       <c r="G177" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="H177">
         <v>201300</v>
@@ -29733,16 +29804,16 @@
         <v>38</v>
       </c>
       <c r="N177" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O177" t="s">
-        <v>2147</v>
+        <v>2151</v>
       </c>
       <c r="P177" t="s">
-        <v>2148</v>
+        <v>2152</v>
       </c>
       <c r="Q177" t="s">
-        <v>2149</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="178" spans="1:17" x14ac:dyDescent="0.25">
@@ -29756,7 +29827,7 @@
         <v>20</v>
       </c>
       <c r="D178" t="s">
-        <v>2150</v>
+        <v>2154</v>
       </c>
       <c r="E178" t="s">
         <v>1240</v>
@@ -29765,7 +29836,7 @@
         <v>1284</v>
       </c>
       <c r="G178" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J178" t="s">
         <v>22</v>
@@ -29780,16 +29851,16 @@
         <v>38</v>
       </c>
       <c r="N178" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O178" t="s">
-        <v>2151</v>
+        <v>2155</v>
       </c>
       <c r="P178" t="s">
-        <v>2152</v>
+        <v>2156</v>
       </c>
       <c r="Q178" t="s">
-        <v>2153</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="179" spans="1:17" x14ac:dyDescent="0.25">
@@ -29812,7 +29883,7 @@
         <v>1274</v>
       </c>
       <c r="G179" t="s">
-        <v>2154</v>
+        <v>2158</v>
       </c>
       <c r="J179" t="s">
         <v>22</v>
@@ -29827,16 +29898,16 @@
         <v>25</v>
       </c>
       <c r="N179" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O179" t="s">
-        <v>2155</v>
+        <v>2159</v>
       </c>
       <c r="P179" t="s">
-        <v>2156</v>
+        <v>2160</v>
       </c>
       <c r="Q179" t="s">
-        <v>2157</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="180" spans="1:17" x14ac:dyDescent="0.25">
@@ -29850,16 +29921,16 @@
         <v>40</v>
       </c>
       <c r="D180" t="s">
-        <v>2073</v>
+        <v>2077</v>
       </c>
       <c r="E180" t="s">
         <v>1289</v>
       </c>
       <c r="F180" t="s">
-        <v>2158</v>
+        <v>2162</v>
       </c>
       <c r="G180" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J180" t="s">
         <v>22</v>
@@ -29874,16 +29945,16 @@
         <v>38</v>
       </c>
       <c r="N180" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O180" t="s">
-        <v>2159</v>
+        <v>2163</v>
       </c>
       <c r="P180" t="s">
-        <v>2160</v>
+        <v>2164</v>
       </c>
       <c r="Q180" t="s">
-        <v>2161</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="181" spans="1:17" x14ac:dyDescent="0.25">
@@ -29897,16 +29968,16 @@
         <v>38</v>
       </c>
       <c r="D181" t="s">
-        <v>2162</v>
+        <v>2166</v>
       </c>
       <c r="E181" t="s">
         <v>1289</v>
       </c>
       <c r="F181" t="s">
-        <v>2163</v>
+        <v>2167</v>
       </c>
       <c r="G181" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J181" t="s">
         <v>22</v>
@@ -29921,16 +29992,16 @@
         <v>38</v>
       </c>
       <c r="N181" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O181" t="s">
-        <v>2164</v>
+        <v>2168</v>
       </c>
       <c r="P181" t="s">
-        <v>2165</v>
+        <v>2169</v>
       </c>
       <c r="Q181" t="s">
-        <v>2166</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="182" spans="1:17" x14ac:dyDescent="0.25">
@@ -29944,16 +30015,16 @@
         <v>28</v>
       </c>
       <c r="D182" t="s">
-        <v>2167</v>
+        <v>2171</v>
       </c>
       <c r="E182" t="s">
         <v>1289</v>
       </c>
       <c r="F182" t="s">
-        <v>2168</v>
+        <v>2172</v>
       </c>
       <c r="G182" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J182" t="s">
         <v>22</v>
@@ -29968,16 +30039,16 @@
         <v>38</v>
       </c>
       <c r="N182" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O182" t="s">
-        <v>2169</v>
+        <v>2173</v>
       </c>
       <c r="P182" t="s">
-        <v>2170</v>
+        <v>2174</v>
       </c>
       <c r="Q182" t="s">
-        <v>2171</v>
+        <v>2175</v>
       </c>
     </row>
     <row r="183" spans="1:17" x14ac:dyDescent="0.25">
@@ -29991,16 +30062,16 @@
         <v>25</v>
       </c>
       <c r="D183" t="s">
-        <v>2172</v>
+        <v>2176</v>
       </c>
       <c r="E183" t="s">
         <v>1289</v>
       </c>
       <c r="F183" t="s">
-        <v>2173</v>
+        <v>2177</v>
       </c>
       <c r="G183" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J183" t="s">
         <v>22</v>
@@ -30015,16 +30086,16 @@
         <v>38</v>
       </c>
       <c r="N183" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O183" t="s">
-        <v>2174</v>
+        <v>2178</v>
       </c>
       <c r="P183" t="s">
-        <v>2175</v>
+        <v>2179</v>
       </c>
       <c r="Q183" t="s">
-        <v>2176</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="184" spans="1:17" x14ac:dyDescent="0.25">
@@ -30038,16 +30109,16 @@
         <v>40</v>
       </c>
       <c r="D184" t="s">
-        <v>2177</v>
+        <v>2181</v>
       </c>
       <c r="E184" t="s">
         <v>1289</v>
       </c>
       <c r="F184" t="s">
-        <v>2173</v>
+        <v>2177</v>
       </c>
       <c r="G184" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J184" t="s">
         <v>22</v>
@@ -30062,16 +30133,16 @@
         <v>38</v>
       </c>
       <c r="N184" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O184" t="s">
-        <v>2178</v>
+        <v>2182</v>
       </c>
       <c r="P184" t="s">
-        <v>2179</v>
+        <v>2183</v>
       </c>
       <c r="Q184" t="s">
-        <v>2180</v>
+        <v>2184</v>
       </c>
     </row>
     <row r="185" spans="1:17" x14ac:dyDescent="0.25">
@@ -30091,10 +30162,10 @@
         <v>1289</v>
       </c>
       <c r="F185" t="s">
-        <v>2181</v>
+        <v>2185</v>
       </c>
       <c r="G185" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J185" t="s">
         <v>22</v>
@@ -30109,16 +30180,16 @@
         <v>38</v>
       </c>
       <c r="N185" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O185" t="s">
-        <v>2182</v>
+        <v>2186</v>
       </c>
       <c r="P185" t="s">
-        <v>2183</v>
+        <v>2187</v>
       </c>
       <c r="Q185" t="s">
-        <v>2184</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="186" spans="1:17" x14ac:dyDescent="0.25">
@@ -30132,16 +30203,16 @@
         <v>18</v>
       </c>
       <c r="D186" t="s">
-        <v>2185</v>
+        <v>2189</v>
       </c>
       <c r="E186" t="s">
         <v>1289</v>
       </c>
       <c r="F186" t="s">
-        <v>2158</v>
+        <v>2162</v>
       </c>
       <c r="G186" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J186" t="s">
         <v>22</v>
@@ -30156,16 +30227,16 @@
         <v>38</v>
       </c>
       <c r="N186" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O186" t="s">
-        <v>2186</v>
+        <v>2190</v>
       </c>
       <c r="P186" t="s">
-        <v>2187</v>
+        <v>2191</v>
       </c>
       <c r="Q186" t="s">
-        <v>2188</v>
+        <v>2192</v>
       </c>
     </row>
     <row r="187" spans="1:17" x14ac:dyDescent="0.25">
@@ -30179,16 +30250,16 @@
         <v>20</v>
       </c>
       <c r="D187" t="s">
-        <v>2189</v>
+        <v>2193</v>
       </c>
       <c r="E187" t="s">
         <v>1289</v>
       </c>
       <c r="F187" t="s">
-        <v>2190</v>
+        <v>2194</v>
       </c>
       <c r="G187" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J187" t="s">
         <v>22</v>
@@ -30203,16 +30274,16 @@
         <v>38</v>
       </c>
       <c r="N187" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O187" t="s">
-        <v>2191</v>
+        <v>2195</v>
       </c>
       <c r="P187" t="s">
-        <v>2192</v>
+        <v>2196</v>
       </c>
       <c r="Q187" t="s">
-        <v>2193</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="188" spans="1:17" x14ac:dyDescent="0.25">
@@ -30226,16 +30297,16 @@
         <v>45</v>
       </c>
       <c r="D188" t="s">
-        <v>2194</v>
+        <v>2198</v>
       </c>
       <c r="E188" t="s">
         <v>1289</v>
       </c>
       <c r="F188" t="s">
-        <v>2195</v>
+        <v>2199</v>
       </c>
       <c r="G188" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J188" t="s">
         <v>22</v>
@@ -30250,16 +30321,16 @@
         <v>25</v>
       </c>
       <c r="N188" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O188" t="s">
-        <v>2196</v>
+        <v>2200</v>
       </c>
       <c r="P188" t="s">
-        <v>2197</v>
+        <v>2201</v>
       </c>
       <c r="Q188" t="s">
-        <v>2198</v>
+        <v>2202</v>
       </c>
     </row>
     <row r="189" spans="1:17" x14ac:dyDescent="0.25">
@@ -30273,16 +30344,16 @@
         <v>15</v>
       </c>
       <c r="D189" t="s">
-        <v>2199</v>
+        <v>2203</v>
       </c>
       <c r="E189" t="s">
-        <v>2200</v>
+        <v>2204</v>
       </c>
       <c r="F189" t="s">
-        <v>2201</v>
+        <v>2205</v>
       </c>
       <c r="G189" t="s">
-        <v>2154</v>
+        <v>2158</v>
       </c>
       <c r="J189" t="s">
         <v>22</v>
@@ -30297,16 +30368,16 @@
         <v>38</v>
       </c>
       <c r="N189" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O189" t="s">
-        <v>2202</v>
+        <v>2206</v>
       </c>
       <c r="P189" t="s">
-        <v>2203</v>
+        <v>2207</v>
       </c>
       <c r="Q189" t="s">
-        <v>2204</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="190" spans="1:17" x14ac:dyDescent="0.25">
@@ -30320,16 +30391,16 @@
         <v>25</v>
       </c>
       <c r="D190" t="s">
-        <v>2205</v>
+        <v>2209</v>
       </c>
       <c r="E190" t="s">
-        <v>2200</v>
+        <v>2204</v>
       </c>
       <c r="F190" t="s">
-        <v>2206</v>
+        <v>2210</v>
       </c>
       <c r="G190" t="s">
-        <v>2154</v>
+        <v>2158</v>
       </c>
       <c r="J190" t="s">
         <v>22</v>
@@ -30344,16 +30415,16 @@
         <v>38</v>
       </c>
       <c r="N190" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O190" t="s">
-        <v>2207</v>
+        <v>2211</v>
       </c>
       <c r="P190" t="s">
-        <v>2208</v>
+        <v>2212</v>
       </c>
       <c r="Q190" t="s">
-        <v>2209</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="191" spans="1:17" x14ac:dyDescent="0.25">
@@ -30367,16 +30438,16 @@
         <v>10</v>
       </c>
       <c r="D191" t="s">
-        <v>2210</v>
+        <v>2214</v>
       </c>
       <c r="E191" t="s">
-        <v>2200</v>
+        <v>2204</v>
       </c>
       <c r="F191" t="s">
-        <v>2211</v>
+        <v>2215</v>
       </c>
       <c r="G191" t="s">
-        <v>2154</v>
+        <v>2158</v>
       </c>
       <c r="J191" t="s">
         <v>22</v>
@@ -30391,16 +30462,16 @@
         <v>38</v>
       </c>
       <c r="N191" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O191" t="s">
-        <v>2212</v>
+        <v>2216</v>
       </c>
       <c r="P191" t="s">
-        <v>2213</v>
+        <v>2217</v>
       </c>
       <c r="Q191" t="s">
-        <v>2214</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="192" spans="1:17" x14ac:dyDescent="0.25">
@@ -30414,16 +30485,16 @@
         <v>8</v>
       </c>
       <c r="D192" t="s">
-        <v>2215</v>
+        <v>2219</v>
       </c>
       <c r="E192" t="s">
-        <v>2200</v>
+        <v>2204</v>
       </c>
       <c r="F192" t="s">
-        <v>2216</v>
+        <v>2220</v>
       </c>
       <c r="G192" t="s">
-        <v>2154</v>
+        <v>2158</v>
       </c>
       <c r="J192" t="s">
         <v>22</v>
@@ -30438,16 +30509,16 @@
         <v>38</v>
       </c>
       <c r="N192" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O192" t="s">
-        <v>2217</v>
+        <v>2221</v>
       </c>
       <c r="P192" t="s">
-        <v>2218</v>
+        <v>2222</v>
       </c>
       <c r="Q192" t="s">
-        <v>2219</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="193" spans="1:17" x14ac:dyDescent="0.25">
@@ -30464,13 +30535,13 @@
         <v>174</v>
       </c>
       <c r="E193" t="s">
-        <v>2220</v>
+        <v>2224</v>
       </c>
       <c r="F193" t="s">
-        <v>2221</v>
+        <v>2225</v>
       </c>
       <c r="G193" t="s">
-        <v>2154</v>
+        <v>2158</v>
       </c>
       <c r="J193" t="s">
         <v>22</v>
@@ -30485,16 +30556,16 @@
         <v>32</v>
       </c>
       <c r="N193" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O193" t="s">
-        <v>2222</v>
+        <v>2226</v>
       </c>
       <c r="P193" t="s">
-        <v>2223</v>
+        <v>2227</v>
       </c>
       <c r="Q193" t="s">
-        <v>2224</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="194" spans="1:17" x14ac:dyDescent="0.25">
@@ -30508,16 +30579,16 @@
         <v>45</v>
       </c>
       <c r="D194" t="s">
-        <v>2225</v>
+        <v>2229</v>
       </c>
       <c r="E194" t="s">
-        <v>2220</v>
+        <v>2224</v>
       </c>
       <c r="F194" t="s">
-        <v>2226</v>
+        <v>2230</v>
       </c>
       <c r="G194" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J194" t="s">
         <v>22</v>
@@ -30532,16 +30603,16 @@
         <v>38</v>
       </c>
       <c r="N194" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O194" t="s">
-        <v>2227</v>
+        <v>2231</v>
       </c>
       <c r="P194" t="s">
-        <v>2228</v>
+        <v>2232</v>
       </c>
       <c r="Q194" t="s">
-        <v>2229</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="195" spans="1:17" x14ac:dyDescent="0.25">
@@ -30555,16 +30626,16 @@
         <v>30</v>
       </c>
       <c r="D195" t="s">
-        <v>2230</v>
+        <v>2234</v>
       </c>
       <c r="E195" t="s">
-        <v>2220</v>
+        <v>2224</v>
       </c>
       <c r="F195" t="s">
-        <v>2221</v>
+        <v>2225</v>
       </c>
       <c r="G195" t="s">
-        <v>2154</v>
+        <v>2158</v>
       </c>
       <c r="J195" t="s">
         <v>22</v>
@@ -30579,16 +30650,16 @@
         <v>38</v>
       </c>
       <c r="N195" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O195" t="s">
-        <v>2231</v>
+        <v>2235</v>
       </c>
       <c r="P195" t="s">
-        <v>2232</v>
+        <v>2236</v>
       </c>
       <c r="Q195" t="s">
-        <v>2233</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="196" spans="1:17" x14ac:dyDescent="0.25">
@@ -30602,16 +30673,16 @@
         <v>78</v>
       </c>
       <c r="D196" t="s">
-        <v>2234</v>
+        <v>2238</v>
       </c>
       <c r="E196" t="s">
-        <v>2220</v>
+        <v>2224</v>
       </c>
       <c r="F196" t="s">
-        <v>2221</v>
+        <v>2225</v>
       </c>
       <c r="G196" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J196" t="s">
         <v>22</v>
@@ -30626,16 +30697,16 @@
         <v>32</v>
       </c>
       <c r="N196" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O196" t="s">
-        <v>2235</v>
+        <v>2239</v>
       </c>
       <c r="P196" t="s">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="Q196" t="s">
-        <v>2237</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="197" spans="1:17" x14ac:dyDescent="0.25">
@@ -30649,16 +30720,16 @@
         <v>70</v>
       </c>
       <c r="D197" t="s">
-        <v>2238</v>
+        <v>2242</v>
       </c>
       <c r="E197" t="s">
-        <v>2239</v>
+        <v>2243</v>
       </c>
       <c r="F197" t="s">
-        <v>2240</v>
+        <v>2244</v>
       </c>
       <c r="G197" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J197" t="s">
         <v>22</v>
@@ -30673,16 +30744,16 @@
         <v>25</v>
       </c>
       <c r="N197" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O197" t="s">
-        <v>2241</v>
+        <v>2245</v>
       </c>
       <c r="P197" t="s">
-        <v>2242</v>
+        <v>2246</v>
       </c>
       <c r="Q197" t="s">
-        <v>2243</v>
+        <v>2247</v>
       </c>
     </row>
     <row r="198" spans="1:17" x14ac:dyDescent="0.25">
@@ -30696,16 +30767,16 @@
         <v>55</v>
       </c>
       <c r="D198" t="s">
+        <v>2248</v>
+      </c>
+      <c r="E198" t="s">
+        <v>2243</v>
+      </c>
+      <c r="F198" t="s">
         <v>2244</v>
       </c>
-      <c r="E198" t="s">
-        <v>2239</v>
-      </c>
-      <c r="F198" t="s">
-        <v>2240</v>
-      </c>
       <c r="G198" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J198" t="s">
         <v>22</v>
@@ -30720,16 +30791,16 @@
         <v>25</v>
       </c>
       <c r="N198" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O198" t="s">
-        <v>2245</v>
+        <v>2249</v>
       </c>
       <c r="P198" t="s">
-        <v>2246</v>
+        <v>2250</v>
       </c>
       <c r="Q198" t="s">
-        <v>2247</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="199" spans="1:17" x14ac:dyDescent="0.25">
@@ -30743,16 +30814,16 @@
         <v>35</v>
       </c>
       <c r="D199" t="s">
-        <v>2248</v>
+        <v>2252</v>
       </c>
       <c r="E199" t="s">
-        <v>2249</v>
+        <v>2253</v>
       </c>
       <c r="F199" t="s">
-        <v>2250</v>
+        <v>2254</v>
       </c>
       <c r="G199" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J199" t="s">
         <v>22</v>
@@ -30767,16 +30838,16 @@
         <v>38</v>
       </c>
       <c r="N199" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O199" t="s">
-        <v>2251</v>
+        <v>2255</v>
       </c>
       <c r="P199" t="s">
-        <v>2252</v>
+        <v>2256</v>
       </c>
       <c r="Q199" t="s">
-        <v>2253</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="200" spans="1:17" x14ac:dyDescent="0.25">
@@ -30790,16 +30861,16 @@
         <v>22</v>
       </c>
       <c r="D200" t="s">
-        <v>2073</v>
+        <v>2077</v>
       </c>
       <c r="E200" t="s">
-        <v>2249</v>
+        <v>2253</v>
       </c>
       <c r="F200" t="s">
-        <v>2250</v>
+        <v>2254</v>
       </c>
       <c r="G200" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J200" t="s">
         <v>22</v>
@@ -30814,16 +30885,16 @@
         <v>38</v>
       </c>
       <c r="N200" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O200" t="s">
-        <v>2254</v>
+        <v>2258</v>
       </c>
       <c r="P200" t="s">
-        <v>2255</v>
+        <v>2259</v>
       </c>
       <c r="Q200" t="s">
-        <v>2256</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="201" spans="1:17" x14ac:dyDescent="0.25">
@@ -30837,16 +30908,16 @@
         <v>42</v>
       </c>
       <c r="D201" t="s">
-        <v>2257</v>
+        <v>2261</v>
       </c>
       <c r="E201" t="s">
-        <v>2249</v>
+        <v>2253</v>
       </c>
       <c r="F201" t="s">
-        <v>2250</v>
+        <v>2254</v>
       </c>
       <c r="G201" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J201" t="s">
         <v>22</v>
@@ -30861,16 +30932,16 @@
         <v>38</v>
       </c>
       <c r="N201" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O201" t="s">
-        <v>2258</v>
+        <v>2262</v>
       </c>
       <c r="P201" t="s">
-        <v>2259</v>
+        <v>2263</v>
       </c>
       <c r="Q201" t="s">
-        <v>2260</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="202" spans="1:17" x14ac:dyDescent="0.25">
@@ -30884,16 +30955,16 @@
         <v>50</v>
       </c>
       <c r="D202" t="s">
-        <v>2261</v>
+        <v>2265</v>
       </c>
       <c r="E202" t="s">
         <v>1351</v>
       </c>
       <c r="F202" t="s">
+        <v>2162</v>
+      </c>
+      <c r="G202" t="s">
         <v>2158</v>
-      </c>
-      <c r="G202" t="s">
-        <v>2154</v>
       </c>
       <c r="H202">
         <v>150000</v>
@@ -30914,16 +30985,16 @@
         <v>25</v>
       </c>
       <c r="N202" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O202" t="s">
-        <v>2262</v>
+        <v>2266</v>
       </c>
       <c r="P202" t="s">
-        <v>2263</v>
+        <v>2267</v>
       </c>
       <c r="Q202" t="s">
-        <v>2264</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="203" spans="1:17" x14ac:dyDescent="0.25">
@@ -30937,16 +31008,16 @@
         <v>35</v>
       </c>
       <c r="D203" t="s">
-        <v>2265</v>
+        <v>2269</v>
       </c>
       <c r="E203" t="s">
         <v>1351</v>
       </c>
       <c r="F203" t="s">
-        <v>2266</v>
+        <v>2270</v>
       </c>
       <c r="G203" t="s">
-        <v>2154</v>
+        <v>2158</v>
       </c>
       <c r="H203">
         <v>140000</v>
@@ -30967,16 +31038,16 @@
         <v>38</v>
       </c>
       <c r="N203" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O203" t="s">
-        <v>2267</v>
+        <v>2271</v>
       </c>
       <c r="P203" t="s">
-        <v>2268</v>
+        <v>2272</v>
       </c>
       <c r="Q203" t="s">
-        <v>2269</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="204" spans="1:17" x14ac:dyDescent="0.25">
@@ -30990,16 +31061,16 @@
         <v>25</v>
       </c>
       <c r="D204" t="s">
-        <v>2270</v>
+        <v>2274</v>
       </c>
       <c r="E204" t="s">
-        <v>2271</v>
+        <v>2275</v>
       </c>
       <c r="F204" t="s">
-        <v>2272</v>
+        <v>2276</v>
       </c>
       <c r="G204" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J204" t="s">
         <v>22</v>
@@ -31014,16 +31085,16 @@
         <v>38</v>
       </c>
       <c r="N204" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O204" t="s">
-        <v>2273</v>
+        <v>2277</v>
       </c>
       <c r="P204" t="s">
-        <v>2274</v>
+        <v>2278</v>
       </c>
       <c r="Q204" t="s">
-        <v>2275</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="205" spans="1:17" x14ac:dyDescent="0.25">
@@ -31037,16 +31108,16 @@
         <v>62</v>
       </c>
       <c r="D205" t="s">
+        <v>2280</v>
+      </c>
+      <c r="E205" t="s">
+        <v>2275</v>
+      </c>
+      <c r="F205" t="s">
         <v>2276</v>
       </c>
-      <c r="E205" t="s">
-        <v>2271</v>
-      </c>
-      <c r="F205" t="s">
-        <v>2272</v>
-      </c>
       <c r="G205" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J205" t="s">
         <v>22</v>
@@ -31061,16 +31132,16 @@
         <v>25</v>
       </c>
       <c r="N205" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O205" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
       <c r="P205" t="s">
-        <v>2278</v>
+        <v>2282</v>
       </c>
       <c r="Q205" t="s">
-        <v>2279</v>
+        <v>2283</v>
       </c>
     </row>
     <row r="206" spans="1:17" x14ac:dyDescent="0.25">
@@ -31084,16 +31155,16 @@
         <v>18</v>
       </c>
       <c r="D206" t="s">
-        <v>2280</v>
+        <v>2284</v>
       </c>
       <c r="E206" t="s">
-        <v>2271</v>
+        <v>2275</v>
       </c>
       <c r="F206" t="s">
-        <v>2281</v>
+        <v>2285</v>
       </c>
       <c r="G206" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J206" t="s">
         <v>22</v>
@@ -31108,16 +31179,16 @@
         <v>38</v>
       </c>
       <c r="N206" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O206" t="s">
-        <v>2282</v>
+        <v>2286</v>
       </c>
       <c r="P206" t="s">
-        <v>2283</v>
+        <v>2287</v>
       </c>
       <c r="Q206" t="s">
-        <v>2284</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="207" spans="1:17" x14ac:dyDescent="0.25">
@@ -31131,16 +31202,16 @@
         <v>45</v>
       </c>
       <c r="D207" t="s">
-        <v>2285</v>
+        <v>2289</v>
       </c>
       <c r="E207" t="s">
-        <v>2286</v>
+        <v>2290</v>
       </c>
       <c r="F207" t="s">
-        <v>2158</v>
+        <v>2162</v>
       </c>
       <c r="G207" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J207" t="s">
         <v>22</v>
@@ -31155,16 +31226,16 @@
         <v>25</v>
       </c>
       <c r="N207" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O207" t="s">
-        <v>2287</v>
+        <v>2291</v>
       </c>
       <c r="P207" t="s">
-        <v>2288</v>
+        <v>2292</v>
       </c>
       <c r="Q207" t="s">
-        <v>2289</v>
+        <v>2293</v>
       </c>
     </row>
     <row r="208" spans="1:17" x14ac:dyDescent="0.25">
@@ -31178,16 +31249,16 @@
         <v>32</v>
       </c>
       <c r="D208" t="s">
+        <v>2294</v>
+      </c>
+      <c r="E208" t="s">
         <v>2290</v>
       </c>
-      <c r="E208" t="s">
-        <v>2286</v>
-      </c>
       <c r="F208" t="s">
-        <v>2291</v>
+        <v>2295</v>
       </c>
       <c r="G208" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J208" t="s">
         <v>22</v>
@@ -31202,16 +31273,16 @@
         <v>38</v>
       </c>
       <c r="N208" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O208" t="s">
-        <v>2292</v>
+        <v>2296</v>
       </c>
       <c r="P208" t="s">
-        <v>2293</v>
+        <v>2297</v>
       </c>
       <c r="Q208" t="s">
-        <v>2294</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="209" spans="1:17" x14ac:dyDescent="0.25">
@@ -31225,16 +31296,16 @@
         <v>42</v>
       </c>
       <c r="D209" t="s">
+        <v>2299</v>
+      </c>
+      <c r="E209" t="s">
+        <v>2290</v>
+      </c>
+      <c r="F209" t="s">
         <v>2295</v>
       </c>
-      <c r="E209" t="s">
-        <v>2286</v>
-      </c>
-      <c r="F209" t="s">
-        <v>2291</v>
-      </c>
       <c r="G209" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="J209" t="s">
         <v>22</v>
@@ -31249,16 +31320,69 @@
         <v>25</v>
       </c>
       <c r="N209" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="O209" t="s">
-        <v>2296</v>
+        <v>2300</v>
       </c>
       <c r="P209" t="s">
-        <v>2297</v>
+        <v>2301</v>
       </c>
       <c r="Q209" t="s">
-        <v>2298</v>
+        <v>2302</v>
+      </c>
+    </row>
+    <row r="210" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>17</v>
+      </c>
+      <c r="B210">
+        <v>52</v>
+      </c>
+      <c r="C210">
+        <v>45</v>
+      </c>
+      <c r="D210" t="s">
+        <v>108</v>
+      </c>
+      <c r="E210" t="s">
+        <v>421</v>
+      </c>
+      <c r="F210" t="s">
+        <v>2303</v>
+      </c>
+      <c r="G210" t="s">
+        <v>1380</v>
+      </c>
+      <c r="H210">
+        <v>219100</v>
+      </c>
+      <c r="I210">
+        <v>219100</v>
+      </c>
+      <c r="J210" t="s">
+        <v>64</v>
+      </c>
+      <c r="K210" t="s">
+        <v>423</v>
+      </c>
+      <c r="L210" t="s">
+        <v>1359</v>
+      </c>
+      <c r="M210" t="s">
+        <v>25</v>
+      </c>
+      <c r="N210" t="s">
+        <v>1365</v>
+      </c>
+      <c r="O210" t="s">
+        <v>2304</v>
+      </c>
+      <c r="P210" t="s">
+        <v>2305</v>
+      </c>
+      <c r="Q210" t="s">
+        <v>2306</v>
       </c>
     </row>
   </sheetData>

--- a/hunt/board.xlsx
+++ b/hunt/board.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6339" uniqueCount="2307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6482" uniqueCount="2354">
   <si>
     <t>Column</t>
   </si>
@@ -4103,6 +4103,96 @@
     <t>https://himalayas.app/companies/particle41/jobs/lead-devops-engineer</t>
   </si>
   <si>
+    <t>Solution Architect: Future Opportunities</t>
+  </si>
+  <si>
+    <t>Stitch Consulting Services, Inc.</t>
+  </si>
+  <si>
+    <t>2026-09-06T14:46:28.146Z</t>
+  </si>
+  <si>
+    <t>Remote, US-wide, and titled Solution Architect with enterprise client-facing advisory work — matches candidate's trusted-advisor engagement style | Fortune 1000 client base means enterprise-scale integration and requirements-gathering, an area the candidate has done for 10 years</t>
+  </si>
+  <si>
+    <t>Core stack is Braze CRM/martech and Databricks — no overlap with candidate's Azure DevOps/GitHub/GHAS/governance depth | Explicitly a pipeline/talent-bank posting, not an open req: 'We're not actively hiring for this role today' | No salary posted and martech consultancies frequently land below the $180K floor</t>
+  </si>
+  <si>
+    <t>https://himalayas.app/companies/stitch-consulting-services-inc/jobs/solution-architect-future-opportunities</t>
+  </si>
+  <si>
+    <t>HealthEdge</t>
+  </si>
+  <si>
+    <t>Healthcare payer domain aligns with candidate's HIPAA-driven compliance architecture background | Remote US role focused on enterprise integration architecture and customer/vendor-facing technical implementation — matches the customer engineer advisory model | Senior Solution Architect title is in the candidate's stated target list</t>
+  </si>
+  <si>
+    <t>Role centers on UST HealthProof core-admin platform integration (EDI/claims ecosystem), not cloud platform/DevOps architecture — candidate has no core-admin domain experience | Confirmed band tops out at $180,000, meaning the candidate's floor is only reachable at the absolute maximum | Scope reads senior-IC integration delivery, below the principal-level scope the candidate targets</t>
+  </si>
+  <si>
+    <t>https://himalayas.app/companies/healthedge/jobs/senior-solution-architect</t>
+  </si>
+  <si>
+    <t>Principal Solutions Architect (AWS Technical Alliances)</t>
+  </si>
+  <si>
+    <t>Tenable</t>
+  </si>
+  <si>
+    <t>Principal-level title and remote US — directly on the candidate's target list and workplace preference | Cybersecurity/exposure-management domain overlaps with candidate's GHAS, Defender for Cloud, and NIST/FIPS compliance work | Confirmed band $175K–$233,666 comfortably clears the $180K floor above the midpoint</t>
+  </si>
+  <si>
+    <t>Role is explicitly an AWS Technical Alliances architect — deep AWS marketplace/service integration depth is the core requirement and the candidate is Azure-primary | Partner/alliances motion involves joint go-to-market and marketplace enablement, which is adjacent to but not the same as the candidate's enterprise delivery advisory</t>
+  </si>
+  <si>
+    <t>https://jobicy.com/jobs/152664-principal-solutions-architect-aws-technical-alliances</t>
+  </si>
+  <si>
+    <t>Platform Architect</t>
+  </si>
+  <si>
+    <t>Instructure</t>
+  </si>
+  <si>
+    <t>Confirmed $200K–$230K remote band, meaningfully above the $180K floor | Developer portal / Platform-as-a-Service architecture and developer experience align with candidate's CI/CD, GitHub Enterprise, and internal-platform enablement work | Architect-level scope with mentoring of engineering teams matches the principal-level ambition</t>
+  </si>
+  <si>
+    <t>Product-engineering architecture role (building Instructure's own platform) rather than customer-facing advisory — candidate's 10 years skew toward consulting/enablement | Likely AWS-centric SaaS stack and deep hands-on distributed-systems design; candidate's Azure-first background may not map cleanly | EdTech domain lacks the regulated-industry precedent the candidate leans on</t>
+  </si>
+  <si>
+    <t>https://jobicy.com/jobs/152637-platform-architect</t>
+  </si>
+  <si>
+    <t>Senior Manager, IT Platform Engineering - FIXED TERM</t>
+  </si>
+  <si>
+    <t>ŌURA</t>
+  </si>
+  <si>
+    <t>Identity, RBAC, and infrastructure ownership map directly onto candidate's Entra ID, Managed Identity, and Key Vault experience | Remote US with a confirmed $169K–$230K band that can clear the $180K floor | Health-tech company with likely HIPAA-adjacent controls the candidate has handled</t>
+  </si>
+  <si>
+    <t>People-management role (leads a team) rather than an architect IC track — candidate's targets are all architect/principal IC titles | FIXED TERM contract, not the permanent full-time employment the candidate is seeking | Corporate IT/workforce platform scope (SaaS, endpoint, identity ops) rather than cloud solution architecture</t>
+  </si>
+  <si>
+    <t>https://jobicy.com/jobs/148338-senior-manager-it-platform-engineering-fixed-term</t>
+  </si>
+  <si>
+    <t>Lead Deployment Architect</t>
+  </si>
+  <si>
+    <t>celonis</t>
+  </si>
+  <si>
+    <t>Lead-level, customer-facing delivery architecture within Celonis Services — matches the candidate's enterprise advisory delivery model | Listed as remote, so no immediate onsite constraint</t>
+  </si>
+  <si>
+    <t>Requires Celonis process-mining platform and Context Model expertise the candidate does not have | Munich-anchored role in the EU, outside the candidate's stated US market scope and likely requiring German work authorization | No salary posted; EU comp is unlikely to reach the $180K USD floor</t>
+  </si>
+  <si>
+    <t>https://www.arbeitnow.com/jobs/companies/celonis/lead-deployment-architect-munich-326905</t>
+  </si>
+  <si>
     <t>Delivery Solutions Architect - Communications, Media, Entertainment &amp; Games</t>
   </si>
   <si>
@@ -6911,9 +7001,6 @@
     <t>https://apply.workable.com/j/D51749C6F9</t>
   </si>
   <si>
-    <t>Platform Architect</t>
-  </si>
-  <si>
     <t>Enterprise architecture governance, current/future-state architectures and technology roadmaps align with the candidate's Azure governance and CAF/WAF advisory work | Public-sector/federal environment fits the candidate's includeFederal scope and compliance experience (NIST, FIPS) | Architect-level scope with modernization and governance ownership</t>
   </si>
   <si>
@@ -6933,6 +7020,60 @@
   </si>
   <si>
     <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8769750002</t>
+  </si>
+  <si>
+    <t>New Jersey</t>
+  </si>
+  <si>
+    <t>Explicitly a trusted-advisor role owning end-to-end technical strategy for customer architects — mirrors the candidate's Customer Engineer engagement model | Posting states candidates outside New Jersey will be considered, softening the location constraint | Confirmed $180K meets the stated salary floor exactly</t>
+  </si>
+  <si>
+    <t>Requires deep Databricks/Spark data &amp; AI platform specialization; candidate's depth is Azure DevOps, GitHub, and governance, not data lakehouse architecture | Vertical focus (Communications, Media, Entertainment, Games) is outside candidate's regulated-industry precedent | Pre-sales SA role tied to account adoption targets, and comp at the floor with no upside band shown</t>
+  </si>
+  <si>
+    <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8755492002</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>Confirmed $219K well above the $180K floor | Senior SA scope with customer technical leadership matches the candidate's target seniority and advisory strengths | Posting notes candidates in other locations will be considered, so Houston-based remote may be viable</t>
+  </si>
+  <si>
+    <t>Databricks lakehouse/data-AI platform depth is the central hiring bar and is absent from the candidate's profile | Chicago-listed role with unclear onsite requirement | Field SA roles carry variable/quota-linked comp and heavy travel not reflected in the candidate's current profile</t>
+  </si>
+  <si>
+    <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8769764002</t>
+  </si>
+  <si>
+    <t>Consultative architecture role including C-level advisory, which matches the candidate's trusted-advisor posture | Production AI infrastructure work touches deployment and pipeline concerns the candidate knows</t>
+  </si>
+  <si>
+    <t>Munich-based German-language posting (m/w/d, German-only description) — outside the candidate's stated US market scope | Requires hands-on LLM/agentic depth (LangGraph, PydanticAI, Mastra, eval pipelines) that the candidate does not demonstrate | No salary listed; German market comp will fall far below a $180K USD floor</t>
+  </si>
+  <si>
+    <t>https://www.arbeitnow.com/jobs/companies/mayflower/senior-ai-architect-consultant-munchen-91359</t>
+  </si>
+  <si>
+    <t>Architect-titled role with technical leadership and direct customer/supplier interfacing</t>
+  </si>
+  <si>
+    <t>Spacecraft propulsion fluidic systems, CFD simulation, and MBSE — zero overlap with cloud/DevOps architecture | Munich onsite role outside the candidate's US market scope | No compensation listed and aerospace engineering pay in Germany is far below the $180K floor</t>
+  </si>
+  <si>
+    <t>https://www.arbeitnow.com/jobs/companies/deltavision/fluidic-system-engineer-architect-munchen-235120</t>
+  </si>
+  <si>
+    <t>Senior Partner Solutions Architect</t>
+  </si>
+  <si>
+    <t>Solutions Architect title and trusted-advisor engagement model align directly with the candidate's current Customer Engineer / Cloud Solutions Architect work with enterprise customers | Confirmed $200K base clears the $180K salary floor comfortably | Partner-enablement work (technical force multiplier, enabling SI/partner teams) maps well to the candidate's DevOps maturity assessment and enterprise advisory experience</t>
+  </si>
+  <si>
+    <t>Elastic PSA roles center on Elasticsearch/observability/security product depth (search, ELK stack, vector/AI search) — the candidate's resume shows no Elastic Stack experience | Partner ecosystem SA work is heavily pre-sales and partner-GTM oriented, a different motion from the candidate's Azure DevOps/GitHub platform delivery focus | Elastic architecture depth is typically AWS/GCP-multicloud-first; candidate's depth is Azure-specific, and no location or workplace type is stated in the posting</t>
+  </si>
+  <si>
+    <t>https://www.arbeitnow.fr/jobs/companies/elastic/senior-partner-solutions-architect-460245</t>
   </si>
 </sst>
 </file>
@@ -7313,7 +7454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q277"/>
+  <dimension ref="A1:Q283"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -21117,6 +21258,312 @@
         <v>1362</v>
       </c>
     </row>
+    <row r="278" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>17</v>
+      </c>
+      <c r="B278">
+        <v>25</v>
+      </c>
+      <c r="C278">
+        <v>30</v>
+      </c>
+      <c r="D278" t="s">
+        <v>1363</v>
+      </c>
+      <c r="E278" t="s">
+        <v>1364</v>
+      </c>
+      <c r="F278" t="s">
+        <v>20</v>
+      </c>
+      <c r="G278" t="s">
+        <v>21</v>
+      </c>
+      <c r="J278" t="s">
+        <v>22</v>
+      </c>
+      <c r="K278" t="s">
+        <v>23</v>
+      </c>
+      <c r="L278" t="s">
+        <v>1365</v>
+      </c>
+      <c r="M278" t="s">
+        <v>38</v>
+      </c>
+      <c r="N278" t="s">
+        <v>26</v>
+      </c>
+      <c r="O278" t="s">
+        <v>1366</v>
+      </c>
+      <c r="P278" t="s">
+        <v>1367</v>
+      </c>
+      <c r="Q278" t="s">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="279" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>17</v>
+      </c>
+      <c r="B279">
+        <v>52</v>
+      </c>
+      <c r="C279">
+        <v>58</v>
+      </c>
+      <c r="D279" t="s">
+        <v>1343</v>
+      </c>
+      <c r="E279" t="s">
+        <v>1369</v>
+      </c>
+      <c r="F279" t="s">
+        <v>20</v>
+      </c>
+      <c r="G279" t="s">
+        <v>21</v>
+      </c>
+      <c r="H279">
+        <v>150000</v>
+      </c>
+      <c r="I279">
+        <v>180000</v>
+      </c>
+      <c r="J279" t="s">
+        <v>64</v>
+      </c>
+      <c r="K279" t="s">
+        <v>23</v>
+      </c>
+      <c r="L279" t="s">
+        <v>1365</v>
+      </c>
+      <c r="M279" t="s">
+        <v>25</v>
+      </c>
+      <c r="N279" t="s">
+        <v>26</v>
+      </c>
+      <c r="O279" t="s">
+        <v>1370</v>
+      </c>
+      <c r="P279" t="s">
+        <v>1371</v>
+      </c>
+      <c r="Q279" t="s">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="280" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>17</v>
+      </c>
+      <c r="B280">
+        <v>66</v>
+      </c>
+      <c r="C280">
+        <v>52</v>
+      </c>
+      <c r="D280" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E280" t="s">
+        <v>1374</v>
+      </c>
+      <c r="F280" t="s">
+        <v>507</v>
+      </c>
+      <c r="G280" t="s">
+        <v>21</v>
+      </c>
+      <c r="H280">
+        <v>175000</v>
+      </c>
+      <c r="I280">
+        <v>233666</v>
+      </c>
+      <c r="J280" t="s">
+        <v>64</v>
+      </c>
+      <c r="K280" t="s">
+        <v>501</v>
+      </c>
+      <c r="L280" t="s">
+        <v>1365</v>
+      </c>
+      <c r="M280" t="s">
+        <v>25</v>
+      </c>
+      <c r="N280" t="s">
+        <v>26</v>
+      </c>
+      <c r="O280" t="s">
+        <v>1375</v>
+      </c>
+      <c r="P280" t="s">
+        <v>1376</v>
+      </c>
+      <c r="Q280" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="281" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>17</v>
+      </c>
+      <c r="B281">
+        <v>62</v>
+      </c>
+      <c r="C281">
+        <v>55</v>
+      </c>
+      <c r="D281" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E281" t="s">
+        <v>1379</v>
+      </c>
+      <c r="F281" t="s">
+        <v>507</v>
+      </c>
+      <c r="G281" t="s">
+        <v>21</v>
+      </c>
+      <c r="H281">
+        <v>200000</v>
+      </c>
+      <c r="I281">
+        <v>230000</v>
+      </c>
+      <c r="J281" t="s">
+        <v>64</v>
+      </c>
+      <c r="K281" t="s">
+        <v>501</v>
+      </c>
+      <c r="L281" t="s">
+        <v>1365</v>
+      </c>
+      <c r="M281" t="s">
+        <v>25</v>
+      </c>
+      <c r="N281" t="s">
+        <v>26</v>
+      </c>
+      <c r="O281" t="s">
+        <v>1380</v>
+      </c>
+      <c r="P281" t="s">
+        <v>1381</v>
+      </c>
+      <c r="Q281" t="s">
+        <v>1382</v>
+      </c>
+    </row>
+    <row r="282" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>17</v>
+      </c>
+      <c r="B282">
+        <v>45</v>
+      </c>
+      <c r="C282">
+        <v>50</v>
+      </c>
+      <c r="D282" t="s">
+        <v>1383</v>
+      </c>
+      <c r="E282" t="s">
+        <v>1384</v>
+      </c>
+      <c r="F282" t="s">
+        <v>507</v>
+      </c>
+      <c r="G282" t="s">
+        <v>21</v>
+      </c>
+      <c r="H282">
+        <v>169000</v>
+      </c>
+      <c r="I282">
+        <v>230000</v>
+      </c>
+      <c r="J282" t="s">
+        <v>64</v>
+      </c>
+      <c r="K282" t="s">
+        <v>501</v>
+      </c>
+      <c r="L282" t="s">
+        <v>1365</v>
+      </c>
+      <c r="M282" t="s">
+        <v>25</v>
+      </c>
+      <c r="N282" t="s">
+        <v>26</v>
+      </c>
+      <c r="O282" t="s">
+        <v>1385</v>
+      </c>
+      <c r="P282" t="s">
+        <v>1386</v>
+      </c>
+      <c r="Q282" t="s">
+        <v>1387</v>
+      </c>
+    </row>
+    <row r="283" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>17</v>
+      </c>
+      <c r="B283">
+        <v>32</v>
+      </c>
+      <c r="C283">
+        <v>35</v>
+      </c>
+      <c r="D283" t="s">
+        <v>1388</v>
+      </c>
+      <c r="E283" t="s">
+        <v>1389</v>
+      </c>
+      <c r="F283" t="s">
+        <v>1016</v>
+      </c>
+      <c r="G283" t="s">
+        <v>21</v>
+      </c>
+      <c r="J283" t="s">
+        <v>22</v>
+      </c>
+      <c r="K283" t="s">
+        <v>557</v>
+      </c>
+      <c r="L283" t="s">
+        <v>1365</v>
+      </c>
+      <c r="M283" t="s">
+        <v>38</v>
+      </c>
+      <c r="N283" t="s">
+        <v>26</v>
+      </c>
+      <c r="O283" t="s">
+        <v>1390</v>
+      </c>
+      <c r="P283" t="s">
+        <v>1391</v>
+      </c>
+      <c r="Q283" t="s">
+        <v>1392</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:Q1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -21126,7 +21573,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q210"/>
+  <dimension ref="A1:Q215"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -21207,7 +21654,7 @@
         <v>52</v>
       </c>
       <c r="D2" t="s">
-        <v>1363</v>
+        <v>1393</v>
       </c>
       <c r="E2" t="s">
         <v>421</v>
@@ -21216,7 +21663,7 @@
         <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="H2">
         <v>180000</v>
@@ -21237,16 +21684,16 @@
         <v>25</v>
       </c>
       <c r="N2" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O2" t="s">
-        <v>1366</v>
+        <v>1396</v>
       </c>
       <c r="P2" t="s">
-        <v>1367</v>
+        <v>1397</v>
       </c>
       <c r="Q2" t="s">
-        <v>1368</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -21260,7 +21707,7 @@
         <v>55</v>
       </c>
       <c r="D3" t="s">
-        <v>1369</v>
+        <v>1399</v>
       </c>
       <c r="E3" t="s">
         <v>421</v>
@@ -21269,7 +21716,7 @@
         <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="H3">
         <v>180000</v>
@@ -21290,16 +21737,16 @@
         <v>25</v>
       </c>
       <c r="N3" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O3" t="s">
-        <v>1370</v>
+        <v>1400</v>
       </c>
       <c r="P3" t="s">
-        <v>1371</v>
+        <v>1401</v>
       </c>
       <c r="Q3" t="s">
-        <v>1372</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
@@ -21313,16 +21760,16 @@
         <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>1373</v>
+        <v>1403</v>
       </c>
       <c r="E4" t="s">
         <v>421</v>
       </c>
       <c r="F4" t="s">
-        <v>1374</v>
+        <v>1404</v>
       </c>
       <c r="G4" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="H4">
         <v>219100</v>
@@ -21343,16 +21790,16 @@
         <v>25</v>
       </c>
       <c r="N4" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O4" t="s">
-        <v>1375</v>
+        <v>1405</v>
       </c>
       <c r="P4" t="s">
-        <v>1376</v>
+        <v>1406</v>
       </c>
       <c r="Q4" t="s">
-        <v>1377</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -21366,16 +21813,16 @@
         <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>1378</v>
+        <v>1408</v>
       </c>
       <c r="E5" t="s">
         <v>421</v>
       </c>
       <c r="F5" t="s">
-        <v>1379</v>
+        <v>1409</v>
       </c>
       <c r="G5" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="H5">
         <v>180000</v>
@@ -21396,16 +21843,16 @@
         <v>25</v>
       </c>
       <c r="N5" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O5" t="s">
-        <v>1381</v>
+        <v>1411</v>
       </c>
       <c r="P5" t="s">
-        <v>1382</v>
+        <v>1412</v>
       </c>
       <c r="Q5" t="s">
-        <v>1383</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -21419,7 +21866,7 @@
         <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>1384</v>
+        <v>1414</v>
       </c>
       <c r="E6" t="s">
         <v>421</v>
@@ -21428,7 +21875,7 @@
         <v>20</v>
       </c>
       <c r="G6" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="H6">
         <v>219100</v>
@@ -21449,16 +21896,16 @@
         <v>38</v>
       </c>
       <c r="N6" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O6" t="s">
-        <v>1385</v>
+        <v>1415</v>
       </c>
       <c r="P6" t="s">
-        <v>1386</v>
+        <v>1416</v>
       </c>
       <c r="Q6" t="s">
-        <v>1387</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -21472,7 +21919,7 @@
         <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>1388</v>
+        <v>1418</v>
       </c>
       <c r="E7" t="s">
         <v>421</v>
@@ -21481,7 +21928,7 @@
         <v>20</v>
       </c>
       <c r="G7" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="H7">
         <v>219100</v>
@@ -21502,16 +21949,16 @@
         <v>25</v>
       </c>
       <c r="N7" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O7" t="s">
-        <v>1389</v>
+        <v>1419</v>
       </c>
       <c r="P7" t="s">
-        <v>1390</v>
+        <v>1420</v>
       </c>
       <c r="Q7" t="s">
-        <v>1391</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -21525,16 +21972,16 @@
         <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>1392</v>
+        <v>1422</v>
       </c>
       <c r="E8" t="s">
         <v>421</v>
       </c>
       <c r="F8" t="s">
-        <v>1393</v>
+        <v>1423</v>
       </c>
       <c r="G8" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J8" t="s">
         <v>22</v>
@@ -21549,16 +21996,16 @@
         <v>38</v>
       </c>
       <c r="N8" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O8" t="s">
-        <v>1394</v>
+        <v>1424</v>
       </c>
       <c r="P8" t="s">
-        <v>1395</v>
+        <v>1425</v>
       </c>
       <c r="Q8" t="s">
-        <v>1396</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -21572,16 +22019,16 @@
         <v>58</v>
       </c>
       <c r="D9" t="s">
-        <v>1397</v>
+        <v>1427</v>
       </c>
       <c r="E9" t="s">
-        <v>1398</v>
+        <v>1428</v>
       </c>
       <c r="F9" t="s">
-        <v>1399</v>
+        <v>1429</v>
       </c>
       <c r="G9" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="H9">
         <v>257000</v>
@@ -21602,16 +22049,16 @@
         <v>25</v>
       </c>
       <c r="N9" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O9" t="s">
-        <v>1400</v>
+        <v>1430</v>
       </c>
       <c r="P9" t="s">
-        <v>1401</v>
+        <v>1431</v>
       </c>
       <c r="Q9" t="s">
-        <v>1402</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -21628,13 +22075,13 @@
         <v>145</v>
       </c>
       <c r="E10" t="s">
-        <v>1403</v>
+        <v>1433</v>
       </c>
       <c r="F10" t="s">
-        <v>1404</v>
+        <v>1434</v>
       </c>
       <c r="G10" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="H10">
         <v>200000</v>
@@ -21655,16 +22102,16 @@
         <v>38</v>
       </c>
       <c r="N10" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O10" t="s">
-        <v>1405</v>
+        <v>1435</v>
       </c>
       <c r="P10" t="s">
-        <v>1406</v>
+        <v>1436</v>
       </c>
       <c r="Q10" t="s">
-        <v>1407</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -21678,16 +22125,16 @@
         <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>1408</v>
+        <v>1438</v>
       </c>
       <c r="E11" t="s">
         <v>698</v>
       </c>
       <c r="F11" t="s">
-        <v>1409</v>
+        <v>1439</v>
       </c>
       <c r="G11" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J11" t="s">
         <v>22</v>
@@ -21702,16 +22149,16 @@
         <v>38</v>
       </c>
       <c r="N11" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O11" t="s">
-        <v>1410</v>
+        <v>1440</v>
       </c>
       <c r="P11" t="s">
-        <v>1411</v>
+        <v>1441</v>
       </c>
       <c r="Q11" t="s">
-        <v>1412</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -21731,10 +22178,10 @@
         <v>698</v>
       </c>
       <c r="F12" t="s">
-        <v>1413</v>
+        <v>1443</v>
       </c>
       <c r="G12" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J12" t="s">
         <v>22</v>
@@ -21749,16 +22196,16 @@
         <v>38</v>
       </c>
       <c r="N12" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O12" t="s">
-        <v>1414</v>
+        <v>1444</v>
       </c>
       <c r="P12" t="s">
-        <v>1415</v>
+        <v>1445</v>
       </c>
       <c r="Q12" t="s">
-        <v>1416</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
@@ -21772,16 +22219,16 @@
         <v>15</v>
       </c>
       <c r="D13" t="s">
-        <v>1417</v>
+        <v>1447</v>
       </c>
       <c r="E13" t="s">
         <v>698</v>
       </c>
       <c r="F13" t="s">
-        <v>1418</v>
+        <v>1448</v>
       </c>
       <c r="G13" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="H13">
         <v>500000</v>
@@ -21802,16 +22249,16 @@
         <v>38</v>
       </c>
       <c r="N13" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O13" t="s">
-        <v>1419</v>
+        <v>1449</v>
       </c>
       <c r="P13" t="s">
-        <v>1420</v>
+        <v>1450</v>
       </c>
       <c r="Q13" t="s">
-        <v>1421</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
@@ -21825,16 +22272,16 @@
         <v>18</v>
       </c>
       <c r="D14" t="s">
-        <v>1422</v>
+        <v>1452</v>
       </c>
       <c r="E14" t="s">
         <v>478</v>
       </c>
       <c r="F14" t="s">
-        <v>1423</v>
+        <v>1453</v>
       </c>
       <c r="G14" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="H14">
         <v>274456</v>
@@ -21855,16 +22302,16 @@
         <v>38</v>
       </c>
       <c r="N14" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O14" t="s">
-        <v>1424</v>
+        <v>1454</v>
       </c>
       <c r="P14" t="s">
-        <v>1425</v>
+        <v>1455</v>
       </c>
       <c r="Q14" t="s">
-        <v>1426</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -21878,16 +22325,16 @@
         <v>30</v>
       </c>
       <c r="D15" t="s">
-        <v>1427</v>
+        <v>1457</v>
       </c>
       <c r="E15" t="s">
         <v>478</v>
       </c>
       <c r="F15" t="s">
-        <v>1428</v>
+        <v>1458</v>
       </c>
       <c r="G15" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J15" t="s">
         <v>22</v>
@@ -21902,16 +22349,16 @@
         <v>38</v>
       </c>
       <c r="N15" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O15" t="s">
-        <v>1429</v>
+        <v>1459</v>
       </c>
       <c r="P15" t="s">
-        <v>1430</v>
+        <v>1460</v>
       </c>
       <c r="Q15" t="s">
-        <v>1431</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
@@ -21925,16 +22372,16 @@
         <v>22</v>
       </c>
       <c r="D16" t="s">
-        <v>1432</v>
+        <v>1462</v>
       </c>
       <c r="E16" t="s">
         <v>478</v>
       </c>
       <c r="F16" t="s">
-        <v>1433</v>
+        <v>1463</v>
       </c>
       <c r="G16" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J16" t="s">
         <v>22</v>
@@ -21949,16 +22396,16 @@
         <v>38</v>
       </c>
       <c r="N16" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O16" t="s">
-        <v>1434</v>
+        <v>1464</v>
       </c>
       <c r="P16" t="s">
-        <v>1435</v>
+        <v>1465</v>
       </c>
       <c r="Q16" t="s">
-        <v>1436</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
@@ -21972,16 +22419,16 @@
         <v>48</v>
       </c>
       <c r="D17" t="s">
-        <v>1437</v>
+        <v>1467</v>
       </c>
       <c r="E17" t="s">
         <v>478</v>
       </c>
       <c r="F17" t="s">
-        <v>1438</v>
+        <v>1468</v>
       </c>
       <c r="G17" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J17" t="s">
         <v>22</v>
@@ -21996,16 +22443,16 @@
         <v>25</v>
       </c>
       <c r="N17" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O17" t="s">
-        <v>1439</v>
+        <v>1469</v>
       </c>
       <c r="P17" t="s">
-        <v>1440</v>
+        <v>1470</v>
       </c>
       <c r="Q17" t="s">
-        <v>1441</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
@@ -22019,16 +22466,16 @@
         <v>25</v>
       </c>
       <c r="D18" t="s">
-        <v>1442</v>
+        <v>1472</v>
       </c>
       <c r="E18" t="s">
         <v>478</v>
       </c>
       <c r="F18" t="s">
-        <v>1443</v>
+        <v>1473</v>
       </c>
       <c r="G18" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J18" t="s">
         <v>22</v>
@@ -22043,16 +22490,16 @@
         <v>38</v>
       </c>
       <c r="N18" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O18" t="s">
-        <v>1444</v>
+        <v>1474</v>
       </c>
       <c r="P18" t="s">
-        <v>1445</v>
+        <v>1475</v>
       </c>
       <c r="Q18" t="s">
-        <v>1446</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -22066,16 +22513,16 @@
         <v>40</v>
       </c>
       <c r="D19" t="s">
-        <v>1447</v>
+        <v>1477</v>
       </c>
       <c r="E19" t="s">
         <v>478</v>
       </c>
       <c r="F19" t="s">
-        <v>1448</v>
+        <v>1478</v>
       </c>
       <c r="G19" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J19" t="s">
         <v>22</v>
@@ -22090,16 +22537,16 @@
         <v>38</v>
       </c>
       <c r="N19" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O19" t="s">
-        <v>1449</v>
+        <v>1479</v>
       </c>
       <c r="P19" t="s">
-        <v>1450</v>
+        <v>1480</v>
       </c>
       <c r="Q19" t="s">
-        <v>1451</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -22113,16 +22560,16 @@
         <v>70</v>
       </c>
       <c r="D20" t="s">
-        <v>1452</v>
+        <v>1482</v>
       </c>
       <c r="E20" t="s">
-        <v>1453</v>
+        <v>1483</v>
       </c>
       <c r="F20" t="s">
-        <v>1454</v>
+        <v>1484</v>
       </c>
       <c r="G20" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J20" t="s">
         <v>22</v>
@@ -22137,16 +22584,16 @@
         <v>38</v>
       </c>
       <c r="N20" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O20" t="s">
-        <v>1455</v>
+        <v>1485</v>
       </c>
       <c r="P20" t="s">
-        <v>1456</v>
+        <v>1486</v>
       </c>
       <c r="Q20" t="s">
-        <v>1457</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
@@ -22160,16 +22607,16 @@
         <v>58</v>
       </c>
       <c r="D21" t="s">
-        <v>1458</v>
+        <v>1488</v>
       </c>
       <c r="E21" t="s">
-        <v>1459</v>
+        <v>1489</v>
       </c>
       <c r="F21" t="s">
-        <v>1443</v>
+        <v>1473</v>
       </c>
       <c r="G21" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J21" t="s">
         <v>22</v>
@@ -22184,16 +22631,16 @@
         <v>38</v>
       </c>
       <c r="N21" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O21" t="s">
-        <v>1460</v>
+        <v>1490</v>
       </c>
       <c r="P21" t="s">
-        <v>1461</v>
+        <v>1491</v>
       </c>
       <c r="Q21" t="s">
-        <v>1462</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -22207,16 +22654,16 @@
         <v>32</v>
       </c>
       <c r="D22" t="s">
-        <v>1463</v>
+        <v>1493</v>
       </c>
       <c r="E22" t="s">
-        <v>1464</v>
+        <v>1494</v>
       </c>
       <c r="F22" t="s">
         <v>1085</v>
       </c>
       <c r="G22" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J22" t="s">
         <v>22</v>
@@ -22231,16 +22678,16 @@
         <v>38</v>
       </c>
       <c r="N22" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O22" t="s">
-        <v>1465</v>
+        <v>1495</v>
       </c>
       <c r="P22" t="s">
-        <v>1466</v>
+        <v>1496</v>
       </c>
       <c r="Q22" t="s">
-        <v>1467</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
@@ -22254,16 +22701,16 @@
         <v>4</v>
       </c>
       <c r="D23" t="s">
-        <v>1468</v>
+        <v>1498</v>
       </c>
       <c r="E23" t="s">
-        <v>1469</v>
+        <v>1499</v>
       </c>
       <c r="F23" t="s">
         <v>1032</v>
       </c>
       <c r="G23" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J23" t="s">
         <v>22</v>
@@ -22278,16 +22725,16 @@
         <v>38</v>
       </c>
       <c r="N23" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O23" t="s">
-        <v>1470</v>
+        <v>1500</v>
       </c>
       <c r="P23" t="s">
-        <v>1471</v>
+        <v>1501</v>
       </c>
       <c r="Q23" t="s">
-        <v>1472</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
@@ -22301,16 +22748,16 @@
         <v>25</v>
       </c>
       <c r="D24" t="s">
-        <v>1473</v>
+        <v>1503</v>
       </c>
       <c r="E24" t="s">
-        <v>1474</v>
+        <v>1504</v>
       </c>
       <c r="F24" t="s">
-        <v>1475</v>
+        <v>1505</v>
       </c>
       <c r="G24" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J24" t="s">
         <v>22</v>
@@ -22325,16 +22772,16 @@
         <v>38</v>
       </c>
       <c r="N24" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O24" t="s">
-        <v>1476</v>
+        <v>1506</v>
       </c>
       <c r="P24" t="s">
-        <v>1477</v>
+        <v>1507</v>
       </c>
       <c r="Q24" t="s">
-        <v>1478</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
@@ -22348,16 +22795,16 @@
         <v>30</v>
       </c>
       <c r="D25" t="s">
-        <v>1479</v>
+        <v>1509</v>
       </c>
       <c r="E25" t="s">
-        <v>1480</v>
+        <v>1510</v>
       </c>
       <c r="F25" t="s">
         <v>1025</v>
       </c>
       <c r="G25" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J25" t="s">
         <v>22</v>
@@ -22372,16 +22819,16 @@
         <v>38</v>
       </c>
       <c r="N25" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O25" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="P25" t="s">
-        <v>1482</v>
+        <v>1512</v>
       </c>
       <c r="Q25" t="s">
-        <v>1483</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
@@ -22395,16 +22842,16 @@
         <v>52</v>
       </c>
       <c r="D26" t="s">
-        <v>1484</v>
+        <v>1514</v>
       </c>
       <c r="E26" t="s">
         <v>421</v>
       </c>
       <c r="F26" t="s">
-        <v>1485</v>
+        <v>1515</v>
       </c>
       <c r="G26" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="H26">
         <v>180000</v>
@@ -22425,16 +22872,16 @@
         <v>25</v>
       </c>
       <c r="N26" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O26" t="s">
-        <v>1486</v>
+        <v>1516</v>
       </c>
       <c r="P26" t="s">
-        <v>1487</v>
+        <v>1517</v>
       </c>
       <c r="Q26" t="s">
-        <v>1488</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
@@ -22448,7 +22895,7 @@
         <v>50</v>
       </c>
       <c r="D27" t="s">
-        <v>1489</v>
+        <v>1519</v>
       </c>
       <c r="E27" t="s">
         <v>421</v>
@@ -22457,7 +22904,7 @@
         <v>20</v>
       </c>
       <c r="G27" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="H27">
         <v>180000</v>
@@ -22478,16 +22925,16 @@
         <v>25</v>
       </c>
       <c r="N27" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O27" t="s">
-        <v>1490</v>
+        <v>1520</v>
       </c>
       <c r="P27" t="s">
-        <v>1491</v>
+        <v>1521</v>
       </c>
       <c r="Q27" t="s">
-        <v>1492</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
@@ -22501,7 +22948,7 @@
         <v>46</v>
       </c>
       <c r="D28" t="s">
-        <v>1493</v>
+        <v>1523</v>
       </c>
       <c r="E28" t="s">
         <v>421</v>
@@ -22510,7 +22957,7 @@
         <v>20</v>
       </c>
       <c r="G28" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="H28">
         <v>180000</v>
@@ -22531,16 +22978,16 @@
         <v>25</v>
       </c>
       <c r="N28" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O28" t="s">
-        <v>1494</v>
+        <v>1524</v>
       </c>
       <c r="P28" t="s">
-        <v>1495</v>
+        <v>1525</v>
       </c>
       <c r="Q28" t="s">
-        <v>1496</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
@@ -22554,7 +23001,7 @@
         <v>38</v>
       </c>
       <c r="D29" t="s">
-        <v>1497</v>
+        <v>1527</v>
       </c>
       <c r="E29" t="s">
         <v>421</v>
@@ -22563,7 +23010,7 @@
         <v>20</v>
       </c>
       <c r="G29" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="H29">
         <v>217800</v>
@@ -22584,16 +23031,16 @@
         <v>38</v>
       </c>
       <c r="N29" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O29" t="s">
-        <v>1498</v>
+        <v>1528</v>
       </c>
       <c r="P29" t="s">
-        <v>1499</v>
+        <v>1529</v>
       </c>
       <c r="Q29" t="s">
-        <v>1500</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
@@ -22613,10 +23060,10 @@
         <v>421</v>
       </c>
       <c r="F30" t="s">
-        <v>1501</v>
+        <v>1531</v>
       </c>
       <c r="G30" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="H30">
         <v>180000</v>
@@ -22637,16 +23084,16 @@
         <v>25</v>
       </c>
       <c r="N30" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O30" t="s">
-        <v>1502</v>
+        <v>1532</v>
       </c>
       <c r="P30" t="s">
-        <v>1503</v>
+        <v>1533</v>
       </c>
       <c r="Q30" t="s">
-        <v>1504</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
@@ -22660,16 +23107,16 @@
         <v>45</v>
       </c>
       <c r="D31" t="s">
-        <v>1505</v>
+        <v>1535</v>
       </c>
       <c r="E31" t="s">
         <v>421</v>
       </c>
       <c r="F31" t="s">
-        <v>1506</v>
+        <v>1536</v>
       </c>
       <c r="G31" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="H31">
         <v>219100</v>
@@ -22690,16 +23137,16 @@
         <v>25</v>
       </c>
       <c r="N31" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O31" t="s">
-        <v>1507</v>
+        <v>1537</v>
       </c>
       <c r="P31" t="s">
-        <v>1508</v>
+        <v>1538</v>
       </c>
       <c r="Q31" t="s">
-        <v>1509</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
@@ -22713,16 +23160,16 @@
         <v>42</v>
       </c>
       <c r="D32" t="s">
-        <v>1510</v>
+        <v>1540</v>
       </c>
       <c r="E32" t="s">
         <v>421</v>
       </c>
       <c r="F32" t="s">
-        <v>1511</v>
+        <v>1541</v>
       </c>
       <c r="G32" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="H32">
         <v>180000</v>
@@ -22743,16 +23190,16 @@
         <v>25</v>
       </c>
       <c r="N32" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O32" t="s">
-        <v>1512</v>
+        <v>1542</v>
       </c>
       <c r="P32" t="s">
-        <v>1513</v>
+        <v>1543</v>
       </c>
       <c r="Q32" t="s">
-        <v>1514</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
@@ -22766,7 +23213,7 @@
         <v>32</v>
       </c>
       <c r="D33" t="s">
-        <v>1515</v>
+        <v>1545</v>
       </c>
       <c r="E33" t="s">
         <v>421</v>
@@ -22775,7 +23222,7 @@
         <v>20</v>
       </c>
       <c r="G33" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="H33">
         <v>219100</v>
@@ -22796,16 +23243,16 @@
         <v>38</v>
       </c>
       <c r="N33" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O33" t="s">
-        <v>1516</v>
+        <v>1546</v>
       </c>
       <c r="P33" t="s">
-        <v>1517</v>
+        <v>1547</v>
       </c>
       <c r="Q33" t="s">
-        <v>1518</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
@@ -22819,7 +23266,7 @@
         <v>35</v>
       </c>
       <c r="D34" t="s">
-        <v>1519</v>
+        <v>1549</v>
       </c>
       <c r="E34" t="s">
         <v>421</v>
@@ -22828,7 +23275,7 @@
         <v>20</v>
       </c>
       <c r="G34" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="H34">
         <v>219100</v>
@@ -22849,16 +23296,16 @@
         <v>38</v>
       </c>
       <c r="N34" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O34" t="s">
-        <v>1520</v>
+        <v>1550</v>
       </c>
       <c r="P34" t="s">
-        <v>1521</v>
+        <v>1551</v>
       </c>
       <c r="Q34" t="s">
-        <v>1522</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
@@ -22872,16 +23319,16 @@
         <v>40</v>
       </c>
       <c r="D35" t="s">
-        <v>1523</v>
+        <v>1553</v>
       </c>
       <c r="E35" t="s">
         <v>421</v>
       </c>
       <c r="F35" t="s">
-        <v>1524</v>
+        <v>1554</v>
       </c>
       <c r="G35" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="H35">
         <v>219100</v>
@@ -22902,16 +23349,16 @@
         <v>25</v>
       </c>
       <c r="N35" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O35" t="s">
-        <v>1525</v>
+        <v>1555</v>
       </c>
       <c r="P35" t="s">
-        <v>1526</v>
+        <v>1556</v>
       </c>
       <c r="Q35" t="s">
-        <v>1527</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
@@ -22925,7 +23372,7 @@
         <v>38</v>
       </c>
       <c r="D36" t="s">
-        <v>1528</v>
+        <v>1558</v>
       </c>
       <c r="E36" t="s">
         <v>421</v>
@@ -22934,7 +23381,7 @@
         <v>437</v>
       </c>
       <c r="G36" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="H36">
         <v>219100</v>
@@ -22955,16 +23402,16 @@
         <v>38</v>
       </c>
       <c r="N36" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O36" t="s">
-        <v>1529</v>
+        <v>1559</v>
       </c>
       <c r="P36" t="s">
-        <v>1530</v>
+        <v>1560</v>
       </c>
       <c r="Q36" t="s">
-        <v>1531</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
@@ -22978,7 +23425,7 @@
         <v>40</v>
       </c>
       <c r="D37" t="s">
-        <v>1532</v>
+        <v>1562</v>
       </c>
       <c r="E37" t="s">
         <v>421</v>
@@ -22987,7 +23434,7 @@
         <v>20</v>
       </c>
       <c r="G37" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="H37">
         <v>219100</v>
@@ -23008,16 +23455,16 @@
         <v>25</v>
       </c>
       <c r="N37" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O37" t="s">
-        <v>1533</v>
+        <v>1563</v>
       </c>
       <c r="P37" t="s">
-        <v>1534</v>
+        <v>1564</v>
       </c>
       <c r="Q37" t="s">
-        <v>1535</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
@@ -23031,16 +23478,16 @@
         <v>33</v>
       </c>
       <c r="D38" t="s">
-        <v>1536</v>
+        <v>1566</v>
       </c>
       <c r="E38" t="s">
         <v>421</v>
       </c>
       <c r="F38" t="s">
-        <v>1537</v>
+        <v>1567</v>
       </c>
       <c r="G38" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="H38">
         <v>219100</v>
@@ -23061,16 +23508,16 @@
         <v>38</v>
       </c>
       <c r="N38" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O38" t="s">
-        <v>1538</v>
+        <v>1568</v>
       </c>
       <c r="P38" t="s">
-        <v>1539</v>
+        <v>1569</v>
       </c>
       <c r="Q38" t="s">
-        <v>1540</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
@@ -23084,16 +23531,16 @@
         <v>48</v>
       </c>
       <c r="D39" t="s">
-        <v>1541</v>
+        <v>1571</v>
       </c>
       <c r="E39" t="s">
-        <v>1398</v>
+        <v>1428</v>
       </c>
       <c r="F39" t="s">
-        <v>1542</v>
+        <v>1572</v>
       </c>
       <c r="G39" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J39" t="s">
         <v>22</v>
@@ -23108,16 +23555,16 @@
         <v>25</v>
       </c>
       <c r="N39" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O39" t="s">
-        <v>1543</v>
+        <v>1573</v>
       </c>
       <c r="P39" t="s">
-        <v>1544</v>
+        <v>1574</v>
       </c>
       <c r="Q39" t="s">
-        <v>1545</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
@@ -23131,16 +23578,16 @@
         <v>40</v>
       </c>
       <c r="D40" t="s">
-        <v>1546</v>
+        <v>1576</v>
       </c>
       <c r="E40" t="s">
-        <v>1403</v>
+        <v>1433</v>
       </c>
       <c r="F40" t="s">
-        <v>1547</v>
+        <v>1577</v>
       </c>
       <c r="G40" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="H40">
         <v>184200</v>
@@ -23161,16 +23608,16 @@
         <v>25</v>
       </c>
       <c r="N40" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O40" t="s">
-        <v>1548</v>
+        <v>1578</v>
       </c>
       <c r="P40" t="s">
-        <v>1549</v>
+        <v>1579</v>
       </c>
       <c r="Q40" t="s">
-        <v>1550</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
@@ -23187,13 +23634,13 @@
         <v>1343</v>
       </c>
       <c r="E41" t="s">
-        <v>1403</v>
+        <v>1433</v>
       </c>
       <c r="F41" t="s">
-        <v>1551</v>
+        <v>1581</v>
       </c>
       <c r="G41" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="H41">
         <v>200000</v>
@@ -23214,16 +23661,16 @@
         <v>38</v>
       </c>
       <c r="N41" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O41" t="s">
-        <v>1552</v>
+        <v>1582</v>
       </c>
       <c r="P41" t="s">
-        <v>1553</v>
+        <v>1583</v>
       </c>
       <c r="Q41" t="s">
-        <v>1554</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
@@ -23237,7 +23684,7 @@
         <v>30</v>
       </c>
       <c r="D42" t="s">
-        <v>1555</v>
+        <v>1585</v>
       </c>
       <c r="E42" t="s">
         <v>698</v>
@@ -23246,7 +23693,7 @@
         <v>707</v>
       </c>
       <c r="G42" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J42" t="s">
         <v>22</v>
@@ -23261,16 +23708,16 @@
         <v>38</v>
       </c>
       <c r="N42" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O42" t="s">
-        <v>1556</v>
+        <v>1586</v>
       </c>
       <c r="P42" t="s">
-        <v>1557</v>
+        <v>1587</v>
       </c>
       <c r="Q42" t="s">
-        <v>1558</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
@@ -23290,10 +23737,10 @@
         <v>698</v>
       </c>
       <c r="F43" t="s">
-        <v>1413</v>
+        <v>1443</v>
       </c>
       <c r="G43" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J43" t="s">
         <v>22</v>
@@ -23308,16 +23755,16 @@
         <v>38</v>
       </c>
       <c r="N43" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O43" t="s">
-        <v>1559</v>
+        <v>1589</v>
       </c>
       <c r="P43" t="s">
-        <v>1560</v>
+        <v>1590</v>
       </c>
       <c r="Q43" t="s">
-        <v>1561</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
@@ -23331,7 +23778,7 @@
         <v>32</v>
       </c>
       <c r="D44" t="s">
-        <v>1562</v>
+        <v>1592</v>
       </c>
       <c r="E44" t="s">
         <v>698</v>
@@ -23340,7 +23787,7 @@
         <v>707</v>
       </c>
       <c r="G44" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J44" t="s">
         <v>22</v>
@@ -23355,16 +23802,16 @@
         <v>38</v>
       </c>
       <c r="N44" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O44" t="s">
-        <v>1563</v>
+        <v>1593</v>
       </c>
       <c r="P44" t="s">
-        <v>1564</v>
+        <v>1594</v>
       </c>
       <c r="Q44" t="s">
-        <v>1565</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
@@ -23378,16 +23825,16 @@
         <v>45</v>
       </c>
       <c r="D45" t="s">
-        <v>1566</v>
+        <v>1596</v>
       </c>
       <c r="E45" t="s">
         <v>478</v>
       </c>
       <c r="F45" t="s">
-        <v>1567</v>
+        <v>1597</v>
       </c>
       <c r="G45" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J45" t="s">
         <v>22</v>
@@ -23402,16 +23849,16 @@
         <v>25</v>
       </c>
       <c r="N45" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O45" t="s">
-        <v>1568</v>
+        <v>1598</v>
       </c>
       <c r="P45" t="s">
-        <v>1569</v>
+        <v>1599</v>
       </c>
       <c r="Q45" t="s">
-        <v>1570</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
@@ -23425,16 +23872,16 @@
         <v>35</v>
       </c>
       <c r="D46" t="s">
-        <v>1571</v>
+        <v>1601</v>
       </c>
       <c r="E46" t="s">
         <v>478</v>
       </c>
       <c r="F46" t="s">
-        <v>1572</v>
+        <v>1602</v>
       </c>
       <c r="G46" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J46" t="s">
         <v>22</v>
@@ -23449,16 +23896,16 @@
         <v>38</v>
       </c>
       <c r="N46" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O46" t="s">
-        <v>1573</v>
+        <v>1603</v>
       </c>
       <c r="P46" t="s">
-        <v>1574</v>
+        <v>1604</v>
       </c>
       <c r="Q46" t="s">
-        <v>1575</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
@@ -23472,7 +23919,7 @@
         <v>35</v>
       </c>
       <c r="D47" t="s">
-        <v>1576</v>
+        <v>1606</v>
       </c>
       <c r="E47" t="s">
         <v>478</v>
@@ -23481,7 +23928,7 @@
         <v>507</v>
       </c>
       <c r="G47" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J47" t="s">
         <v>22</v>
@@ -23496,16 +23943,16 @@
         <v>38</v>
       </c>
       <c r="N47" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O47" t="s">
-        <v>1577</v>
+        <v>1607</v>
       </c>
       <c r="P47" t="s">
-        <v>1578</v>
+        <v>1608</v>
       </c>
       <c r="Q47" t="s">
-        <v>1579</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
@@ -23519,16 +23966,16 @@
         <v>15</v>
       </c>
       <c r="D48" t="s">
-        <v>1580</v>
+        <v>1610</v>
       </c>
       <c r="E48" t="s">
         <v>478</v>
       </c>
       <c r="F48" t="s">
-        <v>1581</v>
+        <v>1611</v>
       </c>
       <c r="G48" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J48" t="s">
         <v>22</v>
@@ -23543,16 +23990,16 @@
         <v>38</v>
       </c>
       <c r="N48" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O48" t="s">
-        <v>1582</v>
+        <v>1612</v>
       </c>
       <c r="P48" t="s">
-        <v>1583</v>
+        <v>1613</v>
       </c>
       <c r="Q48" t="s">
-        <v>1584</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
@@ -23566,16 +24013,16 @@
         <v>25</v>
       </c>
       <c r="D49" t="s">
-        <v>1585</v>
+        <v>1615</v>
       </c>
       <c r="E49" t="s">
         <v>478</v>
       </c>
       <c r="F49" t="s">
-        <v>1586</v>
+        <v>1616</v>
       </c>
       <c r="G49" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J49" t="s">
         <v>22</v>
@@ -23590,16 +24037,16 @@
         <v>38</v>
       </c>
       <c r="N49" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O49" t="s">
-        <v>1587</v>
+        <v>1617</v>
       </c>
       <c r="P49" t="s">
-        <v>1588</v>
+        <v>1618</v>
       </c>
       <c r="Q49" t="s">
-        <v>1589</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
@@ -23613,16 +24060,16 @@
         <v>30</v>
       </c>
       <c r="D50" t="s">
-        <v>1590</v>
+        <v>1620</v>
       </c>
       <c r="E50" t="s">
         <v>478</v>
       </c>
       <c r="F50" t="s">
-        <v>1591</v>
+        <v>1621</v>
       </c>
       <c r="G50" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J50" t="s">
         <v>22</v>
@@ -23637,16 +24084,16 @@
         <v>38</v>
       </c>
       <c r="N50" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O50" t="s">
-        <v>1592</v>
+        <v>1622</v>
       </c>
       <c r="P50" t="s">
-        <v>1593</v>
+        <v>1623</v>
       </c>
       <c r="Q50" t="s">
-        <v>1594</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
@@ -23666,10 +24113,10 @@
         <v>421</v>
       </c>
       <c r="F51" t="s">
-        <v>1551</v>
+        <v>1581</v>
       </c>
       <c r="G51" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J51" t="s">
         <v>22</v>
@@ -23684,16 +24131,16 @@
         <v>38</v>
       </c>
       <c r="N51" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O51" t="s">
-        <v>1595</v>
+        <v>1625</v>
       </c>
       <c r="P51" t="s">
-        <v>1596</v>
+        <v>1626</v>
       </c>
       <c r="Q51" t="s">
-        <v>1597</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
@@ -23713,10 +24160,10 @@
         <v>421</v>
       </c>
       <c r="F52" t="s">
-        <v>1598</v>
+        <v>1628</v>
       </c>
       <c r="G52" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J52" t="s">
         <v>22</v>
@@ -23731,16 +24178,16 @@
         <v>25</v>
       </c>
       <c r="N52" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O52" t="s">
-        <v>1599</v>
+        <v>1629</v>
       </c>
       <c r="P52" t="s">
-        <v>1600</v>
+        <v>1630</v>
       </c>
       <c r="Q52" t="s">
-        <v>1601</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
@@ -23763,7 +24210,7 @@
         <v>764</v>
       </c>
       <c r="G53" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="H53">
         <v>180000</v>
@@ -23784,16 +24231,16 @@
         <v>38</v>
       </c>
       <c r="N53" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O53" t="s">
-        <v>1602</v>
+        <v>1632</v>
       </c>
       <c r="P53" t="s">
-        <v>1603</v>
+        <v>1633</v>
       </c>
       <c r="Q53" t="s">
-        <v>1604</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
@@ -23813,10 +24260,10 @@
         <v>421</v>
       </c>
       <c r="F54" t="s">
-        <v>1605</v>
+        <v>1635</v>
       </c>
       <c r="G54" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="H54">
         <v>180000</v>
@@ -23837,16 +24284,16 @@
         <v>38</v>
       </c>
       <c r="N54" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O54" t="s">
-        <v>1606</v>
+        <v>1636</v>
       </c>
       <c r="P54" t="s">
-        <v>1607</v>
+        <v>1637</v>
       </c>
       <c r="Q54" t="s">
-        <v>1608</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
@@ -23860,16 +24307,16 @@
         <v>20</v>
       </c>
       <c r="D55" t="s">
-        <v>1609</v>
+        <v>1639</v>
       </c>
       <c r="E55" t="s">
         <v>811</v>
       </c>
       <c r="F55" t="s">
-        <v>1610</v>
+        <v>1640</v>
       </c>
       <c r="G55" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J55" t="s">
         <v>22</v>
@@ -23884,16 +24331,16 @@
         <v>38</v>
       </c>
       <c r="N55" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O55" t="s">
-        <v>1611</v>
+        <v>1641</v>
       </c>
       <c r="P55" t="s">
-        <v>1612</v>
+        <v>1642</v>
       </c>
       <c r="Q55" t="s">
-        <v>1613</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
@@ -23907,7 +24354,7 @@
         <v>50</v>
       </c>
       <c r="D56" t="s">
-        <v>1614</v>
+        <v>1644</v>
       </c>
       <c r="E56" t="s">
         <v>811</v>
@@ -23916,7 +24363,7 @@
         <v>20</v>
       </c>
       <c r="G56" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="H56">
         <v>250000</v>
@@ -23937,16 +24384,16 @@
         <v>25</v>
       </c>
       <c r="N56" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O56" t="s">
-        <v>1615</v>
+        <v>1645</v>
       </c>
       <c r="P56" t="s">
-        <v>1616</v>
+        <v>1646</v>
       </c>
       <c r="Q56" t="s">
-        <v>1617</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
@@ -23960,7 +24407,7 @@
         <v>55</v>
       </c>
       <c r="D57" t="s">
-        <v>1618</v>
+        <v>1648</v>
       </c>
       <c r="E57" t="s">
         <v>811</v>
@@ -23969,7 +24416,7 @@
         <v>20</v>
       </c>
       <c r="G57" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="H57">
         <v>200000</v>
@@ -23990,16 +24437,16 @@
         <v>25</v>
       </c>
       <c r="N57" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O57" t="s">
-        <v>1619</v>
+        <v>1649</v>
       </c>
       <c r="P57" t="s">
-        <v>1620</v>
+        <v>1650</v>
       </c>
       <c r="Q57" t="s">
-        <v>1621</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
@@ -24013,7 +24460,7 @@
         <v>52</v>
       </c>
       <c r="D58" t="s">
-        <v>1622</v>
+        <v>1652</v>
       </c>
       <c r="E58" t="s">
         <v>811</v>
@@ -24022,7 +24469,7 @@
         <v>20</v>
       </c>
       <c r="G58" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="H58">
         <v>250000</v>
@@ -24043,16 +24490,16 @@
         <v>25</v>
       </c>
       <c r="N58" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O58" t="s">
-        <v>1623</v>
+        <v>1653</v>
       </c>
       <c r="P58" t="s">
-        <v>1624</v>
+        <v>1654</v>
       </c>
       <c r="Q58" t="s">
-        <v>1625</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
@@ -24066,7 +24513,7 @@
         <v>53</v>
       </c>
       <c r="D59" t="s">
-        <v>1626</v>
+        <v>1656</v>
       </c>
       <c r="E59" t="s">
         <v>811</v>
@@ -24075,7 +24522,7 @@
         <v>20</v>
       </c>
       <c r="G59" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="H59">
         <v>200000</v>
@@ -24096,16 +24543,16 @@
         <v>25</v>
       </c>
       <c r="N59" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O59" t="s">
-        <v>1627</v>
+        <v>1657</v>
       </c>
       <c r="P59" t="s">
-        <v>1628</v>
+        <v>1658</v>
       </c>
       <c r="Q59" t="s">
-        <v>1629</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
@@ -24119,7 +24566,7 @@
         <v>50</v>
       </c>
       <c r="D60" t="s">
-        <v>1630</v>
+        <v>1660</v>
       </c>
       <c r="E60" t="s">
         <v>811</v>
@@ -24128,7 +24575,7 @@
         <v>20</v>
       </c>
       <c r="G60" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="H60">
         <v>200000</v>
@@ -24149,16 +24596,16 @@
         <v>25</v>
       </c>
       <c r="N60" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O60" t="s">
-        <v>1631</v>
+        <v>1661</v>
       </c>
       <c r="P60" t="s">
-        <v>1632</v>
+        <v>1662</v>
       </c>
       <c r="Q60" t="s">
-        <v>1633</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
@@ -24172,7 +24619,7 @@
         <v>55</v>
       </c>
       <c r="D61" t="s">
-        <v>1634</v>
+        <v>1664</v>
       </c>
       <c r="E61" t="s">
         <v>811</v>
@@ -24181,7 +24628,7 @@
         <v>20</v>
       </c>
       <c r="G61" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="H61">
         <v>250000</v>
@@ -24202,16 +24649,16 @@
         <v>25</v>
       </c>
       <c r="N61" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O61" t="s">
-        <v>1635</v>
+        <v>1665</v>
       </c>
       <c r="P61" t="s">
-        <v>1636</v>
+        <v>1666</v>
       </c>
       <c r="Q61" t="s">
-        <v>1637</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
@@ -24225,16 +24672,16 @@
         <v>45</v>
       </c>
       <c r="D62" t="s">
-        <v>1638</v>
+        <v>1668</v>
       </c>
       <c r="E62" t="s">
-        <v>1639</v>
+        <v>1669</v>
       </c>
       <c r="F62" t="s">
-        <v>1640</v>
+        <v>1670</v>
       </c>
       <c r="G62" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="H62">
         <v>154000</v>
@@ -24255,16 +24702,16 @@
         <v>38</v>
       </c>
       <c r="N62" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O62" t="s">
-        <v>1641</v>
+        <v>1671</v>
       </c>
       <c r="P62" t="s">
-        <v>1642</v>
+        <v>1672</v>
       </c>
       <c r="Q62" t="s">
-        <v>1643</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
@@ -24287,7 +24734,7 @@
         <v>437</v>
       </c>
       <c r="G63" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="H63">
         <v>180000</v>
@@ -24308,16 +24755,16 @@
         <v>25</v>
       </c>
       <c r="N63" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O63" t="s">
-        <v>1644</v>
+        <v>1674</v>
       </c>
       <c r="P63" t="s">
-        <v>1645</v>
+        <v>1675</v>
       </c>
       <c r="Q63" t="s">
-        <v>1646</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
@@ -24337,10 +24784,10 @@
         <v>421</v>
       </c>
       <c r="F64" t="s">
-        <v>1501</v>
+        <v>1531</v>
       </c>
       <c r="G64" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="H64">
         <v>219100</v>
@@ -24361,16 +24808,16 @@
         <v>38</v>
       </c>
       <c r="N64" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O64" t="s">
-        <v>1647</v>
+        <v>1677</v>
       </c>
       <c r="P64" t="s">
-        <v>1648</v>
+        <v>1678</v>
       </c>
       <c r="Q64" t="s">
-        <v>1649</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
@@ -24384,7 +24831,7 @@
         <v>25</v>
       </c>
       <c r="D65" t="s">
-        <v>1650</v>
+        <v>1680</v>
       </c>
       <c r="E65" t="s">
         <v>421</v>
@@ -24393,7 +24840,7 @@
         <v>1016</v>
       </c>
       <c r="G65" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J65" t="s">
         <v>22</v>
@@ -24408,16 +24855,16 @@
         <v>38</v>
       </c>
       <c r="N65" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O65" t="s">
-        <v>1651</v>
+        <v>1681</v>
       </c>
       <c r="P65" t="s">
-        <v>1652</v>
+        <v>1682</v>
       </c>
       <c r="Q65" t="s">
-        <v>1653</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
@@ -24437,10 +24884,10 @@
         <v>698</v>
       </c>
       <c r="F66" t="s">
-        <v>1443</v>
+        <v>1473</v>
       </c>
       <c r="G66" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J66" t="s">
         <v>22</v>
@@ -24455,16 +24902,16 @@
         <v>38</v>
       </c>
       <c r="N66" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O66" t="s">
-        <v>1654</v>
+        <v>1684</v>
       </c>
       <c r="P66" t="s">
-        <v>1655</v>
+        <v>1685</v>
       </c>
       <c r="Q66" t="s">
-        <v>1656</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
@@ -24478,16 +24925,16 @@
         <v>15</v>
       </c>
       <c r="D67" t="s">
-        <v>1657</v>
+        <v>1687</v>
       </c>
       <c r="E67" t="s">
-        <v>1658</v>
+        <v>1688</v>
       </c>
       <c r="F67" t="s">
         <v>1032</v>
       </c>
       <c r="G67" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J67" t="s">
         <v>22</v>
@@ -24502,16 +24949,16 @@
         <v>38</v>
       </c>
       <c r="N67" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O67" t="s">
-        <v>1659</v>
+        <v>1689</v>
       </c>
       <c r="P67" t="s">
-        <v>1660</v>
+        <v>1690</v>
       </c>
       <c r="Q67" t="s">
-        <v>1661</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
@@ -24525,16 +24972,16 @@
         <v>12</v>
       </c>
       <c r="D68" t="s">
-        <v>1662</v>
+        <v>1692</v>
       </c>
       <c r="E68" t="s">
-        <v>1663</v>
+        <v>1693</v>
       </c>
       <c r="F68" t="s">
-        <v>1664</v>
+        <v>1694</v>
       </c>
       <c r="G68" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J68" t="s">
         <v>22</v>
@@ -24549,16 +24996,16 @@
         <v>38</v>
       </c>
       <c r="N68" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O68" t="s">
-        <v>1665</v>
+        <v>1695</v>
       </c>
       <c r="P68" t="s">
-        <v>1666</v>
+        <v>1696</v>
       </c>
       <c r="Q68" t="s">
-        <v>1667</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
@@ -24572,16 +25019,16 @@
         <v>42</v>
       </c>
       <c r="D69" t="s">
-        <v>1668</v>
+        <v>1698</v>
       </c>
       <c r="E69" t="s">
         <v>421</v>
       </c>
       <c r="F69" t="s">
-        <v>1669</v>
+        <v>1699</v>
       </c>
       <c r="G69" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="H69">
         <v>180000</v>
@@ -24602,16 +25049,16 @@
         <v>25</v>
       </c>
       <c r="N69" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O69" t="s">
-        <v>1670</v>
+        <v>1700</v>
       </c>
       <c r="P69" t="s">
-        <v>1671</v>
+        <v>1701</v>
       </c>
       <c r="Q69" t="s">
-        <v>1672</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
@@ -24625,16 +25072,16 @@
         <v>22</v>
       </c>
       <c r="D70" t="s">
-        <v>1673</v>
+        <v>1703</v>
       </c>
       <c r="E70" t="s">
-        <v>1403</v>
+        <v>1433</v>
       </c>
       <c r="F70" t="s">
-        <v>1674</v>
+        <v>1704</v>
       </c>
       <c r="G70" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="H70">
         <v>200000</v>
@@ -24655,16 +25102,16 @@
         <v>38</v>
       </c>
       <c r="N70" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O70" t="s">
-        <v>1675</v>
+        <v>1705</v>
       </c>
       <c r="P70" t="s">
-        <v>1676</v>
+        <v>1706</v>
       </c>
       <c r="Q70" t="s">
-        <v>1677</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
@@ -24678,16 +25125,16 @@
         <v>28</v>
       </c>
       <c r="D71" t="s">
-        <v>1678</v>
+        <v>1708</v>
       </c>
       <c r="E71" t="s">
-        <v>1679</v>
+        <v>1709</v>
       </c>
       <c r="F71" t="s">
         <v>1016</v>
       </c>
       <c r="G71" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J71" t="s">
         <v>22</v>
@@ -24702,16 +25149,16 @@
         <v>38</v>
       </c>
       <c r="N71" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O71" t="s">
-        <v>1680</v>
+        <v>1710</v>
       </c>
       <c r="P71" t="s">
-        <v>1681</v>
+        <v>1711</v>
       </c>
       <c r="Q71" t="s">
-        <v>1682</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
@@ -24725,16 +25172,16 @@
         <v>5</v>
       </c>
       <c r="D72" t="s">
-        <v>1683</v>
+        <v>1713</v>
       </c>
       <c r="E72" t="s">
-        <v>1684</v>
+        <v>1714</v>
       </c>
       <c r="F72" t="s">
-        <v>1685</v>
+        <v>1715</v>
       </c>
       <c r="G72" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J72" t="s">
         <v>22</v>
@@ -24749,16 +25196,16 @@
         <v>38</v>
       </c>
       <c r="N72" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O72" t="s">
-        <v>1686</v>
+        <v>1716</v>
       </c>
       <c r="P72" t="s">
-        <v>1687</v>
+        <v>1717</v>
       </c>
       <c r="Q72" t="s">
-        <v>1688</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
@@ -24778,10 +25225,10 @@
         <v>421</v>
       </c>
       <c r="F73" t="s">
-        <v>1689</v>
+        <v>1719</v>
       </c>
       <c r="G73" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J73" t="s">
         <v>22</v>
@@ -24796,16 +25243,16 @@
         <v>25</v>
       </c>
       <c r="N73" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O73" t="s">
-        <v>1690</v>
+        <v>1720</v>
       </c>
       <c r="P73" t="s">
-        <v>1691</v>
+        <v>1721</v>
       </c>
       <c r="Q73" t="s">
-        <v>1692</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
@@ -24819,16 +25266,16 @@
         <v>35</v>
       </c>
       <c r="D74" t="s">
-        <v>1693</v>
+        <v>1723</v>
       </c>
       <c r="E74" t="s">
-        <v>1694</v>
+        <v>1724</v>
       </c>
       <c r="F74" t="s">
         <v>1085</v>
       </c>
       <c r="G74" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J74" t="s">
         <v>22</v>
@@ -24843,16 +25290,16 @@
         <v>38</v>
       </c>
       <c r="N74" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O74" t="s">
-        <v>1695</v>
+        <v>1725</v>
       </c>
       <c r="P74" t="s">
-        <v>1696</v>
+        <v>1726</v>
       </c>
       <c r="Q74" t="s">
-        <v>1697</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
@@ -24866,16 +25313,16 @@
         <v>55</v>
       </c>
       <c r="D75" t="s">
-        <v>1698</v>
+        <v>1728</v>
       </c>
       <c r="E75" t="s">
         <v>421</v>
       </c>
       <c r="F75" t="s">
-        <v>1501</v>
+        <v>1531</v>
       </c>
       <c r="G75" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="H75">
         <v>219100</v>
@@ -24890,22 +25337,22 @@
         <v>423</v>
       </c>
       <c r="L75" t="s">
-        <v>1699</v>
+        <v>1729</v>
       </c>
       <c r="M75" t="s">
         <v>25</v>
       </c>
       <c r="N75" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O75" t="s">
-        <v>1700</v>
+        <v>1730</v>
       </c>
       <c r="P75" t="s">
-        <v>1701</v>
+        <v>1731</v>
       </c>
       <c r="Q75" t="s">
-        <v>1702</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
@@ -24919,16 +25366,16 @@
         <v>50</v>
       </c>
       <c r="D76" t="s">
-        <v>1703</v>
+        <v>1733</v>
       </c>
       <c r="E76" t="s">
-        <v>1403</v>
+        <v>1433</v>
       </c>
       <c r="F76" t="s">
         <v>20</v>
       </c>
       <c r="G76" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="H76">
         <v>200000</v>
@@ -24943,22 +25390,22 @@
         <v>423</v>
       </c>
       <c r="L76" t="s">
-        <v>1699</v>
+        <v>1729</v>
       </c>
       <c r="M76" t="s">
         <v>25</v>
       </c>
       <c r="N76" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O76" t="s">
-        <v>1704</v>
+        <v>1734</v>
       </c>
       <c r="P76" t="s">
-        <v>1705</v>
+        <v>1735</v>
       </c>
       <c r="Q76" t="s">
-        <v>1706</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
@@ -24972,16 +25419,16 @@
         <v>12</v>
       </c>
       <c r="D77" t="s">
-        <v>1707</v>
+        <v>1737</v>
       </c>
       <c r="E77" t="s">
-        <v>1708</v>
+        <v>1738</v>
       </c>
       <c r="F77" t="s">
         <v>1016</v>
       </c>
       <c r="G77" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J77" t="s">
         <v>22</v>
@@ -24990,22 +25437,22 @@
         <v>557</v>
       </c>
       <c r="L77" t="s">
-        <v>1699</v>
+        <v>1729</v>
       </c>
       <c r="M77" t="s">
         <v>38</v>
       </c>
       <c r="N77" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O77" t="s">
-        <v>1709</v>
+        <v>1739</v>
       </c>
       <c r="P77" t="s">
-        <v>1710</v>
+        <v>1740</v>
       </c>
       <c r="Q77" t="s">
-        <v>1711</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
@@ -25019,16 +25466,16 @@
         <v>12</v>
       </c>
       <c r="D78" t="s">
-        <v>1712</v>
+        <v>1742</v>
       </c>
       <c r="E78" t="s">
-        <v>1708</v>
+        <v>1738</v>
       </c>
       <c r="F78" t="s">
         <v>1016</v>
       </c>
       <c r="G78" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J78" t="s">
         <v>22</v>
@@ -25037,22 +25484,22 @@
         <v>557</v>
       </c>
       <c r="L78" t="s">
-        <v>1699</v>
+        <v>1729</v>
       </c>
       <c r="M78" t="s">
         <v>38</v>
       </c>
       <c r="N78" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O78" t="s">
-        <v>1713</v>
+        <v>1743</v>
       </c>
       <c r="P78" t="s">
-        <v>1714</v>
+        <v>1744</v>
       </c>
       <c r="Q78" t="s">
-        <v>1715</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
@@ -25066,16 +25513,16 @@
         <v>3</v>
       </c>
       <c r="D79" t="s">
-        <v>1716</v>
+        <v>1746</v>
       </c>
       <c r="E79" t="s">
-        <v>1708</v>
+        <v>1738</v>
       </c>
       <c r="F79" t="s">
         <v>1016</v>
       </c>
       <c r="G79" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J79" t="s">
         <v>22</v>
@@ -25084,22 +25531,22 @@
         <v>557</v>
       </c>
       <c r="L79" t="s">
-        <v>1699</v>
+        <v>1729</v>
       </c>
       <c r="M79" t="s">
         <v>38</v>
       </c>
       <c r="N79" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O79" t="s">
-        <v>1717</v>
+        <v>1747</v>
       </c>
       <c r="P79" t="s">
-        <v>1718</v>
+        <v>1748</v>
       </c>
       <c r="Q79" t="s">
-        <v>1719</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
@@ -25113,16 +25560,16 @@
         <v>25</v>
       </c>
       <c r="D80" t="s">
-        <v>1720</v>
+        <v>1750</v>
       </c>
       <c r="E80" t="s">
-        <v>1721</v>
+        <v>1751</v>
       </c>
       <c r="F80" t="s">
-        <v>1722</v>
+        <v>1752</v>
       </c>
       <c r="G80" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J80" t="s">
         <v>22</v>
@@ -25131,22 +25578,22 @@
         <v>557</v>
       </c>
       <c r="L80" t="s">
-        <v>1699</v>
+        <v>1729</v>
       </c>
       <c r="M80" t="s">
         <v>38</v>
       </c>
       <c r="N80" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O80" t="s">
-        <v>1723</v>
+        <v>1753</v>
       </c>
       <c r="P80" t="s">
-        <v>1724</v>
+        <v>1754</v>
       </c>
       <c r="Q80" t="s">
-        <v>1725</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
@@ -25160,16 +25607,16 @@
         <v>62</v>
       </c>
       <c r="D81" t="s">
-        <v>1726</v>
+        <v>1756</v>
       </c>
       <c r="E81" t="s">
-        <v>1727</v>
+        <v>1757</v>
       </c>
       <c r="F81" t="s">
-        <v>1728</v>
+        <v>1758</v>
       </c>
       <c r="G81" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J81" t="s">
         <v>22</v>
@@ -25178,22 +25625,22 @@
         <v>557</v>
       </c>
       <c r="L81" t="s">
-        <v>1699</v>
+        <v>1729</v>
       </c>
       <c r="M81" t="s">
         <v>38</v>
       </c>
       <c r="N81" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O81" t="s">
-        <v>1729</v>
+        <v>1759</v>
       </c>
       <c r="P81" t="s">
-        <v>1730</v>
+        <v>1760</v>
       </c>
       <c r="Q81" t="s">
-        <v>1731</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
@@ -25207,16 +25654,16 @@
         <v>68</v>
       </c>
       <c r="D82" t="s">
-        <v>1732</v>
+        <v>1762</v>
       </c>
       <c r="E82" t="s">
-        <v>1727</v>
+        <v>1757</v>
       </c>
       <c r="F82" t="s">
-        <v>1728</v>
+        <v>1758</v>
       </c>
       <c r="G82" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J82" t="s">
         <v>22</v>
@@ -25225,22 +25672,22 @@
         <v>557</v>
       </c>
       <c r="L82" t="s">
-        <v>1699</v>
+        <v>1729</v>
       </c>
       <c r="M82" t="s">
         <v>38</v>
       </c>
       <c r="N82" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O82" t="s">
-        <v>1733</v>
+        <v>1763</v>
       </c>
       <c r="P82" t="s">
-        <v>1734</v>
+        <v>1764</v>
       </c>
       <c r="Q82" t="s">
-        <v>1735</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
@@ -25260,10 +25707,10 @@
         <v>421</v>
       </c>
       <c r="F83" t="s">
-        <v>1736</v>
+        <v>1766</v>
       </c>
       <c r="G83" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="H83">
         <v>180000</v>
@@ -25284,16 +25731,16 @@
         <v>25</v>
       </c>
       <c r="N83" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O83" t="s">
-        <v>1737</v>
+        <v>1767</v>
       </c>
       <c r="P83" t="s">
-        <v>1738</v>
+        <v>1768</v>
       </c>
       <c r="Q83" t="s">
-        <v>1739</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
@@ -25313,10 +25760,10 @@
         <v>421</v>
       </c>
       <c r="F84" t="s">
-        <v>1740</v>
+        <v>1770</v>
       </c>
       <c r="G84" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="H84">
         <v>180000</v>
@@ -25337,16 +25784,16 @@
         <v>25</v>
       </c>
       <c r="N84" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O84" t="s">
-        <v>1741</v>
+        <v>1771</v>
       </c>
       <c r="P84" t="s">
-        <v>1742</v>
+        <v>1772</v>
       </c>
       <c r="Q84" t="s">
-        <v>1743</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
@@ -25360,16 +25807,16 @@
         <v>35</v>
       </c>
       <c r="D85" t="s">
-        <v>1744</v>
+        <v>1774</v>
       </c>
       <c r="E85" t="s">
         <v>421</v>
       </c>
       <c r="F85" t="s">
-        <v>1745</v>
+        <v>1775</v>
       </c>
       <c r="G85" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="H85">
         <v>219100</v>
@@ -25390,16 +25837,16 @@
         <v>25</v>
       </c>
       <c r="N85" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O85" t="s">
-        <v>1746</v>
+        <v>1776</v>
       </c>
       <c r="P85" t="s">
-        <v>1747</v>
+        <v>1777</v>
       </c>
       <c r="Q85" t="s">
-        <v>1748</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
@@ -25413,16 +25860,16 @@
         <v>25</v>
       </c>
       <c r="D86" t="s">
-        <v>1749</v>
+        <v>1779</v>
       </c>
       <c r="E86" t="s">
         <v>478</v>
       </c>
       <c r="F86" t="s">
-        <v>1567</v>
+        <v>1597</v>
       </c>
       <c r="G86" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J86" t="s">
         <v>22</v>
@@ -25437,16 +25884,16 @@
         <v>38</v>
       </c>
       <c r="N86" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O86" t="s">
-        <v>1750</v>
+        <v>1780</v>
       </c>
       <c r="P86" t="s">
-        <v>1751</v>
+        <v>1781</v>
       </c>
       <c r="Q86" t="s">
-        <v>1752</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
@@ -25460,16 +25907,16 @@
         <v>35</v>
       </c>
       <c r="D87" t="s">
-        <v>1753</v>
+        <v>1783</v>
       </c>
       <c r="E87" t="s">
-        <v>1754</v>
+        <v>1784</v>
       </c>
       <c r="F87" t="s">
-        <v>1443</v>
+        <v>1473</v>
       </c>
       <c r="G87" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J87" t="s">
         <v>22</v>
@@ -25484,16 +25931,16 @@
         <v>38</v>
       </c>
       <c r="N87" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O87" t="s">
-        <v>1755</v>
+        <v>1785</v>
       </c>
       <c r="P87" t="s">
-        <v>1756</v>
+        <v>1786</v>
       </c>
       <c r="Q87" t="s">
-        <v>1757</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
@@ -25516,7 +25963,7 @@
         <v>1085</v>
       </c>
       <c r="G88" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="H88">
         <v>200000</v>
@@ -25537,16 +25984,16 @@
         <v>38</v>
       </c>
       <c r="N88" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O88" t="s">
-        <v>1758</v>
+        <v>1788</v>
       </c>
       <c r="P88" t="s">
-        <v>1759</v>
+        <v>1789</v>
       </c>
       <c r="Q88" t="s">
-        <v>1760</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
@@ -25560,7 +26007,7 @@
         <v>38</v>
       </c>
       <c r="D89" t="s">
-        <v>1761</v>
+        <v>1791</v>
       </c>
       <c r="E89" t="s">
         <v>1084</v>
@@ -25569,7 +26016,7 @@
         <v>1085</v>
       </c>
       <c r="G89" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="H89">
         <v>200000</v>
@@ -25590,16 +26037,16 @@
         <v>38</v>
       </c>
       <c r="N89" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O89" t="s">
-        <v>1762</v>
+        <v>1792</v>
       </c>
       <c r="P89" t="s">
-        <v>1763</v>
+        <v>1793</v>
       </c>
       <c r="Q89" t="s">
-        <v>1764</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
@@ -25613,16 +26060,16 @@
         <v>40</v>
       </c>
       <c r="D90" t="s">
-        <v>1546</v>
+        <v>1576</v>
       </c>
       <c r="E90" t="s">
-        <v>1403</v>
+        <v>1433</v>
       </c>
       <c r="F90" t="s">
         <v>713</v>
       </c>
       <c r="G90" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="H90">
         <v>184200</v>
@@ -25643,16 +26090,16 @@
         <v>38</v>
       </c>
       <c r="N90" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O90" t="s">
-        <v>1765</v>
+        <v>1795</v>
       </c>
       <c r="P90" t="s">
-        <v>1766</v>
+        <v>1796</v>
       </c>
       <c r="Q90" t="s">
-        <v>1767</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
@@ -25666,16 +26113,16 @@
         <v>20</v>
       </c>
       <c r="D91" t="s">
-        <v>1768</v>
+        <v>1798</v>
       </c>
       <c r="E91" t="s">
-        <v>1769</v>
+        <v>1799</v>
       </c>
       <c r="F91" t="s">
-        <v>1770</v>
+        <v>1800</v>
       </c>
       <c r="G91" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J91" t="s">
         <v>22</v>
@@ -25690,16 +26137,16 @@
         <v>38</v>
       </c>
       <c r="N91" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O91" t="s">
-        <v>1771</v>
+        <v>1801</v>
       </c>
       <c r="P91" t="s">
-        <v>1772</v>
+        <v>1802</v>
       </c>
       <c r="Q91" t="s">
-        <v>1773</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
@@ -25713,16 +26160,16 @@
         <v>35</v>
       </c>
       <c r="D92" t="s">
-        <v>1774</v>
+        <v>1804</v>
       </c>
       <c r="E92" t="s">
-        <v>1775</v>
+        <v>1805</v>
       </c>
       <c r="F92" t="s">
-        <v>1776</v>
+        <v>1806</v>
       </c>
       <c r="G92" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="H92">
         <v>230000</v>
@@ -25743,16 +26190,16 @@
         <v>38</v>
       </c>
       <c r="N92" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O92" t="s">
-        <v>1777</v>
+        <v>1807</v>
       </c>
       <c r="P92" t="s">
-        <v>1778</v>
+        <v>1808</v>
       </c>
       <c r="Q92" t="s">
-        <v>1779</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
@@ -25772,10 +26219,10 @@
         <v>421</v>
       </c>
       <c r="F93" t="s">
-        <v>1780</v>
+        <v>1810</v>
       </c>
       <c r="G93" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="H93">
         <v>219100</v>
@@ -25796,16 +26243,16 @@
         <v>32</v>
       </c>
       <c r="N93" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O93" t="s">
-        <v>1781</v>
+        <v>1811</v>
       </c>
       <c r="P93" t="s">
-        <v>1782</v>
+        <v>1812</v>
       </c>
       <c r="Q93" t="s">
-        <v>1783</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
@@ -25819,16 +26266,16 @@
         <v>25</v>
       </c>
       <c r="D94" t="s">
-        <v>1784</v>
+        <v>1814</v>
       </c>
       <c r="E94" t="s">
-        <v>1694</v>
+        <v>1724</v>
       </c>
       <c r="F94" t="s">
         <v>1085</v>
       </c>
       <c r="G94" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J94" t="s">
         <v>22</v>
@@ -25843,16 +26290,16 @@
         <v>38</v>
       </c>
       <c r="N94" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O94" t="s">
-        <v>1785</v>
+        <v>1815</v>
       </c>
       <c r="P94" t="s">
-        <v>1786</v>
+        <v>1816</v>
       </c>
       <c r="Q94" t="s">
-        <v>1787</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
@@ -25866,16 +26313,16 @@
         <v>22</v>
       </c>
       <c r="D95" t="s">
-        <v>1788</v>
+        <v>1818</v>
       </c>
       <c r="E95" t="s">
-        <v>1789</v>
+        <v>1819</v>
       </c>
       <c r="F95" t="s">
-        <v>1790</v>
+        <v>1820</v>
       </c>
       <c r="G95" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J95" t="s">
         <v>22</v>
@@ -25890,16 +26337,16 @@
         <v>38</v>
       </c>
       <c r="N95" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O95" t="s">
-        <v>1791</v>
+        <v>1821</v>
       </c>
       <c r="P95" t="s">
-        <v>1792</v>
+        <v>1822</v>
       </c>
       <c r="Q95" t="s">
-        <v>1793</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
@@ -25913,16 +26360,16 @@
         <v>3</v>
       </c>
       <c r="D96" t="s">
-        <v>1794</v>
+        <v>1824</v>
       </c>
       <c r="E96" t="s">
-        <v>1795</v>
+        <v>1825</v>
       </c>
       <c r="F96" t="s">
-        <v>1790</v>
+        <v>1820</v>
       </c>
       <c r="G96" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J96" t="s">
         <v>22</v>
@@ -25937,16 +26384,16 @@
         <v>38</v>
       </c>
       <c r="N96" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O96" t="s">
-        <v>1796</v>
+        <v>1826</v>
       </c>
       <c r="P96" t="s">
-        <v>1797</v>
+        <v>1827</v>
       </c>
       <c r="Q96" t="s">
-        <v>1798</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
@@ -25960,16 +26407,16 @@
         <v>28</v>
       </c>
       <c r="D97" t="s">
-        <v>1799</v>
+        <v>1829</v>
       </c>
       <c r="E97" t="s">
-        <v>1800</v>
+        <v>1830</v>
       </c>
       <c r="F97" t="s">
         <v>1016</v>
       </c>
       <c r="G97" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J97" t="s">
         <v>22</v>
@@ -25984,16 +26431,16 @@
         <v>38</v>
       </c>
       <c r="N97" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O97" t="s">
-        <v>1801</v>
+        <v>1831</v>
       </c>
       <c r="P97" t="s">
-        <v>1802</v>
+        <v>1832</v>
       </c>
       <c r="Q97" t="s">
-        <v>1803</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
@@ -26007,16 +26454,16 @@
         <v>45</v>
       </c>
       <c r="D98" t="s">
-        <v>1804</v>
+        <v>1834</v>
       </c>
       <c r="E98" t="s">
-        <v>1805</v>
+        <v>1835</v>
       </c>
       <c r="F98" t="s">
-        <v>1443</v>
+        <v>1473</v>
       </c>
       <c r="G98" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J98" t="s">
         <v>22</v>
@@ -26031,16 +26478,16 @@
         <v>25</v>
       </c>
       <c r="N98" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O98" t="s">
-        <v>1806</v>
+        <v>1836</v>
       </c>
       <c r="P98" t="s">
-        <v>1807</v>
+        <v>1837</v>
       </c>
       <c r="Q98" t="s">
-        <v>1808</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.25">
@@ -26054,16 +26501,16 @@
         <v>50</v>
       </c>
       <c r="D99" t="s">
-        <v>1809</v>
+        <v>1839</v>
       </c>
       <c r="E99" t="s">
-        <v>1810</v>
+        <v>1840</v>
       </c>
       <c r="F99" t="s">
-        <v>1475</v>
+        <v>1505</v>
       </c>
       <c r="G99" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J99" t="s">
         <v>22</v>
@@ -26078,16 +26525,16 @@
         <v>25</v>
       </c>
       <c r="N99" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O99" t="s">
-        <v>1811</v>
+        <v>1841</v>
       </c>
       <c r="P99" t="s">
-        <v>1812</v>
+        <v>1842</v>
       </c>
       <c r="Q99" t="s">
-        <v>1813</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.25">
@@ -26101,16 +26548,16 @@
         <v>48</v>
       </c>
       <c r="D100" t="s">
-        <v>1814</v>
+        <v>1844</v>
       </c>
       <c r="E100" t="s">
-        <v>1639</v>
+        <v>1669</v>
       </c>
       <c r="F100" t="s">
-        <v>1815</v>
+        <v>1845</v>
       </c>
       <c r="G100" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="H100">
         <v>154000</v>
@@ -26131,16 +26578,16 @@
         <v>25</v>
       </c>
       <c r="N100" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O100" t="s">
-        <v>1816</v>
+        <v>1846</v>
       </c>
       <c r="P100" t="s">
-        <v>1817</v>
+        <v>1847</v>
       </c>
       <c r="Q100" t="s">
-        <v>1818</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.25">
@@ -26154,16 +26601,16 @@
         <v>25</v>
       </c>
       <c r="D101" t="s">
-        <v>1819</v>
+        <v>1849</v>
       </c>
       <c r="E101" t="s">
-        <v>1464</v>
+        <v>1494</v>
       </c>
       <c r="F101" t="s">
         <v>1085</v>
       </c>
       <c r="G101" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J101" t="s">
         <v>22</v>
@@ -26178,16 +26625,16 @@
         <v>38</v>
       </c>
       <c r="N101" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O101" t="s">
-        <v>1820</v>
+        <v>1850</v>
       </c>
       <c r="P101" t="s">
-        <v>1821</v>
+        <v>1851</v>
       </c>
       <c r="Q101" t="s">
-        <v>1822</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.25">
@@ -26201,16 +26648,16 @@
         <v>32</v>
       </c>
       <c r="D102" t="s">
-        <v>1720</v>
+        <v>1750</v>
       </c>
       <c r="E102" t="s">
-        <v>1464</v>
+        <v>1494</v>
       </c>
       <c r="F102" t="s">
         <v>1085</v>
       </c>
       <c r="G102" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J102" t="s">
         <v>22</v>
@@ -26225,16 +26672,16 @@
         <v>38</v>
       </c>
       <c r="N102" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O102" t="s">
-        <v>1823</v>
+        <v>1853</v>
       </c>
       <c r="P102" t="s">
-        <v>1824</v>
+        <v>1854</v>
       </c>
       <c r="Q102" t="s">
-        <v>1825</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.25">
@@ -26248,16 +26695,16 @@
         <v>22</v>
       </c>
       <c r="D103" t="s">
-        <v>1826</v>
+        <v>1856</v>
       </c>
       <c r="E103" t="s">
-        <v>1810</v>
+        <v>1840</v>
       </c>
       <c r="F103" t="s">
-        <v>1790</v>
+        <v>1820</v>
       </c>
       <c r="G103" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J103" t="s">
         <v>22</v>
@@ -26272,16 +26719,16 @@
         <v>38</v>
       </c>
       <c r="N103" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O103" t="s">
-        <v>1827</v>
+        <v>1857</v>
       </c>
       <c r="P103" t="s">
-        <v>1828</v>
+        <v>1858</v>
       </c>
       <c r="Q103" t="s">
-        <v>1829</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.25">
@@ -26295,16 +26742,16 @@
         <v>55</v>
       </c>
       <c r="D104" t="s">
-        <v>1809</v>
+        <v>1839</v>
       </c>
       <c r="E104" t="s">
-        <v>1810</v>
+        <v>1840</v>
       </c>
       <c r="F104" t="s">
-        <v>1830</v>
+        <v>1860</v>
       </c>
       <c r="G104" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J104" t="s">
         <v>22</v>
@@ -26319,16 +26766,16 @@
         <v>38</v>
       </c>
       <c r="N104" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O104" t="s">
-        <v>1831</v>
+        <v>1861</v>
       </c>
       <c r="P104" t="s">
-        <v>1832</v>
+        <v>1862</v>
       </c>
       <c r="Q104" t="s">
-        <v>1833</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.25">
@@ -26342,16 +26789,16 @@
         <v>25</v>
       </c>
       <c r="D105" t="s">
-        <v>1834</v>
+        <v>1864</v>
       </c>
       <c r="E105" t="s">
-        <v>1810</v>
+        <v>1840</v>
       </c>
       <c r="F105" t="s">
-        <v>1830</v>
+        <v>1860</v>
       </c>
       <c r="G105" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J105" t="s">
         <v>22</v>
@@ -26366,16 +26813,16 @@
         <v>38</v>
       </c>
       <c r="N105" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O105" t="s">
-        <v>1835</v>
+        <v>1865</v>
       </c>
       <c r="P105" t="s">
-        <v>1836</v>
+        <v>1866</v>
       </c>
       <c r="Q105" t="s">
-        <v>1837</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.25">
@@ -26389,7 +26836,7 @@
         <v>33</v>
       </c>
       <c r="D106" t="s">
-        <v>1838</v>
+        <v>1868</v>
       </c>
       <c r="E106" t="s">
         <v>421</v>
@@ -26398,7 +26845,7 @@
         <v>1016</v>
       </c>
       <c r="G106" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J106" t="s">
         <v>22</v>
@@ -26413,16 +26860,16 @@
         <v>38</v>
       </c>
       <c r="N106" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O106" t="s">
-        <v>1839</v>
+        <v>1869</v>
       </c>
       <c r="P106" t="s">
-        <v>1840</v>
+        <v>1870</v>
       </c>
       <c r="Q106" t="s">
-        <v>1841</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.25">
@@ -26436,16 +26883,16 @@
         <v>38</v>
       </c>
       <c r="D107" t="s">
-        <v>1842</v>
+        <v>1872</v>
       </c>
       <c r="E107" t="s">
-        <v>1843</v>
+        <v>1873</v>
       </c>
       <c r="F107" t="s">
-        <v>1572</v>
+        <v>1602</v>
       </c>
       <c r="G107" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="H107">
         <v>220000</v>
@@ -26466,16 +26913,16 @@
         <v>38</v>
       </c>
       <c r="N107" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O107" t="s">
-        <v>1844</v>
+        <v>1874</v>
       </c>
       <c r="P107" t="s">
-        <v>1845</v>
+        <v>1875</v>
       </c>
       <c r="Q107" t="s">
-        <v>1846</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.25">
@@ -26489,16 +26936,16 @@
         <v>62</v>
       </c>
       <c r="D108" t="s">
-        <v>1847</v>
+        <v>1877</v>
       </c>
       <c r="E108" t="s">
-        <v>1403</v>
+        <v>1433</v>
       </c>
       <c r="F108" t="s">
         <v>20</v>
       </c>
       <c r="G108" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="H108">
         <v>200000</v>
@@ -26519,16 +26966,16 @@
         <v>25</v>
       </c>
       <c r="N108" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O108" t="s">
-        <v>1848</v>
+        <v>1878</v>
       </c>
       <c r="P108" t="s">
-        <v>1849</v>
+        <v>1879</v>
       </c>
       <c r="Q108" t="s">
-        <v>1850</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.25">
@@ -26542,16 +26989,16 @@
         <v>30</v>
       </c>
       <c r="D109" t="s">
-        <v>1834</v>
+        <v>1864</v>
       </c>
       <c r="E109" t="s">
-        <v>1810</v>
+        <v>1840</v>
       </c>
       <c r="F109" t="s">
-        <v>1790</v>
+        <v>1820</v>
       </c>
       <c r="G109" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J109" t="s">
         <v>22</v>
@@ -26566,16 +27013,16 @@
         <v>38</v>
       </c>
       <c r="N109" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O109" t="s">
-        <v>1851</v>
+        <v>1881</v>
       </c>
       <c r="P109" t="s">
-        <v>1852</v>
+        <v>1882</v>
       </c>
       <c r="Q109" t="s">
-        <v>1853</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.25">
@@ -26589,16 +27036,16 @@
         <v>58</v>
       </c>
       <c r="D110" t="s">
-        <v>1809</v>
+        <v>1839</v>
       </c>
       <c r="E110" t="s">
-        <v>1810</v>
+        <v>1840</v>
       </c>
       <c r="F110" t="s">
-        <v>1475</v>
+        <v>1505</v>
       </c>
       <c r="G110" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J110" t="s">
         <v>22</v>
@@ -26613,16 +27060,16 @@
         <v>38</v>
       </c>
       <c r="N110" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O110" t="s">
-        <v>1854</v>
+        <v>1884</v>
       </c>
       <c r="P110" t="s">
-        <v>1855</v>
+        <v>1885</v>
       </c>
       <c r="Q110" t="s">
-        <v>1856</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.25">
@@ -26636,7 +27083,7 @@
         <v>55</v>
       </c>
       <c r="D111" t="s">
-        <v>1857</v>
+        <v>1887</v>
       </c>
       <c r="E111" t="s">
         <v>421</v>
@@ -26645,7 +27092,7 @@
         <v>20</v>
       </c>
       <c r="G111" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="H111">
         <v>217800</v>
@@ -26666,16 +27113,16 @@
         <v>25</v>
       </c>
       <c r="N111" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O111" t="s">
-        <v>1858</v>
+        <v>1888</v>
       </c>
       <c r="P111" t="s">
-        <v>1859</v>
+        <v>1889</v>
       </c>
       <c r="Q111" t="s">
-        <v>1860</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.25">
@@ -26689,16 +27136,16 @@
         <v>45</v>
       </c>
       <c r="D112" t="s">
-        <v>1861</v>
+        <v>1891</v>
       </c>
       <c r="E112" t="s">
         <v>421</v>
       </c>
       <c r="F112" t="s">
-        <v>1862</v>
+        <v>1892</v>
       </c>
       <c r="G112" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="H112">
         <v>219100</v>
@@ -26719,16 +27166,16 @@
         <v>25</v>
       </c>
       <c r="N112" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O112" t="s">
-        <v>1863</v>
+        <v>1893</v>
       </c>
       <c r="P112" t="s">
-        <v>1864</v>
+        <v>1894</v>
       </c>
       <c r="Q112" t="s">
-        <v>1865</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.25">
@@ -26748,10 +27195,10 @@
         <v>698</v>
       </c>
       <c r="F113" t="s">
-        <v>1866</v>
+        <v>1896</v>
       </c>
       <c r="G113" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J113" t="s">
         <v>22</v>
@@ -26766,16 +27213,16 @@
         <v>38</v>
       </c>
       <c r="N113" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O113" t="s">
-        <v>1867</v>
+        <v>1897</v>
       </c>
       <c r="P113" t="s">
-        <v>1868</v>
+        <v>1898</v>
       </c>
       <c r="Q113" t="s">
-        <v>1869</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.25">
@@ -26789,16 +27236,16 @@
         <v>35</v>
       </c>
       <c r="D114" t="s">
-        <v>1870</v>
+        <v>1900</v>
       </c>
       <c r="E114" t="s">
         <v>421</v>
       </c>
       <c r="F114" t="s">
-        <v>1871</v>
+        <v>1901</v>
       </c>
       <c r="G114" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J114" t="s">
         <v>22</v>
@@ -26813,16 +27260,16 @@
         <v>38</v>
       </c>
       <c r="N114" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O114" t="s">
-        <v>1872</v>
+        <v>1902</v>
       </c>
       <c r="P114" t="s">
-        <v>1873</v>
+        <v>1903</v>
       </c>
       <c r="Q114" t="s">
-        <v>1874</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.25">
@@ -26836,7 +27283,7 @@
         <v>38</v>
       </c>
       <c r="D115" t="s">
-        <v>1875</v>
+        <v>1905</v>
       </c>
       <c r="E115" t="s">
         <v>421</v>
@@ -26845,7 +27292,7 @@
         <v>20</v>
       </c>
       <c r="G115" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="H115">
         <v>219100</v>
@@ -26866,16 +27313,16 @@
         <v>38</v>
       </c>
       <c r="N115" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O115" t="s">
-        <v>1876</v>
+        <v>1906</v>
       </c>
       <c r="P115" t="s">
-        <v>1877</v>
+        <v>1907</v>
       </c>
       <c r="Q115" t="s">
-        <v>1878</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.25">
@@ -26889,16 +27336,16 @@
         <v>22</v>
       </c>
       <c r="D116" t="s">
-        <v>1879</v>
+        <v>1909</v>
       </c>
       <c r="E116" t="s">
-        <v>1880</v>
+        <v>1910</v>
       </c>
       <c r="F116" t="s">
-        <v>1881</v>
+        <v>1911</v>
       </c>
       <c r="G116" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J116" t="s">
         <v>22</v>
@@ -26913,16 +27360,16 @@
         <v>38</v>
       </c>
       <c r="N116" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O116" t="s">
-        <v>1882</v>
+        <v>1912</v>
       </c>
       <c r="P116" t="s">
-        <v>1883</v>
+        <v>1913</v>
       </c>
       <c r="Q116" t="s">
-        <v>1884</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.25">
@@ -26936,16 +27383,16 @@
         <v>35</v>
       </c>
       <c r="D117" t="s">
-        <v>1885</v>
+        <v>1915</v>
       </c>
       <c r="E117" t="s">
-        <v>1886</v>
+        <v>1916</v>
       </c>
       <c r="F117" t="s">
-        <v>1887</v>
+        <v>1917</v>
       </c>
       <c r="G117" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J117" t="s">
         <v>22</v>
@@ -26960,16 +27407,16 @@
         <v>38</v>
       </c>
       <c r="N117" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O117" t="s">
-        <v>1888</v>
+        <v>1918</v>
       </c>
       <c r="P117" t="s">
-        <v>1889</v>
+        <v>1919</v>
       </c>
       <c r="Q117" t="s">
-        <v>1890</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.25">
@@ -26983,7 +27430,7 @@
         <v>55</v>
       </c>
       <c r="D118" t="s">
-        <v>1891</v>
+        <v>1921</v>
       </c>
       <c r="E118" t="s">
         <v>1084</v>
@@ -26992,7 +27439,7 @@
         <v>1085</v>
       </c>
       <c r="G118" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="H118">
         <v>200000</v>
@@ -27013,16 +27460,16 @@
         <v>25</v>
       </c>
       <c r="N118" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O118" t="s">
-        <v>1892</v>
+        <v>1922</v>
       </c>
       <c r="P118" t="s">
-        <v>1893</v>
+        <v>1923</v>
       </c>
       <c r="Q118" t="s">
-        <v>1894</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.25">
@@ -27042,10 +27489,10 @@
         <v>421</v>
       </c>
       <c r="F119" t="s">
-        <v>1895</v>
+        <v>1925</v>
       </c>
       <c r="G119" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="H119">
         <v>180000</v>
@@ -27066,16 +27513,16 @@
         <v>25</v>
       </c>
       <c r="N119" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O119" t="s">
-        <v>1896</v>
+        <v>1926</v>
       </c>
       <c r="P119" t="s">
-        <v>1897</v>
+        <v>1927</v>
       </c>
       <c r="Q119" t="s">
-        <v>1898</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.25">
@@ -27095,10 +27542,10 @@
         <v>698</v>
       </c>
       <c r="F120" t="s">
-        <v>1443</v>
+        <v>1473</v>
       </c>
       <c r="G120" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J120" t="s">
         <v>22</v>
@@ -27113,16 +27560,16 @@
         <v>38</v>
       </c>
       <c r="N120" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O120" t="s">
-        <v>1899</v>
+        <v>1929</v>
       </c>
       <c r="P120" t="s">
-        <v>1900</v>
+        <v>1930</v>
       </c>
       <c r="Q120" t="s">
-        <v>1901</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.25">
@@ -27145,7 +27592,7 @@
         <v>1085</v>
       </c>
       <c r="G121" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J121" t="s">
         <v>22</v>
@@ -27160,16 +27607,16 @@
         <v>38</v>
       </c>
       <c r="N121" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O121" t="s">
-        <v>1902</v>
+        <v>1932</v>
       </c>
       <c r="P121" t="s">
-        <v>1903</v>
+        <v>1933</v>
       </c>
       <c r="Q121" t="s">
-        <v>1904</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.25">
@@ -27192,7 +27639,7 @@
         <v>1085</v>
       </c>
       <c r="G122" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J122" t="s">
         <v>22</v>
@@ -27207,16 +27654,16 @@
         <v>25</v>
       </c>
       <c r="N122" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O122" t="s">
-        <v>1905</v>
+        <v>1935</v>
       </c>
       <c r="P122" t="s">
-        <v>1906</v>
+        <v>1936</v>
       </c>
       <c r="Q122" t="s">
-        <v>1907</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.25">
@@ -27230,16 +27677,16 @@
         <v>32</v>
       </c>
       <c r="D123" t="s">
-        <v>1479</v>
+        <v>1509</v>
       </c>
       <c r="E123" t="s">
-        <v>1480</v>
+        <v>1510</v>
       </c>
       <c r="F123" t="s">
         <v>1025</v>
       </c>
       <c r="G123" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J123" t="s">
         <v>22</v>
@@ -27254,16 +27701,16 @@
         <v>38</v>
       </c>
       <c r="N123" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O123" t="s">
-        <v>1908</v>
+        <v>1938</v>
       </c>
       <c r="P123" t="s">
-        <v>1909</v>
+        <v>1939</v>
       </c>
       <c r="Q123" t="s">
-        <v>1910</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.25">
@@ -27277,7 +27724,7 @@
         <v>30</v>
       </c>
       <c r="D124" t="s">
-        <v>1911</v>
+        <v>1941</v>
       </c>
       <c r="E124" t="s">
         <v>698</v>
@@ -27286,7 +27733,7 @@
         <v>707</v>
       </c>
       <c r="G124" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J124" t="s">
         <v>22</v>
@@ -27301,16 +27748,16 @@
         <v>38</v>
       </c>
       <c r="N124" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O124" t="s">
-        <v>1912</v>
+        <v>1942</v>
       </c>
       <c r="P124" t="s">
-        <v>1913</v>
+        <v>1943</v>
       </c>
       <c r="Q124" t="s">
-        <v>1914</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.25">
@@ -27324,16 +27771,16 @@
         <v>5</v>
       </c>
       <c r="D125" t="s">
-        <v>1468</v>
+        <v>1498</v>
       </c>
       <c r="E125" t="s">
-        <v>1469</v>
+        <v>1499</v>
       </c>
       <c r="F125" t="s">
         <v>1032</v>
       </c>
       <c r="G125" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J125" t="s">
         <v>22</v>
@@ -27348,16 +27795,16 @@
         <v>38</v>
       </c>
       <c r="N125" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O125" t="s">
-        <v>1915</v>
+        <v>1945</v>
       </c>
       <c r="P125" t="s">
-        <v>1916</v>
+        <v>1946</v>
       </c>
       <c r="Q125" t="s">
-        <v>1917</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.25">
@@ -27371,16 +27818,16 @@
         <v>30</v>
       </c>
       <c r="D126" t="s">
-        <v>1473</v>
+        <v>1503</v>
       </c>
       <c r="E126" t="s">
-        <v>1474</v>
+        <v>1504</v>
       </c>
       <c r="F126" t="s">
-        <v>1475</v>
+        <v>1505</v>
       </c>
       <c r="G126" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J126" t="s">
         <v>22</v>
@@ -27395,16 +27842,16 @@
         <v>38</v>
       </c>
       <c r="N126" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O126" t="s">
-        <v>1918</v>
+        <v>1948</v>
       </c>
       <c r="P126" t="s">
-        <v>1919</v>
+        <v>1949</v>
       </c>
       <c r="Q126" t="s">
-        <v>1920</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.25">
@@ -27418,16 +27865,16 @@
         <v>40</v>
       </c>
       <c r="D127" t="s">
-        <v>1921</v>
+        <v>1951</v>
       </c>
       <c r="E127" t="s">
-        <v>1922</v>
+        <v>1952</v>
       </c>
       <c r="F127" t="s">
-        <v>1923</v>
+        <v>1953</v>
       </c>
       <c r="G127" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J127" t="s">
         <v>22</v>
@@ -27442,16 +27889,16 @@
         <v>38</v>
       </c>
       <c r="N127" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O127" t="s">
-        <v>1924</v>
+        <v>1954</v>
       </c>
       <c r="P127" t="s">
-        <v>1925</v>
+        <v>1955</v>
       </c>
       <c r="Q127" t="s">
-        <v>1926</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.25">
@@ -27465,16 +27912,16 @@
         <v>38</v>
       </c>
       <c r="D128" t="s">
-        <v>1927</v>
+        <v>1957</v>
       </c>
       <c r="E128" t="s">
         <v>421</v>
       </c>
       <c r="F128" t="s">
-        <v>1443</v>
+        <v>1473</v>
       </c>
       <c r="G128" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J128" t="s">
         <v>22</v>
@@ -27489,16 +27936,16 @@
         <v>38</v>
       </c>
       <c r="N128" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O128" t="s">
-        <v>1928</v>
+        <v>1958</v>
       </c>
       <c r="P128" t="s">
-        <v>1929</v>
+        <v>1959</v>
       </c>
       <c r="Q128" t="s">
-        <v>1930</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="129" spans="1:17" x14ac:dyDescent="0.25">
@@ -27512,16 +27959,16 @@
         <v>36</v>
       </c>
       <c r="D129" t="s">
-        <v>1931</v>
+        <v>1961</v>
       </c>
       <c r="E129" t="s">
         <v>421</v>
       </c>
       <c r="F129" t="s">
-        <v>1443</v>
+        <v>1473</v>
       </c>
       <c r="G129" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J129" t="s">
         <v>22</v>
@@ -27536,16 +27983,16 @@
         <v>38</v>
       </c>
       <c r="N129" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O129" t="s">
-        <v>1932</v>
+        <v>1962</v>
       </c>
       <c r="P129" t="s">
-        <v>1933</v>
+        <v>1963</v>
       </c>
       <c r="Q129" t="s">
-        <v>1934</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="130" spans="1:17" x14ac:dyDescent="0.25">
@@ -27562,13 +28009,13 @@
         <v>549</v>
       </c>
       <c r="E130" t="s">
-        <v>1935</v>
+        <v>1965</v>
       </c>
       <c r="F130" t="s">
-        <v>1936</v>
+        <v>1966</v>
       </c>
       <c r="G130" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J130" t="s">
         <v>22</v>
@@ -27583,16 +28030,16 @@
         <v>38</v>
       </c>
       <c r="N130" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O130" t="s">
-        <v>1937</v>
+        <v>1967</v>
       </c>
       <c r="P130" t="s">
-        <v>1938</v>
+        <v>1968</v>
       </c>
       <c r="Q130" t="s">
-        <v>1939</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="131" spans="1:17" x14ac:dyDescent="0.25">
@@ -27606,16 +28053,16 @@
         <v>45</v>
       </c>
       <c r="D131" t="s">
-        <v>1940</v>
+        <v>1970</v>
       </c>
       <c r="E131" t="s">
-        <v>1941</v>
+        <v>1971</v>
       </c>
       <c r="F131" t="s">
-        <v>1942</v>
+        <v>1972</v>
       </c>
       <c r="G131" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J131" t="s">
         <v>22</v>
@@ -27630,16 +28077,16 @@
         <v>38</v>
       </c>
       <c r="N131" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O131" t="s">
-        <v>1943</v>
+        <v>1973</v>
       </c>
       <c r="P131" t="s">
-        <v>1944</v>
+        <v>1974</v>
       </c>
       <c r="Q131" t="s">
-        <v>1945</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="132" spans="1:17" x14ac:dyDescent="0.25">
@@ -27653,16 +28100,16 @@
         <v>40</v>
       </c>
       <c r="D132" t="s">
-        <v>1946</v>
+        <v>1976</v>
       </c>
       <c r="E132" t="s">
-        <v>1947</v>
+        <v>1977</v>
       </c>
       <c r="F132" t="s">
         <v>1085</v>
       </c>
       <c r="G132" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J132" t="s">
         <v>22</v>
@@ -27677,16 +28124,16 @@
         <v>38</v>
       </c>
       <c r="N132" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O132" t="s">
-        <v>1948</v>
+        <v>1978</v>
       </c>
       <c r="P132" t="s">
-        <v>1949</v>
+        <v>1979</v>
       </c>
       <c r="Q132" t="s">
-        <v>1950</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="133" spans="1:17" x14ac:dyDescent="0.25">
@@ -27700,16 +28147,16 @@
         <v>40</v>
       </c>
       <c r="D133" t="s">
-        <v>1951</v>
+        <v>1981</v>
       </c>
       <c r="E133" t="s">
-        <v>1947</v>
+        <v>1977</v>
       </c>
       <c r="F133" t="s">
         <v>1085</v>
       </c>
       <c r="G133" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J133" t="s">
         <v>22</v>
@@ -27724,16 +28171,16 @@
         <v>38</v>
       </c>
       <c r="N133" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O133" t="s">
-        <v>1952</v>
+        <v>1982</v>
       </c>
       <c r="P133" t="s">
-        <v>1953</v>
+        <v>1983</v>
       </c>
       <c r="Q133" t="s">
-        <v>1954</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="134" spans="1:17" x14ac:dyDescent="0.25">
@@ -27747,16 +28194,16 @@
         <v>18</v>
       </c>
       <c r="D134" t="s">
-        <v>1707</v>
+        <v>1737</v>
       </c>
       <c r="E134" t="s">
-        <v>1708</v>
+        <v>1738</v>
       </c>
       <c r="F134" t="s">
         <v>1016</v>
       </c>
       <c r="G134" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J134" t="s">
         <v>22</v>
@@ -27771,16 +28218,16 @@
         <v>38</v>
       </c>
       <c r="N134" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O134" t="s">
-        <v>1955</v>
+        <v>1985</v>
       </c>
       <c r="P134" t="s">
-        <v>1956</v>
+        <v>1986</v>
       </c>
       <c r="Q134" t="s">
-        <v>1957</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="135" spans="1:17" x14ac:dyDescent="0.25">
@@ -27794,16 +28241,16 @@
         <v>3</v>
       </c>
       <c r="D135" t="s">
-        <v>1716</v>
+        <v>1746</v>
       </c>
       <c r="E135" t="s">
-        <v>1708</v>
+        <v>1738</v>
       </c>
       <c r="F135" t="s">
         <v>1016</v>
       </c>
       <c r="G135" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J135" t="s">
         <v>22</v>
@@ -27818,16 +28265,16 @@
         <v>38</v>
       </c>
       <c r="N135" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O135" t="s">
-        <v>1958</v>
+        <v>1988</v>
       </c>
       <c r="P135" t="s">
-        <v>1959</v>
+        <v>1989</v>
       </c>
       <c r="Q135" t="s">
-        <v>1960</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="136" spans="1:17" x14ac:dyDescent="0.25">
@@ -27841,16 +28288,16 @@
         <v>38</v>
       </c>
       <c r="D136" t="s">
-        <v>1961</v>
+        <v>1991</v>
       </c>
       <c r="E136" t="s">
-        <v>1962</v>
+        <v>1992</v>
       </c>
       <c r="F136" t="s">
-        <v>1963</v>
+        <v>1993</v>
       </c>
       <c r="G136" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J136" t="s">
         <v>22</v>
@@ -27865,16 +28312,16 @@
         <v>38</v>
       </c>
       <c r="N136" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O136" t="s">
-        <v>1964</v>
+        <v>1994</v>
       </c>
       <c r="P136" t="s">
-        <v>1965</v>
+        <v>1995</v>
       </c>
       <c r="Q136" t="s">
-        <v>1966</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="137" spans="1:17" x14ac:dyDescent="0.25">
@@ -27888,16 +28335,16 @@
         <v>15</v>
       </c>
       <c r="D137" t="s">
-        <v>1967</v>
+        <v>1997</v>
       </c>
       <c r="E137" t="s">
-        <v>1962</v>
+        <v>1992</v>
       </c>
       <c r="F137" t="s">
-        <v>1968</v>
+        <v>1998</v>
       </c>
       <c r="G137" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J137" t="s">
         <v>22</v>
@@ -27912,16 +28359,16 @@
         <v>38</v>
       </c>
       <c r="N137" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O137" t="s">
-        <v>1969</v>
+        <v>1999</v>
       </c>
       <c r="P137" t="s">
-        <v>1970</v>
+        <v>2000</v>
       </c>
       <c r="Q137" t="s">
-        <v>1971</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.25">
@@ -27935,16 +28382,16 @@
         <v>33</v>
       </c>
       <c r="D138" t="s">
-        <v>1972</v>
+        <v>2002</v>
       </c>
       <c r="E138" t="s">
-        <v>1962</v>
+        <v>1992</v>
       </c>
       <c r="F138" t="s">
-        <v>1968</v>
+        <v>1998</v>
       </c>
       <c r="G138" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J138" t="s">
         <v>22</v>
@@ -27959,16 +28406,16 @@
         <v>38</v>
       </c>
       <c r="N138" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O138" t="s">
-        <v>1973</v>
+        <v>2003</v>
       </c>
       <c r="P138" t="s">
-        <v>1974</v>
+        <v>2004</v>
       </c>
       <c r="Q138" t="s">
-        <v>1975</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.25">
@@ -27982,16 +28429,16 @@
         <v>40</v>
       </c>
       <c r="D139" t="s">
-        <v>1976</v>
+        <v>2006</v>
       </c>
       <c r="E139" t="s">
-        <v>1962</v>
+        <v>1992</v>
       </c>
       <c r="F139" t="s">
-        <v>1977</v>
+        <v>2007</v>
       </c>
       <c r="G139" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J139" t="s">
         <v>22</v>
@@ -28006,16 +28453,16 @@
         <v>38</v>
       </c>
       <c r="N139" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O139" t="s">
-        <v>1978</v>
+        <v>2008</v>
       </c>
       <c r="P139" t="s">
-        <v>1979</v>
+        <v>2009</v>
       </c>
       <c r="Q139" t="s">
-        <v>1980</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.25">
@@ -28029,16 +28476,16 @@
         <v>38</v>
       </c>
       <c r="D140" t="s">
-        <v>1981</v>
+        <v>2011</v>
       </c>
       <c r="E140" t="s">
-        <v>1962</v>
+        <v>1992</v>
       </c>
       <c r="F140" t="s">
-        <v>1968</v>
+        <v>1998</v>
       </c>
       <c r="G140" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J140" t="s">
         <v>22</v>
@@ -28053,16 +28500,16 @@
         <v>38</v>
       </c>
       <c r="N140" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O140" t="s">
-        <v>1982</v>
+        <v>2012</v>
       </c>
       <c r="P140" t="s">
-        <v>1983</v>
+        <v>2013</v>
       </c>
       <c r="Q140" t="s">
-        <v>1984</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.25">
@@ -28076,16 +28523,16 @@
         <v>45</v>
       </c>
       <c r="D141" t="s">
-        <v>1985</v>
+        <v>2015</v>
       </c>
       <c r="E141" t="s">
-        <v>1962</v>
+        <v>1992</v>
       </c>
       <c r="F141" t="s">
-        <v>1986</v>
+        <v>2016</v>
       </c>
       <c r="G141" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J141" t="s">
         <v>22</v>
@@ -28100,16 +28547,16 @@
         <v>38</v>
       </c>
       <c r="N141" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O141" t="s">
-        <v>1987</v>
+        <v>2017</v>
       </c>
       <c r="P141" t="s">
-        <v>1988</v>
+        <v>2018</v>
       </c>
       <c r="Q141" t="s">
-        <v>1989</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.25">
@@ -28123,16 +28570,16 @@
         <v>18</v>
       </c>
       <c r="D142" t="s">
-        <v>1990</v>
+        <v>2020</v>
       </c>
       <c r="E142" t="s">
-        <v>1962</v>
+        <v>1992</v>
       </c>
       <c r="F142" t="s">
-        <v>1991</v>
+        <v>2021</v>
       </c>
       <c r="G142" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J142" t="s">
         <v>22</v>
@@ -28147,16 +28594,16 @@
         <v>38</v>
       </c>
       <c r="N142" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O142" t="s">
-        <v>1992</v>
+        <v>2022</v>
       </c>
       <c r="P142" t="s">
-        <v>1993</v>
+        <v>2023</v>
       </c>
       <c r="Q142" t="s">
-        <v>1994</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="143" spans="1:17" x14ac:dyDescent="0.25">
@@ -28170,16 +28617,16 @@
         <v>20</v>
       </c>
       <c r="D143" t="s">
-        <v>1995</v>
+        <v>2025</v>
       </c>
       <c r="E143" t="s">
-        <v>1962</v>
+        <v>1992</v>
       </c>
       <c r="F143" t="s">
-        <v>1968</v>
+        <v>1998</v>
       </c>
       <c r="G143" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J143" t="s">
         <v>22</v>
@@ -28194,16 +28641,16 @@
         <v>38</v>
       </c>
       <c r="N143" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O143" t="s">
-        <v>1996</v>
+        <v>2026</v>
       </c>
       <c r="P143" t="s">
-        <v>1997</v>
+        <v>2027</v>
       </c>
       <c r="Q143" t="s">
-        <v>1998</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="144" spans="1:17" x14ac:dyDescent="0.25">
@@ -28217,16 +28664,16 @@
         <v>60</v>
       </c>
       <c r="D144" t="s">
-        <v>1999</v>
+        <v>2029</v>
       </c>
       <c r="E144" t="s">
-        <v>1962</v>
+        <v>1992</v>
       </c>
       <c r="F144" t="s">
-        <v>2000</v>
+        <v>2030</v>
       </c>
       <c r="G144" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J144" t="s">
         <v>22</v>
@@ -28241,16 +28688,16 @@
         <v>38</v>
       </c>
       <c r="N144" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O144" t="s">
-        <v>2001</v>
+        <v>2031</v>
       </c>
       <c r="P144" t="s">
-        <v>2002</v>
+        <v>2032</v>
       </c>
       <c r="Q144" t="s">
-        <v>2003</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="145" spans="1:17" x14ac:dyDescent="0.25">
@@ -28264,16 +28711,16 @@
         <v>32</v>
       </c>
       <c r="D145" t="s">
-        <v>2004</v>
+        <v>2034</v>
       </c>
       <c r="E145" t="s">
-        <v>1962</v>
+        <v>1992</v>
       </c>
       <c r="F145" t="s">
-        <v>1977</v>
+        <v>2007</v>
       </c>
       <c r="G145" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J145" t="s">
         <v>22</v>
@@ -28288,16 +28735,16 @@
         <v>38</v>
       </c>
       <c r="N145" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O145" t="s">
-        <v>2005</v>
+        <v>2035</v>
       </c>
       <c r="P145" t="s">
-        <v>2006</v>
+        <v>2036</v>
       </c>
       <c r="Q145" t="s">
-        <v>2007</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="146" spans="1:17" x14ac:dyDescent="0.25">
@@ -28311,16 +28758,16 @@
         <v>15</v>
       </c>
       <c r="D146" t="s">
-        <v>2008</v>
+        <v>2038</v>
       </c>
       <c r="E146" t="s">
-        <v>1962</v>
+        <v>1992</v>
       </c>
       <c r="F146" t="s">
-        <v>2009</v>
+        <v>2039</v>
       </c>
       <c r="G146" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J146" t="s">
         <v>22</v>
@@ -28335,16 +28782,16 @@
         <v>38</v>
       </c>
       <c r="N146" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O146" t="s">
-        <v>2010</v>
+        <v>2040</v>
       </c>
       <c r="P146" t="s">
-        <v>2011</v>
+        <v>2041</v>
       </c>
       <c r="Q146" t="s">
-        <v>2012</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="147" spans="1:17" x14ac:dyDescent="0.25">
@@ -28361,13 +28808,13 @@
         <v>280</v>
       </c>
       <c r="E147" t="s">
-        <v>1962</v>
+        <v>1992</v>
       </c>
       <c r="F147" t="s">
-        <v>2013</v>
+        <v>2043</v>
       </c>
       <c r="G147" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J147" t="s">
         <v>22</v>
@@ -28382,16 +28829,16 @@
         <v>38</v>
       </c>
       <c r="N147" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O147" t="s">
-        <v>2014</v>
+        <v>2044</v>
       </c>
       <c r="P147" t="s">
-        <v>2015</v>
+        <v>2045</v>
       </c>
       <c r="Q147" t="s">
-        <v>2016</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="148" spans="1:17" x14ac:dyDescent="0.25">
@@ -28405,16 +28852,16 @@
         <v>20</v>
       </c>
       <c r="D148" t="s">
-        <v>2017</v>
+        <v>2047</v>
       </c>
       <c r="E148" t="s">
-        <v>1962</v>
+        <v>1992</v>
       </c>
       <c r="F148" t="s">
-        <v>1977</v>
+        <v>2007</v>
       </c>
       <c r="G148" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J148" t="s">
         <v>22</v>
@@ -28429,16 +28876,16 @@
         <v>38</v>
       </c>
       <c r="N148" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O148" t="s">
-        <v>2018</v>
+        <v>2048</v>
       </c>
       <c r="P148" t="s">
-        <v>2019</v>
+        <v>2049</v>
       </c>
       <c r="Q148" t="s">
-        <v>2020</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="149" spans="1:17" x14ac:dyDescent="0.25">
@@ -28452,16 +28899,16 @@
         <v>82</v>
       </c>
       <c r="D149" t="s">
-        <v>2021</v>
+        <v>2051</v>
       </c>
       <c r="E149" t="s">
-        <v>1962</v>
+        <v>1992</v>
       </c>
       <c r="F149" t="s">
-        <v>2022</v>
+        <v>2052</v>
       </c>
       <c r="G149" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J149" t="s">
         <v>22</v>
@@ -28476,16 +28923,16 @@
         <v>25</v>
       </c>
       <c r="N149" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O149" t="s">
-        <v>2023</v>
+        <v>2053</v>
       </c>
       <c r="P149" t="s">
-        <v>2024</v>
+        <v>2054</v>
       </c>
       <c r="Q149" t="s">
-        <v>2025</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="150" spans="1:17" x14ac:dyDescent="0.25">
@@ -28499,16 +28946,16 @@
         <v>55</v>
       </c>
       <c r="D150" t="s">
-        <v>2026</v>
+        <v>2056</v>
       </c>
       <c r="E150" t="s">
         <v>1163</v>
       </c>
       <c r="F150" t="s">
-        <v>2027</v>
+        <v>2057</v>
       </c>
       <c r="G150" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J150" t="s">
         <v>22</v>
@@ -28523,16 +28970,16 @@
         <v>38</v>
       </c>
       <c r="N150" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O150" t="s">
-        <v>2028</v>
+        <v>2058</v>
       </c>
       <c r="P150" t="s">
-        <v>2029</v>
+        <v>2059</v>
       </c>
       <c r="Q150" t="s">
-        <v>2030</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="151" spans="1:17" x14ac:dyDescent="0.25">
@@ -28546,16 +28993,16 @@
         <v>28</v>
       </c>
       <c r="D151" t="s">
-        <v>2031</v>
+        <v>2061</v>
       </c>
       <c r="E151" t="s">
         <v>1163</v>
       </c>
       <c r="F151" t="s">
-        <v>2032</v>
+        <v>2062</v>
       </c>
       <c r="G151" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J151" t="s">
         <v>22</v>
@@ -28570,16 +29017,16 @@
         <v>38</v>
       </c>
       <c r="N151" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O151" t="s">
-        <v>2033</v>
+        <v>2063</v>
       </c>
       <c r="P151" t="s">
-        <v>2034</v>
+        <v>2064</v>
       </c>
       <c r="Q151" t="s">
-        <v>2035</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="152" spans="1:17" x14ac:dyDescent="0.25">
@@ -28593,16 +29040,16 @@
         <v>7</v>
       </c>
       <c r="D152" t="s">
-        <v>2036</v>
+        <v>2066</v>
       </c>
       <c r="E152" t="s">
         <v>1163</v>
       </c>
       <c r="F152" t="s">
-        <v>2037</v>
+        <v>2067</v>
       </c>
       <c r="G152" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J152" t="s">
         <v>22</v>
@@ -28617,16 +29064,16 @@
         <v>38</v>
       </c>
       <c r="N152" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O152" t="s">
-        <v>2038</v>
+        <v>2068</v>
       </c>
       <c r="P152" t="s">
-        <v>2039</v>
+        <v>2069</v>
       </c>
       <c r="Q152" t="s">
-        <v>2040</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="153" spans="1:17" x14ac:dyDescent="0.25">
@@ -28640,16 +29087,16 @@
         <v>55</v>
       </c>
       <c r="D153" t="s">
-        <v>2041</v>
+        <v>2071</v>
       </c>
       <c r="E153" t="s">
         <v>1163</v>
       </c>
       <c r="F153" t="s">
-        <v>2042</v>
+        <v>2072</v>
       </c>
       <c r="G153" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="J153" t="s">
         <v>22</v>
@@ -28664,16 +29111,16 @@
         <v>38</v>
       </c>
       <c r="N153" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O153" t="s">
-        <v>2043</v>
+        <v>2073</v>
       </c>
       <c r="P153" t="s">
-        <v>2044</v>
+        <v>2074</v>
       </c>
       <c r="Q153" t="s">
-        <v>2045</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="154" spans="1:17" x14ac:dyDescent="0.25">
@@ -28687,16 +29134,16 @@
         <v>40</v>
       </c>
       <c r="D154" t="s">
-        <v>2046</v>
+        <v>2076</v>
       </c>
       <c r="E154" t="s">
-        <v>2047</v>
+        <v>2077</v>
       </c>
       <c r="F154" t="s">
         <v>1284</v>
       </c>
       <c r="G154" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J154" t="s">
         <v>22</v>
@@ -28711,16 +29158,16 @@
         <v>38</v>
       </c>
       <c r="N154" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O154" t="s">
-        <v>2048</v>
+        <v>2078</v>
       </c>
       <c r="P154" t="s">
-        <v>2049</v>
+        <v>2079</v>
       </c>
       <c r="Q154" t="s">
-        <v>2050</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="155" spans="1:17" x14ac:dyDescent="0.25">
@@ -28734,16 +29181,16 @@
         <v>45</v>
       </c>
       <c r="D155" t="s">
-        <v>2051</v>
+        <v>2081</v>
       </c>
       <c r="E155" t="s">
         <v>1198</v>
       </c>
       <c r="F155" t="s">
-        <v>2052</v>
+        <v>2082</v>
       </c>
       <c r="G155" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J155" t="s">
         <v>22</v>
@@ -28758,16 +29205,16 @@
         <v>38</v>
       </c>
       <c r="N155" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O155" t="s">
-        <v>2053</v>
+        <v>2083</v>
       </c>
       <c r="P155" t="s">
-        <v>2054</v>
+        <v>2084</v>
       </c>
       <c r="Q155" t="s">
-        <v>2055</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="156" spans="1:17" x14ac:dyDescent="0.25">
@@ -28781,16 +29228,16 @@
         <v>38</v>
       </c>
       <c r="D156" t="s">
-        <v>2056</v>
+        <v>2086</v>
       </c>
       <c r="E156" t="s">
         <v>1198</v>
       </c>
       <c r="F156" t="s">
-        <v>2057</v>
+        <v>2087</v>
       </c>
       <c r="G156" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J156" t="s">
         <v>22</v>
@@ -28805,16 +29252,16 @@
         <v>38</v>
       </c>
       <c r="N156" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O156" t="s">
-        <v>2058</v>
+        <v>2088</v>
       </c>
       <c r="P156" t="s">
-        <v>2059</v>
+        <v>2089</v>
       </c>
       <c r="Q156" t="s">
-        <v>2060</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="157" spans="1:17" x14ac:dyDescent="0.25">
@@ -28828,16 +29275,16 @@
         <v>68</v>
       </c>
       <c r="D157" t="s">
-        <v>2061</v>
+        <v>2091</v>
       </c>
       <c r="E157" t="s">
         <v>1198</v>
       </c>
       <c r="F157" t="s">
-        <v>2062</v>
+        <v>2092</v>
       </c>
       <c r="G157" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J157" t="s">
         <v>22</v>
@@ -28852,16 +29299,16 @@
         <v>38</v>
       </c>
       <c r="N157" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O157" t="s">
-        <v>2063</v>
+        <v>2093</v>
       </c>
       <c r="P157" t="s">
-        <v>2064</v>
+        <v>2094</v>
       </c>
       <c r="Q157" t="s">
-        <v>2065</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="158" spans="1:17" x14ac:dyDescent="0.25">
@@ -28881,10 +29328,10 @@
         <v>1198</v>
       </c>
       <c r="F158" t="s">
-        <v>2052</v>
+        <v>2082</v>
       </c>
       <c r="G158" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J158" t="s">
         <v>22</v>
@@ -28899,16 +29346,16 @@
         <v>38</v>
       </c>
       <c r="N158" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O158" t="s">
-        <v>2066</v>
+        <v>2096</v>
       </c>
       <c r="P158" t="s">
-        <v>2067</v>
+        <v>2097</v>
       </c>
       <c r="Q158" t="s">
-        <v>2068</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="159" spans="1:17" x14ac:dyDescent="0.25">
@@ -28928,10 +29375,10 @@
         <v>1198</v>
       </c>
       <c r="F159" t="s">
-        <v>2069</v>
+        <v>2099</v>
       </c>
       <c r="G159" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J159" t="s">
         <v>22</v>
@@ -28946,16 +29393,16 @@
         <v>38</v>
       </c>
       <c r="N159" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O159" t="s">
-        <v>2070</v>
+        <v>2100</v>
       </c>
       <c r="P159" t="s">
-        <v>2071</v>
+        <v>2101</v>
       </c>
       <c r="Q159" t="s">
-        <v>2072</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="160" spans="1:17" x14ac:dyDescent="0.25">
@@ -28969,16 +29416,16 @@
         <v>15</v>
       </c>
       <c r="D160" t="s">
-        <v>2073</v>
+        <v>2103</v>
       </c>
       <c r="E160" t="s">
         <v>1198</v>
       </c>
       <c r="F160" t="s">
-        <v>2052</v>
+        <v>2082</v>
       </c>
       <c r="G160" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J160" t="s">
         <v>22</v>
@@ -28993,16 +29440,16 @@
         <v>38</v>
       </c>
       <c r="N160" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O160" t="s">
-        <v>2074</v>
+        <v>2104</v>
       </c>
       <c r="P160" t="s">
-        <v>2075</v>
+        <v>2105</v>
       </c>
       <c r="Q160" t="s">
-        <v>2076</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="161" spans="1:17" x14ac:dyDescent="0.25">
@@ -29016,16 +29463,16 @@
         <v>22</v>
       </c>
       <c r="D161" t="s">
-        <v>2077</v>
+        <v>2107</v>
       </c>
       <c r="E161" t="s">
         <v>1198</v>
       </c>
       <c r="F161" t="s">
-        <v>2078</v>
+        <v>2108</v>
       </c>
       <c r="G161" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J161" t="s">
         <v>22</v>
@@ -29040,16 +29487,16 @@
         <v>38</v>
       </c>
       <c r="N161" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O161" t="s">
-        <v>2079</v>
+        <v>2109</v>
       </c>
       <c r="P161" t="s">
-        <v>2080</v>
+        <v>2110</v>
       </c>
       <c r="Q161" t="s">
-        <v>2081</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="162" spans="1:17" x14ac:dyDescent="0.25">
@@ -29063,7 +29510,7 @@
         <v>25</v>
       </c>
       <c r="D162" t="s">
-        <v>2082</v>
+        <v>2112</v>
       </c>
       <c r="E162" t="s">
         <v>1207</v>
@@ -29072,7 +29519,7 @@
         <v>1208</v>
       </c>
       <c r="G162" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J162" t="s">
         <v>22</v>
@@ -29087,16 +29534,16 @@
         <v>38</v>
       </c>
       <c r="N162" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O162" t="s">
-        <v>2083</v>
+        <v>2113</v>
       </c>
       <c r="P162" t="s">
-        <v>2084</v>
+        <v>2114</v>
       </c>
       <c r="Q162" t="s">
-        <v>2085</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="163" spans="1:17" x14ac:dyDescent="0.25">
@@ -29110,16 +29557,16 @@
         <v>20</v>
       </c>
       <c r="D163" t="s">
-        <v>2086</v>
+        <v>2116</v>
       </c>
       <c r="E163" t="s">
         <v>1207</v>
       </c>
       <c r="F163" t="s">
-        <v>2087</v>
+        <v>2117</v>
       </c>
       <c r="G163" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J163" t="s">
         <v>22</v>
@@ -29134,16 +29581,16 @@
         <v>38</v>
       </c>
       <c r="N163" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O163" t="s">
-        <v>2088</v>
+        <v>2118</v>
       </c>
       <c r="P163" t="s">
-        <v>2089</v>
+        <v>2119</v>
       </c>
       <c r="Q163" t="s">
-        <v>2090</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="164" spans="1:17" x14ac:dyDescent="0.25">
@@ -29157,16 +29604,16 @@
         <v>12</v>
       </c>
       <c r="D164" t="s">
-        <v>2091</v>
+        <v>2121</v>
       </c>
       <c r="E164" t="s">
         <v>1207</v>
       </c>
       <c r="F164" t="s">
-        <v>2092</v>
+        <v>2122</v>
       </c>
       <c r="G164" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J164" t="s">
         <v>22</v>
@@ -29181,16 +29628,16 @@
         <v>38</v>
       </c>
       <c r="N164" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O164" t="s">
-        <v>2093</v>
+        <v>2123</v>
       </c>
       <c r="P164" t="s">
-        <v>2094</v>
+        <v>2124</v>
       </c>
       <c r="Q164" t="s">
-        <v>2095</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="165" spans="1:17" x14ac:dyDescent="0.25">
@@ -29204,16 +29651,16 @@
         <v>15</v>
       </c>
       <c r="D165" t="s">
-        <v>2096</v>
+        <v>2126</v>
       </c>
       <c r="E165" t="s">
         <v>1207</v>
       </c>
       <c r="F165" t="s">
-        <v>2097</v>
+        <v>2127</v>
       </c>
       <c r="G165" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J165" t="s">
         <v>22</v>
@@ -29228,16 +29675,16 @@
         <v>38</v>
       </c>
       <c r="N165" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O165" t="s">
-        <v>2098</v>
+        <v>2128</v>
       </c>
       <c r="P165" t="s">
-        <v>2099</v>
+        <v>2129</v>
       </c>
       <c r="Q165" t="s">
-        <v>2100</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="166" spans="1:17" x14ac:dyDescent="0.25">
@@ -29251,16 +29698,16 @@
         <v>35</v>
       </c>
       <c r="D166" t="s">
-        <v>2101</v>
+        <v>2131</v>
       </c>
       <c r="E166" t="s">
         <v>1207</v>
       </c>
       <c r="F166" t="s">
-        <v>2102</v>
+        <v>2132</v>
       </c>
       <c r="G166" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J166" t="s">
         <v>22</v>
@@ -29275,16 +29722,16 @@
         <v>38</v>
       </c>
       <c r="N166" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O166" t="s">
-        <v>2103</v>
+        <v>2133</v>
       </c>
       <c r="P166" t="s">
-        <v>2104</v>
+        <v>2134</v>
       </c>
       <c r="Q166" t="s">
-        <v>2105</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="167" spans="1:17" x14ac:dyDescent="0.25">
@@ -29298,16 +29745,16 @@
         <v>20</v>
       </c>
       <c r="D167" t="s">
-        <v>2106</v>
+        <v>2136</v>
       </c>
       <c r="E167" t="s">
         <v>1207</v>
       </c>
       <c r="F167" t="s">
-        <v>2097</v>
+        <v>2127</v>
       </c>
       <c r="G167" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J167" t="s">
         <v>22</v>
@@ -29322,16 +29769,16 @@
         <v>38</v>
       </c>
       <c r="N167" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O167" t="s">
-        <v>2107</v>
+        <v>2137</v>
       </c>
       <c r="P167" t="s">
-        <v>2108</v>
+        <v>2138</v>
       </c>
       <c r="Q167" t="s">
-        <v>2109</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="168" spans="1:17" x14ac:dyDescent="0.25">
@@ -29345,16 +29792,16 @@
         <v>15</v>
       </c>
       <c r="D168" t="s">
-        <v>2110</v>
+        <v>2140</v>
       </c>
       <c r="E168" t="s">
         <v>1207</v>
       </c>
       <c r="F168" t="s">
-        <v>2111</v>
+        <v>2141</v>
       </c>
       <c r="G168" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J168" t="s">
         <v>22</v>
@@ -29369,16 +29816,16 @@
         <v>38</v>
       </c>
       <c r="N168" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O168" t="s">
-        <v>2112</v>
+        <v>2142</v>
       </c>
       <c r="P168" t="s">
-        <v>2113</v>
+        <v>2143</v>
       </c>
       <c r="Q168" t="s">
-        <v>2114</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="169" spans="1:17" x14ac:dyDescent="0.25">
@@ -29392,16 +29839,16 @@
         <v>45</v>
       </c>
       <c r="D169" t="s">
-        <v>2115</v>
+        <v>2145</v>
       </c>
       <c r="E169" t="s">
         <v>1207</v>
       </c>
       <c r="F169" t="s">
-        <v>2097</v>
+        <v>2127</v>
       </c>
       <c r="G169" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J169" t="s">
         <v>22</v>
@@ -29416,16 +29863,16 @@
         <v>38</v>
       </c>
       <c r="N169" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O169" t="s">
-        <v>2116</v>
+        <v>2146</v>
       </c>
       <c r="P169" t="s">
-        <v>2117</v>
+        <v>2147</v>
       </c>
       <c r="Q169" t="s">
-        <v>2118</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="170" spans="1:17" x14ac:dyDescent="0.25">
@@ -29439,16 +29886,16 @@
         <v>40</v>
       </c>
       <c r="D170" t="s">
-        <v>2119</v>
+        <v>2149</v>
       </c>
       <c r="E170" t="s">
         <v>1207</v>
       </c>
       <c r="F170" t="s">
-        <v>2120</v>
+        <v>2150</v>
       </c>
       <c r="G170" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J170" t="s">
         <v>22</v>
@@ -29463,16 +29910,16 @@
         <v>38</v>
       </c>
       <c r="N170" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O170" t="s">
-        <v>2121</v>
+        <v>2151</v>
       </c>
       <c r="P170" t="s">
-        <v>2122</v>
+        <v>2152</v>
       </c>
       <c r="Q170" t="s">
-        <v>2123</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="171" spans="1:17" x14ac:dyDescent="0.25">
@@ -29486,16 +29933,16 @@
         <v>60</v>
       </c>
       <c r="D171" t="s">
-        <v>2124</v>
+        <v>2154</v>
       </c>
       <c r="E171" t="s">
         <v>1207</v>
       </c>
       <c r="F171" t="s">
-        <v>2125</v>
+        <v>2155</v>
       </c>
       <c r="G171" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J171" t="s">
         <v>22</v>
@@ -29510,16 +29957,16 @@
         <v>38</v>
       </c>
       <c r="N171" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O171" t="s">
-        <v>2126</v>
+        <v>2156</v>
       </c>
       <c r="P171" t="s">
-        <v>2127</v>
+        <v>2157</v>
       </c>
       <c r="Q171" t="s">
-        <v>2128</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="172" spans="1:17" x14ac:dyDescent="0.25">
@@ -29533,16 +29980,16 @@
         <v>18</v>
       </c>
       <c r="D172" t="s">
-        <v>2129</v>
+        <v>2159</v>
       </c>
       <c r="E172" t="s">
         <v>1207</v>
       </c>
       <c r="F172" t="s">
-        <v>2125</v>
+        <v>2155</v>
       </c>
       <c r="G172" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J172" t="s">
         <v>22</v>
@@ -29557,16 +30004,16 @@
         <v>38</v>
       </c>
       <c r="N172" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O172" t="s">
-        <v>2130</v>
+        <v>2160</v>
       </c>
       <c r="P172" t="s">
-        <v>2131</v>
+        <v>2161</v>
       </c>
       <c r="Q172" t="s">
-        <v>2132</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="173" spans="1:17" x14ac:dyDescent="0.25">
@@ -29580,7 +30027,7 @@
         <v>12</v>
       </c>
       <c r="D173" t="s">
-        <v>2133</v>
+        <v>2163</v>
       </c>
       <c r="E173" t="s">
         <v>1207</v>
@@ -29589,7 +30036,7 @@
         <v>1208</v>
       </c>
       <c r="G173" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J173" t="s">
         <v>22</v>
@@ -29604,16 +30051,16 @@
         <v>38</v>
       </c>
       <c r="N173" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O173" t="s">
-        <v>2134</v>
+        <v>2164</v>
       </c>
       <c r="P173" t="s">
-        <v>2135</v>
+        <v>2165</v>
       </c>
       <c r="Q173" t="s">
-        <v>2136</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="174" spans="1:17" x14ac:dyDescent="0.25">
@@ -29627,7 +30074,7 @@
         <v>12</v>
       </c>
       <c r="D174" t="s">
-        <v>2137</v>
+        <v>2167</v>
       </c>
       <c r="E174" t="s">
         <v>1207</v>
@@ -29636,7 +30083,7 @@
         <v>1208</v>
       </c>
       <c r="G174" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J174" t="s">
         <v>22</v>
@@ -29651,16 +30098,16 @@
         <v>38</v>
       </c>
       <c r="N174" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O174" t="s">
-        <v>2138</v>
+        <v>2168</v>
       </c>
       <c r="P174" t="s">
-        <v>2139</v>
+        <v>2169</v>
       </c>
       <c r="Q174" t="s">
-        <v>2140</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="175" spans="1:17" x14ac:dyDescent="0.25">
@@ -29674,16 +30121,16 @@
         <v>10</v>
       </c>
       <c r="D175" t="s">
-        <v>2141</v>
+        <v>2171</v>
       </c>
       <c r="E175" t="s">
         <v>1207</v>
       </c>
       <c r="F175" t="s">
-        <v>2097</v>
+        <v>2127</v>
       </c>
       <c r="G175" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J175" t="s">
         <v>22</v>
@@ -29698,16 +30145,16 @@
         <v>38</v>
       </c>
       <c r="N175" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O175" t="s">
-        <v>2142</v>
+        <v>2172</v>
       </c>
       <c r="P175" t="s">
-        <v>2143</v>
+        <v>2173</v>
       </c>
       <c r="Q175" t="s">
-        <v>2144</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="176" spans="1:17" x14ac:dyDescent="0.25">
@@ -29721,16 +30168,16 @@
         <v>15</v>
       </c>
       <c r="D176" t="s">
-        <v>2145</v>
+        <v>2175</v>
       </c>
       <c r="E176" t="s">
         <v>1240</v>
       </c>
       <c r="F176" t="s">
-        <v>2146</v>
+        <v>2176</v>
       </c>
       <c r="G176" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="H176">
         <v>201300</v>
@@ -29751,16 +30198,16 @@
         <v>38</v>
       </c>
       <c r="N176" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O176" t="s">
-        <v>2147</v>
+        <v>2177</v>
       </c>
       <c r="P176" t="s">
-        <v>2148</v>
+        <v>2178</v>
       </c>
       <c r="Q176" t="s">
-        <v>2149</v>
+        <v>2179</v>
       </c>
     </row>
     <row r="177" spans="1:17" x14ac:dyDescent="0.25">
@@ -29774,16 +30221,16 @@
         <v>15</v>
       </c>
       <c r="D177" t="s">
-        <v>2150</v>
+        <v>2180</v>
       </c>
       <c r="E177" t="s">
         <v>1240</v>
       </c>
       <c r="F177" t="s">
-        <v>2146</v>
+        <v>2176</v>
       </c>
       <c r="G177" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="H177">
         <v>201300</v>
@@ -29804,16 +30251,16 @@
         <v>38</v>
       </c>
       <c r="N177" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O177" t="s">
-        <v>2151</v>
+        <v>2181</v>
       </c>
       <c r="P177" t="s">
-        <v>2152</v>
+        <v>2182</v>
       </c>
       <c r="Q177" t="s">
-        <v>2153</v>
+        <v>2183</v>
       </c>
     </row>
     <row r="178" spans="1:17" x14ac:dyDescent="0.25">
@@ -29827,7 +30274,7 @@
         <v>20</v>
       </c>
       <c r="D178" t="s">
-        <v>2154</v>
+        <v>2184</v>
       </c>
       <c r="E178" t="s">
         <v>1240</v>
@@ -29836,7 +30283,7 @@
         <v>1284</v>
       </c>
       <c r="G178" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J178" t="s">
         <v>22</v>
@@ -29851,16 +30298,16 @@
         <v>38</v>
       </c>
       <c r="N178" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O178" t="s">
-        <v>2155</v>
+        <v>2185</v>
       </c>
       <c r="P178" t="s">
-        <v>2156</v>
+        <v>2186</v>
       </c>
       <c r="Q178" t="s">
-        <v>2157</v>
+        <v>2187</v>
       </c>
     </row>
     <row r="179" spans="1:17" x14ac:dyDescent="0.25">
@@ -29883,7 +30330,7 @@
         <v>1274</v>
       </c>
       <c r="G179" t="s">
-        <v>2158</v>
+        <v>2188</v>
       </c>
       <c r="J179" t="s">
         <v>22</v>
@@ -29898,16 +30345,16 @@
         <v>25</v>
       </c>
       <c r="N179" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O179" t="s">
-        <v>2159</v>
+        <v>2189</v>
       </c>
       <c r="P179" t="s">
-        <v>2160</v>
+        <v>2190</v>
       </c>
       <c r="Q179" t="s">
-        <v>2161</v>
+        <v>2191</v>
       </c>
     </row>
     <row r="180" spans="1:17" x14ac:dyDescent="0.25">
@@ -29921,16 +30368,16 @@
         <v>40</v>
       </c>
       <c r="D180" t="s">
-        <v>2077</v>
+        <v>2107</v>
       </c>
       <c r="E180" t="s">
         <v>1289</v>
       </c>
       <c r="F180" t="s">
-        <v>2162</v>
+        <v>2192</v>
       </c>
       <c r="G180" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J180" t="s">
         <v>22</v>
@@ -29945,16 +30392,16 @@
         <v>38</v>
       </c>
       <c r="N180" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O180" t="s">
-        <v>2163</v>
+        <v>2193</v>
       </c>
       <c r="P180" t="s">
-        <v>2164</v>
+        <v>2194</v>
       </c>
       <c r="Q180" t="s">
-        <v>2165</v>
+        <v>2195</v>
       </c>
     </row>
     <row r="181" spans="1:17" x14ac:dyDescent="0.25">
@@ -29968,16 +30415,16 @@
         <v>38</v>
       </c>
       <c r="D181" t="s">
-        <v>2166</v>
+        <v>2196</v>
       </c>
       <c r="E181" t="s">
         <v>1289</v>
       </c>
       <c r="F181" t="s">
-        <v>2167</v>
+        <v>2197</v>
       </c>
       <c r="G181" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J181" t="s">
         <v>22</v>
@@ -29992,16 +30439,16 @@
         <v>38</v>
       </c>
       <c r="N181" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O181" t="s">
-        <v>2168</v>
+        <v>2198</v>
       </c>
       <c r="P181" t="s">
-        <v>2169</v>
+        <v>2199</v>
       </c>
       <c r="Q181" t="s">
-        <v>2170</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="182" spans="1:17" x14ac:dyDescent="0.25">
@@ -30015,16 +30462,16 @@
         <v>28</v>
       </c>
       <c r="D182" t="s">
-        <v>2171</v>
+        <v>2201</v>
       </c>
       <c r="E182" t="s">
         <v>1289</v>
       </c>
       <c r="F182" t="s">
-        <v>2172</v>
+        <v>2202</v>
       </c>
       <c r="G182" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J182" t="s">
         <v>22</v>
@@ -30039,16 +30486,16 @@
         <v>38</v>
       </c>
       <c r="N182" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O182" t="s">
-        <v>2173</v>
+        <v>2203</v>
       </c>
       <c r="P182" t="s">
-        <v>2174</v>
+        <v>2204</v>
       </c>
       <c r="Q182" t="s">
-        <v>2175</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="183" spans="1:17" x14ac:dyDescent="0.25">
@@ -30062,16 +30509,16 @@
         <v>25</v>
       </c>
       <c r="D183" t="s">
-        <v>2176</v>
+        <v>2206</v>
       </c>
       <c r="E183" t="s">
         <v>1289</v>
       </c>
       <c r="F183" t="s">
-        <v>2177</v>
+        <v>2207</v>
       </c>
       <c r="G183" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J183" t="s">
         <v>22</v>
@@ -30086,16 +30533,16 @@
         <v>38</v>
       </c>
       <c r="N183" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O183" t="s">
-        <v>2178</v>
+        <v>2208</v>
       </c>
       <c r="P183" t="s">
-        <v>2179</v>
+        <v>2209</v>
       </c>
       <c r="Q183" t="s">
-        <v>2180</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="184" spans="1:17" x14ac:dyDescent="0.25">
@@ -30109,16 +30556,16 @@
         <v>40</v>
       </c>
       <c r="D184" t="s">
-        <v>2181</v>
+        <v>2211</v>
       </c>
       <c r="E184" t="s">
         <v>1289</v>
       </c>
       <c r="F184" t="s">
-        <v>2177</v>
+        <v>2207</v>
       </c>
       <c r="G184" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J184" t="s">
         <v>22</v>
@@ -30133,16 +30580,16 @@
         <v>38</v>
       </c>
       <c r="N184" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O184" t="s">
-        <v>2182</v>
+        <v>2212</v>
       </c>
       <c r="P184" t="s">
-        <v>2183</v>
+        <v>2213</v>
       </c>
       <c r="Q184" t="s">
-        <v>2184</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="185" spans="1:17" x14ac:dyDescent="0.25">
@@ -30162,10 +30609,10 @@
         <v>1289</v>
       </c>
       <c r="F185" t="s">
-        <v>2185</v>
+        <v>2215</v>
       </c>
       <c r="G185" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J185" t="s">
         <v>22</v>
@@ -30180,16 +30627,16 @@
         <v>38</v>
       </c>
       <c r="N185" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O185" t="s">
-        <v>2186</v>
+        <v>2216</v>
       </c>
       <c r="P185" t="s">
-        <v>2187</v>
+        <v>2217</v>
       </c>
       <c r="Q185" t="s">
-        <v>2188</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="186" spans="1:17" x14ac:dyDescent="0.25">
@@ -30203,16 +30650,16 @@
         <v>18</v>
       </c>
       <c r="D186" t="s">
-        <v>2189</v>
+        <v>2219</v>
       </c>
       <c r="E186" t="s">
         <v>1289</v>
       </c>
       <c r="F186" t="s">
-        <v>2162</v>
+        <v>2192</v>
       </c>
       <c r="G186" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J186" t="s">
         <v>22</v>
@@ -30227,16 +30674,16 @@
         <v>38</v>
       </c>
       <c r="N186" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O186" t="s">
-        <v>2190</v>
+        <v>2220</v>
       </c>
       <c r="P186" t="s">
-        <v>2191</v>
+        <v>2221</v>
       </c>
       <c r="Q186" t="s">
-        <v>2192</v>
+        <v>2222</v>
       </c>
     </row>
     <row r="187" spans="1:17" x14ac:dyDescent="0.25">
@@ -30250,16 +30697,16 @@
         <v>20</v>
       </c>
       <c r="D187" t="s">
-        <v>2193</v>
+        <v>2223</v>
       </c>
       <c r="E187" t="s">
         <v>1289</v>
       </c>
       <c r="F187" t="s">
-        <v>2194</v>
+        <v>2224</v>
       </c>
       <c r="G187" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J187" t="s">
         <v>22</v>
@@ -30274,16 +30721,16 @@
         <v>38</v>
       </c>
       <c r="N187" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O187" t="s">
-        <v>2195</v>
+        <v>2225</v>
       </c>
       <c r="P187" t="s">
-        <v>2196</v>
+        <v>2226</v>
       </c>
       <c r="Q187" t="s">
-        <v>2197</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="188" spans="1:17" x14ac:dyDescent="0.25">
@@ -30297,16 +30744,16 @@
         <v>45</v>
       </c>
       <c r="D188" t="s">
-        <v>2198</v>
+        <v>2228</v>
       </c>
       <c r="E188" t="s">
         <v>1289</v>
       </c>
       <c r="F188" t="s">
-        <v>2199</v>
+        <v>2229</v>
       </c>
       <c r="G188" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J188" t="s">
         <v>22</v>
@@ -30321,16 +30768,16 @@
         <v>25</v>
       </c>
       <c r="N188" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O188" t="s">
-        <v>2200</v>
+        <v>2230</v>
       </c>
       <c r="P188" t="s">
-        <v>2201</v>
+        <v>2231</v>
       </c>
       <c r="Q188" t="s">
-        <v>2202</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="189" spans="1:17" x14ac:dyDescent="0.25">
@@ -30344,16 +30791,16 @@
         <v>15</v>
       </c>
       <c r="D189" t="s">
-        <v>2203</v>
+        <v>2233</v>
       </c>
       <c r="E189" t="s">
-        <v>2204</v>
+        <v>2234</v>
       </c>
       <c r="F189" t="s">
-        <v>2205</v>
+        <v>2235</v>
       </c>
       <c r="G189" t="s">
-        <v>2158</v>
+        <v>2188</v>
       </c>
       <c r="J189" t="s">
         <v>22</v>
@@ -30368,16 +30815,16 @@
         <v>38</v>
       </c>
       <c r="N189" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O189" t="s">
-        <v>2206</v>
+        <v>2236</v>
       </c>
       <c r="P189" t="s">
-        <v>2207</v>
+        <v>2237</v>
       </c>
       <c r="Q189" t="s">
-        <v>2208</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="190" spans="1:17" x14ac:dyDescent="0.25">
@@ -30391,16 +30838,16 @@
         <v>25</v>
       </c>
       <c r="D190" t="s">
-        <v>2209</v>
+        <v>2239</v>
       </c>
       <c r="E190" t="s">
-        <v>2204</v>
+        <v>2234</v>
       </c>
       <c r="F190" t="s">
-        <v>2210</v>
+        <v>2240</v>
       </c>
       <c r="G190" t="s">
-        <v>2158</v>
+        <v>2188</v>
       </c>
       <c r="J190" t="s">
         <v>22</v>
@@ -30415,16 +30862,16 @@
         <v>38</v>
       </c>
       <c r="N190" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O190" t="s">
-        <v>2211</v>
+        <v>2241</v>
       </c>
       <c r="P190" t="s">
-        <v>2212</v>
+        <v>2242</v>
       </c>
       <c r="Q190" t="s">
-        <v>2213</v>
+        <v>2243</v>
       </c>
     </row>
     <row r="191" spans="1:17" x14ac:dyDescent="0.25">
@@ -30438,16 +30885,16 @@
         <v>10</v>
       </c>
       <c r="D191" t="s">
-        <v>2214</v>
+        <v>2244</v>
       </c>
       <c r="E191" t="s">
-        <v>2204</v>
+        <v>2234</v>
       </c>
       <c r="F191" t="s">
-        <v>2215</v>
+        <v>2245</v>
       </c>
       <c r="G191" t="s">
-        <v>2158</v>
+        <v>2188</v>
       </c>
       <c r="J191" t="s">
         <v>22</v>
@@ -30462,16 +30909,16 @@
         <v>38</v>
       </c>
       <c r="N191" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O191" t="s">
-        <v>2216</v>
+        <v>2246</v>
       </c>
       <c r="P191" t="s">
-        <v>2217</v>
+        <v>2247</v>
       </c>
       <c r="Q191" t="s">
-        <v>2218</v>
+        <v>2248</v>
       </c>
     </row>
     <row r="192" spans="1:17" x14ac:dyDescent="0.25">
@@ -30485,16 +30932,16 @@
         <v>8</v>
       </c>
       <c r="D192" t="s">
-        <v>2219</v>
+        <v>2249</v>
       </c>
       <c r="E192" t="s">
-        <v>2204</v>
+        <v>2234</v>
       </c>
       <c r="F192" t="s">
-        <v>2220</v>
+        <v>2250</v>
       </c>
       <c r="G192" t="s">
-        <v>2158</v>
+        <v>2188</v>
       </c>
       <c r="J192" t="s">
         <v>22</v>
@@ -30509,16 +30956,16 @@
         <v>38</v>
       </c>
       <c r="N192" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O192" t="s">
-        <v>2221</v>
+        <v>2251</v>
       </c>
       <c r="P192" t="s">
-        <v>2222</v>
+        <v>2252</v>
       </c>
       <c r="Q192" t="s">
-        <v>2223</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="193" spans="1:17" x14ac:dyDescent="0.25">
@@ -30535,13 +30982,13 @@
         <v>174</v>
       </c>
       <c r="E193" t="s">
-        <v>2224</v>
+        <v>2254</v>
       </c>
       <c r="F193" t="s">
-        <v>2225</v>
+        <v>2255</v>
       </c>
       <c r="G193" t="s">
-        <v>2158</v>
+        <v>2188</v>
       </c>
       <c r="J193" t="s">
         <v>22</v>
@@ -30556,16 +31003,16 @@
         <v>32</v>
       </c>
       <c r="N193" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O193" t="s">
-        <v>2226</v>
+        <v>2256</v>
       </c>
       <c r="P193" t="s">
-        <v>2227</v>
+        <v>2257</v>
       </c>
       <c r="Q193" t="s">
-        <v>2228</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="194" spans="1:17" x14ac:dyDescent="0.25">
@@ -30579,16 +31026,16 @@
         <v>45</v>
       </c>
       <c r="D194" t="s">
-        <v>2229</v>
+        <v>2259</v>
       </c>
       <c r="E194" t="s">
-        <v>2224</v>
+        <v>2254</v>
       </c>
       <c r="F194" t="s">
-        <v>2230</v>
+        <v>2260</v>
       </c>
       <c r="G194" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J194" t="s">
         <v>22</v>
@@ -30603,16 +31050,16 @@
         <v>38</v>
       </c>
       <c r="N194" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O194" t="s">
-        <v>2231</v>
+        <v>2261</v>
       </c>
       <c r="P194" t="s">
-        <v>2232</v>
+        <v>2262</v>
       </c>
       <c r="Q194" t="s">
-        <v>2233</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="195" spans="1:17" x14ac:dyDescent="0.25">
@@ -30626,16 +31073,16 @@
         <v>30</v>
       </c>
       <c r="D195" t="s">
-        <v>2234</v>
+        <v>2264</v>
       </c>
       <c r="E195" t="s">
-        <v>2224</v>
+        <v>2254</v>
       </c>
       <c r="F195" t="s">
-        <v>2225</v>
+        <v>2255</v>
       </c>
       <c r="G195" t="s">
-        <v>2158</v>
+        <v>2188</v>
       </c>
       <c r="J195" t="s">
         <v>22</v>
@@ -30650,16 +31097,16 @@
         <v>38</v>
       </c>
       <c r="N195" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O195" t="s">
-        <v>2235</v>
+        <v>2265</v>
       </c>
       <c r="P195" t="s">
-        <v>2236</v>
+        <v>2266</v>
       </c>
       <c r="Q195" t="s">
-        <v>2237</v>
+        <v>2267</v>
       </c>
     </row>
     <row r="196" spans="1:17" x14ac:dyDescent="0.25">
@@ -30673,16 +31120,16 @@
         <v>78</v>
       </c>
       <c r="D196" t="s">
-        <v>2238</v>
+        <v>2268</v>
       </c>
       <c r="E196" t="s">
-        <v>2224</v>
+        <v>2254</v>
       </c>
       <c r="F196" t="s">
-        <v>2225</v>
+        <v>2255</v>
       </c>
       <c r="G196" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J196" t="s">
         <v>22</v>
@@ -30697,16 +31144,16 @@
         <v>32</v>
       </c>
       <c r="N196" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O196" t="s">
-        <v>2239</v>
+        <v>2269</v>
       </c>
       <c r="P196" t="s">
-        <v>2240</v>
+        <v>2270</v>
       </c>
       <c r="Q196" t="s">
-        <v>2241</v>
+        <v>2271</v>
       </c>
     </row>
     <row r="197" spans="1:17" x14ac:dyDescent="0.25">
@@ -30720,16 +31167,16 @@
         <v>70</v>
       </c>
       <c r="D197" t="s">
-        <v>2242</v>
+        <v>2272</v>
       </c>
       <c r="E197" t="s">
-        <v>2243</v>
+        <v>2273</v>
       </c>
       <c r="F197" t="s">
-        <v>2244</v>
+        <v>2274</v>
       </c>
       <c r="G197" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J197" t="s">
         <v>22</v>
@@ -30744,16 +31191,16 @@
         <v>25</v>
       </c>
       <c r="N197" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O197" t="s">
-        <v>2245</v>
+        <v>2275</v>
       </c>
       <c r="P197" t="s">
-        <v>2246</v>
+        <v>2276</v>
       </c>
       <c r="Q197" t="s">
-        <v>2247</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="198" spans="1:17" x14ac:dyDescent="0.25">
@@ -30767,16 +31214,16 @@
         <v>55</v>
       </c>
       <c r="D198" t="s">
-        <v>2248</v>
+        <v>2278</v>
       </c>
       <c r="E198" t="s">
-        <v>2243</v>
+        <v>2273</v>
       </c>
       <c r="F198" t="s">
-        <v>2244</v>
+        <v>2274</v>
       </c>
       <c r="G198" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J198" t="s">
         <v>22</v>
@@ -30791,16 +31238,16 @@
         <v>25</v>
       </c>
       <c r="N198" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O198" t="s">
-        <v>2249</v>
+        <v>2279</v>
       </c>
       <c r="P198" t="s">
-        <v>2250</v>
+        <v>2280</v>
       </c>
       <c r="Q198" t="s">
-        <v>2251</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="199" spans="1:17" x14ac:dyDescent="0.25">
@@ -30814,16 +31261,16 @@
         <v>35</v>
       </c>
       <c r="D199" t="s">
-        <v>2252</v>
+        <v>2282</v>
       </c>
       <c r="E199" t="s">
-        <v>2253</v>
+        <v>2283</v>
       </c>
       <c r="F199" t="s">
-        <v>2254</v>
+        <v>2284</v>
       </c>
       <c r="G199" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J199" t="s">
         <v>22</v>
@@ -30838,16 +31285,16 @@
         <v>38</v>
       </c>
       <c r="N199" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O199" t="s">
-        <v>2255</v>
+        <v>2285</v>
       </c>
       <c r="P199" t="s">
-        <v>2256</v>
+        <v>2286</v>
       </c>
       <c r="Q199" t="s">
-        <v>2257</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="200" spans="1:17" x14ac:dyDescent="0.25">
@@ -30861,16 +31308,16 @@
         <v>22</v>
       </c>
       <c r="D200" t="s">
-        <v>2077</v>
+        <v>2107</v>
       </c>
       <c r="E200" t="s">
-        <v>2253</v>
+        <v>2283</v>
       </c>
       <c r="F200" t="s">
-        <v>2254</v>
+        <v>2284</v>
       </c>
       <c r="G200" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J200" t="s">
         <v>22</v>
@@ -30885,16 +31332,16 @@
         <v>38</v>
       </c>
       <c r="N200" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O200" t="s">
-        <v>2258</v>
+        <v>2288</v>
       </c>
       <c r="P200" t="s">
-        <v>2259</v>
+        <v>2289</v>
       </c>
       <c r="Q200" t="s">
-        <v>2260</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="201" spans="1:17" x14ac:dyDescent="0.25">
@@ -30908,16 +31355,16 @@
         <v>42</v>
       </c>
       <c r="D201" t="s">
-        <v>2261</v>
+        <v>2291</v>
       </c>
       <c r="E201" t="s">
-        <v>2253</v>
+        <v>2283</v>
       </c>
       <c r="F201" t="s">
-        <v>2254</v>
+        <v>2284</v>
       </c>
       <c r="G201" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J201" t="s">
         <v>22</v>
@@ -30932,16 +31379,16 @@
         <v>38</v>
       </c>
       <c r="N201" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O201" t="s">
-        <v>2262</v>
+        <v>2292</v>
       </c>
       <c r="P201" t="s">
-        <v>2263</v>
+        <v>2293</v>
       </c>
       <c r="Q201" t="s">
-        <v>2264</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="202" spans="1:17" x14ac:dyDescent="0.25">
@@ -30955,16 +31402,16 @@
         <v>50</v>
       </c>
       <c r="D202" t="s">
-        <v>2265</v>
+        <v>2295</v>
       </c>
       <c r="E202" t="s">
         <v>1351</v>
       </c>
       <c r="F202" t="s">
-        <v>2162</v>
+        <v>2192</v>
       </c>
       <c r="G202" t="s">
-        <v>2158</v>
+        <v>2188</v>
       </c>
       <c r="H202">
         <v>150000</v>
@@ -30985,16 +31432,16 @@
         <v>25</v>
       </c>
       <c r="N202" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O202" t="s">
-        <v>2266</v>
+        <v>2296</v>
       </c>
       <c r="P202" t="s">
-        <v>2267</v>
+        <v>2297</v>
       </c>
       <c r="Q202" t="s">
-        <v>2268</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="203" spans="1:17" x14ac:dyDescent="0.25">
@@ -31008,16 +31455,16 @@
         <v>35</v>
       </c>
       <c r="D203" t="s">
-        <v>2269</v>
+        <v>2299</v>
       </c>
       <c r="E203" t="s">
         <v>1351</v>
       </c>
       <c r="F203" t="s">
-        <v>2270</v>
+        <v>2300</v>
       </c>
       <c r="G203" t="s">
-        <v>2158</v>
+        <v>2188</v>
       </c>
       <c r="H203">
         <v>140000</v>
@@ -31038,16 +31485,16 @@
         <v>38</v>
       </c>
       <c r="N203" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O203" t="s">
-        <v>2271</v>
+        <v>2301</v>
       </c>
       <c r="P203" t="s">
-        <v>2272</v>
+        <v>2302</v>
       </c>
       <c r="Q203" t="s">
-        <v>2273</v>
+        <v>2303</v>
       </c>
     </row>
     <row r="204" spans="1:17" x14ac:dyDescent="0.25">
@@ -31061,16 +31508,16 @@
         <v>25</v>
       </c>
       <c r="D204" t="s">
-        <v>2274</v>
+        <v>2304</v>
       </c>
       <c r="E204" t="s">
-        <v>2275</v>
+        <v>2305</v>
       </c>
       <c r="F204" t="s">
-        <v>2276</v>
+        <v>2306</v>
       </c>
       <c r="G204" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J204" t="s">
         <v>22</v>
@@ -31085,16 +31532,16 @@
         <v>38</v>
       </c>
       <c r="N204" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O204" t="s">
-        <v>2277</v>
+        <v>2307</v>
       </c>
       <c r="P204" t="s">
-        <v>2278</v>
+        <v>2308</v>
       </c>
       <c r="Q204" t="s">
-        <v>2279</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="205" spans="1:17" x14ac:dyDescent="0.25">
@@ -31108,16 +31555,16 @@
         <v>62</v>
       </c>
       <c r="D205" t="s">
-        <v>2280</v>
+        <v>2310</v>
       </c>
       <c r="E205" t="s">
-        <v>2275</v>
+        <v>2305</v>
       </c>
       <c r="F205" t="s">
-        <v>2276</v>
+        <v>2306</v>
       </c>
       <c r="G205" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J205" t="s">
         <v>22</v>
@@ -31132,16 +31579,16 @@
         <v>25</v>
       </c>
       <c r="N205" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O205" t="s">
-        <v>2281</v>
+        <v>2311</v>
       </c>
       <c r="P205" t="s">
-        <v>2282</v>
+        <v>2312</v>
       </c>
       <c r="Q205" t="s">
-        <v>2283</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="206" spans="1:17" x14ac:dyDescent="0.25">
@@ -31155,16 +31602,16 @@
         <v>18</v>
       </c>
       <c r="D206" t="s">
-        <v>2284</v>
+        <v>2314</v>
       </c>
       <c r="E206" t="s">
-        <v>2275</v>
+        <v>2305</v>
       </c>
       <c r="F206" t="s">
-        <v>2285</v>
+        <v>2315</v>
       </c>
       <c r="G206" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J206" t="s">
         <v>22</v>
@@ -31179,16 +31626,16 @@
         <v>38</v>
       </c>
       <c r="N206" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O206" t="s">
-        <v>2286</v>
+        <v>2316</v>
       </c>
       <c r="P206" t="s">
-        <v>2287</v>
+        <v>2317</v>
       </c>
       <c r="Q206" t="s">
-        <v>2288</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="207" spans="1:17" x14ac:dyDescent="0.25">
@@ -31202,16 +31649,16 @@
         <v>45</v>
       </c>
       <c r="D207" t="s">
-        <v>2289</v>
+        <v>2319</v>
       </c>
       <c r="E207" t="s">
-        <v>2290</v>
+        <v>2320</v>
       </c>
       <c r="F207" t="s">
-        <v>2162</v>
+        <v>2192</v>
       </c>
       <c r="G207" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J207" t="s">
         <v>22</v>
@@ -31226,16 +31673,16 @@
         <v>25</v>
       </c>
       <c r="N207" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O207" t="s">
-        <v>2291</v>
+        <v>2321</v>
       </c>
       <c r="P207" t="s">
-        <v>2292</v>
+        <v>2322</v>
       </c>
       <c r="Q207" t="s">
-        <v>2293</v>
+        <v>2323</v>
       </c>
     </row>
     <row r="208" spans="1:17" x14ac:dyDescent="0.25">
@@ -31249,16 +31696,16 @@
         <v>32</v>
       </c>
       <c r="D208" t="s">
-        <v>2294</v>
+        <v>2324</v>
       </c>
       <c r="E208" t="s">
-        <v>2290</v>
+        <v>2320</v>
       </c>
       <c r="F208" t="s">
-        <v>2295</v>
+        <v>2325</v>
       </c>
       <c r="G208" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J208" t="s">
         <v>22</v>
@@ -31273,16 +31720,16 @@
         <v>38</v>
       </c>
       <c r="N208" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O208" t="s">
-        <v>2296</v>
+        <v>2326</v>
       </c>
       <c r="P208" t="s">
-        <v>2297</v>
+        <v>2327</v>
       </c>
       <c r="Q208" t="s">
-        <v>2298</v>
+        <v>2328</v>
       </c>
     </row>
     <row r="209" spans="1:17" x14ac:dyDescent="0.25">
@@ -31296,16 +31743,16 @@
         <v>42</v>
       </c>
       <c r="D209" t="s">
-        <v>2299</v>
+        <v>1378</v>
       </c>
       <c r="E209" t="s">
-        <v>2290</v>
+        <v>2320</v>
       </c>
       <c r="F209" t="s">
-        <v>2295</v>
+        <v>2325</v>
       </c>
       <c r="G209" t="s">
-        <v>1364</v>
+        <v>1394</v>
       </c>
       <c r="J209" t="s">
         <v>22</v>
@@ -31320,16 +31767,16 @@
         <v>25</v>
       </c>
       <c r="N209" t="s">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="O209" t="s">
-        <v>2300</v>
+        <v>2329</v>
       </c>
       <c r="P209" t="s">
-        <v>2301</v>
+        <v>2330</v>
       </c>
       <c r="Q209" t="s">
-        <v>2302</v>
+        <v>2331</v>
       </c>
     </row>
     <row r="210" spans="1:17" x14ac:dyDescent="0.25">
@@ -31349,10 +31796,10 @@
         <v>421</v>
       </c>
       <c r="F210" t="s">
-        <v>2303</v>
+        <v>2332</v>
       </c>
       <c r="G210" t="s">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="H210">
         <v>219100</v>
@@ -31373,16 +31820,269 @@
         <v>25</v>
       </c>
       <c r="N210" t="s">
+        <v>1395</v>
+      </c>
+      <c r="O210" t="s">
+        <v>2333</v>
+      </c>
+      <c r="P210" t="s">
+        <v>2334</v>
+      </c>
+      <c r="Q210" t="s">
+        <v>2335</v>
+      </c>
+    </row>
+    <row r="211" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>17</v>
+      </c>
+      <c r="B211">
+        <v>55</v>
+      </c>
+      <c r="C211">
+        <v>48</v>
+      </c>
+      <c r="D211" t="s">
+        <v>749</v>
+      </c>
+      <c r="E211" t="s">
+        <v>421</v>
+      </c>
+      <c r="F211" t="s">
+        <v>2336</v>
+      </c>
+      <c r="G211" t="s">
+        <v>1410</v>
+      </c>
+      <c r="H211">
+        <v>180000</v>
+      </c>
+      <c r="I211">
+        <v>180000</v>
+      </c>
+      <c r="J211" t="s">
+        <v>64</v>
+      </c>
+      <c r="K211" t="s">
+        <v>423</v>
+      </c>
+      <c r="L211" t="s">
         <v>1365</v>
       </c>
-      <c r="O210" t="s">
-        <v>2304</v>
-      </c>
-      <c r="P210" t="s">
-        <v>2305</v>
-      </c>
-      <c r="Q210" t="s">
-        <v>2306</v>
+      <c r="M211" t="s">
+        <v>25</v>
+      </c>
+      <c r="N211" t="s">
+        <v>1395</v>
+      </c>
+      <c r="O211" t="s">
+        <v>2337</v>
+      </c>
+      <c r="P211" t="s">
+        <v>2338</v>
+      </c>
+      <c r="Q211" t="s">
+        <v>2339</v>
+      </c>
+    </row>
+    <row r="212" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>17</v>
+      </c>
+      <c r="B212">
+        <v>58</v>
+      </c>
+      <c r="C212">
+        <v>48</v>
+      </c>
+      <c r="D212" t="s">
+        <v>108</v>
+      </c>
+      <c r="E212" t="s">
+        <v>421</v>
+      </c>
+      <c r="F212" t="s">
+        <v>2340</v>
+      </c>
+      <c r="G212" t="s">
+        <v>1410</v>
+      </c>
+      <c r="H212">
+        <v>219100</v>
+      </c>
+      <c r="I212">
+        <v>219100</v>
+      </c>
+      <c r="J212" t="s">
+        <v>64</v>
+      </c>
+      <c r="K212" t="s">
+        <v>423</v>
+      </c>
+      <c r="L212" t="s">
+        <v>1365</v>
+      </c>
+      <c r="M212" t="s">
+        <v>25</v>
+      </c>
+      <c r="N212" t="s">
+        <v>1395</v>
+      </c>
+      <c r="O212" t="s">
+        <v>2341</v>
+      </c>
+      <c r="P212" t="s">
+        <v>2342</v>
+      </c>
+      <c r="Q212" t="s">
+        <v>2343</v>
+      </c>
+    </row>
+    <row r="213" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>17</v>
+      </c>
+      <c r="B213">
+        <v>15</v>
+      </c>
+      <c r="C213">
+        <v>25</v>
+      </c>
+      <c r="D213" t="s">
+        <v>1818</v>
+      </c>
+      <c r="E213" t="s">
+        <v>1819</v>
+      </c>
+      <c r="F213" t="s">
+        <v>1820</v>
+      </c>
+      <c r="G213" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J213" t="s">
+        <v>22</v>
+      </c>
+      <c r="K213" t="s">
+        <v>557</v>
+      </c>
+      <c r="L213" t="s">
+        <v>1365</v>
+      </c>
+      <c r="M213" t="s">
+        <v>38</v>
+      </c>
+      <c r="N213" t="s">
+        <v>1395</v>
+      </c>
+      <c r="O213" t="s">
+        <v>2344</v>
+      </c>
+      <c r="P213" t="s">
+        <v>2345</v>
+      </c>
+      <c r="Q213" t="s">
+        <v>2346</v>
+      </c>
+    </row>
+    <row r="214" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>17</v>
+      </c>
+      <c r="B214">
+        <v>2</v>
+      </c>
+      <c r="C214">
+        <v>3</v>
+      </c>
+      <c r="D214" t="s">
+        <v>1824</v>
+      </c>
+      <c r="E214" t="s">
+        <v>1825</v>
+      </c>
+      <c r="F214" t="s">
+        <v>1820</v>
+      </c>
+      <c r="G214" t="s">
+        <v>1410</v>
+      </c>
+      <c r="J214" t="s">
+        <v>22</v>
+      </c>
+      <c r="K214" t="s">
+        <v>557</v>
+      </c>
+      <c r="L214" t="s">
+        <v>1365</v>
+      </c>
+      <c r="M214" t="s">
+        <v>38</v>
+      </c>
+      <c r="N214" t="s">
+        <v>1395</v>
+      </c>
+      <c r="O214" t="s">
+        <v>2347</v>
+      </c>
+      <c r="P214" t="s">
+        <v>2348</v>
+      </c>
+      <c r="Q214" t="s">
+        <v>2349</v>
+      </c>
+    </row>
+    <row r="215" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>17</v>
+      </c>
+      <c r="B215">
+        <v>52</v>
+      </c>
+      <c r="C215">
+        <v>48</v>
+      </c>
+      <c r="D215" t="s">
+        <v>2350</v>
+      </c>
+      <c r="E215" t="s">
+        <v>1084</v>
+      </c>
+      <c r="F215" t="s">
+        <v>1085</v>
+      </c>
+      <c r="G215" t="s">
+        <v>1410</v>
+      </c>
+      <c r="H215">
+        <v>200000</v>
+      </c>
+      <c r="I215">
+        <v>200000</v>
+      </c>
+      <c r="J215" t="s">
+        <v>64</v>
+      </c>
+      <c r="K215" t="s">
+        <v>557</v>
+      </c>
+      <c r="L215" t="s">
+        <v>1365</v>
+      </c>
+      <c r="M215" t="s">
+        <v>25</v>
+      </c>
+      <c r="N215" t="s">
+        <v>1395</v>
+      </c>
+      <c r="O215" t="s">
+        <v>2351</v>
+      </c>
+      <c r="P215" t="s">
+        <v>2352</v>
+      </c>
+      <c r="Q215" t="s">
+        <v>2353</v>
       </c>
     </row>
   </sheetData>

--- a/hunt/board.xlsx
+++ b/hunt/board.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6482" uniqueCount="2354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6508" uniqueCount="2362">
   <si>
     <t>Column</t>
   </si>
@@ -4193,6 +4193,18 @@
     <t>https://www.arbeitnow.com/jobs/companies/celonis/lead-deployment-architect-munich-326905</t>
   </si>
   <si>
+    <t>2026-09-07T02:24:20.597Z</t>
+  </si>
+  <si>
+    <t>Listed remote, and duties map closely: cloud architecture design, migration of existing application landscapes, CI/CD pipelines, and IaC-driven security/compliance | Ownership of build, staging, deployment and release processes matches the candidate's Azure DevOps Pipelines and governance depth | Customer consulting component fits the candidate's enterprise trusted-advisor experience</t>
+  </si>
+  <si>
+    <t>Germany-based employer (Köln) — 'remote' almost certainly means remote within Germany/EU, requiring EU work authorization | Microservices development emphasis is lighter on the resume than platform/governance work | Degree in (Business) Informatics is stated as a requirement, and no comp is posted</t>
+  </si>
+  <si>
+    <t>https://www.arbeitnow.com/jobs/companies/trusteq-gmbh/cloud-senior-engineer-architect-m-w-d-koln-168121</t>
+  </si>
+  <si>
     <t>Delivery Solutions Architect - Communications, Media, Entertainment &amp; Games</t>
   </si>
   <si>
@@ -7074,6 +7086,18 @@
   </si>
   <si>
     <t>https://www.arbeitnow.fr/jobs/companies/elastic/senior-partner-solutions-architect-460245</t>
+  </si>
+  <si>
+    <t>Azure Cloud Architect (m/w/d)</t>
+  </si>
+  <si>
+    <t>Core ask is exactly the candidate's wheelhouse: designing Azure PaaS/IaaS solutions, DevOps principles and Infrastructure as Code | Consulting/trusted-advisor engagement on architectures and Azure services matches the candidate's Customer Engineer advisory model | Greenfield and brownfield Azure project ownership aligns with 10 years of enterprise cloud delivery</t>
+  </si>
+  <si>
+    <t>Posting is in German and located in Hamburg, Germany — outside the candidate's stated US market scope, and German-language proficiency is implied | No container/Kubernetes depth called out on the resume, while the role emphasizes Containerdienste | Requires EU work authorization and likely German-market comp far below the $180k floor</t>
+  </si>
+  <si>
+    <t>https://www.arbeitnow.com/jobs/companies/skaylink/azure-cloud-architect-hamburg-427466</t>
   </si>
 </sst>
 </file>
@@ -7454,7 +7478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q283"/>
+  <dimension ref="A1:Q284"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -21564,6 +21588,53 @@
         <v>1392</v>
       </c>
     </row>
+    <row r="284" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>17</v>
+      </c>
+      <c r="B284">
+        <v>40</v>
+      </c>
+      <c r="C284">
+        <v>74</v>
+      </c>
+      <c r="D284" t="s">
+        <v>822</v>
+      </c>
+      <c r="E284" t="s">
+        <v>823</v>
+      </c>
+      <c r="F284" t="s">
+        <v>824</v>
+      </c>
+      <c r="G284" t="s">
+        <v>21</v>
+      </c>
+      <c r="J284" t="s">
+        <v>22</v>
+      </c>
+      <c r="K284" t="s">
+        <v>557</v>
+      </c>
+      <c r="L284" t="s">
+        <v>1393</v>
+      </c>
+      <c r="M284" t="s">
+        <v>25</v>
+      </c>
+      <c r="N284" t="s">
+        <v>26</v>
+      </c>
+      <c r="O284" t="s">
+        <v>1394</v>
+      </c>
+      <c r="P284" t="s">
+        <v>1395</v>
+      </c>
+      <c r="Q284" t="s">
+        <v>1396</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:Q1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -21573,7 +21644,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q215"/>
+  <dimension ref="A1:Q216"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -21654,7 +21725,7 @@
         <v>52</v>
       </c>
       <c r="D2" t="s">
-        <v>1393</v>
+        <v>1397</v>
       </c>
       <c r="E2" t="s">
         <v>421</v>
@@ -21663,7 +21734,7 @@
         <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="H2">
         <v>180000</v>
@@ -21684,16 +21755,16 @@
         <v>25</v>
       </c>
       <c r="N2" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O2" t="s">
-        <v>1396</v>
+        <v>1400</v>
       </c>
       <c r="P2" t="s">
-        <v>1397</v>
+        <v>1401</v>
       </c>
       <c r="Q2" t="s">
-        <v>1398</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -21707,7 +21778,7 @@
         <v>55</v>
       </c>
       <c r="D3" t="s">
-        <v>1399</v>
+        <v>1403</v>
       </c>
       <c r="E3" t="s">
         <v>421</v>
@@ -21716,7 +21787,7 @@
         <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="H3">
         <v>180000</v>
@@ -21737,16 +21808,16 @@
         <v>25</v>
       </c>
       <c r="N3" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O3" t="s">
-        <v>1400</v>
+        <v>1404</v>
       </c>
       <c r="P3" t="s">
-        <v>1401</v>
+        <v>1405</v>
       </c>
       <c r="Q3" t="s">
-        <v>1402</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
@@ -21760,16 +21831,16 @@
         <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>1403</v>
+        <v>1407</v>
       </c>
       <c r="E4" t="s">
         <v>421</v>
       </c>
       <c r="F4" t="s">
-        <v>1404</v>
+        <v>1408</v>
       </c>
       <c r="G4" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="H4">
         <v>219100</v>
@@ -21790,16 +21861,16 @@
         <v>25</v>
       </c>
       <c r="N4" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O4" t="s">
-        <v>1405</v>
+        <v>1409</v>
       </c>
       <c r="P4" t="s">
-        <v>1406</v>
+        <v>1410</v>
       </c>
       <c r="Q4" t="s">
-        <v>1407</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -21813,16 +21884,16 @@
         <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>1408</v>
+        <v>1412</v>
       </c>
       <c r="E5" t="s">
         <v>421</v>
       </c>
       <c r="F5" t="s">
-        <v>1409</v>
+        <v>1413</v>
       </c>
       <c r="G5" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="H5">
         <v>180000</v>
@@ -21843,16 +21914,16 @@
         <v>25</v>
       </c>
       <c r="N5" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O5" t="s">
-        <v>1411</v>
+        <v>1415</v>
       </c>
       <c r="P5" t="s">
-        <v>1412</v>
+        <v>1416</v>
       </c>
       <c r="Q5" t="s">
-        <v>1413</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -21866,7 +21937,7 @@
         <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>1414</v>
+        <v>1418</v>
       </c>
       <c r="E6" t="s">
         <v>421</v>
@@ -21875,7 +21946,7 @@
         <v>20</v>
       </c>
       <c r="G6" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="H6">
         <v>219100</v>
@@ -21896,16 +21967,16 @@
         <v>38</v>
       </c>
       <c r="N6" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O6" t="s">
-        <v>1415</v>
+        <v>1419</v>
       </c>
       <c r="P6" t="s">
-        <v>1416</v>
+        <v>1420</v>
       </c>
       <c r="Q6" t="s">
-        <v>1417</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -21919,7 +21990,7 @@
         <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>1418</v>
+        <v>1422</v>
       </c>
       <c r="E7" t="s">
         <v>421</v>
@@ -21928,7 +21999,7 @@
         <v>20</v>
       </c>
       <c r="G7" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="H7">
         <v>219100</v>
@@ -21949,16 +22020,16 @@
         <v>25</v>
       </c>
       <c r="N7" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O7" t="s">
-        <v>1419</v>
+        <v>1423</v>
       </c>
       <c r="P7" t="s">
-        <v>1420</v>
+        <v>1424</v>
       </c>
       <c r="Q7" t="s">
-        <v>1421</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -21972,16 +22043,16 @@
         <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>1422</v>
+        <v>1426</v>
       </c>
       <c r="E8" t="s">
         <v>421</v>
       </c>
       <c r="F8" t="s">
-        <v>1423</v>
+        <v>1427</v>
       </c>
       <c r="G8" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J8" t="s">
         <v>22</v>
@@ -21996,16 +22067,16 @@
         <v>38</v>
       </c>
       <c r="N8" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O8" t="s">
-        <v>1424</v>
+        <v>1428</v>
       </c>
       <c r="P8" t="s">
-        <v>1425</v>
+        <v>1429</v>
       </c>
       <c r="Q8" t="s">
-        <v>1426</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -22019,16 +22090,16 @@
         <v>58</v>
       </c>
       <c r="D9" t="s">
-        <v>1427</v>
+        <v>1431</v>
       </c>
       <c r="E9" t="s">
-        <v>1428</v>
+        <v>1432</v>
       </c>
       <c r="F9" t="s">
-        <v>1429</v>
+        <v>1433</v>
       </c>
       <c r="G9" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="H9">
         <v>257000</v>
@@ -22049,16 +22120,16 @@
         <v>25</v>
       </c>
       <c r="N9" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O9" t="s">
-        <v>1430</v>
+        <v>1434</v>
       </c>
       <c r="P9" t="s">
-        <v>1431</v>
+        <v>1435</v>
       </c>
       <c r="Q9" t="s">
-        <v>1432</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -22075,13 +22146,13 @@
         <v>145</v>
       </c>
       <c r="E10" t="s">
-        <v>1433</v>
+        <v>1437</v>
       </c>
       <c r="F10" t="s">
-        <v>1434</v>
+        <v>1438</v>
       </c>
       <c r="G10" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="H10">
         <v>200000</v>
@@ -22102,16 +22173,16 @@
         <v>38</v>
       </c>
       <c r="N10" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O10" t="s">
-        <v>1435</v>
+        <v>1439</v>
       </c>
       <c r="P10" t="s">
-        <v>1436</v>
+        <v>1440</v>
       </c>
       <c r="Q10" t="s">
-        <v>1437</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -22125,16 +22196,16 @@
         <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>1438</v>
+        <v>1442</v>
       </c>
       <c r="E11" t="s">
         <v>698</v>
       </c>
       <c r="F11" t="s">
-        <v>1439</v>
+        <v>1443</v>
       </c>
       <c r="G11" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J11" t="s">
         <v>22</v>
@@ -22149,16 +22220,16 @@
         <v>38</v>
       </c>
       <c r="N11" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O11" t="s">
-        <v>1440</v>
+        <v>1444</v>
       </c>
       <c r="P11" t="s">
-        <v>1441</v>
+        <v>1445</v>
       </c>
       <c r="Q11" t="s">
-        <v>1442</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -22178,10 +22249,10 @@
         <v>698</v>
       </c>
       <c r="F12" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G12" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J12" t="s">
         <v>22</v>
@@ -22196,16 +22267,16 @@
         <v>38</v>
       </c>
       <c r="N12" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O12" t="s">
-        <v>1444</v>
+        <v>1448</v>
       </c>
       <c r="P12" t="s">
-        <v>1445</v>
+        <v>1449</v>
       </c>
       <c r="Q12" t="s">
-        <v>1446</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
@@ -22219,16 +22290,16 @@
         <v>15</v>
       </c>
       <c r="D13" t="s">
-        <v>1447</v>
+        <v>1451</v>
       </c>
       <c r="E13" t="s">
         <v>698</v>
       </c>
       <c r="F13" t="s">
-        <v>1448</v>
+        <v>1452</v>
       </c>
       <c r="G13" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="H13">
         <v>500000</v>
@@ -22249,16 +22320,16 @@
         <v>38</v>
       </c>
       <c r="N13" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O13" t="s">
-        <v>1449</v>
+        <v>1453</v>
       </c>
       <c r="P13" t="s">
-        <v>1450</v>
+        <v>1454</v>
       </c>
       <c r="Q13" t="s">
-        <v>1451</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
@@ -22272,16 +22343,16 @@
         <v>18</v>
       </c>
       <c r="D14" t="s">
-        <v>1452</v>
+        <v>1456</v>
       </c>
       <c r="E14" t="s">
         <v>478</v>
       </c>
       <c r="F14" t="s">
-        <v>1453</v>
+        <v>1457</v>
       </c>
       <c r="G14" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="H14">
         <v>274456</v>
@@ -22302,16 +22373,16 @@
         <v>38</v>
       </c>
       <c r="N14" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O14" t="s">
-        <v>1454</v>
+        <v>1458</v>
       </c>
       <c r="P14" t="s">
-        <v>1455</v>
+        <v>1459</v>
       </c>
       <c r="Q14" t="s">
-        <v>1456</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -22325,16 +22396,16 @@
         <v>30</v>
       </c>
       <c r="D15" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
       <c r="E15" t="s">
         <v>478</v>
       </c>
       <c r="F15" t="s">
-        <v>1458</v>
+        <v>1462</v>
       </c>
       <c r="G15" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J15" t="s">
         <v>22</v>
@@ -22349,16 +22420,16 @@
         <v>38</v>
       </c>
       <c r="N15" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O15" t="s">
-        <v>1459</v>
+        <v>1463</v>
       </c>
       <c r="P15" t="s">
-        <v>1460</v>
+        <v>1464</v>
       </c>
       <c r="Q15" t="s">
-        <v>1461</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
@@ -22372,16 +22443,16 @@
         <v>22</v>
       </c>
       <c r="D16" t="s">
-        <v>1462</v>
+        <v>1466</v>
       </c>
       <c r="E16" t="s">
         <v>478</v>
       </c>
       <c r="F16" t="s">
-        <v>1463</v>
+        <v>1467</v>
       </c>
       <c r="G16" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J16" t="s">
         <v>22</v>
@@ -22396,16 +22467,16 @@
         <v>38</v>
       </c>
       <c r="N16" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O16" t="s">
-        <v>1464</v>
+        <v>1468</v>
       </c>
       <c r="P16" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="Q16" t="s">
-        <v>1466</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
@@ -22419,16 +22490,16 @@
         <v>48</v>
       </c>
       <c r="D17" t="s">
-        <v>1467</v>
+        <v>1471</v>
       </c>
       <c r="E17" t="s">
         <v>478</v>
       </c>
       <c r="F17" t="s">
-        <v>1468</v>
+        <v>1472</v>
       </c>
       <c r="G17" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J17" t="s">
         <v>22</v>
@@ -22443,16 +22514,16 @@
         <v>25</v>
       </c>
       <c r="N17" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O17" t="s">
-        <v>1469</v>
+        <v>1473</v>
       </c>
       <c r="P17" t="s">
-        <v>1470</v>
+        <v>1474</v>
       </c>
       <c r="Q17" t="s">
-        <v>1471</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
@@ -22466,16 +22537,16 @@
         <v>25</v>
       </c>
       <c r="D18" t="s">
-        <v>1472</v>
+        <v>1476</v>
       </c>
       <c r="E18" t="s">
         <v>478</v>
       </c>
       <c r="F18" t="s">
-        <v>1473</v>
+        <v>1477</v>
       </c>
       <c r="G18" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J18" t="s">
         <v>22</v>
@@ -22490,16 +22561,16 @@
         <v>38</v>
       </c>
       <c r="N18" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O18" t="s">
-        <v>1474</v>
+        <v>1478</v>
       </c>
       <c r="P18" t="s">
-        <v>1475</v>
+        <v>1479</v>
       </c>
       <c r="Q18" t="s">
-        <v>1476</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -22513,16 +22584,16 @@
         <v>40</v>
       </c>
       <c r="D19" t="s">
-        <v>1477</v>
+        <v>1481</v>
       </c>
       <c r="E19" t="s">
         <v>478</v>
       </c>
       <c r="F19" t="s">
-        <v>1478</v>
+        <v>1482</v>
       </c>
       <c r="G19" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J19" t="s">
         <v>22</v>
@@ -22537,16 +22608,16 @@
         <v>38</v>
       </c>
       <c r="N19" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O19" t="s">
-        <v>1479</v>
+        <v>1483</v>
       </c>
       <c r="P19" t="s">
-        <v>1480</v>
+        <v>1484</v>
       </c>
       <c r="Q19" t="s">
-        <v>1481</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -22560,16 +22631,16 @@
         <v>70</v>
       </c>
       <c r="D20" t="s">
-        <v>1482</v>
+        <v>1486</v>
       </c>
       <c r="E20" t="s">
-        <v>1483</v>
+        <v>1487</v>
       </c>
       <c r="F20" t="s">
-        <v>1484</v>
+        <v>1488</v>
       </c>
       <c r="G20" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J20" t="s">
         <v>22</v>
@@ -22584,16 +22655,16 @@
         <v>38</v>
       </c>
       <c r="N20" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O20" t="s">
-        <v>1485</v>
+        <v>1489</v>
       </c>
       <c r="P20" t="s">
-        <v>1486</v>
+        <v>1490</v>
       </c>
       <c r="Q20" t="s">
-        <v>1487</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
@@ -22607,16 +22678,16 @@
         <v>58</v>
       </c>
       <c r="D21" t="s">
-        <v>1488</v>
+        <v>1492</v>
       </c>
       <c r="E21" t="s">
-        <v>1489</v>
+        <v>1493</v>
       </c>
       <c r="F21" t="s">
-        <v>1473</v>
+        <v>1477</v>
       </c>
       <c r="G21" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J21" t="s">
         <v>22</v>
@@ -22631,16 +22702,16 @@
         <v>38</v>
       </c>
       <c r="N21" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O21" t="s">
-        <v>1490</v>
+        <v>1494</v>
       </c>
       <c r="P21" t="s">
-        <v>1491</v>
+        <v>1495</v>
       </c>
       <c r="Q21" t="s">
-        <v>1492</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -22654,16 +22725,16 @@
         <v>32</v>
       </c>
       <c r="D22" t="s">
-        <v>1493</v>
+        <v>1497</v>
       </c>
       <c r="E22" t="s">
-        <v>1494</v>
+        <v>1498</v>
       </c>
       <c r="F22" t="s">
         <v>1085</v>
       </c>
       <c r="G22" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J22" t="s">
         <v>22</v>
@@ -22678,16 +22749,16 @@
         <v>38</v>
       </c>
       <c r="N22" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O22" t="s">
-        <v>1495</v>
+        <v>1499</v>
       </c>
       <c r="P22" t="s">
-        <v>1496</v>
+        <v>1500</v>
       </c>
       <c r="Q22" t="s">
-        <v>1497</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
@@ -22701,16 +22772,16 @@
         <v>4</v>
       </c>
       <c r="D23" t="s">
-        <v>1498</v>
+        <v>1502</v>
       </c>
       <c r="E23" t="s">
-        <v>1499</v>
+        <v>1503</v>
       </c>
       <c r="F23" t="s">
         <v>1032</v>
       </c>
       <c r="G23" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J23" t="s">
         <v>22</v>
@@ -22725,16 +22796,16 @@
         <v>38</v>
       </c>
       <c r="N23" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O23" t="s">
-        <v>1500</v>
+        <v>1504</v>
       </c>
       <c r="P23" t="s">
-        <v>1501</v>
+        <v>1505</v>
       </c>
       <c r="Q23" t="s">
-        <v>1502</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
@@ -22748,16 +22819,16 @@
         <v>25</v>
       </c>
       <c r="D24" t="s">
-        <v>1503</v>
+        <v>1507</v>
       </c>
       <c r="E24" t="s">
-        <v>1504</v>
+        <v>1508</v>
       </c>
       <c r="F24" t="s">
-        <v>1505</v>
+        <v>1509</v>
       </c>
       <c r="G24" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J24" t="s">
         <v>22</v>
@@ -22772,16 +22843,16 @@
         <v>38</v>
       </c>
       <c r="N24" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O24" t="s">
-        <v>1506</v>
+        <v>1510</v>
       </c>
       <c r="P24" t="s">
-        <v>1507</v>
+        <v>1511</v>
       </c>
       <c r="Q24" t="s">
-        <v>1508</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
@@ -22795,16 +22866,16 @@
         <v>30</v>
       </c>
       <c r="D25" t="s">
-        <v>1509</v>
+        <v>1513</v>
       </c>
       <c r="E25" t="s">
-        <v>1510</v>
+        <v>1514</v>
       </c>
       <c r="F25" t="s">
         <v>1025</v>
       </c>
       <c r="G25" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J25" t="s">
         <v>22</v>
@@ -22819,16 +22890,16 @@
         <v>38</v>
       </c>
       <c r="N25" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O25" t="s">
-        <v>1511</v>
+        <v>1515</v>
       </c>
       <c r="P25" t="s">
-        <v>1512</v>
+        <v>1516</v>
       </c>
       <c r="Q25" t="s">
-        <v>1513</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
@@ -22842,16 +22913,16 @@
         <v>52</v>
       </c>
       <c r="D26" t="s">
-        <v>1514</v>
+        <v>1518</v>
       </c>
       <c r="E26" t="s">
         <v>421</v>
       </c>
       <c r="F26" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="G26" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="H26">
         <v>180000</v>
@@ -22872,16 +22943,16 @@
         <v>25</v>
       </c>
       <c r="N26" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O26" t="s">
-        <v>1516</v>
+        <v>1520</v>
       </c>
       <c r="P26" t="s">
-        <v>1517</v>
+        <v>1521</v>
       </c>
       <c r="Q26" t="s">
-        <v>1518</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
@@ -22895,7 +22966,7 @@
         <v>50</v>
       </c>
       <c r="D27" t="s">
-        <v>1519</v>
+        <v>1523</v>
       </c>
       <c r="E27" t="s">
         <v>421</v>
@@ -22904,7 +22975,7 @@
         <v>20</v>
       </c>
       <c r="G27" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="H27">
         <v>180000</v>
@@ -22925,16 +22996,16 @@
         <v>25</v>
       </c>
       <c r="N27" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O27" t="s">
-        <v>1520</v>
+        <v>1524</v>
       </c>
       <c r="P27" t="s">
-        <v>1521</v>
+        <v>1525</v>
       </c>
       <c r="Q27" t="s">
-        <v>1522</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
@@ -22948,7 +23019,7 @@
         <v>46</v>
       </c>
       <c r="D28" t="s">
-        <v>1523</v>
+        <v>1527</v>
       </c>
       <c r="E28" t="s">
         <v>421</v>
@@ -22957,7 +23028,7 @@
         <v>20</v>
       </c>
       <c r="G28" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="H28">
         <v>180000</v>
@@ -22978,16 +23049,16 @@
         <v>25</v>
       </c>
       <c r="N28" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O28" t="s">
-        <v>1524</v>
+        <v>1528</v>
       </c>
       <c r="P28" t="s">
-        <v>1525</v>
+        <v>1529</v>
       </c>
       <c r="Q28" t="s">
-        <v>1526</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
@@ -23001,7 +23072,7 @@
         <v>38</v>
       </c>
       <c r="D29" t="s">
-        <v>1527</v>
+        <v>1531</v>
       </c>
       <c r="E29" t="s">
         <v>421</v>
@@ -23010,7 +23081,7 @@
         <v>20</v>
       </c>
       <c r="G29" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="H29">
         <v>217800</v>
@@ -23031,16 +23102,16 @@
         <v>38</v>
       </c>
       <c r="N29" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O29" t="s">
-        <v>1528</v>
+        <v>1532</v>
       </c>
       <c r="P29" t="s">
-        <v>1529</v>
+        <v>1533</v>
       </c>
       <c r="Q29" t="s">
-        <v>1530</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
@@ -23060,10 +23131,10 @@
         <v>421</v>
       </c>
       <c r="F30" t="s">
-        <v>1531</v>
+        <v>1535</v>
       </c>
       <c r="G30" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="H30">
         <v>180000</v>
@@ -23084,16 +23155,16 @@
         <v>25</v>
       </c>
       <c r="N30" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O30" t="s">
-        <v>1532</v>
+        <v>1536</v>
       </c>
       <c r="P30" t="s">
-        <v>1533</v>
+        <v>1537</v>
       </c>
       <c r="Q30" t="s">
-        <v>1534</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
@@ -23107,16 +23178,16 @@
         <v>45</v>
       </c>
       <c r="D31" t="s">
-        <v>1535</v>
+        <v>1539</v>
       </c>
       <c r="E31" t="s">
         <v>421</v>
       </c>
       <c r="F31" t="s">
-        <v>1536</v>
+        <v>1540</v>
       </c>
       <c r="G31" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="H31">
         <v>219100</v>
@@ -23137,16 +23208,16 @@
         <v>25</v>
       </c>
       <c r="N31" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O31" t="s">
-        <v>1537</v>
+        <v>1541</v>
       </c>
       <c r="P31" t="s">
-        <v>1538</v>
+        <v>1542</v>
       </c>
       <c r="Q31" t="s">
-        <v>1539</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
@@ -23160,16 +23231,16 @@
         <v>42</v>
       </c>
       <c r="D32" t="s">
-        <v>1540</v>
+        <v>1544</v>
       </c>
       <c r="E32" t="s">
         <v>421</v>
       </c>
       <c r="F32" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="G32" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="H32">
         <v>180000</v>
@@ -23190,16 +23261,16 @@
         <v>25</v>
       </c>
       <c r="N32" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O32" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
       <c r="P32" t="s">
-        <v>1543</v>
+        <v>1547</v>
       </c>
       <c r="Q32" t="s">
-        <v>1544</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
@@ -23213,7 +23284,7 @@
         <v>32</v>
       </c>
       <c r="D33" t="s">
-        <v>1545</v>
+        <v>1549</v>
       </c>
       <c r="E33" t="s">
         <v>421</v>
@@ -23222,7 +23293,7 @@
         <v>20</v>
       </c>
       <c r="G33" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="H33">
         <v>219100</v>
@@ -23243,16 +23314,16 @@
         <v>38</v>
       </c>
       <c r="N33" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O33" t="s">
-        <v>1546</v>
+        <v>1550</v>
       </c>
       <c r="P33" t="s">
-        <v>1547</v>
+        <v>1551</v>
       </c>
       <c r="Q33" t="s">
-        <v>1548</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
@@ -23266,7 +23337,7 @@
         <v>35</v>
       </c>
       <c r="D34" t="s">
-        <v>1549</v>
+        <v>1553</v>
       </c>
       <c r="E34" t="s">
         <v>421</v>
@@ -23275,7 +23346,7 @@
         <v>20</v>
       </c>
       <c r="G34" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="H34">
         <v>219100</v>
@@ -23296,16 +23367,16 @@
         <v>38</v>
       </c>
       <c r="N34" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O34" t="s">
-        <v>1550</v>
+        <v>1554</v>
       </c>
       <c r="P34" t="s">
-        <v>1551</v>
+        <v>1555</v>
       </c>
       <c r="Q34" t="s">
-        <v>1552</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
@@ -23319,16 +23390,16 @@
         <v>40</v>
       </c>
       <c r="D35" t="s">
-        <v>1553</v>
+        <v>1557</v>
       </c>
       <c r="E35" t="s">
         <v>421</v>
       </c>
       <c r="F35" t="s">
-        <v>1554</v>
+        <v>1558</v>
       </c>
       <c r="G35" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="H35">
         <v>219100</v>
@@ -23349,16 +23420,16 @@
         <v>25</v>
       </c>
       <c r="N35" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O35" t="s">
-        <v>1555</v>
+        <v>1559</v>
       </c>
       <c r="P35" t="s">
-        <v>1556</v>
+        <v>1560</v>
       </c>
       <c r="Q35" t="s">
-        <v>1557</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
@@ -23372,7 +23443,7 @@
         <v>38</v>
       </c>
       <c r="D36" t="s">
-        <v>1558</v>
+        <v>1562</v>
       </c>
       <c r="E36" t="s">
         <v>421</v>
@@ -23381,7 +23452,7 @@
         <v>437</v>
       </c>
       <c r="G36" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="H36">
         <v>219100</v>
@@ -23402,16 +23473,16 @@
         <v>38</v>
       </c>
       <c r="N36" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O36" t="s">
-        <v>1559</v>
+        <v>1563</v>
       </c>
       <c r="P36" t="s">
-        <v>1560</v>
+        <v>1564</v>
       </c>
       <c r="Q36" t="s">
-        <v>1561</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
@@ -23425,7 +23496,7 @@
         <v>40</v>
       </c>
       <c r="D37" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="E37" t="s">
         <v>421</v>
@@ -23434,7 +23505,7 @@
         <v>20</v>
       </c>
       <c r="G37" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="H37">
         <v>219100</v>
@@ -23455,16 +23526,16 @@
         <v>25</v>
       </c>
       <c r="N37" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O37" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="P37" t="s">
-        <v>1564</v>
+        <v>1568</v>
       </c>
       <c r="Q37" t="s">
-        <v>1565</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
@@ -23478,16 +23549,16 @@
         <v>33</v>
       </c>
       <c r="D38" t="s">
-        <v>1566</v>
+        <v>1570</v>
       </c>
       <c r="E38" t="s">
         <v>421</v>
       </c>
       <c r="F38" t="s">
-        <v>1567</v>
+        <v>1571</v>
       </c>
       <c r="G38" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="H38">
         <v>219100</v>
@@ -23508,16 +23579,16 @@
         <v>38</v>
       </c>
       <c r="N38" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O38" t="s">
-        <v>1568</v>
+        <v>1572</v>
       </c>
       <c r="P38" t="s">
-        <v>1569</v>
+        <v>1573</v>
       </c>
       <c r="Q38" t="s">
-        <v>1570</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
@@ -23531,16 +23602,16 @@
         <v>48</v>
       </c>
       <c r="D39" t="s">
-        <v>1571</v>
+        <v>1575</v>
       </c>
       <c r="E39" t="s">
-        <v>1428</v>
+        <v>1432</v>
       </c>
       <c r="F39" t="s">
-        <v>1572</v>
+        <v>1576</v>
       </c>
       <c r="G39" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J39" t="s">
         <v>22</v>
@@ -23555,16 +23626,16 @@
         <v>25</v>
       </c>
       <c r="N39" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O39" t="s">
-        <v>1573</v>
+        <v>1577</v>
       </c>
       <c r="P39" t="s">
-        <v>1574</v>
+        <v>1578</v>
       </c>
       <c r="Q39" t="s">
-        <v>1575</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
@@ -23578,16 +23649,16 @@
         <v>40</v>
       </c>
       <c r="D40" t="s">
-        <v>1576</v>
+        <v>1580</v>
       </c>
       <c r="E40" t="s">
-        <v>1433</v>
+        <v>1437</v>
       </c>
       <c r="F40" t="s">
-        <v>1577</v>
+        <v>1581</v>
       </c>
       <c r="G40" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="H40">
         <v>184200</v>
@@ -23608,16 +23679,16 @@
         <v>25</v>
       </c>
       <c r="N40" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O40" t="s">
-        <v>1578</v>
+        <v>1582</v>
       </c>
       <c r="P40" t="s">
-        <v>1579</v>
+        <v>1583</v>
       </c>
       <c r="Q40" t="s">
-        <v>1580</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
@@ -23634,13 +23705,13 @@
         <v>1343</v>
       </c>
       <c r="E41" t="s">
-        <v>1433</v>
+        <v>1437</v>
       </c>
       <c r="F41" t="s">
-        <v>1581</v>
+        <v>1585</v>
       </c>
       <c r="G41" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="H41">
         <v>200000</v>
@@ -23661,16 +23732,16 @@
         <v>38</v>
       </c>
       <c r="N41" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O41" t="s">
-        <v>1582</v>
+        <v>1586</v>
       </c>
       <c r="P41" t="s">
-        <v>1583</v>
+        <v>1587</v>
       </c>
       <c r="Q41" t="s">
-        <v>1584</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
@@ -23684,7 +23755,7 @@
         <v>30</v>
       </c>
       <c r="D42" t="s">
-        <v>1585</v>
+        <v>1589</v>
       </c>
       <c r="E42" t="s">
         <v>698</v>
@@ -23693,7 +23764,7 @@
         <v>707</v>
       </c>
       <c r="G42" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J42" t="s">
         <v>22</v>
@@ -23708,16 +23779,16 @@
         <v>38</v>
       </c>
       <c r="N42" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O42" t="s">
-        <v>1586</v>
+        <v>1590</v>
       </c>
       <c r="P42" t="s">
-        <v>1587</v>
+        <v>1591</v>
       </c>
       <c r="Q42" t="s">
-        <v>1588</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
@@ -23737,10 +23808,10 @@
         <v>698</v>
       </c>
       <c r="F43" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="G43" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J43" t="s">
         <v>22</v>
@@ -23755,16 +23826,16 @@
         <v>38</v>
       </c>
       <c r="N43" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O43" t="s">
-        <v>1589</v>
+        <v>1593</v>
       </c>
       <c r="P43" t="s">
-        <v>1590</v>
+        <v>1594</v>
       </c>
       <c r="Q43" t="s">
-        <v>1591</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
@@ -23778,7 +23849,7 @@
         <v>32</v>
       </c>
       <c r="D44" t="s">
-        <v>1592</v>
+        <v>1596</v>
       </c>
       <c r="E44" t="s">
         <v>698</v>
@@ -23787,7 +23858,7 @@
         <v>707</v>
       </c>
       <c r="G44" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J44" t="s">
         <v>22</v>
@@ -23802,16 +23873,16 @@
         <v>38</v>
       </c>
       <c r="N44" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O44" t="s">
-        <v>1593</v>
+        <v>1597</v>
       </c>
       <c r="P44" t="s">
-        <v>1594</v>
+        <v>1598</v>
       </c>
       <c r="Q44" t="s">
-        <v>1595</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
@@ -23825,16 +23896,16 @@
         <v>45</v>
       </c>
       <c r="D45" t="s">
-        <v>1596</v>
+        <v>1600</v>
       </c>
       <c r="E45" t="s">
         <v>478</v>
       </c>
       <c r="F45" t="s">
-        <v>1597</v>
+        <v>1601</v>
       </c>
       <c r="G45" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J45" t="s">
         <v>22</v>
@@ -23849,16 +23920,16 @@
         <v>25</v>
       </c>
       <c r="N45" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O45" t="s">
-        <v>1598</v>
+        <v>1602</v>
       </c>
       <c r="P45" t="s">
-        <v>1599</v>
+        <v>1603</v>
       </c>
       <c r="Q45" t="s">
-        <v>1600</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
@@ -23872,16 +23943,16 @@
         <v>35</v>
       </c>
       <c r="D46" t="s">
-        <v>1601</v>
+        <v>1605</v>
       </c>
       <c r="E46" t="s">
         <v>478</v>
       </c>
       <c r="F46" t="s">
-        <v>1602</v>
+        <v>1606</v>
       </c>
       <c r="G46" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J46" t="s">
         <v>22</v>
@@ -23896,16 +23967,16 @@
         <v>38</v>
       </c>
       <c r="N46" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O46" t="s">
-        <v>1603</v>
+        <v>1607</v>
       </c>
       <c r="P46" t="s">
-        <v>1604</v>
+        <v>1608</v>
       </c>
       <c r="Q46" t="s">
-        <v>1605</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
@@ -23919,7 +23990,7 @@
         <v>35</v>
       </c>
       <c r="D47" t="s">
-        <v>1606</v>
+        <v>1610</v>
       </c>
       <c r="E47" t="s">
         <v>478</v>
@@ -23928,7 +23999,7 @@
         <v>507</v>
       </c>
       <c r="G47" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J47" t="s">
         <v>22</v>
@@ -23943,16 +24014,16 @@
         <v>38</v>
       </c>
       <c r="N47" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O47" t="s">
-        <v>1607</v>
+        <v>1611</v>
       </c>
       <c r="P47" t="s">
-        <v>1608</v>
+        <v>1612</v>
       </c>
       <c r="Q47" t="s">
-        <v>1609</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
@@ -23966,16 +24037,16 @@
         <v>15</v>
       </c>
       <c r="D48" t="s">
-        <v>1610</v>
+        <v>1614</v>
       </c>
       <c r="E48" t="s">
         <v>478</v>
       </c>
       <c r="F48" t="s">
-        <v>1611</v>
+        <v>1615</v>
       </c>
       <c r="G48" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J48" t="s">
         <v>22</v>
@@ -23990,16 +24061,16 @@
         <v>38</v>
       </c>
       <c r="N48" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O48" t="s">
-        <v>1612</v>
+        <v>1616</v>
       </c>
       <c r="P48" t="s">
-        <v>1613</v>
+        <v>1617</v>
       </c>
       <c r="Q48" t="s">
-        <v>1614</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
@@ -24013,16 +24084,16 @@
         <v>25</v>
       </c>
       <c r="D49" t="s">
-        <v>1615</v>
+        <v>1619</v>
       </c>
       <c r="E49" t="s">
         <v>478</v>
       </c>
       <c r="F49" t="s">
-        <v>1616</v>
+        <v>1620</v>
       </c>
       <c r="G49" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J49" t="s">
         <v>22</v>
@@ -24037,16 +24108,16 @@
         <v>38</v>
       </c>
       <c r="N49" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O49" t="s">
-        <v>1617</v>
+        <v>1621</v>
       </c>
       <c r="P49" t="s">
-        <v>1618</v>
+        <v>1622</v>
       </c>
       <c r="Q49" t="s">
-        <v>1619</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
@@ -24060,16 +24131,16 @@
         <v>30</v>
       </c>
       <c r="D50" t="s">
-        <v>1620</v>
+        <v>1624</v>
       </c>
       <c r="E50" t="s">
         <v>478</v>
       </c>
       <c r="F50" t="s">
-        <v>1621</v>
+        <v>1625</v>
       </c>
       <c r="G50" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J50" t="s">
         <v>22</v>
@@ -24084,16 +24155,16 @@
         <v>38</v>
       </c>
       <c r="N50" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O50" t="s">
-        <v>1622</v>
+        <v>1626</v>
       </c>
       <c r="P50" t="s">
-        <v>1623</v>
+        <v>1627</v>
       </c>
       <c r="Q50" t="s">
-        <v>1624</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
@@ -24113,10 +24184,10 @@
         <v>421</v>
       </c>
       <c r="F51" t="s">
-        <v>1581</v>
+        <v>1585</v>
       </c>
       <c r="G51" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J51" t="s">
         <v>22</v>
@@ -24131,16 +24202,16 @@
         <v>38</v>
       </c>
       <c r="N51" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O51" t="s">
-        <v>1625</v>
+        <v>1629</v>
       </c>
       <c r="P51" t="s">
-        <v>1626</v>
+        <v>1630</v>
       </c>
       <c r="Q51" t="s">
-        <v>1627</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
@@ -24160,10 +24231,10 @@
         <v>421</v>
       </c>
       <c r="F52" t="s">
-        <v>1628</v>
+        <v>1632</v>
       </c>
       <c r="G52" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J52" t="s">
         <v>22</v>
@@ -24178,16 +24249,16 @@
         <v>25</v>
       </c>
       <c r="N52" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O52" t="s">
-        <v>1629</v>
+        <v>1633</v>
       </c>
       <c r="P52" t="s">
-        <v>1630</v>
+        <v>1634</v>
       </c>
       <c r="Q52" t="s">
-        <v>1631</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
@@ -24210,7 +24281,7 @@
         <v>764</v>
       </c>
       <c r="G53" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="H53">
         <v>180000</v>
@@ -24231,16 +24302,16 @@
         <v>38</v>
       </c>
       <c r="N53" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O53" t="s">
-        <v>1632</v>
+        <v>1636</v>
       </c>
       <c r="P53" t="s">
-        <v>1633</v>
+        <v>1637</v>
       </c>
       <c r="Q53" t="s">
-        <v>1634</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
@@ -24260,10 +24331,10 @@
         <v>421</v>
       </c>
       <c r="F54" t="s">
-        <v>1635</v>
+        <v>1639</v>
       </c>
       <c r="G54" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="H54">
         <v>180000</v>
@@ -24284,16 +24355,16 @@
         <v>38</v>
       </c>
       <c r="N54" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O54" t="s">
-        <v>1636</v>
+        <v>1640</v>
       </c>
       <c r="P54" t="s">
-        <v>1637</v>
+        <v>1641</v>
       </c>
       <c r="Q54" t="s">
-        <v>1638</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
@@ -24307,16 +24378,16 @@
         <v>20</v>
       </c>
       <c r="D55" t="s">
-        <v>1639</v>
+        <v>1643</v>
       </c>
       <c r="E55" t="s">
         <v>811</v>
       </c>
       <c r="F55" t="s">
-        <v>1640</v>
+        <v>1644</v>
       </c>
       <c r="G55" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J55" t="s">
         <v>22</v>
@@ -24331,16 +24402,16 @@
         <v>38</v>
       </c>
       <c r="N55" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O55" t="s">
-        <v>1641</v>
+        <v>1645</v>
       </c>
       <c r="P55" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="Q55" t="s">
-        <v>1643</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
@@ -24354,7 +24425,7 @@
         <v>50</v>
       </c>
       <c r="D56" t="s">
-        <v>1644</v>
+        <v>1648</v>
       </c>
       <c r="E56" t="s">
         <v>811</v>
@@ -24363,7 +24434,7 @@
         <v>20</v>
       </c>
       <c r="G56" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="H56">
         <v>250000</v>
@@ -24384,16 +24455,16 @@
         <v>25</v>
       </c>
       <c r="N56" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O56" t="s">
-        <v>1645</v>
+        <v>1649</v>
       </c>
       <c r="P56" t="s">
-        <v>1646</v>
+        <v>1650</v>
       </c>
       <c r="Q56" t="s">
-        <v>1647</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
@@ -24407,7 +24478,7 @@
         <v>55</v>
       </c>
       <c r="D57" t="s">
-        <v>1648</v>
+        <v>1652</v>
       </c>
       <c r="E57" t="s">
         <v>811</v>
@@ -24416,7 +24487,7 @@
         <v>20</v>
       </c>
       <c r="G57" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="H57">
         <v>200000</v>
@@ -24437,16 +24508,16 @@
         <v>25</v>
       </c>
       <c r="N57" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O57" t="s">
-        <v>1649</v>
+        <v>1653</v>
       </c>
       <c r="P57" t="s">
-        <v>1650</v>
+        <v>1654</v>
       </c>
       <c r="Q57" t="s">
-        <v>1651</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
@@ -24460,7 +24531,7 @@
         <v>52</v>
       </c>
       <c r="D58" t="s">
-        <v>1652</v>
+        <v>1656</v>
       </c>
       <c r="E58" t="s">
         <v>811</v>
@@ -24469,7 +24540,7 @@
         <v>20</v>
       </c>
       <c r="G58" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="H58">
         <v>250000</v>
@@ -24490,16 +24561,16 @@
         <v>25</v>
       </c>
       <c r="N58" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O58" t="s">
-        <v>1653</v>
+        <v>1657</v>
       </c>
       <c r="P58" t="s">
-        <v>1654</v>
+        <v>1658</v>
       </c>
       <c r="Q58" t="s">
-        <v>1655</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
@@ -24513,7 +24584,7 @@
         <v>53</v>
       </c>
       <c r="D59" t="s">
-        <v>1656</v>
+        <v>1660</v>
       </c>
       <c r="E59" t="s">
         <v>811</v>
@@ -24522,7 +24593,7 @@
         <v>20</v>
       </c>
       <c r="G59" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="H59">
         <v>200000</v>
@@ -24543,16 +24614,16 @@
         <v>25</v>
       </c>
       <c r="N59" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O59" t="s">
-        <v>1657</v>
+        <v>1661</v>
       </c>
       <c r="P59" t="s">
-        <v>1658</v>
+        <v>1662</v>
       </c>
       <c r="Q59" t="s">
-        <v>1659</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
@@ -24566,7 +24637,7 @@
         <v>50</v>
       </c>
       <c r="D60" t="s">
-        <v>1660</v>
+        <v>1664</v>
       </c>
       <c r="E60" t="s">
         <v>811</v>
@@ -24575,7 +24646,7 @@
         <v>20</v>
       </c>
       <c r="G60" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="H60">
         <v>200000</v>
@@ -24596,16 +24667,16 @@
         <v>25</v>
       </c>
       <c r="N60" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O60" t="s">
-        <v>1661</v>
+        <v>1665</v>
       </c>
       <c r="P60" t="s">
-        <v>1662</v>
+        <v>1666</v>
       </c>
       <c r="Q60" t="s">
-        <v>1663</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
@@ -24619,7 +24690,7 @@
         <v>55</v>
       </c>
       <c r="D61" t="s">
-        <v>1664</v>
+        <v>1668</v>
       </c>
       <c r="E61" t="s">
         <v>811</v>
@@ -24628,7 +24699,7 @@
         <v>20</v>
       </c>
       <c r="G61" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="H61">
         <v>250000</v>
@@ -24649,16 +24720,16 @@
         <v>25</v>
       </c>
       <c r="N61" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O61" t="s">
-        <v>1665</v>
+        <v>1669</v>
       </c>
       <c r="P61" t="s">
-        <v>1666</v>
+        <v>1670</v>
       </c>
       <c r="Q61" t="s">
-        <v>1667</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
@@ -24672,16 +24743,16 @@
         <v>45</v>
       </c>
       <c r="D62" t="s">
-        <v>1668</v>
+        <v>1672</v>
       </c>
       <c r="E62" t="s">
-        <v>1669</v>
+        <v>1673</v>
       </c>
       <c r="F62" t="s">
-        <v>1670</v>
+        <v>1674</v>
       </c>
       <c r="G62" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="H62">
         <v>154000</v>
@@ -24702,16 +24773,16 @@
         <v>38</v>
       </c>
       <c r="N62" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O62" t="s">
-        <v>1671</v>
+        <v>1675</v>
       </c>
       <c r="P62" t="s">
-        <v>1672</v>
+        <v>1676</v>
       </c>
       <c r="Q62" t="s">
-        <v>1673</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
@@ -24734,7 +24805,7 @@
         <v>437</v>
       </c>
       <c r="G63" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="H63">
         <v>180000</v>
@@ -24755,16 +24826,16 @@
         <v>25</v>
       </c>
       <c r="N63" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O63" t="s">
-        <v>1674</v>
+        <v>1678</v>
       </c>
       <c r="P63" t="s">
-        <v>1675</v>
+        <v>1679</v>
       </c>
       <c r="Q63" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
@@ -24784,10 +24855,10 @@
         <v>421</v>
       </c>
       <c r="F64" t="s">
-        <v>1531</v>
+        <v>1535</v>
       </c>
       <c r="G64" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="H64">
         <v>219100</v>
@@ -24808,16 +24879,16 @@
         <v>38</v>
       </c>
       <c r="N64" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O64" t="s">
-        <v>1677</v>
+        <v>1681</v>
       </c>
       <c r="P64" t="s">
-        <v>1678</v>
+        <v>1682</v>
       </c>
       <c r="Q64" t="s">
-        <v>1679</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
@@ -24831,7 +24902,7 @@
         <v>25</v>
       </c>
       <c r="D65" t="s">
-        <v>1680</v>
+        <v>1684</v>
       </c>
       <c r="E65" t="s">
         <v>421</v>
@@ -24840,7 +24911,7 @@
         <v>1016</v>
       </c>
       <c r="G65" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J65" t="s">
         <v>22</v>
@@ -24855,16 +24926,16 @@
         <v>38</v>
       </c>
       <c r="N65" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O65" t="s">
-        <v>1681</v>
+        <v>1685</v>
       </c>
       <c r="P65" t="s">
-        <v>1682</v>
+        <v>1686</v>
       </c>
       <c r="Q65" t="s">
-        <v>1683</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
@@ -24884,10 +24955,10 @@
         <v>698</v>
       </c>
       <c r="F66" t="s">
-        <v>1473</v>
+        <v>1477</v>
       </c>
       <c r="G66" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J66" t="s">
         <v>22</v>
@@ -24902,16 +24973,16 @@
         <v>38</v>
       </c>
       <c r="N66" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O66" t="s">
-        <v>1684</v>
+        <v>1688</v>
       </c>
       <c r="P66" t="s">
-        <v>1685</v>
+        <v>1689</v>
       </c>
       <c r="Q66" t="s">
-        <v>1686</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
@@ -24925,16 +24996,16 @@
         <v>15</v>
       </c>
       <c r="D67" t="s">
-        <v>1687</v>
+        <v>1691</v>
       </c>
       <c r="E67" t="s">
-        <v>1688</v>
+        <v>1692</v>
       </c>
       <c r="F67" t="s">
         <v>1032</v>
       </c>
       <c r="G67" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J67" t="s">
         <v>22</v>
@@ -24949,16 +25020,16 @@
         <v>38</v>
       </c>
       <c r="N67" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O67" t="s">
-        <v>1689</v>
+        <v>1693</v>
       </c>
       <c r="P67" t="s">
-        <v>1690</v>
+        <v>1694</v>
       </c>
       <c r="Q67" t="s">
-        <v>1691</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
@@ -24972,16 +25043,16 @@
         <v>12</v>
       </c>
       <c r="D68" t="s">
-        <v>1692</v>
+        <v>1696</v>
       </c>
       <c r="E68" t="s">
-        <v>1693</v>
+        <v>1697</v>
       </c>
       <c r="F68" t="s">
-        <v>1694</v>
+        <v>1698</v>
       </c>
       <c r="G68" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J68" t="s">
         <v>22</v>
@@ -24996,16 +25067,16 @@
         <v>38</v>
       </c>
       <c r="N68" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O68" t="s">
-        <v>1695</v>
+        <v>1699</v>
       </c>
       <c r="P68" t="s">
-        <v>1696</v>
+        <v>1700</v>
       </c>
       <c r="Q68" t="s">
-        <v>1697</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
@@ -25019,16 +25090,16 @@
         <v>42</v>
       </c>
       <c r="D69" t="s">
-        <v>1698</v>
+        <v>1702</v>
       </c>
       <c r="E69" t="s">
         <v>421</v>
       </c>
       <c r="F69" t="s">
-        <v>1699</v>
+        <v>1703</v>
       </c>
       <c r="G69" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="H69">
         <v>180000</v>
@@ -25049,16 +25120,16 @@
         <v>25</v>
       </c>
       <c r="N69" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O69" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="P69" t="s">
-        <v>1701</v>
+        <v>1705</v>
       </c>
       <c r="Q69" t="s">
-        <v>1702</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
@@ -25072,16 +25143,16 @@
         <v>22</v>
       </c>
       <c r="D70" t="s">
-        <v>1703</v>
+        <v>1707</v>
       </c>
       <c r="E70" t="s">
-        <v>1433</v>
+        <v>1437</v>
       </c>
       <c r="F70" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="G70" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="H70">
         <v>200000</v>
@@ -25102,16 +25173,16 @@
         <v>38</v>
       </c>
       <c r="N70" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O70" t="s">
-        <v>1705</v>
+        <v>1709</v>
       </c>
       <c r="P70" t="s">
-        <v>1706</v>
+        <v>1710</v>
       </c>
       <c r="Q70" t="s">
-        <v>1707</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
@@ -25125,16 +25196,16 @@
         <v>28</v>
       </c>
       <c r="D71" t="s">
-        <v>1708</v>
+        <v>1712</v>
       </c>
       <c r="E71" t="s">
-        <v>1709</v>
+        <v>1713</v>
       </c>
       <c r="F71" t="s">
         <v>1016</v>
       </c>
       <c r="G71" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J71" t="s">
         <v>22</v>
@@ -25149,16 +25220,16 @@
         <v>38</v>
       </c>
       <c r="N71" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O71" t="s">
-        <v>1710</v>
+        <v>1714</v>
       </c>
       <c r="P71" t="s">
-        <v>1711</v>
+        <v>1715</v>
       </c>
       <c r="Q71" t="s">
-        <v>1712</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
@@ -25172,16 +25243,16 @@
         <v>5</v>
       </c>
       <c r="D72" t="s">
-        <v>1713</v>
+        <v>1717</v>
       </c>
       <c r="E72" t="s">
-        <v>1714</v>
+        <v>1718</v>
       </c>
       <c r="F72" t="s">
-        <v>1715</v>
+        <v>1719</v>
       </c>
       <c r="G72" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J72" t="s">
         <v>22</v>
@@ -25196,16 +25267,16 @@
         <v>38</v>
       </c>
       <c r="N72" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O72" t="s">
-        <v>1716</v>
+        <v>1720</v>
       </c>
       <c r="P72" t="s">
-        <v>1717</v>
+        <v>1721</v>
       </c>
       <c r="Q72" t="s">
-        <v>1718</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
@@ -25225,10 +25296,10 @@
         <v>421</v>
       </c>
       <c r="F73" t="s">
-        <v>1719</v>
+        <v>1723</v>
       </c>
       <c r="G73" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J73" t="s">
         <v>22</v>
@@ -25243,16 +25314,16 @@
         <v>25</v>
       </c>
       <c r="N73" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O73" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="P73" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="Q73" t="s">
-        <v>1722</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
@@ -25266,16 +25337,16 @@
         <v>35</v>
       </c>
       <c r="D74" t="s">
-        <v>1723</v>
+        <v>1727</v>
       </c>
       <c r="E74" t="s">
-        <v>1724</v>
+        <v>1728</v>
       </c>
       <c r="F74" t="s">
         <v>1085</v>
       </c>
       <c r="G74" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J74" t="s">
         <v>22</v>
@@ -25290,16 +25361,16 @@
         <v>38</v>
       </c>
       <c r="N74" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O74" t="s">
-        <v>1725</v>
+        <v>1729</v>
       </c>
       <c r="P74" t="s">
-        <v>1726</v>
+        <v>1730</v>
       </c>
       <c r="Q74" t="s">
-        <v>1727</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
@@ -25313,16 +25384,16 @@
         <v>55</v>
       </c>
       <c r="D75" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="E75" t="s">
         <v>421</v>
       </c>
       <c r="F75" t="s">
-        <v>1531</v>
+        <v>1535</v>
       </c>
       <c r="G75" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="H75">
         <v>219100</v>
@@ -25337,22 +25408,22 @@
         <v>423</v>
       </c>
       <c r="L75" t="s">
-        <v>1729</v>
+        <v>1733</v>
       </c>
       <c r="M75" t="s">
         <v>25</v>
       </c>
       <c r="N75" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O75" t="s">
-        <v>1730</v>
+        <v>1734</v>
       </c>
       <c r="P75" t="s">
-        <v>1731</v>
+        <v>1735</v>
       </c>
       <c r="Q75" t="s">
-        <v>1732</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
@@ -25366,16 +25437,16 @@
         <v>50</v>
       </c>
       <c r="D76" t="s">
-        <v>1733</v>
+        <v>1737</v>
       </c>
       <c r="E76" t="s">
-        <v>1433</v>
+        <v>1437</v>
       </c>
       <c r="F76" t="s">
         <v>20</v>
       </c>
       <c r="G76" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="H76">
         <v>200000</v>
@@ -25390,22 +25461,22 @@
         <v>423</v>
       </c>
       <c r="L76" t="s">
-        <v>1729</v>
+        <v>1733</v>
       </c>
       <c r="M76" t="s">
         <v>25</v>
       </c>
       <c r="N76" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O76" t="s">
-        <v>1734</v>
+        <v>1738</v>
       </c>
       <c r="P76" t="s">
-        <v>1735</v>
+        <v>1739</v>
       </c>
       <c r="Q76" t="s">
-        <v>1736</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
@@ -25419,16 +25490,16 @@
         <v>12</v>
       </c>
       <c r="D77" t="s">
-        <v>1737</v>
+        <v>1741</v>
       </c>
       <c r="E77" t="s">
-        <v>1738</v>
+        <v>1742</v>
       </c>
       <c r="F77" t="s">
         <v>1016</v>
       </c>
       <c r="G77" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J77" t="s">
         <v>22</v>
@@ -25437,22 +25508,22 @@
         <v>557</v>
       </c>
       <c r="L77" t="s">
-        <v>1729</v>
+        <v>1733</v>
       </c>
       <c r="M77" t="s">
         <v>38</v>
       </c>
       <c r="N77" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O77" t="s">
-        <v>1739</v>
+        <v>1743</v>
       </c>
       <c r="P77" t="s">
-        <v>1740</v>
+        <v>1744</v>
       </c>
       <c r="Q77" t="s">
-        <v>1741</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
@@ -25466,16 +25537,16 @@
         <v>12</v>
       </c>
       <c r="D78" t="s">
+        <v>1746</v>
+      </c>
+      <c r="E78" t="s">
         <v>1742</v>
-      </c>
-      <c r="E78" t="s">
-        <v>1738</v>
       </c>
       <c r="F78" t="s">
         <v>1016</v>
       </c>
       <c r="G78" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J78" t="s">
         <v>22</v>
@@ -25484,22 +25555,22 @@
         <v>557</v>
       </c>
       <c r="L78" t="s">
-        <v>1729</v>
+        <v>1733</v>
       </c>
       <c r="M78" t="s">
         <v>38</v>
       </c>
       <c r="N78" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O78" t="s">
-        <v>1743</v>
+        <v>1747</v>
       </c>
       <c r="P78" t="s">
-        <v>1744</v>
+        <v>1748</v>
       </c>
       <c r="Q78" t="s">
-        <v>1745</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
@@ -25513,16 +25584,16 @@
         <v>3</v>
       </c>
       <c r="D79" t="s">
-        <v>1746</v>
+        <v>1750</v>
       </c>
       <c r="E79" t="s">
-        <v>1738</v>
+        <v>1742</v>
       </c>
       <c r="F79" t="s">
         <v>1016</v>
       </c>
       <c r="G79" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J79" t="s">
         <v>22</v>
@@ -25531,22 +25602,22 @@
         <v>557</v>
       </c>
       <c r="L79" t="s">
-        <v>1729</v>
+        <v>1733</v>
       </c>
       <c r="M79" t="s">
         <v>38</v>
       </c>
       <c r="N79" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O79" t="s">
-        <v>1747</v>
+        <v>1751</v>
       </c>
       <c r="P79" t="s">
-        <v>1748</v>
+        <v>1752</v>
       </c>
       <c r="Q79" t="s">
-        <v>1749</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
@@ -25560,16 +25631,16 @@
         <v>25</v>
       </c>
       <c r="D80" t="s">
-        <v>1750</v>
+        <v>1754</v>
       </c>
       <c r="E80" t="s">
-        <v>1751</v>
+        <v>1755</v>
       </c>
       <c r="F80" t="s">
-        <v>1752</v>
+        <v>1756</v>
       </c>
       <c r="G80" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J80" t="s">
         <v>22</v>
@@ -25578,22 +25649,22 @@
         <v>557</v>
       </c>
       <c r="L80" t="s">
-        <v>1729</v>
+        <v>1733</v>
       </c>
       <c r="M80" t="s">
         <v>38</v>
       </c>
       <c r="N80" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O80" t="s">
-        <v>1753</v>
+        <v>1757</v>
       </c>
       <c r="P80" t="s">
-        <v>1754</v>
+        <v>1758</v>
       </c>
       <c r="Q80" t="s">
-        <v>1755</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
@@ -25607,16 +25678,16 @@
         <v>62</v>
       </c>
       <c r="D81" t="s">
-        <v>1756</v>
+        <v>1760</v>
       </c>
       <c r="E81" t="s">
-        <v>1757</v>
+        <v>1761</v>
       </c>
       <c r="F81" t="s">
-        <v>1758</v>
+        <v>1762</v>
       </c>
       <c r="G81" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J81" t="s">
         <v>22</v>
@@ -25625,22 +25696,22 @@
         <v>557</v>
       </c>
       <c r="L81" t="s">
-        <v>1729</v>
+        <v>1733</v>
       </c>
       <c r="M81" t="s">
         <v>38</v>
       </c>
       <c r="N81" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O81" t="s">
-        <v>1759</v>
+        <v>1763</v>
       </c>
       <c r="P81" t="s">
-        <v>1760</v>
+        <v>1764</v>
       </c>
       <c r="Q81" t="s">
-        <v>1761</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
@@ -25654,16 +25725,16 @@
         <v>68</v>
       </c>
       <c r="D82" t="s">
+        <v>1766</v>
+      </c>
+      <c r="E82" t="s">
+        <v>1761</v>
+      </c>
+      <c r="F82" t="s">
         <v>1762</v>
       </c>
-      <c r="E82" t="s">
-        <v>1757</v>
-      </c>
-      <c r="F82" t="s">
-        <v>1758</v>
-      </c>
       <c r="G82" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J82" t="s">
         <v>22</v>
@@ -25672,22 +25743,22 @@
         <v>557</v>
       </c>
       <c r="L82" t="s">
-        <v>1729</v>
+        <v>1733</v>
       </c>
       <c r="M82" t="s">
         <v>38</v>
       </c>
       <c r="N82" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O82" t="s">
-        <v>1763</v>
+        <v>1767</v>
       </c>
       <c r="P82" t="s">
-        <v>1764</v>
+        <v>1768</v>
       </c>
       <c r="Q82" t="s">
-        <v>1765</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
@@ -25707,10 +25778,10 @@
         <v>421</v>
       </c>
       <c r="F83" t="s">
-        <v>1766</v>
+        <v>1770</v>
       </c>
       <c r="G83" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="H83">
         <v>180000</v>
@@ -25731,16 +25802,16 @@
         <v>25</v>
       </c>
       <c r="N83" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O83" t="s">
-        <v>1767</v>
+        <v>1771</v>
       </c>
       <c r="P83" t="s">
-        <v>1768</v>
+        <v>1772</v>
       </c>
       <c r="Q83" t="s">
-        <v>1769</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
@@ -25760,10 +25831,10 @@
         <v>421</v>
       </c>
       <c r="F84" t="s">
-        <v>1770</v>
+        <v>1774</v>
       </c>
       <c r="G84" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="H84">
         <v>180000</v>
@@ -25784,16 +25855,16 @@
         <v>25</v>
       </c>
       <c r="N84" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O84" t="s">
-        <v>1771</v>
+        <v>1775</v>
       </c>
       <c r="P84" t="s">
-        <v>1772</v>
+        <v>1776</v>
       </c>
       <c r="Q84" t="s">
-        <v>1773</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
@@ -25807,16 +25878,16 @@
         <v>35</v>
       </c>
       <c r="D85" t="s">
-        <v>1774</v>
+        <v>1778</v>
       </c>
       <c r="E85" t="s">
         <v>421</v>
       </c>
       <c r="F85" t="s">
-        <v>1775</v>
+        <v>1779</v>
       </c>
       <c r="G85" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="H85">
         <v>219100</v>
@@ -25837,16 +25908,16 @@
         <v>25</v>
       </c>
       <c r="N85" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O85" t="s">
-        <v>1776</v>
+        <v>1780</v>
       </c>
       <c r="P85" t="s">
-        <v>1777</v>
+        <v>1781</v>
       </c>
       <c r="Q85" t="s">
-        <v>1778</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
@@ -25860,16 +25931,16 @@
         <v>25</v>
       </c>
       <c r="D86" t="s">
-        <v>1779</v>
+        <v>1783</v>
       </c>
       <c r="E86" t="s">
         <v>478</v>
       </c>
       <c r="F86" t="s">
-        <v>1597</v>
+        <v>1601</v>
       </c>
       <c r="G86" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J86" t="s">
         <v>22</v>
@@ -25884,16 +25955,16 @@
         <v>38</v>
       </c>
       <c r="N86" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O86" t="s">
-        <v>1780</v>
+        <v>1784</v>
       </c>
       <c r="P86" t="s">
-        <v>1781</v>
+        <v>1785</v>
       </c>
       <c r="Q86" t="s">
-        <v>1782</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
@@ -25907,16 +25978,16 @@
         <v>35</v>
       </c>
       <c r="D87" t="s">
-        <v>1783</v>
+        <v>1787</v>
       </c>
       <c r="E87" t="s">
-        <v>1784</v>
+        <v>1788</v>
       </c>
       <c r="F87" t="s">
-        <v>1473</v>
+        <v>1477</v>
       </c>
       <c r="G87" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J87" t="s">
         <v>22</v>
@@ -25931,16 +26002,16 @@
         <v>38</v>
       </c>
       <c r="N87" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O87" t="s">
-        <v>1785</v>
+        <v>1789</v>
       </c>
       <c r="P87" t="s">
-        <v>1786</v>
+        <v>1790</v>
       </c>
       <c r="Q87" t="s">
-        <v>1787</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
@@ -25963,7 +26034,7 @@
         <v>1085</v>
       </c>
       <c r="G88" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="H88">
         <v>200000</v>
@@ -25984,16 +26055,16 @@
         <v>38</v>
       </c>
       <c r="N88" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O88" t="s">
-        <v>1788</v>
+        <v>1792</v>
       </c>
       <c r="P88" t="s">
-        <v>1789</v>
+        <v>1793</v>
       </c>
       <c r="Q88" t="s">
-        <v>1790</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
@@ -26007,7 +26078,7 @@
         <v>38</v>
       </c>
       <c r="D89" t="s">
-        <v>1791</v>
+        <v>1795</v>
       </c>
       <c r="E89" t="s">
         <v>1084</v>
@@ -26016,7 +26087,7 @@
         <v>1085</v>
       </c>
       <c r="G89" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="H89">
         <v>200000</v>
@@ -26037,16 +26108,16 @@
         <v>38</v>
       </c>
       <c r="N89" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O89" t="s">
-        <v>1792</v>
+        <v>1796</v>
       </c>
       <c r="P89" t="s">
-        <v>1793</v>
+        <v>1797</v>
       </c>
       <c r="Q89" t="s">
-        <v>1794</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
@@ -26060,16 +26131,16 @@
         <v>40</v>
       </c>
       <c r="D90" t="s">
-        <v>1576</v>
+        <v>1580</v>
       </c>
       <c r="E90" t="s">
-        <v>1433</v>
+        <v>1437</v>
       </c>
       <c r="F90" t="s">
         <v>713</v>
       </c>
       <c r="G90" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="H90">
         <v>184200</v>
@@ -26090,16 +26161,16 @@
         <v>38</v>
       </c>
       <c r="N90" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O90" t="s">
-        <v>1795</v>
+        <v>1799</v>
       </c>
       <c r="P90" t="s">
-        <v>1796</v>
+        <v>1800</v>
       </c>
       <c r="Q90" t="s">
-        <v>1797</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
@@ -26113,16 +26184,16 @@
         <v>20</v>
       </c>
       <c r="D91" t="s">
-        <v>1798</v>
+        <v>1802</v>
       </c>
       <c r="E91" t="s">
-        <v>1799</v>
+        <v>1803</v>
       </c>
       <c r="F91" t="s">
-        <v>1800</v>
+        <v>1804</v>
       </c>
       <c r="G91" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J91" t="s">
         <v>22</v>
@@ -26137,16 +26208,16 @@
         <v>38</v>
       </c>
       <c r="N91" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O91" t="s">
-        <v>1801</v>
+        <v>1805</v>
       </c>
       <c r="P91" t="s">
-        <v>1802</v>
+        <v>1806</v>
       </c>
       <c r="Q91" t="s">
-        <v>1803</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
@@ -26160,16 +26231,16 @@
         <v>35</v>
       </c>
       <c r="D92" t="s">
-        <v>1804</v>
+        <v>1808</v>
       </c>
       <c r="E92" t="s">
-        <v>1805</v>
+        <v>1809</v>
       </c>
       <c r="F92" t="s">
-        <v>1806</v>
+        <v>1810</v>
       </c>
       <c r="G92" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="H92">
         <v>230000</v>
@@ -26190,16 +26261,16 @@
         <v>38</v>
       </c>
       <c r="N92" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O92" t="s">
-        <v>1807</v>
+        <v>1811</v>
       </c>
       <c r="P92" t="s">
-        <v>1808</v>
+        <v>1812</v>
       </c>
       <c r="Q92" t="s">
-        <v>1809</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
@@ -26219,10 +26290,10 @@
         <v>421</v>
       </c>
       <c r="F93" t="s">
-        <v>1810</v>
+        <v>1814</v>
       </c>
       <c r="G93" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="H93">
         <v>219100</v>
@@ -26243,16 +26314,16 @@
         <v>32</v>
       </c>
       <c r="N93" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O93" t="s">
-        <v>1811</v>
+        <v>1815</v>
       </c>
       <c r="P93" t="s">
-        <v>1812</v>
+        <v>1816</v>
       </c>
       <c r="Q93" t="s">
-        <v>1813</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
@@ -26266,16 +26337,16 @@
         <v>25</v>
       </c>
       <c r="D94" t="s">
-        <v>1814</v>
+        <v>1818</v>
       </c>
       <c r="E94" t="s">
-        <v>1724</v>
+        <v>1728</v>
       </c>
       <c r="F94" t="s">
         <v>1085</v>
       </c>
       <c r="G94" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J94" t="s">
         <v>22</v>
@@ -26290,16 +26361,16 @@
         <v>38</v>
       </c>
       <c r="N94" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O94" t="s">
-        <v>1815</v>
+        <v>1819</v>
       </c>
       <c r="P94" t="s">
-        <v>1816</v>
+        <v>1820</v>
       </c>
       <c r="Q94" t="s">
-        <v>1817</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
@@ -26313,16 +26384,16 @@
         <v>22</v>
       </c>
       <c r="D95" t="s">
-        <v>1818</v>
+        <v>1822</v>
       </c>
       <c r="E95" t="s">
-        <v>1819</v>
+        <v>1823</v>
       </c>
       <c r="F95" t="s">
-        <v>1820</v>
+        <v>1824</v>
       </c>
       <c r="G95" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J95" t="s">
         <v>22</v>
@@ -26337,16 +26408,16 @@
         <v>38</v>
       </c>
       <c r="N95" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O95" t="s">
-        <v>1821</v>
+        <v>1825</v>
       </c>
       <c r="P95" t="s">
-        <v>1822</v>
+        <v>1826</v>
       </c>
       <c r="Q95" t="s">
-        <v>1823</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
@@ -26360,16 +26431,16 @@
         <v>3</v>
       </c>
       <c r="D96" t="s">
+        <v>1828</v>
+      </c>
+      <c r="E96" t="s">
+        <v>1829</v>
+      </c>
+      <c r="F96" t="s">
         <v>1824</v>
       </c>
-      <c r="E96" t="s">
-        <v>1825</v>
-      </c>
-      <c r="F96" t="s">
-        <v>1820</v>
-      </c>
       <c r="G96" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J96" t="s">
         <v>22</v>
@@ -26384,16 +26455,16 @@
         <v>38</v>
       </c>
       <c r="N96" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O96" t="s">
-        <v>1826</v>
+        <v>1830</v>
       </c>
       <c r="P96" t="s">
-        <v>1827</v>
+        <v>1831</v>
       </c>
       <c r="Q96" t="s">
-        <v>1828</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
@@ -26407,16 +26478,16 @@
         <v>28</v>
       </c>
       <c r="D97" t="s">
-        <v>1829</v>
+        <v>1833</v>
       </c>
       <c r="E97" t="s">
-        <v>1830</v>
+        <v>1834</v>
       </c>
       <c r="F97" t="s">
         <v>1016</v>
       </c>
       <c r="G97" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J97" t="s">
         <v>22</v>
@@ -26431,16 +26502,16 @@
         <v>38</v>
       </c>
       <c r="N97" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O97" t="s">
-        <v>1831</v>
+        <v>1835</v>
       </c>
       <c r="P97" t="s">
-        <v>1832</v>
+        <v>1836</v>
       </c>
       <c r="Q97" t="s">
-        <v>1833</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
@@ -26454,16 +26525,16 @@
         <v>45</v>
       </c>
       <c r="D98" t="s">
-        <v>1834</v>
+        <v>1838</v>
       </c>
       <c r="E98" t="s">
-        <v>1835</v>
+        <v>1839</v>
       </c>
       <c r="F98" t="s">
-        <v>1473</v>
+        <v>1477</v>
       </c>
       <c r="G98" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J98" t="s">
         <v>22</v>
@@ -26478,16 +26549,16 @@
         <v>25</v>
       </c>
       <c r="N98" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O98" t="s">
-        <v>1836</v>
+        <v>1840</v>
       </c>
       <c r="P98" t="s">
-        <v>1837</v>
+        <v>1841</v>
       </c>
       <c r="Q98" t="s">
-        <v>1838</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.25">
@@ -26501,16 +26572,16 @@
         <v>50</v>
       </c>
       <c r="D99" t="s">
-        <v>1839</v>
+        <v>1843</v>
       </c>
       <c r="E99" t="s">
-        <v>1840</v>
+        <v>1844</v>
       </c>
       <c r="F99" t="s">
-        <v>1505</v>
+        <v>1509</v>
       </c>
       <c r="G99" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J99" t="s">
         <v>22</v>
@@ -26525,16 +26596,16 @@
         <v>25</v>
       </c>
       <c r="N99" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O99" t="s">
-        <v>1841</v>
+        <v>1845</v>
       </c>
       <c r="P99" t="s">
-        <v>1842</v>
+        <v>1846</v>
       </c>
       <c r="Q99" t="s">
-        <v>1843</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.25">
@@ -26548,16 +26619,16 @@
         <v>48</v>
       </c>
       <c r="D100" t="s">
-        <v>1844</v>
+        <v>1848</v>
       </c>
       <c r="E100" t="s">
-        <v>1669</v>
+        <v>1673</v>
       </c>
       <c r="F100" t="s">
-        <v>1845</v>
+        <v>1849</v>
       </c>
       <c r="G100" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="H100">
         <v>154000</v>
@@ -26578,16 +26649,16 @@
         <v>25</v>
       </c>
       <c r="N100" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O100" t="s">
-        <v>1846</v>
+        <v>1850</v>
       </c>
       <c r="P100" t="s">
-        <v>1847</v>
+        <v>1851</v>
       </c>
       <c r="Q100" t="s">
-        <v>1848</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.25">
@@ -26601,16 +26672,16 @@
         <v>25</v>
       </c>
       <c r="D101" t="s">
-        <v>1849</v>
+        <v>1853</v>
       </c>
       <c r="E101" t="s">
-        <v>1494</v>
+        <v>1498</v>
       </c>
       <c r="F101" t="s">
         <v>1085</v>
       </c>
       <c r="G101" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J101" t="s">
         <v>22</v>
@@ -26625,16 +26696,16 @@
         <v>38</v>
       </c>
       <c r="N101" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O101" t="s">
-        <v>1850</v>
+        <v>1854</v>
       </c>
       <c r="P101" t="s">
-        <v>1851</v>
+        <v>1855</v>
       </c>
       <c r="Q101" t="s">
-        <v>1852</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.25">
@@ -26648,16 +26719,16 @@
         <v>32</v>
       </c>
       <c r="D102" t="s">
-        <v>1750</v>
+        <v>1754</v>
       </c>
       <c r="E102" t="s">
-        <v>1494</v>
+        <v>1498</v>
       </c>
       <c r="F102" t="s">
         <v>1085</v>
       </c>
       <c r="G102" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J102" t="s">
         <v>22</v>
@@ -26672,16 +26743,16 @@
         <v>38</v>
       </c>
       <c r="N102" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O102" t="s">
-        <v>1853</v>
+        <v>1857</v>
       </c>
       <c r="P102" t="s">
-        <v>1854</v>
+        <v>1858</v>
       </c>
       <c r="Q102" t="s">
-        <v>1855</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.25">
@@ -26695,16 +26766,16 @@
         <v>22</v>
       </c>
       <c r="D103" t="s">
-        <v>1856</v>
+        <v>1860</v>
       </c>
       <c r="E103" t="s">
-        <v>1840</v>
+        <v>1844</v>
       </c>
       <c r="F103" t="s">
-        <v>1820</v>
+        <v>1824</v>
       </c>
       <c r="G103" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J103" t="s">
         <v>22</v>
@@ -26719,16 +26790,16 @@
         <v>38</v>
       </c>
       <c r="N103" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O103" t="s">
-        <v>1857</v>
+        <v>1861</v>
       </c>
       <c r="P103" t="s">
-        <v>1858</v>
+        <v>1862</v>
       </c>
       <c r="Q103" t="s">
-        <v>1859</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.25">
@@ -26742,16 +26813,16 @@
         <v>55</v>
       </c>
       <c r="D104" t="s">
-        <v>1839</v>
+        <v>1843</v>
       </c>
       <c r="E104" t="s">
-        <v>1840</v>
+        <v>1844</v>
       </c>
       <c r="F104" t="s">
-        <v>1860</v>
+        <v>1864</v>
       </c>
       <c r="G104" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J104" t="s">
         <v>22</v>
@@ -26766,16 +26837,16 @@
         <v>38</v>
       </c>
       <c r="N104" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O104" t="s">
-        <v>1861</v>
+        <v>1865</v>
       </c>
       <c r="P104" t="s">
-        <v>1862</v>
+        <v>1866</v>
       </c>
       <c r="Q104" t="s">
-        <v>1863</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.25">
@@ -26789,16 +26860,16 @@
         <v>25</v>
       </c>
       <c r="D105" t="s">
+        <v>1868</v>
+      </c>
+      <c r="E105" t="s">
+        <v>1844</v>
+      </c>
+      <c r="F105" t="s">
         <v>1864</v>
       </c>
-      <c r="E105" t="s">
-        <v>1840</v>
-      </c>
-      <c r="F105" t="s">
-        <v>1860</v>
-      </c>
       <c r="G105" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J105" t="s">
         <v>22</v>
@@ -26813,16 +26884,16 @@
         <v>38</v>
       </c>
       <c r="N105" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O105" t="s">
-        <v>1865</v>
+        <v>1869</v>
       </c>
       <c r="P105" t="s">
-        <v>1866</v>
+        <v>1870</v>
       </c>
       <c r="Q105" t="s">
-        <v>1867</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.25">
@@ -26836,7 +26907,7 @@
         <v>33</v>
       </c>
       <c r="D106" t="s">
-        <v>1868</v>
+        <v>1872</v>
       </c>
       <c r="E106" t="s">
         <v>421</v>
@@ -26845,7 +26916,7 @@
         <v>1016</v>
       </c>
       <c r="G106" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J106" t="s">
         <v>22</v>
@@ -26860,16 +26931,16 @@
         <v>38</v>
       </c>
       <c r="N106" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O106" t="s">
-        <v>1869</v>
+        <v>1873</v>
       </c>
       <c r="P106" t="s">
-        <v>1870</v>
+        <v>1874</v>
       </c>
       <c r="Q106" t="s">
-        <v>1871</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.25">
@@ -26883,16 +26954,16 @@
         <v>38</v>
       </c>
       <c r="D107" t="s">
-        <v>1872</v>
+        <v>1876</v>
       </c>
       <c r="E107" t="s">
-        <v>1873</v>
+        <v>1877</v>
       </c>
       <c r="F107" t="s">
-        <v>1602</v>
+        <v>1606</v>
       </c>
       <c r="G107" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="H107">
         <v>220000</v>
@@ -26913,16 +26984,16 @@
         <v>38</v>
       </c>
       <c r="N107" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O107" t="s">
-        <v>1874</v>
+        <v>1878</v>
       </c>
       <c r="P107" t="s">
-        <v>1875</v>
+        <v>1879</v>
       </c>
       <c r="Q107" t="s">
-        <v>1876</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.25">
@@ -26936,16 +27007,16 @@
         <v>62</v>
       </c>
       <c r="D108" t="s">
-        <v>1877</v>
+        <v>1881</v>
       </c>
       <c r="E108" t="s">
-        <v>1433</v>
+        <v>1437</v>
       </c>
       <c r="F108" t="s">
         <v>20</v>
       </c>
       <c r="G108" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="H108">
         <v>200000</v>
@@ -26966,16 +27037,16 @@
         <v>25</v>
       </c>
       <c r="N108" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O108" t="s">
-        <v>1878</v>
+        <v>1882</v>
       </c>
       <c r="P108" t="s">
-        <v>1879</v>
+        <v>1883</v>
       </c>
       <c r="Q108" t="s">
-        <v>1880</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.25">
@@ -26989,16 +27060,16 @@
         <v>30</v>
       </c>
       <c r="D109" t="s">
-        <v>1864</v>
+        <v>1868</v>
       </c>
       <c r="E109" t="s">
-        <v>1840</v>
+        <v>1844</v>
       </c>
       <c r="F109" t="s">
-        <v>1820</v>
+        <v>1824</v>
       </c>
       <c r="G109" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J109" t="s">
         <v>22</v>
@@ -27013,16 +27084,16 @@
         <v>38</v>
       </c>
       <c r="N109" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O109" t="s">
-        <v>1881</v>
+        <v>1885</v>
       </c>
       <c r="P109" t="s">
-        <v>1882</v>
+        <v>1886</v>
       </c>
       <c r="Q109" t="s">
-        <v>1883</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.25">
@@ -27036,16 +27107,16 @@
         <v>58</v>
       </c>
       <c r="D110" t="s">
-        <v>1839</v>
+        <v>1843</v>
       </c>
       <c r="E110" t="s">
-        <v>1840</v>
+        <v>1844</v>
       </c>
       <c r="F110" t="s">
-        <v>1505</v>
+        <v>1509</v>
       </c>
       <c r="G110" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J110" t="s">
         <v>22</v>
@@ -27060,16 +27131,16 @@
         <v>38</v>
       </c>
       <c r="N110" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O110" t="s">
-        <v>1884</v>
+        <v>1888</v>
       </c>
       <c r="P110" t="s">
-        <v>1885</v>
+        <v>1889</v>
       </c>
       <c r="Q110" t="s">
-        <v>1886</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.25">
@@ -27083,7 +27154,7 @@
         <v>55</v>
       </c>
       <c r="D111" t="s">
-        <v>1887</v>
+        <v>1891</v>
       </c>
       <c r="E111" t="s">
         <v>421</v>
@@ -27092,7 +27163,7 @@
         <v>20</v>
       </c>
       <c r="G111" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="H111">
         <v>217800</v>
@@ -27113,16 +27184,16 @@
         <v>25</v>
       </c>
       <c r="N111" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O111" t="s">
-        <v>1888</v>
+        <v>1892</v>
       </c>
       <c r="P111" t="s">
-        <v>1889</v>
+        <v>1893</v>
       </c>
       <c r="Q111" t="s">
-        <v>1890</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.25">
@@ -27136,16 +27207,16 @@
         <v>45</v>
       </c>
       <c r="D112" t="s">
-        <v>1891</v>
+        <v>1895</v>
       </c>
       <c r="E112" t="s">
         <v>421</v>
       </c>
       <c r="F112" t="s">
-        <v>1892</v>
+        <v>1896</v>
       </c>
       <c r="G112" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="H112">
         <v>219100</v>
@@ -27166,16 +27237,16 @@
         <v>25</v>
       </c>
       <c r="N112" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O112" t="s">
-        <v>1893</v>
+        <v>1897</v>
       </c>
       <c r="P112" t="s">
-        <v>1894</v>
+        <v>1898</v>
       </c>
       <c r="Q112" t="s">
-        <v>1895</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.25">
@@ -27195,10 +27266,10 @@
         <v>698</v>
       </c>
       <c r="F113" t="s">
-        <v>1896</v>
+        <v>1900</v>
       </c>
       <c r="G113" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J113" t="s">
         <v>22</v>
@@ -27213,16 +27284,16 @@
         <v>38</v>
       </c>
       <c r="N113" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O113" t="s">
-        <v>1897</v>
+        <v>1901</v>
       </c>
       <c r="P113" t="s">
-        <v>1898</v>
+        <v>1902</v>
       </c>
       <c r="Q113" t="s">
-        <v>1899</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.25">
@@ -27236,16 +27307,16 @@
         <v>35</v>
       </c>
       <c r="D114" t="s">
-        <v>1900</v>
+        <v>1904</v>
       </c>
       <c r="E114" t="s">
         <v>421</v>
       </c>
       <c r="F114" t="s">
-        <v>1901</v>
+        <v>1905</v>
       </c>
       <c r="G114" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J114" t="s">
         <v>22</v>
@@ -27260,16 +27331,16 @@
         <v>38</v>
       </c>
       <c r="N114" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O114" t="s">
-        <v>1902</v>
+        <v>1906</v>
       </c>
       <c r="P114" t="s">
-        <v>1903</v>
+        <v>1907</v>
       </c>
       <c r="Q114" t="s">
-        <v>1904</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.25">
@@ -27283,7 +27354,7 @@
         <v>38</v>
       </c>
       <c r="D115" t="s">
-        <v>1905</v>
+        <v>1909</v>
       </c>
       <c r="E115" t="s">
         <v>421</v>
@@ -27292,7 +27363,7 @@
         <v>20</v>
       </c>
       <c r="G115" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="H115">
         <v>219100</v>
@@ -27313,16 +27384,16 @@
         <v>38</v>
       </c>
       <c r="N115" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O115" t="s">
-        <v>1906</v>
+        <v>1910</v>
       </c>
       <c r="P115" t="s">
-        <v>1907</v>
+        <v>1911</v>
       </c>
       <c r="Q115" t="s">
-        <v>1908</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.25">
@@ -27336,16 +27407,16 @@
         <v>22</v>
       </c>
       <c r="D116" t="s">
-        <v>1909</v>
+        <v>1913</v>
       </c>
       <c r="E116" t="s">
-        <v>1910</v>
+        <v>1914</v>
       </c>
       <c r="F116" t="s">
-        <v>1911</v>
+        <v>1915</v>
       </c>
       <c r="G116" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J116" t="s">
         <v>22</v>
@@ -27360,16 +27431,16 @@
         <v>38</v>
       </c>
       <c r="N116" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O116" t="s">
-        <v>1912</v>
+        <v>1916</v>
       </c>
       <c r="P116" t="s">
-        <v>1913</v>
+        <v>1917</v>
       </c>
       <c r="Q116" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.25">
@@ -27383,16 +27454,16 @@
         <v>35</v>
       </c>
       <c r="D117" t="s">
-        <v>1915</v>
+        <v>1919</v>
       </c>
       <c r="E117" t="s">
-        <v>1916</v>
+        <v>1920</v>
       </c>
       <c r="F117" t="s">
-        <v>1917</v>
+        <v>1921</v>
       </c>
       <c r="G117" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J117" t="s">
         <v>22</v>
@@ -27407,16 +27478,16 @@
         <v>38</v>
       </c>
       <c r="N117" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O117" t="s">
-        <v>1918</v>
+        <v>1922</v>
       </c>
       <c r="P117" t="s">
-        <v>1919</v>
+        <v>1923</v>
       </c>
       <c r="Q117" t="s">
-        <v>1920</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.25">
@@ -27430,7 +27501,7 @@
         <v>55</v>
       </c>
       <c r="D118" t="s">
-        <v>1921</v>
+        <v>1925</v>
       </c>
       <c r="E118" t="s">
         <v>1084</v>
@@ -27439,7 +27510,7 @@
         <v>1085</v>
       </c>
       <c r="G118" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="H118">
         <v>200000</v>
@@ -27460,16 +27531,16 @@
         <v>25</v>
       </c>
       <c r="N118" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O118" t="s">
-        <v>1922</v>
+        <v>1926</v>
       </c>
       <c r="P118" t="s">
-        <v>1923</v>
+        <v>1927</v>
       </c>
       <c r="Q118" t="s">
-        <v>1924</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.25">
@@ -27489,10 +27560,10 @@
         <v>421</v>
       </c>
       <c r="F119" t="s">
-        <v>1925</v>
+        <v>1929</v>
       </c>
       <c r="G119" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="H119">
         <v>180000</v>
@@ -27513,16 +27584,16 @@
         <v>25</v>
       </c>
       <c r="N119" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O119" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="P119" t="s">
-        <v>1927</v>
+        <v>1931</v>
       </c>
       <c r="Q119" t="s">
-        <v>1928</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.25">
@@ -27542,10 +27613,10 @@
         <v>698</v>
       </c>
       <c r="F120" t="s">
-        <v>1473</v>
+        <v>1477</v>
       </c>
       <c r="G120" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J120" t="s">
         <v>22</v>
@@ -27560,16 +27631,16 @@
         <v>38</v>
       </c>
       <c r="N120" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O120" t="s">
-        <v>1929</v>
+        <v>1933</v>
       </c>
       <c r="P120" t="s">
-        <v>1930</v>
+        <v>1934</v>
       </c>
       <c r="Q120" t="s">
-        <v>1931</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.25">
@@ -27592,7 +27663,7 @@
         <v>1085</v>
       </c>
       <c r="G121" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J121" t="s">
         <v>22</v>
@@ -27607,16 +27678,16 @@
         <v>38</v>
       </c>
       <c r="N121" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O121" t="s">
-        <v>1932</v>
+        <v>1936</v>
       </c>
       <c r="P121" t="s">
-        <v>1933</v>
+        <v>1937</v>
       </c>
       <c r="Q121" t="s">
-        <v>1934</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.25">
@@ -27639,7 +27710,7 @@
         <v>1085</v>
       </c>
       <c r="G122" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J122" t="s">
         <v>22</v>
@@ -27654,16 +27725,16 @@
         <v>25</v>
       </c>
       <c r="N122" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O122" t="s">
-        <v>1935</v>
+        <v>1939</v>
       </c>
       <c r="P122" t="s">
-        <v>1936</v>
+        <v>1940</v>
       </c>
       <c r="Q122" t="s">
-        <v>1937</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.25">
@@ -27677,16 +27748,16 @@
         <v>32</v>
       </c>
       <c r="D123" t="s">
-        <v>1509</v>
+        <v>1513</v>
       </c>
       <c r="E123" t="s">
-        <v>1510</v>
+        <v>1514</v>
       </c>
       <c r="F123" t="s">
         <v>1025</v>
       </c>
       <c r="G123" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J123" t="s">
         <v>22</v>
@@ -27701,16 +27772,16 @@
         <v>38</v>
       </c>
       <c r="N123" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O123" t="s">
-        <v>1938</v>
+        <v>1942</v>
       </c>
       <c r="P123" t="s">
-        <v>1939</v>
+        <v>1943</v>
       </c>
       <c r="Q123" t="s">
-        <v>1940</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.25">
@@ -27724,7 +27795,7 @@
         <v>30</v>
       </c>
       <c r="D124" t="s">
-        <v>1941</v>
+        <v>1945</v>
       </c>
       <c r="E124" t="s">
         <v>698</v>
@@ -27733,7 +27804,7 @@
         <v>707</v>
       </c>
       <c r="G124" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J124" t="s">
         <v>22</v>
@@ -27748,16 +27819,16 @@
         <v>38</v>
       </c>
       <c r="N124" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O124" t="s">
-        <v>1942</v>
+        <v>1946</v>
       </c>
       <c r="P124" t="s">
-        <v>1943</v>
+        <v>1947</v>
       </c>
       <c r="Q124" t="s">
-        <v>1944</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.25">
@@ -27771,16 +27842,16 @@
         <v>5</v>
       </c>
       <c r="D125" t="s">
-        <v>1498</v>
+        <v>1502</v>
       </c>
       <c r="E125" t="s">
-        <v>1499</v>
+        <v>1503</v>
       </c>
       <c r="F125" t="s">
         <v>1032</v>
       </c>
       <c r="G125" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J125" t="s">
         <v>22</v>
@@ -27795,16 +27866,16 @@
         <v>38</v>
       </c>
       <c r="N125" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O125" t="s">
-        <v>1945</v>
+        <v>1949</v>
       </c>
       <c r="P125" t="s">
-        <v>1946</v>
+        <v>1950</v>
       </c>
       <c r="Q125" t="s">
-        <v>1947</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.25">
@@ -27818,16 +27889,16 @@
         <v>30</v>
       </c>
       <c r="D126" t="s">
-        <v>1503</v>
+        <v>1507</v>
       </c>
       <c r="E126" t="s">
-        <v>1504</v>
+        <v>1508</v>
       </c>
       <c r="F126" t="s">
-        <v>1505</v>
+        <v>1509</v>
       </c>
       <c r="G126" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J126" t="s">
         <v>22</v>
@@ -27842,16 +27913,16 @@
         <v>38</v>
       </c>
       <c r="N126" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O126" t="s">
-        <v>1948</v>
+        <v>1952</v>
       </c>
       <c r="P126" t="s">
-        <v>1949</v>
+        <v>1953</v>
       </c>
       <c r="Q126" t="s">
-        <v>1950</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.25">
@@ -27865,16 +27936,16 @@
         <v>40</v>
       </c>
       <c r="D127" t="s">
-        <v>1951</v>
+        <v>1955</v>
       </c>
       <c r="E127" t="s">
-        <v>1952</v>
+        <v>1956</v>
       </c>
       <c r="F127" t="s">
-        <v>1953</v>
+        <v>1957</v>
       </c>
       <c r="G127" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J127" t="s">
         <v>22</v>
@@ -27889,16 +27960,16 @@
         <v>38</v>
       </c>
       <c r="N127" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O127" t="s">
-        <v>1954</v>
+        <v>1958</v>
       </c>
       <c r="P127" t="s">
-        <v>1955</v>
+        <v>1959</v>
       </c>
       <c r="Q127" t="s">
-        <v>1956</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.25">
@@ -27912,16 +27983,16 @@
         <v>38</v>
       </c>
       <c r="D128" t="s">
-        <v>1957</v>
+        <v>1961</v>
       </c>
       <c r="E128" t="s">
         <v>421</v>
       </c>
       <c r="F128" t="s">
-        <v>1473</v>
+        <v>1477</v>
       </c>
       <c r="G128" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J128" t="s">
         <v>22</v>
@@ -27936,16 +28007,16 @@
         <v>38</v>
       </c>
       <c r="N128" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O128" t="s">
-        <v>1958</v>
+        <v>1962</v>
       </c>
       <c r="P128" t="s">
-        <v>1959</v>
+        <v>1963</v>
       </c>
       <c r="Q128" t="s">
-        <v>1960</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="129" spans="1:17" x14ac:dyDescent="0.25">
@@ -27959,16 +28030,16 @@
         <v>36</v>
       </c>
       <c r="D129" t="s">
-        <v>1961</v>
+        <v>1965</v>
       </c>
       <c r="E129" t="s">
         <v>421</v>
       </c>
       <c r="F129" t="s">
-        <v>1473</v>
+        <v>1477</v>
       </c>
       <c r="G129" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J129" t="s">
         <v>22</v>
@@ -27983,16 +28054,16 @@
         <v>38</v>
       </c>
       <c r="N129" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O129" t="s">
-        <v>1962</v>
+        <v>1966</v>
       </c>
       <c r="P129" t="s">
-        <v>1963</v>
+        <v>1967</v>
       </c>
       <c r="Q129" t="s">
-        <v>1964</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="130" spans="1:17" x14ac:dyDescent="0.25">
@@ -28009,13 +28080,13 @@
         <v>549</v>
       </c>
       <c r="E130" t="s">
-        <v>1965</v>
+        <v>1969</v>
       </c>
       <c r="F130" t="s">
-        <v>1966</v>
+        <v>1970</v>
       </c>
       <c r="G130" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J130" t="s">
         <v>22</v>
@@ -28030,16 +28101,16 @@
         <v>38</v>
       </c>
       <c r="N130" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O130" t="s">
-        <v>1967</v>
+        <v>1971</v>
       </c>
       <c r="P130" t="s">
-        <v>1968</v>
+        <v>1972</v>
       </c>
       <c r="Q130" t="s">
-        <v>1969</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="131" spans="1:17" x14ac:dyDescent="0.25">
@@ -28053,16 +28124,16 @@
         <v>45</v>
       </c>
       <c r="D131" t="s">
-        <v>1970</v>
+        <v>1974</v>
       </c>
       <c r="E131" t="s">
-        <v>1971</v>
+        <v>1975</v>
       </c>
       <c r="F131" t="s">
-        <v>1972</v>
+        <v>1976</v>
       </c>
       <c r="G131" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J131" t="s">
         <v>22</v>
@@ -28077,16 +28148,16 @@
         <v>38</v>
       </c>
       <c r="N131" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O131" t="s">
-        <v>1973</v>
+        <v>1977</v>
       </c>
       <c r="P131" t="s">
-        <v>1974</v>
+        <v>1978</v>
       </c>
       <c r="Q131" t="s">
-        <v>1975</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="132" spans="1:17" x14ac:dyDescent="0.25">
@@ -28100,16 +28171,16 @@
         <v>40</v>
       </c>
       <c r="D132" t="s">
-        <v>1976</v>
+        <v>1980</v>
       </c>
       <c r="E132" t="s">
-        <v>1977</v>
+        <v>1981</v>
       </c>
       <c r="F132" t="s">
         <v>1085</v>
       </c>
       <c r="G132" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J132" t="s">
         <v>22</v>
@@ -28124,16 +28195,16 @@
         <v>38</v>
       </c>
       <c r="N132" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O132" t="s">
-        <v>1978</v>
+        <v>1982</v>
       </c>
       <c r="P132" t="s">
-        <v>1979</v>
+        <v>1983</v>
       </c>
       <c r="Q132" t="s">
-        <v>1980</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="133" spans="1:17" x14ac:dyDescent="0.25">
@@ -28147,16 +28218,16 @@
         <v>40</v>
       </c>
       <c r="D133" t="s">
+        <v>1985</v>
+      </c>
+      <c r="E133" t="s">
         <v>1981</v>
-      </c>
-      <c r="E133" t="s">
-        <v>1977</v>
       </c>
       <c r="F133" t="s">
         <v>1085</v>
       </c>
       <c r="G133" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J133" t="s">
         <v>22</v>
@@ -28171,16 +28242,16 @@
         <v>38</v>
       </c>
       <c r="N133" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O133" t="s">
-        <v>1982</v>
+        <v>1986</v>
       </c>
       <c r="P133" t="s">
-        <v>1983</v>
+        <v>1987</v>
       </c>
       <c r="Q133" t="s">
-        <v>1984</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="134" spans="1:17" x14ac:dyDescent="0.25">
@@ -28194,16 +28265,16 @@
         <v>18</v>
       </c>
       <c r="D134" t="s">
-        <v>1737</v>
+        <v>1741</v>
       </c>
       <c r="E134" t="s">
-        <v>1738</v>
+        <v>1742</v>
       </c>
       <c r="F134" t="s">
         <v>1016</v>
       </c>
       <c r="G134" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J134" t="s">
         <v>22</v>
@@ -28218,16 +28289,16 @@
         <v>38</v>
       </c>
       <c r="N134" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O134" t="s">
-        <v>1985</v>
+        <v>1989</v>
       </c>
       <c r="P134" t="s">
-        <v>1986</v>
+        <v>1990</v>
       </c>
       <c r="Q134" t="s">
-        <v>1987</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="135" spans="1:17" x14ac:dyDescent="0.25">
@@ -28241,16 +28312,16 @@
         <v>3</v>
       </c>
       <c r="D135" t="s">
-        <v>1746</v>
+        <v>1750</v>
       </c>
       <c r="E135" t="s">
-        <v>1738</v>
+        <v>1742</v>
       </c>
       <c r="F135" t="s">
         <v>1016</v>
       </c>
       <c r="G135" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J135" t="s">
         <v>22</v>
@@ -28265,16 +28336,16 @@
         <v>38</v>
       </c>
       <c r="N135" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O135" t="s">
-        <v>1988</v>
+        <v>1992</v>
       </c>
       <c r="P135" t="s">
-        <v>1989</v>
+        <v>1993</v>
       </c>
       <c r="Q135" t="s">
-        <v>1990</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="136" spans="1:17" x14ac:dyDescent="0.25">
@@ -28288,16 +28359,16 @@
         <v>38</v>
       </c>
       <c r="D136" t="s">
-        <v>1991</v>
+        <v>1995</v>
       </c>
       <c r="E136" t="s">
-        <v>1992</v>
+        <v>1996</v>
       </c>
       <c r="F136" t="s">
-        <v>1993</v>
+        <v>1997</v>
       </c>
       <c r="G136" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J136" t="s">
         <v>22</v>
@@ -28312,16 +28383,16 @@
         <v>38</v>
       </c>
       <c r="N136" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O136" t="s">
-        <v>1994</v>
+        <v>1998</v>
       </c>
       <c r="P136" t="s">
-        <v>1995</v>
+        <v>1999</v>
       </c>
       <c r="Q136" t="s">
-        <v>1996</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="137" spans="1:17" x14ac:dyDescent="0.25">
@@ -28335,16 +28406,16 @@
         <v>15</v>
       </c>
       <c r="D137" t="s">
-        <v>1997</v>
+        <v>2001</v>
       </c>
       <c r="E137" t="s">
-        <v>1992</v>
+        <v>1996</v>
       </c>
       <c r="F137" t="s">
-        <v>1998</v>
+        <v>2002</v>
       </c>
       <c r="G137" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J137" t="s">
         <v>22</v>
@@ -28359,16 +28430,16 @@
         <v>38</v>
       </c>
       <c r="N137" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O137" t="s">
-        <v>1999</v>
+        <v>2003</v>
       </c>
       <c r="P137" t="s">
-        <v>2000</v>
+        <v>2004</v>
       </c>
       <c r="Q137" t="s">
-        <v>2001</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.25">
@@ -28382,16 +28453,16 @@
         <v>33</v>
       </c>
       <c r="D138" t="s">
+        <v>2006</v>
+      </c>
+      <c r="E138" t="s">
+        <v>1996</v>
+      </c>
+      <c r="F138" t="s">
         <v>2002</v>
       </c>
-      <c r="E138" t="s">
-        <v>1992</v>
-      </c>
-      <c r="F138" t="s">
-        <v>1998</v>
-      </c>
       <c r="G138" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J138" t="s">
         <v>22</v>
@@ -28406,16 +28477,16 @@
         <v>38</v>
       </c>
       <c r="N138" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O138" t="s">
-        <v>2003</v>
+        <v>2007</v>
       </c>
       <c r="P138" t="s">
-        <v>2004</v>
+        <v>2008</v>
       </c>
       <c r="Q138" t="s">
-        <v>2005</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.25">
@@ -28429,16 +28500,16 @@
         <v>40</v>
       </c>
       <c r="D139" t="s">
-        <v>2006</v>
+        <v>2010</v>
       </c>
       <c r="E139" t="s">
-        <v>1992</v>
+        <v>1996</v>
       </c>
       <c r="F139" t="s">
-        <v>2007</v>
+        <v>2011</v>
       </c>
       <c r="G139" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J139" t="s">
         <v>22</v>
@@ -28453,16 +28524,16 @@
         <v>38</v>
       </c>
       <c r="N139" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O139" t="s">
-        <v>2008</v>
+        <v>2012</v>
       </c>
       <c r="P139" t="s">
-        <v>2009</v>
+        <v>2013</v>
       </c>
       <c r="Q139" t="s">
-        <v>2010</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.25">
@@ -28476,16 +28547,16 @@
         <v>38</v>
       </c>
       <c r="D140" t="s">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="E140" t="s">
-        <v>1992</v>
+        <v>1996</v>
       </c>
       <c r="F140" t="s">
-        <v>1998</v>
+        <v>2002</v>
       </c>
       <c r="G140" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J140" t="s">
         <v>22</v>
@@ -28500,16 +28571,16 @@
         <v>38</v>
       </c>
       <c r="N140" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O140" t="s">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="P140" t="s">
-        <v>2013</v>
+        <v>2017</v>
       </c>
       <c r="Q140" t="s">
-        <v>2014</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.25">
@@ -28523,16 +28594,16 @@
         <v>45</v>
       </c>
       <c r="D141" t="s">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="E141" t="s">
-        <v>1992</v>
+        <v>1996</v>
       </c>
       <c r="F141" t="s">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="G141" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J141" t="s">
         <v>22</v>
@@ -28547,16 +28618,16 @@
         <v>38</v>
       </c>
       <c r="N141" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O141" t="s">
-        <v>2017</v>
+        <v>2021</v>
       </c>
       <c r="P141" t="s">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="Q141" t="s">
-        <v>2019</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.25">
@@ -28570,16 +28641,16 @@
         <v>18</v>
       </c>
       <c r="D142" t="s">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="E142" t="s">
-        <v>1992</v>
+        <v>1996</v>
       </c>
       <c r="F142" t="s">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="G142" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J142" t="s">
         <v>22</v>
@@ -28594,16 +28665,16 @@
         <v>38</v>
       </c>
       <c r="N142" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O142" t="s">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="P142" t="s">
-        <v>2023</v>
+        <v>2027</v>
       </c>
       <c r="Q142" t="s">
-        <v>2024</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="143" spans="1:17" x14ac:dyDescent="0.25">
@@ -28617,16 +28688,16 @@
         <v>20</v>
       </c>
       <c r="D143" t="s">
-        <v>2025</v>
+        <v>2029</v>
       </c>
       <c r="E143" t="s">
-        <v>1992</v>
+        <v>1996</v>
       </c>
       <c r="F143" t="s">
-        <v>1998</v>
+        <v>2002</v>
       </c>
       <c r="G143" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J143" t="s">
         <v>22</v>
@@ -28641,16 +28712,16 @@
         <v>38</v>
       </c>
       <c r="N143" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O143" t="s">
-        <v>2026</v>
+        <v>2030</v>
       </c>
       <c r="P143" t="s">
-        <v>2027</v>
+        <v>2031</v>
       </c>
       <c r="Q143" t="s">
-        <v>2028</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="144" spans="1:17" x14ac:dyDescent="0.25">
@@ -28664,16 +28735,16 @@
         <v>60</v>
       </c>
       <c r="D144" t="s">
-        <v>2029</v>
+        <v>2033</v>
       </c>
       <c r="E144" t="s">
-        <v>1992</v>
+        <v>1996</v>
       </c>
       <c r="F144" t="s">
-        <v>2030</v>
+        <v>2034</v>
       </c>
       <c r="G144" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J144" t="s">
         <v>22</v>
@@ -28688,16 +28759,16 @@
         <v>38</v>
       </c>
       <c r="N144" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O144" t="s">
-        <v>2031</v>
+        <v>2035</v>
       </c>
       <c r="P144" t="s">
-        <v>2032</v>
+        <v>2036</v>
       </c>
       <c r="Q144" t="s">
-        <v>2033</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="145" spans="1:17" x14ac:dyDescent="0.25">
@@ -28711,16 +28782,16 @@
         <v>32</v>
       </c>
       <c r="D145" t="s">
-        <v>2034</v>
+        <v>2038</v>
       </c>
       <c r="E145" t="s">
-        <v>1992</v>
+        <v>1996</v>
       </c>
       <c r="F145" t="s">
-        <v>2007</v>
+        <v>2011</v>
       </c>
       <c r="G145" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J145" t="s">
         <v>22</v>
@@ -28735,16 +28806,16 @@
         <v>38</v>
       </c>
       <c r="N145" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O145" t="s">
-        <v>2035</v>
+        <v>2039</v>
       </c>
       <c r="P145" t="s">
-        <v>2036</v>
+        <v>2040</v>
       </c>
       <c r="Q145" t="s">
-        <v>2037</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="146" spans="1:17" x14ac:dyDescent="0.25">
@@ -28758,16 +28829,16 @@
         <v>15</v>
       </c>
       <c r="D146" t="s">
-        <v>2038</v>
+        <v>2042</v>
       </c>
       <c r="E146" t="s">
-        <v>1992</v>
+        <v>1996</v>
       </c>
       <c r="F146" t="s">
-        <v>2039</v>
+        <v>2043</v>
       </c>
       <c r="G146" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J146" t="s">
         <v>22</v>
@@ -28782,16 +28853,16 @@
         <v>38</v>
       </c>
       <c r="N146" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O146" t="s">
-        <v>2040</v>
+        <v>2044</v>
       </c>
       <c r="P146" t="s">
-        <v>2041</v>
+        <v>2045</v>
       </c>
       <c r="Q146" t="s">
-        <v>2042</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="147" spans="1:17" x14ac:dyDescent="0.25">
@@ -28808,13 +28879,13 @@
         <v>280</v>
       </c>
       <c r="E147" t="s">
-        <v>1992</v>
+        <v>1996</v>
       </c>
       <c r="F147" t="s">
-        <v>2043</v>
+        <v>2047</v>
       </c>
       <c r="G147" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J147" t="s">
         <v>22</v>
@@ -28829,16 +28900,16 @@
         <v>38</v>
       </c>
       <c r="N147" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O147" t="s">
-        <v>2044</v>
+        <v>2048</v>
       </c>
       <c r="P147" t="s">
-        <v>2045</v>
+        <v>2049</v>
       </c>
       <c r="Q147" t="s">
-        <v>2046</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="148" spans="1:17" x14ac:dyDescent="0.25">
@@ -28852,16 +28923,16 @@
         <v>20</v>
       </c>
       <c r="D148" t="s">
-        <v>2047</v>
+        <v>2051</v>
       </c>
       <c r="E148" t="s">
-        <v>1992</v>
+        <v>1996</v>
       </c>
       <c r="F148" t="s">
-        <v>2007</v>
+        <v>2011</v>
       </c>
       <c r="G148" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J148" t="s">
         <v>22</v>
@@ -28876,16 +28947,16 @@
         <v>38</v>
       </c>
       <c r="N148" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O148" t="s">
-        <v>2048</v>
+        <v>2052</v>
       </c>
       <c r="P148" t="s">
-        <v>2049</v>
+        <v>2053</v>
       </c>
       <c r="Q148" t="s">
-        <v>2050</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="149" spans="1:17" x14ac:dyDescent="0.25">
@@ -28899,16 +28970,16 @@
         <v>82</v>
       </c>
       <c r="D149" t="s">
-        <v>2051</v>
+        <v>2055</v>
       </c>
       <c r="E149" t="s">
-        <v>1992</v>
+        <v>1996</v>
       </c>
       <c r="F149" t="s">
-        <v>2052</v>
+        <v>2056</v>
       </c>
       <c r="G149" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J149" t="s">
         <v>22</v>
@@ -28923,16 +28994,16 @@
         <v>25</v>
       </c>
       <c r="N149" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O149" t="s">
-        <v>2053</v>
+        <v>2057</v>
       </c>
       <c r="P149" t="s">
-        <v>2054</v>
+        <v>2058</v>
       </c>
       <c r="Q149" t="s">
-        <v>2055</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="150" spans="1:17" x14ac:dyDescent="0.25">
@@ -28946,16 +29017,16 @@
         <v>55</v>
       </c>
       <c r="D150" t="s">
-        <v>2056</v>
+        <v>2060</v>
       </c>
       <c r="E150" t="s">
         <v>1163</v>
       </c>
       <c r="F150" t="s">
-        <v>2057</v>
+        <v>2061</v>
       </c>
       <c r="G150" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J150" t="s">
         <v>22</v>
@@ -28970,16 +29041,16 @@
         <v>38</v>
       </c>
       <c r="N150" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O150" t="s">
-        <v>2058</v>
+        <v>2062</v>
       </c>
       <c r="P150" t="s">
-        <v>2059</v>
+        <v>2063</v>
       </c>
       <c r="Q150" t="s">
-        <v>2060</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="151" spans="1:17" x14ac:dyDescent="0.25">
@@ -28993,16 +29064,16 @@
         <v>28</v>
       </c>
       <c r="D151" t="s">
-        <v>2061</v>
+        <v>2065</v>
       </c>
       <c r="E151" t="s">
         <v>1163</v>
       </c>
       <c r="F151" t="s">
-        <v>2062</v>
+        <v>2066</v>
       </c>
       <c r="G151" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J151" t="s">
         <v>22</v>
@@ -29017,16 +29088,16 @@
         <v>38</v>
       </c>
       <c r="N151" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O151" t="s">
-        <v>2063</v>
+        <v>2067</v>
       </c>
       <c r="P151" t="s">
-        <v>2064</v>
+        <v>2068</v>
       </c>
       <c r="Q151" t="s">
-        <v>2065</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="152" spans="1:17" x14ac:dyDescent="0.25">
@@ -29040,16 +29111,16 @@
         <v>7</v>
       </c>
       <c r="D152" t="s">
-        <v>2066</v>
+        <v>2070</v>
       </c>
       <c r="E152" t="s">
         <v>1163</v>
       </c>
       <c r="F152" t="s">
-        <v>2067</v>
+        <v>2071</v>
       </c>
       <c r="G152" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J152" t="s">
         <v>22</v>
@@ -29064,16 +29135,16 @@
         <v>38</v>
       </c>
       <c r="N152" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O152" t="s">
-        <v>2068</v>
+        <v>2072</v>
       </c>
       <c r="P152" t="s">
-        <v>2069</v>
+        <v>2073</v>
       </c>
       <c r="Q152" t="s">
-        <v>2070</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="153" spans="1:17" x14ac:dyDescent="0.25">
@@ -29087,16 +29158,16 @@
         <v>55</v>
       </c>
       <c r="D153" t="s">
-        <v>2071</v>
+        <v>2075</v>
       </c>
       <c r="E153" t="s">
         <v>1163</v>
       </c>
       <c r="F153" t="s">
-        <v>2072</v>
+        <v>2076</v>
       </c>
       <c r="G153" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J153" t="s">
         <v>22</v>
@@ -29111,16 +29182,16 @@
         <v>38</v>
       </c>
       <c r="N153" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O153" t="s">
-        <v>2073</v>
+        <v>2077</v>
       </c>
       <c r="P153" t="s">
-        <v>2074</v>
+        <v>2078</v>
       </c>
       <c r="Q153" t="s">
-        <v>2075</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="154" spans="1:17" x14ac:dyDescent="0.25">
@@ -29134,16 +29205,16 @@
         <v>40</v>
       </c>
       <c r="D154" t="s">
-        <v>2076</v>
+        <v>2080</v>
       </c>
       <c r="E154" t="s">
-        <v>2077</v>
+        <v>2081</v>
       </c>
       <c r="F154" t="s">
         <v>1284</v>
       </c>
       <c r="G154" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J154" t="s">
         <v>22</v>
@@ -29158,16 +29229,16 @@
         <v>38</v>
       </c>
       <c r="N154" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O154" t="s">
-        <v>2078</v>
+        <v>2082</v>
       </c>
       <c r="P154" t="s">
-        <v>2079</v>
+        <v>2083</v>
       </c>
       <c r="Q154" t="s">
-        <v>2080</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="155" spans="1:17" x14ac:dyDescent="0.25">
@@ -29181,16 +29252,16 @@
         <v>45</v>
       </c>
       <c r="D155" t="s">
-        <v>2081</v>
+        <v>2085</v>
       </c>
       <c r="E155" t="s">
         <v>1198</v>
       </c>
       <c r="F155" t="s">
-        <v>2082</v>
+        <v>2086</v>
       </c>
       <c r="G155" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J155" t="s">
         <v>22</v>
@@ -29205,16 +29276,16 @@
         <v>38</v>
       </c>
       <c r="N155" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O155" t="s">
-        <v>2083</v>
+        <v>2087</v>
       </c>
       <c r="P155" t="s">
-        <v>2084</v>
+        <v>2088</v>
       </c>
       <c r="Q155" t="s">
-        <v>2085</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="156" spans="1:17" x14ac:dyDescent="0.25">
@@ -29228,16 +29299,16 @@
         <v>38</v>
       </c>
       <c r="D156" t="s">
-        <v>2086</v>
+        <v>2090</v>
       </c>
       <c r="E156" t="s">
         <v>1198</v>
       </c>
       <c r="F156" t="s">
-        <v>2087</v>
+        <v>2091</v>
       </c>
       <c r="G156" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J156" t="s">
         <v>22</v>
@@ -29252,16 +29323,16 @@
         <v>38</v>
       </c>
       <c r="N156" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O156" t="s">
-        <v>2088</v>
+        <v>2092</v>
       </c>
       <c r="P156" t="s">
-        <v>2089</v>
+        <v>2093</v>
       </c>
       <c r="Q156" t="s">
-        <v>2090</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="157" spans="1:17" x14ac:dyDescent="0.25">
@@ -29275,16 +29346,16 @@
         <v>68</v>
       </c>
       <c r="D157" t="s">
-        <v>2091</v>
+        <v>2095</v>
       </c>
       <c r="E157" t="s">
         <v>1198</v>
       </c>
       <c r="F157" t="s">
-        <v>2092</v>
+        <v>2096</v>
       </c>
       <c r="G157" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J157" t="s">
         <v>22</v>
@@ -29299,16 +29370,16 @@
         <v>38</v>
       </c>
       <c r="N157" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O157" t="s">
-        <v>2093</v>
+        <v>2097</v>
       </c>
       <c r="P157" t="s">
-        <v>2094</v>
+        <v>2098</v>
       </c>
       <c r="Q157" t="s">
-        <v>2095</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="158" spans="1:17" x14ac:dyDescent="0.25">
@@ -29328,10 +29399,10 @@
         <v>1198</v>
       </c>
       <c r="F158" t="s">
-        <v>2082</v>
+        <v>2086</v>
       </c>
       <c r="G158" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J158" t="s">
         <v>22</v>
@@ -29346,16 +29417,16 @@
         <v>38</v>
       </c>
       <c r="N158" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O158" t="s">
-        <v>2096</v>
+        <v>2100</v>
       </c>
       <c r="P158" t="s">
-        <v>2097</v>
+        <v>2101</v>
       </c>
       <c r="Q158" t="s">
-        <v>2098</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="159" spans="1:17" x14ac:dyDescent="0.25">
@@ -29375,10 +29446,10 @@
         <v>1198</v>
       </c>
       <c r="F159" t="s">
-        <v>2099</v>
+        <v>2103</v>
       </c>
       <c r="G159" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J159" t="s">
         <v>22</v>
@@ -29393,16 +29464,16 @@
         <v>38</v>
       </c>
       <c r="N159" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O159" t="s">
-        <v>2100</v>
+        <v>2104</v>
       </c>
       <c r="P159" t="s">
-        <v>2101</v>
+        <v>2105</v>
       </c>
       <c r="Q159" t="s">
-        <v>2102</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="160" spans="1:17" x14ac:dyDescent="0.25">
@@ -29416,16 +29487,16 @@
         <v>15</v>
       </c>
       <c r="D160" t="s">
-        <v>2103</v>
+        <v>2107</v>
       </c>
       <c r="E160" t="s">
         <v>1198</v>
       </c>
       <c r="F160" t="s">
-        <v>2082</v>
+        <v>2086</v>
       </c>
       <c r="G160" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J160" t="s">
         <v>22</v>
@@ -29440,16 +29511,16 @@
         <v>38</v>
       </c>
       <c r="N160" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O160" t="s">
-        <v>2104</v>
+        <v>2108</v>
       </c>
       <c r="P160" t="s">
-        <v>2105</v>
+        <v>2109</v>
       </c>
       <c r="Q160" t="s">
-        <v>2106</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="161" spans="1:17" x14ac:dyDescent="0.25">
@@ -29463,16 +29534,16 @@
         <v>22</v>
       </c>
       <c r="D161" t="s">
-        <v>2107</v>
+        <v>2111</v>
       </c>
       <c r="E161" t="s">
         <v>1198</v>
       </c>
       <c r="F161" t="s">
-        <v>2108</v>
+        <v>2112</v>
       </c>
       <c r="G161" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J161" t="s">
         <v>22</v>
@@ -29487,16 +29558,16 @@
         <v>38</v>
       </c>
       <c r="N161" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O161" t="s">
-        <v>2109</v>
+        <v>2113</v>
       </c>
       <c r="P161" t="s">
-        <v>2110</v>
+        <v>2114</v>
       </c>
       <c r="Q161" t="s">
-        <v>2111</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="162" spans="1:17" x14ac:dyDescent="0.25">
@@ -29510,7 +29581,7 @@
         <v>25</v>
       </c>
       <c r="D162" t="s">
-        <v>2112</v>
+        <v>2116</v>
       </c>
       <c r="E162" t="s">
         <v>1207</v>
@@ -29519,7 +29590,7 @@
         <v>1208</v>
       </c>
       <c r="G162" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J162" t="s">
         <v>22</v>
@@ -29534,16 +29605,16 @@
         <v>38</v>
       </c>
       <c r="N162" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O162" t="s">
-        <v>2113</v>
+        <v>2117</v>
       </c>
       <c r="P162" t="s">
-        <v>2114</v>
+        <v>2118</v>
       </c>
       <c r="Q162" t="s">
-        <v>2115</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="163" spans="1:17" x14ac:dyDescent="0.25">
@@ -29557,16 +29628,16 @@
         <v>20</v>
       </c>
       <c r="D163" t="s">
-        <v>2116</v>
+        <v>2120</v>
       </c>
       <c r="E163" t="s">
         <v>1207</v>
       </c>
       <c r="F163" t="s">
-        <v>2117</v>
+        <v>2121</v>
       </c>
       <c r="G163" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J163" t="s">
         <v>22</v>
@@ -29581,16 +29652,16 @@
         <v>38</v>
       </c>
       <c r="N163" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O163" t="s">
-        <v>2118</v>
+        <v>2122</v>
       </c>
       <c r="P163" t="s">
-        <v>2119</v>
+        <v>2123</v>
       </c>
       <c r="Q163" t="s">
-        <v>2120</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="164" spans="1:17" x14ac:dyDescent="0.25">
@@ -29604,16 +29675,16 @@
         <v>12</v>
       </c>
       <c r="D164" t="s">
-        <v>2121</v>
+        <v>2125</v>
       </c>
       <c r="E164" t="s">
         <v>1207</v>
       </c>
       <c r="F164" t="s">
-        <v>2122</v>
+        <v>2126</v>
       </c>
       <c r="G164" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J164" t="s">
         <v>22</v>
@@ -29628,16 +29699,16 @@
         <v>38</v>
       </c>
       <c r="N164" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O164" t="s">
-        <v>2123</v>
+        <v>2127</v>
       </c>
       <c r="P164" t="s">
-        <v>2124</v>
+        <v>2128</v>
       </c>
       <c r="Q164" t="s">
-        <v>2125</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="165" spans="1:17" x14ac:dyDescent="0.25">
@@ -29651,16 +29722,16 @@
         <v>15</v>
       </c>
       <c r="D165" t="s">
-        <v>2126</v>
+        <v>2130</v>
       </c>
       <c r="E165" t="s">
         <v>1207</v>
       </c>
       <c r="F165" t="s">
-        <v>2127</v>
+        <v>2131</v>
       </c>
       <c r="G165" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J165" t="s">
         <v>22</v>
@@ -29675,16 +29746,16 @@
         <v>38</v>
       </c>
       <c r="N165" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O165" t="s">
-        <v>2128</v>
+        <v>2132</v>
       </c>
       <c r="P165" t="s">
-        <v>2129</v>
+        <v>2133</v>
       </c>
       <c r="Q165" t="s">
-        <v>2130</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="166" spans="1:17" x14ac:dyDescent="0.25">
@@ -29698,16 +29769,16 @@
         <v>35</v>
       </c>
       <c r="D166" t="s">
-        <v>2131</v>
+        <v>2135</v>
       </c>
       <c r="E166" t="s">
         <v>1207</v>
       </c>
       <c r="F166" t="s">
-        <v>2132</v>
+        <v>2136</v>
       </c>
       <c r="G166" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J166" t="s">
         <v>22</v>
@@ -29722,16 +29793,16 @@
         <v>38</v>
       </c>
       <c r="N166" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O166" t="s">
-        <v>2133</v>
+        <v>2137</v>
       </c>
       <c r="P166" t="s">
-        <v>2134</v>
+        <v>2138</v>
       </c>
       <c r="Q166" t="s">
-        <v>2135</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="167" spans="1:17" x14ac:dyDescent="0.25">
@@ -29745,16 +29816,16 @@
         <v>20</v>
       </c>
       <c r="D167" t="s">
-        <v>2136</v>
+        <v>2140</v>
       </c>
       <c r="E167" t="s">
         <v>1207</v>
       </c>
       <c r="F167" t="s">
-        <v>2127</v>
+        <v>2131</v>
       </c>
       <c r="G167" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J167" t="s">
         <v>22</v>
@@ -29769,16 +29840,16 @@
         <v>38</v>
       </c>
       <c r="N167" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O167" t="s">
-        <v>2137</v>
+        <v>2141</v>
       </c>
       <c r="P167" t="s">
-        <v>2138</v>
+        <v>2142</v>
       </c>
       <c r="Q167" t="s">
-        <v>2139</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="168" spans="1:17" x14ac:dyDescent="0.25">
@@ -29792,16 +29863,16 @@
         <v>15</v>
       </c>
       <c r="D168" t="s">
-        <v>2140</v>
+        <v>2144</v>
       </c>
       <c r="E168" t="s">
         <v>1207</v>
       </c>
       <c r="F168" t="s">
-        <v>2141</v>
+        <v>2145</v>
       </c>
       <c r="G168" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J168" t="s">
         <v>22</v>
@@ -29816,16 +29887,16 @@
         <v>38</v>
       </c>
       <c r="N168" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O168" t="s">
-        <v>2142</v>
+        <v>2146</v>
       </c>
       <c r="P168" t="s">
-        <v>2143</v>
+        <v>2147</v>
       </c>
       <c r="Q168" t="s">
-        <v>2144</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="169" spans="1:17" x14ac:dyDescent="0.25">
@@ -29839,16 +29910,16 @@
         <v>45</v>
       </c>
       <c r="D169" t="s">
-        <v>2145</v>
+        <v>2149</v>
       </c>
       <c r="E169" t="s">
         <v>1207</v>
       </c>
       <c r="F169" t="s">
-        <v>2127</v>
+        <v>2131</v>
       </c>
       <c r="G169" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J169" t="s">
         <v>22</v>
@@ -29863,16 +29934,16 @@
         <v>38</v>
       </c>
       <c r="N169" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O169" t="s">
-        <v>2146</v>
+        <v>2150</v>
       </c>
       <c r="P169" t="s">
-        <v>2147</v>
+        <v>2151</v>
       </c>
       <c r="Q169" t="s">
-        <v>2148</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="170" spans="1:17" x14ac:dyDescent="0.25">
@@ -29886,16 +29957,16 @@
         <v>40</v>
       </c>
       <c r="D170" t="s">
-        <v>2149</v>
+        <v>2153</v>
       </c>
       <c r="E170" t="s">
         <v>1207</v>
       </c>
       <c r="F170" t="s">
-        <v>2150</v>
+        <v>2154</v>
       </c>
       <c r="G170" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J170" t="s">
         <v>22</v>
@@ -29910,16 +29981,16 @@
         <v>38</v>
       </c>
       <c r="N170" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O170" t="s">
-        <v>2151</v>
+        <v>2155</v>
       </c>
       <c r="P170" t="s">
-        <v>2152</v>
+        <v>2156</v>
       </c>
       <c r="Q170" t="s">
-        <v>2153</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="171" spans="1:17" x14ac:dyDescent="0.25">
@@ -29933,16 +30004,16 @@
         <v>60</v>
       </c>
       <c r="D171" t="s">
-        <v>2154</v>
+        <v>2158</v>
       </c>
       <c r="E171" t="s">
         <v>1207</v>
       </c>
       <c r="F171" t="s">
-        <v>2155</v>
+        <v>2159</v>
       </c>
       <c r="G171" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J171" t="s">
         <v>22</v>
@@ -29957,16 +30028,16 @@
         <v>38</v>
       </c>
       <c r="N171" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O171" t="s">
-        <v>2156</v>
+        <v>2160</v>
       </c>
       <c r="P171" t="s">
-        <v>2157</v>
+        <v>2161</v>
       </c>
       <c r="Q171" t="s">
-        <v>2158</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="172" spans="1:17" x14ac:dyDescent="0.25">
@@ -29980,16 +30051,16 @@
         <v>18</v>
       </c>
       <c r="D172" t="s">
-        <v>2159</v>
+        <v>2163</v>
       </c>
       <c r="E172" t="s">
         <v>1207</v>
       </c>
       <c r="F172" t="s">
-        <v>2155</v>
+        <v>2159</v>
       </c>
       <c r="G172" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J172" t="s">
         <v>22</v>
@@ -30004,16 +30075,16 @@
         <v>38</v>
       </c>
       <c r="N172" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O172" t="s">
-        <v>2160</v>
+        <v>2164</v>
       </c>
       <c r="P172" t="s">
-        <v>2161</v>
+        <v>2165</v>
       </c>
       <c r="Q172" t="s">
-        <v>2162</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="173" spans="1:17" x14ac:dyDescent="0.25">
@@ -30027,7 +30098,7 @@
         <v>12</v>
       </c>
       <c r="D173" t="s">
-        <v>2163</v>
+        <v>2167</v>
       </c>
       <c r="E173" t="s">
         <v>1207</v>
@@ -30036,7 +30107,7 @@
         <v>1208</v>
       </c>
       <c r="G173" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J173" t="s">
         <v>22</v>
@@ -30051,16 +30122,16 @@
         <v>38</v>
       </c>
       <c r="N173" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O173" t="s">
-        <v>2164</v>
+        <v>2168</v>
       </c>
       <c r="P173" t="s">
-        <v>2165</v>
+        <v>2169</v>
       </c>
       <c r="Q173" t="s">
-        <v>2166</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="174" spans="1:17" x14ac:dyDescent="0.25">
@@ -30074,7 +30145,7 @@
         <v>12</v>
       </c>
       <c r="D174" t="s">
-        <v>2167</v>
+        <v>2171</v>
       </c>
       <c r="E174" t="s">
         <v>1207</v>
@@ -30083,7 +30154,7 @@
         <v>1208</v>
       </c>
       <c r="G174" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J174" t="s">
         <v>22</v>
@@ -30098,16 +30169,16 @@
         <v>38</v>
       </c>
       <c r="N174" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O174" t="s">
-        <v>2168</v>
+        <v>2172</v>
       </c>
       <c r="P174" t="s">
-        <v>2169</v>
+        <v>2173</v>
       </c>
       <c r="Q174" t="s">
-        <v>2170</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="175" spans="1:17" x14ac:dyDescent="0.25">
@@ -30121,16 +30192,16 @@
         <v>10</v>
       </c>
       <c r="D175" t="s">
-        <v>2171</v>
+        <v>2175</v>
       </c>
       <c r="E175" t="s">
         <v>1207</v>
       </c>
       <c r="F175" t="s">
-        <v>2127</v>
+        <v>2131</v>
       </c>
       <c r="G175" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J175" t="s">
         <v>22</v>
@@ -30145,16 +30216,16 @@
         <v>38</v>
       </c>
       <c r="N175" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O175" t="s">
-        <v>2172</v>
+        <v>2176</v>
       </c>
       <c r="P175" t="s">
-        <v>2173</v>
+        <v>2177</v>
       </c>
       <c r="Q175" t="s">
-        <v>2174</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="176" spans="1:17" x14ac:dyDescent="0.25">
@@ -30168,16 +30239,16 @@
         <v>15</v>
       </c>
       <c r="D176" t="s">
-        <v>2175</v>
+        <v>2179</v>
       </c>
       <c r="E176" t="s">
         <v>1240</v>
       </c>
       <c r="F176" t="s">
-        <v>2176</v>
+        <v>2180</v>
       </c>
       <c r="G176" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="H176">
         <v>201300</v>
@@ -30198,16 +30269,16 @@
         <v>38</v>
       </c>
       <c r="N176" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O176" t="s">
-        <v>2177</v>
+        <v>2181</v>
       </c>
       <c r="P176" t="s">
-        <v>2178</v>
+        <v>2182</v>
       </c>
       <c r="Q176" t="s">
-        <v>2179</v>
+        <v>2183</v>
       </c>
     </row>
     <row r="177" spans="1:17" x14ac:dyDescent="0.25">
@@ -30221,16 +30292,16 @@
         <v>15</v>
       </c>
       <c r="D177" t="s">
-        <v>2180</v>
+        <v>2184</v>
       </c>
       <c r="E177" t="s">
         <v>1240</v>
       </c>
       <c r="F177" t="s">
-        <v>2176</v>
+        <v>2180</v>
       </c>
       <c r="G177" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="H177">
         <v>201300</v>
@@ -30251,16 +30322,16 @@
         <v>38</v>
       </c>
       <c r="N177" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O177" t="s">
-        <v>2181</v>
+        <v>2185</v>
       </c>
       <c r="P177" t="s">
-        <v>2182</v>
+        <v>2186</v>
       </c>
       <c r="Q177" t="s">
-        <v>2183</v>
+        <v>2187</v>
       </c>
     </row>
     <row r="178" spans="1:17" x14ac:dyDescent="0.25">
@@ -30274,7 +30345,7 @@
         <v>20</v>
       </c>
       <c r="D178" t="s">
-        <v>2184</v>
+        <v>2188</v>
       </c>
       <c r="E178" t="s">
         <v>1240</v>
@@ -30283,7 +30354,7 @@
         <v>1284</v>
       </c>
       <c r="G178" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J178" t="s">
         <v>22</v>
@@ -30298,16 +30369,16 @@
         <v>38</v>
       </c>
       <c r="N178" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O178" t="s">
-        <v>2185</v>
+        <v>2189</v>
       </c>
       <c r="P178" t="s">
-        <v>2186</v>
+        <v>2190</v>
       </c>
       <c r="Q178" t="s">
-        <v>2187</v>
+        <v>2191</v>
       </c>
     </row>
     <row r="179" spans="1:17" x14ac:dyDescent="0.25">
@@ -30330,7 +30401,7 @@
         <v>1274</v>
       </c>
       <c r="G179" t="s">
-        <v>2188</v>
+        <v>2192</v>
       </c>
       <c r="J179" t="s">
         <v>22</v>
@@ -30345,16 +30416,16 @@
         <v>25</v>
       </c>
       <c r="N179" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O179" t="s">
-        <v>2189</v>
+        <v>2193</v>
       </c>
       <c r="P179" t="s">
-        <v>2190</v>
+        <v>2194</v>
       </c>
       <c r="Q179" t="s">
-        <v>2191</v>
+        <v>2195</v>
       </c>
     </row>
     <row r="180" spans="1:17" x14ac:dyDescent="0.25">
@@ -30368,16 +30439,16 @@
         <v>40</v>
       </c>
       <c r="D180" t="s">
-        <v>2107</v>
+        <v>2111</v>
       </c>
       <c r="E180" t="s">
         <v>1289</v>
       </c>
       <c r="F180" t="s">
-        <v>2192</v>
+        <v>2196</v>
       </c>
       <c r="G180" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J180" t="s">
         <v>22</v>
@@ -30392,16 +30463,16 @@
         <v>38</v>
       </c>
       <c r="N180" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O180" t="s">
-        <v>2193</v>
+        <v>2197</v>
       </c>
       <c r="P180" t="s">
-        <v>2194</v>
+        <v>2198</v>
       </c>
       <c r="Q180" t="s">
-        <v>2195</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="181" spans="1:17" x14ac:dyDescent="0.25">
@@ -30415,16 +30486,16 @@
         <v>38</v>
       </c>
       <c r="D181" t="s">
-        <v>2196</v>
+        <v>2200</v>
       </c>
       <c r="E181" t="s">
         <v>1289</v>
       </c>
       <c r="F181" t="s">
-        <v>2197</v>
+        <v>2201</v>
       </c>
       <c r="G181" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J181" t="s">
         <v>22</v>
@@ -30439,16 +30510,16 @@
         <v>38</v>
       </c>
       <c r="N181" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O181" t="s">
-        <v>2198</v>
+        <v>2202</v>
       </c>
       <c r="P181" t="s">
-        <v>2199</v>
+        <v>2203</v>
       </c>
       <c r="Q181" t="s">
-        <v>2200</v>
+        <v>2204</v>
       </c>
     </row>
     <row r="182" spans="1:17" x14ac:dyDescent="0.25">
@@ -30462,16 +30533,16 @@
         <v>28</v>
       </c>
       <c r="D182" t="s">
-        <v>2201</v>
+        <v>2205</v>
       </c>
       <c r="E182" t="s">
         <v>1289</v>
       </c>
       <c r="F182" t="s">
-        <v>2202</v>
+        <v>2206</v>
       </c>
       <c r="G182" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J182" t="s">
         <v>22</v>
@@ -30486,16 +30557,16 @@
         <v>38</v>
       </c>
       <c r="N182" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O182" t="s">
-        <v>2203</v>
+        <v>2207</v>
       </c>
       <c r="P182" t="s">
-        <v>2204</v>
+        <v>2208</v>
       </c>
       <c r="Q182" t="s">
-        <v>2205</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="183" spans="1:17" x14ac:dyDescent="0.25">
@@ -30509,16 +30580,16 @@
         <v>25</v>
       </c>
       <c r="D183" t="s">
-        <v>2206</v>
+        <v>2210</v>
       </c>
       <c r="E183" t="s">
         <v>1289</v>
       </c>
       <c r="F183" t="s">
-        <v>2207</v>
+        <v>2211</v>
       </c>
       <c r="G183" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J183" t="s">
         <v>22</v>
@@ -30533,16 +30604,16 @@
         <v>38</v>
       </c>
       <c r="N183" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O183" t="s">
-        <v>2208</v>
+        <v>2212</v>
       </c>
       <c r="P183" t="s">
-        <v>2209</v>
+        <v>2213</v>
       </c>
       <c r="Q183" t="s">
-        <v>2210</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="184" spans="1:17" x14ac:dyDescent="0.25">
@@ -30556,16 +30627,16 @@
         <v>40</v>
       </c>
       <c r="D184" t="s">
-        <v>2211</v>
+        <v>2215</v>
       </c>
       <c r="E184" t="s">
         <v>1289</v>
       </c>
       <c r="F184" t="s">
-        <v>2207</v>
+        <v>2211</v>
       </c>
       <c r="G184" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J184" t="s">
         <v>22</v>
@@ -30580,16 +30651,16 @@
         <v>38</v>
       </c>
       <c r="N184" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O184" t="s">
-        <v>2212</v>
+        <v>2216</v>
       </c>
       <c r="P184" t="s">
-        <v>2213</v>
+        <v>2217</v>
       </c>
       <c r="Q184" t="s">
-        <v>2214</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="185" spans="1:17" x14ac:dyDescent="0.25">
@@ -30609,10 +30680,10 @@
         <v>1289</v>
       </c>
       <c r="F185" t="s">
-        <v>2215</v>
+        <v>2219</v>
       </c>
       <c r="G185" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J185" t="s">
         <v>22</v>
@@ -30627,16 +30698,16 @@
         <v>38</v>
       </c>
       <c r="N185" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O185" t="s">
-        <v>2216</v>
+        <v>2220</v>
       </c>
       <c r="P185" t="s">
-        <v>2217</v>
+        <v>2221</v>
       </c>
       <c r="Q185" t="s">
-        <v>2218</v>
+        <v>2222</v>
       </c>
     </row>
     <row r="186" spans="1:17" x14ac:dyDescent="0.25">
@@ -30650,16 +30721,16 @@
         <v>18</v>
       </c>
       <c r="D186" t="s">
-        <v>2219</v>
+        <v>2223</v>
       </c>
       <c r="E186" t="s">
         <v>1289</v>
       </c>
       <c r="F186" t="s">
-        <v>2192</v>
+        <v>2196</v>
       </c>
       <c r="G186" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J186" t="s">
         <v>22</v>
@@ -30674,16 +30745,16 @@
         <v>38</v>
       </c>
       <c r="N186" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O186" t="s">
-        <v>2220</v>
+        <v>2224</v>
       </c>
       <c r="P186" t="s">
-        <v>2221</v>
+        <v>2225</v>
       </c>
       <c r="Q186" t="s">
-        <v>2222</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="187" spans="1:17" x14ac:dyDescent="0.25">
@@ -30697,16 +30768,16 @@
         <v>20</v>
       </c>
       <c r="D187" t="s">
-        <v>2223</v>
+        <v>2227</v>
       </c>
       <c r="E187" t="s">
         <v>1289</v>
       </c>
       <c r="F187" t="s">
-        <v>2224</v>
+        <v>2228</v>
       </c>
       <c r="G187" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J187" t="s">
         <v>22</v>
@@ -30721,16 +30792,16 @@
         <v>38</v>
       </c>
       <c r="N187" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O187" t="s">
-        <v>2225</v>
+        <v>2229</v>
       </c>
       <c r="P187" t="s">
-        <v>2226</v>
+        <v>2230</v>
       </c>
       <c r="Q187" t="s">
-        <v>2227</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="188" spans="1:17" x14ac:dyDescent="0.25">
@@ -30744,16 +30815,16 @@
         <v>45</v>
       </c>
       <c r="D188" t="s">
-        <v>2228</v>
+        <v>2232</v>
       </c>
       <c r="E188" t="s">
         <v>1289</v>
       </c>
       <c r="F188" t="s">
-        <v>2229</v>
+        <v>2233</v>
       </c>
       <c r="G188" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J188" t="s">
         <v>22</v>
@@ -30768,16 +30839,16 @@
         <v>25</v>
       </c>
       <c r="N188" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O188" t="s">
-        <v>2230</v>
+        <v>2234</v>
       </c>
       <c r="P188" t="s">
-        <v>2231</v>
+        <v>2235</v>
       </c>
       <c r="Q188" t="s">
-        <v>2232</v>
+        <v>2236</v>
       </c>
     </row>
     <row r="189" spans="1:17" x14ac:dyDescent="0.25">
@@ -30791,16 +30862,16 @@
         <v>15</v>
       </c>
       <c r="D189" t="s">
-        <v>2233</v>
+        <v>2237</v>
       </c>
       <c r="E189" t="s">
-        <v>2234</v>
+        <v>2238</v>
       </c>
       <c r="F189" t="s">
-        <v>2235</v>
+        <v>2239</v>
       </c>
       <c r="G189" t="s">
-        <v>2188</v>
+        <v>2192</v>
       </c>
       <c r="J189" t="s">
         <v>22</v>
@@ -30815,16 +30886,16 @@
         <v>38</v>
       </c>
       <c r="N189" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O189" t="s">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="P189" t="s">
-        <v>2237</v>
+        <v>2241</v>
       </c>
       <c r="Q189" t="s">
-        <v>2238</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="190" spans="1:17" x14ac:dyDescent="0.25">
@@ -30838,16 +30909,16 @@
         <v>25</v>
       </c>
       <c r="D190" t="s">
-        <v>2239</v>
+        <v>2243</v>
       </c>
       <c r="E190" t="s">
-        <v>2234</v>
+        <v>2238</v>
       </c>
       <c r="F190" t="s">
-        <v>2240</v>
+        <v>2244</v>
       </c>
       <c r="G190" t="s">
-        <v>2188</v>
+        <v>2192</v>
       </c>
       <c r="J190" t="s">
         <v>22</v>
@@ -30862,16 +30933,16 @@
         <v>38</v>
       </c>
       <c r="N190" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O190" t="s">
-        <v>2241</v>
+        <v>2245</v>
       </c>
       <c r="P190" t="s">
-        <v>2242</v>
+        <v>2246</v>
       </c>
       <c r="Q190" t="s">
-        <v>2243</v>
+        <v>2247</v>
       </c>
     </row>
     <row r="191" spans="1:17" x14ac:dyDescent="0.25">
@@ -30885,16 +30956,16 @@
         <v>10</v>
       </c>
       <c r="D191" t="s">
-        <v>2244</v>
+        <v>2248</v>
       </c>
       <c r="E191" t="s">
-        <v>2234</v>
+        <v>2238</v>
       </c>
       <c r="F191" t="s">
-        <v>2245</v>
+        <v>2249</v>
       </c>
       <c r="G191" t="s">
-        <v>2188</v>
+        <v>2192</v>
       </c>
       <c r="J191" t="s">
         <v>22</v>
@@ -30909,16 +30980,16 @@
         <v>38</v>
       </c>
       <c r="N191" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O191" t="s">
-        <v>2246</v>
+        <v>2250</v>
       </c>
       <c r="P191" t="s">
-        <v>2247</v>
+        <v>2251</v>
       </c>
       <c r="Q191" t="s">
-        <v>2248</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="192" spans="1:17" x14ac:dyDescent="0.25">
@@ -30932,16 +31003,16 @@
         <v>8</v>
       </c>
       <c r="D192" t="s">
-        <v>2249</v>
+        <v>2253</v>
       </c>
       <c r="E192" t="s">
-        <v>2234</v>
+        <v>2238</v>
       </c>
       <c r="F192" t="s">
-        <v>2250</v>
+        <v>2254</v>
       </c>
       <c r="G192" t="s">
-        <v>2188</v>
+        <v>2192</v>
       </c>
       <c r="J192" t="s">
         <v>22</v>
@@ -30956,16 +31027,16 @@
         <v>38</v>
       </c>
       <c r="N192" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O192" t="s">
-        <v>2251</v>
+        <v>2255</v>
       </c>
       <c r="P192" t="s">
-        <v>2252</v>
+        <v>2256</v>
       </c>
       <c r="Q192" t="s">
-        <v>2253</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="193" spans="1:17" x14ac:dyDescent="0.25">
@@ -30982,13 +31053,13 @@
         <v>174</v>
       </c>
       <c r="E193" t="s">
-        <v>2254</v>
+        <v>2258</v>
       </c>
       <c r="F193" t="s">
-        <v>2255</v>
+        <v>2259</v>
       </c>
       <c r="G193" t="s">
-        <v>2188</v>
+        <v>2192</v>
       </c>
       <c r="J193" t="s">
         <v>22</v>
@@ -31003,16 +31074,16 @@
         <v>32</v>
       </c>
       <c r="N193" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O193" t="s">
-        <v>2256</v>
+        <v>2260</v>
       </c>
       <c r="P193" t="s">
-        <v>2257</v>
+        <v>2261</v>
       </c>
       <c r="Q193" t="s">
-        <v>2258</v>
+        <v>2262</v>
       </c>
     </row>
     <row r="194" spans="1:17" x14ac:dyDescent="0.25">
@@ -31026,16 +31097,16 @@
         <v>45</v>
       </c>
       <c r="D194" t="s">
-        <v>2259</v>
+        <v>2263</v>
       </c>
       <c r="E194" t="s">
-        <v>2254</v>
+        <v>2258</v>
       </c>
       <c r="F194" t="s">
-        <v>2260</v>
+        <v>2264</v>
       </c>
       <c r="G194" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J194" t="s">
         <v>22</v>
@@ -31050,16 +31121,16 @@
         <v>38</v>
       </c>
       <c r="N194" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O194" t="s">
-        <v>2261</v>
+        <v>2265</v>
       </c>
       <c r="P194" t="s">
-        <v>2262</v>
+        <v>2266</v>
       </c>
       <c r="Q194" t="s">
-        <v>2263</v>
+        <v>2267</v>
       </c>
     </row>
     <row r="195" spans="1:17" x14ac:dyDescent="0.25">
@@ -31073,16 +31144,16 @@
         <v>30</v>
       </c>
       <c r="D195" t="s">
-        <v>2264</v>
+        <v>2268</v>
       </c>
       <c r="E195" t="s">
-        <v>2254</v>
+        <v>2258</v>
       </c>
       <c r="F195" t="s">
-        <v>2255</v>
+        <v>2259</v>
       </c>
       <c r="G195" t="s">
-        <v>2188</v>
+        <v>2192</v>
       </c>
       <c r="J195" t="s">
         <v>22</v>
@@ -31097,16 +31168,16 @@
         <v>38</v>
       </c>
       <c r="N195" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O195" t="s">
-        <v>2265</v>
+        <v>2269</v>
       </c>
       <c r="P195" t="s">
-        <v>2266</v>
+        <v>2270</v>
       </c>
       <c r="Q195" t="s">
-        <v>2267</v>
+        <v>2271</v>
       </c>
     </row>
     <row r="196" spans="1:17" x14ac:dyDescent="0.25">
@@ -31120,16 +31191,16 @@
         <v>78</v>
       </c>
       <c r="D196" t="s">
-        <v>2268</v>
+        <v>2272</v>
       </c>
       <c r="E196" t="s">
-        <v>2254</v>
+        <v>2258</v>
       </c>
       <c r="F196" t="s">
-        <v>2255</v>
+        <v>2259</v>
       </c>
       <c r="G196" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J196" t="s">
         <v>22</v>
@@ -31144,16 +31215,16 @@
         <v>32</v>
       </c>
       <c r="N196" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O196" t="s">
-        <v>2269</v>
+        <v>2273</v>
       </c>
       <c r="P196" t="s">
-        <v>2270</v>
+        <v>2274</v>
       </c>
       <c r="Q196" t="s">
-        <v>2271</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="197" spans="1:17" x14ac:dyDescent="0.25">
@@ -31167,16 +31238,16 @@
         <v>70</v>
       </c>
       <c r="D197" t="s">
-        <v>2272</v>
+        <v>2276</v>
       </c>
       <c r="E197" t="s">
-        <v>2273</v>
+        <v>2277</v>
       </c>
       <c r="F197" t="s">
-        <v>2274</v>
+        <v>2278</v>
       </c>
       <c r="G197" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J197" t="s">
         <v>22</v>
@@ -31191,16 +31262,16 @@
         <v>25</v>
       </c>
       <c r="N197" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O197" t="s">
-        <v>2275</v>
+        <v>2279</v>
       </c>
       <c r="P197" t="s">
-        <v>2276</v>
+        <v>2280</v>
       </c>
       <c r="Q197" t="s">
-        <v>2277</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="198" spans="1:17" x14ac:dyDescent="0.25">
@@ -31214,16 +31285,16 @@
         <v>55</v>
       </c>
       <c r="D198" t="s">
+        <v>2282</v>
+      </c>
+      <c r="E198" t="s">
+        <v>2277</v>
+      </c>
+      <c r="F198" t="s">
         <v>2278</v>
       </c>
-      <c r="E198" t="s">
-        <v>2273</v>
-      </c>
-      <c r="F198" t="s">
-        <v>2274</v>
-      </c>
       <c r="G198" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J198" t="s">
         <v>22</v>
@@ -31238,16 +31309,16 @@
         <v>25</v>
       </c>
       <c r="N198" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O198" t="s">
-        <v>2279</v>
+        <v>2283</v>
       </c>
       <c r="P198" t="s">
-        <v>2280</v>
+        <v>2284</v>
       </c>
       <c r="Q198" t="s">
-        <v>2281</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="199" spans="1:17" x14ac:dyDescent="0.25">
@@ -31261,16 +31332,16 @@
         <v>35</v>
       </c>
       <c r="D199" t="s">
-        <v>2282</v>
+        <v>2286</v>
       </c>
       <c r="E199" t="s">
-        <v>2283</v>
+        <v>2287</v>
       </c>
       <c r="F199" t="s">
-        <v>2284</v>
+        <v>2288</v>
       </c>
       <c r="G199" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J199" t="s">
         <v>22</v>
@@ -31285,16 +31356,16 @@
         <v>38</v>
       </c>
       <c r="N199" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O199" t="s">
-        <v>2285</v>
+        <v>2289</v>
       </c>
       <c r="P199" t="s">
-        <v>2286</v>
+        <v>2290</v>
       </c>
       <c r="Q199" t="s">
-        <v>2287</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="200" spans="1:17" x14ac:dyDescent="0.25">
@@ -31308,16 +31379,16 @@
         <v>22</v>
       </c>
       <c r="D200" t="s">
-        <v>2107</v>
+        <v>2111</v>
       </c>
       <c r="E200" t="s">
-        <v>2283</v>
+        <v>2287</v>
       </c>
       <c r="F200" t="s">
-        <v>2284</v>
+        <v>2288</v>
       </c>
       <c r="G200" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J200" t="s">
         <v>22</v>
@@ -31332,16 +31403,16 @@
         <v>38</v>
       </c>
       <c r="N200" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O200" t="s">
-        <v>2288</v>
+        <v>2292</v>
       </c>
       <c r="P200" t="s">
-        <v>2289</v>
+        <v>2293</v>
       </c>
       <c r="Q200" t="s">
-        <v>2290</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="201" spans="1:17" x14ac:dyDescent="0.25">
@@ -31355,16 +31426,16 @@
         <v>42</v>
       </c>
       <c r="D201" t="s">
-        <v>2291</v>
+        <v>2295</v>
       </c>
       <c r="E201" t="s">
-        <v>2283</v>
+        <v>2287</v>
       </c>
       <c r="F201" t="s">
-        <v>2284</v>
+        <v>2288</v>
       </c>
       <c r="G201" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J201" t="s">
         <v>22</v>
@@ -31379,16 +31450,16 @@
         <v>38</v>
       </c>
       <c r="N201" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O201" t="s">
-        <v>2292</v>
+        <v>2296</v>
       </c>
       <c r="P201" t="s">
-        <v>2293</v>
+        <v>2297</v>
       </c>
       <c r="Q201" t="s">
-        <v>2294</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="202" spans="1:17" x14ac:dyDescent="0.25">
@@ -31402,16 +31473,16 @@
         <v>50</v>
       </c>
       <c r="D202" t="s">
-        <v>2295</v>
+        <v>2299</v>
       </c>
       <c r="E202" t="s">
         <v>1351</v>
       </c>
       <c r="F202" t="s">
+        <v>2196</v>
+      </c>
+      <c r="G202" t="s">
         <v>2192</v>
-      </c>
-      <c r="G202" t="s">
-        <v>2188</v>
       </c>
       <c r="H202">
         <v>150000</v>
@@ -31432,16 +31503,16 @@
         <v>25</v>
       </c>
       <c r="N202" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O202" t="s">
-        <v>2296</v>
+        <v>2300</v>
       </c>
       <c r="P202" t="s">
-        <v>2297</v>
+        <v>2301</v>
       </c>
       <c r="Q202" t="s">
-        <v>2298</v>
+        <v>2302</v>
       </c>
     </row>
     <row r="203" spans="1:17" x14ac:dyDescent="0.25">
@@ -31455,16 +31526,16 @@
         <v>35</v>
       </c>
       <c r="D203" t="s">
-        <v>2299</v>
+        <v>2303</v>
       </c>
       <c r="E203" t="s">
         <v>1351</v>
       </c>
       <c r="F203" t="s">
-        <v>2300</v>
+        <v>2304</v>
       </c>
       <c r="G203" t="s">
-        <v>2188</v>
+        <v>2192</v>
       </c>
       <c r="H203">
         <v>140000</v>
@@ -31485,16 +31556,16 @@
         <v>38</v>
       </c>
       <c r="N203" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O203" t="s">
-        <v>2301</v>
+        <v>2305</v>
       </c>
       <c r="P203" t="s">
-        <v>2302</v>
+        <v>2306</v>
       </c>
       <c r="Q203" t="s">
-        <v>2303</v>
+        <v>2307</v>
       </c>
     </row>
     <row r="204" spans="1:17" x14ac:dyDescent="0.25">
@@ -31508,16 +31579,16 @@
         <v>25</v>
       </c>
       <c r="D204" t="s">
-        <v>2304</v>
+        <v>2308</v>
       </c>
       <c r="E204" t="s">
-        <v>2305</v>
+        <v>2309</v>
       </c>
       <c r="F204" t="s">
-        <v>2306</v>
+        <v>2310</v>
       </c>
       <c r="G204" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J204" t="s">
         <v>22</v>
@@ -31532,16 +31603,16 @@
         <v>38</v>
       </c>
       <c r="N204" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O204" t="s">
-        <v>2307</v>
+        <v>2311</v>
       </c>
       <c r="P204" t="s">
-        <v>2308</v>
+        <v>2312</v>
       </c>
       <c r="Q204" t="s">
-        <v>2309</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="205" spans="1:17" x14ac:dyDescent="0.25">
@@ -31555,16 +31626,16 @@
         <v>62</v>
       </c>
       <c r="D205" t="s">
+        <v>2314</v>
+      </c>
+      <c r="E205" t="s">
+        <v>2309</v>
+      </c>
+      <c r="F205" t="s">
         <v>2310</v>
       </c>
-      <c r="E205" t="s">
-        <v>2305</v>
-      </c>
-      <c r="F205" t="s">
-        <v>2306</v>
-      </c>
       <c r="G205" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J205" t="s">
         <v>22</v>
@@ -31579,16 +31650,16 @@
         <v>25</v>
       </c>
       <c r="N205" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O205" t="s">
-        <v>2311</v>
+        <v>2315</v>
       </c>
       <c r="P205" t="s">
-        <v>2312</v>
+        <v>2316</v>
       </c>
       <c r="Q205" t="s">
-        <v>2313</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="206" spans="1:17" x14ac:dyDescent="0.25">
@@ -31602,16 +31673,16 @@
         <v>18</v>
       </c>
       <c r="D206" t="s">
-        <v>2314</v>
+        <v>2318</v>
       </c>
       <c r="E206" t="s">
-        <v>2305</v>
+        <v>2309</v>
       </c>
       <c r="F206" t="s">
-        <v>2315</v>
+        <v>2319</v>
       </c>
       <c r="G206" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J206" t="s">
         <v>22</v>
@@ -31626,16 +31697,16 @@
         <v>38</v>
       </c>
       <c r="N206" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O206" t="s">
-        <v>2316</v>
+        <v>2320</v>
       </c>
       <c r="P206" t="s">
-        <v>2317</v>
+        <v>2321</v>
       </c>
       <c r="Q206" t="s">
-        <v>2318</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="207" spans="1:17" x14ac:dyDescent="0.25">
@@ -31649,16 +31720,16 @@
         <v>45</v>
       </c>
       <c r="D207" t="s">
-        <v>2319</v>
+        <v>2323</v>
       </c>
       <c r="E207" t="s">
-        <v>2320</v>
+        <v>2324</v>
       </c>
       <c r="F207" t="s">
-        <v>2192</v>
+        <v>2196</v>
       </c>
       <c r="G207" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J207" t="s">
         <v>22</v>
@@ -31673,16 +31744,16 @@
         <v>25</v>
       </c>
       <c r="N207" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O207" t="s">
-        <v>2321</v>
+        <v>2325</v>
       </c>
       <c r="P207" t="s">
-        <v>2322</v>
+        <v>2326</v>
       </c>
       <c r="Q207" t="s">
-        <v>2323</v>
+        <v>2327</v>
       </c>
     </row>
     <row r="208" spans="1:17" x14ac:dyDescent="0.25">
@@ -31696,16 +31767,16 @@
         <v>32</v>
       </c>
       <c r="D208" t="s">
+        <v>2328</v>
+      </c>
+      <c r="E208" t="s">
         <v>2324</v>
       </c>
-      <c r="E208" t="s">
-        <v>2320</v>
-      </c>
       <c r="F208" t="s">
-        <v>2325</v>
+        <v>2329</v>
       </c>
       <c r="G208" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J208" t="s">
         <v>22</v>
@@ -31720,16 +31791,16 @@
         <v>38</v>
       </c>
       <c r="N208" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O208" t="s">
-        <v>2326</v>
+        <v>2330</v>
       </c>
       <c r="P208" t="s">
-        <v>2327</v>
+        <v>2331</v>
       </c>
       <c r="Q208" t="s">
-        <v>2328</v>
+        <v>2332</v>
       </c>
     </row>
     <row r="209" spans="1:17" x14ac:dyDescent="0.25">
@@ -31746,13 +31817,13 @@
         <v>1378</v>
       </c>
       <c r="E209" t="s">
-        <v>2320</v>
+        <v>2324</v>
       </c>
       <c r="F209" t="s">
-        <v>2325</v>
+        <v>2329</v>
       </c>
       <c r="G209" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="J209" t="s">
         <v>22</v>
@@ -31767,16 +31838,16 @@
         <v>25</v>
       </c>
       <c r="N209" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O209" t="s">
-        <v>2329</v>
+        <v>2333</v>
       </c>
       <c r="P209" t="s">
-        <v>2330</v>
+        <v>2334</v>
       </c>
       <c r="Q209" t="s">
-        <v>2331</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="210" spans="1:17" x14ac:dyDescent="0.25">
@@ -31796,10 +31867,10 @@
         <v>421</v>
       </c>
       <c r="F210" t="s">
-        <v>2332</v>
+        <v>2336</v>
       </c>
       <c r="G210" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="H210">
         <v>219100</v>
@@ -31820,16 +31891,16 @@
         <v>25</v>
       </c>
       <c r="N210" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O210" t="s">
-        <v>2333</v>
+        <v>2337</v>
       </c>
       <c r="P210" t="s">
-        <v>2334</v>
+        <v>2338</v>
       </c>
       <c r="Q210" t="s">
-        <v>2335</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="211" spans="1:17" x14ac:dyDescent="0.25">
@@ -31849,10 +31920,10 @@
         <v>421</v>
       </c>
       <c r="F211" t="s">
-        <v>2336</v>
+        <v>2340</v>
       </c>
       <c r="G211" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="H211">
         <v>180000</v>
@@ -31873,16 +31944,16 @@
         <v>25</v>
       </c>
       <c r="N211" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O211" t="s">
-        <v>2337</v>
+        <v>2341</v>
       </c>
       <c r="P211" t="s">
-        <v>2338</v>
+        <v>2342</v>
       </c>
       <c r="Q211" t="s">
-        <v>2339</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="212" spans="1:17" x14ac:dyDescent="0.25">
@@ -31902,10 +31973,10 @@
         <v>421</v>
       </c>
       <c r="F212" t="s">
-        <v>2340</v>
+        <v>2344</v>
       </c>
       <c r="G212" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="H212">
         <v>219100</v>
@@ -31926,16 +31997,16 @@
         <v>25</v>
       </c>
       <c r="N212" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O212" t="s">
-        <v>2341</v>
+        <v>2345</v>
       </c>
       <c r="P212" t="s">
-        <v>2342</v>
+        <v>2346</v>
       </c>
       <c r="Q212" t="s">
-        <v>2343</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="213" spans="1:17" x14ac:dyDescent="0.25">
@@ -31949,16 +32020,16 @@
         <v>25</v>
       </c>
       <c r="D213" t="s">
-        <v>1818</v>
+        <v>1822</v>
       </c>
       <c r="E213" t="s">
-        <v>1819</v>
+        <v>1823</v>
       </c>
       <c r="F213" t="s">
-        <v>1820</v>
+        <v>1824</v>
       </c>
       <c r="G213" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J213" t="s">
         <v>22</v>
@@ -31973,16 +32044,16 @@
         <v>38</v>
       </c>
       <c r="N213" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O213" t="s">
-        <v>2344</v>
+        <v>2348</v>
       </c>
       <c r="P213" t="s">
-        <v>2345</v>
+        <v>2349</v>
       </c>
       <c r="Q213" t="s">
-        <v>2346</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="214" spans="1:17" x14ac:dyDescent="0.25">
@@ -31996,16 +32067,16 @@
         <v>3</v>
       </c>
       <c r="D214" t="s">
+        <v>1828</v>
+      </c>
+      <c r="E214" t="s">
+        <v>1829</v>
+      </c>
+      <c r="F214" t="s">
         <v>1824</v>
       </c>
-      <c r="E214" t="s">
-        <v>1825</v>
-      </c>
-      <c r="F214" t="s">
-        <v>1820</v>
-      </c>
       <c r="G214" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="J214" t="s">
         <v>22</v>
@@ -32020,16 +32091,16 @@
         <v>38</v>
       </c>
       <c r="N214" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O214" t="s">
-        <v>2347</v>
+        <v>2351</v>
       </c>
       <c r="P214" t="s">
-        <v>2348</v>
+        <v>2352</v>
       </c>
       <c r="Q214" t="s">
-        <v>2349</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="215" spans="1:17" x14ac:dyDescent="0.25">
@@ -32043,7 +32114,7 @@
         <v>48</v>
       </c>
       <c r="D215" t="s">
-        <v>2350</v>
+        <v>2354</v>
       </c>
       <c r="E215" t="s">
         <v>1084</v>
@@ -32052,7 +32123,7 @@
         <v>1085</v>
       </c>
       <c r="G215" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="H215">
         <v>200000</v>
@@ -32073,16 +32144,63 @@
         <v>25</v>
       </c>
       <c r="N215" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="O215" t="s">
-        <v>2351</v>
+        <v>2355</v>
       </c>
       <c r="P215" t="s">
-        <v>2352</v>
+        <v>2356</v>
       </c>
       <c r="Q215" t="s">
-        <v>2353</v>
+        <v>2357</v>
+      </c>
+    </row>
+    <row r="216" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>17</v>
+      </c>
+      <c r="B216">
+        <v>33</v>
+      </c>
+      <c r="C216">
+        <v>72</v>
+      </c>
+      <c r="D216" t="s">
+        <v>2358</v>
+      </c>
+      <c r="E216" t="s">
+        <v>1920</v>
+      </c>
+      <c r="F216" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G216" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J216" t="s">
+        <v>22</v>
+      </c>
+      <c r="K216" t="s">
+        <v>557</v>
+      </c>
+      <c r="L216" t="s">
+        <v>1393</v>
+      </c>
+      <c r="M216" t="s">
+        <v>38</v>
+      </c>
+      <c r="N216" t="s">
+        <v>1399</v>
+      </c>
+      <c r="O216" t="s">
+        <v>2359</v>
+      </c>
+      <c r="P216" t="s">
+        <v>2360</v>
+      </c>
+      <c r="Q216" t="s">
+        <v>2361</v>
       </c>
     </row>
   </sheetData>

--- a/hunt/board.xlsx
+++ b/hunt/board.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6508" uniqueCount="2362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6599" uniqueCount="2392">
   <si>
     <t>Column</t>
   </si>
@@ -4205,6 +4205,51 @@
     <t>https://www.arbeitnow.com/jobs/companies/trusteq-gmbh/cloud-senior-engineer-architect-m-w-d-koln-168121</t>
   </si>
   <si>
+    <t>Delivery/DevOps Agile Lead</t>
+  </si>
+  <si>
+    <t>2026-09-07T17:03:45.558Z</t>
+  </si>
+  <si>
+    <t>Remote US role in health insurance/payer space (NASCO serves BCBS plans) — matches candidate's compliance-heavy HIPAA precedent | Explicitly wants DevOps best practices, SDLC discipline, and data-driven delivery metrics — aligns with candidate's Azure DevOps Boards/Analytics OData and DevOps maturity assessment (ITIL/Prosci) experience | Executive-level reporting and stakeholder partnering matches candidate's trusted-advisor engagement model</t>
+  </si>
+  <si>
+    <t>Role is Agile delivery leadership/people-and-process management, not cloud architecture — less use of Azure platform, GHAS, IaC depth | Hands-on software development expertise emphasized; candidate's strength is platform/DevOps tooling rather than application dev leadership | No architect-level scope or title; may sit below the principal-level scope candidate targets</t>
+  </si>
+  <si>
+    <t>https://himalayas.app/companies/nasco/jobs/delivery-devops-agile-lead</t>
+  </si>
+  <si>
+    <t>DevOps Senior</t>
+  </si>
+  <si>
+    <t>Coderio</t>
+  </si>
+  <si>
+    <t>Fully remote and DevOps-focused with CI/CD and infrastructure automation work the candidate does daily | Spanish/English bilingual consulting environment delivering for global enterprise clients</t>
+  </si>
+  <si>
+    <t>LATAM-headquartered (Argentina/Colombia/Peru) staffing model — comp typically far under $180K and US hiring uncertain | Posting is largely in Spanish and requests C1 English plus presumably Spanish working language | Senior IC DevOps engineer scope, below the principal/architect scope the candidate targets; likely AWS-leaning rather than Azure</t>
+  </si>
+  <si>
+    <t>https://weworkremotely.com/remote-jobs/coderio-devops-senior</t>
+  </si>
+  <si>
+    <t>Senior DevOps Engineer (m/f/d)</t>
+  </si>
+  <si>
+    <t>Myneva</t>
+  </si>
+  <si>
+    <t>Remote role owning deployment models, containerization, and operational architecture — overlaps candidate's CI/CD and IaC strengths | Healthcare/care-sector software (myneva) aligns with candidate's HIPAA-style compliance-driven architecture precedent | Positioned as the technical expert advising dev teams, similar to candidate's advisory engagement model</t>
+  </si>
+  <si>
+    <t>Company is Germany/Portugal-based; 'anywhere' likely means EU time zones rather than US hiring with US comp | Senior IC DevOps engineering scope (Kubernetes/containers/runtime), not architect-level cloud strategy | No indication of Azure DevOps/GitHub Enterprise/GHAS toolchain that is the candidate's differentiator</t>
+  </si>
+  <si>
+    <t>https://weworkremotely.com/remote-jobs/myneva-senior-devops-engineer-m-f-d</t>
+  </si>
+  <si>
     <t>Delivery Solutions Architect - Communications, Media, Entertainment &amp; Games</t>
   </si>
   <si>
@@ -7098,6 +7143,51 @@
   </si>
   <si>
     <t>https://www.arbeitnow.com/jobs/companies/skaylink/azure-cloud-architect-hamburg-427466</t>
+  </si>
+  <si>
+    <t>Senior Customer Success Architect</t>
+  </si>
+  <si>
+    <t>Amplitude</t>
+  </si>
+  <si>
+    <t>Customer-facing technical advisory model overlaps with candidate's Customer Engineer trusted-advisor experience | Product analytics platform work touches candidate's TypeScript/React/Next.js product development background</t>
+  </si>
+  <si>
+    <t>London-based role — outside candidate's US market scope and would require international relocation/work authorization | Focus is Amplitude product analytics/instrumentation and customer success motion, not Azure/DevOps cloud architecture | No use of candidate's core differentiators (GHAS, Azure Policy, CI/CD architecture, compliance frameworks)</t>
+  </si>
+  <si>
+    <t>https://www.arbeitnow.co.uk/jobs/companies/amplitude/senior-customer-success-architect-london-114193</t>
+  </si>
+  <si>
+    <t>Directly an Azure cloud platform architect role — matches candidate's core Azure platform, governance, and IaC skill set | Cloud Computing &amp; AI practice focus aligns with candidate's GitHub Copilot / Agentic DevOps experience | Consultancy/systems-integrator model mirrors candidate's enterprise customer advisory engagement style</t>
+  </si>
+  <si>
+    <t>Germany-based (Nuremberg/Hamburg/Münster/Berlin/Mainz/Bochum) — outside stated US market scope and requires EU work authorization | Posting is in German, implying business-fluent German is effectively required | German consultancy comp for senior architects (~€80–100K) is far below the $180K floor</t>
+  </si>
+  <si>
+    <t>https://www.arbeitnow.com/jobs/companies/think-about-it-gmbh/senior-azure-cloud-platform-architect-nuremberg-471086</t>
+  </si>
+  <si>
+    <t>Microsoft-stack cloud strategy and transformation architecture is squarely in the candidate's wheelhouse (CAF/WAF, governance, migration advisory) | Holistic cloud strategy design implies principal-level scope the candidate is targeting | Hybrid arrangement with multiple office options offers some flexibility</t>
+  </si>
+  <si>
+    <t>Nuremberg, Germany location — outside US market scope, needs EU work permit | German-language posting suggests German fluency is a practical requirement | Expected German market comp is materially below the candidate's $180K salary floor</t>
+  </si>
+  <si>
+    <t>https://www.arbeitnow.com/jobs/companies/think-about-it-gmbh/senior-microsoft-cloud-transformation-architect-nuremberg-355412</t>
+  </si>
+  <si>
+    <t>Cloud Solutions Architect  (Google Cloud)</t>
+  </si>
+  <si>
+    <t>Architecture scope is a genuine match in shape: cloud foundations, migration frameworks, CI/CD and platform engineering definition | Consulting/advisory delivery at Devoteam mirrors candidate's customer engineer trusted-advisor role</t>
+  </si>
+  <si>
+    <t>Requires GCP-primary architecture depth (end-to-end GCP designs, GCP migrations) — candidate is Azure-primary with no GCP credentials, a stated not-qualified signal | Riyadh, Saudi Arabia hybrid role — outside US market scope and requires international relocation | No Azure-equivalent acceptance signaled in the posting</t>
+  </si>
+  <si>
+    <t>https://jobs.smartrecruiters.com/Devoteam/744000147849039-cloud-solutions-architect-google-cloud-</t>
   </si>
 </sst>
 </file>
@@ -7478,7 +7568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q284"/>
+  <dimension ref="A1:Q287"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -21635,6 +21725,147 @@
         <v>1396</v>
       </c>
     </row>
+    <row r="285" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>17</v>
+      </c>
+      <c r="B285">
+        <v>63</v>
+      </c>
+      <c r="C285">
+        <v>68</v>
+      </c>
+      <c r="D285" t="s">
+        <v>1397</v>
+      </c>
+      <c r="E285" t="s">
+        <v>603</v>
+      </c>
+      <c r="F285" t="s">
+        <v>20</v>
+      </c>
+      <c r="G285" t="s">
+        <v>21</v>
+      </c>
+      <c r="J285" t="s">
+        <v>22</v>
+      </c>
+      <c r="K285" t="s">
+        <v>23</v>
+      </c>
+      <c r="L285" t="s">
+        <v>1398</v>
+      </c>
+      <c r="M285" t="s">
+        <v>32</v>
+      </c>
+      <c r="N285" t="s">
+        <v>26</v>
+      </c>
+      <c r="O285" t="s">
+        <v>1399</v>
+      </c>
+      <c r="P285" t="s">
+        <v>1400</v>
+      </c>
+      <c r="Q285" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="286" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>17</v>
+      </c>
+      <c r="B286">
+        <v>38</v>
+      </c>
+      <c r="C286">
+        <v>55</v>
+      </c>
+      <c r="D286" t="s">
+        <v>1402</v>
+      </c>
+      <c r="E286" t="s">
+        <v>1403</v>
+      </c>
+      <c r="F286" t="s">
+        <v>569</v>
+      </c>
+      <c r="G286" t="s">
+        <v>21</v>
+      </c>
+      <c r="J286" t="s">
+        <v>22</v>
+      </c>
+      <c r="K286" t="s">
+        <v>570</v>
+      </c>
+      <c r="L286" t="s">
+        <v>1398</v>
+      </c>
+      <c r="M286" t="s">
+        <v>38</v>
+      </c>
+      <c r="N286" t="s">
+        <v>26</v>
+      </c>
+      <c r="O286" t="s">
+        <v>1404</v>
+      </c>
+      <c r="P286" t="s">
+        <v>1405</v>
+      </c>
+      <c r="Q286" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="287" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>17</v>
+      </c>
+      <c r="B287">
+        <v>42</v>
+      </c>
+      <c r="C287">
+        <v>58</v>
+      </c>
+      <c r="D287" t="s">
+        <v>1407</v>
+      </c>
+      <c r="E287" t="s">
+        <v>1408</v>
+      </c>
+      <c r="F287" t="s">
+        <v>569</v>
+      </c>
+      <c r="G287" t="s">
+        <v>21</v>
+      </c>
+      <c r="J287" t="s">
+        <v>22</v>
+      </c>
+      <c r="K287" t="s">
+        <v>570</v>
+      </c>
+      <c r="L287" t="s">
+        <v>1398</v>
+      </c>
+      <c r="M287" t="s">
+        <v>25</v>
+      </c>
+      <c r="N287" t="s">
+        <v>26</v>
+      </c>
+      <c r="O287" t="s">
+        <v>1409</v>
+      </c>
+      <c r="P287" t="s">
+        <v>1410</v>
+      </c>
+      <c r="Q287" t="s">
+        <v>1411</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:Q1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -21644,7 +21875,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q216"/>
+  <dimension ref="A1:Q220"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -21725,7 +21956,7 @@
         <v>52</v>
       </c>
       <c r="D2" t="s">
-        <v>1397</v>
+        <v>1412</v>
       </c>
       <c r="E2" t="s">
         <v>421</v>
@@ -21734,7 +21965,7 @@
         <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="H2">
         <v>180000</v>
@@ -21755,16 +21986,16 @@
         <v>25</v>
       </c>
       <c r="N2" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O2" t="s">
-        <v>1400</v>
+        <v>1415</v>
       </c>
       <c r="P2" t="s">
-        <v>1401</v>
+        <v>1416</v>
       </c>
       <c r="Q2" t="s">
-        <v>1402</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -21778,7 +22009,7 @@
         <v>55</v>
       </c>
       <c r="D3" t="s">
-        <v>1403</v>
+        <v>1418</v>
       </c>
       <c r="E3" t="s">
         <v>421</v>
@@ -21787,7 +22018,7 @@
         <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="H3">
         <v>180000</v>
@@ -21808,16 +22039,16 @@
         <v>25</v>
       </c>
       <c r="N3" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O3" t="s">
-        <v>1404</v>
+        <v>1419</v>
       </c>
       <c r="P3" t="s">
-        <v>1405</v>
+        <v>1420</v>
       </c>
       <c r="Q3" t="s">
-        <v>1406</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
@@ -21831,16 +22062,16 @@
         <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>1407</v>
+        <v>1422</v>
       </c>
       <c r="E4" t="s">
         <v>421</v>
       </c>
       <c r="F4" t="s">
-        <v>1408</v>
+        <v>1423</v>
       </c>
       <c r="G4" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="H4">
         <v>219100</v>
@@ -21861,16 +22092,16 @@
         <v>25</v>
       </c>
       <c r="N4" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O4" t="s">
-        <v>1409</v>
+        <v>1424</v>
       </c>
       <c r="P4" t="s">
-        <v>1410</v>
+        <v>1425</v>
       </c>
       <c r="Q4" t="s">
-        <v>1411</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -21884,16 +22115,16 @@
         <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>1412</v>
+        <v>1427</v>
       </c>
       <c r="E5" t="s">
         <v>421</v>
       </c>
       <c r="F5" t="s">
-        <v>1413</v>
+        <v>1428</v>
       </c>
       <c r="G5" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="H5">
         <v>180000</v>
@@ -21914,16 +22145,16 @@
         <v>25</v>
       </c>
       <c r="N5" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O5" t="s">
-        <v>1415</v>
+        <v>1430</v>
       </c>
       <c r="P5" t="s">
-        <v>1416</v>
+        <v>1431</v>
       </c>
       <c r="Q5" t="s">
-        <v>1417</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -21937,7 +22168,7 @@
         <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>1418</v>
+        <v>1433</v>
       </c>
       <c r="E6" t="s">
         <v>421</v>
@@ -21946,7 +22177,7 @@
         <v>20</v>
       </c>
       <c r="G6" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="H6">
         <v>219100</v>
@@ -21967,16 +22198,16 @@
         <v>38</v>
       </c>
       <c r="N6" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O6" t="s">
-        <v>1419</v>
+        <v>1434</v>
       </c>
       <c r="P6" t="s">
-        <v>1420</v>
+        <v>1435</v>
       </c>
       <c r="Q6" t="s">
-        <v>1421</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -21990,7 +22221,7 @@
         <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>1422</v>
+        <v>1437</v>
       </c>
       <c r="E7" t="s">
         <v>421</v>
@@ -21999,7 +22230,7 @@
         <v>20</v>
       </c>
       <c r="G7" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="H7">
         <v>219100</v>
@@ -22020,16 +22251,16 @@
         <v>25</v>
       </c>
       <c r="N7" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O7" t="s">
-        <v>1423</v>
+        <v>1438</v>
       </c>
       <c r="P7" t="s">
-        <v>1424</v>
+        <v>1439</v>
       </c>
       <c r="Q7" t="s">
-        <v>1425</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -22043,16 +22274,16 @@
         <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>1426</v>
+        <v>1441</v>
       </c>
       <c r="E8" t="s">
         <v>421</v>
       </c>
       <c r="F8" t="s">
-        <v>1427</v>
+        <v>1442</v>
       </c>
       <c r="G8" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J8" t="s">
         <v>22</v>
@@ -22067,16 +22298,16 @@
         <v>38</v>
       </c>
       <c r="N8" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O8" t="s">
-        <v>1428</v>
+        <v>1443</v>
       </c>
       <c r="P8" t="s">
-        <v>1429</v>
+        <v>1444</v>
       </c>
       <c r="Q8" t="s">
-        <v>1430</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -22090,16 +22321,16 @@
         <v>58</v>
       </c>
       <c r="D9" t="s">
-        <v>1431</v>
+        <v>1446</v>
       </c>
       <c r="E9" t="s">
-        <v>1432</v>
+        <v>1447</v>
       </c>
       <c r="F9" t="s">
-        <v>1433</v>
+        <v>1448</v>
       </c>
       <c r="G9" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="H9">
         <v>257000</v>
@@ -22120,16 +22351,16 @@
         <v>25</v>
       </c>
       <c r="N9" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O9" t="s">
-        <v>1434</v>
+        <v>1449</v>
       </c>
       <c r="P9" t="s">
-        <v>1435</v>
+        <v>1450</v>
       </c>
       <c r="Q9" t="s">
-        <v>1436</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -22146,13 +22377,13 @@
         <v>145</v>
       </c>
       <c r="E10" t="s">
-        <v>1437</v>
+        <v>1452</v>
       </c>
       <c r="F10" t="s">
-        <v>1438</v>
+        <v>1453</v>
       </c>
       <c r="G10" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="H10">
         <v>200000</v>
@@ -22173,16 +22404,16 @@
         <v>38</v>
       </c>
       <c r="N10" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O10" t="s">
-        <v>1439</v>
+        <v>1454</v>
       </c>
       <c r="P10" t="s">
-        <v>1440</v>
+        <v>1455</v>
       </c>
       <c r="Q10" t="s">
-        <v>1441</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -22196,16 +22427,16 @@
         <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>1442</v>
+        <v>1457</v>
       </c>
       <c r="E11" t="s">
         <v>698</v>
       </c>
       <c r="F11" t="s">
-        <v>1443</v>
+        <v>1458</v>
       </c>
       <c r="G11" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J11" t="s">
         <v>22</v>
@@ -22220,16 +22451,16 @@
         <v>38</v>
       </c>
       <c r="N11" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O11" t="s">
-        <v>1444</v>
+        <v>1459</v>
       </c>
       <c r="P11" t="s">
-        <v>1445</v>
+        <v>1460</v>
       </c>
       <c r="Q11" t="s">
-        <v>1446</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -22249,10 +22480,10 @@
         <v>698</v>
       </c>
       <c r="F12" t="s">
-        <v>1447</v>
+        <v>1462</v>
       </c>
       <c r="G12" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J12" t="s">
         <v>22</v>
@@ -22267,16 +22498,16 @@
         <v>38</v>
       </c>
       <c r="N12" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O12" t="s">
-        <v>1448</v>
+        <v>1463</v>
       </c>
       <c r="P12" t="s">
-        <v>1449</v>
+        <v>1464</v>
       </c>
       <c r="Q12" t="s">
-        <v>1450</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
@@ -22290,16 +22521,16 @@
         <v>15</v>
       </c>
       <c r="D13" t="s">
-        <v>1451</v>
+        <v>1466</v>
       </c>
       <c r="E13" t="s">
         <v>698</v>
       </c>
       <c r="F13" t="s">
-        <v>1452</v>
+        <v>1467</v>
       </c>
       <c r="G13" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="H13">
         <v>500000</v>
@@ -22320,16 +22551,16 @@
         <v>38</v>
       </c>
       <c r="N13" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O13" t="s">
-        <v>1453</v>
+        <v>1468</v>
       </c>
       <c r="P13" t="s">
-        <v>1454</v>
+        <v>1469</v>
       </c>
       <c r="Q13" t="s">
-        <v>1455</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
@@ -22343,16 +22574,16 @@
         <v>18</v>
       </c>
       <c r="D14" t="s">
-        <v>1456</v>
+        <v>1471</v>
       </c>
       <c r="E14" t="s">
         <v>478</v>
       </c>
       <c r="F14" t="s">
-        <v>1457</v>
+        <v>1472</v>
       </c>
       <c r="G14" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="H14">
         <v>274456</v>
@@ -22373,16 +22604,16 @@
         <v>38</v>
       </c>
       <c r="N14" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O14" t="s">
-        <v>1458</v>
+        <v>1473</v>
       </c>
       <c r="P14" t="s">
-        <v>1459</v>
+        <v>1474</v>
       </c>
       <c r="Q14" t="s">
-        <v>1460</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -22396,16 +22627,16 @@
         <v>30</v>
       </c>
       <c r="D15" t="s">
-        <v>1461</v>
+        <v>1476</v>
       </c>
       <c r="E15" t="s">
         <v>478</v>
       </c>
       <c r="F15" t="s">
-        <v>1462</v>
+        <v>1477</v>
       </c>
       <c r="G15" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J15" t="s">
         <v>22</v>
@@ -22420,16 +22651,16 @@
         <v>38</v>
       </c>
       <c r="N15" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O15" t="s">
-        <v>1463</v>
+        <v>1478</v>
       </c>
       <c r="P15" t="s">
-        <v>1464</v>
+        <v>1479</v>
       </c>
       <c r="Q15" t="s">
-        <v>1465</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
@@ -22443,16 +22674,16 @@
         <v>22</v>
       </c>
       <c r="D16" t="s">
-        <v>1466</v>
+        <v>1481</v>
       </c>
       <c r="E16" t="s">
         <v>478</v>
       </c>
       <c r="F16" t="s">
-        <v>1467</v>
+        <v>1482</v>
       </c>
       <c r="G16" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J16" t="s">
         <v>22</v>
@@ -22467,16 +22698,16 @@
         <v>38</v>
       </c>
       <c r="N16" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O16" t="s">
-        <v>1468</v>
+        <v>1483</v>
       </c>
       <c r="P16" t="s">
-        <v>1469</v>
+        <v>1484</v>
       </c>
       <c r="Q16" t="s">
-        <v>1470</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
@@ -22490,16 +22721,16 @@
         <v>48</v>
       </c>
       <c r="D17" t="s">
-        <v>1471</v>
+        <v>1486</v>
       </c>
       <c r="E17" t="s">
         <v>478</v>
       </c>
       <c r="F17" t="s">
-        <v>1472</v>
+        <v>1487</v>
       </c>
       <c r="G17" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J17" t="s">
         <v>22</v>
@@ -22514,16 +22745,16 @@
         <v>25</v>
       </c>
       <c r="N17" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O17" t="s">
-        <v>1473</v>
+        <v>1488</v>
       </c>
       <c r="P17" t="s">
-        <v>1474</v>
+        <v>1489</v>
       </c>
       <c r="Q17" t="s">
-        <v>1475</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
@@ -22537,16 +22768,16 @@
         <v>25</v>
       </c>
       <c r="D18" t="s">
-        <v>1476</v>
+        <v>1491</v>
       </c>
       <c r="E18" t="s">
         <v>478</v>
       </c>
       <c r="F18" t="s">
-        <v>1477</v>
+        <v>1492</v>
       </c>
       <c r="G18" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J18" t="s">
         <v>22</v>
@@ -22561,16 +22792,16 @@
         <v>38</v>
       </c>
       <c r="N18" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O18" t="s">
-        <v>1478</v>
+        <v>1493</v>
       </c>
       <c r="P18" t="s">
-        <v>1479</v>
+        <v>1494</v>
       </c>
       <c r="Q18" t="s">
-        <v>1480</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -22584,16 +22815,16 @@
         <v>40</v>
       </c>
       <c r="D19" t="s">
-        <v>1481</v>
+        <v>1496</v>
       </c>
       <c r="E19" t="s">
         <v>478</v>
       </c>
       <c r="F19" t="s">
-        <v>1482</v>
+        <v>1497</v>
       </c>
       <c r="G19" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J19" t="s">
         <v>22</v>
@@ -22608,16 +22839,16 @@
         <v>38</v>
       </c>
       <c r="N19" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O19" t="s">
-        <v>1483</v>
+        <v>1498</v>
       </c>
       <c r="P19" t="s">
-        <v>1484</v>
+        <v>1499</v>
       </c>
       <c r="Q19" t="s">
-        <v>1485</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -22631,16 +22862,16 @@
         <v>70</v>
       </c>
       <c r="D20" t="s">
-        <v>1486</v>
+        <v>1501</v>
       </c>
       <c r="E20" t="s">
-        <v>1487</v>
+        <v>1502</v>
       </c>
       <c r="F20" t="s">
-        <v>1488</v>
+        <v>1503</v>
       </c>
       <c r="G20" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J20" t="s">
         <v>22</v>
@@ -22655,16 +22886,16 @@
         <v>38</v>
       </c>
       <c r="N20" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O20" t="s">
-        <v>1489</v>
+        <v>1504</v>
       </c>
       <c r="P20" t="s">
-        <v>1490</v>
+        <v>1505</v>
       </c>
       <c r="Q20" t="s">
-        <v>1491</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
@@ -22678,16 +22909,16 @@
         <v>58</v>
       </c>
       <c r="D21" t="s">
+        <v>1507</v>
+      </c>
+      <c r="E21" t="s">
+        <v>1508</v>
+      </c>
+      <c r="F21" t="s">
         <v>1492</v>
       </c>
-      <c r="E21" t="s">
-        <v>1493</v>
-      </c>
-      <c r="F21" t="s">
-        <v>1477</v>
-      </c>
       <c r="G21" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J21" t="s">
         <v>22</v>
@@ -22702,16 +22933,16 @@
         <v>38</v>
       </c>
       <c r="N21" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O21" t="s">
-        <v>1494</v>
+        <v>1509</v>
       </c>
       <c r="P21" t="s">
-        <v>1495</v>
+        <v>1510</v>
       </c>
       <c r="Q21" t="s">
-        <v>1496</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -22725,16 +22956,16 @@
         <v>32</v>
       </c>
       <c r="D22" t="s">
-        <v>1497</v>
+        <v>1512</v>
       </c>
       <c r="E22" t="s">
-        <v>1498</v>
+        <v>1513</v>
       </c>
       <c r="F22" t="s">
         <v>1085</v>
       </c>
       <c r="G22" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J22" t="s">
         <v>22</v>
@@ -22749,16 +22980,16 @@
         <v>38</v>
       </c>
       <c r="N22" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O22" t="s">
-        <v>1499</v>
+        <v>1514</v>
       </c>
       <c r="P22" t="s">
-        <v>1500</v>
+        <v>1515</v>
       </c>
       <c r="Q22" t="s">
-        <v>1501</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
@@ -22772,16 +23003,16 @@
         <v>4</v>
       </c>
       <c r="D23" t="s">
-        <v>1502</v>
+        <v>1517</v>
       </c>
       <c r="E23" t="s">
-        <v>1503</v>
+        <v>1518</v>
       </c>
       <c r="F23" t="s">
         <v>1032</v>
       </c>
       <c r="G23" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J23" t="s">
         <v>22</v>
@@ -22796,16 +23027,16 @@
         <v>38</v>
       </c>
       <c r="N23" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O23" t="s">
-        <v>1504</v>
+        <v>1519</v>
       </c>
       <c r="P23" t="s">
-        <v>1505</v>
+        <v>1520</v>
       </c>
       <c r="Q23" t="s">
-        <v>1506</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
@@ -22819,16 +23050,16 @@
         <v>25</v>
       </c>
       <c r="D24" t="s">
-        <v>1507</v>
+        <v>1522</v>
       </c>
       <c r="E24" t="s">
-        <v>1508</v>
+        <v>1523</v>
       </c>
       <c r="F24" t="s">
-        <v>1509</v>
+        <v>1524</v>
       </c>
       <c r="G24" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J24" t="s">
         <v>22</v>
@@ -22843,16 +23074,16 @@
         <v>38</v>
       </c>
       <c r="N24" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O24" t="s">
-        <v>1510</v>
+        <v>1525</v>
       </c>
       <c r="P24" t="s">
-        <v>1511</v>
+        <v>1526</v>
       </c>
       <c r="Q24" t="s">
-        <v>1512</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
@@ -22866,16 +23097,16 @@
         <v>30</v>
       </c>
       <c r="D25" t="s">
-        <v>1513</v>
+        <v>1528</v>
       </c>
       <c r="E25" t="s">
-        <v>1514</v>
+        <v>1529</v>
       </c>
       <c r="F25" t="s">
         <v>1025</v>
       </c>
       <c r="G25" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J25" t="s">
         <v>22</v>
@@ -22890,16 +23121,16 @@
         <v>38</v>
       </c>
       <c r="N25" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O25" t="s">
-        <v>1515</v>
+        <v>1530</v>
       </c>
       <c r="P25" t="s">
-        <v>1516</v>
+        <v>1531</v>
       </c>
       <c r="Q25" t="s">
-        <v>1517</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
@@ -22913,16 +23144,16 @@
         <v>52</v>
       </c>
       <c r="D26" t="s">
-        <v>1518</v>
+        <v>1533</v>
       </c>
       <c r="E26" t="s">
         <v>421</v>
       </c>
       <c r="F26" t="s">
-        <v>1519</v>
+        <v>1534</v>
       </c>
       <c r="G26" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="H26">
         <v>180000</v>
@@ -22943,16 +23174,16 @@
         <v>25</v>
       </c>
       <c r="N26" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O26" t="s">
-        <v>1520</v>
+        <v>1535</v>
       </c>
       <c r="P26" t="s">
-        <v>1521</v>
+        <v>1536</v>
       </c>
       <c r="Q26" t="s">
-        <v>1522</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
@@ -22966,7 +23197,7 @@
         <v>50</v>
       </c>
       <c r="D27" t="s">
-        <v>1523</v>
+        <v>1538</v>
       </c>
       <c r="E27" t="s">
         <v>421</v>
@@ -22975,7 +23206,7 @@
         <v>20</v>
       </c>
       <c r="G27" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="H27">
         <v>180000</v>
@@ -22996,16 +23227,16 @@
         <v>25</v>
       </c>
       <c r="N27" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O27" t="s">
-        <v>1524</v>
+        <v>1539</v>
       </c>
       <c r="P27" t="s">
-        <v>1525</v>
+        <v>1540</v>
       </c>
       <c r="Q27" t="s">
-        <v>1526</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
@@ -23019,7 +23250,7 @@
         <v>46</v>
       </c>
       <c r="D28" t="s">
-        <v>1527</v>
+        <v>1542</v>
       </c>
       <c r="E28" t="s">
         <v>421</v>
@@ -23028,7 +23259,7 @@
         <v>20</v>
       </c>
       <c r="G28" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="H28">
         <v>180000</v>
@@ -23049,16 +23280,16 @@
         <v>25</v>
       </c>
       <c r="N28" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O28" t="s">
-        <v>1528</v>
+        <v>1543</v>
       </c>
       <c r="P28" t="s">
-        <v>1529</v>
+        <v>1544</v>
       </c>
       <c r="Q28" t="s">
-        <v>1530</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
@@ -23072,7 +23303,7 @@
         <v>38</v>
       </c>
       <c r="D29" t="s">
-        <v>1531</v>
+        <v>1546</v>
       </c>
       <c r="E29" t="s">
         <v>421</v>
@@ -23081,7 +23312,7 @@
         <v>20</v>
       </c>
       <c r="G29" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="H29">
         <v>217800</v>
@@ -23102,16 +23333,16 @@
         <v>38</v>
       </c>
       <c r="N29" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O29" t="s">
-        <v>1532</v>
+        <v>1547</v>
       </c>
       <c r="P29" t="s">
-        <v>1533</v>
+        <v>1548</v>
       </c>
       <c r="Q29" t="s">
-        <v>1534</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
@@ -23131,10 +23362,10 @@
         <v>421</v>
       </c>
       <c r="F30" t="s">
-        <v>1535</v>
+        <v>1550</v>
       </c>
       <c r="G30" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="H30">
         <v>180000</v>
@@ -23155,16 +23386,16 @@
         <v>25</v>
       </c>
       <c r="N30" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O30" t="s">
-        <v>1536</v>
+        <v>1551</v>
       </c>
       <c r="P30" t="s">
-        <v>1537</v>
+        <v>1552</v>
       </c>
       <c r="Q30" t="s">
-        <v>1538</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
@@ -23178,16 +23409,16 @@
         <v>45</v>
       </c>
       <c r="D31" t="s">
-        <v>1539</v>
+        <v>1554</v>
       </c>
       <c r="E31" t="s">
         <v>421</v>
       </c>
       <c r="F31" t="s">
-        <v>1540</v>
+        <v>1555</v>
       </c>
       <c r="G31" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="H31">
         <v>219100</v>
@@ -23208,16 +23439,16 @@
         <v>25</v>
       </c>
       <c r="N31" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O31" t="s">
-        <v>1541</v>
+        <v>1556</v>
       </c>
       <c r="P31" t="s">
-        <v>1542</v>
+        <v>1557</v>
       </c>
       <c r="Q31" t="s">
-        <v>1543</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
@@ -23231,16 +23462,16 @@
         <v>42</v>
       </c>
       <c r="D32" t="s">
-        <v>1544</v>
+        <v>1559</v>
       </c>
       <c r="E32" t="s">
         <v>421</v>
       </c>
       <c r="F32" t="s">
-        <v>1545</v>
+        <v>1560</v>
       </c>
       <c r="G32" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="H32">
         <v>180000</v>
@@ -23261,16 +23492,16 @@
         <v>25</v>
       </c>
       <c r="N32" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O32" t="s">
-        <v>1546</v>
+        <v>1561</v>
       </c>
       <c r="P32" t="s">
-        <v>1547</v>
+        <v>1562</v>
       </c>
       <c r="Q32" t="s">
-        <v>1548</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
@@ -23284,7 +23515,7 @@
         <v>32</v>
       </c>
       <c r="D33" t="s">
-        <v>1549</v>
+        <v>1564</v>
       </c>
       <c r="E33" t="s">
         <v>421</v>
@@ -23293,7 +23524,7 @@
         <v>20</v>
       </c>
       <c r="G33" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="H33">
         <v>219100</v>
@@ -23314,16 +23545,16 @@
         <v>38</v>
       </c>
       <c r="N33" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O33" t="s">
-        <v>1550</v>
+        <v>1565</v>
       </c>
       <c r="P33" t="s">
-        <v>1551</v>
+        <v>1566</v>
       </c>
       <c r="Q33" t="s">
-        <v>1552</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
@@ -23337,7 +23568,7 @@
         <v>35</v>
       </c>
       <c r="D34" t="s">
-        <v>1553</v>
+        <v>1568</v>
       </c>
       <c r="E34" t="s">
         <v>421</v>
@@ -23346,7 +23577,7 @@
         <v>20</v>
       </c>
       <c r="G34" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="H34">
         <v>219100</v>
@@ -23367,16 +23598,16 @@
         <v>38</v>
       </c>
       <c r="N34" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O34" t="s">
-        <v>1554</v>
+        <v>1569</v>
       </c>
       <c r="P34" t="s">
-        <v>1555</v>
+        <v>1570</v>
       </c>
       <c r="Q34" t="s">
-        <v>1556</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
@@ -23390,16 +23621,16 @@
         <v>40</v>
       </c>
       <c r="D35" t="s">
-        <v>1557</v>
+        <v>1572</v>
       </c>
       <c r="E35" t="s">
         <v>421</v>
       </c>
       <c r="F35" t="s">
-        <v>1558</v>
+        <v>1573</v>
       </c>
       <c r="G35" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="H35">
         <v>219100</v>
@@ -23420,16 +23651,16 @@
         <v>25</v>
       </c>
       <c r="N35" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O35" t="s">
-        <v>1559</v>
+        <v>1574</v>
       </c>
       <c r="P35" t="s">
-        <v>1560</v>
+        <v>1575</v>
       </c>
       <c r="Q35" t="s">
-        <v>1561</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
@@ -23443,7 +23674,7 @@
         <v>38</v>
       </c>
       <c r="D36" t="s">
-        <v>1562</v>
+        <v>1577</v>
       </c>
       <c r="E36" t="s">
         <v>421</v>
@@ -23452,7 +23683,7 @@
         <v>437</v>
       </c>
       <c r="G36" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="H36">
         <v>219100</v>
@@ -23473,16 +23704,16 @@
         <v>38</v>
       </c>
       <c r="N36" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O36" t="s">
-        <v>1563</v>
+        <v>1578</v>
       </c>
       <c r="P36" t="s">
-        <v>1564</v>
+        <v>1579</v>
       </c>
       <c r="Q36" t="s">
-        <v>1565</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
@@ -23496,7 +23727,7 @@
         <v>40</v>
       </c>
       <c r="D37" t="s">
-        <v>1566</v>
+        <v>1581</v>
       </c>
       <c r="E37" t="s">
         <v>421</v>
@@ -23505,7 +23736,7 @@
         <v>20</v>
       </c>
       <c r="G37" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="H37">
         <v>219100</v>
@@ -23526,16 +23757,16 @@
         <v>25</v>
       </c>
       <c r="N37" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O37" t="s">
-        <v>1567</v>
+        <v>1582</v>
       </c>
       <c r="P37" t="s">
-        <v>1568</v>
+        <v>1583</v>
       </c>
       <c r="Q37" t="s">
-        <v>1569</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
@@ -23549,16 +23780,16 @@
         <v>33</v>
       </c>
       <c r="D38" t="s">
-        <v>1570</v>
+        <v>1585</v>
       </c>
       <c r="E38" t="s">
         <v>421</v>
       </c>
       <c r="F38" t="s">
-        <v>1571</v>
+        <v>1586</v>
       </c>
       <c r="G38" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="H38">
         <v>219100</v>
@@ -23579,16 +23810,16 @@
         <v>38</v>
       </c>
       <c r="N38" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O38" t="s">
-        <v>1572</v>
+        <v>1587</v>
       </c>
       <c r="P38" t="s">
-        <v>1573</v>
+        <v>1588</v>
       </c>
       <c r="Q38" t="s">
-        <v>1574</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
@@ -23602,16 +23833,16 @@
         <v>48</v>
       </c>
       <c r="D39" t="s">
-        <v>1575</v>
+        <v>1590</v>
       </c>
       <c r="E39" t="s">
-        <v>1432</v>
+        <v>1447</v>
       </c>
       <c r="F39" t="s">
-        <v>1576</v>
+        <v>1591</v>
       </c>
       <c r="G39" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J39" t="s">
         <v>22</v>
@@ -23626,16 +23857,16 @@
         <v>25</v>
       </c>
       <c r="N39" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O39" t="s">
-        <v>1577</v>
+        <v>1592</v>
       </c>
       <c r="P39" t="s">
-        <v>1578</v>
+        <v>1593</v>
       </c>
       <c r="Q39" t="s">
-        <v>1579</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
@@ -23649,16 +23880,16 @@
         <v>40</v>
       </c>
       <c r="D40" t="s">
-        <v>1580</v>
+        <v>1595</v>
       </c>
       <c r="E40" t="s">
-        <v>1437</v>
+        <v>1452</v>
       </c>
       <c r="F40" t="s">
-        <v>1581</v>
+        <v>1596</v>
       </c>
       <c r="G40" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="H40">
         <v>184200</v>
@@ -23679,16 +23910,16 @@
         <v>25</v>
       </c>
       <c r="N40" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O40" t="s">
-        <v>1582</v>
+        <v>1597</v>
       </c>
       <c r="P40" t="s">
-        <v>1583</v>
+        <v>1598</v>
       </c>
       <c r="Q40" t="s">
-        <v>1584</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
@@ -23705,13 +23936,13 @@
         <v>1343</v>
       </c>
       <c r="E41" t="s">
-        <v>1437</v>
+        <v>1452</v>
       </c>
       <c r="F41" t="s">
-        <v>1585</v>
+        <v>1600</v>
       </c>
       <c r="G41" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="H41">
         <v>200000</v>
@@ -23732,16 +23963,16 @@
         <v>38</v>
       </c>
       <c r="N41" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O41" t="s">
-        <v>1586</v>
+        <v>1601</v>
       </c>
       <c r="P41" t="s">
-        <v>1587</v>
+        <v>1602</v>
       </c>
       <c r="Q41" t="s">
-        <v>1588</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
@@ -23755,7 +23986,7 @@
         <v>30</v>
       </c>
       <c r="D42" t="s">
-        <v>1589</v>
+        <v>1604</v>
       </c>
       <c r="E42" t="s">
         <v>698</v>
@@ -23764,7 +23995,7 @@
         <v>707</v>
       </c>
       <c r="G42" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J42" t="s">
         <v>22</v>
@@ -23779,16 +24010,16 @@
         <v>38</v>
       </c>
       <c r="N42" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O42" t="s">
-        <v>1590</v>
+        <v>1605</v>
       </c>
       <c r="P42" t="s">
-        <v>1591</v>
+        <v>1606</v>
       </c>
       <c r="Q42" t="s">
-        <v>1592</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
@@ -23808,10 +24039,10 @@
         <v>698</v>
       </c>
       <c r="F43" t="s">
-        <v>1447</v>
+        <v>1462</v>
       </c>
       <c r="G43" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J43" t="s">
         <v>22</v>
@@ -23826,16 +24057,16 @@
         <v>38</v>
       </c>
       <c r="N43" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O43" t="s">
-        <v>1593</v>
+        <v>1608</v>
       </c>
       <c r="P43" t="s">
-        <v>1594</v>
+        <v>1609</v>
       </c>
       <c r="Q43" t="s">
-        <v>1595</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
@@ -23849,7 +24080,7 @@
         <v>32</v>
       </c>
       <c r="D44" t="s">
-        <v>1596</v>
+        <v>1611</v>
       </c>
       <c r="E44" t="s">
         <v>698</v>
@@ -23858,7 +24089,7 @@
         <v>707</v>
       </c>
       <c r="G44" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J44" t="s">
         <v>22</v>
@@ -23873,16 +24104,16 @@
         <v>38</v>
       </c>
       <c r="N44" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O44" t="s">
-        <v>1597</v>
+        <v>1612</v>
       </c>
       <c r="P44" t="s">
-        <v>1598</v>
+        <v>1613</v>
       </c>
       <c r="Q44" t="s">
-        <v>1599</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
@@ -23896,16 +24127,16 @@
         <v>45</v>
       </c>
       <c r="D45" t="s">
-        <v>1600</v>
+        <v>1615</v>
       </c>
       <c r="E45" t="s">
         <v>478</v>
       </c>
       <c r="F45" t="s">
-        <v>1601</v>
+        <v>1616</v>
       </c>
       <c r="G45" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J45" t="s">
         <v>22</v>
@@ -23920,16 +24151,16 @@
         <v>25</v>
       </c>
       <c r="N45" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O45" t="s">
-        <v>1602</v>
+        <v>1617</v>
       </c>
       <c r="P45" t="s">
-        <v>1603</v>
+        <v>1618</v>
       </c>
       <c r="Q45" t="s">
-        <v>1604</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
@@ -23943,16 +24174,16 @@
         <v>35</v>
       </c>
       <c r="D46" t="s">
-        <v>1605</v>
+        <v>1620</v>
       </c>
       <c r="E46" t="s">
         <v>478</v>
       </c>
       <c r="F46" t="s">
-        <v>1606</v>
+        <v>1621</v>
       </c>
       <c r="G46" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J46" t="s">
         <v>22</v>
@@ -23967,16 +24198,16 @@
         <v>38</v>
       </c>
       <c r="N46" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O46" t="s">
-        <v>1607</v>
+        <v>1622</v>
       </c>
       <c r="P46" t="s">
-        <v>1608</v>
+        <v>1623</v>
       </c>
       <c r="Q46" t="s">
-        <v>1609</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
@@ -23990,7 +24221,7 @@
         <v>35</v>
       </c>
       <c r="D47" t="s">
-        <v>1610</v>
+        <v>1625</v>
       </c>
       <c r="E47" t="s">
         <v>478</v>
@@ -23999,7 +24230,7 @@
         <v>507</v>
       </c>
       <c r="G47" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J47" t="s">
         <v>22</v>
@@ -24014,16 +24245,16 @@
         <v>38</v>
       </c>
       <c r="N47" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O47" t="s">
-        <v>1611</v>
+        <v>1626</v>
       </c>
       <c r="P47" t="s">
-        <v>1612</v>
+        <v>1627</v>
       </c>
       <c r="Q47" t="s">
-        <v>1613</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
@@ -24037,16 +24268,16 @@
         <v>15</v>
       </c>
       <c r="D48" t="s">
-        <v>1614</v>
+        <v>1629</v>
       </c>
       <c r="E48" t="s">
         <v>478</v>
       </c>
       <c r="F48" t="s">
-        <v>1615</v>
+        <v>1630</v>
       </c>
       <c r="G48" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J48" t="s">
         <v>22</v>
@@ -24061,16 +24292,16 @@
         <v>38</v>
       </c>
       <c r="N48" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O48" t="s">
-        <v>1616</v>
+        <v>1631</v>
       </c>
       <c r="P48" t="s">
-        <v>1617</v>
+        <v>1632</v>
       </c>
       <c r="Q48" t="s">
-        <v>1618</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
@@ -24084,16 +24315,16 @@
         <v>25</v>
       </c>
       <c r="D49" t="s">
-        <v>1619</v>
+        <v>1634</v>
       </c>
       <c r="E49" t="s">
         <v>478</v>
       </c>
       <c r="F49" t="s">
-        <v>1620</v>
+        <v>1635</v>
       </c>
       <c r="G49" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J49" t="s">
         <v>22</v>
@@ -24108,16 +24339,16 @@
         <v>38</v>
       </c>
       <c r="N49" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O49" t="s">
-        <v>1621</v>
+        <v>1636</v>
       </c>
       <c r="P49" t="s">
-        <v>1622</v>
+        <v>1637</v>
       </c>
       <c r="Q49" t="s">
-        <v>1623</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
@@ -24131,16 +24362,16 @@
         <v>30</v>
       </c>
       <c r="D50" t="s">
-        <v>1624</v>
+        <v>1639</v>
       </c>
       <c r="E50" t="s">
         <v>478</v>
       </c>
       <c r="F50" t="s">
-        <v>1625</v>
+        <v>1640</v>
       </c>
       <c r="G50" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J50" t="s">
         <v>22</v>
@@ -24155,16 +24386,16 @@
         <v>38</v>
       </c>
       <c r="N50" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O50" t="s">
-        <v>1626</v>
+        <v>1641</v>
       </c>
       <c r="P50" t="s">
-        <v>1627</v>
+        <v>1642</v>
       </c>
       <c r="Q50" t="s">
-        <v>1628</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
@@ -24184,10 +24415,10 @@
         <v>421</v>
       </c>
       <c r="F51" t="s">
-        <v>1585</v>
+        <v>1600</v>
       </c>
       <c r="G51" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J51" t="s">
         <v>22</v>
@@ -24202,16 +24433,16 @@
         <v>38</v>
       </c>
       <c r="N51" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O51" t="s">
-        <v>1629</v>
+        <v>1644</v>
       </c>
       <c r="P51" t="s">
-        <v>1630</v>
+        <v>1645</v>
       </c>
       <c r="Q51" t="s">
-        <v>1631</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
@@ -24231,10 +24462,10 @@
         <v>421</v>
       </c>
       <c r="F52" t="s">
-        <v>1632</v>
+        <v>1647</v>
       </c>
       <c r="G52" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J52" t="s">
         <v>22</v>
@@ -24249,16 +24480,16 @@
         <v>25</v>
       </c>
       <c r="N52" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O52" t="s">
-        <v>1633</v>
+        <v>1648</v>
       </c>
       <c r="P52" t="s">
-        <v>1634</v>
+        <v>1649</v>
       </c>
       <c r="Q52" t="s">
-        <v>1635</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
@@ -24281,7 +24512,7 @@
         <v>764</v>
       </c>
       <c r="G53" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="H53">
         <v>180000</v>
@@ -24302,16 +24533,16 @@
         <v>38</v>
       </c>
       <c r="N53" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O53" t="s">
-        <v>1636</v>
+        <v>1651</v>
       </c>
       <c r="P53" t="s">
-        <v>1637</v>
+        <v>1652</v>
       </c>
       <c r="Q53" t="s">
-        <v>1638</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
@@ -24331,10 +24562,10 @@
         <v>421</v>
       </c>
       <c r="F54" t="s">
-        <v>1639</v>
+        <v>1654</v>
       </c>
       <c r="G54" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="H54">
         <v>180000</v>
@@ -24355,16 +24586,16 @@
         <v>38</v>
       </c>
       <c r="N54" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O54" t="s">
-        <v>1640</v>
+        <v>1655</v>
       </c>
       <c r="P54" t="s">
-        <v>1641</v>
+        <v>1656</v>
       </c>
       <c r="Q54" t="s">
-        <v>1642</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
@@ -24378,16 +24609,16 @@
         <v>20</v>
       </c>
       <c r="D55" t="s">
-        <v>1643</v>
+        <v>1658</v>
       </c>
       <c r="E55" t="s">
         <v>811</v>
       </c>
       <c r="F55" t="s">
-        <v>1644</v>
+        <v>1659</v>
       </c>
       <c r="G55" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J55" t="s">
         <v>22</v>
@@ -24402,16 +24633,16 @@
         <v>38</v>
       </c>
       <c r="N55" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O55" t="s">
-        <v>1645</v>
+        <v>1660</v>
       </c>
       <c r="P55" t="s">
-        <v>1646</v>
+        <v>1661</v>
       </c>
       <c r="Q55" t="s">
-        <v>1647</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
@@ -24425,7 +24656,7 @@
         <v>50</v>
       </c>
       <c r="D56" t="s">
-        <v>1648</v>
+        <v>1663</v>
       </c>
       <c r="E56" t="s">
         <v>811</v>
@@ -24434,7 +24665,7 @@
         <v>20</v>
       </c>
       <c r="G56" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="H56">
         <v>250000</v>
@@ -24455,16 +24686,16 @@
         <v>25</v>
       </c>
       <c r="N56" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O56" t="s">
-        <v>1649</v>
+        <v>1664</v>
       </c>
       <c r="P56" t="s">
-        <v>1650</v>
+        <v>1665</v>
       </c>
       <c r="Q56" t="s">
-        <v>1651</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
@@ -24478,7 +24709,7 @@
         <v>55</v>
       </c>
       <c r="D57" t="s">
-        <v>1652</v>
+        <v>1667</v>
       </c>
       <c r="E57" t="s">
         <v>811</v>
@@ -24487,7 +24718,7 @@
         <v>20</v>
       </c>
       <c r="G57" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="H57">
         <v>200000</v>
@@ -24508,16 +24739,16 @@
         <v>25</v>
       </c>
       <c r="N57" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O57" t="s">
-        <v>1653</v>
+        <v>1668</v>
       </c>
       <c r="P57" t="s">
-        <v>1654</v>
+        <v>1669</v>
       </c>
       <c r="Q57" t="s">
-        <v>1655</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
@@ -24531,7 +24762,7 @@
         <v>52</v>
       </c>
       <c r="D58" t="s">
-        <v>1656</v>
+        <v>1671</v>
       </c>
       <c r="E58" t="s">
         <v>811</v>
@@ -24540,7 +24771,7 @@
         <v>20</v>
       </c>
       <c r="G58" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="H58">
         <v>250000</v>
@@ -24561,16 +24792,16 @@
         <v>25</v>
       </c>
       <c r="N58" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O58" t="s">
-        <v>1657</v>
+        <v>1672</v>
       </c>
       <c r="P58" t="s">
-        <v>1658</v>
+        <v>1673</v>
       </c>
       <c r="Q58" t="s">
-        <v>1659</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
@@ -24584,7 +24815,7 @@
         <v>53</v>
       </c>
       <c r="D59" t="s">
-        <v>1660</v>
+        <v>1675</v>
       </c>
       <c r="E59" t="s">
         <v>811</v>
@@ -24593,7 +24824,7 @@
         <v>20</v>
       </c>
       <c r="G59" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="H59">
         <v>200000</v>
@@ -24614,16 +24845,16 @@
         <v>25</v>
       </c>
       <c r="N59" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O59" t="s">
-        <v>1661</v>
+        <v>1676</v>
       </c>
       <c r="P59" t="s">
-        <v>1662</v>
+        <v>1677</v>
       </c>
       <c r="Q59" t="s">
-        <v>1663</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
@@ -24637,7 +24868,7 @@
         <v>50</v>
       </c>
       <c r="D60" t="s">
-        <v>1664</v>
+        <v>1679</v>
       </c>
       <c r="E60" t="s">
         <v>811</v>
@@ -24646,7 +24877,7 @@
         <v>20</v>
       </c>
       <c r="G60" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="H60">
         <v>200000</v>
@@ -24667,16 +24898,16 @@
         <v>25</v>
       </c>
       <c r="N60" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O60" t="s">
-        <v>1665</v>
+        <v>1680</v>
       </c>
       <c r="P60" t="s">
-        <v>1666</v>
+        <v>1681</v>
       </c>
       <c r="Q60" t="s">
-        <v>1667</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
@@ -24690,7 +24921,7 @@
         <v>55</v>
       </c>
       <c r="D61" t="s">
-        <v>1668</v>
+        <v>1683</v>
       </c>
       <c r="E61" t="s">
         <v>811</v>
@@ -24699,7 +24930,7 @@
         <v>20</v>
       </c>
       <c r="G61" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="H61">
         <v>250000</v>
@@ -24720,16 +24951,16 @@
         <v>25</v>
       </c>
       <c r="N61" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O61" t="s">
-        <v>1669</v>
+        <v>1684</v>
       </c>
       <c r="P61" t="s">
-        <v>1670</v>
+        <v>1685</v>
       </c>
       <c r="Q61" t="s">
-        <v>1671</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
@@ -24743,16 +24974,16 @@
         <v>45</v>
       </c>
       <c r="D62" t="s">
-        <v>1672</v>
+        <v>1687</v>
       </c>
       <c r="E62" t="s">
-        <v>1673</v>
+        <v>1688</v>
       </c>
       <c r="F62" t="s">
-        <v>1674</v>
+        <v>1689</v>
       </c>
       <c r="G62" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="H62">
         <v>154000</v>
@@ -24773,16 +25004,16 @@
         <v>38</v>
       </c>
       <c r="N62" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O62" t="s">
-        <v>1675</v>
+        <v>1690</v>
       </c>
       <c r="P62" t="s">
-        <v>1676</v>
+        <v>1691</v>
       </c>
       <c r="Q62" t="s">
-        <v>1677</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
@@ -24805,7 +25036,7 @@
         <v>437</v>
       </c>
       <c r="G63" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="H63">
         <v>180000</v>
@@ -24826,16 +25057,16 @@
         <v>25</v>
       </c>
       <c r="N63" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O63" t="s">
-        <v>1678</v>
+        <v>1693</v>
       </c>
       <c r="P63" t="s">
-        <v>1679</v>
+        <v>1694</v>
       </c>
       <c r="Q63" t="s">
-        <v>1680</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
@@ -24855,10 +25086,10 @@
         <v>421</v>
       </c>
       <c r="F64" t="s">
-        <v>1535</v>
+        <v>1550</v>
       </c>
       <c r="G64" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="H64">
         <v>219100</v>
@@ -24879,16 +25110,16 @@
         <v>38</v>
       </c>
       <c r="N64" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O64" t="s">
-        <v>1681</v>
+        <v>1696</v>
       </c>
       <c r="P64" t="s">
-        <v>1682</v>
+        <v>1697</v>
       </c>
       <c r="Q64" t="s">
-        <v>1683</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
@@ -24902,7 +25133,7 @@
         <v>25</v>
       </c>
       <c r="D65" t="s">
-        <v>1684</v>
+        <v>1699</v>
       </c>
       <c r="E65" t="s">
         <v>421</v>
@@ -24911,7 +25142,7 @@
         <v>1016</v>
       </c>
       <c r="G65" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J65" t="s">
         <v>22</v>
@@ -24926,16 +25157,16 @@
         <v>38</v>
       </c>
       <c r="N65" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O65" t="s">
-        <v>1685</v>
+        <v>1700</v>
       </c>
       <c r="P65" t="s">
-        <v>1686</v>
+        <v>1701</v>
       </c>
       <c r="Q65" t="s">
-        <v>1687</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
@@ -24955,10 +25186,10 @@
         <v>698</v>
       </c>
       <c r="F66" t="s">
-        <v>1477</v>
+        <v>1492</v>
       </c>
       <c r="G66" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J66" t="s">
         <v>22</v>
@@ -24973,16 +25204,16 @@
         <v>38</v>
       </c>
       <c r="N66" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O66" t="s">
-        <v>1688</v>
+        <v>1703</v>
       </c>
       <c r="P66" t="s">
-        <v>1689</v>
+        <v>1704</v>
       </c>
       <c r="Q66" t="s">
-        <v>1690</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
@@ -24996,16 +25227,16 @@
         <v>15</v>
       </c>
       <c r="D67" t="s">
-        <v>1691</v>
+        <v>1706</v>
       </c>
       <c r="E67" t="s">
-        <v>1692</v>
+        <v>1707</v>
       </c>
       <c r="F67" t="s">
         <v>1032</v>
       </c>
       <c r="G67" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J67" t="s">
         <v>22</v>
@@ -25020,16 +25251,16 @@
         <v>38</v>
       </c>
       <c r="N67" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O67" t="s">
-        <v>1693</v>
+        <v>1708</v>
       </c>
       <c r="P67" t="s">
-        <v>1694</v>
+        <v>1709</v>
       </c>
       <c r="Q67" t="s">
-        <v>1695</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
@@ -25043,16 +25274,16 @@
         <v>12</v>
       </c>
       <c r="D68" t="s">
-        <v>1696</v>
+        <v>1711</v>
       </c>
       <c r="E68" t="s">
-        <v>1697</v>
+        <v>1712</v>
       </c>
       <c r="F68" t="s">
-        <v>1698</v>
+        <v>1713</v>
       </c>
       <c r="G68" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J68" t="s">
         <v>22</v>
@@ -25067,16 +25298,16 @@
         <v>38</v>
       </c>
       <c r="N68" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O68" t="s">
-        <v>1699</v>
+        <v>1714</v>
       </c>
       <c r="P68" t="s">
-        <v>1700</v>
+        <v>1715</v>
       </c>
       <c r="Q68" t="s">
-        <v>1701</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
@@ -25090,16 +25321,16 @@
         <v>42</v>
       </c>
       <c r="D69" t="s">
-        <v>1702</v>
+        <v>1717</v>
       </c>
       <c r="E69" t="s">
         <v>421</v>
       </c>
       <c r="F69" t="s">
-        <v>1703</v>
+        <v>1718</v>
       </c>
       <c r="G69" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="H69">
         <v>180000</v>
@@ -25120,16 +25351,16 @@
         <v>25</v>
       </c>
       <c r="N69" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O69" t="s">
-        <v>1704</v>
+        <v>1719</v>
       </c>
       <c r="P69" t="s">
-        <v>1705</v>
+        <v>1720</v>
       </c>
       <c r="Q69" t="s">
-        <v>1706</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
@@ -25143,16 +25374,16 @@
         <v>22</v>
       </c>
       <c r="D70" t="s">
-        <v>1707</v>
+        <v>1722</v>
       </c>
       <c r="E70" t="s">
-        <v>1437</v>
+        <v>1452</v>
       </c>
       <c r="F70" t="s">
-        <v>1708</v>
+        <v>1723</v>
       </c>
       <c r="G70" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="H70">
         <v>200000</v>
@@ -25173,16 +25404,16 @@
         <v>38</v>
       </c>
       <c r="N70" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O70" t="s">
-        <v>1709</v>
+        <v>1724</v>
       </c>
       <c r="P70" t="s">
-        <v>1710</v>
+        <v>1725</v>
       </c>
       <c r="Q70" t="s">
-        <v>1711</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
@@ -25196,16 +25427,16 @@
         <v>28</v>
       </c>
       <c r="D71" t="s">
-        <v>1712</v>
+        <v>1727</v>
       </c>
       <c r="E71" t="s">
-        <v>1713</v>
+        <v>1728</v>
       </c>
       <c r="F71" t="s">
         <v>1016</v>
       </c>
       <c r="G71" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J71" t="s">
         <v>22</v>
@@ -25220,16 +25451,16 @@
         <v>38</v>
       </c>
       <c r="N71" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O71" t="s">
-        <v>1714</v>
+        <v>1729</v>
       </c>
       <c r="P71" t="s">
-        <v>1715</v>
+        <v>1730</v>
       </c>
       <c r="Q71" t="s">
-        <v>1716</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
@@ -25243,16 +25474,16 @@
         <v>5</v>
       </c>
       <c r="D72" t="s">
-        <v>1717</v>
+        <v>1732</v>
       </c>
       <c r="E72" t="s">
-        <v>1718</v>
+        <v>1733</v>
       </c>
       <c r="F72" t="s">
-        <v>1719</v>
+        <v>1734</v>
       </c>
       <c r="G72" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J72" t="s">
         <v>22</v>
@@ -25267,16 +25498,16 @@
         <v>38</v>
       </c>
       <c r="N72" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O72" t="s">
-        <v>1720</v>
+        <v>1735</v>
       </c>
       <c r="P72" t="s">
-        <v>1721</v>
+        <v>1736</v>
       </c>
       <c r="Q72" t="s">
-        <v>1722</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
@@ -25296,10 +25527,10 @@
         <v>421</v>
       </c>
       <c r="F73" t="s">
-        <v>1723</v>
+        <v>1738</v>
       </c>
       <c r="G73" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J73" t="s">
         <v>22</v>
@@ -25314,16 +25545,16 @@
         <v>25</v>
       </c>
       <c r="N73" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O73" t="s">
-        <v>1724</v>
+        <v>1739</v>
       </c>
       <c r="P73" t="s">
-        <v>1725</v>
+        <v>1740</v>
       </c>
       <c r="Q73" t="s">
-        <v>1726</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
@@ -25337,16 +25568,16 @@
         <v>35</v>
       </c>
       <c r="D74" t="s">
-        <v>1727</v>
+        <v>1742</v>
       </c>
       <c r="E74" t="s">
-        <v>1728</v>
+        <v>1743</v>
       </c>
       <c r="F74" t="s">
         <v>1085</v>
       </c>
       <c r="G74" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J74" t="s">
         <v>22</v>
@@ -25361,16 +25592,16 @@
         <v>38</v>
       </c>
       <c r="N74" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O74" t="s">
-        <v>1729</v>
+        <v>1744</v>
       </c>
       <c r="P74" t="s">
-        <v>1730</v>
+        <v>1745</v>
       </c>
       <c r="Q74" t="s">
-        <v>1731</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
@@ -25384,16 +25615,16 @@
         <v>55</v>
       </c>
       <c r="D75" t="s">
-        <v>1732</v>
+        <v>1747</v>
       </c>
       <c r="E75" t="s">
         <v>421</v>
       </c>
       <c r="F75" t="s">
-        <v>1535</v>
+        <v>1550</v>
       </c>
       <c r="G75" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="H75">
         <v>219100</v>
@@ -25408,22 +25639,22 @@
         <v>423</v>
       </c>
       <c r="L75" t="s">
-        <v>1733</v>
+        <v>1748</v>
       </c>
       <c r="M75" t="s">
         <v>25</v>
       </c>
       <c r="N75" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O75" t="s">
-        <v>1734</v>
+        <v>1749</v>
       </c>
       <c r="P75" t="s">
-        <v>1735</v>
+        <v>1750</v>
       </c>
       <c r="Q75" t="s">
-        <v>1736</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
@@ -25437,16 +25668,16 @@
         <v>50</v>
       </c>
       <c r="D76" t="s">
-        <v>1737</v>
+        <v>1752</v>
       </c>
       <c r="E76" t="s">
-        <v>1437</v>
+        <v>1452</v>
       </c>
       <c r="F76" t="s">
         <v>20</v>
       </c>
       <c r="G76" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="H76">
         <v>200000</v>
@@ -25461,22 +25692,22 @@
         <v>423</v>
       </c>
       <c r="L76" t="s">
-        <v>1733</v>
+        <v>1748</v>
       </c>
       <c r="M76" t="s">
         <v>25</v>
       </c>
       <c r="N76" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O76" t="s">
-        <v>1738</v>
+        <v>1753</v>
       </c>
       <c r="P76" t="s">
-        <v>1739</v>
+        <v>1754</v>
       </c>
       <c r="Q76" t="s">
-        <v>1740</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
@@ -25490,16 +25721,16 @@
         <v>12</v>
       </c>
       <c r="D77" t="s">
-        <v>1741</v>
+        <v>1756</v>
       </c>
       <c r="E77" t="s">
-        <v>1742</v>
+        <v>1757</v>
       </c>
       <c r="F77" t="s">
         <v>1016</v>
       </c>
       <c r="G77" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J77" t="s">
         <v>22</v>
@@ -25508,22 +25739,22 @@
         <v>557</v>
       </c>
       <c r="L77" t="s">
-        <v>1733</v>
+        <v>1748</v>
       </c>
       <c r="M77" t="s">
         <v>38</v>
       </c>
       <c r="N77" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O77" t="s">
-        <v>1743</v>
+        <v>1758</v>
       </c>
       <c r="P77" t="s">
-        <v>1744</v>
+        <v>1759</v>
       </c>
       <c r="Q77" t="s">
-        <v>1745</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
@@ -25537,16 +25768,16 @@
         <v>12</v>
       </c>
       <c r="D78" t="s">
-        <v>1746</v>
+        <v>1761</v>
       </c>
       <c r="E78" t="s">
-        <v>1742</v>
+        <v>1757</v>
       </c>
       <c r="F78" t="s">
         <v>1016</v>
       </c>
       <c r="G78" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J78" t="s">
         <v>22</v>
@@ -25555,22 +25786,22 @@
         <v>557</v>
       </c>
       <c r="L78" t="s">
-        <v>1733</v>
+        <v>1748</v>
       </c>
       <c r="M78" t="s">
         <v>38</v>
       </c>
       <c r="N78" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O78" t="s">
-        <v>1747</v>
+        <v>1762</v>
       </c>
       <c r="P78" t="s">
-        <v>1748</v>
+        <v>1763</v>
       </c>
       <c r="Q78" t="s">
-        <v>1749</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
@@ -25584,16 +25815,16 @@
         <v>3</v>
       </c>
       <c r="D79" t="s">
-        <v>1750</v>
+        <v>1765</v>
       </c>
       <c r="E79" t="s">
-        <v>1742</v>
+        <v>1757</v>
       </c>
       <c r="F79" t="s">
         <v>1016</v>
       </c>
       <c r="G79" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J79" t="s">
         <v>22</v>
@@ -25602,22 +25833,22 @@
         <v>557</v>
       </c>
       <c r="L79" t="s">
-        <v>1733</v>
+        <v>1748</v>
       </c>
       <c r="M79" t="s">
         <v>38</v>
       </c>
       <c r="N79" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O79" t="s">
-        <v>1751</v>
+        <v>1766</v>
       </c>
       <c r="P79" t="s">
-        <v>1752</v>
+        <v>1767</v>
       </c>
       <c r="Q79" t="s">
-        <v>1753</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
@@ -25631,16 +25862,16 @@
         <v>25</v>
       </c>
       <c r="D80" t="s">
-        <v>1754</v>
+        <v>1769</v>
       </c>
       <c r="E80" t="s">
-        <v>1755</v>
+        <v>1770</v>
       </c>
       <c r="F80" t="s">
-        <v>1756</v>
+        <v>1771</v>
       </c>
       <c r="G80" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J80" t="s">
         <v>22</v>
@@ -25649,22 +25880,22 @@
         <v>557</v>
       </c>
       <c r="L80" t="s">
-        <v>1733</v>
+        <v>1748</v>
       </c>
       <c r="M80" t="s">
         <v>38</v>
       </c>
       <c r="N80" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O80" t="s">
-        <v>1757</v>
+        <v>1772</v>
       </c>
       <c r="P80" t="s">
-        <v>1758</v>
+        <v>1773</v>
       </c>
       <c r="Q80" t="s">
-        <v>1759</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
@@ -25678,16 +25909,16 @@
         <v>62</v>
       </c>
       <c r="D81" t="s">
-        <v>1760</v>
+        <v>1775</v>
       </c>
       <c r="E81" t="s">
-        <v>1761</v>
+        <v>1776</v>
       </c>
       <c r="F81" t="s">
-        <v>1762</v>
+        <v>1777</v>
       </c>
       <c r="G81" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J81" t="s">
         <v>22</v>
@@ -25696,22 +25927,22 @@
         <v>557</v>
       </c>
       <c r="L81" t="s">
-        <v>1733</v>
+        <v>1748</v>
       </c>
       <c r="M81" t="s">
         <v>38</v>
       </c>
       <c r="N81" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O81" t="s">
-        <v>1763</v>
+        <v>1778</v>
       </c>
       <c r="P81" t="s">
-        <v>1764</v>
+        <v>1779</v>
       </c>
       <c r="Q81" t="s">
-        <v>1765</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
@@ -25725,16 +25956,16 @@
         <v>68</v>
       </c>
       <c r="D82" t="s">
-        <v>1766</v>
+        <v>1781</v>
       </c>
       <c r="E82" t="s">
-        <v>1761</v>
+        <v>1776</v>
       </c>
       <c r="F82" t="s">
-        <v>1762</v>
+        <v>1777</v>
       </c>
       <c r="G82" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J82" t="s">
         <v>22</v>
@@ -25743,22 +25974,22 @@
         <v>557</v>
       </c>
       <c r="L82" t="s">
-        <v>1733</v>
+        <v>1748</v>
       </c>
       <c r="M82" t="s">
         <v>38</v>
       </c>
       <c r="N82" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O82" t="s">
-        <v>1767</v>
+        <v>1782</v>
       </c>
       <c r="P82" t="s">
-        <v>1768</v>
+        <v>1783</v>
       </c>
       <c r="Q82" t="s">
-        <v>1769</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
@@ -25778,10 +26009,10 @@
         <v>421</v>
       </c>
       <c r="F83" t="s">
-        <v>1770</v>
+        <v>1785</v>
       </c>
       <c r="G83" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="H83">
         <v>180000</v>
@@ -25802,16 +26033,16 @@
         <v>25</v>
       </c>
       <c r="N83" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O83" t="s">
-        <v>1771</v>
+        <v>1786</v>
       </c>
       <c r="P83" t="s">
-        <v>1772</v>
+        <v>1787</v>
       </c>
       <c r="Q83" t="s">
-        <v>1773</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
@@ -25831,10 +26062,10 @@
         <v>421</v>
       </c>
       <c r="F84" t="s">
-        <v>1774</v>
+        <v>1789</v>
       </c>
       <c r="G84" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="H84">
         <v>180000</v>
@@ -25855,16 +26086,16 @@
         <v>25</v>
       </c>
       <c r="N84" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O84" t="s">
-        <v>1775</v>
+        <v>1790</v>
       </c>
       <c r="P84" t="s">
-        <v>1776</v>
+        <v>1791</v>
       </c>
       <c r="Q84" t="s">
-        <v>1777</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
@@ -25878,16 +26109,16 @@
         <v>35</v>
       </c>
       <c r="D85" t="s">
-        <v>1778</v>
+        <v>1793</v>
       </c>
       <c r="E85" t="s">
         <v>421</v>
       </c>
       <c r="F85" t="s">
-        <v>1779</v>
+        <v>1794</v>
       </c>
       <c r="G85" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="H85">
         <v>219100</v>
@@ -25908,16 +26139,16 @@
         <v>25</v>
       </c>
       <c r="N85" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O85" t="s">
-        <v>1780</v>
+        <v>1795</v>
       </c>
       <c r="P85" t="s">
-        <v>1781</v>
+        <v>1796</v>
       </c>
       <c r="Q85" t="s">
-        <v>1782</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
@@ -25931,16 +26162,16 @@
         <v>25</v>
       </c>
       <c r="D86" t="s">
-        <v>1783</v>
+        <v>1798</v>
       </c>
       <c r="E86" t="s">
         <v>478</v>
       </c>
       <c r="F86" t="s">
-        <v>1601</v>
+        <v>1616</v>
       </c>
       <c r="G86" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J86" t="s">
         <v>22</v>
@@ -25955,16 +26186,16 @@
         <v>38</v>
       </c>
       <c r="N86" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O86" t="s">
-        <v>1784</v>
+        <v>1799</v>
       </c>
       <c r="P86" t="s">
-        <v>1785</v>
+        <v>1800</v>
       </c>
       <c r="Q86" t="s">
-        <v>1786</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
@@ -25978,16 +26209,16 @@
         <v>35</v>
       </c>
       <c r="D87" t="s">
-        <v>1787</v>
+        <v>1802</v>
       </c>
       <c r="E87" t="s">
-        <v>1788</v>
+        <v>1803</v>
       </c>
       <c r="F87" t="s">
-        <v>1477</v>
+        <v>1492</v>
       </c>
       <c r="G87" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J87" t="s">
         <v>22</v>
@@ -26002,16 +26233,16 @@
         <v>38</v>
       </c>
       <c r="N87" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O87" t="s">
-        <v>1789</v>
+        <v>1804</v>
       </c>
       <c r="P87" t="s">
-        <v>1790</v>
+        <v>1805</v>
       </c>
       <c r="Q87" t="s">
-        <v>1791</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
@@ -26034,7 +26265,7 @@
         <v>1085</v>
       </c>
       <c r="G88" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="H88">
         <v>200000</v>
@@ -26055,16 +26286,16 @@
         <v>38</v>
       </c>
       <c r="N88" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O88" t="s">
-        <v>1792</v>
+        <v>1807</v>
       </c>
       <c r="P88" t="s">
-        <v>1793</v>
+        <v>1808</v>
       </c>
       <c r="Q88" t="s">
-        <v>1794</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
@@ -26078,7 +26309,7 @@
         <v>38</v>
       </c>
       <c r="D89" t="s">
-        <v>1795</v>
+        <v>1810</v>
       </c>
       <c r="E89" t="s">
         <v>1084</v>
@@ -26087,7 +26318,7 @@
         <v>1085</v>
       </c>
       <c r="G89" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="H89">
         <v>200000</v>
@@ -26108,16 +26339,16 @@
         <v>38</v>
       </c>
       <c r="N89" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O89" t="s">
-        <v>1796</v>
+        <v>1811</v>
       </c>
       <c r="P89" t="s">
-        <v>1797</v>
+        <v>1812</v>
       </c>
       <c r="Q89" t="s">
-        <v>1798</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
@@ -26131,16 +26362,16 @@
         <v>40</v>
       </c>
       <c r="D90" t="s">
-        <v>1580</v>
+        <v>1595</v>
       </c>
       <c r="E90" t="s">
-        <v>1437</v>
+        <v>1452</v>
       </c>
       <c r="F90" t="s">
         <v>713</v>
       </c>
       <c r="G90" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="H90">
         <v>184200</v>
@@ -26161,16 +26392,16 @@
         <v>38</v>
       </c>
       <c r="N90" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O90" t="s">
-        <v>1799</v>
+        <v>1814</v>
       </c>
       <c r="P90" t="s">
-        <v>1800</v>
+        <v>1815</v>
       </c>
       <c r="Q90" t="s">
-        <v>1801</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
@@ -26184,16 +26415,16 @@
         <v>20</v>
       </c>
       <c r="D91" t="s">
-        <v>1802</v>
+        <v>1817</v>
       </c>
       <c r="E91" t="s">
-        <v>1803</v>
+        <v>1818</v>
       </c>
       <c r="F91" t="s">
-        <v>1804</v>
+        <v>1819</v>
       </c>
       <c r="G91" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J91" t="s">
         <v>22</v>
@@ -26208,16 +26439,16 @@
         <v>38</v>
       </c>
       <c r="N91" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O91" t="s">
-        <v>1805</v>
+        <v>1820</v>
       </c>
       <c r="P91" t="s">
-        <v>1806</v>
+        <v>1821</v>
       </c>
       <c r="Q91" t="s">
-        <v>1807</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
@@ -26231,16 +26462,16 @@
         <v>35</v>
       </c>
       <c r="D92" t="s">
-        <v>1808</v>
+        <v>1823</v>
       </c>
       <c r="E92" t="s">
-        <v>1809</v>
+        <v>1824</v>
       </c>
       <c r="F92" t="s">
-        <v>1810</v>
+        <v>1825</v>
       </c>
       <c r="G92" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="H92">
         <v>230000</v>
@@ -26261,16 +26492,16 @@
         <v>38</v>
       </c>
       <c r="N92" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O92" t="s">
-        <v>1811</v>
+        <v>1826</v>
       </c>
       <c r="P92" t="s">
-        <v>1812</v>
+        <v>1827</v>
       </c>
       <c r="Q92" t="s">
-        <v>1813</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
@@ -26290,10 +26521,10 @@
         <v>421</v>
       </c>
       <c r="F93" t="s">
-        <v>1814</v>
+        <v>1829</v>
       </c>
       <c r="G93" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="H93">
         <v>219100</v>
@@ -26314,16 +26545,16 @@
         <v>32</v>
       </c>
       <c r="N93" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O93" t="s">
-        <v>1815</v>
+        <v>1830</v>
       </c>
       <c r="P93" t="s">
-        <v>1816</v>
+        <v>1831</v>
       </c>
       <c r="Q93" t="s">
-        <v>1817</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
@@ -26337,16 +26568,16 @@
         <v>25</v>
       </c>
       <c r="D94" t="s">
-        <v>1818</v>
+        <v>1833</v>
       </c>
       <c r="E94" t="s">
-        <v>1728</v>
+        <v>1743</v>
       </c>
       <c r="F94" t="s">
         <v>1085</v>
       </c>
       <c r="G94" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J94" t="s">
         <v>22</v>
@@ -26361,16 +26592,16 @@
         <v>38</v>
       </c>
       <c r="N94" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O94" t="s">
-        <v>1819</v>
+        <v>1834</v>
       </c>
       <c r="P94" t="s">
-        <v>1820</v>
+        <v>1835</v>
       </c>
       <c r="Q94" t="s">
-        <v>1821</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
@@ -26384,16 +26615,16 @@
         <v>22</v>
       </c>
       <c r="D95" t="s">
-        <v>1822</v>
+        <v>1837</v>
       </c>
       <c r="E95" t="s">
-        <v>1823</v>
+        <v>1838</v>
       </c>
       <c r="F95" t="s">
-        <v>1824</v>
+        <v>1839</v>
       </c>
       <c r="G95" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J95" t="s">
         <v>22</v>
@@ -26408,16 +26639,16 @@
         <v>38</v>
       </c>
       <c r="N95" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O95" t="s">
-        <v>1825</v>
+        <v>1840</v>
       </c>
       <c r="P95" t="s">
-        <v>1826</v>
+        <v>1841</v>
       </c>
       <c r="Q95" t="s">
-        <v>1827</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
@@ -26431,16 +26662,16 @@
         <v>3</v>
       </c>
       <c r="D96" t="s">
-        <v>1828</v>
+        <v>1843</v>
       </c>
       <c r="E96" t="s">
-        <v>1829</v>
+        <v>1844</v>
       </c>
       <c r="F96" t="s">
-        <v>1824</v>
+        <v>1839</v>
       </c>
       <c r="G96" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J96" t="s">
         <v>22</v>
@@ -26455,16 +26686,16 @@
         <v>38</v>
       </c>
       <c r="N96" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O96" t="s">
-        <v>1830</v>
+        <v>1845</v>
       </c>
       <c r="P96" t="s">
-        <v>1831</v>
+        <v>1846</v>
       </c>
       <c r="Q96" t="s">
-        <v>1832</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
@@ -26478,16 +26709,16 @@
         <v>28</v>
       </c>
       <c r="D97" t="s">
-        <v>1833</v>
+        <v>1848</v>
       </c>
       <c r="E97" t="s">
-        <v>1834</v>
+        <v>1849</v>
       </c>
       <c r="F97" t="s">
         <v>1016</v>
       </c>
       <c r="G97" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J97" t="s">
         <v>22</v>
@@ -26502,16 +26733,16 @@
         <v>38</v>
       </c>
       <c r="N97" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O97" t="s">
-        <v>1835</v>
+        <v>1850</v>
       </c>
       <c r="P97" t="s">
-        <v>1836</v>
+        <v>1851</v>
       </c>
       <c r="Q97" t="s">
-        <v>1837</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
@@ -26525,16 +26756,16 @@
         <v>45</v>
       </c>
       <c r="D98" t="s">
-        <v>1838</v>
+        <v>1853</v>
       </c>
       <c r="E98" t="s">
-        <v>1839</v>
+        <v>1854</v>
       </c>
       <c r="F98" t="s">
-        <v>1477</v>
+        <v>1492</v>
       </c>
       <c r="G98" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J98" t="s">
         <v>22</v>
@@ -26549,16 +26780,16 @@
         <v>25</v>
       </c>
       <c r="N98" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O98" t="s">
-        <v>1840</v>
+        <v>1855</v>
       </c>
       <c r="P98" t="s">
-        <v>1841</v>
+        <v>1856</v>
       </c>
       <c r="Q98" t="s">
-        <v>1842</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.25">
@@ -26572,16 +26803,16 @@
         <v>50</v>
       </c>
       <c r="D99" t="s">
-        <v>1843</v>
+        <v>1858</v>
       </c>
       <c r="E99" t="s">
-        <v>1844</v>
+        <v>1859</v>
       </c>
       <c r="F99" t="s">
-        <v>1509</v>
+        <v>1524</v>
       </c>
       <c r="G99" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J99" t="s">
         <v>22</v>
@@ -26596,16 +26827,16 @@
         <v>25</v>
       </c>
       <c r="N99" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O99" t="s">
-        <v>1845</v>
+        <v>1860</v>
       </c>
       <c r="P99" t="s">
-        <v>1846</v>
+        <v>1861</v>
       </c>
       <c r="Q99" t="s">
-        <v>1847</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.25">
@@ -26619,16 +26850,16 @@
         <v>48</v>
       </c>
       <c r="D100" t="s">
-        <v>1848</v>
+        <v>1863</v>
       </c>
       <c r="E100" t="s">
-        <v>1673</v>
+        <v>1688</v>
       </c>
       <c r="F100" t="s">
-        <v>1849</v>
+        <v>1864</v>
       </c>
       <c r="G100" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="H100">
         <v>154000</v>
@@ -26649,16 +26880,16 @@
         <v>25</v>
       </c>
       <c r="N100" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O100" t="s">
-        <v>1850</v>
+        <v>1865</v>
       </c>
       <c r="P100" t="s">
-        <v>1851</v>
+        <v>1866</v>
       </c>
       <c r="Q100" t="s">
-        <v>1852</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.25">
@@ -26672,16 +26903,16 @@
         <v>25</v>
       </c>
       <c r="D101" t="s">
-        <v>1853</v>
+        <v>1868</v>
       </c>
       <c r="E101" t="s">
-        <v>1498</v>
+        <v>1513</v>
       </c>
       <c r="F101" t="s">
         <v>1085</v>
       </c>
       <c r="G101" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J101" t="s">
         <v>22</v>
@@ -26696,16 +26927,16 @@
         <v>38</v>
       </c>
       <c r="N101" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O101" t="s">
-        <v>1854</v>
+        <v>1869</v>
       </c>
       <c r="P101" t="s">
-        <v>1855</v>
+        <v>1870</v>
       </c>
       <c r="Q101" t="s">
-        <v>1856</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.25">
@@ -26719,16 +26950,16 @@
         <v>32</v>
       </c>
       <c r="D102" t="s">
-        <v>1754</v>
+        <v>1769</v>
       </c>
       <c r="E102" t="s">
-        <v>1498</v>
+        <v>1513</v>
       </c>
       <c r="F102" t="s">
         <v>1085</v>
       </c>
       <c r="G102" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J102" t="s">
         <v>22</v>
@@ -26743,16 +26974,16 @@
         <v>38</v>
       </c>
       <c r="N102" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O102" t="s">
-        <v>1857</v>
+        <v>1872</v>
       </c>
       <c r="P102" t="s">
-        <v>1858</v>
+        <v>1873</v>
       </c>
       <c r="Q102" t="s">
-        <v>1859</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.25">
@@ -26766,16 +26997,16 @@
         <v>22</v>
       </c>
       <c r="D103" t="s">
-        <v>1860</v>
+        <v>1875</v>
       </c>
       <c r="E103" t="s">
-        <v>1844</v>
+        <v>1859</v>
       </c>
       <c r="F103" t="s">
-        <v>1824</v>
+        <v>1839</v>
       </c>
       <c r="G103" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J103" t="s">
         <v>22</v>
@@ -26790,16 +27021,16 @@
         <v>38</v>
       </c>
       <c r="N103" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O103" t="s">
-        <v>1861</v>
+        <v>1876</v>
       </c>
       <c r="P103" t="s">
-        <v>1862</v>
+        <v>1877</v>
       </c>
       <c r="Q103" t="s">
-        <v>1863</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.25">
@@ -26813,16 +27044,16 @@
         <v>55</v>
       </c>
       <c r="D104" t="s">
-        <v>1843</v>
+        <v>1858</v>
       </c>
       <c r="E104" t="s">
-        <v>1844</v>
+        <v>1859</v>
       </c>
       <c r="F104" t="s">
-        <v>1864</v>
+        <v>1879</v>
       </c>
       <c r="G104" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J104" t="s">
         <v>22</v>
@@ -26837,16 +27068,16 @@
         <v>38</v>
       </c>
       <c r="N104" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O104" t="s">
-        <v>1865</v>
+        <v>1880</v>
       </c>
       <c r="P104" t="s">
-        <v>1866</v>
+        <v>1881</v>
       </c>
       <c r="Q104" t="s">
-        <v>1867</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.25">
@@ -26860,16 +27091,16 @@
         <v>25</v>
       </c>
       <c r="D105" t="s">
-        <v>1868</v>
+        <v>1883</v>
       </c>
       <c r="E105" t="s">
-        <v>1844</v>
+        <v>1859</v>
       </c>
       <c r="F105" t="s">
-        <v>1864</v>
+        <v>1879</v>
       </c>
       <c r="G105" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J105" t="s">
         <v>22</v>
@@ -26884,16 +27115,16 @@
         <v>38</v>
       </c>
       <c r="N105" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O105" t="s">
-        <v>1869</v>
+        <v>1884</v>
       </c>
       <c r="P105" t="s">
-        <v>1870</v>
+        <v>1885</v>
       </c>
       <c r="Q105" t="s">
-        <v>1871</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.25">
@@ -26907,7 +27138,7 @@
         <v>33</v>
       </c>
       <c r="D106" t="s">
-        <v>1872</v>
+        <v>1887</v>
       </c>
       <c r="E106" t="s">
         <v>421</v>
@@ -26916,7 +27147,7 @@
         <v>1016</v>
       </c>
       <c r="G106" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J106" t="s">
         <v>22</v>
@@ -26931,16 +27162,16 @@
         <v>38</v>
       </c>
       <c r="N106" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O106" t="s">
-        <v>1873</v>
+        <v>1888</v>
       </c>
       <c r="P106" t="s">
-        <v>1874</v>
+        <v>1889</v>
       </c>
       <c r="Q106" t="s">
-        <v>1875</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.25">
@@ -26954,16 +27185,16 @@
         <v>38</v>
       </c>
       <c r="D107" t="s">
-        <v>1876</v>
+        <v>1891</v>
       </c>
       <c r="E107" t="s">
-        <v>1877</v>
+        <v>1892</v>
       </c>
       <c r="F107" t="s">
-        <v>1606</v>
+        <v>1621</v>
       </c>
       <c r="G107" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="H107">
         <v>220000</v>
@@ -26984,16 +27215,16 @@
         <v>38</v>
       </c>
       <c r="N107" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O107" t="s">
-        <v>1878</v>
+        <v>1893</v>
       </c>
       <c r="P107" t="s">
-        <v>1879</v>
+        <v>1894</v>
       </c>
       <c r="Q107" t="s">
-        <v>1880</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.25">
@@ -27007,16 +27238,16 @@
         <v>62</v>
       </c>
       <c r="D108" t="s">
-        <v>1881</v>
+        <v>1896</v>
       </c>
       <c r="E108" t="s">
-        <v>1437</v>
+        <v>1452</v>
       </c>
       <c r="F108" t="s">
         <v>20</v>
       </c>
       <c r="G108" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="H108">
         <v>200000</v>
@@ -27037,16 +27268,16 @@
         <v>25</v>
       </c>
       <c r="N108" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O108" t="s">
-        <v>1882</v>
+        <v>1897</v>
       </c>
       <c r="P108" t="s">
-        <v>1883</v>
+        <v>1898</v>
       </c>
       <c r="Q108" t="s">
-        <v>1884</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.25">
@@ -27060,16 +27291,16 @@
         <v>30</v>
       </c>
       <c r="D109" t="s">
-        <v>1868</v>
+        <v>1883</v>
       </c>
       <c r="E109" t="s">
-        <v>1844</v>
+        <v>1859</v>
       </c>
       <c r="F109" t="s">
-        <v>1824</v>
+        <v>1839</v>
       </c>
       <c r="G109" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J109" t="s">
         <v>22</v>
@@ -27084,16 +27315,16 @@
         <v>38</v>
       </c>
       <c r="N109" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O109" t="s">
-        <v>1885</v>
+        <v>1900</v>
       </c>
       <c r="P109" t="s">
-        <v>1886</v>
+        <v>1901</v>
       </c>
       <c r="Q109" t="s">
-        <v>1887</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.25">
@@ -27107,16 +27338,16 @@
         <v>58</v>
       </c>
       <c r="D110" t="s">
-        <v>1843</v>
+        <v>1858</v>
       </c>
       <c r="E110" t="s">
-        <v>1844</v>
+        <v>1859</v>
       </c>
       <c r="F110" t="s">
-        <v>1509</v>
+        <v>1524</v>
       </c>
       <c r="G110" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J110" t="s">
         <v>22</v>
@@ -27131,16 +27362,16 @@
         <v>38</v>
       </c>
       <c r="N110" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O110" t="s">
-        <v>1888</v>
+        <v>1903</v>
       </c>
       <c r="P110" t="s">
-        <v>1889</v>
+        <v>1904</v>
       </c>
       <c r="Q110" t="s">
-        <v>1890</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.25">
@@ -27154,7 +27385,7 @@
         <v>55</v>
       </c>
       <c r="D111" t="s">
-        <v>1891</v>
+        <v>1906</v>
       </c>
       <c r="E111" t="s">
         <v>421</v>
@@ -27163,7 +27394,7 @@
         <v>20</v>
       </c>
       <c r="G111" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="H111">
         <v>217800</v>
@@ -27184,16 +27415,16 @@
         <v>25</v>
       </c>
       <c r="N111" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O111" t="s">
-        <v>1892</v>
+        <v>1907</v>
       </c>
       <c r="P111" t="s">
-        <v>1893</v>
+        <v>1908</v>
       </c>
       <c r="Q111" t="s">
-        <v>1894</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.25">
@@ -27207,16 +27438,16 @@
         <v>45</v>
       </c>
       <c r="D112" t="s">
-        <v>1895</v>
+        <v>1910</v>
       </c>
       <c r="E112" t="s">
         <v>421</v>
       </c>
       <c r="F112" t="s">
-        <v>1896</v>
+        <v>1911</v>
       </c>
       <c r="G112" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="H112">
         <v>219100</v>
@@ -27237,16 +27468,16 @@
         <v>25</v>
       </c>
       <c r="N112" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O112" t="s">
-        <v>1897</v>
+        <v>1912</v>
       </c>
       <c r="P112" t="s">
-        <v>1898</v>
+        <v>1913</v>
       </c>
       <c r="Q112" t="s">
-        <v>1899</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.25">
@@ -27266,10 +27497,10 @@
         <v>698</v>
       </c>
       <c r="F113" t="s">
-        <v>1900</v>
+        <v>1915</v>
       </c>
       <c r="G113" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J113" t="s">
         <v>22</v>
@@ -27284,16 +27515,16 @@
         <v>38</v>
       </c>
       <c r="N113" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O113" t="s">
-        <v>1901</v>
+        <v>1916</v>
       </c>
       <c r="P113" t="s">
-        <v>1902</v>
+        <v>1917</v>
       </c>
       <c r="Q113" t="s">
-        <v>1903</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.25">
@@ -27307,16 +27538,16 @@
         <v>35</v>
       </c>
       <c r="D114" t="s">
-        <v>1904</v>
+        <v>1919</v>
       </c>
       <c r="E114" t="s">
         <v>421</v>
       </c>
       <c r="F114" t="s">
-        <v>1905</v>
+        <v>1920</v>
       </c>
       <c r="G114" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J114" t="s">
         <v>22</v>
@@ -27331,16 +27562,16 @@
         <v>38</v>
       </c>
       <c r="N114" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O114" t="s">
-        <v>1906</v>
+        <v>1921</v>
       </c>
       <c r="P114" t="s">
-        <v>1907</v>
+        <v>1922</v>
       </c>
       <c r="Q114" t="s">
-        <v>1908</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.25">
@@ -27354,7 +27585,7 @@
         <v>38</v>
       </c>
       <c r="D115" t="s">
-        <v>1909</v>
+        <v>1924</v>
       </c>
       <c r="E115" t="s">
         <v>421</v>
@@ -27363,7 +27594,7 @@
         <v>20</v>
       </c>
       <c r="G115" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="H115">
         <v>219100</v>
@@ -27384,16 +27615,16 @@
         <v>38</v>
       </c>
       <c r="N115" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O115" t="s">
-        <v>1910</v>
+        <v>1925</v>
       </c>
       <c r="P115" t="s">
-        <v>1911</v>
+        <v>1926</v>
       </c>
       <c r="Q115" t="s">
-        <v>1912</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.25">
@@ -27407,16 +27638,16 @@
         <v>22</v>
       </c>
       <c r="D116" t="s">
-        <v>1913</v>
+        <v>1928</v>
       </c>
       <c r="E116" t="s">
-        <v>1914</v>
+        <v>1929</v>
       </c>
       <c r="F116" t="s">
-        <v>1915</v>
+        <v>1930</v>
       </c>
       <c r="G116" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J116" t="s">
         <v>22</v>
@@ -27431,16 +27662,16 @@
         <v>38</v>
       </c>
       <c r="N116" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O116" t="s">
-        <v>1916</v>
+        <v>1931</v>
       </c>
       <c r="P116" t="s">
-        <v>1917</v>
+        <v>1932</v>
       </c>
       <c r="Q116" t="s">
-        <v>1918</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.25">
@@ -27454,16 +27685,16 @@
         <v>35</v>
       </c>
       <c r="D117" t="s">
-        <v>1919</v>
+        <v>1934</v>
       </c>
       <c r="E117" t="s">
-        <v>1920</v>
+        <v>1935</v>
       </c>
       <c r="F117" t="s">
-        <v>1921</v>
+        <v>1936</v>
       </c>
       <c r="G117" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J117" t="s">
         <v>22</v>
@@ -27478,16 +27709,16 @@
         <v>38</v>
       </c>
       <c r="N117" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O117" t="s">
-        <v>1922</v>
+        <v>1937</v>
       </c>
       <c r="P117" t="s">
-        <v>1923</v>
+        <v>1938</v>
       </c>
       <c r="Q117" t="s">
-        <v>1924</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.25">
@@ -27501,7 +27732,7 @@
         <v>55</v>
       </c>
       <c r="D118" t="s">
-        <v>1925</v>
+        <v>1940</v>
       </c>
       <c r="E118" t="s">
         <v>1084</v>
@@ -27510,7 +27741,7 @@
         <v>1085</v>
       </c>
       <c r="G118" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="H118">
         <v>200000</v>
@@ -27531,16 +27762,16 @@
         <v>25</v>
       </c>
       <c r="N118" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O118" t="s">
-        <v>1926</v>
+        <v>1941</v>
       </c>
       <c r="P118" t="s">
-        <v>1927</v>
+        <v>1942</v>
       </c>
       <c r="Q118" t="s">
-        <v>1928</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.25">
@@ -27560,10 +27791,10 @@
         <v>421</v>
       </c>
       <c r="F119" t="s">
-        <v>1929</v>
+        <v>1944</v>
       </c>
       <c r="G119" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="H119">
         <v>180000</v>
@@ -27584,16 +27815,16 @@
         <v>25</v>
       </c>
       <c r="N119" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O119" t="s">
-        <v>1930</v>
+        <v>1945</v>
       </c>
       <c r="P119" t="s">
-        <v>1931</v>
+        <v>1946</v>
       </c>
       <c r="Q119" t="s">
-        <v>1932</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.25">
@@ -27613,10 +27844,10 @@
         <v>698</v>
       </c>
       <c r="F120" t="s">
-        <v>1477</v>
+        <v>1492</v>
       </c>
       <c r="G120" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J120" t="s">
         <v>22</v>
@@ -27631,16 +27862,16 @@
         <v>38</v>
       </c>
       <c r="N120" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O120" t="s">
-        <v>1933</v>
+        <v>1948</v>
       </c>
       <c r="P120" t="s">
-        <v>1934</v>
+        <v>1949</v>
       </c>
       <c r="Q120" t="s">
-        <v>1935</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.25">
@@ -27663,7 +27894,7 @@
         <v>1085</v>
       </c>
       <c r="G121" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J121" t="s">
         <v>22</v>
@@ -27678,16 +27909,16 @@
         <v>38</v>
       </c>
       <c r="N121" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O121" t="s">
-        <v>1936</v>
+        <v>1951</v>
       </c>
       <c r="P121" t="s">
-        <v>1937</v>
+        <v>1952</v>
       </c>
       <c r="Q121" t="s">
-        <v>1938</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.25">
@@ -27710,7 +27941,7 @@
         <v>1085</v>
       </c>
       <c r="G122" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J122" t="s">
         <v>22</v>
@@ -27725,16 +27956,16 @@
         <v>25</v>
       </c>
       <c r="N122" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O122" t="s">
-        <v>1939</v>
+        <v>1954</v>
       </c>
       <c r="P122" t="s">
-        <v>1940</v>
+        <v>1955</v>
       </c>
       <c r="Q122" t="s">
-        <v>1941</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.25">
@@ -27748,16 +27979,16 @@
         <v>32</v>
       </c>
       <c r="D123" t="s">
-        <v>1513</v>
+        <v>1528</v>
       </c>
       <c r="E123" t="s">
-        <v>1514</v>
+        <v>1529</v>
       </c>
       <c r="F123" t="s">
         <v>1025</v>
       </c>
       <c r="G123" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J123" t="s">
         <v>22</v>
@@ -27772,16 +28003,16 @@
         <v>38</v>
       </c>
       <c r="N123" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O123" t="s">
-        <v>1942</v>
+        <v>1957</v>
       </c>
       <c r="P123" t="s">
-        <v>1943</v>
+        <v>1958</v>
       </c>
       <c r="Q123" t="s">
-        <v>1944</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.25">
@@ -27795,7 +28026,7 @@
         <v>30</v>
       </c>
       <c r="D124" t="s">
-        <v>1945</v>
+        <v>1960</v>
       </c>
       <c r="E124" t="s">
         <v>698</v>
@@ -27804,7 +28035,7 @@
         <v>707</v>
       </c>
       <c r="G124" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J124" t="s">
         <v>22</v>
@@ -27819,16 +28050,16 @@
         <v>38</v>
       </c>
       <c r="N124" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O124" t="s">
-        <v>1946</v>
+        <v>1961</v>
       </c>
       <c r="P124" t="s">
-        <v>1947</v>
+        <v>1962</v>
       </c>
       <c r="Q124" t="s">
-        <v>1948</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.25">
@@ -27842,16 +28073,16 @@
         <v>5</v>
       </c>
       <c r="D125" t="s">
-        <v>1502</v>
+        <v>1517</v>
       </c>
       <c r="E125" t="s">
-        <v>1503</v>
+        <v>1518</v>
       </c>
       <c r="F125" t="s">
         <v>1032</v>
       </c>
       <c r="G125" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J125" t="s">
         <v>22</v>
@@ -27866,16 +28097,16 @@
         <v>38</v>
       </c>
       <c r="N125" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O125" t="s">
-        <v>1949</v>
+        <v>1964</v>
       </c>
       <c r="P125" t="s">
-        <v>1950</v>
+        <v>1965</v>
       </c>
       <c r="Q125" t="s">
-        <v>1951</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.25">
@@ -27889,16 +28120,16 @@
         <v>30</v>
       </c>
       <c r="D126" t="s">
-        <v>1507</v>
+        <v>1522</v>
       </c>
       <c r="E126" t="s">
-        <v>1508</v>
+        <v>1523</v>
       </c>
       <c r="F126" t="s">
-        <v>1509</v>
+        <v>1524</v>
       </c>
       <c r="G126" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J126" t="s">
         <v>22</v>
@@ -27913,16 +28144,16 @@
         <v>38</v>
       </c>
       <c r="N126" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O126" t="s">
-        <v>1952</v>
+        <v>1967</v>
       </c>
       <c r="P126" t="s">
-        <v>1953</v>
+        <v>1968</v>
       </c>
       <c r="Q126" t="s">
-        <v>1954</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.25">
@@ -27936,16 +28167,16 @@
         <v>40</v>
       </c>
       <c r="D127" t="s">
-        <v>1955</v>
+        <v>1970</v>
       </c>
       <c r="E127" t="s">
-        <v>1956</v>
+        <v>1971</v>
       </c>
       <c r="F127" t="s">
-        <v>1957</v>
+        <v>1972</v>
       </c>
       <c r="G127" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J127" t="s">
         <v>22</v>
@@ -27960,16 +28191,16 @@
         <v>38</v>
       </c>
       <c r="N127" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O127" t="s">
-        <v>1958</v>
+        <v>1973</v>
       </c>
       <c r="P127" t="s">
-        <v>1959</v>
+        <v>1974</v>
       </c>
       <c r="Q127" t="s">
-        <v>1960</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.25">
@@ -27983,16 +28214,16 @@
         <v>38</v>
       </c>
       <c r="D128" t="s">
-        <v>1961</v>
+        <v>1976</v>
       </c>
       <c r="E128" t="s">
         <v>421</v>
       </c>
       <c r="F128" t="s">
-        <v>1477</v>
+        <v>1492</v>
       </c>
       <c r="G128" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J128" t="s">
         <v>22</v>
@@ -28007,16 +28238,16 @@
         <v>38</v>
       </c>
       <c r="N128" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O128" t="s">
-        <v>1962</v>
+        <v>1977</v>
       </c>
       <c r="P128" t="s">
-        <v>1963</v>
+        <v>1978</v>
       </c>
       <c r="Q128" t="s">
-        <v>1964</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="129" spans="1:17" x14ac:dyDescent="0.25">
@@ -28030,16 +28261,16 @@
         <v>36</v>
       </c>
       <c r="D129" t="s">
-        <v>1965</v>
+        <v>1980</v>
       </c>
       <c r="E129" t="s">
         <v>421</v>
       </c>
       <c r="F129" t="s">
-        <v>1477</v>
+        <v>1492</v>
       </c>
       <c r="G129" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J129" t="s">
         <v>22</v>
@@ -28054,16 +28285,16 @@
         <v>38</v>
       </c>
       <c r="N129" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O129" t="s">
-        <v>1966</v>
+        <v>1981</v>
       </c>
       <c r="P129" t="s">
-        <v>1967</v>
+        <v>1982</v>
       </c>
       <c r="Q129" t="s">
-        <v>1968</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="130" spans="1:17" x14ac:dyDescent="0.25">
@@ -28080,13 +28311,13 @@
         <v>549</v>
       </c>
       <c r="E130" t="s">
-        <v>1969</v>
+        <v>1984</v>
       </c>
       <c r="F130" t="s">
-        <v>1970</v>
+        <v>1985</v>
       </c>
       <c r="G130" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J130" t="s">
         <v>22</v>
@@ -28101,16 +28332,16 @@
         <v>38</v>
       </c>
       <c r="N130" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O130" t="s">
-        <v>1971</v>
+        <v>1986</v>
       </c>
       <c r="P130" t="s">
-        <v>1972</v>
+        <v>1987</v>
       </c>
       <c r="Q130" t="s">
-        <v>1973</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="131" spans="1:17" x14ac:dyDescent="0.25">
@@ -28124,16 +28355,16 @@
         <v>45</v>
       </c>
       <c r="D131" t="s">
-        <v>1974</v>
+        <v>1989</v>
       </c>
       <c r="E131" t="s">
-        <v>1975</v>
+        <v>1990</v>
       </c>
       <c r="F131" t="s">
-        <v>1976</v>
+        <v>1991</v>
       </c>
       <c r="G131" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J131" t="s">
         <v>22</v>
@@ -28148,16 +28379,16 @@
         <v>38</v>
       </c>
       <c r="N131" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O131" t="s">
-        <v>1977</v>
+        <v>1992</v>
       </c>
       <c r="P131" t="s">
-        <v>1978</v>
+        <v>1993</v>
       </c>
       <c r="Q131" t="s">
-        <v>1979</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="132" spans="1:17" x14ac:dyDescent="0.25">
@@ -28171,16 +28402,16 @@
         <v>40</v>
       </c>
       <c r="D132" t="s">
-        <v>1980</v>
+        <v>1995</v>
       </c>
       <c r="E132" t="s">
-        <v>1981</v>
+        <v>1996</v>
       </c>
       <c r="F132" t="s">
         <v>1085</v>
       </c>
       <c r="G132" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J132" t="s">
         <v>22</v>
@@ -28195,16 +28426,16 @@
         <v>38</v>
       </c>
       <c r="N132" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O132" t="s">
-        <v>1982</v>
+        <v>1997</v>
       </c>
       <c r="P132" t="s">
-        <v>1983</v>
+        <v>1998</v>
       </c>
       <c r="Q132" t="s">
-        <v>1984</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="133" spans="1:17" x14ac:dyDescent="0.25">
@@ -28218,16 +28449,16 @@
         <v>40</v>
       </c>
       <c r="D133" t="s">
-        <v>1985</v>
+        <v>2000</v>
       </c>
       <c r="E133" t="s">
-        <v>1981</v>
+        <v>1996</v>
       </c>
       <c r="F133" t="s">
         <v>1085</v>
       </c>
       <c r="G133" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J133" t="s">
         <v>22</v>
@@ -28242,16 +28473,16 @@
         <v>38</v>
       </c>
       <c r="N133" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O133" t="s">
-        <v>1986</v>
+        <v>2001</v>
       </c>
       <c r="P133" t="s">
-        <v>1987</v>
+        <v>2002</v>
       </c>
       <c r="Q133" t="s">
-        <v>1988</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="134" spans="1:17" x14ac:dyDescent="0.25">
@@ -28265,16 +28496,16 @@
         <v>18</v>
       </c>
       <c r="D134" t="s">
-        <v>1741</v>
+        <v>1756</v>
       </c>
       <c r="E134" t="s">
-        <v>1742</v>
+        <v>1757</v>
       </c>
       <c r="F134" t="s">
         <v>1016</v>
       </c>
       <c r="G134" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J134" t="s">
         <v>22</v>
@@ -28289,16 +28520,16 @@
         <v>38</v>
       </c>
       <c r="N134" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O134" t="s">
-        <v>1989</v>
+        <v>2004</v>
       </c>
       <c r="P134" t="s">
-        <v>1990</v>
+        <v>2005</v>
       </c>
       <c r="Q134" t="s">
-        <v>1991</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="135" spans="1:17" x14ac:dyDescent="0.25">
@@ -28312,16 +28543,16 @@
         <v>3</v>
       </c>
       <c r="D135" t="s">
-        <v>1750</v>
+        <v>1765</v>
       </c>
       <c r="E135" t="s">
-        <v>1742</v>
+        <v>1757</v>
       </c>
       <c r="F135" t="s">
         <v>1016</v>
       </c>
       <c r="G135" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J135" t="s">
         <v>22</v>
@@ -28336,16 +28567,16 @@
         <v>38</v>
       </c>
       <c r="N135" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O135" t="s">
-        <v>1992</v>
+        <v>2007</v>
       </c>
       <c r="P135" t="s">
-        <v>1993</v>
+        <v>2008</v>
       </c>
       <c r="Q135" t="s">
-        <v>1994</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="136" spans="1:17" x14ac:dyDescent="0.25">
@@ -28359,16 +28590,16 @@
         <v>38</v>
       </c>
       <c r="D136" t="s">
-        <v>1995</v>
+        <v>2010</v>
       </c>
       <c r="E136" t="s">
-        <v>1996</v>
+        <v>2011</v>
       </c>
       <c r="F136" t="s">
-        <v>1997</v>
+        <v>2012</v>
       </c>
       <c r="G136" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J136" t="s">
         <v>22</v>
@@ -28383,16 +28614,16 @@
         <v>38</v>
       </c>
       <c r="N136" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O136" t="s">
-        <v>1998</v>
+        <v>2013</v>
       </c>
       <c r="P136" t="s">
-        <v>1999</v>
+        <v>2014</v>
       </c>
       <c r="Q136" t="s">
-        <v>2000</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="137" spans="1:17" x14ac:dyDescent="0.25">
@@ -28406,16 +28637,16 @@
         <v>15</v>
       </c>
       <c r="D137" t="s">
-        <v>2001</v>
+        <v>2016</v>
       </c>
       <c r="E137" t="s">
-        <v>1996</v>
+        <v>2011</v>
       </c>
       <c r="F137" t="s">
-        <v>2002</v>
+        <v>2017</v>
       </c>
       <c r="G137" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J137" t="s">
         <v>22</v>
@@ -28430,16 +28661,16 @@
         <v>38</v>
       </c>
       <c r="N137" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O137" t="s">
-        <v>2003</v>
+        <v>2018</v>
       </c>
       <c r="P137" t="s">
-        <v>2004</v>
+        <v>2019</v>
       </c>
       <c r="Q137" t="s">
-        <v>2005</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.25">
@@ -28453,16 +28684,16 @@
         <v>33</v>
       </c>
       <c r="D138" t="s">
-        <v>2006</v>
+        <v>2021</v>
       </c>
       <c r="E138" t="s">
-        <v>1996</v>
+        <v>2011</v>
       </c>
       <c r="F138" t="s">
-        <v>2002</v>
+        <v>2017</v>
       </c>
       <c r="G138" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J138" t="s">
         <v>22</v>
@@ -28477,16 +28708,16 @@
         <v>38</v>
       </c>
       <c r="N138" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O138" t="s">
-        <v>2007</v>
+        <v>2022</v>
       </c>
       <c r="P138" t="s">
-        <v>2008</v>
+        <v>2023</v>
       </c>
       <c r="Q138" t="s">
-        <v>2009</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.25">
@@ -28500,16 +28731,16 @@
         <v>40</v>
       </c>
       <c r="D139" t="s">
-        <v>2010</v>
+        <v>2025</v>
       </c>
       <c r="E139" t="s">
-        <v>1996</v>
+        <v>2011</v>
       </c>
       <c r="F139" t="s">
-        <v>2011</v>
+        <v>2026</v>
       </c>
       <c r="G139" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J139" t="s">
         <v>22</v>
@@ -28524,16 +28755,16 @@
         <v>38</v>
       </c>
       <c r="N139" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O139" t="s">
-        <v>2012</v>
+        <v>2027</v>
       </c>
       <c r="P139" t="s">
-        <v>2013</v>
+        <v>2028</v>
       </c>
       <c r="Q139" t="s">
-        <v>2014</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.25">
@@ -28547,16 +28778,16 @@
         <v>38</v>
       </c>
       <c r="D140" t="s">
-        <v>2015</v>
+        <v>2030</v>
       </c>
       <c r="E140" t="s">
-        <v>1996</v>
+        <v>2011</v>
       </c>
       <c r="F140" t="s">
-        <v>2002</v>
+        <v>2017</v>
       </c>
       <c r="G140" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J140" t="s">
         <v>22</v>
@@ -28571,16 +28802,16 @@
         <v>38</v>
       </c>
       <c r="N140" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O140" t="s">
-        <v>2016</v>
+        <v>2031</v>
       </c>
       <c r="P140" t="s">
-        <v>2017</v>
+        <v>2032</v>
       </c>
       <c r="Q140" t="s">
-        <v>2018</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.25">
@@ -28594,16 +28825,16 @@
         <v>45</v>
       </c>
       <c r="D141" t="s">
-        <v>2019</v>
+        <v>2034</v>
       </c>
       <c r="E141" t="s">
-        <v>1996</v>
+        <v>2011</v>
       </c>
       <c r="F141" t="s">
-        <v>2020</v>
+        <v>2035</v>
       </c>
       <c r="G141" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J141" t="s">
         <v>22</v>
@@ -28618,16 +28849,16 @@
         <v>38</v>
       </c>
       <c r="N141" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O141" t="s">
-        <v>2021</v>
+        <v>2036</v>
       </c>
       <c r="P141" t="s">
-        <v>2022</v>
+        <v>2037</v>
       </c>
       <c r="Q141" t="s">
-        <v>2023</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.25">
@@ -28641,16 +28872,16 @@
         <v>18</v>
       </c>
       <c r="D142" t="s">
-        <v>2024</v>
+        <v>2039</v>
       </c>
       <c r="E142" t="s">
-        <v>1996</v>
+        <v>2011</v>
       </c>
       <c r="F142" t="s">
-        <v>2025</v>
+        <v>2040</v>
       </c>
       <c r="G142" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J142" t="s">
         <v>22</v>
@@ -28665,16 +28896,16 @@
         <v>38</v>
       </c>
       <c r="N142" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O142" t="s">
-        <v>2026</v>
+        <v>2041</v>
       </c>
       <c r="P142" t="s">
-        <v>2027</v>
+        <v>2042</v>
       </c>
       <c r="Q142" t="s">
-        <v>2028</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="143" spans="1:17" x14ac:dyDescent="0.25">
@@ -28688,16 +28919,16 @@
         <v>20</v>
       </c>
       <c r="D143" t="s">
-        <v>2029</v>
+        <v>2044</v>
       </c>
       <c r="E143" t="s">
-        <v>1996</v>
+        <v>2011</v>
       </c>
       <c r="F143" t="s">
-        <v>2002</v>
+        <v>2017</v>
       </c>
       <c r="G143" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J143" t="s">
         <v>22</v>
@@ -28712,16 +28943,16 @@
         <v>38</v>
       </c>
       <c r="N143" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O143" t="s">
-        <v>2030</v>
+        <v>2045</v>
       </c>
       <c r="P143" t="s">
-        <v>2031</v>
+        <v>2046</v>
       </c>
       <c r="Q143" t="s">
-        <v>2032</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="144" spans="1:17" x14ac:dyDescent="0.25">
@@ -28735,16 +28966,16 @@
         <v>60</v>
       </c>
       <c r="D144" t="s">
-        <v>2033</v>
+        <v>2048</v>
       </c>
       <c r="E144" t="s">
-        <v>1996</v>
+        <v>2011</v>
       </c>
       <c r="F144" t="s">
-        <v>2034</v>
+        <v>2049</v>
       </c>
       <c r="G144" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J144" t="s">
         <v>22</v>
@@ -28759,16 +28990,16 @@
         <v>38</v>
       </c>
       <c r="N144" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O144" t="s">
-        <v>2035</v>
+        <v>2050</v>
       </c>
       <c r="P144" t="s">
-        <v>2036</v>
+        <v>2051</v>
       </c>
       <c r="Q144" t="s">
-        <v>2037</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="145" spans="1:17" x14ac:dyDescent="0.25">
@@ -28782,16 +29013,16 @@
         <v>32</v>
       </c>
       <c r="D145" t="s">
-        <v>2038</v>
+        <v>2053</v>
       </c>
       <c r="E145" t="s">
-        <v>1996</v>
+        <v>2011</v>
       </c>
       <c r="F145" t="s">
-        <v>2011</v>
+        <v>2026</v>
       </c>
       <c r="G145" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J145" t="s">
         <v>22</v>
@@ -28806,16 +29037,16 @@
         <v>38</v>
       </c>
       <c r="N145" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O145" t="s">
-        <v>2039</v>
+        <v>2054</v>
       </c>
       <c r="P145" t="s">
-        <v>2040</v>
+        <v>2055</v>
       </c>
       <c r="Q145" t="s">
-        <v>2041</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="146" spans="1:17" x14ac:dyDescent="0.25">
@@ -28829,16 +29060,16 @@
         <v>15</v>
       </c>
       <c r="D146" t="s">
-        <v>2042</v>
+        <v>2057</v>
       </c>
       <c r="E146" t="s">
-        <v>1996</v>
+        <v>2011</v>
       </c>
       <c r="F146" t="s">
-        <v>2043</v>
+        <v>2058</v>
       </c>
       <c r="G146" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J146" t="s">
         <v>22</v>
@@ -28853,16 +29084,16 @@
         <v>38</v>
       </c>
       <c r="N146" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O146" t="s">
-        <v>2044</v>
+        <v>2059</v>
       </c>
       <c r="P146" t="s">
-        <v>2045</v>
+        <v>2060</v>
       </c>
       <c r="Q146" t="s">
-        <v>2046</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="147" spans="1:17" x14ac:dyDescent="0.25">
@@ -28879,13 +29110,13 @@
         <v>280</v>
       </c>
       <c r="E147" t="s">
-        <v>1996</v>
+        <v>2011</v>
       </c>
       <c r="F147" t="s">
-        <v>2047</v>
+        <v>2062</v>
       </c>
       <c r="G147" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J147" t="s">
         <v>22</v>
@@ -28900,16 +29131,16 @@
         <v>38</v>
       </c>
       <c r="N147" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O147" t="s">
-        <v>2048</v>
+        <v>2063</v>
       </c>
       <c r="P147" t="s">
-        <v>2049</v>
+        <v>2064</v>
       </c>
       <c r="Q147" t="s">
-        <v>2050</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="148" spans="1:17" x14ac:dyDescent="0.25">
@@ -28923,16 +29154,16 @@
         <v>20</v>
       </c>
       <c r="D148" t="s">
-        <v>2051</v>
+        <v>2066</v>
       </c>
       <c r="E148" t="s">
-        <v>1996</v>
+        <v>2011</v>
       </c>
       <c r="F148" t="s">
-        <v>2011</v>
+        <v>2026</v>
       </c>
       <c r="G148" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J148" t="s">
         <v>22</v>
@@ -28947,16 +29178,16 @@
         <v>38</v>
       </c>
       <c r="N148" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O148" t="s">
-        <v>2052</v>
+        <v>2067</v>
       </c>
       <c r="P148" t="s">
-        <v>2053</v>
+        <v>2068</v>
       </c>
       <c r="Q148" t="s">
-        <v>2054</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="149" spans="1:17" x14ac:dyDescent="0.25">
@@ -28970,16 +29201,16 @@
         <v>82</v>
       </c>
       <c r="D149" t="s">
-        <v>2055</v>
+        <v>2070</v>
       </c>
       <c r="E149" t="s">
-        <v>1996</v>
+        <v>2011</v>
       </c>
       <c r="F149" t="s">
-        <v>2056</v>
+        <v>2071</v>
       </c>
       <c r="G149" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J149" t="s">
         <v>22</v>
@@ -28994,16 +29225,16 @@
         <v>25</v>
       </c>
       <c r="N149" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O149" t="s">
-        <v>2057</v>
+        <v>2072</v>
       </c>
       <c r="P149" t="s">
-        <v>2058</v>
+        <v>2073</v>
       </c>
       <c r="Q149" t="s">
-        <v>2059</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="150" spans="1:17" x14ac:dyDescent="0.25">
@@ -29017,16 +29248,16 @@
         <v>55</v>
       </c>
       <c r="D150" t="s">
-        <v>2060</v>
+        <v>2075</v>
       </c>
       <c r="E150" t="s">
         <v>1163</v>
       </c>
       <c r="F150" t="s">
-        <v>2061</v>
+        <v>2076</v>
       </c>
       <c r="G150" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J150" t="s">
         <v>22</v>
@@ -29041,16 +29272,16 @@
         <v>38</v>
       </c>
       <c r="N150" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O150" t="s">
-        <v>2062</v>
+        <v>2077</v>
       </c>
       <c r="P150" t="s">
-        <v>2063</v>
+        <v>2078</v>
       </c>
       <c r="Q150" t="s">
-        <v>2064</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="151" spans="1:17" x14ac:dyDescent="0.25">
@@ -29064,16 +29295,16 @@
         <v>28</v>
       </c>
       <c r="D151" t="s">
-        <v>2065</v>
+        <v>2080</v>
       </c>
       <c r="E151" t="s">
         <v>1163</v>
       </c>
       <c r="F151" t="s">
-        <v>2066</v>
+        <v>2081</v>
       </c>
       <c r="G151" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J151" t="s">
         <v>22</v>
@@ -29088,16 +29319,16 @@
         <v>38</v>
       </c>
       <c r="N151" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O151" t="s">
-        <v>2067</v>
+        <v>2082</v>
       </c>
       <c r="P151" t="s">
-        <v>2068</v>
+        <v>2083</v>
       </c>
       <c r="Q151" t="s">
-        <v>2069</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="152" spans="1:17" x14ac:dyDescent="0.25">
@@ -29111,16 +29342,16 @@
         <v>7</v>
       </c>
       <c r="D152" t="s">
-        <v>2070</v>
+        <v>2085</v>
       </c>
       <c r="E152" t="s">
         <v>1163</v>
       </c>
       <c r="F152" t="s">
-        <v>2071</v>
+        <v>2086</v>
       </c>
       <c r="G152" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J152" t="s">
         <v>22</v>
@@ -29135,16 +29366,16 @@
         <v>38</v>
       </c>
       <c r="N152" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O152" t="s">
-        <v>2072</v>
+        <v>2087</v>
       </c>
       <c r="P152" t="s">
-        <v>2073</v>
+        <v>2088</v>
       </c>
       <c r="Q152" t="s">
-        <v>2074</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="153" spans="1:17" x14ac:dyDescent="0.25">
@@ -29158,16 +29389,16 @@
         <v>55</v>
       </c>
       <c r="D153" t="s">
-        <v>2075</v>
+        <v>2090</v>
       </c>
       <c r="E153" t="s">
         <v>1163</v>
       </c>
       <c r="F153" t="s">
-        <v>2076</v>
+        <v>2091</v>
       </c>
       <c r="G153" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J153" t="s">
         <v>22</v>
@@ -29182,16 +29413,16 @@
         <v>38</v>
       </c>
       <c r="N153" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O153" t="s">
-        <v>2077</v>
+        <v>2092</v>
       </c>
       <c r="P153" t="s">
-        <v>2078</v>
+        <v>2093</v>
       </c>
       <c r="Q153" t="s">
-        <v>2079</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="154" spans="1:17" x14ac:dyDescent="0.25">
@@ -29205,16 +29436,16 @@
         <v>40</v>
       </c>
       <c r="D154" t="s">
-        <v>2080</v>
+        <v>2095</v>
       </c>
       <c r="E154" t="s">
-        <v>2081</v>
+        <v>2096</v>
       </c>
       <c r="F154" t="s">
         <v>1284</v>
       </c>
       <c r="G154" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J154" t="s">
         <v>22</v>
@@ -29229,16 +29460,16 @@
         <v>38</v>
       </c>
       <c r="N154" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O154" t="s">
-        <v>2082</v>
+        <v>2097</v>
       </c>
       <c r="P154" t="s">
-        <v>2083</v>
+        <v>2098</v>
       </c>
       <c r="Q154" t="s">
-        <v>2084</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="155" spans="1:17" x14ac:dyDescent="0.25">
@@ -29252,16 +29483,16 @@
         <v>45</v>
       </c>
       <c r="D155" t="s">
-        <v>2085</v>
+        <v>2100</v>
       </c>
       <c r="E155" t="s">
         <v>1198</v>
       </c>
       <c r="F155" t="s">
-        <v>2086</v>
+        <v>2101</v>
       </c>
       <c r="G155" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J155" t="s">
         <v>22</v>
@@ -29276,16 +29507,16 @@
         <v>38</v>
       </c>
       <c r="N155" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O155" t="s">
-        <v>2087</v>
+        <v>2102</v>
       </c>
       <c r="P155" t="s">
-        <v>2088</v>
+        <v>2103</v>
       </c>
       <c r="Q155" t="s">
-        <v>2089</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="156" spans="1:17" x14ac:dyDescent="0.25">
@@ -29299,16 +29530,16 @@
         <v>38</v>
       </c>
       <c r="D156" t="s">
-        <v>2090</v>
+        <v>2105</v>
       </c>
       <c r="E156" t="s">
         <v>1198</v>
       </c>
       <c r="F156" t="s">
-        <v>2091</v>
+        <v>2106</v>
       </c>
       <c r="G156" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J156" t="s">
         <v>22</v>
@@ -29323,16 +29554,16 @@
         <v>38</v>
       </c>
       <c r="N156" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O156" t="s">
-        <v>2092</v>
+        <v>2107</v>
       </c>
       <c r="P156" t="s">
-        <v>2093</v>
+        <v>2108</v>
       </c>
       <c r="Q156" t="s">
-        <v>2094</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="157" spans="1:17" x14ac:dyDescent="0.25">
@@ -29346,16 +29577,16 @@
         <v>68</v>
       </c>
       <c r="D157" t="s">
-        <v>2095</v>
+        <v>2110</v>
       </c>
       <c r="E157" t="s">
         <v>1198</v>
       </c>
       <c r="F157" t="s">
-        <v>2096</v>
+        <v>2111</v>
       </c>
       <c r="G157" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J157" t="s">
         <v>22</v>
@@ -29370,16 +29601,16 @@
         <v>38</v>
       </c>
       <c r="N157" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O157" t="s">
-        <v>2097</v>
+        <v>2112</v>
       </c>
       <c r="P157" t="s">
-        <v>2098</v>
+        <v>2113</v>
       </c>
       <c r="Q157" t="s">
-        <v>2099</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="158" spans="1:17" x14ac:dyDescent="0.25">
@@ -29399,10 +29630,10 @@
         <v>1198</v>
       </c>
       <c r="F158" t="s">
-        <v>2086</v>
+        <v>2101</v>
       </c>
       <c r="G158" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J158" t="s">
         <v>22</v>
@@ -29417,16 +29648,16 @@
         <v>38</v>
       </c>
       <c r="N158" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O158" t="s">
-        <v>2100</v>
+        <v>2115</v>
       </c>
       <c r="P158" t="s">
-        <v>2101</v>
+        <v>2116</v>
       </c>
       <c r="Q158" t="s">
-        <v>2102</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="159" spans="1:17" x14ac:dyDescent="0.25">
@@ -29446,10 +29677,10 @@
         <v>1198</v>
       </c>
       <c r="F159" t="s">
-        <v>2103</v>
+        <v>2118</v>
       </c>
       <c r="G159" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J159" t="s">
         <v>22</v>
@@ -29464,16 +29695,16 @@
         <v>38</v>
       </c>
       <c r="N159" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O159" t="s">
-        <v>2104</v>
+        <v>2119</v>
       </c>
       <c r="P159" t="s">
-        <v>2105</v>
+        <v>2120</v>
       </c>
       <c r="Q159" t="s">
-        <v>2106</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="160" spans="1:17" x14ac:dyDescent="0.25">
@@ -29487,16 +29718,16 @@
         <v>15</v>
       </c>
       <c r="D160" t="s">
-        <v>2107</v>
+        <v>2122</v>
       </c>
       <c r="E160" t="s">
         <v>1198</v>
       </c>
       <c r="F160" t="s">
-        <v>2086</v>
+        <v>2101</v>
       </c>
       <c r="G160" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J160" t="s">
         <v>22</v>
@@ -29511,16 +29742,16 @@
         <v>38</v>
       </c>
       <c r="N160" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O160" t="s">
-        <v>2108</v>
+        <v>2123</v>
       </c>
       <c r="P160" t="s">
-        <v>2109</v>
+        <v>2124</v>
       </c>
       <c r="Q160" t="s">
-        <v>2110</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="161" spans="1:17" x14ac:dyDescent="0.25">
@@ -29534,16 +29765,16 @@
         <v>22</v>
       </c>
       <c r="D161" t="s">
-        <v>2111</v>
+        <v>2126</v>
       </c>
       <c r="E161" t="s">
         <v>1198</v>
       </c>
       <c r="F161" t="s">
-        <v>2112</v>
+        <v>2127</v>
       </c>
       <c r="G161" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J161" t="s">
         <v>22</v>
@@ -29558,16 +29789,16 @@
         <v>38</v>
       </c>
       <c r="N161" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O161" t="s">
-        <v>2113</v>
+        <v>2128</v>
       </c>
       <c r="P161" t="s">
-        <v>2114</v>
+        <v>2129</v>
       </c>
       <c r="Q161" t="s">
-        <v>2115</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="162" spans="1:17" x14ac:dyDescent="0.25">
@@ -29581,7 +29812,7 @@
         <v>25</v>
       </c>
       <c r="D162" t="s">
-        <v>2116</v>
+        <v>2131</v>
       </c>
       <c r="E162" t="s">
         <v>1207</v>
@@ -29590,7 +29821,7 @@
         <v>1208</v>
       </c>
       <c r="G162" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J162" t="s">
         <v>22</v>
@@ -29605,16 +29836,16 @@
         <v>38</v>
       </c>
       <c r="N162" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O162" t="s">
-        <v>2117</v>
+        <v>2132</v>
       </c>
       <c r="P162" t="s">
-        <v>2118</v>
+        <v>2133</v>
       </c>
       <c r="Q162" t="s">
-        <v>2119</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="163" spans="1:17" x14ac:dyDescent="0.25">
@@ -29628,16 +29859,16 @@
         <v>20</v>
       </c>
       <c r="D163" t="s">
-        <v>2120</v>
+        <v>2135</v>
       </c>
       <c r="E163" t="s">
         <v>1207</v>
       </c>
       <c r="F163" t="s">
-        <v>2121</v>
+        <v>2136</v>
       </c>
       <c r="G163" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J163" t="s">
         <v>22</v>
@@ -29652,16 +29883,16 @@
         <v>38</v>
       </c>
       <c r="N163" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O163" t="s">
-        <v>2122</v>
+        <v>2137</v>
       </c>
       <c r="P163" t="s">
-        <v>2123</v>
+        <v>2138</v>
       </c>
       <c r="Q163" t="s">
-        <v>2124</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="164" spans="1:17" x14ac:dyDescent="0.25">
@@ -29675,16 +29906,16 @@
         <v>12</v>
       </c>
       <c r="D164" t="s">
-        <v>2125</v>
+        <v>2140</v>
       </c>
       <c r="E164" t="s">
         <v>1207</v>
       </c>
       <c r="F164" t="s">
-        <v>2126</v>
+        <v>2141</v>
       </c>
       <c r="G164" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J164" t="s">
         <v>22</v>
@@ -29699,16 +29930,16 @@
         <v>38</v>
       </c>
       <c r="N164" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O164" t="s">
-        <v>2127</v>
+        <v>2142</v>
       </c>
       <c r="P164" t="s">
-        <v>2128</v>
+        <v>2143</v>
       </c>
       <c r="Q164" t="s">
-        <v>2129</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="165" spans="1:17" x14ac:dyDescent="0.25">
@@ -29722,16 +29953,16 @@
         <v>15</v>
       </c>
       <c r="D165" t="s">
-        <v>2130</v>
+        <v>2145</v>
       </c>
       <c r="E165" t="s">
         <v>1207</v>
       </c>
       <c r="F165" t="s">
-        <v>2131</v>
+        <v>2146</v>
       </c>
       <c r="G165" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J165" t="s">
         <v>22</v>
@@ -29746,16 +29977,16 @@
         <v>38</v>
       </c>
       <c r="N165" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O165" t="s">
-        <v>2132</v>
+        <v>2147</v>
       </c>
       <c r="P165" t="s">
-        <v>2133</v>
+        <v>2148</v>
       </c>
       <c r="Q165" t="s">
-        <v>2134</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="166" spans="1:17" x14ac:dyDescent="0.25">
@@ -29769,16 +30000,16 @@
         <v>35</v>
       </c>
       <c r="D166" t="s">
-        <v>2135</v>
+        <v>2150</v>
       </c>
       <c r="E166" t="s">
         <v>1207</v>
       </c>
       <c r="F166" t="s">
-        <v>2136</v>
+        <v>2151</v>
       </c>
       <c r="G166" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J166" t="s">
         <v>22</v>
@@ -29793,16 +30024,16 @@
         <v>38</v>
       </c>
       <c r="N166" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O166" t="s">
-        <v>2137</v>
+        <v>2152</v>
       </c>
       <c r="P166" t="s">
-        <v>2138</v>
+        <v>2153</v>
       </c>
       <c r="Q166" t="s">
-        <v>2139</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="167" spans="1:17" x14ac:dyDescent="0.25">
@@ -29816,16 +30047,16 @@
         <v>20</v>
       </c>
       <c r="D167" t="s">
-        <v>2140</v>
+        <v>2155</v>
       </c>
       <c r="E167" t="s">
         <v>1207</v>
       </c>
       <c r="F167" t="s">
-        <v>2131</v>
+        <v>2146</v>
       </c>
       <c r="G167" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J167" t="s">
         <v>22</v>
@@ -29840,16 +30071,16 @@
         <v>38</v>
       </c>
       <c r="N167" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O167" t="s">
-        <v>2141</v>
+        <v>2156</v>
       </c>
       <c r="P167" t="s">
-        <v>2142</v>
+        <v>2157</v>
       </c>
       <c r="Q167" t="s">
-        <v>2143</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="168" spans="1:17" x14ac:dyDescent="0.25">
@@ -29863,16 +30094,16 @@
         <v>15</v>
       </c>
       <c r="D168" t="s">
-        <v>2144</v>
+        <v>2159</v>
       </c>
       <c r="E168" t="s">
         <v>1207</v>
       </c>
       <c r="F168" t="s">
-        <v>2145</v>
+        <v>2160</v>
       </c>
       <c r="G168" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J168" t="s">
         <v>22</v>
@@ -29887,16 +30118,16 @@
         <v>38</v>
       </c>
       <c r="N168" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O168" t="s">
-        <v>2146</v>
+        <v>2161</v>
       </c>
       <c r="P168" t="s">
-        <v>2147</v>
+        <v>2162</v>
       </c>
       <c r="Q168" t="s">
-        <v>2148</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="169" spans="1:17" x14ac:dyDescent="0.25">
@@ -29910,16 +30141,16 @@
         <v>45</v>
       </c>
       <c r="D169" t="s">
-        <v>2149</v>
+        <v>2164</v>
       </c>
       <c r="E169" t="s">
         <v>1207</v>
       </c>
       <c r="F169" t="s">
-        <v>2131</v>
+        <v>2146</v>
       </c>
       <c r="G169" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J169" t="s">
         <v>22</v>
@@ -29934,16 +30165,16 @@
         <v>38</v>
       </c>
       <c r="N169" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O169" t="s">
-        <v>2150</v>
+        <v>2165</v>
       </c>
       <c r="P169" t="s">
-        <v>2151</v>
+        <v>2166</v>
       </c>
       <c r="Q169" t="s">
-        <v>2152</v>
+        <v>2167</v>
       </c>
     </row>
     <row r="170" spans="1:17" x14ac:dyDescent="0.25">
@@ -29957,16 +30188,16 @@
         <v>40</v>
       </c>
       <c r="D170" t="s">
-        <v>2153</v>
+        <v>2168</v>
       </c>
       <c r="E170" t="s">
         <v>1207</v>
       </c>
       <c r="F170" t="s">
-        <v>2154</v>
+        <v>2169</v>
       </c>
       <c r="G170" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J170" t="s">
         <v>22</v>
@@ -29981,16 +30212,16 @@
         <v>38</v>
       </c>
       <c r="N170" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O170" t="s">
-        <v>2155</v>
+        <v>2170</v>
       </c>
       <c r="P170" t="s">
-        <v>2156</v>
+        <v>2171</v>
       </c>
       <c r="Q170" t="s">
-        <v>2157</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="171" spans="1:17" x14ac:dyDescent="0.25">
@@ -30004,16 +30235,16 @@
         <v>60</v>
       </c>
       <c r="D171" t="s">
-        <v>2158</v>
+        <v>2173</v>
       </c>
       <c r="E171" t="s">
         <v>1207</v>
       </c>
       <c r="F171" t="s">
-        <v>2159</v>
+        <v>2174</v>
       </c>
       <c r="G171" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J171" t="s">
         <v>22</v>
@@ -30028,16 +30259,16 @@
         <v>38</v>
       </c>
       <c r="N171" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O171" t="s">
-        <v>2160</v>
+        <v>2175</v>
       </c>
       <c r="P171" t="s">
-        <v>2161</v>
+        <v>2176</v>
       </c>
       <c r="Q171" t="s">
-        <v>2162</v>
+        <v>2177</v>
       </c>
     </row>
     <row r="172" spans="1:17" x14ac:dyDescent="0.25">
@@ -30051,16 +30282,16 @@
         <v>18</v>
       </c>
       <c r="D172" t="s">
-        <v>2163</v>
+        <v>2178</v>
       </c>
       <c r="E172" t="s">
         <v>1207</v>
       </c>
       <c r="F172" t="s">
-        <v>2159</v>
+        <v>2174</v>
       </c>
       <c r="G172" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J172" t="s">
         <v>22</v>
@@ -30075,16 +30306,16 @@
         <v>38</v>
       </c>
       <c r="N172" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O172" t="s">
-        <v>2164</v>
+        <v>2179</v>
       </c>
       <c r="P172" t="s">
-        <v>2165</v>
+        <v>2180</v>
       </c>
       <c r="Q172" t="s">
-        <v>2166</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="173" spans="1:17" x14ac:dyDescent="0.25">
@@ -30098,7 +30329,7 @@
         <v>12</v>
       </c>
       <c r="D173" t="s">
-        <v>2167</v>
+        <v>2182</v>
       </c>
       <c r="E173" t="s">
         <v>1207</v>
@@ -30107,7 +30338,7 @@
         <v>1208</v>
       </c>
       <c r="G173" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J173" t="s">
         <v>22</v>
@@ -30122,16 +30353,16 @@
         <v>38</v>
       </c>
       <c r="N173" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O173" t="s">
-        <v>2168</v>
+        <v>2183</v>
       </c>
       <c r="P173" t="s">
-        <v>2169</v>
+        <v>2184</v>
       </c>
       <c r="Q173" t="s">
-        <v>2170</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="174" spans="1:17" x14ac:dyDescent="0.25">
@@ -30145,7 +30376,7 @@
         <v>12</v>
       </c>
       <c r="D174" t="s">
-        <v>2171</v>
+        <v>2186</v>
       </c>
       <c r="E174" t="s">
         <v>1207</v>
@@ -30154,7 +30385,7 @@
         <v>1208</v>
       </c>
       <c r="G174" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J174" t="s">
         <v>22</v>
@@ -30169,16 +30400,16 @@
         <v>38</v>
       </c>
       <c r="N174" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O174" t="s">
-        <v>2172</v>
+        <v>2187</v>
       </c>
       <c r="P174" t="s">
-        <v>2173</v>
+        <v>2188</v>
       </c>
       <c r="Q174" t="s">
-        <v>2174</v>
+        <v>2189</v>
       </c>
     </row>
     <row r="175" spans="1:17" x14ac:dyDescent="0.25">
@@ -30192,16 +30423,16 @@
         <v>10</v>
       </c>
       <c r="D175" t="s">
-        <v>2175</v>
+        <v>2190</v>
       </c>
       <c r="E175" t="s">
         <v>1207</v>
       </c>
       <c r="F175" t="s">
-        <v>2131</v>
+        <v>2146</v>
       </c>
       <c r="G175" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J175" t="s">
         <v>22</v>
@@ -30216,16 +30447,16 @@
         <v>38</v>
       </c>
       <c r="N175" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O175" t="s">
-        <v>2176</v>
+        <v>2191</v>
       </c>
       <c r="P175" t="s">
-        <v>2177</v>
+        <v>2192</v>
       </c>
       <c r="Q175" t="s">
-        <v>2178</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="176" spans="1:17" x14ac:dyDescent="0.25">
@@ -30239,16 +30470,16 @@
         <v>15</v>
       </c>
       <c r="D176" t="s">
-        <v>2179</v>
+        <v>2194</v>
       </c>
       <c r="E176" t="s">
         <v>1240</v>
       </c>
       <c r="F176" t="s">
-        <v>2180</v>
+        <v>2195</v>
       </c>
       <c r="G176" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="H176">
         <v>201300</v>
@@ -30269,16 +30500,16 @@
         <v>38</v>
       </c>
       <c r="N176" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O176" t="s">
-        <v>2181</v>
+        <v>2196</v>
       </c>
       <c r="P176" t="s">
-        <v>2182</v>
+        <v>2197</v>
       </c>
       <c r="Q176" t="s">
-        <v>2183</v>
+        <v>2198</v>
       </c>
     </row>
     <row r="177" spans="1:17" x14ac:dyDescent="0.25">
@@ -30292,16 +30523,16 @@
         <v>15</v>
       </c>
       <c r="D177" t="s">
-        <v>2184</v>
+        <v>2199</v>
       </c>
       <c r="E177" t="s">
         <v>1240</v>
       </c>
       <c r="F177" t="s">
-        <v>2180</v>
+        <v>2195</v>
       </c>
       <c r="G177" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="H177">
         <v>201300</v>
@@ -30322,16 +30553,16 @@
         <v>38</v>
       </c>
       <c r="N177" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O177" t="s">
-        <v>2185</v>
+        <v>2200</v>
       </c>
       <c r="P177" t="s">
-        <v>2186</v>
+        <v>2201</v>
       </c>
       <c r="Q177" t="s">
-        <v>2187</v>
+        <v>2202</v>
       </c>
     </row>
     <row r="178" spans="1:17" x14ac:dyDescent="0.25">
@@ -30345,7 +30576,7 @@
         <v>20</v>
       </c>
       <c r="D178" t="s">
-        <v>2188</v>
+        <v>2203</v>
       </c>
       <c r="E178" t="s">
         <v>1240</v>
@@ -30354,7 +30585,7 @@
         <v>1284</v>
       </c>
       <c r="G178" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J178" t="s">
         <v>22</v>
@@ -30369,16 +30600,16 @@
         <v>38</v>
       </c>
       <c r="N178" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O178" t="s">
-        <v>2189</v>
+        <v>2204</v>
       </c>
       <c r="P178" t="s">
-        <v>2190</v>
+        <v>2205</v>
       </c>
       <c r="Q178" t="s">
-        <v>2191</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="179" spans="1:17" x14ac:dyDescent="0.25">
@@ -30401,7 +30632,7 @@
         <v>1274</v>
       </c>
       <c r="G179" t="s">
-        <v>2192</v>
+        <v>2207</v>
       </c>
       <c r="J179" t="s">
         <v>22</v>
@@ -30416,16 +30647,16 @@
         <v>25</v>
       </c>
       <c r="N179" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O179" t="s">
-        <v>2193</v>
+        <v>2208</v>
       </c>
       <c r="P179" t="s">
-        <v>2194</v>
+        <v>2209</v>
       </c>
       <c r="Q179" t="s">
-        <v>2195</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="180" spans="1:17" x14ac:dyDescent="0.25">
@@ -30439,16 +30670,16 @@
         <v>40</v>
       </c>
       <c r="D180" t="s">
-        <v>2111</v>
+        <v>2126</v>
       </c>
       <c r="E180" t="s">
         <v>1289</v>
       </c>
       <c r="F180" t="s">
-        <v>2196</v>
+        <v>2211</v>
       </c>
       <c r="G180" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J180" t="s">
         <v>22</v>
@@ -30463,16 +30694,16 @@
         <v>38</v>
       </c>
       <c r="N180" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O180" t="s">
-        <v>2197</v>
+        <v>2212</v>
       </c>
       <c r="P180" t="s">
-        <v>2198</v>
+        <v>2213</v>
       </c>
       <c r="Q180" t="s">
-        <v>2199</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="181" spans="1:17" x14ac:dyDescent="0.25">
@@ -30486,16 +30717,16 @@
         <v>38</v>
       </c>
       <c r="D181" t="s">
-        <v>2200</v>
+        <v>2215</v>
       </c>
       <c r="E181" t="s">
         <v>1289</v>
       </c>
       <c r="F181" t="s">
-        <v>2201</v>
+        <v>2216</v>
       </c>
       <c r="G181" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J181" t="s">
         <v>22</v>
@@ -30510,16 +30741,16 @@
         <v>38</v>
       </c>
       <c r="N181" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O181" t="s">
-        <v>2202</v>
+        <v>2217</v>
       </c>
       <c r="P181" t="s">
-        <v>2203</v>
+        <v>2218</v>
       </c>
       <c r="Q181" t="s">
-        <v>2204</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="182" spans="1:17" x14ac:dyDescent="0.25">
@@ -30533,16 +30764,16 @@
         <v>28</v>
       </c>
       <c r="D182" t="s">
-        <v>2205</v>
+        <v>2220</v>
       </c>
       <c r="E182" t="s">
         <v>1289</v>
       </c>
       <c r="F182" t="s">
-        <v>2206</v>
+        <v>2221</v>
       </c>
       <c r="G182" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J182" t="s">
         <v>22</v>
@@ -30557,16 +30788,16 @@
         <v>38</v>
       </c>
       <c r="N182" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O182" t="s">
-        <v>2207</v>
+        <v>2222</v>
       </c>
       <c r="P182" t="s">
-        <v>2208</v>
+        <v>2223</v>
       </c>
       <c r="Q182" t="s">
-        <v>2209</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="183" spans="1:17" x14ac:dyDescent="0.25">
@@ -30580,16 +30811,16 @@
         <v>25</v>
       </c>
       <c r="D183" t="s">
-        <v>2210</v>
+        <v>2225</v>
       </c>
       <c r="E183" t="s">
         <v>1289</v>
       </c>
       <c r="F183" t="s">
-        <v>2211</v>
+        <v>2226</v>
       </c>
       <c r="G183" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J183" t="s">
         <v>22</v>
@@ -30604,16 +30835,16 @@
         <v>38</v>
       </c>
       <c r="N183" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O183" t="s">
-        <v>2212</v>
+        <v>2227</v>
       </c>
       <c r="P183" t="s">
-        <v>2213</v>
+        <v>2228</v>
       </c>
       <c r="Q183" t="s">
-        <v>2214</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="184" spans="1:17" x14ac:dyDescent="0.25">
@@ -30627,16 +30858,16 @@
         <v>40</v>
       </c>
       <c r="D184" t="s">
-        <v>2215</v>
+        <v>2230</v>
       </c>
       <c r="E184" t="s">
         <v>1289</v>
       </c>
       <c r="F184" t="s">
-        <v>2211</v>
+        <v>2226</v>
       </c>
       <c r="G184" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J184" t="s">
         <v>22</v>
@@ -30651,16 +30882,16 @@
         <v>38</v>
       </c>
       <c r="N184" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O184" t="s">
-        <v>2216</v>
+        <v>2231</v>
       </c>
       <c r="P184" t="s">
-        <v>2217</v>
+        <v>2232</v>
       </c>
       <c r="Q184" t="s">
-        <v>2218</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="185" spans="1:17" x14ac:dyDescent="0.25">
@@ -30680,10 +30911,10 @@
         <v>1289</v>
       </c>
       <c r="F185" t="s">
-        <v>2219</v>
+        <v>2234</v>
       </c>
       <c r="G185" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J185" t="s">
         <v>22</v>
@@ -30698,16 +30929,16 @@
         <v>38</v>
       </c>
       <c r="N185" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O185" t="s">
-        <v>2220</v>
+        <v>2235</v>
       </c>
       <c r="P185" t="s">
-        <v>2221</v>
+        <v>2236</v>
       </c>
       <c r="Q185" t="s">
-        <v>2222</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="186" spans="1:17" x14ac:dyDescent="0.25">
@@ -30721,16 +30952,16 @@
         <v>18</v>
       </c>
       <c r="D186" t="s">
-        <v>2223</v>
+        <v>2238</v>
       </c>
       <c r="E186" t="s">
         <v>1289</v>
       </c>
       <c r="F186" t="s">
-        <v>2196</v>
+        <v>2211</v>
       </c>
       <c r="G186" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J186" t="s">
         <v>22</v>
@@ -30745,16 +30976,16 @@
         <v>38</v>
       </c>
       <c r="N186" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O186" t="s">
-        <v>2224</v>
+        <v>2239</v>
       </c>
       <c r="P186" t="s">
-        <v>2225</v>
+        <v>2240</v>
       </c>
       <c r="Q186" t="s">
-        <v>2226</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="187" spans="1:17" x14ac:dyDescent="0.25">
@@ -30768,16 +30999,16 @@
         <v>20</v>
       </c>
       <c r="D187" t="s">
-        <v>2227</v>
+        <v>2242</v>
       </c>
       <c r="E187" t="s">
         <v>1289</v>
       </c>
       <c r="F187" t="s">
-        <v>2228</v>
+        <v>2243</v>
       </c>
       <c r="G187" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J187" t="s">
         <v>22</v>
@@ -30792,16 +31023,16 @@
         <v>38</v>
       </c>
       <c r="N187" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O187" t="s">
-        <v>2229</v>
+        <v>2244</v>
       </c>
       <c r="P187" t="s">
-        <v>2230</v>
+        <v>2245</v>
       </c>
       <c r="Q187" t="s">
-        <v>2231</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="188" spans="1:17" x14ac:dyDescent="0.25">
@@ -30815,16 +31046,16 @@
         <v>45</v>
       </c>
       <c r="D188" t="s">
-        <v>2232</v>
+        <v>2247</v>
       </c>
       <c r="E188" t="s">
         <v>1289</v>
       </c>
       <c r="F188" t="s">
-        <v>2233</v>
+        <v>2248</v>
       </c>
       <c r="G188" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J188" t="s">
         <v>22</v>
@@ -30839,16 +31070,16 @@
         <v>25</v>
       </c>
       <c r="N188" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O188" t="s">
-        <v>2234</v>
+        <v>2249</v>
       </c>
       <c r="P188" t="s">
-        <v>2235</v>
+        <v>2250</v>
       </c>
       <c r="Q188" t="s">
-        <v>2236</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="189" spans="1:17" x14ac:dyDescent="0.25">
@@ -30862,16 +31093,16 @@
         <v>15</v>
       </c>
       <c r="D189" t="s">
-        <v>2237</v>
+        <v>2252</v>
       </c>
       <c r="E189" t="s">
-        <v>2238</v>
+        <v>2253</v>
       </c>
       <c r="F189" t="s">
-        <v>2239</v>
+        <v>2254</v>
       </c>
       <c r="G189" t="s">
-        <v>2192</v>
+        <v>2207</v>
       </c>
       <c r="J189" t="s">
         <v>22</v>
@@ -30886,16 +31117,16 @@
         <v>38</v>
       </c>
       <c r="N189" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O189" t="s">
-        <v>2240</v>
+        <v>2255</v>
       </c>
       <c r="P189" t="s">
-        <v>2241</v>
+        <v>2256</v>
       </c>
       <c r="Q189" t="s">
-        <v>2242</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="190" spans="1:17" x14ac:dyDescent="0.25">
@@ -30909,16 +31140,16 @@
         <v>25</v>
       </c>
       <c r="D190" t="s">
-        <v>2243</v>
+        <v>2258</v>
       </c>
       <c r="E190" t="s">
-        <v>2238</v>
+        <v>2253</v>
       </c>
       <c r="F190" t="s">
-        <v>2244</v>
+        <v>2259</v>
       </c>
       <c r="G190" t="s">
-        <v>2192</v>
+        <v>2207</v>
       </c>
       <c r="J190" t="s">
         <v>22</v>
@@ -30933,16 +31164,16 @@
         <v>38</v>
       </c>
       <c r="N190" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O190" t="s">
-        <v>2245</v>
+        <v>2260</v>
       </c>
       <c r="P190" t="s">
-        <v>2246</v>
+        <v>2261</v>
       </c>
       <c r="Q190" t="s">
-        <v>2247</v>
+        <v>2262</v>
       </c>
     </row>
     <row r="191" spans="1:17" x14ac:dyDescent="0.25">
@@ -30956,16 +31187,16 @@
         <v>10</v>
       </c>
       <c r="D191" t="s">
-        <v>2248</v>
+        <v>2263</v>
       </c>
       <c r="E191" t="s">
-        <v>2238</v>
+        <v>2253</v>
       </c>
       <c r="F191" t="s">
-        <v>2249</v>
+        <v>2264</v>
       </c>
       <c r="G191" t="s">
-        <v>2192</v>
+        <v>2207</v>
       </c>
       <c r="J191" t="s">
         <v>22</v>
@@ -30980,16 +31211,16 @@
         <v>38</v>
       </c>
       <c r="N191" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O191" t="s">
-        <v>2250</v>
+        <v>2265</v>
       </c>
       <c r="P191" t="s">
-        <v>2251</v>
+        <v>2266</v>
       </c>
       <c r="Q191" t="s">
-        <v>2252</v>
+        <v>2267</v>
       </c>
     </row>
     <row r="192" spans="1:17" x14ac:dyDescent="0.25">
@@ -31003,16 +31234,16 @@
         <v>8</v>
       </c>
       <c r="D192" t="s">
+        <v>2268</v>
+      </c>
+      <c r="E192" t="s">
         <v>2253</v>
       </c>
-      <c r="E192" t="s">
-        <v>2238</v>
-      </c>
       <c r="F192" t="s">
-        <v>2254</v>
+        <v>2269</v>
       </c>
       <c r="G192" t="s">
-        <v>2192</v>
+        <v>2207</v>
       </c>
       <c r="J192" t="s">
         <v>22</v>
@@ -31027,16 +31258,16 @@
         <v>38</v>
       </c>
       <c r="N192" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O192" t="s">
-        <v>2255</v>
+        <v>2270</v>
       </c>
       <c r="P192" t="s">
-        <v>2256</v>
+        <v>2271</v>
       </c>
       <c r="Q192" t="s">
-        <v>2257</v>
+        <v>2272</v>
       </c>
     </row>
     <row r="193" spans="1:17" x14ac:dyDescent="0.25">
@@ -31053,13 +31284,13 @@
         <v>174</v>
       </c>
       <c r="E193" t="s">
-        <v>2258</v>
+        <v>2273</v>
       </c>
       <c r="F193" t="s">
-        <v>2259</v>
+        <v>2274</v>
       </c>
       <c r="G193" t="s">
-        <v>2192</v>
+        <v>2207</v>
       </c>
       <c r="J193" t="s">
         <v>22</v>
@@ -31074,16 +31305,16 @@
         <v>32</v>
       </c>
       <c r="N193" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O193" t="s">
-        <v>2260</v>
+        <v>2275</v>
       </c>
       <c r="P193" t="s">
-        <v>2261</v>
+        <v>2276</v>
       </c>
       <c r="Q193" t="s">
-        <v>2262</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="194" spans="1:17" x14ac:dyDescent="0.25">
@@ -31097,16 +31328,16 @@
         <v>45</v>
       </c>
       <c r="D194" t="s">
-        <v>2263</v>
+        <v>2278</v>
       </c>
       <c r="E194" t="s">
-        <v>2258</v>
+        <v>2273</v>
       </c>
       <c r="F194" t="s">
-        <v>2264</v>
+        <v>2279</v>
       </c>
       <c r="G194" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J194" t="s">
         <v>22</v>
@@ -31121,16 +31352,16 @@
         <v>38</v>
       </c>
       <c r="N194" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O194" t="s">
-        <v>2265</v>
+        <v>2280</v>
       </c>
       <c r="P194" t="s">
-        <v>2266</v>
+        <v>2281</v>
       </c>
       <c r="Q194" t="s">
-        <v>2267</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="195" spans="1:17" x14ac:dyDescent="0.25">
@@ -31144,16 +31375,16 @@
         <v>30</v>
       </c>
       <c r="D195" t="s">
-        <v>2268</v>
+        <v>2283</v>
       </c>
       <c r="E195" t="s">
-        <v>2258</v>
+        <v>2273</v>
       </c>
       <c r="F195" t="s">
-        <v>2259</v>
+        <v>2274</v>
       </c>
       <c r="G195" t="s">
-        <v>2192</v>
+        <v>2207</v>
       </c>
       <c r="J195" t="s">
         <v>22</v>
@@ -31168,16 +31399,16 @@
         <v>38</v>
       </c>
       <c r="N195" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O195" t="s">
-        <v>2269</v>
+        <v>2284</v>
       </c>
       <c r="P195" t="s">
-        <v>2270</v>
+        <v>2285</v>
       </c>
       <c r="Q195" t="s">
-        <v>2271</v>
+        <v>2286</v>
       </c>
     </row>
     <row r="196" spans="1:17" x14ac:dyDescent="0.25">
@@ -31191,16 +31422,16 @@
         <v>78</v>
       </c>
       <c r="D196" t="s">
-        <v>2272</v>
+        <v>2287</v>
       </c>
       <c r="E196" t="s">
-        <v>2258</v>
+        <v>2273</v>
       </c>
       <c r="F196" t="s">
-        <v>2259</v>
+        <v>2274</v>
       </c>
       <c r="G196" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J196" t="s">
         <v>22</v>
@@ -31215,16 +31446,16 @@
         <v>32</v>
       </c>
       <c r="N196" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O196" t="s">
-        <v>2273</v>
+        <v>2288</v>
       </c>
       <c r="P196" t="s">
-        <v>2274</v>
+        <v>2289</v>
       </c>
       <c r="Q196" t="s">
-        <v>2275</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="197" spans="1:17" x14ac:dyDescent="0.25">
@@ -31238,16 +31469,16 @@
         <v>70</v>
       </c>
       <c r="D197" t="s">
-        <v>2276</v>
+        <v>2291</v>
       </c>
       <c r="E197" t="s">
-        <v>2277</v>
+        <v>2292</v>
       </c>
       <c r="F197" t="s">
-        <v>2278</v>
+        <v>2293</v>
       </c>
       <c r="G197" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J197" t="s">
         <v>22</v>
@@ -31262,16 +31493,16 @@
         <v>25</v>
       </c>
       <c r="N197" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O197" t="s">
-        <v>2279</v>
+        <v>2294</v>
       </c>
       <c r="P197" t="s">
-        <v>2280</v>
+        <v>2295</v>
       </c>
       <c r="Q197" t="s">
-        <v>2281</v>
+        <v>2296</v>
       </c>
     </row>
     <row r="198" spans="1:17" x14ac:dyDescent="0.25">
@@ -31285,16 +31516,16 @@
         <v>55</v>
       </c>
       <c r="D198" t="s">
-        <v>2282</v>
+        <v>2297</v>
       </c>
       <c r="E198" t="s">
-        <v>2277</v>
+        <v>2292</v>
       </c>
       <c r="F198" t="s">
-        <v>2278</v>
+        <v>2293</v>
       </c>
       <c r="G198" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J198" t="s">
         <v>22</v>
@@ -31309,16 +31540,16 @@
         <v>25</v>
       </c>
       <c r="N198" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O198" t="s">
-        <v>2283</v>
+        <v>2298</v>
       </c>
       <c r="P198" t="s">
-        <v>2284</v>
+        <v>2299</v>
       </c>
       <c r="Q198" t="s">
-        <v>2285</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="199" spans="1:17" x14ac:dyDescent="0.25">
@@ -31332,16 +31563,16 @@
         <v>35</v>
       </c>
       <c r="D199" t="s">
-        <v>2286</v>
+        <v>2301</v>
       </c>
       <c r="E199" t="s">
-        <v>2287</v>
+        <v>2302</v>
       </c>
       <c r="F199" t="s">
-        <v>2288</v>
+        <v>2303</v>
       </c>
       <c r="G199" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J199" t="s">
         <v>22</v>
@@ -31356,16 +31587,16 @@
         <v>38</v>
       </c>
       <c r="N199" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O199" t="s">
-        <v>2289</v>
+        <v>2304</v>
       </c>
       <c r="P199" t="s">
-        <v>2290</v>
+        <v>2305</v>
       </c>
       <c r="Q199" t="s">
-        <v>2291</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="200" spans="1:17" x14ac:dyDescent="0.25">
@@ -31379,16 +31610,16 @@
         <v>22</v>
       </c>
       <c r="D200" t="s">
-        <v>2111</v>
+        <v>2126</v>
       </c>
       <c r="E200" t="s">
-        <v>2287</v>
+        <v>2302</v>
       </c>
       <c r="F200" t="s">
-        <v>2288</v>
+        <v>2303</v>
       </c>
       <c r="G200" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J200" t="s">
         <v>22</v>
@@ -31403,16 +31634,16 @@
         <v>38</v>
       </c>
       <c r="N200" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O200" t="s">
-        <v>2292</v>
+        <v>2307</v>
       </c>
       <c r="P200" t="s">
-        <v>2293</v>
+        <v>2308</v>
       </c>
       <c r="Q200" t="s">
-        <v>2294</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="201" spans="1:17" x14ac:dyDescent="0.25">
@@ -31426,16 +31657,16 @@
         <v>42</v>
       </c>
       <c r="D201" t="s">
-        <v>2295</v>
+        <v>2310</v>
       </c>
       <c r="E201" t="s">
-        <v>2287</v>
+        <v>2302</v>
       </c>
       <c r="F201" t="s">
-        <v>2288</v>
+        <v>2303</v>
       </c>
       <c r="G201" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J201" t="s">
         <v>22</v>
@@ -31450,16 +31681,16 @@
         <v>38</v>
       </c>
       <c r="N201" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O201" t="s">
-        <v>2296</v>
+        <v>2311</v>
       </c>
       <c r="P201" t="s">
-        <v>2297</v>
+        <v>2312</v>
       </c>
       <c r="Q201" t="s">
-        <v>2298</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="202" spans="1:17" x14ac:dyDescent="0.25">
@@ -31473,16 +31704,16 @@
         <v>50</v>
       </c>
       <c r="D202" t="s">
-        <v>2299</v>
+        <v>2314</v>
       </c>
       <c r="E202" t="s">
         <v>1351</v>
       </c>
       <c r="F202" t="s">
-        <v>2196</v>
+        <v>2211</v>
       </c>
       <c r="G202" t="s">
-        <v>2192</v>
+        <v>2207</v>
       </c>
       <c r="H202">
         <v>150000</v>
@@ -31503,16 +31734,16 @@
         <v>25</v>
       </c>
       <c r="N202" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O202" t="s">
-        <v>2300</v>
+        <v>2315</v>
       </c>
       <c r="P202" t="s">
-        <v>2301</v>
+        <v>2316</v>
       </c>
       <c r="Q202" t="s">
-        <v>2302</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="203" spans="1:17" x14ac:dyDescent="0.25">
@@ -31526,16 +31757,16 @@
         <v>35</v>
       </c>
       <c r="D203" t="s">
-        <v>2303</v>
+        <v>2318</v>
       </c>
       <c r="E203" t="s">
         <v>1351</v>
       </c>
       <c r="F203" t="s">
-        <v>2304</v>
+        <v>2319</v>
       </c>
       <c r="G203" t="s">
-        <v>2192</v>
+        <v>2207</v>
       </c>
       <c r="H203">
         <v>140000</v>
@@ -31556,16 +31787,16 @@
         <v>38</v>
       </c>
       <c r="N203" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O203" t="s">
-        <v>2305</v>
+        <v>2320</v>
       </c>
       <c r="P203" t="s">
-        <v>2306</v>
+        <v>2321</v>
       </c>
       <c r="Q203" t="s">
-        <v>2307</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="204" spans="1:17" x14ac:dyDescent="0.25">
@@ -31579,16 +31810,16 @@
         <v>25</v>
       </c>
       <c r="D204" t="s">
-        <v>2308</v>
+        <v>2323</v>
       </c>
       <c r="E204" t="s">
-        <v>2309</v>
+        <v>2324</v>
       </c>
       <c r="F204" t="s">
-        <v>2310</v>
+        <v>2325</v>
       </c>
       <c r="G204" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J204" t="s">
         <v>22</v>
@@ -31603,16 +31834,16 @@
         <v>38</v>
       </c>
       <c r="N204" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O204" t="s">
-        <v>2311</v>
+        <v>2326</v>
       </c>
       <c r="P204" t="s">
-        <v>2312</v>
+        <v>2327</v>
       </c>
       <c r="Q204" t="s">
-        <v>2313</v>
+        <v>2328</v>
       </c>
     </row>
     <row r="205" spans="1:17" x14ac:dyDescent="0.25">
@@ -31626,16 +31857,16 @@
         <v>62</v>
       </c>
       <c r="D205" t="s">
-        <v>2314</v>
+        <v>2329</v>
       </c>
       <c r="E205" t="s">
-        <v>2309</v>
+        <v>2324</v>
       </c>
       <c r="F205" t="s">
-        <v>2310</v>
+        <v>2325</v>
       </c>
       <c r="G205" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J205" t="s">
         <v>22</v>
@@ -31650,16 +31881,16 @@
         <v>25</v>
       </c>
       <c r="N205" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O205" t="s">
-        <v>2315</v>
+        <v>2330</v>
       </c>
       <c r="P205" t="s">
-        <v>2316</v>
+        <v>2331</v>
       </c>
       <c r="Q205" t="s">
-        <v>2317</v>
+        <v>2332</v>
       </c>
     </row>
     <row r="206" spans="1:17" x14ac:dyDescent="0.25">
@@ -31673,16 +31904,16 @@
         <v>18</v>
       </c>
       <c r="D206" t="s">
-        <v>2318</v>
+        <v>2333</v>
       </c>
       <c r="E206" t="s">
-        <v>2309</v>
+        <v>2324</v>
       </c>
       <c r="F206" t="s">
-        <v>2319</v>
+        <v>2334</v>
       </c>
       <c r="G206" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J206" t="s">
         <v>22</v>
@@ -31697,16 +31928,16 @@
         <v>38</v>
       </c>
       <c r="N206" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O206" t="s">
-        <v>2320</v>
+        <v>2335</v>
       </c>
       <c r="P206" t="s">
-        <v>2321</v>
+        <v>2336</v>
       </c>
       <c r="Q206" t="s">
-        <v>2322</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="207" spans="1:17" x14ac:dyDescent="0.25">
@@ -31720,16 +31951,16 @@
         <v>45</v>
       </c>
       <c r="D207" t="s">
-        <v>2323</v>
+        <v>2338</v>
       </c>
       <c r="E207" t="s">
-        <v>2324</v>
+        <v>2339</v>
       </c>
       <c r="F207" t="s">
-        <v>2196</v>
+        <v>2211</v>
       </c>
       <c r="G207" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J207" t="s">
         <v>22</v>
@@ -31744,16 +31975,16 @@
         <v>25</v>
       </c>
       <c r="N207" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O207" t="s">
-        <v>2325</v>
+        <v>2340</v>
       </c>
       <c r="P207" t="s">
-        <v>2326</v>
+        <v>2341</v>
       </c>
       <c r="Q207" t="s">
-        <v>2327</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="208" spans="1:17" x14ac:dyDescent="0.25">
@@ -31767,16 +31998,16 @@
         <v>32</v>
       </c>
       <c r="D208" t="s">
-        <v>2328</v>
+        <v>2343</v>
       </c>
       <c r="E208" t="s">
-        <v>2324</v>
+        <v>2339</v>
       </c>
       <c r="F208" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
       <c r="G208" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J208" t="s">
         <v>22</v>
@@ -31791,16 +32022,16 @@
         <v>38</v>
       </c>
       <c r="N208" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O208" t="s">
-        <v>2330</v>
+        <v>2345</v>
       </c>
       <c r="P208" t="s">
-        <v>2331</v>
+        <v>2346</v>
       </c>
       <c r="Q208" t="s">
-        <v>2332</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="209" spans="1:17" x14ac:dyDescent="0.25">
@@ -31817,13 +32048,13 @@
         <v>1378</v>
       </c>
       <c r="E209" t="s">
-        <v>2324</v>
+        <v>2339</v>
       </c>
       <c r="F209" t="s">
-        <v>2329</v>
+        <v>2344</v>
       </c>
       <c r="G209" t="s">
-        <v>1398</v>
+        <v>1413</v>
       </c>
       <c r="J209" t="s">
         <v>22</v>
@@ -31838,16 +32069,16 @@
         <v>25</v>
       </c>
       <c r="N209" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O209" t="s">
-        <v>2333</v>
+        <v>2348</v>
       </c>
       <c r="P209" t="s">
-        <v>2334</v>
+        <v>2349</v>
       </c>
       <c r="Q209" t="s">
-        <v>2335</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="210" spans="1:17" x14ac:dyDescent="0.25">
@@ -31867,10 +32098,10 @@
         <v>421</v>
       </c>
       <c r="F210" t="s">
-        <v>2336</v>
+        <v>2351</v>
       </c>
       <c r="G210" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="H210">
         <v>219100</v>
@@ -31891,16 +32122,16 @@
         <v>25</v>
       </c>
       <c r="N210" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O210" t="s">
-        <v>2337</v>
+        <v>2352</v>
       </c>
       <c r="P210" t="s">
-        <v>2338</v>
+        <v>2353</v>
       </c>
       <c r="Q210" t="s">
-        <v>2339</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="211" spans="1:17" x14ac:dyDescent="0.25">
@@ -31920,10 +32151,10 @@
         <v>421</v>
       </c>
       <c r="F211" t="s">
-        <v>2340</v>
+        <v>2355</v>
       </c>
       <c r="G211" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="H211">
         <v>180000</v>
@@ -31944,16 +32175,16 @@
         <v>25</v>
       </c>
       <c r="N211" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O211" t="s">
-        <v>2341</v>
+        <v>2356</v>
       </c>
       <c r="P211" t="s">
-        <v>2342</v>
+        <v>2357</v>
       </c>
       <c r="Q211" t="s">
-        <v>2343</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="212" spans="1:17" x14ac:dyDescent="0.25">
@@ -31973,10 +32204,10 @@
         <v>421</v>
       </c>
       <c r="F212" t="s">
-        <v>2344</v>
+        <v>2359</v>
       </c>
       <c r="G212" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="H212">
         <v>219100</v>
@@ -31997,16 +32228,16 @@
         <v>25</v>
       </c>
       <c r="N212" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O212" t="s">
-        <v>2345</v>
+        <v>2360</v>
       </c>
       <c r="P212" t="s">
-        <v>2346</v>
+        <v>2361</v>
       </c>
       <c r="Q212" t="s">
-        <v>2347</v>
+        <v>2362</v>
       </c>
     </row>
     <row r="213" spans="1:17" x14ac:dyDescent="0.25">
@@ -32020,16 +32251,16 @@
         <v>25</v>
       </c>
       <c r="D213" t="s">
-        <v>1822</v>
+        <v>1837</v>
       </c>
       <c r="E213" t="s">
-        <v>1823</v>
+        <v>1838</v>
       </c>
       <c r="F213" t="s">
-        <v>1824</v>
+        <v>1839</v>
       </c>
       <c r="G213" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J213" t="s">
         <v>22</v>
@@ -32044,16 +32275,16 @@
         <v>38</v>
       </c>
       <c r="N213" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O213" t="s">
-        <v>2348</v>
+        <v>2363</v>
       </c>
       <c r="P213" t="s">
-        <v>2349</v>
+        <v>2364</v>
       </c>
       <c r="Q213" t="s">
-        <v>2350</v>
+        <v>2365</v>
       </c>
     </row>
     <row r="214" spans="1:17" x14ac:dyDescent="0.25">
@@ -32067,16 +32298,16 @@
         <v>3</v>
       </c>
       <c r="D214" t="s">
-        <v>1828</v>
+        <v>1843</v>
       </c>
       <c r="E214" t="s">
-        <v>1829</v>
+        <v>1844</v>
       </c>
       <c r="F214" t="s">
-        <v>1824</v>
+        <v>1839</v>
       </c>
       <c r="G214" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="J214" t="s">
         <v>22</v>
@@ -32091,16 +32322,16 @@
         <v>38</v>
       </c>
       <c r="N214" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O214" t="s">
-        <v>2351</v>
+        <v>2366</v>
       </c>
       <c r="P214" t="s">
-        <v>2352</v>
+        <v>2367</v>
       </c>
       <c r="Q214" t="s">
-        <v>2353</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="215" spans="1:17" x14ac:dyDescent="0.25">
@@ -32114,7 +32345,7 @@
         <v>48</v>
       </c>
       <c r="D215" t="s">
-        <v>2354</v>
+        <v>2369</v>
       </c>
       <c r="E215" t="s">
         <v>1084</v>
@@ -32123,7 +32354,7 @@
         <v>1085</v>
       </c>
       <c r="G215" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="H215">
         <v>200000</v>
@@ -32144,16 +32375,16 @@
         <v>25</v>
       </c>
       <c r="N215" t="s">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="O215" t="s">
-        <v>2355</v>
+        <v>2370</v>
       </c>
       <c r="P215" t="s">
-        <v>2356</v>
+        <v>2371</v>
       </c>
       <c r="Q215" t="s">
-        <v>2357</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="216" spans="1:17" x14ac:dyDescent="0.25">
@@ -32167,16 +32398,16 @@
         <v>72</v>
       </c>
       <c r="D216" t="s">
-        <v>2358</v>
+        <v>2373</v>
       </c>
       <c r="E216" t="s">
-        <v>1920</v>
+        <v>1935</v>
       </